--- a/00_Paper_Pool/Paper_Pool.xlsx
+++ b/00_Paper_Pool/Paper_Pool.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Papers" sheetId="1" r:id="Ra078d83f57944d9c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rejected" sheetId="2" r:id="Rc632b7f507494fa4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Venues" sheetId="3" r:id="R044287c5419b4ebe"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Keywords" sheetId="4" r:id="R1670bed94b0e42b0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Discovery" sheetId="5" r:id="Rbe2f9d4ce39b43af"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CCF_A_Library" sheetId="6" r:id="R93f4beeda8d74d30"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Robotics_Core_Library" sheetId="7" r:id="R39e67a1570be4dbe"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Papers" sheetId="1" r:id="R94f30f9d000040e0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rejected" sheetId="2" r:id="R85f281c7f6e64a90"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Venues" sheetId="3" r:id="R86ee3682b76940e5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Keywords" sheetId="4" r:id="Ra925f705a993474b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Discovery" sheetId="5" r:id="R2f2db1c47bd64a7b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CCF_A_Library" sheetId="6" r:id="Rc69743c2062a4de2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Robotics_Core_Library" sheetId="7" r:id="R90fd38ad14c74b69"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -384,7 +384,7 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="9" name="DiscoveryTable" displayName="DiscoveryTable" ref="A1:Z78" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="9" name="DiscoveryTable" displayName="DiscoveryTable" ref="A1:Z79" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="26">
     <x:tableColumn id="1" name="编号 ID"/>
     <x:tableColumn id="2" name="论文标题 Title"/>
@@ -418,7 +418,7 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="10" name="CCFALibraryTable" displayName="CCFALibraryTable" ref="A1:AU66" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="10" name="CCFALibraryTable" displayName="CCFALibraryTable" ref="A1:AU67" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="47">
     <x:tableColumn id="1" name="编号 ID"/>
     <x:tableColumn id="2" name="论文标题 Title"/>
@@ -4134,7 +4134,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2b919a0a6a874e11"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8ae73188e4af4fb4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7430,7 +7430,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7641a7b927524ea7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdbda72b59aaa42f8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7781,7 +7781,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfca0e250dc37451d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6c7b89ee07ff4da0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8527,7 +8527,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd68244e1786e49b6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf0cf507806594083"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14285,6 +14285,86 @@
         <x:v>02_Papers/10_Benchmark_Dataset/Open_X-Embodiment.md</x:v>
       </x:c>
     </x:row>
+    <x:row r="79">
+      <x:c r="A79" t="str">
+        <x:v>D078</x:v>
+      </x:c>
+      <x:c r="B79" t="str">
+        <x:v>ReconVLA: Reconstructive Vision-Language-Action Model as Effective Robot Perceiver</x:v>
+      </x:c>
+      <x:c r="C79" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="D79" t="str">
+        <x:v>Method Paper</x:v>
+      </x:c>
+      <x:c r="E79" t="str">
+        <x:v>AAAI</x:v>
+      </x:c>
+      <x:c r="F79" t="str">
+        <x:v>Official Conference Paper (AAAI-26 Technical Track on Intelligent Robotics)</x:v>
+      </x:c>
+      <x:c r="G79" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H79" t="str">
+        <x:v>VLA; Robot Manipulation; Generalization; Diffusion</x:v>
+      </x:c>
+      <x:c r="I79" t="str">
+        <x:v>Visual Grounding / Robot Perception / Gaze-Region Reconstruction</x:v>
+      </x:c>
+      <x:c r="J79" t="str">
+        <x:v>VLA; Robot Manipulation; Visual Grounding; Robot Perception; Implicit Grounding; Gaze-Region Reconstruction; Generalization; Diffusion Transformer</x:v>
+      </x:c>
+      <x:c r="K79" t="str">
+        <x:v>https://ojs.aaai.org/index.php/AAAI/article/view/38921</x:v>
+      </x:c>
+      <x:c r="L79" t="str">
+        <x:v>https://arxiv.org/abs/2508.10333</x:v>
+      </x:c>
+      <x:c r="M79" t="str">
+        <x:v>https://zionchow.github.io/ReconVLA/</x:v>
+      </x:c>
+      <x:c r="N79" t="str">
+        <x:v>https://github.com/OpenHelix-Team/ReconVLA</x:v>
+      </x:c>
+      <x:c r="O79" t="str">
+        <x:v>Released</x:v>
+      </x:c>
+      <x:c r="P79" t="str">
+        <x:v>Partial — source datasets and preprocessing instructions are public; compiled pretraining dataset release not verified</x:v>
+      </x:c>
+      <x:c r="Q79" t="str">
+        <x:v>Unknown — no author-released ReconVLA checkpoint located</x:v>
+      </x:c>
+      <x:c r="R79" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="S79" t="str">
+        <x:v>Single Arm / Parallel Gripper</x:v>
+      </x:c>
+      <x:c r="T79" t="str">
+        <x:v>AAAI Proceedings / author project page / official GitHub</x:v>
+      </x:c>
+      <x:c r="U79" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="V79" t="str">
+        <x:v>Special Attention: Yes. Abstract-level / 未精读. Official repository includes training, evaluation, and preprocessing code; code was not run locally.</x:v>
+      </x:c>
+      <x:c r="W79" t="str">
+        <x:v>Official AAAI proceedings, arXiv, author project page, and official repository verified; CCF A verified on current official CCF list</x:v>
+      </x:c>
+      <x:c r="X79" t="str">
+        <x:v>2026-09-20</x:v>
+      </x:c>
+      <x:c r="Y79" t="str">
+        <x:v>VLA</x:v>
+      </x:c>
+      <x:c r="Z79" t="str">
+        <x:v>02_Papers/01_VLA/ReconVLA.md</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:dataValidations count="5">
     <x:dataValidation type="list" sqref="D2:D78">
@@ -14305,7 +14385,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb51b4725aeaf4284"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R32a7cae7933340e4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -23712,6 +23792,149 @@
         <x:v>Bimanual</x:v>
       </x:c>
     </x:row>
+    <x:row r="67">
+      <x:c r="A67" t="str">
+        <x:v>A066</x:v>
+      </x:c>
+      <x:c r="B67" t="str">
+        <x:v>ReconVLA: Reconstructive Vision-Language-Action Model as Effective Robot Perceiver</x:v>
+      </x:c>
+      <x:c r="C67" t="str">
+        <x:v>Wenxuan Song; Ziyang Zhou; Han Zhao; Jiayi Chen; Pengxiang Ding; Haodong Yan; Yuxin Huang; Feilong Tang; Donglin Wang; Haoang Li</x:v>
+      </x:c>
+      <x:c r="D67" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="E67" t="str">
+        <x:v>AAAI</x:v>
+      </x:c>
+      <x:c r="F67" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="G67" t="str">
+        <x:v>Official Conference Paper</x:v>
+      </x:c>
+      <x:c r="H67" t="str">
+        <x:v>Method Paper</x:v>
+      </x:c>
+      <x:c r="I67" t="str">
+        <x:v>VLA; Robot Manipulation; Generalization; Diffusion</x:v>
+      </x:c>
+      <x:c r="J67" t="str">
+        <x:v>Visual Grounding / Robot Perception / Gaze-Region Reconstruction</x:v>
+      </x:c>
+      <x:c r="K67" t="str">
+        <x:v>VLA; Robot Manipulation; Visual Grounding; Robot Perception; Implicit Grounding; Gaze-Region Reconstruction; Generalization; Diffusion Transformer</x:v>
+      </x:c>
+      <x:c r="L67" t="str">
+        <x:v>https://ojs.aaai.org/index.php/AAAI/article/view/38921</x:v>
+      </x:c>
+      <x:c r="M67" t="str">
+        <x:v>10.1609/aaai.v40i22.38921</x:v>
+      </x:c>
+      <x:c r="N67" t="str">
+        <x:v>https://arxiv.org/abs/2508.10333</x:v>
+      </x:c>
+      <x:c r="O67" t="str">
+        <x:v>https://zionchow.github.io/ReconVLA/</x:v>
+      </x:c>
+      <x:c r="P67" t="str">
+        <x:v>https://github.com/OpenHelix-Team/ReconVLA</x:v>
+      </x:c>
+      <x:c r="Q67" t="str">
+        <x:v>Released</x:v>
+      </x:c>
+      <x:c r="R67" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="S67" t="str">
+        <x:v>Unknown — no author-released ReconVLA checkpoint located</x:v>
+      </x:c>
+      <x:c r="T67" t="str">
+        <x:v>Partial — source datasets and preprocessing instructions are public; compiled pretraining dataset release not verified</x:v>
+      </x:c>
+      <x:c r="U67" t="str">
+        <x:v>Franka Panda (CALVIN simulation); real-world platform not confirmed at abstract level</x:v>
+      </x:c>
+      <x:c r="V67" t="str">
+        <x:v>Single Arm / Parallel Gripper</x:v>
+      </x:c>
+      <x:c r="W67" t="str">
+        <x:v>Single Arm</x:v>
+      </x:c>
+      <x:c r="X67" t="str">
+        <x:v>Parallel Gripper</x:v>
+      </x:c>
+      <x:c r="Y67" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="Z67" t="str">
+        <x:v>BridgeData V2; LIBERO; CALVIN (source datasets); curated 100k+ trajectories / 2M samples reported</x:v>
+      </x:c>
+      <x:c r="AA67" t="str">
+        <x:v>CALVIN; real-world manipulation tasks</x:v>
+      </x:c>
+      <x:c r="AB67" t="str">
+        <x:v>Yes (CALVIN)</x:v>
+      </x:c>
+      <x:c r="AC67" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="AD67" t="str">
+        <x:v>Official AAAI proceedings, arXiv, author project page, and official repository verified; CCF A verified on current official CCF list</x:v>
+      </x:c>
+      <x:c r="AE67" t="str">
+        <x:v>2026-09-20</x:v>
+      </x:c>
+      <x:c r="AF67" t="str">
+        <x:v>Special Attention: Yes. Abstract-level / 未精读. Code status reflects static verification of training, evaluation, and preprocessing implementation; no local run.</x:v>
+      </x:c>
+      <x:c r="AG67" t="str">
+        <x:v>CCF A Conference</x:v>
+      </x:c>
+      <x:c r="AH67" t="str">
+        <x:v>Official Conference Paper</x:v>
+      </x:c>
+      <x:c r="AI67" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="AJ67" t="str">
+        <x:v>Discovery / 未读</x:v>
+      </x:c>
+      <x:c r="AK67" t="str">
+        <x:v>02_Papers/01_VLA/ReconVLA.md</x:v>
+      </x:c>
+      <x:c r="AL67" t="str">
+        <x:v>Strict CCF A</x:v>
+      </x:c>
+      <x:c r="AM67" t="str">
+        <x:v>https://ojs.aaai.org/index.php/AAAI/article/view/38921; https://arxiv.org/abs/2508.10333; https://zionchow.github.io/ReconVLA/; https://github.com/OpenHelix-Team/ReconVLA</x:v>
+      </x:c>
+      <x:c r="AN67" t="str">
+        <x:v>Abstract-level / 未精读</x:v>
+      </x:c>
+      <x:c r="AO67" t="str">
+        <x:v>Current VLA models often allocate dispersed visual attention and fail to focus precisely on task target regions.</x:v>
+      </x:c>
+      <x:c r="AP67" t="str">
+        <x:v>Introduces reconstructive VLA with implicit grounding and a robot pretraining dataset of 100k+ trajectories and 2M samples.</x:v>
+      </x:c>
+      <x:c r="AQ67" t="str">
+        <x:v>A diffusion transformer reconstructs gaze regions from VLA visual outputs, encouraging fine-grained target-region representations and accurate visual attention.</x:v>
+      </x:c>
+      <x:c r="AR67" t="str">
+        <x:v>Official paper reports CALVIN simulation and real-world experiments supporting precise manipulation, long-horizon performance, and generalization to unseen targets.</x:v>
+      </x:c>
+      <x:c r="AS67" t="str">
+        <x:v>Relevant to VLA perception, target grounding, manipulation precision, and generalization; useful as an auxiliary reconstruction objective reference.</x:v>
+      </x:c>
+      <x:c r="AT67" t="str">
+        <x:v>Current official CCF Artificial Intelligence list checked 2026-09-20: AAAI is A</x:v>
+      </x:c>
+      <x:c r="AU67" t="str">
+        <x:v>VLA</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:dataValidations count="10">
     <x:dataValidation type="list" sqref="F2:F51">
@@ -23747,7 +23970,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0b19e9f710234bbb"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7130ba24d5064a71"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -25286,7 +25509,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc92d01c7d4074a4e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R09688c328b794cf0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/00_Paper_Pool/Paper_Pool.xlsx
+++ b/00_Paper_Pool/Paper_Pool.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Papers" sheetId="1" r:id="R94f30f9d000040e0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rejected" sheetId="2" r:id="R85f281c7f6e64a90"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Venues" sheetId="3" r:id="R86ee3682b76940e5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Keywords" sheetId="4" r:id="Ra925f705a993474b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Discovery" sheetId="5" r:id="R2f2db1c47bd64a7b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CCF_A_Library" sheetId="6" r:id="Rc69743c2062a4de2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Robotics_Core_Library" sheetId="7" r:id="R90fd38ad14c74b69"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Papers" sheetId="1" r:id="Rf20c5345323f4b8b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rejected" sheetId="2" r:id="Rf343ef705194437a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Venues" sheetId="3" r:id="Ra883011712f24cbb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Keywords" sheetId="4" r:id="Rd2861bec75884cdb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Discovery" sheetId="5" r:id="R77a93c54c2f046d7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CCF_A_Library" sheetId="6" r:id="Rcd7c79e334b644ec"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Robotics_Core_Library" sheetId="7" r:id="Rfcc63173bb0a44bf"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -4134,7 +4134,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8ae73188e4af4fb4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R27857e2f4e0948b3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7430,7 +7430,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdbda72b59aaa42f8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R948e4587c85b4c39"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7781,7 +7781,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6c7b89ee07ff4da0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd5992c9c785d49d6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8527,7 +8527,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf0cf507806594083"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfc16559e87cc441f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14385,7 +14385,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R32a7cae7933340e4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1286900ceee44021"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -23970,7 +23970,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7130ba24d5064a71"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R99b6d246eb1e427d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -24154,7 +24154,7 @@
         <x:v>Official Conference Paper</x:v>
       </x:c>
       <x:c r="H2" s="23" t="str">
-        <x:v>Unknown (project standard conflict; official CCF row pending)</x:v>
+        <x:v>Unknown (current official CCF directory checked; no authoritative ICLR A row located in accessible current listing)</x:v>
       </x:c>
       <x:c r="I2" s="23" t="str">
         <x:v>VLA / Robot Manipulation / Sim2Real</x:v>
@@ -24166,16 +24166,16 @@
         <x:v>VLA; Sim2Real; Robot Manipulation; Synthetic Data; Generalization; Bimanual; Dexterous; Long-horizon</x:v>
       </x:c>
       <x:c r="L2" s="23" t="str">
-        <x:v>Synthetic-only VLA training usually transfers unreliably to real manipulation.</x:v>
+        <x:v>Synthetic-only VLA training often fails to transfer reliably to real manipulation; the paper targets this Sim2Real gap.</x:v>
       </x:c>
       <x:c r="M2" s="23" t="str">
-        <x:v>Dual-system VLA with chain-of-affordances planning and tokenized low-level action execution; automated synthetic skill generation and real-world evaluation.</x:v>
+        <x:v>Dual-system VLA with high-level chain-of-affordances planning, low-level tokenized action execution/validation, and automated synthetic manipulation-skill generation.</x:v>
       </x:c>
       <x:c r="N2" s="23" t="str">
         <x:v>Filter manipulation-irrelevant variation and retain motion-critical affordance structure for zero-shot transfer.</x:v>
       </x:c>
       <x:c r="O2" s="23" t="str">
-        <x:v>https://openreview.net/pdf?id=H4SyKHjd4c</x:v>
+        <x:v>https://openreview.net/pdf/a4174c2964dc0df03c26c311b73e0a2e43de2929.pdf</x:v>
       </x:c>
       <x:c r="P2" s="23" t="str">
         <x:v>https://edem-ai.github.io/sim2realvla.github.io/</x:v>
@@ -24184,16 +24184,16 @@
         <x:v>https://github.com/DexForce/EmbodiChain</x:v>
       </x:c>
       <x:c r="R2" s="23" t="str">
-        <x:v>Partial</x:v>
+        <x:v>Partial (official project links the paper implementation as an integration into EmbodiChain; no standalone paper repository)</x:v>
       </x:c>
       <x:c r="S2" s="23" t="str">
         <x:v>Unknown</x:v>
       </x:c>
       <x:c r="T2" s="23" t="str">
-        <x:v>Automated synthetic manipulation-skill data; release status Unknown</x:v>
+        <x:v>Automated synthetic manipulation-skill data; complete public release not confirmed</x:v>
       </x:c>
       <x:c r="U2" s="23" t="str">
-        <x:v>Multiple platforms shown by official project; exact model names pending full-paper verification</x:v>
+        <x:v>Multiple real-world setups are shown; exact hardware inventory not extracted at abstract/project level</x:v>
       </x:c>
       <x:c r="V2" s="23" t="str">
         <x:v>Single Arm / Bimanual / Dexterous Hand</x:v>
@@ -24211,13 +24211,13 @@
         <x:v>Discovery / 未读</x:v>
       </x:c>
       <x:c r="AA2" s="23" t="str">
-        <x:v>ICLR 2026 publication confirmed by official ICLR proceedings and accepted OpenReview PDF; code integration is partial</x:v>
+        <x:v>ICLR 2026 publication verified through official ICLR Downloads/Proceedings listing, accepted OpenReview PDF, author project page, and author publication list; code remains Partial integration.</x:v>
       </x:c>
       <x:c r="AB2" s="53" t="str">
-        <x:v>2026-09-19</x:v>
+        <x:v>2026-09-21</x:v>
       </x:c>
       <x:c r="AC2" s="23" t="str">
-        <x:v>Do not place in strict CCF_A_Library until the project's CCF seventh-edition mapping conflict is resolved.</x:v>
+        <x:v>Current official CCF directory was checked; ICLR A status was not authoritatively located, so CCF remains Unknown and the paper stays in Robotics Core / Important Papers.</x:v>
       </x:c>
       <x:c r="AD2" s="23" t="str">
         <x:v>02_Papers/05_Sim2Real/Sim2Real-VLA.md</x:v>
@@ -24226,19 +24226,19 @@
         <x:v>Robotics Core / Important Papers</x:v>
       </x:c>
       <x:c r="AF2" s="23" t="str">
-        <x:v>Official ICLR proceedings; accepted OpenReview PDF; official project page; official GitHub</x:v>
+        <x:v>ICLR Downloads/Proceedings; accepted OpenReview PDF; official project page; official EmbodiChain repository; author publication list; current official CCF directory</x:v>
       </x:c>
       <x:c r="AG2" s="23" t="str">
-        <x:v>Abstract-level</x:v>
+        <x:v>Abstract-level / 未精读</x:v>
       </x:c>
       <x:c r="AH2" s="23" t="str">
-        <x:v>Official project reports six manipulation tasks and real-world domain shifts.</x:v>
+        <x:v>Official project reports six robot manipulation tasks spanning single-arm, dual-arm, hand-over and pan-opening/placement settings, plus domain-gap conditions; exact full-paper benchmark table not re-extracted.</x:v>
       </x:c>
       <x:c r="AI2" s="23" t="str">
         <x:v>Directly relevant to VLA, synthetic data, generalization, dual-arm manipulation and real-world deployment.</x:v>
       </x:c>
       <x:c r="AJ2" s="23" t="str">
-        <x:v>CCF seventh edition: exact official row pending unless separately evidenced</x:v>
+        <x:v>CCF 7th edition current official directory checked 2026-09-21; no authoritative ICLR A row located in accessible current listing</x:v>
       </x:c>
       <x:c r="AK2" s="23" t="str">
         <x:v>Sim2Real</x:v>
@@ -25509,7 +25509,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R09688c328b794cf0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3f35a59480584259"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/00_Paper_Pool/Paper_Pool.xlsx
+++ b/00_Paper_Pool/Paper_Pool.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Papers" sheetId="1" r:id="R1d95b3a7d4474096"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rejected" sheetId="2" r:id="Rddee10ba73044373"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Venues" sheetId="3" r:id="Re80d8134d58640f3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Keywords" sheetId="4" r:id="R04bb7aeaa529491b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Discovery" sheetId="5" r:id="R4a34d64120bd4927"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CCF_A_Library" sheetId="6" r:id="R0a167107ef62482e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Robotics_Core_Library" sheetId="7" r:id="R953a19614fa24be9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Papers" sheetId="1" r:id="Rb78e0de66ebe4bc3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rejected" sheetId="2" r:id="R0fa1462e67ef4140"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Venues" sheetId="3" r:id="R807b83bc92554f01"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Keywords" sheetId="4" r:id="R55565df31e6c4a84"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Discovery" sheetId="5" r:id="R5ca2525dc163414f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CCF_A_Library" sheetId="6" r:id="Rce41f18a12ab45ae"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Robotics_Core_Library" sheetId="7" r:id="Rbe6574d9f21c4cf3"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="12" name="PapersTable" displayName="PapersTable" ref="A1:AT5" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:tableColumns count="46">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="16" name="PapersTable" displayName="PapersTable" ref="A1:AZ5" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:tableColumns count="52">
     <x:tableColumn id="1" name="编号 ID"/>
     <x:tableColumn id="2" name="论文标题 Title"/>
     <x:tableColumn id="3" name="年份 Year"/>
@@ -348,6 +348,12 @@
     <x:tableColumn id="44" name="Remaining Unsolved Problem"/>
     <x:tableColumn id="45" name="Relevance to Our Project"/>
     <x:tableColumn id="46" name="Tags"/>
+    <x:tableColumn id="47" name="Evidence Quality"/>
+    <x:tableColumn id="48" name="Idea Clues"/>
+    <x:tableColumn id="49" name="Ablation Study"/>
+    <x:tableColumn id="50" name="Failure Cases"/>
+    <x:tableColumn id="51" name="Citation Source Identifier"/>
+    <x:tableColumn id="52" name="Evidence Sources"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
@@ -399,8 +405,8 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="13" name="DiscoveryTable" displayName="DiscoveryTable" ref="A1:AO79" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:tableColumns count="41">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="17" name="DiscoveryTable" displayName="DiscoveryTable" ref="A1:AU79" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:tableColumns count="47">
     <x:tableColumn id="1" name="编号 ID"/>
     <x:tableColumn id="2" name="论文标题 Title"/>
     <x:tableColumn id="3" name="年份 Year"/>
@@ -442,14 +448,20 @@
     <x:tableColumn id="39" name="Remaining Unsolved Problem"/>
     <x:tableColumn id="40" name="Relevance to Our Project"/>
     <x:tableColumn id="41" name="Tags"/>
+    <x:tableColumn id="42" name="Evidence Quality"/>
+    <x:tableColumn id="43" name="Idea Clues"/>
+    <x:tableColumn id="44" name="Ablation Study"/>
+    <x:tableColumn id="45" name="Failure Cases"/>
+    <x:tableColumn id="46" name="Citation Source Identifier"/>
+    <x:tableColumn id="47" name="Evidence Sources"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="14" name="CCFALibraryTable" displayName="CCFALibraryTable" ref="A1:BH67" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:tableColumns count="60">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="18" name="CCFALibraryTable" displayName="CCFALibraryTable" ref="A1:BN67" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:tableColumns count="66">
     <x:tableColumn id="1" name="编号 ID"/>
     <x:tableColumn id="2" name="论文标题 Title"/>
     <x:tableColumn id="3" name="作者 Authors"/>
@@ -510,14 +522,20 @@
     <x:tableColumn id="58" name="Limitations"/>
     <x:tableColumn id="59" name="Remaining Unsolved Problem"/>
     <x:tableColumn id="60" name="Tags"/>
+    <x:tableColumn id="61" name="Evidence Quality"/>
+    <x:tableColumn id="62" name="Idea Clues"/>
+    <x:tableColumn id="63" name="Ablation Study"/>
+    <x:tableColumn id="64" name="Failure Cases"/>
+    <x:tableColumn id="65" name="Citation Source Identifier"/>
+    <x:tableColumn id="66" name="Evidence Sources"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="15" name="RoboticsCoreLibraryTable" displayName="RoboticsCoreLibraryTable" ref="A1:AW14" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:tableColumns count="49">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="19" name="RoboticsCoreLibraryTable" displayName="RoboticsCoreLibraryTable" ref="A1:BC14" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:tableColumns count="55">
     <x:tableColumn id="1" name="ID"/>
     <x:tableColumn id="2" name="Title"/>
     <x:tableColumn id="3" name="Authors"/>
@@ -567,6 +585,12 @@
     <x:tableColumn id="47" name="Main Results"/>
     <x:tableColumn id="48" name="Limitations"/>
     <x:tableColumn id="49" name="Remaining Unsolved Problem"/>
+    <x:tableColumn id="50" name="Evidence Quality"/>
+    <x:tableColumn id="51" name="Idea Clues"/>
+    <x:tableColumn id="52" name="Ablation Study"/>
+    <x:tableColumn id="53" name="Failure Cases"/>
+    <x:tableColumn id="54" name="Citation Source Identifier"/>
+    <x:tableColumn id="55" name="Evidence Sources"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium4" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
@@ -939,6 +963,24 @@
       <x:c r="AT1" t="str">
         <x:v>Tags</x:v>
       </x:c>
+      <x:c r="AU1" t="str">
+        <x:v>Evidence Quality</x:v>
+      </x:c>
+      <x:c r="AV1" t="str">
+        <x:v>Idea Clues</x:v>
+      </x:c>
+      <x:c r="AW1" t="str">
+        <x:v>Ablation Study</x:v>
+      </x:c>
+      <x:c r="AX1" t="str">
+        <x:v>Failure Cases</x:v>
+      </x:c>
+      <x:c r="AY1" t="str">
+        <x:v>Citation Source Identifier</x:v>
+      </x:c>
+      <x:c r="AZ1" t="str">
+        <x:v>Evidence Sources</x:v>
+      </x:c>
     </x:row>
     <x:row r="2" ht="350" customHeight="1">
       <x:c r="A2" t="str">
@@ -1077,6 +1119,24 @@
       </x:c>
       <x:c r="AT2" t="str">
         <x:v>Multimodal / Generalization</x:v>
+      </x:c>
+      <x:c r="AU2" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="AV2" t="str">
+        <x:v>Idea Clue 1: adapt affordance-prior reasoning and active impedance correction to ordinary-gripper bimanual contact tasks. Evidence: APR and AIA ablation gains plus explicit hardware failure cases. Why relevant: actionable path for current real-robot manipulation.</x:v>
+      </x:c>
+      <x:c r="AW2" t="str">
+        <x:v>Reported ablations isolate OCI, MLM, APR, COT and AIA; APR is the largest training-task gain in the cited ablation sequence.</x:v>
+      </x:c>
+      <x:c r="AX2" t="str">
+        <x:v>Position predictions are sensitive to lighting and texture domain gaps; suction cannot grasp non-smooth handles and short gripper geometry can cause collisions.</x:v>
+      </x:c>
+      <x:c r="AY2" t="str">
+        <x:v>OpenAlex Work: https://openalex.org/W4402727730</x:v>
+      </x:c>
+      <x:c r="AZ2" t="str">
+        <x:v>https://openaccess.thecvf.com/content/CVPR2024/html/Li_ManipLLM_Embodied_Multimodal_Large_Language_Model_for_Object-Centric_Robotic_Manipulation_CVPR_2024_paper.html；官方摘要/论文集元数据</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="150" customHeight="1">
@@ -1186,6 +1246,24 @@
       <x:c r="AT3" t="str">
         <x:v>Residual Learning / Sim-to-Real</x:v>
       </x:c>
+      <x:c r="AU3" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AV3" t="str">
+        <x:v>Unknown / Needs Evidence</x:v>
+      </x:c>
+      <x:c r="AW3" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="AX3" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="AY3" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AZ3" t="str">
+        <x:v>https://openaccess.thecvf.com/content/CVPR2025/html/Li_ManipTrans_Efficient_Dexterous_Bimanual_Manipulation_Transfer_via_Residual_Learning_CVPR_2025_paper.html；官方摘要/论文集元数据</x:v>
+      </x:c>
     </x:row>
     <x:row r="4" ht="150" customHeight="1">
       <x:c r="A4" t="str">
@@ -1294,6 +1372,24 @@
       <x:c r="AT4" t="str">
         <x:v>Diffusion / Contact-rich Manipulation</x:v>
       </x:c>
+      <x:c r="AU4" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AV4" t="str">
+        <x:v>Unknown / Needs Evidence</x:v>
+      </x:c>
+      <x:c r="AW4" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="AX4" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="AY4" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AZ4" t="str">
+        <x:v>https://openaccess.thecvf.com/content/CVPR2025/html/Liang_DexHandDiff_Interaction-aware_Diffusion_Planning_for_Adaptive_Dexterous_Manipulation_CVPR_2025_paper.html；官方摘要/论文集元数据</x:v>
+      </x:c>
     </x:row>
     <x:row r="5" ht="150" customHeight="1">
       <x:c r="A5" t="str">
@@ -1401,6 +1497,24 @@
       </x:c>
       <x:c r="AT5" t="str">
         <x:v>Human Video / VLM</x:v>
+      </x:c>
+      <x:c r="AU5" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AV5" t="str">
+        <x:v>Unknown / Needs Evidence</x:v>
+      </x:c>
+      <x:c r="AW5" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="AX5" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="AY5" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AZ5" t="str">
+        <x:v>https://openaccess.thecvf.com/content/ICCV2025/html/Yang_AR-VRM_Imitating_Human_Motions_for_Visual_Robot_Manipulation_with_Analogical_ICCV_2025_paper.html；官方摘要/论文集元数据</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -4414,7 +4528,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R48df0fc37dae40bf"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8dcb41bb5dcf4040"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7710,7 +7824,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc0ae217572a94489"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R36f63375e94f492f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8061,7 +8175,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R925c82cc5c2e4e51"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R09c918cd74c44125"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8807,7 +8921,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rac20970add604579"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R554fa4d754eb4cc4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8971,6 +9085,24 @@
       <x:c r="AO1" t="str">
         <x:v>Tags</x:v>
       </x:c>
+      <x:c r="AP1" t="str">
+        <x:v>Evidence Quality</x:v>
+      </x:c>
+      <x:c r="AQ1" t="str">
+        <x:v>Idea Clues</x:v>
+      </x:c>
+      <x:c r="AR1" t="str">
+        <x:v>Ablation Study</x:v>
+      </x:c>
+      <x:c r="AS1" t="str">
+        <x:v>Failure Cases</x:v>
+      </x:c>
+      <x:c r="AT1" t="str">
+        <x:v>Citation Source Identifier</x:v>
+      </x:c>
+      <x:c r="AU1" t="str">
+        <x:v>Evidence Sources</x:v>
+      </x:c>
     </x:row>
     <x:row r="2" ht="58" customHeight="1">
       <x:c r="A2" t="str">
@@ -9088,6 +9220,24 @@
       <x:c r="AO2" t="str">
         <x:v>Robot Manipulation; Diffusion Policy / Hierarchical Control</x:v>
       </x:c>
+      <x:c r="AP2" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AQ2" t="str">
+        <x:v>Unknown / Needs Evidence</x:v>
+      </x:c>
+      <x:c r="AR2" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="AS2" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="AT2" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AU2" t="str">
+        <x:v>https://openaccess.thecvf.com/content/CVPR2024/html/Ma_Hierarchical_Diffusion_Policy_for_Kinematics-Aware_Multi-Task_Robotic_Manipulation_CVPR_2024_paper.html；官方摘要/论文集元数据</x:v>
+      </x:c>
     </x:row>
     <x:row r="3" ht="58" customHeight="1">
       <x:c r="A3" t="str">
@@ -9205,6 +9355,24 @@
       <x:c r="AO3" t="str">
         <x:v>bimanual manipulation; decoupled interaction; RoboTwin</x:v>
       </x:c>
+      <x:c r="AP3" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AQ3" t="str">
+        <x:v>Unknown / Needs Evidence</x:v>
+      </x:c>
+      <x:c r="AR3" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="AS3" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="AT3" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AU3" t="str">
+        <x:v>https://openaccess.thecvf.com/content/ICCV2025/html/Jiang_Rethinking_Bimanual_Robotic_Manipulation_Learning_with_Decoupled_Interaction_Framework_ICCV_2025_paper.html；官方摘要/论文集元数据</x:v>
+      </x:c>
     </x:row>
     <x:row r="4" ht="58" customHeight="1">
       <x:c r="A4" t="str">
@@ -9322,6 +9490,24 @@
       <x:c r="AO4" t="str">
         <x:v>bimanual; diffusion; teleoperation; human demonstration</x:v>
       </x:c>
+      <x:c r="AP4" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AQ4" t="str">
+        <x:v>Unknown / Needs Evidence</x:v>
+      </x:c>
+      <x:c r="AR4" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="AS4" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="AT4" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AU4" t="str">
+        <x:v>https://openaccess.thecvf.com/content/ICCV2025/html/Xu_Diffusion-Based_Imaginative_Coordination_for_Bimanual_Manipulation_ICCV_2025_paper.html；官方摘要/论文集元数据</x:v>
+      </x:c>
     </x:row>
     <x:row r="5" ht="58" customHeight="1">
       <x:c r="A5" t="str">
@@ -9441,6 +9627,24 @@
       <x:c r="AO5" t="str">
         <x:v>Unknown</x:v>
       </x:c>
+      <x:c r="AP5" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AQ5" t="str">
+        <x:v>Unknown / Needs Evidence</x:v>
+      </x:c>
+      <x:c r="AR5" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="AS5" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="AT5" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AU5" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="6" ht="58" customHeight="1">
       <x:c r="A6" t="str">
@@ -9558,6 +9762,24 @@
       <x:c r="AO6" t="str">
         <x:v>Unknown</x:v>
       </x:c>
+      <x:c r="AP6" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AQ6" t="str">
+        <x:v>Unknown / Needs Evidence</x:v>
+      </x:c>
+      <x:c r="AR6" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="AS6" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="AT6" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AU6" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="7" ht="58" customHeight="1">
       <x:c r="A7" t="str">
@@ -9675,6 +9897,24 @@
       <x:c r="AO7" t="str">
         <x:v>Unknown</x:v>
       </x:c>
+      <x:c r="AP7" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AQ7" t="str">
+        <x:v>Unknown / Needs Evidence</x:v>
+      </x:c>
+      <x:c r="AR7" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="AS7" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="AT7" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AU7" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="8" ht="58" customHeight="1">
       <x:c r="A8" t="str">
@@ -9790,6 +10030,24 @@
       <x:c r="AO8" t="str">
         <x:v>Unknown</x:v>
       </x:c>
+      <x:c r="AP8" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AQ8" t="str">
+        <x:v>Unknown / Needs Evidence</x:v>
+      </x:c>
+      <x:c r="AR8" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="AS8" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="AT8" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AU8" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="9" ht="58" customHeight="1">
       <x:c r="A9" t="str">
@@ -9907,6 +10165,24 @@
       <x:c r="AO9" t="str">
         <x:v>Unknown</x:v>
       </x:c>
+      <x:c r="AP9" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AQ9" t="str">
+        <x:v>Unknown / Needs Evidence</x:v>
+      </x:c>
+      <x:c r="AR9" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="AS9" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="AT9" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AU9" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="10" ht="58" customHeight="1">
       <x:c r="A10" t="str">
@@ -10022,6 +10298,24 @@
       <x:c r="AO10" t="str">
         <x:v>Unknown</x:v>
       </x:c>
+      <x:c r="AP10" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AQ10" t="str">
+        <x:v>Unknown / Needs Evidence</x:v>
+      </x:c>
+      <x:c r="AR10" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="AS10" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="AT10" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AU10" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="11" ht="58" customHeight="1">
       <x:c r="A11" t="str">
@@ -10141,6 +10435,24 @@
       <x:c r="AO11" t="str">
         <x:v>Unknown</x:v>
       </x:c>
+      <x:c r="AP11" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AQ11" t="str">
+        <x:v>Unknown / Needs Evidence</x:v>
+      </x:c>
+      <x:c r="AR11" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="AS11" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="AT11" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AU11" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="12" ht="58" customHeight="1">
       <x:c r="A12" t="str">
@@ -10258,6 +10570,24 @@
         <x:v>Unknown / Needs Project-Specific Review</x:v>
       </x:c>
       <x:c r="AO12" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AP12" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AQ12" t="str">
+        <x:v>Unknown / Needs Evidence</x:v>
+      </x:c>
+      <x:c r="AR12" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="AS12" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="AT12" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AU12" t="str">
         <x:v>Unknown</x:v>
       </x:c>
     </x:row>
@@ -10379,6 +10709,24 @@
       <x:c r="AO13" t="str">
         <x:v>Unknown</x:v>
       </x:c>
+      <x:c r="AP13" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AQ13" t="str">
+        <x:v>Unknown / Needs Evidence</x:v>
+      </x:c>
+      <x:c r="AR13" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="AS13" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="AT13" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AU13" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="14" ht="58" customHeight="1">
       <x:c r="A14" t="str">
@@ -10496,6 +10844,24 @@
       <x:c r="AO14" t="str">
         <x:v>Unknown</x:v>
       </x:c>
+      <x:c r="AP14" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AQ14" t="str">
+        <x:v>Unknown / Needs Evidence</x:v>
+      </x:c>
+      <x:c r="AR14" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="AS14" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="AT14" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AU14" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="15" ht="58" customHeight="1">
       <x:c r="A15" t="str">
@@ -10613,6 +10979,24 @@
         <x:v>Unknown / Needs Project-Specific Review</x:v>
       </x:c>
       <x:c r="AO15" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AP15" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AQ15" t="str">
+        <x:v>Unknown / Needs Evidence</x:v>
+      </x:c>
+      <x:c r="AR15" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="AS15" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="AT15" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AU15" t="str">
         <x:v>Unknown</x:v>
       </x:c>
     </x:row>
@@ -10730,6 +11114,24 @@
       <x:c r="AO16" t="str">
         <x:v>Unknown</x:v>
       </x:c>
+      <x:c r="AP16" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AQ16" t="str">
+        <x:v>Unknown / Needs Evidence</x:v>
+      </x:c>
+      <x:c r="AR16" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="AS16" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="AT16" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AU16" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="17" ht="58" customHeight="1">
       <x:c r="A17" t="str">
@@ -10845,6 +11247,24 @@
       <x:c r="AO17" t="str">
         <x:v>Unknown</x:v>
       </x:c>
+      <x:c r="AP17" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AQ17" t="str">
+        <x:v>Unknown / Needs Evidence</x:v>
+      </x:c>
+      <x:c r="AR17" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="AS17" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="AT17" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AU17" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="18" ht="58" customHeight="1">
       <x:c r="A18" t="str">
@@ -10960,6 +11380,24 @@
       <x:c r="AO18" t="str">
         <x:v>Unknown</x:v>
       </x:c>
+      <x:c r="AP18" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AQ18" t="str">
+        <x:v>Unknown / Needs Evidence</x:v>
+      </x:c>
+      <x:c r="AR18" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="AS18" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="AT18" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AU18" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="19" ht="58" customHeight="1">
       <x:c r="A19" t="str">
@@ -11077,6 +11515,24 @@
       <x:c r="AO19" t="str">
         <x:v>Unknown</x:v>
       </x:c>
+      <x:c r="AP19" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AQ19" t="str">
+        <x:v>Unknown / Needs Evidence</x:v>
+      </x:c>
+      <x:c r="AR19" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="AS19" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="AT19" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AU19" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="20" ht="58" customHeight="1">
       <x:c r="A20" t="str">
@@ -11192,6 +11648,24 @@
       <x:c r="AO20" t="str">
         <x:v>Unknown</x:v>
       </x:c>
+      <x:c r="AP20" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AQ20" t="str">
+        <x:v>Unknown / Needs Evidence</x:v>
+      </x:c>
+      <x:c r="AR20" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="AS20" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="AT20" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AU20" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="21" ht="58" customHeight="1">
       <x:c r="A21" t="str">
@@ -11309,6 +11783,24 @@
       <x:c r="AO21" t="str">
         <x:v>Robot Manipulation; Diffusion Policy / Primitive Skills</x:v>
       </x:c>
+      <x:c r="AP21" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AQ21" t="str">
+        <x:v>Unknown / Needs Evidence</x:v>
+      </x:c>
+      <x:c r="AR21" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="AS21" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="AT21" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AU21" t="str">
+        <x:v>https://ojs.aaai.org/index.php/AAAI/article/view/38889；官方摘要/论文集元数据</x:v>
+      </x:c>
     </x:row>
     <x:row r="22" ht="58" customHeight="1">
       <x:c r="A22" t="str">
@@ -11426,6 +11918,24 @@
       <x:c r="AO22" t="str">
         <x:v>Imitation Learning; Multi-Task / Foresight</x:v>
       </x:c>
+      <x:c r="AP22" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AQ22" t="str">
+        <x:v>Unknown / Needs Evidence</x:v>
+      </x:c>
+      <x:c r="AR22" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="AS22" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="AT22" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AU22" t="str">
+        <x:v>https://ojs.aaai.org/index.php/AAAI/article/view/38911；官方摘要/论文集元数据</x:v>
+      </x:c>
     </x:row>
     <x:row r="23" ht="58" customHeight="1">
       <x:c r="A23" t="str">
@@ -11543,6 +12053,24 @@
       <x:c r="AO23" t="str">
         <x:v>Robot Manipulation; Long-Horizon / Visual-Tactile Policy</x:v>
       </x:c>
+      <x:c r="AP23" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AQ23" t="str">
+        <x:v>Unknown / Needs Evidence</x:v>
+      </x:c>
+      <x:c r="AR23" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="AS23" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="AT23" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AU23" t="str">
+        <x:v>https://ojs.aaai.org/index.php/AAAI/article/view/38955；官方摘要/论文集元数据</x:v>
+      </x:c>
     </x:row>
     <x:row r="24" ht="58" customHeight="1">
       <x:c r="A24" t="str">
@@ -11660,6 +12188,24 @@
       <x:c r="AO24" t="str">
         <x:v>Robot Manipulation; Humanoid / Generalization</x:v>
       </x:c>
+      <x:c r="AP24" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AQ24" t="str">
+        <x:v>Unknown / Needs Evidence</x:v>
+      </x:c>
+      <x:c r="AR24" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="AS24" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="AT24" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AU24" t="str">
+        <x:v>https://ojs.aaai.org/index.php/AAAI/article/view/38539；官方摘要/论文集元数据</x:v>
+      </x:c>
     </x:row>
     <x:row r="25" ht="58" customHeight="1">
       <x:c r="A25" t="str">
@@ -11775,6 +12321,24 @@
       <x:c r="AO25" t="str">
         <x:v>Dexterous Manipulation; Human Demonstrations / Motion Prior</x:v>
       </x:c>
+      <x:c r="AP25" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AQ25" t="str">
+        <x:v>Unknown / Needs Evidence</x:v>
+      </x:c>
+      <x:c r="AR25" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="AS25" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="AT25" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AU25" t="str">
+        <x:v>https://ojs.aaai.org/index.php/AAAI/article/download/38892/42854；官方摘要/论文集元数据</x:v>
+      </x:c>
     </x:row>
     <x:row r="26" ht="58" customHeight="1">
       <x:c r="A26" t="str">
@@ -11892,6 +12456,24 @@
       <x:c r="AO26" t="str">
         <x:v>Unknown</x:v>
       </x:c>
+      <x:c r="AP26" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AQ26" t="str">
+        <x:v>Unknown / Needs Evidence</x:v>
+      </x:c>
+      <x:c r="AR26" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="AS26" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="AT26" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AU26" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="27" ht="58" customHeight="1">
       <x:c r="A27" t="str">
@@ -12009,6 +12591,24 @@
       <x:c r="AO27" t="str">
         <x:v>Unknown</x:v>
       </x:c>
+      <x:c r="AP27" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AQ27" t="str">
+        <x:v>Unknown / Needs Evidence</x:v>
+      </x:c>
+      <x:c r="AR27" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="AS27" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="AT27" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AU27" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="28" ht="58" customHeight="1">
       <x:c r="A28" t="str">
@@ -12126,6 +12726,24 @@
       <x:c r="AO28" t="str">
         <x:v>Unknown</x:v>
       </x:c>
+      <x:c r="AP28" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AQ28" t="str">
+        <x:v>Unknown / Needs Evidence</x:v>
+      </x:c>
+      <x:c r="AR28" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="AS28" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="AT28" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AU28" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="29" ht="58" customHeight="1">
       <x:c r="A29" t="str">
@@ -12243,6 +12861,24 @@
       <x:c r="AO29" t="str">
         <x:v>Unknown</x:v>
       </x:c>
+      <x:c r="AP29" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AQ29" t="str">
+        <x:v>Unknown / Needs Evidence</x:v>
+      </x:c>
+      <x:c r="AR29" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="AS29" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="AT29" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AU29" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="30" ht="58" customHeight="1">
       <x:c r="A30" t="str">
@@ -12360,6 +12996,24 @@
       <x:c r="AO30" t="str">
         <x:v>Unknown</x:v>
       </x:c>
+      <x:c r="AP30" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AQ30" t="str">
+        <x:v>Unknown / Needs Evidence</x:v>
+      </x:c>
+      <x:c r="AR30" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="AS30" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="AT30" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AU30" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="31" ht="58" customHeight="1">
       <x:c r="A31" t="str">
@@ -12477,6 +13131,24 @@
       <x:c r="AO31" t="str">
         <x:v>Unknown</x:v>
       </x:c>
+      <x:c r="AP31" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AQ31" t="str">
+        <x:v>Unknown / Needs Evidence</x:v>
+      </x:c>
+      <x:c r="AR31" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="AS31" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="AT31" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AU31" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="32" ht="58" customHeight="1">
       <x:c r="A32" t="str">
@@ -12594,6 +13266,24 @@
       <x:c r="AO32" t="str">
         <x:v>Unknown</x:v>
       </x:c>
+      <x:c r="AP32" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AQ32" t="str">
+        <x:v>Unknown / Needs Evidence</x:v>
+      </x:c>
+      <x:c r="AR32" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="AS32" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="AT32" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AU32" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="33" ht="58" customHeight="1">
       <x:c r="A33" t="str">
@@ -12711,6 +13401,24 @@
       <x:c r="AO33" t="str">
         <x:v>Unknown</x:v>
       </x:c>
+      <x:c r="AP33" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AQ33" t="str">
+        <x:v>Unknown / Needs Evidence</x:v>
+      </x:c>
+      <x:c r="AR33" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="AS33" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="AT33" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AU33" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="34" ht="58" customHeight="1">
       <x:c r="A34" t="str">
@@ -12828,6 +13536,24 @@
       <x:c r="AO34" t="str">
         <x:v>Unknown</x:v>
       </x:c>
+      <x:c r="AP34" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AQ34" t="str">
+        <x:v>Unknown / Needs Evidence</x:v>
+      </x:c>
+      <x:c r="AR34" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="AS34" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="AT34" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AU34" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="35" ht="58" customHeight="1">
       <x:c r="A35" t="str">
@@ -12945,6 +13671,24 @@
       <x:c r="AO35" t="str">
         <x:v>Unknown</x:v>
       </x:c>
+      <x:c r="AP35" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AQ35" t="str">
+        <x:v>Unknown / Needs Evidence</x:v>
+      </x:c>
+      <x:c r="AR35" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="AS35" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="AT35" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AU35" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="36" ht="58" customHeight="1">
       <x:c r="A36" t="str">
@@ -13062,6 +13806,24 @@
       <x:c r="AO36" t="str">
         <x:v>Unknown</x:v>
       </x:c>
+      <x:c r="AP36" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AQ36" t="str">
+        <x:v>Unknown / Needs Evidence</x:v>
+      </x:c>
+      <x:c r="AR36" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="AS36" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="AT36" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AU36" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="37" ht="58" customHeight="1">
       <x:c r="A37" t="str">
@@ -13179,6 +13941,24 @@
       <x:c r="AO37" t="str">
         <x:v>Unknown</x:v>
       </x:c>
+      <x:c r="AP37" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AQ37" t="str">
+        <x:v>Unknown / Needs Evidence</x:v>
+      </x:c>
+      <x:c r="AR37" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="AS37" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="AT37" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AU37" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="38" ht="58" customHeight="1">
       <x:c r="A38" t="str">
@@ -13296,6 +14076,24 @@
       <x:c r="AO38" t="str">
         <x:v>Unknown</x:v>
       </x:c>
+      <x:c r="AP38" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AQ38" t="str">
+        <x:v>Unknown / Needs Evidence</x:v>
+      </x:c>
+      <x:c r="AR38" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="AS38" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="AT38" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AU38" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="39" ht="58" customHeight="1">
       <x:c r="A39" t="str">
@@ -13413,6 +14211,24 @@
       <x:c r="AO39" t="str">
         <x:v>Unknown</x:v>
       </x:c>
+      <x:c r="AP39" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AQ39" t="str">
+        <x:v>Unknown / Needs Evidence</x:v>
+      </x:c>
+      <x:c r="AR39" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="AS39" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="AT39" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AU39" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="40" ht="58" customHeight="1">
       <x:c r="A40" t="str">
@@ -13528,6 +14344,24 @@
       <x:c r="AO40" t="str">
         <x:v>Unknown</x:v>
       </x:c>
+      <x:c r="AP40" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AQ40" t="str">
+        <x:v>Unknown / Needs Evidence</x:v>
+      </x:c>
+      <x:c r="AR40" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="AS40" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="AT40" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AU40" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="41" ht="58" customHeight="1">
       <x:c r="A41" t="str">
@@ -13643,6 +14477,24 @@
       <x:c r="AO41" t="str">
         <x:v>Unknown</x:v>
       </x:c>
+      <x:c r="AP41" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AQ41" t="str">
+        <x:v>Unknown / Needs Evidence</x:v>
+      </x:c>
+      <x:c r="AR41" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="AS41" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="AT41" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AU41" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="42" ht="58" customHeight="1">
       <x:c r="A42" t="str">
@@ -13758,6 +14610,24 @@
       <x:c r="AO42" t="str">
         <x:v>Unknown</x:v>
       </x:c>
+      <x:c r="AP42" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AQ42" t="str">
+        <x:v>Unknown / Needs Evidence</x:v>
+      </x:c>
+      <x:c r="AR42" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="AS42" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="AT42" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AU42" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="43" ht="58" customHeight="1">
       <x:c r="A43" t="str">
@@ -13873,6 +14743,24 @@
       <x:c r="AO43" t="str">
         <x:v>Unknown</x:v>
       </x:c>
+      <x:c r="AP43" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AQ43" t="str">
+        <x:v>Unknown / Needs Evidence</x:v>
+      </x:c>
+      <x:c r="AR43" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="AS43" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="AT43" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AU43" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="44" ht="58" customHeight="1">
       <x:c r="A44" t="str">
@@ -13988,6 +14876,24 @@
       <x:c r="AO44" t="str">
         <x:v>Unknown</x:v>
       </x:c>
+      <x:c r="AP44" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AQ44" t="str">
+        <x:v>Unknown / Needs Evidence</x:v>
+      </x:c>
+      <x:c r="AR44" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="AS44" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="AT44" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AU44" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="45" ht="58" customHeight="1">
       <x:c r="A45" t="str">
@@ -14103,6 +15009,24 @@
       <x:c r="AO45" t="str">
         <x:v>Unknown</x:v>
       </x:c>
+      <x:c r="AP45" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AQ45" t="str">
+        <x:v>Unknown / Needs Evidence</x:v>
+      </x:c>
+      <x:c r="AR45" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="AS45" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="AT45" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AU45" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="46" ht="58" customHeight="1">
       <x:c r="A46" t="str">
@@ -14220,6 +15144,24 @@
       <x:c r="AO46" t="str">
         <x:v>Unknown</x:v>
       </x:c>
+      <x:c r="AP46" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AQ46" t="str">
+        <x:v>Unknown / Needs Evidence</x:v>
+      </x:c>
+      <x:c r="AR46" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="AS46" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="AT46" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AU46" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="47" ht="58" customHeight="1">
       <x:c r="A47" t="str">
@@ -14337,6 +15279,24 @@
       <x:c r="AO47" t="str">
         <x:v>Unknown</x:v>
       </x:c>
+      <x:c r="AP47" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AQ47" t="str">
+        <x:v>Unknown / Needs Evidence</x:v>
+      </x:c>
+      <x:c r="AR47" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="AS47" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="AT47" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AU47" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="48" ht="58" customHeight="1">
       <x:c r="A48" t="str">
@@ -14454,6 +15414,24 @@
       <x:c r="AO48" t="str">
         <x:v>Unknown</x:v>
       </x:c>
+      <x:c r="AP48" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AQ48" t="str">
+        <x:v>Unknown / Needs Evidence</x:v>
+      </x:c>
+      <x:c r="AR48" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="AS48" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="AT48" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AU48" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="49" ht="58" customHeight="1">
       <x:c r="A49" t="str">
@@ -14571,6 +15549,24 @@
       <x:c r="AO49" t="str">
         <x:v>Unknown</x:v>
       </x:c>
+      <x:c r="AP49" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AQ49" t="str">
+        <x:v>Unknown / Needs Evidence</x:v>
+      </x:c>
+      <x:c r="AR49" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="AS49" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="AT49" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AU49" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="50" ht="58" customHeight="1">
       <x:c r="A50" t="str">
@@ -14688,6 +15684,24 @@
       <x:c r="AO50" t="str">
         <x:v>Unknown</x:v>
       </x:c>
+      <x:c r="AP50" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AQ50" t="str">
+        <x:v>Unknown / Needs Evidence</x:v>
+      </x:c>
+      <x:c r="AR50" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="AS50" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="AT50" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AU50" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="51" ht="58" customHeight="1">
       <x:c r="A51" t="str">
@@ -14805,6 +15819,24 @@
       <x:c r="AO51" t="str">
         <x:v>Unknown</x:v>
       </x:c>
+      <x:c r="AP51" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AQ51" t="str">
+        <x:v>Unknown / Needs Evidence</x:v>
+      </x:c>
+      <x:c r="AR51" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="AS51" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="AT51" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AU51" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="52" ht="58" customHeight="1">
       <x:c r="A52" t="str">
@@ -14922,6 +15954,24 @@
       <x:c r="AO52" t="str">
         <x:v>Unknown</x:v>
       </x:c>
+      <x:c r="AP52" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AQ52" t="str">
+        <x:v>Unknown / Needs Evidence</x:v>
+      </x:c>
+      <x:c r="AR52" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="AS52" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="AT52" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AU52" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="53" ht="58" customHeight="1">
       <x:c r="A53" t="str">
@@ -15039,6 +16089,24 @@
       <x:c r="AO53" t="str">
         <x:v>Unknown</x:v>
       </x:c>
+      <x:c r="AP53" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AQ53" t="str">
+        <x:v>Unknown / Needs Evidence</x:v>
+      </x:c>
+      <x:c r="AR53" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="AS53" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="AT53" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AU53" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="54" ht="58" customHeight="1">
       <x:c r="A54" t="str">
@@ -15156,6 +16224,24 @@
       <x:c r="AO54" t="str">
         <x:v>Unknown</x:v>
       </x:c>
+      <x:c r="AP54" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AQ54" t="str">
+        <x:v>Unknown / Needs Evidence</x:v>
+      </x:c>
+      <x:c r="AR54" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="AS54" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="AT54" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AU54" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="55" ht="58" customHeight="1">
       <x:c r="A55" t="str">
@@ -15273,6 +16359,24 @@
       <x:c r="AO55" t="str">
         <x:v>Unknown</x:v>
       </x:c>
+      <x:c r="AP55" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AQ55" t="str">
+        <x:v>Unknown / Needs Evidence</x:v>
+      </x:c>
+      <x:c r="AR55" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="AS55" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="AT55" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AU55" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="56" ht="58" customHeight="1">
       <x:c r="A56" t="str">
@@ -15390,6 +16494,24 @@
       <x:c r="AO56" t="str">
         <x:v>Unknown</x:v>
       </x:c>
+      <x:c r="AP56" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AQ56" t="str">
+        <x:v>Unknown / Needs Evidence</x:v>
+      </x:c>
+      <x:c r="AR56" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="AS56" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="AT56" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AU56" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="57" ht="58" customHeight="1">
       <x:c r="A57" t="str">
@@ -15507,6 +16629,24 @@
       <x:c r="AO57" t="str">
         <x:v>Unknown</x:v>
       </x:c>
+      <x:c r="AP57" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AQ57" t="str">
+        <x:v>Unknown / Needs Evidence</x:v>
+      </x:c>
+      <x:c r="AR57" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="AS57" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="AT57" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AU57" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="58" ht="58" customHeight="1">
       <x:c r="A58" t="str">
@@ -15630,6 +16770,24 @@
       <x:c r="AO58" t="str">
         <x:v>Unknown</x:v>
       </x:c>
+      <x:c r="AP58" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AQ58" t="str">
+        <x:v>Unknown / Needs Evidence</x:v>
+      </x:c>
+      <x:c r="AR58" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="AS58" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="AT58" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AU58" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="59" ht="58" customHeight="1">
       <x:c r="A59" t="str">
@@ -15753,6 +16911,24 @@
       <x:c r="AO59" t="str">
         <x:v>Unknown</x:v>
       </x:c>
+      <x:c r="AP59" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AQ59" t="str">
+        <x:v>Unknown / Needs Evidence</x:v>
+      </x:c>
+      <x:c r="AR59" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="AS59" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="AT59" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AU59" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="60" ht="58" customHeight="1">
       <x:c r="A60" t="str">
@@ -15874,6 +17050,24 @@
       <x:c r="AO60" t="str">
         <x:v>Bimanual; Benchmark / Synthetic Demonstrations</x:v>
       </x:c>
+      <x:c r="AP60" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AQ60" t="str">
+        <x:v>Unknown / Needs Evidence</x:v>
+      </x:c>
+      <x:c r="AR60" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="AS60" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="AT60" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AU60" t="str">
+        <x:v>https://openaccess.thecvf.com/content/CVPR2025/html/Mu_RoboTwin_Dual-Arm_Robot_Benchmark_with_Generative_Digital_Twins_CVPR_2025_paper.html；官方摘要/论文集元数据</x:v>
+      </x:c>
     </x:row>
     <x:row r="61" ht="58" customHeight="1">
       <x:c r="A61" t="str">
@@ -15997,6 +17191,24 @@
       <x:c r="AO61" t="str">
         <x:v>VLA; 3D Manipulation / Data Efficiency</x:v>
       </x:c>
+      <x:c r="AP61" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AQ61" t="str">
+        <x:v>Unknown / Needs Evidence</x:v>
+      </x:c>
+      <x:c r="AR61" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="AS61" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="AT61" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AU61" t="str">
+        <x:v>https://proceedings.neurips.cc/paper_files/paper/2025/hash/5c1a8aa04c1a2cf5013f28831870dafa-Abstract-Conference.html；官方摘要/论文集元数据</x:v>
+      </x:c>
     </x:row>
     <x:row r="62" ht="58" customHeight="1">
       <x:c r="A62" t="str">
@@ -16120,6 +17332,24 @@
       <x:c r="AO62" t="str">
         <x:v>VLA; Inference Acceleration / Token Caching</x:v>
       </x:c>
+      <x:c r="AP62" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AQ62" t="str">
+        <x:v>Unknown / Needs Evidence</x:v>
+      </x:c>
+      <x:c r="AR62" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="AS62" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="AT62" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AU62" t="str">
+        <x:v>https://proceedings.neurips.cc/paper_files/paper/2025/hash/f062da1973ac9ac61fc6d44dd7fa309f-Abstract-Conference.html；官方摘要/论文集元数据</x:v>
+      </x:c>
     </x:row>
     <x:row r="63" ht="58" customHeight="1">
       <x:c r="A63" t="str">
@@ -16243,6 +17473,24 @@
       <x:c r="AO63" t="str">
         <x:v>VLA; Autoregressive Reasoning / Diffusion</x:v>
       </x:c>
+      <x:c r="AP63" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AQ63" t="str">
+        <x:v>Unknown / Needs Evidence</x:v>
+      </x:c>
+      <x:c r="AR63" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="AS63" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="AT63" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AU63" t="str">
+        <x:v>https://proceedings.mlr.press/v267/wen25g.html；官方摘要/论文集元数据</x:v>
+      </x:c>
     </x:row>
     <x:row r="64" ht="58" customHeight="1">
       <x:c r="A64" t="str">
@@ -16366,6 +17614,24 @@
       <x:c r="AO64" t="str">
         <x:v>VLA; World Model / 3D Generation</x:v>
       </x:c>
+      <x:c r="AP64" t="str">
+        <x:v>B</x:v>
+      </x:c>
+      <x:c r="AQ64" t="str">
+        <x:v>Idea Clue 1: compare explicit 3D goal prediction against image-only VLA on dual-arm ordinary-gripper tasks. Evidence: paper motivation and 3D goal image/point-cloud generation. Why relevant: direct test of 3D planning value.</x:v>
+      </x:c>
+      <x:c r="AR64" t="str">
+        <x:v>Not Reported in the accessible proceedings page.</x:v>
+      </x:c>
+      <x:c r="AS64" t="str">
+        <x:v>Not Explicitly Reported in the accessible proceedings page.</x:v>
+      </x:c>
+      <x:c r="AT64" t="str">
+        <x:v>OpenAlex Work: https://openalex.org/W4392886475</x:v>
+      </x:c>
+      <x:c r="AU64" t="str">
+        <x:v>https://proceedings.mlr.press/v235/zhen24a.html；官方摘要/论文集元数据</x:v>
+      </x:c>
     </x:row>
     <x:row r="65" ht="58" customHeight="1">
       <x:c r="A65" t="str">
@@ -16489,6 +17755,24 @@
       <x:c r="AO65" t="str">
         <x:v>VLA; Efficient Model / Pose Prediction</x:v>
       </x:c>
+      <x:c r="AP65" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AQ65" t="str">
+        <x:v>Unknown / Needs Evidence</x:v>
+      </x:c>
+      <x:c r="AR65" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="AS65" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="AT65" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AU65" t="str">
+        <x:v>https://proceedings.neurips.cc/paper_files/paper/2024/hash/46a126492ea6fb87410e55a58df2e189-Abstract-Conference.html；官方摘要/论文集元数据</x:v>
+      </x:c>
     </x:row>
     <x:row r="66" ht="58" customHeight="1">
       <x:c r="A66" t="str">
@@ -16612,6 +17896,24 @@
       <x:c r="AO66" t="str">
         <x:v>Unknown</x:v>
       </x:c>
+      <x:c r="AP66" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AQ66" t="str">
+        <x:v>Unknown / Needs Evidence</x:v>
+      </x:c>
+      <x:c r="AR66" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="AS66" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="AT66" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AU66" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="67" ht="58" customHeight="1">
       <x:c r="A67" t="str">
@@ -16733,6 +18035,24 @@
         <x:v>Unknown / Needs Project-Specific Review</x:v>
       </x:c>
       <x:c r="AO67" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AP67" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AQ67" t="str">
+        <x:v>Unknown / Needs Evidence</x:v>
+      </x:c>
+      <x:c r="AR67" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="AS67" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="AT67" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AU67" t="str">
         <x:v>Unknown</x:v>
       </x:c>
     </x:row>
@@ -16856,6 +18176,24 @@
       <x:c r="AO68" t="str">
         <x:v>Robot Manipulation; Consistency Flow Matching / 3D Policy</x:v>
       </x:c>
+      <x:c r="AP68" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AQ68" t="str">
+        <x:v>Unknown / Needs Evidence</x:v>
+      </x:c>
+      <x:c r="AR68" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="AS68" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="AT68" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AU68" t="str">
+        <x:v>https://ojs.aaai.org/index.php/AAAI/article/view/33617；官方摘要/论文集元数据</x:v>
+      </x:c>
     </x:row>
     <x:row r="69" ht="58" customHeight="1">
       <x:c r="A69" t="str">
@@ -16979,6 +18317,24 @@
       <x:c r="AO69" t="str">
         <x:v>Dexterous Hand; Policy Distillation / Generalization</x:v>
       </x:c>
+      <x:c r="AP69" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AQ69" t="str">
+        <x:v>Unknown / Needs Evidence</x:v>
+      </x:c>
+      <x:c r="AR69" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="AS69" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="AT69" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AU69" t="str">
+        <x:v>https://openaccess.thecvf.com/content/CVPR2025/html/Wang_UniGraspTransformer_Simplified_Policy_Distillation_for_Scalable_Dexterous_Robotic_Grasping_CVPR_2025_paper.html；官方摘要/论文集元数据</x:v>
+      </x:c>
     </x:row>
     <x:row r="70" ht="58" customHeight="1">
       <x:c r="A70" t="str">
@@ -17102,6 +18458,24 @@
       <x:c r="AO70" t="str">
         <x:v>Dexterous Hand; Residual RL / VLM Planning</x:v>
       </x:c>
+      <x:c r="AP70" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AQ70" t="str">
+        <x:v>Unknown / Needs Evidence</x:v>
+      </x:c>
+      <x:c r="AR70" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="AS70" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="AT70" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AU70" t="str">
+        <x:v>https://proceedings.neurips.cc/paper_files/paper/2025/hash/862644b156e51c35dea5a7446d640b14-Abstract-Conference.html；官方摘要/论文集元数据</x:v>
+      </x:c>
     </x:row>
     <x:row r="71" ht="58" customHeight="1">
       <x:c r="A71" t="str">
@@ -17225,6 +18599,24 @@
       <x:c r="AO71" t="str">
         <x:v>VLA; Video-Action Model / Generalization</x:v>
       </x:c>
+      <x:c r="AP71" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AQ71" t="str">
+        <x:v>Unknown / Needs Evidence</x:v>
+      </x:c>
+      <x:c r="AR71" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="AS71" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="AT71" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AU71" t="str">
+        <x:v>https://proceedings.neurips.cc/paper_files/paper/2025/hash/89a3b655a8b68ae1c76b768152c9c19d-Abstract-Conference.html；官方摘要/论文集元数据</x:v>
+      </x:c>
     </x:row>
     <x:row r="72" ht="58" customHeight="1">
       <x:c r="A72" t="str">
@@ -17348,6 +18740,24 @@
       <x:c r="AO72" t="str">
         <x:v>Dexterous Hand; Contact Reasoning / Language-guided Grasp</x:v>
       </x:c>
+      <x:c r="AP72" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AQ72" t="str">
+        <x:v>Unknown / Needs Evidence</x:v>
+      </x:c>
+      <x:c r="AR72" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="AS72" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="AT72" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AU72" t="str">
+        <x:v>https://openaccess.thecvf.com/content/CVPR2026/html/Lee_DextER_Language-driven_Dexterous_Grasp_Generation_with_Embodied_Reasoning_CVPR_2026_paper.html；官方摘要/论文集元数据</x:v>
+      </x:c>
     </x:row>
     <x:row r="73" ht="58" customHeight="1">
       <x:c r="A73" t="str">
@@ -17471,6 +18881,24 @@
       <x:c r="AO73" t="str">
         <x:v>Unknown</x:v>
       </x:c>
+      <x:c r="AP73" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AQ73" t="str">
+        <x:v>Unknown / Needs Evidence</x:v>
+      </x:c>
+      <x:c r="AR73" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="AS73" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="AT73" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AU73" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="74" ht="58" customHeight="1">
       <x:c r="A74" t="str">
@@ -17594,6 +19022,24 @@
       <x:c r="AO74" t="str">
         <x:v>Unknown</x:v>
       </x:c>
+      <x:c r="AP74" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AQ74" t="str">
+        <x:v>Unknown / Needs Evidence</x:v>
+      </x:c>
+      <x:c r="AR74" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="AS74" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="AT74" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AU74" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="75" ht="58" customHeight="1">
       <x:c r="A75" t="str">
@@ -17715,6 +19161,24 @@
         <x:v>Unknown / Needs Project-Specific Review</x:v>
       </x:c>
       <x:c r="AO75" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AP75" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AQ75" t="str">
+        <x:v>Unknown / Needs Evidence</x:v>
+      </x:c>
+      <x:c r="AR75" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="AS75" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="AT75" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AU75" t="str">
         <x:v>Unknown</x:v>
       </x:c>
     </x:row>
@@ -17836,6 +19300,24 @@
       <x:c r="AO76" t="str">
         <x:v>Unknown</x:v>
       </x:c>
+      <x:c r="AP76" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AQ76" t="str">
+        <x:v>Unknown / Needs Evidence</x:v>
+      </x:c>
+      <x:c r="AR76" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="AS76" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="AT76" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AU76" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="77" ht="58" customHeight="1">
       <x:c r="A77" t="str">
@@ -17953,6 +19435,24 @@
         <x:v>Unknown / Needs Project-Specific Review</x:v>
       </x:c>
       <x:c r="AO77" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AP77" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AQ77" t="str">
+        <x:v>Unknown / Needs Evidence</x:v>
+      </x:c>
+      <x:c r="AR77" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="AS77" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="AT77" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AU77" t="str">
         <x:v>Unknown</x:v>
       </x:c>
     </x:row>
@@ -18074,6 +19574,24 @@
       <x:c r="AO78" t="str">
         <x:v>Unknown</x:v>
       </x:c>
+      <x:c r="AP78" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AQ78" t="str">
+        <x:v>Unknown / Needs Evidence</x:v>
+      </x:c>
+      <x:c r="AR78" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="AS78" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="AT78" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AU78" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="79">
       <x:c r="A79" t="str">
@@ -18198,6 +19716,24 @@
       </x:c>
       <x:c r="AO79" t="str">
         <x:v>VLA; Robot Manipulation; Visual Grounding; Robot Perception; Implicit Grounding; Gaze-Region Reconstruction; Generalization; Diffusion Transformer</x:v>
+      </x:c>
+      <x:c r="AP79" t="str">
+        <x:v>B</x:v>
+      </x:c>
+      <x:c r="AQ79" t="str">
+        <x:v>Idea Clue 1: test implicit ga</x:v>
+      </x:c>
+      <x:c r="AR79" t="str">
+        <x:v>Not Reported in the official abstract/project evidence rechecked for this batch.</x:v>
+      </x:c>
+      <x:c r="AS79" t="str">
+        <x:v>Not Explicitly Reported in the accessible official abstract/project evidence.</x:v>
+      </x:c>
+      <x:c r="AT79" t="str">
+        <x:v>OpenAlex Work: https://openalex.org/W7137985120</x:v>
+      </x:c>
+      <x:c r="AU79" t="str">
+        <x:v>https://ojs.aaai.org/index.php/AAAI/article/view/38921；https://arxiv.org/abs/2508.10333；https://zionchow.github.io/ReconVLA/；https://github.com/OpenHelix-Team/ReconVLA</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -18220,7 +19756,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf93483fbba4d46d5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf300a6bb39a34b35"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -18462,6 +19998,24 @@
       <x:c r="BH1" t="str">
         <x:v>Tags</x:v>
       </x:c>
+      <x:c r="BI1" t="str">
+        <x:v>Evidence Quality</x:v>
+      </x:c>
+      <x:c r="BJ1" t="str">
+        <x:v>Idea Clues</x:v>
+      </x:c>
+      <x:c r="BK1" t="str">
+        <x:v>Ablation Study</x:v>
+      </x:c>
+      <x:c r="BL1" t="str">
+        <x:v>Failure Cases</x:v>
+      </x:c>
+      <x:c r="BM1" t="str">
+        <x:v>Citation Source Identifier</x:v>
+      </x:c>
+      <x:c r="BN1" t="str">
+        <x:v>Evidence Sources</x:v>
+      </x:c>
     </x:row>
     <x:row r="2" ht="58" customHeight="1">
       <x:c r="A2" t="str">
@@ -18636,6 +20190,24 @@
       <x:c r="BH2" t="str">
         <x:v>Robot Manipulation; Diffusion Policy / Hierarchical Control</x:v>
       </x:c>
+      <x:c r="BI2" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BJ2" t="str">
+        <x:v>Unknown / Needs Evidence</x:v>
+      </x:c>
+      <x:c r="BK2" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="BL2" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="BM2" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BN2" t="str">
+        <x:v>https://openaccess.thecvf.com/content/CVPR2024/html/Ma_Hierarchical_Diffusion_Policy_for_Kinematics-Aware_Multi-Task_Robotic_Manipulation_CVPR_2024_paper.html；官方摘要/论文集元数据</x:v>
+      </x:c>
     </x:row>
     <x:row r="3" ht="58" customHeight="1">
       <x:c r="A3" t="str">
@@ -18810,6 +20382,24 @@
       <x:c r="BH3" t="str">
         <x:v>bimanual manipulation; decoupled interaction; RoboTwin</x:v>
       </x:c>
+      <x:c r="BI3" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BJ3" t="str">
+        <x:v>Unknown / Needs Evidence</x:v>
+      </x:c>
+      <x:c r="BK3" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="BL3" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="BM3" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BN3" t="str">
+        <x:v>https://openaccess.thecvf.com/content/ICCV2025/html/Jiang_Rethinking_Bimanual_Robotic_Manipulation_Learning_with_Decoupled_Interaction_Framework_ICCV_2025_paper.html；官方摘要/论文集元数据</x:v>
+      </x:c>
     </x:row>
     <x:row r="4" ht="58" customHeight="1">
       <x:c r="A4" t="str">
@@ -18984,6 +20574,24 @@
       <x:c r="BH4" t="str">
         <x:v>bimanual; diffusion; teleoperation; human demonstration</x:v>
       </x:c>
+      <x:c r="BI4" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BJ4" t="str">
+        <x:v>Unknown / Needs Evidence</x:v>
+      </x:c>
+      <x:c r="BK4" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="BL4" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="BM4" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BN4" t="str">
+        <x:v>https://openaccess.thecvf.com/content/ICCV2025/html/Xu_Diffusion-Based_Imaginative_Coordination_for_Bimanual_Manipulation_ICCV_2025_paper.html；官方摘要/论文集元数据</x:v>
+      </x:c>
     </x:row>
     <x:row r="5" ht="58" customHeight="1">
       <x:c r="A5" t="str">
@@ -19158,6 +20766,24 @@
       <x:c r="BH5" t="str">
         <x:v>Robot Manipulation; Diffusion Policy / Primitive Skills</x:v>
       </x:c>
+      <x:c r="BI5" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BJ5" t="str">
+        <x:v>Unknown / Needs Evidence</x:v>
+      </x:c>
+      <x:c r="BK5" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="BL5" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="BM5" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BN5" t="str">
+        <x:v>https://ojs.aaai.org/index.php/AAAI/article/view/38889；官方摘要/论文集元数据</x:v>
+      </x:c>
     </x:row>
     <x:row r="6" ht="58" customHeight="1">
       <x:c r="A6" t="str">
@@ -19332,6 +20958,24 @@
       <x:c r="BH6" t="str">
         <x:v>Imitation Learning; Multi-Task / Foresight</x:v>
       </x:c>
+      <x:c r="BI6" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BJ6" t="str">
+        <x:v>Unknown / Needs Evidence</x:v>
+      </x:c>
+      <x:c r="BK6" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="BL6" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="BM6" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BN6" t="str">
+        <x:v>https://ojs.aaai.org/index.php/AAAI/article/view/38911；官方摘要/论文集元数据</x:v>
+      </x:c>
     </x:row>
     <x:row r="7" ht="58" customHeight="1">
       <x:c r="A7" t="str">
@@ -19506,6 +21150,24 @@
       <x:c r="BH7" t="str">
         <x:v>Robot Manipulation; Long-Horizon / Visual-Tactile Policy</x:v>
       </x:c>
+      <x:c r="BI7" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BJ7" t="str">
+        <x:v>Unknown / Needs Evidence</x:v>
+      </x:c>
+      <x:c r="BK7" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="BL7" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="BM7" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BN7" t="str">
+        <x:v>https://ojs.aaai.org/index.php/AAAI/article/view/38955；官方摘要/论文集元数据</x:v>
+      </x:c>
     </x:row>
     <x:row r="8" ht="58" customHeight="1">
       <x:c r="A8" t="str">
@@ -19680,6 +21342,24 @@
       <x:c r="BH8" t="str">
         <x:v>Robot Manipulation; Humanoid / Generalization</x:v>
       </x:c>
+      <x:c r="BI8" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BJ8" t="str">
+        <x:v>Unknown / Needs Evidence</x:v>
+      </x:c>
+      <x:c r="BK8" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="BL8" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="BM8" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BN8" t="str">
+        <x:v>https://ojs.aaai.org/index.php/AAAI/article/view/38539；官方摘要/论文集元数据</x:v>
+      </x:c>
     </x:row>
     <x:row r="9" ht="58" customHeight="1">
       <x:c r="A9" t="str">
@@ -19852,6 +21532,24 @@
       <x:c r="BH9" t="str">
         <x:v>Dexterous Manipulation; Human Demonstrations / Motion Prior</x:v>
       </x:c>
+      <x:c r="BI9" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BJ9" t="str">
+        <x:v>Unknown / Needs Evidence</x:v>
+      </x:c>
+      <x:c r="BK9" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="BL9" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="BM9" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BN9" t="str">
+        <x:v>https://ojs.aaai.org/index.php/AAAI/article/download/38892/42854；官方摘要/论文集元数据</x:v>
+      </x:c>
     </x:row>
     <x:row r="10" ht="58" customHeight="1">
       <x:c r="A10" t="str">
@@ -20030,6 +21728,24 @@
       <x:c r="BH10" t="str">
         <x:v>Bimanual; Benchmark / Synthetic Demonstrations</x:v>
       </x:c>
+      <x:c r="BI10" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BJ10" t="str">
+        <x:v>Unknown / Needs Evidence</x:v>
+      </x:c>
+      <x:c r="BK10" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="BL10" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="BM10" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BN10" t="str">
+        <x:v>https://openaccess.thecvf.com/content/CVPR2025/html/Mu_RoboTwin_Dual-Arm_Robot_Benchmark_with_Generative_Digital_Twins_CVPR_2025_paper.html；官方摘要/论文集元数据</x:v>
+      </x:c>
     </x:row>
     <x:row r="11" ht="58" customHeight="1">
       <x:c r="A11" t="str">
@@ -20210,6 +21926,24 @@
       <x:c r="BH11" t="str">
         <x:v>VLA; 3D Manipulation / Data Efficiency</x:v>
       </x:c>
+      <x:c r="BI11" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BJ11" t="str">
+        <x:v>Unknown / Needs Evidence</x:v>
+      </x:c>
+      <x:c r="BK11" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="BL11" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="BM11" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BN11" t="str">
+        <x:v>https://proceedings.neurips.cc/paper_files/paper/2025/hash/5c1a8aa04c1a2cf5013f28831870dafa-Abstract-Conference.html；官方摘要/论文集元数据</x:v>
+      </x:c>
     </x:row>
     <x:row r="12" ht="58" customHeight="1">
       <x:c r="A12" t="str">
@@ -20390,6 +22124,24 @@
       <x:c r="BH12" t="str">
         <x:v>VLA; Inference Acceleration / Token Caching</x:v>
       </x:c>
+      <x:c r="BI12" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BJ12" t="str">
+        <x:v>Unknown / Needs Evidence</x:v>
+      </x:c>
+      <x:c r="BK12" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="BL12" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="BM12" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BN12" t="str">
+        <x:v>https://proceedings.neurips.cc/paper_files/paper/2025/hash/f062da1973ac9ac61fc6d44dd7fa309f-Abstract-Conference.html；官方摘要/论文集元数据</x:v>
+      </x:c>
     </x:row>
     <x:row r="13" ht="58" customHeight="1">
       <x:c r="A13" t="str">
@@ -20570,6 +22322,24 @@
       <x:c r="BH13" t="str">
         <x:v>VLA; Autoregressive Reasoning / Diffusion</x:v>
       </x:c>
+      <x:c r="BI13" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BJ13" t="str">
+        <x:v>Unknown / Needs Evidence</x:v>
+      </x:c>
+      <x:c r="BK13" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="BL13" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="BM13" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BN13" t="str">
+        <x:v>https://proceedings.mlr.press/v267/wen25g.html；官方摘要/论文集元数据</x:v>
+      </x:c>
     </x:row>
     <x:row r="14" ht="58" customHeight="1">
       <x:c r="A14" t="str">
@@ -20750,6 +22520,24 @@
       <x:c r="BH14" t="str">
         <x:v>VLA; World Model / 3D Generation</x:v>
       </x:c>
+      <x:c r="BI14" t="str">
+        <x:v>B</x:v>
+      </x:c>
+      <x:c r="BJ14" t="str">
+        <x:v>Idea Clue 1: compare explicit 3D goal prediction against image-only VLA on dual-arm ordinary-gripper tasks. Evidence: paper motivation and 3D goal image/point-cloud generation. Why relevant: direct test of 3D planning value.</x:v>
+      </x:c>
+      <x:c r="BK14" t="str">
+        <x:v>Not Reported in the accessible proceedings page.</x:v>
+      </x:c>
+      <x:c r="BL14" t="str">
+        <x:v>Not Explicitly Reported in the accessible proceedings page.</x:v>
+      </x:c>
+      <x:c r="BM14" t="str">
+        <x:v>OpenAlex Work: https://openalex.org/W4392886475</x:v>
+      </x:c>
+      <x:c r="BN14" t="str">
+        <x:v>https://proceedings.mlr.press/v235/zhen24a.html；官方摘要/论文集元数据</x:v>
+      </x:c>
     </x:row>
     <x:row r="15" ht="58" customHeight="1">
       <x:c r="A15" t="str">
@@ -20929,6 +22717,24 @@
       </x:c>
       <x:c r="BH15" t="str">
         <x:v>VLA; Efficient Model / Pose Prediction</x:v>
+      </x:c>
+      <x:c r="BI15" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BJ15" t="str">
+        <x:v>Unknown / Needs Evidence</x:v>
+      </x:c>
+      <x:c r="BK15" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="BL15" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="BM15" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BN15" t="str">
+        <x:v>https://proceedings.neurips.cc/paper_files/paper/2024/hash/46a126492ea6fb87410e55a58df2e189-Abstract-Conference.html；官方摘要/论文集元数据</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="58" customHeight="1">
@@ -21108,6 +22914,24 @@
       <x:c r="BH16" t="str">
         <x:v>Robot Manipulation; Consistency Flow Matching / 3D Policy</x:v>
       </x:c>
+      <x:c r="BI16" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BJ16" t="str">
+        <x:v>Unknown / Needs Evidence</x:v>
+      </x:c>
+      <x:c r="BK16" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="BL16" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="BM16" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BN16" t="str">
+        <x:v>https://ojs.aaai.org/index.php/AAAI/article/view/33617；官方摘要/论文集元数据</x:v>
+      </x:c>
     </x:row>
     <x:row r="17" ht="58" customHeight="1">
       <x:c r="A17" t="str">
@@ -21288,6 +23112,24 @@
       <x:c r="BH17" t="str">
         <x:v>Dexterous Hand; Policy Distillation / Generalization</x:v>
       </x:c>
+      <x:c r="BI17" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BJ17" t="str">
+        <x:v>Unknown / Needs Evidence</x:v>
+      </x:c>
+      <x:c r="BK17" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="BL17" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="BM17" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BN17" t="str">
+        <x:v>https://openaccess.thecvf.com/content/CVPR2025/html/Wang_UniGraspTransformer_Simplified_Policy_Distillation_for_Scalable_Dexterous_Robotic_Grasping_CVPR_2025_paper.html；官方摘要/论文集元数据</x:v>
+      </x:c>
     </x:row>
     <x:row r="18" ht="58" customHeight="1">
       <x:c r="A18" t="str">
@@ -21468,6 +23310,24 @@
       <x:c r="BH18" t="str">
         <x:v>Dexterous Hand; Residual RL / VLM Planning</x:v>
       </x:c>
+      <x:c r="BI18" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BJ18" t="str">
+        <x:v>Unknown / Needs Evidence</x:v>
+      </x:c>
+      <x:c r="BK18" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="BL18" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="BM18" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BN18" t="str">
+        <x:v>https://proceedings.neurips.cc/paper_files/paper/2025/hash/862644b156e51c35dea5a7446d640b14-Abstract-Conference.html；官方摘要/论文集元数据</x:v>
+      </x:c>
     </x:row>
     <x:row r="19" ht="58" customHeight="1">
       <x:c r="A19" t="str">
@@ -21648,6 +23508,24 @@
       <x:c r="BH19" t="str">
         <x:v>VLA; Video-Action Model / Generalization</x:v>
       </x:c>
+      <x:c r="BI19" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BJ19" t="str">
+        <x:v>Unknown / Needs Evidence</x:v>
+      </x:c>
+      <x:c r="BK19" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="BL19" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="BM19" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BN19" t="str">
+        <x:v>https://proceedings.neurips.cc/paper_files/paper/2025/hash/89a3b655a8b68ae1c76b768152c9c19d-Abstract-Conference.html；官方摘要/论文集元数据</x:v>
+      </x:c>
     </x:row>
     <x:row r="20" ht="58" customHeight="1">
       <x:c r="A20" t="str">
@@ -21828,6 +23706,24 @@
       <x:c r="BH20" t="str">
         <x:v>Dexterous Hand; Contact Reasoning / Language-guided Grasp</x:v>
       </x:c>
+      <x:c r="BI20" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BJ20" t="str">
+        <x:v>Unknown / Needs Evidence</x:v>
+      </x:c>
+      <x:c r="BK20" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="BL20" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="BM20" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BN20" t="str">
+        <x:v>https://openaccess.thecvf.com/content/CVPR2026/html/Lee_DextER_Language-driven_Dexterous_Grasp_Generation_with_Embodied_Reasoning_CVPR_2026_paper.html；官方摘要/论文集元数据</x:v>
+      </x:c>
     </x:row>
     <x:row r="21" ht="58" customHeight="1">
       <x:c r="A21" t="str">
@@ -22010,6 +23906,24 @@
       <x:c r="BH21" t="str">
         <x:v>Multimodal / Generalization</x:v>
       </x:c>
+      <x:c r="BI21" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="BJ21" t="str">
+        <x:v>Idea Clue 1: adapt affordance-prior reasoning and active impedance correction to ordinary-gripper bimanual contact tasks. Evidence: APR and AIA ablation gains plus explicit hardware failure cases. Why relevant: actionable path for current real-robot manipulation.</x:v>
+      </x:c>
+      <x:c r="BK21" t="str">
+        <x:v>Reported ablations isolate OCI, MLM, APR, COT and AIA; APR is the largest training-task gain in the cited ablation sequence.</x:v>
+      </x:c>
+      <x:c r="BL21" t="str">
+        <x:v>Position predictions are sensitive to lighting and texture domain gaps; suction cannot grasp non-smooth handles and short gripper geometry can cause collisions.</x:v>
+      </x:c>
+      <x:c r="BM21" t="str">
+        <x:v>OpenAlex Work: https://openalex.org/W4402727730</x:v>
+      </x:c>
+      <x:c r="BN21" t="str">
+        <x:v>https://openaccess.thecvf.com/content/CVPR2024/html/Li_ManipLLM_Embodied_Multimodal_Large_Language_Model_for_Object-Centric_Robotic_Manipulation_CVPR_2024_paper.html；官方摘要/论文集元数据</x:v>
+      </x:c>
     </x:row>
     <x:row r="22" ht="58" customHeight="1">
       <x:c r="A22" t="str">
@@ -22192,6 +24106,24 @@
       <x:c r="BH22" t="str">
         <x:v>Residual Learning / Sim-to-Real</x:v>
       </x:c>
+      <x:c r="BI22" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BJ22" t="str">
+        <x:v>Unknown / Needs Evidence</x:v>
+      </x:c>
+      <x:c r="BK22" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="BL22" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="BM22" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BN22" t="str">
+        <x:v>https://openaccess.thecvf.com/content/CVPR2025/html/Li_ManipTrans_Efficient_Dexterous_Bimanual_Manipulation_Transfer_via_Residual_Learning_CVPR_2025_paper.html；官方摘要/论文集元数据</x:v>
+      </x:c>
     </x:row>
     <x:row r="23" ht="58" customHeight="1">
       <x:c r="A23" t="str">
@@ -22374,6 +24306,24 @@
       <x:c r="BH23" t="str">
         <x:v>Diffusion / Contact-rich Manipulation</x:v>
       </x:c>
+      <x:c r="BI23" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BJ23" t="str">
+        <x:v>Unknown / Needs Evidence</x:v>
+      </x:c>
+      <x:c r="BK23" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="BL23" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="BM23" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BN23" t="str">
+        <x:v>https://openaccess.thecvf.com/content/CVPR2025/html/Liang_DexHandDiff_Interaction-aware_Diffusion_Planning_for_Adaptive_Dexterous_Manipulation_CVPR_2025_paper.html；官方摘要/论文集元数据</x:v>
+      </x:c>
     </x:row>
     <x:row r="24" ht="58" customHeight="1">
       <x:c r="A24" t="str">
@@ -22556,6 +24506,24 @@
       <x:c r="BH24" t="str">
         <x:v>Human Video / VLM</x:v>
       </x:c>
+      <x:c r="BI24" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BJ24" t="str">
+        <x:v>Unknown / Needs Evidence</x:v>
+      </x:c>
+      <x:c r="BK24" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="BL24" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="BM24" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BN24" t="str">
+        <x:v>https://openaccess.thecvf.com/content/ICCV2025/html/Yang_AR-VRM_Imitating_Human_Motions_for_Visual_Robot_Manipulation_with_Analogical_ICCV_2025_paper.html；官方摘要/论文集元数据</x:v>
+      </x:c>
     </x:row>
     <x:row r="25" ht="58" customHeight="1">
       <x:c r="A25" t="str">
@@ -22738,6 +24706,24 @@
       <x:c r="BH25" t="str">
         <x:v>Dexterous Grasping</x:v>
       </x:c>
+      <x:c r="BI25" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BJ25" t="str">
+        <x:v>Unknown / Needs Evidence</x:v>
+      </x:c>
+      <x:c r="BK25" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="BL25" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="BM25" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BN25" t="str">
+        <x:v>https://openaccess.thecvf.com/content/CVPR2024/html/Xu_Dexterous_Grasp_Transformer_CVPR_2024_paper.html；官方摘要/论文集元数据</x:v>
+      </x:c>
     </x:row>
     <x:row r="26" ht="58" customHeight="1">
       <x:c r="A26" t="str">
@@ -22920,6 +24906,24 @@
       <x:c r="BH26" t="str">
         <x:v>Mobile Manipulation</x:v>
       </x:c>
+      <x:c r="BI26" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BJ26" t="str">
+        <x:v>Unknown / Needs Evidence</x:v>
+      </x:c>
+      <x:c r="BK26" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="BL26" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="BM26" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BN26" t="str">
+        <x:v>https://openaccess.thecvf.com/content/CVPR2025/html/Wu_MoManipVLA_Transferring_Vision-language-action_Models_for_General_Mobile_Manipulation_CVPR_2025_paper.html；官方摘要/论文集元数据</x:v>
+      </x:c>
     </x:row>
     <x:row r="27" ht="58" customHeight="1">
       <x:c r="A27" t="str">
@@ -23102,6 +25106,24 @@
       <x:c r="BH27" t="str">
         <x:v>Action Chunking / Multi-task Policy</x:v>
       </x:c>
+      <x:c r="BI27" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BJ27" t="str">
+        <x:v>Unknown / Needs Evidence</x:v>
+      </x:c>
+      <x:c r="BK27" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="BL27" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="BM27" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BN27" t="str">
+        <x:v>https://proceedings.neurips.cc/paper_files/paper/2024/hash/ff887781480973bd3cb6026feb378d1e-Abstract-Conference.html；官方摘要/论文集元数据</x:v>
+      </x:c>
     </x:row>
     <x:row r="28" ht="58" customHeight="1">
       <x:c r="A28" t="str">
@@ -23284,6 +25306,24 @@
       <x:c r="BH28" t="str">
         <x:v>Surgical Robotics</x:v>
       </x:c>
+      <x:c r="BI28" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BJ28" t="str">
+        <x:v>Unknown / Needs Evidence</x:v>
+      </x:c>
+      <x:c r="BK28" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="BL28" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="BM28" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BN28" t="str">
+        <x:v>https://proceedings.neurips.cc/paper_files/paper/2024/hash/74c4f2b87b7499d365422152c76fd916-Abstract-Datasets_and_Benchmarks_Track.html；官方摘要/论文集元数据</x:v>
+      </x:c>
     </x:row>
     <x:row r="29" ht="58" customHeight="1">
       <x:c r="A29" t="str">
@@ -23466,6 +25506,24 @@
       <x:c r="BH29" t="str">
         <x:v>Video Demonstration / Reward Learning</x:v>
       </x:c>
+      <x:c r="BI29" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BJ29" t="str">
+        <x:v>Unknown / Needs Evidence</x:v>
+      </x:c>
+      <x:c r="BK29" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="BL29" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="BM29" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BN29" t="str">
+        <x:v>https://proceedings.neurips.cc/paper_files/paper/2024/hash/dcd297696d0bb304ba426b3c5a679c37-Abstract-Conference.html；官方摘要/论文集元数据</x:v>
+      </x:c>
     </x:row>
     <x:row r="30" ht="58" customHeight="1">
       <x:c r="A30" t="str">
@@ -23648,6 +25706,24 @@
       <x:c r="BH30" t="str">
         <x:v>Long-Horizon / Failure Recovery</x:v>
       </x:c>
+      <x:c r="BI30" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BJ30" t="str">
+        <x:v>Unknown / Needs Evidence</x:v>
+      </x:c>
+      <x:c r="BK30" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="BL30" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="BM30" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BN30" t="str">
+        <x:v>https://proceedings.neurips.cc/paper_files/paper/2024/hash/fad8962279154544ed69bb63eb14d677-Abstract-Conference.html；官方摘要/论文集元数据</x:v>
+      </x:c>
     </x:row>
     <x:row r="31" ht="58" customHeight="1">
       <x:c r="A31" t="str">
@@ -23830,6 +25906,24 @@
       <x:c r="BH31" t="str">
         <x:v>3D Observation / Contact-rich</x:v>
       </x:c>
+      <x:c r="BI31" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BJ31" t="str">
+        <x:v>Unknown / Needs Evidence</x:v>
+      </x:c>
+      <x:c r="BK31" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="BL31" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="BM31" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BN31" t="str">
+        <x:v>https://proceedings.neurips.cc/paper_files/paper/2024/hash/8e5dc5969a6174fcaaececd890c7f59b-Abstract-Datasets_and_Benchmarks_Track.html；官方摘要/论文集元数据</x:v>
+      </x:c>
     </x:row>
     <x:row r="32" ht="58" customHeight="1">
       <x:c r="A32" t="str">
@@ -24012,6 +26106,24 @@
       <x:c r="BH32" t="str">
         <x:v>Text-conditioned Reward</x:v>
       </x:c>
+      <x:c r="BI32" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BJ32" t="str">
+        <x:v>Unknown / Needs Evidence</x:v>
+      </x:c>
+      <x:c r="BK32" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="BL32" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="BM32" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BN32" t="str">
+        <x:v>https://proceedings.neurips.cc/paper_files/paper/2024/hash/5227ce00add5aa0a12d1c4ee92fcd2dc-Abstract-Conference.html；官方摘要/论文集元数据</x:v>
+      </x:c>
     </x:row>
     <x:row r="33" ht="58" customHeight="1">
       <x:c r="A33" t="str">
@@ -24194,6 +26306,24 @@
       <x:c r="BH33" t="str">
         <x:v>Human-Robot Domain Adaptation</x:v>
       </x:c>
+      <x:c r="BI33" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BJ33" t="str">
+        <x:v>Unknown / Needs Evidence</x:v>
+      </x:c>
+      <x:c r="BK33" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="BL33" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="BM33" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BN33" t="str">
+        <x:v>https://openaccess.thecvf.com/content/CVPR2025/html/Zhou_Mitigating_the_Human-Robot_Domain_Discrepancy_in_Visual_Pre-training_for_Robotic_CVPR_2025_paper.html；官方摘要/论文集元数据</x:v>
+      </x:c>
     </x:row>
     <x:row r="34" ht="58" customHeight="1">
       <x:c r="A34" t="str">
@@ -24376,6 +26506,24 @@
       <x:c r="BH34" t="str">
         <x:v>Grounding / Synthetic Data</x:v>
       </x:c>
+      <x:c r="BI34" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BJ34" t="str">
+        <x:v>Unknown / Needs Evidence</x:v>
+      </x:c>
+      <x:c r="BK34" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="BL34" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="BM34" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BN34" t="str">
+        <x:v>https://openaccess.thecvf.com/content/CVPR2025/html/Huang_RoboGround_Robotic_Manipulation_with_Grounded_Vision-Language_Priors_CVPR_2025_paper.html；官方摘要/论文集元数据</x:v>
+      </x:c>
     </x:row>
     <x:row r="35" ht="58" customHeight="1">
       <x:c r="A35" t="str">
@@ -24558,6 +26706,24 @@
       <x:c r="BH35" t="str">
         <x:v>Synthetic Data / Scene Generation</x:v>
       </x:c>
+      <x:c r="BI35" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BJ35" t="str">
+        <x:v>Unknown / Needs Evidence</x:v>
+      </x:c>
+      <x:c r="BK35" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="BL35" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="BM35" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BN35" t="str">
+        <x:v>https://openaccess.thecvf.com/content/CVPR2025/html/Lee_DynScene_Scalable_Generation_of_Dynamic_Robotic_Manipulation_Scenes_for_Embodied_CVPR_2025_paper.html；官方摘要/论文集元数据</x:v>
+      </x:c>
     </x:row>
     <x:row r="36" ht="58" customHeight="1">
       <x:c r="A36" t="str">
@@ -24740,6 +26906,24 @@
       <x:c r="BH36" t="str">
         <x:v>Lifelong Learning</x:v>
       </x:c>
+      <x:c r="BI36" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BJ36" t="str">
+        <x:v>Unknown / Needs Evidence</x:v>
+      </x:c>
+      <x:c r="BK36" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="BL36" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="BM36" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BN36" t="str">
+        <x:v>https://openaccess.thecvf.com/content/CVPR2025/html/Yao_Think_Small_Act_Big_Primitive_Prompt_Learning_for_Lifelong_Robot_CVPR_2025_paper.html；官方摘要/论文集元数据</x:v>
+      </x:c>
     </x:row>
     <x:row r="37" ht="58" customHeight="1">
       <x:c r="A37" t="str">
@@ -24922,6 +27106,24 @@
       <x:c r="BH37" t="str">
         <x:v>Failure Recovery / 3D Gaussian Splatting</x:v>
       </x:c>
+      <x:c r="BI37" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BJ37" t="str">
+        <x:v>Unknown / Needs Evidence</x:v>
+      </x:c>
+      <x:c r="BK37" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="BL37" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="BM37" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BN37" t="str">
+        <x:v>https://ojs.aaai.org/index.php/AAAI/article/view/34866；官方摘要/论文集元数据</x:v>
+      </x:c>
     </x:row>
     <x:row r="38" ht="58" customHeight="1">
       <x:c r="A38" t="str">
@@ -25104,6 +27306,24 @@
       <x:c r="BH38" t="str">
         <x:v>Articulated Object / Affordance</x:v>
       </x:c>
+      <x:c r="BI38" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BJ38" t="str">
+        <x:v>Unknown / Needs Evidence</x:v>
+      </x:c>
+      <x:c r="BK38" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="BL38" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="BM38" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BN38" t="str">
+        <x:v>https://ojs.aaai.org/index.php/AAAI/article/view/33615；官方摘要/论文集元数据</x:v>
+      </x:c>
     </x:row>
     <x:row r="39" ht="58" customHeight="1">
       <x:c r="A39" t="str">
@@ -25286,6 +27506,24 @@
       <x:c r="BH39" t="str">
         <x:v>Long-Horizon / Mobile Manipulation</x:v>
       </x:c>
+      <x:c r="BI39" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BJ39" t="str">
+        <x:v>Unknown / Needs Evidence</x:v>
+      </x:c>
+      <x:c r="BK39" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="BL39" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="BM39" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BN39" t="str">
+        <x:v>https://ojs.aaai.org/index.php/AAAI/article/view/33610；官方摘要/论文集元数据</x:v>
+      </x:c>
     </x:row>
     <x:row r="40" ht="58" customHeight="1">
       <x:c r="A40" t="str">
@@ -25468,6 +27706,24 @@
       <x:c r="BH40" t="str">
         <x:v>World Model / Video Diffusion</x:v>
       </x:c>
+      <x:c r="BI40" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BJ40" t="str">
+        <x:v>Unknown / Needs Evidence</x:v>
+      </x:c>
+      <x:c r="BK40" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="BL40" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="BM40" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BN40" t="str">
+        <x:v>https://proceedings.neurips.cc/paper_files/paper/2024/hash/481c70828a4ff20d31a646cc6cc95f3d-Abstract-Conference.html；官方摘要/论文集元数据</x:v>
+      </x:c>
     </x:row>
     <x:row r="41" ht="58" customHeight="1">
       <x:c r="A41" t="str">
@@ -25650,6 +27906,24 @@
       <x:c r="BH41" t="str">
         <x:v>Human Video / 3D Affordance</x:v>
       </x:c>
+      <x:c r="BI41" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BJ41" t="str">
+        <x:v>Unknown / Needs Evidence</x:v>
+      </x:c>
+      <x:c r="BK41" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="BL41" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="BM41" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BN41" t="str">
+        <x:v>https://openaccess.thecvf.com/content/CVPR2025/html/Chen_VidBot_Learning_Generalizable_3D_Actions_from_In-the-Wild_2D_Human_Videos_CVPR_2025_paper.html；官方摘要/论文集元数据</x:v>
+      </x:c>
     </x:row>
     <x:row r="42" ht="58" customHeight="1">
       <x:c r="A42" t="str">
@@ -25832,6 +28106,24 @@
       <x:c r="BH42" t="str">
         <x:v>Visual Chain-of-Thought</x:v>
       </x:c>
+      <x:c r="BI42" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BJ42" t="str">
+        <x:v>Unknown / Needs Evidence</x:v>
+      </x:c>
+      <x:c r="BK42" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="BL42" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="BM42" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BN42" t="str">
+        <x:v>https://openaccess.thecvf.com/content/CVPR2025/html/Zhao_CoT-VLA_Visual_Chain-of-Thought_Reasoning_for_Vision-Language-Action_Models_CVPR_2025_paper.html；官方摘要/论文集元数据</x:v>
+      </x:c>
     </x:row>
     <x:row r="43" ht="58" customHeight="1">
       <x:c r="A43" t="str">
@@ -26014,6 +28306,24 @@
       <x:c r="BH43" t="str">
         <x:v>Sim-to-Real / Behavior Cloning</x:v>
       </x:c>
+      <x:c r="BI43" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BJ43" t="str">
+        <x:v>Unknown / Needs Evidence</x:v>
+      </x:c>
+      <x:c r="BK43" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="BL43" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="BM43" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BN43" t="str">
+        <x:v>https://proceedings.neurips.cc/paper_files/paper/2025/hash/1185c89347a3f21ffc48c9d083c9437c-Abstract-Conference.html；官方摘要/论文集元数据</x:v>
+      </x:c>
     </x:row>
     <x:row r="44" ht="58" customHeight="1">
       <x:c r="A44" t="str">
@@ -26196,6 +28506,24 @@
       <x:c r="BH44" t="str">
         <x:v>Long-Horizon / Planning</x:v>
       </x:c>
+      <x:c r="BI44" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BJ44" t="str">
+        <x:v>Unknown / Needs Evidence</x:v>
+      </x:c>
+      <x:c r="BK44" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="BL44" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="BM44" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BN44" t="str">
+        <x:v>https://proceedings.neurips.cc/paper_files/paper/2025/hash/b94310e1c7ecb79f1a24adc757f1b89b-Abstract-Conference.html；官方摘要/论文集元数据</x:v>
+      </x:c>
     </x:row>
     <x:row r="45" ht="58" customHeight="1">
       <x:c r="A45" t="str">
@@ -26378,6 +28706,24 @@
       <x:c r="BH45" t="str">
         <x:v>Stochastic Interpolant / Efficiency</x:v>
       </x:c>
+      <x:c r="BI45" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BJ45" t="str">
+        <x:v>Unknown / Needs Evidence</x:v>
+      </x:c>
+      <x:c r="BK45" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="BL45" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="BM45" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BN45" t="str">
+        <x:v>https://proceedings.neurips.cc/paper_files/paper/2025/hash/49eadcc4a329fc6b74b9f8a82b78cbc3-Abstract-Conference.html；官方摘要/论文集元数据</x:v>
+      </x:c>
     </x:row>
     <x:row r="46" ht="58" customHeight="1">
       <x:c r="A46" t="str">
@@ -26560,6 +28906,24 @@
       <x:c r="BH46" t="str">
         <x:v>Mobile Manipulation / Agent</x:v>
       </x:c>
+      <x:c r="BI46" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BJ46" t="str">
+        <x:v>Unknown / Needs Evidence</x:v>
+      </x:c>
+      <x:c r="BK46" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="BL46" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="BM46" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BN46" t="str">
+        <x:v>https://proceedings.neurips.cc/paper_files/paper/2025/hash/bc97207e3979d1cc23109db0be0e8ed2-Abstract-Conference.html；官方摘要/论文集元数据</x:v>
+      </x:c>
     </x:row>
     <x:row r="47" ht="58" customHeight="1">
       <x:c r="A47" t="str">
@@ -26742,6 +29106,24 @@
       <x:c r="BH47" t="str">
         <x:v>Flow Matching / Visuomotor Policy</x:v>
       </x:c>
+      <x:c r="BI47" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BJ47" t="str">
+        <x:v>Unknown / Needs Evidence</x:v>
+      </x:c>
+      <x:c r="BK47" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="BL47" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="BM47" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BN47" t="str">
+        <x:v>https://proceedings.neurips.cc/paper_files/paper/2025/hash/282c3318be1b047b7bb5ba94fa4f3231-Abstract-Conference.html；官方摘要/论文集元数据</x:v>
+      </x:c>
     </x:row>
     <x:row r="48" ht="58" customHeight="1">
       <x:c r="A48" t="str">
@@ -26924,6 +29306,24 @@
       <x:c r="BH48" t="str">
         <x:v>Tool Use / Generative Design</x:v>
       </x:c>
+      <x:c r="BI48" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BJ48" t="str">
+        <x:v>Unknown / Needs Evidence</x:v>
+      </x:c>
+      <x:c r="BK48" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="BL48" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="BM48" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BN48" t="str">
+        <x:v>https://proceedings.neurips.cc/paper_files/paper/2025/hash/9fc291fef2f9607a46777d367f900a15-Abstract-Conference.html；官方摘要/论文集元数据</x:v>
+      </x:c>
     </x:row>
     <x:row r="49" ht="58" customHeight="1">
       <x:c r="A49" t="str">
@@ -27106,6 +29506,24 @@
       <x:c r="BH49" t="str">
         <x:v>3D Manipulation / Multimodal Policy</x:v>
       </x:c>
+      <x:c r="BI49" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BJ49" t="str">
+        <x:v>Unknown / Needs Evidence</x:v>
+      </x:c>
+      <x:c r="BK49" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="BL49" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="BM49" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BN49" t="str">
+        <x:v>https://proceedings.neurips.cc/paper_files/paper/2025/hash/eacc8ae341d15d2c13c02fef88189db3-Abstract-Conference.html；官方摘要/论文集元数据</x:v>
+      </x:c>
     </x:row>
     <x:row r="50" ht="58" customHeight="1">
       <x:c r="A50" t="str">
@@ -27288,6 +29706,24 @@
       <x:c r="BH50" t="str">
         <x:v>Robot Data / Spatial Reasoning</x:v>
       </x:c>
+      <x:c r="BI50" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BJ50" t="str">
+        <x:v>Unknown / Needs Evidence</x:v>
+      </x:c>
+      <x:c r="BK50" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="BL50" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="BM50" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BN50" t="str">
+        <x:v>https://proceedings.neurips.cc/paper_files/paper/2025/hash/1f467c3e37abf9f86c78f44c6a27ee7c-Abstract-Datasets_and_Benchmarks_Track.html；官方摘要/论文集元数据</x:v>
+      </x:c>
     </x:row>
     <x:row r="51" ht="58" customHeight="1">
       <x:c r="A51" t="str">
@@ -27470,6 +29906,24 @@
       <x:c r="BH51" t="str">
         <x:v>Task Planning / Demonstrations</x:v>
       </x:c>
+      <x:c r="BI51" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BJ51" t="str">
+        <x:v>Unknown / Needs Evidence</x:v>
+      </x:c>
+      <x:c r="BK51" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="BL51" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="BM51" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BN51" t="str">
+        <x:v>https://proceedings.neurips.cc/paper_files/paper/2025/hash/b8358a00e5b870194b974ddf8dd415c3-Abstract-Conference.html；官方摘要/论文集元数据</x:v>
+      </x:c>
     </x:row>
     <x:row r="52" ht="58" customHeight="1">
       <x:c r="A52" t="str">
@@ -27652,6 +30106,24 @@
       <x:c r="BH52" t="str">
         <x:v>Unknown</x:v>
       </x:c>
+      <x:c r="BI52" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BJ52" t="str">
+        <x:v>Unknown / Needs Evidence</x:v>
+      </x:c>
+      <x:c r="BK52" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="BL52" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="BM52" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BN52" t="str">
+        <x:v>https://openaccess.thecvf.com/content/ICCV2025/html/Wang_DexH2R_A_Benchmark_for_Dynamic_Dexterous_Grasping_in_Human-to-Robot_Handover_ICCV_2025_paper.html；官方摘要/论文集元数据</x:v>
+      </x:c>
     </x:row>
     <x:row r="53" ht="58" customHeight="1">
       <x:c r="A53" t="str">
@@ -27834,6 +30306,24 @@
       <x:c r="BH53" t="str">
         <x:v>Unknown</x:v>
       </x:c>
+      <x:c r="BI53" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BJ53" t="str">
+        <x:v>Unknown / Needs Evidence</x:v>
+      </x:c>
+      <x:c r="BK53" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="BL53" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="BM53" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BN53" t="str">
+        <x:v>https://openaccess.thecvf.com/content/CVPR2025/html/Zhang_BimArt_A_Unified_Approach_for_the_Synthesis_of_3D_Bimanual_CVPR_2025_paper.html；官方摘要/论文集元数据</x:v>
+      </x:c>
     </x:row>
     <x:row r="54" ht="58" customHeight="1">
       <x:c r="A54" t="str">
@@ -28016,6 +30506,24 @@
       <x:c r="BH54" t="str">
         <x:v>Unknown</x:v>
       </x:c>
+      <x:c r="BI54" t="str">
+        <x:v>B</x:v>
+      </x:c>
+      <x:c r="BJ54" t="str">
+        <x:v>Idea Clue 1: use part-level language affordances as a perception front-end for bimanual grasp sequencing. Evidence: part-touch/part-grasp metrics and flow pose head. Why relevant: supports target-region and action alignment.</x:v>
+      </x:c>
+      <x:c r="BK54" t="str">
+        <x:v>The paper compares language-enabled DGN2.0* + CLIP against the full VLM/flow model; exact component ablations require supplementary extraction.</x:v>
+      </x:c>
+      <x:c r="BL54" t="str">
+        <x:v>The reported setting focuses on tabletop part-aligned grasps; broader clutter, occlusion and multi-step manipulation are not established by the cited results.</x:v>
+      </x:c>
+      <x:c r="BM54" t="str">
+        <x:v>OpenAlex Work: https://openalex.org/W4417183400</x:v>
+      </x:c>
+      <x:c r="BN54" t="str">
+        <x:v>https://openaccess.thecvf.com/content/ICCV2025/html/He_DexVLG_Dexterous_Vision-Language-Grasp_Model_at_Scale_ICCV_2025_paper.html；官方摘要/论文集元数据</x:v>
+      </x:c>
     </x:row>
     <x:row r="55" ht="58" customHeight="1">
       <x:c r="A55" t="str">
@@ -28198,6 +30706,24 @@
       <x:c r="BH55" t="str">
         <x:v>Unknown</x:v>
       </x:c>
+      <x:c r="BI55" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BJ55" t="str">
+        <x:v>Unknown / Needs Evidence</x:v>
+      </x:c>
+      <x:c r="BK55" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="BL55" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="BM55" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BN55" t="str">
+        <x:v>https://openaccess.thecvf.com/content/CVPR2025/html/Li_LatentHOI_On_the_Generalizable_Hand_Object_Motion_Generation_with_Latent_CVPR_2025_paper.html；官方摘要/论文集元数据</x:v>
+      </x:c>
     </x:row>
     <x:row r="56" ht="58" customHeight="1">
       <x:c r="A56" t="str">
@@ -28380,6 +30906,24 @@
       <x:c r="BH56" t="str">
         <x:v>Unknown</x:v>
       </x:c>
+      <x:c r="BI56" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BJ56" t="str">
+        <x:v>Unknown / Needs Evidence</x:v>
+      </x:c>
+      <x:c r="BK56" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="BL56" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="BM56" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BN56" t="str">
+        <x:v>https://openaccess.thecvf.com/content/CVPR2024/papers/Liu_TACO_Benchmarking_Generalizable_Bimanual_Tool-ACtion-Object_Understanding_CVPR_2024_paper.pdf；官方摘要/论文集元数据</x:v>
+      </x:c>
     </x:row>
     <x:row r="57" ht="58" customHeight="1">
       <x:c r="A57" t="str">
@@ -28562,6 +31106,24 @@
       <x:c r="BH57" t="str">
         <x:v>Unknown</x:v>
       </x:c>
+      <x:c r="BI57" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BJ57" t="str">
+        <x:v>Unknown / Needs Evidence</x:v>
+      </x:c>
+      <x:c r="BK57" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="BL57" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="BM57" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BN57" t="str">
+        <x:v>https://openaccess.thecvf.com/content/CVPR2024/html/Uppal_SPIN_Simultaneous_Perception_Interaction_and_Navigation_CVPR_2024_paper.html；官方摘要/论文集元数据</x:v>
+      </x:c>
     </x:row>
     <x:row r="58" ht="58" customHeight="1">
       <x:c r="A58" t="str">
@@ -28744,6 +31306,24 @@
       <x:c r="BH58" t="str">
         <x:v>Unknown</x:v>
       </x:c>
+      <x:c r="BI58" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="BJ58" t="str">
+        <x:v>Idea Clue 1: use AnyBimanual as a baseline for ordinary-gripper dual-arm transfer with controlled demonstration budgets. Evidence: 12 RLBench2 + 9 real tasks and limited bimanual demonstrations. Why relevant: directly matches current bimanual project.</x:v>
+      </x:c>
+      <x:c r="BK58" t="str">
+        <x:v>The accessible arXiv text describes the separate skill-manager and visual-aligner contributions; full ablation numbers were not re-extracted in this batch.</x:v>
+      </x:c>
+      <x:c r="BL58" t="str">
+        <x:v>The paper identifies observation discrepancy between unimanual and bimanual systems as a transfer risk; detailed failure cases require appendix extraction.</x:v>
+      </x:c>
+      <x:c r="BM58" t="str">
+        <x:v>OpenAlex Work: https://openalex.org/W4405254485</x:v>
+      </x:c>
+      <x:c r="BN58" t="str">
+        <x:v>https://openaccess.thecvf.com/content/ICCV2025/html/Lu_AnyBimanual_Transferring_Unimanual_Policy_for_General_Bimanual_Manipulation_ICCV_2025_paper.html；官方摘要/论文集元数据</x:v>
+      </x:c>
     </x:row>
     <x:row r="59" ht="58" customHeight="1">
       <x:c r="A59" t="str">
@@ -28926,6 +31506,24 @@
       <x:c r="BH59" t="str">
         <x:v>Unknown</x:v>
       </x:c>
+      <x:c r="BI59" t="str">
+        <x:v>B</x:v>
+      </x:c>
+      <x:c r="BJ59" t="str">
+        <x:v>Idea Clue 1: borrow FAAS-style functional action grouping for dual-arm gripper role transfer. Evidence: unified cross-hand action coordinates. Why relevant: possible bridge from dexterous data to ordinary-gripper control.</x:v>
+      </x:c>
+      <x:c r="BK59" t="str">
+        <x:v>Not Reported in the accessible official abstract evidence.</x:v>
+      </x:c>
+      <x:c r="BL59" t="str">
+        <x:v>Cross-hand and retargeting edge cases are not detailed in the accessible abstract; full supplementary review is needed.</x:v>
+      </x:c>
+      <x:c r="BM59" t="str">
+        <x:v>OpenAlex Work: Unknown</x:v>
+      </x:c>
+      <x:c r="BN59" t="str">
+        <x:v>https://openaccess.thecvf.com/content/CVPR2026/html/Zhang_UniDex_A_Robot_Foundation_Suite_for_Universal_Dexterous_Hand_Control_CVPR_2026_paper.html；官方摘要/论文集元数据</x:v>
+      </x:c>
     </x:row>
     <x:row r="60" ht="58" customHeight="1">
       <x:c r="A60" t="str">
@@ -29108,6 +31706,24 @@
       <x:c r="BH60" t="str">
         <x:v>Unknown</x:v>
       </x:c>
+      <x:c r="BI60" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BJ60" t="str">
+        <x:v>Unknown / Needs Evidence</x:v>
+      </x:c>
+      <x:c r="BK60" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="BL60" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="BM60" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BN60" t="str">
+        <x:v>https://openaccess.thecvf.com/content/CVPR2025/html/Zhao_TASTE-Rob_Advancing_Video_Generation_of_Task-Oriented_Hand-Object_Interaction_for_Generalizable_CVPR_2025_paper.html；官方摘要/论文集元数据</x:v>
+      </x:c>
     </x:row>
     <x:row r="61" ht="58" customHeight="1">
       <x:c r="A61" t="str">
@@ -29290,6 +31906,24 @@
       <x:c r="BH61" t="str">
         <x:v>Unknown</x:v>
       </x:c>
+      <x:c r="BI61" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BJ61" t="str">
+        <x:v>Unknown / Needs Evidence</x:v>
+      </x:c>
+      <x:c r="BK61" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="BL61" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="BM61" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BN61" t="str">
+        <x:v>https://ojs.aaai.org/index.php/AAAI/article/view/38874；官方摘要/论文集元数据</x:v>
+      </x:c>
     </x:row>
     <x:row r="62" ht="58" customHeight="1">
       <x:c r="A62" t="str">
@@ -29472,6 +32106,24 @@
       <x:c r="BH62" t="str">
         <x:v>Unknown</x:v>
       </x:c>
+      <x:c r="BI62" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BJ62" t="str">
+        <x:v>Unknown / Needs Evidence</x:v>
+      </x:c>
+      <x:c r="BK62" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="BL62" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="BM62" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BN62" t="str">
+        <x:v>https://proceedings.neurips.cc/paper_files/paper/2025/hash/e4ef7454447baa15a424314e6284441b-Abstract-Conference.html；官方摘要/论文集元数据</x:v>
+      </x:c>
     </x:row>
     <x:row r="63" ht="58" customHeight="1">
       <x:c r="A63" t="str">
@@ -29654,6 +32306,24 @@
       <x:c r="BH63" t="str">
         <x:v>Unknown</x:v>
       </x:c>
+      <x:c r="BI63" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BJ63" t="str">
+        <x:v>Unknown / Needs Evidence</x:v>
+      </x:c>
+      <x:c r="BK63" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="BL63" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="BM63" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BN63" t="str">
+        <x:v>https://ojs.aaai.org/index.php/AAAI/article/view/38313；官方摘要/论文集元数据</x:v>
+      </x:c>
     </x:row>
     <x:row r="64" ht="58" customHeight="1">
       <x:c r="A64" t="str">
@@ -29836,6 +32506,24 @@
       <x:c r="BH64" t="str">
         <x:v>Unknown</x:v>
       </x:c>
+      <x:c r="BI64" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BJ64" t="str">
+        <x:v>Unknown / Needs Evidence</x:v>
+      </x:c>
+      <x:c r="BK64" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="BL64" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="BM64" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BN64" t="str">
+        <x:v>https://ojs.aaai.org/index.php/AAAI/article/view/40127；官方摘要/论文集元数据</x:v>
+      </x:c>
     </x:row>
     <x:row r="65" ht="58" customHeight="1">
       <x:c r="A65" t="str">
@@ -30018,6 +32706,24 @@
       <x:c r="BH65" t="str">
         <x:v>Unknown</x:v>
       </x:c>
+      <x:c r="BI65" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BJ65" t="str">
+        <x:v>Unknown / Needs Evidence</x:v>
+      </x:c>
+      <x:c r="BK65" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="BL65" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="BM65" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BN65" t="str">
+        <x:v>https://ojs.aaai.org/index.php/AAAI/article/view/28266；官方摘要/论文集元数据</x:v>
+      </x:c>
     </x:row>
     <x:row r="66" ht="58" customHeight="1">
       <x:c r="A66" t="str">
@@ -30200,6 +32906,24 @@
       <x:c r="BH66" t="str">
         <x:v>Unknown</x:v>
       </x:c>
+      <x:c r="BI66" t="str">
+        <x:v>B</x:v>
+      </x:c>
+      <x:c r="BJ66" t="str">
+        <x:v>Idea Clue 1: evaluate predicted left/right/both affordances as a front-end for dual-arm task planning. Evidence: explicit hand-taxonomy decoder. Why relevant: actionable perception before VLA action generation.</x:v>
+      </x:c>
+      <x:c r="BK66" t="str">
+        <x:v>VLM-based versus CLIP-based affordance predictor is reported; exact ablation numbers require table extraction.</x:v>
+      </x:c>
+      <x:c r="BL66" t="str">
+        <x:v>The paper notes ambiguity/multi-modality of valid interaction regions; exact failure examples require figure-level review.</x:v>
+      </x:c>
+      <x:c r="BM66" t="str">
+        <x:v>OpenAlex Work: Unknown</x:v>
+      </x:c>
+      <x:c r="BN66" t="str">
+        <x:v>https://openaccess.thecvf.com/content/ICCV2025/html/Heidinger_2HandedAfforder_Learning_Precise_Actionable_Bimanual_Affordances_from_Human_Videos_ICCV_2025_paper.html；官方摘要/论文集元数据</x:v>
+      </x:c>
     </x:row>
     <x:row r="67">
       <x:c r="A67" t="str">
@@ -30381,6 +33105,24 @@
       </x:c>
       <x:c r="BH67" t="str">
         <x:v>VLA; Robot Manipulation; Visual Grounding; Robot Perception; Implicit Grounding; Gaze-Region Reconstruction; Generalization; Diffusion Transformer</x:v>
+      </x:c>
+      <x:c r="BI67" t="str">
+        <x:v>B</x:v>
+      </x:c>
+      <x:c r="BJ67" t="str">
+        <x:v>Idea Clue 1: test implicit ga</x:v>
+      </x:c>
+      <x:c r="BK67" t="str">
+        <x:v>Not Reported in the official abstract/project evidence rechecked for this batch.</x:v>
+      </x:c>
+      <x:c r="BL67" t="str">
+        <x:v>Not Explicitly Reported in the accessible official abstract/project evidence.</x:v>
+      </x:c>
+      <x:c r="BM67" t="str">
+        <x:v>OpenAlex Work: https://openalex.org/W7137985120</x:v>
+      </x:c>
+      <x:c r="BN67" t="str">
+        <x:v>https://ojs.aaai.org/index.php/AAAI/article/view/38921；https://arxiv.org/abs/2508.10333；https://zionchow.github.io/ReconVLA/；https://github.com/OpenHelix-Team/ReconVLA</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -30418,7 +33160,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re18b2744b4b14791"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc302613323ef40fd"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -30614,6 +33356,24 @@
       <x:c r="AW1" t="str">
         <x:v>Remaining Unsolved Problem</x:v>
       </x:c>
+      <x:c r="AX1" t="str">
+        <x:v>Evidence Quality</x:v>
+      </x:c>
+      <x:c r="AY1" t="str">
+        <x:v>Idea Clues</x:v>
+      </x:c>
+      <x:c r="AZ1" t="str">
+        <x:v>Ablation Study</x:v>
+      </x:c>
+      <x:c r="BA1" t="str">
+        <x:v>Failure Cases</x:v>
+      </x:c>
+      <x:c r="BB1" t="str">
+        <x:v>Citation Source Identifier</x:v>
+      </x:c>
+      <x:c r="BC1" t="str">
+        <x:v>Evidence Sources</x:v>
+      </x:c>
     </x:row>
     <x:row r="2" ht="62" customHeight="1">
       <x:c r="A2" t="str">
@@ -30763,6 +33523,24 @@
       <x:c r="AW2" t="str">
         <x:v>Library Analysis / Research Note: Unknown / Needs Full-Paper Verification</x:v>
       </x:c>
+      <x:c r="AX2" t="str">
+        <x:v>B</x:v>
+      </x:c>
+      <x:c r="AY2" t="str">
+        <x:v>Idea Clue 1: use affordance-conditioned dual-arm skill transfer as a controlled baseline for real gripper experiments. Evidence: official six-task and domain-gap evaluation. Why relevant: directly matches bimanual + sim2real direction.</x:v>
+      </x:c>
+      <x:c r="AZ2" t="str">
+        <x:v>Not Reported in the sources rechecked for this batch.</x:v>
+      </x:c>
+      <x:c r="BA2" t="str">
+        <x:v>Domain-gap evaluation explicitly tests background, object, table and combined shifts; exact failure cases require full-paper appendix extraction.</x:v>
+      </x:c>
+      <x:c r="BB2" t="str">
+        <x:v>OpenAlex Work: https://openalex.org/W? title match was not high-confidence for this title; Citation Count remains Unknown.</x:v>
+      </x:c>
+      <x:c r="BC2" t="str">
+        <x:v>Official ICLR Downloads/Proceedings; accepted OpenReview PDF; official project page; official EmbodiChain repository; author publication list; current official CCF directory</x:v>
+      </x:c>
     </x:row>
     <x:row r="3" ht="62" customHeight="1">
       <x:c r="A3" t="str">
@@ -30912,6 +33690,24 @@
       <x:c r="AW3" t="str">
         <x:v>Library Analysis / Research Note: Unknown / Needs Full-Paper Verification</x:v>
       </x:c>
+      <x:c r="AX3" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AY3" t="str">
+        <x:v>Unknown / Needs Evidence</x:v>
+      </x:c>
+      <x:c r="AZ3" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="BA3" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="BB3" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BC3" t="str">
+        <x:v>RSS official proceedings abstract</x:v>
+      </x:c>
     </x:row>
     <x:row r="4" ht="62" customHeight="1">
       <x:c r="A4" t="str">
@@ -31061,6 +33857,24 @@
       <x:c r="AW4" t="str">
         <x:v>Library Analysis / Research Note: Unknown / Needs Full-Paper Verification</x:v>
       </x:c>
+      <x:c r="AX4" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AY4" t="str">
+        <x:v>Unknown / Needs Evidence</x:v>
+      </x:c>
+      <x:c r="AZ4" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="BA4" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="BB4" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BC4" t="str">
+        <x:v>RSS official proceedings abstract</x:v>
+      </x:c>
     </x:row>
     <x:row r="5" ht="62" customHeight="1">
       <x:c r="A5" t="str">
@@ -31210,6 +34024,24 @@
       <x:c r="AW5" t="str">
         <x:v>Library Analysis / Research Note: Unknown / Needs Full-Paper Verification</x:v>
       </x:c>
+      <x:c r="AX5" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AY5" t="str">
+        <x:v>Unknown / Needs Evidence</x:v>
+      </x:c>
+      <x:c r="AZ5" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="BA5" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="BB5" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BC5" t="str">
+        <x:v>RSS official proceedings</x:v>
+      </x:c>
     </x:row>
     <x:row r="6" ht="62" customHeight="1">
       <x:c r="A6" t="str">
@@ -31359,6 +34191,24 @@
       <x:c r="AW6" t="str">
         <x:v>Library Analysis / Research Note: Unknown / Needs Full-Paper Verification</x:v>
       </x:c>
+      <x:c r="AX6" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AY6" t="str">
+        <x:v>Unknown / Needs Evidence</x:v>
+      </x:c>
+      <x:c r="AZ6" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="BA6" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="BB6" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BC6" t="str">
+        <x:v>RSS official proceedings abstract</x:v>
+      </x:c>
     </x:row>
     <x:row r="7" ht="62" customHeight="1">
       <x:c r="A7" t="str">
@@ -31508,6 +34358,24 @@
       <x:c r="AW7" t="str">
         <x:v>Library Analysis / Research Note: Unknown / Needs Full-Paper Verification</x:v>
       </x:c>
+      <x:c r="AX7" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AY7" t="str">
+        <x:v>Unknown / Needs Evidence</x:v>
+      </x:c>
+      <x:c r="AZ7" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="BA7" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="BB7" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BC7" t="str">
+        <x:v>IEEE Xplore abstract; official project page</x:v>
+      </x:c>
     </x:row>
     <x:row r="8" ht="62" customHeight="1">
       <x:c r="A8" t="str">
@@ -31657,6 +34525,24 @@
       <x:c r="AW8" t="str">
         <x:v>Library Analysis / Research Note: Unknown / Needs Full-Paper Verification</x:v>
       </x:c>
+      <x:c r="AX8" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AY8" t="str">
+        <x:v>Unknown / Needs Evidence</x:v>
+      </x:c>
+      <x:c r="AZ8" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="BA8" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="BB8" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BC8" t="str">
+        <x:v>IEEE Xplore abstract</x:v>
+      </x:c>
     </x:row>
     <x:row r="9" ht="62" customHeight="1">
       <x:c r="A9" t="str">
@@ -31806,6 +34692,24 @@
       <x:c r="AW9" t="str">
         <x:v>Library Analysis / Research Note: Unknown / Needs Full-Paper Verification</x:v>
       </x:c>
+      <x:c r="AX9" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AY9" t="str">
+        <x:v>Unknown / Needs Evidence</x:v>
+      </x:c>
+      <x:c r="AZ9" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="BA9" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="BB9" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BC9" t="str">
+        <x:v>IEEE Xplore abstract</x:v>
+      </x:c>
     </x:row>
     <x:row r="10" ht="62" customHeight="1">
       <x:c r="A10" t="str">
@@ -31954,6 +34858,24 @@
       </x:c>
       <x:c r="AW10" t="str">
         <x:v>Library Analysis / Research Note: Unknown / Needs Full-Paper Verification</x:v>
+      </x:c>
+      <x:c r="AX10" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AY10" t="str">
+        <x:v>Unknown / Needs Evidence</x:v>
+      </x:c>
+      <x:c r="AZ10" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="BA10" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="BB10" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BC10" t="str">
+        <x:v>IEEE Xplore abstract</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="62" customHeight="1">
@@ -32082,6 +35004,24 @@
       <x:c r="AW11" t="str">
         <x:v>Library Analysis / Research Note: Unknown / Needs Full-Paper Verification</x:v>
       </x:c>
+      <x:c r="AX11" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AY11" t="str">
+        <x:v>Unknown / Needs Evidence</x:v>
+      </x:c>
+      <x:c r="AZ11" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="BA11" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="BB11" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BC11" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="12" ht="62" customHeight="1">
       <x:c r="A12" t="str">
@@ -32205,6 +35145,24 @@
       <x:c r="AW12" t="str">
         <x:v>Library Analysis / Research Note: Unknown / Needs Full-Paper Verification</x:v>
       </x:c>
+      <x:c r="AX12" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AY12" t="str">
+        <x:v>Unknown / Needs Evidence</x:v>
+      </x:c>
+      <x:c r="AZ12" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="BA12" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="BB12" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BC12" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="13" ht="62" customHeight="1">
       <x:c r="A13" t="str">
@@ -32328,6 +35286,24 @@
       <x:c r="AW13" t="str">
         <x:v>Library Analysis / Research Note: Unknown / Needs Full-Paper Verification</x:v>
       </x:c>
+      <x:c r="AX13" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AY13" t="str">
+        <x:v>Unknown / Needs Evidence</x:v>
+      </x:c>
+      <x:c r="AZ13" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="BA13" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="BB13" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BC13" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="14" ht="62" customHeight="1">
       <x:c r="A14" t="str">
@@ -32450,6 +35426,24 @@
       </x:c>
       <x:c r="AW14" t="str">
         <x:v>Library Analysis / Research Note: Unknown / Needs Full-Paper Verification</x:v>
+      </x:c>
+      <x:c r="AX14" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AY14" t="str">
+        <x:v>Unknown / Needs Evidence</x:v>
+      </x:c>
+      <x:c r="AZ14" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="BA14" t="str">
+        <x:v>Unknown / Not Explicitly Reported</x:v>
+      </x:c>
+      <x:c r="BB14" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BC14" t="str">
+        <x:v>Unknown</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -32469,7 +35463,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re7fe16fb3c4f419a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8743da78aa834f11"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/00_Paper_Pool/Paper_Pool.xlsx
+++ b/00_Paper_Pool/Paper_Pool.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Papers" sheetId="1" r:id="Rb78e0de66ebe4bc3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rejected" sheetId="2" r:id="R0fa1462e67ef4140"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Venues" sheetId="3" r:id="R807b83bc92554f01"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Keywords" sheetId="4" r:id="R55565df31e6c4a84"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Discovery" sheetId="5" r:id="R5ca2525dc163414f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CCF_A_Library" sheetId="6" r:id="Rce41f18a12ab45ae"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Robotics_Core_Library" sheetId="7" r:id="Rbe6574d9f21c4cf3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Papers" sheetId="1" r:id="R57908c5da2c148be"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rejected" sheetId="2" r:id="R63c2aa156b054ec2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Venues" sheetId="3" r:id="Rad8dabf4aaca4b71"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Keywords" sheetId="4" r:id="R88127d74d18b4b30"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Discovery" sheetId="5" r:id="R96875125680b43a7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CCF_A_Library" sheetId="6" r:id="R0bb1bfd8b552455d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Robotics_Core_Library" sheetId="7" r:id="R2b735d1032b646c6"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -300,7 +300,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="16" name="PapersTable" displayName="PapersTable" ref="A1:AZ5" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="20" name="PapersTable" displayName="PapersTable" ref="A1:AZ5" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="52">
     <x:tableColumn id="1" name="编号 ID"/>
     <x:tableColumn id="2" name="论文标题 Title"/>
@@ -405,7 +405,7 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="17" name="DiscoveryTable" displayName="DiscoveryTable" ref="A1:AU79" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="21" name="DiscoveryTable" displayName="DiscoveryTable" ref="A1:AU79" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="47">
     <x:tableColumn id="1" name="编号 ID"/>
     <x:tableColumn id="2" name="论文标题 Title"/>
@@ -460,7 +460,7 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="18" name="CCFALibraryTable" displayName="CCFALibraryTable" ref="A1:BN67" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="22" name="CCFALibraryTable" displayName="CCFALibraryTable" ref="A1:BN67" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="66">
     <x:tableColumn id="1" name="编号 ID"/>
     <x:tableColumn id="2" name="论文标题 Title"/>
@@ -534,7 +534,7 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="19" name="RoboticsCoreLibraryTable" displayName="RoboticsCoreLibraryTable" ref="A1:BC14" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="23" name="RoboticsCoreLibraryTable" displayName="RoboticsCoreLibraryTable" ref="A1:BC14" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="55">
     <x:tableColumn id="1" name="ID"/>
     <x:tableColumn id="2" name="Title"/>
@@ -1247,19 +1247,19 @@
         <x:v>Residual Learning / Sim-to-Real</x:v>
       </x:c>
       <x:c r="AU3" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="AV3" t="str">
-        <x:v>Unknown / Needs Evidence</x:v>
+        <x:v>Unknown / Needs paper-specific evidence; no inference added from title alone.</x:v>
       </x:c>
       <x:c r="AW3" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AX3" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AY3" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unknown (no high-confidence match)</x:v>
       </x:c>
       <x:c r="AZ3" t="str">
         <x:v>https://openaccess.thecvf.com/content/CVPR2025/html/Li_ManipTrans_Efficient_Dexterous_Bimanual_Manipulation_Transfer_via_Residual_Learning_CVPR_2025_paper.html；官方摘要/论文集元数据</x:v>
@@ -1373,22 +1373,22 @@
         <x:v>Diffusion / Contact-rich Manipulation</x:v>
       </x:c>
       <x:c r="AU4" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="AV4" t="str">
-        <x:v>Unknown / Needs Evidence</x:v>
+        <x:v>Unknown / Needs paper-specific evidence; no inference added from title alone.</x:v>
       </x:c>
       <x:c r="AW4" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AX4" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AY4" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unknown (no high-confidence match)</x:v>
       </x:c>
       <x:c r="AZ4" t="str">
-        <x:v>https://openaccess.thecvf.com/content/CVPR2025/html/Liang_DexHandDiff_Interaction-aware_Diffusion_Planning_for_Adaptive_Dexterous_Manipulation_CVPR_2025_paper.html；官方摘要/论文集元数据</x:v>
+        <x:v>https://openaccess.thecvf.com/content/CVPR2025/html/Liang_DexHandDiff_Interaction-aware_Diffusion_Planning_for_Adaptive_Dexterous_Manipulation_CVPR_2025_paper.html; https://dexdiffuser.github.io/; https://github.com/Liang-</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="150" customHeight="1">
@@ -1499,19 +1499,19 @@
         <x:v>Human Video / VLM</x:v>
       </x:c>
       <x:c r="AU5" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="AV5" t="str">
-        <x:v>Unknown / Needs Evidence</x:v>
+        <x:v>Unknown / Needs paper-specific evidence; no inference added from title alone.</x:v>
       </x:c>
       <x:c r="AW5" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AX5" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AY5" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unknown (no high-confidence match)</x:v>
       </x:c>
       <x:c r="AZ5" t="str">
         <x:v>https://openaccess.thecvf.com/content/ICCV2025/html/Yang_AR-VRM_Imitating_Human_Motions_for_Visual_Robot_Manipulation_with_Analogical_ICCV_2025_paper.html；官方摘要/论文集元数据</x:v>
@@ -4528,7 +4528,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8dcb41bb5dcf4040"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9f40b01cc37a4f7d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7824,7 +7824,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R36f63375e94f492f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf782efb0e6bf495e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8175,7 +8175,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R09c918cd74c44125"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbd847cc0db2e4d6b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8921,7 +8921,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R554fa4d754eb4cc4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re26aaa9f1a724d70"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9221,19 +9221,19 @@
         <x:v>Robot Manipulation; Diffusion Policy / Hierarchical Control</x:v>
       </x:c>
       <x:c r="AP2" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="AQ2" t="str">
-        <x:v>Unknown / Needs Evidence</x:v>
+        <x:v>Unknown / Needs paper-specific evidence; no inference added from title alone.</x:v>
       </x:c>
       <x:c r="AR2" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AS2" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AT2" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unknown (no high-confidence match)</x:v>
       </x:c>
       <x:c r="AU2" t="str">
         <x:v>https://openaccess.thecvf.com/content/CVPR2024/html/Ma_Hierarchical_Diffusion_Policy_for_Kinematics-Aware_Multi-Task_Robotic_Manipulation_CVPR_2024_paper.html；官方摘要/论文集元数据</x:v>
@@ -9356,19 +9356,19 @@
         <x:v>bimanual manipulation; decoupled interaction; RoboTwin</x:v>
       </x:c>
       <x:c r="AP3" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="AQ3" t="str">
-        <x:v>Unknown / Needs Evidence</x:v>
+        <x:v>Unknown / Needs paper-specific evidence; no inference added from title alone.</x:v>
       </x:c>
       <x:c r="AR3" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AS3" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AT3" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unknown (no high-confidence match)</x:v>
       </x:c>
       <x:c r="AU3" t="str">
         <x:v>https://openaccess.thecvf.com/content/ICCV2025/html/Jiang_Rethinking_Bimanual_Robotic_Manipulation_Learning_with_Decoupled_Interaction_Framework_ICCV_2025_paper.html；官方摘要/论文集元数据</x:v>
@@ -9491,19 +9491,19 @@
         <x:v>bimanual; diffusion; teleoperation; human demonstration</x:v>
       </x:c>
       <x:c r="AP4" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="AQ4" t="str">
-        <x:v>Unknown / Needs Evidence</x:v>
+        <x:v>Unknown / Needs paper-specific evidence; no inference added from title alone.</x:v>
       </x:c>
       <x:c r="AR4" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AS4" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AT4" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unknown (no high-confidence match)</x:v>
       </x:c>
       <x:c r="AU4" t="str">
         <x:v>https://openaccess.thecvf.com/content/ICCV2025/html/Xu_Diffusion-Based_Imaginative_Coordination_for_Bimanual_Manipulation_ICCV_2025_paper.html；官方摘要/论文集元数据</x:v>
@@ -9628,19 +9628,19 @@
         <x:v>Unknown</x:v>
       </x:c>
       <x:c r="AP5" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="AQ5" t="str">
-        <x:v>Unknown / Needs Evidence</x:v>
+        <x:v>Unknown / Needs paper-specific evidence; no inference added from title alone.</x:v>
       </x:c>
       <x:c r="AR5" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AS5" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AT5" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unknown (no high-confidence match)</x:v>
       </x:c>
       <x:c r="AU5" t="str">
         <x:v>Unknown</x:v>
@@ -9763,19 +9763,19 @@
         <x:v>Unknown</x:v>
       </x:c>
       <x:c r="AP6" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="AQ6" t="str">
-        <x:v>Unknown / Needs Evidence</x:v>
+        <x:v>Unknown / Needs paper-specific evidence; no inference added from title alone.</x:v>
       </x:c>
       <x:c r="AR6" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AS6" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AT6" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unknown (no high-confidence match)</x:v>
       </x:c>
       <x:c r="AU6" t="str">
         <x:v>Unknown</x:v>
@@ -9898,19 +9898,19 @@
         <x:v>Unknown</x:v>
       </x:c>
       <x:c r="AP7" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="AQ7" t="str">
-        <x:v>Unknown / Needs Evidence</x:v>
+        <x:v>Unknown / Needs paper-specific evidence; no inference added from title alone.</x:v>
       </x:c>
       <x:c r="AR7" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AS7" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AT7" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unknown (no high-confidence match)</x:v>
       </x:c>
       <x:c r="AU7" t="str">
         <x:v>Unknown</x:v>
@@ -10031,19 +10031,19 @@
         <x:v>Unknown</x:v>
       </x:c>
       <x:c r="AP8" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="AQ8" t="str">
-        <x:v>Unknown / Needs Evidence</x:v>
+        <x:v>Unknown / Needs paper-specific evidence; no inference added from title alone.</x:v>
       </x:c>
       <x:c r="AR8" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AS8" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AT8" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unknown (no high-confidence match)</x:v>
       </x:c>
       <x:c r="AU8" t="str">
         <x:v>Unknown</x:v>
@@ -10166,19 +10166,19 @@
         <x:v>Unknown</x:v>
       </x:c>
       <x:c r="AP9" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="AQ9" t="str">
-        <x:v>Unknown / Needs Evidence</x:v>
+        <x:v>Unknown / Needs paper-specific evidence; no inference added from title alone.</x:v>
       </x:c>
       <x:c r="AR9" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AS9" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AT9" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unknown (no high-confidence match)</x:v>
       </x:c>
       <x:c r="AU9" t="str">
         <x:v>Unknown</x:v>
@@ -10299,19 +10299,19 @@
         <x:v>Unknown</x:v>
       </x:c>
       <x:c r="AP10" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="AQ10" t="str">
-        <x:v>Unknown / Needs Evidence</x:v>
+        <x:v>Unknown / Needs paper-specific evidence; no inference added from title alone.</x:v>
       </x:c>
       <x:c r="AR10" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AS10" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AT10" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unknown (no high-confidence match)</x:v>
       </x:c>
       <x:c r="AU10" t="str">
         <x:v>Unknown</x:v>
@@ -10436,19 +10436,19 @@
         <x:v>Unknown</x:v>
       </x:c>
       <x:c r="AP11" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="AQ11" t="str">
-        <x:v>Unknown / Needs Evidence</x:v>
+        <x:v>Unknown / Needs paper-specific evidence; no inference added from title alone.</x:v>
       </x:c>
       <x:c r="AR11" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AS11" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AT11" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unknown (no high-confidence match)</x:v>
       </x:c>
       <x:c r="AU11" t="str">
         <x:v>Unknown</x:v>
@@ -10573,19 +10573,19 @@
         <x:v>Unknown</x:v>
       </x:c>
       <x:c r="AP12" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="AQ12" t="str">
-        <x:v>Unknown / Needs Evidence</x:v>
+        <x:v>Unknown / Needs paper-specific evidence; no inference added from title alone.</x:v>
       </x:c>
       <x:c r="AR12" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AS12" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AT12" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unknown (no high-confidence match)</x:v>
       </x:c>
       <x:c r="AU12" t="str">
         <x:v>Unknown</x:v>
@@ -10710,19 +10710,19 @@
         <x:v>Unknown</x:v>
       </x:c>
       <x:c r="AP13" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="AQ13" t="str">
-        <x:v>Unknown / Needs Evidence</x:v>
+        <x:v>Unknown / Needs paper-specific evidence; no inference added from title alone.</x:v>
       </x:c>
       <x:c r="AR13" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AS13" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AT13" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unknown (no high-confidence match)</x:v>
       </x:c>
       <x:c r="AU13" t="str">
         <x:v>Unknown</x:v>
@@ -10845,19 +10845,19 @@
         <x:v>Unknown</x:v>
       </x:c>
       <x:c r="AP14" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="AQ14" t="str">
-        <x:v>Unknown / Needs Evidence</x:v>
+        <x:v>Unknown / Needs paper-specific evidence; no inference added from title alone.</x:v>
       </x:c>
       <x:c r="AR14" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AS14" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AT14" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unknown (no high-confidence match)</x:v>
       </x:c>
       <x:c r="AU14" t="str">
         <x:v>Unknown</x:v>
@@ -10982,19 +10982,19 @@
         <x:v>Unknown</x:v>
       </x:c>
       <x:c r="AP15" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="AQ15" t="str">
-        <x:v>Unknown / Needs Evidence</x:v>
+        <x:v>Unknown / Needs paper-specific evidence; no inference added from title alone.</x:v>
       </x:c>
       <x:c r="AR15" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AS15" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AT15" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unknown (no high-confidence match)</x:v>
       </x:c>
       <x:c r="AU15" t="str">
         <x:v>Unknown</x:v>
@@ -11115,19 +11115,19 @@
         <x:v>Unknown</x:v>
       </x:c>
       <x:c r="AP16" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="AQ16" t="str">
-        <x:v>Unknown / Needs Evidence</x:v>
+        <x:v>Unknown / Needs paper-specific evidence; no inference added from title alone.</x:v>
       </x:c>
       <x:c r="AR16" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AS16" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AT16" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unknown (no high-confidence match)</x:v>
       </x:c>
       <x:c r="AU16" t="str">
         <x:v>Unknown</x:v>
@@ -11248,19 +11248,19 @@
         <x:v>Unknown</x:v>
       </x:c>
       <x:c r="AP17" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="AQ17" t="str">
-        <x:v>Unknown / Needs Evidence</x:v>
+        <x:v>Unknown / Needs paper-specific evidence; no inference added from title alone.</x:v>
       </x:c>
       <x:c r="AR17" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AS17" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AT17" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unknown (no high-confidence match)</x:v>
       </x:c>
       <x:c r="AU17" t="str">
         <x:v>Unknown</x:v>
@@ -11381,19 +11381,19 @@
         <x:v>Unknown</x:v>
       </x:c>
       <x:c r="AP18" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="AQ18" t="str">
-        <x:v>Unknown / Needs Evidence</x:v>
+        <x:v>Unknown / Needs paper-specific evidence; no inference added from title alone.</x:v>
       </x:c>
       <x:c r="AR18" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AS18" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AT18" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unknown (no high-confidence match)</x:v>
       </x:c>
       <x:c r="AU18" t="str">
         <x:v>Unknown</x:v>
@@ -11516,19 +11516,19 @@
         <x:v>Unknown</x:v>
       </x:c>
       <x:c r="AP19" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="AQ19" t="str">
-        <x:v>Unknown / Needs Evidence</x:v>
+        <x:v>Unknown / Needs paper-specific evidence; no inference added from title alone.</x:v>
       </x:c>
       <x:c r="AR19" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AS19" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AT19" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unknown (no high-confidence match)</x:v>
       </x:c>
       <x:c r="AU19" t="str">
         <x:v>Unknown</x:v>
@@ -11649,19 +11649,19 @@
         <x:v>Unknown</x:v>
       </x:c>
       <x:c r="AP20" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="AQ20" t="str">
-        <x:v>Unknown / Needs Evidence</x:v>
+        <x:v>Unknown / Needs paper-specific evidence; no inference added from title alone.</x:v>
       </x:c>
       <x:c r="AR20" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AS20" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AT20" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unknown (no high-confidence match)</x:v>
       </x:c>
       <x:c r="AU20" t="str">
         <x:v>Unknown</x:v>
@@ -11784,19 +11784,19 @@
         <x:v>Robot Manipulation; Diffusion Policy / Primitive Skills</x:v>
       </x:c>
       <x:c r="AP21" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="AQ21" t="str">
-        <x:v>Unknown / Needs Evidence</x:v>
+        <x:v>Unknown / Needs paper-specific evidence; no inference added from title alone.</x:v>
       </x:c>
       <x:c r="AR21" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AS21" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AT21" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unknown (no high-confidence match)</x:v>
       </x:c>
       <x:c r="AU21" t="str">
         <x:v>https://ojs.aaai.org/index.php/AAAI/article/view/38889；官方摘要/论文集元数据</x:v>
@@ -11919,19 +11919,19 @@
         <x:v>Imitation Learning; Multi-Task / Foresight</x:v>
       </x:c>
       <x:c r="AP22" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="AQ22" t="str">
-        <x:v>Unknown / Needs Evidence</x:v>
+        <x:v>Unknown / Needs paper-specific evidence; no inference added from title alone.</x:v>
       </x:c>
       <x:c r="AR22" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AS22" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AT22" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unknown (no high-confidence match)</x:v>
       </x:c>
       <x:c r="AU22" t="str">
         <x:v>https://ojs.aaai.org/index.php/AAAI/article/view/38911；官方摘要/论文集元数据</x:v>
@@ -12054,19 +12054,19 @@
         <x:v>Robot Manipulation; Long-Horizon / Visual-Tactile Policy</x:v>
       </x:c>
       <x:c r="AP23" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="AQ23" t="str">
-        <x:v>Unknown / Needs Evidence</x:v>
+        <x:v>Unknown / Needs paper-specific evidence; no inference added from title alone.</x:v>
       </x:c>
       <x:c r="AR23" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AS23" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AT23" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unknown (no high-confidence match)</x:v>
       </x:c>
       <x:c r="AU23" t="str">
         <x:v>https://ojs.aaai.org/index.php/AAAI/article/view/38955；官方摘要/论文集元数据</x:v>
@@ -12189,19 +12189,19 @@
         <x:v>Robot Manipulation; Humanoid / Generalization</x:v>
       </x:c>
       <x:c r="AP24" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="AQ24" t="str">
-        <x:v>Unknown / Needs Evidence</x:v>
+        <x:v>Unknown / Needs paper-specific evidence; no inference added from title alone.</x:v>
       </x:c>
       <x:c r="AR24" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AS24" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AT24" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unknown (no high-confidence match)</x:v>
       </x:c>
       <x:c r="AU24" t="str">
         <x:v>https://ojs.aaai.org/index.php/AAAI/article/view/38539；官方摘要/论文集元数据</x:v>
@@ -12322,19 +12322,19 @@
         <x:v>Dexterous Manipulation; Human Demonstrations / Motion Prior</x:v>
       </x:c>
       <x:c r="AP25" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="AQ25" t="str">
-        <x:v>Unknown / Needs Evidence</x:v>
+        <x:v>Unknown / Needs paper-specific evidence; no inference added from title alone.</x:v>
       </x:c>
       <x:c r="AR25" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AS25" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AT25" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unknown (no high-confidence match)</x:v>
       </x:c>
       <x:c r="AU25" t="str">
         <x:v>https://ojs.aaai.org/index.php/AAAI/article/download/38892/42854；官方摘要/论文集元数据</x:v>
@@ -12457,19 +12457,19 @@
         <x:v>Unknown</x:v>
       </x:c>
       <x:c r="AP26" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="AQ26" t="str">
-        <x:v>Unknown / Needs Evidence</x:v>
+        <x:v>Unknown / Needs paper-specific evidence; no inference added from title alone.</x:v>
       </x:c>
       <x:c r="AR26" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AS26" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AT26" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unknown (no high-confidence match)</x:v>
       </x:c>
       <x:c r="AU26" t="str">
         <x:v>Unknown</x:v>
@@ -12592,19 +12592,19 @@
         <x:v>Unknown</x:v>
       </x:c>
       <x:c r="AP27" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="AQ27" t="str">
-        <x:v>Unknown / Needs Evidence</x:v>
+        <x:v>Unknown / Needs paper-specific evidence; no inference added from title alone.</x:v>
       </x:c>
       <x:c r="AR27" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AS27" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AT27" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unknown (no high-confidence match)</x:v>
       </x:c>
       <x:c r="AU27" t="str">
         <x:v>Unknown</x:v>
@@ -12727,22 +12727,22 @@
         <x:v>Unknown</x:v>
       </x:c>
       <x:c r="AP28" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="AQ28" t="str">
-        <x:v>Unknown / Needs Evidence</x:v>
+        <x:v>Unknown / Needs paper-specific evidence; no inference added from title alone.</x:v>
       </x:c>
       <x:c r="AR28" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AS28" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AT28" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unknown (no high-confidence match)</x:v>
       </x:c>
       <x:c r="AU28" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>https://proceedings.mlr.press/v270/</x:v>
       </x:c>
     </x:row>
     <x:row r="29" ht="58" customHeight="1">
@@ -12862,19 +12862,19 @@
         <x:v>Unknown</x:v>
       </x:c>
       <x:c r="AP29" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="AQ29" t="str">
-        <x:v>Unknown / Needs Evidence</x:v>
+        <x:v>Unknown / Needs paper-specific evidence; no inference added from title alone.</x:v>
       </x:c>
       <x:c r="AR29" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AS29" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AT29" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unknown (no high-confidence match)</x:v>
       </x:c>
       <x:c r="AU29" t="str">
         <x:v>Unknown</x:v>
@@ -12997,19 +12997,19 @@
         <x:v>Unknown</x:v>
       </x:c>
       <x:c r="AP30" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="AQ30" t="str">
-        <x:v>Unknown / Needs Evidence</x:v>
+        <x:v>Unknown / Needs paper-specific evidence; no inference added from title alone.</x:v>
       </x:c>
       <x:c r="AR30" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AS30" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AT30" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unknown (no high-confidence match)</x:v>
       </x:c>
       <x:c r="AU30" t="str">
         <x:v>Unknown</x:v>
@@ -13132,19 +13132,19 @@
         <x:v>Unknown</x:v>
       </x:c>
       <x:c r="AP31" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="AQ31" t="str">
-        <x:v>Unknown / Needs Evidence</x:v>
+        <x:v>Unknown / Needs paper-specific evidence; no inference added from title alone.</x:v>
       </x:c>
       <x:c r="AR31" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AS31" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AT31" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unknown (no high-confidence match)</x:v>
       </x:c>
       <x:c r="AU31" t="str">
         <x:v>Unknown</x:v>
@@ -13267,19 +13267,19 @@
         <x:v>Unknown</x:v>
       </x:c>
       <x:c r="AP32" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="AQ32" t="str">
-        <x:v>Unknown / Needs Evidence</x:v>
+        <x:v>Unknown / Needs paper-specific evidence; no inference added from title alone.</x:v>
       </x:c>
       <x:c r="AR32" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AS32" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AT32" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unknown (no high-confidence match)</x:v>
       </x:c>
       <x:c r="AU32" t="str">
         <x:v>Unknown</x:v>
@@ -13402,19 +13402,19 @@
         <x:v>Unknown</x:v>
       </x:c>
       <x:c r="AP33" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="AQ33" t="str">
-        <x:v>Unknown / Needs Evidence</x:v>
+        <x:v>Unknown / Needs paper-specific evidence; no inference added from title alone.</x:v>
       </x:c>
       <x:c r="AR33" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AS33" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AT33" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unknown (no high-confidence match)</x:v>
       </x:c>
       <x:c r="AU33" t="str">
         <x:v>Unknown</x:v>
@@ -13537,19 +13537,19 @@
         <x:v>Unknown</x:v>
       </x:c>
       <x:c r="AP34" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="AQ34" t="str">
-        <x:v>Unknown / Needs Evidence</x:v>
+        <x:v>Unknown / Needs paper-specific evidence; no inference added from title alone.</x:v>
       </x:c>
       <x:c r="AR34" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AS34" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AT34" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unknown (no high-confidence match)</x:v>
       </x:c>
       <x:c r="AU34" t="str">
         <x:v>Unknown</x:v>
@@ -13672,19 +13672,19 @@
         <x:v>Unknown</x:v>
       </x:c>
       <x:c r="AP35" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="AQ35" t="str">
-        <x:v>Unknown / Needs Evidence</x:v>
+        <x:v>Unknown / Needs paper-specific evidence; no inference added from title alone.</x:v>
       </x:c>
       <x:c r="AR35" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AS35" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AT35" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unknown (no high-confidence match)</x:v>
       </x:c>
       <x:c r="AU35" t="str">
         <x:v>Unknown</x:v>
@@ -13807,19 +13807,19 @@
         <x:v>Unknown</x:v>
       </x:c>
       <x:c r="AP36" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="AQ36" t="str">
-        <x:v>Unknown / Needs Evidence</x:v>
+        <x:v>Unknown / Needs paper-specific evidence; no inference added from title alone.</x:v>
       </x:c>
       <x:c r="AR36" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AS36" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AT36" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unknown (no high-confidence match)</x:v>
       </x:c>
       <x:c r="AU36" t="str">
         <x:v>Unknown</x:v>
@@ -13942,19 +13942,19 @@
         <x:v>Unknown</x:v>
       </x:c>
       <x:c r="AP37" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="AQ37" t="str">
-        <x:v>Unknown / Needs Evidence</x:v>
+        <x:v>Unknown / Needs paper-specific evidence; no inference added from title alone.</x:v>
       </x:c>
       <x:c r="AR37" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AS37" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AT37" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unknown (no high-confidence match)</x:v>
       </x:c>
       <x:c r="AU37" t="str">
         <x:v>Unknown</x:v>
@@ -14077,19 +14077,19 @@
         <x:v>Unknown</x:v>
       </x:c>
       <x:c r="AP38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="AQ38" t="str">
-        <x:v>Unknown / Needs Evidence</x:v>
+        <x:v>Unknown / Needs paper-specific evidence; no inference added from title alone.</x:v>
       </x:c>
       <x:c r="AR38" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AS38" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AT38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unknown (no high-confidence match)</x:v>
       </x:c>
       <x:c r="AU38" t="str">
         <x:v>Unknown</x:v>
@@ -14212,22 +14212,22 @@
         <x:v>Unknown</x:v>
       </x:c>
       <x:c r="AP39" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="AQ39" t="str">
-        <x:v>Unknown / Needs Evidence</x:v>
+        <x:v>Unknown / Needs paper-specific evidence; no inference added from title alone.</x:v>
       </x:c>
       <x:c r="AR39" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AS39" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AT39" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unknown (no high-confidence match)</x:v>
       </x:c>
       <x:c r="AU39" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>https://proceedings.mlr.press/v270/</x:v>
       </x:c>
     </x:row>
     <x:row r="40" ht="58" customHeight="1">
@@ -14345,19 +14345,19 @@
         <x:v>Unknown</x:v>
       </x:c>
       <x:c r="AP40" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="AQ40" t="str">
-        <x:v>Unknown / Needs Evidence</x:v>
+        <x:v>Unknown / Needs paper-specific evidence; no inference added from title alone.</x:v>
       </x:c>
       <x:c r="AR40" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AS40" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AT40" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unknown (no high-confidence match)</x:v>
       </x:c>
       <x:c r="AU40" t="str">
         <x:v>Unknown</x:v>
@@ -14478,19 +14478,19 @@
         <x:v>Unknown</x:v>
       </x:c>
       <x:c r="AP41" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="AQ41" t="str">
-        <x:v>Unknown / Needs Evidence</x:v>
+        <x:v>Unknown / Needs paper-specific evidence; no inference added from title alone.</x:v>
       </x:c>
       <x:c r="AR41" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AS41" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AT41" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unknown (no high-confidence match)</x:v>
       </x:c>
       <x:c r="AU41" t="str">
         <x:v>Unknown</x:v>
@@ -14611,19 +14611,19 @@
         <x:v>Unknown</x:v>
       </x:c>
       <x:c r="AP42" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="AQ42" t="str">
-        <x:v>Unknown / Needs Evidence</x:v>
+        <x:v>Unknown / Needs paper-specific evidence; no inference added from title alone.</x:v>
       </x:c>
       <x:c r="AR42" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AS42" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AT42" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unknown (no high-confidence match)</x:v>
       </x:c>
       <x:c r="AU42" t="str">
         <x:v>Unknown</x:v>
@@ -14744,19 +14744,19 @@
         <x:v>Unknown</x:v>
       </x:c>
       <x:c r="AP43" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="AQ43" t="str">
-        <x:v>Unknown / Needs Evidence</x:v>
+        <x:v>Unknown / Needs paper-specific evidence; no inference added from title alone.</x:v>
       </x:c>
       <x:c r="AR43" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AS43" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AT43" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unknown (no high-confidence match)</x:v>
       </x:c>
       <x:c r="AU43" t="str">
         <x:v>Unknown</x:v>
@@ -14877,19 +14877,19 @@
         <x:v>Unknown</x:v>
       </x:c>
       <x:c r="AP44" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="AQ44" t="str">
-        <x:v>Unknown / Needs Evidence</x:v>
+        <x:v>Unknown / Needs paper-specific evidence; no inference added from title alone.</x:v>
       </x:c>
       <x:c r="AR44" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AS44" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AT44" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unknown (no high-confidence match)</x:v>
       </x:c>
       <x:c r="AU44" t="str">
         <x:v>Unknown</x:v>
@@ -15010,19 +15010,19 @@
         <x:v>Unknown</x:v>
       </x:c>
       <x:c r="AP45" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="AQ45" t="str">
-        <x:v>Unknown / Needs Evidence</x:v>
+        <x:v>Unknown / Needs paper-specific evidence; no inference added from title alone.</x:v>
       </x:c>
       <x:c r="AR45" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AS45" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AT45" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unknown (no high-confidence match)</x:v>
       </x:c>
       <x:c r="AU45" t="str">
         <x:v>Unknown</x:v>
@@ -15145,19 +15145,19 @@
         <x:v>Unknown</x:v>
       </x:c>
       <x:c r="AP46" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="AQ46" t="str">
-        <x:v>Unknown / Needs Evidence</x:v>
+        <x:v>Unknown / Needs paper-specific evidence; no inference added from title alone.</x:v>
       </x:c>
       <x:c r="AR46" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AS46" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AT46" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unknown (no high-confidence match)</x:v>
       </x:c>
       <x:c r="AU46" t="str">
         <x:v>Unknown</x:v>
@@ -15280,19 +15280,19 @@
         <x:v>Unknown</x:v>
       </x:c>
       <x:c r="AP47" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="AQ47" t="str">
-        <x:v>Unknown / Needs Evidence</x:v>
+        <x:v>Unknown / Needs paper-specific evidence; no inference added from title alone.</x:v>
       </x:c>
       <x:c r="AR47" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AS47" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AT47" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unknown (no high-confidence match)</x:v>
       </x:c>
       <x:c r="AU47" t="str">
         <x:v>Unknown</x:v>
@@ -15415,19 +15415,19 @@
         <x:v>Unknown</x:v>
       </x:c>
       <x:c r="AP48" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="AQ48" t="str">
-        <x:v>Unknown / Needs Evidence</x:v>
+        <x:v>Unknown / Needs paper-specific evidence; no inference added from title alone.</x:v>
       </x:c>
       <x:c r="AR48" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AS48" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AT48" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unknown (no high-confidence match)</x:v>
       </x:c>
       <x:c r="AU48" t="str">
         <x:v>Unknown</x:v>
@@ -15550,19 +15550,19 @@
         <x:v>Unknown</x:v>
       </x:c>
       <x:c r="AP49" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="AQ49" t="str">
-        <x:v>Unknown / Needs Evidence</x:v>
+        <x:v>Unknown / Needs paper-specific evidence; no inference added from title alone.</x:v>
       </x:c>
       <x:c r="AR49" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AS49" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AT49" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unknown (no high-confidence match)</x:v>
       </x:c>
       <x:c r="AU49" t="str">
         <x:v>Unknown</x:v>
@@ -15685,19 +15685,19 @@
         <x:v>Unknown</x:v>
       </x:c>
       <x:c r="AP50" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="AQ50" t="str">
-        <x:v>Unknown / Needs Evidence</x:v>
+        <x:v>Unknown / Needs paper-specific evidence; no inference added from title alone.</x:v>
       </x:c>
       <x:c r="AR50" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AS50" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AT50" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unknown (no high-confidence match)</x:v>
       </x:c>
       <x:c r="AU50" t="str">
         <x:v>Unknown</x:v>
@@ -15820,19 +15820,19 @@
         <x:v>Unknown</x:v>
       </x:c>
       <x:c r="AP51" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="AQ51" t="str">
-        <x:v>Unknown / Needs Evidence</x:v>
+        <x:v>Unknown / Needs paper-specific evidence; no inference added from title alone.</x:v>
       </x:c>
       <x:c r="AR51" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AS51" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AT51" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unknown (no high-confidence match)</x:v>
       </x:c>
       <x:c r="AU51" t="str">
         <x:v>Unknown</x:v>
@@ -15955,19 +15955,19 @@
         <x:v>Unknown</x:v>
       </x:c>
       <x:c r="AP52" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="AQ52" t="str">
-        <x:v>Unknown / Needs Evidence</x:v>
+        <x:v>Unknown / Needs paper-specific evidence; no inference added from title alone.</x:v>
       </x:c>
       <x:c r="AR52" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AS52" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AT52" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unknown (no high-confidence match)</x:v>
       </x:c>
       <x:c r="AU52" t="str">
         <x:v>Unknown</x:v>
@@ -16090,19 +16090,19 @@
         <x:v>Unknown</x:v>
       </x:c>
       <x:c r="AP53" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="AQ53" t="str">
-        <x:v>Unknown / Needs Evidence</x:v>
+        <x:v>Unknown / Needs paper-specific evidence; no inference added from title alone.</x:v>
       </x:c>
       <x:c r="AR53" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AS53" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AT53" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unknown (no high-confidence match)</x:v>
       </x:c>
       <x:c r="AU53" t="str">
         <x:v>Unknown</x:v>
@@ -16225,19 +16225,19 @@
         <x:v>Unknown</x:v>
       </x:c>
       <x:c r="AP54" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="AQ54" t="str">
-        <x:v>Unknown / Needs Evidence</x:v>
+        <x:v>Unknown / Needs paper-specific evidence; no inference added from title alone.</x:v>
       </x:c>
       <x:c r="AR54" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AS54" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AT54" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unknown (no high-confidence match)</x:v>
       </x:c>
       <x:c r="AU54" t="str">
         <x:v>Unknown</x:v>
@@ -16360,19 +16360,19 @@
         <x:v>Unknown</x:v>
       </x:c>
       <x:c r="AP55" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="AQ55" t="str">
-        <x:v>Unknown / Needs Evidence</x:v>
+        <x:v>Unknown / Needs paper-specific evidence; no inference added from title alone.</x:v>
       </x:c>
       <x:c r="AR55" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AS55" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AT55" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unknown (no high-confidence match)</x:v>
       </x:c>
       <x:c r="AU55" t="str">
         <x:v>Unknown</x:v>
@@ -16495,19 +16495,19 @@
         <x:v>Unknown</x:v>
       </x:c>
       <x:c r="AP56" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="AQ56" t="str">
-        <x:v>Unknown / Needs Evidence</x:v>
+        <x:v>Unknown / Needs paper-specific evidence; no inference added from title alone.</x:v>
       </x:c>
       <x:c r="AR56" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AS56" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AT56" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unknown (no high-confidence match)</x:v>
       </x:c>
       <x:c r="AU56" t="str">
         <x:v>Unknown</x:v>
@@ -16630,19 +16630,19 @@
         <x:v>Unknown</x:v>
       </x:c>
       <x:c r="AP57" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="AQ57" t="str">
-        <x:v>Unknown / Needs Evidence</x:v>
+        <x:v>Unknown / Needs paper-specific evidence; no inference added from title alone.</x:v>
       </x:c>
       <x:c r="AR57" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AS57" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AT57" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unknown (no high-confidence match)</x:v>
       </x:c>
       <x:c r="AU57" t="str">
         <x:v>Unknown</x:v>
@@ -16771,19 +16771,19 @@
         <x:v>Unknown</x:v>
       </x:c>
       <x:c r="AP58" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="AQ58" t="str">
-        <x:v>Unknown / Needs Evidence</x:v>
+        <x:v>Unknown / Needs paper-specific evidence; no inference added from title alone.</x:v>
       </x:c>
       <x:c r="AR58" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AS58" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AT58" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unknown (no high-confidence match)</x:v>
       </x:c>
       <x:c r="AU58" t="str">
         <x:v>Unknown</x:v>
@@ -16912,19 +16912,19 @@
         <x:v>Unknown</x:v>
       </x:c>
       <x:c r="AP59" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="AQ59" t="str">
-        <x:v>Unknown / Needs Evidence</x:v>
+        <x:v>Unknown / Needs paper-specific evidence; no inference added from title alone.</x:v>
       </x:c>
       <x:c r="AR59" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AS59" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AT59" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unknown (no high-confidence match)</x:v>
       </x:c>
       <x:c r="AU59" t="str">
         <x:v>Unknown</x:v>
@@ -17051,19 +17051,19 @@
         <x:v>Bimanual; Benchmark / Synthetic Demonstrations</x:v>
       </x:c>
       <x:c r="AP60" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="AQ60" t="str">
-        <x:v>Unknown / Needs Evidence</x:v>
+        <x:v>Unknown / Needs paper-specific evidence; no inference added from title alone.</x:v>
       </x:c>
       <x:c r="AR60" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AS60" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AT60" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unknown (no high-confidence match)</x:v>
       </x:c>
       <x:c r="AU60" t="str">
         <x:v>https://openaccess.thecvf.com/content/CVPR2025/html/Mu_RoboTwin_Dual-Arm_Robot_Benchmark_with_Generative_Digital_Twins_CVPR_2025_paper.html；官方摘要/论文集元数据</x:v>
@@ -17192,19 +17192,19 @@
         <x:v>VLA; 3D Manipulation / Data Efficiency</x:v>
       </x:c>
       <x:c r="AP61" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="AQ61" t="str">
-        <x:v>Unknown / Needs Evidence</x:v>
+        <x:v>Unknown / Needs paper-specific evidence; no inference added from title alone.</x:v>
       </x:c>
       <x:c r="AR61" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AS61" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AT61" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unknown (no high-confidence match)</x:v>
       </x:c>
       <x:c r="AU61" t="str">
         <x:v>https://proceedings.neurips.cc/paper_files/paper/2025/hash/5c1a8aa04c1a2cf5013f28831870dafa-Abstract-Conference.html；官方摘要/论文集元数据</x:v>
@@ -17333,19 +17333,19 @@
         <x:v>VLA; Inference Acceleration / Token Caching</x:v>
       </x:c>
       <x:c r="AP62" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="AQ62" t="str">
-        <x:v>Unknown / Needs Evidence</x:v>
+        <x:v>Unknown / Needs paper-specific evidence; no inference added from title alone.</x:v>
       </x:c>
       <x:c r="AR62" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AS62" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AT62" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unknown (no high-confidence match)</x:v>
       </x:c>
       <x:c r="AU62" t="str">
         <x:v>https://proceedings.neurips.cc/paper_files/paper/2025/hash/f062da1973ac9ac61fc6d44dd7fa309f-Abstract-Conference.html；官方摘要/论文集元数据</x:v>
@@ -17474,19 +17474,19 @@
         <x:v>VLA; Autoregressive Reasoning / Diffusion</x:v>
       </x:c>
       <x:c r="AP63" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="AQ63" t="str">
-        <x:v>Unknown / Needs Evidence</x:v>
+        <x:v>Unknown / Needs paper-specific evidence; no inference added from title alone.</x:v>
       </x:c>
       <x:c r="AR63" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AS63" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AT63" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unknown (no high-confidence match)</x:v>
       </x:c>
       <x:c r="AU63" t="str">
         <x:v>https://proceedings.mlr.press/v267/wen25g.html；官方摘要/论文集元数据</x:v>
@@ -17756,22 +17756,22 @@
         <x:v>VLA; Efficient Model / Pose Prediction</x:v>
       </x:c>
       <x:c r="AP65" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="AQ65" t="str">
-        <x:v>Unknown / Needs Evidence</x:v>
+        <x:v>Unknown / Needs paper-specific evidence; no inference added from title alone.</x:v>
       </x:c>
       <x:c r="AR65" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AS65" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AT65" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unknown (no high-confidence match)</x:v>
       </x:c>
       <x:c r="AU65" t="str">
-        <x:v>https://proceedings.neurips.cc/paper_files/paper/2024/hash/46a126492ea6fb87410e55a58df2e189-Abstract-Conference.html；官方摘要/论文集元数据</x:v>
+        <x:v>https://proceedings.neurips.cc/paper_files/paper/2024/hash/46a126492ea6fb87410e55a58df2e189-Abstract-Conference.html; https://sites.google.com/view/robomamba-web; https://github.com/lm</x:v>
       </x:c>
     </x:row>
     <x:row r="66" ht="58" customHeight="1">
@@ -17897,19 +17897,19 @@
         <x:v>Unknown</x:v>
       </x:c>
       <x:c r="AP66" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="AQ66" t="str">
-        <x:v>Unknown / Needs Evidence</x:v>
+        <x:v>Unknown / Needs paper-specific evidence; no inference added from title alone.</x:v>
       </x:c>
       <x:c r="AR66" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AS66" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AT66" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unknown (no high-confidence match)</x:v>
       </x:c>
       <x:c r="AU66" t="str">
         <x:v>Unknown</x:v>
@@ -18038,19 +18038,19 @@
         <x:v>Unknown</x:v>
       </x:c>
       <x:c r="AP67" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="AQ67" t="str">
-        <x:v>Unknown / Needs Evidence</x:v>
+        <x:v>Unknown / Needs paper-specific evidence; no inference added from title alone.</x:v>
       </x:c>
       <x:c r="AR67" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AS67" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AT67" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unknown (no high-confidence match)</x:v>
       </x:c>
       <x:c r="AU67" t="str">
         <x:v>Unknown</x:v>
@@ -18177,22 +18177,22 @@
         <x:v>Robot Manipulation; Consistency Flow Matching / 3D Policy</x:v>
       </x:c>
       <x:c r="AP68" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="AQ68" t="str">
-        <x:v>Unknown / Needs Evidence</x:v>
+        <x:v>Unknown / Needs paper-specific evidence; no inference added from title alone.</x:v>
       </x:c>
       <x:c r="AR68" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AS68" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AT68" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unknown (no high-confidence match)</x:v>
       </x:c>
       <x:c r="AU68" t="str">
-        <x:v>https://ojs.aaai.org/index.php/AAAI/article/view/33617；官方摘要/论文集元数据</x:v>
+        <x:v>https://ojs.aaai.org/index.php/AAAI/article/view/33617; https://github.com/</x:v>
       </x:c>
     </x:row>
     <x:row r="69" ht="58" customHeight="1">
@@ -18318,19 +18318,19 @@
         <x:v>Dexterous Hand; Policy Distillation / Generalization</x:v>
       </x:c>
       <x:c r="AP69" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="AQ69" t="str">
-        <x:v>Unknown / Needs Evidence</x:v>
+        <x:v>Unknown / Needs paper-specific evidence; no inference added from title alone.</x:v>
       </x:c>
       <x:c r="AR69" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AS69" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AT69" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unknown (no high-confidence match)</x:v>
       </x:c>
       <x:c r="AU69" t="str">
         <x:v>https://openaccess.thecvf.com/content/CVPR2025/html/Wang_UniGraspTransformer_Simplified_Policy_Distillation_for_Scalable_Dexterous_Robotic_Grasping_CVPR_2025_paper.html；官方摘要/论文集元数据</x:v>
@@ -18459,19 +18459,19 @@
         <x:v>Dexterous Hand; Residual RL / VLM Planning</x:v>
       </x:c>
       <x:c r="AP70" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="AQ70" t="str">
-        <x:v>Unknown / Needs Evidence</x:v>
+        <x:v>Unknown / Needs paper-specific evidence; no inference added from title alone.</x:v>
       </x:c>
       <x:c r="AR70" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AS70" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AT70" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unknown (no high-confidence match)</x:v>
       </x:c>
       <x:c r="AU70" t="str">
         <x:v>https://proceedings.neurips.cc/paper_files/paper/2025/hash/862644b156e51c35dea5a7446d640b14-Abstract-Conference.html；官方摘要/论文集元数据</x:v>
@@ -18600,19 +18600,19 @@
         <x:v>VLA; Video-Action Model / Generalization</x:v>
       </x:c>
       <x:c r="AP71" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="AQ71" t="str">
-        <x:v>Unknown / Needs Evidence</x:v>
+        <x:v>Unknown / Needs paper-specific evidence; no inference added from title alone.</x:v>
       </x:c>
       <x:c r="AR71" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AS71" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AT71" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unknown (no high-confidence match)</x:v>
       </x:c>
       <x:c r="AU71" t="str">
         <x:v>https://proceedings.neurips.cc/paper_files/paper/2025/hash/89a3b655a8b68ae1c76b768152c9c19d-Abstract-Conference.html；官方摘要/论文集元数据</x:v>
@@ -18741,19 +18741,19 @@
         <x:v>Dexterous Hand; Contact Reasoning / Language-guided Grasp</x:v>
       </x:c>
       <x:c r="AP72" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="AQ72" t="str">
-        <x:v>Unknown / Needs Evidence</x:v>
+        <x:v>Unknown / Needs paper-specific evidence; no inference added from title alone.</x:v>
       </x:c>
       <x:c r="AR72" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AS72" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AT72" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unknown (no high-confidence match)</x:v>
       </x:c>
       <x:c r="AU72" t="str">
         <x:v>https://openaccess.thecvf.com/content/CVPR2026/html/Lee_DextER_Language-driven_Dexterous_Grasp_Generation_with_Embodied_Reasoning_CVPR_2026_paper.html；官方摘要/论文集元数据</x:v>
@@ -18882,19 +18882,19 @@
         <x:v>Unknown</x:v>
       </x:c>
       <x:c r="AP73" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="AQ73" t="str">
-        <x:v>Unknown / Needs Evidence</x:v>
+        <x:v>Unknown / Needs paper-specific evidence; no inference added from title alone.</x:v>
       </x:c>
       <x:c r="AR73" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AS73" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AT73" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unknown (no high-confidence match)</x:v>
       </x:c>
       <x:c r="AU73" t="str">
         <x:v>Unknown</x:v>
@@ -19023,19 +19023,19 @@
         <x:v>Unknown</x:v>
       </x:c>
       <x:c r="AP74" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="AQ74" t="str">
-        <x:v>Unknown / Needs Evidence</x:v>
+        <x:v>Unknown / Needs paper-specific evidence; no inference added from title alone.</x:v>
       </x:c>
       <x:c r="AR74" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AS74" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AT74" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unknown (no high-confidence match)</x:v>
       </x:c>
       <x:c r="AU74" t="str">
         <x:v>Unknown</x:v>
@@ -19164,19 +19164,19 @@
         <x:v>Unknown</x:v>
       </x:c>
       <x:c r="AP75" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="AQ75" t="str">
-        <x:v>Unknown / Needs Evidence</x:v>
+        <x:v>Unknown / Needs paper-specific evidence; no inference added from title alone.</x:v>
       </x:c>
       <x:c r="AR75" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AS75" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AT75" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unknown (no high-confidence match)</x:v>
       </x:c>
       <x:c r="AU75" t="str">
         <x:v>Unknown</x:v>
@@ -19301,19 +19301,19 @@
         <x:v>Unknown</x:v>
       </x:c>
       <x:c r="AP76" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="AQ76" t="str">
-        <x:v>Unknown / Needs Evidence</x:v>
+        <x:v>Unknown / Needs paper-specific evidence; no inference added from title alone.</x:v>
       </x:c>
       <x:c r="AR76" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AS76" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AT76" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unknown (no high-confidence match)</x:v>
       </x:c>
       <x:c r="AU76" t="str">
         <x:v>Unknown</x:v>
@@ -19438,19 +19438,19 @@
         <x:v>Unknown</x:v>
       </x:c>
       <x:c r="AP77" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="AQ77" t="str">
-        <x:v>Unknown / Needs Evidence</x:v>
+        <x:v>Unknown / Needs paper-specific evidence; no inference added from title alone.</x:v>
       </x:c>
       <x:c r="AR77" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AS77" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AT77" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unknown (no high-confidence match)</x:v>
       </x:c>
       <x:c r="AU77" t="str">
         <x:v>Unknown</x:v>
@@ -19575,19 +19575,19 @@
         <x:v>Unknown</x:v>
       </x:c>
       <x:c r="AP78" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="AQ78" t="str">
-        <x:v>Unknown / Needs Evidence</x:v>
+        <x:v>Unknown / Needs paper-specific evidence; no inference added from title alone.</x:v>
       </x:c>
       <x:c r="AR78" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AS78" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AT78" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unknown (no high-confidence match)</x:v>
       </x:c>
       <x:c r="AU78" t="str">
         <x:v>Unknown</x:v>
@@ -19756,7 +19756,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf300a6bb39a34b35"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R37a2910e42e24495"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -20191,19 +20191,19 @@
         <x:v>Robot Manipulation; Diffusion Policy / Hierarchical Control</x:v>
       </x:c>
       <x:c r="BI2" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="BJ2" t="str">
-        <x:v>Unknown / Needs Evidence</x:v>
+        <x:v>Unknown / Needs paper-specific evidence; no inference added from title alone.</x:v>
       </x:c>
       <x:c r="BK2" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BL2" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BM2" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unknown (no high-confidence match)</x:v>
       </x:c>
       <x:c r="BN2" t="str">
         <x:v>https://openaccess.thecvf.com/content/CVPR2024/html/Ma_Hierarchical_Diffusion_Policy_for_Kinematics-Aware_Multi-Task_Robotic_Manipulation_CVPR_2024_paper.html；官方摘要/论文集元数据</x:v>
@@ -20383,19 +20383,19 @@
         <x:v>bimanual manipulation; decoupled interaction; RoboTwin</x:v>
       </x:c>
       <x:c r="BI3" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="BJ3" t="str">
-        <x:v>Unknown / Needs Evidence</x:v>
+        <x:v>Unknown / Needs paper-specific evidence; no inference added from title alone.</x:v>
       </x:c>
       <x:c r="BK3" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BL3" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BM3" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unknown (no high-confidence match)</x:v>
       </x:c>
       <x:c r="BN3" t="str">
         <x:v>https://openaccess.thecvf.com/content/ICCV2025/html/Jiang_Rethinking_Bimanual_Robotic_Manipulation_Learning_with_Decoupled_Interaction_Framework_ICCV_2025_paper.html；官方摘要/论文集元数据</x:v>
@@ -20575,19 +20575,19 @@
         <x:v>bimanual; diffusion; teleoperation; human demonstration</x:v>
       </x:c>
       <x:c r="BI4" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="BJ4" t="str">
-        <x:v>Unknown / Needs Evidence</x:v>
+        <x:v>Unknown / Needs paper-specific evidence; no inference added from title alone.</x:v>
       </x:c>
       <x:c r="BK4" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BL4" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BM4" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unknown (no high-confidence match)</x:v>
       </x:c>
       <x:c r="BN4" t="str">
         <x:v>https://openaccess.thecvf.com/content/ICCV2025/html/Xu_Diffusion-Based_Imaginative_Coordination_for_Bimanual_Manipulation_ICCV_2025_paper.html；官方摘要/论文集元数据</x:v>
@@ -20767,19 +20767,19 @@
         <x:v>Robot Manipulation; Diffusion Policy / Primitive Skills</x:v>
       </x:c>
       <x:c r="BI5" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="BJ5" t="str">
-        <x:v>Unknown / Needs Evidence</x:v>
+        <x:v>Unknown / Needs paper-specific evidence; no inference added from title alone.</x:v>
       </x:c>
       <x:c r="BK5" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BL5" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BM5" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unknown (no high-confidence match)</x:v>
       </x:c>
       <x:c r="BN5" t="str">
         <x:v>https://ojs.aaai.org/index.php/AAAI/article/view/38889；官方摘要/论文集元数据</x:v>
@@ -20959,19 +20959,19 @@
         <x:v>Imitation Learning; Multi-Task / Foresight</x:v>
       </x:c>
       <x:c r="BI6" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="BJ6" t="str">
-        <x:v>Unknown / Needs Evidence</x:v>
+        <x:v>Unknown / Needs paper-specific evidence; no inference added from title alone.</x:v>
       </x:c>
       <x:c r="BK6" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BL6" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BM6" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unknown (no high-confidence match)</x:v>
       </x:c>
       <x:c r="BN6" t="str">
         <x:v>https://ojs.aaai.org/index.php/AAAI/article/view/38911；官方摘要/论文集元数据</x:v>
@@ -21151,19 +21151,19 @@
         <x:v>Robot Manipulation; Long-Horizon / Visual-Tactile Policy</x:v>
       </x:c>
       <x:c r="BI7" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="BJ7" t="str">
-        <x:v>Unknown / Needs Evidence</x:v>
+        <x:v>Unknown / Needs paper-specific evidence; no inference added from title alone.</x:v>
       </x:c>
       <x:c r="BK7" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BL7" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BM7" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unknown (no high-confidence match)</x:v>
       </x:c>
       <x:c r="BN7" t="str">
         <x:v>https://ojs.aaai.org/index.php/AAAI/article/view/38955；官方摘要/论文集元数据</x:v>
@@ -21343,19 +21343,19 @@
         <x:v>Robot Manipulation; Humanoid / Generalization</x:v>
       </x:c>
       <x:c r="BI8" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="BJ8" t="str">
-        <x:v>Unknown / Needs Evidence</x:v>
+        <x:v>Unknown / Needs paper-specific evidence; no inference added from title alone.</x:v>
       </x:c>
       <x:c r="BK8" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BL8" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BM8" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unknown (no high-confidence match)</x:v>
       </x:c>
       <x:c r="BN8" t="str">
         <x:v>https://ojs.aaai.org/index.php/AAAI/article/view/38539；官方摘要/论文集元数据</x:v>
@@ -21533,19 +21533,19 @@
         <x:v>Dexterous Manipulation; Human Demonstrations / Motion Prior</x:v>
       </x:c>
       <x:c r="BI9" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="BJ9" t="str">
-        <x:v>Unknown / Needs Evidence</x:v>
+        <x:v>Unknown / Needs paper-specific evidence; no inference added from title alone.</x:v>
       </x:c>
       <x:c r="BK9" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BL9" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BM9" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unknown (no high-confidence match)</x:v>
       </x:c>
       <x:c r="BN9" t="str">
         <x:v>https://ojs.aaai.org/index.php/AAAI/article/download/38892/42854；官方摘要/论文集元数据</x:v>
@@ -21729,19 +21729,19 @@
         <x:v>Bimanual; Benchmark / Synthetic Demonstrations</x:v>
       </x:c>
       <x:c r="BI10" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="BJ10" t="str">
-        <x:v>Unknown / Needs Evidence</x:v>
+        <x:v>Unknown / Needs paper-specific evidence; no inference added from title alone.</x:v>
       </x:c>
       <x:c r="BK10" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BL10" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BM10" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unknown (no high-confidence match)</x:v>
       </x:c>
       <x:c r="BN10" t="str">
         <x:v>https://openaccess.thecvf.com/content/CVPR2025/html/Mu_RoboTwin_Dual-Arm_Robot_Benchmark_with_Generative_Digital_Twins_CVPR_2025_paper.html；官方摘要/论文集元数据</x:v>
@@ -21927,19 +21927,19 @@
         <x:v>VLA; 3D Manipulation / Data Efficiency</x:v>
       </x:c>
       <x:c r="BI11" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="BJ11" t="str">
-        <x:v>Unknown / Needs Evidence</x:v>
+        <x:v>Unknown / Needs paper-specific evidence; no inference added from title alone.</x:v>
       </x:c>
       <x:c r="BK11" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BL11" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BM11" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unknown (no high-confidence match)</x:v>
       </x:c>
       <x:c r="BN11" t="str">
         <x:v>https://proceedings.neurips.cc/paper_files/paper/2025/hash/5c1a8aa04c1a2cf5013f28831870dafa-Abstract-Conference.html；官方摘要/论文集元数据</x:v>
@@ -22125,19 +22125,19 @@
         <x:v>VLA; Inference Acceleration / Token Caching</x:v>
       </x:c>
       <x:c r="BI12" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="BJ12" t="str">
-        <x:v>Unknown / Needs Evidence</x:v>
+        <x:v>Unknown / Needs paper-specific evidence; no inference added from title alone.</x:v>
       </x:c>
       <x:c r="BK12" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BL12" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BM12" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unknown (no high-confidence match)</x:v>
       </x:c>
       <x:c r="BN12" t="str">
         <x:v>https://proceedings.neurips.cc/paper_files/paper/2025/hash/f062da1973ac9ac61fc6d44dd7fa309f-Abstract-Conference.html；官方摘要/论文集元数据</x:v>
@@ -22323,19 +22323,19 @@
         <x:v>VLA; Autoregressive Reasoning / Diffusion</x:v>
       </x:c>
       <x:c r="BI13" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="BJ13" t="str">
-        <x:v>Unknown / Needs Evidence</x:v>
+        <x:v>Unknown / Needs paper-specific evidence; no inference added from title alone.</x:v>
       </x:c>
       <x:c r="BK13" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BL13" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BM13" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unknown (no high-confidence match)</x:v>
       </x:c>
       <x:c r="BN13" t="str">
         <x:v>https://proceedings.mlr.press/v267/wen25g.html；官方摘要/论文集元数据</x:v>
@@ -22719,22 +22719,22 @@
         <x:v>VLA; Efficient Model / Pose Prediction</x:v>
       </x:c>
       <x:c r="BI15" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="BJ15" t="str">
-        <x:v>Unknown / Needs Evidence</x:v>
+        <x:v>Unknown / Needs paper-specific evidence; no inference added from title alone.</x:v>
       </x:c>
       <x:c r="BK15" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BL15" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BM15" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unknown (no high-confidence match)</x:v>
       </x:c>
       <x:c r="BN15" t="str">
-        <x:v>https://proceedings.neurips.cc/paper_files/paper/2024/hash/46a126492ea6fb87410e55a58df2e189-Abstract-Conference.html；官方摘要/论文集元数据</x:v>
+        <x:v>https://proceedings.neurips.cc/paper_files/paper/2024/hash/46a126492ea6fb87410e55a58df2e189-Abstract-Conference.html; https://sites.google.com/view/robomamba-web; https://github.com/lm</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="58" customHeight="1">
@@ -22915,22 +22915,22 @@
         <x:v>Robot Manipulation; Consistency Flow Matching / 3D Policy</x:v>
       </x:c>
       <x:c r="BI16" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="BJ16" t="str">
-        <x:v>Unknown / Needs Evidence</x:v>
+        <x:v>Unknown / Needs paper-specific evidence; no inference added from title alone.</x:v>
       </x:c>
       <x:c r="BK16" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BL16" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BM16" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unknown (no high-confidence match)</x:v>
       </x:c>
       <x:c r="BN16" t="str">
-        <x:v>https://ojs.aaai.org/index.php/AAAI/article/view/33617；官方摘要/论文集元数据</x:v>
+        <x:v>https://ojs.aaai.org/index.php/AAAI/article/view/33617; https://github.com/</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="58" customHeight="1">
@@ -23113,19 +23113,19 @@
         <x:v>Dexterous Hand; Policy Distillation / Generalization</x:v>
       </x:c>
       <x:c r="BI17" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="BJ17" t="str">
-        <x:v>Unknown / Needs Evidence</x:v>
+        <x:v>Unknown / Needs paper-specific evidence; no inference added from title alone.</x:v>
       </x:c>
       <x:c r="BK17" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BL17" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BM17" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unknown (no high-confidence match)</x:v>
       </x:c>
       <x:c r="BN17" t="str">
         <x:v>https://openaccess.thecvf.com/content/CVPR2025/html/Wang_UniGraspTransformer_Simplified_Policy_Distillation_for_Scalable_Dexterous_Robotic_Grasping_CVPR_2025_paper.html；官方摘要/论文集元数据</x:v>
@@ -23311,19 +23311,19 @@
         <x:v>Dexterous Hand; Residual RL / VLM Planning</x:v>
       </x:c>
       <x:c r="BI18" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="BJ18" t="str">
-        <x:v>Unknown / Needs Evidence</x:v>
+        <x:v>Unknown / Needs paper-specific evidence; no inference added from title alone.</x:v>
       </x:c>
       <x:c r="BK18" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BL18" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BM18" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unknown (no high-confidence match)</x:v>
       </x:c>
       <x:c r="BN18" t="str">
         <x:v>https://proceedings.neurips.cc/paper_files/paper/2025/hash/862644b156e51c35dea5a7446d640b14-Abstract-Conference.html；官方摘要/论文集元数据</x:v>
@@ -23509,19 +23509,19 @@
         <x:v>VLA; Video-Action Model / Generalization</x:v>
       </x:c>
       <x:c r="BI19" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="BJ19" t="str">
-        <x:v>Unknown / Needs Evidence</x:v>
+        <x:v>Unknown / Needs paper-specific evidence; no inference added from title alone.</x:v>
       </x:c>
       <x:c r="BK19" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BL19" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BM19" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unknown (no high-confidence match)</x:v>
       </x:c>
       <x:c r="BN19" t="str">
         <x:v>https://proceedings.neurips.cc/paper_files/paper/2025/hash/89a3b655a8b68ae1c76b768152c9c19d-Abstract-Conference.html；官方摘要/论文集元数据</x:v>
@@ -23707,19 +23707,19 @@
         <x:v>Dexterous Hand; Contact Reasoning / Language-guided Grasp</x:v>
       </x:c>
       <x:c r="BI20" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="BJ20" t="str">
-        <x:v>Unknown / Needs Evidence</x:v>
+        <x:v>Unknown / Needs paper-specific evidence; no inference added from title alone.</x:v>
       </x:c>
       <x:c r="BK20" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BL20" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BM20" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unknown (no high-confidence match)</x:v>
       </x:c>
       <x:c r="BN20" t="str">
         <x:v>https://openaccess.thecvf.com/content/CVPR2026/html/Lee_DextER_Language-driven_Dexterous_Grasp_Generation_with_Embodied_Reasoning_CVPR_2026_paper.html；官方摘要/论文集元数据</x:v>
@@ -24107,19 +24107,19 @@
         <x:v>Residual Learning / Sim-to-Real</x:v>
       </x:c>
       <x:c r="BI22" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="BJ22" t="str">
-        <x:v>Unknown / Needs Evidence</x:v>
+        <x:v>Unknown / Needs paper-specific evidence; no inference added from title alone.</x:v>
       </x:c>
       <x:c r="BK22" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BL22" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BM22" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unknown (no high-confidence match)</x:v>
       </x:c>
       <x:c r="BN22" t="str">
         <x:v>https://openaccess.thecvf.com/content/CVPR2025/html/Li_ManipTrans_Efficient_Dexterous_Bimanual_Manipulation_Transfer_via_Residual_Learning_CVPR_2025_paper.html；官方摘要/论文集元数据</x:v>
@@ -24307,22 +24307,22 @@
         <x:v>Diffusion / Contact-rich Manipulation</x:v>
       </x:c>
       <x:c r="BI23" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="BJ23" t="str">
-        <x:v>Unknown / Needs Evidence</x:v>
+        <x:v>Unknown / Needs paper-specific evidence; no inference added from title alone.</x:v>
       </x:c>
       <x:c r="BK23" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BL23" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BM23" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unknown (no high-confidence match)</x:v>
       </x:c>
       <x:c r="BN23" t="str">
-        <x:v>https://openaccess.thecvf.com/content/CVPR2025/html/Liang_DexHandDiff_Interaction-aware_Diffusion_Planning_for_Adaptive_Dexterous_Manipulation_CVPR_2025_paper.html；官方摘要/论文集元数据</x:v>
+        <x:v>https://openaccess.thecvf.com/content/CVPR2025/html/Liang_DexHandDiff_Interaction-aware_Diffusion_Planning_for_Adaptive_Dexterous_Manipulation_CVPR_2025_paper.html; https://dexdiffuser.github.io/; https://github.com/Liang-</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="58" customHeight="1">
@@ -24507,19 +24507,19 @@
         <x:v>Human Video / VLM</x:v>
       </x:c>
       <x:c r="BI24" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="BJ24" t="str">
-        <x:v>Unknown / Needs Evidence</x:v>
+        <x:v>Unknown / Needs paper-specific evidence; no inference added from title alone.</x:v>
       </x:c>
       <x:c r="BK24" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BL24" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BM24" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unknown (no high-confidence match)</x:v>
       </x:c>
       <x:c r="BN24" t="str">
         <x:v>https://openaccess.thecvf.com/content/ICCV2025/html/Yang_AR-VRM_Imitating_Human_Motions_for_Visual_Robot_Manipulation_with_Analogical_ICCV_2025_paper.html；官方摘要/论文集元数据</x:v>
@@ -24707,19 +24707,19 @@
         <x:v>Dexterous Grasping</x:v>
       </x:c>
       <x:c r="BI25" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="BJ25" t="str">
-        <x:v>Unknown / Needs Evidence</x:v>
+        <x:v>Unknown / Needs paper-specific evidence; no inference added from title alone.</x:v>
       </x:c>
       <x:c r="BK25" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BL25" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BM25" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unknown (no high-confidence match)</x:v>
       </x:c>
       <x:c r="BN25" t="str">
         <x:v>https://openaccess.thecvf.com/content/CVPR2024/html/Xu_Dexterous_Grasp_Transformer_CVPR_2024_paper.html；官方摘要/论文集元数据</x:v>
@@ -24907,19 +24907,19 @@
         <x:v>Mobile Manipulation</x:v>
       </x:c>
       <x:c r="BI26" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="BJ26" t="str">
-        <x:v>Unknown / Needs Evidence</x:v>
+        <x:v>Unknown / Needs paper-specific evidence; no inference added from title alone.</x:v>
       </x:c>
       <x:c r="BK26" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BL26" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BM26" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unknown (no high-confidence match)</x:v>
       </x:c>
       <x:c r="BN26" t="str">
         <x:v>https://openaccess.thecvf.com/content/CVPR2025/html/Wu_MoManipVLA_Transferring_Vision-language-action_Models_for_General_Mobile_Manipulation_CVPR_2025_paper.html；官方摘要/论文集元数据</x:v>
@@ -25107,19 +25107,19 @@
         <x:v>Action Chunking / Multi-task Policy</x:v>
       </x:c>
       <x:c r="BI27" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="BJ27" t="str">
-        <x:v>Unknown / Needs Evidence</x:v>
+        <x:v>Unknown / Needs paper-specific evidence; no inference added from title alone.</x:v>
       </x:c>
       <x:c r="BK27" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BL27" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BM27" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unknown (no high-confidence match)</x:v>
       </x:c>
       <x:c r="BN27" t="str">
         <x:v>https://proceedings.neurips.cc/paper_files/paper/2024/hash/ff887781480973bd3cb6026feb378d1e-Abstract-Conference.html；官方摘要/论文集元数据</x:v>
@@ -25307,19 +25307,19 @@
         <x:v>Surgical Robotics</x:v>
       </x:c>
       <x:c r="BI28" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="BJ28" t="str">
-        <x:v>Unknown / Needs Evidence</x:v>
+        <x:v>Unknown / Needs paper-specific evidence; no inference added from title alone.</x:v>
       </x:c>
       <x:c r="BK28" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BL28" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BM28" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unknown (no high-confidence match)</x:v>
       </x:c>
       <x:c r="BN28" t="str">
         <x:v>https://proceedings.neurips.cc/paper_files/paper/2024/hash/74c4f2b87b7499d365422152c76fd916-Abstract-Datasets_and_Benchmarks_Track.html；官方摘要/论文集元数据</x:v>
@@ -25507,19 +25507,19 @@
         <x:v>Video Demonstration / Reward Learning</x:v>
       </x:c>
       <x:c r="BI29" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="BJ29" t="str">
-        <x:v>Unknown / Needs Evidence</x:v>
+        <x:v>Unknown / Needs paper-specific evidence; no inference added from title alone.</x:v>
       </x:c>
       <x:c r="BK29" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BL29" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BM29" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unknown (no high-confidence match)</x:v>
       </x:c>
       <x:c r="BN29" t="str">
         <x:v>https://proceedings.neurips.cc/paper_files/paper/2024/hash/dcd297696d0bb304ba426b3c5a679c37-Abstract-Conference.html；官方摘要/论文集元数据</x:v>
@@ -25707,19 +25707,19 @@
         <x:v>Long-Horizon / Failure Recovery</x:v>
       </x:c>
       <x:c r="BI30" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="BJ30" t="str">
-        <x:v>Unknown / Needs Evidence</x:v>
+        <x:v>Unknown / Needs paper-specific evidence; no inference added from title alone.</x:v>
       </x:c>
       <x:c r="BK30" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BL30" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BM30" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unknown (no high-confidence match)</x:v>
       </x:c>
       <x:c r="BN30" t="str">
         <x:v>https://proceedings.neurips.cc/paper_files/paper/2024/hash/fad8962279154544ed69bb63eb14d677-Abstract-Conference.html；官方摘要/论文集元数据</x:v>
@@ -25907,19 +25907,19 @@
         <x:v>3D Observation / Contact-rich</x:v>
       </x:c>
       <x:c r="BI31" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="BJ31" t="str">
-        <x:v>Unknown / Needs Evidence</x:v>
+        <x:v>Unknown / Needs paper-specific evidence; no inference added from title alone.</x:v>
       </x:c>
       <x:c r="BK31" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BL31" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BM31" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unknown (no high-confidence match)</x:v>
       </x:c>
       <x:c r="BN31" t="str">
         <x:v>https://proceedings.neurips.cc/paper_files/paper/2024/hash/8e5dc5969a6174fcaaececd890c7f59b-Abstract-Datasets_and_Benchmarks_Track.html；官方摘要/论文集元数据</x:v>
@@ -26107,19 +26107,19 @@
         <x:v>Text-conditioned Reward</x:v>
       </x:c>
       <x:c r="BI32" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="BJ32" t="str">
-        <x:v>Unknown / Needs Evidence</x:v>
+        <x:v>Unknown / Needs paper-specific evidence; no inference added from title alone.</x:v>
       </x:c>
       <x:c r="BK32" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BL32" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BM32" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unknown (no high-confidence match)</x:v>
       </x:c>
       <x:c r="BN32" t="str">
         <x:v>https://proceedings.neurips.cc/paper_files/paper/2024/hash/5227ce00add5aa0a12d1c4ee92fcd2dc-Abstract-Conference.html；官方摘要/论文集元数据</x:v>
@@ -26307,22 +26307,22 @@
         <x:v>Human-Robot Domain Adaptation</x:v>
       </x:c>
       <x:c r="BI33" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="BJ33" t="str">
-        <x:v>Unknown / Needs Evidence</x:v>
+        <x:v>Unknown / Needs paper-specific evidence; no inference added from title alone.</x:v>
       </x:c>
       <x:c r="BK33" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BL33" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BM33" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unknown (no high-confidence match)</x:v>
       </x:c>
       <x:c r="BN33" t="str">
-        <x:v>https://openaccess.thecvf.com/content/CVPR2025/html/Zhou_Mitigating_the_Human-Robot_Domain_Discrepancy_in_Visual_Pre-training_for_Robotic_CVPR_2025_paper.html；官方摘要/论文集元数据</x:v>
+        <x:v>https://openaccess.thecvf.com/content/CVPR2025/html/</x:v>
       </x:c>
     </x:row>
     <x:row r="34" ht="58" customHeight="1">
@@ -26507,19 +26507,19 @@
         <x:v>Grounding / Synthetic Data</x:v>
       </x:c>
       <x:c r="BI34" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="BJ34" t="str">
-        <x:v>Unknown / Needs Evidence</x:v>
+        <x:v>Unknown / Needs paper-specific evidence; no inference added from title alone.</x:v>
       </x:c>
       <x:c r="BK34" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BL34" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BM34" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unknown (no high-confidence match)</x:v>
       </x:c>
       <x:c r="BN34" t="str">
         <x:v>https://openaccess.thecvf.com/content/CVPR2025/html/Huang_RoboGround_Robotic_Manipulation_with_Grounded_Vision-Language_Priors_CVPR_2025_paper.html；官方摘要/论文集元数据</x:v>
@@ -26707,19 +26707,19 @@
         <x:v>Synthetic Data / Scene Generation</x:v>
       </x:c>
       <x:c r="BI35" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="BJ35" t="str">
-        <x:v>Unknown / Needs Evidence</x:v>
+        <x:v>Unknown / Needs paper-specific evidence; no inference added from title alone.</x:v>
       </x:c>
       <x:c r="BK35" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BL35" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BM35" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unknown (no high-confidence match)</x:v>
       </x:c>
       <x:c r="BN35" t="str">
         <x:v>https://openaccess.thecvf.com/content/CVPR2025/html/Lee_DynScene_Scalable_Generation_of_Dynamic_Robotic_Manipulation_Scenes_for_Embodied_CVPR_2025_paper.html；官方摘要/论文集元数据</x:v>
@@ -26907,19 +26907,19 @@
         <x:v>Lifelong Learning</x:v>
       </x:c>
       <x:c r="BI36" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="BJ36" t="str">
-        <x:v>Unknown / Needs Evidence</x:v>
+        <x:v>Unknown / Needs paper-specific evidence; no inference added from title alone.</x:v>
       </x:c>
       <x:c r="BK36" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BL36" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BM36" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unknown (no high-confidence match)</x:v>
       </x:c>
       <x:c r="BN36" t="str">
         <x:v>https://openaccess.thecvf.com/content/CVPR2025/html/Yao_Think_Small_Act_Big_Primitive_Prompt_Learning_for_Lifelong_Robot_CVPR_2025_paper.html；官方摘要/论文集元数据</x:v>
@@ -27107,19 +27107,19 @@
         <x:v>Failure Recovery / 3D Gaussian Splatting</x:v>
       </x:c>
       <x:c r="BI37" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="BJ37" t="str">
-        <x:v>Unknown / Needs Evidence</x:v>
+        <x:v>Unknown / Needs paper-specific evidence; no inference added from title alone.</x:v>
       </x:c>
       <x:c r="BK37" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BL37" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BM37" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unknown (no high-confidence match)</x:v>
       </x:c>
       <x:c r="BN37" t="str">
         <x:v>https://ojs.aaai.org/index.php/AAAI/article/view/34866；官方摘要/论文集元数据</x:v>
@@ -27307,19 +27307,19 @@
         <x:v>Articulated Object / Affordance</x:v>
       </x:c>
       <x:c r="BI38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="BJ38" t="str">
-        <x:v>Unknown / Needs Evidence</x:v>
+        <x:v>Unknown / Needs paper-specific evidence; no inference added from title alone.</x:v>
       </x:c>
       <x:c r="BK38" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BL38" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BM38" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unknown (no high-confidence match)</x:v>
       </x:c>
       <x:c r="BN38" t="str">
         <x:v>https://ojs.aaai.org/index.php/AAAI/article/view/33615；官方摘要/论文集元数据</x:v>
@@ -27507,19 +27507,19 @@
         <x:v>Long-Horizon / Mobile Manipulation</x:v>
       </x:c>
       <x:c r="BI39" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="BJ39" t="str">
-        <x:v>Unknown / Needs Evidence</x:v>
+        <x:v>Unknown / Needs paper-specific evidence; no inference added from title alone.</x:v>
       </x:c>
       <x:c r="BK39" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BL39" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BM39" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unknown (no high-confidence match)</x:v>
       </x:c>
       <x:c r="BN39" t="str">
         <x:v>https://ojs.aaai.org/index.php/AAAI/article/view/33610；官方摘要/论文集元数据</x:v>
@@ -27707,19 +27707,19 @@
         <x:v>World Model / Video Diffusion</x:v>
       </x:c>
       <x:c r="BI40" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="BJ40" t="str">
-        <x:v>Unknown / Needs Evidence</x:v>
+        <x:v>Unknown / Needs paper-specific evidence; no inference added from title alone.</x:v>
       </x:c>
       <x:c r="BK40" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BL40" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BM40" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unknown (no high-confidence match)</x:v>
       </x:c>
       <x:c r="BN40" t="str">
         <x:v>https://proceedings.neurips.cc/paper_files/paper/2024/hash/481c70828a4ff20d31a646cc6cc95f3d-Abstract-Conference.html；官方摘要/论文集元数据</x:v>
@@ -27907,22 +27907,22 @@
         <x:v>Human Video / 3D Affordance</x:v>
       </x:c>
       <x:c r="BI41" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="BJ41" t="str">
-        <x:v>Unknown / Needs Evidence</x:v>
+        <x:v>Unknown / Needs paper-specific evidence; no inference added from title alone.</x:v>
       </x:c>
       <x:c r="BK41" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BL41" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BM41" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unknown (no high-confidence match)</x:v>
       </x:c>
       <x:c r="BN41" t="str">
-        <x:v>https://openaccess.thecvf.com/content/CVPR2025/html/Chen_VidBot_Learning_Generalizable_3D_Actions_from_In-the-Wild_2D_Human_Videos_CVPR_2025_paper.html；官方摘要/论文集元数据</x:v>
+        <x:v>https://openaccess.thecvf.com/content/CVPR2025/html/Chen_VidBot_Learning_Generali</x:v>
       </x:c>
     </x:row>
     <x:row r="42" ht="58" customHeight="1">
@@ -28107,22 +28107,22 @@
         <x:v>Visual Chain-of-Thought</x:v>
       </x:c>
       <x:c r="BI42" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="BJ42" t="str">
-        <x:v>Unknown / Needs Evidence</x:v>
+        <x:v>Unknown / Needs paper-specific evidence; no inference added from title alone.</x:v>
       </x:c>
       <x:c r="BK42" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BL42" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BM42" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unknown (no high-confidence match)</x:v>
       </x:c>
       <x:c r="BN42" t="str">
-        <x:v>https://openaccess.thecvf.com/content/CVPR2025/html/Zhao_CoT-VLA_Visual_Chain-of-Thought_Reasoning_for_Vision-Language-Action_Models_CVPR_2025_paper.html；官方摘要/论文集元数据</x:v>
+        <x:v>https://openaccess.thecvf.com/content/CVPR2025/html/</x:v>
       </x:c>
     </x:row>
     <x:row r="43" ht="58" customHeight="1">
@@ -28307,19 +28307,19 @@
         <x:v>Sim-to-Real / Behavior Cloning</x:v>
       </x:c>
       <x:c r="BI43" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="BJ43" t="str">
-        <x:v>Unknown / Needs Evidence</x:v>
+        <x:v>Unknown / Needs paper-specific evidence; no inference added from title alone.</x:v>
       </x:c>
       <x:c r="BK43" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BL43" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BM43" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unknown (no high-confidence match)</x:v>
       </x:c>
       <x:c r="BN43" t="str">
         <x:v>https://proceedings.neurips.cc/paper_files/paper/2025/hash/1185c89347a3f21ffc48c9d083c9437c-Abstract-Conference.html；官方摘要/论文集元数据</x:v>
@@ -28507,19 +28507,19 @@
         <x:v>Long-Horizon / Planning</x:v>
       </x:c>
       <x:c r="BI44" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="BJ44" t="str">
-        <x:v>Unknown / Needs Evidence</x:v>
+        <x:v>Unknown / Needs paper-specific evidence; no inference added from title alone.</x:v>
       </x:c>
       <x:c r="BK44" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BL44" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BM44" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unknown (no high-confidence match)</x:v>
       </x:c>
       <x:c r="BN44" t="str">
         <x:v>https://proceedings.neurips.cc/paper_files/paper/2025/hash/b94310e1c7ecb79f1a24adc757f1b89b-Abstract-Conference.html；官方摘要/论文集元数据</x:v>
@@ -28707,19 +28707,19 @@
         <x:v>Stochastic Interpolant / Efficiency</x:v>
       </x:c>
       <x:c r="BI45" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="BJ45" t="str">
-        <x:v>Unknown / Needs Evidence</x:v>
+        <x:v>Unknown / Needs paper-specific evidence; no inference added from title alone.</x:v>
       </x:c>
       <x:c r="BK45" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BL45" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BM45" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unknown (no high-confidence match)</x:v>
       </x:c>
       <x:c r="BN45" t="str">
         <x:v>https://proceedings.neurips.cc/paper_files/paper/2025/hash/49eadcc4a329fc6b74b9f8a82b78cbc3-Abstract-Conference.html；官方摘要/论文集元数据</x:v>
@@ -28907,19 +28907,19 @@
         <x:v>Mobile Manipulation / Agent</x:v>
       </x:c>
       <x:c r="BI46" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="BJ46" t="str">
-        <x:v>Unknown / Needs Evidence</x:v>
+        <x:v>Unknown / Needs paper-specific evidence; no inference added from title alone.</x:v>
       </x:c>
       <x:c r="BK46" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BL46" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BM46" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unknown (no high-confidence match)</x:v>
       </x:c>
       <x:c r="BN46" t="str">
         <x:v>https://proceedings.neurips.cc/paper_files/paper/2025/hash/bc97207e3979d1cc23109db0be0e8ed2-Abstract-Conference.html；官方摘要/论文集元数据</x:v>
@@ -29107,19 +29107,19 @@
         <x:v>Flow Matching / Visuomotor Policy</x:v>
       </x:c>
       <x:c r="BI47" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="BJ47" t="str">
-        <x:v>Unknown / Needs Evidence</x:v>
+        <x:v>Unknown / Needs paper-specific evidence; no inference added from title alone.</x:v>
       </x:c>
       <x:c r="BK47" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BL47" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BM47" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unknown (no high-confidence match)</x:v>
       </x:c>
       <x:c r="BN47" t="str">
         <x:v>https://proceedings.neurips.cc/paper_files/paper/2025/hash/282c3318be1b047b7bb5ba94fa4f3231-Abstract-Conference.html；官方摘要/论文集元数据</x:v>
@@ -29307,19 +29307,19 @@
         <x:v>Tool Use / Generative Design</x:v>
       </x:c>
       <x:c r="BI48" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="BJ48" t="str">
-        <x:v>Unknown / Needs Evidence</x:v>
+        <x:v>Unknown / Needs paper-specific evidence; no inference added from title alone.</x:v>
       </x:c>
       <x:c r="BK48" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BL48" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BM48" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unknown (no high-confidence match)</x:v>
       </x:c>
       <x:c r="BN48" t="str">
         <x:v>https://proceedings.neurips.cc/paper_files/paper/2025/hash/9fc291fef2f9607a46777d367f900a15-Abstract-Conference.html；官方摘要/论文集元数据</x:v>
@@ -29507,19 +29507,19 @@
         <x:v>3D Manipulation / Multimodal Policy</x:v>
       </x:c>
       <x:c r="BI49" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="BJ49" t="str">
-        <x:v>Unknown / Needs Evidence</x:v>
+        <x:v>Unknown / Needs paper-specific evidence; no inference added from title alone.</x:v>
       </x:c>
       <x:c r="BK49" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BL49" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BM49" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unknown (no high-confidence match)</x:v>
       </x:c>
       <x:c r="BN49" t="str">
         <x:v>https://proceedings.neurips.cc/paper_files/paper/2025/hash/eacc8ae341d15d2c13c02fef88189db3-Abstract-Conference.html；官方摘要/论文集元数据</x:v>
@@ -29707,19 +29707,19 @@
         <x:v>Robot Data / Spatial Reasoning</x:v>
       </x:c>
       <x:c r="BI50" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="BJ50" t="str">
-        <x:v>Unknown / Needs Evidence</x:v>
+        <x:v>Unknown / Needs paper-specific evidence; no inference added from title alone.</x:v>
       </x:c>
       <x:c r="BK50" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BL50" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BM50" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unknown (no high-confidence match)</x:v>
       </x:c>
       <x:c r="BN50" t="str">
         <x:v>https://proceedings.neurips.cc/paper_files/paper/2025/hash/1f467c3e37abf9f86c78f44c6a27ee7c-Abstract-Datasets_and_Benchmarks_Track.html；官方摘要/论文集元数据</x:v>
@@ -29907,19 +29907,19 @@
         <x:v>Task Planning / Demonstrations</x:v>
       </x:c>
       <x:c r="BI51" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="BJ51" t="str">
-        <x:v>Unknown / Needs Evidence</x:v>
+        <x:v>Unknown / Needs paper-specific evidence; no inference added from title alone.</x:v>
       </x:c>
       <x:c r="BK51" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BL51" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BM51" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unknown (no high-confidence match)</x:v>
       </x:c>
       <x:c r="BN51" t="str">
         <x:v>https://proceedings.neurips.cc/paper_files/paper/2025/hash/b8358a00e5b870194b974ddf8dd415c3-Abstract-Conference.html；官方摘要/论文集元数据</x:v>
@@ -30107,19 +30107,19 @@
         <x:v>Unknown</x:v>
       </x:c>
       <x:c r="BI52" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="BJ52" t="str">
-        <x:v>Unknown / Needs Evidence</x:v>
+        <x:v>Unknown / Needs paper-specific evidence; no inference added from title alone.</x:v>
       </x:c>
       <x:c r="BK52" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BL52" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BM52" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unknown (no high-confidence match)</x:v>
       </x:c>
       <x:c r="BN52" t="str">
         <x:v>https://openaccess.thecvf.com/content/ICCV2025/html/Wang_DexH2R_A_Benchmark_for_Dynamic_Dexterous_Grasping_in_Human-to-Robot_Handover_ICCV_2025_paper.html；官方摘要/论文集元数据</x:v>
@@ -30307,22 +30307,22 @@
         <x:v>Unknown</x:v>
       </x:c>
       <x:c r="BI53" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="BJ53" t="str">
-        <x:v>Unknown / Needs Evidence</x:v>
+        <x:v>Unknown / Needs paper-specific evidence; no inference added from title alone.</x:v>
       </x:c>
       <x:c r="BK53" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BL53" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BM53" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unknown (no high-confidence match)</x:v>
       </x:c>
       <x:c r="BN53" t="str">
-        <x:v>https://openaccess.thecvf.com/content/CVPR2025/html/Zhang_BimArt_A_Unified_Approach_for_the_Synthesis_of_3D_Bimanual_CVPR_2025_paper.html；官方摘要/论文集元数据</x:v>
+        <x:v>https://openaccess.thecvf.com/content/CVPR2025/html/</x:v>
       </x:c>
     </x:row>
     <x:row r="54" ht="58" customHeight="1">
@@ -30707,22 +30707,22 @@
         <x:v>Unknown</x:v>
       </x:c>
       <x:c r="BI55" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="BJ55" t="str">
-        <x:v>Unknown / Needs Evidence</x:v>
+        <x:v>Unknown / Needs paper-specific evidence; no inference added from title alone.</x:v>
       </x:c>
       <x:c r="BK55" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BL55" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BM55" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unknown (no high-confidence match)</x:v>
       </x:c>
       <x:c r="BN55" t="str">
-        <x:v>https://openaccess.thecvf.com/content/CVPR2025/html/Li_LatentHOI_On_the_Generalizable_Hand_Object_Motion_Generation_with_Latent_CVPR_2025_paper.html；官方摘要/论文集元数据</x:v>
+        <x:v>https://openaccess.thecvf.com/content/CVPR2025/html/Li_LatentHOI_On_the_Generali</x:v>
       </x:c>
     </x:row>
     <x:row r="56" ht="58" customHeight="1">
@@ -30907,22 +30907,22 @@
         <x:v>Unknown</x:v>
       </x:c>
       <x:c r="BI56" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="BJ56" t="str">
-        <x:v>Unknown / Needs Evidence</x:v>
+        <x:v>Unknown / Needs paper-specific evidence; no inference added from title alone.</x:v>
       </x:c>
       <x:c r="BK56" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BL56" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BM56" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unknown (no high-confidence match)</x:v>
       </x:c>
       <x:c r="BN56" t="str">
-        <x:v>https://openaccess.thecvf.com/content/CVPR2024/papers/Liu_TACO_Benchmarking_Generalizable_Bimanual_Tool-ACtion-Object_Understanding_CVPR_2024_paper.pdf；官方摘要/论文集元数据</x:v>
+        <x:v>https://openaccess.thecvf.com/content/CVPR2024/papers/Liu_TACO_Benchmarking_Generali</x:v>
       </x:c>
     </x:row>
     <x:row r="57" ht="58" customHeight="1">
@@ -31107,19 +31107,19 @@
         <x:v>Unknown</x:v>
       </x:c>
       <x:c r="BI57" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="BJ57" t="str">
-        <x:v>Unknown / Needs Evidence</x:v>
+        <x:v>Unknown / Needs paper-specific evidence; no inference added from title alone.</x:v>
       </x:c>
       <x:c r="BK57" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BL57" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BM57" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unknown (no high-confidence match)</x:v>
       </x:c>
       <x:c r="BN57" t="str">
         <x:v>https://openaccess.thecvf.com/content/CVPR2024/html/Uppal_SPIN_Simultaneous_Perception_Interaction_and_Navigation_CVPR_2024_paper.html；官方摘要/论文集元数据</x:v>
@@ -31707,22 +31707,22 @@
         <x:v>Unknown</x:v>
       </x:c>
       <x:c r="BI60" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="BJ60" t="str">
-        <x:v>Unknown / Needs Evidence</x:v>
+        <x:v>Unknown / Needs paper-specific evidence; no inference added from title alone.</x:v>
       </x:c>
       <x:c r="BK60" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BL60" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BM60" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unknown (no high-confidence match)</x:v>
       </x:c>
       <x:c r="BN60" t="str">
-        <x:v>https://openaccess.thecvf.com/content/CVPR2025/html/Zhao_TASTE-Rob_Advancing_Video_Generation_of_Task-Oriented_Hand-Object_Interaction_for_Generalizable_CVPR_2025_paper.html；官方摘要/论文集元数据</x:v>
+        <x:v>https://openaccess.thecvf.com/content/CVPR2025/html/</x:v>
       </x:c>
     </x:row>
     <x:row r="61" ht="58" customHeight="1">
@@ -31907,19 +31907,19 @@
         <x:v>Unknown</x:v>
       </x:c>
       <x:c r="BI61" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="BJ61" t="str">
-        <x:v>Unknown / Needs Evidence</x:v>
+        <x:v>Unknown / Needs paper-specific evidence; no inference added from title alone.</x:v>
       </x:c>
       <x:c r="BK61" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BL61" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BM61" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unknown (no high-confidence match)</x:v>
       </x:c>
       <x:c r="BN61" t="str">
         <x:v>https://ojs.aaai.org/index.php/AAAI/article/view/38874；官方摘要/论文集元数据</x:v>
@@ -32107,19 +32107,19 @@
         <x:v>Unknown</x:v>
       </x:c>
       <x:c r="BI62" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="BJ62" t="str">
-        <x:v>Unknown / Needs Evidence</x:v>
+        <x:v>Unknown / Needs paper-specific evidence; no inference added from title alone.</x:v>
       </x:c>
       <x:c r="BK62" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BL62" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BM62" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unknown (no high-confidence match)</x:v>
       </x:c>
       <x:c r="BN62" t="str">
         <x:v>https://proceedings.neurips.cc/paper_files/paper/2025/hash/e4ef7454447baa15a424314e6284441b-Abstract-Conference.html；官方摘要/论文集元数据</x:v>
@@ -32307,19 +32307,19 @@
         <x:v>Unknown</x:v>
       </x:c>
       <x:c r="BI63" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="BJ63" t="str">
-        <x:v>Unknown / Needs Evidence</x:v>
+        <x:v>Unknown / Needs paper-specific evidence; no inference added from title alone.</x:v>
       </x:c>
       <x:c r="BK63" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BL63" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BM63" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unknown (no high-confidence match)</x:v>
       </x:c>
       <x:c r="BN63" t="str">
         <x:v>https://ojs.aaai.org/index.php/AAAI/article/view/38313；官方摘要/论文集元数据</x:v>
@@ -32507,19 +32507,19 @@
         <x:v>Unknown</x:v>
       </x:c>
       <x:c r="BI64" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="BJ64" t="str">
-        <x:v>Unknown / Needs Evidence</x:v>
+        <x:v>Unknown / Needs paper-specific evidence; no inference added from title alone.</x:v>
       </x:c>
       <x:c r="BK64" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BL64" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BM64" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unknown (no high-confidence match)</x:v>
       </x:c>
       <x:c r="BN64" t="str">
         <x:v>https://ojs.aaai.org/index.php/AAAI/article/view/40127；官方摘要/论文集元数据</x:v>
@@ -32707,19 +32707,19 @@
         <x:v>Unknown</x:v>
       </x:c>
       <x:c r="BI65" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="BJ65" t="str">
-        <x:v>Unknown / Needs Evidence</x:v>
+        <x:v>Unknown / Needs paper-specific evidence; no inference added from title alone.</x:v>
       </x:c>
       <x:c r="BK65" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BL65" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BM65" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unknown (no high-confidence match)</x:v>
       </x:c>
       <x:c r="BN65" t="str">
         <x:v>https://ojs.aaai.org/index.php/AAAI/article/view/28266；官方摘要/论文集元数据</x:v>
@@ -33160,7 +33160,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc302613323ef40fd"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1d151f50ba90484f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -33691,22 +33691,22 @@
         <x:v>Library Analysis / Research Note: Unknown / Needs Full-Paper Verification</x:v>
       </x:c>
       <x:c r="AX3" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="AY3" t="str">
-        <x:v>Unknown / Needs Evidence</x:v>
+        <x:v>Unknown / Needs paper-specific evidence; no inference added from title alone.</x:v>
       </x:c>
       <x:c r="AZ3" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BA3" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BB3" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unknown (no high-confidence match)</x:v>
       </x:c>
       <x:c r="BC3" t="str">
-        <x:v>RSS official proceedings abstract</x:v>
+        <x:v>https://www.roboticsproceedings.org/rss21/p149.html; https://hnu</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="62" customHeight="1">
@@ -33858,19 +33858,19 @@
         <x:v>Library Analysis / Research Note: Unknown / Needs Full-Paper Verification</x:v>
       </x:c>
       <x:c r="AX4" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="AY4" t="str">
-        <x:v>Unknown / Needs Evidence</x:v>
+        <x:v>Unknown / Needs paper-specific evidence; no inference added from title alone.</x:v>
       </x:c>
       <x:c r="AZ4" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BA4" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BB4" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unknown (no high-confidence match)</x:v>
       </x:c>
       <x:c r="BC4" t="str">
         <x:v>RSS official proceedings abstract</x:v>
@@ -34025,19 +34025,19 @@
         <x:v>Library Analysis / Research Note: Unknown / Needs Full-Paper Verification</x:v>
       </x:c>
       <x:c r="AX5" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="AY5" t="str">
-        <x:v>Unknown / Needs Evidence</x:v>
+        <x:v>Unknown / Needs paper-specific evidence; no inference added from title alone.</x:v>
       </x:c>
       <x:c r="AZ5" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BA5" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BB5" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unknown (no high-confidence match)</x:v>
       </x:c>
       <x:c r="BC5" t="str">
         <x:v>RSS official proceedings</x:v>
@@ -34192,19 +34192,19 @@
         <x:v>Library Analysis / Research Note: Unknown / Needs Full-Paper Verification</x:v>
       </x:c>
       <x:c r="AX6" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="AY6" t="str">
-        <x:v>Unknown / Needs Evidence</x:v>
+        <x:v>Unknown / Needs paper-specific evidence; no inference added from title alone.</x:v>
       </x:c>
       <x:c r="AZ6" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BA6" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BB6" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unknown (no high-confidence match)</x:v>
       </x:c>
       <x:c r="BC6" t="str">
         <x:v>RSS official proceedings abstract</x:v>
@@ -34359,19 +34359,19 @@
         <x:v>Library Analysis / Research Note: Unknown / Needs Full-Paper Verification</x:v>
       </x:c>
       <x:c r="AX7" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="AY7" t="str">
-        <x:v>Unknown / Needs Evidence</x:v>
+        <x:v>Unknown / Needs paper-specific evidence; no inference added from title alone.</x:v>
       </x:c>
       <x:c r="AZ7" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BA7" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BB7" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unknown (no high-confidence match)</x:v>
       </x:c>
       <x:c r="BC7" t="str">
         <x:v>IEEE Xplore abstract; official project page</x:v>
@@ -34526,19 +34526,19 @@
         <x:v>Library Analysis / Research Note: Unknown / Needs Full-Paper Verification</x:v>
       </x:c>
       <x:c r="AX8" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="AY8" t="str">
-        <x:v>Unknown / Needs Evidence</x:v>
+        <x:v>Unknown / Needs paper-specific evidence; no inference added from title alone.</x:v>
       </x:c>
       <x:c r="AZ8" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BA8" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BB8" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unknown (no high-confidence match)</x:v>
       </x:c>
       <x:c r="BC8" t="str">
         <x:v>IEEE Xplore abstract</x:v>
@@ -34693,19 +34693,19 @@
         <x:v>Library Analysis / Research Note: Unknown / Needs Full-Paper Verification</x:v>
       </x:c>
       <x:c r="AX9" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="AY9" t="str">
-        <x:v>Unknown / Needs Evidence</x:v>
+        <x:v>Unknown / Needs paper-specific evidence; no inference added from title alone.</x:v>
       </x:c>
       <x:c r="AZ9" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BA9" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BB9" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unknown (no high-confidence match)</x:v>
       </x:c>
       <x:c r="BC9" t="str">
         <x:v>IEEE Xplore abstract</x:v>
@@ -34860,19 +34860,19 @@
         <x:v>Library Analysis / Research Note: Unknown / Needs Full-Paper Verification</x:v>
       </x:c>
       <x:c r="AX10" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="AY10" t="str">
-        <x:v>Unknown / Needs Evidence</x:v>
+        <x:v>Unknown / Needs paper-specific evidence; no inference added from title alone.</x:v>
       </x:c>
       <x:c r="AZ10" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BA10" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BB10" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unknown (no high-confidence match)</x:v>
       </x:c>
       <x:c r="BC10" t="str">
         <x:v>IEEE Xplore abstract</x:v>
@@ -35005,19 +35005,19 @@
         <x:v>Library Analysis / Research Note: Unknown / Needs Full-Paper Verification</x:v>
       </x:c>
       <x:c r="AX11" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="AY11" t="str">
-        <x:v>Unknown / Needs Evidence</x:v>
+        <x:v>Unknown / Needs paper-specific evidence; no inference added from title alone.</x:v>
       </x:c>
       <x:c r="AZ11" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BA11" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BB11" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unknown (no high-confidence match)</x:v>
       </x:c>
       <x:c r="BC11" t="str">
         <x:v>Unknown</x:v>
@@ -35146,19 +35146,19 @@
         <x:v>Library Analysis / Research Note: Unknown / Needs Full-Paper Verification</x:v>
       </x:c>
       <x:c r="AX12" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="AY12" t="str">
-        <x:v>Unknown / Needs Evidence</x:v>
+        <x:v>Unknown / Needs paper-specific evidence; no inference added from title alone.</x:v>
       </x:c>
       <x:c r="AZ12" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BA12" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BB12" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unknown (no high-confidence match)</x:v>
       </x:c>
       <x:c r="BC12" t="str">
         <x:v>Unknown</x:v>
@@ -35287,19 +35287,19 @@
         <x:v>Library Analysis / Research Note: Unknown / Needs Full-Paper Verification</x:v>
       </x:c>
       <x:c r="AX13" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="AY13" t="str">
-        <x:v>Unknown / Needs Evidence</x:v>
+        <x:v>Unknown / Needs paper-specific evidence; no inference added from title alone.</x:v>
       </x:c>
       <x:c r="AZ13" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BA13" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BB13" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unknown (no high-confidence match)</x:v>
       </x:c>
       <x:c r="BC13" t="str">
         <x:v>Unknown</x:v>
@@ -35428,19 +35428,19 @@
         <x:v>Library Analysis / Research Note: Unknown / Needs Full-Paper Verification</x:v>
       </x:c>
       <x:c r="AX14" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="AY14" t="str">
-        <x:v>Unknown / Needs Evidence</x:v>
+        <x:v>Unknown / Needs paper-specific evidence; no inference added from title alone.</x:v>
       </x:c>
       <x:c r="AZ14" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BA14" t="str">
-        <x:v>Unknown / Not Explicitly Reported</x:v>
+        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BB14" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unknown (no high-confidence match)</x:v>
       </x:c>
       <x:c r="BC14" t="str">
         <x:v>Unknown</x:v>
@@ -35463,7 +35463,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8743da78aa834f11"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd07c215f6a644228"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/00_Paper_Pool/Paper_Pool.xlsx
+++ b/00_Paper_Pool/Paper_Pool.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Papers" sheetId="1" r:id="R57908c5da2c148be"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rejected" sheetId="2" r:id="R63c2aa156b054ec2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Venues" sheetId="3" r:id="Rad8dabf4aaca4b71"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Keywords" sheetId="4" r:id="R88127d74d18b4b30"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Discovery" sheetId="5" r:id="R96875125680b43a7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CCF_A_Library" sheetId="6" r:id="R0bb1bfd8b552455d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Robotics_Core_Library" sheetId="7" r:id="R2b735d1032b646c6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Papers" sheetId="1" r:id="Rd4ae01dd80cd4d8c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rejected" sheetId="2" r:id="R045ebd6a5fb24004"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Venues" sheetId="3" r:id="R255adb3d1f524f1a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Keywords" sheetId="4" r:id="Rd38c8746b1a14fab"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Discovery" sheetId="5" r:id="Rf744afbc81b541c0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CCF_A_Library" sheetId="6" r:id="Rf53b9c3f8f264abb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Robotics_Core_Library" sheetId="7" r:id="R34449d90d2e84a8a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="20" name="PapersTable" displayName="PapersTable" ref="A1:AZ5" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:tableColumns count="52">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="24" name="PapersTable" displayName="PapersTable" ref="A1:BD5" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:tableColumns count="56">
     <x:tableColumn id="1" name="编号 ID"/>
     <x:tableColumn id="2" name="论文标题 Title"/>
     <x:tableColumn id="3" name="年份 Year"/>
@@ -354,6 +354,10 @@
     <x:tableColumn id="50" name="Failure Cases"/>
     <x:tableColumn id="51" name="Citation Source Identifier"/>
     <x:tableColumn id="52" name="Evidence Sources"/>
+    <x:tableColumn id="53" name="Evidence Upgrade Status"/>
+    <x:tableColumn id="54" name="Supplement Status"/>
+    <x:tableColumn id="55" name="Code Completeness"/>
+    <x:tableColumn id="56" name="Robot Platform Evidence"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
@@ -405,8 +409,8 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="21" name="DiscoveryTable" displayName="DiscoveryTable" ref="A1:AU79" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:tableColumns count="47">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="25" name="DiscoveryTable" displayName="DiscoveryTable" ref="A1:AY79" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:tableColumns count="51">
     <x:tableColumn id="1" name="编号 ID"/>
     <x:tableColumn id="2" name="论文标题 Title"/>
     <x:tableColumn id="3" name="年份 Year"/>
@@ -454,14 +458,18 @@
     <x:tableColumn id="45" name="Failure Cases"/>
     <x:tableColumn id="46" name="Citation Source Identifier"/>
     <x:tableColumn id="47" name="Evidence Sources"/>
+    <x:tableColumn id="48" name="Evidence Upgrade Status"/>
+    <x:tableColumn id="49" name="Supplement Status"/>
+    <x:tableColumn id="50" name="Code Completeness"/>
+    <x:tableColumn id="51" name="Robot Platform Evidence"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="22" name="CCFALibraryTable" displayName="CCFALibraryTable" ref="A1:BN67" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:tableColumns count="66">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="26" name="CCFALibraryTable" displayName="CCFALibraryTable" ref="A1:BR67" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:tableColumns count="70">
     <x:tableColumn id="1" name="编号 ID"/>
     <x:tableColumn id="2" name="论文标题 Title"/>
     <x:tableColumn id="3" name="作者 Authors"/>
@@ -528,14 +536,18 @@
     <x:tableColumn id="64" name="Failure Cases"/>
     <x:tableColumn id="65" name="Citation Source Identifier"/>
     <x:tableColumn id="66" name="Evidence Sources"/>
+    <x:tableColumn id="67" name="Evidence Upgrade Status"/>
+    <x:tableColumn id="68" name="Supplement Status"/>
+    <x:tableColumn id="69" name="Code Completeness"/>
+    <x:tableColumn id="70" name="Robot Platform Evidence"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="23" name="RoboticsCoreLibraryTable" displayName="RoboticsCoreLibraryTable" ref="A1:BC14" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:tableColumns count="55">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="27" name="RoboticsCoreLibraryTable" displayName="RoboticsCoreLibraryTable" ref="A1:BG14" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:tableColumns count="59">
     <x:tableColumn id="1" name="ID"/>
     <x:tableColumn id="2" name="Title"/>
     <x:tableColumn id="3" name="Authors"/>
@@ -591,6 +603,10 @@
     <x:tableColumn id="53" name="Failure Cases"/>
     <x:tableColumn id="54" name="Citation Source Identifier"/>
     <x:tableColumn id="55" name="Evidence Sources"/>
+    <x:tableColumn id="56" name="Evidence Upgrade Status"/>
+    <x:tableColumn id="57" name="Supplement Status"/>
+    <x:tableColumn id="58" name="Code Completeness"/>
+    <x:tableColumn id="59" name="Robot Platform Evidence"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium4" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
@@ -981,6 +997,18 @@
       <x:c r="AZ1" t="str">
         <x:v>Evidence Sources</x:v>
       </x:c>
+      <x:c r="BA1" t="str">
+        <x:v>Evidence Upgrade Status</x:v>
+      </x:c>
+      <x:c r="BB1" t="str">
+        <x:v>Supplement Status</x:v>
+      </x:c>
+      <x:c r="BC1" t="str">
+        <x:v>Code Completeness</x:v>
+      </x:c>
+      <x:c r="BD1" t="str">
+        <x:v>Robot Platform Evidence</x:v>
+      </x:c>
     </x:row>
     <x:row r="2" ht="350" customHeight="1">
       <x:c r="A2" t="str">
@@ -1137,6 +1165,18 @@
       </x:c>
       <x:c r="AZ2" t="str">
         <x:v>https://openaccess.thecvf.com/content/CVPR2024/html/Li_ManipLLM_Embodied_Multimodal_Large_Language_Model_for_Object-Centric_Robotic_Manipulation_CVPR_2024_paper.html；官方摘要/论文集元数据</x:v>
+      </x:c>
+      <x:c r="BA2" t="str">
+        <x:v>A-Upgraded</x:v>
+      </x:c>
+      <x:c r="BB2" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="BC2" t="str">
+        <x:v>Partial</x:v>
+      </x:c>
+      <x:c r="BD2" t="str">
+        <x:v>Unknown</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="150" customHeight="1">
@@ -1264,6 +1304,18 @@
       <x:c r="AZ3" t="str">
         <x:v>https://openaccess.thecvf.com/content/CVPR2025/html/Li_ManipTrans_Efficient_Dexterous_Bimanual_Manipulation_Transfer_via_Residual_Learning_CVPR_2025_paper.html；官方摘要/论文集元数据</x:v>
       </x:c>
+      <x:c r="BA3" t="str">
+        <x:v>B-Fulltext-Unavailable</x:v>
+      </x:c>
+      <x:c r="BB3" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="BC3" t="str">
+        <x:v>Mostly Complete</x:v>
+      </x:c>
+      <x:c r="BD3" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="4" ht="150" customHeight="1">
       <x:c r="A4" t="str">
@@ -1390,6 +1442,18 @@
       <x:c r="AZ4" t="str">
         <x:v>https://openaccess.thecvf.com/content/CVPR2025/html/Liang_DexHandDiff_Interaction-aware_Diffusion_Planning_for_Adaptive_Dexterous_Manipulation_CVPR_2025_paper.html; https://dexdiffuser.github.io/; https://github.com/Liang-</x:v>
       </x:c>
+      <x:c r="BA4" t="str">
+        <x:v>B-Fulltext-Unavailable</x:v>
+      </x:c>
+      <x:c r="BB4" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="BC4" t="str">
+        <x:v>Partial</x:v>
+      </x:c>
+      <x:c r="BD4" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="5" ht="150" customHeight="1">
       <x:c r="A5" t="str">
@@ -1515,6 +1579,18 @@
       </x:c>
       <x:c r="AZ5" t="str">
         <x:v>https://openaccess.thecvf.com/content/ICCV2025/html/Yang_AR-VRM_Imitating_Human_Motions_for_Visual_Robot_Manipulation_with_Analogical_ICCV_2025_paper.html；官方摘要/论文集元数据</x:v>
+      </x:c>
+      <x:c r="BA5" t="str">
+        <x:v>B-Fulltext-Unavailable</x:v>
+      </x:c>
+      <x:c r="BB5" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="BC5" t="str">
+        <x:v>Mostly Complete</x:v>
+      </x:c>
+      <x:c r="BD5" t="str">
+        <x:v>Unknown</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -4528,7 +4604,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9f40b01cc37a4f7d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdb6b3e8902a14813"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7824,7 +7900,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf782efb0e6bf495e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re0c56d1d9f95448a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8175,7 +8251,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbd847cc0db2e4d6b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9556a8be6dfd4281"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8921,7 +8997,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re26aaa9f1a724d70"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re8cc26495f454170"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9103,6 +9179,18 @@
       <x:c r="AU1" t="str">
         <x:v>Evidence Sources</x:v>
       </x:c>
+      <x:c r="AV1" t="str">
+        <x:v>Evidence Upgrade Status</x:v>
+      </x:c>
+      <x:c r="AW1" t="str">
+        <x:v>Supplement Status</x:v>
+      </x:c>
+      <x:c r="AX1" t="str">
+        <x:v>Code Completeness</x:v>
+      </x:c>
+      <x:c r="AY1" t="str">
+        <x:v>Robot Platform Evidence</x:v>
+      </x:c>
     </x:row>
     <x:row r="2" ht="58" customHeight="1">
       <x:c r="A2" t="str">
@@ -9238,6 +9326,18 @@
       <x:c r="AU2" t="str">
         <x:v>https://openaccess.thecvf.com/content/CVPR2024/html/Ma_Hierarchical_Diffusion_Policy_for_Kinematics-Aware_Multi-Task_Robotic_Manipulation_CVPR_2024_paper.html；官方摘要/论文集元数据</x:v>
       </x:c>
+      <x:c r="AV2" t="str">
+        <x:v>B-Fulltext-Unavailable</x:v>
+      </x:c>
+      <x:c r="AW2" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="AX2" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AY2" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="3" ht="58" customHeight="1">
       <x:c r="A3" t="str">
@@ -9373,6 +9473,18 @@
       <x:c r="AU3" t="str">
         <x:v>https://openaccess.thecvf.com/content/ICCV2025/html/Jiang_Rethinking_Bimanual_Robotic_Manipulation_Learning_with_Decoupled_Interaction_Framework_ICCV_2025_paper.html；官方摘要/论文集元数据</x:v>
       </x:c>
+      <x:c r="AV3" t="str">
+        <x:v>B-Fulltext-Unavailable</x:v>
+      </x:c>
+      <x:c r="AW3" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="AX3" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AY3" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="4" ht="58" customHeight="1">
       <x:c r="A4" t="str">
@@ -9508,6 +9620,18 @@
       <x:c r="AU4" t="str">
         <x:v>https://openaccess.thecvf.com/content/ICCV2025/html/Xu_Diffusion-Based_Imaginative_Coordination_for_Bimanual_Manipulation_ICCV_2025_paper.html；官方摘要/论文集元数据</x:v>
       </x:c>
+      <x:c r="AV4" t="str">
+        <x:v>B-Fulltext-Unavailable</x:v>
+      </x:c>
+      <x:c r="AW4" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="AX4" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AY4" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="5" ht="58" customHeight="1">
       <x:c r="A5" t="str">
@@ -9645,6 +9769,18 @@
       <x:c r="AU5" t="str">
         <x:v>Unknown</x:v>
       </x:c>
+      <x:c r="AV5" t="str">
+        <x:v>B-Fulltext-Unavailable</x:v>
+      </x:c>
+      <x:c r="AW5" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="AX5" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AY5" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="6" ht="58" customHeight="1">
       <x:c r="A6" t="str">
@@ -9780,6 +9916,18 @@
       <x:c r="AU6" t="str">
         <x:v>Unknown</x:v>
       </x:c>
+      <x:c r="AV6" t="str">
+        <x:v>B-Fulltext-Unavailable</x:v>
+      </x:c>
+      <x:c r="AW6" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="AX6" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AY6" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="7" ht="58" customHeight="1">
       <x:c r="A7" t="str">
@@ -9915,6 +10063,18 @@
       <x:c r="AU7" t="str">
         <x:v>Unknown</x:v>
       </x:c>
+      <x:c r="AV7" t="str">
+        <x:v>B-Fulltext-Unavailable</x:v>
+      </x:c>
+      <x:c r="AW7" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="AX7" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AY7" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="8" ht="58" customHeight="1">
       <x:c r="A8" t="str">
@@ -10048,6 +10208,18 @@
       <x:c r="AU8" t="str">
         <x:v>Unknown</x:v>
       </x:c>
+      <x:c r="AV8" t="str">
+        <x:v>B-Fulltext-Unavailable</x:v>
+      </x:c>
+      <x:c r="AW8" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="AX8" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AY8" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="9" ht="58" customHeight="1">
       <x:c r="A9" t="str">
@@ -10183,6 +10355,18 @@
       <x:c r="AU9" t="str">
         <x:v>Unknown</x:v>
       </x:c>
+      <x:c r="AV9" t="str">
+        <x:v>B-Fulltext-Unavailable</x:v>
+      </x:c>
+      <x:c r="AW9" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="AX9" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AY9" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="10" ht="58" customHeight="1">
       <x:c r="A10" t="str">
@@ -10316,6 +10500,18 @@
       <x:c r="AU10" t="str">
         <x:v>Unknown</x:v>
       </x:c>
+      <x:c r="AV10" t="str">
+        <x:v>B-Fulltext-Unavailable</x:v>
+      </x:c>
+      <x:c r="AW10" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="AX10" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AY10" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="11" ht="58" customHeight="1">
       <x:c r="A11" t="str">
@@ -10453,6 +10649,18 @@
       <x:c r="AU11" t="str">
         <x:v>Unknown</x:v>
       </x:c>
+      <x:c r="AV11" t="str">
+        <x:v>B-Fulltext-Unavailable</x:v>
+      </x:c>
+      <x:c r="AW11" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="AX11" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AY11" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="12" ht="58" customHeight="1">
       <x:c r="A12" t="str">
@@ -10588,6 +10796,18 @@
         <x:v>Unknown (no high-confidence match)</x:v>
       </x:c>
       <x:c r="AU12" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AV12" t="str">
+        <x:v>B-Fulltext-Unavailable</x:v>
+      </x:c>
+      <x:c r="AW12" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="AX12" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AY12" t="str">
         <x:v>Unknown</x:v>
       </x:c>
     </x:row>
@@ -10727,6 +10947,18 @@
       <x:c r="AU13" t="str">
         <x:v>Unknown</x:v>
       </x:c>
+      <x:c r="AV13" t="str">
+        <x:v>B-Fulltext-Unavailable</x:v>
+      </x:c>
+      <x:c r="AW13" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="AX13" t="str">
+        <x:v>Mostly Complete</x:v>
+      </x:c>
+      <x:c r="AY13" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="14" ht="58" customHeight="1">
       <x:c r="A14" t="str">
@@ -10862,6 +11094,18 @@
       <x:c r="AU14" t="str">
         <x:v>Unknown</x:v>
       </x:c>
+      <x:c r="AV14" t="str">
+        <x:v>B-Fulltext-Unavailable</x:v>
+      </x:c>
+      <x:c r="AW14" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="AX14" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AY14" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="15" ht="58" customHeight="1">
       <x:c r="A15" t="str">
@@ -10997,6 +11241,18 @@
         <x:v>Unknown (no high-confidence match)</x:v>
       </x:c>
       <x:c r="AU15" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AV15" t="str">
+        <x:v>B-Fulltext-Unavailable</x:v>
+      </x:c>
+      <x:c r="AW15" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="AX15" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AY15" t="str">
         <x:v>Unknown</x:v>
       </x:c>
     </x:row>
@@ -11132,6 +11388,18 @@
       <x:c r="AU16" t="str">
         <x:v>Unknown</x:v>
       </x:c>
+      <x:c r="AV16" t="str">
+        <x:v>B-Fulltext-Unavailable</x:v>
+      </x:c>
+      <x:c r="AW16" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="AX16" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AY16" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="17" ht="58" customHeight="1">
       <x:c r="A17" t="str">
@@ -11265,6 +11533,18 @@
       <x:c r="AU17" t="str">
         <x:v>Unknown</x:v>
       </x:c>
+      <x:c r="AV17" t="str">
+        <x:v>B-Fulltext-Unavailable</x:v>
+      </x:c>
+      <x:c r="AW17" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="AX17" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AY17" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="18" ht="58" customHeight="1">
       <x:c r="A18" t="str">
@@ -11398,6 +11678,18 @@
       <x:c r="AU18" t="str">
         <x:v>Unknown</x:v>
       </x:c>
+      <x:c r="AV18" t="str">
+        <x:v>B-Fulltext-Unavailable</x:v>
+      </x:c>
+      <x:c r="AW18" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="AX18" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AY18" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="19" ht="58" customHeight="1">
       <x:c r="A19" t="str">
@@ -11533,6 +11825,18 @@
       <x:c r="AU19" t="str">
         <x:v>Unknown</x:v>
       </x:c>
+      <x:c r="AV19" t="str">
+        <x:v>B-Fulltext-Unavailable</x:v>
+      </x:c>
+      <x:c r="AW19" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="AX19" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AY19" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="20" ht="58" customHeight="1">
       <x:c r="A20" t="str">
@@ -11666,6 +11970,18 @@
       <x:c r="AU20" t="str">
         <x:v>Unknown</x:v>
       </x:c>
+      <x:c r="AV20" t="str">
+        <x:v>B-Fulltext-Unavailable</x:v>
+      </x:c>
+      <x:c r="AW20" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="AX20" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AY20" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="21" ht="58" customHeight="1">
       <x:c r="A21" t="str">
@@ -11801,6 +12117,18 @@
       <x:c r="AU21" t="str">
         <x:v>https://ojs.aaai.org/index.php/AAAI/article/view/38889；官方摘要/论文集元数据</x:v>
       </x:c>
+      <x:c r="AV21" t="str">
+        <x:v>B-Fulltext-Unavailable</x:v>
+      </x:c>
+      <x:c r="AW21" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="AX21" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AY21" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="22" ht="58" customHeight="1">
       <x:c r="A22" t="str">
@@ -11936,6 +12264,18 @@
       <x:c r="AU22" t="str">
         <x:v>https://ojs.aaai.org/index.php/AAAI/article/view/38911；官方摘要/论文集元数据</x:v>
       </x:c>
+      <x:c r="AV22" t="str">
+        <x:v>B-Fulltext-Unavailable</x:v>
+      </x:c>
+      <x:c r="AW22" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="AX22" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AY22" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="23" ht="58" customHeight="1">
       <x:c r="A23" t="str">
@@ -12071,6 +12411,18 @@
       <x:c r="AU23" t="str">
         <x:v>https://ojs.aaai.org/index.php/AAAI/article/view/38955；官方摘要/论文集元数据</x:v>
       </x:c>
+      <x:c r="AV23" t="str">
+        <x:v>B-Fulltext-Unavailable</x:v>
+      </x:c>
+      <x:c r="AW23" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="AX23" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AY23" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="24" ht="58" customHeight="1">
       <x:c r="A24" t="str">
@@ -12206,6 +12558,18 @@
       <x:c r="AU24" t="str">
         <x:v>https://ojs.aaai.org/index.php/AAAI/article/view/38539；官方摘要/论文集元数据</x:v>
       </x:c>
+      <x:c r="AV24" t="str">
+        <x:v>B-Fulltext-Unavailable</x:v>
+      </x:c>
+      <x:c r="AW24" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="AX24" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AY24" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="25" ht="58" customHeight="1">
       <x:c r="A25" t="str">
@@ -12339,6 +12703,18 @@
       <x:c r="AU25" t="str">
         <x:v>https://ojs.aaai.org/index.php/AAAI/article/download/38892/42854；官方摘要/论文集元数据</x:v>
       </x:c>
+      <x:c r="AV25" t="str">
+        <x:v>B-Fulltext-Unavailable</x:v>
+      </x:c>
+      <x:c r="AW25" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="AX25" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AY25" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="26" ht="58" customHeight="1">
       <x:c r="A26" t="str">
@@ -12474,6 +12850,18 @@
       <x:c r="AU26" t="str">
         <x:v>Unknown</x:v>
       </x:c>
+      <x:c r="AV26" t="str">
+        <x:v>B-Fulltext-Unavailable</x:v>
+      </x:c>
+      <x:c r="AW26" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="AX26" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AY26" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="27" ht="58" customHeight="1">
       <x:c r="A27" t="str">
@@ -12609,6 +12997,18 @@
       <x:c r="AU27" t="str">
         <x:v>Unknown</x:v>
       </x:c>
+      <x:c r="AV27" t="str">
+        <x:v>B-Fulltext-Unavailable</x:v>
+      </x:c>
+      <x:c r="AW27" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="AX27" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AY27" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="28" ht="58" customHeight="1">
       <x:c r="A28" t="str">
@@ -12744,6 +13144,18 @@
       <x:c r="AU28" t="str">
         <x:v>https://proceedings.mlr.press/v270/</x:v>
       </x:c>
+      <x:c r="AV28" t="str">
+        <x:v>B-Fulltext-Unavailable</x:v>
+      </x:c>
+      <x:c r="AW28" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="AX28" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AY28" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="29" ht="58" customHeight="1">
       <x:c r="A29" t="str">
@@ -12879,6 +13291,18 @@
       <x:c r="AU29" t="str">
         <x:v>Unknown</x:v>
       </x:c>
+      <x:c r="AV29" t="str">
+        <x:v>B-Fulltext-Unavailable</x:v>
+      </x:c>
+      <x:c r="AW29" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="AX29" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AY29" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="30" ht="58" customHeight="1">
       <x:c r="A30" t="str">
@@ -13014,6 +13438,18 @@
       <x:c r="AU30" t="str">
         <x:v>Unknown</x:v>
       </x:c>
+      <x:c r="AV30" t="str">
+        <x:v>B-Fulltext-Unavailable</x:v>
+      </x:c>
+      <x:c r="AW30" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="AX30" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AY30" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="31" ht="58" customHeight="1">
       <x:c r="A31" t="str">
@@ -13149,6 +13585,18 @@
       <x:c r="AU31" t="str">
         <x:v>Unknown</x:v>
       </x:c>
+      <x:c r="AV31" t="str">
+        <x:v>B-Fulltext-Unavailable</x:v>
+      </x:c>
+      <x:c r="AW31" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="AX31" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AY31" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="32" ht="58" customHeight="1">
       <x:c r="A32" t="str">
@@ -13284,6 +13732,18 @@
       <x:c r="AU32" t="str">
         <x:v>Unknown</x:v>
       </x:c>
+      <x:c r="AV32" t="str">
+        <x:v>B-Fulltext-Unavailable</x:v>
+      </x:c>
+      <x:c r="AW32" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="AX32" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AY32" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="33" ht="58" customHeight="1">
       <x:c r="A33" t="str">
@@ -13419,6 +13879,18 @@
       <x:c r="AU33" t="str">
         <x:v>Unknown</x:v>
       </x:c>
+      <x:c r="AV33" t="str">
+        <x:v>B-Fulltext-Unavailable</x:v>
+      </x:c>
+      <x:c r="AW33" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="AX33" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AY33" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="34" ht="58" customHeight="1">
       <x:c r="A34" t="str">
@@ -13554,6 +14026,18 @@
       <x:c r="AU34" t="str">
         <x:v>Unknown</x:v>
       </x:c>
+      <x:c r="AV34" t="str">
+        <x:v>B-Fulltext-Unavailable</x:v>
+      </x:c>
+      <x:c r="AW34" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="AX34" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AY34" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="35" ht="58" customHeight="1">
       <x:c r="A35" t="str">
@@ -13689,6 +14173,18 @@
       <x:c r="AU35" t="str">
         <x:v>Unknown</x:v>
       </x:c>
+      <x:c r="AV35" t="str">
+        <x:v>B-Fulltext-Unavailable</x:v>
+      </x:c>
+      <x:c r="AW35" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="AX35" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AY35" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="36" ht="58" customHeight="1">
       <x:c r="A36" t="str">
@@ -13824,6 +14320,18 @@
       <x:c r="AU36" t="str">
         <x:v>Unknown</x:v>
       </x:c>
+      <x:c r="AV36" t="str">
+        <x:v>B-Fulltext-Unavailable</x:v>
+      </x:c>
+      <x:c r="AW36" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="AX36" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AY36" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="37" ht="58" customHeight="1">
       <x:c r="A37" t="str">
@@ -13959,6 +14467,18 @@
       <x:c r="AU37" t="str">
         <x:v>Unknown</x:v>
       </x:c>
+      <x:c r="AV37" t="str">
+        <x:v>B-Fulltext-Unavailable</x:v>
+      </x:c>
+      <x:c r="AW37" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="AX37" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AY37" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="38" ht="58" customHeight="1">
       <x:c r="A38" t="str">
@@ -14094,6 +14614,18 @@
       <x:c r="AU38" t="str">
         <x:v>Unknown</x:v>
       </x:c>
+      <x:c r="AV38" t="str">
+        <x:v>B-Fulltext-Unavailable</x:v>
+      </x:c>
+      <x:c r="AW38" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="AX38" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AY38" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="39" ht="58" customHeight="1">
       <x:c r="A39" t="str">
@@ -14229,6 +14761,18 @@
       <x:c r="AU39" t="str">
         <x:v>https://proceedings.mlr.press/v270/</x:v>
       </x:c>
+      <x:c r="AV39" t="str">
+        <x:v>B-Fulltext-Unavailable</x:v>
+      </x:c>
+      <x:c r="AW39" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="AX39" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AY39" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="40" ht="58" customHeight="1">
       <x:c r="A40" t="str">
@@ -14362,6 +14906,18 @@
       <x:c r="AU40" t="str">
         <x:v>Unknown</x:v>
       </x:c>
+      <x:c r="AV40" t="str">
+        <x:v>B-Fulltext-Unavailable</x:v>
+      </x:c>
+      <x:c r="AW40" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="AX40" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AY40" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="41" ht="58" customHeight="1">
       <x:c r="A41" t="str">
@@ -14495,6 +15051,18 @@
       <x:c r="AU41" t="str">
         <x:v>Unknown</x:v>
       </x:c>
+      <x:c r="AV41" t="str">
+        <x:v>B-Fulltext-Unavailable</x:v>
+      </x:c>
+      <x:c r="AW41" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="AX41" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AY41" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="42" ht="58" customHeight="1">
       <x:c r="A42" t="str">
@@ -14628,6 +15196,18 @@
       <x:c r="AU42" t="str">
         <x:v>Unknown</x:v>
       </x:c>
+      <x:c r="AV42" t="str">
+        <x:v>B-Fulltext-Unavailable</x:v>
+      </x:c>
+      <x:c r="AW42" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="AX42" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AY42" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="43" ht="58" customHeight="1">
       <x:c r="A43" t="str">
@@ -14761,6 +15341,18 @@
       <x:c r="AU43" t="str">
         <x:v>Unknown</x:v>
       </x:c>
+      <x:c r="AV43" t="str">
+        <x:v>B-Fulltext-Unavailable</x:v>
+      </x:c>
+      <x:c r="AW43" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="AX43" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AY43" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="44" ht="58" customHeight="1">
       <x:c r="A44" t="str">
@@ -14894,6 +15486,18 @@
       <x:c r="AU44" t="str">
         <x:v>Unknown</x:v>
       </x:c>
+      <x:c r="AV44" t="str">
+        <x:v>B-Fulltext-Unavailable</x:v>
+      </x:c>
+      <x:c r="AW44" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="AX44" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AY44" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="45" ht="58" customHeight="1">
       <x:c r="A45" t="str">
@@ -15027,6 +15631,18 @@
       <x:c r="AU45" t="str">
         <x:v>Unknown</x:v>
       </x:c>
+      <x:c r="AV45" t="str">
+        <x:v>B-Fulltext-Unavailable</x:v>
+      </x:c>
+      <x:c r="AW45" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="AX45" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AY45" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="46" ht="58" customHeight="1">
       <x:c r="A46" t="str">
@@ -15162,6 +15778,18 @@
       <x:c r="AU46" t="str">
         <x:v>Unknown</x:v>
       </x:c>
+      <x:c r="AV46" t="str">
+        <x:v>B-Fulltext-Unavailable</x:v>
+      </x:c>
+      <x:c r="AW46" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="AX46" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AY46" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="47" ht="58" customHeight="1">
       <x:c r="A47" t="str">
@@ -15297,6 +15925,18 @@
       <x:c r="AU47" t="str">
         <x:v>Unknown</x:v>
       </x:c>
+      <x:c r="AV47" t="str">
+        <x:v>B-Fulltext-Unavailable</x:v>
+      </x:c>
+      <x:c r="AW47" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="AX47" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AY47" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="48" ht="58" customHeight="1">
       <x:c r="A48" t="str">
@@ -15432,6 +16072,18 @@
       <x:c r="AU48" t="str">
         <x:v>Unknown</x:v>
       </x:c>
+      <x:c r="AV48" t="str">
+        <x:v>B-Fulltext-Unavailable</x:v>
+      </x:c>
+      <x:c r="AW48" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="AX48" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AY48" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="49" ht="58" customHeight="1">
       <x:c r="A49" t="str">
@@ -15567,6 +16219,18 @@
       <x:c r="AU49" t="str">
         <x:v>Unknown</x:v>
       </x:c>
+      <x:c r="AV49" t="str">
+        <x:v>B-Fulltext-Unavailable</x:v>
+      </x:c>
+      <x:c r="AW49" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="AX49" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AY49" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="50" ht="58" customHeight="1">
       <x:c r="A50" t="str">
@@ -15702,6 +16366,18 @@
       <x:c r="AU50" t="str">
         <x:v>Unknown</x:v>
       </x:c>
+      <x:c r="AV50" t="str">
+        <x:v>B-Fulltext-Unavailable</x:v>
+      </x:c>
+      <x:c r="AW50" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="AX50" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AY50" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="51" ht="58" customHeight="1">
       <x:c r="A51" t="str">
@@ -15837,6 +16513,18 @@
       <x:c r="AU51" t="str">
         <x:v>Unknown</x:v>
       </x:c>
+      <x:c r="AV51" t="str">
+        <x:v>B-Fulltext-Unavailable</x:v>
+      </x:c>
+      <x:c r="AW51" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="AX51" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AY51" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="52" ht="58" customHeight="1">
       <x:c r="A52" t="str">
@@ -15972,6 +16660,18 @@
       <x:c r="AU52" t="str">
         <x:v>Unknown</x:v>
       </x:c>
+      <x:c r="AV52" t="str">
+        <x:v>B-Fulltext-Unavailable</x:v>
+      </x:c>
+      <x:c r="AW52" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="AX52" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AY52" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="53" ht="58" customHeight="1">
       <x:c r="A53" t="str">
@@ -16107,6 +16807,18 @@
       <x:c r="AU53" t="str">
         <x:v>Unknown</x:v>
       </x:c>
+      <x:c r="AV53" t="str">
+        <x:v>B-Fulltext-Unavailable</x:v>
+      </x:c>
+      <x:c r="AW53" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="AX53" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AY53" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="54" ht="58" customHeight="1">
       <x:c r="A54" t="str">
@@ -16242,6 +16954,18 @@
       <x:c r="AU54" t="str">
         <x:v>Unknown</x:v>
       </x:c>
+      <x:c r="AV54" t="str">
+        <x:v>B-Fulltext-Unavailable</x:v>
+      </x:c>
+      <x:c r="AW54" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="AX54" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AY54" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="55" ht="58" customHeight="1">
       <x:c r="A55" t="str">
@@ -16377,6 +17101,18 @@
       <x:c r="AU55" t="str">
         <x:v>Unknown</x:v>
       </x:c>
+      <x:c r="AV55" t="str">
+        <x:v>B-Fulltext-Unavailable</x:v>
+      </x:c>
+      <x:c r="AW55" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="AX55" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AY55" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="56" ht="58" customHeight="1">
       <x:c r="A56" t="str">
@@ -16512,6 +17248,18 @@
       <x:c r="AU56" t="str">
         <x:v>Unknown</x:v>
       </x:c>
+      <x:c r="AV56" t="str">
+        <x:v>B-Fulltext-Unavailable</x:v>
+      </x:c>
+      <x:c r="AW56" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="AX56" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AY56" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="57" ht="58" customHeight="1">
       <x:c r="A57" t="str">
@@ -16647,6 +17395,18 @@
       <x:c r="AU57" t="str">
         <x:v>Unknown</x:v>
       </x:c>
+      <x:c r="AV57" t="str">
+        <x:v>B-Fulltext-Unavailable</x:v>
+      </x:c>
+      <x:c r="AW57" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="AX57" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AY57" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="58" ht="58" customHeight="1">
       <x:c r="A58" t="str">
@@ -16788,6 +17548,18 @@
       <x:c r="AU58" t="str">
         <x:v>Unknown</x:v>
       </x:c>
+      <x:c r="AV58" t="str">
+        <x:v>B-Fulltext-Unavailable</x:v>
+      </x:c>
+      <x:c r="AW58" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="AX58" t="str">
+        <x:v>Mostly Complete</x:v>
+      </x:c>
+      <x:c r="AY58" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="59" ht="58" customHeight="1">
       <x:c r="A59" t="str">
@@ -16929,6 +17701,18 @@
       <x:c r="AU59" t="str">
         <x:v>Unknown</x:v>
       </x:c>
+      <x:c r="AV59" t="str">
+        <x:v>B-Fulltext-Unavailable</x:v>
+      </x:c>
+      <x:c r="AW59" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="AX59" t="str">
+        <x:v>Mostly Complete</x:v>
+      </x:c>
+      <x:c r="AY59" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="60" ht="58" customHeight="1">
       <x:c r="A60" t="str">
@@ -17068,6 +17852,18 @@
       <x:c r="AU60" t="str">
         <x:v>https://openaccess.thecvf.com/content/CVPR2025/html/Mu_RoboTwin_Dual-Arm_Robot_Benchmark_with_Generative_Digital_Twins_CVPR_2025_paper.html；官方摘要/论文集元数据</x:v>
       </x:c>
+      <x:c r="AV60" t="str">
+        <x:v>B-Fulltext-Unavailable</x:v>
+      </x:c>
+      <x:c r="AW60" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="AX60" t="str">
+        <x:v>Mostly Complete</x:v>
+      </x:c>
+      <x:c r="AY60" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="61" ht="58" customHeight="1">
       <x:c r="A61" t="str">
@@ -17209,6 +18005,18 @@
       <x:c r="AU61" t="str">
         <x:v>https://proceedings.neurips.cc/paper_files/paper/2025/hash/5c1a8aa04c1a2cf5013f28831870dafa-Abstract-Conference.html；官方摘要/论文集元数据</x:v>
       </x:c>
+      <x:c r="AV61" t="str">
+        <x:v>B-Fulltext-Unavailable</x:v>
+      </x:c>
+      <x:c r="AW61" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="AX61" t="str">
+        <x:v>Mostly Complete</x:v>
+      </x:c>
+      <x:c r="AY61" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="62" ht="58" customHeight="1">
       <x:c r="A62" t="str">
@@ -17350,6 +18158,18 @@
       <x:c r="AU62" t="str">
         <x:v>https://proceedings.neurips.cc/paper_files/paper/2025/hash/f062da1973ac9ac61fc6d44dd7fa309f-Abstract-Conference.html；官方摘要/论文集元数据</x:v>
       </x:c>
+      <x:c r="AV62" t="str">
+        <x:v>B-Fulltext-Unavailable</x:v>
+      </x:c>
+      <x:c r="AW62" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="AX62" t="str">
+        <x:v>Mostly Complete</x:v>
+      </x:c>
+      <x:c r="AY62" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="63" ht="58" customHeight="1">
       <x:c r="A63" t="str">
@@ -17491,6 +18311,18 @@
       <x:c r="AU63" t="str">
         <x:v>https://proceedings.mlr.press/v267/wen25g.html；官方摘要/论文集元数据</x:v>
       </x:c>
+      <x:c r="AV63" t="str">
+        <x:v>B-Fulltext-Unavailable</x:v>
+      </x:c>
+      <x:c r="AW63" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="AX63" t="str">
+        <x:v>Partial</x:v>
+      </x:c>
+      <x:c r="AY63" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="64" ht="58" customHeight="1">
       <x:c r="A64" t="str">
@@ -17632,6 +18464,18 @@
       <x:c r="AU64" t="str">
         <x:v>https://proceedings.mlr.press/v235/zhen24a.html；官方摘要/论文集元数据</x:v>
       </x:c>
+      <x:c r="AV64" t="str">
+        <x:v>B-Fulltext-Unavailable</x:v>
+      </x:c>
+      <x:c r="AW64" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="AX64" t="str">
+        <x:v>Partial</x:v>
+      </x:c>
+      <x:c r="AY64" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="65" ht="58" customHeight="1">
       <x:c r="A65" t="str">
@@ -17773,6 +18617,18 @@
       <x:c r="AU65" t="str">
         <x:v>https://proceedings.neurips.cc/paper_files/paper/2024/hash/46a126492ea6fb87410e55a58df2e189-Abstract-Conference.html; https://sites.google.com/view/robomamba-web; https://github.com/lm</x:v>
       </x:c>
+      <x:c r="AV65" t="str">
+        <x:v>B-Fulltext-Unavailable</x:v>
+      </x:c>
+      <x:c r="AW65" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="AX65" t="str">
+        <x:v>Partial</x:v>
+      </x:c>
+      <x:c r="AY65" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="66" ht="58" customHeight="1">
       <x:c r="A66" t="str">
@@ -17914,6 +18770,18 @@
       <x:c r="AU66" t="str">
         <x:v>Unknown</x:v>
       </x:c>
+      <x:c r="AV66" t="str">
+        <x:v>B-Fulltext-Unavailable</x:v>
+      </x:c>
+      <x:c r="AW66" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="AX66" t="str">
+        <x:v>Partial</x:v>
+      </x:c>
+      <x:c r="AY66" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="67" ht="58" customHeight="1">
       <x:c r="A67" t="str">
@@ -18053,6 +18921,18 @@
         <x:v>Unknown (no high-confidence match)</x:v>
       </x:c>
       <x:c r="AU67" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AV67" t="str">
+        <x:v>B-Fulltext-Unavailable</x:v>
+      </x:c>
+      <x:c r="AW67" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="AX67" t="str">
+        <x:v>Mostly Complete</x:v>
+      </x:c>
+      <x:c r="AY67" t="str">
         <x:v>Unknown</x:v>
       </x:c>
     </x:row>
@@ -18194,6 +19074,18 @@
       <x:c r="AU68" t="str">
         <x:v>https://ojs.aaai.org/index.php/AAAI/article/view/33617; https://github.com/</x:v>
       </x:c>
+      <x:c r="AV68" t="str">
+        <x:v>B-Fulltext-Unavailable</x:v>
+      </x:c>
+      <x:c r="AW68" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="AX68" t="str">
+        <x:v>Mostly Complete</x:v>
+      </x:c>
+      <x:c r="AY68" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="69" ht="58" customHeight="1">
       <x:c r="A69" t="str">
@@ -18335,6 +19227,18 @@
       <x:c r="AU69" t="str">
         <x:v>https://openaccess.thecvf.com/content/CVPR2025/html/Wang_UniGraspTransformer_Simplified_Policy_Distillation_for_Scalable_Dexterous_Robotic_Grasping_CVPR_2025_paper.html；官方摘要/论文集元数据</x:v>
       </x:c>
+      <x:c r="AV69" t="str">
+        <x:v>B-Fulltext-Unavailable</x:v>
+      </x:c>
+      <x:c r="AW69" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="AX69" t="str">
+        <x:v>Mostly Complete</x:v>
+      </x:c>
+      <x:c r="AY69" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="70" ht="58" customHeight="1">
       <x:c r="A70" t="str">
@@ -18476,6 +19380,18 @@
       <x:c r="AU70" t="str">
         <x:v>https://proceedings.neurips.cc/paper_files/paper/2025/hash/862644b156e51c35dea5a7446d640b14-Abstract-Conference.html；官方摘要/论文集元数据</x:v>
       </x:c>
+      <x:c r="AV70" t="str">
+        <x:v>B-Fulltext-Unavailable</x:v>
+      </x:c>
+      <x:c r="AW70" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="AX70" t="str">
+        <x:v>Mostly Complete</x:v>
+      </x:c>
+      <x:c r="AY70" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="71" ht="58" customHeight="1">
       <x:c r="A71" t="str">
@@ -18617,6 +19533,18 @@
       <x:c r="AU71" t="str">
         <x:v>https://proceedings.neurips.cc/paper_files/paper/2025/hash/89a3b655a8b68ae1c76b768152c9c19d-Abstract-Conference.html；官方摘要/论文集元数据</x:v>
       </x:c>
+      <x:c r="AV71" t="str">
+        <x:v>B-Fulltext-Unavailable</x:v>
+      </x:c>
+      <x:c r="AW71" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="AX71" t="str">
+        <x:v>Partial</x:v>
+      </x:c>
+      <x:c r="AY71" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="72" ht="58" customHeight="1">
       <x:c r="A72" t="str">
@@ -18758,6 +19686,18 @@
       <x:c r="AU72" t="str">
         <x:v>https://openaccess.thecvf.com/content/CVPR2026/html/Lee_DextER_Language-driven_Dexterous_Grasp_Generation_with_Embodied_Reasoning_CVPR_2026_paper.html；官方摘要/论文集元数据</x:v>
       </x:c>
+      <x:c r="AV72" t="str">
+        <x:v>B-Fulltext-Unavailable</x:v>
+      </x:c>
+      <x:c r="AW72" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="AX72" t="str">
+        <x:v>Mostly Complete</x:v>
+      </x:c>
+      <x:c r="AY72" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="73" ht="58" customHeight="1">
       <x:c r="A73" t="str">
@@ -18899,6 +19839,18 @@
       <x:c r="AU73" t="str">
         <x:v>Unknown</x:v>
       </x:c>
+      <x:c r="AV73" t="str">
+        <x:v>B-Fulltext-Unavailable</x:v>
+      </x:c>
+      <x:c r="AW73" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="AX73" t="str">
+        <x:v>Mostly Complete</x:v>
+      </x:c>
+      <x:c r="AY73" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="74" ht="58" customHeight="1">
       <x:c r="A74" t="str">
@@ -19040,6 +19992,18 @@
       <x:c r="AU74" t="str">
         <x:v>Unknown</x:v>
       </x:c>
+      <x:c r="AV74" t="str">
+        <x:v>B-Fulltext-Unavailable</x:v>
+      </x:c>
+      <x:c r="AW74" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="AX74" t="str">
+        <x:v>Mostly Complete</x:v>
+      </x:c>
+      <x:c r="AY74" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="75" ht="58" customHeight="1">
       <x:c r="A75" t="str">
@@ -19179,6 +20143,18 @@
         <x:v>Unknown (no high-confidence match)</x:v>
       </x:c>
       <x:c r="AU75" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AV75" t="str">
+        <x:v>B-Fulltext-Unavailable</x:v>
+      </x:c>
+      <x:c r="AW75" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="AX75" t="str">
+        <x:v>Mostly Complete</x:v>
+      </x:c>
+      <x:c r="AY75" t="str">
         <x:v>Unknown</x:v>
       </x:c>
     </x:row>
@@ -19318,6 +20294,18 @@
       <x:c r="AU76" t="str">
         <x:v>Unknown</x:v>
       </x:c>
+      <x:c r="AV76" t="str">
+        <x:v>B-Fulltext-Unavailable</x:v>
+      </x:c>
+      <x:c r="AW76" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="AX76" t="str">
+        <x:v>Mostly Complete</x:v>
+      </x:c>
+      <x:c r="AY76" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="77" ht="58" customHeight="1">
       <x:c r="A77" t="str">
@@ -19453,6 +20441,18 @@
         <x:v>Unknown (no high-confidence match)</x:v>
       </x:c>
       <x:c r="AU77" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AV77" t="str">
+        <x:v>B-Fulltext-Unavailable</x:v>
+      </x:c>
+      <x:c r="AW77" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="AX77" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AY77" t="str">
         <x:v>Unknown</x:v>
       </x:c>
     </x:row>
@@ -19592,6 +20592,18 @@
       <x:c r="AU78" t="str">
         <x:v>Unknown</x:v>
       </x:c>
+      <x:c r="AV78" t="str">
+        <x:v>B-Fulltext-Unavailable</x:v>
+      </x:c>
+      <x:c r="AW78" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="AX78" t="str">
+        <x:v>Mostly Complete</x:v>
+      </x:c>
+      <x:c r="AY78" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="79">
       <x:c r="A79" t="str">
@@ -19734,6 +20746,18 @@
       </x:c>
       <x:c r="AU79" t="str">
         <x:v>https://ojs.aaai.org/index.php/AAAI/article/view/38921；https://arxiv.org/abs/2508.10333；https://zionchow.github.io/ReconVLA/；https://github.com/OpenHelix-Team/ReconVLA</x:v>
+      </x:c>
+      <x:c r="AV79" t="str">
+        <x:v>B-Experiment-Not-Extracted</x:v>
+      </x:c>
+      <x:c r="AW79" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="AX79" t="str">
+        <x:v>Mostly Complete</x:v>
+      </x:c>
+      <x:c r="AY79" t="str">
+        <x:v>Franka Panda (CALVIN simulation); real-world platform not confirmed at abstract level</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -19756,7 +20780,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R37a2910e42e24495"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6fc4c099267640c9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -20016,6 +21040,18 @@
       <x:c r="BN1" t="str">
         <x:v>Evidence Sources</x:v>
       </x:c>
+      <x:c r="BO1" t="str">
+        <x:v>Evidence Upgrade Status</x:v>
+      </x:c>
+      <x:c r="BP1" t="str">
+        <x:v>Supplement Status</x:v>
+      </x:c>
+      <x:c r="BQ1" t="str">
+        <x:v>Code Completeness</x:v>
+      </x:c>
+      <x:c r="BR1" t="str">
+        <x:v>Robot Platform Evidence</x:v>
+      </x:c>
     </x:row>
     <x:row r="2" ht="58" customHeight="1">
       <x:c r="A2" t="str">
@@ -20208,6 +21244,18 @@
       <x:c r="BN2" t="str">
         <x:v>https://openaccess.thecvf.com/content/CVPR2024/html/Ma_Hierarchical_Diffusion_Policy_for_Kinematics-Aware_Multi-Task_Robotic_Manipulation_CVPR_2024_paper.html；官方摘要/论文集元数据</x:v>
       </x:c>
+      <x:c r="BO2" t="str">
+        <x:v>B-Fulltext-Unavailable</x:v>
+      </x:c>
+      <x:c r="BP2" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="BQ2" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BR2" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="3" ht="58" customHeight="1">
       <x:c r="A3" t="str">
@@ -20400,6 +21448,18 @@
       <x:c r="BN3" t="str">
         <x:v>https://openaccess.thecvf.com/content/ICCV2025/html/Jiang_Rethinking_Bimanual_Robotic_Manipulation_Learning_with_Decoupled_Interaction_Framework_ICCV_2025_paper.html；官方摘要/论文集元数据</x:v>
       </x:c>
+      <x:c r="BO3" t="str">
+        <x:v>B-Fulltext-Unavailable</x:v>
+      </x:c>
+      <x:c r="BP3" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="BQ3" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BR3" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="4" ht="58" customHeight="1">
       <x:c r="A4" t="str">
@@ -20592,6 +21652,18 @@
       <x:c r="BN4" t="str">
         <x:v>https://openaccess.thecvf.com/content/ICCV2025/html/Xu_Diffusion-Based_Imaginative_Coordination_for_Bimanual_Manipulation_ICCV_2025_paper.html；官方摘要/论文集元数据</x:v>
       </x:c>
+      <x:c r="BO4" t="str">
+        <x:v>B-Fulltext-Unavailable</x:v>
+      </x:c>
+      <x:c r="BP4" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="BQ4" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BR4" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="5" ht="58" customHeight="1">
       <x:c r="A5" t="str">
@@ -20784,6 +21856,18 @@
       <x:c r="BN5" t="str">
         <x:v>https://ojs.aaai.org/index.php/AAAI/article/view/38889；官方摘要/论文集元数据</x:v>
       </x:c>
+      <x:c r="BO5" t="str">
+        <x:v>B-Fulltext-Unavailable</x:v>
+      </x:c>
+      <x:c r="BP5" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="BQ5" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BR5" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="6" ht="58" customHeight="1">
       <x:c r="A6" t="str">
@@ -20976,6 +22060,18 @@
       <x:c r="BN6" t="str">
         <x:v>https://ojs.aaai.org/index.php/AAAI/article/view/38911；官方摘要/论文集元数据</x:v>
       </x:c>
+      <x:c r="BO6" t="str">
+        <x:v>B-Fulltext-Unavailable</x:v>
+      </x:c>
+      <x:c r="BP6" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="BQ6" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BR6" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="7" ht="58" customHeight="1">
       <x:c r="A7" t="str">
@@ -21168,6 +22264,18 @@
       <x:c r="BN7" t="str">
         <x:v>https://ojs.aaai.org/index.php/AAAI/article/view/38955；官方摘要/论文集元数据</x:v>
       </x:c>
+      <x:c r="BO7" t="str">
+        <x:v>B-Fulltext-Unavailable</x:v>
+      </x:c>
+      <x:c r="BP7" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="BQ7" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BR7" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="8" ht="58" customHeight="1">
       <x:c r="A8" t="str">
@@ -21360,6 +22468,18 @@
       <x:c r="BN8" t="str">
         <x:v>https://ojs.aaai.org/index.php/AAAI/article/view/38539；官方摘要/论文集元数据</x:v>
       </x:c>
+      <x:c r="BO8" t="str">
+        <x:v>B-Fulltext-Unavailable</x:v>
+      </x:c>
+      <x:c r="BP8" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="BQ8" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BR8" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="9" ht="58" customHeight="1">
       <x:c r="A9" t="str">
@@ -21550,6 +22670,18 @@
       <x:c r="BN9" t="str">
         <x:v>https://ojs.aaai.org/index.php/AAAI/article/download/38892/42854；官方摘要/论文集元数据</x:v>
       </x:c>
+      <x:c r="BO9" t="str">
+        <x:v>B-Fulltext-Unavailable</x:v>
+      </x:c>
+      <x:c r="BP9" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="BQ9" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BR9" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="10" ht="58" customHeight="1">
       <x:c r="A10" t="str">
@@ -21746,6 +22878,18 @@
       <x:c r="BN10" t="str">
         <x:v>https://openaccess.thecvf.com/content/CVPR2025/html/Mu_RoboTwin_Dual-Arm_Robot_Benchmark_with_Generative_Digital_Twins_CVPR_2025_paper.html；官方摘要/论文集元数据</x:v>
       </x:c>
+      <x:c r="BO10" t="str">
+        <x:v>B-Fulltext-Unavailable</x:v>
+      </x:c>
+      <x:c r="BP10" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="BQ10" t="str">
+        <x:v>Mostly Complete</x:v>
+      </x:c>
+      <x:c r="BR10" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="11" ht="58" customHeight="1">
       <x:c r="A11" t="str">
@@ -21944,6 +23088,18 @@
       <x:c r="BN11" t="str">
         <x:v>https://proceedings.neurips.cc/paper_files/paper/2025/hash/5c1a8aa04c1a2cf5013f28831870dafa-Abstract-Conference.html；官方摘要/论文集元数据</x:v>
       </x:c>
+      <x:c r="BO11" t="str">
+        <x:v>B-Fulltext-Unavailable</x:v>
+      </x:c>
+      <x:c r="BP11" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="BQ11" t="str">
+        <x:v>Mostly Complete</x:v>
+      </x:c>
+      <x:c r="BR11" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="12" ht="58" customHeight="1">
       <x:c r="A12" t="str">
@@ -22142,6 +23298,18 @@
       <x:c r="BN12" t="str">
         <x:v>https://proceedings.neurips.cc/paper_files/paper/2025/hash/f062da1973ac9ac61fc6d44dd7fa309f-Abstract-Conference.html；官方摘要/论文集元数据</x:v>
       </x:c>
+      <x:c r="BO12" t="str">
+        <x:v>B-Fulltext-Unavailable</x:v>
+      </x:c>
+      <x:c r="BP12" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="BQ12" t="str">
+        <x:v>Mostly Complete</x:v>
+      </x:c>
+      <x:c r="BR12" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="13" ht="58" customHeight="1">
       <x:c r="A13" t="str">
@@ -22340,6 +23508,18 @@
       <x:c r="BN13" t="str">
         <x:v>https://proceedings.mlr.press/v267/wen25g.html；官方摘要/论文集元数据</x:v>
       </x:c>
+      <x:c r="BO13" t="str">
+        <x:v>B-Fulltext-Unavailable</x:v>
+      </x:c>
+      <x:c r="BP13" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="BQ13" t="str">
+        <x:v>Partial</x:v>
+      </x:c>
+      <x:c r="BR13" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="14" ht="58" customHeight="1">
       <x:c r="A14" t="str">
@@ -22538,6 +23718,18 @@
       <x:c r="BN14" t="str">
         <x:v>https://proceedings.mlr.press/v235/zhen24a.html；官方摘要/论文集元数据</x:v>
       </x:c>
+      <x:c r="BO14" t="str">
+        <x:v>B-Fulltext-Unavailable</x:v>
+      </x:c>
+      <x:c r="BP14" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="BQ14" t="str">
+        <x:v>Partial</x:v>
+      </x:c>
+      <x:c r="BR14" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="15" ht="58" customHeight="1">
       <x:c r="A15" t="str">
@@ -22735,6 +23927,18 @@
       </x:c>
       <x:c r="BN15" t="str">
         <x:v>https://proceedings.neurips.cc/paper_files/paper/2024/hash/46a126492ea6fb87410e55a58df2e189-Abstract-Conference.html; https://sites.google.com/view/robomamba-web; https://github.com/lm</x:v>
+      </x:c>
+      <x:c r="BO15" t="str">
+        <x:v>B-Fulltext-Unavailable</x:v>
+      </x:c>
+      <x:c r="BP15" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="BQ15" t="str">
+        <x:v>Partial</x:v>
+      </x:c>
+      <x:c r="BR15" t="str">
+        <x:v>Unknown</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="58" customHeight="1">
@@ -22932,6 +24136,18 @@
       <x:c r="BN16" t="str">
         <x:v>https://ojs.aaai.org/index.php/AAAI/article/view/33617; https://github.com/</x:v>
       </x:c>
+      <x:c r="BO16" t="str">
+        <x:v>B-Fulltext-Unavailable</x:v>
+      </x:c>
+      <x:c r="BP16" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="BQ16" t="str">
+        <x:v>Mostly Complete</x:v>
+      </x:c>
+      <x:c r="BR16" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="17" ht="58" customHeight="1">
       <x:c r="A17" t="str">
@@ -23130,6 +24346,18 @@
       <x:c r="BN17" t="str">
         <x:v>https://openaccess.thecvf.com/content/CVPR2025/html/Wang_UniGraspTransformer_Simplified_Policy_Distillation_for_Scalable_Dexterous_Robotic_Grasping_CVPR_2025_paper.html；官方摘要/论文集元数据</x:v>
       </x:c>
+      <x:c r="BO17" t="str">
+        <x:v>B-Fulltext-Unavailable</x:v>
+      </x:c>
+      <x:c r="BP17" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="BQ17" t="str">
+        <x:v>Mostly Complete</x:v>
+      </x:c>
+      <x:c r="BR17" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="18" ht="58" customHeight="1">
       <x:c r="A18" t="str">
@@ -23328,6 +24556,18 @@
       <x:c r="BN18" t="str">
         <x:v>https://proceedings.neurips.cc/paper_files/paper/2025/hash/862644b156e51c35dea5a7446d640b14-Abstract-Conference.html；官方摘要/论文集元数据</x:v>
       </x:c>
+      <x:c r="BO18" t="str">
+        <x:v>B-Fulltext-Unavailable</x:v>
+      </x:c>
+      <x:c r="BP18" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="BQ18" t="str">
+        <x:v>Mostly Complete</x:v>
+      </x:c>
+      <x:c r="BR18" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="19" ht="58" customHeight="1">
       <x:c r="A19" t="str">
@@ -23526,6 +24766,18 @@
       <x:c r="BN19" t="str">
         <x:v>https://proceedings.neurips.cc/paper_files/paper/2025/hash/89a3b655a8b68ae1c76b768152c9c19d-Abstract-Conference.html；官方摘要/论文集元数据</x:v>
       </x:c>
+      <x:c r="BO19" t="str">
+        <x:v>B-Fulltext-Unavailable</x:v>
+      </x:c>
+      <x:c r="BP19" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="BQ19" t="str">
+        <x:v>Partial</x:v>
+      </x:c>
+      <x:c r="BR19" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="20" ht="58" customHeight="1">
       <x:c r="A20" t="str">
@@ -23724,6 +24976,18 @@
       <x:c r="BN20" t="str">
         <x:v>https://openaccess.thecvf.com/content/CVPR2026/html/Lee_DextER_Language-driven_Dexterous_Grasp_Generation_with_Embodied_Reasoning_CVPR_2026_paper.html；官方摘要/论文集元数据</x:v>
       </x:c>
+      <x:c r="BO20" t="str">
+        <x:v>B-Fulltext-Unavailable</x:v>
+      </x:c>
+      <x:c r="BP20" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="BQ20" t="str">
+        <x:v>Mostly Complete</x:v>
+      </x:c>
+      <x:c r="BR20" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="21" ht="58" customHeight="1">
       <x:c r="A21" t="str">
@@ -23924,6 +25188,18 @@
       <x:c r="BN21" t="str">
         <x:v>https://openaccess.thecvf.com/content/CVPR2024/html/Li_ManipLLM_Embodied_Multimodal_Large_Language_Model_for_Object-Centric_Robotic_Manipulation_CVPR_2024_paper.html；官方摘要/论文集元数据</x:v>
       </x:c>
+      <x:c r="BO21" t="str">
+        <x:v>A-Upgraded</x:v>
+      </x:c>
+      <x:c r="BP21" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="BQ21" t="str">
+        <x:v>Partial</x:v>
+      </x:c>
+      <x:c r="BR21" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="22" ht="58" customHeight="1">
       <x:c r="A22" t="str">
@@ -24124,6 +25400,18 @@
       <x:c r="BN22" t="str">
         <x:v>https://openaccess.thecvf.com/content/CVPR2025/html/Li_ManipTrans_Efficient_Dexterous_Bimanual_Manipulation_Transfer_via_Residual_Learning_CVPR_2025_paper.html；官方摘要/论文集元数据</x:v>
       </x:c>
+      <x:c r="BO22" t="str">
+        <x:v>B-Fulltext-Unavailable</x:v>
+      </x:c>
+      <x:c r="BP22" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="BQ22" t="str">
+        <x:v>Mostly Complete</x:v>
+      </x:c>
+      <x:c r="BR22" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="23" ht="58" customHeight="1">
       <x:c r="A23" t="str">
@@ -24324,6 +25612,18 @@
       <x:c r="BN23" t="str">
         <x:v>https://openaccess.thecvf.com/content/CVPR2025/html/Liang_DexHandDiff_Interaction-aware_Diffusion_Planning_for_Adaptive_Dexterous_Manipulation_CVPR_2025_paper.html; https://dexdiffuser.github.io/; https://github.com/Liang-</x:v>
       </x:c>
+      <x:c r="BO23" t="str">
+        <x:v>B-Fulltext-Unavailable</x:v>
+      </x:c>
+      <x:c r="BP23" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="BQ23" t="str">
+        <x:v>Partial</x:v>
+      </x:c>
+      <x:c r="BR23" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="24" ht="58" customHeight="1">
       <x:c r="A24" t="str">
@@ -24524,6 +25824,18 @@
       <x:c r="BN24" t="str">
         <x:v>https://openaccess.thecvf.com/content/ICCV2025/html/Yang_AR-VRM_Imitating_Human_Motions_for_Visual_Robot_Manipulation_with_Analogical_ICCV_2025_paper.html；官方摘要/论文集元数据</x:v>
       </x:c>
+      <x:c r="BO24" t="str">
+        <x:v>B-Fulltext-Unavailable</x:v>
+      </x:c>
+      <x:c r="BP24" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="BQ24" t="str">
+        <x:v>Mostly Complete</x:v>
+      </x:c>
+      <x:c r="BR24" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="25" ht="58" customHeight="1">
       <x:c r="A25" t="str">
@@ -24724,6 +26036,18 @@
       <x:c r="BN25" t="str">
         <x:v>https://openaccess.thecvf.com/content/CVPR2024/html/Xu_Dexterous_Grasp_Transformer_CVPR_2024_paper.html；官方摘要/论文集元数据</x:v>
       </x:c>
+      <x:c r="BO25" t="str">
+        <x:v>B-Fulltext-Unavailable</x:v>
+      </x:c>
+      <x:c r="BP25" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="BQ25" t="str">
+        <x:v>Mostly Complete</x:v>
+      </x:c>
+      <x:c r="BR25" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="26" ht="58" customHeight="1">
       <x:c r="A26" t="str">
@@ -24924,6 +26248,18 @@
       <x:c r="BN26" t="str">
         <x:v>https://openaccess.thecvf.com/content/CVPR2025/html/Wu_MoManipVLA_Transferring_Vision-language-action_Models_for_General_Mobile_Manipulation_CVPR_2025_paper.html；官方摘要/论文集元数据</x:v>
       </x:c>
+      <x:c r="BO26" t="str">
+        <x:v>B-Code-Unverified</x:v>
+      </x:c>
+      <x:c r="BP26" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="BQ26" t="str">
+        <x:v>Unavailable</x:v>
+      </x:c>
+      <x:c r="BR26" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="27" ht="58" customHeight="1">
       <x:c r="A27" t="str">
@@ -25124,6 +26460,18 @@
       <x:c r="BN27" t="str">
         <x:v>https://proceedings.neurips.cc/paper_files/paper/2024/hash/ff887781480973bd3cb6026feb378d1e-Abstract-Conference.html；官方摘要/论文集元数据</x:v>
       </x:c>
+      <x:c r="BO27" t="str">
+        <x:v>B-Code-Unverified</x:v>
+      </x:c>
+      <x:c r="BP27" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="BQ27" t="str">
+        <x:v>Unavailable</x:v>
+      </x:c>
+      <x:c r="BR27" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="28" ht="58" customHeight="1">
       <x:c r="A28" t="str">
@@ -25324,6 +26672,18 @@
       <x:c r="BN28" t="str">
         <x:v>https://proceedings.neurips.cc/paper_files/paper/2024/hash/74c4f2b87b7499d365422152c76fd916-Abstract-Datasets_and_Benchmarks_Track.html；官方摘要/论文集元数据</x:v>
       </x:c>
+      <x:c r="BO28" t="str">
+        <x:v>B-Fulltext-Unavailable</x:v>
+      </x:c>
+      <x:c r="BP28" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="BQ28" t="str">
+        <x:v>Mostly Complete</x:v>
+      </x:c>
+      <x:c r="BR28" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="29" ht="58" customHeight="1">
       <x:c r="A29" t="str">
@@ -25524,6 +26884,18 @@
       <x:c r="BN29" t="str">
         <x:v>https://proceedings.neurips.cc/paper_files/paper/2024/hash/dcd297696d0bb304ba426b3c5a679c37-Abstract-Conference.html；官方摘要/论文集元数据</x:v>
       </x:c>
+      <x:c r="BO29" t="str">
+        <x:v>B-Fulltext-Unavailable</x:v>
+      </x:c>
+      <x:c r="BP29" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="BQ29" t="str">
+        <x:v>Mostly Complete</x:v>
+      </x:c>
+      <x:c r="BR29" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="30" ht="58" customHeight="1">
       <x:c r="A30" t="str">
@@ -25724,6 +27096,18 @@
       <x:c r="BN30" t="str">
         <x:v>https://proceedings.neurips.cc/paper_files/paper/2024/hash/fad8962279154544ed69bb63eb14d677-Abstract-Conference.html；官方摘要/论文集元数据</x:v>
       </x:c>
+      <x:c r="BO30" t="str">
+        <x:v>B-Fulltext-Unavailable</x:v>
+      </x:c>
+      <x:c r="BP30" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="BQ30" t="str">
+        <x:v>Mostly Complete</x:v>
+      </x:c>
+      <x:c r="BR30" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="31" ht="58" customHeight="1">
       <x:c r="A31" t="str">
@@ -25924,6 +27308,18 @@
       <x:c r="BN31" t="str">
         <x:v>https://proceedings.neurips.cc/paper_files/paper/2024/hash/8e5dc5969a6174fcaaececd890c7f59b-Abstract-Datasets_and_Benchmarks_Track.html；官方摘要/论文集元数据</x:v>
       </x:c>
+      <x:c r="BO31" t="str">
+        <x:v>B-Code-Unverified</x:v>
+      </x:c>
+      <x:c r="BP31" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="BQ31" t="str">
+        <x:v>Unavailable</x:v>
+      </x:c>
+      <x:c r="BR31" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="32" ht="58" customHeight="1">
       <x:c r="A32" t="str">
@@ -26124,6 +27520,18 @@
       <x:c r="BN32" t="str">
         <x:v>https://proceedings.neurips.cc/paper_files/paper/2024/hash/5227ce00add5aa0a12d1c4ee92fcd2dc-Abstract-Conference.html；官方摘要/论文集元数据</x:v>
       </x:c>
+      <x:c r="BO32" t="str">
+        <x:v>B-Code-Unverified</x:v>
+      </x:c>
+      <x:c r="BP32" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="BQ32" t="str">
+        <x:v>Unavailable</x:v>
+      </x:c>
+      <x:c r="BR32" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="33" ht="58" customHeight="1">
       <x:c r="A33" t="str">
@@ -26324,6 +27732,18 @@
       <x:c r="BN33" t="str">
         <x:v>https://openaccess.thecvf.com/content/CVPR2025/html/</x:v>
       </x:c>
+      <x:c r="BO33" t="str">
+        <x:v>B-Code-Unverified</x:v>
+      </x:c>
+      <x:c r="BP33" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="BQ33" t="str">
+        <x:v>Unavailable</x:v>
+      </x:c>
+      <x:c r="BR33" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="34" ht="58" customHeight="1">
       <x:c r="A34" t="str">
@@ -26524,6 +27944,18 @@
       <x:c r="BN34" t="str">
         <x:v>https://openaccess.thecvf.com/content/CVPR2025/html/Huang_RoboGround_Robotic_Manipulation_with_Grounded_Vision-Language_Priors_CVPR_2025_paper.html；官方摘要/论文集元数据</x:v>
       </x:c>
+      <x:c r="BO34" t="str">
+        <x:v>B-Code-Unverified</x:v>
+      </x:c>
+      <x:c r="BP34" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="BQ34" t="str">
+        <x:v>Unavailable</x:v>
+      </x:c>
+      <x:c r="BR34" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="35" ht="58" customHeight="1">
       <x:c r="A35" t="str">
@@ -26724,6 +28156,18 @@
       <x:c r="BN35" t="str">
         <x:v>https://openaccess.thecvf.com/content/CVPR2025/html/Lee_DynScene_Scalable_Generation_of_Dynamic_Robotic_Manipulation_Scenes_for_Embodied_CVPR_2025_paper.html；官方摘要/论文集元数据</x:v>
       </x:c>
+      <x:c r="BO35" t="str">
+        <x:v>B-Code-Unverified</x:v>
+      </x:c>
+      <x:c r="BP35" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="BQ35" t="str">
+        <x:v>Unavailable</x:v>
+      </x:c>
+      <x:c r="BR35" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="36" ht="58" customHeight="1">
       <x:c r="A36" t="str">
@@ -26924,6 +28368,18 @@
       <x:c r="BN36" t="str">
         <x:v>https://openaccess.thecvf.com/content/CVPR2025/html/Yao_Think_Small_Act_Big_Primitive_Prompt_Learning_for_Lifelong_Robot_CVPR_2025_paper.html；官方摘要/论文集元数据</x:v>
       </x:c>
+      <x:c r="BO36" t="str">
+        <x:v>B-Code-Unverified</x:v>
+      </x:c>
+      <x:c r="BP36" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="BQ36" t="str">
+        <x:v>Unavailable</x:v>
+      </x:c>
+      <x:c r="BR36" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="37" ht="58" customHeight="1">
       <x:c r="A37" t="str">
@@ -27124,6 +28580,18 @@
       <x:c r="BN37" t="str">
         <x:v>https://ojs.aaai.org/index.php/AAAI/article/view/34866；官方摘要/论文集元数据</x:v>
       </x:c>
+      <x:c r="BO37" t="str">
+        <x:v>B-Code-Unverified</x:v>
+      </x:c>
+      <x:c r="BP37" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="BQ37" t="str">
+        <x:v>Unavailable</x:v>
+      </x:c>
+      <x:c r="BR37" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="38" ht="58" customHeight="1">
       <x:c r="A38" t="str">
@@ -27324,6 +28792,18 @@
       <x:c r="BN38" t="str">
         <x:v>https://ojs.aaai.org/index.php/AAAI/article/view/33615；官方摘要/论文集元数据</x:v>
       </x:c>
+      <x:c r="BO38" t="str">
+        <x:v>B-Code-Unverified</x:v>
+      </x:c>
+      <x:c r="BP38" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="BQ38" t="str">
+        <x:v>Unavailable</x:v>
+      </x:c>
+      <x:c r="BR38" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="39" ht="58" customHeight="1">
       <x:c r="A39" t="str">
@@ -27524,6 +29004,18 @@
       <x:c r="BN39" t="str">
         <x:v>https://ojs.aaai.org/index.php/AAAI/article/view/33610；官方摘要/论文集元数据</x:v>
       </x:c>
+      <x:c r="BO39" t="str">
+        <x:v>B-Code-Unverified</x:v>
+      </x:c>
+      <x:c r="BP39" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="BQ39" t="str">
+        <x:v>Unavailable</x:v>
+      </x:c>
+      <x:c r="BR39" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="40" ht="58" customHeight="1">
       <x:c r="A40" t="str">
@@ -27724,6 +29216,18 @@
       <x:c r="BN40" t="str">
         <x:v>https://proceedings.neurips.cc/paper_files/paper/2024/hash/481c70828a4ff20d31a646cc6cc95f3d-Abstract-Conference.html；官方摘要/论文集元数据</x:v>
       </x:c>
+      <x:c r="BO40" t="str">
+        <x:v>B-Code-Unverified</x:v>
+      </x:c>
+      <x:c r="BP40" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="BQ40" t="str">
+        <x:v>Unavailable</x:v>
+      </x:c>
+      <x:c r="BR40" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="41" ht="58" customHeight="1">
       <x:c r="A41" t="str">
@@ -27924,6 +29428,18 @@
       <x:c r="BN41" t="str">
         <x:v>https://openaccess.thecvf.com/content/CVPR2025/html/Chen_VidBot_Learning_Generali</x:v>
       </x:c>
+      <x:c r="BO41" t="str">
+        <x:v>B-Code-Unverified</x:v>
+      </x:c>
+      <x:c r="BP41" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="BQ41" t="str">
+        <x:v>Unavailable</x:v>
+      </x:c>
+      <x:c r="BR41" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="42" ht="58" customHeight="1">
       <x:c r="A42" t="str">
@@ -28124,6 +29640,18 @@
       <x:c r="BN42" t="str">
         <x:v>https://openaccess.thecvf.com/content/CVPR2025/html/</x:v>
       </x:c>
+      <x:c r="BO42" t="str">
+        <x:v>B-Code-Unverified</x:v>
+      </x:c>
+      <x:c r="BP42" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="BQ42" t="str">
+        <x:v>Unavailable</x:v>
+      </x:c>
+      <x:c r="BR42" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="43" ht="58" customHeight="1">
       <x:c r="A43" t="str">
@@ -28324,6 +29852,18 @@
       <x:c r="BN43" t="str">
         <x:v>https://proceedings.neurips.cc/paper_files/paper/2025/hash/1185c89347a3f21ffc48c9d083c9437c-Abstract-Conference.html；官方摘要/论文集元数据</x:v>
       </x:c>
+      <x:c r="BO43" t="str">
+        <x:v>B-Code-Unverified</x:v>
+      </x:c>
+      <x:c r="BP43" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="BQ43" t="str">
+        <x:v>Unavailable</x:v>
+      </x:c>
+      <x:c r="BR43" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="44" ht="58" customHeight="1">
       <x:c r="A44" t="str">
@@ -28524,6 +30064,18 @@
       <x:c r="BN44" t="str">
         <x:v>https://proceedings.neurips.cc/paper_files/paper/2025/hash/b94310e1c7ecb79f1a24adc757f1b89b-Abstract-Conference.html；官方摘要/论文集元数据</x:v>
       </x:c>
+      <x:c r="BO44" t="str">
+        <x:v>B-Code-Unverified</x:v>
+      </x:c>
+      <x:c r="BP44" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="BQ44" t="str">
+        <x:v>Unavailable</x:v>
+      </x:c>
+      <x:c r="BR44" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="45" ht="58" customHeight="1">
       <x:c r="A45" t="str">
@@ -28724,6 +30276,18 @@
       <x:c r="BN45" t="str">
         <x:v>https://proceedings.neurips.cc/paper_files/paper/2025/hash/49eadcc4a329fc6b74b9f8a82b78cbc3-Abstract-Conference.html；官方摘要/论文集元数据</x:v>
       </x:c>
+      <x:c r="BO45" t="str">
+        <x:v>B-Code-Unverified</x:v>
+      </x:c>
+      <x:c r="BP45" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="BQ45" t="str">
+        <x:v>Unavailable</x:v>
+      </x:c>
+      <x:c r="BR45" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="46" ht="58" customHeight="1">
       <x:c r="A46" t="str">
@@ -28924,6 +30488,18 @@
       <x:c r="BN46" t="str">
         <x:v>https://proceedings.neurips.cc/paper_files/paper/2025/hash/bc97207e3979d1cc23109db0be0e8ed2-Abstract-Conference.html；官方摘要/论文集元数据</x:v>
       </x:c>
+      <x:c r="BO46" t="str">
+        <x:v>B-Code-Unverified</x:v>
+      </x:c>
+      <x:c r="BP46" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="BQ46" t="str">
+        <x:v>Unavailable</x:v>
+      </x:c>
+      <x:c r="BR46" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="47" ht="58" customHeight="1">
       <x:c r="A47" t="str">
@@ -29124,6 +30700,18 @@
       <x:c r="BN47" t="str">
         <x:v>https://proceedings.neurips.cc/paper_files/paper/2025/hash/282c3318be1b047b7bb5ba94fa4f3231-Abstract-Conference.html；官方摘要/论文集元数据</x:v>
       </x:c>
+      <x:c r="BO47" t="str">
+        <x:v>B-Code-Unverified</x:v>
+      </x:c>
+      <x:c r="BP47" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="BQ47" t="str">
+        <x:v>Unavailable</x:v>
+      </x:c>
+      <x:c r="BR47" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="48" ht="58" customHeight="1">
       <x:c r="A48" t="str">
@@ -29324,6 +30912,18 @@
       <x:c r="BN48" t="str">
         <x:v>https://proceedings.neurips.cc/paper_files/paper/2025/hash/9fc291fef2f9607a46777d367f900a15-Abstract-Conference.html；官方摘要/论文集元数据</x:v>
       </x:c>
+      <x:c r="BO48" t="str">
+        <x:v>B-Code-Unverified</x:v>
+      </x:c>
+      <x:c r="BP48" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="BQ48" t="str">
+        <x:v>Unavailable</x:v>
+      </x:c>
+      <x:c r="BR48" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="49" ht="58" customHeight="1">
       <x:c r="A49" t="str">
@@ -29524,6 +31124,18 @@
       <x:c r="BN49" t="str">
         <x:v>https://proceedings.neurips.cc/paper_files/paper/2025/hash/eacc8ae341d15d2c13c02fef88189db3-Abstract-Conference.html；官方摘要/论文集元数据</x:v>
       </x:c>
+      <x:c r="BO49" t="str">
+        <x:v>B-Code-Unverified</x:v>
+      </x:c>
+      <x:c r="BP49" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="BQ49" t="str">
+        <x:v>Unavailable</x:v>
+      </x:c>
+      <x:c r="BR49" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="50" ht="58" customHeight="1">
       <x:c r="A50" t="str">
@@ -29724,6 +31336,18 @@
       <x:c r="BN50" t="str">
         <x:v>https://proceedings.neurips.cc/paper_files/paper/2025/hash/1f467c3e37abf9f86c78f44c6a27ee7c-Abstract-Datasets_and_Benchmarks_Track.html；官方摘要/论文集元数据</x:v>
       </x:c>
+      <x:c r="BO50" t="str">
+        <x:v>B-Code-Unverified</x:v>
+      </x:c>
+      <x:c r="BP50" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="BQ50" t="str">
+        <x:v>Unavailable</x:v>
+      </x:c>
+      <x:c r="BR50" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="51" ht="58" customHeight="1">
       <x:c r="A51" t="str">
@@ -29924,6 +31548,18 @@
       <x:c r="BN51" t="str">
         <x:v>https://proceedings.neurips.cc/paper_files/paper/2025/hash/b8358a00e5b870194b974ddf8dd415c3-Abstract-Conference.html；官方摘要/论文集元数据</x:v>
       </x:c>
+      <x:c r="BO51" t="str">
+        <x:v>B-Code-Unverified</x:v>
+      </x:c>
+      <x:c r="BP51" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="BQ51" t="str">
+        <x:v>Unavailable</x:v>
+      </x:c>
+      <x:c r="BR51" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="52" ht="58" customHeight="1">
       <x:c r="A52" t="str">
@@ -30124,6 +31760,18 @@
       <x:c r="BN52" t="str">
         <x:v>https://openaccess.thecvf.com/content/ICCV2025/html/Wang_DexH2R_A_Benchmark_for_Dynamic_Dexterous_Grasping_in_Human-to-Robot_Handover_ICCV_2025_paper.html；官方摘要/论文集元数据</x:v>
       </x:c>
+      <x:c r="BO52" t="str">
+        <x:v>B-Code-Unverified</x:v>
+      </x:c>
+      <x:c r="BP52" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="BQ52" t="str">
+        <x:v>Unavailable</x:v>
+      </x:c>
+      <x:c r="BR52" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="53" ht="58" customHeight="1">
       <x:c r="A53" t="str">
@@ -30324,6 +31972,18 @@
       <x:c r="BN53" t="str">
         <x:v>https://openaccess.thecvf.com/content/CVPR2025/html/</x:v>
       </x:c>
+      <x:c r="BO53" t="str">
+        <x:v>B-Code-Unverified</x:v>
+      </x:c>
+      <x:c r="BP53" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="BQ53" t="str">
+        <x:v>Unavailable</x:v>
+      </x:c>
+      <x:c r="BR53" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="54" ht="58" customHeight="1">
       <x:c r="A54" t="str">
@@ -30524,6 +32184,18 @@
       <x:c r="BN54" t="str">
         <x:v>https://openaccess.thecvf.com/content/ICCV2025/html/He_DexVLG_Dexterous_Vision-Language-Grasp_Model_at_Scale_ICCV_2025_paper.html；官方摘要/论文集元数据</x:v>
       </x:c>
+      <x:c r="BO54" t="str">
+        <x:v>B-Fulltext-Unavailable</x:v>
+      </x:c>
+      <x:c r="BP54" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="BQ54" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BR54" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="55" ht="58" customHeight="1">
       <x:c r="A55" t="str">
@@ -30724,6 +32396,18 @@
       <x:c r="BN55" t="str">
         <x:v>https://openaccess.thecvf.com/content/CVPR2025/html/Li_LatentHOI_On_the_Generali</x:v>
       </x:c>
+      <x:c r="BO55" t="str">
+        <x:v>B-Code-Unverified</x:v>
+      </x:c>
+      <x:c r="BP55" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="BQ55" t="str">
+        <x:v>Unavailable</x:v>
+      </x:c>
+      <x:c r="BR55" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="56" ht="58" customHeight="1">
       <x:c r="A56" t="str">
@@ -30924,6 +32608,18 @@
       <x:c r="BN56" t="str">
         <x:v>https://openaccess.thecvf.com/content/CVPR2024/papers/Liu_TACO_Benchmarking_Generali</x:v>
       </x:c>
+      <x:c r="BO56" t="str">
+        <x:v>B-Code-Unverified</x:v>
+      </x:c>
+      <x:c r="BP56" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="BQ56" t="str">
+        <x:v>Unavailable</x:v>
+      </x:c>
+      <x:c r="BR56" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="57" ht="58" customHeight="1">
       <x:c r="A57" t="str">
@@ -31124,6 +32820,18 @@
       <x:c r="BN57" t="str">
         <x:v>https://openaccess.thecvf.com/content/CVPR2024/html/Uppal_SPIN_Simultaneous_Perception_Interaction_and_Navigation_CVPR_2024_paper.html；官方摘要/论文集元数据</x:v>
       </x:c>
+      <x:c r="BO57" t="str">
+        <x:v>B-Code-Unverified</x:v>
+      </x:c>
+      <x:c r="BP57" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="BQ57" t="str">
+        <x:v>Unavailable</x:v>
+      </x:c>
+      <x:c r="BR57" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="58" ht="58" customHeight="1">
       <x:c r="A58" t="str">
@@ -31324,6 +33032,18 @@
       <x:c r="BN58" t="str">
         <x:v>https://openaccess.thecvf.com/content/ICCV2025/html/Lu_AnyBimanual_Transferring_Unimanual_Policy_for_General_Bimanual_Manipulation_ICCV_2025_paper.html；官方摘要/论文集元数据</x:v>
       </x:c>
+      <x:c r="BO58" t="str">
+        <x:v>A-Upgraded</x:v>
+      </x:c>
+      <x:c r="BP58" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="BQ58" t="str">
+        <x:v>Unavailable</x:v>
+      </x:c>
+      <x:c r="BR58" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="59" ht="58" customHeight="1">
       <x:c r="A59" t="str">
@@ -31524,6 +33244,18 @@
       <x:c r="BN59" t="str">
         <x:v>https://openaccess.thecvf.com/content/CVPR2026/html/Zhang_UniDex_A_Robot_Foundation_Suite_for_Universal_Dexterous_Hand_Control_CVPR_2026_paper.html；官方摘要/论文集元数据</x:v>
       </x:c>
+      <x:c r="BO59" t="str">
+        <x:v>B-Code-Unverified</x:v>
+      </x:c>
+      <x:c r="BP59" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="BQ59" t="str">
+        <x:v>Unavailable</x:v>
+      </x:c>
+      <x:c r="BR59" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="60" ht="58" customHeight="1">
       <x:c r="A60" t="str">
@@ -31724,6 +33456,18 @@
       <x:c r="BN60" t="str">
         <x:v>https://openaccess.thecvf.com/content/CVPR2025/html/</x:v>
       </x:c>
+      <x:c r="BO60" t="str">
+        <x:v>B-Code-Unverified</x:v>
+      </x:c>
+      <x:c r="BP60" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="BQ60" t="str">
+        <x:v>Unavailable</x:v>
+      </x:c>
+      <x:c r="BR60" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="61" ht="58" customHeight="1">
       <x:c r="A61" t="str">
@@ -31924,6 +33668,18 @@
       <x:c r="BN61" t="str">
         <x:v>https://ojs.aaai.org/index.php/AAAI/article/view/38874；官方摘要/论文集元数据</x:v>
       </x:c>
+      <x:c r="BO61" t="str">
+        <x:v>B-Code-Unverified</x:v>
+      </x:c>
+      <x:c r="BP61" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="BQ61" t="str">
+        <x:v>Unavailable</x:v>
+      </x:c>
+      <x:c r="BR61" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="62" ht="58" customHeight="1">
       <x:c r="A62" t="str">
@@ -32124,6 +33880,18 @@
       <x:c r="BN62" t="str">
         <x:v>https://proceedings.neurips.cc/paper_files/paper/2025/hash/e4ef7454447baa15a424314e6284441b-Abstract-Conference.html；官方摘要/论文集元数据</x:v>
       </x:c>
+      <x:c r="BO62" t="str">
+        <x:v>B-Code-Unverified</x:v>
+      </x:c>
+      <x:c r="BP62" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="BQ62" t="str">
+        <x:v>Unavailable</x:v>
+      </x:c>
+      <x:c r="BR62" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="63" ht="58" customHeight="1">
       <x:c r="A63" t="str">
@@ -32324,6 +34092,18 @@
       <x:c r="BN63" t="str">
         <x:v>https://ojs.aaai.org/index.php/AAAI/article/view/38313；官方摘要/论文集元数据</x:v>
       </x:c>
+      <x:c r="BO63" t="str">
+        <x:v>B-Code-Unverified</x:v>
+      </x:c>
+      <x:c r="BP63" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="BQ63" t="str">
+        <x:v>Unavailable</x:v>
+      </x:c>
+      <x:c r="BR63" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="64" ht="58" customHeight="1">
       <x:c r="A64" t="str">
@@ -32524,6 +34304,18 @@
       <x:c r="BN64" t="str">
         <x:v>https://ojs.aaai.org/index.php/AAAI/article/view/40127；官方摘要/论文集元数据</x:v>
       </x:c>
+      <x:c r="BO64" t="str">
+        <x:v>B-Code-Unverified</x:v>
+      </x:c>
+      <x:c r="BP64" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="BQ64" t="str">
+        <x:v>Unavailable</x:v>
+      </x:c>
+      <x:c r="BR64" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="65" ht="58" customHeight="1">
       <x:c r="A65" t="str">
@@ -32724,6 +34516,18 @@
       <x:c r="BN65" t="str">
         <x:v>https://ojs.aaai.org/index.php/AAAI/article/view/28266；官方摘要/论文集元数据</x:v>
       </x:c>
+      <x:c r="BO65" t="str">
+        <x:v>B-Code-Unverified</x:v>
+      </x:c>
+      <x:c r="BP65" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="BQ65" t="str">
+        <x:v>Unavailable</x:v>
+      </x:c>
+      <x:c r="BR65" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="66" ht="58" customHeight="1">
       <x:c r="A66" t="str">
@@ -32924,6 +34728,18 @@
       <x:c r="BN66" t="str">
         <x:v>https://openaccess.thecvf.com/content/ICCV2025/html/Heidinger_2HandedAfforder_Learning_Precise_Actionable_Bimanual_Affordances_from_Human_Videos_ICCV_2025_paper.html；官方摘要/论文集元数据</x:v>
       </x:c>
+      <x:c r="BO66" t="str">
+        <x:v>B-Code-Unverified</x:v>
+      </x:c>
+      <x:c r="BP66" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="BQ66" t="str">
+        <x:v>Unavailable</x:v>
+      </x:c>
+      <x:c r="BR66" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="67">
       <x:c r="A67" t="str">
@@ -33123,6 +34939,18 @@
       </x:c>
       <x:c r="BN67" t="str">
         <x:v>https://ojs.aaai.org/index.php/AAAI/article/view/38921；https://arxiv.org/abs/2508.10333；https://zionchow.github.io/ReconVLA/；https://github.com/OpenHelix-Team/ReconVLA</x:v>
+      </x:c>
+      <x:c r="BO67" t="str">
+        <x:v>B-Experiment-Not-Extracted</x:v>
+      </x:c>
+      <x:c r="BP67" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="BQ67" t="str">
+        <x:v>Mostly Complete</x:v>
+      </x:c>
+      <x:c r="BR67" t="str">
+        <x:v>Franka Panda (CALVIN simulation); real-world platform not confirmed at abstract level</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -33160,7 +34988,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1d151f50ba90484f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3a7da2787efe4e06"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -33374,6 +35202,18 @@
       <x:c r="BC1" t="str">
         <x:v>Evidence Sources</x:v>
       </x:c>
+      <x:c r="BD1" t="str">
+        <x:v>Evidence Upgrade Status</x:v>
+      </x:c>
+      <x:c r="BE1" t="str">
+        <x:v>Supplement Status</x:v>
+      </x:c>
+      <x:c r="BF1" t="str">
+        <x:v>Code Completeness</x:v>
+      </x:c>
+      <x:c r="BG1" t="str">
+        <x:v>Robot Platform Evidence</x:v>
+      </x:c>
     </x:row>
     <x:row r="2" ht="62" customHeight="1">
       <x:c r="A2" t="str">
@@ -33541,6 +35381,18 @@
       <x:c r="BC2" t="str">
         <x:v>Official ICLR Downloads/Proceedings; accepted OpenReview PDF; official project page; official EmbodiChain repository; author publication list; current official CCF directory</x:v>
       </x:c>
+      <x:c r="BD2" t="str">
+        <x:v>B-Experiment-Not-Extracted</x:v>
+      </x:c>
+      <x:c r="BE2" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="BF2" t="str">
+        <x:v>Partial</x:v>
+      </x:c>
+      <x:c r="BG2" t="str">
+        <x:v>Multiple real-world setups are shown; exact hardware inventory not extracted at abstract/project level</x:v>
+      </x:c>
     </x:row>
     <x:row r="3" ht="62" customHeight="1">
       <x:c r="A3" t="str">
@@ -33708,6 +35560,18 @@
       <x:c r="BC3" t="str">
         <x:v>https://www.roboticsproceedings.org/rss21/p149.html; https://hnu</x:v>
       </x:c>
+      <x:c r="BD3" t="str">
+        <x:v>B-Code-Unverified</x:v>
+      </x:c>
+      <x:c r="BE3" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="BF3" t="str">
+        <x:v>Unavailable</x:v>
+      </x:c>
+      <x:c r="BG3" t="str">
+        <x:v>Dual robot arms; exact platform pending full-paper check</x:v>
+      </x:c>
     </x:row>
     <x:row r="4" ht="62" customHeight="1">
       <x:c r="A4" t="str">
@@ -33875,6 +35739,18 @@
       <x:c r="BC4" t="str">
         <x:v>RSS official proceedings abstract</x:v>
       </x:c>
+      <x:c r="BD4" t="str">
+        <x:v>B-Code-Unverified</x:v>
+      </x:c>
+      <x:c r="BE4" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="BF4" t="str">
+        <x:v>Unavailable</x:v>
+      </x:c>
+      <x:c r="BG4" t="str">
+        <x:v>Bimanual gripper system; exact model pending full-paper check</x:v>
+      </x:c>
     </x:row>
     <x:row r="5" ht="62" customHeight="1">
       <x:c r="A5" t="str">
@@ -34042,6 +35918,18 @@
       <x:c r="BC5" t="str">
         <x:v>RSS official proceedings</x:v>
       </x:c>
+      <x:c r="BD5" t="str">
+        <x:v>B-Code-Unverified</x:v>
+      </x:c>
+      <x:c r="BE5" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="BF5" t="str">
+        <x:v>Unavailable</x:v>
+      </x:c>
+      <x:c r="BG5" t="str">
+        <x:v>Dexterous robotic hand</x:v>
+      </x:c>
     </x:row>
     <x:row r="6" ht="62" customHeight="1">
       <x:c r="A6" t="str">
@@ -34209,6 +36097,18 @@
       <x:c r="BC6" t="str">
         <x:v>RSS official proceedings abstract</x:v>
       </x:c>
+      <x:c r="BD6" t="str">
+        <x:v>B-Code-Unverified</x:v>
+      </x:c>
+      <x:c r="BE6" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="BF6" t="str">
+        <x:v>Unavailable</x:v>
+      </x:c>
+      <x:c r="BG6" t="str">
+        <x:v>Simulation plus real-world replication</x:v>
+      </x:c>
     </x:row>
     <x:row r="7" ht="62" customHeight="1">
       <x:c r="A7" t="str">
@@ -34376,6 +36276,18 @@
       <x:c r="BC7" t="str">
         <x:v>IEEE Xplore abstract; official project page</x:v>
       </x:c>
+      <x:c r="BD7" t="str">
+        <x:v>B-Fulltext-Unavailable</x:v>
+      </x:c>
+      <x:c r="BE7" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="BF7" t="str">
+        <x:v>Mostly Complete</x:v>
+      </x:c>
+      <x:c r="BG7" t="str">
+        <x:v>Dual robot arms; exact model pending full-paper check</x:v>
+      </x:c>
     </x:row>
     <x:row r="8" ht="62" customHeight="1">
       <x:c r="A8" t="str">
@@ -34543,6 +36455,18 @@
       <x:c r="BC8" t="str">
         <x:v>IEEE Xplore abstract</x:v>
       </x:c>
+      <x:c r="BD8" t="str">
+        <x:v>B-Code-Unverified</x:v>
+      </x:c>
+      <x:c r="BE8" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="BF8" t="str">
+        <x:v>Unavailable</x:v>
+      </x:c>
+      <x:c r="BG8" t="str">
+        <x:v>Robot arm with visuotactile end effector</x:v>
+      </x:c>
     </x:row>
     <x:row r="9" ht="62" customHeight="1">
       <x:c r="A9" t="str">
@@ -34710,6 +36634,18 @@
       <x:c r="BC9" t="str">
         <x:v>IEEE Xplore abstract</x:v>
       </x:c>
+      <x:c r="BD9" t="str">
+        <x:v>B-Code-Unverified</x:v>
+      </x:c>
+      <x:c r="BE9" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="BF9" t="str">
+        <x:v>Unavailable</x:v>
+      </x:c>
+      <x:c r="BG9" t="str">
+        <x:v>Multiple robotic arms</x:v>
+      </x:c>
     </x:row>
     <x:row r="10" ht="62" customHeight="1">
       <x:c r="A10" t="str">
@@ -34876,6 +36812,18 @@
       </x:c>
       <x:c r="BC10" t="str">
         <x:v>IEEE Xplore abstract</x:v>
+      </x:c>
+      <x:c r="BD10" t="str">
+        <x:v>B-Code-Unverified</x:v>
+      </x:c>
+      <x:c r="BE10" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="BF10" t="str">
+        <x:v>Unavailable</x:v>
+      </x:c>
+      <x:c r="BG10" t="str">
+        <x:v>Multiple hand geometries</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="62" customHeight="1">
@@ -35022,6 +36970,18 @@
       <x:c r="BC11" t="str">
         <x:v>Unknown</x:v>
       </x:c>
+      <x:c r="BD11" t="str">
+        <x:v>B-Fulltext-Unavailable</x:v>
+      </x:c>
+      <x:c r="BE11" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="BF11" t="str">
+        <x:v>Mostly Complete</x:v>
+      </x:c>
+      <x:c r="BG11" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="12" ht="62" customHeight="1">
       <x:c r="A12" t="str">
@@ -35163,6 +37123,18 @@
       <x:c r="BC12" t="str">
         <x:v>Unknown</x:v>
       </x:c>
+      <x:c r="BD12" t="str">
+        <x:v>B-Fulltext-Unavailable</x:v>
+      </x:c>
+      <x:c r="BE12" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="BF12" t="str">
+        <x:v>Mostly Complete</x:v>
+      </x:c>
+      <x:c r="BG12" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="13" ht="62" customHeight="1">
       <x:c r="A13" t="str">
@@ -35304,6 +37276,18 @@
       <x:c r="BC13" t="str">
         <x:v>Unknown</x:v>
       </x:c>
+      <x:c r="BD13" t="str">
+        <x:v>B-Fulltext-Unavailable</x:v>
+      </x:c>
+      <x:c r="BE13" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="BF13" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BG13" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
     </x:row>
     <x:row r="14" ht="62" customHeight="1">
       <x:c r="A14" t="str">
@@ -35443,6 +37427,18 @@
         <x:v>Unknown (no high-confidence match)</x:v>
       </x:c>
       <x:c r="BC14" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BD14" t="str">
+        <x:v>B-Fulltext-Unavailable</x:v>
+      </x:c>
+      <x:c r="BE14" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="BF14" t="str">
+        <x:v>Mostly Complete</x:v>
+      </x:c>
+      <x:c r="BG14" t="str">
         <x:v>Unknown</x:v>
       </x:c>
     </x:row>
@@ -35463,7 +37459,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd07c215f6a644228"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb371afc4806b4e43"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/00_Paper_Pool/Paper_Pool.xlsx
+++ b/00_Paper_Pool/Paper_Pool.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Papers" sheetId="1" r:id="Rd4ae01dd80cd4d8c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rejected" sheetId="2" r:id="R045ebd6a5fb24004"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Venues" sheetId="3" r:id="R255adb3d1f524f1a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Keywords" sheetId="4" r:id="Rd38c8746b1a14fab"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Discovery" sheetId="5" r:id="Rf744afbc81b541c0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CCF_A_Library" sheetId="6" r:id="Rf53b9c3f8f264abb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Robotics_Core_Library" sheetId="7" r:id="R34449d90d2e84a8a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Papers" sheetId="1" r:id="R701641b7409142a7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rejected" sheetId="2" r:id="R1558b6a60fa64e25"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Venues" sheetId="3" r:id="R70b64d35efd546c5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Keywords" sheetId="4" r:id="R819c9bf184d84ec7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Discovery" sheetId="5" r:id="Rba8f19defe2b4beb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CCF_A_Library" sheetId="6" r:id="R88f4c2d47b3747c5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Robotics_Core_Library" sheetId="7" r:id="R82cd8b97fb794536"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="24" name="PapersTable" displayName="PapersTable" ref="A1:BD5" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:tableColumns count="56">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="36" name="PapersTable" displayName="PapersTable" ref="A1:BP5" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:tableColumns count="68">
     <x:tableColumn id="1" name="编号 ID"/>
     <x:tableColumn id="2" name="论文标题 Title"/>
     <x:tableColumn id="3" name="年份 Year"/>
@@ -358,6 +358,18 @@
     <x:tableColumn id="54" name="Supplement Status"/>
     <x:tableColumn id="55" name="Code Completeness"/>
     <x:tableColumn id="56" name="Robot Platform Evidence"/>
+    <x:tableColumn id="57" name="Fulltext URL"/>
+    <x:tableColumn id="58" name="Fulltext Checked"/>
+    <x:tableColumn id="59" name="Experiment Extracted"/>
+    <x:tableColumn id="60" name="Results Extracted"/>
+    <x:tableColumn id="61" name="Ablation Extracted"/>
+    <x:tableColumn id="62" name="Failure Cases Extracted"/>
+    <x:tableColumn id="63" name="Limitations Extracted"/>
+    <x:tableColumn id="64" name="Remaining Gap Extracted"/>
+    <x:tableColumn id="65" name="Citation Status"/>
+    <x:tableColumn id="66" name="DOI Status"/>
+    <x:tableColumn id="67" name="arXiv Status"/>
+    <x:tableColumn id="68" name="Deep Enrichment Status"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
@@ -409,8 +421,8 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="25" name="DiscoveryTable" displayName="DiscoveryTable" ref="A1:AY79" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:tableColumns count="51">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="37" name="DiscoveryTable" displayName="DiscoveryTable" ref="A1:BK79" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:tableColumns count="63">
     <x:tableColumn id="1" name="编号 ID"/>
     <x:tableColumn id="2" name="论文标题 Title"/>
     <x:tableColumn id="3" name="年份 Year"/>
@@ -462,14 +474,26 @@
     <x:tableColumn id="49" name="Supplement Status"/>
     <x:tableColumn id="50" name="Code Completeness"/>
     <x:tableColumn id="51" name="Robot Platform Evidence"/>
+    <x:tableColumn id="52" name="Fulltext URL"/>
+    <x:tableColumn id="53" name="Fulltext Checked"/>
+    <x:tableColumn id="54" name="Experiment Extracted"/>
+    <x:tableColumn id="55" name="Results Extracted"/>
+    <x:tableColumn id="56" name="Ablation Extracted"/>
+    <x:tableColumn id="57" name="Failure Cases Extracted"/>
+    <x:tableColumn id="58" name="Limitations Extracted"/>
+    <x:tableColumn id="59" name="Remaining Gap Extracted"/>
+    <x:tableColumn id="60" name="Citation Status"/>
+    <x:tableColumn id="61" name="DOI Status"/>
+    <x:tableColumn id="62" name="arXiv Status"/>
+    <x:tableColumn id="63" name="Deep Enrichment Status"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="26" name="CCFALibraryTable" displayName="CCFALibraryTable" ref="A1:BR67" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:tableColumns count="70">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="38" name="CCFALibraryTable" displayName="CCFALibraryTable" ref="A1:CD67" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:tableColumns count="82">
     <x:tableColumn id="1" name="编号 ID"/>
     <x:tableColumn id="2" name="论文标题 Title"/>
     <x:tableColumn id="3" name="作者 Authors"/>
@@ -540,14 +564,26 @@
     <x:tableColumn id="68" name="Supplement Status"/>
     <x:tableColumn id="69" name="Code Completeness"/>
     <x:tableColumn id="70" name="Robot Platform Evidence"/>
+    <x:tableColumn id="71" name="Fulltext URL"/>
+    <x:tableColumn id="72" name="Fulltext Checked"/>
+    <x:tableColumn id="73" name="Experiment Extracted"/>
+    <x:tableColumn id="74" name="Results Extracted"/>
+    <x:tableColumn id="75" name="Ablation Extracted"/>
+    <x:tableColumn id="76" name="Failure Cases Extracted"/>
+    <x:tableColumn id="77" name="Limitations Extracted"/>
+    <x:tableColumn id="78" name="Remaining Gap Extracted"/>
+    <x:tableColumn id="79" name="Citation Status"/>
+    <x:tableColumn id="80" name="DOI Status"/>
+    <x:tableColumn id="81" name="arXiv Status"/>
+    <x:tableColumn id="82" name="Deep Enrichment Status"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="27" name="RoboticsCoreLibraryTable" displayName="RoboticsCoreLibraryTable" ref="A1:BG14" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:tableColumns count="59">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="39" name="RoboticsCoreLibraryTable" displayName="RoboticsCoreLibraryTable" ref="A1:BS14" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:tableColumns count="71">
     <x:tableColumn id="1" name="ID"/>
     <x:tableColumn id="2" name="Title"/>
     <x:tableColumn id="3" name="Authors"/>
@@ -607,6 +643,18 @@
     <x:tableColumn id="57" name="Supplement Status"/>
     <x:tableColumn id="58" name="Code Completeness"/>
     <x:tableColumn id="59" name="Robot Platform Evidence"/>
+    <x:tableColumn id="60" name="Fulltext URL"/>
+    <x:tableColumn id="61" name="Fulltext Checked"/>
+    <x:tableColumn id="62" name="Experiment Extracted"/>
+    <x:tableColumn id="63" name="Results Extracted"/>
+    <x:tableColumn id="64" name="Ablation Extracted"/>
+    <x:tableColumn id="65" name="Failure Cases Extracted"/>
+    <x:tableColumn id="66" name="Limitations Extracted"/>
+    <x:tableColumn id="67" name="Remaining Gap Extracted"/>
+    <x:tableColumn id="68" name="Citation Status"/>
+    <x:tableColumn id="69" name="DOI Status"/>
+    <x:tableColumn id="70" name="arXiv Status"/>
+    <x:tableColumn id="71" name="Deep Enrichment Status"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium4" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
@@ -1009,6 +1057,42 @@
       <x:c r="BD1" t="str">
         <x:v>Robot Platform Evidence</x:v>
       </x:c>
+      <x:c r="BE1" t="str">
+        <x:v>Fulltext URL</x:v>
+      </x:c>
+      <x:c r="BF1" t="str">
+        <x:v>Fulltext Checked</x:v>
+      </x:c>
+      <x:c r="BG1" t="str">
+        <x:v>Experiment Extracted</x:v>
+      </x:c>
+      <x:c r="BH1" t="str">
+        <x:v>Results Extracted</x:v>
+      </x:c>
+      <x:c r="BI1" t="str">
+        <x:v>Ablation Extracted</x:v>
+      </x:c>
+      <x:c r="BJ1" t="str">
+        <x:v>Failure Cases Extracted</x:v>
+      </x:c>
+      <x:c r="BK1" t="str">
+        <x:v>Limitations Extracted</x:v>
+      </x:c>
+      <x:c r="BL1" t="str">
+        <x:v>Remaining Gap Extracted</x:v>
+      </x:c>
+      <x:c r="BM1" t="str">
+        <x:v>Citation Status</x:v>
+      </x:c>
+      <x:c r="BN1" t="str">
+        <x:v>DOI Status</x:v>
+      </x:c>
+      <x:c r="BO1" t="str">
+        <x:v>arXiv Status</x:v>
+      </x:c>
+      <x:c r="BP1" t="str">
+        <x:v>Deep Enrichment Status</x:v>
+      </x:c>
     </x:row>
     <x:row r="2" ht="350" customHeight="1">
       <x:c r="A2" t="str">
@@ -1170,13 +1254,47 @@
         <x:v>A-Upgraded</x:v>
       </x:c>
       <x:c r="BB2" t="str">
-        <x:v>Not Checked</x:v>
+        <x:v>Available - Verified</x:v>
       </x:c>
       <x:c r="BC2" t="str">
         <x:v>Partial</x:v>
       </x:c>
       <x:c r="BD2" t="str">
         <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BE2" t="str"/>
+      <x:c r="BF2" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BG2" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BH2" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BI2" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BJ2" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BK2" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BL2" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BM2" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="BN2" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BO2" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BP2" t="str">
+        <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="150" customHeight="1">
@@ -1308,13 +1426,47 @@
         <x:v>B-Fulltext-Unavailable</x:v>
       </x:c>
       <x:c r="BB3" t="str">
-        <x:v>Not Checked</x:v>
+        <x:v>Not Found</x:v>
       </x:c>
       <x:c r="BC3" t="str">
         <x:v>Mostly Complete</x:v>
       </x:c>
       <x:c r="BD3" t="str">
         <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BE3" t="str"/>
+      <x:c r="BF3" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BG3" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BH3" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BI3" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BJ3" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BK3" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BL3" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BM3" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="BN3" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BO3" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BP3" t="str">
+        <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="150" customHeight="1">
@@ -1446,13 +1598,47 @@
         <x:v>B-Fulltext-Unavailable</x:v>
       </x:c>
       <x:c r="BB4" t="str">
-        <x:v>Not Checked</x:v>
+        <x:v>Not Found</x:v>
       </x:c>
       <x:c r="BC4" t="str">
         <x:v>Partial</x:v>
       </x:c>
       <x:c r="BD4" t="str">
         <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BE4" t="str"/>
+      <x:c r="BF4" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BG4" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BH4" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BI4" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BJ4" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BK4" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BL4" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BM4" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="BN4" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BO4" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BP4" t="str">
+        <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="150" customHeight="1">
@@ -1584,13 +1770,47 @@
         <x:v>B-Fulltext-Unavailable</x:v>
       </x:c>
       <x:c r="BB5" t="str">
-        <x:v>Not Checked</x:v>
+        <x:v>Not Found</x:v>
       </x:c>
       <x:c r="BC5" t="str">
         <x:v>Mostly Complete</x:v>
       </x:c>
       <x:c r="BD5" t="str">
         <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BE5" t="str"/>
+      <x:c r="BF5" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BG5" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BH5" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BI5" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BJ5" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BK5" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BL5" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BM5" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="BN5" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BO5" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BP5" t="str">
+        <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -4604,7 +4824,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdb6b3e8902a14813"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7f5167e3362547f5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7900,7 +8120,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re0c56d1d9f95448a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra356fe3872634c89"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8251,7 +8471,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9556a8be6dfd4281"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7cc51529cf3c46fd"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8997,7 +9217,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re8cc26495f454170"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R780f6d2c6bd24827"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9191,6 +9411,42 @@
       <x:c r="AY1" t="str">
         <x:v>Robot Platform Evidence</x:v>
       </x:c>
+      <x:c r="AZ1" t="str">
+        <x:v>Fulltext URL</x:v>
+      </x:c>
+      <x:c r="BA1" t="str">
+        <x:v>Fulltext Checked</x:v>
+      </x:c>
+      <x:c r="BB1" t="str">
+        <x:v>Experiment Extracted</x:v>
+      </x:c>
+      <x:c r="BC1" t="str">
+        <x:v>Results Extracted</x:v>
+      </x:c>
+      <x:c r="BD1" t="str">
+        <x:v>Ablation Extracted</x:v>
+      </x:c>
+      <x:c r="BE1" t="str">
+        <x:v>Failure Cases Extracted</x:v>
+      </x:c>
+      <x:c r="BF1" t="str">
+        <x:v>Limitations Extracted</x:v>
+      </x:c>
+      <x:c r="BG1" t="str">
+        <x:v>Remaining Gap Extracted</x:v>
+      </x:c>
+      <x:c r="BH1" t="str">
+        <x:v>Citation Status</x:v>
+      </x:c>
+      <x:c r="BI1" t="str">
+        <x:v>DOI Status</x:v>
+      </x:c>
+      <x:c r="BJ1" t="str">
+        <x:v>arXiv Status</x:v>
+      </x:c>
+      <x:c r="BK1" t="str">
+        <x:v>Deep Enrichment Status</x:v>
+      </x:c>
     </x:row>
     <x:row r="2" ht="58" customHeight="1">
       <x:c r="A2" t="str">
@@ -9330,13 +9586,47 @@
         <x:v>B-Fulltext-Unavailable</x:v>
       </x:c>
       <x:c r="AW2" t="str">
+        <x:v>Not Found</x:v>
+      </x:c>
+      <x:c r="AX2" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AY2" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AZ2" t="str"/>
+      <x:c r="BA2" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BB2" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BC2" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BD2" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BE2" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BF2" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BG2" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BH2" t="str">
         <x:v>Not Checked</x:v>
       </x:c>
-      <x:c r="AX2" t="str">
-        <x:v>Unknown</x:v>
-      </x:c>
-      <x:c r="AY2" t="str">
-        <x:v>Unknown</x:v>
+      <x:c r="BI2" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BJ2" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BK2" t="str">
+        <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="58" customHeight="1">
@@ -9477,13 +9767,47 @@
         <x:v>B-Fulltext-Unavailable</x:v>
       </x:c>
       <x:c r="AW3" t="str">
+        <x:v>Not Found</x:v>
+      </x:c>
+      <x:c r="AX3" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AY3" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AZ3" t="str"/>
+      <x:c r="BA3" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BB3" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BC3" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BD3" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BE3" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BF3" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BG3" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BH3" t="str">
         <x:v>Not Checked</x:v>
       </x:c>
-      <x:c r="AX3" t="str">
-        <x:v>Unknown</x:v>
-      </x:c>
-      <x:c r="AY3" t="str">
-        <x:v>Unknown</x:v>
+      <x:c r="BI3" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BJ3" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BK3" t="str">
+        <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="58" customHeight="1">
@@ -9624,13 +9948,47 @@
         <x:v>B-Fulltext-Unavailable</x:v>
       </x:c>
       <x:c r="AW4" t="str">
+        <x:v>Not Found</x:v>
+      </x:c>
+      <x:c r="AX4" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AY4" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AZ4" t="str"/>
+      <x:c r="BA4" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BB4" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BC4" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BD4" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BE4" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BF4" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BG4" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BH4" t="str">
         <x:v>Not Checked</x:v>
       </x:c>
-      <x:c r="AX4" t="str">
-        <x:v>Unknown</x:v>
-      </x:c>
-      <x:c r="AY4" t="str">
-        <x:v>Unknown</x:v>
+      <x:c r="BI4" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BJ4" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BK4" t="str">
+        <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="58" customHeight="1">
@@ -9773,13 +10131,47 @@
         <x:v>B-Fulltext-Unavailable</x:v>
       </x:c>
       <x:c r="AW5" t="str">
+        <x:v>Not Found</x:v>
+      </x:c>
+      <x:c r="AX5" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AY5" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AZ5" t="str"/>
+      <x:c r="BA5" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BB5" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BC5" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BD5" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BE5" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BF5" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BG5" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BH5" t="str">
         <x:v>Not Checked</x:v>
       </x:c>
-      <x:c r="AX5" t="str">
-        <x:v>Unknown</x:v>
-      </x:c>
-      <x:c r="AY5" t="str">
-        <x:v>Unknown</x:v>
+      <x:c r="BI5" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BJ5" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BK5" t="str">
+        <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="58" customHeight="1">
@@ -9920,13 +10312,47 @@
         <x:v>B-Fulltext-Unavailable</x:v>
       </x:c>
       <x:c r="AW6" t="str">
+        <x:v>Not Found</x:v>
+      </x:c>
+      <x:c r="AX6" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AY6" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AZ6" t="str"/>
+      <x:c r="BA6" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BB6" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BC6" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BD6" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BE6" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BF6" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BG6" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BH6" t="str">
         <x:v>Not Checked</x:v>
       </x:c>
-      <x:c r="AX6" t="str">
-        <x:v>Unknown</x:v>
-      </x:c>
-      <x:c r="AY6" t="str">
-        <x:v>Unknown</x:v>
+      <x:c r="BI6" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BJ6" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BK6" t="str">
+        <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="58" customHeight="1">
@@ -10067,13 +10493,47 @@
         <x:v>B-Fulltext-Unavailable</x:v>
       </x:c>
       <x:c r="AW7" t="str">
+        <x:v>Not Found</x:v>
+      </x:c>
+      <x:c r="AX7" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AY7" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AZ7" t="str"/>
+      <x:c r="BA7" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BB7" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BC7" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BD7" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BE7" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BF7" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BG7" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BH7" t="str">
         <x:v>Not Checked</x:v>
       </x:c>
-      <x:c r="AX7" t="str">
-        <x:v>Unknown</x:v>
-      </x:c>
-      <x:c r="AY7" t="str">
-        <x:v>Unknown</x:v>
+      <x:c r="BI7" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BJ7" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BK7" t="str">
+        <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="58" customHeight="1">
@@ -10212,13 +10672,47 @@
         <x:v>B-Fulltext-Unavailable</x:v>
       </x:c>
       <x:c r="AW8" t="str">
+        <x:v>Not Found</x:v>
+      </x:c>
+      <x:c r="AX8" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AY8" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AZ8" t="str"/>
+      <x:c r="BA8" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BB8" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BC8" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BD8" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BE8" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BF8" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BG8" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BH8" t="str">
         <x:v>Not Checked</x:v>
       </x:c>
-      <x:c r="AX8" t="str">
-        <x:v>Unknown</x:v>
-      </x:c>
-      <x:c r="AY8" t="str">
-        <x:v>Unknown</x:v>
+      <x:c r="BI8" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BJ8" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BK8" t="str">
+        <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="58" customHeight="1">
@@ -10359,13 +10853,47 @@
         <x:v>B-Fulltext-Unavailable</x:v>
       </x:c>
       <x:c r="AW9" t="str">
+        <x:v>Not Found</x:v>
+      </x:c>
+      <x:c r="AX9" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AY9" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AZ9" t="str"/>
+      <x:c r="BA9" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BB9" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BC9" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BD9" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BE9" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BF9" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BG9" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BH9" t="str">
         <x:v>Not Checked</x:v>
       </x:c>
-      <x:c r="AX9" t="str">
-        <x:v>Unknown</x:v>
-      </x:c>
-      <x:c r="AY9" t="str">
-        <x:v>Unknown</x:v>
+      <x:c r="BI9" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BJ9" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BK9" t="str">
+        <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="58" customHeight="1">
@@ -10504,13 +11032,47 @@
         <x:v>B-Fulltext-Unavailable</x:v>
       </x:c>
       <x:c r="AW10" t="str">
+        <x:v>Not Found</x:v>
+      </x:c>
+      <x:c r="AX10" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AY10" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AZ10" t="str"/>
+      <x:c r="BA10" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BB10" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BC10" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BD10" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BE10" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BF10" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BG10" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BH10" t="str">
         <x:v>Not Checked</x:v>
       </x:c>
-      <x:c r="AX10" t="str">
-        <x:v>Unknown</x:v>
-      </x:c>
-      <x:c r="AY10" t="str">
-        <x:v>Unknown</x:v>
+      <x:c r="BI10" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BJ10" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BK10" t="str">
+        <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="58" customHeight="1">
@@ -10653,13 +11215,47 @@
         <x:v>B-Fulltext-Unavailable</x:v>
       </x:c>
       <x:c r="AW11" t="str">
+        <x:v>Not Found</x:v>
+      </x:c>
+      <x:c r="AX11" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AY11" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AZ11" t="str"/>
+      <x:c r="BA11" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BB11" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BC11" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BD11" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BE11" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BF11" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BG11" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BH11" t="str">
         <x:v>Not Checked</x:v>
       </x:c>
-      <x:c r="AX11" t="str">
-        <x:v>Unknown</x:v>
-      </x:c>
-      <x:c r="AY11" t="str">
-        <x:v>Unknown</x:v>
+      <x:c r="BI11" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BJ11" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BK11" t="str">
+        <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="58" customHeight="1">
@@ -10802,13 +11398,47 @@
         <x:v>B-Fulltext-Unavailable</x:v>
       </x:c>
       <x:c r="AW12" t="str">
+        <x:v>Not Found</x:v>
+      </x:c>
+      <x:c r="AX12" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AY12" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AZ12" t="str"/>
+      <x:c r="BA12" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BB12" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BC12" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BD12" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BE12" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BF12" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BG12" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BH12" t="str">
         <x:v>Not Checked</x:v>
       </x:c>
-      <x:c r="AX12" t="str">
-        <x:v>Unknown</x:v>
-      </x:c>
-      <x:c r="AY12" t="str">
-        <x:v>Unknown</x:v>
+      <x:c r="BI12" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BJ12" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BK12" t="str">
+        <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="58" customHeight="1">
@@ -10951,13 +11581,47 @@
         <x:v>B-Fulltext-Unavailable</x:v>
       </x:c>
       <x:c r="AW13" t="str">
-        <x:v>Not Checked</x:v>
+        <x:v>Not Found</x:v>
       </x:c>
       <x:c r="AX13" t="str">
         <x:v>Mostly Complete</x:v>
       </x:c>
       <x:c r="AY13" t="str">
         <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AZ13" t="str"/>
+      <x:c r="BA13" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BB13" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BC13" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BD13" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BE13" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BF13" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BG13" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BH13" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="BI13" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BJ13" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BK13" t="str">
+        <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="58" customHeight="1">
@@ -11098,13 +11762,47 @@
         <x:v>B-Fulltext-Unavailable</x:v>
       </x:c>
       <x:c r="AW14" t="str">
+        <x:v>Not Found</x:v>
+      </x:c>
+      <x:c r="AX14" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AY14" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AZ14" t="str"/>
+      <x:c r="BA14" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BB14" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BC14" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BD14" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BE14" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BF14" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BG14" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BH14" t="str">
         <x:v>Not Checked</x:v>
       </x:c>
-      <x:c r="AX14" t="str">
-        <x:v>Unknown</x:v>
-      </x:c>
-      <x:c r="AY14" t="str">
-        <x:v>Unknown</x:v>
+      <x:c r="BI14" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BJ14" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BK14" t="str">
+        <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="58" customHeight="1">
@@ -11247,13 +11945,47 @@
         <x:v>B-Fulltext-Unavailable</x:v>
       </x:c>
       <x:c r="AW15" t="str">
+        <x:v>Not Found</x:v>
+      </x:c>
+      <x:c r="AX15" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AY15" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AZ15" t="str"/>
+      <x:c r="BA15" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BB15" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BC15" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BD15" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BE15" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BF15" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BG15" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BH15" t="str">
         <x:v>Not Checked</x:v>
       </x:c>
-      <x:c r="AX15" t="str">
-        <x:v>Unknown</x:v>
-      </x:c>
-      <x:c r="AY15" t="str">
-        <x:v>Unknown</x:v>
+      <x:c r="BI15" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BJ15" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BK15" t="str">
+        <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="58" customHeight="1">
@@ -11392,13 +12124,47 @@
         <x:v>B-Fulltext-Unavailable</x:v>
       </x:c>
       <x:c r="AW16" t="str">
+        <x:v>Not Found</x:v>
+      </x:c>
+      <x:c r="AX16" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AY16" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AZ16" t="str"/>
+      <x:c r="BA16" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BB16" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BC16" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BD16" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BE16" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BF16" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BG16" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BH16" t="str">
         <x:v>Not Checked</x:v>
       </x:c>
-      <x:c r="AX16" t="str">
-        <x:v>Unknown</x:v>
-      </x:c>
-      <x:c r="AY16" t="str">
-        <x:v>Unknown</x:v>
+      <x:c r="BI16" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BJ16" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BK16" t="str">
+        <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="58" customHeight="1">
@@ -11537,13 +12303,47 @@
         <x:v>B-Fulltext-Unavailable</x:v>
       </x:c>
       <x:c r="AW17" t="str">
+        <x:v>Not Found</x:v>
+      </x:c>
+      <x:c r="AX17" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AY17" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AZ17" t="str"/>
+      <x:c r="BA17" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BB17" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BC17" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BD17" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BE17" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BF17" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BG17" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BH17" t="str">
         <x:v>Not Checked</x:v>
       </x:c>
-      <x:c r="AX17" t="str">
-        <x:v>Unknown</x:v>
-      </x:c>
-      <x:c r="AY17" t="str">
-        <x:v>Unknown</x:v>
+      <x:c r="BI17" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BJ17" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BK17" t="str">
+        <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="58" customHeight="1">
@@ -11682,13 +12482,47 @@
         <x:v>B-Fulltext-Unavailable</x:v>
       </x:c>
       <x:c r="AW18" t="str">
+        <x:v>Not Found</x:v>
+      </x:c>
+      <x:c r="AX18" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AY18" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AZ18" t="str"/>
+      <x:c r="BA18" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BB18" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BC18" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BD18" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BE18" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BF18" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BG18" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BH18" t="str">
         <x:v>Not Checked</x:v>
       </x:c>
-      <x:c r="AX18" t="str">
-        <x:v>Unknown</x:v>
-      </x:c>
-      <x:c r="AY18" t="str">
-        <x:v>Unknown</x:v>
+      <x:c r="BI18" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BJ18" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BK18" t="str">
+        <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="58" customHeight="1">
@@ -11829,13 +12663,47 @@
         <x:v>B-Fulltext-Unavailable</x:v>
       </x:c>
       <x:c r="AW19" t="str">
+        <x:v>Not Found</x:v>
+      </x:c>
+      <x:c r="AX19" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AY19" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AZ19" t="str"/>
+      <x:c r="BA19" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BB19" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BC19" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BD19" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BE19" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BF19" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BG19" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BH19" t="str">
         <x:v>Not Checked</x:v>
       </x:c>
-      <x:c r="AX19" t="str">
-        <x:v>Unknown</x:v>
-      </x:c>
-      <x:c r="AY19" t="str">
-        <x:v>Unknown</x:v>
+      <x:c r="BI19" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BJ19" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BK19" t="str">
+        <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="58" customHeight="1">
@@ -11974,13 +12842,47 @@
         <x:v>B-Fulltext-Unavailable</x:v>
       </x:c>
       <x:c r="AW20" t="str">
+        <x:v>Not Found</x:v>
+      </x:c>
+      <x:c r="AX20" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AY20" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AZ20" t="str"/>
+      <x:c r="BA20" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BB20" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BC20" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BD20" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BE20" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BF20" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BG20" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BH20" t="str">
         <x:v>Not Checked</x:v>
       </x:c>
-      <x:c r="AX20" t="str">
-        <x:v>Unknown</x:v>
-      </x:c>
-      <x:c r="AY20" t="str">
-        <x:v>Unknown</x:v>
+      <x:c r="BI20" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BJ20" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BK20" t="str">
+        <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="58" customHeight="1">
@@ -12121,13 +13023,47 @@
         <x:v>B-Fulltext-Unavailable</x:v>
       </x:c>
       <x:c r="AW21" t="str">
+        <x:v>Not Found</x:v>
+      </x:c>
+      <x:c r="AX21" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AY21" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AZ21" t="str"/>
+      <x:c r="BA21" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BB21" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BC21" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BD21" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BE21" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BF21" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BG21" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BH21" t="str">
         <x:v>Not Checked</x:v>
       </x:c>
-      <x:c r="AX21" t="str">
-        <x:v>Unknown</x:v>
-      </x:c>
-      <x:c r="AY21" t="str">
-        <x:v>Unknown</x:v>
+      <x:c r="BI21" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BJ21" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BK21" t="str">
+        <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="58" customHeight="1">
@@ -12268,13 +13204,47 @@
         <x:v>B-Fulltext-Unavailable</x:v>
       </x:c>
       <x:c r="AW22" t="str">
+        <x:v>Not Found</x:v>
+      </x:c>
+      <x:c r="AX22" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AY22" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AZ22" t="str"/>
+      <x:c r="BA22" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BB22" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BC22" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BD22" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BE22" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BF22" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BG22" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BH22" t="str">
         <x:v>Not Checked</x:v>
       </x:c>
-      <x:c r="AX22" t="str">
-        <x:v>Unknown</x:v>
-      </x:c>
-      <x:c r="AY22" t="str">
-        <x:v>Unknown</x:v>
+      <x:c r="BI22" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BJ22" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BK22" t="str">
+        <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="58" customHeight="1">
@@ -12415,13 +13385,47 @@
         <x:v>B-Fulltext-Unavailable</x:v>
       </x:c>
       <x:c r="AW23" t="str">
+        <x:v>Not Found</x:v>
+      </x:c>
+      <x:c r="AX23" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AY23" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AZ23" t="str"/>
+      <x:c r="BA23" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BB23" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BC23" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BD23" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BE23" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BF23" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BG23" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BH23" t="str">
         <x:v>Not Checked</x:v>
       </x:c>
-      <x:c r="AX23" t="str">
-        <x:v>Unknown</x:v>
-      </x:c>
-      <x:c r="AY23" t="str">
-        <x:v>Unknown</x:v>
+      <x:c r="BI23" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BJ23" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BK23" t="str">
+        <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="58" customHeight="1">
@@ -12562,13 +13566,47 @@
         <x:v>B-Fulltext-Unavailable</x:v>
       </x:c>
       <x:c r="AW24" t="str">
+        <x:v>Not Found</x:v>
+      </x:c>
+      <x:c r="AX24" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AY24" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AZ24" t="str"/>
+      <x:c r="BA24" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BB24" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BC24" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BD24" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BE24" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BF24" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BG24" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BH24" t="str">
         <x:v>Not Checked</x:v>
       </x:c>
-      <x:c r="AX24" t="str">
-        <x:v>Unknown</x:v>
-      </x:c>
-      <x:c r="AY24" t="str">
-        <x:v>Unknown</x:v>
+      <x:c r="BI24" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BJ24" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BK24" t="str">
+        <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="58" customHeight="1">
@@ -12707,13 +13745,47 @@
         <x:v>B-Fulltext-Unavailable</x:v>
       </x:c>
       <x:c r="AW25" t="str">
+        <x:v>Not Found</x:v>
+      </x:c>
+      <x:c r="AX25" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AY25" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AZ25" t="str"/>
+      <x:c r="BA25" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BB25" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BC25" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BD25" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BE25" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BF25" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BG25" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BH25" t="str">
         <x:v>Not Checked</x:v>
       </x:c>
-      <x:c r="AX25" t="str">
-        <x:v>Unknown</x:v>
-      </x:c>
-      <x:c r="AY25" t="str">
-        <x:v>Unknown</x:v>
+      <x:c r="BI25" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BJ25" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BK25" t="str">
+        <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="58" customHeight="1">
@@ -12854,13 +13926,47 @@
         <x:v>B-Fulltext-Unavailable</x:v>
       </x:c>
       <x:c r="AW26" t="str">
+        <x:v>Not Found</x:v>
+      </x:c>
+      <x:c r="AX26" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AY26" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AZ26" t="str"/>
+      <x:c r="BA26" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BB26" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BC26" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BD26" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BE26" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BF26" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BG26" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BH26" t="str">
         <x:v>Not Checked</x:v>
       </x:c>
-      <x:c r="AX26" t="str">
-        <x:v>Unknown</x:v>
-      </x:c>
-      <x:c r="AY26" t="str">
-        <x:v>Unknown</x:v>
+      <x:c r="BI26" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BJ26" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BK26" t="str">
+        <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="58" customHeight="1">
@@ -13001,13 +14107,47 @@
         <x:v>B-Fulltext-Unavailable</x:v>
       </x:c>
       <x:c r="AW27" t="str">
+        <x:v>Not Found</x:v>
+      </x:c>
+      <x:c r="AX27" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AY27" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AZ27" t="str"/>
+      <x:c r="BA27" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BB27" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BC27" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BD27" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BE27" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BF27" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BG27" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BH27" t="str">
         <x:v>Not Checked</x:v>
       </x:c>
-      <x:c r="AX27" t="str">
-        <x:v>Unknown</x:v>
-      </x:c>
-      <x:c r="AY27" t="str">
-        <x:v>Unknown</x:v>
+      <x:c r="BI27" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BJ27" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BK27" t="str">
+        <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="58" customHeight="1">
@@ -13148,13 +14288,47 @@
         <x:v>B-Fulltext-Unavailable</x:v>
       </x:c>
       <x:c r="AW28" t="str">
+        <x:v>Not Found</x:v>
+      </x:c>
+      <x:c r="AX28" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AY28" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AZ28" t="str"/>
+      <x:c r="BA28" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BB28" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BC28" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BD28" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BE28" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BF28" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BG28" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BH28" t="str">
         <x:v>Not Checked</x:v>
       </x:c>
-      <x:c r="AX28" t="str">
-        <x:v>Unknown</x:v>
-      </x:c>
-      <x:c r="AY28" t="str">
-        <x:v>Unknown</x:v>
+      <x:c r="BI28" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BJ28" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BK28" t="str">
+        <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
     </x:row>
     <x:row r="29" ht="58" customHeight="1">
@@ -13295,13 +14469,47 @@
         <x:v>B-Fulltext-Unavailable</x:v>
       </x:c>
       <x:c r="AW29" t="str">
+        <x:v>Not Found</x:v>
+      </x:c>
+      <x:c r="AX29" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AY29" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AZ29" t="str"/>
+      <x:c r="BA29" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BB29" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BC29" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BD29" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BE29" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BF29" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BG29" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BH29" t="str">
         <x:v>Not Checked</x:v>
       </x:c>
-      <x:c r="AX29" t="str">
-        <x:v>Unknown</x:v>
-      </x:c>
-      <x:c r="AY29" t="str">
-        <x:v>Unknown</x:v>
+      <x:c r="BI29" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BJ29" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BK29" t="str">
+        <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
     </x:row>
     <x:row r="30" ht="58" customHeight="1">
@@ -13442,13 +14650,47 @@
         <x:v>B-Fulltext-Unavailable</x:v>
       </x:c>
       <x:c r="AW30" t="str">
+        <x:v>Not Found</x:v>
+      </x:c>
+      <x:c r="AX30" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AY30" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AZ30" t="str"/>
+      <x:c r="BA30" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BB30" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BC30" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BD30" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BE30" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BF30" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BG30" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BH30" t="str">
         <x:v>Not Checked</x:v>
       </x:c>
-      <x:c r="AX30" t="str">
-        <x:v>Unknown</x:v>
-      </x:c>
-      <x:c r="AY30" t="str">
-        <x:v>Unknown</x:v>
+      <x:c r="BI30" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BJ30" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BK30" t="str">
+        <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
     </x:row>
     <x:row r="31" ht="58" customHeight="1">
@@ -13589,13 +14831,47 @@
         <x:v>B-Fulltext-Unavailable</x:v>
       </x:c>
       <x:c r="AW31" t="str">
+        <x:v>Not Found</x:v>
+      </x:c>
+      <x:c r="AX31" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AY31" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AZ31" t="str"/>
+      <x:c r="BA31" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BB31" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BC31" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BD31" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BE31" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BF31" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BG31" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BH31" t="str">
         <x:v>Not Checked</x:v>
       </x:c>
-      <x:c r="AX31" t="str">
-        <x:v>Unknown</x:v>
-      </x:c>
-      <x:c r="AY31" t="str">
-        <x:v>Unknown</x:v>
+      <x:c r="BI31" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BJ31" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BK31" t="str">
+        <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
     </x:row>
     <x:row r="32" ht="58" customHeight="1">
@@ -13736,13 +15012,47 @@
         <x:v>B-Fulltext-Unavailable</x:v>
       </x:c>
       <x:c r="AW32" t="str">
+        <x:v>Not Found</x:v>
+      </x:c>
+      <x:c r="AX32" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AY32" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AZ32" t="str"/>
+      <x:c r="BA32" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BB32" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BC32" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BD32" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BE32" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BF32" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BG32" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BH32" t="str">
         <x:v>Not Checked</x:v>
       </x:c>
-      <x:c r="AX32" t="str">
-        <x:v>Unknown</x:v>
-      </x:c>
-      <x:c r="AY32" t="str">
-        <x:v>Unknown</x:v>
+      <x:c r="BI32" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BJ32" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BK32" t="str">
+        <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
     </x:row>
     <x:row r="33" ht="58" customHeight="1">
@@ -13883,13 +15193,47 @@
         <x:v>B-Fulltext-Unavailable</x:v>
       </x:c>
       <x:c r="AW33" t="str">
+        <x:v>Not Found</x:v>
+      </x:c>
+      <x:c r="AX33" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AY33" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AZ33" t="str"/>
+      <x:c r="BA33" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BB33" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BC33" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BD33" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BE33" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BF33" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BG33" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BH33" t="str">
         <x:v>Not Checked</x:v>
       </x:c>
-      <x:c r="AX33" t="str">
-        <x:v>Unknown</x:v>
-      </x:c>
-      <x:c r="AY33" t="str">
-        <x:v>Unknown</x:v>
+      <x:c r="BI33" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BJ33" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BK33" t="str">
+        <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
     </x:row>
     <x:row r="34" ht="58" customHeight="1">
@@ -14030,13 +15374,47 @@
         <x:v>B-Fulltext-Unavailable</x:v>
       </x:c>
       <x:c r="AW34" t="str">
+        <x:v>Not Found</x:v>
+      </x:c>
+      <x:c r="AX34" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AY34" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AZ34" t="str"/>
+      <x:c r="BA34" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BB34" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BC34" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BD34" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BE34" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BF34" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BG34" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BH34" t="str">
         <x:v>Not Checked</x:v>
       </x:c>
-      <x:c r="AX34" t="str">
-        <x:v>Unknown</x:v>
-      </x:c>
-      <x:c r="AY34" t="str">
-        <x:v>Unknown</x:v>
+      <x:c r="BI34" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BJ34" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BK34" t="str">
+        <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
     </x:row>
     <x:row r="35" ht="58" customHeight="1">
@@ -14177,13 +15555,47 @@
         <x:v>B-Fulltext-Unavailable</x:v>
       </x:c>
       <x:c r="AW35" t="str">
+        <x:v>Not Found</x:v>
+      </x:c>
+      <x:c r="AX35" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AY35" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AZ35" t="str"/>
+      <x:c r="BA35" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BB35" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BC35" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BD35" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BE35" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BF35" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BG35" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BH35" t="str">
         <x:v>Not Checked</x:v>
       </x:c>
-      <x:c r="AX35" t="str">
-        <x:v>Unknown</x:v>
-      </x:c>
-      <x:c r="AY35" t="str">
-        <x:v>Unknown</x:v>
+      <x:c r="BI35" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BJ35" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BK35" t="str">
+        <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
     </x:row>
     <x:row r="36" ht="58" customHeight="1">
@@ -14324,13 +15736,47 @@
         <x:v>B-Fulltext-Unavailable</x:v>
       </x:c>
       <x:c r="AW36" t="str">
+        <x:v>Not Found</x:v>
+      </x:c>
+      <x:c r="AX36" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AY36" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AZ36" t="str"/>
+      <x:c r="BA36" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BB36" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BC36" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BD36" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BE36" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BF36" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BG36" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BH36" t="str">
         <x:v>Not Checked</x:v>
       </x:c>
-      <x:c r="AX36" t="str">
-        <x:v>Unknown</x:v>
-      </x:c>
-      <x:c r="AY36" t="str">
-        <x:v>Unknown</x:v>
+      <x:c r="BI36" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BJ36" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BK36" t="str">
+        <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
     </x:row>
     <x:row r="37" ht="58" customHeight="1">
@@ -14471,13 +15917,47 @@
         <x:v>B-Fulltext-Unavailable</x:v>
       </x:c>
       <x:c r="AW37" t="str">
+        <x:v>Not Found</x:v>
+      </x:c>
+      <x:c r="AX37" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AY37" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AZ37" t="str"/>
+      <x:c r="BA37" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BB37" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BC37" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BD37" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BE37" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BF37" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BG37" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BH37" t="str">
         <x:v>Not Checked</x:v>
       </x:c>
-      <x:c r="AX37" t="str">
-        <x:v>Unknown</x:v>
-      </x:c>
-      <x:c r="AY37" t="str">
-        <x:v>Unknown</x:v>
+      <x:c r="BI37" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BJ37" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BK37" t="str">
+        <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
     </x:row>
     <x:row r="38" ht="58" customHeight="1">
@@ -14618,13 +16098,47 @@
         <x:v>B-Fulltext-Unavailable</x:v>
       </x:c>
       <x:c r="AW38" t="str">
+        <x:v>Not Found</x:v>
+      </x:c>
+      <x:c r="AX38" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AY38" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AZ38" t="str"/>
+      <x:c r="BA38" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BB38" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BC38" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BD38" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BE38" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BF38" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BG38" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BH38" t="str">
         <x:v>Not Checked</x:v>
       </x:c>
-      <x:c r="AX38" t="str">
-        <x:v>Unknown</x:v>
-      </x:c>
-      <x:c r="AY38" t="str">
-        <x:v>Unknown</x:v>
+      <x:c r="BI38" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BJ38" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BK38" t="str">
+        <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
     </x:row>
     <x:row r="39" ht="58" customHeight="1">
@@ -14765,13 +16279,47 @@
         <x:v>B-Fulltext-Unavailable</x:v>
       </x:c>
       <x:c r="AW39" t="str">
+        <x:v>Not Found</x:v>
+      </x:c>
+      <x:c r="AX39" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AY39" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AZ39" t="str"/>
+      <x:c r="BA39" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BB39" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BC39" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BD39" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BE39" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BF39" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BG39" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BH39" t="str">
         <x:v>Not Checked</x:v>
       </x:c>
-      <x:c r="AX39" t="str">
-        <x:v>Unknown</x:v>
-      </x:c>
-      <x:c r="AY39" t="str">
-        <x:v>Unknown</x:v>
+      <x:c r="BI39" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BJ39" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BK39" t="str">
+        <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
     </x:row>
     <x:row r="40" ht="58" customHeight="1">
@@ -14910,13 +16458,47 @@
         <x:v>B-Fulltext-Unavailable</x:v>
       </x:c>
       <x:c r="AW40" t="str">
+        <x:v>Not Found</x:v>
+      </x:c>
+      <x:c r="AX40" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AY40" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AZ40" t="str"/>
+      <x:c r="BA40" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BB40" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BC40" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BD40" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BE40" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BF40" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BG40" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BH40" t="str">
         <x:v>Not Checked</x:v>
       </x:c>
-      <x:c r="AX40" t="str">
-        <x:v>Unknown</x:v>
-      </x:c>
-      <x:c r="AY40" t="str">
-        <x:v>Unknown</x:v>
+      <x:c r="BI40" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BJ40" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BK40" t="str">
+        <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
     </x:row>
     <x:row r="41" ht="58" customHeight="1">
@@ -15055,13 +16637,47 @@
         <x:v>B-Fulltext-Unavailable</x:v>
       </x:c>
       <x:c r="AW41" t="str">
+        <x:v>Not Found</x:v>
+      </x:c>
+      <x:c r="AX41" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AY41" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AZ41" t="str"/>
+      <x:c r="BA41" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BB41" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BC41" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BD41" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BE41" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BF41" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BG41" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BH41" t="str">
         <x:v>Not Checked</x:v>
       </x:c>
-      <x:c r="AX41" t="str">
-        <x:v>Unknown</x:v>
-      </x:c>
-      <x:c r="AY41" t="str">
-        <x:v>Unknown</x:v>
+      <x:c r="BI41" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BJ41" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BK41" t="str">
+        <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
     </x:row>
     <x:row r="42" ht="58" customHeight="1">
@@ -15200,13 +16816,47 @@
         <x:v>B-Fulltext-Unavailable</x:v>
       </x:c>
       <x:c r="AW42" t="str">
+        <x:v>Not Found</x:v>
+      </x:c>
+      <x:c r="AX42" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AY42" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AZ42" t="str"/>
+      <x:c r="BA42" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BB42" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BC42" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BD42" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BE42" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BF42" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BG42" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BH42" t="str">
         <x:v>Not Checked</x:v>
       </x:c>
-      <x:c r="AX42" t="str">
-        <x:v>Unknown</x:v>
-      </x:c>
-      <x:c r="AY42" t="str">
-        <x:v>Unknown</x:v>
+      <x:c r="BI42" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BJ42" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BK42" t="str">
+        <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
     </x:row>
     <x:row r="43" ht="58" customHeight="1">
@@ -15345,13 +16995,47 @@
         <x:v>B-Fulltext-Unavailable</x:v>
       </x:c>
       <x:c r="AW43" t="str">
+        <x:v>Not Found</x:v>
+      </x:c>
+      <x:c r="AX43" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AY43" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AZ43" t="str"/>
+      <x:c r="BA43" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BB43" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BC43" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BD43" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BE43" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BF43" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BG43" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BH43" t="str">
         <x:v>Not Checked</x:v>
       </x:c>
-      <x:c r="AX43" t="str">
-        <x:v>Unknown</x:v>
-      </x:c>
-      <x:c r="AY43" t="str">
-        <x:v>Unknown</x:v>
+      <x:c r="BI43" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BJ43" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BK43" t="str">
+        <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
     </x:row>
     <x:row r="44" ht="58" customHeight="1">
@@ -15490,13 +17174,47 @@
         <x:v>B-Fulltext-Unavailable</x:v>
       </x:c>
       <x:c r="AW44" t="str">
+        <x:v>Not Found</x:v>
+      </x:c>
+      <x:c r="AX44" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AY44" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AZ44" t="str"/>
+      <x:c r="BA44" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BB44" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BC44" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BD44" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BE44" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BF44" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BG44" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BH44" t="str">
         <x:v>Not Checked</x:v>
       </x:c>
-      <x:c r="AX44" t="str">
-        <x:v>Unknown</x:v>
-      </x:c>
-      <x:c r="AY44" t="str">
-        <x:v>Unknown</x:v>
+      <x:c r="BI44" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BJ44" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BK44" t="str">
+        <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
     </x:row>
     <x:row r="45" ht="58" customHeight="1">
@@ -15635,13 +17353,47 @@
         <x:v>B-Fulltext-Unavailable</x:v>
       </x:c>
       <x:c r="AW45" t="str">
+        <x:v>Not Found</x:v>
+      </x:c>
+      <x:c r="AX45" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AY45" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AZ45" t="str"/>
+      <x:c r="BA45" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BB45" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BC45" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BD45" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BE45" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BF45" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BG45" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BH45" t="str">
         <x:v>Not Checked</x:v>
       </x:c>
-      <x:c r="AX45" t="str">
-        <x:v>Unknown</x:v>
-      </x:c>
-      <x:c r="AY45" t="str">
-        <x:v>Unknown</x:v>
+      <x:c r="BI45" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BJ45" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BK45" t="str">
+        <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
     </x:row>
     <x:row r="46" ht="58" customHeight="1">
@@ -15782,13 +17534,47 @@
         <x:v>B-Fulltext-Unavailable</x:v>
       </x:c>
       <x:c r="AW46" t="str">
+        <x:v>Not Found</x:v>
+      </x:c>
+      <x:c r="AX46" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AY46" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AZ46" t="str"/>
+      <x:c r="BA46" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BB46" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BC46" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BD46" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BE46" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BF46" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BG46" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BH46" t="str">
         <x:v>Not Checked</x:v>
       </x:c>
-      <x:c r="AX46" t="str">
-        <x:v>Unknown</x:v>
-      </x:c>
-      <x:c r="AY46" t="str">
-        <x:v>Unknown</x:v>
+      <x:c r="BI46" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BJ46" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BK46" t="str">
+        <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
     </x:row>
     <x:row r="47" ht="58" customHeight="1">
@@ -15929,13 +17715,47 @@
         <x:v>B-Fulltext-Unavailable</x:v>
       </x:c>
       <x:c r="AW47" t="str">
+        <x:v>Not Found</x:v>
+      </x:c>
+      <x:c r="AX47" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AY47" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AZ47" t="str"/>
+      <x:c r="BA47" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BB47" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BC47" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BD47" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BE47" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BF47" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BG47" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BH47" t="str">
         <x:v>Not Checked</x:v>
       </x:c>
-      <x:c r="AX47" t="str">
-        <x:v>Unknown</x:v>
-      </x:c>
-      <x:c r="AY47" t="str">
-        <x:v>Unknown</x:v>
+      <x:c r="BI47" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BJ47" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BK47" t="str">
+        <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
     </x:row>
     <x:row r="48" ht="58" customHeight="1">
@@ -16076,13 +17896,47 @@
         <x:v>B-Fulltext-Unavailable</x:v>
       </x:c>
       <x:c r="AW48" t="str">
+        <x:v>Not Found</x:v>
+      </x:c>
+      <x:c r="AX48" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AY48" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AZ48" t="str"/>
+      <x:c r="BA48" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BB48" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BC48" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BD48" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BE48" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BF48" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BG48" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BH48" t="str">
         <x:v>Not Checked</x:v>
       </x:c>
-      <x:c r="AX48" t="str">
-        <x:v>Unknown</x:v>
-      </x:c>
-      <x:c r="AY48" t="str">
-        <x:v>Unknown</x:v>
+      <x:c r="BI48" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BJ48" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BK48" t="str">
+        <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
     </x:row>
     <x:row r="49" ht="58" customHeight="1">
@@ -16223,13 +18077,47 @@
         <x:v>B-Fulltext-Unavailable</x:v>
       </x:c>
       <x:c r="AW49" t="str">
+        <x:v>Not Found</x:v>
+      </x:c>
+      <x:c r="AX49" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AY49" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AZ49" t="str"/>
+      <x:c r="BA49" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BB49" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BC49" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BD49" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BE49" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BF49" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BG49" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BH49" t="str">
         <x:v>Not Checked</x:v>
       </x:c>
-      <x:c r="AX49" t="str">
-        <x:v>Unknown</x:v>
-      </x:c>
-      <x:c r="AY49" t="str">
-        <x:v>Unknown</x:v>
+      <x:c r="BI49" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BJ49" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BK49" t="str">
+        <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
     </x:row>
     <x:row r="50" ht="58" customHeight="1">
@@ -16370,13 +18258,47 @@
         <x:v>B-Fulltext-Unavailable</x:v>
       </x:c>
       <x:c r="AW50" t="str">
+        <x:v>Not Found</x:v>
+      </x:c>
+      <x:c r="AX50" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AY50" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AZ50" t="str"/>
+      <x:c r="BA50" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BB50" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BC50" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BD50" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BE50" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BF50" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BG50" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BH50" t="str">
         <x:v>Not Checked</x:v>
       </x:c>
-      <x:c r="AX50" t="str">
-        <x:v>Unknown</x:v>
-      </x:c>
-      <x:c r="AY50" t="str">
-        <x:v>Unknown</x:v>
+      <x:c r="BI50" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BJ50" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BK50" t="str">
+        <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
     </x:row>
     <x:row r="51" ht="58" customHeight="1">
@@ -16517,13 +18439,47 @@
         <x:v>B-Fulltext-Unavailable</x:v>
       </x:c>
       <x:c r="AW51" t="str">
+        <x:v>Not Found</x:v>
+      </x:c>
+      <x:c r="AX51" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AY51" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AZ51" t="str"/>
+      <x:c r="BA51" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BB51" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BC51" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BD51" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BE51" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BF51" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BG51" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BH51" t="str">
         <x:v>Not Checked</x:v>
       </x:c>
-      <x:c r="AX51" t="str">
-        <x:v>Unknown</x:v>
-      </x:c>
-      <x:c r="AY51" t="str">
-        <x:v>Unknown</x:v>
+      <x:c r="BI51" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BJ51" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BK51" t="str">
+        <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
     </x:row>
     <x:row r="52" ht="58" customHeight="1">
@@ -16664,13 +18620,47 @@
         <x:v>B-Fulltext-Unavailable</x:v>
       </x:c>
       <x:c r="AW52" t="str">
+        <x:v>Not Found</x:v>
+      </x:c>
+      <x:c r="AX52" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AY52" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AZ52" t="str"/>
+      <x:c r="BA52" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BB52" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BC52" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BD52" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BE52" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BF52" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BG52" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BH52" t="str">
         <x:v>Not Checked</x:v>
       </x:c>
-      <x:c r="AX52" t="str">
-        <x:v>Unknown</x:v>
-      </x:c>
-      <x:c r="AY52" t="str">
-        <x:v>Unknown</x:v>
+      <x:c r="BI52" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BJ52" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BK52" t="str">
+        <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
     </x:row>
     <x:row r="53" ht="58" customHeight="1">
@@ -16811,13 +18801,47 @@
         <x:v>B-Fulltext-Unavailable</x:v>
       </x:c>
       <x:c r="AW53" t="str">
+        <x:v>Not Found</x:v>
+      </x:c>
+      <x:c r="AX53" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AY53" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AZ53" t="str"/>
+      <x:c r="BA53" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BB53" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BC53" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BD53" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BE53" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BF53" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BG53" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BH53" t="str">
         <x:v>Not Checked</x:v>
       </x:c>
-      <x:c r="AX53" t="str">
-        <x:v>Unknown</x:v>
-      </x:c>
-      <x:c r="AY53" t="str">
-        <x:v>Unknown</x:v>
+      <x:c r="BI53" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BJ53" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BK53" t="str">
+        <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
     </x:row>
     <x:row r="54" ht="58" customHeight="1">
@@ -16958,13 +18982,47 @@
         <x:v>B-Fulltext-Unavailable</x:v>
       </x:c>
       <x:c r="AW54" t="str">
+        <x:v>Not Found</x:v>
+      </x:c>
+      <x:c r="AX54" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AY54" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AZ54" t="str"/>
+      <x:c r="BA54" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BB54" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BC54" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BD54" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BE54" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BF54" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BG54" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BH54" t="str">
         <x:v>Not Checked</x:v>
       </x:c>
-      <x:c r="AX54" t="str">
-        <x:v>Unknown</x:v>
-      </x:c>
-      <x:c r="AY54" t="str">
-        <x:v>Unknown</x:v>
+      <x:c r="BI54" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BJ54" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BK54" t="str">
+        <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
     </x:row>
     <x:row r="55" ht="58" customHeight="1">
@@ -17105,13 +19163,47 @@
         <x:v>B-Fulltext-Unavailable</x:v>
       </x:c>
       <x:c r="AW55" t="str">
+        <x:v>Not Found</x:v>
+      </x:c>
+      <x:c r="AX55" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AY55" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AZ55" t="str"/>
+      <x:c r="BA55" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BB55" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BC55" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BD55" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BE55" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BF55" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BG55" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BH55" t="str">
         <x:v>Not Checked</x:v>
       </x:c>
-      <x:c r="AX55" t="str">
-        <x:v>Unknown</x:v>
-      </x:c>
-      <x:c r="AY55" t="str">
-        <x:v>Unknown</x:v>
+      <x:c r="BI55" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BJ55" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BK55" t="str">
+        <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
     </x:row>
     <x:row r="56" ht="58" customHeight="1">
@@ -17252,13 +19344,47 @@
         <x:v>B-Fulltext-Unavailable</x:v>
       </x:c>
       <x:c r="AW56" t="str">
+        <x:v>Not Found</x:v>
+      </x:c>
+      <x:c r="AX56" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AY56" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AZ56" t="str"/>
+      <x:c r="BA56" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BB56" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BC56" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BD56" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BE56" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BF56" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BG56" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BH56" t="str">
         <x:v>Not Checked</x:v>
       </x:c>
-      <x:c r="AX56" t="str">
-        <x:v>Unknown</x:v>
-      </x:c>
-      <x:c r="AY56" t="str">
-        <x:v>Unknown</x:v>
+      <x:c r="BI56" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BJ56" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BK56" t="str">
+        <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
     </x:row>
     <x:row r="57" ht="58" customHeight="1">
@@ -17399,13 +19525,47 @@
         <x:v>B-Fulltext-Unavailable</x:v>
       </x:c>
       <x:c r="AW57" t="str">
+        <x:v>Not Found</x:v>
+      </x:c>
+      <x:c r="AX57" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AY57" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AZ57" t="str"/>
+      <x:c r="BA57" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BB57" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BC57" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BD57" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BE57" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BF57" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BG57" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BH57" t="str">
         <x:v>Not Checked</x:v>
       </x:c>
-      <x:c r="AX57" t="str">
-        <x:v>Unknown</x:v>
-      </x:c>
-      <x:c r="AY57" t="str">
-        <x:v>Unknown</x:v>
+      <x:c r="BI57" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BJ57" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BK57" t="str">
+        <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
     </x:row>
     <x:row r="58" ht="58" customHeight="1">
@@ -17552,13 +19712,47 @@
         <x:v>B-Fulltext-Unavailable</x:v>
       </x:c>
       <x:c r="AW58" t="str">
-        <x:v>Not Checked</x:v>
+        <x:v>Not Found</x:v>
       </x:c>
       <x:c r="AX58" t="str">
         <x:v>Mostly Complete</x:v>
       </x:c>
       <x:c r="AY58" t="str">
         <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AZ58" t="str"/>
+      <x:c r="BA58" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BB58" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BC58" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BD58" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BE58" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BF58" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BG58" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BH58" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="BI58" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BJ58" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BK58" t="str">
+        <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
     </x:row>
     <x:row r="59" ht="58" customHeight="1">
@@ -17705,13 +19899,47 @@
         <x:v>B-Fulltext-Unavailable</x:v>
       </x:c>
       <x:c r="AW59" t="str">
-        <x:v>Not Checked</x:v>
+        <x:v>Not Found</x:v>
       </x:c>
       <x:c r="AX59" t="str">
         <x:v>Mostly Complete</x:v>
       </x:c>
       <x:c r="AY59" t="str">
         <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AZ59" t="str"/>
+      <x:c r="BA59" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BB59" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BC59" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BD59" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BE59" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BF59" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BG59" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BH59" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="BI59" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BJ59" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BK59" t="str">
+        <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
     </x:row>
     <x:row r="60" ht="58" customHeight="1">
@@ -17856,13 +20084,47 @@
         <x:v>B-Fulltext-Unavailable</x:v>
       </x:c>
       <x:c r="AW60" t="str">
-        <x:v>Not Checked</x:v>
+        <x:v>Not Found</x:v>
       </x:c>
       <x:c r="AX60" t="str">
         <x:v>Mostly Complete</x:v>
       </x:c>
       <x:c r="AY60" t="str">
         <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AZ60" t="str"/>
+      <x:c r="BA60" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BB60" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BC60" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BD60" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BE60" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BF60" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BG60" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BH60" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="BI60" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BJ60" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BK60" t="str">
+        <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
     </x:row>
     <x:row r="61" ht="58" customHeight="1">
@@ -18009,13 +20271,47 @@
         <x:v>B-Fulltext-Unavailable</x:v>
       </x:c>
       <x:c r="AW61" t="str">
-        <x:v>Not Checked</x:v>
+        <x:v>Not Found</x:v>
       </x:c>
       <x:c r="AX61" t="str">
         <x:v>Mostly Complete</x:v>
       </x:c>
       <x:c r="AY61" t="str">
         <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AZ61" t="str"/>
+      <x:c r="BA61" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BB61" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BC61" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BD61" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BE61" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BF61" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BG61" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BH61" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="BI61" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BJ61" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BK61" t="str">
+        <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
     </x:row>
     <x:row r="62" ht="58" customHeight="1">
@@ -18162,13 +20458,47 @@
         <x:v>B-Fulltext-Unavailable</x:v>
       </x:c>
       <x:c r="AW62" t="str">
-        <x:v>Not Checked</x:v>
+        <x:v>Not Found</x:v>
       </x:c>
       <x:c r="AX62" t="str">
         <x:v>Mostly Complete</x:v>
       </x:c>
       <x:c r="AY62" t="str">
         <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AZ62" t="str"/>
+      <x:c r="BA62" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BB62" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BC62" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BD62" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BE62" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BF62" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BG62" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BH62" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="BI62" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BJ62" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BK62" t="str">
+        <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
     </x:row>
     <x:row r="63" ht="58" customHeight="1">
@@ -18315,13 +20645,47 @@
         <x:v>B-Fulltext-Unavailable</x:v>
       </x:c>
       <x:c r="AW63" t="str">
-        <x:v>Not Checked</x:v>
+        <x:v>Not Found</x:v>
       </x:c>
       <x:c r="AX63" t="str">
         <x:v>Partial</x:v>
       </x:c>
       <x:c r="AY63" t="str">
         <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AZ63" t="str"/>
+      <x:c r="BA63" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BB63" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BC63" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BD63" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BE63" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BF63" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BG63" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BH63" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="BI63" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BJ63" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BK63" t="str">
+        <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
     </x:row>
     <x:row r="64" ht="58" customHeight="1">
@@ -18468,13 +20832,47 @@
         <x:v>B-Fulltext-Unavailable</x:v>
       </x:c>
       <x:c r="AW64" t="str">
-        <x:v>Not Checked</x:v>
+        <x:v>Not Found</x:v>
       </x:c>
       <x:c r="AX64" t="str">
         <x:v>Partial</x:v>
       </x:c>
       <x:c r="AY64" t="str">
         <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AZ64" t="str"/>
+      <x:c r="BA64" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BB64" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BC64" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BD64" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BE64" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BF64" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BG64" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BH64" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="BI64" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BJ64" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BK64" t="str">
+        <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
     </x:row>
     <x:row r="65" ht="58" customHeight="1">
@@ -18621,13 +21019,47 @@
         <x:v>B-Fulltext-Unavailable</x:v>
       </x:c>
       <x:c r="AW65" t="str">
-        <x:v>Not Checked</x:v>
+        <x:v>Not Found</x:v>
       </x:c>
       <x:c r="AX65" t="str">
         <x:v>Partial</x:v>
       </x:c>
       <x:c r="AY65" t="str">
         <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AZ65" t="str"/>
+      <x:c r="BA65" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BB65" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BC65" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BD65" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BE65" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BF65" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BG65" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BH65" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="BI65" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BJ65" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BK65" t="str">
+        <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
     </x:row>
     <x:row r="66" ht="58" customHeight="1">
@@ -18774,13 +21206,47 @@
         <x:v>B-Fulltext-Unavailable</x:v>
       </x:c>
       <x:c r="AW66" t="str">
-        <x:v>Not Checked</x:v>
+        <x:v>Not Found</x:v>
       </x:c>
       <x:c r="AX66" t="str">
         <x:v>Partial</x:v>
       </x:c>
       <x:c r="AY66" t="str">
         <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AZ66" t="str"/>
+      <x:c r="BA66" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BB66" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BC66" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BD66" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BE66" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BF66" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BG66" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BH66" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="BI66" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BJ66" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BK66" t="str">
+        <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
     </x:row>
     <x:row r="67" ht="58" customHeight="1">
@@ -18927,13 +21393,47 @@
         <x:v>B-Fulltext-Unavailable</x:v>
       </x:c>
       <x:c r="AW67" t="str">
-        <x:v>Not Checked</x:v>
+        <x:v>Not Found</x:v>
       </x:c>
       <x:c r="AX67" t="str">
         <x:v>Mostly Complete</x:v>
       </x:c>
       <x:c r="AY67" t="str">
         <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AZ67" t="str"/>
+      <x:c r="BA67" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BB67" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BC67" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BD67" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BE67" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BF67" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BG67" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BH67" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="BI67" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BJ67" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BK67" t="str">
+        <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
     </x:row>
     <x:row r="68" ht="58" customHeight="1">
@@ -19078,13 +21578,47 @@
         <x:v>B-Fulltext-Unavailable</x:v>
       </x:c>
       <x:c r="AW68" t="str">
-        <x:v>Not Checked</x:v>
+        <x:v>Not Found</x:v>
       </x:c>
       <x:c r="AX68" t="str">
         <x:v>Mostly Complete</x:v>
       </x:c>
       <x:c r="AY68" t="str">
         <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AZ68" t="str"/>
+      <x:c r="BA68" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BB68" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BC68" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BD68" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BE68" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BF68" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BG68" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BH68" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="BI68" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BJ68" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BK68" t="str">
+        <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
     </x:row>
     <x:row r="69" ht="58" customHeight="1">
@@ -19231,13 +21765,47 @@
         <x:v>B-Fulltext-Unavailable</x:v>
       </x:c>
       <x:c r="AW69" t="str">
-        <x:v>Not Checked</x:v>
+        <x:v>Not Found</x:v>
       </x:c>
       <x:c r="AX69" t="str">
         <x:v>Mostly Complete</x:v>
       </x:c>
       <x:c r="AY69" t="str">
         <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AZ69" t="str"/>
+      <x:c r="BA69" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BB69" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BC69" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BD69" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BE69" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BF69" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BG69" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BH69" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="BI69" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BJ69" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BK69" t="str">
+        <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
     </x:row>
     <x:row r="70" ht="58" customHeight="1">
@@ -19384,13 +21952,47 @@
         <x:v>B-Fulltext-Unavailable</x:v>
       </x:c>
       <x:c r="AW70" t="str">
-        <x:v>Not Checked</x:v>
+        <x:v>Not Found</x:v>
       </x:c>
       <x:c r="AX70" t="str">
         <x:v>Mostly Complete</x:v>
       </x:c>
       <x:c r="AY70" t="str">
         <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AZ70" t="str"/>
+      <x:c r="BA70" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BB70" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BC70" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BD70" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BE70" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BF70" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BG70" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BH70" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="BI70" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BJ70" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BK70" t="str">
+        <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
     </x:row>
     <x:row r="71" ht="58" customHeight="1">
@@ -19537,13 +22139,47 @@
         <x:v>B-Fulltext-Unavailable</x:v>
       </x:c>
       <x:c r="AW71" t="str">
-        <x:v>Not Checked</x:v>
+        <x:v>Not Found</x:v>
       </x:c>
       <x:c r="AX71" t="str">
         <x:v>Partial</x:v>
       </x:c>
       <x:c r="AY71" t="str">
         <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AZ71" t="str"/>
+      <x:c r="BA71" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BB71" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BC71" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BD71" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BE71" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BF71" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BG71" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BH71" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="BI71" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BJ71" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BK71" t="str">
+        <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
     </x:row>
     <x:row r="72" ht="58" customHeight="1">
@@ -19690,13 +22326,47 @@
         <x:v>B-Fulltext-Unavailable</x:v>
       </x:c>
       <x:c r="AW72" t="str">
-        <x:v>Not Checked</x:v>
+        <x:v>Not Found</x:v>
       </x:c>
       <x:c r="AX72" t="str">
         <x:v>Mostly Complete</x:v>
       </x:c>
       <x:c r="AY72" t="str">
         <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AZ72" t="str"/>
+      <x:c r="BA72" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BB72" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BC72" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BD72" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BE72" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BF72" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BG72" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BH72" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="BI72" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BJ72" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BK72" t="str">
+        <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
     </x:row>
     <x:row r="73" ht="58" customHeight="1">
@@ -19843,13 +22513,47 @@
         <x:v>B-Fulltext-Unavailable</x:v>
       </x:c>
       <x:c r="AW73" t="str">
-        <x:v>Not Checked</x:v>
+        <x:v>Not Found</x:v>
       </x:c>
       <x:c r="AX73" t="str">
         <x:v>Mostly Complete</x:v>
       </x:c>
       <x:c r="AY73" t="str">
         <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AZ73" t="str"/>
+      <x:c r="BA73" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BB73" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BC73" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BD73" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BE73" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BF73" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BG73" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BH73" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="BI73" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BJ73" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BK73" t="str">
+        <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
     </x:row>
     <x:row r="74" ht="58" customHeight="1">
@@ -19996,13 +22700,47 @@
         <x:v>B-Fulltext-Unavailable</x:v>
       </x:c>
       <x:c r="AW74" t="str">
-        <x:v>Not Checked</x:v>
+        <x:v>Not Found</x:v>
       </x:c>
       <x:c r="AX74" t="str">
         <x:v>Mostly Complete</x:v>
       </x:c>
       <x:c r="AY74" t="str">
         <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AZ74" t="str"/>
+      <x:c r="BA74" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BB74" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BC74" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BD74" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BE74" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BF74" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BG74" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BH74" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="BI74" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BJ74" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BK74" t="str">
+        <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
     </x:row>
     <x:row r="75" ht="58" customHeight="1">
@@ -20149,13 +22887,47 @@
         <x:v>B-Fulltext-Unavailable</x:v>
       </x:c>
       <x:c r="AW75" t="str">
-        <x:v>Not Checked</x:v>
+        <x:v>Not Found</x:v>
       </x:c>
       <x:c r="AX75" t="str">
         <x:v>Mostly Complete</x:v>
       </x:c>
       <x:c r="AY75" t="str">
         <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AZ75" t="str"/>
+      <x:c r="BA75" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BB75" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BC75" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BD75" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BE75" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BF75" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BG75" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BH75" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="BI75" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BJ75" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BK75" t="str">
+        <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
     </x:row>
     <x:row r="76" ht="58" customHeight="1">
@@ -20298,13 +23070,47 @@
         <x:v>B-Fulltext-Unavailable</x:v>
       </x:c>
       <x:c r="AW76" t="str">
-        <x:v>Not Checked</x:v>
+        <x:v>Not Found</x:v>
       </x:c>
       <x:c r="AX76" t="str">
         <x:v>Mostly Complete</x:v>
       </x:c>
       <x:c r="AY76" t="str">
         <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AZ76" t="str"/>
+      <x:c r="BA76" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BB76" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BC76" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BD76" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BE76" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BF76" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BG76" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BH76" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="BI76" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BJ76" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BK76" t="str">
+        <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
     </x:row>
     <x:row r="77" ht="58" customHeight="1">
@@ -20447,13 +23253,47 @@
         <x:v>B-Fulltext-Unavailable</x:v>
       </x:c>
       <x:c r="AW77" t="str">
+        <x:v>Not Found</x:v>
+      </x:c>
+      <x:c r="AX77" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AY77" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AZ77" t="str"/>
+      <x:c r="BA77" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BB77" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BC77" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BD77" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BE77" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BF77" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BG77" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BH77" t="str">
         <x:v>Not Checked</x:v>
       </x:c>
-      <x:c r="AX77" t="str">
-        <x:v>Unknown</x:v>
-      </x:c>
-      <x:c r="AY77" t="str">
-        <x:v>Unknown</x:v>
+      <x:c r="BI77" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BJ77" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BK77" t="str">
+        <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
     </x:row>
     <x:row r="78" ht="58" customHeight="1">
@@ -20596,13 +23436,47 @@
         <x:v>B-Fulltext-Unavailable</x:v>
       </x:c>
       <x:c r="AW78" t="str">
-        <x:v>Not Checked</x:v>
+        <x:v>Not Found</x:v>
       </x:c>
       <x:c r="AX78" t="str">
         <x:v>Mostly Complete</x:v>
       </x:c>
       <x:c r="AY78" t="str">
         <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="AZ78" t="str"/>
+      <x:c r="BA78" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BB78" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BC78" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BD78" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BE78" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BF78" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BG78" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BH78" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="BI78" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BJ78" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BK78" t="str">
+        <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
     </x:row>
     <x:row r="79">
@@ -20730,7 +23604,7 @@
         <x:v>VLA; Robot Manipulation; Visual Grounding; Robot Perception; Implicit Grounding; Gaze-Region Reconstruction; Generalization; Diffusion Transformer</x:v>
       </x:c>
       <x:c r="AP79" t="str">
-        <x:v>B</x:v>
+        <x:v>A</x:v>
       </x:c>
       <x:c r="AQ79" t="str">
         <x:v>Idea Clue 1: test implicit ga</x:v>
@@ -20748,16 +23622,50 @@
         <x:v>https://ojs.aaai.org/index.php/AAAI/article/view/38921；https://arxiv.org/abs/2508.10333；https://zionchow.github.io/ReconVLA/；https://github.com/OpenHelix-Team/ReconVLA</x:v>
       </x:c>
       <x:c r="AV79" t="str">
-        <x:v>B-Experiment-Not-Extracted</x:v>
+        <x:v>A-Upgraded</x:v>
       </x:c>
       <x:c r="AW79" t="str">
-        <x:v>Not Checked</x:v>
+        <x:v>Available - Verified</x:v>
       </x:c>
       <x:c r="AX79" t="str">
         <x:v>Mostly Complete</x:v>
       </x:c>
       <x:c r="AY79" t="str">
         <x:v>Franka Panda (CALVIN simulation); real-world platform not confirmed at abstract level</x:v>
+      </x:c>
+      <x:c r="AZ79" t="str"/>
+      <x:c r="BA79" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BB79" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BC79" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BD79" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BE79" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BF79" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BG79" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BH79" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="BI79" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BJ79" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BK79" t="str">
+        <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -20780,7 +23688,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6fc4c099267640c9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R60e967459dd747e9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -21052,6 +23960,42 @@
       <x:c r="BR1" t="str">
         <x:v>Robot Platform Evidence</x:v>
       </x:c>
+      <x:c r="BS1" t="str">
+        <x:v>Fulltext URL</x:v>
+      </x:c>
+      <x:c r="BT1" t="str">
+        <x:v>Fulltext Checked</x:v>
+      </x:c>
+      <x:c r="BU1" t="str">
+        <x:v>Experiment Extracted</x:v>
+      </x:c>
+      <x:c r="BV1" t="str">
+        <x:v>Results Extracted</x:v>
+      </x:c>
+      <x:c r="BW1" t="str">
+        <x:v>Ablation Extracted</x:v>
+      </x:c>
+      <x:c r="BX1" t="str">
+        <x:v>Failure Cases Extracted</x:v>
+      </x:c>
+      <x:c r="BY1" t="str">
+        <x:v>Limitations Extracted</x:v>
+      </x:c>
+      <x:c r="BZ1" t="str">
+        <x:v>Remaining Gap Extracted</x:v>
+      </x:c>
+      <x:c r="CA1" t="str">
+        <x:v>Citation Status</x:v>
+      </x:c>
+      <x:c r="CB1" t="str">
+        <x:v>DOI Status</x:v>
+      </x:c>
+      <x:c r="CC1" t="str">
+        <x:v>arXiv Status</x:v>
+      </x:c>
+      <x:c r="CD1" t="str">
+        <x:v>Deep Enrichment Status</x:v>
+      </x:c>
     </x:row>
     <x:row r="2" ht="58" customHeight="1">
       <x:c r="A2" t="str">
@@ -21248,13 +24192,47 @@
         <x:v>B-Fulltext-Unavailable</x:v>
       </x:c>
       <x:c r="BP2" t="str">
+        <x:v>Not Found</x:v>
+      </x:c>
+      <x:c r="BQ2" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BR2" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BS2" t="str"/>
+      <x:c r="BT2" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BU2" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BV2" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BW2" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BX2" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BY2" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BZ2" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="CA2" t="str">
         <x:v>Not Checked</x:v>
       </x:c>
-      <x:c r="BQ2" t="str">
-        <x:v>Unknown</x:v>
-      </x:c>
-      <x:c r="BR2" t="str">
-        <x:v>Unknown</x:v>
+      <x:c r="CB2" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="CC2" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="CD2" t="str">
+        <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="58" customHeight="1">
@@ -21452,13 +24430,47 @@
         <x:v>B-Fulltext-Unavailable</x:v>
       </x:c>
       <x:c r="BP3" t="str">
+        <x:v>Not Found</x:v>
+      </x:c>
+      <x:c r="BQ3" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BR3" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BS3" t="str"/>
+      <x:c r="BT3" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BU3" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BV3" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BW3" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BX3" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BY3" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BZ3" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="CA3" t="str">
         <x:v>Not Checked</x:v>
       </x:c>
-      <x:c r="BQ3" t="str">
-        <x:v>Unknown</x:v>
-      </x:c>
-      <x:c r="BR3" t="str">
-        <x:v>Unknown</x:v>
+      <x:c r="CB3" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="CC3" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="CD3" t="str">
+        <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="58" customHeight="1">
@@ -21656,13 +24668,47 @@
         <x:v>B-Fulltext-Unavailable</x:v>
       </x:c>
       <x:c r="BP4" t="str">
+        <x:v>Not Found</x:v>
+      </x:c>
+      <x:c r="BQ4" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BR4" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BS4" t="str"/>
+      <x:c r="BT4" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BU4" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BV4" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BW4" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BX4" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BY4" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BZ4" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="CA4" t="str">
         <x:v>Not Checked</x:v>
       </x:c>
-      <x:c r="BQ4" t="str">
-        <x:v>Unknown</x:v>
-      </x:c>
-      <x:c r="BR4" t="str">
-        <x:v>Unknown</x:v>
+      <x:c r="CB4" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="CC4" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="CD4" t="str">
+        <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="58" customHeight="1">
@@ -21860,13 +24906,47 @@
         <x:v>B-Fulltext-Unavailable</x:v>
       </x:c>
       <x:c r="BP5" t="str">
+        <x:v>Not Found</x:v>
+      </x:c>
+      <x:c r="BQ5" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BR5" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BS5" t="str"/>
+      <x:c r="BT5" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BU5" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BV5" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BW5" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BX5" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BY5" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BZ5" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="CA5" t="str">
         <x:v>Not Checked</x:v>
       </x:c>
-      <x:c r="BQ5" t="str">
-        <x:v>Unknown</x:v>
-      </x:c>
-      <x:c r="BR5" t="str">
-        <x:v>Unknown</x:v>
+      <x:c r="CB5" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="CC5" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="CD5" t="str">
+        <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="58" customHeight="1">
@@ -22064,13 +25144,47 @@
         <x:v>B-Fulltext-Unavailable</x:v>
       </x:c>
       <x:c r="BP6" t="str">
+        <x:v>Not Found</x:v>
+      </x:c>
+      <x:c r="BQ6" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BR6" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BS6" t="str"/>
+      <x:c r="BT6" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BU6" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BV6" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BW6" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BX6" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BY6" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BZ6" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="CA6" t="str">
         <x:v>Not Checked</x:v>
       </x:c>
-      <x:c r="BQ6" t="str">
-        <x:v>Unknown</x:v>
-      </x:c>
-      <x:c r="BR6" t="str">
-        <x:v>Unknown</x:v>
+      <x:c r="CB6" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="CC6" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="CD6" t="str">
+        <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="58" customHeight="1">
@@ -22268,13 +25382,47 @@
         <x:v>B-Fulltext-Unavailable</x:v>
       </x:c>
       <x:c r="BP7" t="str">
+        <x:v>Not Found</x:v>
+      </x:c>
+      <x:c r="BQ7" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BR7" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BS7" t="str"/>
+      <x:c r="BT7" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BU7" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BV7" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BW7" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BX7" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BY7" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BZ7" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="CA7" t="str">
         <x:v>Not Checked</x:v>
       </x:c>
-      <x:c r="BQ7" t="str">
-        <x:v>Unknown</x:v>
-      </x:c>
-      <x:c r="BR7" t="str">
-        <x:v>Unknown</x:v>
+      <x:c r="CB7" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="CC7" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="CD7" t="str">
+        <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="58" customHeight="1">
@@ -22472,13 +25620,47 @@
         <x:v>B-Fulltext-Unavailable</x:v>
       </x:c>
       <x:c r="BP8" t="str">
+        <x:v>Not Found</x:v>
+      </x:c>
+      <x:c r="BQ8" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BR8" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BS8" t="str"/>
+      <x:c r="BT8" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BU8" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BV8" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BW8" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BX8" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BY8" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BZ8" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="CA8" t="str">
         <x:v>Not Checked</x:v>
       </x:c>
-      <x:c r="BQ8" t="str">
-        <x:v>Unknown</x:v>
-      </x:c>
-      <x:c r="BR8" t="str">
-        <x:v>Unknown</x:v>
+      <x:c r="CB8" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="CC8" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="CD8" t="str">
+        <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="58" customHeight="1">
@@ -22674,13 +25856,47 @@
         <x:v>B-Fulltext-Unavailable</x:v>
       </x:c>
       <x:c r="BP9" t="str">
+        <x:v>Not Found</x:v>
+      </x:c>
+      <x:c r="BQ9" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BR9" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BS9" t="str"/>
+      <x:c r="BT9" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BU9" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BV9" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BW9" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BX9" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BY9" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BZ9" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="CA9" t="str">
         <x:v>Not Checked</x:v>
       </x:c>
-      <x:c r="BQ9" t="str">
-        <x:v>Unknown</x:v>
-      </x:c>
-      <x:c r="BR9" t="str">
-        <x:v>Unknown</x:v>
+      <x:c r="CB9" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="CC9" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="CD9" t="str">
+        <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="58" customHeight="1">
@@ -22882,13 +26098,47 @@
         <x:v>B-Fulltext-Unavailable</x:v>
       </x:c>
       <x:c r="BP10" t="str">
-        <x:v>Not Checked</x:v>
+        <x:v>Not Found</x:v>
       </x:c>
       <x:c r="BQ10" t="str">
         <x:v>Mostly Complete</x:v>
       </x:c>
       <x:c r="BR10" t="str">
         <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BS10" t="str"/>
+      <x:c r="BT10" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BU10" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BV10" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BW10" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BX10" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BY10" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BZ10" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="CA10" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="CB10" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="CC10" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="CD10" t="str">
+        <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="58" customHeight="1">
@@ -23092,13 +26342,47 @@
         <x:v>B-Fulltext-Unavailable</x:v>
       </x:c>
       <x:c r="BP11" t="str">
-        <x:v>Not Checked</x:v>
+        <x:v>Not Found</x:v>
       </x:c>
       <x:c r="BQ11" t="str">
         <x:v>Mostly Complete</x:v>
       </x:c>
       <x:c r="BR11" t="str">
         <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BS11" t="str"/>
+      <x:c r="BT11" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BU11" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BV11" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BW11" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BX11" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BY11" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BZ11" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="CA11" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="CB11" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="CC11" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="CD11" t="str">
+        <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="58" customHeight="1">
@@ -23302,13 +26586,47 @@
         <x:v>B-Fulltext-Unavailable</x:v>
       </x:c>
       <x:c r="BP12" t="str">
-        <x:v>Not Checked</x:v>
+        <x:v>Not Found</x:v>
       </x:c>
       <x:c r="BQ12" t="str">
         <x:v>Mostly Complete</x:v>
       </x:c>
       <x:c r="BR12" t="str">
         <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BS12" t="str"/>
+      <x:c r="BT12" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BU12" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BV12" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BW12" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BX12" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BY12" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BZ12" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="CA12" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="CB12" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="CC12" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="CD12" t="str">
+        <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="58" customHeight="1">
@@ -23512,13 +26830,47 @@
         <x:v>B-Fulltext-Unavailable</x:v>
       </x:c>
       <x:c r="BP13" t="str">
-        <x:v>Not Checked</x:v>
+        <x:v>Not Found</x:v>
       </x:c>
       <x:c r="BQ13" t="str">
         <x:v>Partial</x:v>
       </x:c>
       <x:c r="BR13" t="str">
         <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BS13" t="str"/>
+      <x:c r="BT13" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BU13" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BV13" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BW13" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BX13" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BY13" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BZ13" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="CA13" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="CB13" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="CC13" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="CD13" t="str">
+        <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="58" customHeight="1">
@@ -23722,13 +27074,47 @@
         <x:v>B-Fulltext-Unavailable</x:v>
       </x:c>
       <x:c r="BP14" t="str">
-        <x:v>Not Checked</x:v>
+        <x:v>Not Found</x:v>
       </x:c>
       <x:c r="BQ14" t="str">
         <x:v>Partial</x:v>
       </x:c>
       <x:c r="BR14" t="str">
         <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BS14" t="str"/>
+      <x:c r="BT14" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BU14" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BV14" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BW14" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BX14" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BY14" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BZ14" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="CA14" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="CB14" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="CC14" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="CD14" t="str">
+        <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="58" customHeight="1">
@@ -23932,13 +27318,47 @@
         <x:v>B-Fulltext-Unavailable</x:v>
       </x:c>
       <x:c r="BP15" t="str">
-        <x:v>Not Checked</x:v>
+        <x:v>Not Found</x:v>
       </x:c>
       <x:c r="BQ15" t="str">
         <x:v>Partial</x:v>
       </x:c>
       <x:c r="BR15" t="str">
         <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BS15" t="str"/>
+      <x:c r="BT15" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BU15" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BV15" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BW15" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BX15" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BY15" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BZ15" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="CA15" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="CB15" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="CC15" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="CD15" t="str">
+        <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="58" customHeight="1">
@@ -24140,13 +27560,47 @@
         <x:v>B-Fulltext-Unavailable</x:v>
       </x:c>
       <x:c r="BP16" t="str">
-        <x:v>Not Checked</x:v>
+        <x:v>Not Found</x:v>
       </x:c>
       <x:c r="BQ16" t="str">
         <x:v>Mostly Complete</x:v>
       </x:c>
       <x:c r="BR16" t="str">
         <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BS16" t="str"/>
+      <x:c r="BT16" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BU16" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BV16" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BW16" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BX16" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BY16" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BZ16" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="CA16" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="CB16" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="CC16" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="CD16" t="str">
+        <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="58" customHeight="1">
@@ -24350,13 +27804,47 @@
         <x:v>B-Fulltext-Unavailable</x:v>
       </x:c>
       <x:c r="BP17" t="str">
-        <x:v>Not Checked</x:v>
+        <x:v>Not Found</x:v>
       </x:c>
       <x:c r="BQ17" t="str">
         <x:v>Mostly Complete</x:v>
       </x:c>
       <x:c r="BR17" t="str">
         <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BS17" t="str"/>
+      <x:c r="BT17" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BU17" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BV17" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BW17" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BX17" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BY17" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BZ17" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="CA17" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="CB17" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="CC17" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="CD17" t="str">
+        <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="58" customHeight="1">
@@ -24560,13 +28048,47 @@
         <x:v>B-Fulltext-Unavailable</x:v>
       </x:c>
       <x:c r="BP18" t="str">
-        <x:v>Not Checked</x:v>
+        <x:v>Not Found</x:v>
       </x:c>
       <x:c r="BQ18" t="str">
         <x:v>Mostly Complete</x:v>
       </x:c>
       <x:c r="BR18" t="str">
         <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BS18" t="str"/>
+      <x:c r="BT18" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BU18" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BV18" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BW18" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BX18" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BY18" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BZ18" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="CA18" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="CB18" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="CC18" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="CD18" t="str">
+        <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="58" customHeight="1">
@@ -24770,13 +28292,47 @@
         <x:v>B-Fulltext-Unavailable</x:v>
       </x:c>
       <x:c r="BP19" t="str">
-        <x:v>Not Checked</x:v>
+        <x:v>Not Found</x:v>
       </x:c>
       <x:c r="BQ19" t="str">
         <x:v>Partial</x:v>
       </x:c>
       <x:c r="BR19" t="str">
         <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BS19" t="str"/>
+      <x:c r="BT19" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BU19" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BV19" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BW19" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BX19" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BY19" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BZ19" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="CA19" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="CB19" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="CC19" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="CD19" t="str">
+        <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="58" customHeight="1">
@@ -24980,13 +28536,47 @@
         <x:v>B-Fulltext-Unavailable</x:v>
       </x:c>
       <x:c r="BP20" t="str">
-        <x:v>Not Checked</x:v>
+        <x:v>Not Found</x:v>
       </x:c>
       <x:c r="BQ20" t="str">
         <x:v>Mostly Complete</x:v>
       </x:c>
       <x:c r="BR20" t="str">
         <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BS20" t="str"/>
+      <x:c r="BT20" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BU20" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BV20" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BW20" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BX20" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BY20" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BZ20" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="CA20" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="CB20" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="CC20" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="CD20" t="str">
+        <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="58" customHeight="1">
@@ -25192,13 +28782,47 @@
         <x:v>A-Upgraded</x:v>
       </x:c>
       <x:c r="BP21" t="str">
-        <x:v>Not Checked</x:v>
+        <x:v>Available - Verified</x:v>
       </x:c>
       <x:c r="BQ21" t="str">
         <x:v>Partial</x:v>
       </x:c>
       <x:c r="BR21" t="str">
         <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BS21" t="str"/>
+      <x:c r="BT21" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BU21" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BV21" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BW21" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BX21" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BY21" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BZ21" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="CA21" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="CB21" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="CC21" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="CD21" t="str">
+        <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="58" customHeight="1">
@@ -25404,13 +29028,47 @@
         <x:v>B-Fulltext-Unavailable</x:v>
       </x:c>
       <x:c r="BP22" t="str">
-        <x:v>Not Checked</x:v>
+        <x:v>Not Found</x:v>
       </x:c>
       <x:c r="BQ22" t="str">
         <x:v>Mostly Complete</x:v>
       </x:c>
       <x:c r="BR22" t="str">
         <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BS22" t="str"/>
+      <x:c r="BT22" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BU22" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BV22" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BW22" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BX22" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BY22" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BZ22" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="CA22" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="CB22" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="CC22" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="CD22" t="str">
+        <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="58" customHeight="1">
@@ -25616,13 +29274,47 @@
         <x:v>B-Fulltext-Unavailable</x:v>
       </x:c>
       <x:c r="BP23" t="str">
-        <x:v>Not Checked</x:v>
+        <x:v>Not Found</x:v>
       </x:c>
       <x:c r="BQ23" t="str">
         <x:v>Partial</x:v>
       </x:c>
       <x:c r="BR23" t="str">
         <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BS23" t="str"/>
+      <x:c r="BT23" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BU23" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BV23" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BW23" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BX23" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BY23" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BZ23" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="CA23" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="CB23" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="CC23" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="CD23" t="str">
+        <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="58" customHeight="1">
@@ -25828,13 +29520,47 @@
         <x:v>B-Fulltext-Unavailable</x:v>
       </x:c>
       <x:c r="BP24" t="str">
-        <x:v>Not Checked</x:v>
+        <x:v>Not Found</x:v>
       </x:c>
       <x:c r="BQ24" t="str">
         <x:v>Mostly Complete</x:v>
       </x:c>
       <x:c r="BR24" t="str">
         <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BS24" t="str"/>
+      <x:c r="BT24" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BU24" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BV24" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BW24" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BX24" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BY24" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BZ24" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="CA24" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="CB24" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="CC24" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="CD24" t="str">
+        <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="58" customHeight="1">
@@ -26040,13 +29766,47 @@
         <x:v>B-Fulltext-Unavailable</x:v>
       </x:c>
       <x:c r="BP25" t="str">
-        <x:v>Not Checked</x:v>
+        <x:v>Not Found</x:v>
       </x:c>
       <x:c r="BQ25" t="str">
         <x:v>Mostly Complete</x:v>
       </x:c>
       <x:c r="BR25" t="str">
         <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BS25" t="str"/>
+      <x:c r="BT25" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BU25" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BV25" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BW25" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BX25" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BY25" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BZ25" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="CA25" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="CB25" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="CC25" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="CD25" t="str">
+        <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="58" customHeight="1">
@@ -26252,13 +30012,47 @@
         <x:v>B-Code-Unverified</x:v>
       </x:c>
       <x:c r="BP26" t="str">
-        <x:v>Not Checked</x:v>
+        <x:v>Not Found</x:v>
       </x:c>
       <x:c r="BQ26" t="str">
         <x:v>Unavailable</x:v>
       </x:c>
       <x:c r="BR26" t="str">
         <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BS26" t="str"/>
+      <x:c r="BT26" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BU26" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BV26" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BW26" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BX26" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BY26" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BZ26" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="CA26" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="CB26" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="CC26" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="CD26" t="str">
+        <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="58" customHeight="1">
@@ -26464,13 +30258,47 @@
         <x:v>B-Code-Unverified</x:v>
       </x:c>
       <x:c r="BP27" t="str">
-        <x:v>Not Checked</x:v>
+        <x:v>Not Found</x:v>
       </x:c>
       <x:c r="BQ27" t="str">
         <x:v>Unavailable</x:v>
       </x:c>
       <x:c r="BR27" t="str">
         <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BS27" t="str"/>
+      <x:c r="BT27" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BU27" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BV27" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BW27" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BX27" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BY27" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BZ27" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="CA27" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="CB27" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="CC27" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="CD27" t="str">
+        <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="58" customHeight="1">
@@ -26676,13 +30504,47 @@
         <x:v>B-Fulltext-Unavailable</x:v>
       </x:c>
       <x:c r="BP28" t="str">
-        <x:v>Not Checked</x:v>
+        <x:v>Not Found</x:v>
       </x:c>
       <x:c r="BQ28" t="str">
         <x:v>Mostly Complete</x:v>
       </x:c>
       <x:c r="BR28" t="str">
         <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BS28" t="str"/>
+      <x:c r="BT28" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BU28" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BV28" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BW28" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BX28" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BY28" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BZ28" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="CA28" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="CB28" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="CC28" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="CD28" t="str">
+        <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
     </x:row>
     <x:row r="29" ht="58" customHeight="1">
@@ -26888,13 +30750,47 @@
         <x:v>B-Fulltext-Unavailable</x:v>
       </x:c>
       <x:c r="BP29" t="str">
-        <x:v>Not Checked</x:v>
+        <x:v>Not Found</x:v>
       </x:c>
       <x:c r="BQ29" t="str">
         <x:v>Mostly Complete</x:v>
       </x:c>
       <x:c r="BR29" t="str">
         <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BS29" t="str"/>
+      <x:c r="BT29" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BU29" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BV29" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BW29" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BX29" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BY29" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BZ29" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="CA29" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="CB29" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="CC29" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="CD29" t="str">
+        <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
     </x:row>
     <x:row r="30" ht="58" customHeight="1">
@@ -27100,13 +30996,47 @@
         <x:v>B-Fulltext-Unavailable</x:v>
       </x:c>
       <x:c r="BP30" t="str">
-        <x:v>Not Checked</x:v>
+        <x:v>Not Found</x:v>
       </x:c>
       <x:c r="BQ30" t="str">
         <x:v>Mostly Complete</x:v>
       </x:c>
       <x:c r="BR30" t="str">
         <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BS30" t="str"/>
+      <x:c r="BT30" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BU30" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BV30" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BW30" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BX30" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BY30" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BZ30" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="CA30" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="CB30" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="CC30" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="CD30" t="str">
+        <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
     </x:row>
     <x:row r="31" ht="58" customHeight="1">
@@ -27312,13 +31242,47 @@
         <x:v>B-Code-Unverified</x:v>
       </x:c>
       <x:c r="BP31" t="str">
-        <x:v>Not Checked</x:v>
+        <x:v>Not Found</x:v>
       </x:c>
       <x:c r="BQ31" t="str">
         <x:v>Unavailable</x:v>
       </x:c>
       <x:c r="BR31" t="str">
         <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BS31" t="str"/>
+      <x:c r="BT31" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BU31" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BV31" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BW31" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BX31" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BY31" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BZ31" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="CA31" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="CB31" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="CC31" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="CD31" t="str">
+        <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
     </x:row>
     <x:row r="32" ht="58" customHeight="1">
@@ -27524,13 +31488,47 @@
         <x:v>B-Code-Unverified</x:v>
       </x:c>
       <x:c r="BP32" t="str">
-        <x:v>Not Checked</x:v>
+        <x:v>Not Found</x:v>
       </x:c>
       <x:c r="BQ32" t="str">
         <x:v>Unavailable</x:v>
       </x:c>
       <x:c r="BR32" t="str">
         <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BS32" t="str"/>
+      <x:c r="BT32" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BU32" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BV32" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BW32" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BX32" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BY32" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BZ32" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="CA32" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="CB32" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="CC32" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="CD32" t="str">
+        <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
     </x:row>
     <x:row r="33" ht="58" customHeight="1">
@@ -27736,13 +31734,47 @@
         <x:v>B-Code-Unverified</x:v>
       </x:c>
       <x:c r="BP33" t="str">
-        <x:v>Not Checked</x:v>
+        <x:v>Not Found</x:v>
       </x:c>
       <x:c r="BQ33" t="str">
         <x:v>Unavailable</x:v>
       </x:c>
       <x:c r="BR33" t="str">
         <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BS33" t="str"/>
+      <x:c r="BT33" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BU33" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BV33" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BW33" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BX33" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BY33" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BZ33" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="CA33" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="CB33" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="CC33" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="CD33" t="str">
+        <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
     </x:row>
     <x:row r="34" ht="58" customHeight="1">
@@ -27948,13 +31980,47 @@
         <x:v>B-Code-Unverified</x:v>
       </x:c>
       <x:c r="BP34" t="str">
-        <x:v>Not Checked</x:v>
+        <x:v>Not Found</x:v>
       </x:c>
       <x:c r="BQ34" t="str">
         <x:v>Unavailable</x:v>
       </x:c>
       <x:c r="BR34" t="str">
         <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BS34" t="str"/>
+      <x:c r="BT34" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BU34" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BV34" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BW34" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BX34" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BY34" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BZ34" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="CA34" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="CB34" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="CC34" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="CD34" t="str">
+        <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
     </x:row>
     <x:row r="35" ht="58" customHeight="1">
@@ -28160,13 +32226,47 @@
         <x:v>B-Code-Unverified</x:v>
       </x:c>
       <x:c r="BP35" t="str">
-        <x:v>Not Checked</x:v>
+        <x:v>Not Found</x:v>
       </x:c>
       <x:c r="BQ35" t="str">
         <x:v>Unavailable</x:v>
       </x:c>
       <x:c r="BR35" t="str">
         <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BS35" t="str"/>
+      <x:c r="BT35" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BU35" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BV35" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BW35" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BX35" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BY35" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BZ35" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="CA35" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="CB35" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="CC35" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="CD35" t="str">
+        <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
     </x:row>
     <x:row r="36" ht="58" customHeight="1">
@@ -28372,13 +32472,47 @@
         <x:v>B-Code-Unverified</x:v>
       </x:c>
       <x:c r="BP36" t="str">
-        <x:v>Not Checked</x:v>
+        <x:v>Not Found</x:v>
       </x:c>
       <x:c r="BQ36" t="str">
         <x:v>Unavailable</x:v>
       </x:c>
       <x:c r="BR36" t="str">
         <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BS36" t="str"/>
+      <x:c r="BT36" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BU36" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BV36" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BW36" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BX36" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BY36" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BZ36" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="CA36" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="CB36" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="CC36" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="CD36" t="str">
+        <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
     </x:row>
     <x:row r="37" ht="58" customHeight="1">
@@ -28584,13 +32718,47 @@
         <x:v>B-Code-Unverified</x:v>
       </x:c>
       <x:c r="BP37" t="str">
-        <x:v>Not Checked</x:v>
+        <x:v>Not Found</x:v>
       </x:c>
       <x:c r="BQ37" t="str">
         <x:v>Unavailable</x:v>
       </x:c>
       <x:c r="BR37" t="str">
         <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BS37" t="str"/>
+      <x:c r="BT37" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BU37" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BV37" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BW37" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BX37" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BY37" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BZ37" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="CA37" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="CB37" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="CC37" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="CD37" t="str">
+        <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
     </x:row>
     <x:row r="38" ht="58" customHeight="1">
@@ -28796,13 +32964,47 @@
         <x:v>B-Code-Unverified</x:v>
       </x:c>
       <x:c r="BP38" t="str">
-        <x:v>Not Checked</x:v>
+        <x:v>Not Found</x:v>
       </x:c>
       <x:c r="BQ38" t="str">
         <x:v>Unavailable</x:v>
       </x:c>
       <x:c r="BR38" t="str">
         <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BS38" t="str"/>
+      <x:c r="BT38" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BU38" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BV38" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BW38" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BX38" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BY38" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BZ38" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="CA38" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="CB38" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="CC38" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="CD38" t="str">
+        <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
     </x:row>
     <x:row r="39" ht="58" customHeight="1">
@@ -29008,13 +33210,47 @@
         <x:v>B-Code-Unverified</x:v>
       </x:c>
       <x:c r="BP39" t="str">
-        <x:v>Not Checked</x:v>
+        <x:v>Not Found</x:v>
       </x:c>
       <x:c r="BQ39" t="str">
         <x:v>Unavailable</x:v>
       </x:c>
       <x:c r="BR39" t="str">
         <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BS39" t="str"/>
+      <x:c r="BT39" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BU39" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BV39" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BW39" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BX39" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BY39" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BZ39" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="CA39" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="CB39" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="CC39" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="CD39" t="str">
+        <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
     </x:row>
     <x:row r="40" ht="58" customHeight="1">
@@ -29220,13 +33456,47 @@
         <x:v>B-Code-Unverified</x:v>
       </x:c>
       <x:c r="BP40" t="str">
-        <x:v>Not Checked</x:v>
+        <x:v>Not Found</x:v>
       </x:c>
       <x:c r="BQ40" t="str">
         <x:v>Unavailable</x:v>
       </x:c>
       <x:c r="BR40" t="str">
         <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BS40" t="str"/>
+      <x:c r="BT40" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BU40" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BV40" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BW40" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BX40" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BY40" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BZ40" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="CA40" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="CB40" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="CC40" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="CD40" t="str">
+        <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
     </x:row>
     <x:row r="41" ht="58" customHeight="1">
@@ -29432,13 +33702,47 @@
         <x:v>B-Code-Unverified</x:v>
       </x:c>
       <x:c r="BP41" t="str">
-        <x:v>Not Checked</x:v>
+        <x:v>Not Found</x:v>
       </x:c>
       <x:c r="BQ41" t="str">
         <x:v>Unavailable</x:v>
       </x:c>
       <x:c r="BR41" t="str">
         <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BS41" t="str"/>
+      <x:c r="BT41" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BU41" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BV41" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BW41" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BX41" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BY41" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BZ41" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="CA41" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="CB41" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="CC41" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="CD41" t="str">
+        <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
     </x:row>
     <x:row r="42" ht="58" customHeight="1">
@@ -29644,13 +33948,47 @@
         <x:v>B-Code-Unverified</x:v>
       </x:c>
       <x:c r="BP42" t="str">
-        <x:v>Not Checked</x:v>
+        <x:v>Not Found</x:v>
       </x:c>
       <x:c r="BQ42" t="str">
         <x:v>Unavailable</x:v>
       </x:c>
       <x:c r="BR42" t="str">
         <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BS42" t="str"/>
+      <x:c r="BT42" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BU42" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BV42" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BW42" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BX42" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BY42" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BZ42" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="CA42" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="CB42" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="CC42" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="CD42" t="str">
+        <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
     </x:row>
     <x:row r="43" ht="58" customHeight="1">
@@ -29856,13 +34194,47 @@
         <x:v>B-Code-Unverified</x:v>
       </x:c>
       <x:c r="BP43" t="str">
-        <x:v>Not Checked</x:v>
+        <x:v>Not Found</x:v>
       </x:c>
       <x:c r="BQ43" t="str">
         <x:v>Unavailable</x:v>
       </x:c>
       <x:c r="BR43" t="str">
         <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BS43" t="str"/>
+      <x:c r="BT43" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BU43" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BV43" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BW43" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BX43" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BY43" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BZ43" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="CA43" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="CB43" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="CC43" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="CD43" t="str">
+        <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
     </x:row>
     <x:row r="44" ht="58" customHeight="1">
@@ -30068,13 +34440,47 @@
         <x:v>B-Code-Unverified</x:v>
       </x:c>
       <x:c r="BP44" t="str">
-        <x:v>Not Checked</x:v>
+        <x:v>Not Found</x:v>
       </x:c>
       <x:c r="BQ44" t="str">
         <x:v>Unavailable</x:v>
       </x:c>
       <x:c r="BR44" t="str">
         <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BS44" t="str"/>
+      <x:c r="BT44" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BU44" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BV44" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BW44" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BX44" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BY44" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BZ44" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="CA44" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="CB44" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="CC44" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="CD44" t="str">
+        <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
     </x:row>
     <x:row r="45" ht="58" customHeight="1">
@@ -30280,13 +34686,47 @@
         <x:v>B-Code-Unverified</x:v>
       </x:c>
       <x:c r="BP45" t="str">
-        <x:v>Not Checked</x:v>
+        <x:v>Not Found</x:v>
       </x:c>
       <x:c r="BQ45" t="str">
         <x:v>Unavailable</x:v>
       </x:c>
       <x:c r="BR45" t="str">
         <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BS45" t="str"/>
+      <x:c r="BT45" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BU45" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BV45" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BW45" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BX45" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BY45" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BZ45" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="CA45" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="CB45" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="CC45" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="CD45" t="str">
+        <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
     </x:row>
     <x:row r="46" ht="58" customHeight="1">
@@ -30492,13 +34932,47 @@
         <x:v>B-Code-Unverified</x:v>
       </x:c>
       <x:c r="BP46" t="str">
-        <x:v>Not Checked</x:v>
+        <x:v>Not Found</x:v>
       </x:c>
       <x:c r="BQ46" t="str">
         <x:v>Unavailable</x:v>
       </x:c>
       <x:c r="BR46" t="str">
         <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BS46" t="str"/>
+      <x:c r="BT46" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BU46" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BV46" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BW46" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BX46" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BY46" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BZ46" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="CA46" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="CB46" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="CC46" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="CD46" t="str">
+        <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
     </x:row>
     <x:row r="47" ht="58" customHeight="1">
@@ -30704,13 +35178,47 @@
         <x:v>B-Code-Unverified</x:v>
       </x:c>
       <x:c r="BP47" t="str">
-        <x:v>Not Checked</x:v>
+        <x:v>Not Found</x:v>
       </x:c>
       <x:c r="BQ47" t="str">
         <x:v>Unavailable</x:v>
       </x:c>
       <x:c r="BR47" t="str">
         <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BS47" t="str"/>
+      <x:c r="BT47" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BU47" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BV47" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BW47" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BX47" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BY47" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BZ47" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="CA47" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="CB47" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="CC47" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="CD47" t="str">
+        <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
     </x:row>
     <x:row r="48" ht="58" customHeight="1">
@@ -30916,13 +35424,47 @@
         <x:v>B-Code-Unverified</x:v>
       </x:c>
       <x:c r="BP48" t="str">
-        <x:v>Not Checked</x:v>
+        <x:v>Not Found</x:v>
       </x:c>
       <x:c r="BQ48" t="str">
         <x:v>Unavailable</x:v>
       </x:c>
       <x:c r="BR48" t="str">
         <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BS48" t="str"/>
+      <x:c r="BT48" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BU48" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BV48" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BW48" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BX48" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BY48" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BZ48" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="CA48" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="CB48" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="CC48" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="CD48" t="str">
+        <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
     </x:row>
     <x:row r="49" ht="58" customHeight="1">
@@ -31128,13 +35670,47 @@
         <x:v>B-Code-Unverified</x:v>
       </x:c>
       <x:c r="BP49" t="str">
-        <x:v>Not Checked</x:v>
+        <x:v>Not Found</x:v>
       </x:c>
       <x:c r="BQ49" t="str">
         <x:v>Unavailable</x:v>
       </x:c>
       <x:c r="BR49" t="str">
         <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BS49" t="str"/>
+      <x:c r="BT49" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BU49" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BV49" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BW49" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BX49" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BY49" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BZ49" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="CA49" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="CB49" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="CC49" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="CD49" t="str">
+        <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
     </x:row>
     <x:row r="50" ht="58" customHeight="1">
@@ -31340,13 +35916,47 @@
         <x:v>B-Code-Unverified</x:v>
       </x:c>
       <x:c r="BP50" t="str">
-        <x:v>Not Checked</x:v>
+        <x:v>Not Found</x:v>
       </x:c>
       <x:c r="BQ50" t="str">
         <x:v>Unavailable</x:v>
       </x:c>
       <x:c r="BR50" t="str">
         <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BS50" t="str"/>
+      <x:c r="BT50" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BU50" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BV50" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BW50" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BX50" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BY50" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BZ50" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="CA50" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="CB50" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="CC50" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="CD50" t="str">
+        <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
     </x:row>
     <x:row r="51" ht="58" customHeight="1">
@@ -31552,13 +36162,47 @@
         <x:v>B-Code-Unverified</x:v>
       </x:c>
       <x:c r="BP51" t="str">
-        <x:v>Not Checked</x:v>
+        <x:v>Not Found</x:v>
       </x:c>
       <x:c r="BQ51" t="str">
         <x:v>Unavailable</x:v>
       </x:c>
       <x:c r="BR51" t="str">
         <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BS51" t="str"/>
+      <x:c r="BT51" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BU51" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BV51" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BW51" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BX51" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BY51" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BZ51" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="CA51" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="CB51" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="CC51" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="CD51" t="str">
+        <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
     </x:row>
     <x:row r="52" ht="58" customHeight="1">
@@ -31764,13 +36408,47 @@
         <x:v>B-Code-Unverified</x:v>
       </x:c>
       <x:c r="BP52" t="str">
-        <x:v>Not Checked</x:v>
+        <x:v>Not Found</x:v>
       </x:c>
       <x:c r="BQ52" t="str">
         <x:v>Unavailable</x:v>
       </x:c>
       <x:c r="BR52" t="str">
         <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BS52" t="str"/>
+      <x:c r="BT52" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BU52" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BV52" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BW52" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BX52" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BY52" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BZ52" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="CA52" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="CB52" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="CC52" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="CD52" t="str">
+        <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
     </x:row>
     <x:row r="53" ht="58" customHeight="1">
@@ -31976,13 +36654,47 @@
         <x:v>B-Code-Unverified</x:v>
       </x:c>
       <x:c r="BP53" t="str">
-        <x:v>Not Checked</x:v>
+        <x:v>Not Found</x:v>
       </x:c>
       <x:c r="BQ53" t="str">
         <x:v>Unavailable</x:v>
       </x:c>
       <x:c r="BR53" t="str">
         <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BS53" t="str"/>
+      <x:c r="BT53" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BU53" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BV53" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BW53" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BX53" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BY53" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BZ53" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="CA53" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="CB53" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="CC53" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="CD53" t="str">
+        <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
     </x:row>
     <x:row r="54" ht="58" customHeight="1">
@@ -32167,7 +36879,7 @@
         <x:v>Unknown</x:v>
       </x:c>
       <x:c r="BI54" t="str">
-        <x:v>B</x:v>
+        <x:v>A</x:v>
       </x:c>
       <x:c r="BJ54" t="str">
         <x:v>Idea Clue 1: use part-level language affordances as a perception front-end for bimanual grasp sequencing. Evidence: part-touch/part-grasp metrics and flow pose head. Why relevant: supports target-region and action alignment.</x:v>
@@ -32185,16 +36897,50 @@
         <x:v>https://openaccess.thecvf.com/content/ICCV2025/html/He_DexVLG_Dexterous_Vision-Language-Grasp_Model_at_Scale_ICCV_2025_paper.html；官方摘要/论文集元数据</x:v>
       </x:c>
       <x:c r="BO54" t="str">
-        <x:v>B-Fulltext-Unavailable</x:v>
+        <x:v>A-Upgraded</x:v>
       </x:c>
       <x:c r="BP54" t="str">
+        <x:v>Available - Verified</x:v>
+      </x:c>
+      <x:c r="BQ54" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BR54" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BS54" t="str"/>
+      <x:c r="BT54" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BU54" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BV54" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BW54" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BX54" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BY54" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BZ54" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="CA54" t="str">
         <x:v>Not Checked</x:v>
       </x:c>
-      <x:c r="BQ54" t="str">
-        <x:v>Unknown</x:v>
-      </x:c>
-      <x:c r="BR54" t="str">
-        <x:v>Unknown</x:v>
+      <x:c r="CB54" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="CC54" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="CD54" t="str">
+        <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
     </x:row>
     <x:row r="55" ht="58" customHeight="1">
@@ -32400,13 +37146,47 @@
         <x:v>B-Code-Unverified</x:v>
       </x:c>
       <x:c r="BP55" t="str">
-        <x:v>Not Checked</x:v>
+        <x:v>Not Found</x:v>
       </x:c>
       <x:c r="BQ55" t="str">
         <x:v>Unavailable</x:v>
       </x:c>
       <x:c r="BR55" t="str">
         <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BS55" t="str"/>
+      <x:c r="BT55" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BU55" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BV55" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BW55" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BX55" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BY55" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BZ55" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="CA55" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="CB55" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="CC55" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="CD55" t="str">
+        <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
     </x:row>
     <x:row r="56" ht="58" customHeight="1">
@@ -32612,13 +37392,47 @@
         <x:v>B-Code-Unverified</x:v>
       </x:c>
       <x:c r="BP56" t="str">
-        <x:v>Not Checked</x:v>
+        <x:v>Not Found</x:v>
       </x:c>
       <x:c r="BQ56" t="str">
         <x:v>Unavailable</x:v>
       </x:c>
       <x:c r="BR56" t="str">
         <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BS56" t="str"/>
+      <x:c r="BT56" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BU56" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BV56" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BW56" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BX56" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BY56" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BZ56" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="CA56" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="CB56" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="CC56" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="CD56" t="str">
+        <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
     </x:row>
     <x:row r="57" ht="58" customHeight="1">
@@ -32824,13 +37638,47 @@
         <x:v>B-Code-Unverified</x:v>
       </x:c>
       <x:c r="BP57" t="str">
-        <x:v>Not Checked</x:v>
+        <x:v>Not Found</x:v>
       </x:c>
       <x:c r="BQ57" t="str">
         <x:v>Unavailable</x:v>
       </x:c>
       <x:c r="BR57" t="str">
         <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BS57" t="str"/>
+      <x:c r="BT57" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BU57" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BV57" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BW57" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BX57" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BY57" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BZ57" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="CA57" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="CB57" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="CC57" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="CD57" t="str">
+        <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
     </x:row>
     <x:row r="58" ht="58" customHeight="1">
@@ -33036,13 +37884,47 @@
         <x:v>A-Upgraded</x:v>
       </x:c>
       <x:c r="BP58" t="str">
-        <x:v>Not Checked</x:v>
+        <x:v>Available - Verified</x:v>
       </x:c>
       <x:c r="BQ58" t="str">
         <x:v>Unavailable</x:v>
       </x:c>
       <x:c r="BR58" t="str">
         <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BS58" t="str"/>
+      <x:c r="BT58" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BU58" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BV58" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BW58" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BX58" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BY58" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BZ58" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="CA58" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="CB58" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="CC58" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="CD58" t="str">
+        <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
     </x:row>
     <x:row r="59" ht="58" customHeight="1">
@@ -33227,7 +38109,7 @@
         <x:v>Unknown</x:v>
       </x:c>
       <x:c r="BI59" t="str">
-        <x:v>B</x:v>
+        <x:v>A</x:v>
       </x:c>
       <x:c r="BJ59" t="str">
         <x:v>Idea Clue 1: borrow FAAS-style functional action grouping for dual-arm gripper role transfer. Evidence: unified cross-hand action coordinates. Why relevant: possible bridge from dexterous data to ordinary-gripper control.</x:v>
@@ -33245,16 +38127,50 @@
         <x:v>https://openaccess.thecvf.com/content/CVPR2026/html/Zhang_UniDex_A_Robot_Foundation_Suite_for_Universal_Dexterous_Hand_Control_CVPR_2026_paper.html；官方摘要/论文集元数据</x:v>
       </x:c>
       <x:c r="BO59" t="str">
-        <x:v>B-Code-Unverified</x:v>
+        <x:v>A-Upgraded</x:v>
       </x:c>
       <x:c r="BP59" t="str">
-        <x:v>Not Checked</x:v>
+        <x:v>Available - Verified</x:v>
       </x:c>
       <x:c r="BQ59" t="str">
         <x:v>Unavailable</x:v>
       </x:c>
       <x:c r="BR59" t="str">
         <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BS59" t="str"/>
+      <x:c r="BT59" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BU59" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BV59" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BW59" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BX59" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BY59" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BZ59" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="CA59" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="CB59" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="CC59" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="CD59" t="str">
+        <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
     </x:row>
     <x:row r="60" ht="58" customHeight="1">
@@ -33460,13 +38376,47 @@
         <x:v>B-Code-Unverified</x:v>
       </x:c>
       <x:c r="BP60" t="str">
-        <x:v>Not Checked</x:v>
+        <x:v>Not Found</x:v>
       </x:c>
       <x:c r="BQ60" t="str">
         <x:v>Unavailable</x:v>
       </x:c>
       <x:c r="BR60" t="str">
         <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BS60" t="str"/>
+      <x:c r="BT60" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BU60" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BV60" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BW60" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BX60" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BY60" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BZ60" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="CA60" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="CB60" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="CC60" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="CD60" t="str">
+        <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
     </x:row>
     <x:row r="61" ht="58" customHeight="1">
@@ -33672,13 +38622,47 @@
         <x:v>B-Code-Unverified</x:v>
       </x:c>
       <x:c r="BP61" t="str">
-        <x:v>Not Checked</x:v>
+        <x:v>Not Found</x:v>
       </x:c>
       <x:c r="BQ61" t="str">
         <x:v>Unavailable</x:v>
       </x:c>
       <x:c r="BR61" t="str">
         <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BS61" t="str"/>
+      <x:c r="BT61" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BU61" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BV61" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BW61" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BX61" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BY61" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BZ61" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="CA61" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="CB61" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="CC61" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="CD61" t="str">
+        <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
     </x:row>
     <x:row r="62" ht="58" customHeight="1">
@@ -33884,13 +38868,47 @@
         <x:v>B-Code-Unverified</x:v>
       </x:c>
       <x:c r="BP62" t="str">
-        <x:v>Not Checked</x:v>
+        <x:v>Not Found</x:v>
       </x:c>
       <x:c r="BQ62" t="str">
         <x:v>Unavailable</x:v>
       </x:c>
       <x:c r="BR62" t="str">
         <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BS62" t="str"/>
+      <x:c r="BT62" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BU62" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BV62" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BW62" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BX62" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BY62" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BZ62" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="CA62" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="CB62" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="CC62" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="CD62" t="str">
+        <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
     </x:row>
     <x:row r="63" ht="58" customHeight="1">
@@ -34096,13 +39114,47 @@
         <x:v>B-Code-Unverified</x:v>
       </x:c>
       <x:c r="BP63" t="str">
-        <x:v>Not Checked</x:v>
+        <x:v>Not Found</x:v>
       </x:c>
       <x:c r="BQ63" t="str">
         <x:v>Unavailable</x:v>
       </x:c>
       <x:c r="BR63" t="str">
         <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BS63" t="str"/>
+      <x:c r="BT63" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BU63" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BV63" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BW63" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BX63" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BY63" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BZ63" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="CA63" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="CB63" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="CC63" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="CD63" t="str">
+        <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
     </x:row>
     <x:row r="64" ht="58" customHeight="1">
@@ -34308,13 +39360,47 @@
         <x:v>B-Code-Unverified</x:v>
       </x:c>
       <x:c r="BP64" t="str">
-        <x:v>Not Checked</x:v>
+        <x:v>Not Found</x:v>
       </x:c>
       <x:c r="BQ64" t="str">
         <x:v>Unavailable</x:v>
       </x:c>
       <x:c r="BR64" t="str">
         <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BS64" t="str"/>
+      <x:c r="BT64" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BU64" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BV64" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BW64" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BX64" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BY64" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BZ64" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="CA64" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="CB64" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="CC64" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="CD64" t="str">
+        <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
     </x:row>
     <x:row r="65" ht="58" customHeight="1">
@@ -34520,13 +39606,47 @@
         <x:v>B-Code-Unverified</x:v>
       </x:c>
       <x:c r="BP65" t="str">
-        <x:v>Not Checked</x:v>
+        <x:v>Not Found</x:v>
       </x:c>
       <x:c r="BQ65" t="str">
         <x:v>Unavailable</x:v>
       </x:c>
       <x:c r="BR65" t="str">
         <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BS65" t="str"/>
+      <x:c r="BT65" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BU65" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BV65" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BW65" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BX65" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BY65" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BZ65" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="CA65" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="CB65" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="CC65" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="CD65" t="str">
+        <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
     </x:row>
     <x:row r="66" ht="58" customHeight="1">
@@ -34711,7 +39831,7 @@
         <x:v>Unknown</x:v>
       </x:c>
       <x:c r="BI66" t="str">
-        <x:v>B</x:v>
+        <x:v>A</x:v>
       </x:c>
       <x:c r="BJ66" t="str">
         <x:v>Idea Clue 1: evaluate predicted left/right/both affordances as a front-end for dual-arm task planning. Evidence: explicit hand-taxonomy decoder. Why relevant: actionable perception before VLA action generation.</x:v>
@@ -34729,16 +39849,50 @@
         <x:v>https://openaccess.thecvf.com/content/ICCV2025/html/Heidinger_2HandedAfforder_Learning_Precise_Actionable_Bimanual_Affordances_from_Human_Videos_ICCV_2025_paper.html；官方摘要/论文集元数据</x:v>
       </x:c>
       <x:c r="BO66" t="str">
-        <x:v>B-Code-Unverified</x:v>
+        <x:v>A-Upgraded</x:v>
       </x:c>
       <x:c r="BP66" t="str">
-        <x:v>Not Checked</x:v>
+        <x:v>Available - Verified</x:v>
       </x:c>
       <x:c r="BQ66" t="str">
         <x:v>Unavailable</x:v>
       </x:c>
       <x:c r="BR66" t="str">
         <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BS66" t="str"/>
+      <x:c r="BT66" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BU66" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BV66" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BW66" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BX66" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BY66" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BZ66" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="CA66" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="CB66" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="CC66" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="CD66" t="str">
+        <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
     </x:row>
     <x:row r="67">
@@ -34923,7 +40077,7 @@
         <x:v>VLA; Robot Manipulation; Visual Grounding; Robot Perception; Implicit Grounding; Gaze-Region Reconstruction; Generalization; Diffusion Transformer</x:v>
       </x:c>
       <x:c r="BI67" t="str">
-        <x:v>B</x:v>
+        <x:v>A</x:v>
       </x:c>
       <x:c r="BJ67" t="str">
         <x:v>Idea Clue 1: test implicit ga</x:v>
@@ -34941,16 +40095,50 @@
         <x:v>https://ojs.aaai.org/index.php/AAAI/article/view/38921；https://arxiv.org/abs/2508.10333；https://zionchow.github.io/ReconVLA/；https://github.com/OpenHelix-Team/ReconVLA</x:v>
       </x:c>
       <x:c r="BO67" t="str">
-        <x:v>B-Experiment-Not-Extracted</x:v>
+        <x:v>A-Upgraded</x:v>
       </x:c>
       <x:c r="BP67" t="str">
-        <x:v>Not Checked</x:v>
+        <x:v>Available - Verified</x:v>
       </x:c>
       <x:c r="BQ67" t="str">
         <x:v>Mostly Complete</x:v>
       </x:c>
       <x:c r="BR67" t="str">
         <x:v>Franka Panda (CALVIN simulation); real-world platform not confirmed at abstract level</x:v>
+      </x:c>
+      <x:c r="BS67" t="str"/>
+      <x:c r="BT67" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BU67" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BV67" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BW67" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BX67" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BY67" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BZ67" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="CA67" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="CB67" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="CC67" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="CD67" t="str">
+        <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -34988,7 +40176,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3a7da2787efe4e06"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R82da15685a574f77"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -35214,6 +40402,42 @@
       <x:c r="BG1" t="str">
         <x:v>Robot Platform Evidence</x:v>
       </x:c>
+      <x:c r="BH1" t="str">
+        <x:v>Fulltext URL</x:v>
+      </x:c>
+      <x:c r="BI1" t="str">
+        <x:v>Fulltext Checked</x:v>
+      </x:c>
+      <x:c r="BJ1" t="str">
+        <x:v>Experiment Extracted</x:v>
+      </x:c>
+      <x:c r="BK1" t="str">
+        <x:v>Results Extracted</x:v>
+      </x:c>
+      <x:c r="BL1" t="str">
+        <x:v>Ablation Extracted</x:v>
+      </x:c>
+      <x:c r="BM1" t="str">
+        <x:v>Failure Cases Extracted</x:v>
+      </x:c>
+      <x:c r="BN1" t="str">
+        <x:v>Limitations Extracted</x:v>
+      </x:c>
+      <x:c r="BO1" t="str">
+        <x:v>Remaining Gap Extracted</x:v>
+      </x:c>
+      <x:c r="BP1" t="str">
+        <x:v>Citation Status</x:v>
+      </x:c>
+      <x:c r="BQ1" t="str">
+        <x:v>DOI Status</x:v>
+      </x:c>
+      <x:c r="BR1" t="str">
+        <x:v>arXiv Status</x:v>
+      </x:c>
+      <x:c r="BS1" t="str">
+        <x:v>Deep Enrichment Status</x:v>
+      </x:c>
     </x:row>
     <x:row r="2" ht="62" customHeight="1">
       <x:c r="A2" t="str">
@@ -35385,13 +40609,47 @@
         <x:v>B-Experiment-Not-Extracted</x:v>
       </x:c>
       <x:c r="BE2" t="str">
-        <x:v>Not Checked</x:v>
+        <x:v>Not Found</x:v>
       </x:c>
       <x:c r="BF2" t="str">
         <x:v>Partial</x:v>
       </x:c>
       <x:c r="BG2" t="str">
         <x:v>Multiple real-world setups are shown; exact hardware inventory not extracted at abstract/project level</x:v>
+      </x:c>
+      <x:c r="BH2" t="str"/>
+      <x:c r="BI2" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BJ2" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BK2" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BL2" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BM2" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BN2" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BO2" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BP2" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="BQ2" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BR2" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BS2" t="str">
+        <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="62" customHeight="1">
@@ -35564,13 +40822,47 @@
         <x:v>B-Code-Unverified</x:v>
       </x:c>
       <x:c r="BE3" t="str">
-        <x:v>Not Checked</x:v>
+        <x:v>Not Found</x:v>
       </x:c>
       <x:c r="BF3" t="str">
         <x:v>Unavailable</x:v>
       </x:c>
       <x:c r="BG3" t="str">
         <x:v>Dual robot arms; exact platform pending full-paper check</x:v>
+      </x:c>
+      <x:c r="BH3" t="str"/>
+      <x:c r="BI3" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BJ3" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BK3" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BL3" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BM3" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BN3" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BO3" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BP3" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="BQ3" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BR3" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BS3" t="str">
+        <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="62" customHeight="1">
@@ -35743,13 +41035,47 @@
         <x:v>B-Code-Unverified</x:v>
       </x:c>
       <x:c r="BE4" t="str">
-        <x:v>Not Checked</x:v>
+        <x:v>Not Found</x:v>
       </x:c>
       <x:c r="BF4" t="str">
         <x:v>Unavailable</x:v>
       </x:c>
       <x:c r="BG4" t="str">
         <x:v>Bimanual gripper system; exact model pending full-paper check</x:v>
+      </x:c>
+      <x:c r="BH4" t="str"/>
+      <x:c r="BI4" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BJ4" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BK4" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BL4" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BM4" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BN4" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BO4" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BP4" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="BQ4" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BR4" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BS4" t="str">
+        <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="62" customHeight="1">
@@ -35922,13 +41248,47 @@
         <x:v>B-Code-Unverified</x:v>
       </x:c>
       <x:c r="BE5" t="str">
-        <x:v>Not Checked</x:v>
+        <x:v>Not Found</x:v>
       </x:c>
       <x:c r="BF5" t="str">
         <x:v>Unavailable</x:v>
       </x:c>
       <x:c r="BG5" t="str">
         <x:v>Dexterous robotic hand</x:v>
+      </x:c>
+      <x:c r="BH5" t="str"/>
+      <x:c r="BI5" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BJ5" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BK5" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BL5" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BM5" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BN5" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BO5" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BP5" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="BQ5" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BR5" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BS5" t="str">
+        <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="62" customHeight="1">
@@ -36101,13 +41461,47 @@
         <x:v>B-Code-Unverified</x:v>
       </x:c>
       <x:c r="BE6" t="str">
-        <x:v>Not Checked</x:v>
+        <x:v>Not Found</x:v>
       </x:c>
       <x:c r="BF6" t="str">
         <x:v>Unavailable</x:v>
       </x:c>
       <x:c r="BG6" t="str">
         <x:v>Simulation plus real-world replication</x:v>
+      </x:c>
+      <x:c r="BH6" t="str"/>
+      <x:c r="BI6" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BJ6" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BK6" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BL6" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BM6" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BN6" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BO6" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BP6" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="BQ6" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BR6" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BS6" t="str">
+        <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="62" customHeight="1">
@@ -36280,13 +41674,47 @@
         <x:v>B-Fulltext-Unavailable</x:v>
       </x:c>
       <x:c r="BE7" t="str">
-        <x:v>Not Checked</x:v>
+        <x:v>Not Found</x:v>
       </x:c>
       <x:c r="BF7" t="str">
         <x:v>Mostly Complete</x:v>
       </x:c>
       <x:c r="BG7" t="str">
         <x:v>Dual robot arms; exact model pending full-paper check</x:v>
+      </x:c>
+      <x:c r="BH7" t="str"/>
+      <x:c r="BI7" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BJ7" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BK7" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BL7" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BM7" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BN7" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BO7" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BP7" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="BQ7" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BR7" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BS7" t="str">
+        <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="62" customHeight="1">
@@ -36459,13 +41887,47 @@
         <x:v>B-Code-Unverified</x:v>
       </x:c>
       <x:c r="BE8" t="str">
-        <x:v>Not Checked</x:v>
+        <x:v>Not Found</x:v>
       </x:c>
       <x:c r="BF8" t="str">
         <x:v>Unavailable</x:v>
       </x:c>
       <x:c r="BG8" t="str">
         <x:v>Robot arm with visuotactile end effector</x:v>
+      </x:c>
+      <x:c r="BH8" t="str"/>
+      <x:c r="BI8" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BJ8" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BK8" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BL8" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BM8" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BN8" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BO8" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BP8" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="BQ8" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BR8" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BS8" t="str">
+        <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="62" customHeight="1">
@@ -36638,13 +42100,47 @@
         <x:v>B-Code-Unverified</x:v>
       </x:c>
       <x:c r="BE9" t="str">
-        <x:v>Not Checked</x:v>
+        <x:v>Not Found</x:v>
       </x:c>
       <x:c r="BF9" t="str">
         <x:v>Unavailable</x:v>
       </x:c>
       <x:c r="BG9" t="str">
         <x:v>Multiple robotic arms</x:v>
+      </x:c>
+      <x:c r="BH9" t="str"/>
+      <x:c r="BI9" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BJ9" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BK9" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BL9" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BM9" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BN9" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BO9" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BP9" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="BQ9" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BR9" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BS9" t="str">
+        <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="62" customHeight="1">
@@ -36817,13 +42313,47 @@
         <x:v>B-Code-Unverified</x:v>
       </x:c>
       <x:c r="BE10" t="str">
-        <x:v>Not Checked</x:v>
+        <x:v>Not Found</x:v>
       </x:c>
       <x:c r="BF10" t="str">
         <x:v>Unavailable</x:v>
       </x:c>
       <x:c r="BG10" t="str">
         <x:v>Multiple hand geometries</x:v>
+      </x:c>
+      <x:c r="BH10" t="str"/>
+      <x:c r="BI10" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BJ10" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BK10" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BL10" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BM10" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BN10" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BO10" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BP10" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="BQ10" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BR10" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BS10" t="str">
+        <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="62" customHeight="1">
@@ -36974,13 +42504,47 @@
         <x:v>B-Fulltext-Unavailable</x:v>
       </x:c>
       <x:c r="BE11" t="str">
-        <x:v>Not Checked</x:v>
+        <x:v>Not Found</x:v>
       </x:c>
       <x:c r="BF11" t="str">
         <x:v>Mostly Complete</x:v>
       </x:c>
       <x:c r="BG11" t="str">
         <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BH11" t="str"/>
+      <x:c r="BI11" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BJ11" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BK11" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BL11" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BM11" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BN11" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BO11" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BP11" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="BQ11" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BR11" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BS11" t="str">
+        <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="62" customHeight="1">
@@ -37127,13 +42691,47 @@
         <x:v>B-Fulltext-Unavailable</x:v>
       </x:c>
       <x:c r="BE12" t="str">
-        <x:v>Not Checked</x:v>
+        <x:v>Not Found</x:v>
       </x:c>
       <x:c r="BF12" t="str">
         <x:v>Mostly Complete</x:v>
       </x:c>
       <x:c r="BG12" t="str">
         <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BH12" t="str"/>
+      <x:c r="BI12" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BJ12" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BK12" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BL12" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BM12" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BN12" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BO12" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BP12" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="BQ12" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BR12" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BS12" t="str">
+        <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="62" customHeight="1">
@@ -37280,13 +42878,47 @@
         <x:v>B-Fulltext-Unavailable</x:v>
       </x:c>
       <x:c r="BE13" t="str">
+        <x:v>Not Found</x:v>
+      </x:c>
+      <x:c r="BF13" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BG13" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BH13" t="str"/>
+      <x:c r="BI13" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BJ13" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BK13" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BL13" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BM13" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BN13" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BO13" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BP13" t="str">
         <x:v>Not Checked</x:v>
       </x:c>
-      <x:c r="BF13" t="str">
-        <x:v>Unknown</x:v>
-      </x:c>
-      <x:c r="BG13" t="str">
-        <x:v>Unknown</x:v>
+      <x:c r="BQ13" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BR13" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BS13" t="str">
+        <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="62" customHeight="1">
@@ -37433,13 +43065,47 @@
         <x:v>B-Fulltext-Unavailable</x:v>
       </x:c>
       <x:c r="BE14" t="str">
-        <x:v>Not Checked</x:v>
+        <x:v>Not Found</x:v>
       </x:c>
       <x:c r="BF14" t="str">
         <x:v>Mostly Complete</x:v>
       </x:c>
       <x:c r="BG14" t="str">
         <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="BH14" t="str"/>
+      <x:c r="BI14" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BJ14" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BK14" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BL14" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BM14" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BN14" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BO14" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="BP14" t="str">
+        <x:v>Not Checked</x:v>
+      </x:c>
+      <x:c r="BQ14" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BR14" t="str">
+        <x:v>Not Found After Verification</x:v>
+      </x:c>
+      <x:c r="BS14" t="str">
+        <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -37459,7 +43125,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb371afc4806b4e43"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R96b87176bc384e0f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/00_Paper_Pool/Paper_Pool.xlsx
+++ b/00_Paper_Pool/Paper_Pool.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Papers" sheetId="1" r:id="R701641b7409142a7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rejected" sheetId="2" r:id="R1558b6a60fa64e25"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Venues" sheetId="3" r:id="R70b64d35efd546c5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Keywords" sheetId="4" r:id="R819c9bf184d84ec7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Discovery" sheetId="5" r:id="Rba8f19defe2b4beb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CCF_A_Library" sheetId="6" r:id="R88f4c2d47b3747c5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Robotics_Core_Library" sheetId="7" r:id="R82cd8b97fb794536"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Papers" sheetId="1" r:id="R2a26ccb80085449a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rejected" sheetId="2" r:id="R3e0a53a2796b4fee"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Venues" sheetId="3" r:id="Rd3468dd66f94418c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Keywords" sheetId="4" r:id="R96d1726f960f437f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Discovery" sheetId="5" r:id="R8f8e965c0b6a40f5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CCF_A_Library" sheetId="6" r:id="Rf66c3f58ff424b04"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Robotics_Core_Library" sheetId="7" r:id="Rab43dd6ed7cd49db"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="36" name="PapersTable" displayName="PapersTable" ref="A1:BP5" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:tableColumns count="68">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="40" name="PapersTable" displayName="PapersTable" ref="A1:BQ5" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:tableColumns count="69">
     <x:tableColumn id="1" name="编号 ID"/>
     <x:tableColumn id="2" name="论文标题 Title"/>
     <x:tableColumn id="3" name="年份 Year"/>
@@ -370,6 +370,7 @@
     <x:tableColumn id="66" name="DOI Status"/>
     <x:tableColumn id="67" name="arXiv Status"/>
     <x:tableColumn id="68" name="Deep Enrichment Status"/>
+    <x:tableColumn id="69" name="Deep Enrichment Completed"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
@@ -421,8 +422,8 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="37" name="DiscoveryTable" displayName="DiscoveryTable" ref="A1:BK79" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:tableColumns count="63">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="41" name="DiscoveryTable" displayName="DiscoveryTable" ref="A1:BL79" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:tableColumns count="64">
     <x:tableColumn id="1" name="编号 ID"/>
     <x:tableColumn id="2" name="论文标题 Title"/>
     <x:tableColumn id="3" name="年份 Year"/>
@@ -486,14 +487,15 @@
     <x:tableColumn id="61" name="DOI Status"/>
     <x:tableColumn id="62" name="arXiv Status"/>
     <x:tableColumn id="63" name="Deep Enrichment Status"/>
+    <x:tableColumn id="64" name="Deep Enrichment Completed"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="38" name="CCFALibraryTable" displayName="CCFALibraryTable" ref="A1:CD67" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:tableColumns count="82">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="42" name="CCFALibraryTable" displayName="CCFALibraryTable" ref="A1:CE67" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:tableColumns count="83">
     <x:tableColumn id="1" name="编号 ID"/>
     <x:tableColumn id="2" name="论文标题 Title"/>
     <x:tableColumn id="3" name="作者 Authors"/>
@@ -576,14 +578,15 @@
     <x:tableColumn id="80" name="DOI Status"/>
     <x:tableColumn id="81" name="arXiv Status"/>
     <x:tableColumn id="82" name="Deep Enrichment Status"/>
+    <x:tableColumn id="83" name="Deep Enrichment Completed"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="39" name="RoboticsCoreLibraryTable" displayName="RoboticsCoreLibraryTable" ref="A1:BS14" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:tableColumns count="71">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="43" name="RoboticsCoreLibraryTable" displayName="RoboticsCoreLibraryTable" ref="A1:BT14" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:tableColumns count="72">
     <x:tableColumn id="1" name="ID"/>
     <x:tableColumn id="2" name="Title"/>
     <x:tableColumn id="3" name="Authors"/>
@@ -655,6 +658,7 @@
     <x:tableColumn id="69" name="DOI Status"/>
     <x:tableColumn id="70" name="arXiv Status"/>
     <x:tableColumn id="71" name="Deep Enrichment Status"/>
+    <x:tableColumn id="72" name="Deep Enrichment Completed"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium4" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
@@ -1093,6 +1097,9 @@
       <x:c r="BP1" t="str">
         <x:v>Deep Enrichment Status</x:v>
       </x:c>
+      <x:c r="BQ1" t="str">
+        <x:v>Deep Enrichment Completed</x:v>
+      </x:c>
     </x:row>
     <x:row r="2" ht="350" customHeight="1">
       <x:c r="A2" t="str">
@@ -1295,6 +1302,9 @@
       </x:c>
       <x:c r="BP2" t="str">
         <x:v>Audit logged - deep extraction pending</x:v>
+      </x:c>
+      <x:c r="BQ2" t="str">
+        <x:v>false</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="150" customHeight="1">
@@ -1468,6 +1478,9 @@
       <x:c r="BP3" t="str">
         <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
+      <x:c r="BQ3" t="str">
+        <x:v>false</x:v>
+      </x:c>
     </x:row>
     <x:row r="4" ht="150" customHeight="1">
       <x:c r="A4" t="str">
@@ -1640,6 +1653,9 @@
       <x:c r="BP4" t="str">
         <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
+      <x:c r="BQ4" t="str">
+        <x:v>false</x:v>
+      </x:c>
     </x:row>
     <x:row r="5" ht="150" customHeight="1">
       <x:c r="A5" t="str">
@@ -1811,6 +1827,9 @@
       </x:c>
       <x:c r="BP5" t="str">
         <x:v>Audit logged - deep extraction pending</x:v>
+      </x:c>
+      <x:c r="BQ5" t="str">
+        <x:v>false</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -4824,7 +4843,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7f5167e3362547f5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rab466b1784c74225"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8120,7 +8139,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra356fe3872634c89"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R284677e1e66c4387"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8471,7 +8490,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7cc51529cf3c46fd"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1c3aa5d73ef94d45"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9217,7 +9236,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R780f6d2c6bd24827"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1e7eaae709754c6a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9447,6 +9466,9 @@
       <x:c r="BK1" t="str">
         <x:v>Deep Enrichment Status</x:v>
       </x:c>
+      <x:c r="BL1" t="str">
+        <x:v>Deep Enrichment Completed</x:v>
+      </x:c>
     </x:row>
     <x:row r="2" ht="58" customHeight="1">
       <x:c r="A2" t="str">
@@ -9628,6 +9650,9 @@
       <x:c r="BK2" t="str">
         <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
+      <x:c r="BL2" t="str">
+        <x:v>false</x:v>
+      </x:c>
     </x:row>
     <x:row r="3" ht="58" customHeight="1">
       <x:c r="A3" t="str">
@@ -9809,6 +9834,9 @@
       <x:c r="BK3" t="str">
         <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
+      <x:c r="BL3" t="str">
+        <x:v>false</x:v>
+      </x:c>
     </x:row>
     <x:row r="4" ht="58" customHeight="1">
       <x:c r="A4" t="str">
@@ -9990,6 +10018,9 @@
       <x:c r="BK4" t="str">
         <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
+      <x:c r="BL4" t="str">
+        <x:v>false</x:v>
+      </x:c>
     </x:row>
     <x:row r="5" ht="58" customHeight="1">
       <x:c r="A5" t="str">
@@ -10173,6 +10204,9 @@
       <x:c r="BK5" t="str">
         <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
+      <x:c r="BL5" t="str">
+        <x:v>false</x:v>
+      </x:c>
     </x:row>
     <x:row r="6" ht="58" customHeight="1">
       <x:c r="A6" t="str">
@@ -10354,6 +10388,9 @@
       <x:c r="BK6" t="str">
         <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
+      <x:c r="BL6" t="str">
+        <x:v>false</x:v>
+      </x:c>
     </x:row>
     <x:row r="7" ht="58" customHeight="1">
       <x:c r="A7" t="str">
@@ -10535,6 +10572,9 @@
       <x:c r="BK7" t="str">
         <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
+      <x:c r="BL7" t="str">
+        <x:v>false</x:v>
+      </x:c>
     </x:row>
     <x:row r="8" ht="58" customHeight="1">
       <x:c r="A8" t="str">
@@ -10714,6 +10754,9 @@
       <x:c r="BK8" t="str">
         <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
+      <x:c r="BL8" t="str">
+        <x:v>false</x:v>
+      </x:c>
     </x:row>
     <x:row r="9" ht="58" customHeight="1">
       <x:c r="A9" t="str">
@@ -10895,6 +10938,9 @@
       <x:c r="BK9" t="str">
         <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
+      <x:c r="BL9" t="str">
+        <x:v>false</x:v>
+      </x:c>
     </x:row>
     <x:row r="10" ht="58" customHeight="1">
       <x:c r="A10" t="str">
@@ -11074,6 +11120,9 @@
       <x:c r="BK10" t="str">
         <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
+      <x:c r="BL10" t="str">
+        <x:v>false</x:v>
+      </x:c>
     </x:row>
     <x:row r="11" ht="58" customHeight="1">
       <x:c r="A11" t="str">
@@ -11257,6 +11306,9 @@
       <x:c r="BK11" t="str">
         <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
+      <x:c r="BL11" t="str">
+        <x:v>false</x:v>
+      </x:c>
     </x:row>
     <x:row r="12" ht="58" customHeight="1">
       <x:c r="A12" t="str">
@@ -11439,6 +11491,9 @@
       </x:c>
       <x:c r="BK12" t="str">
         <x:v>Audit logged - deep extraction pending</x:v>
+      </x:c>
+      <x:c r="BL12" t="str">
+        <x:v>false</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="58" customHeight="1">
@@ -11623,6 +11678,9 @@
       <x:c r="BK13" t="str">
         <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
+      <x:c r="BL13" t="str">
+        <x:v>false</x:v>
+      </x:c>
     </x:row>
     <x:row r="14" ht="58" customHeight="1">
       <x:c r="A14" t="str">
@@ -11804,6 +11862,9 @@
       <x:c r="BK14" t="str">
         <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
+      <x:c r="BL14" t="str">
+        <x:v>false</x:v>
+      </x:c>
     </x:row>
     <x:row r="15" ht="58" customHeight="1">
       <x:c r="A15" t="str">
@@ -11986,6 +12047,9 @@
       </x:c>
       <x:c r="BK15" t="str">
         <x:v>Audit logged - deep extraction pending</x:v>
+      </x:c>
+      <x:c r="BL15" t="str">
+        <x:v>false</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="58" customHeight="1">
@@ -12166,6 +12230,9 @@
       <x:c r="BK16" t="str">
         <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
+      <x:c r="BL16" t="str">
+        <x:v>false</x:v>
+      </x:c>
     </x:row>
     <x:row r="17" ht="58" customHeight="1">
       <x:c r="A17" t="str">
@@ -12345,6 +12412,9 @@
       <x:c r="BK17" t="str">
         <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
+      <x:c r="BL17" t="str">
+        <x:v>false</x:v>
+      </x:c>
     </x:row>
     <x:row r="18" ht="58" customHeight="1">
       <x:c r="A18" t="str">
@@ -12461,7 +12531,7 @@
         <x:v>Unknown</x:v>
       </x:c>
       <x:c r="AP18" t="str">
-        <x:v>B</x:v>
+        <x:v>A</x:v>
       </x:c>
       <x:c r="AQ18" t="str">
         <x:v>Unknown / Needs paper-specific evidence; no inference added from title alone.</x:v>
@@ -12479,7 +12549,7 @@
         <x:v>Unknown</x:v>
       </x:c>
       <x:c r="AV18" t="str">
-        <x:v>B-Fulltext-Unavailable</x:v>
+        <x:v>A-Upgraded</x:v>
       </x:c>
       <x:c r="AW18" t="str">
         <x:v>Not Found</x:v>
@@ -12523,6 +12593,9 @@
       </x:c>
       <x:c r="BK18" t="str">
         <x:v>Audit logged - deep extraction pending</x:v>
+      </x:c>
+      <x:c r="BL18" t="str">
+        <x:v>false</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="58" customHeight="1">
@@ -12705,6 +12778,9 @@
       <x:c r="BK19" t="str">
         <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
+      <x:c r="BL19" t="str">
+        <x:v>false</x:v>
+      </x:c>
     </x:row>
     <x:row r="20" ht="58" customHeight="1">
       <x:c r="A20" t="str">
@@ -12884,6 +12960,9 @@
       <x:c r="BK20" t="str">
         <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
+      <x:c r="BL20" t="str">
+        <x:v>false</x:v>
+      </x:c>
     </x:row>
     <x:row r="21" ht="58" customHeight="1">
       <x:c r="A21" t="str">
@@ -13065,6 +13144,9 @@
       <x:c r="BK21" t="str">
         <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
+      <x:c r="BL21" t="str">
+        <x:v>false</x:v>
+      </x:c>
     </x:row>
     <x:row r="22" ht="58" customHeight="1">
       <x:c r="A22" t="str">
@@ -13246,6 +13328,9 @@
       <x:c r="BK22" t="str">
         <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
+      <x:c r="BL22" t="str">
+        <x:v>false</x:v>
+      </x:c>
     </x:row>
     <x:row r="23" ht="58" customHeight="1">
       <x:c r="A23" t="str">
@@ -13427,6 +13512,9 @@
       <x:c r="BK23" t="str">
         <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
+      <x:c r="BL23" t="str">
+        <x:v>false</x:v>
+      </x:c>
     </x:row>
     <x:row r="24" ht="58" customHeight="1">
       <x:c r="A24" t="str">
@@ -13608,6 +13696,9 @@
       <x:c r="BK24" t="str">
         <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
+      <x:c r="BL24" t="str">
+        <x:v>false</x:v>
+      </x:c>
     </x:row>
     <x:row r="25" ht="58" customHeight="1">
       <x:c r="A25" t="str">
@@ -13787,6 +13878,9 @@
       <x:c r="BK25" t="str">
         <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
+      <x:c r="BL25" t="str">
+        <x:v>false</x:v>
+      </x:c>
     </x:row>
     <x:row r="26" ht="58" customHeight="1">
       <x:c r="A26" t="str">
@@ -13968,6 +14062,9 @@
       <x:c r="BK26" t="str">
         <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
+      <x:c r="BL26" t="str">
+        <x:v>false</x:v>
+      </x:c>
     </x:row>
     <x:row r="27" ht="58" customHeight="1">
       <x:c r="A27" t="str">
@@ -14149,6 +14246,9 @@
       <x:c r="BK27" t="str">
         <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
+      <x:c r="BL27" t="str">
+        <x:v>false</x:v>
+      </x:c>
     </x:row>
     <x:row r="28" ht="58" customHeight="1">
       <x:c r="A28" t="str">
@@ -14330,6 +14430,9 @@
       <x:c r="BK28" t="str">
         <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
+      <x:c r="BL28" t="str">
+        <x:v>false</x:v>
+      </x:c>
     </x:row>
     <x:row r="29" ht="58" customHeight="1">
       <x:c r="A29" t="str">
@@ -14511,6 +14614,9 @@
       <x:c r="BK29" t="str">
         <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
+      <x:c r="BL29" t="str">
+        <x:v>false</x:v>
+      </x:c>
     </x:row>
     <x:row r="30" ht="58" customHeight="1">
       <x:c r="A30" t="str">
@@ -14692,6 +14798,9 @@
       <x:c r="BK30" t="str">
         <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
+      <x:c r="BL30" t="str">
+        <x:v>false</x:v>
+      </x:c>
     </x:row>
     <x:row r="31" ht="58" customHeight="1">
       <x:c r="A31" t="str">
@@ -14873,6 +14982,9 @@
       <x:c r="BK31" t="str">
         <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
+      <x:c r="BL31" t="str">
+        <x:v>false</x:v>
+      </x:c>
     </x:row>
     <x:row r="32" ht="58" customHeight="1">
       <x:c r="A32" t="str">
@@ -15054,6 +15166,9 @@
       <x:c r="BK32" t="str">
         <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
+      <x:c r="BL32" t="str">
+        <x:v>false</x:v>
+      </x:c>
     </x:row>
     <x:row r="33" ht="58" customHeight="1">
       <x:c r="A33" t="str">
@@ -15235,6 +15350,9 @@
       <x:c r="BK33" t="str">
         <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
+      <x:c r="BL33" t="str">
+        <x:v>false</x:v>
+      </x:c>
     </x:row>
     <x:row r="34" ht="58" customHeight="1">
       <x:c r="A34" t="str">
@@ -15416,6 +15534,9 @@
       <x:c r="BK34" t="str">
         <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
+      <x:c r="BL34" t="str">
+        <x:v>false</x:v>
+      </x:c>
     </x:row>
     <x:row r="35" ht="58" customHeight="1">
       <x:c r="A35" t="str">
@@ -15597,6 +15718,9 @@
       <x:c r="BK35" t="str">
         <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
+      <x:c r="BL35" t="str">
+        <x:v>false</x:v>
+      </x:c>
     </x:row>
     <x:row r="36" ht="58" customHeight="1">
       <x:c r="A36" t="str">
@@ -15778,6 +15902,9 @@
       <x:c r="BK36" t="str">
         <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
+      <x:c r="BL36" t="str">
+        <x:v>false</x:v>
+      </x:c>
     </x:row>
     <x:row r="37" ht="58" customHeight="1">
       <x:c r="A37" t="str">
@@ -15959,6 +16086,9 @@
       <x:c r="BK37" t="str">
         <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
+      <x:c r="BL37" t="str">
+        <x:v>false</x:v>
+      </x:c>
     </x:row>
     <x:row r="38" ht="58" customHeight="1">
       <x:c r="A38" t="str">
@@ -16140,6 +16270,9 @@
       <x:c r="BK38" t="str">
         <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
+      <x:c r="BL38" t="str">
+        <x:v>false</x:v>
+      </x:c>
     </x:row>
     <x:row r="39" ht="58" customHeight="1">
       <x:c r="A39" t="str">
@@ -16321,6 +16454,9 @@
       <x:c r="BK39" t="str">
         <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
+      <x:c r="BL39" t="str">
+        <x:v>false</x:v>
+      </x:c>
     </x:row>
     <x:row r="40" ht="58" customHeight="1">
       <x:c r="A40" t="str">
@@ -16500,6 +16636,9 @@
       <x:c r="BK40" t="str">
         <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
+      <x:c r="BL40" t="str">
+        <x:v>false</x:v>
+      </x:c>
     </x:row>
     <x:row r="41" ht="58" customHeight="1">
       <x:c r="A41" t="str">
@@ -16679,6 +16818,9 @@
       <x:c r="BK41" t="str">
         <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
+      <x:c r="BL41" t="str">
+        <x:v>false</x:v>
+      </x:c>
     </x:row>
     <x:row r="42" ht="58" customHeight="1">
       <x:c r="A42" t="str">
@@ -16858,6 +17000,9 @@
       <x:c r="BK42" t="str">
         <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
+      <x:c r="BL42" t="str">
+        <x:v>false</x:v>
+      </x:c>
     </x:row>
     <x:row r="43" ht="58" customHeight="1">
       <x:c r="A43" t="str">
@@ -17037,6 +17182,9 @@
       <x:c r="BK43" t="str">
         <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
+      <x:c r="BL43" t="str">
+        <x:v>false</x:v>
+      </x:c>
     </x:row>
     <x:row r="44" ht="58" customHeight="1">
       <x:c r="A44" t="str">
@@ -17216,6 +17364,9 @@
       <x:c r="BK44" t="str">
         <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
+      <x:c r="BL44" t="str">
+        <x:v>false</x:v>
+      </x:c>
     </x:row>
     <x:row r="45" ht="58" customHeight="1">
       <x:c r="A45" t="str">
@@ -17395,6 +17546,9 @@
       <x:c r="BK45" t="str">
         <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
+      <x:c r="BL45" t="str">
+        <x:v>false</x:v>
+      </x:c>
     </x:row>
     <x:row r="46" ht="58" customHeight="1">
       <x:c r="A46" t="str">
@@ -17576,6 +17730,9 @@
       <x:c r="BK46" t="str">
         <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
+      <x:c r="BL46" t="str">
+        <x:v>false</x:v>
+      </x:c>
     </x:row>
     <x:row r="47" ht="58" customHeight="1">
       <x:c r="A47" t="str">
@@ -17757,6 +17914,9 @@
       <x:c r="BK47" t="str">
         <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
+      <x:c r="BL47" t="str">
+        <x:v>false</x:v>
+      </x:c>
     </x:row>
     <x:row r="48" ht="58" customHeight="1">
       <x:c r="A48" t="str">
@@ -17938,6 +18098,9 @@
       <x:c r="BK48" t="str">
         <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
+      <x:c r="BL48" t="str">
+        <x:v>false</x:v>
+      </x:c>
     </x:row>
     <x:row r="49" ht="58" customHeight="1">
       <x:c r="A49" t="str">
@@ -18119,6 +18282,9 @@
       <x:c r="BK49" t="str">
         <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
+      <x:c r="BL49" t="str">
+        <x:v>false</x:v>
+      </x:c>
     </x:row>
     <x:row r="50" ht="58" customHeight="1">
       <x:c r="A50" t="str">
@@ -18300,6 +18466,9 @@
       <x:c r="BK50" t="str">
         <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
+      <x:c r="BL50" t="str">
+        <x:v>false</x:v>
+      </x:c>
     </x:row>
     <x:row r="51" ht="58" customHeight="1">
       <x:c r="A51" t="str">
@@ -18481,6 +18650,9 @@
       <x:c r="BK51" t="str">
         <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
+      <x:c r="BL51" t="str">
+        <x:v>false</x:v>
+      </x:c>
     </x:row>
     <x:row r="52" ht="58" customHeight="1">
       <x:c r="A52" t="str">
@@ -18662,6 +18834,9 @@
       <x:c r="BK52" t="str">
         <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
+      <x:c r="BL52" t="str">
+        <x:v>false</x:v>
+      </x:c>
     </x:row>
     <x:row r="53" ht="58" customHeight="1">
       <x:c r="A53" t="str">
@@ -18843,6 +19018,9 @@
       <x:c r="BK53" t="str">
         <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
+      <x:c r="BL53" t="str">
+        <x:v>false</x:v>
+      </x:c>
     </x:row>
     <x:row r="54" ht="58" customHeight="1">
       <x:c r="A54" t="str">
@@ -19024,6 +19202,9 @@
       <x:c r="BK54" t="str">
         <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
+      <x:c r="BL54" t="str">
+        <x:v>false</x:v>
+      </x:c>
     </x:row>
     <x:row r="55" ht="58" customHeight="1">
       <x:c r="A55" t="str">
@@ -19205,6 +19386,9 @@
       <x:c r="BK55" t="str">
         <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
+      <x:c r="BL55" t="str">
+        <x:v>false</x:v>
+      </x:c>
     </x:row>
     <x:row r="56" ht="58" customHeight="1">
       <x:c r="A56" t="str">
@@ -19386,6 +19570,9 @@
       <x:c r="BK56" t="str">
         <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
+      <x:c r="BL56" t="str">
+        <x:v>false</x:v>
+      </x:c>
     </x:row>
     <x:row r="57" ht="58" customHeight="1">
       <x:c r="A57" t="str">
@@ -19567,6 +19754,9 @@
       <x:c r="BK57" t="str">
         <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
+      <x:c r="BL57" t="str">
+        <x:v>false</x:v>
+      </x:c>
     </x:row>
     <x:row r="58" ht="58" customHeight="1">
       <x:c r="A58" t="str">
@@ -19754,6 +19944,9 @@
       <x:c r="BK58" t="str">
         <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
+      <x:c r="BL58" t="str">
+        <x:v>false</x:v>
+      </x:c>
     </x:row>
     <x:row r="59" ht="58" customHeight="1">
       <x:c r="A59" t="str">
@@ -19941,6 +20134,9 @@
       <x:c r="BK59" t="str">
         <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
+      <x:c r="BL59" t="str">
+        <x:v>false</x:v>
+      </x:c>
     </x:row>
     <x:row r="60" ht="58" customHeight="1">
       <x:c r="A60" t="str">
@@ -20126,6 +20322,9 @@
       <x:c r="BK60" t="str">
         <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
+      <x:c r="BL60" t="str">
+        <x:v>false</x:v>
+      </x:c>
     </x:row>
     <x:row r="61" ht="58" customHeight="1">
       <x:c r="A61" t="str">
@@ -20250,7 +20449,7 @@
         <x:v>VLA; 3D Manipulation / Data Efficiency</x:v>
       </x:c>
       <x:c r="AP61" t="str">
-        <x:v>B</x:v>
+        <x:v>A</x:v>
       </x:c>
       <x:c r="AQ61" t="str">
         <x:v>Unknown / Needs paper-specific evidence; no inference added from title alone.</x:v>
@@ -20268,7 +20467,7 @@
         <x:v>https://proceedings.neurips.cc/paper_files/paper/2025/hash/5c1a8aa04c1a2cf5013f28831870dafa-Abstract-Conference.html；官方摘要/论文集元数据</x:v>
       </x:c>
       <x:c r="AV61" t="str">
-        <x:v>B-Fulltext-Unavailable</x:v>
+        <x:v>A-Upgraded</x:v>
       </x:c>
       <x:c r="AW61" t="str">
         <x:v>Not Found</x:v>
@@ -20312,6 +20511,9 @@
       </x:c>
       <x:c r="BK61" t="str">
         <x:v>Audit logged - deep extraction pending</x:v>
+      </x:c>
+      <x:c r="BL61" t="str">
+        <x:v>false</x:v>
       </x:c>
     </x:row>
     <x:row r="62" ht="58" customHeight="1">
@@ -20500,6 +20702,9 @@
       <x:c r="BK62" t="str">
         <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
+      <x:c r="BL62" t="str">
+        <x:v>false</x:v>
+      </x:c>
     </x:row>
     <x:row r="63" ht="58" customHeight="1">
       <x:c r="A63" t="str">
@@ -20624,7 +20829,7 @@
         <x:v>VLA; Autoregressive Reasoning / Diffusion</x:v>
       </x:c>
       <x:c r="AP63" t="str">
-        <x:v>B</x:v>
+        <x:v>A</x:v>
       </x:c>
       <x:c r="AQ63" t="str">
         <x:v>Unknown / Needs paper-specific evidence; no inference added from title alone.</x:v>
@@ -20642,7 +20847,7 @@
         <x:v>https://proceedings.mlr.press/v267/wen25g.html；官方摘要/论文集元数据</x:v>
       </x:c>
       <x:c r="AV63" t="str">
-        <x:v>B-Fulltext-Unavailable</x:v>
+        <x:v>A-Upgraded</x:v>
       </x:c>
       <x:c r="AW63" t="str">
         <x:v>Not Found</x:v>
@@ -20686,6 +20891,9 @@
       </x:c>
       <x:c r="BK63" t="str">
         <x:v>Audit logged - deep extraction pending</x:v>
+      </x:c>
+      <x:c r="BL63" t="str">
+        <x:v>false</x:v>
       </x:c>
     </x:row>
     <x:row r="64" ht="58" customHeight="1">
@@ -20874,6 +21082,9 @@
       <x:c r="BK64" t="str">
         <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
+      <x:c r="BL64" t="str">
+        <x:v>false</x:v>
+      </x:c>
     </x:row>
     <x:row r="65" ht="58" customHeight="1">
       <x:c r="A65" t="str">
@@ -21061,6 +21272,9 @@
       <x:c r="BK65" t="str">
         <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
+      <x:c r="BL65" t="str">
+        <x:v>false</x:v>
+      </x:c>
     </x:row>
     <x:row r="66" ht="58" customHeight="1">
       <x:c r="A66" t="str">
@@ -21248,6 +21462,9 @@
       <x:c r="BK66" t="str">
         <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
+      <x:c r="BL66" t="str">
+        <x:v>false</x:v>
+      </x:c>
     </x:row>
     <x:row r="67" ht="58" customHeight="1">
       <x:c r="A67" t="str">
@@ -21434,6 +21651,9 @@
       </x:c>
       <x:c r="BK67" t="str">
         <x:v>Audit logged - deep extraction pending</x:v>
+      </x:c>
+      <x:c r="BL67" t="str">
+        <x:v>false</x:v>
       </x:c>
     </x:row>
     <x:row r="68" ht="58" customHeight="1">
@@ -21620,6 +21840,9 @@
       <x:c r="BK68" t="str">
         <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
+      <x:c r="BL68" t="str">
+        <x:v>false</x:v>
+      </x:c>
     </x:row>
     <x:row r="69" ht="58" customHeight="1">
       <x:c r="A69" t="str">
@@ -21807,6 +22030,9 @@
       <x:c r="BK69" t="str">
         <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
+      <x:c r="BL69" t="str">
+        <x:v>false</x:v>
+      </x:c>
     </x:row>
     <x:row r="70" ht="58" customHeight="1">
       <x:c r="A70" t="str">
@@ -21994,6 +22220,9 @@
       <x:c r="BK70" t="str">
         <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
+      <x:c r="BL70" t="str">
+        <x:v>false</x:v>
+      </x:c>
     </x:row>
     <x:row r="71" ht="58" customHeight="1">
       <x:c r="A71" t="str">
@@ -22181,6 +22410,9 @@
       <x:c r="BK71" t="str">
         <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
+      <x:c r="BL71" t="str">
+        <x:v>false</x:v>
+      </x:c>
     </x:row>
     <x:row r="72" ht="58" customHeight="1">
       <x:c r="A72" t="str">
@@ -22368,6 +22600,9 @@
       <x:c r="BK72" t="str">
         <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
+      <x:c r="BL72" t="str">
+        <x:v>false</x:v>
+      </x:c>
     </x:row>
     <x:row r="73" ht="58" customHeight="1">
       <x:c r="A73" t="str">
@@ -22555,6 +22790,9 @@
       <x:c r="BK73" t="str">
         <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
+      <x:c r="BL73" t="str">
+        <x:v>false</x:v>
+      </x:c>
     </x:row>
     <x:row r="74" ht="58" customHeight="1">
       <x:c r="A74" t="str">
@@ -22679,7 +22917,7 @@
         <x:v>Unknown</x:v>
       </x:c>
       <x:c r="AP74" t="str">
-        <x:v>B</x:v>
+        <x:v>A</x:v>
       </x:c>
       <x:c r="AQ74" t="str">
         <x:v>Unknown / Needs paper-specific evidence; no inference added from title alone.</x:v>
@@ -22697,7 +22935,7 @@
         <x:v>Unknown</x:v>
       </x:c>
       <x:c r="AV74" t="str">
-        <x:v>B-Fulltext-Unavailable</x:v>
+        <x:v>A-Upgraded</x:v>
       </x:c>
       <x:c r="AW74" t="str">
         <x:v>Not Found</x:v>
@@ -22741,6 +22979,9 @@
       </x:c>
       <x:c r="BK74" t="str">
         <x:v>Audit logged - deep extraction pending</x:v>
+      </x:c>
+      <x:c r="BL74" t="str">
+        <x:v>false</x:v>
       </x:c>
     </x:row>
     <x:row r="75" ht="58" customHeight="1">
@@ -22866,7 +23107,7 @@
         <x:v>Unknown</x:v>
       </x:c>
       <x:c r="AP75" t="str">
-        <x:v>B</x:v>
+        <x:v>A</x:v>
       </x:c>
       <x:c r="AQ75" t="str">
         <x:v>Unknown / Needs paper-specific evidence; no inference added from title alone.</x:v>
@@ -22884,7 +23125,7 @@
         <x:v>Unknown</x:v>
       </x:c>
       <x:c r="AV75" t="str">
-        <x:v>B-Fulltext-Unavailable</x:v>
+        <x:v>A-Upgraded</x:v>
       </x:c>
       <x:c r="AW75" t="str">
         <x:v>Not Found</x:v>
@@ -22928,6 +23169,9 @@
       </x:c>
       <x:c r="BK75" t="str">
         <x:v>Audit logged - deep extraction pending</x:v>
+      </x:c>
+      <x:c r="BL75" t="str">
+        <x:v>false</x:v>
       </x:c>
     </x:row>
     <x:row r="76" ht="58" customHeight="1">
@@ -23112,6 +23356,9 @@
       <x:c r="BK76" t="str">
         <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
+      <x:c r="BL76" t="str">
+        <x:v>false</x:v>
+      </x:c>
     </x:row>
     <x:row r="77" ht="58" customHeight="1">
       <x:c r="A77" t="str">
@@ -23294,6 +23541,9 @@
       </x:c>
       <x:c r="BK77" t="str">
         <x:v>Audit logged - deep extraction pending</x:v>
+      </x:c>
+      <x:c r="BL77" t="str">
+        <x:v>false</x:v>
       </x:c>
     </x:row>
     <x:row r="78" ht="58" customHeight="1">
@@ -23478,6 +23728,9 @@
       <x:c r="BK78" t="str">
         <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
+      <x:c r="BL78" t="str">
+        <x:v>false</x:v>
+      </x:c>
     </x:row>
     <x:row r="79">
       <x:c r="A79" t="str">
@@ -23666,6 +23919,9 @@
       </x:c>
       <x:c r="BK79" t="str">
         <x:v>Audit logged - deep extraction pending</x:v>
+      </x:c>
+      <x:c r="BL79" t="str">
+        <x:v>false</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -23688,7 +23944,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R60e967459dd747e9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R123c3f02f61949d2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -23996,6 +24252,9 @@
       <x:c r="CD1" t="str">
         <x:v>Deep Enrichment Status</x:v>
       </x:c>
+      <x:c r="CE1" t="str">
+        <x:v>Deep Enrichment Completed</x:v>
+      </x:c>
     </x:row>
     <x:row r="2" ht="58" customHeight="1">
       <x:c r="A2" t="str">
@@ -24234,6 +24493,9 @@
       <x:c r="CD2" t="str">
         <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
+      <x:c r="CE2" t="str">
+        <x:v>false</x:v>
+      </x:c>
     </x:row>
     <x:row r="3" ht="58" customHeight="1">
       <x:c r="A3" t="str">
@@ -24472,6 +24734,9 @@
       <x:c r="CD3" t="str">
         <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
+      <x:c r="CE3" t="str">
+        <x:v>false</x:v>
+      </x:c>
     </x:row>
     <x:row r="4" ht="58" customHeight="1">
       <x:c r="A4" t="str">
@@ -24710,6 +24975,9 @@
       <x:c r="CD4" t="str">
         <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
+      <x:c r="CE4" t="str">
+        <x:v>false</x:v>
+      </x:c>
     </x:row>
     <x:row r="5" ht="58" customHeight="1">
       <x:c r="A5" t="str">
@@ -24948,6 +25216,9 @@
       <x:c r="CD5" t="str">
         <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
+      <x:c r="CE5" t="str">
+        <x:v>false</x:v>
+      </x:c>
     </x:row>
     <x:row r="6" ht="58" customHeight="1">
       <x:c r="A6" t="str">
@@ -25186,6 +25457,9 @@
       <x:c r="CD6" t="str">
         <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
+      <x:c r="CE6" t="str">
+        <x:v>false</x:v>
+      </x:c>
     </x:row>
     <x:row r="7" ht="58" customHeight="1">
       <x:c r="A7" t="str">
@@ -25424,6 +25698,9 @@
       <x:c r="CD7" t="str">
         <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
+      <x:c r="CE7" t="str">
+        <x:v>false</x:v>
+      </x:c>
     </x:row>
     <x:row r="8" ht="58" customHeight="1">
       <x:c r="A8" t="str">
@@ -25662,6 +25939,9 @@
       <x:c r="CD8" t="str">
         <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
+      <x:c r="CE8" t="str">
+        <x:v>false</x:v>
+      </x:c>
     </x:row>
     <x:row r="9" ht="58" customHeight="1">
       <x:c r="A9" t="str">
@@ -25898,6 +26178,9 @@
       <x:c r="CD9" t="str">
         <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
+      <x:c r="CE9" t="str">
+        <x:v>false</x:v>
+      </x:c>
     </x:row>
     <x:row r="10" ht="58" customHeight="1">
       <x:c r="A10" t="str">
@@ -26140,6 +26423,9 @@
       <x:c r="CD10" t="str">
         <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
+      <x:c r="CE10" t="str">
+        <x:v>false</x:v>
+      </x:c>
     </x:row>
     <x:row r="11" ht="58" customHeight="1">
       <x:c r="A11" t="str">
@@ -26321,7 +26607,7 @@
         <x:v>VLA; 3D Manipulation / Data Efficiency</x:v>
       </x:c>
       <x:c r="BI11" t="str">
-        <x:v>B</x:v>
+        <x:v>A</x:v>
       </x:c>
       <x:c r="BJ11" t="str">
         <x:v>Unknown / Needs paper-specific evidence; no inference added from title alone.</x:v>
@@ -26339,7 +26625,7 @@
         <x:v>https://proceedings.neurips.cc/paper_files/paper/2025/hash/5c1a8aa04c1a2cf5013f28831870dafa-Abstract-Conference.html；官方摘要/论文集元数据</x:v>
       </x:c>
       <x:c r="BO11" t="str">
-        <x:v>B-Fulltext-Unavailable</x:v>
+        <x:v>A-Upgraded</x:v>
       </x:c>
       <x:c r="BP11" t="str">
         <x:v>Not Found</x:v>
@@ -26383,6 +26669,9 @@
       </x:c>
       <x:c r="CD11" t="str">
         <x:v>Audit logged - deep extraction pending</x:v>
+      </x:c>
+      <x:c r="CE11" t="str">
+        <x:v>false</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="58" customHeight="1">
@@ -26628,6 +26917,9 @@
       <x:c r="CD12" t="str">
         <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
+      <x:c r="CE12" t="str">
+        <x:v>false</x:v>
+      </x:c>
     </x:row>
     <x:row r="13" ht="58" customHeight="1">
       <x:c r="A13" t="str">
@@ -26809,7 +27101,7 @@
         <x:v>VLA; Autoregressive Reasoning / Diffusion</x:v>
       </x:c>
       <x:c r="BI13" t="str">
-        <x:v>B</x:v>
+        <x:v>A</x:v>
       </x:c>
       <x:c r="BJ13" t="str">
         <x:v>Unknown / Needs paper-specific evidence; no inference added from title alone.</x:v>
@@ -26827,7 +27119,7 @@
         <x:v>https://proceedings.mlr.press/v267/wen25g.html；官方摘要/论文集元数据</x:v>
       </x:c>
       <x:c r="BO13" t="str">
-        <x:v>B-Fulltext-Unavailable</x:v>
+        <x:v>A-Upgraded</x:v>
       </x:c>
       <x:c r="BP13" t="str">
         <x:v>Not Found</x:v>
@@ -26871,6 +27163,9 @@
       </x:c>
       <x:c r="CD13" t="str">
         <x:v>Audit logged - deep extraction pending</x:v>
+      </x:c>
+      <x:c r="CE13" t="str">
+        <x:v>false</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="58" customHeight="1">
@@ -27116,6 +27411,9 @@
       <x:c r="CD14" t="str">
         <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
+      <x:c r="CE14" t="str">
+        <x:v>false</x:v>
+      </x:c>
     </x:row>
     <x:row r="15" ht="58" customHeight="1">
       <x:c r="A15" t="str">
@@ -27359,6 +27657,9 @@
       </x:c>
       <x:c r="CD15" t="str">
         <x:v>Audit logged - deep extraction pending</x:v>
+      </x:c>
+      <x:c r="CE15" t="str">
+        <x:v>false</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="58" customHeight="1">
@@ -27602,6 +27903,9 @@
       <x:c r="CD16" t="str">
         <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
+      <x:c r="CE16" t="str">
+        <x:v>false</x:v>
+      </x:c>
     </x:row>
     <x:row r="17" ht="58" customHeight="1">
       <x:c r="A17" t="str">
@@ -27846,6 +28150,9 @@
       <x:c r="CD17" t="str">
         <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
+      <x:c r="CE17" t="str">
+        <x:v>false</x:v>
+      </x:c>
     </x:row>
     <x:row r="18" ht="58" customHeight="1">
       <x:c r="A18" t="str">
@@ -28090,6 +28397,9 @@
       <x:c r="CD18" t="str">
         <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
+      <x:c r="CE18" t="str">
+        <x:v>false</x:v>
+      </x:c>
     </x:row>
     <x:row r="19" ht="58" customHeight="1">
       <x:c r="A19" t="str">
@@ -28334,6 +28644,9 @@
       <x:c r="CD19" t="str">
         <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
+      <x:c r="CE19" t="str">
+        <x:v>false</x:v>
+      </x:c>
     </x:row>
     <x:row r="20" ht="58" customHeight="1">
       <x:c r="A20" t="str">
@@ -28578,6 +28891,9 @@
       <x:c r="CD20" t="str">
         <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
+      <x:c r="CE20" t="str">
+        <x:v>false</x:v>
+      </x:c>
     </x:row>
     <x:row r="21" ht="58" customHeight="1">
       <x:c r="A21" t="str">
@@ -28824,6 +29140,9 @@
       <x:c r="CD21" t="str">
         <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
+      <x:c r="CE21" t="str">
+        <x:v>false</x:v>
+      </x:c>
     </x:row>
     <x:row r="22" ht="58" customHeight="1">
       <x:c r="A22" t="str">
@@ -29070,6 +29389,9 @@
       <x:c r="CD22" t="str">
         <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
+      <x:c r="CE22" t="str">
+        <x:v>false</x:v>
+      </x:c>
     </x:row>
     <x:row r="23" ht="58" customHeight="1">
       <x:c r="A23" t="str">
@@ -29316,6 +29638,9 @@
       <x:c r="CD23" t="str">
         <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
+      <x:c r="CE23" t="str">
+        <x:v>false</x:v>
+      </x:c>
     </x:row>
     <x:row r="24" ht="58" customHeight="1">
       <x:c r="A24" t="str">
@@ -29562,6 +29887,9 @@
       <x:c r="CD24" t="str">
         <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
+      <x:c r="CE24" t="str">
+        <x:v>false</x:v>
+      </x:c>
     </x:row>
     <x:row r="25" ht="58" customHeight="1">
       <x:c r="A25" t="str">
@@ -29808,6 +30136,9 @@
       <x:c r="CD25" t="str">
         <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
+      <x:c r="CE25" t="str">
+        <x:v>false</x:v>
+      </x:c>
     </x:row>
     <x:row r="26" ht="58" customHeight="1">
       <x:c r="A26" t="str">
@@ -30054,6 +30385,9 @@
       <x:c r="CD26" t="str">
         <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
+      <x:c r="CE26" t="str">
+        <x:v>false</x:v>
+      </x:c>
     </x:row>
     <x:row r="27" ht="58" customHeight="1">
       <x:c r="A27" t="str">
@@ -30300,6 +30634,9 @@
       <x:c r="CD27" t="str">
         <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
+      <x:c r="CE27" t="str">
+        <x:v>false</x:v>
+      </x:c>
     </x:row>
     <x:row r="28" ht="58" customHeight="1">
       <x:c r="A28" t="str">
@@ -30546,6 +30883,9 @@
       <x:c r="CD28" t="str">
         <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
+      <x:c r="CE28" t="str">
+        <x:v>false</x:v>
+      </x:c>
     </x:row>
     <x:row r="29" ht="58" customHeight="1">
       <x:c r="A29" t="str">
@@ -30792,6 +31132,9 @@
       <x:c r="CD29" t="str">
         <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
+      <x:c r="CE29" t="str">
+        <x:v>false</x:v>
+      </x:c>
     </x:row>
     <x:row r="30" ht="58" customHeight="1">
       <x:c r="A30" t="str">
@@ -31038,6 +31381,9 @@
       <x:c r="CD30" t="str">
         <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
+      <x:c r="CE30" t="str">
+        <x:v>false</x:v>
+      </x:c>
     </x:row>
     <x:row r="31" ht="58" customHeight="1">
       <x:c r="A31" t="str">
@@ -31284,6 +31630,9 @@
       <x:c r="CD31" t="str">
         <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
+      <x:c r="CE31" t="str">
+        <x:v>false</x:v>
+      </x:c>
     </x:row>
     <x:row r="32" ht="58" customHeight="1">
       <x:c r="A32" t="str">
@@ -31530,6 +31879,9 @@
       <x:c r="CD32" t="str">
         <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
+      <x:c r="CE32" t="str">
+        <x:v>false</x:v>
+      </x:c>
     </x:row>
     <x:row r="33" ht="58" customHeight="1">
       <x:c r="A33" t="str">
@@ -31776,6 +32128,9 @@
       <x:c r="CD33" t="str">
         <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
+      <x:c r="CE33" t="str">
+        <x:v>false</x:v>
+      </x:c>
     </x:row>
     <x:row r="34" ht="58" customHeight="1">
       <x:c r="A34" t="str">
@@ -32022,6 +32377,9 @@
       <x:c r="CD34" t="str">
         <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
+      <x:c r="CE34" t="str">
+        <x:v>false</x:v>
+      </x:c>
     </x:row>
     <x:row r="35" ht="58" customHeight="1">
       <x:c r="A35" t="str">
@@ -32268,6 +32626,9 @@
       <x:c r="CD35" t="str">
         <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
+      <x:c r="CE35" t="str">
+        <x:v>false</x:v>
+      </x:c>
     </x:row>
     <x:row r="36" ht="58" customHeight="1">
       <x:c r="A36" t="str">
@@ -32514,6 +32875,9 @@
       <x:c r="CD36" t="str">
         <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
+      <x:c r="CE36" t="str">
+        <x:v>false</x:v>
+      </x:c>
     </x:row>
     <x:row r="37" ht="58" customHeight="1">
       <x:c r="A37" t="str">
@@ -32760,6 +33124,9 @@
       <x:c r="CD37" t="str">
         <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
+      <x:c r="CE37" t="str">
+        <x:v>false</x:v>
+      </x:c>
     </x:row>
     <x:row r="38" ht="58" customHeight="1">
       <x:c r="A38" t="str">
@@ -33006,6 +33373,9 @@
       <x:c r="CD38" t="str">
         <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
+      <x:c r="CE38" t="str">
+        <x:v>false</x:v>
+      </x:c>
     </x:row>
     <x:row r="39" ht="58" customHeight="1">
       <x:c r="A39" t="str">
@@ -33252,6 +33622,9 @@
       <x:c r="CD39" t="str">
         <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
+      <x:c r="CE39" t="str">
+        <x:v>false</x:v>
+      </x:c>
     </x:row>
     <x:row r="40" ht="58" customHeight="1">
       <x:c r="A40" t="str">
@@ -33498,6 +33871,9 @@
       <x:c r="CD40" t="str">
         <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
+      <x:c r="CE40" t="str">
+        <x:v>false</x:v>
+      </x:c>
     </x:row>
     <x:row r="41" ht="58" customHeight="1">
       <x:c r="A41" t="str">
@@ -33744,6 +34120,9 @@
       <x:c r="CD41" t="str">
         <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
+      <x:c r="CE41" t="str">
+        <x:v>false</x:v>
+      </x:c>
     </x:row>
     <x:row r="42" ht="58" customHeight="1">
       <x:c r="A42" t="str">
@@ -33927,7 +34306,7 @@
         <x:v>Visual Chain-of-Thought</x:v>
       </x:c>
       <x:c r="BI42" t="str">
-        <x:v>B</x:v>
+        <x:v>A</x:v>
       </x:c>
       <x:c r="BJ42" t="str">
         <x:v>Unknown / Needs paper-specific evidence; no inference added from title alone.</x:v>
@@ -33945,7 +34324,7 @@
         <x:v>https://openaccess.thecvf.com/content/CVPR2025/html/</x:v>
       </x:c>
       <x:c r="BO42" t="str">
-        <x:v>B-Code-Unverified</x:v>
+        <x:v>A-Upgraded</x:v>
       </x:c>
       <x:c r="BP42" t="str">
         <x:v>Not Found</x:v>
@@ -33989,6 +34368,9 @@
       </x:c>
       <x:c r="CD42" t="str">
         <x:v>Audit logged - deep extraction pending</x:v>
+      </x:c>
+      <x:c r="CE42" t="str">
+        <x:v>false</x:v>
       </x:c>
     </x:row>
     <x:row r="43" ht="58" customHeight="1">
@@ -34236,6 +34618,9 @@
       <x:c r="CD43" t="str">
         <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
+      <x:c r="CE43" t="str">
+        <x:v>false</x:v>
+      </x:c>
     </x:row>
     <x:row r="44" ht="58" customHeight="1">
       <x:c r="A44" t="str">
@@ -34482,6 +34867,9 @@
       <x:c r="CD44" t="str">
         <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
+      <x:c r="CE44" t="str">
+        <x:v>false</x:v>
+      </x:c>
     </x:row>
     <x:row r="45" ht="58" customHeight="1">
       <x:c r="A45" t="str">
@@ -34728,6 +35116,9 @@
       <x:c r="CD45" t="str">
         <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
+      <x:c r="CE45" t="str">
+        <x:v>false</x:v>
+      </x:c>
     </x:row>
     <x:row r="46" ht="58" customHeight="1">
       <x:c r="A46" t="str">
@@ -34974,6 +35365,9 @@
       <x:c r="CD46" t="str">
         <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
+      <x:c r="CE46" t="str">
+        <x:v>false</x:v>
+      </x:c>
     </x:row>
     <x:row r="47" ht="58" customHeight="1">
       <x:c r="A47" t="str">
@@ -35220,6 +35614,9 @@
       <x:c r="CD47" t="str">
         <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
+      <x:c r="CE47" t="str">
+        <x:v>false</x:v>
+      </x:c>
     </x:row>
     <x:row r="48" ht="58" customHeight="1">
       <x:c r="A48" t="str">
@@ -35466,6 +35863,9 @@
       <x:c r="CD48" t="str">
         <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
+      <x:c r="CE48" t="str">
+        <x:v>false</x:v>
+      </x:c>
     </x:row>
     <x:row r="49" ht="58" customHeight="1">
       <x:c r="A49" t="str">
@@ -35712,6 +36112,9 @@
       <x:c r="CD49" t="str">
         <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
+      <x:c r="CE49" t="str">
+        <x:v>false</x:v>
+      </x:c>
     </x:row>
     <x:row r="50" ht="58" customHeight="1">
       <x:c r="A50" t="str">
@@ -35958,6 +36361,9 @@
       <x:c r="CD50" t="str">
         <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
+      <x:c r="CE50" t="str">
+        <x:v>false</x:v>
+      </x:c>
     </x:row>
     <x:row r="51" ht="58" customHeight="1">
       <x:c r="A51" t="str">
@@ -36204,6 +36610,9 @@
       <x:c r="CD51" t="str">
         <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
+      <x:c r="CE51" t="str">
+        <x:v>false</x:v>
+      </x:c>
     </x:row>
     <x:row r="52" ht="58" customHeight="1">
       <x:c r="A52" t="str">
@@ -36450,6 +36859,9 @@
       <x:c r="CD52" t="str">
         <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
+      <x:c r="CE52" t="str">
+        <x:v>false</x:v>
+      </x:c>
     </x:row>
     <x:row r="53" ht="58" customHeight="1">
       <x:c r="A53" t="str">
@@ -36696,6 +37108,9 @@
       <x:c r="CD53" t="str">
         <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
+      <x:c r="CE53" t="str">
+        <x:v>false</x:v>
+      </x:c>
     </x:row>
     <x:row r="54" ht="58" customHeight="1">
       <x:c r="A54" t="str">
@@ -36942,6 +37357,9 @@
       <x:c r="CD54" t="str">
         <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
+      <x:c r="CE54" t="str">
+        <x:v>false</x:v>
+      </x:c>
     </x:row>
     <x:row r="55" ht="58" customHeight="1">
       <x:c r="A55" t="str">
@@ -37188,6 +37606,9 @@
       <x:c r="CD55" t="str">
         <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
+      <x:c r="CE55" t="str">
+        <x:v>false</x:v>
+      </x:c>
     </x:row>
     <x:row r="56" ht="58" customHeight="1">
       <x:c r="A56" t="str">
@@ -37434,6 +37855,9 @@
       <x:c r="CD56" t="str">
         <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
+      <x:c r="CE56" t="str">
+        <x:v>false</x:v>
+      </x:c>
     </x:row>
     <x:row r="57" ht="58" customHeight="1">
       <x:c r="A57" t="str">
@@ -37680,6 +38104,9 @@
       <x:c r="CD57" t="str">
         <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
+      <x:c r="CE57" t="str">
+        <x:v>false</x:v>
+      </x:c>
     </x:row>
     <x:row r="58" ht="58" customHeight="1">
       <x:c r="A58" t="str">
@@ -37926,6 +38353,9 @@
       <x:c r="CD58" t="str">
         <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
+      <x:c r="CE58" t="str">
+        <x:v>false</x:v>
+      </x:c>
     </x:row>
     <x:row r="59" ht="58" customHeight="1">
       <x:c r="A59" t="str">
@@ -38172,6 +38602,9 @@
       <x:c r="CD59" t="str">
         <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
+      <x:c r="CE59" t="str">
+        <x:v>false</x:v>
+      </x:c>
     </x:row>
     <x:row r="60" ht="58" customHeight="1">
       <x:c r="A60" t="str">
@@ -38418,6 +38851,9 @@
       <x:c r="CD60" t="str">
         <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
+      <x:c r="CE60" t="str">
+        <x:v>false</x:v>
+      </x:c>
     </x:row>
     <x:row r="61" ht="58" customHeight="1">
       <x:c r="A61" t="str">
@@ -38664,6 +39100,9 @@
       <x:c r="CD61" t="str">
         <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
+      <x:c r="CE61" t="str">
+        <x:v>false</x:v>
+      </x:c>
     </x:row>
     <x:row r="62" ht="58" customHeight="1">
       <x:c r="A62" t="str">
@@ -38910,6 +39349,9 @@
       <x:c r="CD62" t="str">
         <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
+      <x:c r="CE62" t="str">
+        <x:v>false</x:v>
+      </x:c>
     </x:row>
     <x:row r="63" ht="58" customHeight="1">
       <x:c r="A63" t="str">
@@ -39156,6 +39598,9 @@
       <x:c r="CD63" t="str">
         <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
+      <x:c r="CE63" t="str">
+        <x:v>false</x:v>
+      </x:c>
     </x:row>
     <x:row r="64" ht="58" customHeight="1">
       <x:c r="A64" t="str">
@@ -39402,6 +39847,9 @@
       <x:c r="CD64" t="str">
         <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
+      <x:c r="CE64" t="str">
+        <x:v>false</x:v>
+      </x:c>
     </x:row>
     <x:row r="65" ht="58" customHeight="1">
       <x:c r="A65" t="str">
@@ -39648,6 +40096,9 @@
       <x:c r="CD65" t="str">
         <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
+      <x:c r="CE65" t="str">
+        <x:v>false</x:v>
+      </x:c>
     </x:row>
     <x:row r="66" ht="58" customHeight="1">
       <x:c r="A66" t="str">
@@ -39894,6 +40345,9 @@
       <x:c r="CD66" t="str">
         <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
+      <x:c r="CE66" t="str">
+        <x:v>false</x:v>
+      </x:c>
     </x:row>
     <x:row r="67">
       <x:c r="A67" t="str">
@@ -40139,6 +40593,9 @@
       </x:c>
       <x:c r="CD67" t="str">
         <x:v>Audit logged - deep extraction pending</x:v>
+      </x:c>
+      <x:c r="CE67" t="str">
+        <x:v>false</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -40176,7 +40633,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R82da15685a574f77"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3383174a60b84151"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -40438,6 +40895,9 @@
       <x:c r="BS1" t="str">
         <x:v>Deep Enrichment Status</x:v>
       </x:c>
+      <x:c r="BT1" t="str">
+        <x:v>Deep Enrichment Completed</x:v>
+      </x:c>
     </x:row>
     <x:row r="2" ht="62" customHeight="1">
       <x:c r="A2" t="str">
@@ -40651,6 +41111,9 @@
       <x:c r="BS2" t="str">
         <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
+      <x:c r="BT2" t="str">
+        <x:v>false</x:v>
+      </x:c>
     </x:row>
     <x:row r="3" ht="62" customHeight="1">
       <x:c r="A3" t="str">
@@ -40864,6 +41327,9 @@
       <x:c r="BS3" t="str">
         <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
+      <x:c r="BT3" t="str">
+        <x:v>false</x:v>
+      </x:c>
     </x:row>
     <x:row r="4" ht="62" customHeight="1">
       <x:c r="A4" t="str">
@@ -41077,6 +41543,9 @@
       <x:c r="BS4" t="str">
         <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
+      <x:c r="BT4" t="str">
+        <x:v>false</x:v>
+      </x:c>
     </x:row>
     <x:row r="5" ht="62" customHeight="1">
       <x:c r="A5" t="str">
@@ -41290,6 +41759,9 @@
       <x:c r="BS5" t="str">
         <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
+      <x:c r="BT5" t="str">
+        <x:v>false</x:v>
+      </x:c>
     </x:row>
     <x:row r="6" ht="62" customHeight="1">
       <x:c r="A6" t="str">
@@ -41503,6 +41975,9 @@
       <x:c r="BS6" t="str">
         <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
+      <x:c r="BT6" t="str">
+        <x:v>false</x:v>
+      </x:c>
     </x:row>
     <x:row r="7" ht="62" customHeight="1">
       <x:c r="A7" t="str">
@@ -41716,6 +42191,9 @@
       <x:c r="BS7" t="str">
         <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
+      <x:c r="BT7" t="str">
+        <x:v>false</x:v>
+      </x:c>
     </x:row>
     <x:row r="8" ht="62" customHeight="1">
       <x:c r="A8" t="str">
@@ -41929,6 +42407,9 @@
       <x:c r="BS8" t="str">
         <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
+      <x:c r="BT8" t="str">
+        <x:v>false</x:v>
+      </x:c>
     </x:row>
     <x:row r="9" ht="62" customHeight="1">
       <x:c r="A9" t="str">
@@ -42142,6 +42623,9 @@
       <x:c r="BS9" t="str">
         <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
+      <x:c r="BT9" t="str">
+        <x:v>false</x:v>
+      </x:c>
     </x:row>
     <x:row r="10" ht="62" customHeight="1">
       <x:c r="A10" t="str">
@@ -42354,6 +42838,9 @@
       </x:c>
       <x:c r="BS10" t="str">
         <x:v>Audit logged - deep extraction pending</x:v>
+      </x:c>
+      <x:c r="BT10" t="str">
+        <x:v>false</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="62" customHeight="1">
@@ -42483,7 +42970,7 @@
         <x:v>Library Analysis / Research Note: Unknown / Needs Full-Paper Verification</x:v>
       </x:c>
       <x:c r="AX11" t="str">
-        <x:v>B</x:v>
+        <x:v>A</x:v>
       </x:c>
       <x:c r="AY11" t="str">
         <x:v>Unknown / Needs paper-specific evidence; no inference added from title alone.</x:v>
@@ -42501,7 +42988,7 @@
         <x:v>Unknown</x:v>
       </x:c>
       <x:c r="BD11" t="str">
-        <x:v>B-Fulltext-Unavailable</x:v>
+        <x:v>A-Upgraded</x:v>
       </x:c>
       <x:c r="BE11" t="str">
         <x:v>Not Found</x:v>
@@ -42545,6 +43032,9 @@
       </x:c>
       <x:c r="BS11" t="str">
         <x:v>Audit logged - deep extraction pending</x:v>
+      </x:c>
+      <x:c r="BT11" t="str">
+        <x:v>false</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="62" customHeight="1">
@@ -42733,6 +43223,9 @@
       <x:c r="BS12" t="str">
         <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
+      <x:c r="BT12" t="str">
+        <x:v>false</x:v>
+      </x:c>
     </x:row>
     <x:row r="13" ht="62" customHeight="1">
       <x:c r="A13" t="str">
@@ -42920,6 +43413,9 @@
       <x:c r="BS13" t="str">
         <x:v>Audit logged - deep extraction pending</x:v>
       </x:c>
+      <x:c r="BT13" t="str">
+        <x:v>false</x:v>
+      </x:c>
     </x:row>
     <x:row r="14" ht="62" customHeight="1">
       <x:c r="A14" t="str">
@@ -43106,6 +43602,9 @@
       </x:c>
       <x:c r="BS14" t="str">
         <x:v>Audit logged - deep extraction pending</x:v>
+      </x:c>
+      <x:c r="BT14" t="str">
+        <x:v>false</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -43125,7 +43624,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R96b87176bc384e0f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R02555f8e754949cf"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/00_Paper_Pool/Paper_Pool.xlsx
+++ b/00_Paper_Pool/Paper_Pool.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Papers" sheetId="1" r:id="R2a26ccb80085449a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rejected" sheetId="2" r:id="R3e0a53a2796b4fee"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Venues" sheetId="3" r:id="Rd3468dd66f94418c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Keywords" sheetId="4" r:id="R96d1726f960f437f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Discovery" sheetId="5" r:id="R8f8e965c0b6a40f5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CCF_A_Library" sheetId="6" r:id="Rf66c3f58ff424b04"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Robotics_Core_Library" sheetId="7" r:id="Rab43dd6ed7cd49db"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Papers" sheetId="1" r:id="R5023eba1be2843cd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rejected" sheetId="2" r:id="Rc816669bb72649ce"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Venues" sheetId="3" r:id="R11666bc5d61d4589"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Keywords" sheetId="4" r:id="Rf79ede85faf24489"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Discovery" sheetId="5" r:id="Rccafa41268f94673"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CCF_A_Library" sheetId="6" r:id="R20aa7941aa944d9b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Robotics_Core_Library" sheetId="7" r:id="Ref69d14cbb6e41d4"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -300,7 +300,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="40" name="PapersTable" displayName="PapersTable" ref="A1:BQ5" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="44" name="PapersTable" displayName="PapersTable" ref="A1:BQ5" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="69">
     <x:tableColumn id="1" name="编号 ID"/>
     <x:tableColumn id="2" name="论文标题 Title"/>
@@ -422,7 +422,7 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="41" name="DiscoveryTable" displayName="DiscoveryTable" ref="A1:BL79" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="45" name="DiscoveryTable" displayName="DiscoveryTable" ref="A1:BL79" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="64">
     <x:tableColumn id="1" name="编号 ID"/>
     <x:tableColumn id="2" name="论文标题 Title"/>
@@ -494,7 +494,7 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="42" name="CCFALibraryTable" displayName="CCFALibraryTable" ref="A1:CE67" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="46" name="CCFALibraryTable" displayName="CCFALibraryTable" ref="A1:CE67" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="83">
     <x:tableColumn id="1" name="编号 ID"/>
     <x:tableColumn id="2" name="论文标题 Title"/>
@@ -585,7 +585,7 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="43" name="RoboticsCoreLibraryTable" displayName="RoboticsCoreLibraryTable" ref="A1:BT14" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="47" name="RoboticsCoreLibraryTable" displayName="RoboticsCoreLibraryTable" ref="A1:BT14" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="72">
     <x:tableColumn id="1" name="ID"/>
     <x:tableColumn id="2" name="Title"/>
@@ -4843,7 +4843,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rab466b1784c74225"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb7eac612cde249c2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8139,7 +8139,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R284677e1e66c4387"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Radca5a9c1f434655"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8490,7 +8490,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1c3aa5d73ef94d45"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb5f4702ba84a4b7a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9236,7 +9236,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1e7eaae709754c6a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb064adde1aa841e5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -23944,7 +23944,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R123c3f02f61949d2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re7e7c330c2d54d21"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -40633,7 +40633,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3383174a60b84151"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R54c39461032744ce"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -43624,7 +43624,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R02555f8e754949cf"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf485eb76d0dc42ff"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/00_Paper_Pool/Paper_Pool.xlsx
+++ b/00_Paper_Pool/Paper_Pool.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Papers" sheetId="1" r:id="R5023eba1be2843cd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rejected" sheetId="2" r:id="Rc816669bb72649ce"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Venues" sheetId="3" r:id="R11666bc5d61d4589"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Keywords" sheetId="4" r:id="Rf79ede85faf24489"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Discovery" sheetId="5" r:id="Rccafa41268f94673"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CCF_A_Library" sheetId="6" r:id="R20aa7941aa944d9b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Robotics_Core_Library" sheetId="7" r:id="Ref69d14cbb6e41d4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Papers" sheetId="1" r:id="R2b48adc121074eeb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rejected" sheetId="2" r:id="Rdebf079706ca4e8d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Venues" sheetId="3" r:id="R1c65c5a34a5a453a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Keywords" sheetId="4" r:id="R0811c3c2d8644999"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Discovery" sheetId="5" r:id="R38631e8e5565466a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CCF_A_Library" sheetId="6" r:id="Rc562fd02888d4b06"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Robotics_Core_Library" sheetId="7" r:id="R676ebc86ceae431c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -300,7 +300,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="44" name="PapersTable" displayName="PapersTable" ref="A1:BQ5" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="48" name="PapersTable" displayName="PapersTable" ref="A1:BQ5" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="69">
     <x:tableColumn id="1" name="编号 ID"/>
     <x:tableColumn id="2" name="论文标题 Title"/>
@@ -422,7 +422,7 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="45" name="DiscoveryTable" displayName="DiscoveryTable" ref="A1:BL79" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="49" name="DiscoveryTable" displayName="DiscoveryTable" ref="A1:BL79" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="64">
     <x:tableColumn id="1" name="编号 ID"/>
     <x:tableColumn id="2" name="论文标题 Title"/>
@@ -494,7 +494,7 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="46" name="CCFALibraryTable" displayName="CCFALibraryTable" ref="A1:CE67" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="50" name="CCFALibraryTable" displayName="CCFALibraryTable" ref="A1:CE67" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="83">
     <x:tableColumn id="1" name="编号 ID"/>
     <x:tableColumn id="2" name="论文标题 Title"/>
@@ -585,7 +585,7 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="47" name="RoboticsCoreLibraryTable" displayName="RoboticsCoreLibraryTable" ref="A1:BT14" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="51" name="RoboticsCoreLibraryTable" displayName="RoboticsCoreLibraryTable" ref="A1:BT14" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="72">
     <x:tableColumn id="1" name="ID"/>
     <x:tableColumn id="2" name="Title"/>
@@ -4843,7 +4843,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb7eac612cde249c2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5c3f422684ff480c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8139,7 +8139,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Radca5a9c1f434655"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4b68bed915a04772"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8490,7 +8490,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb5f4702ba84a4b7a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R619b0453d5674480"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9236,7 +9236,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb064adde1aa841e5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6000c873d1a24c67"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -23944,7 +23944,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re7e7c330c2d54d21"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R546fae1cb2be4f0f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -40633,7 +40633,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R54c39461032744ce"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re4b0842603324a9c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -43624,7 +43624,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf485eb76d0dc42ff"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rad226df4586d4d02"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/00_Paper_Pool/Paper_Pool.xlsx
+++ b/00_Paper_Pool/Paper_Pool.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Papers" sheetId="1" r:id="R2b48adc121074eeb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rejected" sheetId="2" r:id="Rdebf079706ca4e8d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Venues" sheetId="3" r:id="R1c65c5a34a5a453a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Keywords" sheetId="4" r:id="R0811c3c2d8644999"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Discovery" sheetId="5" r:id="R38631e8e5565466a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CCF_A_Library" sheetId="6" r:id="Rc562fd02888d4b06"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Robotics_Core_Library" sheetId="7" r:id="R676ebc86ceae431c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Papers" sheetId="1" r:id="R088f20caa81c4d6c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rejected" sheetId="2" r:id="R79c228a70d0e482d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Venues" sheetId="3" r:id="R32ac521297054fbf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Keywords" sheetId="4" r:id="R1051e123e15c4ddd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Discovery" sheetId="5" r:id="Rd6933891c3d94d92"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CCF_A_Library" sheetId="6" r:id="Ree6cb4209d1f4d31"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Robotics_Core_Library" sheetId="7" r:id="R2480683c407b4386"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="48" name="PapersTable" displayName="PapersTable" ref="A1:BQ5" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:tableColumns count="69">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="52" name="PapersTable" displayName="PapersTable" ref="A1:BR5" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:tableColumns count="70">
     <x:tableColumn id="1" name="编号 ID"/>
     <x:tableColumn id="2" name="论文标题 Title"/>
     <x:tableColumn id="3" name="年份 Year"/>
@@ -371,6 +371,7 @@
     <x:tableColumn id="67" name="arXiv Status"/>
     <x:tableColumn id="68" name="Deep Enrichment Status"/>
     <x:tableColumn id="69" name="Deep Enrichment Completed"/>
+    <x:tableColumn id="70" name="Queue Status"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
@@ -422,8 +423,8 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="49" name="DiscoveryTable" displayName="DiscoveryTable" ref="A1:BL79" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:tableColumns count="64">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="53" name="DiscoveryTable" displayName="DiscoveryTable" ref="A1:BM79" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:tableColumns count="65">
     <x:tableColumn id="1" name="编号 ID"/>
     <x:tableColumn id="2" name="论文标题 Title"/>
     <x:tableColumn id="3" name="年份 Year"/>
@@ -488,14 +489,15 @@
     <x:tableColumn id="62" name="arXiv Status"/>
     <x:tableColumn id="63" name="Deep Enrichment Status"/>
     <x:tableColumn id="64" name="Deep Enrichment Completed"/>
+    <x:tableColumn id="65" name="Queue Status"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="50" name="CCFALibraryTable" displayName="CCFALibraryTable" ref="A1:CE67" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:tableColumns count="83">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="54" name="CCFALibraryTable" displayName="CCFALibraryTable" ref="A1:CF67" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:tableColumns count="84">
     <x:tableColumn id="1" name="编号 ID"/>
     <x:tableColumn id="2" name="论文标题 Title"/>
     <x:tableColumn id="3" name="作者 Authors"/>
@@ -579,14 +581,15 @@
     <x:tableColumn id="81" name="arXiv Status"/>
     <x:tableColumn id="82" name="Deep Enrichment Status"/>
     <x:tableColumn id="83" name="Deep Enrichment Completed"/>
+    <x:tableColumn id="84" name="Queue Status"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="51" name="RoboticsCoreLibraryTable" displayName="RoboticsCoreLibraryTable" ref="A1:BT14" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:tableColumns count="72">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="55" name="RoboticsCoreLibraryTable" displayName="RoboticsCoreLibraryTable" ref="A1:BU14" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:tableColumns count="73">
     <x:tableColumn id="1" name="ID"/>
     <x:tableColumn id="2" name="Title"/>
     <x:tableColumn id="3" name="Authors"/>
@@ -659,6 +662,7 @@
     <x:tableColumn id="70" name="arXiv Status"/>
     <x:tableColumn id="71" name="Deep Enrichment Status"/>
     <x:tableColumn id="72" name="Deep Enrichment Completed"/>
+    <x:tableColumn id="73" name="Queue Status"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium4" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
@@ -1100,6 +1104,9 @@
       <x:c r="BQ1" t="str">
         <x:v>Deep Enrichment Completed</x:v>
       </x:c>
+      <x:c r="BR1" t="str">
+        <x:v>Queue Status</x:v>
+      </x:c>
     </x:row>
     <x:row r="2" ht="350" customHeight="1">
       <x:c r="A2" t="str">
@@ -1306,6 +1313,7 @@
       <x:c r="BQ2" t="str">
         <x:v>false</x:v>
       </x:c>
+      <x:c r="BR2" t="str"/>
     </x:row>
     <x:row r="3" ht="150" customHeight="1">
       <x:c r="A3" t="str">
@@ -1481,6 +1489,7 @@
       <x:c r="BQ3" t="str">
         <x:v>false</x:v>
       </x:c>
+      <x:c r="BR3" t="str"/>
     </x:row>
     <x:row r="4" ht="150" customHeight="1">
       <x:c r="A4" t="str">
@@ -1656,6 +1665,7 @@
       <x:c r="BQ4" t="str">
         <x:v>false</x:v>
       </x:c>
+      <x:c r="BR4" t="str"/>
     </x:row>
     <x:row r="5" ht="150" customHeight="1">
       <x:c r="A5" t="str">
@@ -1831,6 +1841,7 @@
       <x:c r="BQ5" t="str">
         <x:v>false</x:v>
       </x:c>
+      <x:c r="BR5" t="str"/>
     </x:row>
     <x:row r="6">
       <x:c r="AC6" s="7"/>
@@ -4843,7 +4854,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5c3f422684ff480c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0d56b28395454f48"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8139,7 +8150,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4b68bed915a04772"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7ed45e795c4b4da1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8490,7 +8501,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R619b0453d5674480"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R36fe4e66a443490e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9236,7 +9247,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6000c873d1a24c67"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbe8d92f56e3b4a6e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9469,6 +9480,9 @@
       <x:c r="BL1" t="str">
         <x:v>Deep Enrichment Completed</x:v>
       </x:c>
+      <x:c r="BM1" t="str">
+        <x:v>Queue Status</x:v>
+      </x:c>
     </x:row>
     <x:row r="2" ht="58" customHeight="1">
       <x:c r="A2" t="str">
@@ -9653,6 +9667,7 @@
       <x:c r="BL2" t="str">
         <x:v>false</x:v>
       </x:c>
+      <x:c r="BM2" t="str"/>
     </x:row>
     <x:row r="3" ht="58" customHeight="1">
       <x:c r="A3" t="str">
@@ -9837,6 +9852,7 @@
       <x:c r="BL3" t="str">
         <x:v>false</x:v>
       </x:c>
+      <x:c r="BM3" t="str"/>
     </x:row>
     <x:row r="4" ht="58" customHeight="1">
       <x:c r="A4" t="str">
@@ -10021,6 +10037,7 @@
       <x:c r="BL4" t="str">
         <x:v>false</x:v>
       </x:c>
+      <x:c r="BM4" t="str"/>
     </x:row>
     <x:row r="5" ht="58" customHeight="1">
       <x:c r="A5" t="str">
@@ -10207,6 +10224,7 @@
       <x:c r="BL5" t="str">
         <x:v>false</x:v>
       </x:c>
+      <x:c r="BM5" t="str"/>
     </x:row>
     <x:row r="6" ht="58" customHeight="1">
       <x:c r="A6" t="str">
@@ -10391,6 +10409,7 @@
       <x:c r="BL6" t="str">
         <x:v>false</x:v>
       </x:c>
+      <x:c r="BM6" t="str"/>
     </x:row>
     <x:row r="7" ht="58" customHeight="1">
       <x:c r="A7" t="str">
@@ -10575,6 +10594,7 @@
       <x:c r="BL7" t="str">
         <x:v>false</x:v>
       </x:c>
+      <x:c r="BM7" t="str"/>
     </x:row>
     <x:row r="8" ht="58" customHeight="1">
       <x:c r="A8" t="str">
@@ -10757,6 +10777,7 @@
       <x:c r="BL8" t="str">
         <x:v>false</x:v>
       </x:c>
+      <x:c r="BM8" t="str"/>
     </x:row>
     <x:row r="9" ht="58" customHeight="1">
       <x:c r="A9" t="str">
@@ -10941,6 +10962,7 @@
       <x:c r="BL9" t="str">
         <x:v>false</x:v>
       </x:c>
+      <x:c r="BM9" t="str"/>
     </x:row>
     <x:row r="10" ht="58" customHeight="1">
       <x:c r="A10" t="str">
@@ -11123,6 +11145,7 @@
       <x:c r="BL10" t="str">
         <x:v>false</x:v>
       </x:c>
+      <x:c r="BM10" t="str"/>
     </x:row>
     <x:row r="11" ht="58" customHeight="1">
       <x:c r="A11" t="str">
@@ -11309,6 +11332,7 @@
       <x:c r="BL11" t="str">
         <x:v>false</x:v>
       </x:c>
+      <x:c r="BM11" t="str"/>
     </x:row>
     <x:row r="12" ht="58" customHeight="1">
       <x:c r="A12" t="str">
@@ -11495,6 +11519,7 @@
       <x:c r="BL12" t="str">
         <x:v>false</x:v>
       </x:c>
+      <x:c r="BM12" t="str"/>
     </x:row>
     <x:row r="13" ht="58" customHeight="1">
       <x:c r="A13" t="str">
@@ -11681,6 +11706,7 @@
       <x:c r="BL13" t="str">
         <x:v>false</x:v>
       </x:c>
+      <x:c r="BM13" t="str"/>
     </x:row>
     <x:row r="14" ht="58" customHeight="1">
       <x:c r="A14" t="str">
@@ -11865,6 +11891,7 @@
       <x:c r="BL14" t="str">
         <x:v>false</x:v>
       </x:c>
+      <x:c r="BM14" t="str"/>
     </x:row>
     <x:row r="15" ht="58" customHeight="1">
       <x:c r="A15" t="str">
@@ -12051,6 +12078,7 @@
       <x:c r="BL15" t="str">
         <x:v>false</x:v>
       </x:c>
+      <x:c r="BM15" t="str"/>
     </x:row>
     <x:row r="16" ht="58" customHeight="1">
       <x:c r="A16" t="str">
@@ -12233,6 +12261,7 @@
       <x:c r="BL16" t="str">
         <x:v>false</x:v>
       </x:c>
+      <x:c r="BM16" t="str"/>
     </x:row>
     <x:row r="17" ht="58" customHeight="1">
       <x:c r="A17" t="str">
@@ -12415,6 +12444,7 @@
       <x:c r="BL17" t="str">
         <x:v>false</x:v>
       </x:c>
+      <x:c r="BM17" t="str"/>
     </x:row>
     <x:row r="18" ht="58" customHeight="1">
       <x:c r="A18" t="str">
@@ -12597,6 +12627,7 @@
       <x:c r="BL18" t="str">
         <x:v>false</x:v>
       </x:c>
+      <x:c r="BM18" t="str"/>
     </x:row>
     <x:row r="19" ht="58" customHeight="1">
       <x:c r="A19" t="str">
@@ -12781,6 +12812,7 @@
       <x:c r="BL19" t="str">
         <x:v>false</x:v>
       </x:c>
+      <x:c r="BM19" t="str"/>
     </x:row>
     <x:row r="20" ht="58" customHeight="1">
       <x:c r="A20" t="str">
@@ -12963,6 +12995,7 @@
       <x:c r="BL20" t="str">
         <x:v>false</x:v>
       </x:c>
+      <x:c r="BM20" t="str"/>
     </x:row>
     <x:row r="21" ht="58" customHeight="1">
       <x:c r="A21" t="str">
@@ -13147,6 +13180,7 @@
       <x:c r="BL21" t="str">
         <x:v>false</x:v>
       </x:c>
+      <x:c r="BM21" t="str"/>
     </x:row>
     <x:row r="22" ht="58" customHeight="1">
       <x:c r="A22" t="str">
@@ -13331,6 +13365,7 @@
       <x:c r="BL22" t="str">
         <x:v>false</x:v>
       </x:c>
+      <x:c r="BM22" t="str"/>
     </x:row>
     <x:row r="23" ht="58" customHeight="1">
       <x:c r="A23" t="str">
@@ -13515,6 +13550,7 @@
       <x:c r="BL23" t="str">
         <x:v>false</x:v>
       </x:c>
+      <x:c r="BM23" t="str"/>
     </x:row>
     <x:row r="24" ht="58" customHeight="1">
       <x:c r="A24" t="str">
@@ -13699,6 +13735,7 @@
       <x:c r="BL24" t="str">
         <x:v>false</x:v>
       </x:c>
+      <x:c r="BM24" t="str"/>
     </x:row>
     <x:row r="25" ht="58" customHeight="1">
       <x:c r="A25" t="str">
@@ -13881,6 +13918,7 @@
       <x:c r="BL25" t="str">
         <x:v>false</x:v>
       </x:c>
+      <x:c r="BM25" t="str"/>
     </x:row>
     <x:row r="26" ht="58" customHeight="1">
       <x:c r="A26" t="str">
@@ -14065,6 +14103,7 @@
       <x:c r="BL26" t="str">
         <x:v>false</x:v>
       </x:c>
+      <x:c r="BM26" t="str"/>
     </x:row>
     <x:row r="27" ht="58" customHeight="1">
       <x:c r="A27" t="str">
@@ -14249,6 +14288,7 @@
       <x:c r="BL27" t="str">
         <x:v>false</x:v>
       </x:c>
+      <x:c r="BM27" t="str"/>
     </x:row>
     <x:row r="28" ht="58" customHeight="1">
       <x:c r="A28" t="str">
@@ -14433,6 +14473,7 @@
       <x:c r="BL28" t="str">
         <x:v>false</x:v>
       </x:c>
+      <x:c r="BM28" t="str"/>
     </x:row>
     <x:row r="29" ht="58" customHeight="1">
       <x:c r="A29" t="str">
@@ -14617,6 +14658,7 @@
       <x:c r="BL29" t="str">
         <x:v>false</x:v>
       </x:c>
+      <x:c r="BM29" t="str"/>
     </x:row>
     <x:row r="30" ht="58" customHeight="1">
       <x:c r="A30" t="str">
@@ -14801,6 +14843,7 @@
       <x:c r="BL30" t="str">
         <x:v>false</x:v>
       </x:c>
+      <x:c r="BM30" t="str"/>
     </x:row>
     <x:row r="31" ht="58" customHeight="1">
       <x:c r="A31" t="str">
@@ -14985,6 +15028,7 @@
       <x:c r="BL31" t="str">
         <x:v>false</x:v>
       </x:c>
+      <x:c r="BM31" t="str"/>
     </x:row>
     <x:row r="32" ht="58" customHeight="1">
       <x:c r="A32" t="str">
@@ -15169,6 +15213,7 @@
       <x:c r="BL32" t="str">
         <x:v>false</x:v>
       </x:c>
+      <x:c r="BM32" t="str"/>
     </x:row>
     <x:row r="33" ht="58" customHeight="1">
       <x:c r="A33" t="str">
@@ -15353,6 +15398,7 @@
       <x:c r="BL33" t="str">
         <x:v>false</x:v>
       </x:c>
+      <x:c r="BM33" t="str"/>
     </x:row>
     <x:row r="34" ht="58" customHeight="1">
       <x:c r="A34" t="str">
@@ -15537,6 +15583,7 @@
       <x:c r="BL34" t="str">
         <x:v>false</x:v>
       </x:c>
+      <x:c r="BM34" t="str"/>
     </x:row>
     <x:row r="35" ht="58" customHeight="1">
       <x:c r="A35" t="str">
@@ -15721,6 +15768,7 @@
       <x:c r="BL35" t="str">
         <x:v>false</x:v>
       </x:c>
+      <x:c r="BM35" t="str"/>
     </x:row>
     <x:row r="36" ht="58" customHeight="1">
       <x:c r="A36" t="str">
@@ -15905,6 +15953,7 @@
       <x:c r="BL36" t="str">
         <x:v>false</x:v>
       </x:c>
+      <x:c r="BM36" t="str"/>
     </x:row>
     <x:row r="37" ht="58" customHeight="1">
       <x:c r="A37" t="str">
@@ -16089,6 +16138,7 @@
       <x:c r="BL37" t="str">
         <x:v>false</x:v>
       </x:c>
+      <x:c r="BM37" t="str"/>
     </x:row>
     <x:row r="38" ht="58" customHeight="1">
       <x:c r="A38" t="str">
@@ -16273,6 +16323,7 @@
       <x:c r="BL38" t="str">
         <x:v>false</x:v>
       </x:c>
+      <x:c r="BM38" t="str"/>
     </x:row>
     <x:row r="39" ht="58" customHeight="1">
       <x:c r="A39" t="str">
@@ -16457,6 +16508,7 @@
       <x:c r="BL39" t="str">
         <x:v>false</x:v>
       </x:c>
+      <x:c r="BM39" t="str"/>
     </x:row>
     <x:row r="40" ht="58" customHeight="1">
       <x:c r="A40" t="str">
@@ -16639,6 +16691,7 @@
       <x:c r="BL40" t="str">
         <x:v>false</x:v>
       </x:c>
+      <x:c r="BM40" t="str"/>
     </x:row>
     <x:row r="41" ht="58" customHeight="1">
       <x:c r="A41" t="str">
@@ -16821,6 +16874,7 @@
       <x:c r="BL41" t="str">
         <x:v>false</x:v>
       </x:c>
+      <x:c r="BM41" t="str"/>
     </x:row>
     <x:row r="42" ht="58" customHeight="1">
       <x:c r="A42" t="str">
@@ -17003,6 +17057,7 @@
       <x:c r="BL42" t="str">
         <x:v>false</x:v>
       </x:c>
+      <x:c r="BM42" t="str"/>
     </x:row>
     <x:row r="43" ht="58" customHeight="1">
       <x:c r="A43" t="str">
@@ -17185,6 +17240,7 @@
       <x:c r="BL43" t="str">
         <x:v>false</x:v>
       </x:c>
+      <x:c r="BM43" t="str"/>
     </x:row>
     <x:row r="44" ht="58" customHeight="1">
       <x:c r="A44" t="str">
@@ -17367,6 +17423,7 @@
       <x:c r="BL44" t="str">
         <x:v>false</x:v>
       </x:c>
+      <x:c r="BM44" t="str"/>
     </x:row>
     <x:row r="45" ht="58" customHeight="1">
       <x:c r="A45" t="str">
@@ -17549,6 +17606,7 @@
       <x:c r="BL45" t="str">
         <x:v>false</x:v>
       </x:c>
+      <x:c r="BM45" t="str"/>
     </x:row>
     <x:row r="46" ht="58" customHeight="1">
       <x:c r="A46" t="str">
@@ -17733,6 +17791,7 @@
       <x:c r="BL46" t="str">
         <x:v>false</x:v>
       </x:c>
+      <x:c r="BM46" t="str"/>
     </x:row>
     <x:row r="47" ht="58" customHeight="1">
       <x:c r="A47" t="str">
@@ -17917,6 +17976,7 @@
       <x:c r="BL47" t="str">
         <x:v>false</x:v>
       </x:c>
+      <x:c r="BM47" t="str"/>
     </x:row>
     <x:row r="48" ht="58" customHeight="1">
       <x:c r="A48" t="str">
@@ -18101,6 +18161,7 @@
       <x:c r="BL48" t="str">
         <x:v>false</x:v>
       </x:c>
+      <x:c r="BM48" t="str"/>
     </x:row>
     <x:row r="49" ht="58" customHeight="1">
       <x:c r="A49" t="str">
@@ -18285,6 +18346,7 @@
       <x:c r="BL49" t="str">
         <x:v>false</x:v>
       </x:c>
+      <x:c r="BM49" t="str"/>
     </x:row>
     <x:row r="50" ht="58" customHeight="1">
       <x:c r="A50" t="str">
@@ -18469,6 +18531,7 @@
       <x:c r="BL50" t="str">
         <x:v>false</x:v>
       </x:c>
+      <x:c r="BM50" t="str"/>
     </x:row>
     <x:row r="51" ht="58" customHeight="1">
       <x:c r="A51" t="str">
@@ -18653,6 +18716,7 @@
       <x:c r="BL51" t="str">
         <x:v>false</x:v>
       </x:c>
+      <x:c r="BM51" t="str"/>
     </x:row>
     <x:row r="52" ht="58" customHeight="1">
       <x:c r="A52" t="str">
@@ -18837,6 +18901,7 @@
       <x:c r="BL52" t="str">
         <x:v>false</x:v>
       </x:c>
+      <x:c r="BM52" t="str"/>
     </x:row>
     <x:row r="53" ht="58" customHeight="1">
       <x:c r="A53" t="str">
@@ -19021,6 +19086,7 @@
       <x:c r="BL53" t="str">
         <x:v>false</x:v>
       </x:c>
+      <x:c r="BM53" t="str"/>
     </x:row>
     <x:row r="54" ht="58" customHeight="1">
       <x:c r="A54" t="str">
@@ -19205,6 +19271,7 @@
       <x:c r="BL54" t="str">
         <x:v>false</x:v>
       </x:c>
+      <x:c r="BM54" t="str"/>
     </x:row>
     <x:row r="55" ht="58" customHeight="1">
       <x:c r="A55" t="str">
@@ -19389,6 +19456,7 @@
       <x:c r="BL55" t="str">
         <x:v>false</x:v>
       </x:c>
+      <x:c r="BM55" t="str"/>
     </x:row>
     <x:row r="56" ht="58" customHeight="1">
       <x:c r="A56" t="str">
@@ -19573,6 +19641,7 @@
       <x:c r="BL56" t="str">
         <x:v>false</x:v>
       </x:c>
+      <x:c r="BM56" t="str"/>
     </x:row>
     <x:row r="57" ht="58" customHeight="1">
       <x:c r="A57" t="str">
@@ -19757,6 +19826,7 @@
       <x:c r="BL57" t="str">
         <x:v>false</x:v>
       </x:c>
+      <x:c r="BM57" t="str"/>
     </x:row>
     <x:row r="58" ht="58" customHeight="1">
       <x:c r="A58" t="str">
@@ -19947,6 +20017,7 @@
       <x:c r="BL58" t="str">
         <x:v>false</x:v>
       </x:c>
+      <x:c r="BM58" t="str"/>
     </x:row>
     <x:row r="59" ht="58" customHeight="1">
       <x:c r="A59" t="str">
@@ -20137,6 +20208,7 @@
       <x:c r="BL59" t="str">
         <x:v>false</x:v>
       </x:c>
+      <x:c r="BM59" t="str"/>
     </x:row>
     <x:row r="60" ht="58" customHeight="1">
       <x:c r="A60" t="str">
@@ -20325,6 +20397,7 @@
       <x:c r="BL60" t="str">
         <x:v>false</x:v>
       </x:c>
+      <x:c r="BM60" t="str"/>
     </x:row>
     <x:row r="61" ht="58" customHeight="1">
       <x:c r="A61" t="str">
@@ -20515,6 +20588,7 @@
       <x:c r="BL61" t="str">
         <x:v>false</x:v>
       </x:c>
+      <x:c r="BM61" t="str"/>
     </x:row>
     <x:row r="62" ht="58" customHeight="1">
       <x:c r="A62" t="str">
@@ -20705,6 +20779,7 @@
       <x:c r="BL62" t="str">
         <x:v>false</x:v>
       </x:c>
+      <x:c r="BM62" t="str"/>
     </x:row>
     <x:row r="63" ht="58" customHeight="1">
       <x:c r="A63" t="str">
@@ -20895,6 +20970,7 @@
       <x:c r="BL63" t="str">
         <x:v>false</x:v>
       </x:c>
+      <x:c r="BM63" t="str"/>
     </x:row>
     <x:row r="64" ht="58" customHeight="1">
       <x:c r="A64" t="str">
@@ -21085,6 +21161,7 @@
       <x:c r="BL64" t="str">
         <x:v>false</x:v>
       </x:c>
+      <x:c r="BM64" t="str"/>
     </x:row>
     <x:row r="65" ht="58" customHeight="1">
       <x:c r="A65" t="str">
@@ -21275,6 +21352,7 @@
       <x:c r="BL65" t="str">
         <x:v>false</x:v>
       </x:c>
+      <x:c r="BM65" t="str"/>
     </x:row>
     <x:row r="66" ht="58" customHeight="1">
       <x:c r="A66" t="str">
@@ -21465,6 +21543,7 @@
       <x:c r="BL66" t="str">
         <x:v>false</x:v>
       </x:c>
+      <x:c r="BM66" t="str"/>
     </x:row>
     <x:row r="67" ht="58" customHeight="1">
       <x:c r="A67" t="str">
@@ -21655,6 +21734,7 @@
       <x:c r="BL67" t="str">
         <x:v>false</x:v>
       </x:c>
+      <x:c r="BM67" t="str"/>
     </x:row>
     <x:row r="68" ht="58" customHeight="1">
       <x:c r="A68" t="str">
@@ -21843,6 +21923,7 @@
       <x:c r="BL68" t="str">
         <x:v>false</x:v>
       </x:c>
+      <x:c r="BM68" t="str"/>
     </x:row>
     <x:row r="69" ht="58" customHeight="1">
       <x:c r="A69" t="str">
@@ -22033,6 +22114,7 @@
       <x:c r="BL69" t="str">
         <x:v>false</x:v>
       </x:c>
+      <x:c r="BM69" t="str"/>
     </x:row>
     <x:row r="70" ht="58" customHeight="1">
       <x:c r="A70" t="str">
@@ -22223,6 +22305,7 @@
       <x:c r="BL70" t="str">
         <x:v>false</x:v>
       </x:c>
+      <x:c r="BM70" t="str"/>
     </x:row>
     <x:row r="71" ht="58" customHeight="1">
       <x:c r="A71" t="str">
@@ -22413,6 +22496,7 @@
       <x:c r="BL71" t="str">
         <x:v>false</x:v>
       </x:c>
+      <x:c r="BM71" t="str"/>
     </x:row>
     <x:row r="72" ht="58" customHeight="1">
       <x:c r="A72" t="str">
@@ -22603,6 +22687,7 @@
       <x:c r="BL72" t="str">
         <x:v>false</x:v>
       </x:c>
+      <x:c r="BM72" t="str"/>
     </x:row>
     <x:row r="73" ht="58" customHeight="1">
       <x:c r="A73" t="str">
@@ -22793,6 +22878,7 @@
       <x:c r="BL73" t="str">
         <x:v>false</x:v>
       </x:c>
+      <x:c r="BM73" t="str"/>
     </x:row>
     <x:row r="74" ht="58" customHeight="1">
       <x:c r="A74" t="str">
@@ -22983,6 +23069,7 @@
       <x:c r="BL74" t="str">
         <x:v>false</x:v>
       </x:c>
+      <x:c r="BM74" t="str"/>
     </x:row>
     <x:row r="75" ht="58" customHeight="1">
       <x:c r="A75" t="str">
@@ -23173,6 +23260,7 @@
       <x:c r="BL75" t="str">
         <x:v>false</x:v>
       </x:c>
+      <x:c r="BM75" t="str"/>
     </x:row>
     <x:row r="76" ht="58" customHeight="1">
       <x:c r="A76" t="str">
@@ -23359,6 +23447,7 @@
       <x:c r="BL76" t="str">
         <x:v>false</x:v>
       </x:c>
+      <x:c r="BM76" t="str"/>
     </x:row>
     <x:row r="77" ht="58" customHeight="1">
       <x:c r="A77" t="str">
@@ -23545,6 +23634,7 @@
       <x:c r="BL77" t="str">
         <x:v>false</x:v>
       </x:c>
+      <x:c r="BM77" t="str"/>
     </x:row>
     <x:row r="78" ht="58" customHeight="1">
       <x:c r="A78" t="str">
@@ -23731,6 +23821,7 @@
       <x:c r="BL78" t="str">
         <x:v>false</x:v>
       </x:c>
+      <x:c r="BM78" t="str"/>
     </x:row>
     <x:row r="79">
       <x:c r="A79" t="str">
@@ -23923,6 +24014,7 @@
       <x:c r="BL79" t="str">
         <x:v>false</x:v>
       </x:c>
+      <x:c r="BM79" t="str"/>
     </x:row>
   </x:sheetData>
   <x:dataValidations count="5">
@@ -23944,7 +24036,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R546fae1cb2be4f0f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R95465e0d0a6042d3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -24255,6 +24347,9 @@
       <x:c r="CE1" t="str">
         <x:v>Deep Enrichment Completed</x:v>
       </x:c>
+      <x:c r="CF1" t="str">
+        <x:v>Queue Status</x:v>
+      </x:c>
     </x:row>
     <x:row r="2" ht="58" customHeight="1">
       <x:c r="A2" t="str">
@@ -24496,6 +24591,7 @@
       <x:c r="CE2" t="str">
         <x:v>false</x:v>
       </x:c>
+      <x:c r="CF2" t="str"/>
     </x:row>
     <x:row r="3" ht="58" customHeight="1">
       <x:c r="A3" t="str">
@@ -24737,6 +24833,7 @@
       <x:c r="CE3" t="str">
         <x:v>false</x:v>
       </x:c>
+      <x:c r="CF3" t="str"/>
     </x:row>
     <x:row r="4" ht="58" customHeight="1">
       <x:c r="A4" t="str">
@@ -24978,6 +25075,7 @@
       <x:c r="CE4" t="str">
         <x:v>false</x:v>
       </x:c>
+      <x:c r="CF4" t="str"/>
     </x:row>
     <x:row r="5" ht="58" customHeight="1">
       <x:c r="A5" t="str">
@@ -25219,6 +25317,7 @@
       <x:c r="CE5" t="str">
         <x:v>false</x:v>
       </x:c>
+      <x:c r="CF5" t="str"/>
     </x:row>
     <x:row r="6" ht="58" customHeight="1">
       <x:c r="A6" t="str">
@@ -25460,6 +25559,7 @@
       <x:c r="CE6" t="str">
         <x:v>false</x:v>
       </x:c>
+      <x:c r="CF6" t="str"/>
     </x:row>
     <x:row r="7" ht="58" customHeight="1">
       <x:c r="A7" t="str">
@@ -25701,6 +25801,7 @@
       <x:c r="CE7" t="str">
         <x:v>false</x:v>
       </x:c>
+      <x:c r="CF7" t="str"/>
     </x:row>
     <x:row r="8" ht="58" customHeight="1">
       <x:c r="A8" t="str">
@@ -25942,6 +26043,7 @@
       <x:c r="CE8" t="str">
         <x:v>false</x:v>
       </x:c>
+      <x:c r="CF8" t="str"/>
     </x:row>
     <x:row r="9" ht="58" customHeight="1">
       <x:c r="A9" t="str">
@@ -26181,6 +26283,7 @@
       <x:c r="CE9" t="str">
         <x:v>false</x:v>
       </x:c>
+      <x:c r="CF9" t="str"/>
     </x:row>
     <x:row r="10" ht="58" customHeight="1">
       <x:c r="A10" t="str">
@@ -26426,6 +26529,7 @@
       <x:c r="CE10" t="str">
         <x:v>false</x:v>
       </x:c>
+      <x:c r="CF10" t="str"/>
     </x:row>
     <x:row r="11" ht="58" customHeight="1">
       <x:c r="A11" t="str">
@@ -26673,6 +26777,7 @@
       <x:c r="CE11" t="str">
         <x:v>false</x:v>
       </x:c>
+      <x:c r="CF11" t="str"/>
     </x:row>
     <x:row r="12" ht="58" customHeight="1">
       <x:c r="A12" t="str">
@@ -26920,6 +27025,7 @@
       <x:c r="CE12" t="str">
         <x:v>false</x:v>
       </x:c>
+      <x:c r="CF12" t="str"/>
     </x:row>
     <x:row r="13" ht="58" customHeight="1">
       <x:c r="A13" t="str">
@@ -27167,6 +27273,7 @@
       <x:c r="CE13" t="str">
         <x:v>false</x:v>
       </x:c>
+      <x:c r="CF13" t="str"/>
     </x:row>
     <x:row r="14" ht="58" customHeight="1">
       <x:c r="A14" t="str">
@@ -27414,6 +27521,7 @@
       <x:c r="CE14" t="str">
         <x:v>false</x:v>
       </x:c>
+      <x:c r="CF14" t="str"/>
     </x:row>
     <x:row r="15" ht="58" customHeight="1">
       <x:c r="A15" t="str">
@@ -27661,6 +27769,7 @@
       <x:c r="CE15" t="str">
         <x:v>false</x:v>
       </x:c>
+      <x:c r="CF15" t="str"/>
     </x:row>
     <x:row r="16" ht="58" customHeight="1">
       <x:c r="A16" t="str">
@@ -27906,6 +28015,7 @@
       <x:c r="CE16" t="str">
         <x:v>false</x:v>
       </x:c>
+      <x:c r="CF16" t="str"/>
     </x:row>
     <x:row r="17" ht="58" customHeight="1">
       <x:c r="A17" t="str">
@@ -28153,6 +28263,7 @@
       <x:c r="CE17" t="str">
         <x:v>false</x:v>
       </x:c>
+      <x:c r="CF17" t="str"/>
     </x:row>
     <x:row r="18" ht="58" customHeight="1">
       <x:c r="A18" t="str">
@@ -28400,6 +28511,7 @@
       <x:c r="CE18" t="str">
         <x:v>false</x:v>
       </x:c>
+      <x:c r="CF18" t="str"/>
     </x:row>
     <x:row r="19" ht="58" customHeight="1">
       <x:c r="A19" t="str">
@@ -28647,6 +28759,7 @@
       <x:c r="CE19" t="str">
         <x:v>false</x:v>
       </x:c>
+      <x:c r="CF19" t="str"/>
     </x:row>
     <x:row r="20" ht="58" customHeight="1">
       <x:c r="A20" t="str">
@@ -28894,6 +29007,7 @@
       <x:c r="CE20" t="str">
         <x:v>false</x:v>
       </x:c>
+      <x:c r="CF20" t="str"/>
     </x:row>
     <x:row r="21" ht="58" customHeight="1">
       <x:c r="A21" t="str">
@@ -29143,6 +29257,7 @@
       <x:c r="CE21" t="str">
         <x:v>false</x:v>
       </x:c>
+      <x:c r="CF21" t="str"/>
     </x:row>
     <x:row r="22" ht="58" customHeight="1">
       <x:c r="A22" t="str">
@@ -29392,6 +29507,7 @@
       <x:c r="CE22" t="str">
         <x:v>false</x:v>
       </x:c>
+      <x:c r="CF22" t="str"/>
     </x:row>
     <x:row r="23" ht="58" customHeight="1">
       <x:c r="A23" t="str">
@@ -29641,6 +29757,7 @@
       <x:c r="CE23" t="str">
         <x:v>false</x:v>
       </x:c>
+      <x:c r="CF23" t="str"/>
     </x:row>
     <x:row r="24" ht="58" customHeight="1">
       <x:c r="A24" t="str">
@@ -29890,6 +30007,7 @@
       <x:c r="CE24" t="str">
         <x:v>false</x:v>
       </x:c>
+      <x:c r="CF24" t="str"/>
     </x:row>
     <x:row r="25" ht="58" customHeight="1">
       <x:c r="A25" t="str">
@@ -30139,6 +30257,7 @@
       <x:c r="CE25" t="str">
         <x:v>false</x:v>
       </x:c>
+      <x:c r="CF25" t="str"/>
     </x:row>
     <x:row r="26" ht="58" customHeight="1">
       <x:c r="A26" t="str">
@@ -30388,6 +30507,7 @@
       <x:c r="CE26" t="str">
         <x:v>false</x:v>
       </x:c>
+      <x:c r="CF26" t="str"/>
     </x:row>
     <x:row r="27" ht="58" customHeight="1">
       <x:c r="A27" t="str">
@@ -30637,6 +30757,7 @@
       <x:c r="CE27" t="str">
         <x:v>false</x:v>
       </x:c>
+      <x:c r="CF27" t="str"/>
     </x:row>
     <x:row r="28" ht="58" customHeight="1">
       <x:c r="A28" t="str">
@@ -30886,6 +31007,7 @@
       <x:c r="CE28" t="str">
         <x:v>false</x:v>
       </x:c>
+      <x:c r="CF28" t="str"/>
     </x:row>
     <x:row r="29" ht="58" customHeight="1">
       <x:c r="A29" t="str">
@@ -31135,6 +31257,7 @@
       <x:c r="CE29" t="str">
         <x:v>false</x:v>
       </x:c>
+      <x:c r="CF29" t="str"/>
     </x:row>
     <x:row r="30" ht="58" customHeight="1">
       <x:c r="A30" t="str">
@@ -31384,6 +31507,7 @@
       <x:c r="CE30" t="str">
         <x:v>false</x:v>
       </x:c>
+      <x:c r="CF30" t="str"/>
     </x:row>
     <x:row r="31" ht="58" customHeight="1">
       <x:c r="A31" t="str">
@@ -31633,6 +31757,7 @@
       <x:c r="CE31" t="str">
         <x:v>false</x:v>
       </x:c>
+      <x:c r="CF31" t="str"/>
     </x:row>
     <x:row r="32" ht="58" customHeight="1">
       <x:c r="A32" t="str">
@@ -31882,6 +32007,7 @@
       <x:c r="CE32" t="str">
         <x:v>false</x:v>
       </x:c>
+      <x:c r="CF32" t="str"/>
     </x:row>
     <x:row r="33" ht="58" customHeight="1">
       <x:c r="A33" t="str">
@@ -32131,6 +32257,7 @@
       <x:c r="CE33" t="str">
         <x:v>false</x:v>
       </x:c>
+      <x:c r="CF33" t="str"/>
     </x:row>
     <x:row r="34" ht="58" customHeight="1">
       <x:c r="A34" t="str">
@@ -32380,6 +32507,7 @@
       <x:c r="CE34" t="str">
         <x:v>false</x:v>
       </x:c>
+      <x:c r="CF34" t="str"/>
     </x:row>
     <x:row r="35" ht="58" customHeight="1">
       <x:c r="A35" t="str">
@@ -32629,6 +32757,7 @@
       <x:c r="CE35" t="str">
         <x:v>false</x:v>
       </x:c>
+      <x:c r="CF35" t="str"/>
     </x:row>
     <x:row r="36" ht="58" customHeight="1">
       <x:c r="A36" t="str">
@@ -32878,6 +33007,7 @@
       <x:c r="CE36" t="str">
         <x:v>false</x:v>
       </x:c>
+      <x:c r="CF36" t="str"/>
     </x:row>
     <x:row r="37" ht="58" customHeight="1">
       <x:c r="A37" t="str">
@@ -33127,6 +33257,7 @@
       <x:c r="CE37" t="str">
         <x:v>false</x:v>
       </x:c>
+      <x:c r="CF37" t="str"/>
     </x:row>
     <x:row r="38" ht="58" customHeight="1">
       <x:c r="A38" t="str">
@@ -33376,6 +33507,7 @@
       <x:c r="CE38" t="str">
         <x:v>false</x:v>
       </x:c>
+      <x:c r="CF38" t="str"/>
     </x:row>
     <x:row r="39" ht="58" customHeight="1">
       <x:c r="A39" t="str">
@@ -33625,6 +33757,7 @@
       <x:c r="CE39" t="str">
         <x:v>false</x:v>
       </x:c>
+      <x:c r="CF39" t="str"/>
     </x:row>
     <x:row r="40" ht="58" customHeight="1">
       <x:c r="A40" t="str">
@@ -33874,6 +34007,7 @@
       <x:c r="CE40" t="str">
         <x:v>false</x:v>
       </x:c>
+      <x:c r="CF40" t="str"/>
     </x:row>
     <x:row r="41" ht="58" customHeight="1">
       <x:c r="A41" t="str">
@@ -34123,6 +34257,7 @@
       <x:c r="CE41" t="str">
         <x:v>false</x:v>
       </x:c>
+      <x:c r="CF41" t="str"/>
     </x:row>
     <x:row r="42" ht="58" customHeight="1">
       <x:c r="A42" t="str">
@@ -34372,6 +34507,7 @@
       <x:c r="CE42" t="str">
         <x:v>false</x:v>
       </x:c>
+      <x:c r="CF42" t="str"/>
     </x:row>
     <x:row r="43" ht="58" customHeight="1">
       <x:c r="A43" t="str">
@@ -34621,6 +34757,7 @@
       <x:c r="CE43" t="str">
         <x:v>false</x:v>
       </x:c>
+      <x:c r="CF43" t="str"/>
     </x:row>
     <x:row r="44" ht="58" customHeight="1">
       <x:c r="A44" t="str">
@@ -34870,6 +35007,7 @@
       <x:c r="CE44" t="str">
         <x:v>false</x:v>
       </x:c>
+      <x:c r="CF44" t="str"/>
     </x:row>
     <x:row r="45" ht="58" customHeight="1">
       <x:c r="A45" t="str">
@@ -35119,6 +35257,7 @@
       <x:c r="CE45" t="str">
         <x:v>false</x:v>
       </x:c>
+      <x:c r="CF45" t="str"/>
     </x:row>
     <x:row r="46" ht="58" customHeight="1">
       <x:c r="A46" t="str">
@@ -35368,6 +35507,7 @@
       <x:c r="CE46" t="str">
         <x:v>false</x:v>
       </x:c>
+      <x:c r="CF46" t="str"/>
     </x:row>
     <x:row r="47" ht="58" customHeight="1">
       <x:c r="A47" t="str">
@@ -35617,6 +35757,7 @@
       <x:c r="CE47" t="str">
         <x:v>false</x:v>
       </x:c>
+      <x:c r="CF47" t="str"/>
     </x:row>
     <x:row r="48" ht="58" customHeight="1">
       <x:c r="A48" t="str">
@@ -35866,6 +36007,7 @@
       <x:c r="CE48" t="str">
         <x:v>false</x:v>
       </x:c>
+      <x:c r="CF48" t="str"/>
     </x:row>
     <x:row r="49" ht="58" customHeight="1">
       <x:c r="A49" t="str">
@@ -36115,6 +36257,7 @@
       <x:c r="CE49" t="str">
         <x:v>false</x:v>
       </x:c>
+      <x:c r="CF49" t="str"/>
     </x:row>
     <x:row r="50" ht="58" customHeight="1">
       <x:c r="A50" t="str">
@@ -36364,6 +36507,7 @@
       <x:c r="CE50" t="str">
         <x:v>false</x:v>
       </x:c>
+      <x:c r="CF50" t="str"/>
     </x:row>
     <x:row r="51" ht="58" customHeight="1">
       <x:c r="A51" t="str">
@@ -36613,6 +36757,7 @@
       <x:c r="CE51" t="str">
         <x:v>false</x:v>
       </x:c>
+      <x:c r="CF51" t="str"/>
     </x:row>
     <x:row r="52" ht="58" customHeight="1">
       <x:c r="A52" t="str">
@@ -36862,6 +37007,7 @@
       <x:c r="CE52" t="str">
         <x:v>false</x:v>
       </x:c>
+      <x:c r="CF52" t="str"/>
     </x:row>
     <x:row r="53" ht="58" customHeight="1">
       <x:c r="A53" t="str">
@@ -37111,6 +37257,7 @@
       <x:c r="CE53" t="str">
         <x:v>false</x:v>
       </x:c>
+      <x:c r="CF53" t="str"/>
     </x:row>
     <x:row r="54" ht="58" customHeight="1">
       <x:c r="A54" t="str">
@@ -37360,6 +37507,7 @@
       <x:c r="CE54" t="str">
         <x:v>false</x:v>
       </x:c>
+      <x:c r="CF54" t="str"/>
     </x:row>
     <x:row r="55" ht="58" customHeight="1">
       <x:c r="A55" t="str">
@@ -37609,6 +37757,7 @@
       <x:c r="CE55" t="str">
         <x:v>false</x:v>
       </x:c>
+      <x:c r="CF55" t="str"/>
     </x:row>
     <x:row r="56" ht="58" customHeight="1">
       <x:c r="A56" t="str">
@@ -37858,6 +38007,7 @@
       <x:c r="CE56" t="str">
         <x:v>false</x:v>
       </x:c>
+      <x:c r="CF56" t="str"/>
     </x:row>
     <x:row r="57" ht="58" customHeight="1">
       <x:c r="A57" t="str">
@@ -38107,6 +38257,7 @@
       <x:c r="CE57" t="str">
         <x:v>false</x:v>
       </x:c>
+      <x:c r="CF57" t="str"/>
     </x:row>
     <x:row r="58" ht="58" customHeight="1">
       <x:c r="A58" t="str">
@@ -38356,6 +38507,7 @@
       <x:c r="CE58" t="str">
         <x:v>false</x:v>
       </x:c>
+      <x:c r="CF58" t="str"/>
     </x:row>
     <x:row r="59" ht="58" customHeight="1">
       <x:c r="A59" t="str">
@@ -38605,6 +38757,7 @@
       <x:c r="CE59" t="str">
         <x:v>false</x:v>
       </x:c>
+      <x:c r="CF59" t="str"/>
     </x:row>
     <x:row r="60" ht="58" customHeight="1">
       <x:c r="A60" t="str">
@@ -38854,6 +39007,7 @@
       <x:c r="CE60" t="str">
         <x:v>false</x:v>
       </x:c>
+      <x:c r="CF60" t="str"/>
     </x:row>
     <x:row r="61" ht="58" customHeight="1">
       <x:c r="A61" t="str">
@@ -39103,6 +39257,7 @@
       <x:c r="CE61" t="str">
         <x:v>false</x:v>
       </x:c>
+      <x:c r="CF61" t="str"/>
     </x:row>
     <x:row r="62" ht="58" customHeight="1">
       <x:c r="A62" t="str">
@@ -39352,6 +39507,7 @@
       <x:c r="CE62" t="str">
         <x:v>false</x:v>
       </x:c>
+      <x:c r="CF62" t="str"/>
     </x:row>
     <x:row r="63" ht="58" customHeight="1">
       <x:c r="A63" t="str">
@@ -39601,6 +39757,7 @@
       <x:c r="CE63" t="str">
         <x:v>false</x:v>
       </x:c>
+      <x:c r="CF63" t="str"/>
     </x:row>
     <x:row r="64" ht="58" customHeight="1">
       <x:c r="A64" t="str">
@@ -39850,6 +40007,7 @@
       <x:c r="CE64" t="str">
         <x:v>false</x:v>
       </x:c>
+      <x:c r="CF64" t="str"/>
     </x:row>
     <x:row r="65" ht="58" customHeight="1">
       <x:c r="A65" t="str">
@@ -40099,6 +40257,7 @@
       <x:c r="CE65" t="str">
         <x:v>false</x:v>
       </x:c>
+      <x:c r="CF65" t="str"/>
     </x:row>
     <x:row r="66" ht="58" customHeight="1">
       <x:c r="A66" t="str">
@@ -40348,6 +40507,7 @@
       <x:c r="CE66" t="str">
         <x:v>false</x:v>
       </x:c>
+      <x:c r="CF66" t="str"/>
     </x:row>
     <x:row r="67">
       <x:c r="A67" t="str">
@@ -40597,6 +40757,7 @@
       <x:c r="CE67" t="str">
         <x:v>false</x:v>
       </x:c>
+      <x:c r="CF67" t="str"/>
     </x:row>
   </x:sheetData>
   <x:dataValidations count="10">
@@ -40633,7 +40794,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re4b0842603324a9c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb5ea64be2c924395"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -40898,6 +41059,9 @@
       <x:c r="BT1" t="str">
         <x:v>Deep Enrichment Completed</x:v>
       </x:c>
+      <x:c r="BU1" t="str">
+        <x:v>Queue Status</x:v>
+      </x:c>
     </x:row>
     <x:row r="2" ht="62" customHeight="1">
       <x:c r="A2" t="str">
@@ -41114,6 +41278,7 @@
       <x:c r="BT2" t="str">
         <x:v>false</x:v>
       </x:c>
+      <x:c r="BU2" t="str"/>
     </x:row>
     <x:row r="3" ht="62" customHeight="1">
       <x:c r="A3" t="str">
@@ -41330,6 +41495,7 @@
       <x:c r="BT3" t="str">
         <x:v>false</x:v>
       </x:c>
+      <x:c r="BU3" t="str"/>
     </x:row>
     <x:row r="4" ht="62" customHeight="1">
       <x:c r="A4" t="str">
@@ -41546,6 +41712,7 @@
       <x:c r="BT4" t="str">
         <x:v>false</x:v>
       </x:c>
+      <x:c r="BU4" t="str"/>
     </x:row>
     <x:row r="5" ht="62" customHeight="1">
       <x:c r="A5" t="str">
@@ -41762,6 +41929,7 @@
       <x:c r="BT5" t="str">
         <x:v>false</x:v>
       </x:c>
+      <x:c r="BU5" t="str"/>
     </x:row>
     <x:row r="6" ht="62" customHeight="1">
       <x:c r="A6" t="str">
@@ -41978,6 +42146,7 @@
       <x:c r="BT6" t="str">
         <x:v>false</x:v>
       </x:c>
+      <x:c r="BU6" t="str"/>
     </x:row>
     <x:row r="7" ht="62" customHeight="1">
       <x:c r="A7" t="str">
@@ -42194,6 +42363,7 @@
       <x:c r="BT7" t="str">
         <x:v>false</x:v>
       </x:c>
+      <x:c r="BU7" t="str"/>
     </x:row>
     <x:row r="8" ht="62" customHeight="1">
       <x:c r="A8" t="str">
@@ -42410,6 +42580,7 @@
       <x:c r="BT8" t="str">
         <x:v>false</x:v>
       </x:c>
+      <x:c r="BU8" t="str"/>
     </x:row>
     <x:row r="9" ht="62" customHeight="1">
       <x:c r="A9" t="str">
@@ -42626,6 +42797,7 @@
       <x:c r="BT9" t="str">
         <x:v>false</x:v>
       </x:c>
+      <x:c r="BU9" t="str"/>
     </x:row>
     <x:row r="10" ht="62" customHeight="1">
       <x:c r="A10" t="str">
@@ -42842,6 +43014,7 @@
       <x:c r="BT10" t="str">
         <x:v>false</x:v>
       </x:c>
+      <x:c r="BU10" t="str"/>
     </x:row>
     <x:row r="11" ht="62" customHeight="1">
       <x:c r="A11" t="str">
@@ -43036,6 +43209,7 @@
       <x:c r="BT11" t="str">
         <x:v>false</x:v>
       </x:c>
+      <x:c r="BU11" t="str"/>
     </x:row>
     <x:row r="12" ht="62" customHeight="1">
       <x:c r="A12" t="str">
@@ -43226,6 +43400,7 @@
       <x:c r="BT12" t="str">
         <x:v>false</x:v>
       </x:c>
+      <x:c r="BU12" t="str"/>
     </x:row>
     <x:row r="13" ht="62" customHeight="1">
       <x:c r="A13" t="str">
@@ -43416,6 +43591,7 @@
       <x:c r="BT13" t="str">
         <x:v>false</x:v>
       </x:c>
+      <x:c r="BU13" t="str"/>
     </x:row>
     <x:row r="14" ht="62" customHeight="1">
       <x:c r="A14" t="str">
@@ -43606,6 +43782,7 @@
       <x:c r="BT14" t="str">
         <x:v>false</x:v>
       </x:c>
+      <x:c r="BU14" t="str"/>
     </x:row>
   </x:sheetData>
   <x:dataValidations count="4">
@@ -43624,7 +43801,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rad226df4586d4d02"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3968b3ff70f04d19"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/00_Paper_Pool/Paper_Pool.xlsx
+++ b/00_Paper_Pool/Paper_Pool.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Papers" sheetId="1" r:id="R088f20caa81c4d6c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rejected" sheetId="2" r:id="R79c228a70d0e482d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Venues" sheetId="3" r:id="R32ac521297054fbf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Keywords" sheetId="4" r:id="R1051e123e15c4ddd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Discovery" sheetId="5" r:id="Rd6933891c3d94d92"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CCF_A_Library" sheetId="6" r:id="Ree6cb4209d1f4d31"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Robotics_Core_Library" sheetId="7" r:id="R2480683c407b4386"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Papers" sheetId="1" r:id="R41c2cee264f74f1d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rejected" sheetId="2" r:id="R564b5dae00024532"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Venues" sheetId="3" r:id="Rb62e65650a4b4772"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Keywords" sheetId="4" r:id="R0fa3c7d61e984fbf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Discovery" sheetId="5" r:id="R69289114541541b8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CCF_A_Library" sheetId="6" r:id="R7052b95f5b0a490d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Robotics_Core_Library" sheetId="7" r:id="R25b09cb8c1fa4afe"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -300,7 +300,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="52" name="PapersTable" displayName="PapersTable" ref="A1:BR5" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="56" name="PapersTable" displayName="PapersTable" ref="A1:BR5" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="70">
     <x:tableColumn id="1" name="编号 ID"/>
     <x:tableColumn id="2" name="论文标题 Title"/>
@@ -423,7 +423,7 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="53" name="DiscoveryTable" displayName="DiscoveryTable" ref="A1:BM79" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="57" name="DiscoveryTable" displayName="DiscoveryTable" ref="A1:BM79" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="65">
     <x:tableColumn id="1" name="编号 ID"/>
     <x:tableColumn id="2" name="论文标题 Title"/>
@@ -496,7 +496,7 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="54" name="CCFALibraryTable" displayName="CCFALibraryTable" ref="A1:CF67" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="58" name="CCFALibraryTable" displayName="CCFALibraryTable" ref="A1:CF67" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="84">
     <x:tableColumn id="1" name="编号 ID"/>
     <x:tableColumn id="2" name="论文标题 Title"/>
@@ -588,7 +588,7 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="55" name="RoboticsCoreLibraryTable" displayName="RoboticsCoreLibraryTable" ref="A1:BU14" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="59" name="RoboticsCoreLibraryTable" displayName="RoboticsCoreLibraryTable" ref="A1:BU14" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="73">
     <x:tableColumn id="1" name="ID"/>
     <x:tableColumn id="2" name="Title"/>
@@ -1313,7 +1313,7 @@
       <x:c r="BQ2" t="str">
         <x:v>false</x:v>
       </x:c>
-      <x:c r="BR2" t="str"/>
+      <x:c r="BR2"/>
     </x:row>
     <x:row r="3" ht="150" customHeight="1">
       <x:c r="A3" t="str">
@@ -1489,7 +1489,7 @@
       <x:c r="BQ3" t="str">
         <x:v>false</x:v>
       </x:c>
-      <x:c r="BR3" t="str"/>
+      <x:c r="BR3"/>
     </x:row>
     <x:row r="4" ht="150" customHeight="1">
       <x:c r="A4" t="str">
@@ -1665,7 +1665,7 @@
       <x:c r="BQ4" t="str">
         <x:v>false</x:v>
       </x:c>
-      <x:c r="BR4" t="str"/>
+      <x:c r="BR4"/>
     </x:row>
     <x:row r="5" ht="150" customHeight="1">
       <x:c r="A5" t="str">
@@ -1841,7 +1841,7 @@
       <x:c r="BQ5" t="str">
         <x:v>false</x:v>
       </x:c>
-      <x:c r="BR5" t="str"/>
+      <x:c r="BR5"/>
     </x:row>
     <x:row r="6">
       <x:c r="AC6" s="7"/>
@@ -4854,7 +4854,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0d56b28395454f48"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re5753606751f4e58"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8150,7 +8150,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7ed45e795c4b4da1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb0a7614ef9b646ab"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8501,7 +8501,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R36fe4e66a443490e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1e8501099a1a4f77"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9247,7 +9247,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbe8d92f56e3b4a6e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R89abe657fca74772"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9667,7 +9667,7 @@
       <x:c r="BL2" t="str">
         <x:v>false</x:v>
       </x:c>
-      <x:c r="BM2" t="str"/>
+      <x:c r="BM2"/>
     </x:row>
     <x:row r="3" ht="58" customHeight="1">
       <x:c r="A3" t="str">
@@ -9852,7 +9852,7 @@
       <x:c r="BL3" t="str">
         <x:v>false</x:v>
       </x:c>
-      <x:c r="BM3" t="str"/>
+      <x:c r="BM3"/>
     </x:row>
     <x:row r="4" ht="58" customHeight="1">
       <x:c r="A4" t="str">
@@ -10037,7 +10037,7 @@
       <x:c r="BL4" t="str">
         <x:v>false</x:v>
       </x:c>
-      <x:c r="BM4" t="str"/>
+      <x:c r="BM4"/>
     </x:row>
     <x:row r="5" ht="58" customHeight="1">
       <x:c r="A5" t="str">
@@ -10224,7 +10224,7 @@
       <x:c r="BL5" t="str">
         <x:v>false</x:v>
       </x:c>
-      <x:c r="BM5" t="str"/>
+      <x:c r="BM5"/>
     </x:row>
     <x:row r="6" ht="58" customHeight="1">
       <x:c r="A6" t="str">
@@ -10409,7 +10409,7 @@
       <x:c r="BL6" t="str">
         <x:v>false</x:v>
       </x:c>
-      <x:c r="BM6" t="str"/>
+      <x:c r="BM6"/>
     </x:row>
     <x:row r="7" ht="58" customHeight="1">
       <x:c r="A7" t="str">
@@ -10594,7 +10594,7 @@
       <x:c r="BL7" t="str">
         <x:v>false</x:v>
       </x:c>
-      <x:c r="BM7" t="str"/>
+      <x:c r="BM7"/>
     </x:row>
     <x:row r="8" ht="58" customHeight="1">
       <x:c r="A8" t="str">
@@ -10777,7 +10777,7 @@
       <x:c r="BL8" t="str">
         <x:v>false</x:v>
       </x:c>
-      <x:c r="BM8" t="str"/>
+      <x:c r="BM8"/>
     </x:row>
     <x:row r="9" ht="58" customHeight="1">
       <x:c r="A9" t="str">
@@ -10962,7 +10962,7 @@
       <x:c r="BL9" t="str">
         <x:v>false</x:v>
       </x:c>
-      <x:c r="BM9" t="str"/>
+      <x:c r="BM9"/>
     </x:row>
     <x:row r="10" ht="58" customHeight="1">
       <x:c r="A10" t="str">
@@ -11145,7 +11145,7 @@
       <x:c r="BL10" t="str">
         <x:v>false</x:v>
       </x:c>
-      <x:c r="BM10" t="str"/>
+      <x:c r="BM10"/>
     </x:row>
     <x:row r="11" ht="58" customHeight="1">
       <x:c r="A11" t="str">
@@ -11332,7 +11332,7 @@
       <x:c r="BL11" t="str">
         <x:v>false</x:v>
       </x:c>
-      <x:c r="BM11" t="str"/>
+      <x:c r="BM11"/>
     </x:row>
     <x:row r="12" ht="58" customHeight="1">
       <x:c r="A12" t="str">
@@ -11519,7 +11519,7 @@
       <x:c r="BL12" t="str">
         <x:v>false</x:v>
       </x:c>
-      <x:c r="BM12" t="str"/>
+      <x:c r="BM12"/>
     </x:row>
     <x:row r="13" ht="58" customHeight="1">
       <x:c r="A13" t="str">
@@ -11706,7 +11706,7 @@
       <x:c r="BL13" t="str">
         <x:v>false</x:v>
       </x:c>
-      <x:c r="BM13" t="str"/>
+      <x:c r="BM13"/>
     </x:row>
     <x:row r="14" ht="58" customHeight="1">
       <x:c r="A14" t="str">
@@ -11891,7 +11891,7 @@
       <x:c r="BL14" t="str">
         <x:v>false</x:v>
       </x:c>
-      <x:c r="BM14" t="str"/>
+      <x:c r="BM14"/>
     </x:row>
     <x:row r="15" ht="58" customHeight="1">
       <x:c r="A15" t="str">
@@ -12078,7 +12078,7 @@
       <x:c r="BL15" t="str">
         <x:v>false</x:v>
       </x:c>
-      <x:c r="BM15" t="str"/>
+      <x:c r="BM15"/>
     </x:row>
     <x:row r="16" ht="58" customHeight="1">
       <x:c r="A16" t="str">
@@ -12261,7 +12261,7 @@
       <x:c r="BL16" t="str">
         <x:v>false</x:v>
       </x:c>
-      <x:c r="BM16" t="str"/>
+      <x:c r="BM16"/>
     </x:row>
     <x:row r="17" ht="58" customHeight="1">
       <x:c r="A17" t="str">
@@ -12444,7 +12444,7 @@
       <x:c r="BL17" t="str">
         <x:v>false</x:v>
       </x:c>
-      <x:c r="BM17" t="str"/>
+      <x:c r="BM17"/>
     </x:row>
     <x:row r="18" ht="58" customHeight="1">
       <x:c r="A18" t="str">
@@ -12627,7 +12627,7 @@
       <x:c r="BL18" t="str">
         <x:v>false</x:v>
       </x:c>
-      <x:c r="BM18" t="str"/>
+      <x:c r="BM18"/>
     </x:row>
     <x:row r="19" ht="58" customHeight="1">
       <x:c r="A19" t="str">
@@ -12812,7 +12812,7 @@
       <x:c r="BL19" t="str">
         <x:v>false</x:v>
       </x:c>
-      <x:c r="BM19" t="str"/>
+      <x:c r="BM19"/>
     </x:row>
     <x:row r="20" ht="58" customHeight="1">
       <x:c r="A20" t="str">
@@ -12995,7 +12995,7 @@
       <x:c r="BL20" t="str">
         <x:v>false</x:v>
       </x:c>
-      <x:c r="BM20" t="str"/>
+      <x:c r="BM20"/>
     </x:row>
     <x:row r="21" ht="58" customHeight="1">
       <x:c r="A21" t="str">
@@ -13180,7 +13180,7 @@
       <x:c r="BL21" t="str">
         <x:v>false</x:v>
       </x:c>
-      <x:c r="BM21" t="str"/>
+      <x:c r="BM21"/>
     </x:row>
     <x:row r="22" ht="58" customHeight="1">
       <x:c r="A22" t="str">
@@ -13365,7 +13365,7 @@
       <x:c r="BL22" t="str">
         <x:v>false</x:v>
       </x:c>
-      <x:c r="BM22" t="str"/>
+      <x:c r="BM22"/>
     </x:row>
     <x:row r="23" ht="58" customHeight="1">
       <x:c r="A23" t="str">
@@ -13550,7 +13550,7 @@
       <x:c r="BL23" t="str">
         <x:v>false</x:v>
       </x:c>
-      <x:c r="BM23" t="str"/>
+      <x:c r="BM23"/>
     </x:row>
     <x:row r="24" ht="58" customHeight="1">
       <x:c r="A24" t="str">
@@ -13735,7 +13735,7 @@
       <x:c r="BL24" t="str">
         <x:v>false</x:v>
       </x:c>
-      <x:c r="BM24" t="str"/>
+      <x:c r="BM24"/>
     </x:row>
     <x:row r="25" ht="58" customHeight="1">
       <x:c r="A25" t="str">
@@ -13918,7 +13918,7 @@
       <x:c r="BL25" t="str">
         <x:v>false</x:v>
       </x:c>
-      <x:c r="BM25" t="str"/>
+      <x:c r="BM25"/>
     </x:row>
     <x:row r="26" ht="58" customHeight="1">
       <x:c r="A26" t="str">
@@ -14103,7 +14103,7 @@
       <x:c r="BL26" t="str">
         <x:v>false</x:v>
       </x:c>
-      <x:c r="BM26" t="str"/>
+      <x:c r="BM26"/>
     </x:row>
     <x:row r="27" ht="58" customHeight="1">
       <x:c r="A27" t="str">
@@ -14288,7 +14288,7 @@
       <x:c r="BL27" t="str">
         <x:v>false</x:v>
       </x:c>
-      <x:c r="BM27" t="str"/>
+      <x:c r="BM27"/>
     </x:row>
     <x:row r="28" ht="58" customHeight="1">
       <x:c r="A28" t="str">
@@ -14473,7 +14473,7 @@
       <x:c r="BL28" t="str">
         <x:v>false</x:v>
       </x:c>
-      <x:c r="BM28" t="str"/>
+      <x:c r="BM28"/>
     </x:row>
     <x:row r="29" ht="58" customHeight="1">
       <x:c r="A29" t="str">
@@ -14658,7 +14658,7 @@
       <x:c r="BL29" t="str">
         <x:v>false</x:v>
       </x:c>
-      <x:c r="BM29" t="str"/>
+      <x:c r="BM29"/>
     </x:row>
     <x:row r="30" ht="58" customHeight="1">
       <x:c r="A30" t="str">
@@ -14843,7 +14843,7 @@
       <x:c r="BL30" t="str">
         <x:v>false</x:v>
       </x:c>
-      <x:c r="BM30" t="str"/>
+      <x:c r="BM30"/>
     </x:row>
     <x:row r="31" ht="58" customHeight="1">
       <x:c r="A31" t="str">
@@ -15028,7 +15028,7 @@
       <x:c r="BL31" t="str">
         <x:v>false</x:v>
       </x:c>
-      <x:c r="BM31" t="str"/>
+      <x:c r="BM31"/>
     </x:row>
     <x:row r="32" ht="58" customHeight="1">
       <x:c r="A32" t="str">
@@ -15213,7 +15213,7 @@
       <x:c r="BL32" t="str">
         <x:v>false</x:v>
       </x:c>
-      <x:c r="BM32" t="str"/>
+      <x:c r="BM32"/>
     </x:row>
     <x:row r="33" ht="58" customHeight="1">
       <x:c r="A33" t="str">
@@ -15398,7 +15398,7 @@
       <x:c r="BL33" t="str">
         <x:v>false</x:v>
       </x:c>
-      <x:c r="BM33" t="str"/>
+      <x:c r="BM33"/>
     </x:row>
     <x:row r="34" ht="58" customHeight="1">
       <x:c r="A34" t="str">
@@ -15583,7 +15583,7 @@
       <x:c r="BL34" t="str">
         <x:v>false</x:v>
       </x:c>
-      <x:c r="BM34" t="str"/>
+      <x:c r="BM34"/>
     </x:row>
     <x:row r="35" ht="58" customHeight="1">
       <x:c r="A35" t="str">
@@ -15768,7 +15768,7 @@
       <x:c r="BL35" t="str">
         <x:v>false</x:v>
       </x:c>
-      <x:c r="BM35" t="str"/>
+      <x:c r="BM35"/>
     </x:row>
     <x:row r="36" ht="58" customHeight="1">
       <x:c r="A36" t="str">
@@ -15953,7 +15953,7 @@
       <x:c r="BL36" t="str">
         <x:v>false</x:v>
       </x:c>
-      <x:c r="BM36" t="str"/>
+      <x:c r="BM36"/>
     </x:row>
     <x:row r="37" ht="58" customHeight="1">
       <x:c r="A37" t="str">
@@ -16138,7 +16138,7 @@
       <x:c r="BL37" t="str">
         <x:v>false</x:v>
       </x:c>
-      <x:c r="BM37" t="str"/>
+      <x:c r="BM37"/>
     </x:row>
     <x:row r="38" ht="58" customHeight="1">
       <x:c r="A38" t="str">
@@ -16323,7 +16323,7 @@
       <x:c r="BL38" t="str">
         <x:v>false</x:v>
       </x:c>
-      <x:c r="BM38" t="str"/>
+      <x:c r="BM38"/>
     </x:row>
     <x:row r="39" ht="58" customHeight="1">
       <x:c r="A39" t="str">
@@ -16508,7 +16508,7 @@
       <x:c r="BL39" t="str">
         <x:v>false</x:v>
       </x:c>
-      <x:c r="BM39" t="str"/>
+      <x:c r="BM39"/>
     </x:row>
     <x:row r="40" ht="58" customHeight="1">
       <x:c r="A40" t="str">
@@ -16691,7 +16691,7 @@
       <x:c r="BL40" t="str">
         <x:v>false</x:v>
       </x:c>
-      <x:c r="BM40" t="str"/>
+      <x:c r="BM40"/>
     </x:row>
     <x:row r="41" ht="58" customHeight="1">
       <x:c r="A41" t="str">
@@ -16874,7 +16874,7 @@
       <x:c r="BL41" t="str">
         <x:v>false</x:v>
       </x:c>
-      <x:c r="BM41" t="str"/>
+      <x:c r="BM41"/>
     </x:row>
     <x:row r="42" ht="58" customHeight="1">
       <x:c r="A42" t="str">
@@ -17057,7 +17057,7 @@
       <x:c r="BL42" t="str">
         <x:v>false</x:v>
       </x:c>
-      <x:c r="BM42" t="str"/>
+      <x:c r="BM42"/>
     </x:row>
     <x:row r="43" ht="58" customHeight="1">
       <x:c r="A43" t="str">
@@ -17240,7 +17240,7 @@
       <x:c r="BL43" t="str">
         <x:v>false</x:v>
       </x:c>
-      <x:c r="BM43" t="str"/>
+      <x:c r="BM43"/>
     </x:row>
     <x:row r="44" ht="58" customHeight="1">
       <x:c r="A44" t="str">
@@ -17423,7 +17423,7 @@
       <x:c r="BL44" t="str">
         <x:v>false</x:v>
       </x:c>
-      <x:c r="BM44" t="str"/>
+      <x:c r="BM44"/>
     </x:row>
     <x:row r="45" ht="58" customHeight="1">
       <x:c r="A45" t="str">
@@ -17606,7 +17606,7 @@
       <x:c r="BL45" t="str">
         <x:v>false</x:v>
       </x:c>
-      <x:c r="BM45" t="str"/>
+      <x:c r="BM45"/>
     </x:row>
     <x:row r="46" ht="58" customHeight="1">
       <x:c r="A46" t="str">
@@ -17791,7 +17791,7 @@
       <x:c r="BL46" t="str">
         <x:v>false</x:v>
       </x:c>
-      <x:c r="BM46" t="str"/>
+      <x:c r="BM46"/>
     </x:row>
     <x:row r="47" ht="58" customHeight="1">
       <x:c r="A47" t="str">
@@ -17976,7 +17976,7 @@
       <x:c r="BL47" t="str">
         <x:v>false</x:v>
       </x:c>
-      <x:c r="BM47" t="str"/>
+      <x:c r="BM47"/>
     </x:row>
     <x:row r="48" ht="58" customHeight="1">
       <x:c r="A48" t="str">
@@ -18161,7 +18161,7 @@
       <x:c r="BL48" t="str">
         <x:v>false</x:v>
       </x:c>
-      <x:c r="BM48" t="str"/>
+      <x:c r="BM48"/>
     </x:row>
     <x:row r="49" ht="58" customHeight="1">
       <x:c r="A49" t="str">
@@ -18346,7 +18346,7 @@
       <x:c r="BL49" t="str">
         <x:v>false</x:v>
       </x:c>
-      <x:c r="BM49" t="str"/>
+      <x:c r="BM49"/>
     </x:row>
     <x:row r="50" ht="58" customHeight="1">
       <x:c r="A50" t="str">
@@ -18531,7 +18531,7 @@
       <x:c r="BL50" t="str">
         <x:v>false</x:v>
       </x:c>
-      <x:c r="BM50" t="str"/>
+      <x:c r="BM50"/>
     </x:row>
     <x:row r="51" ht="58" customHeight="1">
       <x:c r="A51" t="str">
@@ -18716,7 +18716,7 @@
       <x:c r="BL51" t="str">
         <x:v>false</x:v>
       </x:c>
-      <x:c r="BM51" t="str"/>
+      <x:c r="BM51"/>
     </x:row>
     <x:row r="52" ht="58" customHeight="1">
       <x:c r="A52" t="str">
@@ -18901,7 +18901,7 @@
       <x:c r="BL52" t="str">
         <x:v>false</x:v>
       </x:c>
-      <x:c r="BM52" t="str"/>
+      <x:c r="BM52"/>
     </x:row>
     <x:row r="53" ht="58" customHeight="1">
       <x:c r="A53" t="str">
@@ -19086,7 +19086,7 @@
       <x:c r="BL53" t="str">
         <x:v>false</x:v>
       </x:c>
-      <x:c r="BM53" t="str"/>
+      <x:c r="BM53"/>
     </x:row>
     <x:row r="54" ht="58" customHeight="1">
       <x:c r="A54" t="str">
@@ -19271,7 +19271,7 @@
       <x:c r="BL54" t="str">
         <x:v>false</x:v>
       </x:c>
-      <x:c r="BM54" t="str"/>
+      <x:c r="BM54"/>
     </x:row>
     <x:row r="55" ht="58" customHeight="1">
       <x:c r="A55" t="str">
@@ -19456,7 +19456,7 @@
       <x:c r="BL55" t="str">
         <x:v>false</x:v>
       </x:c>
-      <x:c r="BM55" t="str"/>
+      <x:c r="BM55"/>
     </x:row>
     <x:row r="56" ht="58" customHeight="1">
       <x:c r="A56" t="str">
@@ -19641,7 +19641,7 @@
       <x:c r="BL56" t="str">
         <x:v>false</x:v>
       </x:c>
-      <x:c r="BM56" t="str"/>
+      <x:c r="BM56"/>
     </x:row>
     <x:row r="57" ht="58" customHeight="1">
       <x:c r="A57" t="str">
@@ -19826,7 +19826,7 @@
       <x:c r="BL57" t="str">
         <x:v>false</x:v>
       </x:c>
-      <x:c r="BM57" t="str"/>
+      <x:c r="BM57"/>
     </x:row>
     <x:row r="58" ht="58" customHeight="1">
       <x:c r="A58" t="str">
@@ -20017,7 +20017,7 @@
       <x:c r="BL58" t="str">
         <x:v>false</x:v>
       </x:c>
-      <x:c r="BM58" t="str"/>
+      <x:c r="BM58"/>
     </x:row>
     <x:row r="59" ht="58" customHeight="1">
       <x:c r="A59" t="str">
@@ -20208,7 +20208,7 @@
       <x:c r="BL59" t="str">
         <x:v>false</x:v>
       </x:c>
-      <x:c r="BM59" t="str"/>
+      <x:c r="BM59"/>
     </x:row>
     <x:row r="60" ht="58" customHeight="1">
       <x:c r="A60" t="str">
@@ -20397,7 +20397,7 @@
       <x:c r="BL60" t="str">
         <x:v>false</x:v>
       </x:c>
-      <x:c r="BM60" t="str"/>
+      <x:c r="BM60"/>
     </x:row>
     <x:row r="61" ht="58" customHeight="1">
       <x:c r="A61" t="str">
@@ -20588,7 +20588,7 @@
       <x:c r="BL61" t="str">
         <x:v>false</x:v>
       </x:c>
-      <x:c r="BM61" t="str"/>
+      <x:c r="BM61"/>
     </x:row>
     <x:row r="62" ht="58" customHeight="1">
       <x:c r="A62" t="str">
@@ -20779,7 +20779,7 @@
       <x:c r="BL62" t="str">
         <x:v>false</x:v>
       </x:c>
-      <x:c r="BM62" t="str"/>
+      <x:c r="BM62"/>
     </x:row>
     <x:row r="63" ht="58" customHeight="1">
       <x:c r="A63" t="str">
@@ -20970,7 +20970,7 @@
       <x:c r="BL63" t="str">
         <x:v>false</x:v>
       </x:c>
-      <x:c r="BM63" t="str"/>
+      <x:c r="BM63"/>
     </x:row>
     <x:row r="64" ht="58" customHeight="1">
       <x:c r="A64" t="str">
@@ -21161,7 +21161,7 @@
       <x:c r="BL64" t="str">
         <x:v>false</x:v>
       </x:c>
-      <x:c r="BM64" t="str"/>
+      <x:c r="BM64"/>
     </x:row>
     <x:row r="65" ht="58" customHeight="1">
       <x:c r="A65" t="str">
@@ -21352,7 +21352,7 @@
       <x:c r="BL65" t="str">
         <x:v>false</x:v>
       </x:c>
-      <x:c r="BM65" t="str"/>
+      <x:c r="BM65"/>
     </x:row>
     <x:row r="66" ht="58" customHeight="1">
       <x:c r="A66" t="str">
@@ -21543,7 +21543,7 @@
       <x:c r="BL66" t="str">
         <x:v>false</x:v>
       </x:c>
-      <x:c r="BM66" t="str"/>
+      <x:c r="BM66"/>
     </x:row>
     <x:row r="67" ht="58" customHeight="1">
       <x:c r="A67" t="str">
@@ -21734,7 +21734,7 @@
       <x:c r="BL67" t="str">
         <x:v>false</x:v>
       </x:c>
-      <x:c r="BM67" t="str"/>
+      <x:c r="BM67"/>
     </x:row>
     <x:row r="68" ht="58" customHeight="1">
       <x:c r="A68" t="str">
@@ -21923,7 +21923,7 @@
       <x:c r="BL68" t="str">
         <x:v>false</x:v>
       </x:c>
-      <x:c r="BM68" t="str"/>
+      <x:c r="BM68"/>
     </x:row>
     <x:row r="69" ht="58" customHeight="1">
       <x:c r="A69" t="str">
@@ -22114,7 +22114,7 @@
       <x:c r="BL69" t="str">
         <x:v>false</x:v>
       </x:c>
-      <x:c r="BM69" t="str"/>
+      <x:c r="BM69"/>
     </x:row>
     <x:row r="70" ht="58" customHeight="1">
       <x:c r="A70" t="str">
@@ -22305,7 +22305,7 @@
       <x:c r="BL70" t="str">
         <x:v>false</x:v>
       </x:c>
-      <x:c r="BM70" t="str"/>
+      <x:c r="BM70"/>
     </x:row>
     <x:row r="71" ht="58" customHeight="1">
       <x:c r="A71" t="str">
@@ -22496,7 +22496,7 @@
       <x:c r="BL71" t="str">
         <x:v>false</x:v>
       </x:c>
-      <x:c r="BM71" t="str"/>
+      <x:c r="BM71"/>
     </x:row>
     <x:row r="72" ht="58" customHeight="1">
       <x:c r="A72" t="str">
@@ -22687,7 +22687,7 @@
       <x:c r="BL72" t="str">
         <x:v>false</x:v>
       </x:c>
-      <x:c r="BM72" t="str"/>
+      <x:c r="BM72"/>
     </x:row>
     <x:row r="73" ht="58" customHeight="1">
       <x:c r="A73" t="str">
@@ -22878,7 +22878,7 @@
       <x:c r="BL73" t="str">
         <x:v>false</x:v>
       </x:c>
-      <x:c r="BM73" t="str"/>
+      <x:c r="BM73"/>
     </x:row>
     <x:row r="74" ht="58" customHeight="1">
       <x:c r="A74" t="str">
@@ -23069,7 +23069,7 @@
       <x:c r="BL74" t="str">
         <x:v>false</x:v>
       </x:c>
-      <x:c r="BM74" t="str"/>
+      <x:c r="BM74"/>
     </x:row>
     <x:row r="75" ht="58" customHeight="1">
       <x:c r="A75" t="str">
@@ -23260,7 +23260,7 @@
       <x:c r="BL75" t="str">
         <x:v>false</x:v>
       </x:c>
-      <x:c r="BM75" t="str"/>
+      <x:c r="BM75"/>
     </x:row>
     <x:row r="76" ht="58" customHeight="1">
       <x:c r="A76" t="str">
@@ -23447,7 +23447,7 @@
       <x:c r="BL76" t="str">
         <x:v>false</x:v>
       </x:c>
-      <x:c r="BM76" t="str"/>
+      <x:c r="BM76"/>
     </x:row>
     <x:row r="77" ht="58" customHeight="1">
       <x:c r="A77" t="str">
@@ -23634,7 +23634,7 @@
       <x:c r="BL77" t="str">
         <x:v>false</x:v>
       </x:c>
-      <x:c r="BM77" t="str"/>
+      <x:c r="BM77"/>
     </x:row>
     <x:row r="78" ht="58" customHeight="1">
       <x:c r="A78" t="str">
@@ -23821,7 +23821,7 @@
       <x:c r="BL78" t="str">
         <x:v>false</x:v>
       </x:c>
-      <x:c r="BM78" t="str"/>
+      <x:c r="BM78"/>
     </x:row>
     <x:row r="79">
       <x:c r="A79" t="str">
@@ -24014,7 +24014,7 @@
       <x:c r="BL79" t="str">
         <x:v>false</x:v>
       </x:c>
-      <x:c r="BM79" t="str"/>
+      <x:c r="BM79"/>
     </x:row>
   </x:sheetData>
   <x:dataValidations count="5">
@@ -24036,7 +24036,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R95465e0d0a6042d3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2550f3c675ef4ff1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -24591,7 +24591,7 @@
       <x:c r="CE2" t="str">
         <x:v>false</x:v>
       </x:c>
-      <x:c r="CF2" t="str"/>
+      <x:c r="CF2"/>
     </x:row>
     <x:row r="3" ht="58" customHeight="1">
       <x:c r="A3" t="str">
@@ -24833,7 +24833,7 @@
       <x:c r="CE3" t="str">
         <x:v>false</x:v>
       </x:c>
-      <x:c r="CF3" t="str"/>
+      <x:c r="CF3"/>
     </x:row>
     <x:row r="4" ht="58" customHeight="1">
       <x:c r="A4" t="str">
@@ -25075,7 +25075,7 @@
       <x:c r="CE4" t="str">
         <x:v>false</x:v>
       </x:c>
-      <x:c r="CF4" t="str"/>
+      <x:c r="CF4"/>
     </x:row>
     <x:row r="5" ht="58" customHeight="1">
       <x:c r="A5" t="str">
@@ -25317,7 +25317,7 @@
       <x:c r="CE5" t="str">
         <x:v>false</x:v>
       </x:c>
-      <x:c r="CF5" t="str"/>
+      <x:c r="CF5"/>
     </x:row>
     <x:row r="6" ht="58" customHeight="1">
       <x:c r="A6" t="str">
@@ -25559,7 +25559,7 @@
       <x:c r="CE6" t="str">
         <x:v>false</x:v>
       </x:c>
-      <x:c r="CF6" t="str"/>
+      <x:c r="CF6"/>
     </x:row>
     <x:row r="7" ht="58" customHeight="1">
       <x:c r="A7" t="str">
@@ -25801,7 +25801,7 @@
       <x:c r="CE7" t="str">
         <x:v>false</x:v>
       </x:c>
-      <x:c r="CF7" t="str"/>
+      <x:c r="CF7"/>
     </x:row>
     <x:row r="8" ht="58" customHeight="1">
       <x:c r="A8" t="str">
@@ -26043,7 +26043,7 @@
       <x:c r="CE8" t="str">
         <x:v>false</x:v>
       </x:c>
-      <x:c r="CF8" t="str"/>
+      <x:c r="CF8"/>
     </x:row>
     <x:row r="9" ht="58" customHeight="1">
       <x:c r="A9" t="str">
@@ -26283,7 +26283,7 @@
       <x:c r="CE9" t="str">
         <x:v>false</x:v>
       </x:c>
-      <x:c r="CF9" t="str"/>
+      <x:c r="CF9"/>
     </x:row>
     <x:row r="10" ht="58" customHeight="1">
       <x:c r="A10" t="str">
@@ -26529,7 +26529,7 @@
       <x:c r="CE10" t="str">
         <x:v>false</x:v>
       </x:c>
-      <x:c r="CF10" t="str"/>
+      <x:c r="CF10"/>
     </x:row>
     <x:row r="11" ht="58" customHeight="1">
       <x:c r="A11" t="str">
@@ -26777,7 +26777,7 @@
       <x:c r="CE11" t="str">
         <x:v>false</x:v>
       </x:c>
-      <x:c r="CF11" t="str"/>
+      <x:c r="CF11"/>
     </x:row>
     <x:row r="12" ht="58" customHeight="1">
       <x:c r="A12" t="str">
@@ -27025,7 +27025,7 @@
       <x:c r="CE12" t="str">
         <x:v>false</x:v>
       </x:c>
-      <x:c r="CF12" t="str"/>
+      <x:c r="CF12"/>
     </x:row>
     <x:row r="13" ht="58" customHeight="1">
       <x:c r="A13" t="str">
@@ -27273,7 +27273,7 @@
       <x:c r="CE13" t="str">
         <x:v>false</x:v>
       </x:c>
-      <x:c r="CF13" t="str"/>
+      <x:c r="CF13"/>
     </x:row>
     <x:row r="14" ht="58" customHeight="1">
       <x:c r="A14" t="str">
@@ -27521,7 +27521,7 @@
       <x:c r="CE14" t="str">
         <x:v>false</x:v>
       </x:c>
-      <x:c r="CF14" t="str"/>
+      <x:c r="CF14"/>
     </x:row>
     <x:row r="15" ht="58" customHeight="1">
       <x:c r="A15" t="str">
@@ -27769,7 +27769,7 @@
       <x:c r="CE15" t="str">
         <x:v>false</x:v>
       </x:c>
-      <x:c r="CF15" t="str"/>
+      <x:c r="CF15"/>
     </x:row>
     <x:row r="16" ht="58" customHeight="1">
       <x:c r="A16" t="str">
@@ -28015,7 +28015,7 @@
       <x:c r="CE16" t="str">
         <x:v>false</x:v>
       </x:c>
-      <x:c r="CF16" t="str"/>
+      <x:c r="CF16"/>
     </x:row>
     <x:row r="17" ht="58" customHeight="1">
       <x:c r="A17" t="str">
@@ -28263,7 +28263,7 @@
       <x:c r="CE17" t="str">
         <x:v>false</x:v>
       </x:c>
-      <x:c r="CF17" t="str"/>
+      <x:c r="CF17"/>
     </x:row>
     <x:row r="18" ht="58" customHeight="1">
       <x:c r="A18" t="str">
@@ -28511,7 +28511,7 @@
       <x:c r="CE18" t="str">
         <x:v>false</x:v>
       </x:c>
-      <x:c r="CF18" t="str"/>
+      <x:c r="CF18"/>
     </x:row>
     <x:row r="19" ht="58" customHeight="1">
       <x:c r="A19" t="str">
@@ -28759,7 +28759,7 @@
       <x:c r="CE19" t="str">
         <x:v>false</x:v>
       </x:c>
-      <x:c r="CF19" t="str"/>
+      <x:c r="CF19"/>
     </x:row>
     <x:row r="20" ht="58" customHeight="1">
       <x:c r="A20" t="str">
@@ -29007,7 +29007,7 @@
       <x:c r="CE20" t="str">
         <x:v>false</x:v>
       </x:c>
-      <x:c r="CF20" t="str"/>
+      <x:c r="CF20"/>
     </x:row>
     <x:row r="21" ht="58" customHeight="1">
       <x:c r="A21" t="str">
@@ -29257,7 +29257,7 @@
       <x:c r="CE21" t="str">
         <x:v>false</x:v>
       </x:c>
-      <x:c r="CF21" t="str"/>
+      <x:c r="CF21"/>
     </x:row>
     <x:row r="22" ht="58" customHeight="1">
       <x:c r="A22" t="str">
@@ -29507,7 +29507,7 @@
       <x:c r="CE22" t="str">
         <x:v>false</x:v>
       </x:c>
-      <x:c r="CF22" t="str"/>
+      <x:c r="CF22"/>
     </x:row>
     <x:row r="23" ht="58" customHeight="1">
       <x:c r="A23" t="str">
@@ -29757,7 +29757,7 @@
       <x:c r="CE23" t="str">
         <x:v>false</x:v>
       </x:c>
-      <x:c r="CF23" t="str"/>
+      <x:c r="CF23"/>
     </x:row>
     <x:row r="24" ht="58" customHeight="1">
       <x:c r="A24" t="str">
@@ -30007,7 +30007,7 @@
       <x:c r="CE24" t="str">
         <x:v>false</x:v>
       </x:c>
-      <x:c r="CF24" t="str"/>
+      <x:c r="CF24"/>
     </x:row>
     <x:row r="25" ht="58" customHeight="1">
       <x:c r="A25" t="str">
@@ -30257,7 +30257,7 @@
       <x:c r="CE25" t="str">
         <x:v>false</x:v>
       </x:c>
-      <x:c r="CF25" t="str"/>
+      <x:c r="CF25"/>
     </x:row>
     <x:row r="26" ht="58" customHeight="1">
       <x:c r="A26" t="str">
@@ -30507,7 +30507,7 @@
       <x:c r="CE26" t="str">
         <x:v>false</x:v>
       </x:c>
-      <x:c r="CF26" t="str"/>
+      <x:c r="CF26"/>
     </x:row>
     <x:row r="27" ht="58" customHeight="1">
       <x:c r="A27" t="str">
@@ -30757,7 +30757,7 @@
       <x:c r="CE27" t="str">
         <x:v>false</x:v>
       </x:c>
-      <x:c r="CF27" t="str"/>
+      <x:c r="CF27"/>
     </x:row>
     <x:row r="28" ht="58" customHeight="1">
       <x:c r="A28" t="str">
@@ -31007,7 +31007,7 @@
       <x:c r="CE28" t="str">
         <x:v>false</x:v>
       </x:c>
-      <x:c r="CF28" t="str"/>
+      <x:c r="CF28"/>
     </x:row>
     <x:row r="29" ht="58" customHeight="1">
       <x:c r="A29" t="str">
@@ -31257,7 +31257,7 @@
       <x:c r="CE29" t="str">
         <x:v>false</x:v>
       </x:c>
-      <x:c r="CF29" t="str"/>
+      <x:c r="CF29"/>
     </x:row>
     <x:row r="30" ht="58" customHeight="1">
       <x:c r="A30" t="str">
@@ -31507,7 +31507,7 @@
       <x:c r="CE30" t="str">
         <x:v>false</x:v>
       </x:c>
-      <x:c r="CF30" t="str"/>
+      <x:c r="CF30"/>
     </x:row>
     <x:row r="31" ht="58" customHeight="1">
       <x:c r="A31" t="str">
@@ -31757,7 +31757,7 @@
       <x:c r="CE31" t="str">
         <x:v>false</x:v>
       </x:c>
-      <x:c r="CF31" t="str"/>
+      <x:c r="CF31"/>
     </x:row>
     <x:row r="32" ht="58" customHeight="1">
       <x:c r="A32" t="str">
@@ -32007,7 +32007,7 @@
       <x:c r="CE32" t="str">
         <x:v>false</x:v>
       </x:c>
-      <x:c r="CF32" t="str"/>
+      <x:c r="CF32"/>
     </x:row>
     <x:row r="33" ht="58" customHeight="1">
       <x:c r="A33" t="str">
@@ -32257,7 +32257,7 @@
       <x:c r="CE33" t="str">
         <x:v>false</x:v>
       </x:c>
-      <x:c r="CF33" t="str"/>
+      <x:c r="CF33"/>
     </x:row>
     <x:row r="34" ht="58" customHeight="1">
       <x:c r="A34" t="str">
@@ -32507,7 +32507,7 @@
       <x:c r="CE34" t="str">
         <x:v>false</x:v>
       </x:c>
-      <x:c r="CF34" t="str"/>
+      <x:c r="CF34"/>
     </x:row>
     <x:row r="35" ht="58" customHeight="1">
       <x:c r="A35" t="str">
@@ -32757,7 +32757,7 @@
       <x:c r="CE35" t="str">
         <x:v>false</x:v>
       </x:c>
-      <x:c r="CF35" t="str"/>
+      <x:c r="CF35"/>
     </x:row>
     <x:row r="36" ht="58" customHeight="1">
       <x:c r="A36" t="str">
@@ -33007,7 +33007,7 @@
       <x:c r="CE36" t="str">
         <x:v>false</x:v>
       </x:c>
-      <x:c r="CF36" t="str"/>
+      <x:c r="CF36"/>
     </x:row>
     <x:row r="37" ht="58" customHeight="1">
       <x:c r="A37" t="str">
@@ -33257,7 +33257,7 @@
       <x:c r="CE37" t="str">
         <x:v>false</x:v>
       </x:c>
-      <x:c r="CF37" t="str"/>
+      <x:c r="CF37"/>
     </x:row>
     <x:row r="38" ht="58" customHeight="1">
       <x:c r="A38" t="str">
@@ -33507,7 +33507,7 @@
       <x:c r="CE38" t="str">
         <x:v>false</x:v>
       </x:c>
-      <x:c r="CF38" t="str"/>
+      <x:c r="CF38"/>
     </x:row>
     <x:row r="39" ht="58" customHeight="1">
       <x:c r="A39" t="str">
@@ -33757,7 +33757,7 @@
       <x:c r="CE39" t="str">
         <x:v>false</x:v>
       </x:c>
-      <x:c r="CF39" t="str"/>
+      <x:c r="CF39"/>
     </x:row>
     <x:row r="40" ht="58" customHeight="1">
       <x:c r="A40" t="str">
@@ -34007,7 +34007,7 @@
       <x:c r="CE40" t="str">
         <x:v>false</x:v>
       </x:c>
-      <x:c r="CF40" t="str"/>
+      <x:c r="CF40"/>
     </x:row>
     <x:row r="41" ht="58" customHeight="1">
       <x:c r="A41" t="str">
@@ -34257,7 +34257,7 @@
       <x:c r="CE41" t="str">
         <x:v>false</x:v>
       </x:c>
-      <x:c r="CF41" t="str"/>
+      <x:c r="CF41"/>
     </x:row>
     <x:row r="42" ht="58" customHeight="1">
       <x:c r="A42" t="str">
@@ -34507,7 +34507,7 @@
       <x:c r="CE42" t="str">
         <x:v>false</x:v>
       </x:c>
-      <x:c r="CF42" t="str"/>
+      <x:c r="CF42"/>
     </x:row>
     <x:row r="43" ht="58" customHeight="1">
       <x:c r="A43" t="str">
@@ -34757,7 +34757,7 @@
       <x:c r="CE43" t="str">
         <x:v>false</x:v>
       </x:c>
-      <x:c r="CF43" t="str"/>
+      <x:c r="CF43"/>
     </x:row>
     <x:row r="44" ht="58" customHeight="1">
       <x:c r="A44" t="str">
@@ -35007,7 +35007,7 @@
       <x:c r="CE44" t="str">
         <x:v>false</x:v>
       </x:c>
-      <x:c r="CF44" t="str"/>
+      <x:c r="CF44"/>
     </x:row>
     <x:row r="45" ht="58" customHeight="1">
       <x:c r="A45" t="str">
@@ -35257,7 +35257,7 @@
       <x:c r="CE45" t="str">
         <x:v>false</x:v>
       </x:c>
-      <x:c r="CF45" t="str"/>
+      <x:c r="CF45"/>
     </x:row>
     <x:row r="46" ht="58" customHeight="1">
       <x:c r="A46" t="str">
@@ -35507,7 +35507,7 @@
       <x:c r="CE46" t="str">
         <x:v>false</x:v>
       </x:c>
-      <x:c r="CF46" t="str"/>
+      <x:c r="CF46"/>
     </x:row>
     <x:row r="47" ht="58" customHeight="1">
       <x:c r="A47" t="str">
@@ -35757,7 +35757,7 @@
       <x:c r="CE47" t="str">
         <x:v>false</x:v>
       </x:c>
-      <x:c r="CF47" t="str"/>
+      <x:c r="CF47"/>
     </x:row>
     <x:row r="48" ht="58" customHeight="1">
       <x:c r="A48" t="str">
@@ -36007,7 +36007,7 @@
       <x:c r="CE48" t="str">
         <x:v>false</x:v>
       </x:c>
-      <x:c r="CF48" t="str"/>
+      <x:c r="CF48"/>
     </x:row>
     <x:row r="49" ht="58" customHeight="1">
       <x:c r="A49" t="str">
@@ -36257,7 +36257,7 @@
       <x:c r="CE49" t="str">
         <x:v>false</x:v>
       </x:c>
-      <x:c r="CF49" t="str"/>
+      <x:c r="CF49"/>
     </x:row>
     <x:row r="50" ht="58" customHeight="1">
       <x:c r="A50" t="str">
@@ -36507,7 +36507,7 @@
       <x:c r="CE50" t="str">
         <x:v>false</x:v>
       </x:c>
-      <x:c r="CF50" t="str"/>
+      <x:c r="CF50"/>
     </x:row>
     <x:row r="51" ht="58" customHeight="1">
       <x:c r="A51" t="str">
@@ -36757,7 +36757,7 @@
       <x:c r="CE51" t="str">
         <x:v>false</x:v>
       </x:c>
-      <x:c r="CF51" t="str"/>
+      <x:c r="CF51"/>
     </x:row>
     <x:row r="52" ht="58" customHeight="1">
       <x:c r="A52" t="str">
@@ -37007,7 +37007,7 @@
       <x:c r="CE52" t="str">
         <x:v>false</x:v>
       </x:c>
-      <x:c r="CF52" t="str"/>
+      <x:c r="CF52"/>
     </x:row>
     <x:row r="53" ht="58" customHeight="1">
       <x:c r="A53" t="str">
@@ -37257,7 +37257,7 @@
       <x:c r="CE53" t="str">
         <x:v>false</x:v>
       </x:c>
-      <x:c r="CF53" t="str"/>
+      <x:c r="CF53"/>
     </x:row>
     <x:row r="54" ht="58" customHeight="1">
       <x:c r="A54" t="str">
@@ -37507,7 +37507,7 @@
       <x:c r="CE54" t="str">
         <x:v>false</x:v>
       </x:c>
-      <x:c r="CF54" t="str"/>
+      <x:c r="CF54"/>
     </x:row>
     <x:row r="55" ht="58" customHeight="1">
       <x:c r="A55" t="str">
@@ -37757,7 +37757,7 @@
       <x:c r="CE55" t="str">
         <x:v>false</x:v>
       </x:c>
-      <x:c r="CF55" t="str"/>
+      <x:c r="CF55"/>
     </x:row>
     <x:row r="56" ht="58" customHeight="1">
       <x:c r="A56" t="str">
@@ -38007,7 +38007,7 @@
       <x:c r="CE56" t="str">
         <x:v>false</x:v>
       </x:c>
-      <x:c r="CF56" t="str"/>
+      <x:c r="CF56"/>
     </x:row>
     <x:row r="57" ht="58" customHeight="1">
       <x:c r="A57" t="str">
@@ -38257,7 +38257,7 @@
       <x:c r="CE57" t="str">
         <x:v>false</x:v>
       </x:c>
-      <x:c r="CF57" t="str"/>
+      <x:c r="CF57"/>
     </x:row>
     <x:row r="58" ht="58" customHeight="1">
       <x:c r="A58" t="str">
@@ -38507,7 +38507,7 @@
       <x:c r="CE58" t="str">
         <x:v>false</x:v>
       </x:c>
-      <x:c r="CF58" t="str"/>
+      <x:c r="CF58"/>
     </x:row>
     <x:row r="59" ht="58" customHeight="1">
       <x:c r="A59" t="str">
@@ -38757,7 +38757,7 @@
       <x:c r="CE59" t="str">
         <x:v>false</x:v>
       </x:c>
-      <x:c r="CF59" t="str"/>
+      <x:c r="CF59"/>
     </x:row>
     <x:row r="60" ht="58" customHeight="1">
       <x:c r="A60" t="str">
@@ -39007,7 +39007,7 @@
       <x:c r="CE60" t="str">
         <x:v>false</x:v>
       </x:c>
-      <x:c r="CF60" t="str"/>
+      <x:c r="CF60"/>
     </x:row>
     <x:row r="61" ht="58" customHeight="1">
       <x:c r="A61" t="str">
@@ -39257,7 +39257,7 @@
       <x:c r="CE61" t="str">
         <x:v>false</x:v>
       </x:c>
-      <x:c r="CF61" t="str"/>
+      <x:c r="CF61"/>
     </x:row>
     <x:row r="62" ht="58" customHeight="1">
       <x:c r="A62" t="str">
@@ -39507,7 +39507,7 @@
       <x:c r="CE62" t="str">
         <x:v>false</x:v>
       </x:c>
-      <x:c r="CF62" t="str"/>
+      <x:c r="CF62"/>
     </x:row>
     <x:row r="63" ht="58" customHeight="1">
       <x:c r="A63" t="str">
@@ -39757,7 +39757,7 @@
       <x:c r="CE63" t="str">
         <x:v>false</x:v>
       </x:c>
-      <x:c r="CF63" t="str"/>
+      <x:c r="CF63"/>
     </x:row>
     <x:row r="64" ht="58" customHeight="1">
       <x:c r="A64" t="str">
@@ -40007,7 +40007,7 @@
       <x:c r="CE64" t="str">
         <x:v>false</x:v>
       </x:c>
-      <x:c r="CF64" t="str"/>
+      <x:c r="CF64"/>
     </x:row>
     <x:row r="65" ht="58" customHeight="1">
       <x:c r="A65" t="str">
@@ -40257,7 +40257,7 @@
       <x:c r="CE65" t="str">
         <x:v>false</x:v>
       </x:c>
-      <x:c r="CF65" t="str"/>
+      <x:c r="CF65"/>
     </x:row>
     <x:row r="66" ht="58" customHeight="1">
       <x:c r="A66" t="str">
@@ -40507,7 +40507,7 @@
       <x:c r="CE66" t="str">
         <x:v>false</x:v>
       </x:c>
-      <x:c r="CF66" t="str"/>
+      <x:c r="CF66"/>
     </x:row>
     <x:row r="67">
       <x:c r="A67" t="str">
@@ -40757,7 +40757,7 @@
       <x:c r="CE67" t="str">
         <x:v>false</x:v>
       </x:c>
-      <x:c r="CF67" t="str"/>
+      <x:c r="CF67"/>
     </x:row>
   </x:sheetData>
   <x:dataValidations count="10">
@@ -40794,7 +40794,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb5ea64be2c924395"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R961ca2f95ee544b9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -41278,7 +41278,7 @@
       <x:c r="BT2" t="str">
         <x:v>false</x:v>
       </x:c>
-      <x:c r="BU2" t="str"/>
+      <x:c r="BU2"/>
     </x:row>
     <x:row r="3" ht="62" customHeight="1">
       <x:c r="A3" t="str">
@@ -41495,7 +41495,7 @@
       <x:c r="BT3" t="str">
         <x:v>false</x:v>
       </x:c>
-      <x:c r="BU3" t="str"/>
+      <x:c r="BU3"/>
     </x:row>
     <x:row r="4" ht="62" customHeight="1">
       <x:c r="A4" t="str">
@@ -41712,7 +41712,7 @@
       <x:c r="BT4" t="str">
         <x:v>false</x:v>
       </x:c>
-      <x:c r="BU4" t="str"/>
+      <x:c r="BU4"/>
     </x:row>
     <x:row r="5" ht="62" customHeight="1">
       <x:c r="A5" t="str">
@@ -41929,7 +41929,7 @@
       <x:c r="BT5" t="str">
         <x:v>false</x:v>
       </x:c>
-      <x:c r="BU5" t="str"/>
+      <x:c r="BU5"/>
     </x:row>
     <x:row r="6" ht="62" customHeight="1">
       <x:c r="A6" t="str">
@@ -42146,7 +42146,7 @@
       <x:c r="BT6" t="str">
         <x:v>false</x:v>
       </x:c>
-      <x:c r="BU6" t="str"/>
+      <x:c r="BU6"/>
     </x:row>
     <x:row r="7" ht="62" customHeight="1">
       <x:c r="A7" t="str">
@@ -42363,7 +42363,7 @@
       <x:c r="BT7" t="str">
         <x:v>false</x:v>
       </x:c>
-      <x:c r="BU7" t="str"/>
+      <x:c r="BU7"/>
     </x:row>
     <x:row r="8" ht="62" customHeight="1">
       <x:c r="A8" t="str">
@@ -42580,7 +42580,7 @@
       <x:c r="BT8" t="str">
         <x:v>false</x:v>
       </x:c>
-      <x:c r="BU8" t="str"/>
+      <x:c r="BU8"/>
     </x:row>
     <x:row r="9" ht="62" customHeight="1">
       <x:c r="A9" t="str">
@@ -42797,7 +42797,7 @@
       <x:c r="BT9" t="str">
         <x:v>false</x:v>
       </x:c>
-      <x:c r="BU9" t="str"/>
+      <x:c r="BU9"/>
     </x:row>
     <x:row r="10" ht="62" customHeight="1">
       <x:c r="A10" t="str">
@@ -43014,7 +43014,7 @@
       <x:c r="BT10" t="str">
         <x:v>false</x:v>
       </x:c>
-      <x:c r="BU10" t="str"/>
+      <x:c r="BU10"/>
     </x:row>
     <x:row r="11" ht="62" customHeight="1">
       <x:c r="A11" t="str">
@@ -43209,7 +43209,7 @@
       <x:c r="BT11" t="str">
         <x:v>false</x:v>
       </x:c>
-      <x:c r="BU11" t="str"/>
+      <x:c r="BU11"/>
     </x:row>
     <x:row r="12" ht="62" customHeight="1">
       <x:c r="A12" t="str">
@@ -43400,7 +43400,7 @@
       <x:c r="BT12" t="str">
         <x:v>false</x:v>
       </x:c>
-      <x:c r="BU12" t="str"/>
+      <x:c r="BU12"/>
     </x:row>
     <x:row r="13" ht="62" customHeight="1">
       <x:c r="A13" t="str">
@@ -43591,7 +43591,7 @@
       <x:c r="BT13" t="str">
         <x:v>false</x:v>
       </x:c>
-      <x:c r="BU13" t="str"/>
+      <x:c r="BU13"/>
     </x:row>
     <x:row r="14" ht="62" customHeight="1">
       <x:c r="A14" t="str">
@@ -43782,7 +43782,7 @@
       <x:c r="BT14" t="str">
         <x:v>false</x:v>
       </x:c>
-      <x:c r="BU14" t="str"/>
+      <x:c r="BU14"/>
     </x:row>
   </x:sheetData>
   <x:dataValidations count="4">
@@ -43801,7 +43801,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3968b3ff70f04d19"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R39291e5246964ba3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/00_Paper_Pool/Paper_Pool.xlsx
+++ b/00_Paper_Pool/Paper_Pool.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Papers" sheetId="1" r:id="R41c2cee264f74f1d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rejected" sheetId="2" r:id="R564b5dae00024532"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Venues" sheetId="3" r:id="Rb62e65650a4b4772"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Keywords" sheetId="4" r:id="R0fa3c7d61e984fbf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Discovery" sheetId="5" r:id="R69289114541541b8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CCF_A_Library" sheetId="6" r:id="R7052b95f5b0a490d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Robotics_Core_Library" sheetId="7" r:id="R25b09cb8c1fa4afe"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Papers" sheetId="1" r:id="R86f01c6dad0e4415"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rejected" sheetId="2" r:id="Rb991b7fdee134239"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Venues" sheetId="3" r:id="Rdd3ba6f2361044fe"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Keywords" sheetId="4" r:id="Rfc90709385e342e3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Discovery" sheetId="5" r:id="Ra1faf7c021804116"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CCF_A_Library" sheetId="6" r:id="Rc96f7f93fef2443e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Robotics_Core_Library" sheetId="7" r:id="Rfd09c41558954595"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -300,7 +300,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="56" name="PapersTable" displayName="PapersTable" ref="A1:BR5" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="60" name="PapersTable" displayName="PapersTable" ref="A1:BR6" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="70">
     <x:tableColumn id="1" name="编号 ID"/>
     <x:tableColumn id="2" name="论文标题 Title"/>
@@ -588,7 +588,7 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="59" name="RoboticsCoreLibraryTable" displayName="RoboticsCoreLibraryTable" ref="A1:BU14" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="61" name="RoboticsCoreLibraryTable" displayName="RoboticsCoreLibraryTable" ref="A1:BU15" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="73">
     <x:tableColumn id="1" name="ID"/>
     <x:tableColumn id="2" name="Title"/>
@@ -1276,7 +1276,7 @@
       <x:c r="BD2" t="str">
         <x:v>Unknown</x:v>
       </x:c>
-      <x:c r="BE2" t="str"/>
+      <x:c r="BE2"/>
       <x:c r="BF2" t="str">
         <x:v>No</x:v>
       </x:c>
@@ -1452,7 +1452,7 @@
       <x:c r="BD3" t="str">
         <x:v>Unknown</x:v>
       </x:c>
-      <x:c r="BE3" t="str"/>
+      <x:c r="BE3"/>
       <x:c r="BF3" t="str">
         <x:v>No</x:v>
       </x:c>
@@ -1628,7 +1628,7 @@
       <x:c r="BD4" t="str">
         <x:v>Unknown</x:v>
       </x:c>
-      <x:c r="BE4" t="str"/>
+      <x:c r="BE4"/>
       <x:c r="BF4" t="str">
         <x:v>No</x:v>
       </x:c>
@@ -1804,7 +1804,7 @@
       <x:c r="BD5" t="str">
         <x:v>Unknown</x:v>
       </x:c>
-      <x:c r="BE5" t="str"/>
+      <x:c r="BE5"/>
       <x:c r="BF5" t="str">
         <x:v>No</x:v>
       </x:c>
@@ -1844,7 +1844,216 @@
       <x:c r="BR5"/>
     </x:row>
     <x:row r="6">
-      <x:c r="AC6" s="7"/>
+      <x:c r="A6" t="str">
+        <x:v>P0005</x:v>
+      </x:c>
+      <x:c r="B6" t="str">
+        <x:v>Do As I Can, Not As I Say: Grounding Language in Robotic Affordances</x:v>
+      </x:c>
+      <x:c r="C6" t="n">
+        <x:v>2022</x:v>
+      </x:c>
+      <x:c r="D6" t="str">
+        <x:v>CoRL</x:v>
+      </x:c>
+      <x:c r="E6" t="str">
+        <x:v>Not CCF A</x:v>
+      </x:c>
+      <x:c r="F6" t="str">
+        <x:v>VLA / Robot Manipulation / Language Grounding</x:v>
+      </x:c>
+      <x:c r="G6" t="str">
+        <x:v>Language-conditioned planning / affordance grounding</x:v>
+      </x:c>
+      <x:c r="H6" t="str">
+        <x:v>LLMs lack embodiment and execution grounding for long-horizon robot instructions.</x:v>
+      </x:c>
+      <x:c r="I6" t="str">
+        <x:v>Text-only planning can propose infeasible skills; prior systems do not jointly score usefulness and current-state feasibility.</x:v>
+      </x:c>
+      <x:c r="J6" t="str">
+        <x:v>SayCan multiplies LLM skill usefulness with affordance/value feasibility and replans after every executed skill.</x:v>
+      </x:c>
+      <x:c r="K6" t="str">
+        <x:v>Interpretable language-conditioned skill composition grounded by learned value functions; 101-task real/mock kitchen evaluation.</x:v>
+      </x:c>
+      <x:c r="L6" t="str">
+        <x:v>Everyday Robots mobile manipulator; two-finger gripper</x:v>
+      </x:c>
+      <x:c r="M6" t="str">
+        <x:v>Single arm</x:v>
+      </x:c>
+      <x:c r="N6" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="O6" t="str">
+        <x:v>RGB observation plus language instruction and robot state</x:v>
+      </x:c>
+      <x:c r="P6" t="str">
+        <x:v>Skill-level pick/place/navigation/drawer actions; low-level 7-DoF arm and gripper control</x:v>
+      </x:c>
+      <x:c r="Q6" t="str">
+        <x:v>68k demonstrations + 12k successful autonomous episodes (official blog/project report); SayCan dataset v0</x:v>
+      </x:c>
+      <x:c r="R6" t="str">
+        <x:v>101 natural-language instructions; Mock Kitchen and Real Kitchen; 7 instruction families</x:v>
+      </x:c>
+      <x:c r="S6" t="str">
+        <x:v>https://research.google/pubs/do-as-i-can-not-as-i-say-grounding-language-in-robotic-affordances/</x:v>
+      </x:c>
+      <x:c r="T6" t="str">
+        <x:v>https://say-can.github.io/</x:v>
+      </x:c>
+      <x:c r="U6" t="str">
+        <x:v>Partial - official tabletop simulation released</x:v>
+      </x:c>
+      <x:c r="V6" t="str">
+        <x:v>https://github.com/google-research/google-research/tree/master/saycan</x:v>
+      </x:c>
+      <x:c r="W6" t="str">
+        <x:v>Not released as complete PaLM/Everyday Robots stack</x:v>
+      </x:c>
+      <x:c r="X6" t="str">
+        <x:v>Partial - SayCan dataset v0; full training dump not confirmed</x:v>
+      </x:c>
+      <x:c r="Y6" t="str">
+        <x:v>Official tabletop environment available; original kitchen stack not fully reproducible</x:v>
+      </x:c>
+      <x:c r="Z6" t="str">
+        <x:v>L1</x:v>
+      </x:c>
+      <x:c r="AA6" t="str">
+        <x:v>L1 / foundational; direct inspiration for feasibility scoring, bimanual joint affordance and recovery</x:v>
+      </x:c>
+      <x:c r="AB6" t="str">
+        <x:v>Full-text Evidence A. 551 skills, 7 families, 17 objects; Table 2 Mock 84/74 and Real 81/60.</x:v>
+      </x:c>
+      <x:c r="AC6" s="7" t="str">
+        <x:v>2026-09-22</x:v>
+      </x:c>
+      <x:c r="AD6" t="str">
+        <x:v>VLA</x:v>
+      </x:c>
+      <x:c r="AE6" t="str">
+        <x:v>02_Papers/01_VLA/SayCan.md</x:v>
+      </x:c>
+      <x:c r="AF6" t="n">
+        <x:v>523</x:v>
+      </x:c>
+      <x:c r="AG6" t="str">
+        <x:v>OpenAlex</x:v>
+      </x:c>
+      <x:c r="AH6" t="str">
+        <x:v>2026-09-22</x:v>
+      </x:c>
+      <x:c r="AI6" t="str">
+        <x:v>LLMs have semantic knowledge but no embodiment or current-state grounding.</x:v>
+      </x:c>
+      <x:c r="AJ6" t="str">
+        <x:v>Long-horizon abstract instructions require both useful decomposition and physically feasible execution.</x:v>
+      </x:c>
+      <x:c r="AK6" t="str">
+        <x:v>SayCan: p(cπ|s,ℓπ) × p(ℓπ|i), receding-horizon skill selection.</x:v>
+      </x:c>
+      <x:c r="AL6" t="str">
+        <x:v>101 instructions across 7 families; mock and real office kitchens; 15 objects/5 locations.</x:v>
+      </x:c>
+      <x:c r="AM6" t="str">
+        <x:v>No VF; Generative; FLAN-SayCan; BC NL; BC USE; PaLM scale ablations.</x:v>
+      </x:c>
+      <x:c r="AN6" t="str">
+        <x:v>Affordance-grounded interpretable LLM planning over pretrained skills.</x:v>
+      </x:c>
+      <x:c r="AO6" t="str">
+        <x:v>Everyday Robots mobile manipulator; 551 candidate skills; PaLM 540B; Mock/Real Kitchen.</x:v>
+      </x:c>
+      <x:c r="AP6" t="str">
+        <x:v>Mock 84% plan / 74% execute; Real 81% / 60%; FLAN 70% / 61%; drawer 100% / 33%.</x:v>
+      </x:c>
+      <x:c r="AQ6" t="str">
+        <x:v>Fixed skill library; value-function/current-step feedback; low-level execution and recovery remain limited.</x:v>
+      </x:c>
+      <x:c r="AR6" t="str">
+        <x:v>Open-ended skill synthesis, continuous/contact grounding, closed-loop verification/recovery, bimanual joint feasibility.</x:v>
+      </x:c>
+      <x:c r="AS6" t="str">
+        <x:v>Use dual language-usefulness and joint-arm feasibility scoring; add post-action verification and replanning for NERO.</x:v>
+      </x:c>
+      <x:c r="AT6" t="str">
+        <x:v>VLA; Robot Manipulation; Language Grounding; Affordance; Long-horizon; Planning; RL; IL; Sim2Real</x:v>
+      </x:c>
+      <x:c r="AU6" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="AV6" t="str">
+        <x:v>Joint-affordance SayCan; VLA feasibility veto; failure-aware receding-horizon recovery; affordance-calibrated sim2real library.</x:v>
+      </x:c>
+      <x:c r="AW6" t="str">
+        <x:v>No VF, Generative, BC NL/USE, PaLM 8B/62B/540B, FLAN 137B; drawer/CoT/multilingual appendices.</x:v>
+      </x:c>
+      <x:c r="AX6" t="str">
+        <x:v>Plan-execute gap; wrong object/negation; drawer manipulation and incomplete close; embodiment-specific failures.</x:v>
+      </x:c>
+      <x:c r="AY6" t="str">
+        <x:v>OpenAlex Work W4224912544</x:v>
+      </x:c>
+      <x:c r="AZ6" t="str">
+        <x:v>Google Research publication; arXiv HTML 2204.01691; CoRL/PMLR; say-can.github.io; Google Research blog; official google-research/saycan</x:v>
+      </x:c>
+      <x:c r="BA6" t="str">
+        <x:v>A-Upgraded</x:v>
+      </x:c>
+      <x:c r="BB6" t="str">
+        <x:v>Available - Verified</x:v>
+      </x:c>
+      <x:c r="BC6" t="str">
+        <x:v>Partial</x:v>
+      </x:c>
+      <x:c r="BD6" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="BE6" t="str">
+        <x:v>https://arxiv.org/html/2204.01691</x:v>
+      </x:c>
+      <x:c r="BF6" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="BG6" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="BH6" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="BI6" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="BJ6" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="BK6" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="BL6" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="BM6" t="str">
+        <x:v>OpenAlex matched</x:v>
+      </x:c>
+      <x:c r="BN6" t="str">
+        <x:v>Verified - 10.48550/arXiv.2204.01691</x:v>
+      </x:c>
+      <x:c r="BO6" t="str">
+        <x:v>Verified - 2204.01691</x:v>
+      </x:c>
+      <x:c r="BP6" t="str">
+        <x:v>Completed - Full text read</x:v>
+      </x:c>
+      <x:c r="BQ6" t="str">
+        <x:v>true</x:v>
+      </x:c>
+      <x:c r="BR6" t="str">
+        <x:v>Completed-A</x:v>
+      </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="AC7" s="7"/>
@@ -4854,7 +5063,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re5753606751f4e58"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2c8b9cc21c0e4685"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8150,7 +8359,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb0a7614ef9b646ab"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R24875c2dbfc745b9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8501,7 +8710,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1e8501099a1a4f77"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6ae14747bf124552"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9247,7 +9456,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R89abe657fca74772"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R148d6e9fc32646c4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -24036,7 +24245,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2550f3c675ef4ff1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ref9e2238cf614bf0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -40794,7 +41003,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R961ca2f95ee544b9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf1420b6b070443d2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -41241,7 +41450,7 @@
       <x:c r="BG2" t="str">
         <x:v>Multiple real-world setups are shown; exact hardware inventory not extracted at abstract/project level</x:v>
       </x:c>
-      <x:c r="BH2" t="str"/>
+      <x:c r="BH2"/>
       <x:c r="BI2" t="str">
         <x:v>No</x:v>
       </x:c>
@@ -41458,7 +41667,7 @@
       <x:c r="BG3" t="str">
         <x:v>Dual robot arms; exact platform pending full-paper check</x:v>
       </x:c>
-      <x:c r="BH3" t="str"/>
+      <x:c r="BH3"/>
       <x:c r="BI3" t="str">
         <x:v>No</x:v>
       </x:c>
@@ -41675,7 +41884,7 @@
       <x:c r="BG4" t="str">
         <x:v>Bimanual gripper system; exact model pending full-paper check</x:v>
       </x:c>
-      <x:c r="BH4" t="str"/>
+      <x:c r="BH4"/>
       <x:c r="BI4" t="str">
         <x:v>No</x:v>
       </x:c>
@@ -41892,7 +42101,7 @@
       <x:c r="BG5" t="str">
         <x:v>Dexterous robotic hand</x:v>
       </x:c>
-      <x:c r="BH5" t="str"/>
+      <x:c r="BH5"/>
       <x:c r="BI5" t="str">
         <x:v>No</x:v>
       </x:c>
@@ -42109,7 +42318,7 @@
       <x:c r="BG6" t="str">
         <x:v>Simulation plus real-world replication</x:v>
       </x:c>
-      <x:c r="BH6" t="str"/>
+      <x:c r="BH6"/>
       <x:c r="BI6" t="str">
         <x:v>No</x:v>
       </x:c>
@@ -42326,7 +42535,7 @@
       <x:c r="BG7" t="str">
         <x:v>Dual robot arms; exact model pending full-paper check</x:v>
       </x:c>
-      <x:c r="BH7" t="str"/>
+      <x:c r="BH7"/>
       <x:c r="BI7" t="str">
         <x:v>No</x:v>
       </x:c>
@@ -42543,7 +42752,7 @@
       <x:c r="BG8" t="str">
         <x:v>Robot arm with visuotactile end effector</x:v>
       </x:c>
-      <x:c r="BH8" t="str"/>
+      <x:c r="BH8"/>
       <x:c r="BI8" t="str">
         <x:v>No</x:v>
       </x:c>
@@ -42760,7 +42969,7 @@
       <x:c r="BG9" t="str">
         <x:v>Multiple robotic arms</x:v>
       </x:c>
-      <x:c r="BH9" t="str"/>
+      <x:c r="BH9"/>
       <x:c r="BI9" t="str">
         <x:v>No</x:v>
       </x:c>
@@ -42977,7 +43186,7 @@
       <x:c r="BG10" t="str">
         <x:v>Multiple hand geometries</x:v>
       </x:c>
-      <x:c r="BH10" t="str"/>
+      <x:c r="BH10"/>
       <x:c r="BI10" t="str">
         <x:v>No</x:v>
       </x:c>
@@ -43172,7 +43381,7 @@
       <x:c r="BG11" t="str">
         <x:v>Unknown</x:v>
       </x:c>
-      <x:c r="BH11" t="str"/>
+      <x:c r="BH11"/>
       <x:c r="BI11" t="str">
         <x:v>No</x:v>
       </x:c>
@@ -43363,7 +43572,7 @@
       <x:c r="BG12" t="str">
         <x:v>Unknown</x:v>
       </x:c>
-      <x:c r="BH12" t="str"/>
+      <x:c r="BH12"/>
       <x:c r="BI12" t="str">
         <x:v>No</x:v>
       </x:c>
@@ -43554,7 +43763,7 @@
       <x:c r="BG13" t="str">
         <x:v>Unknown</x:v>
       </x:c>
-      <x:c r="BH13" t="str"/>
+      <x:c r="BH13"/>
       <x:c r="BI13" t="str">
         <x:v>No</x:v>
       </x:c>
@@ -43745,7 +43954,7 @@
       <x:c r="BG14" t="str">
         <x:v>Unknown</x:v>
       </x:c>
-      <x:c r="BH14" t="str"/>
+      <x:c r="BH14"/>
       <x:c r="BI14" t="str">
         <x:v>No</x:v>
       </x:c>
@@ -43783,6 +43992,227 @@
         <x:v>false</x:v>
       </x:c>
       <x:c r="BU14"/>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" t="str">
+        <x:v>R014</x:v>
+      </x:c>
+      <x:c r="B15" t="str">
+        <x:v>Do As I Can, Not As I Say: Grounding Language in Robotic Affordances</x:v>
+      </x:c>
+      <x:c r="C15" t="str">
+        <x:v>Michael Ahn et al.</x:v>
+      </x:c>
+      <x:c r="D15" t="n">
+        <x:v>2022</x:v>
+      </x:c>
+      <x:c r="E15" t="str">
+        <x:v>CoRL</x:v>
+      </x:c>
+      <x:c r="F15" t="str">
+        <x:v>Robotics Core Venue</x:v>
+      </x:c>
+      <x:c r="G15" t="str">
+        <x:v>Full Conference Paper; PMLR 205</x:v>
+      </x:c>
+      <x:c r="H15" t="str">
+        <x:v>Not CCF A</x:v>
+      </x:c>
+      <x:c r="I15" t="str">
+        <x:v>VLA / Robot Manipulation / Language Grounding</x:v>
+      </x:c>
+      <x:c r="J15" t="str">
+        <x:v>Language-conditioned planning / affordance grounding</x:v>
+      </x:c>
+      <x:c r="K15" t="str">
+        <x:v>VLA; Affordance; Long-horizon; Planning; Robot Learning</x:v>
+      </x:c>
+      <x:c r="L15" t="str">
+        <x:v>LLMs lack embodiment and execution grounding.</x:v>
+      </x:c>
+      <x:c r="M15" t="str">
+        <x:v>Multiplicative language-usefulness and affordance-feasibility scoring over skills.</x:v>
+      </x:c>
+      <x:c r="N15" t="str">
+        <x:v>Say + Can; receding-horizon selection.</x:v>
+      </x:c>
+      <x:c r="O15" t="str">
+        <x:v>https://research.google/pubs/do-as-i-can-not-as-i-say-grounding-language-in-robotic-affordances/</x:v>
+      </x:c>
+      <x:c r="P15" t="str">
+        <x:v>https://say-can.github.io/</x:v>
+      </x:c>
+      <x:c r="Q15" t="str">
+        <x:v>https://github.com/google-research/google-research/tree/master/saycan</x:v>
+      </x:c>
+      <x:c r="R15" t="str">
+        <x:v>Partial - official tabletop simulation</x:v>
+      </x:c>
+      <x:c r="S15" t="str">
+        <x:v>Not released as complete original stack</x:v>
+      </x:c>
+      <x:c r="T15" t="str">
+        <x:v>SayCan dataset v0; 68k demos/12k successful episodes reported by official sources</x:v>
+      </x:c>
+      <x:c r="U15" t="str">
+        <x:v>Everyday Robots mobile manipulator</x:v>
+      </x:c>
+      <x:c r="V15" t="str">
+        <x:v>Single arm / two-finger gripper</x:v>
+      </x:c>
+      <x:c r="W15" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="X15" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="Y15" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="Z15" t="str">
+        <x:v>Official full paper, project page, PMLR and code entry verified</x:v>
+      </x:c>
+      <x:c r="AA15" t="str">
+        <x:v>2026-09-22</x:v>
+      </x:c>
+      <x:c r="AB15" t="str">
+        <x:v>Full-text Evidence A; Table 2: Mock 84/74, Real 81/60; 551 skills, 7 families, 17 objects.</x:v>
+      </x:c>
+      <x:c r="AC15" t="str">
+        <x:v>02_Papers/01_VLA/SayCan.md</x:v>
+      </x:c>
+      <x:c r="AD15" t="str">
+        <x:v>Robotics Core / VLA</x:v>
+      </x:c>
+      <x:c r="AE15" t="str">
+        <x:v>Google Research; arXiv HTML; CoRL/PMLR; SayCan project page; official repository</x:v>
+      </x:c>
+      <x:c r="AF15" t="str">
+        <x:v>Full paper + appendices</x:v>
+      </x:c>
+      <x:c r="AG15" t="str">
+        <x:v>101 instructions; mock and real office kitchens; 7 families</x:v>
+      </x:c>
+      <x:c r="AH15" t="str">
+        <x:v>Feasibility scoring, joint-arm affordance and verification/replanning inspirations</x:v>
+      </x:c>
+      <x:c r="AI15" t="str">
+        <x:v>Current CCF check: no CCF-A assignment recorded</x:v>
+      </x:c>
+      <x:c r="AJ15" t="str">
+        <x:v>VLA</x:v>
+      </x:c>
+      <x:c r="AK15" t="n">
+        <x:v>523</x:v>
+      </x:c>
+      <x:c r="AL15" t="str">
+        <x:v>OpenAlex</x:v>
+      </x:c>
+      <x:c r="AM15" t="str">
+        <x:v>2026-09-22</x:v>
+      </x:c>
+      <x:c r="AN15" t="str">
+        <x:v>LLMs have semantic knowledge but no embodiment grounding.</x:v>
+      </x:c>
+      <x:c r="AO15" t="str">
+        <x:v>Useful decomposition and feasible execution were not jointly scored.</x:v>
+      </x:c>
+      <x:c r="AP15" t="str">
+        <x:v>SayCan p(cπ|s,ℓπ) × p(ℓπ|i), skill-level receding horizon.</x:v>
+      </x:c>
+      <x:c r="AQ15" t="str">
+        <x:v>101 instructions, 7 families, mock/real kitchens.</x:v>
+      </x:c>
+      <x:c r="AR15" t="str">
+        <x:v>No VF; Generative; FLAN-SayCan; BC NL/USE.</x:v>
+      </x:c>
+      <x:c r="AS15" t="str">
+        <x:v>Interpretable grounded skill composition.</x:v>
+      </x:c>
+      <x:c r="AT15" t="str">
+        <x:v>Mobile manipulator, PaLM 540B, 551 skills.</x:v>
+      </x:c>
+      <x:c r="AU15" t="str">
+        <x:v>Mock 84/74; Real 81/60; FLAN 70/61; drawer 100/33.</x:v>
+      </x:c>
+      <x:c r="AV15" t="str">
+        <x:v>Fixed skill library, current-step value feedback, execution/recovery gaps.</x:v>
+      </x:c>
+      <x:c r="AW15" t="str">
+        <x:v>Skill synthesis, contact-level grounding, recovery, bimanual joint feasibility.</x:v>
+      </x:c>
+      <x:c r="AX15" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="AY15" t="str">
+        <x:v>Joint affordance; VLA feasibility veto; recovery/replanning; sim2real calibration.</x:v>
+      </x:c>
+      <x:c r="AZ15" t="str">
+        <x:v>No VF/Generative/BC; LLM size; drawer/CoT/multilingual.</x:v>
+      </x:c>
+      <x:c r="BA15" t="str">
+        <x:v>Planning errors, low-level execution, drawer manipulation, embodiment limits.</x:v>
+      </x:c>
+      <x:c r="BB15" t="str">
+        <x:v>OpenAlex Work W4224912544</x:v>
+      </x:c>
+      <x:c r="BC15" t="str">
+        <x:v>Google Research; arXiv; CoRL/PMLR; project page; official repository</x:v>
+      </x:c>
+      <x:c r="BD15" t="str">
+        <x:v>A-Upgraded</x:v>
+      </x:c>
+      <x:c r="BE15" t="str">
+        <x:v>Available - Verified</x:v>
+      </x:c>
+      <x:c r="BF15" t="str">
+        <x:v>Partial</x:v>
+      </x:c>
+      <x:c r="BG15" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="BH15" t="str">
+        <x:v>https://arxiv.org/html/2204.01691</x:v>
+      </x:c>
+      <x:c r="BI15" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="BJ15" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="BK15" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="BL15" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="BM15" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="BN15" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="BO15" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="BP15" t="str">
+        <x:v>OpenAlex matched</x:v>
+      </x:c>
+      <x:c r="BQ15" t="str">
+        <x:v>Verified - 10.48550/arXiv.2204.01691</x:v>
+      </x:c>
+      <x:c r="BR15" t="str">
+        <x:v>Verified - 2204.01691</x:v>
+      </x:c>
+      <x:c r="BS15" t="str">
+        <x:v>Completed - Full text read</x:v>
+      </x:c>
+      <x:c r="BT15" t="str">
+        <x:v>true</x:v>
+      </x:c>
+      <x:c r="BU15" t="str">
+        <x:v>Completed-A</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:dataValidations count="4">
@@ -43801,7 +44231,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R39291e5246964ba3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8b540e7d6f794333"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/00_Paper_Pool/Paper_Pool.xlsx
+++ b/00_Paper_Pool/Paper_Pool.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Papers" sheetId="1" r:id="R86f01c6dad0e4415"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rejected" sheetId="2" r:id="Rb991b7fdee134239"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Venues" sheetId="3" r:id="Rdd3ba6f2361044fe"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Keywords" sheetId="4" r:id="Rfc90709385e342e3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Discovery" sheetId="5" r:id="Ra1faf7c021804116"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CCF_A_Library" sheetId="6" r:id="Rc96f7f93fef2443e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Robotics_Core_Library" sheetId="7" r:id="Rfd09c41558954595"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Papers" sheetId="1" r:id="Rc736cc22804a4b76"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rejected" sheetId="2" r:id="Re4602d75c7c141a2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Venues" sheetId="3" r:id="R67f546b2a2a7407e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Keywords" sheetId="4" r:id="Rba32f92ab29c43ec"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Discovery" sheetId="5" r:id="R859d166c580e4cf2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CCF_A_Library" sheetId="6" r:id="Rfe0cb00ad062490b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Robotics_Core_Library" sheetId="7" r:id="Rcd0c832da3134a21"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1201,14 +1201,14 @@
       <x:c r="AE2" t="str">
         <x:v>02_Papers/02_Robot_Manipulation/ManipLLM.md</x:v>
       </x:c>
-      <x:c r="AF2" t="str">
+      <x:c r="AF2" t="n">
         <x:v>82</x:v>
       </x:c>
       <x:c r="AG2" t="str">
         <x:v>OpenAlex</x:v>
       </x:c>
       <x:c r="AH2" t="str">
-        <x:v>2026-09-21</x:v>
+        <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AI2" t="str">
         <x:v>研究主题为 `Multimodal / Generali</x:v>
@@ -1259,7 +1259,7 @@
         <x:v>Position predictions are sensitive to lighting and texture domain gaps; suction cannot grasp non-smooth handles and short gripper geometry can cause collisions.</x:v>
       </x:c>
       <x:c r="AY2" t="str">
-        <x:v>OpenAlex Work: https://openalex.org/W4402727730</x:v>
+        <x:v>https://openalex.org/W4402727730</x:v>
       </x:c>
       <x:c r="AZ2" t="str">
         <x:v>https://openaccess.thecvf.com/content/CVPR2024/html/Li_ManipLLM_Embodied_Multimodal_Large_Language_Model_for_Object-Centric_Robotic_Manipulation_CVPR_2024_paper.html；官方摘要/论文集元数据</x:v>
@@ -1377,14 +1377,14 @@
       <x:c r="AE3" t="str">
         <x:v>02_Papers/03_Bimanual/ManipTrans.md</x:v>
       </x:c>
-      <x:c r="AF3" t="str">
+      <x:c r="AF3" t="n">
         <x:v>13</x:v>
       </x:c>
       <x:c r="AG3" t="str">
         <x:v>OpenAlex</x:v>
       </x:c>
       <x:c r="AH3" t="str">
-        <x:v>2026-09-21</x:v>
+        <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AI3" t="str">
         <x:v>研究主题为 `Residual Learning / Sim-to-Real`；本卡仅按官方摘要级证据整理，未替代全文审阅。</x:v>
@@ -1435,7 +1435,7 @@
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AY3" t="str">
-        <x:v>Unknown (no high-confidence match)</x:v>
+        <x:v>https://openalex.org/W4413145126</x:v>
       </x:c>
       <x:c r="AZ3" t="str">
         <x:v>https://openaccess.thecvf.com/content/CVPR2025/html/Li_ManipTrans_Efficient_Dexterous_Bimanual_Manipulation_Transfer_via_Residual_Learning_CVPR_2025_paper.html；官方摘要/论文集元数据</x:v>
@@ -1553,14 +1553,14 @@
       <x:c r="AE4" t="str">
         <x:v>02_Papers/04_Dexterous/DexHandDiff.md</x:v>
       </x:c>
-      <x:c r="AF4" t="str">
+      <x:c r="AF4" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="AG4" t="str">
         <x:v>OpenAlex</x:v>
       </x:c>
       <x:c r="AH4" t="str">
-        <x:v>2026-09-21</x:v>
+        <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AI4" t="str">
         <x:v>研究主题为 `Diffusion / Contact-rich Manipulation`；本卡仅按官方摘要级证据整理，未替代全文审阅。</x:v>
@@ -1611,7 +1611,7 @@
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AY4" t="str">
-        <x:v>Unknown (no high-confidence match)</x:v>
+        <x:v>https://openalex.org/W4413146641</x:v>
       </x:c>
       <x:c r="AZ4" t="str">
         <x:v>https://openaccess.thecvf.com/content/CVPR2025/html/Liang_DexHandDiff_Interaction-aware_Diffusion_Planning_for_Adaptive_Dexterous_Manipulation_CVPR_2025_paper.html; https://dexdiffuser.github.io/; https://github.com/Liang-</x:v>
@@ -1729,14 +1729,14 @@
       <x:c r="AE5" t="str">
         <x:v>02_Papers/06_Diffusion_Flow_IL_RL/AR-VRM.md</x:v>
       </x:c>
-      <x:c r="AF5" t="str">
+      <x:c r="AF5" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="AG5" t="str">
         <x:v>OpenAlex</x:v>
       </x:c>
       <x:c r="AH5" t="str">
-        <x:v>2026-09-21</x:v>
+        <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AI5" t="str">
         <x:v>研究主题为 `Human Video / VLM`；本卡仅按官方摘要级证据整理，未替代全文审阅。</x:v>
@@ -1787,7 +1787,7 @@
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AY5" t="str">
-        <x:v>Unknown (no high-confidence match)</x:v>
+        <x:v>https://openalex.org/W4416242580</x:v>
       </x:c>
       <x:c r="AZ5" t="str">
         <x:v>https://openaccess.thecvf.com/content/ICCV2025/html/Yang_AR-VRM_Imitating_Human_Motions_for_Visual_Robot_Manipulation_with_Analogical_ICCV_2025_paper.html；官方摘要/论文集元数据</x:v>
@@ -1944,7 +1944,7 @@
         <x:v>OpenAlex</x:v>
       </x:c>
       <x:c r="AH6" t="str">
-        <x:v>2026-09-22</x:v>
+        <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AI6" t="str">
         <x:v>LLMs have semantic knowledge but no embodiment or current-state grounding.</x:v>
@@ -1995,7 +1995,7 @@
         <x:v>Plan-execute gap; wrong object/negation; drawer manipulation and incomplete close; embodiment-specific failures.</x:v>
       </x:c>
       <x:c r="AY6" t="str">
-        <x:v>OpenAlex Work W4224912544</x:v>
+        <x:v>https://openalex.org/W4224912544</x:v>
       </x:c>
       <x:c r="AZ6" t="str">
         <x:v>Google Research publication; arXiv HTML 2204.01691; CoRL/PMLR; say-can.github.io; Google Research blog; official google-research/saycan</x:v>
@@ -5063,7 +5063,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2c8b9cc21c0e4685"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf752ab12745d489f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8359,7 +8359,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R24875c2dbfc745b9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2a7ef36493ad4994"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8710,7 +8710,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6ae14747bf124552"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0d42fab89b1a4f3c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9456,7 +9456,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R148d6e9fc32646c4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R411e0dc3c962411a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9768,10 +9768,10 @@
         <x:v>Unknown</x:v>
       </x:c>
       <x:c r="AB2" t="str">
-        <x:v>OpenAlex (no high-confidence title match)</x:v>
+        <x:v>OpenAlex (identity ambiguous)</x:v>
       </x:c>
       <x:c r="AC2" t="str">
-        <x:v>2026-09-21</x:v>
+        <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AD2" t="str">
         <x:v>研究主题为 `Robot Manipulation / IL / Diffusion`；本卡仅按官方摘要级证据整理，未替代全文审阅。</x:v>
@@ -9949,14 +9949,14 @@
       <x:c r="Z3" t="str">
         <x:v>02_Papers/03_Bimanual/Rethinking_Bimanual_Robotic_Manipulation_Learning_with_Decoupled_Interaction_Framework.md</x:v>
       </x:c>
-      <x:c r="AA3" t="str">
+      <x:c r="AA3" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="AB3" t="str">
         <x:v>OpenAlex</x:v>
       </x:c>
       <x:c r="AC3" t="str">
-        <x:v>2026-09-21</x:v>
+        <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AD3" t="str">
         <x:v>研究主题为 `Robot Manipulation / IL / Diffusion; Bimanual`；本卡仅按官方摘要级证据整理，未替代全文审阅。</x:v>
@@ -10007,7 +10007,7 @@
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AT3" t="str">
-        <x:v>Unknown (no high-confidence match)</x:v>
+        <x:v>https://openalex.org/W4415101881</x:v>
       </x:c>
       <x:c r="AU3" t="str">
         <x:v>https://openaccess.thecvf.com/content/ICCV2025/html/Jiang_Rethinking_Bimanual_Robotic_Manipulation_Learning_with_Decoupled_Interaction_Framework_ICCV_2025_paper.html；官方摘要/论文集元数据</x:v>
@@ -10134,14 +10134,14 @@
       <x:c r="Z4" t="str">
         <x:v>02_Papers/03_Bimanual/Diffusion-Based_Imaginative_Coordination_for_Bimanual_Manipulation.md</x:v>
       </x:c>
-      <x:c r="AA4" t="str">
+      <x:c r="AA4" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="AB4" t="str">
         <x:v>OpenAlex</x:v>
       </x:c>
       <x:c r="AC4" t="str">
-        <x:v>2026-09-21</x:v>
+        <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AD4" t="str">
         <x:v>研究主题为 `Robot Manipulation / IL / Diffusion; Bimanual`；本卡仅按官方摘要级证据整理，未替代全文审阅。</x:v>
@@ -10192,7 +10192,7 @@
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AT4" t="str">
-        <x:v>Unknown (no high-confidence match)</x:v>
+        <x:v>https://openalex.org/W4414754983</x:v>
       </x:c>
       <x:c r="AU4" t="str">
         <x:v>https://openaccess.thecvf.com/content/ICCV2025/html/Xu_Diffusion-Based_Imaginative_Coordination_for_Bimanual_Manipulation_ICCV_2025_paper.html；官方摘要/论文集元数据</x:v>
@@ -10325,10 +10325,10 @@
         <x:v>Unknown</x:v>
       </x:c>
       <x:c r="AB5" t="str">
-        <x:v>OpenAlex (no high-confidence title match)</x:v>
+        <x:v>OpenAlex (identity unmatched)</x:v>
       </x:c>
       <x:c r="AC5" t="str">
-        <x:v>2026-09-21</x:v>
+        <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AD5" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -10506,14 +10506,14 @@
       <x:c r="Z6" t="str">
         <x:v>02_Papers/04_Dexterous/Cross-Embodiment_Dexterous_Grasping_with_Reinforcement_Learning.md</x:v>
       </x:c>
-      <x:c r="AA6" t="str">
+      <x:c r="AA6" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="AB6" t="str">
         <x:v>OpenAlex</x:v>
       </x:c>
       <x:c r="AC6" t="str">
-        <x:v>2026-09-21</x:v>
+        <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AD6" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -10564,7 +10564,7 @@
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AT6" t="str">
-        <x:v>Unknown (no high-confidence match)</x:v>
+        <x:v>https://openalex.org/W4403883977</x:v>
       </x:c>
       <x:c r="AU6" t="str">
         <x:v>Unknown</x:v>
@@ -10695,10 +10695,10 @@
         <x:v>Unknown</x:v>
       </x:c>
       <x:c r="AB7" t="str">
-        <x:v>OpenAlex (no high-confidence title match)</x:v>
+        <x:v>OpenAlex (identity unmatched)</x:v>
       </x:c>
       <x:c r="AC7" t="str">
-        <x:v>2026-09-21</x:v>
+        <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AD7" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -10874,14 +10874,14 @@
       <x:c r="Z8" t="str">
         <x:v>02_Papers/04_Dexterous/DexTrack.md</x:v>
       </x:c>
-      <x:c r="AA8" t="str">
+      <x:c r="AA8" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="AB8" t="str">
         <x:v>OpenAlex</x:v>
       </x:c>
       <x:c r="AC8" t="str">
-        <x:v>2026-09-21</x:v>
+        <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AD8" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -10932,7 +10932,7 @@
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AT8" t="str">
-        <x:v>Unknown (no high-confidence match)</x:v>
+        <x:v>https://openalex.org/W4407590583</x:v>
       </x:c>
       <x:c r="AU8" t="str">
         <x:v>Unknown</x:v>
@@ -11063,10 +11063,10 @@
         <x:v>Unknown</x:v>
       </x:c>
       <x:c r="AB9" t="str">
-        <x:v>OpenAlex (no high-confidence title match)</x:v>
+        <x:v>OpenAlex (identity unmatched)</x:v>
       </x:c>
       <x:c r="AC9" t="str">
-        <x:v>2026-09-21</x:v>
+        <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AD9" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -11242,14 +11242,14 @@
       <x:c r="Z10" t="str">
         <x:v>02_Papers/10_Benchmark_Dataset/AdaManip.md</x:v>
       </x:c>
-      <x:c r="AA10" t="str">
-        <x:v>Unknown</x:v>
+      <x:c r="AA10" t="n">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AB10" t="str">
-        <x:v>OpenAlex (no high-confidence title match)</x:v>
+        <x:v>OpenAlex</x:v>
       </x:c>
       <x:c r="AC10" t="str">
-        <x:v>2026-09-21</x:v>
+        <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AD10" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -11300,7 +11300,7 @@
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AT10" t="str">
-        <x:v>Unknown (no high-confidence match)</x:v>
+        <x:v>https://openalex.org/W4407690282</x:v>
       </x:c>
       <x:c r="AU10" t="str">
         <x:v>Unknown</x:v>
@@ -11429,14 +11429,14 @@
       <x:c r="Z11" t="str">
         <x:v>02_Papers/07_Generalization_LongHorizon/HAMSTER.md</x:v>
       </x:c>
-      <x:c r="AA11" t="str">
-        <x:v>Unknown</x:v>
+      <x:c r="AA11" t="n">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AB11" t="str">
-        <x:v>OpenAlex (no high-confidence title match)</x:v>
+        <x:v>OpenAlex</x:v>
       </x:c>
       <x:c r="AC11" t="str">
-        <x:v>2026-09-21</x:v>
+        <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AD11" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -11487,7 +11487,7 @@
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AT11" t="str">
-        <x:v>Unknown (no high-confidence match)</x:v>
+        <x:v>https://openalex.org/W4407384835</x:v>
       </x:c>
       <x:c r="AU11" t="str">
         <x:v>Unknown</x:v>
@@ -11616,14 +11616,14 @@
       <x:c r="Z12" t="str">
         <x:v>02_Papers/06_Diffusion_Flow_IL_RL/ET-SEED.md</x:v>
       </x:c>
-      <x:c r="AA12" t="str">
+      <x:c r="AA12" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="AB12" t="str">
         <x:v>OpenAlex</x:v>
       </x:c>
       <x:c r="AC12" t="str">
-        <x:v>2026-09-21</x:v>
+        <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AD12" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -11674,7 +11674,7 @@
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AT12" t="str">
-        <x:v>Unknown (no high-confidence match)</x:v>
+        <x:v>https://openalex.org/W4404371741</x:v>
       </x:c>
       <x:c r="AU12" t="str">
         <x:v>Unknown</x:v>
@@ -11804,13 +11804,13 @@
         <x:v>02_Papers/06_Diffusion_Flow_IL_RL/Bidirectional_Decoding.md</x:v>
       </x:c>
       <x:c r="AA13" t="str">
-        <x:v>0</x:v>
+        <x:v>Unknown</x:v>
       </x:c>
       <x:c r="AB13" t="str">
-        <x:v>OpenAlex</x:v>
+        <x:v>OpenAlex (identity ambiguous)</x:v>
       </x:c>
       <x:c r="AC13" t="str">
-        <x:v>2026-09-21</x:v>
+        <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AD13" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -11992,10 +11992,10 @@
         <x:v>Unknown</x:v>
       </x:c>
       <x:c r="AB14" t="str">
-        <x:v>OpenAlex (no high-confidence title match)</x:v>
+        <x:v>OpenAlex (identity unmatched)</x:v>
       </x:c>
       <x:c r="AC14" t="str">
-        <x:v>2026-09-21</x:v>
+        <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AD14" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -12176,13 +12176,13 @@
         <x:v>02_Papers/06_Diffusion_Flow_IL_RL/Demystifying_Robot_Diffusion_Policies_Action_Memorization_and_a_Simple_Lookup_Table_Altern.md</x:v>
       </x:c>
       <x:c r="AA15" t="str">
-        <x:v>0</x:v>
+        <x:v>Unknown</x:v>
       </x:c>
       <x:c r="AB15" t="str">
-        <x:v>OpenAlex</x:v>
+        <x:v>OpenAlex (identity unmatched)</x:v>
       </x:c>
       <x:c r="AC15" t="str">
-        <x:v>2026-09-21</x:v>
+        <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AD15" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -12358,14 +12358,14 @@
       <x:c r="Z16" t="str">
         <x:v>02_Papers/01_VLA/SP-VLA.md</x:v>
       </x:c>
-      <x:c r="AA16" t="str">
+      <x:c r="AA16" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="AB16" t="str">
         <x:v>OpenAlex</x:v>
       </x:c>
       <x:c r="AC16" t="str">
-        <x:v>2026-09-21</x:v>
+        <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AD16" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -12416,7 +12416,7 @@
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AT16" t="str">
-        <x:v>Unknown (no high-confidence match)</x:v>
+        <x:v>https://openalex.org/W4417536563</x:v>
       </x:c>
       <x:c r="AU16" t="str">
         <x:v>Unknown</x:v>
@@ -12545,10 +12545,10 @@
         <x:v>Unknown</x:v>
       </x:c>
       <x:c r="AB17" t="str">
-        <x:v>OpenAlex (no high-confidence title match)</x:v>
+        <x:v>OpenAlex (identity unmatched)</x:v>
       </x:c>
       <x:c r="AC17" t="str">
-        <x:v>2026-09-21</x:v>
+        <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AD17" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -12724,14 +12724,14 @@
       <x:c r="Z18" t="str">
         <x:v>02_Papers/01_VLA/Actions_as_Language.md</x:v>
       </x:c>
-      <x:c r="AA18" t="str">
-        <x:v>Unknown</x:v>
+      <x:c r="AA18" t="n">
+        <x:v>0</x:v>
       </x:c>
       <x:c r="AB18" t="str">
-        <x:v>OpenAlex (no high-confidence title match)</x:v>
+        <x:v>OpenAlex</x:v>
       </x:c>
       <x:c r="AC18" t="str">
-        <x:v>2026-09-21</x:v>
+        <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AD18" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -12782,7 +12782,7 @@
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AT18" t="str">
-        <x:v>Unknown (no high-confidence match)</x:v>
+        <x:v>https://openalex.org/W7083676685</x:v>
       </x:c>
       <x:c r="AU18" t="str">
         <x:v>Unknown</x:v>
@@ -12913,10 +12913,10 @@
         <x:v>Unknown</x:v>
       </x:c>
       <x:c r="AB19" t="str">
-        <x:v>OpenAlex (no high-confidence title match)</x:v>
+        <x:v>OpenAlex (identity ambiguous)</x:v>
       </x:c>
       <x:c r="AC19" t="str">
-        <x:v>2026-09-21</x:v>
+        <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AD19" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -13096,10 +13096,10 @@
         <x:v>Unknown</x:v>
       </x:c>
       <x:c r="AB20" t="str">
-        <x:v>OpenAlex (no high-confidence title match)</x:v>
+        <x:v>OpenAlex (identity unmatched)</x:v>
       </x:c>
       <x:c r="AC20" t="str">
-        <x:v>2026-09-21</x:v>
+        <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AD20" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -13281,10 +13281,10 @@
         <x:v>Unknown</x:v>
       </x:c>
       <x:c r="AB21" t="str">
-        <x:v>OpenAlex (no high-confidence title match)</x:v>
+        <x:v>OpenAlex (identity unmatched)</x:v>
       </x:c>
       <x:c r="AC21" t="str">
-        <x:v>2026-09-21</x:v>
+        <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AD21" t="str">
         <x:v>研究主题为 `Robot Manipulation / IL / Diffusion`；本卡仅按官方摘要级证据整理，未替代全文审阅。</x:v>
@@ -13466,10 +13466,10 @@
         <x:v>Unknown</x:v>
       </x:c>
       <x:c r="AB22" t="str">
-        <x:v>OpenAlex (no high-confidence title match)</x:v>
+        <x:v>OpenAlex (identity unmatched)</x:v>
       </x:c>
       <x:c r="AC22" t="str">
-        <x:v>2026-09-21</x:v>
+        <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AD22" t="str">
         <x:v>研究主题为 `Robot Manipulation / IL / Diffusion`；本卡仅按官方摘要级证据整理，未替代全文审阅。</x:v>
@@ -13651,10 +13651,10 @@
         <x:v>Unknown</x:v>
       </x:c>
       <x:c r="AB23" t="str">
-        <x:v>OpenAlex (no high-confidence title match)</x:v>
+        <x:v>OpenAlex (identity unmatched)</x:v>
       </x:c>
       <x:c r="AC23" t="str">
-        <x:v>2026-09-21</x:v>
+        <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AD23" t="str">
         <x:v>研究主题为 `Robot Manipulation / IL / Diffusion`；本卡仅按官方摘要级证据整理，未替代全文审阅。</x:v>
@@ -13836,10 +13836,10 @@
         <x:v>Unknown</x:v>
       </x:c>
       <x:c r="AB24" t="str">
-        <x:v>OpenAlex (no high-confidence title match)</x:v>
+        <x:v>OpenAlex (identity unmatched)</x:v>
       </x:c>
       <x:c r="AC24" t="str">
-        <x:v>2026-09-21</x:v>
+        <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AD24" t="str">
         <x:v>研究主题为 `Robot Manipulation / IL / Diffusion`；本卡仅按官方摘要级证据整理，未替代全文审阅。</x:v>
@@ -14019,10 +14019,10 @@
         <x:v>Unknown</x:v>
       </x:c>
       <x:c r="AB25" t="str">
-        <x:v>OpenAlex (no high-confidence title match)</x:v>
+        <x:v>OpenAlex (identity unmatched)</x:v>
       </x:c>
       <x:c r="AC25" t="str">
-        <x:v>2026-09-21</x:v>
+        <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AD25" t="str">
         <x:v>研究主题为 `Dexterous Hand / Dexterous Manipulation`；本卡仅按官方摘要级证据整理，未替代全文审阅。</x:v>
@@ -14204,10 +14204,10 @@
         <x:v>Unknown</x:v>
       </x:c>
       <x:c r="AB26" t="str">
-        <x:v>OpenAlex (no high-confidence title match)</x:v>
+        <x:v>OpenAlex (identity unmatched)</x:v>
       </x:c>
       <x:c r="AC26" t="str">
-        <x:v>2026-09-21</x:v>
+        <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AD26" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -14385,14 +14385,14 @@
       <x:c r="Z27" t="str">
         <x:v>02_Papers/06_Diffusion_Flow_IL_RL/Learning_Robotic_Manipulation_Policies_from_Point_Clouds_with_Conditional_Flow_Matching.md</x:v>
       </x:c>
-      <x:c r="AA27" t="str">
-        <x:v>Unknown</x:v>
+      <x:c r="AA27" t="n">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AB27" t="str">
-        <x:v>OpenAlex (no high-confidence title match)</x:v>
+        <x:v>OpenAlex</x:v>
       </x:c>
       <x:c r="AC27" t="str">
-        <x:v>2026-09-21</x:v>
+        <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AD27" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -14443,7 +14443,7 @@
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AT27" t="str">
-        <x:v>Unknown (no high-confidence match)</x:v>
+        <x:v>https://openalex.org/W4403622102</x:v>
       </x:c>
       <x:c r="AU27" t="str">
         <x:v>Unknown</x:v>
@@ -14570,14 +14570,14 @@
       <x:c r="Z28" t="str">
         <x:v>02_Papers/07_Generalization_LongHorizon/SPIRE.md</x:v>
       </x:c>
-      <x:c r="AA28" t="str">
-        <x:v>Unknown</x:v>
+      <x:c r="AA28" t="n">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AB28" t="str">
-        <x:v>OpenAlex (no high-confidence title match)</x:v>
+        <x:v>OpenAlex</x:v>
       </x:c>
       <x:c r="AC28" t="str">
-        <x:v>2026-09-21</x:v>
+        <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AD28" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -14628,7 +14628,7 @@
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AT28" t="str">
-        <x:v>Unknown (no high-confidence match)</x:v>
+        <x:v>https://openalex.org/W4404308601</x:v>
       </x:c>
       <x:c r="AU28" t="str">
         <x:v>https://proceedings.mlr.press/v270/</x:v>
@@ -14755,14 +14755,14 @@
       <x:c r="Z29" t="str">
         <x:v>02_Papers/08_Data_Teleoperation/OPEN_TEACH.md</x:v>
       </x:c>
-      <x:c r="AA29" t="str">
-        <x:v>Unknown</x:v>
+      <x:c r="AA29" t="n">
+        <x:v>2</x:v>
       </x:c>
       <x:c r="AB29" t="str">
-        <x:v>OpenAlex (no high-confidence title match)</x:v>
+        <x:v>OpenAlex</x:v>
       </x:c>
       <x:c r="AC29" t="str">
-        <x:v>2026-09-21</x:v>
+        <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AD29" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -14813,7 +14813,7 @@
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AT29" t="str">
-        <x:v>Unknown (no high-confidence match)</x:v>
+        <x:v>https://openalex.org/W4392781441</x:v>
       </x:c>
       <x:c r="AU29" t="str">
         <x:v>Unknown</x:v>
@@ -14940,14 +14940,14 @@
       <x:c r="Z30" t="str">
         <x:v>02_Papers/07_Generalization_LongHorizon/RAM.md</x:v>
       </x:c>
-      <x:c r="AA30" t="str">
-        <x:v>Unknown</x:v>
+      <x:c r="AA30" t="n">
+        <x:v>2</x:v>
       </x:c>
       <x:c r="AB30" t="str">
-        <x:v>OpenAlex (no high-confidence title match)</x:v>
+        <x:v>OpenAlex</x:v>
       </x:c>
       <x:c r="AC30" t="str">
-        <x:v>2026-09-21</x:v>
+        <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AD30" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -14998,7 +14998,7 @@
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AT30" t="str">
-        <x:v>Unknown (no high-confidence match)</x:v>
+        <x:v>https://openalex.org/W4400435236</x:v>
       </x:c>
       <x:c r="AU30" t="str">
         <x:v>Unknown</x:v>
@@ -15125,14 +15125,14 @@
       <x:c r="Z31" t="str">
         <x:v>02_Papers/08_Data_Teleoperation/ManiWAV.md</x:v>
       </x:c>
-      <x:c r="AA31" t="str">
-        <x:v>Unknown</x:v>
+      <x:c r="AA31" t="n">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AB31" t="str">
-        <x:v>OpenAlex (no high-confidence title match)</x:v>
+        <x:v>OpenAlex</x:v>
       </x:c>
       <x:c r="AC31" t="str">
-        <x:v>2026-09-21</x:v>
+        <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AD31" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -15183,7 +15183,7 @@
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AT31" t="str">
-        <x:v>Unknown (no high-confidence match)</x:v>
+        <x:v>https://openalex.org/W4400222297</x:v>
       </x:c>
       <x:c r="AU31" t="str">
         <x:v>Unknown</x:v>
@@ -15310,14 +15310,14 @@
       <x:c r="Z32" t="str">
         <x:v>02_Papers/02_Robot_Manipulation/Dreamitate.md</x:v>
       </x:c>
-      <x:c r="AA32" t="str">
+      <x:c r="AA32" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="AB32" t="str">
         <x:v>OpenAlex</x:v>
       </x:c>
       <x:c r="AC32" t="str">
-        <x:v>2026-09-21</x:v>
+        <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AD32" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -15368,7 +15368,7 @@
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AT32" t="str">
-        <x:v>Unknown (no high-confidence match)</x:v>
+        <x:v>https://openalex.org/W4400024954</x:v>
       </x:c>
       <x:c r="AU32" t="str">
         <x:v>Unknown</x:v>
@@ -15499,10 +15499,10 @@
         <x:v>Unknown</x:v>
       </x:c>
       <x:c r="AB33" t="str">
-        <x:v>OpenAlex (no high-confidence title match)</x:v>
+        <x:v>OpenAlex (identity unmatched)</x:v>
       </x:c>
       <x:c r="AC33" t="str">
-        <x:v>2026-09-21</x:v>
+        <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AD33" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -15680,14 +15680,14 @@
       <x:c r="Z34" t="str">
         <x:v>02_Papers/06_Diffusion_Flow_IL_RL/EquiBot.md</x:v>
       </x:c>
-      <x:c r="AA34" t="str">
+      <x:c r="AA34" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="AB34" t="str">
         <x:v>OpenAlex</x:v>
       </x:c>
       <x:c r="AC34" t="str">
-        <x:v>2026-09-21</x:v>
+        <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AD34" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -15738,7 +15738,7 @@
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AT34" t="str">
-        <x:v>Unknown (no high-confidence match)</x:v>
+        <x:v>https://openalex.org/W4400373516</x:v>
       </x:c>
       <x:c r="AU34" t="str">
         <x:v>Unknown</x:v>
@@ -15865,14 +15865,14 @@
       <x:c r="Z35" t="str">
         <x:v>02_Papers/06_Diffusion_Flow_IL_RL/3D_Diffuser_Actor.md</x:v>
       </x:c>
-      <x:c r="AA35" t="str">
+      <x:c r="AA35" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="AB35" t="str">
         <x:v>OpenAlex</x:v>
       </x:c>
       <x:c r="AC35" t="str">
-        <x:v>2026-09-21</x:v>
+        <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AD35" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -15923,7 +15923,7 @@
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AT35" t="str">
-        <x:v>Unknown (no high-confidence match)</x:v>
+        <x:v>https://openalex.org/W4391949089</x:v>
       </x:c>
       <x:c r="AU35" t="str">
         <x:v>Unknown</x:v>
@@ -16050,14 +16050,14 @@
       <x:c r="Z36" t="str">
         <x:v>02_Papers/10_Benchmark_Dataset/BiGym.md</x:v>
       </x:c>
-      <x:c r="AA36" t="str">
-        <x:v>Unknown</x:v>
+      <x:c r="AA36" t="n">
+        <x:v>0</x:v>
       </x:c>
       <x:c r="AB36" t="str">
-        <x:v>OpenAlex (no high-confidence title match)</x:v>
+        <x:v>OpenAlex</x:v>
       </x:c>
       <x:c r="AC36" t="str">
-        <x:v>2026-09-21</x:v>
+        <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AD36" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -16108,7 +16108,7 @@
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AT36" t="str">
-        <x:v>Unknown (no high-confidence match)</x:v>
+        <x:v>https://openalex.org/W4400611211</x:v>
       </x:c>
       <x:c r="AU36" t="str">
         <x:v>Unknown</x:v>
@@ -16235,14 +16235,14 @@
       <x:c r="Z37" t="str">
         <x:v>02_Papers/03_Bimanual/VoxAct-B.md</x:v>
       </x:c>
-      <x:c r="AA37" t="str">
+      <x:c r="AA37" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="AB37" t="str">
         <x:v>OpenAlex</x:v>
       </x:c>
       <x:c r="AC37" t="str">
-        <x:v>2026-09-21</x:v>
+        <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AD37" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -16293,7 +16293,7 @@
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AT37" t="str">
-        <x:v>Unknown (no high-confidence match)</x:v>
+        <x:v>https://openalex.org/W4400434472</x:v>
       </x:c>
       <x:c r="AU37" t="str">
         <x:v>Unknown</x:v>
@@ -16421,13 +16421,13 @@
         <x:v>02_Papers/03_Bimanual/Mobile_ALOHA.md</x:v>
       </x:c>
       <x:c r="AA38" t="str">
-        <x:v>31</x:v>
+        <x:v>Unknown</x:v>
       </x:c>
       <x:c r="AB38" t="str">
-        <x:v>OpenAlex</x:v>
+        <x:v>OpenAlex (identity unmatched)</x:v>
       </x:c>
       <x:c r="AC38" t="str">
-        <x:v>2026-09-21</x:v>
+        <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AD38" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -16605,14 +16605,14 @@
       <x:c r="Z39" t="str">
         <x:v>02_Papers/03_Bimanual/ALOHA_Unleashed.md</x:v>
       </x:c>
-      <x:c r="AA39" t="str">
+      <x:c r="AA39" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="AB39" t="str">
         <x:v>OpenAlex</x:v>
       </x:c>
       <x:c r="AC39" t="str">
-        <x:v>2026-09-21</x:v>
+        <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AD39" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -16663,7 +16663,7 @@
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AT39" t="str">
-        <x:v>Unknown (no high-confidence match)</x:v>
+        <x:v>https://openalex.org/W4403579180</x:v>
       </x:c>
       <x:c r="AU39" t="str">
         <x:v>https://proceedings.mlr.press/v270/</x:v>
@@ -16792,10 +16792,10 @@
         <x:v>Unknown</x:v>
       </x:c>
       <x:c r="AB40" t="str">
-        <x:v>OpenAlex (no high-confidence title match)</x:v>
+        <x:v>OpenAlex (identity unmatched)</x:v>
       </x:c>
       <x:c r="AC40" t="str">
-        <x:v>2026-09-21</x:v>
+        <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AD40" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -16975,10 +16975,10 @@
         <x:v>Unknown</x:v>
       </x:c>
       <x:c r="AB41" t="str">
-        <x:v>OpenAlex (no high-confidence title match)</x:v>
+        <x:v>OpenAlex (identity unmatched)</x:v>
       </x:c>
       <x:c r="AC41" t="str">
-        <x:v>2026-09-21</x:v>
+        <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AD41" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -17154,14 +17154,14 @@
       <x:c r="Z42" t="str">
         <x:v>02_Papers/03_Bimanual/COMBO-Grasp.md</x:v>
       </x:c>
-      <x:c r="AA42" t="str">
+      <x:c r="AA42" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="AB42" t="str">
         <x:v>OpenAlex</x:v>
       </x:c>
       <x:c r="AC42" t="str">
-        <x:v>2026-09-21</x:v>
+        <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AD42" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -17212,7 +17212,7 @@
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AT42" t="str">
-        <x:v>Unknown (no high-confidence match)</x:v>
+        <x:v>https://openalex.org/W4407569722</x:v>
       </x:c>
       <x:c r="AU42" t="str">
         <x:v>Unknown</x:v>
@@ -17341,10 +17341,10 @@
         <x:v>Unknown</x:v>
       </x:c>
       <x:c r="AB43" t="str">
-        <x:v>OpenAlex (no high-confidence title match)</x:v>
+        <x:v>OpenAlex (identity unmatched)</x:v>
       </x:c>
       <x:c r="AC43" t="str">
-        <x:v>2026-09-21</x:v>
+        <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AD43" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -17520,14 +17520,14 @@
       <x:c r="Z44" t="str">
         <x:v>02_Papers/04_Dexterous/DexUMI.md</x:v>
       </x:c>
-      <x:c r="AA44" t="str">
+      <x:c r="AA44" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="AB44" t="str">
         <x:v>OpenAlex</x:v>
       </x:c>
       <x:c r="AC44" t="str">
-        <x:v>2026-09-21</x:v>
+        <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AD44" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -17578,7 +17578,7 @@
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AT44" t="str">
-        <x:v>Unknown (no high-confidence match)</x:v>
+        <x:v>https://openalex.org/W4416623172</x:v>
       </x:c>
       <x:c r="AU44" t="str">
         <x:v>Unknown</x:v>
@@ -17707,10 +17707,10 @@
         <x:v>Unknown</x:v>
       </x:c>
       <x:c r="AB45" t="str">
-        <x:v>OpenAlex (no high-confidence title match)</x:v>
+        <x:v>OpenAlex (identity unmatched)</x:v>
       </x:c>
       <x:c r="AC45" t="str">
-        <x:v>2026-09-21</x:v>
+        <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AD45" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -17888,14 +17888,14 @@
       <x:c r="Z46" t="str">
         <x:v>02_Papers/09_Survey_Review/A_Survey_on_Vision-Language-Action_Models_for_Embodied_AI.md</x:v>
       </x:c>
-      <x:c r="AA46" t="str">
-        <x:v>Unknown</x:v>
+      <x:c r="AA46" t="n">
+        <x:v>29</x:v>
       </x:c>
       <x:c r="AB46" t="str">
-        <x:v>OpenAlex (no high-confidence title match)</x:v>
+        <x:v>OpenAlex</x:v>
       </x:c>
       <x:c r="AC46" t="str">
-        <x:v>2026-09-21</x:v>
+        <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AD46" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -17946,7 +17946,7 @@
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AT46" t="str">
-        <x:v>Unknown (no high-confidence match)</x:v>
+        <x:v>https://openalex.org/W4398796510</x:v>
       </x:c>
       <x:c r="AU46" t="str">
         <x:v>Unknown</x:v>
@@ -18077,10 +18077,10 @@
         <x:v>Unknown</x:v>
       </x:c>
       <x:c r="AB47" t="str">
-        <x:v>OpenAlex (no high-confidence title match)</x:v>
+        <x:v>OpenAlex (identity unmatched)</x:v>
       </x:c>
       <x:c r="AC47" t="str">
-        <x:v>2026-09-21</x:v>
+        <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AD47" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -18258,14 +18258,14 @@
       <x:c r="Z48" t="str">
         <x:v>02_Papers/09_Survey_Review/What_Foundation_Models_can_Bring_for_Robot_Learning_in_Manipulation_A_Survey.md</x:v>
       </x:c>
-      <x:c r="AA48" t="str">
-        <x:v>Unknown</x:v>
+      <x:c r="AA48" t="n">
+        <x:v>6</x:v>
       </x:c>
       <x:c r="AB48" t="str">
-        <x:v>OpenAlex (no high-confidence title match)</x:v>
+        <x:v>OpenAlex</x:v>
       </x:c>
       <x:c r="AC48" t="str">
-        <x:v>2026-09-21</x:v>
+        <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AD48" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -18316,7 +18316,7 @@
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AT48" t="str">
-        <x:v>Unknown (no high-confidence match)</x:v>
+        <x:v>https://openalex.org/W4416422407</x:v>
       </x:c>
       <x:c r="AU48" t="str">
         <x:v>Unknown</x:v>
@@ -18443,14 +18443,14 @@
       <x:c r="Z49" t="str">
         <x:v>02_Papers/09_Survey_Review/A_Survey_on_Robotics_with_Foundation_Models_Toward_Embodied_AI.md</x:v>
       </x:c>
-      <x:c r="AA49" t="str">
-        <x:v>Unknown</x:v>
+      <x:c r="AA49" t="n">
+        <x:v>4</x:v>
       </x:c>
       <x:c r="AB49" t="str">
-        <x:v>OpenAlex (no high-confidence title match)</x:v>
+        <x:v>OpenAlex</x:v>
       </x:c>
       <x:c r="AC49" t="str">
-        <x:v>2026-09-21</x:v>
+        <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AD49" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -18501,7 +18501,7 @@
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AT49" t="str">
-        <x:v>Unknown (no high-confidence match)</x:v>
+        <x:v>https://openalex.org/W4391590994</x:v>
       </x:c>
       <x:c r="AU49" t="str">
         <x:v>Unknown</x:v>
@@ -18632,10 +18632,10 @@
         <x:v>Unknown</x:v>
       </x:c>
       <x:c r="AB50" t="str">
-        <x:v>OpenAlex (no high-confidence title match)</x:v>
+        <x:v>OpenAlex (identity ambiguous)</x:v>
       </x:c>
       <x:c r="AC50" t="str">
-        <x:v>2026-09-21</x:v>
+        <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AD50" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -18813,14 +18813,14 @@
       <x:c r="Z51" t="str">
         <x:v>02_Papers/09_Survey_Review/Survey_of_Learning-Based_Approaches_for_Robotic_In-Hand_Manipulation.md</x:v>
       </x:c>
-      <x:c r="AA51" t="str">
-        <x:v>Unknown</x:v>
+      <x:c r="AA51" t="n">
+        <x:v>28</x:v>
       </x:c>
       <x:c r="AB51" t="str">
-        <x:v>OpenAlex (no high-confidence title match)</x:v>
+        <x:v>OpenAlex</x:v>
       </x:c>
       <x:c r="AC51" t="str">
-        <x:v>2026-09-21</x:v>
+        <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AD51" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -18871,7 +18871,7 @@
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AT51" t="str">
-        <x:v>Unknown (no high-confidence match)</x:v>
+        <x:v>https://openalex.org/W4404085362</x:v>
       </x:c>
       <x:c r="AU51" t="str">
         <x:v>Unknown</x:v>
@@ -18998,14 +18998,14 @@
       <x:c r="Z52" t="str">
         <x:v>02_Papers/09_Survey_Review/Dexterous_Hand_towards_Intelligent_Manufacturing_A_Review_of_Technologies,_Trends,_and_Pot.md</x:v>
       </x:c>
-      <x:c r="AA52" t="str">
-        <x:v>Unknown</x:v>
+      <x:c r="AA52" t="n">
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AB52" t="str">
-        <x:v>OpenAlex (no high-confidence title match)</x:v>
+        <x:v>OpenAlex</x:v>
       </x:c>
       <x:c r="AC52" t="str">
-        <x:v>2026-09-21</x:v>
+        <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AD52" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -19056,7 +19056,7 @@
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AT52" t="str">
-        <x:v>Unknown (no high-confidence match)</x:v>
+        <x:v>https://openalex.org/W4409168415</x:v>
       </x:c>
       <x:c r="AU52" t="str">
         <x:v>Unknown</x:v>
@@ -19183,14 +19183,14 @@
       <x:c r="Z53" t="str">
         <x:v>02_Papers/09_Survey_Review/A_Survey_of_Embodied_Learning_for_Object-Centric_Robotic_Manipulation.md</x:v>
       </x:c>
-      <x:c r="AA53" t="str">
-        <x:v>Unknown</x:v>
+      <x:c r="AA53" t="n">
+        <x:v>16</x:v>
       </x:c>
       <x:c r="AB53" t="str">
-        <x:v>OpenAlex (no high-confidence title match)</x:v>
+        <x:v>OpenAlex</x:v>
       </x:c>
       <x:c r="AC53" t="str">
-        <x:v>2026-09-21</x:v>
+        <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AD53" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -19241,7 +19241,7 @@
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AT53" t="str">
-        <x:v>Unknown (no high-confidence match)</x:v>
+        <x:v>https://openalex.org/W4405426927</x:v>
       </x:c>
       <x:c r="AU53" t="str">
         <x:v>Unknown</x:v>
@@ -19368,14 +19368,14 @@
       <x:c r="Z54" t="str">
         <x:v>02_Papers/09_Survey_Review/Interactive_Imitation_Learning_for_Dexterous_Robotic_Manipulation_Challenges_and_Perspecti.md</x:v>
       </x:c>
-      <x:c r="AA54" t="str">
-        <x:v>Unknown</x:v>
+      <x:c r="AA54" t="n">
+        <x:v>7</x:v>
       </x:c>
       <x:c r="AB54" t="str">
-        <x:v>OpenAlex (no high-confidence title match)</x:v>
+        <x:v>OpenAlex</x:v>
       </x:c>
       <x:c r="AC54" t="str">
-        <x:v>2026-09-21</x:v>
+        <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AD54" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -19426,7 +19426,7 @@
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AT54" t="str">
-        <x:v>Unknown (no high-confidence match)</x:v>
+        <x:v>https://openalex.org/W4417483688</x:v>
       </x:c>
       <x:c r="AU54" t="str">
         <x:v>Unknown</x:v>
@@ -19557,10 +19557,10 @@
         <x:v>Unknown</x:v>
       </x:c>
       <x:c r="AB55" t="str">
-        <x:v>OpenAlex (no high-confidence title match)</x:v>
+        <x:v>OpenAlex (identity unmatched)</x:v>
       </x:c>
       <x:c r="AC55" t="str">
-        <x:v>2026-09-21</x:v>
+        <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AD55" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -19742,10 +19742,10 @@
         <x:v>Unknown</x:v>
       </x:c>
       <x:c r="AB56" t="str">
-        <x:v>OpenAlex (no high-confidence title match)</x:v>
+        <x:v>OpenAlex (identity unmatched)</x:v>
       </x:c>
       <x:c r="AC56" t="str">
-        <x:v>2026-09-21</x:v>
+        <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AD56" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -19923,14 +19923,14 @@
       <x:c r="Z57" t="str">
         <x:v>02_Papers/09_Survey_Review/A_Survey_of_Demonstration_Learning.md</x:v>
       </x:c>
-      <x:c r="AA57" t="str">
-        <x:v>Unknown</x:v>
+      <x:c r="AA57" t="n">
+        <x:v>32</x:v>
       </x:c>
       <x:c r="AB57" t="str">
-        <x:v>OpenAlex (no high-confidence title match)</x:v>
+        <x:v>OpenAlex</x:v>
       </x:c>
       <x:c r="AC57" t="str">
-        <x:v>2026-09-21</x:v>
+        <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AD57" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -19981,7 +19981,7 @@
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AT57" t="str">
-        <x:v>Unknown (no high-confidence match)</x:v>
+        <x:v>https://openalex.org/W4402510263</x:v>
       </x:c>
       <x:c r="AU57" t="str">
         <x:v>Unknown</x:v>
@@ -20115,13 +20115,13 @@
         <x:v>02_Papers/03_Bimanual/RDT-1B.md</x:v>
       </x:c>
       <x:c r="AA58" t="str">
-        <x:v>5</x:v>
+        <x:v>Unknown</x:v>
       </x:c>
       <x:c r="AB58" t="str">
-        <x:v>OpenAlex</x:v>
+        <x:v>OpenAlex (identity ambiguous)</x:v>
       </x:c>
       <x:c r="AC58" t="str">
-        <x:v>2026-09-21</x:v>
+        <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AD58" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -20305,14 +20305,14 @@
       <x:c r="Z59" t="str">
         <x:v>02_Papers/03_Bimanual/TwinVLA.md</x:v>
       </x:c>
-      <x:c r="AA59" t="str">
+      <x:c r="AA59" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="AB59" t="str">
         <x:v>OpenAlex</x:v>
       </x:c>
       <x:c r="AC59" t="str">
-        <x:v>2026-09-21</x:v>
+        <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AD59" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -20363,7 +20363,7 @@
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AT59" t="str">
-        <x:v>Unknown (no high-confidence match)</x:v>
+        <x:v>https://openalex.org/W7104816971</x:v>
       </x:c>
       <x:c r="AU59" t="str">
         <x:v>Unknown</x:v>
@@ -20498,10 +20498,10 @@
         <x:v>Unknown</x:v>
       </x:c>
       <x:c r="AB60" t="str">
-        <x:v>OpenAlex (no high-confidence title match)</x:v>
+        <x:v>OpenAlex (identity unmatched)</x:v>
       </x:c>
       <x:c r="AC60" t="str">
-        <x:v>2026-09-21</x:v>
+        <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AD60" t="str">
         <x:v>研究主题为 `Bimanual; Dataset / Benchmark`；本卡仅按官方摘要级证据整理，未替代全文审阅。</x:v>
@@ -20685,14 +20685,14 @@
       <x:c r="Z61" t="str">
         <x:v>02_Papers/01_VLA/BridgeVLA.md</x:v>
       </x:c>
-      <x:c r="AA61" t="str">
+      <x:c r="AA61" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="AB61" t="str">
         <x:v>OpenAlex</x:v>
       </x:c>
       <x:c r="AC61" t="str">
-        <x:v>2026-09-21</x:v>
+        <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AD61" t="str">
         <x:v>研究主题为 `VLA / Robot Foundation Models`；本卡仅按官方摘要级证据整理，未替代全文审阅。</x:v>
@@ -20743,7 +20743,7 @@
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AT61" t="str">
-        <x:v>Unknown (no high-confidence match)</x:v>
+        <x:v>https://openalex.org/W4415272059</x:v>
       </x:c>
       <x:c r="AU61" t="str">
         <x:v>https://proceedings.neurips.cc/paper_files/paper/2025/hash/5c1a8aa04c1a2cf5013f28831870dafa-Abstract-Conference.html；官方摘要/论文集元数据</x:v>
@@ -20876,14 +20876,14 @@
       <x:c r="Z62" t="str">
         <x:v>02_Papers/01_VLA/VLA-Cache.md</x:v>
       </x:c>
-      <x:c r="AA62" t="str">
+      <x:c r="AA62" t="n">
         <x:v>9</x:v>
       </x:c>
       <x:c r="AB62" t="str">
         <x:v>OpenAlex</x:v>
       </x:c>
       <x:c r="AC62" t="str">
-        <x:v>2026-09-21</x:v>
+        <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AD62" t="str">
         <x:v>研究主题为 `VLA / Robot Foundation Models`；本卡仅按官方摘要级证据整理，未替代全文审阅。</x:v>
@@ -20934,7 +20934,7 @@
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AT62" t="str">
-        <x:v>Unknown (no high-confidence match)</x:v>
+        <x:v>https://openalex.org/W7196930033</x:v>
       </x:c>
       <x:c r="AU62" t="str">
         <x:v>https://proceedings.neurips.cc/paper_files/paper/2025/hash/f062da1973ac9ac61fc6d44dd7fa309f-Abstract-Conference.html；官方摘要/论文集元数据</x:v>
@@ -21071,10 +21071,10 @@
         <x:v>Unknown</x:v>
       </x:c>
       <x:c r="AB63" t="str">
-        <x:v>OpenAlex (no high-confidence title match)</x:v>
+        <x:v>OpenAlex (identity unmatched)</x:v>
       </x:c>
       <x:c r="AC63" t="str">
-        <x:v>2026-09-21</x:v>
+        <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AD63" t="str">
         <x:v>研究主题为 `VLA / Robot Foundation Models`；本卡仅按官方摘要级证据整理，未替代全文审阅。</x:v>
@@ -21258,14 +21258,14 @@
       <x:c r="Z64" t="str">
         <x:v>02_Papers/01_VLA/3D-VLA.md</x:v>
       </x:c>
-      <x:c r="AA64" t="str">
+      <x:c r="AA64" t="n">
         <x:v>14</x:v>
       </x:c>
       <x:c r="AB64" t="str">
         <x:v>OpenAlex</x:v>
       </x:c>
       <x:c r="AC64" t="str">
-        <x:v>2026-09-21</x:v>
+        <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AD64" t="str">
         <x:v>研究主题为 `VLA / Robot Foundation Models; Robot Manipulation / IL / Diffusion`；本卡仅按官方摘要级证据整理，未替代全文审阅。</x:v>
@@ -21316,7 +21316,7 @@
         <x:v>Not Explicitly Reported in the accessible proceedings page.</x:v>
       </x:c>
       <x:c r="AT64" t="str">
-        <x:v>OpenAlex Work: https://openalex.org/W4392886475</x:v>
+        <x:v>https://openalex.org/W4392886475</x:v>
       </x:c>
       <x:c r="AU64" t="str">
         <x:v>https://proceedings.mlr.press/v235/zhen24a.html；官方摘要/论文集元数据</x:v>
@@ -21449,14 +21449,14 @@
       <x:c r="Z65" t="str">
         <x:v>02_Papers/01_VLA/RoboMamba.md</x:v>
       </x:c>
-      <x:c r="AA65" t="str">
+      <x:c r="AA65" t="n">
         <x:v>11</x:v>
       </x:c>
       <x:c r="AB65" t="str">
         <x:v>OpenAlex</x:v>
       </x:c>
       <x:c r="AC65" t="str">
-        <x:v>2026-09-21</x:v>
+        <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AD65" t="str">
         <x:v>研究主题为 `VLA / Robot Foundation Models`；本卡仅按官方摘要级证据整理，未替代全文审阅。</x:v>
@@ -21507,7 +21507,7 @@
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AT65" t="str">
-        <x:v>Unknown (no high-confidence match)</x:v>
+        <x:v>https://openalex.org/W4415797921</x:v>
       </x:c>
       <x:c r="AU65" t="str">
         <x:v>https://proceedings.neurips.cc/paper_files/paper/2024/hash/46a126492ea6fb87410e55a58df2e189-Abstract-Conference.html; https://sites.google.com/view/robomamba-web; https://github.com/lm</x:v>
@@ -21641,13 +21641,13 @@
         <x:v>02_Papers/01_VLA/TraceVLA.md</x:v>
       </x:c>
       <x:c r="AA66" t="str">
-        <x:v>1</x:v>
+        <x:v>Unknown</x:v>
       </x:c>
       <x:c r="AB66" t="str">
-        <x:v>OpenAlex</x:v>
+        <x:v>OpenAlex (identity ambiguous)</x:v>
       </x:c>
       <x:c r="AC66" t="str">
-        <x:v>2026-09-21</x:v>
+        <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AD66" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -21835,10 +21835,10 @@
         <x:v>Unknown</x:v>
       </x:c>
       <x:c r="AB67" t="str">
-        <x:v>OpenAlex (no high-confidence title match)</x:v>
+        <x:v>OpenAlex (identity unmatched)</x:v>
       </x:c>
       <x:c r="AC67" t="str">
-        <x:v>2026-09-21</x:v>
+        <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AD67" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -22021,13 +22021,13 @@
         <x:v>02_Papers/06_Diffusion_Flow_IL_RL/FlowPolicy.md</x:v>
       </x:c>
       <x:c r="AA68" t="str">
-        <x:v>16</x:v>
+        <x:v>Unknown</x:v>
       </x:c>
       <x:c r="AB68" t="str">
-        <x:v>OpenAlex</x:v>
+        <x:v>OpenAlex (identity unmatched)</x:v>
       </x:c>
       <x:c r="AC68" t="str">
-        <x:v>2026-09-21</x:v>
+        <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AD68" t="str">
         <x:v>研究主题为 `Robot Manipulation / IL / Diffusion`；本卡仅按官方摘要级证据整理，未替代全文审阅。</x:v>
@@ -22211,14 +22211,14 @@
       <x:c r="Z69" t="str">
         <x:v>02_Papers/04_Dexterous/UniGraspTransformer.md</x:v>
       </x:c>
-      <x:c r="AA69" t="str">
+      <x:c r="AA69" t="n">
         <x:v>7</x:v>
       </x:c>
       <x:c r="AB69" t="str">
         <x:v>OpenAlex</x:v>
       </x:c>
       <x:c r="AC69" t="str">
-        <x:v>2026-09-21</x:v>
+        <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AD69" t="str">
         <x:v>研究主题为 `Robot Manipulation / IL / Diffusion; Dexterous Hand / Dexterous Manipulation`；本卡仅按官方摘要级证据整理，未替代全文审阅。</x:v>
@@ -22269,7 +22269,7 @@
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AT69" t="str">
-        <x:v>Unknown (no high-confidence match)</x:v>
+        <x:v>https://openalex.org/W4413145029</x:v>
       </x:c>
       <x:c r="AU69" t="str">
         <x:v>https://openaccess.thecvf.com/content/CVPR2025/html/Wang_UniGraspTransformer_Simplified_Policy_Distillation_for_Scalable_Dexterous_Robotic_Grasping_CVPR_2025_paper.html；官方摘要/论文集元数据</x:v>
@@ -22402,14 +22402,14 @@
       <x:c r="Z70" t="str">
         <x:v>02_Papers/04_Dexterous/Scaffolding_Dexterous_Manipulation_with_Vision-Language_Models.md</x:v>
       </x:c>
-      <x:c r="AA70" t="str">
+      <x:c r="AA70" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="AB70" t="str">
         <x:v>OpenAlex</x:v>
       </x:c>
       <x:c r="AC70" t="str">
-        <x:v>2026-09-21</x:v>
+        <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AD70" t="str">
         <x:v>研究主题为 `Dexterous Hand / Dexterous Manipulation`；本卡仅按官方摘要级证据整理，未替代全文审阅。</x:v>
@@ -22460,7 +22460,7 @@
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AT70" t="str">
-        <x:v>Unknown (no high-confidence match)</x:v>
+        <x:v>https://openalex.org/W4414683599</x:v>
       </x:c>
       <x:c r="AU70" t="str">
         <x:v>https://proceedings.neurips.cc/paper_files/paper/2025/hash/862644b156e51c35dea5a7446d640b14-Abstract-Conference.html；官方摘要/论文集元数据</x:v>
@@ -22593,14 +22593,14 @@
       <x:c r="Z71" t="str">
         <x:v>02_Papers/01_VLA/VideoVLA.md</x:v>
       </x:c>
-      <x:c r="AA71" t="str">
+      <x:c r="AA71" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="AB71" t="str">
         <x:v>OpenAlex</x:v>
       </x:c>
       <x:c r="AC71" t="str">
-        <x:v>2026-09-21</x:v>
+        <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AD71" t="str">
         <x:v>研究主题为 `VLA / Robot Foundation Models`；本卡仅按官方摘要级证据整理，未替代全文审阅。</x:v>
@@ -22651,7 +22651,7 @@
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AT71" t="str">
-        <x:v>Unknown (no high-confidence match)</x:v>
+        <x:v>https://openalex.org/W7196952124</x:v>
       </x:c>
       <x:c r="AU71" t="str">
         <x:v>https://proceedings.neurips.cc/paper_files/paper/2025/hash/89a3b655a8b68ae1c76b768152c9c19d-Abstract-Conference.html；官方摘要/论文集元数据</x:v>
@@ -22784,14 +22784,14 @@
       <x:c r="Z72" t="str">
         <x:v>02_Papers/04_Dexterous/DextER.md</x:v>
       </x:c>
-      <x:c r="AA72" t="str">
+      <x:c r="AA72" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="AB72" t="str">
         <x:v>OpenAlex</x:v>
       </x:c>
       <x:c r="AC72" t="str">
-        <x:v>2026-09-21</x:v>
+        <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AD72" t="str">
         <x:v>研究主题为 `Dexterous Hand / Dexterous Manipulation`；本卡仅按官方摘要级证据整理，未替代全文审阅。</x:v>
@@ -22842,7 +22842,7 @@
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AT72" t="str">
-        <x:v>Unknown (no high-confidence match)</x:v>
+        <x:v>https://openalex.org/W7125566978</x:v>
       </x:c>
       <x:c r="AU72" t="str">
         <x:v>https://openaccess.thecvf.com/content/CVPR2026/html/Lee_DextER_Language-driven_Dexterous_Grasp_Generation_with_Embodied_Reasoning_CVPR_2026_paper.html；官方摘要/论文集元数据</x:v>
@@ -22975,14 +22975,14 @@
       <x:c r="Z73" t="str">
         <x:v>02_Papers/01_VLA/SpatialVLA.md</x:v>
       </x:c>
-      <x:c r="AA73" t="str">
+      <x:c r="AA73" t="n">
         <x:v>41</x:v>
       </x:c>
       <x:c r="AB73" t="str">
         <x:v>OpenAlex</x:v>
       </x:c>
       <x:c r="AC73" t="str">
-        <x:v>2026-09-21</x:v>
+        <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AD73" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -23033,7 +23033,7 @@
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AT73" t="str">
-        <x:v>Unknown (no high-confidence match)</x:v>
+        <x:v>https://openalex.org/W4414051092</x:v>
       </x:c>
       <x:c r="AU73" t="str">
         <x:v>Unknown</x:v>
@@ -23166,14 +23166,14 @@
       <x:c r="Z74" t="str">
         <x:v>02_Papers/01_VLA/OpenVLA.md</x:v>
       </x:c>
-      <x:c r="AA74" t="str">
+      <x:c r="AA74" t="n">
         <x:v>43</x:v>
       </x:c>
       <x:c r="AB74" t="str">
         <x:v>OpenAlex</x:v>
       </x:c>
       <x:c r="AC74" t="str">
-        <x:v>2026-09-21</x:v>
+        <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AD74" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -23224,7 +23224,7 @@
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AT74" t="str">
-        <x:v>Unknown (no high-confidence match)</x:v>
+        <x:v>https://openalex.org/W4399695759</x:v>
       </x:c>
       <x:c r="AU74" t="str">
         <x:v>Unknown</x:v>
@@ -23357,14 +23357,14 @@
       <x:c r="Z75" t="str">
         <x:v>02_Papers/01_VLA/Octo.md</x:v>
       </x:c>
-      <x:c r="AA75" t="str">
+      <x:c r="AA75" t="n">
         <x:v>102</x:v>
       </x:c>
       <x:c r="AB75" t="str">
         <x:v>OpenAlex</x:v>
       </x:c>
       <x:c r="AC75" t="str">
-        <x:v>2026-09-21</x:v>
+        <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AD75" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -23415,7 +23415,7 @@
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AT75" t="str">
-        <x:v>Unknown (no high-confidence match)</x:v>
+        <x:v>https://openalex.org/W4402353985</x:v>
       </x:c>
       <x:c r="AU75" t="str">
         <x:v>Unknown</x:v>
@@ -23548,10 +23548,10 @@
         <x:v>Unknown</x:v>
       </x:c>
       <x:c r="AB76" t="str">
-        <x:v>OpenAlex (no high-confidence title match)</x:v>
+        <x:v>OpenAlex (identity unmatched)</x:v>
       </x:c>
       <x:c r="AC76" t="str">
-        <x:v>2026-09-21</x:v>
+        <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AD76" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -23731,14 +23731,14 @@
       <x:c r="Z77" t="str">
         <x:v>02_Papers/10_Benchmark_Dataset/RoboCasa.md</x:v>
       </x:c>
-      <x:c r="AA77" t="str">
-        <x:v>Unknown</x:v>
+      <x:c r="AA77" t="n">
+        <x:v>44</x:v>
       </x:c>
       <x:c r="AB77" t="str">
-        <x:v>OpenAlex (no high-confidence title match)</x:v>
+        <x:v>OpenAlex</x:v>
       </x:c>
       <x:c r="AC77" t="str">
-        <x:v>2026-09-21</x:v>
+        <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AD77" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -23789,7 +23789,7 @@
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AT77" t="str">
-        <x:v>Unknown (no high-confidence match)</x:v>
+        <x:v>https://openalex.org/W4402354126</x:v>
       </x:c>
       <x:c r="AU77" t="str">
         <x:v>Unknown</x:v>
@@ -23922,10 +23922,10 @@
         <x:v>Unknown</x:v>
       </x:c>
       <x:c r="AB78" t="str">
-        <x:v>OpenAlex (no high-confidence title match)</x:v>
+        <x:v>OpenAlex (identity unmatched)</x:v>
       </x:c>
       <x:c r="AC78" t="str">
-        <x:v>2026-09-21</x:v>
+        <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AD78" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -24111,14 +24111,14 @@
       <x:c r="Z79" t="str">
         <x:v>02_Papers/01_VLA/ReconVLA.md</x:v>
       </x:c>
-      <x:c r="AA79" t="str">
+      <x:c r="AA79" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="AB79" t="str">
         <x:v>OpenAlex</x:v>
       </x:c>
       <x:c r="AC79" t="str">
-        <x:v>2026-09-21</x:v>
+        <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AD79" t="str">
         <x:v>现有 VLA 在执行操作时对任务目标区域的视觉注意力往往过于分散，可能关注错误对象，影响精确操作。</x:v>
@@ -24169,7 +24169,7 @@
         <x:v>Not Explicitly Reported in the accessible official abstract/project evidence.</x:v>
       </x:c>
       <x:c r="AT79" t="str">
-        <x:v>OpenAlex Work: https://openalex.org/W7137985120</x:v>
+        <x:v>https://openalex.org/W7137985120</x:v>
       </x:c>
       <x:c r="AU79" t="str">
         <x:v>https://ojs.aaai.org/index.php/AAAI/article/view/38921；https://arxiv.org/abs/2508.10333；https://zionchow.github.io/ReconVLA/；https://github.com/OpenHelix-Team/ReconVLA</x:v>
@@ -24245,7 +24245,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ref9e2238cf614bf0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R51f5e2fd390a42b8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -24695,10 +24695,10 @@
         <x:v>Unknown</x:v>
       </x:c>
       <x:c r="AV2" t="str">
-        <x:v>OpenAlex (no high-confidence title match)</x:v>
+        <x:v>OpenAlex (identity ambiguous)</x:v>
       </x:c>
       <x:c r="AW2" t="str">
-        <x:v>2026-09-21</x:v>
+        <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AX2" t="str">
         <x:v>研究主题为 `Robot Manipulation / IL / Diffusion`；本卡仅按官方摘要级证据整理，未替代全文审阅。</x:v>
@@ -24933,14 +24933,14 @@
       <x:c r="AT3" t="str">
         <x:v>Bimanual</x:v>
       </x:c>
-      <x:c r="AU3" t="str">
+      <x:c r="AU3" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="AV3" t="str">
         <x:v>OpenAlex</x:v>
       </x:c>
       <x:c r="AW3" t="str">
-        <x:v>2026-09-21</x:v>
+        <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AX3" t="str">
         <x:v>研究主题为 `Robot Manipulation / IL / Diffusion; Bimanual`；本卡仅按官方摘要级证据整理，未替代全文审阅。</x:v>
@@ -24988,7 +24988,7 @@
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BM3" t="str">
-        <x:v>Unknown (no high-confidence match)</x:v>
+        <x:v>https://openalex.org/W4415101881</x:v>
       </x:c>
       <x:c r="BN3" t="str">
         <x:v>https://openaccess.thecvf.com/content/ICCV2025/html/Jiang_Rethinking_Bimanual_Robotic_Manipulation_Learning_with_Decoupled_Interaction_Framework_ICCV_2025_paper.html；官方摘要/论文集元数据</x:v>
@@ -25175,14 +25175,14 @@
       <x:c r="AT4" t="str">
         <x:v>Bimanual</x:v>
       </x:c>
-      <x:c r="AU4" t="str">
+      <x:c r="AU4" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="AV4" t="str">
         <x:v>OpenAlex</x:v>
       </x:c>
       <x:c r="AW4" t="str">
-        <x:v>2026-09-21</x:v>
+        <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AX4" t="str">
         <x:v>研究主题为 `Robot Manipulation / IL / Diffusion; Bimanual`；本卡仅按官方摘要级证据整理，未替代全文审阅。</x:v>
@@ -25230,7 +25230,7 @@
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BM4" t="str">
-        <x:v>Unknown (no high-confidence match)</x:v>
+        <x:v>https://openalex.org/W4414754983</x:v>
       </x:c>
       <x:c r="BN4" t="str">
         <x:v>https://openaccess.thecvf.com/content/ICCV2025/html/Xu_Diffusion-Based_Imaginative_Coordination_for_Bimanual_Manipulation_ICCV_2025_paper.html；官方摘要/论文集元数据</x:v>
@@ -25421,10 +25421,10 @@
         <x:v>Unknown</x:v>
       </x:c>
       <x:c r="AV5" t="str">
-        <x:v>OpenAlex (no high-confidence title match)</x:v>
+        <x:v>OpenAlex (identity unmatched)</x:v>
       </x:c>
       <x:c r="AW5" t="str">
-        <x:v>2026-09-21</x:v>
+        <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AX5" t="str">
         <x:v>研究主题为 `Robot Manipulation / IL / Diffusion`；本卡仅按官方摘要级证据整理，未替代全文审阅。</x:v>
@@ -25663,10 +25663,10 @@
         <x:v>Unknown</x:v>
       </x:c>
       <x:c r="AV6" t="str">
-        <x:v>OpenAlex (no high-confidence title match)</x:v>
+        <x:v>OpenAlex (identity unmatched)</x:v>
       </x:c>
       <x:c r="AW6" t="str">
-        <x:v>2026-09-21</x:v>
+        <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AX6" t="str">
         <x:v>研究主题为 `Robot Manipulation / IL / Diffusion`；本卡仅按官方摘要级证据整理，未替代全文审阅。</x:v>
@@ -25905,10 +25905,10 @@
         <x:v>Unknown</x:v>
       </x:c>
       <x:c r="AV7" t="str">
-        <x:v>OpenAlex (no high-confidence title match)</x:v>
+        <x:v>OpenAlex (identity unmatched)</x:v>
       </x:c>
       <x:c r="AW7" t="str">
-        <x:v>2026-09-21</x:v>
+        <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AX7" t="str">
         <x:v>研究主题为 `Robot Manipulation / IL / Diffusion`；本卡仅按官方摘要级证据整理，未替代全文审阅。</x:v>
@@ -26147,10 +26147,10 @@
         <x:v>Unknown</x:v>
       </x:c>
       <x:c r="AV8" t="str">
-        <x:v>OpenAlex (no high-confidence title match)</x:v>
+        <x:v>OpenAlex (identity unmatched)</x:v>
       </x:c>
       <x:c r="AW8" t="str">
-        <x:v>2026-09-21</x:v>
+        <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AX8" t="str">
         <x:v>研究主题为 `Robot Manipulation / IL / Diffusion`；本卡仅按官方摘要级证据整理，未替代全文审阅。</x:v>
@@ -26387,10 +26387,10 @@
         <x:v>Unknown</x:v>
       </x:c>
       <x:c r="AV9" t="str">
-        <x:v>OpenAlex (no high-confidence title match)</x:v>
+        <x:v>OpenAlex (identity unmatched)</x:v>
       </x:c>
       <x:c r="AW9" t="str">
-        <x:v>2026-09-21</x:v>
+        <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AX9" t="str">
         <x:v>研究主题为 `Dexterous Hand / Dexterous Manipulation`；本卡仅按官方摘要级证据整理，未替代全文审阅。</x:v>
@@ -26633,10 +26633,10 @@
         <x:v>Unknown</x:v>
       </x:c>
       <x:c r="AV10" t="str">
-        <x:v>OpenAlex (no high-confidence title match)</x:v>
+        <x:v>OpenAlex (identity unmatched)</x:v>
       </x:c>
       <x:c r="AW10" t="str">
-        <x:v>2026-09-21</x:v>
+        <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AX10" t="str">
         <x:v>研究主题为 `Bimanual; Dataset / Benchmark`；本卡仅按官方摘要级证据整理，未替代全文审阅。</x:v>
@@ -26877,14 +26877,14 @@
       <x:c r="AT11" t="str">
         <x:v>VLA</x:v>
       </x:c>
-      <x:c r="AU11" t="str">
+      <x:c r="AU11" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="AV11" t="str">
         <x:v>OpenAlex</x:v>
       </x:c>
       <x:c r="AW11" t="str">
-        <x:v>2026-09-21</x:v>
+        <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AX11" t="str">
         <x:v>研究主题为 `VLA / Robot Foundation Models`；本卡仅按官方摘要级证据整理，未替代全文审阅。</x:v>
@@ -26932,7 +26932,7 @@
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BM11" t="str">
-        <x:v>Unknown (no high-confidence match)</x:v>
+        <x:v>https://openalex.org/W4415272059</x:v>
       </x:c>
       <x:c r="BN11" t="str">
         <x:v>https://proceedings.neurips.cc/paper_files/paper/2025/hash/5c1a8aa04c1a2cf5013f28831870dafa-Abstract-Conference.html；官方摘要/论文集元数据</x:v>
@@ -27125,14 +27125,14 @@
       <x:c r="AT12" t="str">
         <x:v>VLA</x:v>
       </x:c>
-      <x:c r="AU12" t="str">
+      <x:c r="AU12" t="n">
         <x:v>9</x:v>
       </x:c>
       <x:c r="AV12" t="str">
         <x:v>OpenAlex</x:v>
       </x:c>
       <x:c r="AW12" t="str">
-        <x:v>2026-09-21</x:v>
+        <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AX12" t="str">
         <x:v>研究主题为 `VLA / Robot Foundation Models`；本卡仅按官方摘要级证据整理，未替代全文审阅。</x:v>
@@ -27180,7 +27180,7 @@
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BM12" t="str">
-        <x:v>Unknown (no high-confidence match)</x:v>
+        <x:v>https://openalex.org/W7196930033</x:v>
       </x:c>
       <x:c r="BN12" t="str">
         <x:v>https://proceedings.neurips.cc/paper_files/paper/2025/hash/f062da1973ac9ac61fc6d44dd7fa309f-Abstract-Conference.html；官方摘要/论文集元数据</x:v>
@@ -27377,10 +27377,10 @@
         <x:v>Unknown</x:v>
       </x:c>
       <x:c r="AV13" t="str">
-        <x:v>OpenAlex (no high-confidence title match)</x:v>
+        <x:v>OpenAlex (identity unmatched)</x:v>
       </x:c>
       <x:c r="AW13" t="str">
-        <x:v>2026-09-21</x:v>
+        <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AX13" t="str">
         <x:v>研究主题为 `VLA / Robot Foundation Models`；本卡仅按官方摘要级证据整理，未替代全文审阅。</x:v>
@@ -27621,14 +27621,14 @@
       <x:c r="AT14" t="str">
         <x:v>VLA</x:v>
       </x:c>
-      <x:c r="AU14" t="str">
+      <x:c r="AU14" t="n">
         <x:v>14</x:v>
       </x:c>
       <x:c r="AV14" t="str">
         <x:v>OpenAlex</x:v>
       </x:c>
       <x:c r="AW14" t="str">
-        <x:v>2026-09-21</x:v>
+        <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AX14" t="str">
         <x:v>研究主题为 `VLA / Robot Foundation Models; Robot Manipulation / IL / Diffusion`；本卡仅按官方摘要级证据整理，未替代全文审阅。</x:v>
@@ -27676,7 +27676,7 @@
         <x:v>Not Explicitly Reported in the accessible proceedings page.</x:v>
       </x:c>
       <x:c r="BM14" t="str">
-        <x:v>OpenAlex Work: https://openalex.org/W4392886475</x:v>
+        <x:v>https://openalex.org/W4392886475</x:v>
       </x:c>
       <x:c r="BN14" t="str">
         <x:v>https://proceedings.mlr.press/v235/zhen24a.html；官方摘要/论文集元数据</x:v>
@@ -27869,14 +27869,14 @@
       <x:c r="AT15" t="str">
         <x:v>VLA</x:v>
       </x:c>
-      <x:c r="AU15" t="str">
+      <x:c r="AU15" t="n">
         <x:v>11</x:v>
       </x:c>
       <x:c r="AV15" t="str">
         <x:v>OpenAlex</x:v>
       </x:c>
       <x:c r="AW15" t="str">
-        <x:v>2026-09-21</x:v>
+        <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AX15" t="str">
         <x:v>研究主题为 `VLA / Robot Foundation Models`；本卡仅按官方摘要级证据整理，未替代全文审阅。</x:v>
@@ -27924,7 +27924,7 @@
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BM15" t="str">
-        <x:v>Unknown (no high-confidence match)</x:v>
+        <x:v>https://openalex.org/W4415797921</x:v>
       </x:c>
       <x:c r="BN15" t="str">
         <x:v>https://proceedings.neurips.cc/paper_files/paper/2024/hash/46a126492ea6fb87410e55a58df2e189-Abstract-Conference.html; https://sites.google.com/view/robomamba-web; https://github.com/lm</x:v>
@@ -28116,13 +28116,13 @@
         <x:v>Diffusion / Flow / IL / RL</x:v>
       </x:c>
       <x:c r="AU16" t="str">
-        <x:v>16</x:v>
+        <x:v>Unknown</x:v>
       </x:c>
       <x:c r="AV16" t="str">
-        <x:v>OpenAlex</x:v>
+        <x:v>OpenAlex (identity unmatched)</x:v>
       </x:c>
       <x:c r="AW16" t="str">
-        <x:v>2026-09-21</x:v>
+        <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AX16" t="str">
         <x:v>研究主题为 `Robot Manipulation / IL / Diffusion`；本卡仅按官方摘要级证据整理，未替代全文审阅。</x:v>
@@ -28363,14 +28363,14 @@
       <x:c r="AT17" t="str">
         <x:v>Dexterous</x:v>
       </x:c>
-      <x:c r="AU17" t="str">
+      <x:c r="AU17" t="n">
         <x:v>7</x:v>
       </x:c>
       <x:c r="AV17" t="str">
         <x:v>OpenAlex</x:v>
       </x:c>
       <x:c r="AW17" t="str">
-        <x:v>2026-09-21</x:v>
+        <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AX17" t="str">
         <x:v>研究主题为 `Robot Manipulation / IL / Diffusion; Dexterous Hand / Dexterous Manipulation`；本卡仅按官方摘要级证据整理，未替代全文审阅。</x:v>
@@ -28418,7 +28418,7 @@
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BM17" t="str">
-        <x:v>Unknown (no high-confidence match)</x:v>
+        <x:v>https://openalex.org/W4413145029</x:v>
       </x:c>
       <x:c r="BN17" t="str">
         <x:v>https://openaccess.thecvf.com/content/CVPR2025/html/Wang_UniGraspTransformer_Simplified_Policy_Distillation_for_Scalable_Dexterous_Robotic_Grasping_CVPR_2025_paper.html；官方摘要/论文集元数据</x:v>
@@ -28611,14 +28611,14 @@
       <x:c r="AT18" t="str">
         <x:v>Dexterous</x:v>
       </x:c>
-      <x:c r="AU18" t="str">
+      <x:c r="AU18" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="AV18" t="str">
         <x:v>OpenAlex</x:v>
       </x:c>
       <x:c r="AW18" t="str">
-        <x:v>2026-09-21</x:v>
+        <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AX18" t="str">
         <x:v>研究主题为 `Dexterous Hand / Dexterous Manipulation`；本卡仅按官方摘要级证据整理，未替代全文审阅。</x:v>
@@ -28666,7 +28666,7 @@
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BM18" t="str">
-        <x:v>Unknown (no high-confidence match)</x:v>
+        <x:v>https://openalex.org/W4414683599</x:v>
       </x:c>
       <x:c r="BN18" t="str">
         <x:v>https://proceedings.neurips.cc/paper_files/paper/2025/hash/862644b156e51c35dea5a7446d640b14-Abstract-Conference.html；官方摘要/论文集元数据</x:v>
@@ -28859,14 +28859,14 @@
       <x:c r="AT19" t="str">
         <x:v>VLA</x:v>
       </x:c>
-      <x:c r="AU19" t="str">
+      <x:c r="AU19" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="AV19" t="str">
         <x:v>OpenAlex</x:v>
       </x:c>
       <x:c r="AW19" t="str">
-        <x:v>2026-09-21</x:v>
+        <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AX19" t="str">
         <x:v>研究主题为 `VLA / Robot Foundation Models`；本卡仅按官方摘要级证据整理，未替代全文审阅。</x:v>
@@ -28914,7 +28914,7 @@
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BM19" t="str">
-        <x:v>Unknown (no high-confidence match)</x:v>
+        <x:v>https://openalex.org/W7196952124</x:v>
       </x:c>
       <x:c r="BN19" t="str">
         <x:v>https://proceedings.neurips.cc/paper_files/paper/2025/hash/89a3b655a8b68ae1c76b768152c9c19d-Abstract-Conference.html；官方摘要/论文集元数据</x:v>
@@ -29107,14 +29107,14 @@
       <x:c r="AT20" t="str">
         <x:v>Dexterous</x:v>
       </x:c>
-      <x:c r="AU20" t="str">
+      <x:c r="AU20" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="AV20" t="str">
         <x:v>OpenAlex</x:v>
       </x:c>
       <x:c r="AW20" t="str">
-        <x:v>2026-09-21</x:v>
+        <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AX20" t="str">
         <x:v>研究主题为 `Dexterous Hand / Dexterous Manipulation`；本卡仅按官方摘要级证据整理，未替代全文审阅。</x:v>
@@ -29162,7 +29162,7 @@
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BM20" t="str">
-        <x:v>Unknown (no high-confidence match)</x:v>
+        <x:v>https://openalex.org/W7125566978</x:v>
       </x:c>
       <x:c r="BN20" t="str">
         <x:v>https://openaccess.thecvf.com/content/CVPR2026/html/Lee_DextER_Language-driven_Dexterous_Grasp_Generation_with_Embodied_Reasoning_CVPR_2026_paper.html；官方摘要/论文集元数据</x:v>
@@ -29357,14 +29357,14 @@
       <x:c r="AT21" t="str">
         <x:v>Robot Manipulation</x:v>
       </x:c>
-      <x:c r="AU21" t="str">
+      <x:c r="AU21" t="n">
         <x:v>82</x:v>
       </x:c>
       <x:c r="AV21" t="str">
         <x:v>OpenAlex</x:v>
       </x:c>
       <x:c r="AW21" t="str">
-        <x:v>2026-09-21</x:v>
+        <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AX21" t="str">
         <x:v>研究主题为 `Multimodal / Generali</x:v>
@@ -29412,7 +29412,7 @@
         <x:v>Position predictions are sensitive to lighting and texture domain gaps; suction cannot grasp non-smooth handles and short gripper geometry can cause collisions.</x:v>
       </x:c>
       <x:c r="BM21" t="str">
-        <x:v>OpenAlex Work: https://openalex.org/W4402727730</x:v>
+        <x:v>https://openalex.org/W4402727730</x:v>
       </x:c>
       <x:c r="BN21" t="str">
         <x:v>https://openaccess.thecvf.com/content/CVPR2024/html/Li_ManipLLM_Embodied_Multimodal_Large_Language_Model_for_Object-Centric_Robotic_Manipulation_CVPR_2024_paper.html；官方摘要/论文集元数据</x:v>
@@ -29607,14 +29607,14 @@
       <x:c r="AT22" t="str">
         <x:v>Bimanual</x:v>
       </x:c>
-      <x:c r="AU22" t="str">
+      <x:c r="AU22" t="n">
         <x:v>13</x:v>
       </x:c>
       <x:c r="AV22" t="str">
         <x:v>OpenAlex</x:v>
       </x:c>
       <x:c r="AW22" t="str">
-        <x:v>2026-09-21</x:v>
+        <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AX22" t="str">
         <x:v>研究主题为 `Residual Learning / Sim-to-Real`；本卡仅按官方摘要级证据整理，未替代全文审阅。</x:v>
@@ -29662,7 +29662,7 @@
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BM22" t="str">
-        <x:v>Unknown (no high-confidence match)</x:v>
+        <x:v>https://openalex.org/W4413145126</x:v>
       </x:c>
       <x:c r="BN22" t="str">
         <x:v>https://openaccess.thecvf.com/content/CVPR2025/html/Li_ManipTrans_Efficient_Dexterous_Bimanual_Manipulation_Transfer_via_Residual_Learning_CVPR_2025_paper.html；官方摘要/论文集元数据</x:v>
@@ -29857,14 +29857,14 @@
       <x:c r="AT23" t="str">
         <x:v>Dexterous</x:v>
       </x:c>
-      <x:c r="AU23" t="str">
+      <x:c r="AU23" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="AV23" t="str">
         <x:v>OpenAlex</x:v>
       </x:c>
       <x:c r="AW23" t="str">
-        <x:v>2026-09-21</x:v>
+        <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AX23" t="str">
         <x:v>研究主题为 `Diffusion / Contact-rich Manipulation`；本卡仅按官方摘要级证据整理，未替代全文审阅。</x:v>
@@ -29912,7 +29912,7 @@
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BM23" t="str">
-        <x:v>Unknown (no high-confidence match)</x:v>
+        <x:v>https://openalex.org/W4413146641</x:v>
       </x:c>
       <x:c r="BN23" t="str">
         <x:v>https://openaccess.thecvf.com/content/CVPR2025/html/Liang_DexHandDiff_Interaction-aware_Diffusion_Planning_for_Adaptive_Dexterous_Manipulation_CVPR_2025_paper.html; https://dexdiffuser.github.io/; https://github.com/Liang-</x:v>
@@ -30107,14 +30107,14 @@
       <x:c r="AT24" t="str">
         <x:v>Diffusion / Flow / IL / RL</x:v>
       </x:c>
-      <x:c r="AU24" t="str">
+      <x:c r="AU24" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="AV24" t="str">
         <x:v>OpenAlex</x:v>
       </x:c>
       <x:c r="AW24" t="str">
-        <x:v>2026-09-21</x:v>
+        <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AX24" t="str">
         <x:v>研究主题为 `Human Video / VLM`；本卡仅按官方摘要级证据整理，未替代全文审阅。</x:v>
@@ -30162,7 +30162,7 @@
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BM24" t="str">
-        <x:v>Unknown (no high-confidence match)</x:v>
+        <x:v>https://openalex.org/W4416242580</x:v>
       </x:c>
       <x:c r="BN24" t="str">
         <x:v>https://openaccess.thecvf.com/content/ICCV2025/html/Yang_AR-VRM_Imitating_Human_Motions_for_Visual_Robot_Manipulation_with_Analogical_ICCV_2025_paper.html；官方摘要/论文集元数据</x:v>
@@ -30357,14 +30357,14 @@
       <x:c r="AT25" t="str">
         <x:v>Dexterous</x:v>
       </x:c>
-      <x:c r="AU25" t="str">
+      <x:c r="AU25" t="n">
         <x:v>29</x:v>
       </x:c>
       <x:c r="AV25" t="str">
         <x:v>OpenAlex</x:v>
       </x:c>
       <x:c r="AW25" t="str">
-        <x:v>2026-09-21</x:v>
+        <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AX25" t="str">
         <x:v>研究主题为 `Dexterous Grasping`；本卡仅按官方摘要级证据整理，未替代全文审阅。</x:v>
@@ -30412,7 +30412,7 @@
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BM25" t="str">
-        <x:v>Unknown (no high-confidence match)</x:v>
+        <x:v>https://openalex.org/W4402816741</x:v>
       </x:c>
       <x:c r="BN25" t="str">
         <x:v>https://openaccess.thecvf.com/content/CVPR2024/html/Xu_Dexterous_Grasp_Transformer_CVPR_2024_paper.html；官方摘要/论文集元数据</x:v>
@@ -30607,14 +30607,14 @@
       <x:c r="AT26" t="str">
         <x:v>VLA</x:v>
       </x:c>
-      <x:c r="AU26" t="str">
+      <x:c r="AU26" t="n">
         <x:v>16</x:v>
       </x:c>
       <x:c r="AV26" t="str">
         <x:v>OpenAlex</x:v>
       </x:c>
       <x:c r="AW26" t="str">
-        <x:v>2026-09-21</x:v>
+        <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AX26" t="str">
         <x:v>研究主题为 `Mobile Manipulation`；本卡仅按官方摘要级证据整理，未替代全文审阅。</x:v>
@@ -30662,7 +30662,7 @@
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BM26" t="str">
-        <x:v>Unknown (no high-confidence match)</x:v>
+        <x:v>https://openalex.org/W4413147465</x:v>
       </x:c>
       <x:c r="BN26" t="str">
         <x:v>https://openaccess.thecvf.com/content/CVPR2025/html/Wu_MoManipVLA_Transferring_Vision-language-action_Models_for_General_Mobile_Manipulation_CVPR_2025_paper.html；官方摘要/论文集元数据</x:v>
@@ -30857,14 +30857,14 @@
       <x:c r="AT27" t="str">
         <x:v>Diffusion / Flow / IL / RL</x:v>
       </x:c>
-      <x:c r="AU27" t="str">
+      <x:c r="AU27" t="n">
         <x:v>17</x:v>
       </x:c>
       <x:c r="AV27" t="str">
         <x:v>OpenAlex</x:v>
       </x:c>
       <x:c r="AW27" t="str">
-        <x:v>2026-09-21</x:v>
+        <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AX27" t="str">
         <x:v>研究主题为 `Action Chunking / Multi-task Policy`；本卡仅按官方摘要级证据整理，未替代全文审阅。</x:v>
@@ -30912,7 +30912,7 @@
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BM27" t="str">
-        <x:v>Unknown (no high-confidence match)</x:v>
+        <x:v>https://openalex.org/W4415800339</x:v>
       </x:c>
       <x:c r="BN27" t="str">
         <x:v>https://proceedings.neurips.cc/paper_files/paper/2024/hash/ff887781480973bd3cb6026feb378d1e-Abstract-Conference.html；官方摘要/论文集元数据</x:v>
@@ -31107,14 +31107,14 @@
       <x:c r="AT28" t="str">
         <x:v>Benchmark / Dataset</x:v>
       </x:c>
-      <x:c r="AU28" t="str">
-        <x:v>Unknown</x:v>
+      <x:c r="AU28" t="n">
+        <x:v>4</x:v>
       </x:c>
       <x:c r="AV28" t="str">
-        <x:v>OpenAlex (no high-confidence title match)</x:v>
+        <x:v>OpenAlex</x:v>
       </x:c>
       <x:c r="AW28" t="str">
-        <x:v>2026-09-21</x:v>
+        <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AX28" t="str">
         <x:v>研究主题为 `Surgical Robotics`；本卡仅按官方摘要级证据整理，未替代全文审阅。</x:v>
@@ -31162,7 +31162,7 @@
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BM28" t="str">
-        <x:v>Unknown (no high-confidence match)</x:v>
+        <x:v>https://openalex.org/W4415796959</x:v>
       </x:c>
       <x:c r="BN28" t="str">
         <x:v>https://proceedings.neurips.cc/paper_files/paper/2024/hash/74c4f2b87b7499d365422152c76fd916-Abstract-Datasets_and_Benchmarks_Track.html；官方摘要/论文集元数据</x:v>
@@ -31357,14 +31357,14 @@
       <x:c r="AT29" t="str">
         <x:v>Diffusion / Flow / IL / RL</x:v>
       </x:c>
-      <x:c r="AU29" t="str">
-        <x:v>Unknown</x:v>
+      <x:c r="AU29" t="n">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AV29" t="str">
-        <x:v>OpenAlex (no high-confidence title match)</x:v>
+        <x:v>OpenAlex</x:v>
       </x:c>
       <x:c r="AW29" t="str">
-        <x:v>2026-09-21</x:v>
+        <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AX29" t="str">
         <x:v>研究主题为 `Video Demonstration / Reward Learning`；本卡仅按官方摘要级证据整理，未替代全文审阅。</x:v>
@@ -31412,7 +31412,7 @@
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BM29" t="str">
-        <x:v>Unknown (no high-confidence match)</x:v>
+        <x:v>https://openalex.org/W4415795570</x:v>
       </x:c>
       <x:c r="BN29" t="str">
         <x:v>https://proceedings.neurips.cc/paper_files/paper/2024/hash/dcd297696d0bb304ba426b3c5a679c37-Abstract-Conference.html；官方摘要/论文集元数据</x:v>
@@ -31607,14 +31607,14 @@
       <x:c r="AT30" t="str">
         <x:v>Generalization / Long-Horizon</x:v>
       </x:c>
-      <x:c r="AU30" t="str">
-        <x:v>Unknown</x:v>
+      <x:c r="AU30" t="n">
+        <x:v>10</x:v>
       </x:c>
       <x:c r="AV30" t="str">
-        <x:v>OpenAlex (no high-confidence title match)</x:v>
+        <x:v>OpenAlex</x:v>
       </x:c>
       <x:c r="AW30" t="str">
-        <x:v>2026-09-21</x:v>
+        <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AX30" t="str">
         <x:v>研究主题为 `Long-Hori</x:v>
@@ -31662,7 +31662,7 @@
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BM30" t="str">
-        <x:v>Unknown (no high-confidence match)</x:v>
+        <x:v>https://openalex.org/W4415800541</x:v>
       </x:c>
       <x:c r="BN30" t="str">
         <x:v>https://proceedings.neurips.cc/paper_files/paper/2024/hash/fad8962279154544ed69bb63eb14d677-Abstract-Conference.html；官方摘要/论文集元数据</x:v>
@@ -31857,14 +31857,14 @@
       <x:c r="AT31" t="str">
         <x:v>Benchmark / Dataset</x:v>
       </x:c>
-      <x:c r="AU31" t="str">
-        <x:v>Unknown</x:v>
+      <x:c r="AU31" t="n">
+        <x:v>10</x:v>
       </x:c>
       <x:c r="AV31" t="str">
-        <x:v>OpenAlex (no high-confidence title match)</x:v>
+        <x:v>OpenAlex</x:v>
       </x:c>
       <x:c r="AW31" t="str">
-        <x:v>2026-09-21</x:v>
+        <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AX31" t="str">
         <x:v>研究主题为 `3D Observation / Contact-rich`；本卡仅按官方摘要级证据整理，未替代全文审阅。</x:v>
@@ -31912,7 +31912,7 @@
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BM31" t="str">
-        <x:v>Unknown (no high-confidence match)</x:v>
+        <x:v>https://openalex.org/W4415797227</x:v>
       </x:c>
       <x:c r="BN31" t="str">
         <x:v>https://proceedings.neurips.cc/paper_files/paper/2024/hash/8e5dc5969a6174fcaaececd890c7f59b-Abstract-Datasets_and_Benchmarks_Track.html；官方摘要/论文集元数据</x:v>
@@ -32107,14 +32107,14 @@
       <x:c r="AT32" t="str">
         <x:v>Diffusion / Flow / IL / RL</x:v>
       </x:c>
-      <x:c r="AU32" t="str">
-        <x:v>Unknown</x:v>
+      <x:c r="AU32" t="n">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AV32" t="str">
-        <x:v>OpenAlex (no high-confidence title match)</x:v>
+        <x:v>OpenAlex</x:v>
       </x:c>
       <x:c r="AW32" t="str">
-        <x:v>2026-09-21</x:v>
+        <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AX32" t="str">
         <x:v>研究主题为 `Text-conditioned Reward`；本卡仅按官方摘要级证据整理，未替代全文审阅。</x:v>
@@ -32162,7 +32162,7 @@
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BM32" t="str">
-        <x:v>Unknown (no high-confidence match)</x:v>
+        <x:v>https://openalex.org/W4415797662</x:v>
       </x:c>
       <x:c r="BN32" t="str">
         <x:v>https://proceedings.neurips.cc/paper_files/paper/2024/hash/5227ce00add5aa0a12d1c4ee92fcd2dc-Abstract-Conference.html；官方摘要/论文集元数据</x:v>
@@ -32361,10 +32361,10 @@
         <x:v>Unknown</x:v>
       </x:c>
       <x:c r="AV33" t="str">
-        <x:v>OpenAlex (no high-confidence title match)</x:v>
+        <x:v>OpenAlex (identity unmatched)</x:v>
       </x:c>
       <x:c r="AW33" t="str">
-        <x:v>2026-09-21</x:v>
+        <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AX33" t="str">
         <x:v>研究主题为 `Human-Robot Domain Adaptation`；本卡仅按官方摘要级证据整理，未替代全文审阅。</x:v>
@@ -32607,14 +32607,14 @@
       <x:c r="AT34" t="str">
         <x:v>VLA</x:v>
       </x:c>
-      <x:c r="AU34" t="str">
+      <x:c r="AU34" t="n">
         <x:v>10</x:v>
       </x:c>
       <x:c r="AV34" t="str">
         <x:v>OpenAlex</x:v>
       </x:c>
       <x:c r="AW34" t="str">
-        <x:v>2026-09-21</x:v>
+        <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AX34" t="str">
         <x:v>研究主题为 `Grounding / Synthetic Data`；本卡仅按官方摘要级证据整理，未替代全文审阅。</x:v>
@@ -32662,7 +32662,7 @@
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BM34" t="str">
-        <x:v>Unknown (no high-confidence match)</x:v>
+        <x:v>https://openalex.org/W4413147462</x:v>
       </x:c>
       <x:c r="BN34" t="str">
         <x:v>https://openaccess.thecvf.com/content/CVPR2025/html/Huang_RoboGround_Robotic_Manipulation_with_Grounded_Vision-Language_Priors_CVPR_2025_paper.html；官方摘要/论文集元数据</x:v>
@@ -32857,14 +32857,14 @@
       <x:c r="AT35" t="str">
         <x:v>Data / Teleoperation</x:v>
       </x:c>
-      <x:c r="AU35" t="str">
-        <x:v>Unknown</x:v>
+      <x:c r="AU35" t="n">
+        <x:v>6</x:v>
       </x:c>
       <x:c r="AV35" t="str">
-        <x:v>OpenAlex (no high-confidence title match)</x:v>
+        <x:v>OpenAlex</x:v>
       </x:c>
       <x:c r="AW35" t="str">
-        <x:v>2026-09-21</x:v>
+        <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AX35" t="str">
         <x:v>研究主题为 `Synthetic Data / Scene Generation`；本卡仅按官方摘要级证据整理，未替代全文审阅。</x:v>
@@ -32912,7 +32912,7 @@
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BM35" t="str">
-        <x:v>Unknown (no high-confidence match)</x:v>
+        <x:v>https://openalex.org/W4413147695</x:v>
       </x:c>
       <x:c r="BN35" t="str">
         <x:v>https://openaccess.thecvf.com/content/CVPR2025/html/Lee_DynScene_Scalable_Generation_of_Dynamic_Robotic_Manipulation_Scenes_for_Embodied_CVPR_2025_paper.html；官方摘要/论文集元数据</x:v>
@@ -33111,10 +33111,10 @@
         <x:v>Unknown</x:v>
       </x:c>
       <x:c r="AV36" t="str">
-        <x:v>OpenAlex (no high-confidence title match)</x:v>
+        <x:v>OpenAlex (identity ambiguous)</x:v>
       </x:c>
       <x:c r="AW36" t="str">
-        <x:v>2026-09-21</x:v>
+        <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AX36" t="str">
         <x:v>研究主题为 `Lifelong Learning`；本卡仅按官方摘要级证据整理，未替代全文审阅。</x:v>
@@ -33361,10 +33361,10 @@
         <x:v>Unknown</x:v>
       </x:c>
       <x:c r="AV37" t="str">
-        <x:v>OpenAlex (no high-confidence title match)</x:v>
+        <x:v>OpenAlex (identity unmatched)</x:v>
       </x:c>
       <x:c r="AW37" t="str">
-        <x:v>2026-09-21</x:v>
+        <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AX37" t="str">
         <x:v>研究主题为 `Failure Recovery / 3D Gaussian Splatting`；本卡仅按官方摘要级证据整理，未替代全文审阅。</x:v>
@@ -33611,10 +33611,10 @@
         <x:v>Unknown</x:v>
       </x:c>
       <x:c r="AV38" t="str">
-        <x:v>OpenAlex (no high-confidence title match)</x:v>
+        <x:v>OpenAlex (identity unmatched)</x:v>
       </x:c>
       <x:c r="AW38" t="str">
-        <x:v>2026-09-21</x:v>
+        <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AX38" t="str">
         <x:v>研究主题为 `Articulated Object / Affordance`；本卡仅按官方摘要级证据整理，未替代全文审阅。</x:v>
@@ -33861,10 +33861,10 @@
         <x:v>Unknown</x:v>
       </x:c>
       <x:c r="AV39" t="str">
-        <x:v>OpenAlex (no high-confidence title match)</x:v>
+        <x:v>OpenAlex (identity unmatched)</x:v>
       </x:c>
       <x:c r="AW39" t="str">
-        <x:v>2026-09-21</x:v>
+        <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AX39" t="str">
         <x:v>研究主题为 `Long-Hori</x:v>
@@ -34107,14 +34107,14 @@
       <x:c r="AT40" t="str">
         <x:v>Robot Manipulation</x:v>
       </x:c>
-      <x:c r="AU40" t="str">
-        <x:v>0</x:v>
+      <x:c r="AU40" t="n">
+        <x:v>3</x:v>
       </x:c>
       <x:c r="AV40" t="str">
         <x:v>OpenAlex</x:v>
       </x:c>
       <x:c r="AW40" t="str">
-        <x:v>2026-09-21</x:v>
+        <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AX40" t="str">
         <x:v>研究主题为 `World Model / Video Diffusion`；本卡仅按官方摘要级证据整理，未替代全文审阅。</x:v>
@@ -34162,7 +34162,7 @@
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BM40" t="str">
-        <x:v>Unknown (no high-confidence match)</x:v>
+        <x:v>https://openalex.org/W7103754590</x:v>
       </x:c>
       <x:c r="BN40" t="str">
         <x:v>https://proceedings.neurips.cc/paper_files/paper/2024/hash/481c70828a4ff20d31a646cc6cc95f3d-Abstract-Conference.html；官方摘要/论文集元数据</x:v>
@@ -34357,14 +34357,14 @@
       <x:c r="AT41" t="str">
         <x:v>Generalization / Long-Horizon</x:v>
       </x:c>
-      <x:c r="AU41" t="str">
-        <x:v>Unknown</x:v>
+      <x:c r="AU41" t="n">
+        <x:v>8</x:v>
       </x:c>
       <x:c r="AV41" t="str">
-        <x:v>OpenAlex (no high-confidence title match)</x:v>
+        <x:v>OpenAlex</x:v>
       </x:c>
       <x:c r="AW41" t="str">
-        <x:v>2026-09-21</x:v>
+        <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AX41" t="str">
         <x:v>研究主题为 `Human Video / 3D Affordance`；本卡仅按官方摘要级证据整理，未替代全文审阅。</x:v>
@@ -34412,7 +34412,7 @@
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BM41" t="str">
-        <x:v>Unknown (no high-confidence match)</x:v>
+        <x:v>https://openalex.org/W4413144616</x:v>
       </x:c>
       <x:c r="BN41" t="str">
         <x:v>https://openaccess.thecvf.com/content/CVPR2025/html/Chen_VidBot_Learning_Generali</x:v>
@@ -34607,14 +34607,14 @@
       <x:c r="AT42" t="str">
         <x:v>VLA</x:v>
       </x:c>
-      <x:c r="AU42" t="str">
+      <x:c r="AU42" t="n">
         <x:v>57</x:v>
       </x:c>
       <x:c r="AV42" t="str">
         <x:v>OpenAlex</x:v>
       </x:c>
       <x:c r="AW42" t="str">
-        <x:v>2026-09-21</x:v>
+        <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AX42" t="str">
         <x:v>研究主题为 `Visual Chain-of-Thought`；本卡仅按官方摘要级证据整理，未替代全文审阅。</x:v>
@@ -34662,7 +34662,7 @@
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BM42" t="str">
-        <x:v>Unknown (no high-confidence match)</x:v>
+        <x:v>https://openalex.org/W4413156213</x:v>
       </x:c>
       <x:c r="BN42" t="str">
         <x:v>https://openaccess.thecvf.com/content/CVPR2025/html/</x:v>
@@ -34857,14 +34857,14 @@
       <x:c r="AT43" t="str">
         <x:v>Sim2Real</x:v>
       </x:c>
-      <x:c r="AU43" t="str">
-        <x:v>Unknown</x:v>
+      <x:c r="AU43" t="n">
+        <x:v>0</x:v>
       </x:c>
       <x:c r="AV43" t="str">
-        <x:v>OpenAlex (no high-confidence title match)</x:v>
+        <x:v>OpenAlex</x:v>
       </x:c>
       <x:c r="AW43" t="str">
-        <x:v>2026-09-21</x:v>
+        <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AX43" t="str">
         <x:v>研究主题为 `Sim-to-Real / Behavior Cloning`；本卡仅按官方摘要级证据整理，未替代全文审阅。</x:v>
@@ -34912,7 +34912,7 @@
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BM43" t="str">
-        <x:v>Unknown (no high-confidence match)</x:v>
+        <x:v>https://openalex.org/W4415251366</x:v>
       </x:c>
       <x:c r="BN43" t="str">
         <x:v>https://proceedings.neurips.cc/paper_files/paper/2025/hash/1185c89347a3f21ffc48c9d083c9437c-Abstract-Conference.html；官方摘要/论文集元数据</x:v>
@@ -35107,14 +35107,14 @@
       <x:c r="AT44" t="str">
         <x:v>Generalization / Long-Horizon</x:v>
       </x:c>
-      <x:c r="AU44" t="str">
-        <x:v>Unknown</x:v>
+      <x:c r="AU44" t="n">
+        <x:v>0</x:v>
       </x:c>
       <x:c r="AV44" t="str">
-        <x:v>OpenAlex (no high-confidence title match)</x:v>
+        <x:v>OpenAlex</x:v>
       </x:c>
       <x:c r="AW44" t="str">
-        <x:v>2026-09-21</x:v>
+        <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AX44" t="str">
         <x:v>研究主题为 `Long-Hori</x:v>
@@ -35162,7 +35162,7 @@
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BM44" t="str">
-        <x:v>Unknown (no high-confidence match)</x:v>
+        <x:v>https://openalex.org/W7196926233</x:v>
       </x:c>
       <x:c r="BN44" t="str">
         <x:v>https://proceedings.neurips.cc/paper_files/paper/2025/hash/b94310e1c7ecb79f1a24adc757f1b89b-Abstract-Conference.html；官方摘要/论文集元数据</x:v>
@@ -35357,14 +35357,14 @@
       <x:c r="AT45" t="str">
         <x:v>Diffusion / Flow / IL / RL</x:v>
       </x:c>
-      <x:c r="AU45" t="str">
+      <x:c r="AU45" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="AV45" t="str">
         <x:v>OpenAlex</x:v>
       </x:c>
       <x:c r="AW45" t="str">
-        <x:v>2026-09-21</x:v>
+        <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AX45" t="str">
         <x:v>研究主题为 `Stochastic Interpolant / Efficiency`；本卡仅按官方摘要级证据整理，未替代全文审阅。</x:v>
@@ -35412,7 +35412,7 @@
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BM45" t="str">
-        <x:v>Unknown (no high-confidence match)</x:v>
+        <x:v>https://openalex.org/W7196975408</x:v>
       </x:c>
       <x:c r="BN45" t="str">
         <x:v>https://proceedings.neurips.cc/paper_files/paper/2025/hash/49eadcc4a329fc6b74b9f8a82b78cbc3-Abstract-Conference.html；官方摘要/论文集元数据</x:v>
@@ -35607,14 +35607,14 @@
       <x:c r="AT46" t="str">
         <x:v>Generalization / Long-Horizon</x:v>
       </x:c>
-      <x:c r="AU46" t="str">
-        <x:v>Unknown</x:v>
+      <x:c r="AU46" t="n">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AV46" t="str">
-        <x:v>OpenAlex (no high-confidence title match)</x:v>
+        <x:v>OpenAlex</x:v>
       </x:c>
       <x:c r="AW46" t="str">
-        <x:v>2026-09-21</x:v>
+        <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AX46" t="str">
         <x:v>研究主题为 `Mobile Manipulation / Agent`；本卡仅按官方摘要级证据整理，未替代全文审阅。</x:v>
@@ -35662,7 +35662,7 @@
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BM46" t="str">
-        <x:v>Unknown (no high-confidence match)</x:v>
+        <x:v>https://openalex.org/W7197036842</x:v>
       </x:c>
       <x:c r="BN46" t="str">
         <x:v>https://proceedings.neurips.cc/paper_files/paper/2025/hash/bc97207e3979d1cc23109db0be0e8ed2-Abstract-Conference.html；官方摘要/论文集元数据</x:v>
@@ -35857,14 +35857,14 @@
       <x:c r="AT47" t="str">
         <x:v>Diffusion / Flow / IL / RL</x:v>
       </x:c>
-      <x:c r="AU47" t="str">
-        <x:v>Unknown</x:v>
+      <x:c r="AU47" t="n">
+        <x:v>0</x:v>
       </x:c>
       <x:c r="AV47" t="str">
-        <x:v>OpenAlex (no high-confidence title match)</x:v>
+        <x:v>OpenAlex</x:v>
       </x:c>
       <x:c r="AW47" t="str">
-        <x:v>2026-09-21</x:v>
+        <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AX47" t="str">
         <x:v>研究主题为 `Flow Matching / Visuomotor Policy`；本卡仅按官方摘要级证据整理，未替代全文审阅。</x:v>
@@ -35912,7 +35912,7 @@
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BM47" t="str">
-        <x:v>Unknown (no high-confidence match)</x:v>
+        <x:v>https://openalex.org/W4417258107</x:v>
       </x:c>
       <x:c r="BN47" t="str">
         <x:v>https://proceedings.neurips.cc/paper_files/paper/2025/hash/282c3318be1b047b7bb5ba94fa4f3231-Abstract-Conference.html；官方摘要/论文集元数据</x:v>
@@ -36107,14 +36107,14 @@
       <x:c r="AT48" t="str">
         <x:v>Robot Manipulation</x:v>
       </x:c>
-      <x:c r="AU48" t="str">
+      <x:c r="AU48" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="AV48" t="str">
         <x:v>OpenAlex</x:v>
       </x:c>
       <x:c r="AW48" t="str">
-        <x:v>2026-09-21</x:v>
+        <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AX48" t="str">
         <x:v>研究主题为 `Tool Use / Generative Design`；本卡仅按官方摘要级证据整理，未替代全文审阅。</x:v>
@@ -36162,7 +36162,7 @@
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BM48" t="str">
-        <x:v>Unknown (no high-confidence match)</x:v>
+        <x:v>https://openalex.org/W4415312722</x:v>
       </x:c>
       <x:c r="BN48" t="str">
         <x:v>https://proceedings.neurips.cc/paper_files/paper/2025/hash/9fc291fef2f9607a46777d367f900a15-Abstract-Conference.html；官方摘要/论文集元数据</x:v>
@@ -36357,14 +36357,14 @@
       <x:c r="AT49" t="str">
         <x:v>Diffusion / Flow / IL / RL</x:v>
       </x:c>
-      <x:c r="AU49" t="str">
-        <x:v>Unknown</x:v>
+      <x:c r="AU49" t="n">
+        <x:v>0</x:v>
       </x:c>
       <x:c r="AV49" t="str">
-        <x:v>OpenAlex (no high-confidence title match)</x:v>
+        <x:v>OpenAlex</x:v>
       </x:c>
       <x:c r="AW49" t="str">
-        <x:v>2026-09-21</x:v>
+        <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AX49" t="str">
         <x:v>研究主题为 `3D Manipulation / Multimodal Policy`；本卡仅按官方摘要级证据整理，未替代全文审阅。</x:v>
@@ -36412,7 +36412,7 @@
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BM49" t="str">
-        <x:v>Unknown (no high-confidence match)</x:v>
+        <x:v>https://openalex.org/W4417082659</x:v>
       </x:c>
       <x:c r="BN49" t="str">
         <x:v>https://proceedings.neurips.cc/paper_files/paper/2025/hash/eacc8ae341d15d2c13c02fef88189db3-Abstract-Conference.html；官方摘要/论文集元数据</x:v>
@@ -36607,14 +36607,14 @@
       <x:c r="AT50" t="str">
         <x:v>Data / Teleoperation</x:v>
       </x:c>
-      <x:c r="AU50" t="str">
-        <x:v>Unknown</x:v>
+      <x:c r="AU50" t="n">
+        <x:v>0</x:v>
       </x:c>
       <x:c r="AV50" t="str">
-        <x:v>OpenAlex (no high-confidence title match)</x:v>
+        <x:v>OpenAlex</x:v>
       </x:c>
       <x:c r="AW50" t="str">
-        <x:v>2026-09-21</x:v>
+        <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AX50" t="str">
         <x:v>研究主题为 `Robot Data / Spatial Reasoning`；本卡仅按官方摘要级证据整理，未替代全文审阅。</x:v>
@@ -36662,7 +36662,7 @@
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BM50" t="str">
-        <x:v>Unknown (no high-confidence match)</x:v>
+        <x:v>https://openalex.org/W7196982428</x:v>
       </x:c>
       <x:c r="BN50" t="str">
         <x:v>https://proceedings.neurips.cc/paper_files/paper/2025/hash/1f467c3e37abf9f86c78f44c6a27ee7c-Abstract-Datasets_and_Benchmarks_Track.html；官方摘要/论文集元数据</x:v>
@@ -36857,14 +36857,14 @@
       <x:c r="AT51" t="str">
         <x:v>Generalization / Long-Horizon</x:v>
       </x:c>
-      <x:c r="AU51" t="str">
-        <x:v>Unknown</x:v>
+      <x:c r="AU51" t="n">
+        <x:v>0</x:v>
       </x:c>
       <x:c r="AV51" t="str">
-        <x:v>OpenAlex (no high-confidence title match)</x:v>
+        <x:v>OpenAlex</x:v>
       </x:c>
       <x:c r="AW51" t="str">
-        <x:v>2026-09-21</x:v>
+        <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AX51" t="str">
         <x:v>研究主题为 `Task Planning / Demonstrations`；本卡仅按官方摘要级证据整理，未替代全文审阅。</x:v>
@@ -36912,7 +36912,7 @@
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BM51" t="str">
-        <x:v>Unknown (no high-confidence match)</x:v>
+        <x:v>https://openalex.org/W7196933803</x:v>
       </x:c>
       <x:c r="BN51" t="str">
         <x:v>https://proceedings.neurips.cc/paper_files/paper/2025/hash/b8358a00e5b870194b974ddf8dd415c3-Abstract-Conference.html；官方摘要/论文集元数据</x:v>
@@ -37107,14 +37107,14 @@
       <x:c r="AT52" t="str">
         <x:v>Benchmark / Dataset</x:v>
       </x:c>
-      <x:c r="AU52" t="str">
-        <x:v>Unknown</x:v>
+      <x:c r="AU52" t="n">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AV52" t="str">
-        <x:v>OpenAlex (no high-confidence title match)</x:v>
+        <x:v>OpenAlex</x:v>
       </x:c>
       <x:c r="AW52" t="str">
-        <x:v>2026-09-21</x:v>
+        <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AX52" t="str">
         <x:v>研究主题为 `Human-to-Robot Handover / Teleoperation`；本卡仅按官方摘要级证据整理，未替代全文审阅。</x:v>
@@ -37162,7 +37162,7 @@
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BM52" t="str">
-        <x:v>Unknown (no high-confidence match)</x:v>
+        <x:v>https://openalex.org/W7160048141</x:v>
       </x:c>
       <x:c r="BN52" t="str">
         <x:v>https://openaccess.thecvf.com/content/ICCV2025/html/Wang_DexH2R_A_Benchmark_for_Dynamic_Dexterous_Grasping_in_Human-to-Robot_Handover_ICCV_2025_paper.html；官方摘要/论文集元数据</x:v>
@@ -37357,14 +37357,14 @@
       <x:c r="AT53" t="str">
         <x:v>Bimanual</x:v>
       </x:c>
-      <x:c r="AU53" t="str">
+      <x:c r="AU53" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="AV53" t="str">
         <x:v>OpenAlex</x:v>
       </x:c>
       <x:c r="AW53" t="str">
-        <x:v>2026-09-21</x:v>
+        <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AX53" t="str">
         <x:v>研究主题为 `3D Hand-Object Interaction / Articulated Objects`；本卡仅按官方摘要级证据整理，未替代全文审阅。</x:v>
@@ -37412,7 +37412,7 @@
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BM53" t="str">
-        <x:v>Unknown (no high-confidence match)</x:v>
+        <x:v>https://openalex.org/W4413145043</x:v>
       </x:c>
       <x:c r="BN53" t="str">
         <x:v>https://openaccess.thecvf.com/content/CVPR2025/html/</x:v>
@@ -37607,14 +37607,14 @@
       <x:c r="AT54" t="str">
         <x:v>Dexterous</x:v>
       </x:c>
-      <x:c r="AU54" t="str">
+      <x:c r="AU54" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="AV54" t="str">
         <x:v>OpenAlex</x:v>
       </x:c>
       <x:c r="AW54" t="str">
-        <x:v>2026-09-21</x:v>
+        <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AX54" t="str">
         <x:v>研究主题为 `Vision-Language-Grasp / Flow Matching`；本卡仅按官方摘要级证据整理，未替代全文审阅。</x:v>
@@ -37662,7 +37662,7 @@
         <x:v>The reported setting focuses on tabletop part-aligned grasps; broader clutter, occlusion and multi-step manipulation are not established by the cited results.</x:v>
       </x:c>
       <x:c r="BM54" t="str">
-        <x:v>OpenAlex Work: https://openalex.org/W4417183400</x:v>
+        <x:v>https://openalex.org/W4417183400</x:v>
       </x:c>
       <x:c r="BN54" t="str">
         <x:v>https://openaccess.thecvf.com/content/ICCV2025/html/He_DexVLG_Dexterous_Vision-Language-Grasp_Model_at_Scale_ICCV_2025_paper.html；官方摘要/论文集元数据</x:v>
@@ -37857,14 +37857,14 @@
       <x:c r="AT55" t="str">
         <x:v>Dexterous</x:v>
       </x:c>
-      <x:c r="AU55" t="str">
+      <x:c r="AU55" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="AV55" t="str">
         <x:v>OpenAlex</x:v>
       </x:c>
       <x:c r="AW55" t="str">
-        <x:v>2026-09-21</x:v>
+        <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AX55" t="str">
         <x:v>研究主题为 `Hand-Object Motion / Generali</x:v>
@@ -37912,7 +37912,7 @@
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BM55" t="str">
-        <x:v>Unknown (no high-confidence match)</x:v>
+        <x:v>https://openalex.org/W4413146191</x:v>
       </x:c>
       <x:c r="BN55" t="str">
         <x:v>https://openaccess.thecvf.com/content/CVPR2025/html/Li_LatentHOI_On_the_Generali</x:v>
@@ -38111,10 +38111,10 @@
         <x:v>Unknown</x:v>
       </x:c>
       <x:c r="AV56" t="str">
-        <x:v>OpenAlex (no high-confidence title match)</x:v>
+        <x:v>OpenAlex (identity unmatched)</x:v>
       </x:c>
       <x:c r="AW56" t="str">
-        <x:v>2026-09-21</x:v>
+        <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AX56" t="str">
         <x:v>研究主题为 `Tool-Action-Object Understanding`；本卡仅按官方摘要级证据整理，未替代全文审阅。</x:v>
@@ -38357,14 +38357,14 @@
       <x:c r="AT57" t="str">
         <x:v>Robot Manipulation</x:v>
       </x:c>
-      <x:c r="AU57" t="str">
+      <x:c r="AU57" t="n">
         <x:v>13</x:v>
       </x:c>
       <x:c r="AV57" t="str">
         <x:v>OpenAlex</x:v>
       </x:c>
       <x:c r="AW57" t="str">
-        <x:v>2026-09-21</x:v>
+        <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AX57" t="str">
         <x:v>研究主题为 `Mobile Manipulation / Navigation`；本卡仅按官方摘要级证据整理，未替代全文审阅。</x:v>
@@ -38412,7 +38412,7 @@
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BM57" t="str">
-        <x:v>Unknown (no high-confidence match)</x:v>
+        <x:v>https://openalex.org/W4402772268</x:v>
       </x:c>
       <x:c r="BN57" t="str">
         <x:v>https://openaccess.thecvf.com/content/CVPR2024/html/Uppal_SPIN_Simultaneous_Perception_Interaction_and_Navigation_CVPR_2024_paper.html；官方摘要/论文集元数据</x:v>
@@ -38607,14 +38607,14 @@
       <x:c r="AT58" t="str">
         <x:v>Bimanual</x:v>
       </x:c>
-      <x:c r="AU58" t="str">
+      <x:c r="AU58" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="AV58" t="str">
         <x:v>OpenAlex</x:v>
       </x:c>
       <x:c r="AW58" t="str">
-        <x:v>2026-09-21</x:v>
+        <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AX58" t="str">
         <x:v>研究主题为 `Policy Transfer / Generali</x:v>
@@ -38662,7 +38662,7 @@
         <x:v>The paper identifies observation discrepancy between unimanual and bimanual systems as a transfer risk; detailed failure cases require appendix extraction.</x:v>
       </x:c>
       <x:c r="BM58" t="str">
-        <x:v>OpenAlex Work: https://openalex.org/W4405254485</x:v>
+        <x:v>https://openalex.org/W4405254485</x:v>
       </x:c>
       <x:c r="BN58" t="str">
         <x:v>https://openaccess.thecvf.com/content/ICCV2025/html/Lu_AnyBimanual_Transferring_Unimanual_Policy_for_General_Bimanual_Manipulation_ICCV_2025_paper.html；官方摘要/论文集元数据</x:v>
@@ -38857,14 +38857,14 @@
       <x:c r="AT59" t="str">
         <x:v>Dexterous</x:v>
       </x:c>
-      <x:c r="AU59" t="str">
+      <x:c r="AU59" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="AV59" t="str">
         <x:v>OpenAlex</x:v>
       </x:c>
       <x:c r="AW59" t="str">
-        <x:v>2026-09-21</x:v>
+        <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AX59" t="str">
         <x:v>研究主题为 `Cross-Embodiment / Human Video`；本卡仅按官方摘要级证据整理，未替代全文审阅。</x:v>
@@ -38912,7 +38912,7 @@
         <x:v>Cross-hand and retargeting edge cases are not detailed in the accessible abstract; full supplementary review is needed.</x:v>
       </x:c>
       <x:c r="BM59" t="str">
-        <x:v>OpenAlex Work: Unknown</x:v>
+        <x:v>https://openalex.org/W7140345735</x:v>
       </x:c>
       <x:c r="BN59" t="str">
         <x:v>https://openaccess.thecvf.com/content/CVPR2026/html/Zhang_UniDex_A_Robot_Foundation_Suite_for_Universal_Dexterous_Hand_Control_CVPR_2026_paper.html；官方摘要/论文集元数据</x:v>
@@ -39111,10 +39111,10 @@
         <x:v>Unknown</x:v>
       </x:c>
       <x:c r="AV60" t="str">
-        <x:v>OpenAlex (no high-confidence title match)</x:v>
+        <x:v>OpenAlex (identity ambiguous)</x:v>
       </x:c>
       <x:c r="AW60" t="str">
-        <x:v>2026-09-21</x:v>
+        <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AX60" t="str">
         <x:v>研究主题为 `Video Generation / Hand-Object Interaction`；本卡仅按官方摘要级证据整理，未替代全文审阅。</x:v>
@@ -39357,14 +39357,14 @@
       <x:c r="AT61" t="str">
         <x:v>Dexterous</x:v>
       </x:c>
-      <x:c r="AU61" t="str">
+      <x:c r="AU61" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="AV61" t="str">
         <x:v>OpenAlex</x:v>
       </x:c>
       <x:c r="AW61" t="str">
-        <x:v>2026-09-21</x:v>
+        <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AX61" t="str">
         <x:v>研究主题为 `Human Video / Motion Retargeting`；本卡仅按官方摘要级证据整理，未替代全文审阅。</x:v>
@@ -39412,7 +39412,7 @@
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BM61" t="str">
-        <x:v>Unknown (no high-confidence match)</x:v>
+        <x:v>https://openalex.org/W7138113519</x:v>
       </x:c>
       <x:c r="BN61" t="str">
         <x:v>https://ojs.aaai.org/index.php/AAAI/article/view/38874；官方摘要/论文集元数据</x:v>
@@ -39607,14 +39607,14 @@
       <x:c r="AT62" t="str">
         <x:v>Bimanual</x:v>
       </x:c>
-      <x:c r="AU62" t="str">
+      <x:c r="AU62" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="AV62" t="str">
         <x:v>OpenAlex</x:v>
       </x:c>
       <x:c r="AW62" t="str">
-        <x:v>2026-09-21</x:v>
+        <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AX62" t="str">
         <x:v>研究主题为 `Humanoid / Synthetic Demonstrations / LLM Planning`；本卡仅按官方摘要级证据整理，未替代全文审阅。</x:v>
@@ -39662,7 +39662,7 @@
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BM62" t="str">
-        <x:v>Unknown (no high-confidence match)</x:v>
+        <x:v>https://openalex.org/W4417041439</x:v>
       </x:c>
       <x:c r="BN62" t="str">
         <x:v>https://proceedings.neurips.cc/paper_files/paper/2025/hash/e4ef7454447baa15a424314e6284441b-Abstract-Conference.html；官方摘要/论文集元数据</x:v>
@@ -39857,14 +39857,14 @@
       <x:c r="AT63" t="str">
         <x:v>Dexterous</x:v>
       </x:c>
-      <x:c r="AU63" t="str">
+      <x:c r="AU63" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="AV63" t="str">
         <x:v>OpenAlex</x:v>
       </x:c>
       <x:c r="AW63" t="str">
-        <x:v>2026-09-21</x:v>
+        <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AX63" t="str">
         <x:v>研究主题为 `Affordance / Policy Distillation`；本卡仅按官方摘要级证据整理，未替代全文审阅。</x:v>
@@ -39912,7 +39912,7 @@
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BM63" t="str">
-        <x:v>Unknown (no high-confidence match)</x:v>
+        <x:v>https://openalex.org/W7138302344</x:v>
       </x:c>
       <x:c r="BN63" t="str">
         <x:v>https://ojs.aaai.org/index.php/AAAI/article/view/38313；官方摘要/论文集元数据</x:v>
@@ -40107,14 +40107,14 @@
       <x:c r="AT64" t="str">
         <x:v>Bimanual</x:v>
       </x:c>
-      <x:c r="AU64" t="str">
+      <x:c r="AU64" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="AV64" t="str">
         <x:v>OpenAlex</x:v>
       </x:c>
       <x:c r="AW64" t="str">
-        <x:v>2026-09-21</x:v>
+        <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AX64" t="str">
         <x:v>研究主题为 `Human Demonstrations / Reinforcement Learning`；本卡仅按官方摘要级证据整理，未替代全文审阅。</x:v>
@@ -40162,7 +40162,7 @@
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BM64" t="str">
-        <x:v>Unknown (no high-confidence match)</x:v>
+        <x:v>https://openalex.org/W7138037195</x:v>
       </x:c>
       <x:c r="BN64" t="str">
         <x:v>https://ojs.aaai.org/index.php/AAAI/article/view/40127；官方摘要/论文集元数据</x:v>
@@ -40357,14 +40357,14 @@
       <x:c r="AT65" t="str">
         <x:v>Bimanual</x:v>
       </x:c>
-      <x:c r="AU65" t="str">
+      <x:c r="AU65" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="AV65" t="str">
         <x:v>OpenAlex</x:v>
       </x:c>
       <x:c r="AW65" t="str">
-        <x:v>2026-09-21</x:v>
+        <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AX65" t="str">
         <x:v>研究主题为 `Motion Forecasting / Hand-Object Contact`；本卡仅按官方摘要级证据整理，未替代全文审阅。</x:v>
@@ -40412,7 +40412,7 @@
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BM65" t="str">
-        <x:v>Unknown (no high-confidence match)</x:v>
+        <x:v>https://openalex.org/W4393158202</x:v>
       </x:c>
       <x:c r="BN65" t="str">
         <x:v>https://ojs.aaai.org/index.php/AAAI/article/view/28266；官方摘要/论文集元数据</x:v>
@@ -40607,14 +40607,14 @@
       <x:c r="AT66" t="str">
         <x:v>Bimanual</x:v>
       </x:c>
-      <x:c r="AU66" t="str">
+      <x:c r="AU66" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="AV66" t="str">
         <x:v>OpenAlex</x:v>
       </x:c>
       <x:c r="AW66" t="str">
-        <x:v>2026-09-21</x:v>
+        <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AX66" t="str">
         <x:v>研究主题为 `Human Video / Affordance`；本卡仅按官方摘要级证据整理，未替代全文审阅。</x:v>
@@ -40662,7 +40662,7 @@
         <x:v>The paper notes ambiguity/multi-modality of valid interaction regions; exact failure examples require figure-level review.</x:v>
       </x:c>
       <x:c r="BM66" t="str">
-        <x:v>OpenAlex Work: Unknown</x:v>
+        <x:v>https://openalex.org/W4416031407</x:v>
       </x:c>
       <x:c r="BN66" t="str">
         <x:v>https://openaccess.thecvf.com/content/ICCV2025/html/Heidinger_2HandedAfforder_Learning_Precise_Actionable_Bimanual_Affordances_from_Human_Videos_ICCV_2025_paper.html；官方摘要/论文集元数据</x:v>
@@ -40857,14 +40857,14 @@
       <x:c r="AT67" t="str">
         <x:v>VLA</x:v>
       </x:c>
-      <x:c r="AU67" t="str">
+      <x:c r="AU67" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="AV67" t="str">
         <x:v>OpenAlex</x:v>
       </x:c>
       <x:c r="AW67" t="str">
-        <x:v>2026-09-21</x:v>
+        <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AX67" t="str">
         <x:v>现有 VLA 在执行操作时对任务目标区域的视觉注意力往往过于分散，可能关注错误对象，影响精确操作。</x:v>
@@ -40912,7 +40912,7 @@
         <x:v>Not Explicitly Reported in the accessible official abstract/project evidence.</x:v>
       </x:c>
       <x:c r="BM67" t="str">
-        <x:v>OpenAlex Work: https://openalex.org/W7137985120</x:v>
+        <x:v>https://openalex.org/W7137985120</x:v>
       </x:c>
       <x:c r="BN67" t="str">
         <x:v>https://ojs.aaai.org/index.php/AAAI/article/view/38921；https://arxiv.org/abs/2508.10333；https://zionchow.github.io/ReconVLA/；https://github.com/OpenHelix-Team/ReconVLA</x:v>
@@ -41003,7 +41003,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf1420b6b070443d2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5d79457ce1774232"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -41385,10 +41385,10 @@
         <x:v>Unknown</x:v>
       </x:c>
       <x:c r="AL2" t="str">
-        <x:v>OpenAlex (no high-confidence title match)</x:v>
+        <x:v>OpenAlex (identity unmatched)</x:v>
       </x:c>
       <x:c r="AM2" t="str">
-        <x:v>2026-09-21</x:v>
+        <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AN2" t="str">
         <x:v>Synthetic-only VLA training usually transfers unreliably to real manipulation.</x:v>
@@ -41433,7 +41433,7 @@
         <x:v>Domain-gap evaluation explicitly tests background, object, table and combined shifts; exact failure cases require full-paper appendix extraction.</x:v>
       </x:c>
       <x:c r="BB2" t="str">
-        <x:v>OpenAlex Work: https://openalex.org/W? title match was not high-confidence for this title; Citation Count remains Unknown.</x:v>
+        <x:v>Unknown (no high-confidence match)</x:v>
       </x:c>
       <x:c r="BC2" t="str">
         <x:v>Official ICLR Downloads/Proceedings; accepted OpenReview PDF; official project page; official EmbodiChain repository; author publication list; current official CCF directory</x:v>
@@ -41598,14 +41598,14 @@
       <x:c r="AJ3" t="str">
         <x:v>Bimanual</x:v>
       </x:c>
-      <x:c r="AK3" t="str">
+      <x:c r="AK3" t="n">
         <x:v>7</x:v>
       </x:c>
       <x:c r="AL3" t="str">
         <x:v>OpenAlex</x:v>
       </x:c>
       <x:c r="AM3" t="str">
-        <x:v>2026-09-21</x:v>
+        <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AN3" t="str">
         <x:v>Learning coordinated bimanual skills with low demonstration cost.</x:v>
@@ -41650,7 +41650,7 @@
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BB3" t="str">
-        <x:v>Unknown (no high-confidence match)</x:v>
+        <x:v>https://openalex.org/W4414050937</x:v>
       </x:c>
       <x:c r="BC3" t="str">
         <x:v>https://www.roboticsproceedings.org/rss21/p149.html; https://hnu</x:v>
@@ -41815,14 +41815,14 @@
       <x:c r="AJ4" t="str">
         <x:v>Bimanual</x:v>
       </x:c>
-      <x:c r="AK4" t="str">
+      <x:c r="AK4" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="AL4" t="str">
         <x:v>OpenAlex</x:v>
       </x:c>
       <x:c r="AM4" t="str">
-        <x:v>2026-09-21</x:v>
+        <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AN4" t="str">
         <x:v>Bimanual policies must combine spatial locali</x:v>
@@ -41867,7 +41867,7 @@
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BB4" t="str">
-        <x:v>Unknown (no high-confidence match)</x:v>
+        <x:v>https://openalex.org/W4414050727</x:v>
       </x:c>
       <x:c r="BC4" t="str">
         <x:v>RSS official proceedings abstract</x:v>
@@ -42036,10 +42036,10 @@
         <x:v>Unknown</x:v>
       </x:c>
       <x:c r="AL5" t="str">
-        <x:v>OpenAlex (no high-confidence title match)</x:v>
+        <x:v>OpenAlex (identity ambiguous)</x:v>
       </x:c>
       <x:c r="AM5" t="str">
-        <x:v>2026-09-21</x:v>
+        <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AN5" t="str">
         <x:v>Collecting detailed, portable human-hand demonstrations for dexterous robot learning.</x:v>
@@ -42253,10 +42253,10 @@
         <x:v>Unknown</x:v>
       </x:c>
       <x:c r="AL6" t="str">
-        <x:v>OpenAlex (no high-confidence title match)</x:v>
+        <x:v>OpenAlex (identity unmatched)</x:v>
       </x:c>
       <x:c r="AM6" t="str">
-        <x:v>2026-09-21</x:v>
+        <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AN6" t="str">
         <x:v>Manipulation policies are often evaluated too close to training conditions.</x:v>
@@ -42466,14 +42466,14 @@
       <x:c r="AJ7" t="str">
         <x:v>Bimanual</x:v>
       </x:c>
-      <x:c r="AK7" t="str">
+      <x:c r="AK7" t="n">
         <x:v>11</x:v>
       </x:c>
       <x:c r="AL7" t="str">
         <x:v>OpenAlex</x:v>
       </x:c>
       <x:c r="AM7" t="str">
-        <x:v>2026-09-21</x:v>
+        <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AN7" t="str">
         <x:v>Planning while maintaining a fixed transform between two end effectors creates difficult equality constraints.</x:v>
@@ -42518,7 +42518,7 @@
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BB7" t="str">
-        <x:v>Unknown (no high-confidence match)</x:v>
+        <x:v>https://openalex.org/W4401415458</x:v>
       </x:c>
       <x:c r="BC7" t="str">
         <x:v>IEEE Xplore abstract; official project page</x:v>
@@ -42683,14 +42683,14 @@
       <x:c r="AJ8" t="str">
         <x:v>Diffusion / Flow / IL / RL</x:v>
       </x:c>
-      <x:c r="AK8" t="str">
-        <x:v>Unknown</x:v>
+      <x:c r="AK8" t="n">
+        <x:v>14</x:v>
       </x:c>
       <x:c r="AL8" t="str">
-        <x:v>OpenAlex (no high-confidence title match)</x:v>
+        <x:v>OpenAlex</x:v>
       </x:c>
       <x:c r="AM8" t="str">
-        <x:v>2026-09-21</x:v>
+        <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AN8" t="str">
         <x:v>Contact-rich imitation must reproduce forces and switch sensing/control modes reliably.</x:v>
@@ -42735,7 +42735,7 @@
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BB8" t="str">
-        <x:v>Unknown (no high-confidence match)</x:v>
+        <x:v>https://openalex.org/W4405753615</x:v>
       </x:c>
       <x:c r="BC8" t="str">
         <x:v>IEEE Xplore abstract</x:v>
@@ -42900,14 +42900,14 @@
       <x:c r="AJ9" t="str">
         <x:v>Bimanual</x:v>
       </x:c>
-      <x:c r="AK9" t="str">
+      <x:c r="AK9" t="n">
         <x:v>10</x:v>
       </x:c>
       <x:c r="AL9" t="str">
         <x:v>OpenAlex</x:v>
       </x:c>
       <x:c r="AM9" t="str">
-        <x:v>2026-09-21</x:v>
+        <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AN9" t="str">
         <x:v>Multiple arms need online trajectory adaptation and collision avoidance in shared workspaces.</x:v>
@@ -42952,7 +42952,7 @@
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BB9" t="str">
-        <x:v>Unknown (no high-confidence match)</x:v>
+        <x:v>https://openalex.org/W4404520558</x:v>
       </x:c>
       <x:c r="BC9" t="str">
         <x:v>IEEE Xplore abstract</x:v>
@@ -43121,10 +43121,10 @@
         <x:v>Unknown</x:v>
       </x:c>
       <x:c r="AL10" t="str">
-        <x:v>OpenAlex (no high-confidence title match)</x:v>
+        <x:v>OpenAlex (identity unmatched)</x:v>
       </x:c>
       <x:c r="AM10" t="str">
-        <x:v>2026-09-21</x:v>
+        <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AN10" t="str">
         <x:v>State and action representations may not transfer across reality gaps or hand geometries.</x:v>
@@ -43312,14 +43312,14 @@
       <x:c r="AJ11" t="str">
         <x:v>VLA</x:v>
       </x:c>
-      <x:c r="AK11" t="str">
+      <x:c r="AK11" t="n">
         <x:v>102</x:v>
       </x:c>
       <x:c r="AL11" t="str">
         <x:v>OpenAlex</x:v>
       </x:c>
       <x:c r="AM11" t="str">
-        <x:v>2026-09-21</x:v>
+        <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AN11" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -43364,7 +43364,7 @@
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BB11" t="str">
-        <x:v>Unknown (no high-confidence match)</x:v>
+        <x:v>https://openalex.org/W4402353985</x:v>
       </x:c>
       <x:c r="BC11" t="str">
         <x:v>Unknown</x:v>
@@ -43507,10 +43507,10 @@
         <x:v>Unknown</x:v>
       </x:c>
       <x:c r="AL12" t="str">
-        <x:v>OpenAlex (no high-confidence title match)</x:v>
+        <x:v>OpenAlex (identity unmatched)</x:v>
       </x:c>
       <x:c r="AM12" t="str">
-        <x:v>2026-09-21</x:v>
+        <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AN12" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -43694,14 +43694,14 @@
       <x:c r="AJ13" t="str">
         <x:v>Benchmark / Dataset</x:v>
       </x:c>
-      <x:c r="AK13" t="str">
-        <x:v>Unknown</x:v>
+      <x:c r="AK13" t="n">
+        <x:v>44</x:v>
       </x:c>
       <x:c r="AL13" t="str">
-        <x:v>OpenAlex (no high-confidence title match)</x:v>
+        <x:v>OpenAlex</x:v>
       </x:c>
       <x:c r="AM13" t="str">
-        <x:v>2026-09-21</x:v>
+        <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AN13" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -43746,7 +43746,7 @@
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BB13" t="str">
-        <x:v>Unknown (no high-confidence match)</x:v>
+        <x:v>https://openalex.org/W4402354126</x:v>
       </x:c>
       <x:c r="BC13" t="str">
         <x:v>Unknown</x:v>
@@ -43889,10 +43889,10 @@
         <x:v>Unknown</x:v>
       </x:c>
       <x:c r="AL14" t="str">
-        <x:v>OpenAlex (no high-confidence title match)</x:v>
+        <x:v>OpenAlex (identity unmatched)</x:v>
       </x:c>
       <x:c r="AM14" t="str">
-        <x:v>2026-09-21</x:v>
+        <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AN14" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -44109,7 +44109,7 @@
         <x:v>OpenAlex</x:v>
       </x:c>
       <x:c r="AM15" t="str">
-        <x:v>2026-09-22</x:v>
+        <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AN15" t="str">
         <x:v>LLMs have semantic knowledge but no embodiment grounding.</x:v>
@@ -44154,7 +44154,7 @@
         <x:v>Planning errors, low-level execution, drawer manipulation, embodiment limits.</x:v>
       </x:c>
       <x:c r="BB15" t="str">
-        <x:v>OpenAlex Work W4224912544</x:v>
+        <x:v>https://openalex.org/W4224912544</x:v>
       </x:c>
       <x:c r="BC15" t="str">
         <x:v>Google Research; arXiv; CoRL/PMLR; project page; official repository</x:v>
@@ -44231,7 +44231,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8b540e7d6f794333"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Reac433e9ea2f47c2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/00_Paper_Pool/Paper_Pool.xlsx
+++ b/00_Paper_Pool/Paper_Pool.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Papers" sheetId="1" r:id="Rd7dcc0ac56394c8c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rejected" sheetId="2" r:id="R7448a56545904e20"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Venues" sheetId="3" r:id="R9b7b26e4745c4905"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Keywords" sheetId="4" r:id="Rcf2be3f795624e86"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Discovery" sheetId="5" r:id="R8d975dbf60684592"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CCF_A_Library" sheetId="6" r:id="R1fa979e4dff3454f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Robotics_Core_Library" sheetId="7" r:id="R10b9c115b21d4b71"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Papers" sheetId="1" r:id="Rf34e3ef76b4247fd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rejected" sheetId="2" r:id="R72e1a1bcb5f740e0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Venues" sheetId="3" r:id="R81f52f8342df421e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Keywords" sheetId="4" r:id="R82d4680386654c31"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Discovery" sheetId="5" r:id="R06b05290bbbe48c6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CCF_A_Library" sheetId="6" r:id="Rf1c22db630ed47e2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Robotics_Core_Library" sheetId="7" r:id="Rb1f17bc3bb304c1c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -300,7 +300,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="66" name="PapersTable" displayName="PapersTable" ref="A1:CE6" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="74" name="PapersTable" displayName="PapersTable" ref="A1:CE6" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="83">
     <x:tableColumn id="1" name="编号 ID"/>
     <x:tableColumn id="2" name="论文标题 Title"/>
@@ -436,7 +436,7 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="67" name="DiscoveryTable" displayName="DiscoveryTable" ref="A1:BZ79" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="75" name="DiscoveryTable" displayName="DiscoveryTable" ref="A1:BZ79" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="78">
     <x:tableColumn id="1" name="编号 ID"/>
     <x:tableColumn id="2" name="论文标题 Title"/>
@@ -522,7 +522,7 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="68" name="CCFALibraryTable" displayName="CCFALibraryTable" ref="A1:CS67" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="76" name="CCFALibraryTable" displayName="CCFALibraryTable" ref="A1:CS67" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="97">
     <x:tableColumn id="1" name="编号 ID"/>
     <x:tableColumn id="2" name="论文标题 Title"/>
@@ -627,7 +627,7 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="69" name="RoboticsCoreLibraryTable" displayName="RoboticsCoreLibraryTable" ref="A1:CH15" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="77" name="RoboticsCoreLibraryTable" displayName="RoboticsCoreLibraryTable" ref="A1:CH15" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="86">
     <x:tableColumn id="1" name="ID"/>
     <x:tableColumn id="2" name="Title"/>
@@ -1302,7 +1302,7 @@
         <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AI2" t="str">
-        <x:v>MLLMs have strong visual-language reasoning but lack object-centric manipulation grounding, precise contact poses and robust real-world execution.</x:v>
+        <x:v>多模态大模型能理解图像和语言，但不一定能给出可执行的接触点与夹爪姿态。</x:v>
       </x:c>
       <x:c r="AJ2" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -1311,7 +1311,7 @@
         <x:v>以 `Multimodal / Generali</x:v>
       </x:c>
       <x:c r="AL2" t="str">
-        <x:v>Simulation data from PartNet-Mobility-style articulated objects in SAPIEN; real-world household-object evaluation with a Franka arm, suction gripper and RealSense D415.</x:v>
+        <x:v>论文中的物体操作任务与消融设置；具体数据集名称见原卡实验部分。</x:v>
       </x:c>
       <x:c r="AM2" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -1406,34 +1406,34 @@
       </x:c>
       <x:c r="BR2"/>
       <x:c r="BS2" t="str">
-        <x:v>Evidence-backed — MLLMs have strong visual-language reasoning but lack object-centric manipulation grounding, precise contact poses and robust real-world execution.</x:v>
+        <x:v>多模态大模型能理解图像和语言，但不一定能给出可执行的接触点与夹爪姿态。</x:v>
       </x:c>
       <x:c r="BT2" t="str">
-        <x:v>Author-stated: prior MLLMs do not directly provide manipulation-aware localization and pose prediction; simulator-to-real differences affect position predictions.</x:v>
+        <x:v>物体级 Grounding 与精确接触几何没有自然地从语言推理转成机器人动作。</x:v>
       </x:c>
       <x:c r="BU2" t="str">
-        <x:v>ManipLLM fine-tunes LLaMA-Adapter with category identification, affordance-prior reasoning, pose fine-tuning and masked language modeling. It predicts contact point and gripper orientation, then uses chain-of-thought inference and active impedance adaptation with test-time visual adaptation.</x:v>
+        <x:v>ManipLLM 结合物体类别识别、affordance 推理和位姿微调，预测接触点与夹爪朝向，并通过分步推理和主动交互改进执行。</x:v>
       </x:c>
       <x:c r="BV2" t="str">
         <x:v>Ablations compare FT, OCI, MLM, APR, COT and AIA components; the paper also compares manipulation performance against prior object-centric methods.</x:v>
       </x:c>
       <x:c r="BW2" t="str">
-        <x:v>Ablation average rises from 0.41 (FT only) to 0.59 with the full training/inference stack. OCI adds about 3%, MLM about 6%, APR about 9%; removing COT decreases about 3%, and removing AIA reduces long-distance performance from 0.57 to 0.50.</x:v>
+        <x:v>卡片记录消融平均指标从仅 FT 的 0.41 提升到完整方法的 0.59；各模块贡献见原卡 Main Results。</x:v>
       </x:c>
       <x:c r="BX2" t="str">
-        <x:v>Provides a concrete method or benchmark for the documented gap: Author-stated: prior MLLMs do not directly provide manipulation-aware localization and pose prediction; simulator-to-real…</x:v>
+        <x:v>让语言推理落到普通夹爪可执行的接触几何上。</x:v>
       </x:c>
       <x:c r="BY2" t="str">
-        <x:v>Author-stated: visual position prediction remains domain-sensitive; hardware-specific suction constraints require test-time adaptation.</x:v>
+        <x:v>作者指出视觉位置预测仍受域变化影响；特定吸盘硬件约束需要测试时适配。</x:v>
       </x:c>
       <x:c r="BZ2" t="str">
         <x:v>Library Analysis: broader gripper geometries, bimanual coordination and long-horizon recovery are outside the demonstrated setup.</x:v>
       </x:c>
       <x:c r="CA2" t="str">
-        <x:v>Medium — relevant to robot manipulation; transfer to dual-arm real hardware needs validation.</x:v>
+        <x:v>High：直接对应夹爪接触点、动作前可行性验证和真机操作。</x:v>
       </x:c>
       <x:c r="CB2" t="str">
-        <x:v>Official abstract / paper page; https://arxiv.org/html/2312.16217; checked 2026-09-23. Rapid summary only; existing Evidence Quality is unchanged.</x:v>
+        <x:v>官方摘要/论文页; https://arxiv.org/html/2312.16217; 核验于 2026-09-23. 仅为摘要级速读；原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="CC2" t="str">
         <x:v>Exact work identity verified</x:v>
@@ -1517,7 +1517,7 @@
         <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AI3" t="str">
-        <x:v>Human hands play a central role in interacting, motivating increasing research in dexterous robotic manipulation.</x:v>
+        <x:v>人类双手操作能力丰富，但难以直接迁移到机器人灵巧手。</x:v>
       </x:c>
       <x:c r="AJ3" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -1526,7 +1526,7 @@
         <x:v>以 `Residual Learning / Sim-to-Real` 为主要方法/能力线索；更细的结构和消融结论待正文核验。</x:v>
       </x:c>
       <x:c r="AL3" t="str">
-        <x:v>Not specified in checked abstract/card.</x:v>
+        <x:v>双手灵巧操作仿真任务；详细任务和基线见论文。</x:v>
       </x:c>
       <x:c r="AM3" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -1619,30 +1619,30 @@
       </x:c>
       <x:c r="BR3"/>
       <x:c r="BS3" t="str">
-        <x:v>Evidence-backed — Human hands play a central role in interacting, motivating increasing research in dexterous robotic manipulation.</x:v>
+        <x:v>人类双手操作能力丰富，但难以直接迁移到机器人灵巧手。</x:v>
       </x:c>
       <x:c r="BT3" t="str">
-        <x:v>Not established in checked summary source.</x:v>
+        <x:v>人手和机器人手的运动学、接触方式不同，逐帧模仿不能保证可执行。</x:v>
       </x:c>
       <x:c r="BU3" t="str">
-        <x:v>To address this, we introduce ManipTrans, a novel two-stage method for efficiently transferring human bimanual skills to dexterous robotic hands in simulation.</x:v>
+        <x:v>ManipTrans 用两阶段流程，在仿真中把人类双手技能迁移到机器人灵巧手策略。</x:v>
       </x:c>
       <x:c r="BV3" t="str"/>
       <x:c r="BW3" t="str">
-        <x:v>Experiments show that ManipTrans surpasses state-of-the-art methods in success rate, fidelity, and efficiency.</x:v>
+        <x:v>作者报告成功率、动作保真度与训练效率优于所比较方法；摘要未给统一数字。</x:v>
       </x:c>
       <x:c r="BX3" t="str">
-        <x:v>High — directly informs dual-arm coordination, data or ordinary-gripper policy design.</x:v>
+        <x:v>展示 Human Video / Human Motion 到机器人双手动作的转换思路。</x:v>
       </x:c>
       <x:c r="BY3" t="str">
-        <x:v>Not established by the checked summary source; consult the full paper.</x:v>
+        <x:v>仿真到真机与普通夹爪迁移尚不能从摘要确认。</x:v>
       </x:c>
       <x:c r="BZ3" t="str"/>
       <x:c r="CA3" t="str">
-        <x:v>High — directly informs dual-arm coordination, data or ordinary-gripper policy design.</x:v>
+        <x:v>Medium：手型不同，普通夹爪适配仍需单独建模。</x:v>
       </x:c>
       <x:c r="CB3" t="str">
-        <x:v>Official abstract / paper page; https://openaccess.thecvf.com/content/CVPR2025/html/Li_ManipTrans_Efficient_Dexterous_Bimanual_Manipulation_Transfer_via_Residual_Learning_CVPR_2025_paper.html; checked 2026-09-23. Rapid summary only; existing Evidence Quality is unchanged.</x:v>
+        <x:v>官方摘要/论文页; https://openaccess.thecvf.com/content/CVPR2025/html/Li_ManipTrans_Efficient_Dexterous_Bimanual_Manipulation_Transfer_via_Residual_Learning_CVPR_2025_paper.html; 核验于 2026-09-23. 仅为摘要级速读；原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="CC3" t="str">
         <x:v>Exact work identity verified</x:v>
@@ -1726,7 +1726,7 @@
         <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AI4" t="str">
-        <x:v>Dexterous manipulation with contact-rich interactions is crucial for advanced robotics.</x:v>
+        <x:v>接触密集的灵巧操作需要根据目标与环境变化调整动作。</x:v>
       </x:c>
       <x:c r="AJ4" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -1735,7 +1735,7 @@
         <x:v>以 `Diffusion / Contact-rich Manipulation` 为主要方法/能力线索；更细的结构和消融结论待正文核验。</x:v>
       </x:c>
       <x:c r="AL4" t="str">
-        <x:v>Not specified in checked abstract/card.</x:v>
+        <x:v>已核验摘要未明确说明；需查阅论文方法与实验章节。</x:v>
       </x:c>
       <x:c r="AM4" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -1828,30 +1828,30 @@
       </x:c>
       <x:c r="BR4"/>
       <x:c r="BS4" t="str">
-        <x:v>Evidence-backed — Dexterous manipulation with contact-rich interactions is crucial for advanced robotics.</x:v>
+        <x:v>接触密集的灵巧操作需要根据目标与环境变化调整动作。</x:v>
       </x:c>
       <x:c r="BT4" t="str">
-        <x:v>While recent diffusion-based planning approaches show promise for simple manipulation tasks, they often produce unrealistic ghost states (e.g., the object automatically moves without hand contact) or lack adaptability when handling complex sequential…</x:v>
+        <x:v>固定轨迹或单一接触模式难适应复杂手—物交互。</x:v>
       </x:c>
       <x:c r="BU4" t="str">
-        <x:v>In this work, we introduce DexHandDiff, an interaction-aware diffusion planning framework for adaptive dexterous manipulation.</x:v>
+        <x:v>DexHandDiff 用交互感知的扩散式规划生成可适应目标变化的灵巧手动作。</x:v>
       </x:c>
       <x:c r="BV4" t="str"/>
       <x:c r="BW4" t="str">
-        <x:v>Our framework achieves an average of 70.7% success rate on goal adaptive dexterous tasks, highlighting its robustness and flexibility in contact-rich manipulation.</x:v>
+        <x:v>官方摘要报告目标自适应任务平均成功率 70.7%。</x:v>
       </x:c>
       <x:c r="BX4" t="str">
-        <x:v>Provides a concrete method or benchmark for the documented gap: While recent diffusion-based planning approaches show promise for simple manipulation tasks, they often produce unrealistic ghost…</x:v>
+        <x:v>展示生成式策略如何表达多种接触动作。</x:v>
       </x:c>
       <x:c r="BY4" t="str">
-        <x:v>Not established by the checked summary source; consult the full paper.</x:v>
+        <x:v>需检查真机接触、动作延迟和跨硬件泛化。</x:v>
       </x:c>
       <x:c r="BZ4" t="str"/>
       <x:c r="CA4" t="str">
-        <x:v>Medium — transferable learning ideas may apply, but the hand hardware differs from ordinary grippers.</x:v>
+        <x:v>Medium：可借鉴动作生成机制，但灵巧手与普通夹爪不同。</x:v>
       </x:c>
       <x:c r="CB4" t="str">
-        <x:v>Official abstract / paper page; https://openaccess.thecvf.com/content/CVPR2025/html/Liang_DexHandDiff_Interaction-aware_Diffusion_Planning_for_Adaptive_Dexterous_Manipulation_CVPR_2025_paper.html; checked 2026-09-23. Rapid summary only; existing Evidence Quality is unchanged.</x:v>
+        <x:v>官方摘要/论文页; https://openaccess.thecvf.com/content/CVPR2025/html/Liang_DexHandDiff_Interaction-aware_Diffusion_Planning_for_Adaptive_Dexterous_Manipulation_CVPR_2025_paper.html; 核验于 2026-09-23. 仅为摘要级速读；原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="CC4" t="str">
         <x:v>Exact work identity verified</x:v>
@@ -1935,7 +1935,7 @@
         <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AI5" t="str">
-        <x:v>Visual Robot Manipulation (VRM) aims to enable a robot to follow natural language instructions based on robot states and visual observations, and therefore requires costly multi- modal data.</x:v>
+        <x:v>视觉机器人操作要根据语言、视觉和状态输出可执行动作。</x:v>
       </x:c>
       <x:c r="AJ5" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -1944,7 +1944,7 @@
         <x:v>以 `Human Video / VLM` 为主要方法/能力线索；更细的结构和消融结论待正文核验。</x:v>
       </x:c>
       <x:c r="AL5" t="str">
-        <x:v>Not specified in checked abstract/card.</x:v>
+        <x:v>已核验摘要未明确说明；需查阅论文方法与实验章节。</x:v>
       </x:c>
       <x:c r="AM5" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -2037,30 +2037,30 @@
       </x:c>
       <x:c r="BR5"/>
       <x:c r="BS5" t="str">
-        <x:v>Evidence-backed — Visual Robot Manipulation (VRM) aims to enable a robot to follow natural language instructions based on robot states and visual observations, and therefore requires costly multi- modal data.</x:v>
+        <x:v>视觉机器人操作要根据语言、视觉和状态输出可执行动作。</x:v>
       </x:c>
       <x:c r="BT5" t="str">
-        <x:v>However, they either utilize web data that differs from robotic tasks, or train the model in an implicit way (e.g., predicting future frames at the pixel level), thus showing limited generalization ability under in- sufficient robot data.</x:v>
+        <x:v>只依赖少量机器人示范，难以利用大量人类动作视频。</x:v>
       </x:c>
       <x:c r="BU5" t="str">
-        <x:v>In this paper, we propose to learn from large-scale human action video datasets in an explicit way (i.e., imitating human actions from hand keypoints), introduc- ing Visual Robot Manipulation with Analogical Reasoning (AR-VRM).</x:v>
+        <x:v>AR-VRM 显式利用人类动作视频学习视觉操作表示，再适配机器人策略。</x:v>
       </x:c>
       <x:c r="BV5" t="str"/>
       <x:c r="BW5" t="str">
-        <x:v>In few-shot scenarios, our AR-VRM outperforms previous meth- ods by large margins, underscoring the effectiveness of explicitly imitating human actions under data scarcity.</x:v>
+        <x:v>作者报告小样本设置下优于所比较方法；摘要未给可安全复述的统一数值。</x:v>
       </x:c>
       <x:c r="BX5" t="str">
-        <x:v>Provides a concrete method or benchmark for the documented gap: However, they either utilize web data that differs from robotic tasks, or train the model in an implicit way (e.g., predicting…</x:v>
+        <x:v>为人类视频转机器人动作提供另一种数据路线。</x:v>
       </x:c>
       <x:c r="BY5" t="str">
-        <x:v>Not established by the checked summary source; consult the full paper.</x:v>
+        <x:v>人体动作和机器人动作空间差异需要明确对齐。</x:v>
       </x:c>
       <x:c r="BZ5" t="str"/>
       <x:c r="CA5" t="str">
-        <x:v>Medium — relevant to robot manipulation; transfer to dual-arm real hardware needs validation.</x:v>
+        <x:v>Medium：与低成本数据收集相关，双臂夹爪迁移待验。</x:v>
       </x:c>
       <x:c r="CB5" t="str">
-        <x:v>Official abstract / paper page; https://openaccess.thecvf.com/content/ICCV2025/html/Yang_AR-VRM_Imitating_Human_Motions_for_Visual_Robot_Manipulation_with_Analogical_ICCV_2025_paper.html; checked 2026-09-23. Rapid summary only; existing Evidence Quality is unchanged.</x:v>
+        <x:v>官方摘要/论文页; https://openaccess.thecvf.com/content/ICCV2025/html/Yang_AR-VRM_Imitating_Human_Motions_for_Visual_Robot_Manipulation_with_Analogical_ICCV_2025_paper.html; 核验于 2026-09-23. 仅为摘要级速读；原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="CC5" t="str">
         <x:v>Exact work identity verified</x:v>
@@ -2176,7 +2176,7 @@
         <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AI6" t="str">
-        <x:v>Large language models contain semantic knowledge for decomposing abstract, temporally extended instructions but are not grounded in a robot embodiment, current scene, action repertoire or execution consequences. A text-only answer can therefore be sensible in language yet infeasible or unsafe for the robot.</x:v>
+        <x:v>LLM 能拆解长指令，但不知道当前机器人真正能做什么。</x:v>
       </x:c>
       <x:c r="AJ6" t="str">
         <x:v>Long-horizon abstract instructions require both useful decomposition and physically feasible execution.</x:v>
@@ -2185,7 +2185,7 @@
         <x:v>SayCan: p(cπ|s,ℓπ) × p(ℓπ|i), receding-horizon skill selection.</x:v>
       </x:c>
       <x:c r="AL6" t="str">
-        <x:v>The main test contains 101 natural-language instructions in 7 families: NL single primitive, NL nouns, NL verbs, structured language, embodiment variations, crowd-sourced requests…</x:v>
+        <x:v>Mock Kitchen 与真实办公室厨房任务。</x:v>
       </x:c>
       <x:c r="AM6" t="str">
         <x:v>No VF; Generative; FLAN-SayCan; BC NL; BC USE; PaLM scale ablations.</x:v>
@@ -2282,23 +2282,23 @@
         <x:v>Completed-A</x:v>
       </x:c>
       <x:c r="BS6" t="str">
-        <x:v>Evidence-backed — Large language models contain semantic knowledge for decomposing abstract, temporally extended instructions but are not grounded in a robot embodiment, current scene, action repertoire or execution consequences. A text-only answer can therefore be sensible in language yet infeasible or unsafe for the robot.</x:v>
+        <x:v>LLM 能拆解长指令，但不知道当前机器人真正能做什么。</x:v>
       </x:c>
       <x:c r="BT6" t="str">
-        <x:v>Prior language-conditioned robot systems typically handle short atomic commands, while LLM planning can suggest actions outside the robot's skill set. The missing bridge is a shared interface that scores usefulness toward the instruction and feasibility in…</x:v>
+        <x:v>只按语言相关性选技能，可能生成物理上不可执行的计划。</x:v>
       </x:c>
       <x:c r="BU6" t="str">
-        <x:v>We propose to provide real-world grounding by means of pretrained skills, which are used to constrain the model to propose natural language actions that are both feasible and contextually appropriate.</x:v>
+        <x:v>SayCan 结合语言模型的技能匹配分数与技能价值/可供性估计，逐步选择当前可执行的操作。</x:v>
       </x:c>
       <x:c r="BV6" t="str"/>
       <x:c r="BW6" t="str">
-        <x:v>Mock Kitchen / training environment (Table 2): PaLM-SayCan plan 84%, execute 74% over 101 instructions. - Real office kitchen (Table 2): plan 81%, execute 60%. - PaLM vs FLAN (Table 3): PaLM-SayCan 84% plan / 74% execute; FLAN-SayCan 70% / 61%. - No…</x:v>
+        <x:v>卡片记录 Mock Kitchen 101 条指令中规划成功 84%、物理执行 74%；真实办公室厨房规划 81%，完整执行值见 Table 2。</x:v>
       </x:c>
       <x:c r="BX6" t="str">
-        <x:v>Provides a concrete method or benchmark for the documented gap: Prior language-conditioned robot systems typically handle short atomic commands, while LLM planning can suggest actions outside…</x:v>
+        <x:v>把语言规划和机器人可执行性明确连接起来。</x:v>
       </x:c>
       <x:c r="BY6" t="str">
-        <x:v>Author-stated: vanilla SayCan only receives environmental feedback through current-step value functions; after a skill fails or the environment changes, necessary feedback may be unavailable. The authors point to…</x:v>
+        <x:v>技能库、价值估计和环境假设依赖特定机器人；规划成功不保证动作完成。</x:v>
       </x:c>
       <x:c r="BZ6" t="str">
         <x:v>1. Open-ended tasks outside the fixed skill library remain unsupported (Sec. 3–4 evidence).
@@ -2308,10 +2308,10 @@
 5. Joint feasibility and role allocation for bimanual ordinary-gripper systems are not evaluated (library/project analysis).</x:v>
       </x:c>
       <x:c r="CA6" t="str">
-        <x:v>High — informs transfer from simulation to NERO real-robot manipulation.</x:v>
+        <x:v>High：双臂普通夹爪需要在动作前判断技能是否可行。</x:v>
       </x:c>
       <x:c r="CB6" t="str">
-        <x:v>Official abstract / paper page; https://arxiv.org/html/2204.01691; checked 2026-09-23. Rapid summary only; existing Evidence Quality is unchanged.</x:v>
+        <x:v>官方摘要/论文页; https://arxiv.org/html/2204.01691; 核验于 2026-09-23. 仅为摘要级速读；原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="CC6" t="str">
         <x:v>Exact work identity verified</x:v>
@@ -5331,7 +5331,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc0949f0498f94907"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9f302552a21844f9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8627,7 +8627,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R44bad5d5dcff4f88"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3f032058dcc948d8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8978,7 +8978,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdac9bbd2b3984fdc"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R785ce104cd4d4572"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9724,7 +9724,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2a9444c64f9e4656"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3af23533ecd0437a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10081,7 +10081,7 @@
         <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AD2" t="str">
-        <x:v>This paper introduces Hierarchical Diffusion Policy (HDP) a hierarchical agent for multi-task robotic manipulation.</x:v>
+        <x:v>多任务机器人操作要同时决定高层子目标和符合运动学的连续动作。</x:v>
       </x:c>
       <x:c r="AE2" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -10090,7 +10090,7 @@
         <x:v>以 `Robot Manipulation; Diffusion Policy / Hierarchical Control` 为主要方法/能力线索；更细的结构和消融结论待正文核验。</x:v>
       </x:c>
       <x:c r="AG2" t="str">
-        <x:v>Not specified in checked abstract/card.</x:v>
+        <x:v>已核验摘要未明确说明；需查阅论文方法与实验章节。</x:v>
       </x:c>
       <x:c r="AH2" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -10183,30 +10183,30 @@
       </x:c>
       <x:c r="BM2"/>
       <x:c r="BN2" t="str">
-        <x:v>Evidence-backed — This paper introduces Hierarchical Diffusion Policy (HDP) a hierarchical agent for multi-task robotic manipulation.</x:v>
+        <x:v>多任务机器人操作要同时决定高层子目标和符合运动学的连续动作。</x:v>
       </x:c>
       <x:c r="BO2" t="str">
-        <x:v>The factorised policy representation allows HDP to tackle both long-horizon task planning while generating fine-grained low-level actions.</x:v>
+        <x:v>单层扩散策略可能难兼顾长任务结构与局部可达性。</x:v>
       </x:c>
       <x:c r="BP2" t="str">
-        <x:v>This paper introduces Hierarchical Diffusion Policy (HDP) a hierarchical agent for multi-task robotic manipulation.</x:v>
+        <x:v>Hierarchical Diffusion Policy 将任务规划与运动学感知的动作生成分层处理。</x:v>
       </x:c>
       <x:c r="BQ2" t="str"/>
       <x:c r="BR2" t="str">
-        <x:v>Empirically we show that HDP achieves a significantly higher success rate than the state-of-the-art methods in both simulation and real-world.</x:v>
+        <x:v>作者报告仿真和真机成功率高于所比较方法；具体数值见实验表。</x:v>
       </x:c>
       <x:c r="BS2" t="str">
-        <x:v>Provides a concrete method or benchmark for the documented gap: The factorised policy representation allows HDP to tackle both long-horizon task planning while generating fine-grained low-level…</x:v>
+        <x:v>可对照双臂任务中高层分工与低层动作生成。</x:v>
       </x:c>
       <x:c r="BT2" t="str">
-        <x:v>Not established by the checked summary source; consult the full paper.</x:v>
+        <x:v>需核验在两臂共享工作空间中的约束处理。</x:v>
       </x:c>
       <x:c r="BU2" t="str"/>
       <x:c r="BV2" t="str">
-        <x:v>Medium — relevant to robot manipulation; transfer to dual-arm real hardware needs validation.</x:v>
+        <x:v>High：双臂普通夹爪也需要运动学约束和任务分解。</x:v>
       </x:c>
       <x:c r="BW2" t="str">
-        <x:v>Official abstract / paper page; https://openaccess.thecvf.com/content/CVPR2024/html/Ma_Hierarchical_Diffusion_Policy_for_Kinematics-Aware_Multi-Task_Robotic_Manipulation_CVPR_2024_paper.html; checked 2026-09-23. Rapid summary only; existing Evidence Quality is unchanged.</x:v>
+        <x:v>官方摘要/论文页; https://openaccess.thecvf.com/content/CVPR2024/html/Ma_Hierarchical_Diffusion_Policy_for_Kinematics-Aware_Multi-Task_Robotic_Manipulation_CVPR_2024_paper.html; 核验于 2026-09-23. 仅为摘要级速读；原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="BX2" t="str">
         <x:v>Unresolved</x:v>
@@ -10299,7 +10299,7 @@
         <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AD3" t="str">
-        <x:v>Bimanual robotic manipulation is an emerging and critical topic in the robotics community.</x:v>
+        <x:v>不同双臂任务的交互结构不同，统一耦合方式未必合适。</x:v>
       </x:c>
       <x:c r="AE3" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -10308,7 +10308,7 @@
         <x:v>以 `bimanual manipulation; decoupled interaction; RoboTwin` 为主要方法/能力线索；更细的结构和消融结论待正文核验。</x:v>
       </x:c>
       <x:c r="AG3" t="str">
-        <x:v>Not specified in checked abstract/card.</x:v>
+        <x:v>RoboTwin 七项任务。</x:v>
       </x:c>
       <x:c r="AH3" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -10401,30 +10401,30 @@
       </x:c>
       <x:c r="BM3"/>
       <x:c r="BN3" t="str">
-        <x:v>Evidence-backed — Bimanual robotic manipulation is an emerging and critical topic in the robotics community.</x:v>
+        <x:v>不同双臂任务的交互结构不同，统一耦合方式未必合适。</x:v>
       </x:c>
       <x:c r="BO3" t="str">
-        <x:v>However, we think bimanual manipulation involves not only coordinated tasks but also various uncoordinated tasks that do not require explicit cooperation during execution, such as grasping objects with the closest hand, which integrated control frameworks…</x:v>
+        <x:v>始终联合预测双臂动作，可能忽略支撑手与操作手的不同职责。</x:v>
       </x:c>
       <x:c r="BP3" t="str">
-        <x:v>In this paper, we propose a novel decoupled interaction framework that considers the characteristics of different tasks in bimanual manipulation.</x:v>
+        <x:v>按任务交互特点设计解耦框架，让双臂策略分别处理可分解的部分并保持必要协调。</x:v>
       </x:c>
       <x:c r="BQ3" t="str"/>
       <x:c r="BR3" t="str">
-        <x:v>Extensive experiments on seven tasks in the RoboTwin dataset demonstrate that: (1) Our framework achieves outstanding performance, with a 23.5% boost over the SOTA method. (2) Our framework is flexible and can be seamlessly integrated into existing methods.…</x:v>
+        <x:v>论文报告在七项 RoboTwin 任务上较所比较 SOTA 提升 23.5%；具体指标定义见原文。</x:v>
       </x:c>
       <x:c r="BS3" t="str">
-        <x:v>Provides a concrete method or benchmark for the documented gap: However, we think bimanual manipulation involves not only coordinated tasks but also various uncoordinated tasks that do not…</x:v>
+        <x:v>为联合预测与分臂预测的实验对照提供方法。</x:v>
       </x:c>
       <x:c r="BT3" t="str">
-        <x:v>Not established by the checked summary source; consult the full paper.</x:v>
+        <x:v>仿真 benchmark 上的优势仍需真机接触任务验证。</x:v>
       </x:c>
       <x:c r="BU3" t="str"/>
       <x:c r="BV3" t="str">
-        <x:v>High — directly informs dual-arm coordination, data or ordinary-gripper policy design.</x:v>
+        <x:v>High：普通夹爪常有支撑—操作分工。</x:v>
       </x:c>
       <x:c r="BW3" t="str">
-        <x:v>Official abstract / paper page; https://openaccess.thecvf.com/content/ICCV2025/html/Jiang_Rethinking_Bimanual_Robotic_Manipulation_Learning_with_Decoupled_Interaction_Framework_ICCV_2025_paper.html; checked 2026-09-23. Rapid summary only; existing Evidence Quality is unchanged.</x:v>
+        <x:v>官方摘要/论文页; https://openaccess.thecvf.com/content/ICCV2025/html/Jiang_Rethinking_Bimanual_Robotic_Manipulation_Learning_with_Decoupled_Interaction_Framework_ICCV_2025_paper.html; 核验于 2026-09-23. 仅为摘要级速读；原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="BX3" t="str">
         <x:v>Exact work identity verified</x:v>
@@ -10517,7 +10517,7 @@
         <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AD4" t="str">
-        <x:v>Bimanual manipulation is crucial in robotics, enabling complex tasks in industrial automation and household services.</x:v>
+        <x:v>复杂双臂任务需要预测动作，也需要理解后续视觉状态。</x:v>
       </x:c>
       <x:c r="AE4" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -10526,7 +10526,7 @@
         <x:v>以 `bimanual; diffusion; teleoperation; human demonstration` 为主要方法/能力线索；更细的结构和消融结论待正文核验。</x:v>
       </x:c>
       <x:c r="AG4" t="str">
-        <x:v>Not specified in checked abstract/card.</x:v>
+        <x:v>两项仿真 benchmark 与一项真机设置。</x:v>
       </x:c>
       <x:c r="AH4" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -10619,30 +10619,30 @@
       </x:c>
       <x:c r="BM4"/>
       <x:c r="BN4" t="str">
-        <x:v>Evidence-backed — Bimanual manipulation is crucial in robotics, enabling complex tasks in industrial automation and household services.</x:v>
+        <x:v>复杂双臂任务需要预测动作，也需要理解后续视觉状态。</x:v>
       </x:c>
       <x:c r="BO4" t="str">
-        <x:v>However, it poses significant challenges due to the high-dimensional action space and intricate coordination requirements.</x:v>
+        <x:v>只学动作或只生成视频，可能无法协调两臂与物体变化。</x:v>
       </x:c>
       <x:c r="BP4" t="str">
-        <x:v>To bridge this gap, we propose a unified diffusion-based framework for the joint optimization of video and action prediction.</x:v>
+        <x:v>联合优化视频预测与双臂动作生成，让策略在想象未来场景的同时协调执行。</x:v>
       </x:c>
       <x:c r="BQ4" t="str"/>
       <x:c r="BR4" t="str">
-        <x:v>Experiments on two simulated benchmarks and a real-world setting demonstrate a significant improvement in the success rate over the strong baseline ACT using our method, achieving a 24.9% increase on ALOHA, an 11.1% increase on RoboTwin, and a 32.5% increase…</x:v>
+        <x:v>论文报告在上述设置中成功率高于 ACT 基线；具体差值需核对实验表。</x:v>
       </x:c>
       <x:c r="BS4" t="str">
-        <x:v>Provides a concrete method or benchmark for the documented gap: However, it poses significant challenges due to the high-dimensional action space and intricate coordination requirements.</x:v>
+        <x:v>可测试视觉预期是否改善双臂协调。</x:v>
       </x:c>
       <x:c r="BT4" t="str">
-        <x:v>Not established by the checked summary source; consult the full paper.</x:v>
+        <x:v>真机环境和失败类型的完整覆盖仍需查正文。</x:v>
       </x:c>
       <x:c r="BU4" t="str"/>
       <x:c r="BV4" t="str">
-        <x:v>High — directly informs dual-arm coordination, data or ordinary-gripper policy design.</x:v>
+        <x:v>High：双臂普通夹爪可对照 ACT 与带未来预测的策略。</x:v>
       </x:c>
       <x:c r="BW4" t="str">
-        <x:v>Official abstract / paper page; https://openaccess.thecvf.com/content/ICCV2025/html/Xu_Diffusion-Based_Imaginative_Coordination_for_Bimanual_Manipulation_ICCV_2025_paper.html; checked 2026-09-23. Rapid summary only; existing Evidence Quality is unchanged.</x:v>
+        <x:v>官方摘要/论文页; https://openaccess.thecvf.com/content/ICCV2025/html/Xu_Diffusion-Based_Imaginative_Coordination_for_Bimanual_Manipulation_ICCV_2025_paper.html; 核验于 2026-09-23. 仅为摘要级速读；原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="BX4" t="str">
         <x:v>Exact work identity verified</x:v>
@@ -10737,7 +10737,7 @@
         <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AD5" t="str">
-        <x:v>Vision and touch are the most commonly used senses in human manipulation.</x:v>
+        <x:v>灵巧操作需要结合视觉和触觉，而人类操作视频的机器人预训练多限于视觉与语言。</x:v>
       </x:c>
       <x:c r="AE5" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -10746,7 +10746,7 @@
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
       </x:c>
       <x:c r="AG5" t="str">
-        <x:v>Not specified in checked abstract/card.</x:v>
+        <x:v>六项复杂灵巧操作任务；论文比较 18 种方法。</x:v>
       </x:c>
       <x:c r="AH5" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -10839,30 +10839,30 @@
       </x:c>
       <x:c r="BM5"/>
       <x:c r="BN5" t="str">
-        <x:v>Evidence-backed — Vision and touch are the most commonly used senses in human manipulation.</x:v>
+        <x:v>灵巧操作需要结合视觉和触觉，而人类操作视频的机器人预训练多限于视觉与语言。</x:v>
       </x:c>
       <x:c r="BO5" t="str">
-        <x:v>While leveraging human manipulation videos for robotic task pretraining has shown promise in prior works, it is limited to image and language modalities and deployment to simple parallel grippers.</x:v>
+        <x:v>已有视频预训练主要在简单平行夹爪上部署，难覆盖触觉驱动的灵巧手任务。</x:v>
       </x:c>
       <x:c r="BP5" t="str">
-        <x:v>Also, we introduce a novel benchmark, featuring six complex dexterous manipulation tasks and a reinforcement learning-based vision-tactile skill learning framework. 18 non-pretraining and pretraining methods within the framework are designed and compared to investigate the effectiveness of different modalities and pertaining strategies.</x:v>
+        <x:v>VTDexManip 提供视觉—触觉灵巧操作基准和强化学习技能框架，比较 18 种预训练或非预训练方法。</x:v>
       </x:c>
       <x:c r="BQ5" t="str"/>
       <x:c r="BR5" t="str">
-        <x:v>Qualitative or numerical result not established by checked source.</x:v>
+        <x:v>摘要给出六任务与 18 方法的评测设置；本轮未确认可直接引用的胜率。</x:v>
       </x:c>
       <x:c r="BS5" t="str">
-        <x:v>Provides a concrete method or benchmark for the documented gap: While leveraging human manipulation videos for robotic task pretraining has shown promise in prior works, it is limited to image…</x:v>
+        <x:v>有助于辨别触觉信息在灵巧操作中的作用。</x:v>
       </x:c>
       <x:c r="BT5" t="str">
-        <x:v>Not established by the checked summary source; consult the full paper.</x:v>
+        <x:v>摘要不能证明触觉收益能在无触觉或低成本普通夹爪上复现。</x:v>
       </x:c>
       <x:c r="BU5" t="str"/>
       <x:c r="BV5" t="str">
-        <x:v>Medium — transferable learning ideas may apply, but the hand hardware differs from ordinary grippers.</x:v>
+        <x:v>Medium：多模态融合可借鉴，但灵巧手任务与普通夹爪不同。</x:v>
       </x:c>
       <x:c r="BW5" t="str">
-        <x:v>Official abstract / paper page; https://proceedings.iclr.cc/paper_files/paper/2025/hash/e19b6f65791e350347bcff8a3955cb5b-Abstract-Conference.html; checked 2026-09-23. Rapid summary only; existing Evidence Quality is unchanged.</x:v>
+        <x:v>官方摘要/论文页; https://proceedings.iclr.cc/paper_files/paper/2025/hash/e19b6f65791e350347bcff8a3955cb5b-Abstract-Conference.html; 核验于 2026-09-23. 仅为摘要级速读；原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="BX5" t="str">
         <x:v>Unresolved</x:v>
@@ -10955,7 +10955,7 @@
         <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AD6" t="str">
-        <x:v>Dexterous hands exhibit significant potential for complex real-world grasping tasks.</x:v>
+        <x:v>不同灵巧手硬件如何共享抓取能力。</x:v>
       </x:c>
       <x:c r="AE6" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -10964,7 +10964,7 @@
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
       </x:c>
       <x:c r="AG6" t="str">
-        <x:v>Not specified in checked abstract/card.</x:v>
+        <x:v>已核验摘要未明确说明；需查阅论文方法与实验章节。</x:v>
       </x:c>
       <x:c r="AH6" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -11057,30 +11057,30 @@
       </x:c>
       <x:c r="BM6"/>
       <x:c r="BN6" t="str">
-        <x:v>Evidence-backed — Dexterous hands exhibit significant potential for complex real-world grasping tasks.</x:v>
+        <x:v>不同灵巧手硬件如何共享抓取能力。</x:v>
       </x:c>
       <x:c r="BO6" t="str">
-        <x:v>While recent studies have primarily focused on learning policies for specific robotic hands, the development of a universal policy that controls diverse dexterous hands remains largely unexplored.In this work, we study the learning of cross-embodiment…</x:v>
+        <x:v>各手型关节和动作维度不同，单一策略难直接复用。</x:v>
       </x:c>
       <x:c r="BP6" t="str">
-        <x:v>Inspired by the capability of human hands to control various dexterous hands through teleoperation, we propose a universal action space based on the human hand's eigengrasps.</x:v>
+        <x:v>通过统一动作表示与强化学习，训练可跨不同灵巧手迁移的抓取策略。具体接口需核对正文。</x:v>
       </x:c>
       <x:c r="BQ6" t="str"/>
       <x:c r="BR6" t="str">
-        <x:v>Qualitative or numerical result not established by checked source.</x:v>
+        <x:v>已核验摘要未给可安全复述的统一量化结果。</x:v>
       </x:c>
       <x:c r="BS6" t="str">
-        <x:v>Provides a concrete method or benchmark for the documented gap: While recent studies have primarily focused on learning policies for specific robotic hands, the development of a universal…</x:v>
+        <x:v>强调动作接口是跨本体迁移的关键。</x:v>
       </x:c>
       <x:c r="BT6" t="str">
-        <x:v>Not established by the checked summary source; consult the full paper.</x:v>
+        <x:v>跨手型实验不能直接证明跨普通夹爪双臂成功。</x:v>
       </x:c>
       <x:c r="BU6" t="str"/>
       <x:c r="BV6" t="str">
-        <x:v>Medium — transferable learning ideas may apply, but the hand hardware differs from ordinary grippers.</x:v>
+        <x:v>Medium：普通夹爪硬件不同，但统一动作表示的思路有用。</x:v>
       </x:c>
       <x:c r="BW6" t="str">
-        <x:v>Official abstract / paper page; https://proceedings.iclr.cc/paper_files/paper/2025/hash/ca8c6f28d8ba1e732e3f217ab05c4ec0-Abstract-Conference.html; checked 2026-09-23. Rapid summary only; existing Evidence Quality is unchanged.</x:v>
+        <x:v>官方摘要/论文页; https://proceedings.iclr.cc/paper_files/paper/2025/hash/ca8c6f28d8ba1e732e3f217ab05c4ec0-Abstract-Conference.html; 核验于 2026-09-23. 仅为摘要级速读；原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="BX6" t="str">
         <x:v>Exact work identity verified</x:v>
@@ -11173,7 +11173,7 @@
         <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AD7" t="str">
-        <x:v>Robot learning requires a considerable amount of high-quality data to realize the promise of generalization.</x:v>
+        <x:v>机器人策略泛化需要大量高质量真实数据。</x:v>
       </x:c>
       <x:c r="AE7" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -11182,7 +11182,7 @@
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
       </x:c>
       <x:c r="AG7" t="str">
-        <x:v>Not specified in checked abstract/card.</x:v>
+        <x:v>已核验摘要未明确说明；需查阅论文方法与实验章节。</x:v>
       </x:c>
       <x:c r="AH7" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -11275,30 +11275,30 @@
       </x:c>
       <x:c r="BM7"/>
       <x:c r="BN7" t="str">
-        <x:v>Evidence-backed — Robot learning requires a considerable amount of high-quality data to realize the promise of generalization.</x:v>
+        <x:v>机器人策略泛化需要大量高质量真实数据。</x:v>
       </x:c>
       <x:c r="BO7" t="str">
-        <x:v>However, large data sets are costly to collect in the real world.</x:v>
+        <x:v>普通微调方法在真机新任务上仍需要较多示范。</x:v>
       </x:c>
       <x:c r="BP7" t="str">
-        <x:v>This paper introduces the \emph{Simulation-Guided Fine-tuning} (SGFT) framework, which demonstrates how to extract structural priors from physics simulators to substantially accelerate real-world adaptation.</x:v>
+        <x:v>Simulation-Guided Fine-Tuning 从物理仿真提取结构先验，加速真机策略适配。</x:v>
       </x:c>
       <x:c r="BQ7" t="str"/>
       <x:c r="BR7" t="str">
-        <x:v>We further demonstrate our framework substantially outperforms baseline fine-tuning methods, requiring up to an order of magnitude fewer real-world samples and succeeding at difficult tasks where prior approaches fail entirely.</x:v>
+        <x:v>作者报告所需真实样本最多减少约一个数量级，并优于基线微调方法；具体任务见论文。</x:v>
       </x:c>
       <x:c r="BS7" t="str">
-        <x:v>Provides a concrete method or benchmark for the documented gap: However, large data sets are costly to collect in the real world.</x:v>
+        <x:v>提供小数据真机适配的可比较路线。</x:v>
       </x:c>
       <x:c r="BT7" t="str">
-        <x:v>Not established by the checked summary source; consult the full paper.</x:v>
+        <x:v>仿真先验对接触和相机变化的稳定性需在目标硬件验证。</x:v>
       </x:c>
       <x:c r="BU7" t="str"/>
       <x:c r="BV7" t="str">
-        <x:v>High — informs transfer from simulation to NERO real-robot manipulation.</x:v>
+        <x:v>High：双臂普通夹爪的真实示范预算有限。</x:v>
       </x:c>
       <x:c r="BW7" t="str">
-        <x:v>Official abstract / paper page; https://proceedings.iclr.cc/paper_files/paper/2025/hash/e68274fc4f158dbcbd4dddc672f7ee9c-Abstract-Conference.html; checked 2026-09-23. Rapid summary only; existing Evidence Quality is unchanged.</x:v>
+        <x:v>官方摘要/论文页; https://proceedings.iclr.cc/paper_files/paper/2025/hash/e68274fc4f158dbcbd4dddc672f7ee9c-Abstract-Conference.html; 核验于 2026-09-23. 仅为摘要级速读；原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="BX7" t="str">
         <x:v>Unresolved</x:v>
@@ -11389,7 +11389,7 @@
         <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AD8" t="str">
-        <x:v>We address the challenge of developing a generalizable neural tracking controller for dexterous manipulation from human references.</x:v>
+        <x:v>机器人灵巧手如何稳定跟踪人类参考动作。</x:v>
       </x:c>
       <x:c r="AE8" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -11398,7 +11398,7 @@
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
       </x:c>
       <x:c r="AG8" t="str">
-        <x:v>Not specified in checked abstract/card.</x:v>
+        <x:v>已核验摘要未明确说明；需查阅论文方法与实验章节。</x:v>
       </x:c>
       <x:c r="AH8" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -11491,30 +11491,30 @@
       </x:c>
       <x:c r="BM8"/>
       <x:c r="BN8" t="str">
-        <x:v>Evidence-backed — We address the challenge of developing a generalizable neural tracking controller for dexterous manipulation from human references.</x:v>
+        <x:v>机器人灵巧手如何稳定跟踪人类参考动作。</x:v>
       </x:c>
       <x:c r="BO8" t="str">
-        <x:v>Not established in checked summary source.</x:v>
+        <x:v>人手参考轨迹与真实机器人控制之间存在可达性和动力学差异。</x:v>
       </x:c>
       <x:c r="BP8" t="str">
-        <x:v>We introduce an approach that curates large-scale successful robot tracking demonstrations, comprising pairs of human references and robot actions, to train a neural controller.</x:v>
+        <x:v>整理大规模成功跟踪示范，训练可泛化的神经控制器对齐人类参考。</x:v>
       </x:c>
       <x:c r="BQ8" t="str"/>
       <x:c r="BR8" t="str">
-        <x:v>Our method achieves over a 10% improvement in success rates compared to leading baselines.</x:v>
+        <x:v>作者报告成功率比主要基线高 10 个百分点以上。</x:v>
       </x:c>
       <x:c r="BS8" t="str">
-        <x:v>Medium — transferable learning ideas may apply, but the hand hardware differs from ordinary grippers.</x:v>
+        <x:v>提供从人体动作到机器人控制的跟踪基线。</x:v>
       </x:c>
       <x:c r="BT8" t="str">
-        <x:v>Not established by the checked summary source; consult the full paper.</x:v>
+        <x:v>人手跟踪成功不等于真实物体操作成功。</x:v>
       </x:c>
       <x:c r="BU8" t="str"/>
       <x:c r="BV8" t="str">
-        <x:v>Medium — transferable learning ideas may apply, but the hand hardware differs from ordinary grippers.</x:v>
+        <x:v>Medium：对双臂数据重定向有启发，但夹爪动作更简单。</x:v>
       </x:c>
       <x:c r="BW8" t="str">
-        <x:v>Official abstract / paper page; https://proceedings.iclr.cc/paper_files/paper/2025/hash/d5a1f97d2b922da92e880d13b7d2bf02-Abstract-Conference.html; checked 2026-09-23. Rapid summary only; existing Evidence Quality is unchanged.</x:v>
+        <x:v>官方摘要/论文页; https://proceedings.iclr.cc/paper_files/paper/2025/hash/d5a1f97d2b922da92e880d13b7d2bf02-Abstract-Conference.html; 核验于 2026-09-23. 仅为摘要级速读；原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="BX8" t="str">
         <x:v>Exact work identity verified</x:v>
@@ -11607,7 +11607,7 @@
         <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AD9" t="str">
-        <x:v>Training embodied agents to perform complex robotic tasks presents significant challenges due to the entangled factors of task compositionality, environmental diversity, and dynamic changes.</x:v>
+        <x:v>复杂操作把任务理解、感知和控制混在一起，难以稳定学习。</x:v>
       </x:c>
       <x:c r="AE9" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -11616,7 +11616,7 @@
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
       </x:c>
       <x:c r="AG9" t="str">
-        <x:v>Not specified in checked abstract/card.</x:v>
+        <x:v>已核验摘要未明确说明；需查阅论文方法与实验章节。</x:v>
       </x:c>
       <x:c r="AH9" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -11709,30 +11709,30 @@
       </x:c>
       <x:c r="BM9"/>
       <x:c r="BN9" t="str">
-        <x:v>Evidence-backed — Training embodied agents to perform complex robotic tasks presents significant challenges due to the entangled factors of task compositionality, environmental diversity, and dynamic changes.</x:v>
+        <x:v>复杂操作把任务理解、感知和控制混在一起，难以稳定学习。</x:v>
       </x:c>
       <x:c r="BO9" t="str">
-        <x:v>Experiments demonstrate that our approach significantly outperforms baseline methods across a range of tasks and environments, while showcasing emergent consistency in motion patterns associated with the discovered manipulation concepts.</x:v>
+        <x:v>开环概念提示不能根据新观测及时修正动作。</x:v>
       </x:c>
       <x:c r="BP9" t="str">
-        <x:v>In this work, we introduce a novel imitation learning framework to train closed-loop concept-guided policies that enhance long-horizon task performance by leveraging discovered manipulation concepts.</x:v>
+        <x:v>AutoCGP 建立闭环、概念引导的模仿学习策略，让概念状态参与长任务决策。</x:v>
       </x:c>
       <x:c r="BQ9" t="str"/>
       <x:c r="BR9" t="str">
-        <x:v>Qualitative or numerical result not established by checked source.</x:v>
+        <x:v>已核验摘要未给可安全复述的统一量化结果。</x:v>
       </x:c>
       <x:c r="BS9" t="str">
-        <x:v>Provides a concrete method or benchmark for the documented gap: Experiments demonstrate that our approach significantly outperforms baseline methods across a range of tasks and environments…</x:v>
+        <x:v>提示可以把可解释概念放在 VLA 与底层控制之间。</x:v>
       </x:c>
       <x:c r="BT9" t="str">
-        <x:v>Not established by the checked summary source; consult the full paper.</x:v>
+        <x:v>需核验概念误判和真机长任务失败案例。</x:v>
       </x:c>
       <x:c r="BU9" t="str"/>
       <x:c r="BV9" t="str">
-        <x:v>Medium — relevant to robot manipulation; transfer to dual-arm real hardware needs validation.</x:v>
+        <x:v>Medium：有助于设计双臂任务状态检查。</x:v>
       </x:c>
       <x:c r="BW9" t="str">
-        <x:v>Official abstract / paper page; https://proceedings.iclr.cc/paper_files/paper/2025/hash/6eed1e1d5ed52deee53234786998245e-Abstract-Conference.html; checked 2026-09-23. Rapid summary only; existing Evidence Quality is unchanged.</x:v>
+        <x:v>官方摘要/论文页; https://proceedings.iclr.cc/paper_files/paper/2025/hash/6eed1e1d5ed52deee53234786998245e-Abstract-Conference.html; 核验于 2026-09-23. 仅为摘要级速读；原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="BX9" t="str">
         <x:v>Unresolved</x:v>
@@ -11823,7 +11823,7 @@
         <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AD10" t="str">
-        <x:v>Articulated object manipulation is a critical capability for robots to perform various tasks in real-world scenarios.Composed of multiple parts connected by joints, articulated objects are endowed with diverse functional mechanisms through complex relative motions.</x:v>
+        <x:v>机器人需要操作具有多部件、关节及隐藏约束的铰接物体。</x:v>
       </x:c>
       <x:c r="AE10" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -11832,7 +11832,7 @@
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
       </x:c>
       <x:c r="AG10" t="str">
-        <x:v>Not specified in checked abstract/card.</x:v>
+        <x:v>AdaManip 铰接物体仿真环境与数据集；规模需按全文核验。</x:v>
       </x:c>
       <x:c r="AH10" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -11925,30 +11925,30 @@
       </x:c>
       <x:c r="BM10"/>
       <x:c r="BN10" t="str">
-        <x:v>Evidence-backed — Articulated object manipulation is a critical capability for robots to perform various tasks in real-world scenarios.Composed of multiple parts connected by joints, articulated objects are endowed with diverse functional mechanisms through complex relative motions.</x:v>
+        <x:v>机器人需要操作具有多部件、关节及隐藏约束的铰接物体。</x:v>
       </x:c>
       <x:c r="BO10" t="str">
-        <x:v>However, previous datasets and simulation environments for articulated objects have primarily focused on simple manipulation mechanisms where the complete manipulation process can be inferred from the object's appearance.</x:v>
+        <x:v>以往数据集多关注从外观即可推断完整步骤的简单机构，对先解锁再开启的自适应机制覆盖不足。</x:v>
       </x:c>
       <x:c r="BP10" t="str">
-        <x:v>For example, a safe consists of a door, a handle, and a lock, where the door can only be opened when the latch is unlocked.</x:v>
+        <x:v>AdaManip 建立包含自适应机制的铰接物体环境与数据集，并研究相应策略学习；保险箱门先解锁再打开是论文中的例子。</x:v>
       </x:c>
       <x:c r="BQ10" t="str"/>
       <x:c r="BR10" t="str">
-        <x:v>Qualitative or numerical result not established by checked source.</x:v>
+        <x:v>已核验摘要说明新环境与数据集；本轮不复述未经表格核实的成功率。</x:v>
       </x:c>
       <x:c r="BS10" t="str">
-        <x:v>Provides a concrete method or benchmark for the documented gap: However, previous datasets and simulation environments for articulated objects have primarily focused on simple manipulation…</x:v>
+        <x:v>顺序依赖和隐藏状态对长程操作与失败恢复有参考价值。</x:v>
       </x:c>
       <x:c r="BT10" t="str">
-        <x:v>Not established by the checked summary source; consult the full paper.</x:v>
+        <x:v>摘要层级尚不能确认不同机制的泛化边界与真实机器人表现。</x:v>
       </x:c>
       <x:c r="BU10" t="str"/>
       <x:c r="BV10" t="str">
-        <x:v>Medium — useful for method selection, data design and evaluation.</x:v>
+        <x:v>Medium：可借鉴机制约束任务设计；与本项目双臂普通夹爪平台的迁移需另测。</x:v>
       </x:c>
       <x:c r="BW10" t="str">
-        <x:v>Official abstract / paper page; https://proceedings.iclr.cc/paper_files/paper/2025/hash/9cd0c57170f48520749d5ae62838241f-Abstract-Conference.html; checked 2026-09-23. Rapid summary only; existing Evidence Quality is unchanged.</x:v>
+        <x:v>官方摘要/论文页; https://proceedings.iclr.cc/paper_files/paper/2025/hash/9cd0c57170f48520749d5ae62838241f-Abstract-Conference.html; 核验于 2026-09-23. 仅为摘要级速读；原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="BX10" t="str">
         <x:v>Exact work identity verified</x:v>
@@ -12043,7 +12043,7 @@
         <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AD11" t="str">
-        <x:v>Large foundation models have shown strong open-world generalization to complex problems in vision and language, but similar levels of generalization have yet to be achieved in robotics.</x:v>
+        <x:v>开放世界操作需要利用基础模型知识，但机器人动作数据昂贵。</x:v>
       </x:c>
       <x:c r="AE11" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -12052,7 +12052,7 @@
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
       </x:c>
       <x:c r="AG11" t="str">
-        <x:v>Not specified in checked abstract/card.</x:v>
+        <x:v>已核验摘要未明确说明；需查阅论文方法与实验章节。</x:v>
       </x:c>
       <x:c r="AH11" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -12145,30 +12145,30 @@
       </x:c>
       <x:c r="BM11"/>
       <x:c r="BN11" t="str">
-        <x:v>Evidence-backed — Large foundation models have shown strong open-world generalization to complex problems in vision and language, but similar levels of generalization have yet to be achieved in robotics.</x:v>
+        <x:v>开放世界操作需要利用基础模型知识，但机器人动作数据昂贵。</x:v>
       </x:c>
       <x:c r="BO11" t="str">
-        <x:v>One fundamental challenge is the lack of robotic data, which are typically obtained through expensive on-robot operation.</x:v>
+        <x:v>高层 VLM 不适合直接生成精细控制，低层策略又缺少广泛语义知识。</x:v>
       </x:c>
       <x:c r="BP11" t="str">
-        <x:v>One fundamental challenge is the lack of robotic data, which are typically obtained through expensive on-robot operation.</x:v>
+        <x:v>HAMSTER 将高层任务理解与低层动作控制分工，降低双方负担。</x:v>
       </x:c>
       <x:c r="BQ11" t="str"/>
       <x:c r="BR11" t="str">
-        <x:v>Doing so alleviates the high-level VLM from fine-grained action prediction, while reducing the low-level policy's burden on complex task-level reasoning.We show that, with the hierarchical design, the high-level VLM can transfer across significant domain gaps…</x:v>
+        <x:v>论文摘要报告该分层设计改善任务执行；统一数字需查实验表。</x:v>
       </x:c>
       <x:c r="BS11" t="str">
-        <x:v>Provides a concrete method or benchmark for the documented gap: One fundamental challenge is the lack of robotic data, which are typically obtained through expensive on-robot operation.</x:v>
+        <x:v>是比较分层规划和端到端 VLA 的阅读入口。</x:v>
       </x:c>
       <x:c r="BT11" t="str">
-        <x:v>Not established by the checked summary source; consult the full paper.</x:v>
+        <x:v>高低层接口不一致会造成目标误解或执行失败。</x:v>
       </x:c>
       <x:c r="BU11" t="str"/>
       <x:c r="BV11" t="str">
-        <x:v>High — informs language-conditioned manipulation and VLA design.</x:v>
+        <x:v>High：双臂普通夹爪可能需要高层分工和低层安全控制。</x:v>
       </x:c>
       <x:c r="BW11" t="str">
-        <x:v>Official abstract / paper page; https://proceedings.iclr.cc/paper_files/paper/2025/hash/3bfee3bc6639c36e6e7b058db909f760-Abstract-Conference.html; checked 2026-09-23. Rapid summary only; existing Evidence Quality is unchanged.</x:v>
+        <x:v>官方摘要/论文页; https://proceedings.iclr.cc/paper_files/paper/2025/hash/3bfee3bc6639c36e6e7b058db909f760-Abstract-Conference.html; 核验于 2026-09-23. 仅为摘要级速读；原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="BX11" t="str">
         <x:v>Exact work identity verified</x:v>
@@ -12263,7 +12263,7 @@
         <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AD12" t="str">
-        <x:v>Imitation learning, e.g., diffusion policy, has been proven effective in various robotic manipulation tasks.However, extensive demonstrations are required for policy robustness and generalization.To reduce the demonstration reliance, we leverage spatial symmetry and propose ET-SEED, an efficient trajectory-level SE(3) equivariant diffusion model for generating action sequences in complex robot…</x:v>
+        <x:v>机器人模仿学习通常需要大量专家示范。</x:v>
       </x:c>
       <x:c r="AE12" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -12272,7 +12272,7 @@
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
       </x:c>
       <x:c r="AG12" t="str">
-        <x:v>Not specified in checked abstract/card.</x:v>
+        <x:v>已核验摘要未明确说明；需查阅论文方法与实验章节。</x:v>
       </x:c>
       <x:c r="AH12" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -12365,30 +12365,30 @@
       </x:c>
       <x:c r="BM12"/>
       <x:c r="BN12" t="str">
-        <x:v>Evidence-backed — Imitation learning, e.g., diffusion policy, has been proven effective in various robotic manipulation tasks.However, extensive demonstrations are required for policy robustness and generalization.To reduce the demonstration reliance, we leverage spatial symmetry and propose ET-SEED, an efficient trajectory-level SE(3) equivariant diffusion model for generating action sequences in complex robot…</x:v>
+        <x:v>机器人模仿学习通常需要大量专家示范。</x:v>
       </x:c>
       <x:c r="BO12" t="str">
-        <x:v>Not established in checked summary source.</x:v>
+        <x:v>如果没有适合的空间表示，少量示范难以支持稳定动作生成。</x:v>
       </x:c>
       <x:c r="BP12" t="str">
-        <x:v>Website: https://et-seed.github.io/</x:v>
+        <x:v>ET-SEED 研究带空间结构的扩散式操作策略；具体模块与输入输出需核验官方正文，不能只凭项目页推断。</x:v>
       </x:c>
       <x:c r="BQ12" t="str"/>
       <x:c r="BR12" t="str">
-        <x:v>Qualitative or numerical result not established by checked source.</x:v>
+        <x:v>当前摘要来源没有足以安全复述的统一量化结果。</x:v>
       </x:c>
       <x:c r="BS12" t="str">
-        <x:v>Medium — relevant to robot manipulation; transfer to dual-arm real hardware needs validation.</x:v>
+        <x:v>可作为三维动作表示与数据效率的待核验候选。</x:v>
       </x:c>
       <x:c r="BT12" t="str">
-        <x:v>Not established by the checked summary source; consult the full paper.</x:v>
+        <x:v>原卡方法字段混入项目网址，需优先重新阅读正式方法章节。</x:v>
       </x:c>
       <x:c r="BU12" t="str"/>
       <x:c r="BV12" t="str">
-        <x:v>Medium — relevant to robot manipulation; transfer to dual-arm real hardware needs validation.</x:v>
+        <x:v>Medium：与低示范双臂操作相关，但证据细节仍待查。</x:v>
       </x:c>
       <x:c r="BW12" t="str">
-        <x:v>Official abstract / paper page; https://proceedings.iclr.cc/paper_files/paper/2025/hash/969a11f489c59c50c2cfe8c407c68a9b-Abstract-Conference.html; checked 2026-09-23. Rapid summary only; existing Evidence Quality is unchanged.</x:v>
+        <x:v>官方摘要/论文页; https://proceedings.iclr.cc/paper_files/paper/2025/hash/969a11f489c59c50c2cfe8c407c68a9b-Abstract-Conference.html; 核验于 2026-09-23. 仅为摘要级速读；原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="BX12" t="str">
         <x:v>Exact work identity verified</x:v>
@@ -12483,7 +12483,7 @@
         <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AD13" t="str">
-        <x:v>Predicting and executing a sequence of actions without intermediate replanning, known as action chunking, is increasingly used in robot learning from human demonstrations.</x:v>
+        <x:v>Action Chunk 减少推理调用，却可能降低中途修正能力。</x:v>
       </x:c>
       <x:c r="AE13" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -12492,7 +12492,7 @@
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
       </x:c>
       <x:c r="AG13" t="str">
-        <x:v>Not specified in checked abstract/card.</x:v>
+        <x:v>已核验摘要未明确说明；需查阅论文方法与实验章节。</x:v>
       </x:c>
       <x:c r="AH13" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -12585,30 +12585,30 @@
       </x:c>
       <x:c r="BM13"/>
       <x:c r="BN13" t="str">
-        <x:v>Evidence-backed — Predicting and executing a sequence of actions without intermediate replanning, known as action chunking, is increasingly used in robot learning from human demonstrations.</x:v>
+        <x:v>Action Chunk 减少推理调用，却可能降低中途修正能力。</x:v>
       </x:c>
       <x:c r="BO13" t="str">
-        <x:v>Yet, its effects on the learned policy remain inconsistent: some studies find it crucial for achieving strong results, while others observe decreased performance.</x:v>
+        <x:v>固定动作块开环执行与每步重新规划之间存在速度—反应性权衡。</x:v>
       </x:c>
       <x:c r="BP13" t="str">
-        <x:v>To address this tradeoff, we propose Bidirectional Decoding (BID), a test-time inference algorithm that bridges action chunking with closed-loop adaptation.</x:v>
+        <x:v>Bidirectional Decoding 在测试时调整生成式策略的动作解码，连接动作块与在线反馈。</x:v>
       </x:c>
       <x:c r="BQ13" t="str"/>
       <x:c r="BR13" t="str">
-        <x:v>Experimental results show that our method boosts the performance of two state-of-the-art generative policies across seven simulation benchmarks and two real-world tasks.</x:v>
+        <x:v>作者报告在七项仿真任务上提升两类生成式策略表现；详细数值见论文。</x:v>
       </x:c>
       <x:c r="BS13" t="str">
-        <x:v>Provides a concrete method or benchmark for the documented gap: Yet, its effects on the learned policy remain inconsistent: some studies find it crucial for achieving strong results, while…</x:v>
+        <x:v>可用来设计低延迟但可中途纠正的双臂控制。</x:v>
       </x:c>
       <x:c r="BT13" t="str">
-        <x:v>Not established by the checked summary source; consult the full paper.</x:v>
+        <x:v>测试时解码的额外延迟和真机接触效果需核验。</x:v>
       </x:c>
       <x:c r="BU13" t="str"/>
       <x:c r="BV13" t="str">
-        <x:v>Medium — relevant to robot manipulation; transfer to dual-arm real hardware needs validation.</x:v>
+        <x:v>High：真机操作需要在动作块速度和失败恢复之间折中。</x:v>
       </x:c>
       <x:c r="BW13" t="str">
-        <x:v>Official abstract / paper page; https://proceedings.iclr.cc/paper_files/paper/2025/hash/0d78dd998f7b9ac79604d47a2d79bb0d-Abstract-Conference.html; checked 2026-09-23. Rapid summary only; existing Evidence Quality is unchanged.</x:v>
+        <x:v>官方摘要/论文页; https://proceedings.iclr.cc/paper_files/paper/2025/hash/0d78dd998f7b9ac79604d47a2d79bb0d-Abstract-Conference.html; 核验于 2026-09-23. 仅为摘要级速读；原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="BX13" t="str">
         <x:v>Unresolved</x:v>
@@ -12701,7 +12701,7 @@
         <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AD14" t="str">
-        <x:v>Recent advancements in robot learning have used imitation learning with large models and extensive demonstrations to develop effective policies.</x:v>
+        <x:v>大型模仿策略在新环境中仍可能出现局部失误。</x:v>
       </x:c>
       <x:c r="AE14" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -12710,7 +12710,7 @@
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
       </x:c>
       <x:c r="AG14" t="str">
-        <x:v>Not specified in checked abstract/card.</x:v>
+        <x:v>ManiSkill 与 Adroit，共八项任务。</x:v>
       </x:c>
       <x:c r="AH14" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -12803,30 +12803,30 @@
       </x:c>
       <x:c r="BM14"/>
       <x:c r="BN14" t="str">
-        <x:v>Evidence-backed — Recent advancements in robot learning have used imitation learning with large models and extensive demonstrations to develop effective policies.</x:v>
+        <x:v>大型模仿策略在新环境中仍可能出现局部失误。</x:v>
       </x:c>
       <x:c r="BO14" t="str">
-        <x:v>However, these models are often limited by the quantity quality, and diversity of demonstrations.</x:v>
+        <x:v>重新训练完整策略成本高，且难快速修复特定失败。</x:v>
       </x:c>
       <x:c r="BP14" t="str">
-        <x:v>We introduce Policy Decorator, which uses a model-agnostic residual policy to refine large imitation learning models during online interactions.</x:v>
+        <x:v>Policy Decorator 在已有模仿策略外加模型无关的 residual policy，对执行动作进行局部修正。</x:v>
       </x:c>
       <x:c r="BQ14" t="str"/>
       <x:c r="BR14" t="str">
-        <x:v>Our evaluation spans eight tasks across two benchmarks—ManiSkill and Adroit—and involves two state-of-the-art imitation learning models (Behavior Transformer and Diffusion Policy).</x:v>
+        <x:v>作者报告在两项 benchmark 的八个任务上提升所比较策略；具体幅度需查论文表格。</x:v>
       </x:c>
       <x:c r="BS14" t="str">
-        <x:v>Provides a concrete method or benchmark for the documented gap: However, these models are often limited by the quantity quality, and diversity of demonstrations.</x:v>
+        <x:v>提供不改动主策略的轻量失败修正路线。</x:v>
       </x:c>
       <x:c r="BT14" t="str">
-        <x:v>Not established by the checked summary source; consult the full paper.</x:v>
+        <x:v>残差动作要经过安全限幅，避免真机接触中的突然修正。</x:v>
       </x:c>
       <x:c r="BU14" t="str"/>
       <x:c r="BV14" t="str">
-        <x:v>Medium — relevant to robot manipulation; transfer to dual-arm real hardware needs validation.</x:v>
+        <x:v>High：可作为双臂 VLA 或 ACT 的附加纠错层。</x:v>
       </x:c>
       <x:c r="BW14" t="str">
-        <x:v>Official abstract / paper page; https://proceedings.iclr.cc/paper_files/paper/2025/hash/45c361d4117d598d4bb6568b407e9ac9-Abstract-Conference.html; checked 2026-09-23. Rapid summary only; existing Evidence Quality is unchanged.</x:v>
+        <x:v>官方摘要/论文页; https://proceedings.iclr.cc/paper_files/paper/2025/hash/45c361d4117d598d4bb6568b407e9ac9-Abstract-Conference.html; 核验于 2026-09-23. 仅为摘要级速读；原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="BX14" t="str">
         <x:v>Unresolved</x:v>
@@ -12921,7 +12921,7 @@
         <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AD15" t="str">
-        <x:v>Diffusion policies for visuomotor robot manipulation tasks achieve remarkable dexterity and robustness while only training on a small number of task demonstrations.</x:v>
+        <x:v>Diffusion Policy 在少量示范下表现强，但其成功来源不够清楚。</x:v>
       </x:c>
       <x:c r="AE15" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -12930,7 +12930,7 @@
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
       </x:c>
       <x:c r="AG15" t="str">
-        <x:v>Not specified in checked abstract/card.</x:v>
+        <x:v>已核验摘要未明确说明；需查阅论文方法与实验章节。</x:v>
       </x:c>
       <x:c r="AH15" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -13023,30 +13023,30 @@
       </x:c>
       <x:c r="BM15"/>
       <x:c r="BN15" t="str">
-        <x:v>Evidence-backed — Diffusion policies for visuomotor robot manipulation tasks achieve remarkable dexterity and robustness while only training on a small number of task demonstrations.</x:v>
+        <x:v>Diffusion Policy 在少量示范下表现强，但其成功来源不够清楚。</x:v>
       </x:c>
       <x:c r="BO15" t="str">
-        <x:v>However, the reason for this performance remains a mystery.</x:v>
+        <x:v>需要区分动作分布建模、记忆和插值各自的贡献。</x:v>
       </x:c>
       <x:c r="BP15" t="str">
-        <x:v>As a simple alternative to Diffusion Policy, we introduce the Action Lookup Table (ALT) policy, showing that an explicit lookup table policy can perform comparably in this low data regime.</x:v>
+        <x:v>提出 Action Lookup Table 作为简单对照，分析 Diffusion Policy 与 ACT 在动作记忆和插值上的差异。</x:v>
       </x:c>
       <x:c r="BQ15" t="str"/>
       <x:c r="BR15" t="str">
-        <x:v>We show that Diffusion Policy gives strong action memorization giving surprising robustness in OOD regimes, ACT shows action interpolation with poor robustness in OOD regimes, and GR00T (benefiting from substantial pre-training) shows both action…</x:v>
+        <x:v>论文报告 Diffusion Policy 有较强动作记忆，ACT 更偏动作插值；精确性能比较需看实验表。</x:v>
       </x:c>
       <x:c r="BS15" t="str">
-        <x:v>Provides a concrete method or benchmark for the documented gap: However, the reason for this performance remains a mystery.</x:v>
+        <x:v>防止把复杂模型的优势误判成真正泛化。</x:v>
       </x:c>
       <x:c r="BT15" t="str">
-        <x:v>Not established by the checked summary source; consult the full paper.</x:v>
+        <x:v>简单查表基线的有效性依赖示范分布；真机长任务仍需验证。</x:v>
       </x:c>
       <x:c r="BU15" t="str"/>
       <x:c r="BV15" t="str">
-        <x:v>Medium — relevant to robot manipulation; transfer to dual-arm real hardware needs validation.</x:v>
+        <x:v>High：项目需用未见物体和场景测试真实泛化。</x:v>
       </x:c>
       <x:c r="BW15" t="str">
-        <x:v>Official abstract / paper page; https://proceedings.iclr.cc/paper_files/paper/2026/hash/122ea6470232ee5e79a2649243348005-Abstract-Conference.html; checked 2026-09-23. Rapid summary only; existing Evidence Quality is unchanged.</x:v>
+        <x:v>官方摘要/论文页; https://proceedings.iclr.cc/paper_files/paper/2026/hash/122ea6470232ee5e79a2649243348005-Abstract-Conference.html; 核验于 2026-09-23. 仅为摘要级速读；原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="BX15" t="str">
         <x:v>Unresolved</x:v>
@@ -13137,7 +13137,7 @@
         <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AD16" t="str">
-        <x:v>Vision-Language-Action (VLA) models have attracted increasing attention for their strong control capabilities.</x:v>
+        <x:v>VLA 推理开销大，在线控制频率受限。</x:v>
       </x:c>
       <x:c r="AE16" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -13146,7 +13146,7 @@
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
       </x:c>
       <x:c r="AG16" t="str">
-        <x:v>Not specified in checked abstract/card.</x:v>
+        <x:v>LIBERO、SimplerEnv 与论文列出的真机任务。</x:v>
       </x:c>
       <x:c r="AH16" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -13239,30 +13239,30 @@
       </x:c>
       <x:c r="BM16"/>
       <x:c r="BN16" t="str">
-        <x:v>Evidence-backed — Vision-Language-Action (VLA) models have attracted increasing attention for their strong control capabilities.</x:v>
+        <x:v>VLA 推理开销大，在线控制频率受限。</x:v>
       </x:c>
       <x:c r="BO16" t="str">
-        <x:v>However, their high computational cost and low execution frequency hinder their suitability for real-time tasks such as robotic manipulation and autonomous navigation.</x:v>
+        <x:v>固定模型规模与统一 token 处理会浪费简单状态的计算。</x:v>
       </x:c>
       <x:c r="BP16" t="str">
-        <x:v>To this end, we propose SP-VLA , a unified framework that accelerates VLA models by jointly scheduling models and pruning tokens.</x:v>
+        <x:v>SP-VLA 联合进行模型调度与 token 剪枝，在不同状态分配不同推理计算量。</x:v>
       </x:c>
       <x:c r="BQ16" t="str"/>
       <x:c r="BR16" t="str">
-        <x:v>Extensive experiments show that our method achieves 1.5 × \times lossless acceleration in LIBERO and 2.4 × \times in SimplerEnv, with up to 6% average performance gain.</x:v>
+        <x:v>论文报告 LIBERO 无损加速约 1.5 倍、SimplerEnv 约 2.4 倍；平均成功率变化需按论文设置理解。</x:v>
       </x:c>
       <x:c r="BS16" t="str">
-        <x:v>Provides a concrete method or benchmark for the documented gap: However, their high computational cost and low execution frequency hinder their suitability for real-time tasks such as robotic…</x:v>
+        <x:v>为双臂 VLA 真机控制提供延迟优化方向。</x:v>
       </x:c>
       <x:c r="BT16" t="str">
-        <x:v>Not established by the checked summary source; consult the full paper.</x:v>
+        <x:v>剪枝造成的少数困难状态失误，需用真实任务失败案例检验。</x:v>
       </x:c>
       <x:c r="BU16" t="str"/>
       <x:c r="BV16" t="str">
-        <x:v>High — informs language-conditioned manipulation and VLA design.</x:v>
+        <x:v>High：控制频率会影响双臂同步和失败恢复。</x:v>
       </x:c>
       <x:c r="BW16" t="str">
-        <x:v>Official abstract / paper page; https://arxiv.org/html/2506.12723; checked 2026-09-23. Rapid summary only; existing Evidence Quality is unchanged.</x:v>
+        <x:v>官方摘要/论文页; https://arxiv.org/html/2506.12723; 核验于 2026-09-23. 仅为摘要级速读；原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="BX16" t="str">
         <x:v>Exact work identity verified</x:v>
@@ -13353,7 +13353,7 @@
         <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AD17" t="str">
-        <x:v>Vision-Language-Action (VLA) models have recently emerged as a powerful paradigm for robotic manipulation.</x:v>
+        <x:v>预训练 VLA 在新操作任务上仍需更有效的策略改进。</x:v>
       </x:c>
       <x:c r="AE17" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -13362,7 +13362,7 @@
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
       </x:c>
       <x:c r="AG17" t="str">
-        <x:v>OpenVLA-OFT on LIBERO, RoboTwin 1.0/2.0 and real-world tasks; the paper emphasizes reducing dependence on demonstrations.</x:v>
+        <x:v>LIBERO、RoboTwin 与真机任务。</x:v>
       </x:c>
       <x:c r="AH17" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -13455,30 +13455,30 @@
       </x:c>
       <x:c r="BM17"/>
       <x:c r="BN17" t="str">
-        <x:v>Evidence-backed — Vision-Language-Action (VLA) models have recently emerged as a powerful paradigm for robotic manipulation.</x:v>
+        <x:v>预训练 VLA 在新操作任务上仍需更有效的策略改进。</x:v>
       </x:c>
       <x:c r="BO17" t="str">
-        <x:v>Despite substantial progress enabled by large-scale pretraining and supervised fine-tuning (SFT), these models face two fundamental challenges: (i) the scarcity and high cost of large-scale human-operated robotic trajectories required for SFT scaling, and…</x:v>
+        <x:v>只做监督微调可能难利用真实成功/失败反馈。</x:v>
       </x:c>
       <x:c r="BP17" t="str">
-        <x:v>In this work, we introduce SimpleVLA-RL , an efficient RL framework tailored for VLA models.</x:v>
+        <x:v>SimpleVLA-RL 针对 VLA 设计高效强化学习与探索机制，继续优化操作策略。</x:v>
       </x:c>
       <x:c r="BQ17" t="str"/>
       <x:c r="BR17" t="str">
-        <x:v>achieves state-of-the-art LIBERO performance, surpasses π0 on RoboTwin with exploration enhancements, and outperforms SFT on real-world tasks (abstract, Sec. 4).</x:v>
+        <x:v>作者报告 LIBERO 上达到先进水平，在 RoboTwin 和真机任务上优于所比较方法；完整数值见论文表格。</x:v>
       </x:c>
       <x:c r="BS17" t="str">
-        <x:v>Provides a concrete method or benchmark for the documented gap: Despite substantial progress enabled by large-scale pretraining and supervised fine-tuning (SFT), these models face two…</x:v>
+        <x:v>为 VLA 从示范学习走向结果反馈优化提供基线。</x:v>
       </x:c>
       <x:c r="BT17" t="str">
-        <x:v>Author-stated — RL rollout cost and reward sparsity; Library Analysis — transfer beyond evaluated embodiments remains open.</x:v>
+        <x:v>真机 RL 的数据成本、失败代价和安全边界必须单独评估。</x:v>
       </x:c>
       <x:c r="BU17" t="str"/>
       <x:c r="BV17" t="str">
-        <x:v>High — informs language-conditioned manipulation and VLA design.</x:v>
+        <x:v>High：双臂真机可关注安全约束下的策略改善。</x:v>
       </x:c>
       <x:c r="BW17" t="str">
-        <x:v>Official abstract / paper page; https://arxiv.org/html/2509.09674; checked 2026-09-23. Rapid summary only; existing Evidence Quality is unchanged.</x:v>
+        <x:v>官方摘要/论文页; https://arxiv.org/html/2509.09674; 核验于 2026-09-23. 仅为摘要级速读；原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="BX17" t="str">
         <x:v>Unresolved</x:v>
@@ -13569,7 +13569,7 @@
         <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AD18" t="str">
-        <x:v>Fine-tuning vision-language models (VLMs) on robot teleoperation data to create vision-language-action (VLA) models is a promising paradigm for training generalist policies, but it suffers from a fundamental tradeoff: learning to produce actions often diminishes the VLM’s foundational reasoning and multimodal understanding, hindering generalization to novel scenarios, instruction following, and…</x:v>
+        <x:v>直接用机器人动作微调 VLM，可能损伤原有语言与多模态推理能力。</x:v>
       </x:c>
       <x:c r="AE18" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -13578,7 +13578,7 @@
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
       </x:c>
       <x:c r="AG18" t="str">
-        <x:v>human-teleoperated BridgeV2 trajectories are relabeled into hierarchical language; automatic labeling cost about $900, with manual spot checks (Appendix 6.1).</x:v>
+        <x:v>BridgeData V2 遥操作轨迹被重新标成分层语言；标注成本和抽查方法见 Appendix 6.1。</x:v>
       </x:c>
       <x:c r="AH18" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -13671,30 +13671,30 @@
       </x:c>
       <x:c r="BM18"/>
       <x:c r="BN18" t="str">
-        <x:v>Evidence-backed — Fine-tuning vision-language models (VLMs) on robot teleoperation data to create vision-language-action (VLA) models is a promising paradigm for training generalist policies, but it suffers from a fundamental tradeoff: learning to produce actions often diminishes the VLM’s foundational reasoning and multimodal understanding, hindering generalization to novel scenarios, instruction following, and…</x:v>
+        <x:v>直接用机器人动作微调 VLM，可能损伤原有语言与多模态推理能力。</x:v>
       </x:c>
       <x:c r="BO18" t="str">
-        <x:v>Not established in checked summary source.</x:v>
+        <x:v>直接把底层动作当作特殊 token 微调，可能与 VLM 的语言预训练形式不一致。</x:v>
       </x:c>
       <x:c r="BP18" t="str">
-        <x:v>Inspired by this observation, we introduce VLM2VLA: a VLA training paradigm that first resolves this mismatch at the data level by representing low-level actions with natural language .</x:v>
+        <x:v>VLM2VLA 先把底层动作写成自然语言形式，使机器人动作数据与 VLM 的原有输出形式更一致。</x:v>
       </x:c>
       <x:c r="BQ18" t="str"/>
       <x:c r="BR18" t="str">
-        <x:v>in the “Item Above Ash Ketchum” task, VLM2VLA reaches 60% versus 30% for the token-action ablation; median action-generation cycle latency is 6.1 s (Sec. 4.2.2, 5.1).</x:v>
+        <x:v>在 “Item Above Ash Ketchum” 任务上，VLM2VLA 成功率为 60%，动作 token 消融为 30%；动作生成周期中位延迟为 6.1 s（Sec. 4.2.2、5.1）。</x:v>
       </x:c>
       <x:c r="BS18" t="str">
-        <x:v>High — informs language-conditioned manipulation and VLA design.</x:v>
+        <x:v>提出一种尽量保留 VLM 推理能力的 VLA 微调接口；延迟也提示真机部署成本。</x:v>
       </x:c>
       <x:c r="BT18" t="str">
-        <x:v>Author-stated — 6.1 s latency, translational-only control, coarse motion plans, and single-embodiment training (Sec. 5.1). Library Analysis — dexterous rotation and cross-embodiment transfer remain unvalidated.</x:v>
+        <x:v>作者报告动作生成中位延迟 6.1 s，实验控制维度和本体范围有限；复杂旋转及跨本体迁移仍需验证。</x:v>
       </x:c>
       <x:c r="BU18" t="str"/>
       <x:c r="BV18" t="str">
-        <x:v>High — informs language-conditioned manipulation and VLA design.</x:v>
+        <x:v>High：有助于研究语言条件操作与 VLA 设计。</x:v>
       </x:c>
       <x:c r="BW18" t="str">
-        <x:v>Official abstract / paper page; https://arxiv.org/html/2509.22195; checked 2026-09-23. Rapid summary only; existing Evidence Quality is unchanged.</x:v>
+        <x:v>官方摘要/论文页; https://arxiv.org/html/2509.22195; 核验于 2026-09-23. 仅为摘要级速读；原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="BX18" t="str">
         <x:v>Exact work identity verified</x:v>
@@ -13787,7 +13787,7 @@
         <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AD19" t="str">
-        <x:v>Real-time execution is essential for cyber-physical systems such as robots.</x:v>
+        <x:v>机器人必须实时响应，但动作块策略可能错过中途变化。</x:v>
       </x:c>
       <x:c r="AE19" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -13796,7 +13796,7 @@
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
       </x:c>
       <x:c r="AG19" t="str">
-        <x:v>Not specified in checked abstract/card.</x:v>
+        <x:v>已核验摘要未明确说明；需查阅论文方法与实验章节。</x:v>
       </x:c>
       <x:c r="AH19" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -13889,30 +13889,30 @@
       </x:c>
       <x:c r="BM19"/>
       <x:c r="BN19" t="str">
-        <x:v>Evidence-backed — Real-time execution is essential for cyber-physical systems such as robots.</x:v>
+        <x:v>机器人必须实时响应，但动作块策略可能错过中途变化。</x:v>
       </x:c>
       <x:c r="BO19" t="str">
-        <x:v>Asynchronous inference has recently emerged as a system-level paradigm for real-time robot manipulation, enabling the next action chunk to be predicted while the current one is being executed.</x:v>
+        <x:v>固定动作块执行快，却不容易及时修正已预测动作。</x:v>
       </x:c>
       <x:c r="BP19" t="str">
-        <x:v>To address this, we propose REMAC, which learns corrective adjustments on the pretrained policy through masked action chunking, enabling the policy to remain resilient under mismatches between intended actions and actual execution during asynchronous inference.</x:v>
+        <x:v>REMAC 用 masked action chunking 学习对预训练策略动作的修正。</x:v>
       </x:c>
       <x:c r="BQ19" t="str"/>
       <x:c r="BR19" t="str">
-        <x:v>Extensive experiments in both simulation and real-world settings demonstrate that our method enables faster task execution, maintains robustness across varying delays, and consistently achieves higher completion rates.</x:v>
+        <x:v>作者报告仿真与真机中执行更快，并保持任务表现；具体延迟和成功率需查论文。</x:v>
       </x:c>
       <x:c r="BS19" t="str">
-        <x:v>Provides a concrete method or benchmark for the documented gap: Asynchronous inference has recently emerged as a system-level paradigm for real-time robot manipulation, enabling the next action…</x:v>
+        <x:v>直接对应普通夹爪真机的实时执行与修正。</x:v>
       </x:c>
       <x:c r="BT19" t="str">
-        <x:v>Not established by the checked summary source; consult the full paper.</x:v>
+        <x:v>在线修正是否产生不安全突变需在控制器层验证。</x:v>
       </x:c>
       <x:c r="BU19" t="str"/>
       <x:c r="BV19" t="str">
-        <x:v>Medium — relevant to robot manipulation; transfer to dual-arm real hardware needs validation.</x:v>
+        <x:v>High：可比较动作块长度、控制频率和失败恢复。</x:v>
       </x:c>
       <x:c r="BW19" t="str">
-        <x:v>Official abstract / paper page; https://proceedings.iclr.cc/paper_files/paper/2026/hash/c35834443b7881e782e52b3519fe27c7-Abstract-Conference.html; checked 2026-09-23. Rapid summary only; existing Evidence Quality is unchanged.</x:v>
+        <x:v>官方摘要/论文页; https://proceedings.iclr.cc/paper_files/paper/2026/hash/c35834443b7881e782e52b3519fe27c7-Abstract-Conference.html; 核验于 2026-09-23. 仅为摘要级速读；原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="BX19" t="str">
         <x:v>Unresolved</x:v>
@@ -14003,7 +14003,7 @@
         <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AD20" t="str">
-        <x:v>This paper presents a theoretical analysis of two of the most impactful interventions in modern learning from demonstration in robotics and continuous control: the practice of action-chunking (predicting sequences of actions in open-loop) and exploratory augmentation of expert demonstrations.</x:v>
+        <x:v>模仿学习的单步误差会在长轨迹中不断积累。</x:v>
       </x:c>
       <x:c r="AE20" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -14012,7 +14012,7 @@
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
       </x:c>
       <x:c r="AG20" t="str">
-        <x:v>Not specified in checked abstract/card.</x:v>
+        <x:v>已核验摘要未明确说明；需查阅论文方法与实验章节。</x:v>
       </x:c>
       <x:c r="AH20" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -14105,30 +14105,30 @@
       </x:c>
       <x:c r="BM20"/>
       <x:c r="BN20" t="str">
-        <x:v>Evidence-backed — This paper presents a theoretical analysis of two of the most impactful interventions in modern learning from demonstration in robotics and continuous control: the practice of action-chunking (predicting sequences of actions in open-loop) and exploratory augmentation of expert demonstrations.</x:v>
+        <x:v>模仿学习的单步误差会在长轨迹中不断积累。</x:v>
       </x:c>
       <x:c r="BO20" t="str">
-        <x:v>Not established in checked summary source.</x:v>
+        <x:v>需要解释 Action Chunk 与数据增强为何能改善行为克隆，而不只看经验结果。</x:v>
       </x:c>
       <x:c r="BP20" t="str">
-        <x:v>Though recent results show that learning from demonstration, also known as imitation learning (IL), can suffer errors that compound exponentially with task horizon in continuous settings, we demonstrate that action chunking and exploratory data collection circumvent exponential compounding errors in different regimes.</x:v>
+        <x:v>用控制理论分析动作块和数据增强对误差传播的影响，并给出相应实验。</x:v>
       </x:c>
       <x:c r="BQ20" t="str"/>
       <x:c r="BR20" t="str">
-        <x:v>On the theoretical side, we demonstrate that the control-theoretic lens provides fine-grained insights into how compounding error arises, leading to tighter statistical guarantees on imitation learning error when these interventions are applied than previous…</x:v>
+        <x:v>作者报告理论分析能解释误差积累与这些训练措施的作用；具体界限与实验数字见原文。</x:v>
       </x:c>
       <x:c r="BS20" t="str">
-        <x:v>Medium — relevant to robot manipulation; transfer to dual-arm real hardware needs validation.</x:v>
+        <x:v>为选择动作块长度和数据增强方式提供理论背景。</x:v>
       </x:c>
       <x:c r="BT20" t="str">
-        <x:v>Not established by the checked summary source; consult the full paper.</x:v>
+        <x:v>理论假设与真机接触、感知噪声之间的差距需核对。</x:v>
       </x:c>
       <x:c r="BU20" t="str"/>
       <x:c r="BV20" t="str">
-        <x:v>Medium — relevant to robot manipulation; transfer to dual-arm real hardware needs validation.</x:v>
+        <x:v>High：双臂长任务的误差积累需要明确评测。</x:v>
       </x:c>
       <x:c r="BW20" t="str">
-        <x:v>Official abstract / paper page; https://proceedings.iclr.cc/paper_files/paper/2026/hash/cd96cb9a239c37b39dbf34f3f5a4c56f-Abstract-Conference.html; checked 2026-09-23. Rapid summary only; existing Evidence Quality is unchanged.</x:v>
+        <x:v>官方摘要/论文页; https://proceedings.iclr.cc/paper_files/paper/2026/hash/cd96cb9a239c37b39dbf34f3f5a4c56f-Abstract-Conference.html; 核验于 2026-09-23. 仅为摘要级速读；原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="BX20" t="str">
         <x:v>Unresolved</x:v>
@@ -14221,7 +14221,7 @@
         <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AD21" t="str">
-        <x:v>Long manipulation tasks are difficult for a single low-level policy to learn from sparse data.</x:v>
+        <x:v>长任务的高层指令与短时动作之间容易出现不一致。</x:v>
       </x:c>
       <x:c r="AE21" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -14230,7 +14230,7 @@
         <x:v>以 `Robot Manipulation; Diffusion Policy / Primitive Skills` 为主要方法/能力线索；更细的结构和消融结论待正文核验。</x:v>
       </x:c>
       <x:c r="AG21" t="str">
-        <x:v>Not specified in checked abstract/card.</x:v>
+        <x:v>两项仿真 benchmark 与真机操作评测。</x:v>
       </x:c>
       <x:c r="AH21" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -14323,30 +14323,30 @@
       </x:c>
       <x:c r="BM21"/>
       <x:c r="BN21" t="str">
-        <x:v>Evidence-backed — Long manipulation tasks are difficult for a single low-level policy to learn from sparse data.</x:v>
+        <x:v>长任务的高层指令与短时动作之间容易出现不一致。</x:v>
       </x:c>
       <x:c r="BO21" t="str">
-        <x:v>Not established in checked summary source.</x:v>
+        <x:v>只用全局指令条件化扩散策略，难以保证每段动作符合当前小技能。</x:v>
       </x:c>
       <x:c r="BP21" t="str">
-        <x:v>官方题名与元数据已确认；具体表述待补读官方摘要或正文。</x:v>
+        <x:v>SDP 把复杂任务拆成八种 primitive skills，用 VLM 提取离散状态表示，再由轻量 router 选择技能条件化扩散策略。</x:v>
       </x:c>
       <x:c r="BQ21" t="str"/>
       <x:c r="BR21" t="str">
-        <x:v>Qualitative or numerical result not established by checked source.</x:v>
+        <x:v>AAAI 摘要报告在两项仿真 benchmark 和真机任务中优于所比较方法；未给统一量化值。</x:v>
       </x:c>
       <x:c r="BS21" t="str">
-        <x:v>Medium — relevant to robot manipulation; transfer to dual-arm real hardware needs validation.</x:v>
+        <x:v>可作为“高层技能调度 + 低层动作生成”的双臂基线。</x:v>
       </x:c>
       <x:c r="BT21" t="str">
-        <x:v>Not established by the checked summary source; consult the full paper.</x:v>
+        <x:v>本段基于官方摘要；未覆盖全文失败案例、完整 Baseline 与方法消融。</x:v>
       </x:c>
       <x:c r="BU21" t="str"/>
       <x:c r="BV21" t="str">
-        <x:v>Medium — relevant to robot manipulation; transfer to dual-arm real hardware needs validation.</x:v>
+        <x:v>Medium：方法可借鉴，但迁移到当前双臂硬件需验证。</x:v>
       </x:c>
       <x:c r="BW21" t="str">
-        <x:v>Official abstract / paper page; https://ojs.aaai.org/index.php/AAAI/article/view/38889; checked 2026-09-23. Rapid summary only; existing Evidence Quality is unchanged.</x:v>
+        <x:v>官方摘要/论文页：https://ojs.aaai.org/index.php/AAAI/article/view/38889；核验于 2026-09-23。仅为摘要级速读，原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="BX21" t="str">
         <x:v>Unresolved</x:v>
@@ -14439,7 +14439,7 @@
         <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AD22" t="str">
-        <x:v>Multi-task imitation policies can miss goal context and future task progress.</x:v>
+        <x:v>多任务模仿学习策略需要可靠动作，也需要用少量示范适应未见任务。</x:v>
       </x:c>
       <x:c r="AE22" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -14448,7 +14448,7 @@
         <x:v>以 `Imitation Learning; Multi-Task / Foresight` 为主要方法/能力线索；更细的结构和消融结论待正文核验。</x:v>
       </x:c>
       <x:c r="AG22" t="str">
-        <x:v>Not specified in checked abstract/card.</x:v>
+        <x:v>超过 100 项仿真/真机任务；官方发布的仿真任务套件。</x:v>
       </x:c>
       <x:c r="AH22" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -14541,30 +14541,30 @@
       </x:c>
       <x:c r="BM22"/>
       <x:c r="BN22" t="str">
-        <x:v>Evidence-backed — Multi-task imitation policies can miss goal context and future task progress.</x:v>
+        <x:v>多任务模仿学习策略需要可靠动作，也需要用少量示范适应未见任务。</x:v>
       </x:c>
       <x:c r="BO22" t="str">
-        <x:v>Not established in checked summary source.</x:v>
+        <x:v>只根据当前状态重建动作，可能缺少对动作视觉后果的预测。</x:v>
       </x:c>
       <x:c r="BP22" t="str">
-        <x:v>官方题名与元数据已确认；具体表述待补读官方摘要或正文。</x:v>
+        <x:v>FoAM 输入多模态目标，在动作重建之外加入 foresight augmentation，让策略利用预期视觉结果。</x:v>
       </x:c>
       <x:c r="BQ22" t="str"/>
       <x:c r="BR22" t="str">
-        <x:v>Qualitative or numerical result not established by checked source.</x:v>
+        <x:v>AAAI 摘要报告仿真与真机超过 100 项任务，成功率相对基线最高提升 41%；另发布 80 多项仿真任务。</x:v>
       </x:c>
       <x:c r="BS22" t="str">
-        <x:v>Medium — relevant to robot manipulation; transfer to dual-arm real hardware needs validation.</x:v>
+        <x:v>可比较“预见动作后果”是否帮助双臂动作前验证。</x:v>
       </x:c>
       <x:c r="BT22" t="str">
-        <x:v>Not established by the checked summary source; consult the full paper.</x:v>
+        <x:v>本段基于官方摘要；未覆盖全文失败案例、完整 Baseline 与方法消融。</x:v>
       </x:c>
       <x:c r="BU22" t="str"/>
       <x:c r="BV22" t="str">
-        <x:v>Medium — relevant to robot manipulation; transfer to dual-arm real hardware needs validation.</x:v>
+        <x:v>Medium：方法可借鉴，但迁移到当前双臂硬件需验证。</x:v>
       </x:c>
       <x:c r="BW22" t="str">
-        <x:v>Official abstract / paper page; https://ojs.aaai.org/index.php/AAAI/article/view/38911; checked 2026-09-23. Rapid summary only; existing Evidence Quality is unchanged.</x:v>
+        <x:v>官方摘要/论文页：https://ojs.aaai.org/index.php/AAAI/article/view/38911；核验于 2026-09-23。仅为摘要级速读，原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="BX22" t="str">
         <x:v>Unresolved</x:v>
@@ -14657,7 +14657,7 @@
         <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AD23" t="str">
-        <x:v>Gentle manipulation needs force-aware behavior and compositional task execution.</x:v>
+        <x:v>长时序接触操作既要完成任务，也要避免过大接触力损伤物体。</x:v>
       </x:c>
       <x:c r="AE23" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -14666,7 +14666,7 @@
         <x:v>以 `Robot Manipulation; Long-Hori</x:v>
       </x:c>
       <x:c r="AG23" t="str">
-        <x:v>Not specified in checked abstract/card.</x:v>
+        <x:v>仿真与实体机器人接触操作任务。</x:v>
       </x:c>
       <x:c r="AH23" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -14759,30 +14759,30 @@
       </x:c>
       <x:c r="BM23"/>
       <x:c r="BN23" t="str">
-        <x:v>Evidence-backed — Gentle manipulation needs force-aware behavior and compositional task execution.</x:v>
+        <x:v>长时序接触操作既要完成任务，也要避免过大接触力损伤物体。</x:v>
       </x:c>
       <x:c r="BO23" t="str">
-        <x:v>Not established in checked summary source.</x:v>
+        <x:v>真机专家示范昂贵，分层技能和安全约束难以同时获得。</x:v>
       </x:c>
       <x:c r="BP23" t="str">
-        <x:v>官方题名与元数据已确认；具体表述待补读官方摘要或正文。</x:v>
+        <x:v>在仿真中用带力约束的 RL 训练原子技能，再由 VLM 规划任务，最后蒸馏到视觉—触觉 Diffusion Policy。</x:v>
       </x:c>
       <x:c r="BQ23" t="str"/>
       <x:c r="BR23" t="str">
-        <x:v>Qualitative or numerical result not established by checked source.</x:v>
+        <x:v>AAAI 官方摘要报告仿真与实体机器人验证，并进行了规划器和蒸馏方法消融；未给统一数值。</x:v>
       </x:c>
       <x:c r="BS23" t="str">
-        <x:v>Medium — relevant to robot manipulation; transfer to dual-arm real hardware needs validation.</x:v>
+        <x:v>为普通夹爪的接触安全和低成本技能数据生成提供参考。</x:v>
       </x:c>
       <x:c r="BT23" t="str">
-        <x:v>Not established by the checked summary source; consult the full paper.</x:v>
+        <x:v>本段基于官方摘要；未覆盖全文失败案例、完整 Baseline 与方法消融。</x:v>
       </x:c>
       <x:c r="BU23" t="str"/>
       <x:c r="BV23" t="str">
-        <x:v>Medium — relevant to robot manipulation; transfer to dual-arm real hardware needs validation.</x:v>
+        <x:v>Medium：方法可借鉴，但迁移到当前双臂硬件需验证。</x:v>
       </x:c>
       <x:c r="BW23" t="str">
-        <x:v>Official abstract / paper page; https://ojs.aaai.org/index.php/AAAI/article/view/38955; checked 2026-09-23. Rapid summary only; existing Evidence Quality is unchanged.</x:v>
+        <x:v>官方摘要/论文页：https://ojs.aaai.org/index.php/AAAI/article/view/38955；核验于 2026-09-23。仅为摘要级速读，原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="BX23" t="str">
         <x:v>Unresolved</x:v>
@@ -14875,7 +14875,7 @@
         <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AD24" t="str">
-        <x:v>Generalizable humanoid manipulation needs robust geometric reasoning with limited data.</x:v>
+        <x:v>通用人形机器人操作常依赖大量示范，未见场景中的几何推理仍薄弱。</x:v>
       </x:c>
       <x:c r="AE24" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -14884,7 +14884,7 @@
         <x:v>以 `Robot Manipulation; Humanoid / Generali</x:v>
       </x:c>
       <x:c r="AG24" t="str">
-        <x:v>Not specified in checked abstract/card.</x:v>
+        <x:v>人形机器人与桌面机器人操作评测。</x:v>
       </x:c>
       <x:c r="AH24" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -14977,30 +14977,30 @@
       </x:c>
       <x:c r="BM24"/>
       <x:c r="BN24" t="str">
-        <x:v>Evidence-backed — Generalizable humanoid manipulation needs robust geometric reasoning with limited data.</x:v>
+        <x:v>通用人形机器人操作常依赖大量示范，未见场景中的几何推理仍薄弱。</x:v>
       </x:c>
       <x:c r="BO24" t="str">
-        <x:v>We propose RGMP, combining geometric-prior skill selection and recurrent Gaussian motion generation.</x:v>
+        <x:v>单纯数据驱动策略难以高效建模机器人与目标之间的空间关系。</x:v>
       </x:c>
       <x:c r="BP24" t="str">
-        <x:v>官方题名与元数据已确认；具体表述待补读官方摘要或正文。</x:v>
+        <x:v>RGMP 用带几何先验的技能选择器推理子任务，再用递归 Gaussian 网络生成动作。</x:v>
       </x:c>
       <x:c r="BQ24" t="str"/>
       <x:c r="BR24" t="str">
-        <x:v>The official abstract reports 87 percent generalization success and fivefold data efficiency in its evaluation.</x:v>
+        <x:v>AAAI 官方摘要报告泛化测试成功率 87%，数据效率约为所比较 SOTA 的 5 倍。</x:v>
       </x:c>
       <x:c r="BS24" t="str">
-        <x:v>Provides a concrete method or benchmark for the documented gap: We propose RGMP, combining geometric-prior skill selection and recurrent Gaussian motion generation.</x:v>
+        <x:v>可启发双臂任务的几何关系表示，但硬件差异需要单独验证。</x:v>
       </x:c>
       <x:c r="BT24" t="str">
-        <x:v>Not established by the checked summary source; consult the full paper.</x:v>
+        <x:v>本段基于官方摘要；未覆盖全文失败案例、完整 Baseline 与方法消融。</x:v>
       </x:c>
       <x:c r="BU24" t="str"/>
       <x:c r="BV24" t="str">
-        <x:v>Medium — relevant to robot manipulation; transfer to dual-arm real hardware needs validation.</x:v>
+        <x:v>Medium：方法可借鉴，但迁移到当前双臂硬件需验证。</x:v>
       </x:c>
       <x:c r="BW24" t="str">
-        <x:v>Official abstract / paper page; https://ojs.aaai.org/index.php/AAAI/article/view/38539; checked 2026-09-23. Rapid summary only; existing Evidence Quality is unchanged.</x:v>
+        <x:v>官方摘要/论文页：https://ojs.aaai.org/index.php/AAAI/article/view/38539；核验于 2026-09-23。仅为摘要级速读，原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="BX24" t="str">
         <x:v>Unresolved</x:v>
@@ -15091,7 +15091,7 @@
         <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AD25" t="str">
-        <x:v>Dexterous manipulation across diverse objects is hard because hand dynamics and task-specific rewards do not transfer easily.</x:v>
+        <x:v>多指灵巧手操作不同物体时，任务奖励设计和跨手型泛化都很难。</x:v>
       </x:c>
       <x:c r="AE25" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -15100,7 +15100,7 @@
         <x:v>以 `Dexterous Manipulation; Human Demonstrations / Motion Prior` 为主要方法/能力线索；更细的结构和消融结论待正文核验。</x:v>
       </x:c>
       <x:c r="AG25" t="str">
-        <x:v>Not specified in checked abstract/card.</x:v>
+        <x:v>三类灵巧操作任务；具体数据集见官方论文。</x:v>
       </x:c>
       <x:c r="AH25" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -15193,30 +15193,30 @@
       </x:c>
       <x:c r="BM25"/>
       <x:c r="BN25" t="str">
-        <x:v>Evidence-backed — Dexterous manipulation across diverse objects is hard because hand dynamics and task-specific rewards do not transfer easily.</x:v>
+        <x:v>多指灵巧手操作不同物体时，任务奖励设计和跨手型泛化都很难。</x:v>
       </x:c>
       <x:c r="BO25" t="str">
-        <x:v>Not established in checked summary source.</x:v>
+        <x:v>只模仿人手轨迹，难以把物体未来状态变成通用训练目标。</x:v>
       </x:c>
       <x:c r="BP25" t="str">
-        <x:v>官方题名与元数据已确认；具体表述待补读官方摘要或正文。</x:v>
+        <x:v>从人—物交互数据学习物体运动先验，预测未来物体状态，再把它用于强化学习奖励。</x:v>
       </x:c>
       <x:c r="BQ25" t="str"/>
       <x:c r="BR25" t="str">
-        <x:v>Qualitative or numerical result not established by checked source.</x:v>
+        <x:v>官方 AAAI 摘要报告三类仿真与真机任务上的成功率和新物体泛化优于对比方法，并展示跨机械手部署；摘要未给统一数值。</x:v>
       </x:c>
       <x:c r="BS25" t="str">
-        <x:v>Medium — transferable learning ideas may apply, but the hand hardware differs from ordinary grippers.</x:v>
+        <x:v>提出“预测物体状态作为奖励”的路线，可与普通夹爪任务中的目标状态验证比较。</x:v>
       </x:c>
       <x:c r="BT25" t="str">
-        <x:v>Not established by the checked summary source; consult the full paper.</x:v>
+        <x:v>本段基于官方摘要；未覆盖全文失败案例、完整 Baseline 与方法消融。</x:v>
       </x:c>
       <x:c r="BU25" t="str"/>
       <x:c r="BV25" t="str">
-        <x:v>Medium — transferable learning ideas may apply, but the hand hardware differs from ordinary grippers.</x:v>
+        <x:v>Medium：方法可借鉴，但迁移到当前双臂硬件需验证。</x:v>
       </x:c>
       <x:c r="BW25" t="str">
-        <x:v>Official abstract / paper page; https://ojs.aaai.org/index.php/AAAI/article/view/38892; checked 2026-09-23. Rapid summary only; existing Evidence Quality is unchanged.</x:v>
+        <x:v>官方摘要/论文页：https://ojs.aaai.org/index.php/AAAI/article/view/38892；核验于 2026-09-23。仅为摘要级速读，原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="BX25" t="str">
         <x:v>Unresolved</x:v>
@@ -15309,7 +15309,7 @@
         <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AD26" t="str">
-        <x:v>Data collection in imitation learning often requires significant, laborious human supervision, such as numerous demonstrations, and/or frequent environment resets for methods that incorporate reinforcement learning.</x:v>
+        <x:v>模仿学习的数据采集通常需要多次人工示范和环境复位。</x:v>
       </x:c>
       <x:c r="AE26" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -15318,7 +15318,7 @@
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
       </x:c>
       <x:c r="AG26" t="str">
-        <x:v>Not specified in checked abstract/card.</x:v>
+        <x:v>已核验摘要未明确说明；需查阅论文方法与实验章节。</x:v>
       </x:c>
       <x:c r="AH26" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -15411,30 +15411,30 @@
       </x:c>
       <x:c r="BM26"/>
       <x:c r="BN26" t="str">
-        <x:v>Evidence-backed — Data collection in imitation learning often requires significant, laborious human supervision, such as numerous demonstrations, and/or frequent environment resets for methods that incorporate reinforcement learning.</x:v>
+        <x:v>模仿学习的数据采集通常需要多次人工示范和环境复位。</x:v>
       </x:c>
       <x:c r="BO26" t="str">
-        <x:v>Not established in checked summary source.</x:v>
+        <x:v>昂贵的人工监督限制新任务的快速适配。</x:v>
       </x:c>
       <x:c r="BP26" t="str">
-        <x:v>In this work, we propose an alternative approach, MILES: a fully autonomous, self-supervised data collection paradigm, and we show that this enables efficient policy learning from just a single demonstration and a single environment reset.</x:v>
+        <x:v>MILES 从单条示范出发，以自主自监督方式继续收集训练经验。</x:v>
       </x:c>
       <x:c r="BQ26" t="str"/>
       <x:c r="BR26" t="str">
-        <x:v>We found that, under the constraints of a single demonstration and no repeated environment resetting, MILES significantly outperforms state-of-the-art alternatives like imitation learning methods that leverage reinforcement learning.</x:v>
+        <x:v>作者报告在单示范、无需反复复位的约束下优于对比方法；统一数字需查正文。</x:v>
       </x:c>
       <x:c r="BS26" t="str">
-        <x:v>Medium — relevant to robot manipulation; transfer to dual-arm real hardware needs validation.</x:v>
+        <x:v>可以减少普通夹爪真机的示范采集成本。</x:v>
       </x:c>
       <x:c r="BT26" t="str">
-        <x:v>Not established by the checked summary source; consult the full paper.</x:v>
+        <x:v>自主收集失败轨迹时的安全和错误标签需要严格控制。</x:v>
       </x:c>
       <x:c r="BU26" t="str"/>
       <x:c r="BV26" t="str">
-        <x:v>Medium — relevant to robot manipulation; transfer to dual-arm real hardware needs validation.</x:v>
+        <x:v>High：项目可测自主采集是否安全且节省人力。</x:v>
       </x:c>
       <x:c r="BW26" t="str">
-        <x:v>Official abstract / paper page; https://proceedings.mlr.press/v270/papagiannis25a.html; checked 2026-09-23. Rapid summary only; existing Evidence Quality is unchanged.</x:v>
+        <x:v>官方摘要/论文页; https://proceedings.mlr.press/v270/papagiannis25a.html; 核验于 2026-09-23. 仅为摘要级速读；原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="BX26" t="str">
         <x:v>Unresolved</x:v>
@@ -15527,7 +15527,7 @@
         <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AD27" t="str">
-        <x:v>Learning from expert demonstrations is a popular approach to train robotic manipulation policies from limited data.</x:v>
+        <x:v>少量示范条件下，策略输入和动作生成目标的选择影响操作表现。</x:v>
       </x:c>
       <x:c r="AE27" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -15536,7 +15536,7 @@
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
       </x:c>
       <x:c r="AG27" t="str">
-        <x:v>Not specified in checked abstract/card.</x:v>
+        <x:v>RLBench。</x:v>
       </x:c>
       <x:c r="AH27" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -15629,30 +15629,30 @@
       </x:c>
       <x:c r="BM27"/>
       <x:c r="BN27" t="str">
-        <x:v>Evidence-backed — Learning from expert demonstrations is a popular approach to train robotic manipulation policies from limited data.</x:v>
+        <x:v>少量示范条件下，策略输入和动作生成目标的选择影响操作表现。</x:v>
       </x:c>
       <x:c r="BO27" t="str">
-        <x:v>However, imitation learning algorithms require a number of design choices ranging from the input modality, training objective, and 6-DoF end-effector pose representation.</x:v>
+        <x:v>二维图像可能丢失三维几何；迭代生成动作又增加延迟。</x:v>
       </x:c>
       <x:c r="BP27" t="str">
-        <x:v>However, imitation learning algorithms require a number of design choices ranging from the input modality, training objective, and 6-DoF end-effector pose representation.</x:v>
+        <x:v>PointFlowMatch 从点云观测学习条件 Flow Matching 策略，生成机器人操作动作。</x:v>
       </x:c>
       <x:c r="BQ27" t="str"/>
       <x:c r="BR27" t="str">
-        <x:v>We perform extensive experiments on RLBench which demonstrate that our proposed PointFlowMatch approach achieves a state-of-the-art average success rate of 67.8% over eight tasks, double the performance of the next best method.</x:v>
+        <x:v>作者报告在 RLBench 上达到有竞争力的结果；完整数值需看论文表格。</x:v>
       </x:c>
       <x:c r="BS27" t="str">
-        <x:v>Provides a concrete method or benchmark for the documented gap: However, imitation learning algorithms require a number of design choices ranging from the input modality, training objective…</x:v>
+        <x:v>为点云输入加流式动作生成提供基线。</x:v>
       </x:c>
       <x:c r="BT27" t="str">
-        <x:v>Not established by the checked summary source; consult the full paper.</x:v>
+        <x:v>仿真点云与真机深度噪声之间可能存在差距。</x:v>
       </x:c>
       <x:c r="BU27" t="str"/>
       <x:c r="BV27" t="str">
-        <x:v>Medium — relevant to robot manipulation; transfer to dual-arm real hardware needs validation.</x:v>
+        <x:v>Medium：双夹爪三维定位可借鉴，但真机点云质量需检查。</x:v>
       </x:c>
       <x:c r="BW27" t="str">
-        <x:v>Official abstract / paper page; https://proceedings.mlr.press/v270/chisari25a.html; checked 2026-09-23. Rapid summary only; existing Evidence Quality is unchanged.</x:v>
+        <x:v>官方摘要/论文页; https://proceedings.mlr.press/v270/chisari25a.html; 核验于 2026-09-23. 仅为摘要级速读；原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="BX27" t="str">
         <x:v>Exact work identity verified</x:v>
@@ -15745,7 +15745,7 @@
         <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AD28" t="str">
-        <x:v>Robot learning has proven to be a general and effective technique for programming manipulators.</x:v>
+        <x:v>复杂操作任务需要既能规划步骤，又能执行可靠动作。</x:v>
       </x:c>
       <x:c r="AE28" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -15754,7 +15754,7 @@
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
       </x:c>
       <x:c r="AG28" t="str">
-        <x:v>Not specified in checked abstract/card.</x:v>
+        <x:v>已核验摘要未明确说明；需查阅论文方法与实验章节。</x:v>
       </x:c>
       <x:c r="AH28" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -15847,30 +15847,30 @@
       </x:c>
       <x:c r="BM28"/>
       <x:c r="BN28" t="str">
-        <x:v>Evidence-backed — Robot learning has proven to be a general and effective technique for programming manipulators.</x:v>
+        <x:v>复杂操作任务需要既能规划步骤，又能执行可靠动作。</x:v>
       </x:c>
       <x:c r="BO28" t="str">
-        <x:v>Reinforcement learning uses exploration to discover better behaviors; however, the space of possible improvements can be too large to start from scratch.</x:v>
+        <x:v>只用模仿学习或强化学习，可能难以组织长时序任务。</x:v>
       </x:c>
       <x:c r="BP28" t="str">
-        <x:v>Accounting for this, we propose SPIRE, a system that first uses Task and Motion Planning (TAMP) to decompose tasks into smaller learning subproblems and second combines imitation and reinforcement learning to maximize their strengths.</x:v>
+        <x:v>SPIRE 先用 Task and Motion Planning（TAMP）分解任务，再将学习策略用于具体执行。</x:v>
       </x:c>
       <x:c r="BQ28" t="str"/>
       <x:c r="BR28" t="str">
-        <x:v>We find that SPIRE outperforms prior approaches that integrate imitation learning, reinforcement learning, and planning by 35% to 50% in average task performance, is 6 times more data efficient in the number of human demonstrations needed to train proficient…</x:v>
+        <x:v>作者报告相对其他结合模仿学习、强化学习与规划的方法取得更好表现；数字见原文。</x:v>
       </x:c>
       <x:c r="BS28" t="str">
-        <x:v>Provides a concrete method or benchmark for the documented gap: Reinforcement learning uses exploration to discover better behaviors; however, the space of possible improvements can be too…</x:v>
+        <x:v>提供规划与学习策略组合的系统基线。</x:v>
       </x:c>
       <x:c r="BT28" t="str">
-        <x:v>Not established by the checked summary source; consult the full paper.</x:v>
+        <x:v>规划模型与真实接触差异可能造成执行偏差。</x:v>
       </x:c>
       <x:c r="BU28" t="str"/>
       <x:c r="BV28" t="str">
-        <x:v>Medium — relevant to robot manipulation; transfer to dual-arm real hardware needs validation.</x:v>
+        <x:v>High：双臂长任务可测试分解与执行后检查。</x:v>
       </x:c>
       <x:c r="BW28" t="str">
-        <x:v>OpenAlex indexed abstract; https://api.openalex.org/works/W4404308601; checked 2026-09-23. Rapid summary only; existing Evidence Quality is unchanged.</x:v>
+        <x:v>OpenAlex 索引摘要; https://api.openalex.org/works/W4404308601; 核验于 2026-09-23. 仅为摘要级速读；原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="BX28" t="str">
         <x:v>Exact work identity verified</x:v>
@@ -15963,7 +15963,7 @@
         <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AD29" t="str">
-        <x:v>Open-sourced, user-friendly tools form the bedrock of scientific advancement across disciplines.</x:v>
+        <x:v>开放、易用的遥操作工具是低成本收集机器人示范的基础。</x:v>
       </x:c>
       <x:c r="AE29" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -15972,7 +15972,7 @@
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
       </x:c>
       <x:c r="AG29" t="str">
-        <x:v>Not specified in checked abstract/card.</x:v>
+        <x:v>已核验摘要未明确说明；需查阅论文方法与实验章节。</x:v>
       </x:c>
       <x:c r="AH29" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -16065,30 +16065,30 @@
       </x:c>
       <x:c r="BM29"/>
       <x:c r="BN29" t="str">
-        <x:v>Evidence-backed — Open-sourced, user-friendly tools form the bedrock of scientific advancement across disciplines.</x:v>
+        <x:v>开放、易用的遥操作工具是低成本收集机器人示范的基础。</x:v>
       </x:c>
       <x:c r="BO29" t="str">
-        <x:v>However, existing data collection platforms are often proprietary, costly, or tailored to specific robotic morphologies.</x:v>
+        <x:v>复杂专有系统阻碍示范采集的复现和共享。</x:v>
       </x:c>
       <x:c r="BP29" t="str">
-        <x:v>We present OPEN TEACH, a new teleoperation system leveraging VR headsets to immerse users in mixed reality for intuitive robot control. built on the affordable Meta Quest 3, which costs $500, OPEN TEACH enables real-time control of various robots, including multi-fingered hands, bimanual arms, and mobile manipulators, through an easy-to-use app.</x:v>
+        <x:v>OPEN TEACH 用 VR 头显与混合现实界面进行直观机器人遥操作。</x:v>
       </x:c>
       <x:c r="BQ29" t="str"/>
       <x:c r="BR29" t="str">
-        <x:v>Qualitative or numerical result not established by checked source.</x:v>
+        <x:v>已核验摘要未给可安全复述的统一量化结果。</x:v>
       </x:c>
       <x:c r="BS29" t="str">
-        <x:v>Provides a concrete method or benchmark for the documented gap: However, existing data collection platforms are often proprietary, costly, or tailored to specific robotic morphologies.</x:v>
+        <x:v>为建立本项目示范采集流程提供开源系统参考。</x:v>
       </x:c>
       <x:c r="BT29" t="str">
-        <x:v>Not established by the checked summary source; consult the full paper.</x:v>
+        <x:v>VR 延迟、标定和安全机制需按目标硬件核验。</x:v>
       </x:c>
       <x:c r="BU29" t="str"/>
       <x:c r="BV29" t="str">
-        <x:v>Medium — useful for method selection, data design and evaluation.</x:v>
+        <x:v>High：可比较普通夹爪双臂遥操作的学习成本。</x:v>
       </x:c>
       <x:c r="BW29" t="str">
-        <x:v>Official abstract / paper page; https://proceedings.mlr.press/v270/iyer25a.html; checked 2026-09-23. Rapid summary only; existing Evidence Quality is unchanged.</x:v>
+        <x:v>官方摘要/论文页; https://proceedings.mlr.press/v270/iyer25a.html; 核验于 2026-09-23. 仅为摘要级速读；原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="BX29" t="str">
         <x:v>Exact work identity verified</x:v>
@@ -16181,7 +16181,7 @@
         <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AD30" t="str">
-        <x:v>This work proposes a retrieve-and-transfer framework for zero-shot robotic manipulation, dubbed RAM, featuring generalizability across various objects, environments, and embodiments.</x:v>
+        <x:v>新任务缺少目标域示范时，机器人如何零样本操作。</x:v>
       </x:c>
       <x:c r="AE30" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -16190,7 +16190,7 @@
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
       </x:c>
       <x:c r="AG30" t="str">
-        <x:v>Not specified in checked abstract/card.</x:v>
+        <x:v>已核验摘要未明确说明；需查阅论文方法与实验章节。</x:v>
       </x:c>
       <x:c r="AH30" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -16283,30 +16283,30 @@
       </x:c>
       <x:c r="BM30"/>
       <x:c r="BN30" t="str">
-        <x:v>Evidence-backed — This work proposes a retrieve-and-transfer framework for zero-shot robotic manipulation, dubbed RAM, featuring generalizability across various objects, environments, and embodiments.</x:v>
+        <x:v>新任务缺少目标域示范时，机器人如何零样本操作。</x:v>
       </x:c>
       <x:c r="BO30" t="str">
-        <x:v>Not established in checked summary source.</x:v>
+        <x:v>为每项任务单独收集示范的成本太高。</x:v>
       </x:c>
       <x:c r="BP30" t="str">
-        <x:v>Unlike existing approaches that learn manipulation from expensive in-domain demonstrations, RAM capitalizes on a retrieval-based affordance transfer paradigm to acquire versatile manipulation capabilities from abundant out-of-domain data.</x:v>
+        <x:v>RAM 检索相关已有行为，再把它迁移到当前物体和操作设置。</x:v>
       </x:c>
       <x:c r="BQ30" t="str"/>
       <x:c r="BR30" t="str">
-        <x:v>Extensive simulation and real-world evaluations demonstrate that our RAM consistently outperforms existing works in diverse daily tasks.</x:v>
+        <x:v>作者报告仿真与真机评测中优于所比较方法；具体数字需查正文。</x:v>
       </x:c>
       <x:c r="BS30" t="str">
-        <x:v>Medium — relevant to robot manipulation; transfer to dual-arm real hardware needs validation.</x:v>
+        <x:v>展示通过检索复用经验而非每次重训的路径。</x:v>
       </x:c>
       <x:c r="BT30" t="str">
-        <x:v>Not established by the checked summary source; consult the full paper.</x:v>
+        <x:v>检索到的动作若与当前夹爪或物体不匹配，可能无法执行。</x:v>
       </x:c>
       <x:c r="BU30" t="str"/>
       <x:c r="BV30" t="str">
-        <x:v>Medium — relevant to robot manipulation; transfer to dual-arm real hardware needs validation.</x:v>
+        <x:v>Medium：可用于双臂任务的技能复用，但动作适配需验证。</x:v>
       </x:c>
       <x:c r="BW30" t="str">
-        <x:v>OpenAlex indexed abstract; https://api.openalex.org/works/W4400435236; checked 2026-09-23. Rapid summary only; existing Evidence Quality is unchanged.</x:v>
+        <x:v>OpenAlex 索引摘要; https://api.openalex.org/works/W4400435236; 核验于 2026-09-23. 仅为摘要级速读；原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="BX30" t="str">
         <x:v>Exact work identity verified</x:v>
@@ -16399,7 +16399,7 @@
         <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AD31" t="str">
-        <x:v>Audio signals provide rich information for the robot interaction and object properties through contact.</x:v>
+        <x:v>接触声音包含物体和交互信息，但普通示范数据很少记录音频。</x:v>
       </x:c>
       <x:c r="AE31" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -16408,7 +16408,7 @@
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
       </x:c>
       <x:c r="AG31" t="str">
-        <x:v>Not specified in checked abstract/card.</x:v>
+        <x:v>已核验摘要未明确说明；需查阅论文方法与实验章节。</x:v>
       </x:c>
       <x:c r="AH31" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -16501,30 +16501,30 @@
       </x:c>
       <x:c r="BM31"/>
       <x:c r="BN31" t="str">
-        <x:v>Evidence-backed — Audio signals provide rich information for the robot interaction and object properties through contact.</x:v>
+        <x:v>接触声音包含物体和交互信息，但普通示范数据很少记录音频。</x:v>
       </x:c>
       <x:c r="BO31" t="str">
-        <x:v>However, the usage of audio data in robot manipulation has been constrained to teleoperated demonstrations collected by either attaching a microphone to the robot or object, which significantly limits its usage in robot learning pipelines.</x:v>
+        <x:v>只用视觉可能难判断接触是否成功或物体是否滑动。</x:v>
       </x:c>
       <x:c r="BP31" t="str">
-        <x:v>In this work, we introduce ManiWAV: an 'ear-in-hand' data collection device to collect in-the-wild human demonstrations with synchronous audio and visual feedback, and a corresponding policy interface to learn robot manipulation policy directly from the demonstrations.</x:v>
+        <x:v>ManiWAV 用 ear-in-hand 装置采集带同步音频的人类野外示范。</x:v>
       </x:c>
       <x:c r="BQ31" t="str"/>
       <x:c r="BR31" t="str">
-        <x:v>In addition, we show that our system can generalize to unseen in-the-wild environments by learning from diverse in-the-wild human demonstrations.</x:v>
+        <x:v>作者报告利用多样野外示范可迁移到未见环境；具体数字需查论文。</x:v>
       </x:c>
       <x:c r="BS31" t="str">
-        <x:v>Provides a concrete method or benchmark for the documented gap: However, the usage of audio data in robot manipulation has been constrained to teleoperated demonstrations collected by either…</x:v>
+        <x:v>声音可成为普通夹爪动作后成功验证的补充信号。</x:v>
       </x:c>
       <x:c r="BT31" t="str">
-        <x:v>Not established by the checked summary source; consult the full paper.</x:v>
+        <x:v>人类示范音频与机器人电机噪声分布不同。</x:v>
       </x:c>
       <x:c r="BU31" t="str"/>
       <x:c r="BV31" t="str">
-        <x:v>Medium — useful for method selection, data design and evaluation.</x:v>
+        <x:v>Medium：取决于本项目是否能低成本采集同步音频。</x:v>
       </x:c>
       <x:c r="BW31" t="str">
-        <x:v>OpenAlex indexed abstract; https://api.openalex.org/works/W4400222297; checked 2026-09-23. Rapid summary only; existing Evidence Quality is unchanged.</x:v>
+        <x:v>OpenAlex 索引摘要; https://api.openalex.org/works/W4400222297; 核验于 2026-09-23. 仅为摘要级速读；原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="BX31" t="str">
         <x:v>Exact work identity verified</x:v>
@@ -16617,7 +16617,7 @@
         <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AD32" t="str">
-        <x:v>A key challenge in manipulation is learning a policy that can robustly generalize to diverse visual environments.</x:v>
+        <x:v>机器人模仿学习策略在新视觉环境中往往难以保持稳定表现。</x:v>
       </x:c>
       <x:c r="AE32" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -16626,7 +16626,7 @@
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
       </x:c>
       <x:c r="AG32" t="str">
-        <x:v>Not specified in checked abstract/card.</x:v>
+        <x:v>论文评估四项复杂度递增的操作任务；具体任务设置见 CoRL 论文。</x:v>
       </x:c>
       <x:c r="AH32" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -16719,30 +16719,30 @@
       </x:c>
       <x:c r="BM32"/>
       <x:c r="BN32" t="str">
-        <x:v>Evidence-backed — A key challenge in manipulation is learning a policy that can robustly generalize to diverse visual environments.</x:v>
+        <x:v>机器人模仿学习策略在新视觉环境中往往难以保持稳定表现。</x:v>
       </x:c>
       <x:c r="BO32" t="str">
-        <x:v>Not established in checked summary source.</x:v>
+        <x:v>少量机器人示范不足以覆盖环境外观变化；直接行为克隆的泛化有限。</x:v>
       </x:c>
       <x:c r="BP32" t="str">
-        <x:v>In this paper, we propose a visuomotor policy learning framework that fine-tunes a video diffusion model on human demonstrations of a given task.</x:v>
+        <x:v>Dreamitate 用人类任务示范微调视频扩散模型，再利用生成的视频辅助学习视觉运动策略。</x:v>
       </x:c>
       <x:c r="BQ32" t="str"/>
       <x:c r="BR32" t="str">
-        <x:v>We evaluate our approach on four tasks of increasing complexity and demonstrate that harnessing internet-scale generative models allows the learned policy to achieve a significantly higher degree of generalization than existing behavior cloning approaches.</x:v>
+        <x:v>官方摘要报告比现有行为克隆方法具有更强的视觉环境泛化；摘要未给出统一成功率数字。</x:v>
       </x:c>
       <x:c r="BS32" t="str">
-        <x:v>High — informs language-conditioned manipulation and VLA design.</x:v>
+        <x:v>探索大规模视频生成模型如何补充少量机器人示范。</x:v>
       </x:c>
       <x:c r="BT32" t="str">
-        <x:v>Not established by the checked summary source; consult the full paper.</x:v>
+        <x:v>已核验摘要未明确列出全部失败情形；需读实验和局限章节。</x:v>
       </x:c>
       <x:c r="BU32" t="str"/>
       <x:c r="BV32" t="str">
-        <x:v>High — informs language-conditioned manipulation and VLA design.</x:v>
+        <x:v>Medium：可借鉴视频到动作的数据利用方式，但双臂普通夹爪需单独验证。</x:v>
       </x:c>
       <x:c r="BW32" t="str">
-        <x:v>Official abstract / paper page; https://arxiv.org/html/2406.16862; checked 2026-09-23. Rapid summary only; existing Evidence Quality is unchanged.</x:v>
+        <x:v>官方摘要/论文页; https://arxiv.org/html/2406.16862; 核验于 2026-09-23. 仅为摘要级速读；原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="BX32" t="str">
         <x:v>Exact work identity verified</x:v>
@@ -16835,7 +16835,7 @@
         <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AD33" t="str">
-        <x:v>Recent work has shown diffusion models are an effective approach to learning the multimodal distributions arising from demonstration data in behavior cloning.</x:v>
+        <x:v>扩散策略善于表达多种动作，但少量数据下泛化仍有挑战。</x:v>
       </x:c>
       <x:c r="AE33" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -16844,7 +16844,7 @@
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
       </x:c>
       <x:c r="AG33" t="str">
-        <x:v>Not specified in checked abstract/card.</x:v>
+        <x:v>已核验摘要未明确说明；需查阅论文方法与实验章节。</x:v>
       </x:c>
       <x:c r="AH33" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -16937,30 +16937,30 @@
       </x:c>
       <x:c r="BM33"/>
       <x:c r="BN33" t="str">
-        <x:v>Evidence-backed — Recent work has shown diffusion models are an effective approach to learning the multimodal distributions arising from demonstration data in behavior cloning.</x:v>
+        <x:v>扩散策略善于表达多种动作，但少量数据下泛化仍有挑战。</x:v>
       </x:c>
       <x:c r="BO33" t="str">
-        <x:v>However, a drawback of this approach is the need to learn a denoising function, which is significantly more complex than learning an explicit policy.</x:v>
+        <x:v>不利用任务的几何对称性会增加学习样本需求。</x:v>
       </x:c>
       <x:c r="BP33" t="str">
-        <x:v>In this work, we propose Equivariant Diffusion Policy, a novel diffusion policy learning method that leverages domain symmetries to obtain better sample efficiency and generalization in the denoising function.</x:v>
+        <x:v>Equivariant Diffusion Policy 把空间对称性引入扩散式动作策略。</x:v>
       </x:c>
       <x:c r="BQ33" t="str"/>
       <x:c r="BR33" t="str">
-        <x:v>We also evaluate the method on a real-world system to show that effective policies can be learned with relatively few training samples, whereas the baseline Diffusion Policy cannot.</x:v>
+        <x:v>作者报告在真机系统上可用较少示范学到有效策略；具体数值见原文。</x:v>
       </x:c>
       <x:c r="BS33" t="str">
-        <x:v>Provides a concrete method or benchmark for the documented gap: However, a drawback of this approach is the need to learn a denoising function, which is significantly more complex than learning…</x:v>
+        <x:v>将几何先验与生成式动作结合。</x:v>
       </x:c>
       <x:c r="BT33" t="str">
-        <x:v>Not established by the checked summary source; consult the full paper.</x:v>
+        <x:v>需要核验所假设的对称性在复杂接触和双臂协作中是否成立。</x:v>
       </x:c>
       <x:c r="BU33" t="str"/>
       <x:c r="BV33" t="str">
-        <x:v>Medium — relevant to robot manipulation; transfer to dual-arm real hardware needs validation.</x:v>
+        <x:v>Medium：可用于双夹爪空间变化实验。</x:v>
       </x:c>
       <x:c r="BW33" t="str">
-        <x:v>Official abstract / paper page; https://proceedings.mlr.press/v270/wang25a.html; checked 2026-09-23. Rapid summary only; existing Evidence Quality is unchanged.</x:v>
+        <x:v>官方摘要/论文页; https://proceedings.mlr.press/v270/wang25a.html; 核验于 2026-09-23. 仅为摘要级速读；原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="BX33" t="str">
         <x:v>Unresolved</x:v>
@@ -17053,7 +17053,7 @@
         <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AD34" t="str">
-        <x:v>Building effective imitation learning methods that enable robots to learn from limited data and still generalize across diverse real-world environments is a long-standing problem in robot learning.</x:v>
+        <x:v>少量示范条件下，操作策略要面对物体和空间变化。</x:v>
       </x:c>
       <x:c r="AE34" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -17062,7 +17062,7 @@
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
       </x:c>
       <x:c r="AG34" t="str">
-        <x:v>Not specified in checked abstract/card.</x:v>
+        <x:v>已核验摘要未明确说明；需查阅论文方法与实验章节。</x:v>
       </x:c>
       <x:c r="AH34" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -17155,30 +17155,30 @@
       </x:c>
       <x:c r="BM34"/>
       <x:c r="BN34" t="str">
-        <x:v>Evidence-backed — Building effective imitation learning methods that enable robots to learn from limited data and still generalize across diverse real-world environments is a long-standing problem in robot learning.</x:v>
+        <x:v>少量示范条件下，操作策略要面对物体和空间变化。</x:v>
       </x:c>
       <x:c r="BO34" t="str">
-        <x:v>This ensures that our learned policies are invariant to changes in scale, rotation, and translation, enhancing their applicability to unseen environments while retaining the benefits of diffusion-based policy learning such as multi-modality and robustness.</x:v>
+        <x:v>普通网络不一定充分利用旋转、平移等几何对称性。</x:v>
       </x:c>
       <x:c r="BP34" t="str">
-        <x:v>We propose EquiBot, a robust, data-efficient, and generalizable approach for robot manipulation task learning.</x:v>
+        <x:v>EquiBot 在模仿学习策略中加入等变结构，提高数据效率和空间泛化。</x:v>
       </x:c>
       <x:c r="BQ34" t="str"/>
       <x:c r="BR34" t="str">
-        <x:v>In the real world, with 10 variations of 6 mobile manipulation tasks, we show that our method can easily generalize to novel objects and scenes after learning from just 5 minutes of human demonstrations in each task.</x:v>
+        <x:v>作者报告在六项移动操作任务的多个真机变化中展示泛化；具体数值见论文。</x:v>
       </x:c>
       <x:c r="BS34" t="str">
-        <x:v>Provides a concrete method or benchmark for the documented gap: This ensures that our learned policies are invariant to changes in scale, rotation, and translation, enhancing their…</x:v>
+        <x:v>提供以结构先验替代部分示范数据的路线。</x:v>
       </x:c>
       <x:c r="BT34" t="str">
-        <x:v>Not established by the checked summary source; consult the full paper.</x:v>
+        <x:v>移动操作结果不能直接替代普通夹爪双臂评测。</x:v>
       </x:c>
       <x:c r="BU34" t="str"/>
       <x:c r="BV34" t="str">
-        <x:v>Medium — relevant to robot manipulation; transfer to dual-arm real hardware needs validation.</x:v>
+        <x:v>Medium：双臂空间变化可能受益，但平台不同。</x:v>
       </x:c>
       <x:c r="BW34" t="str">
-        <x:v>Official abstract / paper page; https://proceedings.mlr.press/v270/yang25a.html; checked 2026-09-23. Rapid summary only; existing Evidence Quality is unchanged.</x:v>
+        <x:v>官方摘要/论文页; https://proceedings.mlr.press/v270/yang25a.html; 核验于 2026-09-23. 仅为摘要级速读；原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="BX34" t="str">
         <x:v>Exact work identity verified</x:v>
@@ -17271,7 +17271,7 @@
         <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AD35" t="str">
-        <x:v>Diffusion policies are conditional diffusion models that learn robot action distributions conditioned on the robot and environment state.</x:v>
+        <x:v>机器人动作有多种合理解，二维图像策略对三维几何理解不足。</x:v>
       </x:c>
       <x:c r="AE35" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -17280,7 +17280,7 @@
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
       </x:c>
       <x:c r="AG35" t="str">
-        <x:v>Not specified in checked abstract/card.</x:v>
+        <x:v>已核验摘要未明确说明；需查阅论文方法与实验章节。</x:v>
       </x:c>
       <x:c r="AH35" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -17373,30 +17373,30 @@
       </x:c>
       <x:c r="BM35"/>
       <x:c r="BN35" t="str">
-        <x:v>Evidence-backed — Diffusion policies are conditional diffusion models that learn robot action distributions conditioned on the robot and environment state.</x:v>
+        <x:v>机器人动作有多种合理解，二维图像策略对三维几何理解不足。</x:v>
       </x:c>
       <x:c r="BO35" t="str">
-        <x:v>Not established in checked summary source.</x:v>
+        <x:v>直接回归动作或只用二维表示，可能难以表达多模态三维操作。</x:v>
       </x:c>
       <x:c r="BP35" t="str">
-        <x:v>Through thorough comparisons with the current SOTA policies and ablations of our model, we show 3D Diffuser Actor ’s design choices dramatically outperform 2D representations, regression and classification objectives, absolute attentions, and holistic non-tokenized 3D scene embeddings.</x:v>
+        <x:v>3D Diffuser Actor 在三维场景表示上生成动作，并通过扩散模型刻画多种可行轨迹。</x:v>
       </x:c>
       <x:c r="BQ35" t="str"/>
       <x:c r="BR35" t="str">
-        <x:v>They have recently shown to outperform both deterministic and alternative action distribution learning formulations. 3D robot policies use 3D scene feature representations aggregated from a single or multiple camera views using sensed depth.</x:v>
+        <x:v>论文报告与二维表示、回归及其他设计的消融比较，完整数字应以原论文表格为准。</x:v>
       </x:c>
       <x:c r="BS35" t="str">
-        <x:v>Medium — relevant to robot manipulation; transfer to dual-arm real hardware needs validation.</x:v>
+        <x:v>是比较三维感知与生成式动作的基础方法。</x:v>
       </x:c>
       <x:c r="BT35" t="str">
-        <x:v>Not established by the checked summary source; consult the full paper.</x:v>
+        <x:v>摘要不足以判断不同真机接触和双臂协调任务的完整覆盖。</x:v>
       </x:c>
       <x:c r="BU35" t="str"/>
       <x:c r="BV35" t="str">
-        <x:v>Medium — relevant to robot manipulation; transfer to dual-arm real hardware needs validation.</x:v>
+        <x:v>High：可为双普通夹爪的三维目标位姿生成提供基线。</x:v>
       </x:c>
       <x:c r="BW35" t="str">
-        <x:v>Official abstract / paper page; https://proceedings.mlr.press/v270/ke25a.html; checked 2026-09-23. Rapid summary only; existing Evidence Quality is unchanged.</x:v>
+        <x:v>官方摘要/论文页; https://proceedings.mlr.press/v270/ke25a.html; 核验于 2026-09-23. 仅为摘要级速读；原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="BX35" t="str">
         <x:v>Exact work identity verified</x:v>
@@ -17489,7 +17489,7 @@
         <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AD36" t="str">
-        <x:v>We introduce BiGym, a new benchmark and learning environment for mobile bi-manual demo-driven robotic manipulation.</x:v>
+        <x:v>缺少覆盖家庭场景移动双臂操作的示范驱动学习基准。</x:v>
       </x:c>
       <x:c r="AE36" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -17498,7 +17498,7 @@
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
       </x:c>
       <x:c r="AG36" t="str">
-        <x:v>Not specified in checked abstract/card.</x:v>
+        <x:v>BiGym：40 项家庭环境任务；示范规模与具体划分需查正文。</x:v>
       </x:c>
       <x:c r="AH36" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -17591,30 +17591,30 @@
       </x:c>
       <x:c r="BM36"/>
       <x:c r="BN36" t="str">
-        <x:v>Evidence-backed — We introduce BiGym, a new benchmark and learning environment for mobile bi-manual demo-driven robotic manipulation.</x:v>
+        <x:v>缺少覆盖家庭场景移动双臂操作的示范驱动学习基准。</x:v>
       </x:c>
       <x:c r="BO36" t="str">
-        <x:v>Not established in checked summary source.</x:v>
+        <x:v>已核验摘要未明确说明；需查阅论文方法与实验章节。</x:v>
       </x:c>
       <x:c r="BP36" t="str">
-        <x:v>BiGym features 40 diverse tasks set in home environments, ranging from simple target reaching to complex kitchen cleaning.</x:v>
+        <x:v>BiGym 提供移动双臂学习环境，包含从目标触达到厨房清理的 40 项任务。</x:v>
       </x:c>
       <x:c r="BQ36" t="str"/>
       <x:c r="BR36" t="str">
-        <x:v>Qualitative or numerical result not established by checked source.</x:v>
+        <x:v>摘要支持 40 项任务这一规模；具体算法胜率需查实验表格。</x:v>
       </x:c>
       <x:c r="BS36" t="str">
-        <x:v>High — directly informs dual-arm coordination, data or ordinary-gripper policy design.</x:v>
+        <x:v>将双臂协作、移动性和家庭长程任务放在同一评测入口。</x:v>
       </x:c>
       <x:c r="BT36" t="str">
-        <x:v>Not established by the checked summary source; consult the full paper.</x:v>
+        <x:v>是否能迁移至本项目固定平台与硬件配置，摘要不能确定。</x:v>
       </x:c>
       <x:c r="BU36" t="str"/>
       <x:c r="BV36" t="str">
-        <x:v>High — directly informs dual-arm coordination, data or ordinary-gripper policy design.</x:v>
+        <x:v>High：适合筛选普通夹爪双臂任务及示范学习基线。</x:v>
       </x:c>
       <x:c r="BW36" t="str">
-        <x:v>Official abstract / paper page; https://proceedings.mlr.press/v270/chernyadev25a.html; checked 2026-09-23. Rapid summary only; existing Evidence Quality is unchanged.</x:v>
+        <x:v>官方摘要/论文页; https://proceedings.mlr.press/v270/chernyadev25a.html; 核验于 2026-09-23. 仅为摘要级速读；原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="BX36" t="str">
         <x:v>Exact work identity verified</x:v>
@@ -17707,7 +17707,7 @@
         <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AD37" t="str">
-        <x:v>Bimanual manipulation is critical to many robotics applications.</x:v>
+        <x:v>细粒度双臂操作需要在三维场景中同时定位两只手的关键区域。</x:v>
       </x:c>
       <x:c r="AE37" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -17716,7 +17716,7 @@
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
       </x:c>
       <x:c r="AG37" t="str">
-        <x:v>Not specified in checked abstract/card.</x:v>
+        <x:v>仿真细粒度双臂任务；真机覆盖需进一步核验。</x:v>
       </x:c>
       <x:c r="AH37" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -17809,30 +17809,30 @@
       </x:c>
       <x:c r="BM37"/>
       <x:c r="BN37" t="str">
-        <x:v>Evidence-backed — Bimanual manipulation is critical to many robotics applications.</x:v>
+        <x:v>细粒度双臂操作需要在三维场景中同时定位两只手的关键区域。</x:v>
       </x:c>
       <x:c r="BO37" t="str">
-        <x:v>Prior works leverage large amounts of data and primitive actions to address this problem, but may suffer from sample inefficiency and limited generalization across various tasks.</x:v>
+        <x:v>直接从全局图像预测高维双臂动作，可能忽略局部空间线索。</x:v>
       </x:c>
       <x:c r="BP37" t="str">
-        <x:v>To this end, we propose VoxAct-B, a language-conditioned, voxel-based method that leverages Vision Language Models (VLMs) to prioritize key regions within the scene and reconstruct a voxel grid.</x:v>
+        <x:v>VoxAct-B 用 VLM 关注关键区域，再在体素空间中生成语言条件的双臂动作。</x:v>
       </x:c>
       <x:c r="BQ37" t="str"/>
       <x:c r="BR37" t="str">
-        <x:v>In simulation, we show that VoxAct-B outperforms strong baselines on fine-grained bimanual manipulation tasks.</x:v>
+        <x:v>作者报告在仿真任务上优于所比较基线；摘要未给统一量化值。</x:v>
       </x:c>
       <x:c r="BS37" t="str">
-        <x:v>Provides a concrete method or benchmark for the documented gap: Prior works leverage large amounts of data and primitive actions to address this problem, but may suffer from sample inefficiency…</x:v>
+        <x:v>把视觉目标定位与双臂三维动作表示连接起来。</x:v>
       </x:c>
       <x:c r="BT37" t="str">
-        <x:v>Not established by the checked summary source; consult the full paper.</x:v>
+        <x:v>体素分辨率与真机延迟、遮挡和接触误差需验证。</x:v>
       </x:c>
       <x:c r="BU37" t="str"/>
       <x:c r="BV37" t="str">
-        <x:v>High — directly informs dual-arm coordination, data or ordinary-gripper policy design.</x:v>
+        <x:v>High：可参考两只普通夹爪的空间目标表示。</x:v>
       </x:c>
       <x:c r="BW37" t="str">
-        <x:v>Official abstract / paper page; https://proceedings.mlr.press/v270/liu25i.html; checked 2026-09-23. Rapid summary only; existing Evidence Quality is unchanged.</x:v>
+        <x:v>官方摘要/论文页; https://proceedings.mlr.press/v270/liu25i.html; 核验于 2026-09-23. 仅为摘要级速读；原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="BX37" t="str">
         <x:v>Exact work identity verified</x:v>
@@ -17925,7 +17925,7 @@
         <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AD38" t="str">
-        <x:v>Imitation learning from human demonstrations has shown impressive performance in robotics.</x:v>
+        <x:v>双臂移动操作要求机器人在移动底座上同时协调两只机械臂。</x:v>
       </x:c>
       <x:c r="AE38" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -17934,7 +17934,7 @@
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
       </x:c>
       <x:c r="AG38" t="str">
-        <x:v>Not specified in checked abstract/card.</x:v>
+        <x:v>Mobile ALOHA 平台上的移动双臂操作示范。</x:v>
       </x:c>
       <x:c r="AH38" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -18027,30 +18027,30 @@
       </x:c>
       <x:c r="BM38"/>
       <x:c r="BN38" t="str">
-        <x:v>Evidence-backed — Imitation learning from human demonstrations has shown impressive performance in robotics.</x:v>
+        <x:v>双臂移动操作要求机器人在移动底座上同时协调两只机械臂。</x:v>
       </x:c>
       <x:c r="BO38" t="str">
-        <x:v>However, most results focus on table-top manipulation, lacking the mobility and dexterity necessary for generally useful tasks.</x:v>
+        <x:v>传统固定底座示范不能直接覆盖全身移动与操作的耦合。</x:v>
       </x:c>
       <x:c r="BP38" t="str">
-        <x:v>In this work, we develop a system for imitating mobile manipulation tasks that are bimanual and require whole-body control.</x:v>
+        <x:v>Mobile ALOHA 建立双臂移动操作系统，并采集示范训练端到端模仿策略。</x:v>
       </x:c>
       <x:c r="BQ38" t="str"/>
       <x:c r="BR38" t="str">
-        <x:v>Qualitative or numerical result not established by checked source.</x:v>
+        <x:v>已核验摘要未给可安全复述的统一量化结果；具体任务表现见论文评测。</x:v>
       </x:c>
       <x:c r="BS38" t="str">
-        <x:v>Provides a concrete method or benchmark for the documented gap: However, most results focus on table-top manipulation, lacking the mobility and dexterity necessary for generally useful tasks.</x:v>
+        <x:v>提供移动双臂真机系统和示范采集的完整参照。</x:v>
       </x:c>
       <x:c r="BT38" t="str">
-        <x:v>Not established by the checked summary source; consult the full paper.</x:v>
+        <x:v>移动和操作同时变化，难单独归因哪一环节带来失败。</x:v>
       </x:c>
       <x:c r="BU38" t="str"/>
       <x:c r="BV38" t="str">
-        <x:v>High — directly informs dual-arm coordination, data or ordinary-gripper policy design.</x:v>
+        <x:v>High：双臂与普通夹爪相关；移动底座部分需与本项目区分。</x:v>
       </x:c>
       <x:c r="BW38" t="str">
-        <x:v>Official abstract / paper page; https://proceedings.mlr.press/v270/fu25b.html; checked 2026-09-23. Rapid summary only; existing Evidence Quality is unchanged.</x:v>
+        <x:v>官方摘要/论文页; https://proceedings.mlr.press/v270/fu25b.html; 核验于 2026-09-23. 仅为摘要级速读；原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="BX38" t="str">
         <x:v>Unresolved</x:v>
@@ -18143,7 +18143,7 @@
         <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AD39" t="str">
-        <x:v>Recent work has shown promising results for learning end-to-end robot policies using imitation learning.</x:v>
+        <x:v>复杂灵巧操作需要足够多的真机示范和能表达多种动作的策略。</x:v>
       </x:c>
       <x:c r="AE39" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -18152,7 +18152,7 @@
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
       </x:c>
       <x:c r="AG39" t="str">
-        <x:v>Not specified in checked abstract/card.</x:v>
+        <x:v>ALOHA 2 真机示范和论文列出的复杂操作任务。</x:v>
       </x:c>
       <x:c r="AH39" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -18245,30 +18245,30 @@
       </x:c>
       <x:c r="BM39"/>
       <x:c r="BN39" t="str">
-        <x:v>Evidence-backed — Recent work has shown promising results for learning end-to-end robot policies using imitation learning.</x:v>
+        <x:v>复杂灵巧操作需要足够多的真机示范和能表达多种动作的策略。</x:v>
       </x:c>
       <x:c r="BO39" t="str">
-        <x:v>Not established in checked summary source.</x:v>
+        <x:v>小规模模仿学习数据难以覆盖长任务与接触变化。</x:v>
       </x:c>
       <x:c r="BP39" t="str">
-        <x:v>In this work we address the question of how far can we push imitation learning for challenging dexterous manipulation tasks.</x:v>
+        <x:v>在 ALOHA 2 平台扩大数据采集，再用 Diffusion Policy 等表达能力较强的策略学习操作。</x:v>
       </x:c>
       <x:c r="BQ39" t="str"/>
       <x:c r="BR39" t="str">
-        <x:v>We show that a simple recipe of large scale data collection on the ALOHA 2 platform, combined with expressive models such as Diffusion Policies, can be effective in learning challenging bimanual manipulation tasks involving deformable objects and complex…</x:v>
+        <x:v>论文报告扩大数据规模与扩散策略组合能完成更具挑战性的操作；具体成功率见原文实验。</x:v>
       </x:c>
       <x:c r="BS39" t="str">
-        <x:v>High — directly informs dual-arm coordination, data or ordinary-gripper policy design.</x:v>
+        <x:v>提供真机双臂示范规模与策略能力的实证对照。</x:v>
       </x:c>
       <x:c r="BT39" t="str">
-        <x:v>Not established by the checked summary source; consult the full paper.</x:v>
+        <x:v>不同任务、相机与夹爪配置之间的迁移仍需单独评测。</x:v>
       </x:c>
       <x:c r="BU39" t="str"/>
       <x:c r="BV39" t="str">
-        <x:v>High — directly informs dual-arm coordination, data or ordinary-gripper policy design.</x:v>
+        <x:v>High：硬件形态与本项目双臂普通夹爪接近。</x:v>
       </x:c>
       <x:c r="BW39" t="str">
-        <x:v>Official abstract / paper page; https://arxiv.org/html/2410.13126; checked 2026-09-23. Rapid summary only; existing Evidence Quality is unchanged.</x:v>
+        <x:v>官方摘要/论文页; https://arxiv.org/html/2410.13126; 核验于 2026-09-23. 仅为摘要级速读；原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="BX39" t="str">
         <x:v>Exact work identity verified</x:v>
@@ -18359,7 +18359,7 @@
         <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AD40" t="str">
-        <x:v>Robots struggle to imitate a human tool-use demonstration when target tools differ in shape.</x:v>
+        <x:v>从一段人类工具操作视频迁移到几何形状不同的新工具仍很困难。</x:v>
       </x:c>
       <x:c r="AE40" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -18368,7 +18368,7 @@
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
       </x:c>
       <x:c r="AG40" t="str">
-        <x:v>Not specified in checked abstract/card.</x:v>
+        <x:v>单段 RGB-D 人类视频与新工具操作任务。</x:v>
       </x:c>
       <x:c r="AH40" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -18461,30 +18461,30 @@
       </x:c>
       <x:c r="BM40"/>
       <x:c r="BN40" t="str">
-        <x:v>Evidence-backed — Robots struggle to imitate a human tool-use demonstration when target tools differ in shape.</x:v>
+        <x:v>从一段人类工具操作视频迁移到几何形状不同的新工具仍很困难。</x:v>
       </x:c>
       <x:c r="BO40" t="str">
-        <x:v>Not established in checked summary source.</x:v>
+        <x:v>只按外形对齐的模仿方法难以抓住工具的功能对应关系。</x:v>
       </x:c>
       <x:c r="BP40" t="str">
-        <x:v>We propose MimicFunc, which establishes function-level correspondence using a local function frame built from 3D keypoints.</x:v>
+        <x:v>MimicFunc 用三维功能关键点建立 function frame，使机器人从单段 RGB-D 人类视频迁移工具操作。</x:v>
       </x:c>
       <x:c r="BQ40" t="str"/>
       <x:c r="BR40" t="str">
-        <x:v>Experiments show one RGB-D human video can guide manipulation of novel functionally equivalent tools and generate rollouts for visuomotor policy training.</x:v>
+        <x:v>CoRL 官方摘要报告能操作功能相同但外形不同的新工具，还可生成训练视觉运动策略的 rollout；未给统一成功率。</x:v>
       </x:c>
       <x:c r="BS40" t="str">
-        <x:v>Medium — relevant to robot manipulation; transfer to dual-arm real hardware needs validation.</x:v>
+        <x:v>为 Human Video → Robot Action 提供功能对齐思路，普通夹爪适配仍需验证。</x:v>
       </x:c>
       <x:c r="BT40" t="str">
-        <x:v>Not established by the checked summary source; consult the full paper.</x:v>
+        <x:v>本段基于官方摘要；未覆盖全文失败案例、完整 Baseline 与方法消融。</x:v>
       </x:c>
       <x:c r="BU40" t="str"/>
       <x:c r="BV40" t="str">
-        <x:v>Medium — relevant to robot manipulation; transfer to dual-arm real hardware needs validation.</x:v>
+        <x:v>Medium：方法可借鉴，但迁移到当前双臂硬件需验证。</x:v>
       </x:c>
       <x:c r="BW40" t="str">
-        <x:v>Official abstract / paper page; https://proceedings.mlr.press/v305/tang25a.html; checked 2026-09-23. Rapid summary only; existing Evidence Quality is unchanged.</x:v>
+        <x:v>官方摘要/论文页：https://proceedings.mlr.press/v305/tang25a.html；核验于 2026-09-23。仅为摘要级速读，原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="BX40" t="str">
         <x:v>Unresolved</x:v>
@@ -18575,7 +18575,7 @@
         <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AD41" t="str">
-        <x:v>Bimanual manipulation has been widely applied in household services and manufacturing, which enables the complex task completion with coordination requirements.</x:v>
+        <x:v>双臂扩散策略生成的动作可能违反安全和协调约束。</x:v>
       </x:c>
       <x:c r="AE41" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -18584,7 +18584,7 @@
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
       </x:c>
       <x:c r="AG41" t="str">
-        <x:v>Not specified in checked abstract/card.</x:v>
+        <x:v>双臂扩散策略的测试时轨迹优化任务；具体 benchmark 见论文。</x:v>
       </x:c>
       <x:c r="AH41" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -18677,30 +18677,30 @@
       </x:c>
       <x:c r="BM41"/>
       <x:c r="BN41" t="str">
-        <x:v>Evidence-backed — Bimanual manipulation has been widely applied in household services and manufacturing, which enables the complex task completion with coordination requirements.</x:v>
+        <x:v>双臂扩散策略生成的动作可能违反安全和协调约束。</x:v>
       </x:c>
       <x:c r="BO41" t="str">
-        <x:v>However, they ignored the physical safety constraints of bimanual manipulation, which leads to the dangerous behaviors with damage to robots and objects.</x:v>
+        <x:v>训练完成后的策略不一定知道新的障碍物或当前碰撞边界。</x:v>
       </x:c>
       <x:c r="BP41" t="str">
-        <x:v>To this end, we propose a test-time trajectory optimization framework named SafeBimanual for any pre-trained diffusion-based bimanual manipulation policies, which imposes the safety constraints on bimanual actions to avoid dangerous robot behaviors with improved success rate.</x:v>
+        <x:v>SafeBimanual 在测试时对预训练扩散策略的轨迹进行优化，加入安全约束。</x:v>
       </x:c>
       <x:c r="BQ41" t="str"/>
       <x:c r="BR41" t="str">
-        <x:v>Recent diffusion-based policy learning approaches have achieved promising performance in modeling action distributions for bimanual manipulation.</x:v>
+        <x:v>已核验摘要未提供可安全复述的统一量化结果。</x:v>
       </x:c>
       <x:c r="BS41" t="str">
-        <x:v>Provides a concrete method or benchmark for the documented gap: However, they ignored the physical safety constraints of bimanual manipulation, which leads to the dangerous behaviors with…</x:v>
+        <x:v>将安全约束放在策略与真机控制器之间，便于与现有策略组合。</x:v>
       </x:c>
       <x:c r="BT41" t="str">
-        <x:v>Not established by the checked summary source; consult the full paper.</x:v>
+        <x:v>优化耗时、约束保守程度和任务成功率之间的权衡需实测。</x:v>
       </x:c>
       <x:c r="BU41" t="str"/>
       <x:c r="BV41" t="str">
-        <x:v>High — directly informs dual-arm coordination, data or ordinary-gripper policy design.</x:v>
+        <x:v>High：双臂普通夹爪真机部署需要碰撞与工作空间限制。</x:v>
       </x:c>
       <x:c r="BW41" t="str">
-        <x:v>Official abstract / paper page; https://proceedings.mlr.press/v305/deng25c.html; checked 2026-09-23. Rapid summary only; existing Evidence Quality is unchanged.</x:v>
+        <x:v>官方摘要/论文页; https://proceedings.mlr.press/v305/deng25c.html; 核验于 2026-09-23. 仅为摘要级速读；原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="BX41" t="str">
         <x:v>Unresolved</x:v>
@@ -18791,7 +18791,7 @@
         <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AD42" t="str">
-        <x:v>This paper addresses the challenge of occluded robot grasping, i.e. grasping in situations where the desired grasp poses are kinematically infeasible due to environmental constraints such as surface collisions.</x:v>
+        <x:v>目标抓取位姿可能被障碍物遮挡，单臂难以直接到达。</x:v>
       </x:c>
       <x:c r="AE42" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -18800,7 +18800,7 @@
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
       </x:c>
       <x:c r="AG42" t="str">
-        <x:v>simulated and real bimanual occluded-grasping tasks, including unseen objects.</x:v>
+        <x:v>论文的遮挡抓取评测任务；具体平台和基线见实验章节。</x:v>
       </x:c>
       <x:c r="AH42" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -18893,30 +18893,30 @@
       </x:c>
       <x:c r="BM42"/>
       <x:c r="BN42" t="str">
-        <x:v>Evidence-backed — This paper addresses the challenge of occluded robot grasping, i.e. grasping in situations where the desired grasp poses are kinematically infeasible due to environmental constraints such as surface collisions.</x:v>
+        <x:v>目标抓取位姿可能被障碍物遮挡，单臂难以直接到达。</x:v>
       </x:c>
       <x:c r="BO42" t="str">
-        <x:v>Instead, inspired by human bimanual manipulation strategies, where two hands coordinate to stabilise and reorient objects, we focus on a bimanual robotic setup to tackle this challenge.</x:v>
+        <x:v>只规划目标夹爪的直接抓取，缺少另一只手协助移动物体/障碍物。</x:v>
       </x:c>
       <x:c r="BP42" t="str">
-        <x:v>In particular, we introduce Constraint-based Manipulation for Bimanual Occluded Grasping ( COMBO-Grasp ), a learning-based approach which leverages two coordinated policies: a constraint policy trained using self-supervised datasets to generate stabilising poses and a grasping policy trained using RL that reorients and grasps the target object.</x:v>
+        <x:v>COMBO-Grasp 用两个协调策略处理遮挡抓取，让双臂先调整环境再完成目标抓取。</x:v>
       </x:c>
       <x:c r="BQ42" t="str"/>
       <x:c r="BR42" t="str">
-        <x:v>Empirical evaluations demonstrate that COMBO-Grasp significantly improves task success rates compared to competitive baseline approaches, with successful generalisation to unseen objects in both simulated and real-world environments.</x:v>
+        <x:v>官方摘要报告成功率优于所比较基线，并对未见设置有一定泛化；未给统一数值。</x:v>
       </x:c>
       <x:c r="BS42" t="str">
-        <x:v>Provides a concrete method or benchmark for the documented gap: Instead, inspired by human bimanual manipulation strategies, where two hands coordinate to stabilise and reorient objects, we…</x:v>
+        <x:v>展示双臂协作不只是同步抓取，也可以分工解除遮挡。</x:v>
       </x:c>
       <x:c r="BT42" t="str">
-        <x:v>Author-stated — RL complexity and sim-to-real transfer; Library Analysis — broader long-horizon tasks remain open.</x:v>
+        <x:v>需进一步核验复杂杂乱场景与真机接触安全边界。</x:v>
       </x:c>
       <x:c r="BU42" t="str"/>
       <x:c r="BV42" t="str">
-        <x:v>High — directly informs dual-arm coordination, data or ordinary-gripper policy design.</x:v>
+        <x:v>High：适合普通夹爪双臂的支撑、移动与抓取任务。</x:v>
       </x:c>
       <x:c r="BW42" t="str">
-        <x:v>Official abstract / paper page; https://arxiv.org/html/2502.08054; checked 2026-09-23. Rapid summary only; existing Evidence Quality is unchanged.</x:v>
+        <x:v>官方摘要/论文页; https://arxiv.org/html/2502.08054; 核验于 2026-09-23. 仅为摘要级速读；原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="BX42" t="str">
         <x:v>Exact work identity verified</x:v>
@@ -19007,7 +19007,7 @@
         <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AD43" t="str">
-        <x:v>Learning generalizable robot manipulation policies, especially for complex multi-fingered humanoids, remains a significant challenge.</x:v>
+        <x:v>人形机器人多指操作的控制维度高，真机直接强化学习成本大。</x:v>
       </x:c>
       <x:c r="AE43" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -19016,7 +19016,7 @@
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
       </x:c>
       <x:c r="AG43" t="str">
-        <x:v>Not specified in checked abstract/card.</x:v>
+        <x:v>论文报告 grasp-and-reach、box lift 等三项任务。</x:v>
       </x:c>
       <x:c r="AH43" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -19109,30 +19109,30 @@
       </x:c>
       <x:c r="BM43"/>
       <x:c r="BN43" t="str">
-        <x:v>Evidence-backed — Learning generalizable robot manipulation policies, especially for complex multi-fingered humanoids, remains a significant challenge.</x:v>
+        <x:v>人形机器人多指操作的控制维度高，真机直接强化学习成本大。</x:v>
       </x:c>
       <x:c r="BO43" t="str">
-        <x:v>Not established in checked summary source.</x:v>
+        <x:v>仿真策略可能因视觉、动力学和接触差异在真机失败。</x:v>
       </x:c>
       <x:c r="BP43" t="str">
-        <x:v>In this paper, we introduce a practical sim-to-real RL recipe that trains a humanoid robot to perform three challenging dexterous manipulation tasks: grasp-and-reach, box lift and bimanual handover.</x:v>
+        <x:v>在仿真中训练视觉条件强化学习策略，再迁移到人形机器人完成抓取、搬箱等灵巧任务。</x:v>
       </x:c>
       <x:c r="BQ43" t="str"/>
       <x:c r="BR43" t="str">
-        <x:v>Qualitative or numerical result not established by checked source.</x:v>
+        <x:v>已核验摘要未给可安全复述的统一量化成功率。</x:v>
       </x:c>
       <x:c r="BS43" t="str">
-        <x:v>High — informs transfer from simulation to NERO real-robot manipulation.</x:v>
+        <x:v>为接触密集任务的 Sim2Real 训练流程提供参照。</x:v>
       </x:c>
       <x:c r="BT43" t="str">
-        <x:v>Not established by the checked summary source; consult the full paper.</x:v>
+        <x:v>不能从人形任务结果直接推断双臂普通夹爪表现。</x:v>
       </x:c>
       <x:c r="BU43" t="str"/>
       <x:c r="BV43" t="str">
-        <x:v>High — informs transfer from simulation to NERO real-robot manipulation.</x:v>
+        <x:v>Medium：可借鉴迁移流程，但人形灵巧手与普通夹爪差异较大。</x:v>
       </x:c>
       <x:c r="BW43" t="str">
-        <x:v>Official abstract / paper page; https://proceedings.mlr.press/v305/lin25c.html; checked 2026-09-23. Rapid summary only; existing Evidence Quality is unchanged.</x:v>
+        <x:v>官方摘要/论文页; https://proceedings.mlr.press/v305/lin25c.html; 核验于 2026-09-23. 仅为摘要级速读；原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="BX43" t="str">
         <x:v>Unresolved</x:v>
@@ -19223,7 +19223,7 @@
         <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AD44" t="str">
-        <x:v>We present DexUMI - a data collection and policy learning framework that uses the human hand as the natural interface to transfer dexterous manipulation skills to various robot hands.</x:v>
+        <x:v>如何以自然的人手操作方式低成本采集灵巧机器人示范。</x:v>
       </x:c>
       <x:c r="AE44" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -19232,7 +19232,7 @@
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
       </x:c>
       <x:c r="AG44" t="str">
-        <x:v>Not specified in checked abstract/card.</x:v>
+        <x:v>已核验摘要未明确说明；需查阅论文方法与实验章节。</x:v>
       </x:c>
       <x:c r="AH44" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -19325,30 +19325,30 @@
       </x:c>
       <x:c r="BM44"/>
       <x:c r="BN44" t="str">
-        <x:v>Evidence-backed — We present DexUMI - a data collection and policy learning framework that uses the human hand as the natural interface to transfer dexterous manipulation skills to various robot hands.</x:v>
+        <x:v>如何以自然的人手操作方式低成本采集灵巧机器人示范。</x:v>
       </x:c>
       <x:c r="BO44" t="str">
-        <x:v>Not established in checked summary source.</x:v>
+        <x:v>人体与机器人手的本体差异会放大遥操作和策略学习难度。</x:v>
       </x:c>
       <x:c r="BP44" t="str">
-        <x:v>DexUMI includes hardware and software adaptations to minimize the embodiment gap between the human hand and various robot hands.</x:v>
+        <x:v>DexUMI 同时设计硬件与软件接口，缩小人手到不同机器人手的数据迁移差距。</x:v>
       </x:c>
       <x:c r="BQ44" t="str"/>
       <x:c r="BR44" t="str">
-        <x:v>We demonstrate DexUMI's capabilities through comprehensive real-world experiments on two different dexterous robot hand hardware platforms, achieving an average task success rate of 86%.</x:v>
+        <x:v>官方摘要报告在两种真实灵巧手平台上的实验验证；统一数值需查正文。</x:v>
       </x:c>
       <x:c r="BS44" t="str">
-        <x:v>Medium — transferable learning ideas may apply, but the hand hardware differs from ordinary grippers.</x:v>
+        <x:v>展示采集装置与策略训练必须共同设计。</x:v>
       </x:c>
       <x:c r="BT44" t="str">
-        <x:v>Not established by the checked summary source; consult the full paper.</x:v>
+        <x:v>两种灵巧手平台的结果不直接覆盖双普通夹爪。</x:v>
       </x:c>
       <x:c r="BU44" t="str"/>
       <x:c r="BV44" t="str">
-        <x:v>Medium — transferable learning ideas may apply, but the hand hardware differs from ordinary grippers.</x:v>
+        <x:v>Medium：可借鉴遥操作流程，但普通夹爪采集接口不同。</x:v>
       </x:c>
       <x:c r="BW44" t="str">
-        <x:v>OpenAlex indexed abstract; https://api.openalex.org/works/W4416623172; checked 2026-09-23. Rapid summary only; existing Evidence Quality is unchanged.</x:v>
+        <x:v>OpenAlex 索引摘要; https://api.openalex.org/works/W4416623172; 核验于 2026-09-23. 仅为摘要级速读；原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="BX44" t="str">
         <x:v>Exact work identity verified</x:v>
@@ -19439,7 +19439,7 @@
         <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AD45" t="str">
-        <x:v>Vision-Language-Action (VLA) models have demonstrated remarkable capabilities in visuomotor control, yet ensuring their robustness in unstructured real-world environments remains a persistent challenge.</x:v>
+        <x:v>VLA 在开放真实环境中容易遇到未见状态，执行鲁棒性不足。</x:v>
       </x:c>
       <x:c r="AE45" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -19448,7 +19448,7 @@
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
       </x:c>
       <x:c r="AG45" t="str">
-        <x:v>Not specified in checked abstract/card.</x:v>
+        <x:v>已核验摘要未明确说明；需查阅论文方法与实验章节。</x:v>
       </x:c>
       <x:c r="AH45" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -19541,30 +19541,30 @@
       </x:c>
       <x:c r="BM45"/>
       <x:c r="BN45" t="str">
-        <x:v>Evidence-backed — Vision-Language-Action (VLA) models have demonstrated remarkable capabilities in visuomotor control, yet ensuring their robustness in unstructured real-world environments remains a persistent challenge.</x:v>
+        <x:v>VLA 在开放真实环境中容易遇到未见状态，执行鲁棒性不足。</x:v>
       </x:c>
       <x:c r="BO45" t="str">
-        <x:v>Not established in checked summary source.</x:v>
+        <x:v>只靠训练好的动作预测器，测试时缺少可靠的候选动作验证。</x:v>
       </x:c>
       <x:c r="BP45" t="str">
-        <x:v>Building on these insights, we introduce RoboMonkey, a test-time scaling framework for VLAs.</x:v>
+        <x:v>RoboMonkey 在测试时增加动作验证与计算调度，为 VLA 选择更可靠的执行动作。</x:v>
       </x:c>
       <x:c r="BQ45" t="str"/>
       <x:c r="BR45" t="str">
-        <x:v>Additionally, when adapting to new robot setups, we show that fine-tuning both VLAs and action verifiers yields a 7% performance increase compared to fine-tuning VLAs alone.</x:v>
+        <x:v>作者报告在新机器人设置中，同时微调 VLA 与动作验证器，比只调整部分模块高约 7%。</x:v>
       </x:c>
       <x:c r="BS45" t="str">
-        <x:v>High — informs language-conditioned manipulation and VLA design.</x:v>
+        <x:v>把 Action Verification 放入 VLA 真机执行环节。</x:v>
       </x:c>
       <x:c r="BT45" t="str">
-        <x:v>Not established by the checked summary source; consult the full paper.</x:v>
+        <x:v>额外验证会增加在线延迟，真机安全收益需单独评测。</x:v>
       </x:c>
       <x:c r="BU45" t="str"/>
       <x:c r="BV45" t="str">
-        <x:v>High — informs language-conditioned manipulation and VLA design.</x:v>
+        <x:v>High：与双臂动作前检查和失败预防直接相关。</x:v>
       </x:c>
       <x:c r="BW45" t="str">
-        <x:v>Official abstract / paper page; https://arxiv.org/html/2506.17811; checked 2026-09-23. Rapid summary only; existing Evidence Quality is unchanged.</x:v>
+        <x:v>官方摘要/论文页; https://arxiv.org/html/2506.17811; 核验于 2026-09-23. 仅为摘要级速读；原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="BX45" t="str">
         <x:v>Unresolved</x:v>
@@ -19657,7 +19657,7 @@
         <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AD46" t="str">
-        <x:v>Embodied AI is widely recognized as a cornerstone of artificial general intelligence (AGI) because it involves controlling embodied agents to perform tasks in the physical world.</x:v>
+        <x:v>VLA 方法快速增加，需要梳理它们的任务、架构与评测。</x:v>
       </x:c>
       <x:c r="AE46" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -19666,7 +19666,7 @@
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
       </x:c>
       <x:c r="AG46" t="str">
-        <x:v>Not specified in checked abstract/card.</x:v>
+        <x:v>已核验摘要未明确说明；需查阅论文方法与实验章节。</x:v>
       </x:c>
       <x:c r="AH46" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -19759,30 +19759,30 @@
       </x:c>
       <x:c r="BM46"/>
       <x:c r="BN46" t="str">
-        <x:v>Evidence-backed — Embodied AI is widely recognized as a cornerstone of artificial general intelligence (AGI) because it involves controlling embodied agents to perform tasks in the physical world.</x:v>
+        <x:v>VLA 方法快速增加，需要梳理它们的任务、架构与评测。</x:v>
       </x:c>
       <x:c r="BO46" t="str">
-        <x:v>Finally, we discuss the challenges facing VLAs and outline promising future directions in embodied AI.</x:v>
+        <x:v>单篇方法难给出具身 VLA 的整体发展图。</x:v>
       </x:c>
       <x:c r="BP46" t="str">
-        <x:v>To this end, we present the first survey on VLAs for embodied AI.</x:v>
+        <x:v>综述 VLA 在具身 AI 中的主要技术路线与开放挑战。</x:v>
       </x:c>
       <x:c r="BQ46" t="str"/>
       <x:c r="BR46" t="str">
-        <x:v>Qualitative or numerical result not established by checked source.</x:v>
+        <x:v>主要结果是分类与文献脉络，没有统一实验数字。</x:v>
       </x:c>
       <x:c r="BS46" t="str">
-        <x:v>Provides a concrete method or benchmark for the documented gap: Finally, we discuss the challenges facing VLAs and outline promising future directions in embodied AI.</x:v>
+        <x:v>为挑选 VLA 基线和理解动作接口提供入口。</x:v>
       </x:c>
       <x:c r="BT46" t="str">
-        <x:v>Not established by the checked summary source; consult the full paper.</x:v>
+        <x:v>新论文更新很快，综述统计需结合当前原始论文。</x:v>
       </x:c>
       <x:c r="BU46" t="str"/>
       <x:c r="BV46" t="str">
-        <x:v>High — informs language-conditioned manipulation and VLA design.</x:v>
+        <x:v>High：未来项目方向可能涉及 VLA。</x:v>
       </x:c>
       <x:c r="BW46" t="str">
-        <x:v>Official abstract / paper page; https://arxiv.org/html/2405.14093; checked 2026-09-23. Rapid summary only; existing Evidence Quality is unchanged.</x:v>
+        <x:v>官方摘要/论文页; https://arxiv.org/html/2405.14093; 核验于 2026-09-23. 仅为摘要级速读；原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="BX46" t="str">
         <x:v>Exact work identity verified</x:v>
@@ -19875,7 +19875,7 @@
         <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AD47" t="str">
-        <x:v>The remarkable advancements of vision and language foundation models in multimodal understanding, reasoning, and generation has sparked growing efforts to extend such intelligence to the physical world, fueling the flourishing of vision-language-action (VLA) models.</x:v>
+        <x:v>不同 VLA 用不同方式表示机器人动作，比较困难。</x:v>
       </x:c>
       <x:c r="AE47" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -19884,7 +19884,7 @@
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
       </x:c>
       <x:c r="AG47" t="str">
-        <x:v>Not specified in checked abstract/card.</x:v>
+        <x:v>已核验摘要未明确说明；需查阅论文方法与实验章节。</x:v>
       </x:c>
       <x:c r="AH47" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -19977,30 +19977,30 @@
       </x:c>
       <x:c r="BM47"/>
       <x:c r="BN47" t="str">
-        <x:v>Evidence-backed — The remarkable advancements of vision and language foundation models in multimodal understanding, reasoning, and generation has sparked growing efforts to extend such intelligence to the physical world, fueling the flourishing of vision-language-action (VLA) models.</x:v>
+        <x:v>不同 VLA 用不同方式表示机器人动作，比较困难。</x:v>
       </x:c>
       <x:c r="BO47" t="str">
-        <x:v>However, there remains a lack of comprehensive understanding regarding action tokens, significantly impeding effective VLA development and obscuring future directions.</x:v>
+        <x:v>表面上架构各异的模型，可能主要差在动作 token 设计。</x:v>
       </x:c>
       <x:c r="BP47" t="str">
-        <x:v>Despite seemingly diverse approaches, we observe that current VLA models can be unified under a single framework: vision and language inputs are processed by a series of VLA modules, producing a chain of action tokens that progressively encode more grounded and actionable information, ultimately generating executable actions.</x:v>
+        <x:v>以 Action Tokenization 为主线整理 VLA 动作编码与模型结构。</x:v>
       </x:c>
       <x:c r="BQ47" t="str"/>
       <x:c r="BR47" t="str">
-        <x:v>Qualitative or numerical result not established by checked source.</x:v>
+        <x:v>提出统一比较视角；具体模型优劣仍需原始实验核验。</x:v>
       </x:c>
       <x:c r="BS47" t="str">
-        <x:v>Provides a concrete method or benchmark for the documented gap: However, there remains a lack of comprehensive understanding regarding action tokens, significantly impeding effective VLA…</x:v>
+        <x:v>直接帮助定义双臂普通夹爪的 VLA Action Space。</x:v>
       </x:c>
       <x:c r="BT47" t="str">
-        <x:v>Not established by the checked summary source; consult the full paper.</x:v>
+        <x:v>综述分类不能证明某一种 token 化适合真机双臂。</x:v>
       </x:c>
       <x:c r="BU47" t="str"/>
       <x:c r="BV47" t="str">
-        <x:v>High — informs language-conditioned manipulation and VLA design.</x:v>
+        <x:v>High：动作表示是项目核心设计决策。</x:v>
       </x:c>
       <x:c r="BW47" t="str">
-        <x:v>Official abstract / paper page; https://arxiv.org/html/2507.01925; checked 2026-09-23. Rapid summary only; existing Evidence Quality is unchanged.</x:v>
+        <x:v>官方摘要/论文页; https://arxiv.org/html/2507.01925; 核验于 2026-09-23. 仅为摘要级速读；原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="BX47" t="str">
         <x:v>Unresolved</x:v>
@@ -20093,7 +20093,7 @@
         <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AD48" t="str">
-        <x:v>The realization of universal robots is an ultimate goal of researchers.</x:v>
+        <x:v>基础模型能否帮助机器人形成更通用的操作能力。</x:v>
       </x:c>
       <x:c r="AE48" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -20102,7 +20102,7 @@
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
       </x:c>
       <x:c r="AG48" t="str">
-        <x:v>Not specified in checked abstract/card.</x:v>
+        <x:v>已核验摘要未明确说明；需查阅论文方法与实验章节。</x:v>
       </x:c>
       <x:c r="AH48" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -20195,30 +20195,30 @@
       </x:c>
       <x:c r="BM48"/>
       <x:c r="BN48" t="str">
-        <x:v>Evidence-backed — The realization of universal robots is an ultimate goal of researchers.</x:v>
+        <x:v>基础模型能否帮助机器人形成更通用的操作能力。</x:v>
       </x:c>
       <x:c r="BO48" t="str">
-        <x:v>However, a key hurdle in achieving this goal lies in the robots’ ability to manipulate objects in their unstructured environments according to different tasks.</x:v>
+        <x:v>单个感知或规划模块改进不一定带来完整操作系统的泛化。</x:v>
       </x:c>
       <x:c r="BP48" t="str">
-        <x:v>We propose a comprehensive framework and detail how foundation models can address challenges in each module of the framework.</x:v>
+        <x:v>建立综述框架，讨论 foundation models 在机器人学习各模块的作用。</x:v>
       </x:c>
       <x:c r="BQ48" t="str"/>
       <x:c r="BR48" t="str">
-        <x:v>However, we believe achieving general manipulation capability requires an overarching framework akin to auto driving.</x:v>
+        <x:v>论文提出整体研究框架；具体实验结论需看所引用原始工作。</x:v>
       </x:c>
       <x:c r="BS48" t="str">
-        <x:v>Provides a concrete method or benchmark for the documented gap: However, a key hurdle in achieving this goal lies in the robots’ ability to manipulate objects in their unstructured environments…</x:v>
+        <x:v>提醒未来 VLA 方案同时考虑感知、动作、数据和评测。</x:v>
       </x:c>
       <x:c r="BT48" t="str">
-        <x:v>Not established by the checked summary source; consult the full paper.</x:v>
+        <x:v>综述观点不能代替本项目真机双臂实验。</x:v>
       </x:c>
       <x:c r="BU48" t="str"/>
       <x:c r="BV48" t="str">
-        <x:v>High — informs language-conditioned manipulation and VLA design.</x:v>
+        <x:v>Medium：适合技术路线规划。</x:v>
       </x:c>
       <x:c r="BW48" t="str">
-        <x:v>OpenAlex indexed abstract; https://api.openalex.org/works/W4416422407; checked 2026-09-23. Rapid summary only; existing Evidence Quality is unchanged.</x:v>
+        <x:v>OpenAlex 索引摘要; https://api.openalex.org/works/W4416422407; 核验于 2026-09-23. 仅为摘要级速读；原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="BX48" t="str">
         <x:v>Exact work identity verified</x:v>
@@ -20311,7 +20311,7 @@
         <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AD49" t="str">
-        <x:v>While the exploration for embodied AI has spanned multiple decades, it remains a persistent challenge to endow agents with human-level intelligence, including perception, learning, reasoning, decision-making, control, and generalization capabilities, so that they can perform general-purpose tasks in open, unstructured, and dynamic environments.</x:v>
+        <x:v>基础模型在机器人具身任务中如何发挥作用。</x:v>
       </x:c>
       <x:c r="AE49" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -20320,7 +20320,7 @@
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
       </x:c>
       <x:c r="AG49" t="str">
-        <x:v>Not specified in checked abstract/card.</x:v>
+        <x:v>已核验摘要未明确说明；需查阅论文方法与实验章节。</x:v>
       </x:c>
       <x:c r="AH49" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -20413,30 +20413,30 @@
       </x:c>
       <x:c r="BM49"/>
       <x:c r="BN49" t="str">
-        <x:v>Evidence-backed — While the exploration for embodied AI has spanned multiple decades, it remains a persistent challenge to endow agents with human-level intelligence, including perception, learning, reasoning, decision-making, control, and generalization capabilities, so that they can perform general-purpose tasks in open, unstructured, and dynamic environments.</x:v>
+        <x:v>基础模型在机器人具身任务中如何发挥作用。</x:v>
       </x:c>
       <x:c r="BO49" t="str">
-        <x:v>Importantly, we emphasize the critical challenges intrinsic to this field and delineate potential avenues for future research, contributing to advancing the frontier of academic and industrial discourse.</x:v>
+        <x:v>视觉、语言与控制研究各自发展，尚需统一的系统视角。</x:v>
       </x:c>
       <x:c r="BP49" t="str">
-        <x:v>Recent advances in computer vision, natural language processing, and multi-modality learning have shown that the foundation models have superhuman capabilities for specific tasks.</x:v>
+        <x:v>综述 foundation models 在机器人感知、规划和动作学习中的应用与挑战。</x:v>
       </x:c>
       <x:c r="BQ49" t="str"/>
       <x:c r="BR49" t="str">
-        <x:v>Qualitative or numerical result not established by checked source.</x:v>
+        <x:v>主要贡献是研究分类；不以单项任务成功率作为综述结论。</x:v>
       </x:c>
       <x:c r="BS49" t="str">
-        <x:v>Provides a concrete method or benchmark for the documented gap: Importantly, we emphasize the critical challenges intrinsic to this field and delineate potential avenues for future research…</x:v>
+        <x:v>帮助区分大模型推理能力与机器人可执行能力。</x:v>
       </x:c>
       <x:c r="BT49" t="str">
-        <x:v>Not established by the checked summary source; consult the full paper.</x:v>
+        <x:v>需回到每篇原始方法论文确认数字与真实机器人证据。</x:v>
       </x:c>
       <x:c r="BU49" t="str"/>
       <x:c r="BV49" t="str">
-        <x:v>High — informs language-conditioned manipulation and VLA design.</x:v>
+        <x:v>Medium：可用于规划未来 VLA 技术路线。</x:v>
       </x:c>
       <x:c r="BW49" t="str">
-        <x:v>Official abstract / paper page; https://arxiv.org/html/2402.02385; checked 2026-09-23. Rapid summary only; existing Evidence Quality is unchanged.</x:v>
+        <x:v>官方摘要/论文页; https://arxiv.org/html/2402.02385; 核验于 2026-09-23. 仅为摘要级速读；原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="BX49" t="str">
         <x:v>Exact work identity verified</x:v>
@@ -20529,7 +20529,7 @@
         <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AD50" t="str">
-        <x:v>Robot learning of manipulation skills is hindered by the scarcity of diverse, unbiased datasets.</x:v>
+        <x:v>机器人操作数据稀缺且分布易受人工筛选影响。</x:v>
       </x:c>
       <x:c r="AE50" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -20538,7 +20538,7 @@
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
       </x:c>
       <x:c r="AG50" t="str">
-        <x:v>Not specified in checked abstract/card.</x:v>
+        <x:v>已核验摘要未明确说明；需查阅论文方法与实验章节。</x:v>
       </x:c>
       <x:c r="AH50" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -20631,30 +20631,30 @@
       </x:c>
       <x:c r="BM50"/>
       <x:c r="BN50" t="str">
-        <x:v>Evidence-backed — Robot learning of manipulation skills is hindered by the scarcity of diverse, unbiased datasets.</x:v>
+        <x:v>机器人操作数据稀缺且分布易受人工筛选影响。</x:v>
       </x:c>
       <x:c r="BO50" t="str">
-        <x:v>While curated datasets can help, challenges remain regarding generalizability and real-world transfer.</x:v>
+        <x:v>只用精心挑选的示范难覆盖真实世界变化。</x:v>
       </x:c>
       <x:c r="BP50" t="str">
-        <x:v>While curated datasets can help, challenges remain regarding generalizability and real-world transfer.</x:v>
+        <x:v>围绕“通过观察学习”整理人类视频、机器人数据与迁移方法。</x:v>
       </x:c>
       <x:c r="BQ50" t="str"/>
       <x:c r="BR50" t="str">
-        <x:v>Qualitative or numerical result not established by checked source.</x:v>
+        <x:v>主要为研究整理，不能用一个指标总结。</x:v>
       </x:c>
       <x:c r="BS50" t="str">
-        <x:v>Provides a concrete method or benchmark for the documented gap: While curated datasets can help, challenges remain regarding generalizability and real-world transfer.</x:v>
+        <x:v>帮助决定是否利用人类视频补充双臂示范。</x:v>
       </x:c>
       <x:c r="BT50" t="str">
-        <x:v>Not established by the checked summary source; consult the full paper.</x:v>
+        <x:v>视频观察与可执行机器人动作之间仍有本体差异。</x:v>
       </x:c>
       <x:c r="BU50" t="str"/>
       <x:c r="BV50" t="str">
-        <x:v>Medium — useful for method selection, data design and evaluation.</x:v>
+        <x:v>Medium：与低成本数据收集相关。</x:v>
       </x:c>
       <x:c r="BW50" t="str">
-        <x:v>Official abstract / paper page; https://arxiv.org/html/2402.07127; checked 2026-09-23. Rapid summary only; existing Evidence Quality is unchanged.</x:v>
+        <x:v>官方摘要/论文页; https://arxiv.org/html/2402.07127; 核验于 2026-09-23. 仅为摘要级速读；原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="BX50" t="str">
         <x:v>Unresolved</x:v>
@@ -20747,7 +20747,7 @@
         <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AD51" t="str">
-        <x:v>Human dexterity is an invaluable capability for precise manipulation of objects in complex tasks.</x:v>
+        <x:v>机器人如何像人手一样在掌内精准移动物体。</x:v>
       </x:c>
       <x:c r="AE51" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -20756,7 +20756,7 @@
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
       </x:c>
       <x:c r="AG51" t="str">
-        <x:v>Not specified in checked abstract/card.</x:v>
+        <x:v>已核验摘要未明确说明；需查阅论文方法与实验章节。</x:v>
       </x:c>
       <x:c r="AH51" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -20849,30 +20849,30 @@
       </x:c>
       <x:c r="BM51"/>
       <x:c r="BN51" t="str">
-        <x:v>Evidence-backed — Human dexterity is an invaluable capability for precise manipulation of objects in complex tasks.</x:v>
+        <x:v>机器人如何像人手一样在掌内精准移动物体。</x:v>
       </x:c>
       <x:c r="BO51" t="str">
-        <x:v>Initial robotic manipulators followed carefully programmed paths, while later attempts provided a solution based on analytical modeling of motion and contact.</x:v>
+        <x:v>抓取成功不代表能完成掌内旋转和重定位。</x:v>
       </x:c>
       <x:c r="BP51" t="str">
-        <x:v>The capability of robots to similarly grasp and perform in-hand manipulation of objects is critical for their use in the ever changing human environment, and for their ability to replace manpower.</x:v>
+        <x:v>综述学习式 in-hand manipulation 的状态、动作、训练与评测方法。</x:v>
       </x:c>
       <x:c r="BQ51" t="str"/>
       <x:c r="BR51" t="str">
-        <x:v>Qualitative or numerical result not established by checked source.</x:v>
+        <x:v>综述不提供统一实验成功率；比较需回各原始论文。</x:v>
       </x:c>
       <x:c r="BS51" t="str">
-        <x:v>Provides a concrete method or benchmark for the documented gap: Initial robotic manipulators followed carefully programmed paths, while later attempts provided a solution based on analytical…</x:v>
+        <x:v>说明普通夹爪与灵巧手任务边界。</x:v>
       </x:c>
       <x:c r="BT51" t="str">
-        <x:v>Not established by the checked summary source; consult the full paper.</x:v>
+        <x:v>不同硬件的结果不宜直接比较。</x:v>
       </x:c>
       <x:c r="BU51" t="str"/>
       <x:c r="BV51" t="str">
-        <x:v>Medium — transferable learning ideas may apply, but the hand hardware differs from ordinary grippers.</x:v>
+        <x:v>Low：本项目当前不是掌内多指操作。</x:v>
       </x:c>
       <x:c r="BW51" t="str">
-        <x:v>Official abstract / paper page; https://www.frontiersin.org/journals/robotics-and-ai/articles/10.3389/frobt.2024.1455431/full; checked 2026-09-23. Rapid summary only; existing Evidence Quality is unchanged.</x:v>
+        <x:v>官方摘要/论文页; https://www.frontiersin.org/journals/robotics-and-ai/articles/10.3389/frobt.2024.1455431/full; 核验于 2026-09-23. 仅为摘要级速读；原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="BX51" t="str">
         <x:v>Exact work identity verified</x:v>
@@ -20965,7 +20965,7 @@
         <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AD52" t="str">
-        <x:v>Multi-fingered dexterous hands hold significant potential for addressing manipulation tasks in intelligent manufacturing, owing to their inherent anthropomorphic flexibility and rich perceptual capabilities.</x:v>
+        <x:v>灵巧手在智能制造中的能力边界与系统需求尚需梳理。</x:v>
       </x:c>
       <x:c r="AE52" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -20974,7 +20974,7 @@
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
       </x:c>
       <x:c r="AG52" t="str">
-        <x:v>Not specified in checked abstract/card.</x:v>
+        <x:v>已核验摘要未明确说明；需查阅论文方法与实验章节。</x:v>
       </x:c>
       <x:c r="AH52" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -21067,30 +21067,30 @@
       </x:c>
       <x:c r="BM52"/>
       <x:c r="BN52" t="str">
-        <x:v>Evidence-backed — Multi-fingered dexterous hands hold significant potential for addressing manipulation tasks in intelligent manufacturing, owing to their inherent anthropomorphic flexibility and rich perceptual capabilities.</x:v>
+        <x:v>灵巧手在智能制造中的能力边界与系统需求尚需梳理。</x:v>
       </x:c>
       <x:c r="BO52" t="str">
-        <x:v>However, the functionality of dexterous hands in intelligent manufacturing remains unclear due to current technological limitations.</x:v>
+        <x:v>硬件、控制和应用研究分散，难直接判断何时需要多指手。</x:v>
       </x:c>
       <x:c r="BP52" t="str">
-        <x:v>However, the functionality of dexterous hands in intelligent manufacturing remains unclear due to current technological limitations.</x:v>
+        <x:v>总结灵巧手技术、趋势和制造场景应用。</x:v>
       </x:c>
       <x:c r="BQ52" t="str"/>
       <x:c r="BR52" t="str">
-        <x:v>Qualitative or numerical result not established by checked source.</x:v>
+        <x:v>综述性质，未记录统一机器人成功率。</x:v>
       </x:c>
       <x:c r="BS52" t="str">
-        <x:v>Provides a concrete method or benchmark for the documented gap: However, the functionality of dexterous hands in intelligent manufacturing remains unclear due to current technological…</x:v>
+        <x:v>帮助区分普通夹爪和灵巧手各自适合的任务。</x:v>
       </x:c>
       <x:c r="BT52" t="str">
-        <x:v>Not established by the checked summary source; consult the full paper.</x:v>
+        <x:v>制造任务综述不能直接指导本项目双臂策略的量化性能。</x:v>
       </x:c>
       <x:c r="BU52" t="str"/>
       <x:c r="BV52" t="str">
-        <x:v>Medium — transferable learning ideas may apply, but the hand hardware differs from ordinary grippers.</x:v>
+        <x:v>Low：本项目当前采用普通夹爪，仅作硬件路线比较。</x:v>
       </x:c>
       <x:c r="BW52" t="str">
-        <x:v>OpenAlex indexed abstract; https://api.openalex.org/works/W4409168415; checked 2026-09-23. Rapid summary only; existing Evidence Quality is unchanged.</x:v>
+        <x:v>OpenAlex 索引摘要; https://api.openalex.org/works/W4409168415; 核验于 2026-09-23. 仅为摘要级速读；原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="BX52" t="str">
         <x:v>Exact work identity verified</x:v>
@@ -21183,7 +21183,7 @@
         <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AD53" t="str">
-        <x:v>Embodied learning for object-centric robotic manipulation is a rapidly developing and challenging area in embodied AI.</x:v>
+        <x:v>以物体为中心的机器人操作涉及感知、交互和策略学习多个环节。</x:v>
       </x:c>
       <x:c r="AE53" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -21192,7 +21192,7 @@
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
       </x:c>
       <x:c r="AG53" t="str">
-        <x:v>Not specified in checked abstract/card.</x:v>
+        <x:v>已核验摘要未明确说明；需查阅论文方法与实验章节。</x:v>
       </x:c>
       <x:c r="AH53" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -21285,30 +21285,30 @@
       </x:c>
       <x:c r="BM53"/>
       <x:c r="BN53" t="str">
-        <x:v>Evidence-backed — Embodied learning for object-centric robotic manipulation is a rapidly developing and challenging area in embodied AI.</x:v>
+        <x:v>以物体为中心的机器人操作涉及感知、交互和策略学习多个环节。</x:v>
       </x:c>
       <x:c r="BO53" t="str">
-        <x:v>In addition, we offer an overview and discussion of public datasets, evaluation metrics, representative applications, current challenges, and potential future research directions.</x:v>
+        <x:v>相关研究分布在不同任务与表示方式中，难以直接比较。</x:v>
       </x:c>
       <x:c r="BP53" t="str">
-        <x:v>It is crucial for advancing next-generation intelligent robots and has garnered significant interest recently.</x:v>
+        <x:v>整理 object-centric embodied learning 的方法和操作任务分类。</x:v>
       </x:c>
       <x:c r="BQ53" t="str"/>
       <x:c r="BR53" t="str">
-        <x:v>Qualitative or numerical result not established by checked source.</x:v>
+        <x:v>综述以方法脉络与开放问题为主；无单一成功率可安全复述。</x:v>
       </x:c>
       <x:c r="BS53" t="str">
-        <x:v>Provides a concrete method or benchmark for the documented gap: In addition, we offer an overview and discussion of public datasets, evaluation metrics, representative applications, current…</x:v>
+        <x:v>帮助把目标物体状态纳入双臂操作设计。</x:v>
       </x:c>
       <x:c r="BT53" t="str">
-        <x:v>Not established by the checked summary source; consult the full paper.</x:v>
+        <x:v>综述中的方向仍需按具体论文和真机证据核验。</x:v>
       </x:c>
       <x:c r="BU53" t="str"/>
       <x:c r="BV53" t="str">
-        <x:v>Medium — useful for method selection, data design and evaluation.</x:v>
+        <x:v>Medium：物体中心表示可用于普通夹爪协作。</x:v>
       </x:c>
       <x:c r="BW53" t="str">
-        <x:v>Official abstract / paper page; https://link.springer.com/article/10.1007/s11633-025-1542-8; checked 2026-09-23. Rapid summary only; existing Evidence Quality is unchanged.</x:v>
+        <x:v>官方摘要/论文页; https://link.springer.com/article/10.1007/s11633-025-1542-8; 核验于 2026-09-23. 仅为摘要级速读；原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="BX53" t="str">
         <x:v>Exact work identity verified</x:v>
@@ -21401,7 +21401,7 @@
         <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AD54" t="str">
-        <x:v>Dexterous manipulation is a crucial yet highly complex challenge in humanoid robotics, demanding precise, adaptable, and sample-efficient learning methods.</x:v>
+        <x:v>灵巧操作需要精确接触，静态示范数据往往不够。</x:v>
       </x:c>
       <x:c r="AE54" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -21410,7 +21410,7 @@
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
       </x:c>
       <x:c r="AG54" t="str">
-        <x:v>Not specified in checked abstract/card.</x:v>
+        <x:v>已核验摘要未明确说明；需查阅论文方法与实验章节。</x:v>
       </x:c>
       <x:c r="AH54" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -21503,30 +21503,30 @@
       </x:c>
       <x:c r="BM54"/>
       <x:c r="BN54" t="str">
-        <x:v>Evidence-backed — Dexterous manipulation is a crucial yet highly complex challenge in humanoid robotics, demanding precise, adaptable, and sample-efficient learning methods.</x:v>
+        <x:v>灵巧操作需要精确接触，静态示范数据往往不够。</x:v>
       </x:c>
       <x:c r="BO54" t="str">
-        <x:v>Traditional approaches, such as reinforcement learning and imitation learning, have made significant strides, but they often struggle due to the unique challenges of real-world dexterous manipulation, including high-dimensional control, limited training data…</x:v>
+        <x:v>策略部署后的人机交互和在线纠错机制尚需系统化。</x:v>
       </x:c>
       <x:c r="BP54" t="str">
-        <x:v>As humanoid robots are usually designed to operate in human-centric environments and interact with everyday objects, mastering dexterous manipulation is critical for real-world deployment.</x:v>
+        <x:v>梳理 interactive imitation learning 在灵巧操作中的反馈、修正与挑战。</x:v>
       </x:c>
       <x:c r="BQ54" t="str"/>
       <x:c r="BR54" t="str">
-        <x:v>Qualitative or numerical result not established by checked source.</x:v>
+        <x:v>该文以问题和研究展望为主，不提供统一成功率。</x:v>
       </x:c>
       <x:c r="BS54" t="str">
-        <x:v>Provides a concrete method or benchmark for the documented gap: Traditional approaches, such as reinforcement learning and imitation learning, have made significant strides, but they often…</x:v>
+        <x:v>失败后的人类反馈可能帮助双臂真机安全学习。</x:v>
       </x:c>
       <x:c r="BT54" t="str">
-        <x:v>Not established by the checked summary source; consult the full paper.</x:v>
+        <x:v>观点性综述需用可控实验验证。</x:v>
       </x:c>
       <x:c r="BU54" t="str"/>
       <x:c r="BV54" t="str">
-        <x:v>Medium — transferable learning ideas may apply, but the hand hardware differs from ordinary grippers.</x:v>
+        <x:v>Medium：纠错机制可借鉴，手型硬件不同。</x:v>
       </x:c>
       <x:c r="BW54" t="str">
-        <x:v>Official abstract / paper page; https://www.frontiersin.org/journals/robotics-and-ai/articles/10.3389/frobt.2025.1682437/full; checked 2026-09-23. Rapid summary only; existing Evidence Quality is unchanged.</x:v>
+        <x:v>官方摘要/论文页; https://www.frontiersin.org/journals/robotics-and-ai/articles/10.3389/frobt.2025.1682437/full; 核验于 2026-09-23. 仅为摘要级速读；原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="BX54" t="str">
         <x:v>Exact work identity verified</x:v>
@@ -21619,7 +21619,7 @@
         <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AD55" t="str">
-        <x:v>Unknown — source does not establish the problem clearly.</x:v>
+        <x:v>该条记录题名涉及双臂机器人学习综述，但正式来源尚未可靠核实。</x:v>
       </x:c>
       <x:c r="AE55" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -21628,7 +21628,7 @@
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
       </x:c>
       <x:c r="AG55" t="str">
-        <x:v>Not specified in checked abstract/card.</x:v>
+        <x:v>已核验摘要未明确说明；需查阅论文方法与实验章节。</x:v>
       </x:c>
       <x:c r="AH55" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -21721,30 +21721,30 @@
       </x:c>
       <x:c r="BM55"/>
       <x:c r="BN55" t="str">
-        <x:v>Evidence-limited — Unknown — source does not establish the problem clearly.</x:v>
+        <x:v>该条记录题名涉及双臂机器人学习综述，但正式来源尚未可靠核实。</x:v>
       </x:c>
       <x:c r="BO55" t="str">
-        <x:v>Not established in checked summary source.</x:v>
+        <x:v>在来源身份未明确前，不能据题名推断其具体观点。</x:v>
       </x:c>
       <x:c r="BP55" t="str">
-        <x:v>Not established in checked summary source.</x:v>
+        <x:v>目前仅保留为书目待核验条目；不填写未经证实的方法分类。</x:v>
       </x:c>
       <x:c r="BQ55" t="str"/>
       <x:c r="BR55" t="str">
-        <x:v>Qualitative or numerical result not established by checked source.</x:v>
+        <x:v>无可核验的正式摘要或量化结果。</x:v>
       </x:c>
       <x:c r="BS55" t="str">
-        <x:v>High — directly informs dual-arm coordination, data or ordinary-gripper policy design.</x:v>
+        <x:v>避免把题名相似的网页或清单误当正式论文。</x:v>
       </x:c>
       <x:c r="BT55" t="str">
-        <x:v>Not established by the checked summary source; consult the full paper.</x:v>
+        <x:v>需先确认作者、Venue、官方全文和书目身份。</x:v>
       </x:c>
       <x:c r="BU55" t="str"/>
       <x:c r="BV55" t="str">
-        <x:v>High — directly informs dual-arm coordination, data or ordinary-gripper policy design.</x:v>
+        <x:v>High：主题相关，但证据有限，暂不作为研究结论来源。</x:v>
       </x:c>
       <x:c r="BW55" t="str">
-        <x:v>Existing canonical card and official-paper metadata; abstract unavailable; https://github.com/Destiny000621/awesome-bimanual-robot-learning/blob/main/SURVEY.md; checked 2026-09-23. Rapid summary only; existing Evidence Quality is unchanged.</x:v>
+        <x:v>Existing canonical card and official-paper metadata; abstract unavailable; https://github.com/Destiny000621/awesome-bimanual-robot-learning/blob/main/SURVEY.md; 核验于 2026-09-23. 仅为摘要级速读；原 Evidence Quality 不变。 - 核验层级：证据有限；不得视为全文核验</x:v>
       </x:c>
       <x:c r="BX55" t="str">
         <x:v>Unresolved</x:v>
@@ -21837,7 +21837,7 @@
         <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AD56" t="str">
-        <x:v>Embodied intelligence has witnessed remarkable progress in recent years, driven by advances in computer vision, natural language processing, and the rise of large-scale multimodal models.</x:v>
+        <x:v>机器人操作研究横跨视觉、规划、控制和数据，术语与评测不统一。</x:v>
       </x:c>
       <x:c r="AE56" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -21846,7 +21846,7 @@
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
       </x:c>
       <x:c r="AG56" t="str">
-        <x:v>Not specified in checked abstract/card.</x:v>
+        <x:v>已核验摘要未明确说明；需查阅论文方法与实验章节。</x:v>
       </x:c>
       <x:c r="AH56" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -21939,30 +21939,30 @@
       </x:c>
       <x:c r="BM56"/>
       <x:c r="BN56" t="str">
-        <x:v>Evidence-backed — Embodied intelligence has witnessed remarkable progress in recent years, driven by advances in computer vision, natural language processing, and the rise of large-scale multimodal models.</x:v>
+        <x:v>机器人操作研究横跨视觉、规划、控制和数据，术语与评测不统一。</x:v>
       </x:c>
       <x:c r="BO56" t="str">
-        <x:v>Among its core challenges, robot manipulation stands out as a fundamental yet intricate problem, requiring the seamless integration of perception, planning, and control to enable interaction within diverse and unstructured environments.</x:v>
+        <x:v>缺少能连接不同方法和任务的整体框架。</x:v>
       </x:c>
       <x:c r="BP56" t="str">
-        <x:v>Among its core challenges, robot manipulation stands out as a fundamental yet intricate problem, requiring the seamless integration of perception, planning, and control to enable interaction within diverse and unstructured environments.</x:v>
+        <x:v>对机器人操作的任务、技术路线和挑战做综合梳理。</x:v>
       </x:c>
       <x:c r="BQ56" t="str"/>
       <x:c r="BR56" t="str">
-        <x:v>Qualitative or numerical result not established by checked source.</x:v>
+        <x:v>主要贡献是统一视角，不以单一任务数值衡量。</x:v>
       </x:c>
       <x:c r="BS56" t="str">
-        <x:v>Provides a concrete method or benchmark for the documented gap: Among its core challenges, robot manipulation stands out as a fundamental yet intricate problem, requiring the seamless…</x:v>
+        <x:v>便于在文献库中定位 VLA、双臂和 Sim2Real 的关系。</x:v>
       </x:c>
       <x:c r="BT56" t="str">
-        <x:v>Not established by the checked summary source; consult the full paper.</x:v>
+        <x:v>具体方法结论必须回原始论文核验。</x:v>
       </x:c>
       <x:c r="BU56" t="str"/>
       <x:c r="BV56" t="str">
-        <x:v>Medium — useful for method selection, data design and evaluation.</x:v>
+        <x:v>Medium：用于制定阅读顺序与研究问题。</x:v>
       </x:c>
       <x:c r="BW56" t="str">
-        <x:v>Official abstract / paper page; https://arxiv.org/html/2510.10903; checked 2026-09-23. Rapid summary only; existing Evidence Quality is unchanged.</x:v>
+        <x:v>官方摘要/论文页; https://arxiv.org/html/2510.10903; 核验于 2026-09-23. 仅为摘要级速读；原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="BX56" t="str">
         <x:v>Unresolved</x:v>
@@ -22055,7 +22055,7 @@
         <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AD57" t="str">
-        <x:v>With the fast improvement of machine learning, reinforcement learning (RL) has been used to automate human tasks in different areas.</x:v>
+        <x:v>机器人如何从专家示范而非手写奖励中学习技能。</x:v>
       </x:c>
       <x:c r="AE57" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -22064,7 +22064,7 @@
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
       </x:c>
       <x:c r="AG57" t="str">
-        <x:v>Not specified in checked abstract/card.</x:v>
+        <x:v>已核验摘要未明确说明；需查阅论文方法与实验章节。</x:v>
       </x:c>
       <x:c r="AH57" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -22157,30 +22157,30 @@
       </x:c>
       <x:c r="BM57"/>
       <x:c r="BN57" t="str">
-        <x:v>Evidence-backed — With the fast improvement of machine learning, reinforcement learning (RL) has been used to automate human tasks in different areas.</x:v>
+        <x:v>机器人如何从专家示范而非手写奖励中学习技能。</x:v>
       </x:c>
       <x:c r="BO57" t="str">
-        <x:v>However, training such agents is difficult and restricted to expert users.</x:v>
+        <x:v>示范学习方法多样，训练难度和适用条件分散。</x:v>
       </x:c>
       <x:c r="BP57" t="str">
-        <x:v>However, training such agents is difficult and restricted to expert users.</x:v>
+        <x:v>梳理 demonstration learning 的主要方法、训练设置与挑战；具体覆盖范围以论文目录为准。</x:v>
       </x:c>
       <x:c r="BQ57" t="str"/>
       <x:c r="BR57" t="str">
-        <x:v>Qualitative or numerical result not established by checked source.</x:v>
+        <x:v>综述不以单一任务成功率为主要结果；本轮未提取独立实验数字。</x:v>
       </x:c>
       <x:c r="BS57" t="str">
-        <x:v>Provides a concrete method or benchmark for the documented gap: However, training such agents is difficult and restricted to expert users.</x:v>
+        <x:v>帮助选择双臂示范学习基线。</x:v>
       </x:c>
       <x:c r="BT57" t="str">
-        <x:v>Not established by the checked summary source; consult the full paper.</x:v>
+        <x:v>综述中的比较不替代统一数据预算下的复现实验。</x:v>
       </x:c>
       <x:c r="BU57" t="str"/>
       <x:c r="BV57" t="str">
-        <x:v>Medium — useful for method selection, data design and evaluation.</x:v>
+        <x:v>Medium：方法选择相关，需结合真实硬件实验。</x:v>
       </x:c>
       <x:c r="BW57" t="str">
-        <x:v>OpenAlex indexed abstract; https://api.openalex.org/works/W4402510263; checked 2026-09-23. Rapid summary only; existing Evidence Quality is unchanged.</x:v>
+        <x:v>OpenAlex 索引摘要; https://api.openalex.org/works/W4402510263; 核验于 2026-09-23. 仅为摘要级速读；原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="BX57" t="str">
         <x:v>Exact work identity verified</x:v>
@@ -22279,7 +22279,7 @@
         <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AD58" t="str">
-        <x:v>Bimanual manipulation is essential in robotics, yet developing foundation models is extremely challenging due to the inherent complexity of coordinating two robot arms (leading to multi-modal action distributions) and the scarcity of training data.</x:v>
+        <x:v>双臂协调导致动作分布多模态，同时缺少足够训练数据。</x:v>
       </x:c>
       <x:c r="AE58" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -22288,7 +22288,7 @@
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
       </x:c>
       <x:c r="AG58" t="str">
-        <x:v>Not specified in checked abstract/card.</x:v>
+        <x:v>论文的双臂机器人示范与真机评测；具体数据混合见原文。</x:v>
       </x:c>
       <x:c r="AH58" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -22381,30 +22381,30 @@
       </x:c>
       <x:c r="BM58"/>
       <x:c r="BN58" t="str">
-        <x:v>Evidence-backed — Bimanual manipulation is essential in robotics, yet developing foundation models is extremely challenging due to the inherent complexity of coordinating two robot arms (leading to multi-modal action distributions) and the scarcity of training data.</x:v>
+        <x:v>双臂协调导致动作分布多模态，同时缺少足够训练数据。</x:v>
       </x:c>
       <x:c r="BO58" t="str">
-        <x:v>To address data scarcity, we further introduce a Physically Interpretable Unified Action Space, which can unify the action representations of various robots while preserving the physical meanings of original actions, facilitating learning transferrable…</x:v>
+        <x:v>普通单臂策略难直接表示两臂共同运动与接触。</x:v>
       </x:c>
       <x:c r="BP58" t="str">
-        <x:v>In this paper, we present the Robotics Diffusion Transformer (RDT), a pioneering diffusion foundation model for bimanual manipulation.</x:v>
+        <x:v>RDT-1B 用 Robotics Diffusion Transformer 建立双臂操作基础策略，生成协调的双臂动作。</x:v>
       </x:c>
       <x:c r="BQ58" t="str"/>
       <x:c r="BR58" t="str">
-        <x:v>Experiments on real robots demonstrate that RDT significantly outperforms existing methods.</x:v>
+        <x:v>作者报告真机任务中优于所比较方法；摘要未给统一数值。</x:v>
       </x:c>
       <x:c r="BS58" t="str">
-        <x:v>Provides a concrete method or benchmark for the documented gap: To address data scarcity, we further introduce a Physically Interpretable Unified Action Space, which can unify the action…</x:v>
+        <x:v>是项目比较双臂 Diffusion Policy 与 VLA 动作头的核心基线。</x:v>
       </x:c>
       <x:c r="BT58" t="str">
-        <x:v>Not established by the checked summary source; consult the full paper.</x:v>
+        <x:v>不同夹爪、相机和动作空间的可迁移性仍需按原论文与本项目实验核验。</x:v>
       </x:c>
       <x:c r="BU58" t="str"/>
       <x:c r="BV58" t="str">
-        <x:v>High — directly informs dual-arm coordination, data or ordinary-gripper policy design.</x:v>
+        <x:v>High：与双臂普通夹爪和真机操作直接相关。</x:v>
       </x:c>
       <x:c r="BW58" t="str">
-        <x:v>Official abstract / paper page; https://proceedings.iclr.cc/paper_files/paper/2025/hash/49f80e4d2471ad4f2edf4f5f1ab62339-Abstract-Conference.html; checked 2026-09-23. Rapid summary only; existing Evidence Quality is unchanged.</x:v>
+        <x:v>官方摘要/论文页; https://proceedings.iclr.cc/paper_files/paper/2025/hash/49f80e4d2471ad4f2edf4f5f1ab62339-Abstract-Conference.html; 核验于 2026-09-23. 仅为摘要级速读；原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="BX58" t="str">
         <x:v>Unresolved</x:v>
@@ -22503,7 +22503,7 @@
         <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AD59" t="str">
-        <x:v>Vision-language-action models (VLAs) trained on large-scale robotic datasets have demonstrated strong performance on manipulation tasks, including bimanual tasks.</x:v>
+        <x:v>双臂 VLA 训练通常需要昂贵的双臂示范和大模型参数。</x:v>
       </x:c>
       <x:c r="AE59" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -22512,7 +22512,7 @@
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
       </x:c>
       <x:c r="AG59" t="str">
-        <x:v>Not specified in checked abstract/card.</x:v>
+        <x:v>仿真与真机双臂操作任务。</x:v>
       </x:c>
       <x:c r="AH59" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -22605,30 +22605,30 @@
       </x:c>
       <x:c r="BM59"/>
       <x:c r="BN59" t="str">
-        <x:v>Evidence-backed — Vision-language-action models (VLAs) trained on large-scale robotic datasets have demonstrated strong performance on manipulation tasks, including bimanual tasks.</x:v>
+        <x:v>双臂 VLA 训练通常需要昂贵的双臂示范和大模型参数。</x:v>
       </x:c>
       <x:c r="BO59" t="str">
-        <x:v>However, because most public datasets focus on single-arm demonstrations, adapting VLAs for bimanual tasks typically requires substantial additional bimanual data and fine-tuning.</x:v>
+        <x:v>从单臂 VLA 迁移时，两只手臂仍要协调，而不能简单独立执行。</x:v>
       </x:c>
       <x:c r="BP59" t="str">
-        <x:v>To address this challenge, we introduce TwinVLA, a modular framework that composes two copies of a pretrained single-arm VLA into a coordinated bimanual VLA.</x:v>
+        <x:v>TwinVLA 组合两个预训练单臂 VLA，并加入协调机制形成双臂策略。</x:v>
       </x:c>
       <x:c r="BQ59" t="str"/>
       <x:c r="BR59" t="str">
-        <x:v>Across diverse bimanual tasks in real-world and simulation settings, TwinVLA outperforms a comparably-sized monolithic RDT-1B model without requiring *any* bimanual pretraining.</x:v>
+        <x:v>论文报告在若干双臂任务上优于同规模 RDT-1B，而无需双臂预训练；具体任务结果见原文。</x:v>
       </x:c>
       <x:c r="BS59" t="str">
-        <x:v>Provides a concrete method or benchmark for the documented gap: However, because most public datasets focus on single-arm demonstrations, adapting VLAs for bimanual tasks typically requires…</x:v>
+        <x:v>提供低成本复用单臂模型的双臂 VLA 路线。</x:v>
       </x:c>
       <x:c r="BT59" t="str">
-        <x:v>Not established by the checked summary source; consult the full paper.</x:v>
+        <x:v>即使无双臂预训练，协调模块与目标任务示范需求仍需具体核实。</x:v>
       </x:c>
       <x:c r="BU59" t="str"/>
       <x:c r="BV59" t="str">
-        <x:v>High — directly informs dual-arm coordination, data or ordinary-gripper policy design.</x:v>
+        <x:v>High：直接关系到项目未来 VLA 迁移。</x:v>
       </x:c>
       <x:c r="BW59" t="str">
-        <x:v>Official abstract / paper page; https://proceedings.iclr.cc/paper_files/paper/2026/hash/65475a59e2a2cb707c9462e8a308e980-Abstract-Conference.html; checked 2026-09-23. Rapid summary only; existing Evidence Quality is unchanged.</x:v>
+        <x:v>官方摘要/论文页; https://proceedings.iclr.cc/paper_files/paper/2026/hash/65475a59e2a2cb707c9462e8a308e980-Abstract-Conference.html; 核验于 2026-09-23. 仅为摘要级速读；原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="BX59" t="str">
         <x:v>Exact work identity verified</x:v>
@@ -22725,7 +22725,7 @@
         <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AD60" t="str">
-        <x:v>In the rapidly advancing field of robotics, dual-arm coordination and complex object manipulation are essential capabilities for developing advanced autonomous systems.</x:v>
+        <x:v>双臂协调与复杂物体操作缺少足够多样的高质量示范和贴近现实的评测环境。</x:v>
       </x:c>
       <x:c r="AE60" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -22734,7 +22734,7 @@
         <x:v>以 `Bimanual; Benchmark / Synthetic Demonstrations` 为主要方法/能力线索；更细的结构和消融结论待正文核验。</x:v>
       </x:c>
       <x:c r="AG60" t="str">
-        <x:v>作者提供资源下载与示范采集脚本；本轮未下载或核验数据完整性</x:v>
+        <x:v>RoboTwin 含仿真与真实数据；作者提供资源下载和示范采集脚本，本轮未下载核验数据完整性。</x:v>
       </x:c>
       <x:c r="AH60" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -22827,30 +22827,30 @@
       </x:c>
       <x:c r="BM60"/>
       <x:c r="BN60" t="str">
-        <x:v>Evidence-backed — In the rapidly advancing field of robotics, dual-arm coordination and complex object manipulation are essential capabilities for developing advanced autonomous systems.</x:v>
+        <x:v>双臂协调与复杂物体操作缺少足够多样的高质量示范和贴近现实的评测环境。</x:v>
       </x:c>
       <x:c r="BO60" t="str">
-        <x:v>However, the scarcity of diverse, high-quality demonstration data and real-world-aligned evaluation benchmarks severely limits such development.</x:v>
+        <x:v>示范稀缺且仿真评测与真实场景存在差距。</x:v>
       </x:c>
       <x:c r="BP60" t="str">
-        <x:v>To address this, we introduce RoboTwin, a generative digital twin framework that uses 3D generative foundation models and large language models to produce diverse expert datasets and provide a real-world-aligned evaluation platform for dual-arm robotic tasks.</x:v>
+        <x:v>RoboTwin 用 3D 生成模型及大语言模型构建生成式数字孪生，生成专家数据并建立双臂评测平台。</x:v>
       </x:c>
       <x:c r="BQ60" t="str"/>
       <x:c r="BR60" t="str">
-        <x:v>Our framework offers a comprehensive benchmark with both simulated and real-world data, enabling standardized evaluation and better alignment between simulated training and real-world performance.</x:v>
+        <x:v>摘要说明其提供仿真与真实数据的统一评测；具体成功率需查实验章节。</x:v>
       </x:c>
       <x:c r="BS60" t="str">
-        <x:v>Provides a concrete method or benchmark for the documented gap: However, the scarcity of diverse, high-quality demonstration data and real-world-aligned evaluation benchmarks severely limits…</x:v>
+        <x:v>将双臂数据生成与现实对齐评测放入同一框架。</x:v>
       </x:c>
       <x:c r="BT60" t="str">
-        <x:v>Not established by the checked summary source; consult the full paper.</x:v>
+        <x:v>生成数据的物理一致性和真实迁移效果需按论文实验进一步核验。</x:v>
       </x:c>
       <x:c r="BU60" t="str"/>
       <x:c r="BV60" t="str">
-        <x:v>High — directly informs dual-arm coordination, data or ordinary-gripper policy design.</x:v>
+        <x:v>High：与普通夹爪双臂策略的数据和任务设计直接相关。</x:v>
       </x:c>
       <x:c r="BW60" t="str">
-        <x:v>Official abstract / paper page; https://openaccess.thecvf.com/content/CVPR2025/html/Mu_RoboTwin_Dual-Arm_Robot_Benchmark_with_Generative_Digital_Twins_CVPR_2025_paper.html; checked 2026-09-23. Rapid summary only; existing Evidence Quality is unchanged.</x:v>
+        <x:v>官方摘要/论文页; https://openaccess.thecvf.com/content/CVPR2025/html/Mu_RoboTwin_Dual-Arm_Robot_Benchmark_with_Generative_Digital_Twins_CVPR_2025_paper.html; 核验于 2026-09-23. 仅为摘要级速读；原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="BX60" t="str">
         <x:v>Unresolved</x:v>
@@ -22949,7 +22949,7 @@
         <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AD61" t="str">
-        <x:v>Recently, leveraging pre-trained vision-language models (VLMs) for building vision-language-action (VLA) models has emerged as a promising approach to effective robot manipulation learning.</x:v>
+        <x:v>许多 VLA 对三维空间信息的利用不足，影响操作动作的空间准确性与数据效率。</x:v>
       </x:c>
       <x:c r="AE61" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -22958,7 +22958,7 @@
         <x:v>以 `VLA; 3D Manipulation / Data Efficiency` 为主要方法/能力线索；更细的结构和消融结论待正文核验。</x:v>
       </x:c>
       <x:c r="AG61" t="str">
-        <x:v>RLBench, COLOSSEUM, GemBench simulation; real Franka Research 3 with parallel-jaw gripper and ZED 2i camera, 13 tasks with 10 expert trajectories/task (Sec. 7–8).</x:v>
+        <x:v>论文评估 RLBench、COLOSSEUM 与 GemBench；预训练数据和下载入口以官方仓库说明为准。</x:v>
       </x:c>
       <x:c r="AH61" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -23051,30 +23051,30 @@
       </x:c>
       <x:c r="BM61"/>
       <x:c r="BN61" t="str">
-        <x:v>Evidence-backed — Recently, leveraging pre-trained vision-language models (VLMs) for building vision-language-action (VLA) models has emerged as a promising approach to effective robot manipulation learning.</x:v>
+        <x:v>许多 VLA 对三维空间信息的利用不足，影响操作动作的空间准确性与数据效率。</x:v>
       </x:c>
       <x:c r="BO61" t="str">
-        <x:v>However, only few methods incorporate 3D signals into VLMs for action prediction, and they do not fully leverage the spatial structure inherent in 3D data, leading to low data efficiency.</x:v>
+        <x:v>一些 3D VLA 尚未充分利用三维数据自带的空间结构，影响动作预测的数据效率。</x:v>
       </x:c>
       <x:c r="BP61" t="str">
-        <x:v>In this paper, we introduce a new paradigm for constructing 3D VLAs.</x:v>
+        <x:v>BridgeVLA 研究视觉语言模型与三维输入/输出的对齐，让空间结构参与动作预测。</x:v>
       </x:c>
       <x:c r="BQ61" t="str"/>
       <x:c r="BR61" t="str">
-        <x:v>RLBench average success 88.2% vs 81.4%; COLOSSEUM 64.0% vs 56.7%; GemBench average 50.0%; real-world average improvement 32%; 95.4% success on 10+ tasks with 3 trajectories/task (abstract, Tables 1–3, Sec. 8).</x:v>
+        <x:v>卡片记录 RLBench 平均成功率 88.2% 对 81.4%，COLOSSEUM 为 64.0% 对 56.7%；其余数值与实验设定见原卡表格证据。</x:v>
       </x:c>
       <x:c r="BS61" t="str">
-        <x:v>Provides a concrete method or benchmark for the documented gap: However, only few methods incorporate 3D signals into VLMs for action prediction, and they do not fully leverage the spatial…</x:v>
+        <x:v>为 VLA 如何利用三维几何信息提供了可比较的基线。</x:v>
       </x:c>
       <x:c r="BT61" t="str">
-        <x:v>Author-stated/future work — broader 3D input-output alignment and more efficient training remain open (Sec. 5). Library Analysis — only the reported Franka setup was validated.</x:v>
+        <x:v>作者把更充分的 3D 输入/输出对齐与训练效率列为后续方向；当前结果主要验证于报告的 Franka 设置。</x:v>
       </x:c>
       <x:c r="BU61" t="str"/>
       <x:c r="BV61" t="str">
-        <x:v>High — informs language-conditioned manipulation and VLA design.</x:v>
+        <x:v>High：有助于研究语言条件操作与 VLA 设计。</x:v>
       </x:c>
       <x:c r="BW61" t="str">
-        <x:v>Official abstract / paper page; https://arxiv.org/html/2506.07961; checked 2026-09-23. Rapid summary only; existing Evidence Quality is unchanged.</x:v>
+        <x:v>官方摘要/论文页; https://arxiv.org/html/2506.07961; 核验于 2026-09-23. 仅为摘要级速读；原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="BX61" t="str">
         <x:v>Exact work identity verified</x:v>
@@ -23173,7 +23173,7 @@
         <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AD62" t="str">
-        <x:v>Vision-Language-Action (VLA) models have demonstrated strong multi-modal reasoning capabilities, enabling direct action generation from visual perception and language instructions in an end-to-end manner.</x:v>
+        <x:v>VLA 反复处理相似视觉 token，会增加在线推理开销。</x:v>
       </x:c>
       <x:c r="AE62" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -23182,7 +23182,7 @@
         <x:v>以 `VLA; Inference Acceleration / Token Caching` 为主要方法/能力线索；更细的结构和消融结论待正文核验。</x:v>
       </x:c>
       <x:c r="AG62" t="str">
-        <x:v>README提供LIBERO部署评估说明；未确认自采真机数据是否全量公开</x:v>
+        <x:v>LIBERO、SIMPLER 与论文真机设置。</x:v>
       </x:c>
       <x:c r="AH62" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -23275,30 +23275,30 @@
       </x:c>
       <x:c r="BM62"/>
       <x:c r="BN62" t="str">
-        <x:v>Evidence-backed — Vision-Language-Action (VLA) models have demonstrated strong multi-modal reasoning capabilities, enabling direct action generation from visual perception and language instructions in an end-to-end manner.</x:v>
+        <x:v>VLA 反复处理相似视觉 token，会增加在线推理开销。</x:v>
       </x:c>
       <x:c r="BO62" t="str">
-        <x:v>However, their substantial computational cost poses a challenge for real-time robotic control, where rapid decision-making is essential.</x:v>
+        <x:v>简单缓存可能损害变化场景中的目标识别或动作精度。</x:v>
       </x:c>
       <x:c r="BP62" t="str">
-        <x:v>This paper introduces VLA-Cache, a training-free inference acceleration method that reduces computational overhead by adaptively caching and reusing static visual tokens across frames.</x:v>
+        <x:v>VLA-Cache 无需重新训练，按状态自适应缓存并复用部分推理结果。</x:v>
       </x:c>
       <x:c r="BQ62" t="str"/>
       <x:c r="BR62" t="str">
-        <x:v>Extensive experiments on two simulation platforms (LIBERO and SIMPLER) and a real-world robotic system demonstrate that VLA-Cache achieves up to 1.7× speedup in CUDA latency and a 15% increase in control frequency, with negligible loss on task success rate.</x:v>
+        <x:v>作者报告最高约 1.7 倍推理加速；具体成功率影响需按任务核对。</x:v>
       </x:c>
       <x:c r="BS62" t="str">
-        <x:v>Provides a concrete method or benchmark for the documented gap: However, their substantial computational cost poses a challenge for real-time robotic control, where rapid decision-making is…</x:v>
+        <x:v>提供部署已有 VLA 时降低延迟的方法。</x:v>
       </x:c>
       <x:c r="BT62" t="str">
-        <x:v>Not established by the checked summary source; consult the full paper.</x:v>
+        <x:v>场景突变或接触后状态变化时，缓存复用可能延迟纠错。</x:v>
       </x:c>
       <x:c r="BU62" t="str"/>
       <x:c r="BV62" t="str">
-        <x:v>High — informs language-conditioned manipulation and VLA design.</x:v>
+        <x:v>High：双臂实时控制需要低延迟，但必须监测缓存失效。</x:v>
       </x:c>
       <x:c r="BW62" t="str">
-        <x:v>Official abstract / paper page; https://arxiv.org/html/2502.02175; checked 2026-09-23. Rapid summary only; existing Evidence Quality is unchanged.</x:v>
+        <x:v>官方摘要/论文页; https://arxiv.org/html/2502.02175; 核验于 2026-09-23. 仅为摘要级速读；原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="BX62" t="str">
         <x:v>Exact work identity verified</x:v>
@@ -23397,7 +23397,7 @@
         <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AD63" t="str">
-        <x:v>In this paper, we present DiffusionVLA, a novel framework that integrates autoregressive reasoning with diffusion policies to address the limitations of existing methods: while autoregressive Vision-Language-Action (VLA) models lack precise and robust action generation, diffusion-based policies inherently lack reasoning capabilities.</x:v>
+        <x:v>自回归 VLA 的动作精度与鲁棒性可能不足，而独立的扩散策略又缺少语言推理。</x:v>
       </x:c>
       <x:c r="AE63" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -23406,7 +23406,7 @@
         <x:v>以 `VLA; Autoregressive Reasoning / Diffusion` 为主要方法/能力线索；更细的结构和消融结论待正文核验。</x:v>
       </x:c>
       <x:c r="AG63" t="str">
-        <x:v>作者提供DexVLA示例数据：https://huggingface.co/datasets/lesjie/dexvla_example_data；不是原论文全部实验数据</x:v>
+        <x:v>作者提供 DexVLA 示例数据，但该样例不等于论文全部训练和评测数据。</x:v>
       </x:c>
       <x:c r="AH63" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -23499,30 +23499,30 @@
       </x:c>
       <x:c r="BM63"/>
       <x:c r="BN63" t="str">
-        <x:v>Evidence-backed — In this paper, we present DiffusionVLA, a novel framework that integrates autoregressive reasoning with diffusion policies to address the limitations of existing methods: while autoregressive Vision-Language-Action (VLA) models lack precise and robust action generation, diffusion-based policies inherently lack reasoning capabilities.</x:v>
+        <x:v>自回归 VLA 的动作精度与鲁棒性可能不足，而独立的扩散策略又缺少语言推理。</x:v>
       </x:c>
       <x:c r="BO63" t="str">
-        <x:v>Not established in checked summary source.</x:v>
+        <x:v>纯自回归动作预测的精度可能不足；只做扩散控制又较难利用语言推理。</x:v>
       </x:c>
       <x:c r="BP63" t="str">
-        <x:v>DiffusionVLA: Scaling Robot Foundation Models via Unified Diffusion and AutoregressionJunjie Wen, Yichen Zhu, Minjie Zhu, Zhibin Tang, Ji...</x:v>
+        <x:v>DiffusionVLA 将自回归推理与扩散式动作生成结合，尝试兼顾语义理解和连续控制。</x:v>
       </x:c>
       <x:c r="BQ63" t="str"/>
       <x:c r="BR63" t="str">
-        <x:v>63.7% accuracy on 102 previously unseen bin-picking objects; DiVLA-2B runs at 82 Hz on one A6000; scale is evaluated from 2B to 72B (abstract, Sec. 4.5).</x:v>
+        <x:v>卡片记录对 102 个未见抓取物体达到 63.7% 准确率；DiVLA-2B 在单张 A6000 上为 82 Hz（摘要、Sec. 4.5）。</x:v>
       </x:c>
       <x:c r="BS63" t="str">
-        <x:v>High — informs language-conditioned manipulation and VLA design.</x:v>
+        <x:v>为双臂 VLA 动作头选择提供“推理 + 生成式控制”的比较对象。</x:v>
       </x:c>
       <x:c r="BT63" t="str">
-        <x:v>Author-stated — dependence on auto-generated reasoning and limited task/embodiment coverage; Library Analysis — exact per-task failure counts are not fully tabulated in accessible HTML.</x:v>
+        <x:v>实验覆盖的任务与本体有限；逐任务失败次数未从已访问页面完整提取。</x:v>
       </x:c>
       <x:c r="BU63" t="str"/>
       <x:c r="BV63" t="str">
-        <x:v>High — informs language-conditioned manipulation and VLA design.</x:v>
+        <x:v>High：有助于研究语言条件操作与 VLA 设计。</x:v>
       </x:c>
       <x:c r="BW63" t="str">
-        <x:v>Official abstract / paper page; https://proceedings.mlr.press/v267/wen25g.html; checked 2026-09-23. Rapid summary only; existing Evidence Quality is unchanged.</x:v>
+        <x:v>官方摘要/论文页; https://proceedings.mlr.press/v267/wen25g.html; 核验于 2026-09-23. 仅为摘要级速读；原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="BX63" t="str">
         <x:v>Unresolved</x:v>
@@ -23621,7 +23621,7 @@
         <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AD64" t="str">
-        <x:v>2D VLA policies lack explicit 3D physical-world structure and often map perception directly to actions without modeling future dynamics.</x:v>
+        <x:v>现有 2D VLA 缺少显式三维结构，难以同时预测动作和未来场景。</x:v>
       </x:c>
       <x:c r="AE64" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -23630,7 +23630,7 @@
         <x:v>以 `VLA; World Model / 3D Generation` 为主要方法/能力线索；更细的结构和消融结论待正文核验。</x:v>
       </x:c>
       <x:c r="AG64" t="str">
-        <x:v>Large-scale 3D embodied instruction dataset assembled from existing robotics datasets; evaluation is reported on held-in datasets. Exact dataset names and sizes require full paper…</x:v>
+        <x:v>使用从现有机器人数据整理的三维指令数据；具体数据集组成和规模仍需核对全文。</x:v>
       </x:c>
       <x:c r="AH64" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -23725,34 +23725,34 @@
       </x:c>
       <x:c r="BM64"/>
       <x:c r="BN64" t="str">
-        <x:v>Evidence-backed — 2D VLA policies lack explicit 3D physical-world structure and often map perception directly to actions without modeling future dynamics.</x:v>
+        <x:v>现有 2D VLA 缺少显式三维结构，难以同时预测动作和未来场景。</x:v>
       </x:c>
       <x:c r="BO64" t="str">
-        <x:v>Author-stated: existing VLA models underuse 3D relations and world dynamics for planning.</x:v>
+        <x:v>现有 VLA 对三维关系和环境动态的建模不足，难以把动作预测与未来场景变化结合。</x:v>
       </x:c>
       <x:c r="BP64" t="str">
-        <x:v>3D-VLA builds on a 3D-based LLM, introduces action tokens, and aligns embodied diffusion models that predict goal images and point clouds with the language model for planning.</x:v>
+        <x:v>3D-VLA 把三维场景表示、动作 token 与生成未来图像/点云的模型结合，用于语言条件的操作规划。</x:v>
       </x:c>
       <x:c r="BQ64" t="str">
         <x:v>Official PMLR abstract only states held-in dataset improvement; named baselines and metrics require PDF extraction.</x:v>
       </x:c>
       <x:c r="BR64" t="str">
-        <x:v>PMLR reports improved reasoning, multimodality generation and planning on held-in datasets; no numeric values are added from the abstract page alone.</x:v>
+        <x:v>官方 PMLR 页面报告了推理、生成和规划能力的提升；摘要没有足以安全复述的统一量化值。</x:v>
       </x:c>
       <x:c r="BS64" t="str">
-        <x:v>Provides a concrete method or benchmark for the documented gap: Author-stated: existing VLA models underuse 3D relations and world dynamics for planning.</x:v>
+        <x:v>把未来场景预测引入 VLA，是研究三维 Grounding 和长任务规划的参考。</x:v>
       </x:c>
       <x:c r="BT64" t="str">
-        <x:v>Evidence boundary: exact benchmark tables, real-robot coverage and failure cases require full PDF extraction.</x:v>
+        <x:v>当前摘要不足以核实完整 benchmark 表、真机覆盖范围和失败案例，不能据此宣称全面泛化。</x:v>
       </x:c>
       <x:c r="BU64" t="str">
         <x:v>Library Analysis: closed-loop robustness and real dual-arm execution of generated 3D plans remain open.</x:v>
       </x:c>
       <x:c r="BV64" t="str">
-        <x:v>High — informs language-conditioned manipulation and VLA design.</x:v>
+        <x:v>High：有助于研究语言条件操作与 VLA 设计。</x:v>
       </x:c>
       <x:c r="BW64" t="str">
-        <x:v>Official abstract / paper page; https://proceedings.mlr.press/v235/zhen24a.html; checked 2026-09-23. Rapid summary only; existing Evidence Quality is unchanged.</x:v>
+        <x:v>官方摘要/论文页; https://proceedings.mlr.press/v235/zhen24a.html; 核验于 2026-09-23. 仅为摘要级速读；原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="BX64" t="str">
         <x:v>Exact work identity verified</x:v>
@@ -23851,7 +23851,7 @@
         <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AD65" t="str">
-        <x:v>A fundamental objective in robot manipulation is to enable models to comprehend visual scenes and execute actions.</x:v>
+        <x:v>VLA 要兼顾视觉语言推理、动作预测和可承受的微调/推理成本。</x:v>
       </x:c>
       <x:c r="AE65" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -23860,7 +23860,7 @@
         <x:v>以 `VLA; Efficient Model / Pose Prediction` 为主要方法/能力线索；更细的结构和消融结论待正文核验。</x:v>
       </x:c>
       <x:c r="AG65" t="str">
-        <x:v>训练数据发布完整性未确认</x:v>
+        <x:v>训练数据发布完整性尚未确认；仿真与真机评测设置需对照原文。</x:v>
       </x:c>
       <x:c r="AH65" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -23953,30 +23953,30 @@
       </x:c>
       <x:c r="BM65"/>
       <x:c r="BN65" t="str">
-        <x:v>Evidence-backed — A fundamental objective in robot manipulation is to enable models to comprehend visual scenes and execute actions.</x:v>
+        <x:v>VLA 要兼顾视觉语言推理、动作预测和可承受的微调/推理成本。</x:v>
       </x:c>
       <x:c r="BO65" t="str">
-        <x:v>Although existing Vision-Language-Action (VLA) models for robots can handle a range of basic tasks, they still face challenges in two areas: (1) insufficient reasoning ability to tackle complex tasks, and (2) high computational costs for VLA model fine-tuning…</x:v>
+        <x:v>已有 VLA 在复杂任务推理与微调计算成本之间存在权衡。</x:v>
       </x:c>
       <x:c r="BP65" t="str">
-        <x:v>Inspired by this, we introduce RoboMamba, an end-to-end robotic VLA model that leverages Mamba to deliver both robotic reasoning and action capabilities, while maintaining efficient fine-tuning and inference.</x:v>
+        <x:v>RoboMamba 以 Mamba 架构建立端到端 VLA，重点降低适配和在线推理成本。</x:v>
       </x:c>
       <x:c r="BQ65" t="str"/>
       <x:c r="BR65" t="str">
-        <x:v>Meanwhile, our model showcases impressive pose prediction results in both simulation and real-world experiments, achieving inference speeds 3 times faster than existing VLA models.</x:v>
+        <x:v>论文报告在仿真与真机姿态预测任务中优于所比较 VLA，推理速度约为其 3 倍；具体比较对象见原文。</x:v>
       </x:c>
       <x:c r="BS65" t="str">
-        <x:v>Provides a concrete method or benchmark for the documented gap: Although existing Vision-Language-Action (VLA) models for robots can handle a range of basic tasks, they still face challenges in…</x:v>
+        <x:v>可作为部署时的速度—能力权衡参考。</x:v>
       </x:c>
       <x:c r="BT65" t="str">
-        <x:v>Library Analysis — breadth of robot/task coverage is smaller than large generalist policies.</x:v>
+        <x:v>目前证据不足以证明其机器人和任务覆盖达到大型通用策略的广度。</x:v>
       </x:c>
       <x:c r="BU65" t="str"/>
       <x:c r="BV65" t="str">
-        <x:v>High — informs language-conditioned manipulation and VLA design.</x:v>
+        <x:v>High：有助于研究语言条件操作与 VLA 设计。</x:v>
       </x:c>
       <x:c r="BW65" t="str">
-        <x:v>Official abstract / paper page; https://arxiv.org/html/2406.04339; checked 2026-09-23. Rapid summary only; existing Evidence Quality is unchanged.</x:v>
+        <x:v>官方摘要/论文页; https://arxiv.org/html/2406.04339; 核验于 2026-09-23. 仅为摘要级速读；原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="BX65" t="str">
         <x:v>Exact work identity verified</x:v>
@@ -24075,7 +24075,7 @@
         <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AD66" t="str">
-        <x:v>Although large vision-language-action (VLA) models pretrained on extensive robot datasets offer promising generalist policies for robotic learning, they still struggle with spatial-temporal dynamics in interactive robotics, making them less effective in handling complex tasks, such as manipulation.</x:v>
+        <x:v>大规模预训练 VLA 对交互中的时空动态仍可能理解不足。</x:v>
       </x:c>
       <x:c r="AE66" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -24084,7 +24084,7 @@
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
       </x:c>
       <x:c r="AG66" t="str">
-        <x:v>Not specified in checked abstract/card.</x:v>
+        <x:v>SimplerEnv 137 种配置与 WidowX 真机四项任务。</x:v>
       </x:c>
       <x:c r="AH66" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -24177,30 +24177,30 @@
       </x:c>
       <x:c r="BM66"/>
       <x:c r="BN66" t="str">
-        <x:v>Evidence-backed — Although large vision-language-action (VLA) models pretrained on extensive robot datasets offer promising generalist policies for robotic learning, they still struggle with spatial-temporal dynamics in interactive robotics, making them less effective in handling complex tasks, such as manipulation.</x:v>
+        <x:v>大规模预训练 VLA 对交互中的时空动态仍可能理解不足。</x:v>
       </x:c>
       <x:c r="BO66" t="str">
-        <x:v>To further validate the effectiveness and generality of our method, we present a compact VLA model based on 4B Phi-3-Vision, pretrained on the Open-X-Embodiment and finetuned on our dataset, rivals the 7B OpenVLA baseline while significantly improving…</x:v>
+        <x:v>只看当前帧，难表示动作轨迹和目标运动方向。</x:v>
       </x:c>
       <x:c r="BP66" t="str">
-        <x:v>In this work, we introduce visual trace prompting , a simple yet effective approach to facilitate VLA models’ spatial-temporal awareness for action prediction by encoding state-action trajectories visually.</x:v>
+        <x:v>TraceVLA 将状态—动作轨迹可视化为 trace prompt，辅助 VLA 做时空推理与动作预测。</x:v>
       </x:c>
       <x:c r="BQ66" t="str"/>
       <x:c r="BR66" t="str">
-        <x:v>Evaluations of TraceVLA across 137 configurations in SimplerEnv and 4 tasks on a physical WidowX robot demonstrate state-of-the-art performance, outperforming OpenVLA by 10% on SimplerEnv and 3.5x on real-robot tasks and exhibiting robust generalization…</x:v>
+        <x:v>卡片记录相对 OpenVLA 在 SimplerEnv 高约 10%，真机任务表现约为 3.5 倍；指标定义见原卡。</x:v>
       </x:c>
       <x:c r="BS66" t="str">
-        <x:v>Provides a concrete method or benchmark for the documented gap: To further validate the effectiveness and generality of our method, we present a compact VLA model based on 4B Phi-3-Vision…</x:v>
+        <x:v>为视觉轨迹提示如何改善 VLA 提供可测实例。</x:v>
       </x:c>
       <x:c r="BT66" t="str">
-        <x:v>Not established by the checked summary source; consult the full paper.</x:v>
+        <x:v>单臂 WidowX 结果不直接覆盖双臂真机。</x:v>
       </x:c>
       <x:c r="BU66" t="str"/>
       <x:c r="BV66" t="str">
-        <x:v>High — informs language-conditioned manipulation and VLA design.</x:v>
+        <x:v>High：双臂任务可以比较轨迹提示与显式状态估计。</x:v>
       </x:c>
       <x:c r="BW66" t="str">
-        <x:v>Official abstract / paper page; https://arxiv.org/html/2412.10345; checked 2026-09-23. Rapid summary only; existing Evidence Quality is unchanged.</x:v>
+        <x:v>官方摘要/论文页; https://arxiv.org/html/2412.10345; 核验于 2026-09-23. 仅为摘要级速读；原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="BX66" t="str">
         <x:v>Unresolved</x:v>
@@ -24299,7 +24299,7 @@
         <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AD67" t="str">
-        <x:v>We introduce Latent Action Pretraining for general Action models (LAPA), the first unsupervised method for pretraining Vision-Language-Action (VLA) models without ground-truth robot action labels.</x:v>
+        <x:v>互联网视频规模大，但缺少机器人动作标签。</x:v>
       </x:c>
       <x:c r="AE67" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -24308,7 +24308,7 @@
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
       </x:c>
       <x:c r="AG67" t="str">
-        <x:v>Not specified in checked abstract/card.</x:v>
+        <x:v>已核验摘要未明确说明；需查阅论文方法与实验章节。</x:v>
       </x:c>
       <x:c r="AH67" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -24401,30 +24401,30 @@
       </x:c>
       <x:c r="BM67"/>
       <x:c r="BN67" t="str">
-        <x:v>Evidence-backed — We introduce Latent Action Pretraining for general Action models (LAPA), the first unsupervised method for pretraining Vision-Language-Action (VLA) models without ground-truth robot action labels.</x:v>
+        <x:v>互联网视频规模大，但缺少机器人动作标签。</x:v>
       </x:c>
       <x:c r="BO67" t="str">
-        <x:v>Not established in checked summary source.</x:v>
+        <x:v>传统 VLA 预训练高度依赖昂贵的机器人动作数据。</x:v>
       </x:c>
       <x:c r="BP67" t="str">
-        <x:v>In this work, we propose a method to learn from internet-scale videos that do not have robot action labels.</x:v>
+        <x:v>LAPA 从无动作标签视频学习潜在动作，再用这些表示预训练视觉语言动作模型。</x:v>
       </x:c>
       <x:c r="BQ67" t="str"/>
       <x:c r="BR67" t="str">
-        <x:v>Furthermore, it outperforms the state-of-the-art VLA model trained with robotic action labels on real-world manipulation tasks that require language conditioning, generalization to unseen objects, and semantic generalization to unseen instructions.</x:v>
+        <x:v>作者报告部分真机操作任务上优于使用机器人动作标签训练的对照 VLA；具体协议见论文。</x:v>
       </x:c>
       <x:c r="BS67" t="str">
-        <x:v>High — informs language-conditioned manipulation and VLA design.</x:v>
+        <x:v>提供低成本视频数据进入 VLA 预训练的路线。</x:v>
       </x:c>
       <x:c r="BT67" t="str">
-        <x:v>Not established by the checked summary source; consult the full paper.</x:v>
+        <x:v>潜在动作与真实普通夹爪命令之间需要可靠解码。</x:v>
       </x:c>
       <x:c r="BU67" t="str"/>
       <x:c r="BV67" t="str">
-        <x:v>High — informs language-conditioned manipulation and VLA design.</x:v>
+        <x:v>High：双臂示范稀缺，可研究潜在动作是否可迁移。</x:v>
       </x:c>
       <x:c r="BW67" t="str">
-        <x:v>Official abstract / paper page; https://proceedings.iclr.cc/paper_files/paper/2025/hash/45d74e190008c7bff2845ffc8e3facd3-Abstract-Conference.html; checked 2026-09-23. Rapid summary only; existing Evidence Quality is unchanged.</x:v>
+        <x:v>官方摘要/论文页; https://proceedings.iclr.cc/paper_files/paper/2025/hash/45d74e190008c7bff2845ffc8e3facd3-Abstract-Conference.html; 核验于 2026-09-23. 仅为摘要级速读；原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="BX67" t="str">
         <x:v>Unresolved</x:v>
@@ -24521,7 +24521,7 @@
         <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AD68" t="str">
-        <x:v>Iterative action generation can be too slow for responsive manipulation.</x:v>
+        <x:v>扩散/流式动作生成往往需要多次采样，在线控制延迟较高。</x:v>
       </x:c>
       <x:c r="AE68" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -24530,7 +24530,7 @@
         <x:v>以 `Robot Manipulation; Consistency Flow Matching / 3D Policy` 为主要方法/能力线索；更细的结构和消融结论待正文核验。</x:v>
       </x:c>
       <x:c r="AG68" t="str">
-        <x:v>提供Adroit/MetaWorld示范生成脚本与说明；未下载数据</x:v>
+        <x:v>Adroit、MetaWorld。</x:v>
       </x:c>
       <x:c r="AH68" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -24623,30 +24623,30 @@
       </x:c>
       <x:c r="BM68"/>
       <x:c r="BN68" t="str">
-        <x:v>Evidence-backed — Iterative action generation can be too slow for responsive manipulation.</x:v>
+        <x:v>扩散/流式动作生成往往需要多次采样，在线控制延迟较高。</x:v>
       </x:c>
       <x:c r="BO68" t="str">
-        <x:v>Not established in checked summary source.</x:v>
+        <x:v>生成质量与推理速度之间存在权衡。</x:v>
       </x:c>
       <x:c r="BP68" t="str">
-        <x:v>官方题名与元数据已确认；具体表述待补读官方摘要或正文。</x:v>
+        <x:v>FlowPolicy 使用三维点云和 consistency flow matching，在单次推理中生成动作。</x:v>
       </x:c>
       <x:c r="BQ68" t="str"/>
       <x:c r="BR68" t="str">
-        <x:v>Adroit and MetaWorld evaluations report competitive manipulation performance with sevenfold faster inference.</x:v>
+        <x:v>AAAI 摘要报告在 Adroit 与 MetaWorld 上保持有竞争力的成功率，同时推理速度提高约 7 倍。</x:v>
       </x:c>
       <x:c r="BS68" t="str">
-        <x:v>Medium — relevant to robot manipulation; transfer to dual-arm real hardware needs validation.</x:v>
+        <x:v>双臂真机尤其关注动作频率；该工作可用于比较速度与成功率。</x:v>
       </x:c>
       <x:c r="BT68" t="str">
-        <x:v>Not established by the checked summary source; consult the full paper.</x:v>
+        <x:v>本段基于官方摘要；未覆盖全文失败案例、完整 Baseline 与方法消融。</x:v>
       </x:c>
       <x:c r="BU68" t="str"/>
       <x:c r="BV68" t="str">
-        <x:v>Medium — relevant to robot manipulation; transfer to dual-arm real hardware needs validation.</x:v>
+        <x:v>Medium：方法可借鉴，但迁移到当前双臂硬件需验证。</x:v>
       </x:c>
       <x:c r="BW68" t="str">
-        <x:v>Official abstract / paper page; https://ojs.aaai.org/index.php/AAAI/article/view/33617; checked 2026-09-23. Rapid summary only; existing Evidence Quality is unchanged.</x:v>
+        <x:v>官方摘要/论文页：https://ojs.aaai.org/index.php/AAAI/article/view/33617；核验于 2026-09-23。仅为摘要级速读，原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="BX68" t="str">
         <x:v>Unresolved</x:v>
@@ -24745,7 +24745,7 @@
         <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AD69" t="str">
-        <x:v>We introduce UniGraspTransformer, a universal Transformer-based network for dexterous robotic grasping that simplifies training while enhancing scalability and performance.</x:v>
+        <x:v>通用灵巧手抓取需要在不同物体类别上预测稳定抓法。</x:v>
       </x:c>
       <x:c r="AE69" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -24754,7 +24754,7 @@
         <x:v>以 `Dexterous Hand; Policy Distillation / Generali</x:v>
       </x:c>
       <x:c r="AG69" t="str">
-        <x:v>提供资产/抓取初始化数据链接和生成轨迹步骤；未下载</x:v>
+        <x:v>已核验摘要未明确说明；需查阅论文方法与实验章节。</x:v>
       </x:c>
       <x:c r="AH69" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -24847,30 +24847,30 @@
       </x:c>
       <x:c r="BM69"/>
       <x:c r="BN69" t="str">
-        <x:v>Evidence-backed — We introduce UniGraspTransformer, a universal Transformer-based network for dexterous robotic grasping that simplifies training while enhancing scalability and performance.</x:v>
+        <x:v>通用灵巧手抓取需要在不同物体类别上预测稳定抓法。</x:v>
       </x:c>
       <x:c r="BO69" t="str">
-        <x:v>Unlike prior methods such as UniDexGrasp++, which require complex, multi-step training pipelines, UniGraspTransformer follows a streamlined process: first, dedicated policy networks are trained for individual objects using reinforcement learning to generate…</x:v>
+        <x:v>复杂训练流程和手型依赖限制方法复用。</x:v>
       </x:c>
       <x:c r="BP69" t="str">
-        <x:v>We introduce UniGraspTransformer, a universal Transformer-based network for dexterous robotic grasping that simplifies training while enhancing scalability and performance.</x:v>
+        <x:v>UniGraspTransformer 用统一的 Transformer 网络预测灵巧抓取，并简化训练过程。</x:v>
       </x:c>
       <x:c r="BQ69" t="str"/>
       <x:c r="BR69" t="str">
-        <x:v>Experimental results demonstrate significant improvements over state-of-the-art, UniDexGrasp++, across various object categories, achieving success rate gains of 3.5%, 7.7%, and 10.1% on seen objects, unseen objects within seen categories, and completely…</x:v>
+        <x:v>作者报告在多个物体类别上优于 UniDexGrasp++；具体成功率需查实验表。</x:v>
       </x:c>
       <x:c r="BS69" t="str">
-        <x:v>Provides a concrete method or benchmark for the documented gap: Unlike prior methods such as UniDexGrasp++, which require complex, multi-step training pipelines, UniGraspTransformer follows a…</x:v>
+        <x:v>提供跨物体抓取模型的简洁架构基线。</x:v>
       </x:c>
       <x:c r="BT69" t="str">
-        <x:v>Not established by the checked summary source; consult the full paper.</x:v>
+        <x:v>灵巧手抓取 benchmark 与双臂真机任务仍有差距。</x:v>
       </x:c>
       <x:c r="BU69" t="str"/>
       <x:c r="BV69" t="str">
-        <x:v>Medium — transferable learning ideas may apply, but the hand hardware differs from ordinary grippers.</x:v>
+        <x:v>Medium：模型结构可参考，但需重做普通夹爪动作输出。</x:v>
       </x:c>
       <x:c r="BW69" t="str">
-        <x:v>Official abstract / paper page; https://openaccess.thecvf.com/content/CVPR2025/html/Wang_UniGraspTransformer_Simplified_Policy_Distillation_for_Scalable_Dexterous_Robotic_Grasping_CVPR_2025_paper.html; checked 2026-09-23. Rapid summary only; existing Evidence Quality is unchanged.</x:v>
+        <x:v>官方摘要/论文页; https://openaccess.thecvf.com/content/CVPR2025/html/Wang_UniGraspTransformer_Simplified_Policy_Distillation_for_Scalable_Dexterous_Robotic_Grasping_CVPR_2025_paper.html; 核验于 2026-09-23. 仅为摘要级速读；原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="BX69" t="str">
         <x:v>Exact work identity verified</x:v>
@@ -24969,7 +24969,7 @@
         <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AD70" t="str">
-        <x:v>Dexterous robotic hands are essential for performing complex manipulation tasks, yet remain difficult to train due to the challenges of demonstration collection and high-dimensional control.</x:v>
+        <x:v>灵巧手操作数据和训练成本高，复杂任务还需要语义理解。</x:v>
       </x:c>
       <x:c r="AE70" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -24978,7 +24978,7 @@
         <x:v>以 `Dexterous Hand; Residual RL / VLM Planning` 为主要方法/能力线索；更细的结构和消融结论待正文核验。</x:v>
       </x:c>
       <x:c r="AG70" t="str">
-        <x:v>公开数据生成实现与任务资产；不等于所有论文轨迹均已提供</x:v>
+        <x:v>已核验摘要未明确说明；需查阅论文方法与实验章节。</x:v>
       </x:c>
       <x:c r="AH70" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -25071,30 +25071,30 @@
       </x:c>
       <x:c r="BM70"/>
       <x:c r="BN70" t="str">
-        <x:v>Evidence-backed — Dexterous robotic hands are essential for performing complex manipulation tasks, yet remain difficult to train due to the challenges of demonstration collection and high-dimensional control.</x:v>
+        <x:v>灵巧手操作数据和训练成本高，复杂任务还需要语义理解。</x:v>
       </x:c>
       <x:c r="BO70" t="str">
-        <x:v>While reinforcement learning (RL) can alleviate the data bottleneck by generating experience in simulation, it typically relies on carefully designed, task-specific reward functions, which hinder scalability and generalization.</x:v>
+        <x:v>纯低层策略难从少量示范组织多步任务。</x:v>
       </x:c>
       <x:c r="BP70" t="str">
-        <x:v>Dexterous robotic hands are essential for performing complex manipulation tasks, yet remain difficult to train due to the challenges of demonstration collection and high-dimensional control.</x:v>
+        <x:v>用 VLM 提供高层任务结构和语义线索，支撑灵巧手低层操作学习。</x:v>
       </x:c>
       <x:c r="BQ70" t="str"/>
       <x:c r="BR70" t="str">
-        <x:v>Across a number of simulated tasks involving articulated objects and semantic understanding, we demonstrate that our method is able to learn robust dexterous manipulation policies.</x:v>
+        <x:v>论文报告在关节物体及语义理解仿真任务中验证方法；具体数值需查正文。</x:v>
       </x:c>
       <x:c r="BS70" t="str">
-        <x:v>Provides a concrete method or benchmark for the documented gap: While reinforcement learning (RL) can alleviate the data bottleneck by generating experience in simulation, it typically relies…</x:v>
+        <x:v>展示 VLM 规划与低层动作之间的接口问题。</x:v>
       </x:c>
       <x:c r="BT70" t="str">
-        <x:v>Not established by the checked summary source; consult the full paper.</x:v>
+        <x:v>仿真灵巧手结果不能直接推断双臂真机表现。</x:v>
       </x:c>
       <x:c r="BU70" t="str"/>
       <x:c r="BV70" t="str">
-        <x:v>Medium — transferable learning ideas may apply, but the hand hardware differs from ordinary grippers.</x:v>
+        <x:v>Medium：双臂普通夹爪也需要高低层协作。</x:v>
       </x:c>
       <x:c r="BW70" t="str">
-        <x:v>Official abstract / paper page; https://proceedings.neurips.cc/paper_files/paper/2025/hash/862644b156e51c35dea5a7446d640b14-Abstract-Conference.html; checked 2026-09-23. Rapid summary only; existing Evidence Quality is unchanged.</x:v>
+        <x:v>官方摘要/论文页; https://proceedings.neurips.cc/paper_files/paper/2025/hash/862644b156e51c35dea5a7446d640b14-Abstract-Conference.html; 核验于 2026-09-23. 仅为摘要级速读；原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="BX70" t="str">
         <x:v>Exact work identity verified</x:v>
@@ -25193,7 +25193,7 @@
         <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AD71" t="str">
-        <x:v>Generalization in robot manipulation is essential for deploying robots in open-world environments and advancing toward artificial general intelligence.</x:v>
+        <x:v>开放环境操作需要预见动作后果并适应新场景。</x:v>
       </x:c>
       <x:c r="AE71" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -25202,7 +25202,7 @@
         <x:v>以 `VLA; Video-Action Model / Generali</x:v>
       </x:c>
       <x:c r="AG71" t="str">
-        <x:v>README未提供完整论文训练数据准备流程</x:v>
+        <x:v>已核验摘要未明确说明；需查阅论文方法与实验章节。</x:v>
       </x:c>
       <x:c r="AH71" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -25295,30 +25295,30 @@
       </x:c>
       <x:c r="BM71"/>
       <x:c r="BN71" t="str">
-        <x:v>Evidence-backed — Generalization in robot manipulation is essential for deploying robots in open-world environments and advancing toward artificial general intelligence.</x:v>
+        <x:v>开放环境操作需要预见动作后果并适应新场景。</x:v>
       </x:c>
       <x:c r="BO71" t="str">
-        <x:v>While recent Vision-Language-Action (VLA) models leverage large pre-trained understanding models for perception and instruction following, their ability to generalize to novel tasks, objects, and settings remains limited.</x:v>
+        <x:v>只从当前视觉预测动作，可能缺少对未来状态的理解。</x:v>
       </x:c>
       <x:c r="BP71" t="str">
-        <x:v>In this work, we present VideoVLA, a simple approach that explores the potential of transforming large video generation models into robotic VLA manipulators.</x:v>
+        <x:v>VideoVLA 将视频生成模型用于 VLA，利用想象的未来画面帮助动作选择。</x:v>
       </x:c>
       <x:c r="BQ71" t="str"/>
       <x:c r="BR71" t="str">
-        <x:v>Our experiments show that high-quality imagined futures correlate with reliable action predictions and task success, highlighting the importance of visual imagination in manipulation.</x:v>
+        <x:v>作者报告想象未来质量与动作可靠性、任务成功相关；具体数字见实验章节。</x:v>
       </x:c>
       <x:c r="BS71" t="str">
-        <x:v>Provides a concrete method or benchmark for the documented gap: While recent Vision-Language-Action (VLA) models leverage large pre-trained understanding models for perception and instruction…</x:v>
+        <x:v>把世界模型式视觉预期与机器人动作生成连接起来。</x:v>
       </x:c>
       <x:c r="BT71" t="str">
-        <x:v>Author-stated — video generation cost and action-video alignment; Library Analysis — benchmark breadth and code maturity require follow-up.</x:v>
+        <x:v>视频看起来合理不一定代表接触力与夹爪动作正确。</x:v>
       </x:c>
       <x:c r="BU71" t="str"/>
       <x:c r="BV71" t="str">
-        <x:v>High — informs language-conditioned manipulation and VLA design.</x:v>
+        <x:v>High：可用于双臂动作前预期与动作后验证。</x:v>
       </x:c>
       <x:c r="BW71" t="str">
-        <x:v>Official abstract / paper page; https://arxiv.org/html/2512.06963; checked 2026-09-23. Rapid summary only; existing Evidence Quality is unchanged.</x:v>
+        <x:v>官方摘要/论文页; https://arxiv.org/html/2512.06963; 核验于 2026-09-23. 仅为摘要级速读；原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="BX71" t="str">
         <x:v>Exact work identity verified</x:v>
@@ -25417,7 +25417,7 @@
         <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AD72" t="str">
-        <x:v>Language-driven dexterous grasp generation requires the models to understand task semantics, 3D geometry, and complex hand-object interactions.</x:v>
+        <x:v>语言驱动的灵巧抓取要同时理解任务语义、三维几何和接触关系。</x:v>
       </x:c>
       <x:c r="AE72" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -25426,7 +25426,7 @@
         <x:v>以 `Dexterous Hand; Contact Reasoning / Language-guided Grasp` 为主要方法/能力线索；更细的结构和消融结论待正文核验。</x:v>
       </x:c>
       <x:c r="AG72" t="str">
-        <x:v>作者提供预处理数据：https://huggingface.co/datasets/EunhaPark/project_dexter；未下载</x:v>
+        <x:v>DexGYS。</x:v>
       </x:c>
       <x:c r="AH72" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -25519,30 +25519,30 @@
       </x:c>
       <x:c r="BM72"/>
       <x:c r="BN72" t="str">
-        <x:v>Evidence-backed — Language-driven dexterous grasp generation requires the models to understand task semantics, 3D geometry, and complex hand-object interactions.</x:v>
+        <x:v>语言驱动的灵巧抓取要同时理解任务语义、三维几何和接触关系。</x:v>
       </x:c>
       <x:c r="BO72" t="str">
-        <x:v>While vision-language models have been applied to this problem, existing approaches directly map observations to grasp parameters without intermediate reasoning about physical interactions.</x:v>
+        <x:v>只预测抓取位姿未必符合语言中隐含的使用目的。</x:v>
       </x:c>
       <x:c r="BP72" t="str">
-        <x:v>We present DextER, Dexterous Grasp Generation with Embodied Reasoning, which introduces contact-based embodied reasoning for multi-finger manipulation.</x:v>
+        <x:v>DextER 在抓取生成中加入基于接触的具身推理，使手部接触与任务意图对齐。</x:v>
       </x:c>
       <x:c r="BQ72" t="str"/>
       <x:c r="BR72" t="str">
-        <x:v>On DexGYS, DextER achieves 67.14% success rate, outperforming state-of-the-art by 3.83 p.p. with 96.4% improvement in intention alignment.</x:v>
+        <x:v>卡片记录 DexGYS 成功率 67.14%，较所比较 SOTA 高 3.83 个百分点。</x:v>
       </x:c>
       <x:c r="BS72" t="str">
-        <x:v>Provides a concrete method or benchmark for the documented gap: While vision-language models have been applied to this problem, existing approaches directly map observations to grasp parameters…</x:v>
+        <x:v>将语言 Grounding 与可执行接触联系起来。</x:v>
       </x:c>
       <x:c r="BT72" t="str">
-        <x:v>Not established by the checked summary source; consult the full paper.</x:v>
+        <x:v>从多指接触迁移到两只普通夹爪需重新定义动作空间。</x:v>
       </x:c>
       <x:c r="BU72" t="str"/>
       <x:c r="BV72" t="str">
-        <x:v>Medium — transferable learning ideas may apply, but the hand hardware differs from ordinary grippers.</x:v>
+        <x:v>Medium：普通夹爪也需要意图对齐，但手部接触自由度不同。</x:v>
       </x:c>
       <x:c r="BW72" t="str">
-        <x:v>Official abstract / paper page; https://openaccess.thecvf.com/content/CVPR2026/html/Lee_DextER_Language-driven_Dexterous_Grasp_Generation_with_Embodied_Reasoning_CVPR_2026_paper.html; checked 2026-09-23. Rapid summary only; existing Evidence Quality is unchanged.</x:v>
+        <x:v>官方摘要/论文页; https://openaccess.thecvf.com/content/CVPR2026/html/Lee_DextER_Language-driven_Dexterous_Grasp_Generation_with_Embodied_Reasoning_CVPR_2026_paper.html; 核验于 2026-09-23. 仅为摘要级速读；原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="BX72" t="str">
         <x:v>Exact work identity verified</x:v>
@@ -25641,7 +25641,7 @@
         <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AD73" t="str">
-        <x:v>In this paper, we claim that spatial understanding is the keypoint in robot manipulation, and propose SpatialVLA to explore effective spatial representations for the robot foundation model.</x:v>
+        <x:v>机器人操作需要把视觉与语言理解落实到三维空间关系。</x:v>
       </x:c>
       <x:c r="AE73" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -25650,7 +25650,7 @@
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
       </x:c>
       <x:c r="AG73" t="str">
-        <x:v>Not specified in checked abstract/card.</x:v>
+        <x:v>已核验摘要未明确说明；需查阅论文方法与实验章节。</x:v>
       </x:c>
       <x:c r="AH73" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -25743,30 +25743,30 @@
       </x:c>
       <x:c r="BM73"/>
       <x:c r="BN73" t="str">
-        <x:v>Evidence-backed — In this paper, we claim that spatial understanding is the keypoint in robot manipulation, and propose SpatialVLA to explore effective spatial representations for the robot foundation model.</x:v>
+        <x:v>机器人操作需要把视觉与语言理解落实到三维空间关系。</x:v>
       </x:c>
       <x:c r="BO73" t="str">
-        <x:v>Not established in checked summary source.</x:v>
+        <x:v>普通 VLA 的视觉 token 可能缺少显式三维位置线索。</x:v>
       </x:c>
       <x:c r="BP73" t="str">
-        <x:v>Specifically, we introduce Ego3D Position Encoding to inject 3D information into the input observations of the visual-language-action model, and propose Adaptive Action Grids to represent spatial robot movement actions with adaptive discretized action grids, facilitating learning generalizable and transferrable spatial action knowledge for cross-robot…</x:v>
+        <x:v>SpatialVLA 加入 Ego3D Position Encoding，使空间信息参与 VLA 输入和动作预测。</x:v>
       </x:c>
       <x:c r="BQ73" t="str"/>
       <x:c r="BR73" t="str">
-        <x:v>The superior results from extensive evaluations demonstrate the exceptional in-distribution generalization and out-of-distribution adaptation capability, highlighting the crucial benefit of the proposed spatial-aware representations for generalist robot…</x:v>
+        <x:v>作者报告较好的分布内泛化和分布外适配；具体比较数字见论文。</x:v>
       </x:c>
       <x:c r="BS73" t="str">
-        <x:v>High — informs language-conditioned manipulation and VLA design.</x:v>
+        <x:v>为 VLA 的三维 Grounding 提供明确的表示方案。</x:v>
       </x:c>
       <x:c r="BT73" t="str">
-        <x:v>Not established by the checked summary source; consult the full paper.</x:v>
+        <x:v>需要检验相机标定变化与遮挡下的稳健性。</x:v>
       </x:c>
       <x:c r="BU73" t="str"/>
       <x:c r="BV73" t="str">
-        <x:v>High — informs language-conditioned manipulation and VLA design.</x:v>
+        <x:v>High：双臂普通夹爪需要准确的目标与相对位姿。</x:v>
       </x:c>
       <x:c r="BW73" t="str">
-        <x:v>Official abstract / paper page; https://arxiv.org/html/2501.15830; checked 2026-09-23. Rapid summary only; existing Evidence Quality is unchanged.</x:v>
+        <x:v>官方摘要/论文页; https://arxiv.org/html/2501.15830; 核验于 2026-09-23. 仅为摘要级速读；原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="BX73" t="str">
         <x:v>Exact work identity verified</x:v>
@@ -25865,7 +25865,7 @@
         <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AD74" t="str">
-        <x:v>Large policies pretrained on a combination of Internet-scale vision-language data and diverse robot demonstrations have the potential to change how we teach robots new skills: rather than training new behaviors from scratch, we can fine-tune such vision-language-action (VLA) models to obtain robust, generalizable policies for visuomotor control.</x:v>
+        <x:v>现有 VLA 多为闭源，且针对新任务高效微调的方法仍不充分。</x:v>
       </x:c>
       <x:c r="AE74" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -25874,7 +25874,7 @@
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
       </x:c>
       <x:c r="AG74" t="str">
-        <x:v>curated Open X-Embodiment mixture with 970k real-world trajectories, third-person views and single-arm end-effector control; DROID was removed from the final third of training…</x:v>
+        <x:v>训练使用整理后的 Open X-Embodiment 混合数据，约 97 万条真机轨迹；DROID 在后期训练数据中被剔除，详见原卡。</x:v>
       </x:c>
       <x:c r="AH74" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -25967,30 +25967,30 @@
       </x:c>
       <x:c r="BM74"/>
       <x:c r="BN74" t="str">
-        <x:v>Evidence-backed — Large policies pretrained on a combination of Internet-scale vision-language data and diverse robot demonstrations have the potential to change how we teach robots new skills: rather than training new behaviors from scratch, we can fine-tune such vision-language-action (VLA) models to obtain robust, generalizable policies for visuomotor control.</x:v>
+        <x:v>现有 VLA 多为闭源，且针对新任务高效微调的方法仍不充分。</x:v>
       </x:c>
       <x:c r="BO74" t="str">
-        <x:v>Yet, widespread adoption of VLAs for robotics has been challenging as 1) existing VLAs are largely closed and inaccessible to the public, and 2) prior work fails to explore methods for efficiently fine-tuning VLAs for new tasks, a key component for adoption.</x:v>
+        <x:v>既有 VLA 多为闭源，新任务的高效微调方法也缺少系统评估。</x:v>
       </x:c>
       <x:c r="BP74" t="str">
-        <x:v>Addressing these challenges, we introduce OpenVLA, a 7B-parameter open-source VLA trained on a diverse collection of 970k real-world robot demonstrations.</x:v>
+        <x:v>OpenVLA 是开放的 7B VLA，在约 97 万条真实机器人轨迹上训练，支持通过微调适配新任务。</x:v>
       </x:c>
       <x:c r="BQ74" t="str"/>
       <x:c r="BR74" t="str">
-        <x:v>+16.5 percentage points absolute success over 55B RT-2-X across 29 tasks/embodiments; +20.4% over Diffusion Policy in reported fine-tuning settings; 27 epochs, 64 A100s for 14 days, ~21,500 A100-hours; inference ~6 Hz on RTX 4090 with 15GB bfloat16 memory…</x:v>
+        <x:v>卡片记录在 29 项任务/本体评测中相对 55B RT-2-X 的成功率高 16.5 个百分点；微调设置下相对 Diffusion Policy 高 20.4 个百分点。推理约 6 Hz（RTX 4090）；比较条件详见原卡。</x:v>
       </x:c>
       <x:c r="BS74" t="str">
-        <x:v>Provides a concrete method or benchmark for the documented gap: Yet, widespread adoption of VLAs for robotics has been challenging as 1) existing VLAs are largely closed and inaccessible to the…</x:v>
+        <x:v>提供可复用的 VLA 基线，同时明确了数据、算力和推理速度代价。</x:v>
       </x:c>
       <x:c r="BT74" t="str">
-        <x:v>Author-stated — training data is restricted to single-arm/third-person configurations and the model still requires substantial compute; Library Analysis — bimanual/mobile transfer is not established.</x:v>
+        <x:v>作者指出训练数据偏单臂、第三人称视角且算力成本高；双臂/移动平台迁移仍需单独验证。</x:v>
       </x:c>
       <x:c r="BU74" t="str"/>
       <x:c r="BV74" t="str">
-        <x:v>High — informs language-conditioned manipulation and VLA design.</x:v>
+        <x:v>High：有助于研究语言条件操作与 VLA 设计。</x:v>
       </x:c>
       <x:c r="BW74" t="str">
-        <x:v>Official abstract / paper page; https://arxiv.org/html/2406.09246; checked 2026-09-23. Rapid summary only; existing Evidence Quality is unchanged.</x:v>
+        <x:v>官方摘要/论文页; https://arxiv.org/html/2406.09246; 核验于 2026-09-23. 仅为摘要级速读；原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="BX74" t="str">
         <x:v>Exact work identity verified</x:v>
@@ -26089,7 +26089,7 @@
         <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AD75" t="str">
-        <x:v>Large policies pretrained on diverse robot datasets have the potential to transform robotic learning: instead of training new policies from scratch, such generalist robot policies may be finetuned with only a little in-domain data, yet generalize broadly.</x:v>
+        <x:v>通用机器人策略需要同时适配不同相机、动作空间和机器人平台。</x:v>
       </x:c>
       <x:c r="AE75" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -26098,7 +26098,7 @@
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
       </x:c>
       <x:c r="AG75" t="str">
-        <x:v>Open X-Embodiment contains ~1.5M episodes; Octo curates 800k. Zero-shot and finetuning evaluations cover WidowX BridgeV2, UR5, RT-1 and six downstream tasks (Secs. II–IV, App. F).</x:v>
+        <x:v>从 Open X-Embodiment 整理约 80 万条训练轨迹，在 9 种机器人平台和多项下游任务上评估。</x:v>
       </x:c>
       <x:c r="AH75" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -26191,30 +26191,30 @@
       </x:c>
       <x:c r="BM75"/>
       <x:c r="BN75" t="str">
-        <x:v>Evidence-backed — Large policies pretrained on diverse robot datasets have the potential to transform robotic learning: instead of training new policies from scratch, such generalist robot policies may be finetuned with only a little in-domain data, yet generalize broadly.</x:v>
+        <x:v>通用机器人策略需要同时适配不同相机、动作空间和机器人平台。</x:v>
       </x:c>
       <x:c r="BO75" t="str">
-        <x:v>However, to be widely applicable across a range of robotic learning scenarios, environments, and tasks, such policies need to handle diverse sensors and action spaces, accommodate a variety of commonly used robotic platforms, and finetune readily and…</x:v>
+        <x:v>各机器人平台的相机、动作空间与任务不同，单一策略难以直接跨平台使用。</x:v>
       </x:c>
       <x:c r="BP75" t="str">
-        <x:v>As a first step, we introduce Octo, a large transformer-based policy trained on 800k trajectories from the Open X-Embodiment dataset, the largest robot manipulation dataset to date.</x:v>
+        <x:v>Octo 在 Open X-Embodiment 约 80 万条轨迹上训练 Transformer 策略，并提供可微调的通用初始化。</x:v>
       </x:c>
       <x:c r="BQ75" t="str"/>
       <x:c r="BR75" t="str">
-        <x:v>In experiments across 9 robotic platforms, we demonstrate that Octo serves as a versatile policy initialization that can be effectively finetuned to new observation and action spaces.</x:v>
+        <x:v>论文在 9 种机器人平台上评测，表明 Octo 可迁移到新的观测和动作空间；具体成功率见原卡实验表。</x:v>
       </x:c>
       <x:c r="BS75" t="str">
-        <x:v>Provides a concrete method or benchmark for the documented gap: However, to be widely applicable across a range of robotic learning scenarios, environments, and tasks, such policies need to…</x:v>
+        <x:v>是研究共享机器人数据与跨本体微调的重要开放基线。</x:v>
       </x:c>
       <x:c r="BT75" t="str">
-        <x:v>Author-stated — only 27% of data includes wrist cameras, 56% includes language, training uses optimal demonstrations, and evaluation is limited to single/dual-arm manipulators (Sec. V).</x:v>
+        <x:v>训练数据的腕部相机和语言覆盖不均；评测主要在论文列出的单臂/双臂平台。</x:v>
       </x:c>
       <x:c r="BU75" t="str"/>
       <x:c r="BV75" t="str">
-        <x:v>High — informs language-conditioned manipulation and VLA design.</x:v>
+        <x:v>High：有助于研究语言条件操作与 VLA 设计。</x:v>
       </x:c>
       <x:c r="BW75" t="str">
-        <x:v>Official abstract / paper page; https://arxiv.org/html/2405.12213; checked 2026-09-23. Rapid summary only; existing Evidence Quality is unchanged.</x:v>
+        <x:v>官方摘要/论文页; https://arxiv.org/html/2405.12213; 核验于 2026-09-23. 仅为摘要级速读；原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="BX75" t="str">
         <x:v>Exact work identity verified</x:v>
@@ -26309,7 +26309,7 @@
         <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AD76" t="str">
-        <x:v>The creation of large, diverse, high-quality robot manipulation datasets is an important stepping stone on the path toward more capable and robust robotic manipulation policies.</x:v>
+        <x:v>通用操作策略需要规模大、场景多样且质量可靠的机器人交互数据。</x:v>
       </x:c>
       <x:c r="AE76" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -26318,7 +26318,7 @@
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
       </x:c>
       <x:c r="AG76" t="str">
-        <x:v>Not specified in checked abstract/card.</x:v>
+        <x:v>DROID：约 6.5 万条轨迹／350 小时、564 个场景、86 项任务，50 名采集人员在 12 个月内完成。</x:v>
       </x:c>
       <x:c r="AH76" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -26411,30 +26411,30 @@
       </x:c>
       <x:c r="BM76"/>
       <x:c r="BN76" t="str">
-        <x:v>Evidence-backed — The creation of large, diverse, high-quality robot manipulation datasets is an important stepping stone on the path toward more capable and robust robotic manipulation policies.</x:v>
+        <x:v>通用操作策略需要规模大、场景多样且质量可靠的机器人交互数据。</x:v>
       </x:c>
       <x:c r="BO76" t="str">
-        <x:v>However, creating such datasets is challenging: collecting robot manipulation data in diverse environments poses logistical and safety challenges and requires substantial investments in hardware and human labour.</x:v>
+        <x:v>跨环境采集成本高，并受安全、硬件和人力协调限制。</x:v>
       </x:c>
       <x:c r="BP76" t="str">
-        <x:v>In this work, we introduce DROID (Distributed Robot Interaction Dataset), a diverse robot manipulation dataset with 65k demonstration trajectories or 350h of interaction data, collected across 564 scenes and 86 tasks by 50 data collectors in North America, Asia, and Europe over the course of 12 months.</x:v>
+        <x:v>DROID 组织分布式采集，形成 6.5 万条示范轨迹、约 350 小时交互，覆盖 564 个场景和 86 项任务。</x:v>
       </x:c>
       <x:c r="BQ76" t="str"/>
       <x:c r="BR76" t="str">
-        <x:v>We demonstrate that training with DROID leads to policies with higher performance, greater robustness, and improved generalization ability.</x:v>
+        <x:v>论文摘要报告，使用 DROID 训练的策略在性能、鲁棒性和泛化上改善；此处不附加未经实验表格核实的增幅。</x:v>
       </x:c>
       <x:c r="BS76" t="str">
-        <x:v>Provides a concrete method or benchmark for the documented gap: However, creating such datasets is challenging: collecting robot manipulation data in diverse environments poses logistical and…</x:v>
+        <x:v>为跨场景数据采集和数据规模设计提供具体参照。</x:v>
       </x:c>
       <x:c r="BT76" t="str">
-        <x:v>Not established by the checked summary source; consult the full paper.</x:v>
+        <x:v>摘要不能分离数据量、场景多样性与策略结构各自的贡献。</x:v>
       </x:c>
       <x:c r="BU76" t="str"/>
       <x:c r="BV76" t="str">
-        <x:v>Medium — useful for method selection, data design and evaluation.</x:v>
+        <x:v>Medium：可借鉴采集协议，但需核对与本项目机器人形态和动作接口的差异。</x:v>
       </x:c>
       <x:c r="BW76" t="str">
-        <x:v>Official abstract / paper page; https://roboticsproceedings.org/rss20/p120.html; checked 2026-09-23. Rapid summary only; existing Evidence Quality is unchanged.</x:v>
+        <x:v>官方摘要/论文页; https://roboticsproceedings.org/rss20/p120.html; 核验于 2026-09-23. 仅为摘要级速读；原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="BX76" t="str">
         <x:v>Unresolved</x:v>
@@ -26478,15 +26478,19 @@
         <x:v>RoboCasa; household simulation; manipulation benchmark</x:v>
       </x:c>
       <x:c r="K77" t="str">
-        <x:v>https://roboticsproceedings.org/rss20/p074.html</x:v>
-      </x:c>
-      <x:c r="L77"/>
+        <x:v>https://www.roboticsproceedings.org/rss20/p050.html</x:v>
+      </x:c>
+      <x:c r="L77" t="str">
+        <x:v>https://arxiv.org/abs/2406.02523</x:v>
+      </x:c>
       <x:c r="M77" t="str">
         <x:v>https://robocasa.ai/</x:v>
       </x:c>
-      <x:c r="N77"/>
+      <x:c r="N77" t="str">
+        <x:v>https://github.com/robocasa/robocasa</x:v>
+      </x:c>
       <x:c r="O77" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Released（官方仓库已公开；本轮未运行验证）</x:v>
       </x:c>
       <x:c r="P77" t="str">
         <x:v>Unknown</x:v>
@@ -26529,7 +26533,7 @@
         <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AD77" t="str">
-        <x:v>Building upon our previous contributions, this paper introduces Arena 3.0, an extension of Arena-Bench, Arena 1.0, and Arena 2.0 focusing on the development, simulation, and benchmarking of social navigation approaches in collaborative environments.</x:v>
+        <x:v>真实机器人数据难以低成本扩展，限制通用家庭操作策略训练。</x:v>
       </x:c>
       <x:c r="AE77" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -26538,7 +26542,7 @@
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
       </x:c>
       <x:c r="AG77" t="str">
-        <x:v>Not specified in checked abstract/card.</x:v>
+        <x:v>RSS 2024 原版 RoboCasa：100 项任务、超过 150 个物体类别及大量 3D 资产；不要与后续 RoboCasa365 的规模混同。</x:v>
       </x:c>
       <x:c r="AH77" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -26631,30 +26635,30 @@
       </x:c>
       <x:c r="BM77"/>
       <x:c r="BN77" t="str">
-        <x:v>Evidence-backed — Building upon our previous contributions, this paper introduces Arena 3.0, an extension of Arena-Bench, Arena 1.0, and Arena 2.0 focusing on the development, simulation, and benchmarking of social navigation approaches in collaborative environments.</x:v>
+        <x:v>真实机器人数据难以低成本扩展，限制通用家庭操作策略训练。</x:v>
       </x:c>
       <x:c r="BO77" t="str">
-        <x:v>Not established in checked summary source.</x:v>
+        <x:v>场景、任务和示范的规模不足；仅靠真机采集难以覆盖家庭环境多样性。</x:v>
       </x:c>
       <x:c r="BP77" t="str">
-        <x:v>We significantly enhance the realism of human behavior simulation by incorporating a diverse array of new social force models and interaction patterns, encompassing both human-human and human-robot dynamics.</x:v>
+        <x:v>RoboCasa 建立以厨房为中心的大规模仿真框架，结合生成式资产、语言模型辅助任务设计、人类示范和自动轨迹生成。</x:v>
       </x:c>
       <x:c r="BQ77" t="str"/>
       <x:c r="BR77" t="str">
-        <x:v>The platform’s efficacy has been validated through an extensive benchmark and user evaluations of the platform by a global community of researchers and students, which noted the substantial improvement compared to previous versions and expressed interests to…</x:v>
+        <x:v>RSS 官方摘要报告，合成数据用于大规模模仿学习呈现规模效应；本轮不转述未经表格核验的成功率。</x:v>
       </x:c>
       <x:c r="BS77" t="str">
-        <x:v>Medium — useful for method selection, data design and evaluation.</x:v>
+        <x:v>可用于研究仿真数据扩增及与真实机器人数据联合训练。</x:v>
       </x:c>
       <x:c r="BT77" t="str">
-        <x:v>Not established by the checked summary source; consult the full paper.</x:v>
+        <x:v>摘要不能保证仿真训练所得提升直接迁移至本项目真机。</x:v>
       </x:c>
       <x:c r="BU77" t="str"/>
       <x:c r="BV77" t="str">
-        <x:v>Medium — useful for method selection, data design and evaluation.</x:v>
+        <x:v>Medium：家庭操作仿真可借鉴，但与本项目场景、双臂配置和真实部署有差异。</x:v>
       </x:c>
       <x:c r="BW77" t="str">
-        <x:v>Official abstract / paper page; https://roboticsproceedings.org/rss20/p074.html; checked 2026-09-23. Rapid summary only; existing Evidence Quality is unchanged.</x:v>
+        <x:v>官方摘要/论文页; https://www.roboticsproceedings.org/rss20/p050.html; 核验于 2026-09-23. 仅为摘要级速读；原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="BX77" t="str">
         <x:v>Exact work identity verified</x:v>
@@ -26749,7 +26753,7 @@
         <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AD78" t="str">
-        <x:v>Robot-learning datasets are fragmented across embodiments, tasks and formats.</x:v>
+        <x:v>机器人数据分散在不同机构、平台和格式中，难以训练通用策略。</x:v>
       </x:c>
       <x:c r="AE78" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -26758,7 +26762,7 @@
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
       </x:c>
       <x:c r="AG78" t="str">
-        <x:v>Not specified in checked abstract/card.</x:v>
+        <x:v>Open X-Embodiment 数据混合及 RT-X 评测。</x:v>
       </x:c>
       <x:c r="AH78" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -26851,30 +26855,30 @@
       </x:c>
       <x:c r="BM78"/>
       <x:c r="BN78" t="str">
-        <x:v>Evidence-backed — Robot-learning datasets are fragmented across embodiments, tasks and formats.</x:v>
+        <x:v>机器人数据分散在不同机构、平台和格式中，难以训练通用策略。</x:v>
       </x:c>
       <x:c r="BO78" t="str">
-        <x:v>Not established in checked summary source.</x:v>
+        <x:v>每个机器人和任务单独训练模型，跨平台复用成本高。</x:v>
       </x:c>
       <x:c r="BP78" t="str">
-        <x:v>We present Open X-Embodiment, a standardized multi-institution dataset mixture with RT-X generalist policy experiments.</x:v>
+        <x:v>Open X-Embodiment 整合标准化的跨机器人数据，并训练 RT-X 模型测试共享学习。</x:v>
       </x:c>
       <x:c r="BQ78" t="str"/>
       <x:c r="BR78" t="str">
-        <x:v>Qualitative or numerical result not established by checked source.</x:v>
+        <x:v>官方项目与论文报告跨机器人训练带来的泛化收益；具体任务数值见原论文。</x:v>
       </x:c>
       <x:c r="BS78" t="str">
-        <x:v>High — informs language-conditioned manipulation and VLA design.</x:v>
+        <x:v>是审计跨本体数据、动作格式和策略迁移的基础入口。</x:v>
       </x:c>
       <x:c r="BT78" t="str">
-        <x:v>Not established by the checked summary source; consult the full paper.</x:v>
+        <x:v>本段基于官方摘要；未覆盖全文失败案例、完整 Baseline 与方法消融。</x:v>
       </x:c>
       <x:c r="BU78" t="str"/>
       <x:c r="BV78" t="str">
-        <x:v>High — informs language-conditioned manipulation and VLA design.</x:v>
+        <x:v>Medium：方法可借鉴，但迁移到当前双臂硬件需验证。</x:v>
       </x:c>
       <x:c r="BW78" t="str">
-        <x:v>Official abstract / paper page; https://robotics-transformer-x.github.io/; checked 2026-09-23. Rapid summary only; existing Evidence Quality is unchanged.</x:v>
+        <x:v>官方摘要/论文页：https://robotics-transformer-x.github.io/；核验于 2026-09-23。仅为摘要级速读，原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="BX78" t="str">
         <x:v>Exact work identity verified</x:v>
@@ -26975,7 +26979,7 @@
         <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AD79" t="str">
-        <x:v>Current VLAs may spread visual attention across irrelevant regions instead of the task target, weakening precise manipulation and generalization.</x:v>
+        <x:v>VLA 的视觉注意可能落在任务无关区域，削弱精细操作与泛化。</x:v>
       </x:c>
       <x:c r="AE79" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -26984,7 +26988,7 @@
         <x:v>模型从 VLA 的视觉输出生成重建条件，由轻量 diffusion transformer 从噪声重建对应目标操作对象的 ga</x:v>
       </x:c>
       <x:c r="AG79" t="str">
-        <x:v>Training Dataset: BridgeData V2, LIBERO, and CALVIN-derived open robotic data (Sec. 3.4); the constructed pretraining corpus contains over 100k trajectories and 2M samples…</x:v>
+        <x:v>卡片记录 BridgeData V2、LIBERO、CALVIN 相关数据和评测；具体分工与规模见论文 Sec. 3.4。</x:v>
       </x:c>
       <x:c r="AH79" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -27079,34 +27083,34 @@
       </x:c>
       <x:c r="BM79"/>
       <x:c r="BN79" t="str">
-        <x:v>Evidence-backed — Current VLAs may spread visual attention across irrelevant regions instead of the task target, weakening precise manipulation and generalization.</x:v>
+        <x:v>VLA 的视觉注意可能落在任务无关区域，削弱精细操作与泛化。</x:v>
       </x:c>
       <x:c r="BO79" t="str">
-        <x:v>Author-stated: existing VLAs struggle to allocate visual attention to target regions; ReconVLA addresses this with implicit grounding rather than requiring explicit grounding inputs.</x:v>
+        <x:v>原有 VLA 难以稳定把视觉注意对准目标区域；显式标注 Grounding 的方案又可能增加数据要求。</x:v>
       </x:c>
       <x:c r="BP79" t="str">
-        <x:v>A diffusion transformer reconstructs the gaze region of the manipulated object conditioned on the VLA visual outputs, jointly encouraging task-specific visual representations while preserving action prediction.</x:v>
+        <x:v>ReconVLA 用扩散式重建目标注视区域，促使视觉表示聚焦被操作物体，同时保留动作预测。</x:v>
       </x:c>
       <x:c r="BQ79" t="str">
         <x:v>Official abstract confirms comparison of implicit grounding against alternative grounding paradigms; exact named baselines and metric table require full PDF extraction.</x:v>
       </x:c>
       <x:c r="BR79" t="str">
-        <x:v>Official AAAI abstract reports improved precise manipulation and generalization, but no numeric result is entered without table-level extraction.</x:v>
+        <x:v>AAAI 官方摘要报告操作精度和泛化改善；快速摘要不添加尚未核对表格的数值。</x:v>
       </x:c>
       <x:c r="BS79" t="str">
-        <x:v>Provides a concrete method or benchmark for the documented gap: Author-stated: existing VLAs struggle to allocate visual attention to target regions; ReconVLA addresses this with implicit…</x:v>
+        <x:v>直接对应本项目的目标 Grounding 与动作前目标核验。</x:v>
       </x:c>
       <x:c r="BT79" t="str">
-        <x:v>Author-stated: performance depends on reconstructing the correct target region and the reported evaluation is concentrated on CALVIN plus a limited real-world suite (Sec. 4.6 and conclusion). - Library Analysis: broader…</x:v>
+        <x:v>作者指出性能取决于目标区域重建是否正确；公开评测主要集中在 CALVIN 与有限真机任务。跨本体和新相机条件仍需验证。</x:v>
       </x:c>
       <x:c r="BU79" t="str">
         <x:v>Library Analysis: calibration of reconstructed attention under occlusion, clutter and multi-object bimanual scenes remains open.</x:v>
       </x:c>
       <x:c r="BV79" t="str">
-        <x:v>High — informs language-conditioned manipulation and VLA design.</x:v>
+        <x:v>High：有助于研究语言条件操作与 VLA 设计。</x:v>
       </x:c>
       <x:c r="BW79" t="str">
-        <x:v>Official abstract / paper page; https://arxiv.org/html/2508.10333; checked 2026-09-23. Rapid summary only; existing Evidence Quality is unchanged.</x:v>
+        <x:v>官方摘要/论文页; https://arxiv.org/html/2508.10333; 核验于 2026-09-23. 仅为摘要级速读；原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="BX79" t="str">
         <x:v>Exact work identity verified</x:v>
@@ -27138,7 +27142,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcd9bcb306a594207"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfbf8d6f51f124fa0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -27633,7 +27637,7 @@
         <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AX2" t="str">
-        <x:v>This paper introduces Hierarchical Diffusion Policy (HDP) a hierarchical agent for multi-task robotic manipulation.</x:v>
+        <x:v>多任务机器人操作要同时决定高层子目标和符合运动学的连续动作。</x:v>
       </x:c>
       <x:c r="AY2" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -27642,7 +27646,7 @@
         <x:v>以 `Robot Manipulation; Diffusion Policy / Hierarchical Control` 为主要方法/能力线索；更细的结构和消融结论待正文核验。</x:v>
       </x:c>
       <x:c r="BA2" t="str">
-        <x:v>Not specified in checked abstract/card.</x:v>
+        <x:v>已核验摘要未明确说明；需查阅论文方法与实验章节。</x:v>
       </x:c>
       <x:c r="BB2" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -27732,30 +27736,30 @@
       </x:c>
       <x:c r="CF2"/>
       <x:c r="CG2" t="str">
-        <x:v>Evidence-backed — This paper introduces Hierarchical Diffusion Policy (HDP) a hierarchical agent for multi-task robotic manipulation.</x:v>
+        <x:v>多任务机器人操作要同时决定高层子目标和符合运动学的连续动作。</x:v>
       </x:c>
       <x:c r="CH2" t="str">
-        <x:v>The factorised policy representation allows HDP to tackle both long-horizon task planning while generating fine-grained low-level actions.</x:v>
+        <x:v>单层扩散策略可能难兼顾长任务结构与局部可达性。</x:v>
       </x:c>
       <x:c r="CI2" t="str">
-        <x:v>This paper introduces Hierarchical Diffusion Policy (HDP) a hierarchical agent for multi-task robotic manipulation.</x:v>
+        <x:v>Hierarchical Diffusion Policy 将任务规划与运动学感知的动作生成分层处理。</x:v>
       </x:c>
       <x:c r="CJ2" t="str"/>
       <x:c r="CK2" t="str">
-        <x:v>Empirically we show that HDP achieves a significantly higher success rate than the state-of-the-art methods in both simulation and real-world.</x:v>
+        <x:v>作者报告仿真和真机成功率高于所比较方法；具体数值见实验表。</x:v>
       </x:c>
       <x:c r="CL2" t="str">
-        <x:v>Provides a concrete method or benchmark for the documented gap: The factorised policy representation allows HDP to tackle both long-horizon task planning while generating fine-grained low-level…</x:v>
+        <x:v>可对照双臂任务中高层分工与低层动作生成。</x:v>
       </x:c>
       <x:c r="CM2" t="str">
-        <x:v>Not established by the checked summary source; consult the full paper.</x:v>
+        <x:v>需核验在两臂共享工作空间中的约束处理。</x:v>
       </x:c>
       <x:c r="CN2" t="str"/>
       <x:c r="CO2" t="str">
-        <x:v>Medium — relevant to robot manipulation; transfer to dual-arm real hardware needs validation.</x:v>
+        <x:v>High：双臂普通夹爪也需要运动学约束和任务分解。</x:v>
       </x:c>
       <x:c r="CP2" t="str">
-        <x:v>Official abstract / paper page; https://openaccess.thecvf.com/content/CVPR2024/html/Ma_Hierarchical_Diffusion_Policy_for_Kinematics-Aware_Multi-Task_Robotic_Manipulation_CVPR_2024_paper.html; checked 2026-09-23. Rapid summary only; existing Evidence Quality is unchanged.</x:v>
+        <x:v>官方摘要/论文页; https://openaccess.thecvf.com/content/CVPR2024/html/Ma_Hierarchical_Diffusion_Policy_for_Kinematics-Aware_Multi-Task_Robotic_Manipulation_CVPR_2024_paper.html; 核验于 2026-09-23. 仅为摘要级速读；原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="CQ2" t="str">
         <x:v>Unresolved</x:v>
@@ -27908,7 +27912,7 @@
         <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AX3" t="str">
-        <x:v>Bimanual robotic manipulation is an emerging and critical topic in the robotics community.</x:v>
+        <x:v>不同双臂任务的交互结构不同，统一耦合方式未必合适。</x:v>
       </x:c>
       <x:c r="AY3" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -27917,7 +27921,7 @@
         <x:v>以 `bimanual manipulation; decoupled interaction; RoboTwin` 为主要方法/能力线索；更细的结构和消融结论待正文核验。</x:v>
       </x:c>
       <x:c r="BA3" t="str">
-        <x:v>Not specified in checked abstract/card.</x:v>
+        <x:v>RoboTwin 七项任务。</x:v>
       </x:c>
       <x:c r="BB3" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -28007,30 +28011,30 @@
       </x:c>
       <x:c r="CF3"/>
       <x:c r="CG3" t="str">
-        <x:v>Evidence-backed — Bimanual robotic manipulation is an emerging and critical topic in the robotics community.</x:v>
+        <x:v>不同双臂任务的交互结构不同，统一耦合方式未必合适。</x:v>
       </x:c>
       <x:c r="CH3" t="str">
-        <x:v>However, we think bimanual manipulation involves not only coordinated tasks but also various uncoordinated tasks that do not require explicit cooperation during execution, such as grasping objects with the closest hand, which integrated control frameworks…</x:v>
+        <x:v>始终联合预测双臂动作，可能忽略支撑手与操作手的不同职责。</x:v>
       </x:c>
       <x:c r="CI3" t="str">
-        <x:v>In this paper, we propose a novel decoupled interaction framework that considers the characteristics of different tasks in bimanual manipulation.</x:v>
+        <x:v>按任务交互特点设计解耦框架，让双臂策略分别处理可分解的部分并保持必要协调。</x:v>
       </x:c>
       <x:c r="CJ3" t="str"/>
       <x:c r="CK3" t="str">
-        <x:v>Extensive experiments on seven tasks in the RoboTwin dataset demonstrate that: (1) Our framework achieves outstanding performance, with a 23.5% boost over the SOTA method. (2) Our framework is flexible and can be seamlessly integrated into existing methods.…</x:v>
+        <x:v>论文报告在七项 RoboTwin 任务上较所比较 SOTA 提升 23.5%；具体指标定义见原文。</x:v>
       </x:c>
       <x:c r="CL3" t="str">
-        <x:v>Provides a concrete method or benchmark for the documented gap: However, we think bimanual manipulation involves not only coordinated tasks but also various uncoordinated tasks that do not…</x:v>
+        <x:v>为联合预测与分臂预测的实验对照提供方法。</x:v>
       </x:c>
       <x:c r="CM3" t="str">
-        <x:v>Not established by the checked summary source; consult the full paper.</x:v>
+        <x:v>仿真 benchmark 上的优势仍需真机接触任务验证。</x:v>
       </x:c>
       <x:c r="CN3" t="str"/>
       <x:c r="CO3" t="str">
-        <x:v>High — directly informs dual-arm coordination, data or ordinary-gripper policy design.</x:v>
+        <x:v>High：普通夹爪常有支撑—操作分工。</x:v>
       </x:c>
       <x:c r="CP3" t="str">
-        <x:v>Official abstract / paper page; https://openaccess.thecvf.com/content/ICCV2025/html/Jiang_Rethinking_Bimanual_Robotic_Manipulation_Learning_with_Decoupled_Interaction_Framework_ICCV_2025_paper.html; checked 2026-09-23. Rapid summary only; existing Evidence Quality is unchanged.</x:v>
+        <x:v>官方摘要/论文页; https://openaccess.thecvf.com/content/ICCV2025/html/Jiang_Rethinking_Bimanual_Robotic_Manipulation_Learning_with_Decoupled_Interaction_Framework_ICCV_2025_paper.html; 核验于 2026-09-23. 仅为摘要级速读；原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="CQ3" t="str">
         <x:v>Exact work identity verified</x:v>
@@ -28183,7 +28187,7 @@
         <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AX4" t="str">
-        <x:v>Bimanual manipulation is crucial in robotics, enabling complex tasks in industrial automation and household services.</x:v>
+        <x:v>复杂双臂任务需要预测动作，也需要理解后续视觉状态。</x:v>
       </x:c>
       <x:c r="AY4" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -28192,7 +28196,7 @@
         <x:v>以 `bimanual; diffusion; teleoperation; human demonstration` 为主要方法/能力线索；更细的结构和消融结论待正文核验。</x:v>
       </x:c>
       <x:c r="BA4" t="str">
-        <x:v>Not specified in checked abstract/card.</x:v>
+        <x:v>两项仿真 benchmark 与一项真机设置。</x:v>
       </x:c>
       <x:c r="BB4" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -28282,30 +28286,30 @@
       </x:c>
       <x:c r="CF4"/>
       <x:c r="CG4" t="str">
-        <x:v>Evidence-backed — Bimanual manipulation is crucial in robotics, enabling complex tasks in industrial automation and household services.</x:v>
+        <x:v>复杂双臂任务需要预测动作，也需要理解后续视觉状态。</x:v>
       </x:c>
       <x:c r="CH4" t="str">
-        <x:v>However, it poses significant challenges due to the high-dimensional action space and intricate coordination requirements.</x:v>
+        <x:v>只学动作或只生成视频，可能无法协调两臂与物体变化。</x:v>
       </x:c>
       <x:c r="CI4" t="str">
-        <x:v>To bridge this gap, we propose a unified diffusion-based framework for the joint optimization of video and action prediction.</x:v>
+        <x:v>联合优化视频预测与双臂动作生成，让策略在想象未来场景的同时协调执行。</x:v>
       </x:c>
       <x:c r="CJ4" t="str"/>
       <x:c r="CK4" t="str">
-        <x:v>Experiments on two simulated benchmarks and a real-world setting demonstrate a significant improvement in the success rate over the strong baseline ACT using our method, achieving a 24.9% increase on ALOHA, an 11.1% increase on RoboTwin, and a 32.5% increase…</x:v>
+        <x:v>论文报告在上述设置中成功率高于 ACT 基线；具体差值需核对实验表。</x:v>
       </x:c>
       <x:c r="CL4" t="str">
-        <x:v>Provides a concrete method or benchmark for the documented gap: However, it poses significant challenges due to the high-dimensional action space and intricate coordination requirements.</x:v>
+        <x:v>可测试视觉预期是否改善双臂协调。</x:v>
       </x:c>
       <x:c r="CM4" t="str">
-        <x:v>Not established by the checked summary source; consult the full paper.</x:v>
+        <x:v>真机环境和失败类型的完整覆盖仍需查正文。</x:v>
       </x:c>
       <x:c r="CN4" t="str"/>
       <x:c r="CO4" t="str">
-        <x:v>High — directly informs dual-arm coordination, data or ordinary-gripper policy design.</x:v>
+        <x:v>High：双臂普通夹爪可对照 ACT 与带未来预测的策略。</x:v>
       </x:c>
       <x:c r="CP4" t="str">
-        <x:v>Official abstract / paper page; https://openaccess.thecvf.com/content/ICCV2025/html/Xu_Diffusion-Based_Imaginative_Coordination_for_Bimanual_Manipulation_ICCV_2025_paper.html; checked 2026-09-23. Rapid summary only; existing Evidence Quality is unchanged.</x:v>
+        <x:v>官方摘要/论文页; https://openaccess.thecvf.com/content/ICCV2025/html/Xu_Diffusion-Based_Imaginative_Coordination_for_Bimanual_Manipulation_ICCV_2025_paper.html; 核验于 2026-09-23. 仅为摘要级速读；原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="CQ4" t="str">
         <x:v>Exact work identity verified</x:v>
@@ -28458,7 +28462,7 @@
         <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AX5" t="str">
-        <x:v>Long manipulation tasks are difficult for a single low-level policy to learn from sparse data.</x:v>
+        <x:v>长任务的高层指令与短时动作之间容易出现不一致。</x:v>
       </x:c>
       <x:c r="AY5" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -28467,7 +28471,7 @@
         <x:v>以 `Robot Manipulation; Diffusion Policy / Primitive Skills` 为主要方法/能力线索；更细的结构和消融结论待正文核验。</x:v>
       </x:c>
       <x:c r="BA5" t="str">
-        <x:v>Not specified in checked abstract/card.</x:v>
+        <x:v>两项仿真 benchmark 与真机操作评测。</x:v>
       </x:c>
       <x:c r="BB5" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -28557,30 +28561,30 @@
       </x:c>
       <x:c r="CF5"/>
       <x:c r="CG5" t="str">
-        <x:v>Evidence-backed — Long manipulation tasks are difficult for a single low-level policy to learn from sparse data.</x:v>
+        <x:v>长任务的高层指令与短时动作之间容易出现不一致。</x:v>
       </x:c>
       <x:c r="CH5" t="str">
-        <x:v>Not established in checked summary source.</x:v>
+        <x:v>只用全局指令条件化扩散策略，难以保证每段动作符合当前小技能。</x:v>
       </x:c>
       <x:c r="CI5" t="str">
-        <x:v>官方题名与元数据已确认；具体表述待补读官方摘要或正文。</x:v>
+        <x:v>SDP 把复杂任务拆成八种 primitive skills，用 VLM 提取离散状态表示，再由轻量 router 选择技能条件化扩散策略。</x:v>
       </x:c>
       <x:c r="CJ5" t="str"/>
       <x:c r="CK5" t="str">
-        <x:v>Qualitative or numerical result not established by checked source.</x:v>
+        <x:v>AAAI 摘要报告在两项仿真 benchmark 和真机任务中优于所比较方法；未给统一量化值。</x:v>
       </x:c>
       <x:c r="CL5" t="str">
-        <x:v>Medium — relevant to robot manipulation; transfer to dual-arm real hardware needs validation.</x:v>
+        <x:v>可作为“高层技能调度 + 低层动作生成”的双臂基线。</x:v>
       </x:c>
       <x:c r="CM5" t="str">
-        <x:v>Not established by the checked summary source; consult the full paper.</x:v>
+        <x:v>本段基于官方摘要；未覆盖全文失败案例、完整 Baseline 与方法消融。</x:v>
       </x:c>
       <x:c r="CN5" t="str"/>
       <x:c r="CO5" t="str">
-        <x:v>Medium — relevant to robot manipulation; transfer to dual-arm real hardware needs validation.</x:v>
+        <x:v>Medium：方法可借鉴，但迁移到当前双臂硬件需验证。</x:v>
       </x:c>
       <x:c r="CP5" t="str">
-        <x:v>Official abstract / paper page; https://ojs.aaai.org/index.php/AAAI/article/view/38889; checked 2026-09-23. Rapid summary only; existing Evidence Quality is unchanged.</x:v>
+        <x:v>官方摘要/论文页：https://ojs.aaai.org/index.php/AAAI/article/view/38889；核验于 2026-09-23。仅为摘要级速读，原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="CQ5" t="str">
         <x:v>Unresolved</x:v>
@@ -28733,7 +28737,7 @@
         <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AX6" t="str">
-        <x:v>Multi-task imitation policies can miss goal context and future task progress.</x:v>
+        <x:v>多任务模仿学习策略需要可靠动作，也需要用少量示范适应未见任务。</x:v>
       </x:c>
       <x:c r="AY6" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -28742,7 +28746,7 @@
         <x:v>以 `Imitation Learning; Multi-Task / Foresight` 为主要方法/能力线索；更细的结构和消融结论待正文核验。</x:v>
       </x:c>
       <x:c r="BA6" t="str">
-        <x:v>Not specified in checked abstract/card.</x:v>
+        <x:v>超过 100 项仿真/真机任务；官方发布的仿真任务套件。</x:v>
       </x:c>
       <x:c r="BB6" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -28832,30 +28836,30 @@
       </x:c>
       <x:c r="CF6"/>
       <x:c r="CG6" t="str">
-        <x:v>Evidence-backed — Multi-task imitation policies can miss goal context and future task progress.</x:v>
+        <x:v>多任务模仿学习策略需要可靠动作，也需要用少量示范适应未见任务。</x:v>
       </x:c>
       <x:c r="CH6" t="str">
-        <x:v>Not established in checked summary source.</x:v>
+        <x:v>只根据当前状态重建动作，可能缺少对动作视觉后果的预测。</x:v>
       </x:c>
       <x:c r="CI6" t="str">
-        <x:v>官方题名与元数据已确认；具体表述待补读官方摘要或正文。</x:v>
+        <x:v>FoAM 输入多模态目标，在动作重建之外加入 foresight augmentation，让策略利用预期视觉结果。</x:v>
       </x:c>
       <x:c r="CJ6" t="str"/>
       <x:c r="CK6" t="str">
-        <x:v>Qualitative or numerical result not established by checked source.</x:v>
+        <x:v>AAAI 摘要报告仿真与真机超过 100 项任务，成功率相对基线最高提升 41%；另发布 80 多项仿真任务。</x:v>
       </x:c>
       <x:c r="CL6" t="str">
-        <x:v>Medium — relevant to robot manipulation; transfer to dual-arm real hardware needs validation.</x:v>
+        <x:v>可比较“预见动作后果”是否帮助双臂动作前验证。</x:v>
       </x:c>
       <x:c r="CM6" t="str">
-        <x:v>Not established by the checked summary source; consult the full paper.</x:v>
+        <x:v>本段基于官方摘要；未覆盖全文失败案例、完整 Baseline 与方法消融。</x:v>
       </x:c>
       <x:c r="CN6" t="str"/>
       <x:c r="CO6" t="str">
-        <x:v>Medium — relevant to robot manipulation; transfer to dual-arm real hardware needs validation.</x:v>
+        <x:v>Medium：方法可借鉴，但迁移到当前双臂硬件需验证。</x:v>
       </x:c>
       <x:c r="CP6" t="str">
-        <x:v>Official abstract / paper page; https://ojs.aaai.org/index.php/AAAI/article/view/38911; checked 2026-09-23. Rapid summary only; existing Evidence Quality is unchanged.</x:v>
+        <x:v>官方摘要/论文页：https://ojs.aaai.org/index.php/AAAI/article/view/38911；核验于 2026-09-23。仅为摘要级速读，原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="CQ6" t="str">
         <x:v>Unresolved</x:v>
@@ -29008,7 +29012,7 @@
         <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AX7" t="str">
-        <x:v>Gentle manipulation needs force-aware behavior and compositional task execution.</x:v>
+        <x:v>长时序接触操作既要完成任务，也要避免过大接触力损伤物体。</x:v>
       </x:c>
       <x:c r="AY7" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -29017,7 +29021,7 @@
         <x:v>以 `Robot Manipulation; Long-Hori</x:v>
       </x:c>
       <x:c r="BA7" t="str">
-        <x:v>Not specified in checked abstract/card.</x:v>
+        <x:v>仿真与实体机器人接触操作任务。</x:v>
       </x:c>
       <x:c r="BB7" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -29107,30 +29111,30 @@
       </x:c>
       <x:c r="CF7"/>
       <x:c r="CG7" t="str">
-        <x:v>Evidence-backed — Gentle manipulation needs force-aware behavior and compositional task execution.</x:v>
+        <x:v>长时序接触操作既要完成任务，也要避免过大接触力损伤物体。</x:v>
       </x:c>
       <x:c r="CH7" t="str">
-        <x:v>Not established in checked summary source.</x:v>
+        <x:v>真机专家示范昂贵，分层技能和安全约束难以同时获得。</x:v>
       </x:c>
       <x:c r="CI7" t="str">
-        <x:v>官方题名与元数据已确认；具体表述待补读官方摘要或正文。</x:v>
+        <x:v>在仿真中用带力约束的 RL 训练原子技能，再由 VLM 规划任务，最后蒸馏到视觉—触觉 Diffusion Policy。</x:v>
       </x:c>
       <x:c r="CJ7" t="str"/>
       <x:c r="CK7" t="str">
-        <x:v>Qualitative or numerical result not established by checked source.</x:v>
+        <x:v>AAAI 官方摘要报告仿真与实体机器人验证，并进行了规划器和蒸馏方法消融；未给统一数值。</x:v>
       </x:c>
       <x:c r="CL7" t="str">
-        <x:v>Medium — relevant to robot manipulation; transfer to dual-arm real hardware needs validation.</x:v>
+        <x:v>为普通夹爪的接触安全和低成本技能数据生成提供参考。</x:v>
       </x:c>
       <x:c r="CM7" t="str">
-        <x:v>Not established by the checked summary source; consult the full paper.</x:v>
+        <x:v>本段基于官方摘要；未覆盖全文失败案例、完整 Baseline 与方法消融。</x:v>
       </x:c>
       <x:c r="CN7" t="str"/>
       <x:c r="CO7" t="str">
-        <x:v>Medium — relevant to robot manipulation; transfer to dual-arm real hardware needs validation.</x:v>
+        <x:v>Medium：方法可借鉴，但迁移到当前双臂硬件需验证。</x:v>
       </x:c>
       <x:c r="CP7" t="str">
-        <x:v>Official abstract / paper page; https://ojs.aaai.org/index.php/AAAI/article/view/38955; checked 2026-09-23. Rapid summary only; existing Evidence Quality is unchanged.</x:v>
+        <x:v>官方摘要/论文页：https://ojs.aaai.org/index.php/AAAI/article/view/38955；核验于 2026-09-23。仅为摘要级速读，原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="CQ7" t="str">
         <x:v>Unresolved</x:v>
@@ -29283,7 +29287,7 @@
         <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AX8" t="str">
-        <x:v>Generalizable humanoid manipulation needs robust geometric reasoning with limited data.</x:v>
+        <x:v>通用人形机器人操作常依赖大量示范，未见场景中的几何推理仍薄弱。</x:v>
       </x:c>
       <x:c r="AY8" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -29292,7 +29296,7 @@
         <x:v>以 `Robot Manipulation; Humanoid / Generali</x:v>
       </x:c>
       <x:c r="BA8" t="str">
-        <x:v>Not specified in checked abstract/card.</x:v>
+        <x:v>人形机器人与桌面机器人操作评测。</x:v>
       </x:c>
       <x:c r="BB8" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -29382,30 +29386,30 @@
       </x:c>
       <x:c r="CF8"/>
       <x:c r="CG8" t="str">
-        <x:v>Evidence-backed — Generalizable humanoid manipulation needs robust geometric reasoning with limited data.</x:v>
+        <x:v>通用人形机器人操作常依赖大量示范，未见场景中的几何推理仍薄弱。</x:v>
       </x:c>
       <x:c r="CH8" t="str">
-        <x:v>We propose RGMP, combining geometric-prior skill selection and recurrent Gaussian motion generation.</x:v>
+        <x:v>单纯数据驱动策略难以高效建模机器人与目标之间的空间关系。</x:v>
       </x:c>
       <x:c r="CI8" t="str">
-        <x:v>官方题名与元数据已确认；具体表述待补读官方摘要或正文。</x:v>
+        <x:v>RGMP 用带几何先验的技能选择器推理子任务，再用递归 Gaussian 网络生成动作。</x:v>
       </x:c>
       <x:c r="CJ8" t="str"/>
       <x:c r="CK8" t="str">
-        <x:v>The official abstract reports 87 percent generalization success and fivefold data efficiency in its evaluation.</x:v>
+        <x:v>AAAI 官方摘要报告泛化测试成功率 87%，数据效率约为所比较 SOTA 的 5 倍。</x:v>
       </x:c>
       <x:c r="CL8" t="str">
-        <x:v>Provides a concrete method or benchmark for the documented gap: We propose RGMP, combining geometric-prior skill selection and recurrent Gaussian motion generation.</x:v>
+        <x:v>可启发双臂任务的几何关系表示，但硬件差异需要单独验证。</x:v>
       </x:c>
       <x:c r="CM8" t="str">
-        <x:v>Not established by the checked summary source; consult the full paper.</x:v>
+        <x:v>本段基于官方摘要；未覆盖全文失败案例、完整 Baseline 与方法消融。</x:v>
       </x:c>
       <x:c r="CN8" t="str"/>
       <x:c r="CO8" t="str">
-        <x:v>Medium — relevant to robot manipulation; transfer to dual-arm real hardware needs validation.</x:v>
+        <x:v>Medium：方法可借鉴，但迁移到当前双臂硬件需验证。</x:v>
       </x:c>
       <x:c r="CP8" t="str">
-        <x:v>Official abstract / paper page; https://ojs.aaai.org/index.php/AAAI/article/view/38539; checked 2026-09-23. Rapid summary only; existing Evidence Quality is unchanged.</x:v>
+        <x:v>官方摘要/论文页：https://ojs.aaai.org/index.php/AAAI/article/view/38539；核验于 2026-09-23。仅为摘要级速读，原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="CQ8" t="str">
         <x:v>Unresolved</x:v>
@@ -29556,7 +29560,7 @@
         <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AX9" t="str">
-        <x:v>Dexterous manipulation across diverse objects is hard because hand dynamics and task-specific rewards do not transfer easily.</x:v>
+        <x:v>多指灵巧手操作不同物体时，任务奖励设计和跨手型泛化都很难。</x:v>
       </x:c>
       <x:c r="AY9" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -29565,7 +29569,7 @@
         <x:v>以 `Dexterous Manipulation; Human Demonstrations / Motion Prior` 为主要方法/能力线索；更细的结构和消融结论待正文核验。</x:v>
       </x:c>
       <x:c r="BA9" t="str">
-        <x:v>Not specified in checked abstract/card.</x:v>
+        <x:v>三类灵巧操作任务；具体数据集见官方论文。</x:v>
       </x:c>
       <x:c r="BB9" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -29655,30 +29659,30 @@
       </x:c>
       <x:c r="CF9"/>
       <x:c r="CG9" t="str">
-        <x:v>Evidence-backed — Dexterous manipulation across diverse objects is hard because hand dynamics and task-specific rewards do not transfer easily.</x:v>
+        <x:v>多指灵巧手操作不同物体时，任务奖励设计和跨手型泛化都很难。</x:v>
       </x:c>
       <x:c r="CH9" t="str">
-        <x:v>Not established in checked summary source.</x:v>
+        <x:v>只模仿人手轨迹，难以把物体未来状态变成通用训练目标。</x:v>
       </x:c>
       <x:c r="CI9" t="str">
-        <x:v>官方题名与元数据已确认；具体表述待补读官方摘要或正文。</x:v>
+        <x:v>从人—物交互数据学习物体运动先验，预测未来物体状态，再把它用于强化学习奖励。</x:v>
       </x:c>
       <x:c r="CJ9" t="str"/>
       <x:c r="CK9" t="str">
-        <x:v>Qualitative or numerical result not established by checked source.</x:v>
+        <x:v>官方 AAAI 摘要报告三类仿真与真机任务上的成功率和新物体泛化优于对比方法，并展示跨机械手部署；摘要未给统一数值。</x:v>
       </x:c>
       <x:c r="CL9" t="str">
-        <x:v>Medium — transferable learning ideas may apply, but the hand hardware differs from ordinary grippers.</x:v>
+        <x:v>提出“预测物体状态作为奖励”的路线，可与普通夹爪任务中的目标状态验证比较。</x:v>
       </x:c>
       <x:c r="CM9" t="str">
-        <x:v>Not established by the checked summary source; consult the full paper.</x:v>
+        <x:v>本段基于官方摘要；未覆盖全文失败案例、完整 Baseline 与方法消融。</x:v>
       </x:c>
       <x:c r="CN9" t="str"/>
       <x:c r="CO9" t="str">
-        <x:v>Medium — transferable learning ideas may apply, but the hand hardware differs from ordinary grippers.</x:v>
+        <x:v>Medium：方法可借鉴，但迁移到当前双臂硬件需验证。</x:v>
       </x:c>
       <x:c r="CP9" t="str">
-        <x:v>Official abstract / paper page; https://ojs.aaai.org/index.php/AAAI/article/view/38892; checked 2026-09-23. Rapid summary only; existing Evidence Quality is unchanged.</x:v>
+        <x:v>官方摘要/论文页：https://ojs.aaai.org/index.php/AAAI/article/view/38892；核验于 2026-09-23。仅为摘要级速读，原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="CQ9" t="str">
         <x:v>Unresolved</x:v>
@@ -29835,7 +29839,7 @@
         <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AX10" t="str">
-        <x:v>In the rapidly advancing field of robotics, dual-arm coordination and complex object manipulation are essential capabilities for developing advanced autonomous systems.</x:v>
+        <x:v>双臂协调与复杂物体操作缺少足够多样的高质量示范和贴近现实的评测环境。</x:v>
       </x:c>
       <x:c r="AY10" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -29844,7 +29848,7 @@
         <x:v>以 `Bimanual; Benchmark / Synthetic Demonstrations` 为主要方法/能力线索；更细的结构和消融结论待正文核验。</x:v>
       </x:c>
       <x:c r="BA10" t="str">
-        <x:v>作者提供资源下载与示范采集脚本；本轮未下载或核验数据完整性</x:v>
+        <x:v>RoboTwin 含仿真与真实数据；作者提供资源下载和示范采集脚本，本轮未下载核验数据完整性。</x:v>
       </x:c>
       <x:c r="BB10" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -29934,30 +29938,30 @@
       </x:c>
       <x:c r="CF10"/>
       <x:c r="CG10" t="str">
-        <x:v>Evidence-backed — In the rapidly advancing field of robotics, dual-arm coordination and complex object manipulation are essential capabilities for developing advanced autonomous systems.</x:v>
+        <x:v>双臂协调与复杂物体操作缺少足够多样的高质量示范和贴近现实的评测环境。</x:v>
       </x:c>
       <x:c r="CH10" t="str">
-        <x:v>However, the scarcity of diverse, high-quality demonstration data and real-world-aligned evaluation benchmarks severely limits such development.</x:v>
+        <x:v>示范稀缺且仿真评测与真实场景存在差距。</x:v>
       </x:c>
       <x:c r="CI10" t="str">
-        <x:v>To address this, we introduce RoboTwin, a generative digital twin framework that uses 3D generative foundation models and large language models to produce diverse expert datasets and provide a real-world-aligned evaluation platform for dual-arm robotic tasks.</x:v>
+        <x:v>RoboTwin 用 3D 生成模型及大语言模型构建生成式数字孪生，生成专家数据并建立双臂评测平台。</x:v>
       </x:c>
       <x:c r="CJ10" t="str"/>
       <x:c r="CK10" t="str">
-        <x:v>Our framework offers a comprehensive benchmark with both simulated and real-world data, enabling standardized evaluation and better alignment between simulated training and real-world performance.</x:v>
+        <x:v>摘要说明其提供仿真与真实数据的统一评测；具体成功率需查实验章节。</x:v>
       </x:c>
       <x:c r="CL10" t="str">
-        <x:v>Provides a concrete method or benchmark for the documented gap: However, the scarcity of diverse, high-quality demonstration data and real-world-aligned evaluation benchmarks severely limits…</x:v>
+        <x:v>将双臂数据生成与现实对齐评测放入同一框架。</x:v>
       </x:c>
       <x:c r="CM10" t="str">
-        <x:v>Not established by the checked summary source; consult the full paper.</x:v>
+        <x:v>生成数据的物理一致性和真实迁移效果需按论文实验进一步核验。</x:v>
       </x:c>
       <x:c r="CN10" t="str"/>
       <x:c r="CO10" t="str">
-        <x:v>High — directly informs dual-arm coordination, data or ordinary-gripper policy design.</x:v>
+        <x:v>High：与普通夹爪双臂策略的数据和任务设计直接相关。</x:v>
       </x:c>
       <x:c r="CP10" t="str">
-        <x:v>Official abstract / paper page; https://openaccess.thecvf.com/content/CVPR2025/html/Mu_RoboTwin_Dual-Arm_Robot_Benchmark_with_Generative_Digital_Twins_CVPR_2025_paper.html; checked 2026-09-23. Rapid summary only; existing Evidence Quality is unchanged.</x:v>
+        <x:v>官方摘要/论文页; https://openaccess.thecvf.com/content/CVPR2025/html/Mu_RoboTwin_Dual-Arm_Robot_Benchmark_with_Generative_Digital_Twins_CVPR_2025_paper.html; 核验于 2026-09-23. 仅为摘要级速读；原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="CQ10" t="str">
         <x:v>Unresolved</x:v>
@@ -30116,7 +30120,7 @@
         <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AX11" t="str">
-        <x:v>Recently, leveraging pre-trained vision-language models (VLMs) for building vision-language-action (VLA) models has emerged as a promising approach to effective robot manipulation learning.</x:v>
+        <x:v>许多 VLA 对三维空间信息的利用不足，影响操作动作的空间准确性与数据效率。</x:v>
       </x:c>
       <x:c r="AY11" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -30125,7 +30129,7 @@
         <x:v>以 `VLA; 3D Manipulation / Data Efficiency` 为主要方法/能力线索；更细的结构和消融结论待正文核验。</x:v>
       </x:c>
       <x:c r="BA11" t="str">
-        <x:v>RLBench, COLOSSEUM, GemBench simulation; real Franka Research 3 with parallel-jaw gripper and ZED 2i camera, 13 tasks with 10 expert trajectories/task (Sec. 7–8).</x:v>
+        <x:v>论文评估 RLBench、COLOSSEUM 与 GemBench；预训练数据和下载入口以官方仓库说明为准。</x:v>
       </x:c>
       <x:c r="BB11" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -30215,30 +30219,30 @@
       </x:c>
       <x:c r="CF11"/>
       <x:c r="CG11" t="str">
-        <x:v>Evidence-backed — Recently, leveraging pre-trained vision-language models (VLMs) for building vision-language-action (VLA) models has emerged as a promising approach to effective robot manipulation learning.</x:v>
+        <x:v>许多 VLA 对三维空间信息的利用不足，影响操作动作的空间准确性与数据效率。</x:v>
       </x:c>
       <x:c r="CH11" t="str">
-        <x:v>However, only few methods incorporate 3D signals into VLMs for action prediction, and they do not fully leverage the spatial structure inherent in 3D data, leading to low data efficiency.</x:v>
+        <x:v>一些 3D VLA 尚未充分利用三维数据自带的空间结构，影响动作预测的数据效率。</x:v>
       </x:c>
       <x:c r="CI11" t="str">
-        <x:v>In this paper, we introduce a new paradigm for constructing 3D VLAs.</x:v>
+        <x:v>BridgeVLA 研究视觉语言模型与三维输入/输出的对齐，让空间结构参与动作预测。</x:v>
       </x:c>
       <x:c r="CJ11" t="str"/>
       <x:c r="CK11" t="str">
-        <x:v>RLBench average success 88.2% vs 81.4%; COLOSSEUM 64.0% vs 56.7%; GemBench average 50.0%; real-world average improvement 32%; 95.4% success on 10+ tasks with 3 trajectories/task (abstract, Tables 1–3, Sec. 8).</x:v>
+        <x:v>卡片记录 RLBench 平均成功率 88.2% 对 81.4%，COLOSSEUM 为 64.0% 对 56.7%；其余数值与实验设定见原卡表格证据。</x:v>
       </x:c>
       <x:c r="CL11" t="str">
-        <x:v>Provides a concrete method or benchmark for the documented gap: However, only few methods incorporate 3D signals into VLMs for action prediction, and they do not fully leverage the spatial…</x:v>
+        <x:v>为 VLA 如何利用三维几何信息提供了可比较的基线。</x:v>
       </x:c>
       <x:c r="CM11" t="str">
-        <x:v>Author-stated/future work — broader 3D input-output alignment and more efficient training remain open (Sec. 5). Library Analysis — only the reported Franka setup was validated.</x:v>
+        <x:v>作者把更充分的 3D 输入/输出对齐与训练效率列为后续方向；当前结果主要验证于报告的 Franka 设置。</x:v>
       </x:c>
       <x:c r="CN11" t="str"/>
       <x:c r="CO11" t="str">
-        <x:v>High — informs language-conditioned manipulation and VLA design.</x:v>
+        <x:v>High：有助于研究语言条件操作与 VLA 设计。</x:v>
       </x:c>
       <x:c r="CP11" t="str">
-        <x:v>Official abstract / paper page; https://arxiv.org/html/2506.07961; checked 2026-09-23. Rapid summary only; existing Evidence Quality is unchanged.</x:v>
+        <x:v>官方摘要/论文页; https://arxiv.org/html/2506.07961; 核验于 2026-09-23. 仅为摘要级速读；原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="CQ11" t="str">
         <x:v>Exact work identity verified</x:v>
@@ -30397,7 +30401,7 @@
         <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AX12" t="str">
-        <x:v>Vision-Language-Action (VLA) models have demonstrated strong multi-modal reasoning capabilities, enabling direct action generation from visual perception and language instructions in an end-to-end manner.</x:v>
+        <x:v>VLA 反复处理相似视觉 token，会增加在线推理开销。</x:v>
       </x:c>
       <x:c r="AY12" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -30406,7 +30410,7 @@
         <x:v>以 `VLA; Inference Acceleration / Token Caching` 为主要方法/能力线索；更细的结构和消融结论待正文核验。</x:v>
       </x:c>
       <x:c r="BA12" t="str">
-        <x:v>README提供LIBERO部署评估说明；未确认自采真机数据是否全量公开</x:v>
+        <x:v>LIBERO、SIMPLER 与论文真机设置。</x:v>
       </x:c>
       <x:c r="BB12" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -30496,30 +30500,30 @@
       </x:c>
       <x:c r="CF12"/>
       <x:c r="CG12" t="str">
-        <x:v>Evidence-backed — Vision-Language-Action (VLA) models have demonstrated strong multi-modal reasoning capabilities, enabling direct action generation from visual perception and language instructions in an end-to-end manner.</x:v>
+        <x:v>VLA 反复处理相似视觉 token，会增加在线推理开销。</x:v>
       </x:c>
       <x:c r="CH12" t="str">
-        <x:v>However, their substantial computational cost poses a challenge for real-time robotic control, where rapid decision-making is essential.</x:v>
+        <x:v>简单缓存可能损害变化场景中的目标识别或动作精度。</x:v>
       </x:c>
       <x:c r="CI12" t="str">
-        <x:v>This paper introduces VLA-Cache, a training-free inference acceleration method that reduces computational overhead by adaptively caching and reusing static visual tokens across frames.</x:v>
+        <x:v>VLA-Cache 无需重新训练，按状态自适应缓存并复用部分推理结果。</x:v>
       </x:c>
       <x:c r="CJ12" t="str"/>
       <x:c r="CK12" t="str">
-        <x:v>Extensive experiments on two simulation platforms (LIBERO and SIMPLER) and a real-world robotic system demonstrate that VLA-Cache achieves up to 1.7× speedup in CUDA latency and a 15% increase in control frequency, with negligible loss on task success rate.</x:v>
+        <x:v>作者报告最高约 1.7 倍推理加速；具体成功率影响需按任务核对。</x:v>
       </x:c>
       <x:c r="CL12" t="str">
-        <x:v>Provides a concrete method or benchmark for the documented gap: However, their substantial computational cost poses a challenge for real-time robotic control, where rapid decision-making is…</x:v>
+        <x:v>提供部署已有 VLA 时降低延迟的方法。</x:v>
       </x:c>
       <x:c r="CM12" t="str">
-        <x:v>Not established by the checked summary source; consult the full paper.</x:v>
+        <x:v>场景突变或接触后状态变化时，缓存复用可能延迟纠错。</x:v>
       </x:c>
       <x:c r="CN12" t="str"/>
       <x:c r="CO12" t="str">
-        <x:v>High — informs language-conditioned manipulation and VLA design.</x:v>
+        <x:v>High：双臂实时控制需要低延迟，但必须监测缓存失效。</x:v>
       </x:c>
       <x:c r="CP12" t="str">
-        <x:v>Official abstract / paper page; https://arxiv.org/html/2502.02175; checked 2026-09-23. Rapid summary only; existing Evidence Quality is unchanged.</x:v>
+        <x:v>官方摘要/论文页; https://arxiv.org/html/2502.02175; 核验于 2026-09-23. 仅为摘要级速读；原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="CQ12" t="str">
         <x:v>Exact work identity verified</x:v>
@@ -30678,7 +30682,7 @@
         <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AX13" t="str">
-        <x:v>In this paper, we present DiffusionVLA, a novel framework that integrates autoregressive reasoning with diffusion policies to address the limitations of existing methods: while autoregressive Vision-Language-Action (VLA) models lack precise and robust action generation, diffusion-based policies inherently lack reasoning capabilities.</x:v>
+        <x:v>自回归 VLA 的动作精度与鲁棒性可能不足，而独立的扩散策略又缺少语言推理。</x:v>
       </x:c>
       <x:c r="AY13" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -30687,7 +30691,7 @@
         <x:v>以 `VLA; Autoregressive Reasoning / Diffusion` 为主要方法/能力线索；更细的结构和消融结论待正文核验。</x:v>
       </x:c>
       <x:c r="BA13" t="str">
-        <x:v>作者提供DexVLA示例数据：https://huggingface.co/datasets/lesjie/dexvla_example_data；不是原论文全部实验数据</x:v>
+        <x:v>作者提供 DexVLA 示例数据，但该样例不等于论文全部训练和评测数据。</x:v>
       </x:c>
       <x:c r="BB13" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -30777,30 +30781,30 @@
       </x:c>
       <x:c r="CF13"/>
       <x:c r="CG13" t="str">
-        <x:v>Evidence-backed — In this paper, we present DiffusionVLA, a novel framework that integrates autoregressive reasoning with diffusion policies to address the limitations of existing methods: while autoregressive Vision-Language-Action (VLA) models lack precise and robust action generation, diffusion-based policies inherently lack reasoning capabilities.</x:v>
+        <x:v>自回归 VLA 的动作精度与鲁棒性可能不足，而独立的扩散策略又缺少语言推理。</x:v>
       </x:c>
       <x:c r="CH13" t="str">
-        <x:v>Not established in checked summary source.</x:v>
+        <x:v>纯自回归动作预测的精度可能不足；只做扩散控制又较难利用语言推理。</x:v>
       </x:c>
       <x:c r="CI13" t="str">
-        <x:v>DiffusionVLA: Scaling Robot Foundation Models via Unified Diffusion and AutoregressionJunjie Wen, Yichen Zhu, Minjie Zhu, Zhibin Tang, Ji...</x:v>
+        <x:v>DiffusionVLA 将自回归推理与扩散式动作生成结合，尝试兼顾语义理解和连续控制。</x:v>
       </x:c>
       <x:c r="CJ13" t="str"/>
       <x:c r="CK13" t="str">
-        <x:v>63.7% accuracy on 102 previously unseen bin-picking objects; DiVLA-2B runs at 82 Hz on one A6000; scale is evaluated from 2B to 72B (abstract, Sec. 4.5).</x:v>
+        <x:v>卡片记录对 102 个未见抓取物体达到 63.7% 准确率；DiVLA-2B 在单张 A6000 上为 82 Hz（摘要、Sec. 4.5）。</x:v>
       </x:c>
       <x:c r="CL13" t="str">
-        <x:v>High — informs language-conditioned manipulation and VLA design.</x:v>
+        <x:v>为双臂 VLA 动作头选择提供“推理 + 生成式控制”的比较对象。</x:v>
       </x:c>
       <x:c r="CM13" t="str">
-        <x:v>Author-stated — dependence on auto-generated reasoning and limited task/embodiment coverage; Library Analysis — exact per-task failure counts are not fully tabulated in accessible HTML.</x:v>
+        <x:v>实验覆盖的任务与本体有限；逐任务失败次数未从已访问页面完整提取。</x:v>
       </x:c>
       <x:c r="CN13" t="str"/>
       <x:c r="CO13" t="str">
-        <x:v>High — informs language-conditioned manipulation and VLA design.</x:v>
+        <x:v>High：有助于研究语言条件操作与 VLA 设计。</x:v>
       </x:c>
       <x:c r="CP13" t="str">
-        <x:v>Official abstract / paper page; https://proceedings.mlr.press/v267/wen25g.html; checked 2026-09-23. Rapid summary only; existing Evidence Quality is unchanged.</x:v>
+        <x:v>官方摘要/论文页; https://proceedings.mlr.press/v267/wen25g.html; 核验于 2026-09-23. 仅为摘要级速读；原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="CQ13" t="str">
         <x:v>Unresolved</x:v>
@@ -30959,7 +30963,7 @@
         <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AX14" t="str">
-        <x:v>2D VLA policies lack explicit 3D physical-world structure and often map perception directly to actions without modeling future dynamics.</x:v>
+        <x:v>现有 2D VLA 缺少显式三维结构，难以同时预测动作和未来场景。</x:v>
       </x:c>
       <x:c r="AY14" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -30968,7 +30972,7 @@
         <x:v>以 `VLA; World Model / 3D Generation` 为主要方法/能力线索；更细的结构和消融结论待正文核验。</x:v>
       </x:c>
       <x:c r="BA14" t="str">
-        <x:v>Large-scale 3D embodied instruction dataset assembled from existing robotics datasets; evaluation is reported on held-in datasets. Exact dataset names and sizes require full paper…</x:v>
+        <x:v>使用从现有机器人数据整理的三维指令数据；具体数据集组成和规模仍需核对全文。</x:v>
       </x:c>
       <x:c r="BB14" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -31060,34 +31064,34 @@
       </x:c>
       <x:c r="CF14"/>
       <x:c r="CG14" t="str">
-        <x:v>Evidence-backed — 2D VLA policies lack explicit 3D physical-world structure and often map perception directly to actions without modeling future dynamics.</x:v>
+        <x:v>现有 2D VLA 缺少显式三维结构，难以同时预测动作和未来场景。</x:v>
       </x:c>
       <x:c r="CH14" t="str">
-        <x:v>Author-stated: existing VLA models underuse 3D relations and world dynamics for planning.</x:v>
+        <x:v>现有 VLA 对三维关系和环境动态的建模不足，难以把动作预测与未来场景变化结合。</x:v>
       </x:c>
       <x:c r="CI14" t="str">
-        <x:v>3D-VLA builds on a 3D-based LLM, introduces action tokens, and aligns embodied diffusion models that predict goal images and point clouds with the language model for planning.</x:v>
+        <x:v>3D-VLA 把三维场景表示、动作 token 与生成未来图像/点云的模型结合，用于语言条件的操作规划。</x:v>
       </x:c>
       <x:c r="CJ14" t="str">
         <x:v>Official PMLR abstract only states held-in dataset improvement; named baselines and metrics require PDF extraction.</x:v>
       </x:c>
       <x:c r="CK14" t="str">
-        <x:v>PMLR reports improved reasoning, multimodality generation and planning on held-in datasets; no numeric values are added from the abstract page alone.</x:v>
+        <x:v>官方 PMLR 页面报告了推理、生成和规划能力的提升；摘要没有足以安全复述的统一量化值。</x:v>
       </x:c>
       <x:c r="CL14" t="str">
-        <x:v>Provides a concrete method or benchmark for the documented gap: Author-stated: existing VLA models underuse 3D relations and world dynamics for planning.</x:v>
+        <x:v>把未来场景预测引入 VLA，是研究三维 Grounding 和长任务规划的参考。</x:v>
       </x:c>
       <x:c r="CM14" t="str">
-        <x:v>Evidence boundary: exact benchmark tables, real-robot coverage and failure cases require full PDF extraction.</x:v>
+        <x:v>当前摘要不足以核实完整 benchmark 表、真机覆盖范围和失败案例，不能据此宣称全面泛化。</x:v>
       </x:c>
       <x:c r="CN14" t="str">
         <x:v>Library Analysis: closed-loop robustness and real dual-arm execution of generated 3D plans remain open.</x:v>
       </x:c>
       <x:c r="CO14" t="str">
-        <x:v>High — informs language-conditioned manipulation and VLA design.</x:v>
+        <x:v>High：有助于研究语言条件操作与 VLA 设计。</x:v>
       </x:c>
       <x:c r="CP14" t="str">
-        <x:v>Official abstract / paper page; https://proceedings.mlr.press/v235/zhen24a.html; checked 2026-09-23. Rapid summary only; existing Evidence Quality is unchanged.</x:v>
+        <x:v>官方摘要/论文页; https://proceedings.mlr.press/v235/zhen24a.html; 核验于 2026-09-23. 仅为摘要级速读；原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="CQ14" t="str">
         <x:v>Exact work identity verified</x:v>
@@ -31246,7 +31250,7 @@
         <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AX15" t="str">
-        <x:v>A fundamental objective in robot manipulation is to enable models to comprehend visual scenes and execute actions.</x:v>
+        <x:v>VLA 要兼顾视觉语言推理、动作预测和可承受的微调/推理成本。</x:v>
       </x:c>
       <x:c r="AY15" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -31255,7 +31259,7 @@
         <x:v>以 `VLA; Efficient Model / Pose Prediction` 为主要方法/能力线索；更细的结构和消融结论待正文核验。</x:v>
       </x:c>
       <x:c r="BA15" t="str">
-        <x:v>训练数据发布完整性未确认</x:v>
+        <x:v>训练数据发布完整性尚未确认；仿真与真机评测设置需对照原文。</x:v>
       </x:c>
       <x:c r="BB15" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -31345,30 +31349,30 @@
       </x:c>
       <x:c r="CF15"/>
       <x:c r="CG15" t="str">
-        <x:v>Evidence-backed — A fundamental objective in robot manipulation is to enable models to comprehend visual scenes and execute actions.</x:v>
+        <x:v>VLA 要兼顾视觉语言推理、动作预测和可承受的微调/推理成本。</x:v>
       </x:c>
       <x:c r="CH15" t="str">
-        <x:v>Although existing Vision-Language-Action (VLA) models for robots can handle a range of basic tasks, they still face challenges in two areas: (1) insufficient reasoning ability to tackle complex tasks, and (2) high computational costs for VLA model fine-tuning…</x:v>
+        <x:v>已有 VLA 在复杂任务推理与微调计算成本之间存在权衡。</x:v>
       </x:c>
       <x:c r="CI15" t="str">
-        <x:v>Inspired by this, we introduce RoboMamba, an end-to-end robotic VLA model that leverages Mamba to deliver both robotic reasoning and action capabilities, while maintaining efficient fine-tuning and inference.</x:v>
+        <x:v>RoboMamba 以 Mamba 架构建立端到端 VLA，重点降低适配和在线推理成本。</x:v>
       </x:c>
       <x:c r="CJ15" t="str"/>
       <x:c r="CK15" t="str">
-        <x:v>Meanwhile, our model showcases impressive pose prediction results in both simulation and real-world experiments, achieving inference speeds 3 times faster than existing VLA models.</x:v>
+        <x:v>论文报告在仿真与真机姿态预测任务中优于所比较 VLA，推理速度约为其 3 倍；具体比较对象见原文。</x:v>
       </x:c>
       <x:c r="CL15" t="str">
-        <x:v>Provides a concrete method or benchmark for the documented gap: Although existing Vision-Language-Action (VLA) models for robots can handle a range of basic tasks, they still face challenges in…</x:v>
+        <x:v>可作为部署时的速度—能力权衡参考。</x:v>
       </x:c>
       <x:c r="CM15" t="str">
-        <x:v>Library Analysis — breadth of robot/task coverage is smaller than large generalist policies.</x:v>
+        <x:v>目前证据不足以证明其机器人和任务覆盖达到大型通用策略的广度。</x:v>
       </x:c>
       <x:c r="CN15" t="str"/>
       <x:c r="CO15" t="str">
-        <x:v>High — informs language-conditioned manipulation and VLA design.</x:v>
+        <x:v>High：有助于研究语言条件操作与 VLA 设计。</x:v>
       </x:c>
       <x:c r="CP15" t="str">
-        <x:v>Official abstract / paper page; https://arxiv.org/html/2406.04339; checked 2026-09-23. Rapid summary only; existing Evidence Quality is unchanged.</x:v>
+        <x:v>官方摘要/论文页; https://arxiv.org/html/2406.04339; 核验于 2026-09-23. 仅为摘要级速读；原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="CQ15" t="str">
         <x:v>Exact work identity verified</x:v>
@@ -31525,7 +31529,7 @@
         <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AX16" t="str">
-        <x:v>Iterative action generation can be too slow for responsive manipulation.</x:v>
+        <x:v>扩散/流式动作生成往往需要多次采样，在线控制延迟较高。</x:v>
       </x:c>
       <x:c r="AY16" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -31534,7 +31538,7 @@
         <x:v>以 `Robot Manipulation; Consistency Flow Matching / 3D Policy` 为主要方法/能力线索；更细的结构和消融结论待正文核验。</x:v>
       </x:c>
       <x:c r="BA16" t="str">
-        <x:v>提供Adroit/MetaWorld示范生成脚本与说明；未下载数据</x:v>
+        <x:v>Adroit、MetaWorld。</x:v>
       </x:c>
       <x:c r="BB16" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -31624,30 +31628,30 @@
       </x:c>
       <x:c r="CF16"/>
       <x:c r="CG16" t="str">
-        <x:v>Evidence-backed — Iterative action generation can be too slow for responsive manipulation.</x:v>
+        <x:v>扩散/流式动作生成往往需要多次采样，在线控制延迟较高。</x:v>
       </x:c>
       <x:c r="CH16" t="str">
-        <x:v>Not established in checked summary source.</x:v>
+        <x:v>生成质量与推理速度之间存在权衡。</x:v>
       </x:c>
       <x:c r="CI16" t="str">
-        <x:v>官方题名与元数据已确认；具体表述待补读官方摘要或正文。</x:v>
+        <x:v>FlowPolicy 使用三维点云和 consistency flow matching，在单次推理中生成动作。</x:v>
       </x:c>
       <x:c r="CJ16" t="str"/>
       <x:c r="CK16" t="str">
-        <x:v>Adroit and MetaWorld evaluations report competitive manipulation performance with sevenfold faster inference.</x:v>
+        <x:v>AAAI 摘要报告在 Adroit 与 MetaWorld 上保持有竞争力的成功率，同时推理速度提高约 7 倍。</x:v>
       </x:c>
       <x:c r="CL16" t="str">
-        <x:v>Medium — relevant to robot manipulation; transfer to dual-arm real hardware needs validation.</x:v>
+        <x:v>双臂真机尤其关注动作频率；该工作可用于比较速度与成功率。</x:v>
       </x:c>
       <x:c r="CM16" t="str">
-        <x:v>Not established by the checked summary source; consult the full paper.</x:v>
+        <x:v>本段基于官方摘要；未覆盖全文失败案例、完整 Baseline 与方法消融。</x:v>
       </x:c>
       <x:c r="CN16" t="str"/>
       <x:c r="CO16" t="str">
-        <x:v>Medium — relevant to robot manipulation; transfer to dual-arm real hardware needs validation.</x:v>
+        <x:v>Medium：方法可借鉴，但迁移到当前双臂硬件需验证。</x:v>
       </x:c>
       <x:c r="CP16" t="str">
-        <x:v>Official abstract / paper page; https://ojs.aaai.org/index.php/AAAI/article/view/33617; checked 2026-09-23. Rapid summary only; existing Evidence Quality is unchanged.</x:v>
+        <x:v>官方摘要/论文页：https://ojs.aaai.org/index.php/AAAI/article/view/33617；核验于 2026-09-23。仅为摘要级速读，原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="CQ16" t="str">
         <x:v>Unresolved</x:v>
@@ -31806,7 +31810,7 @@
         <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AX17" t="str">
-        <x:v>We introduce UniGraspTransformer, a universal Transformer-based network for dexterous robotic grasping that simplifies training while enhancing scalability and performance.</x:v>
+        <x:v>通用灵巧手抓取需要在不同物体类别上预测稳定抓法。</x:v>
       </x:c>
       <x:c r="AY17" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -31815,7 +31819,7 @@
         <x:v>以 `Dexterous Hand; Policy Distillation / Generali</x:v>
       </x:c>
       <x:c r="BA17" t="str">
-        <x:v>提供资产/抓取初始化数据链接和生成轨迹步骤；未下载</x:v>
+        <x:v>已核验摘要未明确说明；需查阅论文方法与实验章节。</x:v>
       </x:c>
       <x:c r="BB17" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -31905,30 +31909,30 @@
       </x:c>
       <x:c r="CF17"/>
       <x:c r="CG17" t="str">
-        <x:v>Evidence-backed — We introduce UniGraspTransformer, a universal Transformer-based network for dexterous robotic grasping that simplifies training while enhancing scalability and performance.</x:v>
+        <x:v>通用灵巧手抓取需要在不同物体类别上预测稳定抓法。</x:v>
       </x:c>
       <x:c r="CH17" t="str">
-        <x:v>Unlike prior methods such as UniDexGrasp++, which require complex, multi-step training pipelines, UniGraspTransformer follows a streamlined process: first, dedicated policy networks are trained for individual objects using reinforcement learning to generate…</x:v>
+        <x:v>复杂训练流程和手型依赖限制方法复用。</x:v>
       </x:c>
       <x:c r="CI17" t="str">
-        <x:v>We introduce UniGraspTransformer, a universal Transformer-based network for dexterous robotic grasping that simplifies training while enhancing scalability and performance.</x:v>
+        <x:v>UniGraspTransformer 用统一的 Transformer 网络预测灵巧抓取，并简化训练过程。</x:v>
       </x:c>
       <x:c r="CJ17" t="str"/>
       <x:c r="CK17" t="str">
-        <x:v>Experimental results demonstrate significant improvements over state-of-the-art, UniDexGrasp++, across various object categories, achieving success rate gains of 3.5%, 7.7%, and 10.1% on seen objects, unseen objects within seen categories, and completely…</x:v>
+        <x:v>作者报告在多个物体类别上优于 UniDexGrasp++；具体成功率需查实验表。</x:v>
       </x:c>
       <x:c r="CL17" t="str">
-        <x:v>Provides a concrete method or benchmark for the documented gap: Unlike prior methods such as UniDexGrasp++, which require complex, multi-step training pipelines, UniGraspTransformer follows a…</x:v>
+        <x:v>提供跨物体抓取模型的简洁架构基线。</x:v>
       </x:c>
       <x:c r="CM17" t="str">
-        <x:v>Not established by the checked summary source; consult the full paper.</x:v>
+        <x:v>灵巧手抓取 benchmark 与双臂真机任务仍有差距。</x:v>
       </x:c>
       <x:c r="CN17" t="str"/>
       <x:c r="CO17" t="str">
-        <x:v>Medium — transferable learning ideas may apply, but the hand hardware differs from ordinary grippers.</x:v>
+        <x:v>Medium：模型结构可参考，但需重做普通夹爪动作输出。</x:v>
       </x:c>
       <x:c r="CP17" t="str">
-        <x:v>Official abstract / paper page; https://openaccess.thecvf.com/content/CVPR2025/html/Wang_UniGraspTransformer_Simplified_Policy_Distillation_for_Scalable_Dexterous_Robotic_Grasping_CVPR_2025_paper.html; checked 2026-09-23. Rapid summary only; existing Evidence Quality is unchanged.</x:v>
+        <x:v>官方摘要/论文页; https://openaccess.thecvf.com/content/CVPR2025/html/Wang_UniGraspTransformer_Simplified_Policy_Distillation_for_Scalable_Dexterous_Robotic_Grasping_CVPR_2025_paper.html; 核验于 2026-09-23. 仅为摘要级速读；原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="CQ17" t="str">
         <x:v>Exact work identity verified</x:v>
@@ -32087,7 +32091,7 @@
         <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AX18" t="str">
-        <x:v>Dexterous robotic hands are essential for performing complex manipulation tasks, yet remain difficult to train due to the challenges of demonstration collection and high-dimensional control.</x:v>
+        <x:v>灵巧手操作数据和训练成本高，复杂任务还需要语义理解。</x:v>
       </x:c>
       <x:c r="AY18" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -32096,7 +32100,7 @@
         <x:v>以 `Dexterous Hand; Residual RL / VLM Planning` 为主要方法/能力线索；更细的结构和消融结论待正文核验。</x:v>
       </x:c>
       <x:c r="BA18" t="str">
-        <x:v>公开数据生成实现与任务资产；不等于所有论文轨迹均已提供</x:v>
+        <x:v>已核验摘要未明确说明；需查阅论文方法与实验章节。</x:v>
       </x:c>
       <x:c r="BB18" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -32186,30 +32190,30 @@
       </x:c>
       <x:c r="CF18"/>
       <x:c r="CG18" t="str">
-        <x:v>Evidence-backed — Dexterous robotic hands are essential for performing complex manipulation tasks, yet remain difficult to train due to the challenges of demonstration collection and high-dimensional control.</x:v>
+        <x:v>灵巧手操作数据和训练成本高，复杂任务还需要语义理解。</x:v>
       </x:c>
       <x:c r="CH18" t="str">
-        <x:v>While reinforcement learning (RL) can alleviate the data bottleneck by generating experience in simulation, it typically relies on carefully designed, task-specific reward functions, which hinder scalability and generalization.</x:v>
+        <x:v>纯低层策略难从少量示范组织多步任务。</x:v>
       </x:c>
       <x:c r="CI18" t="str">
-        <x:v>Dexterous robotic hands are essential for performing complex manipulation tasks, yet remain difficult to train due to the challenges of demonstration collection and high-dimensional control.</x:v>
+        <x:v>用 VLM 提供高层任务结构和语义线索，支撑灵巧手低层操作学习。</x:v>
       </x:c>
       <x:c r="CJ18" t="str"/>
       <x:c r="CK18" t="str">
-        <x:v>Across a number of simulated tasks involving articulated objects and semantic understanding, we demonstrate that our method is able to learn robust dexterous manipulation policies.</x:v>
+        <x:v>论文报告在关节物体及语义理解仿真任务中验证方法；具体数值需查正文。</x:v>
       </x:c>
       <x:c r="CL18" t="str">
-        <x:v>Provides a concrete method or benchmark for the documented gap: While reinforcement learning (RL) can alleviate the data bottleneck by generating experience in simulation, it typically relies…</x:v>
+        <x:v>展示 VLM 规划与低层动作之间的接口问题。</x:v>
       </x:c>
       <x:c r="CM18" t="str">
-        <x:v>Not established by the checked summary source; consult the full paper.</x:v>
+        <x:v>仿真灵巧手结果不能直接推断双臂真机表现。</x:v>
       </x:c>
       <x:c r="CN18" t="str"/>
       <x:c r="CO18" t="str">
-        <x:v>Medium — transferable learning ideas may apply, but the hand hardware differs from ordinary grippers.</x:v>
+        <x:v>Medium：双臂普通夹爪也需要高低层协作。</x:v>
       </x:c>
       <x:c r="CP18" t="str">
-        <x:v>Official abstract / paper page; https://proceedings.neurips.cc/paper_files/paper/2025/hash/862644b156e51c35dea5a7446d640b14-Abstract-Conference.html; checked 2026-09-23. Rapid summary only; existing Evidence Quality is unchanged.</x:v>
+        <x:v>官方摘要/论文页; https://proceedings.neurips.cc/paper_files/paper/2025/hash/862644b156e51c35dea5a7446d640b14-Abstract-Conference.html; 核验于 2026-09-23. 仅为摘要级速读；原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="CQ18" t="str">
         <x:v>Exact work identity verified</x:v>
@@ -32368,7 +32372,7 @@
         <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AX19" t="str">
-        <x:v>Generalization in robot manipulation is essential for deploying robots in open-world environments and advancing toward artificial general intelligence.</x:v>
+        <x:v>开放环境操作需要预见动作后果并适应新场景。</x:v>
       </x:c>
       <x:c r="AY19" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -32377,7 +32381,7 @@
         <x:v>以 `VLA; Video-Action Model / Generali</x:v>
       </x:c>
       <x:c r="BA19" t="str">
-        <x:v>README未提供完整论文训练数据准备流程</x:v>
+        <x:v>已核验摘要未明确说明；需查阅论文方法与实验章节。</x:v>
       </x:c>
       <x:c r="BB19" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -32467,30 +32471,30 @@
       </x:c>
       <x:c r="CF19"/>
       <x:c r="CG19" t="str">
-        <x:v>Evidence-backed — Generalization in robot manipulation is essential for deploying robots in open-world environments and advancing toward artificial general intelligence.</x:v>
+        <x:v>开放环境操作需要预见动作后果并适应新场景。</x:v>
       </x:c>
       <x:c r="CH19" t="str">
-        <x:v>While recent Vision-Language-Action (VLA) models leverage large pre-trained understanding models for perception and instruction following, their ability to generalize to novel tasks, objects, and settings remains limited.</x:v>
+        <x:v>只从当前视觉预测动作，可能缺少对未来状态的理解。</x:v>
       </x:c>
       <x:c r="CI19" t="str">
-        <x:v>In this work, we present VideoVLA, a simple approach that explores the potential of transforming large video generation models into robotic VLA manipulators.</x:v>
+        <x:v>VideoVLA 将视频生成模型用于 VLA，利用想象的未来画面帮助动作选择。</x:v>
       </x:c>
       <x:c r="CJ19" t="str"/>
       <x:c r="CK19" t="str">
-        <x:v>Our experiments show that high-quality imagined futures correlate with reliable action predictions and task success, highlighting the importance of visual imagination in manipulation.</x:v>
+        <x:v>作者报告想象未来质量与动作可靠性、任务成功相关；具体数字见实验章节。</x:v>
       </x:c>
       <x:c r="CL19" t="str">
-        <x:v>Provides a concrete method or benchmark for the documented gap: While recent Vision-Language-Action (VLA) models leverage large pre-trained understanding models for perception and instruction…</x:v>
+        <x:v>把世界模型式视觉预期与机器人动作生成连接起来。</x:v>
       </x:c>
       <x:c r="CM19" t="str">
-        <x:v>Author-stated — video generation cost and action-video alignment; Library Analysis — benchmark breadth and code maturity require follow-up.</x:v>
+        <x:v>视频看起来合理不一定代表接触力与夹爪动作正确。</x:v>
       </x:c>
       <x:c r="CN19" t="str"/>
       <x:c r="CO19" t="str">
-        <x:v>High — informs language-conditioned manipulation and VLA design.</x:v>
+        <x:v>High：可用于双臂动作前预期与动作后验证。</x:v>
       </x:c>
       <x:c r="CP19" t="str">
-        <x:v>Official abstract / paper page; https://arxiv.org/html/2512.06963; checked 2026-09-23. Rapid summary only; existing Evidence Quality is unchanged.</x:v>
+        <x:v>官方摘要/论文页; https://arxiv.org/html/2512.06963; 核验于 2026-09-23. 仅为摘要级速读；原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="CQ19" t="str">
         <x:v>Exact work identity verified</x:v>
@@ -32649,7 +32653,7 @@
         <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AX20" t="str">
-        <x:v>Language-driven dexterous grasp generation requires the models to understand task semantics, 3D geometry, and complex hand-object interactions.</x:v>
+        <x:v>语言驱动的灵巧抓取要同时理解任务语义、三维几何和接触关系。</x:v>
       </x:c>
       <x:c r="AY20" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -32658,7 +32662,7 @@
         <x:v>以 `Dexterous Hand; Contact Reasoning / Language-guided Grasp` 为主要方法/能力线索；更细的结构和消融结论待正文核验。</x:v>
       </x:c>
       <x:c r="BA20" t="str">
-        <x:v>作者提供预处理数据：https://huggingface.co/datasets/EunhaPark/project_dexter；未下载</x:v>
+        <x:v>DexGYS。</x:v>
       </x:c>
       <x:c r="BB20" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -32748,30 +32752,30 @@
       </x:c>
       <x:c r="CF20"/>
       <x:c r="CG20" t="str">
-        <x:v>Evidence-backed — Language-driven dexterous grasp generation requires the models to understand task semantics, 3D geometry, and complex hand-object interactions.</x:v>
+        <x:v>语言驱动的灵巧抓取要同时理解任务语义、三维几何和接触关系。</x:v>
       </x:c>
       <x:c r="CH20" t="str">
-        <x:v>While vision-language models have been applied to this problem, existing approaches directly map observations to grasp parameters without intermediate reasoning about physical interactions.</x:v>
+        <x:v>只预测抓取位姿未必符合语言中隐含的使用目的。</x:v>
       </x:c>
       <x:c r="CI20" t="str">
-        <x:v>We present DextER, Dexterous Grasp Generation with Embodied Reasoning, which introduces contact-based embodied reasoning for multi-finger manipulation.</x:v>
+        <x:v>DextER 在抓取生成中加入基于接触的具身推理，使手部接触与任务意图对齐。</x:v>
       </x:c>
       <x:c r="CJ20" t="str"/>
       <x:c r="CK20" t="str">
-        <x:v>On DexGYS, DextER achieves 67.14% success rate, outperforming state-of-the-art by 3.83 p.p. with 96.4% improvement in intention alignment.</x:v>
+        <x:v>卡片记录 DexGYS 成功率 67.14%，较所比较 SOTA 高 3.83 个百分点。</x:v>
       </x:c>
       <x:c r="CL20" t="str">
-        <x:v>Provides a concrete method or benchmark for the documented gap: While vision-language models have been applied to this problem, existing approaches directly map observations to grasp parameters…</x:v>
+        <x:v>将语言 Grounding 与可执行接触联系起来。</x:v>
       </x:c>
       <x:c r="CM20" t="str">
-        <x:v>Not established by the checked summary source; consult the full paper.</x:v>
+        <x:v>从多指接触迁移到两只普通夹爪需重新定义动作空间。</x:v>
       </x:c>
       <x:c r="CN20" t="str"/>
       <x:c r="CO20" t="str">
-        <x:v>Medium — transferable learning ideas may apply, but the hand hardware differs from ordinary grippers.</x:v>
+        <x:v>Medium：普通夹爪也需要意图对齐，但手部接触自由度不同。</x:v>
       </x:c>
       <x:c r="CP20" t="str">
-        <x:v>Official abstract / paper page; https://openaccess.thecvf.com/content/CVPR2026/html/Lee_DextER_Language-driven_Dexterous_Grasp_Generation_with_Embodied_Reasoning_CVPR_2026_paper.html; checked 2026-09-23. Rapid summary only; existing Evidence Quality is unchanged.</x:v>
+        <x:v>官方摘要/论文页; https://openaccess.thecvf.com/content/CVPR2026/html/Lee_DextER_Language-driven_Dexterous_Grasp_Generation_with_Embodied_Reasoning_CVPR_2026_paper.html; 核验于 2026-09-23. 仅为摘要级速读；原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="CQ20" t="str">
         <x:v>Exact work identity verified</x:v>
@@ -32932,7 +32936,7 @@
         <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AX21" t="str">
-        <x:v>MLLMs have strong visual-language reasoning but lack object-centric manipulation grounding, precise contact poses and robust real-world execution.</x:v>
+        <x:v>多模态大模型能理解图像和语言，但不一定能给出可执行的接触点与夹爪姿态。</x:v>
       </x:c>
       <x:c r="AY21" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -32941,7 +32945,7 @@
         <x:v>以 `Multimodal / Generali</x:v>
       </x:c>
       <x:c r="BA21" t="str">
-        <x:v>Simulation data from PartNet-Mobility-style articulated objects in SAPIEN; real-world household-object evaluation with a Franka arm, suction gripper and RealSense D415.</x:v>
+        <x:v>论文中的物体操作任务与消融设置；具体数据集名称见原卡实验部分。</x:v>
       </x:c>
       <x:c r="BB21" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -33033,34 +33037,34 @@
       </x:c>
       <x:c r="CF21"/>
       <x:c r="CG21" t="str">
-        <x:v>Evidence-backed — MLLMs have strong visual-language reasoning but lack object-centric manipulation grounding, precise contact poses and robust real-world execution.</x:v>
+        <x:v>多模态大模型能理解图像和语言，但不一定能给出可执行的接触点与夹爪姿态。</x:v>
       </x:c>
       <x:c r="CH21" t="str">
-        <x:v>Author-stated: prior MLLMs do not directly provide manipulation-aware localization and pose prediction; simulator-to-real differences affect position predictions.</x:v>
+        <x:v>物体级 Grounding 与精确接触几何没有自然地从语言推理转成机器人动作。</x:v>
       </x:c>
       <x:c r="CI21" t="str">
-        <x:v>ManipLLM fine-tunes LLaMA-Adapter with category identification, affordance-prior reasoning, pose fine-tuning and masked language modeling. It predicts contact point and gripper orientation, then uses chain-of-thought inference and active impedance adaptation with test-time visual adaptation.</x:v>
+        <x:v>ManipLLM 结合物体类别识别、affordance 推理和位姿微调，预测接触点与夹爪朝向，并通过分步推理和主动交互改进执行。</x:v>
       </x:c>
       <x:c r="CJ21" t="str">
         <x:v>Ablations compare FT, OCI, MLM, APR, COT and AIA components; the paper also compares manipulation performance against prior object-centric methods.</x:v>
       </x:c>
       <x:c r="CK21" t="str">
-        <x:v>Ablation average rises from 0.41 (FT only) to 0.59 with the full training/inference stack. OCI adds about 3%, MLM about 6%, APR about 9%; removing COT decreases about 3%, and removing AIA reduces long-distance performance from 0.57 to 0.50.</x:v>
+        <x:v>卡片记录消融平均指标从仅 FT 的 0.41 提升到完整方法的 0.59；各模块贡献见原卡 Main Results。</x:v>
       </x:c>
       <x:c r="CL21" t="str">
-        <x:v>Provides a concrete method or benchmark for the documented gap: Author-stated: prior MLLMs do not directly provide manipulation-aware localization and pose prediction; simulator-to-real…</x:v>
+        <x:v>让语言推理落到普通夹爪可执行的接触几何上。</x:v>
       </x:c>
       <x:c r="CM21" t="str">
-        <x:v>Author-stated: visual position prediction remains domain-sensitive; hardware-specific suction constraints require test-time adaptation.</x:v>
+        <x:v>作者指出视觉位置预测仍受域变化影响；特定吸盘硬件约束需要测试时适配。</x:v>
       </x:c>
       <x:c r="CN21" t="str">
         <x:v>Library Analysis: broader gripper geometries, bimanual coordination and long-horizon recovery are outside the demonstrated setup.</x:v>
       </x:c>
       <x:c r="CO21" t="str">
-        <x:v>Medium — relevant to robot manipulation; transfer to dual-arm real hardware needs validation.</x:v>
+        <x:v>High：直接对应夹爪接触点、动作前可行性验证和真机操作。</x:v>
       </x:c>
       <x:c r="CP21" t="str">
-        <x:v>Official abstract / paper page; https://arxiv.org/html/2312.16217; checked 2026-09-23. Rapid summary only; existing Evidence Quality is unchanged.</x:v>
+        <x:v>官方摘要/论文页; https://arxiv.org/html/2312.16217; 核验于 2026-09-23. 仅为摘要级速读；原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="CQ21" t="str">
         <x:v>Exact work identity verified</x:v>
@@ -33221,7 +33225,7 @@
         <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AX22" t="str">
-        <x:v>Human hands play a central role in interacting, motivating increasing research in dexterous robotic manipulation.</x:v>
+        <x:v>人类双手操作能力丰富，但难以直接迁移到机器人灵巧手。</x:v>
       </x:c>
       <x:c r="AY22" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -33230,7 +33234,7 @@
         <x:v>以 `Residual Learning / Sim-to-Real` 为主要方法/能力线索；更细的结构和消融结论待正文核验。</x:v>
       </x:c>
       <x:c r="BA22" t="str">
-        <x:v>Not specified in checked abstract/card.</x:v>
+        <x:v>双手灵巧操作仿真任务；详细任务和基线见论文。</x:v>
       </x:c>
       <x:c r="BB22" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -33320,30 +33324,30 @@
       </x:c>
       <x:c r="CF22"/>
       <x:c r="CG22" t="str">
-        <x:v>Evidence-backed — Human hands play a central role in interacting, motivating increasing research in dexterous robotic manipulation.</x:v>
+        <x:v>人类双手操作能力丰富，但难以直接迁移到机器人灵巧手。</x:v>
       </x:c>
       <x:c r="CH22" t="str">
-        <x:v>Not established in checked summary source.</x:v>
+        <x:v>人手和机器人手的运动学、接触方式不同，逐帧模仿不能保证可执行。</x:v>
       </x:c>
       <x:c r="CI22" t="str">
-        <x:v>To address this, we introduce ManipTrans, a novel two-stage method for efficiently transferring human bimanual skills to dexterous robotic hands in simulation.</x:v>
+        <x:v>ManipTrans 用两阶段流程，在仿真中把人类双手技能迁移到机器人灵巧手策略。</x:v>
       </x:c>
       <x:c r="CJ22" t="str"/>
       <x:c r="CK22" t="str">
-        <x:v>Experiments show that ManipTrans surpasses state-of-the-art methods in success rate, fidelity, and efficiency.</x:v>
+        <x:v>作者报告成功率、动作保真度与训练效率优于所比较方法；摘要未给统一数字。</x:v>
       </x:c>
       <x:c r="CL22" t="str">
-        <x:v>High — directly informs dual-arm coordination, data or ordinary-gripper policy design.</x:v>
+        <x:v>展示 Human Video / Human Motion 到机器人双手动作的转换思路。</x:v>
       </x:c>
       <x:c r="CM22" t="str">
-        <x:v>Not established by the checked summary source; consult the full paper.</x:v>
+        <x:v>仿真到真机与普通夹爪迁移尚不能从摘要确认。</x:v>
       </x:c>
       <x:c r="CN22" t="str"/>
       <x:c r="CO22" t="str">
-        <x:v>High — directly informs dual-arm coordination, data or ordinary-gripper policy design.</x:v>
+        <x:v>Medium：手型不同，普通夹爪适配仍需单独建模。</x:v>
       </x:c>
       <x:c r="CP22" t="str">
-        <x:v>Official abstract / paper page; https://openaccess.thecvf.com/content/CVPR2025/html/Li_ManipTrans_Efficient_Dexterous_Bimanual_Manipulation_Transfer_via_Residual_Learning_CVPR_2025_paper.html; checked 2026-09-23. Rapid summary only; existing Evidence Quality is unchanged.</x:v>
+        <x:v>官方摘要/论文页; https://openaccess.thecvf.com/content/CVPR2025/html/Li_ManipTrans_Efficient_Dexterous_Bimanual_Manipulation_Transfer_via_Residual_Learning_CVPR_2025_paper.html; 核验于 2026-09-23. 仅为摘要级速读；原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="CQ22" t="str">
         <x:v>Exact work identity verified</x:v>
@@ -33504,7 +33508,7 @@
         <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AX23" t="str">
-        <x:v>Dexterous manipulation with contact-rich interactions is crucial for advanced robotics.</x:v>
+        <x:v>接触密集的灵巧操作需要根据目标与环境变化调整动作。</x:v>
       </x:c>
       <x:c r="AY23" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -33513,7 +33517,7 @@
         <x:v>以 `Diffusion / Contact-rich Manipulation` 为主要方法/能力线索；更细的结构和消融结论待正文核验。</x:v>
       </x:c>
       <x:c r="BA23" t="str">
-        <x:v>Not specified in checked abstract/card.</x:v>
+        <x:v>已核验摘要未明确说明；需查阅论文方法与实验章节。</x:v>
       </x:c>
       <x:c r="BB23" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -33603,30 +33607,30 @@
       </x:c>
       <x:c r="CF23"/>
       <x:c r="CG23" t="str">
-        <x:v>Evidence-backed — Dexterous manipulation with contact-rich interactions is crucial for advanced robotics.</x:v>
+        <x:v>接触密集的灵巧操作需要根据目标与环境变化调整动作。</x:v>
       </x:c>
       <x:c r="CH23" t="str">
-        <x:v>While recent diffusion-based planning approaches show promise for simple manipulation tasks, they often produce unrealistic ghost states (e.g., the object automatically moves without hand contact) or lack adaptability when handling complex sequential…</x:v>
+        <x:v>固定轨迹或单一接触模式难适应复杂手—物交互。</x:v>
       </x:c>
       <x:c r="CI23" t="str">
-        <x:v>In this work, we introduce DexHandDiff, an interaction-aware diffusion planning framework for adaptive dexterous manipulation.</x:v>
+        <x:v>DexHandDiff 用交互感知的扩散式规划生成可适应目标变化的灵巧手动作。</x:v>
       </x:c>
       <x:c r="CJ23" t="str"/>
       <x:c r="CK23" t="str">
-        <x:v>Our framework achieves an average of 70.7% success rate on goal adaptive dexterous tasks, highlighting its robustness and flexibility in contact-rich manipulation.</x:v>
+        <x:v>官方摘要报告目标自适应任务平均成功率 70.7%。</x:v>
       </x:c>
       <x:c r="CL23" t="str">
-        <x:v>Provides a concrete method or benchmark for the documented gap: While recent diffusion-based planning approaches show promise for simple manipulation tasks, they often produce unrealistic ghost…</x:v>
+        <x:v>展示生成式策略如何表达多种接触动作。</x:v>
       </x:c>
       <x:c r="CM23" t="str">
-        <x:v>Not established by the checked summary source; consult the full paper.</x:v>
+        <x:v>需检查真机接触、动作延迟和跨硬件泛化。</x:v>
       </x:c>
       <x:c r="CN23" t="str"/>
       <x:c r="CO23" t="str">
-        <x:v>Medium — transferable learning ideas may apply, but the hand hardware differs from ordinary grippers.</x:v>
+        <x:v>Medium：可借鉴动作生成机制，但灵巧手与普通夹爪不同。</x:v>
       </x:c>
       <x:c r="CP23" t="str">
-        <x:v>Official abstract / paper page; https://openaccess.thecvf.com/content/CVPR2025/html/Liang_DexHandDiff_Interaction-aware_Diffusion_Planning_for_Adaptive_Dexterous_Manipulation_CVPR_2025_paper.html; checked 2026-09-23. Rapid summary only; existing Evidence Quality is unchanged.</x:v>
+        <x:v>官方摘要/论文页; https://openaccess.thecvf.com/content/CVPR2025/html/Liang_DexHandDiff_Interaction-aware_Diffusion_Planning_for_Adaptive_Dexterous_Manipulation_CVPR_2025_paper.html; 核验于 2026-09-23. 仅为摘要级速读；原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="CQ23" t="str">
         <x:v>Exact work identity verified</x:v>
@@ -33787,7 +33791,7 @@
         <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AX24" t="str">
-        <x:v>Visual Robot Manipulation (VRM) aims to enable a robot to follow natural language instructions based on robot states and visual observations, and therefore requires costly multi- modal data.</x:v>
+        <x:v>视觉机器人操作要根据语言、视觉和状态输出可执行动作。</x:v>
       </x:c>
       <x:c r="AY24" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -33796,7 +33800,7 @@
         <x:v>以 `Human Video / VLM` 为主要方法/能力线索；更细的结构和消融结论待正文核验。</x:v>
       </x:c>
       <x:c r="BA24" t="str">
-        <x:v>Not specified in checked abstract/card.</x:v>
+        <x:v>已核验摘要未明确说明；需查阅论文方法与实验章节。</x:v>
       </x:c>
       <x:c r="BB24" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -33886,30 +33890,30 @@
       </x:c>
       <x:c r="CF24"/>
       <x:c r="CG24" t="str">
-        <x:v>Evidence-backed — Visual Robot Manipulation (VRM) aims to enable a robot to follow natural language instructions based on robot states and visual observations, and therefore requires costly multi- modal data.</x:v>
+        <x:v>视觉机器人操作要根据语言、视觉和状态输出可执行动作。</x:v>
       </x:c>
       <x:c r="CH24" t="str">
-        <x:v>However, they either utilize web data that differs from robotic tasks, or train the model in an implicit way (e.g., predicting future frames at the pixel level), thus showing limited generalization ability under in- sufficient robot data.</x:v>
+        <x:v>只依赖少量机器人示范，难以利用大量人类动作视频。</x:v>
       </x:c>
       <x:c r="CI24" t="str">
-        <x:v>In this paper, we propose to learn from large-scale human action video datasets in an explicit way (i.e., imitating human actions from hand keypoints), introduc- ing Visual Robot Manipulation with Analogical Reasoning (AR-VRM).</x:v>
+        <x:v>AR-VRM 显式利用人类动作视频学习视觉操作表示，再适配机器人策略。</x:v>
       </x:c>
       <x:c r="CJ24" t="str"/>
       <x:c r="CK24" t="str">
-        <x:v>In few-shot scenarios, our AR-VRM outperforms previous meth- ods by large margins, underscoring the effectiveness of explicitly imitating human actions under data scarcity.</x:v>
+        <x:v>作者报告小样本设置下优于所比较方法；摘要未给可安全复述的统一数值。</x:v>
       </x:c>
       <x:c r="CL24" t="str">
-        <x:v>Provides a concrete method or benchmark for the documented gap: However, they either utilize web data that differs from robotic tasks, or train the model in an implicit way (e.g., predicting…</x:v>
+        <x:v>为人类视频转机器人动作提供另一种数据路线。</x:v>
       </x:c>
       <x:c r="CM24" t="str">
-        <x:v>Not established by the checked summary source; consult the full paper.</x:v>
+        <x:v>人体动作和机器人动作空间差异需要明确对齐。</x:v>
       </x:c>
       <x:c r="CN24" t="str"/>
       <x:c r="CO24" t="str">
-        <x:v>Medium — relevant to robot manipulation; transfer to dual-arm real hardware needs validation.</x:v>
+        <x:v>Medium：与低成本数据收集相关，双臂夹爪迁移待验。</x:v>
       </x:c>
       <x:c r="CP24" t="str">
-        <x:v>Official abstract / paper page; https://openaccess.thecvf.com/content/ICCV2025/html/Yang_AR-VRM_Imitating_Human_Motions_for_Visual_Robot_Manipulation_with_Analogical_ICCV_2025_paper.html; checked 2026-09-23. Rapid summary only; existing Evidence Quality is unchanged.</x:v>
+        <x:v>官方摘要/论文页; https://openaccess.thecvf.com/content/ICCV2025/html/Yang_AR-VRM_Imitating_Human_Motions_for_Visual_Robot_Manipulation_with_Analogical_ICCV_2025_paper.html; 核验于 2026-09-23. 仅为摘要级速读；原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="CQ24" t="str">
         <x:v>Exact work identity verified</x:v>
@@ -34070,7 +34074,7 @@
         <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AX25" t="str">
-        <x:v>In this work we propose a novel discriminative framework for dexterous grasp generation named Dexterous Grasp TRansformer (DGTR) capable of predicting a diverse set of feasible grasp poses by processing the object point cloud with only one forward pass.</x:v>
+        <x:v>灵巧手抓取不仅要可行，还要生成多样姿态。</x:v>
       </x:c>
       <x:c r="AY25" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -34079,7 +34083,7 @@
         <x:v>以 `Dexterous Grasping` 为主要方法/能力线索；更细的结构和消融结论待正文核验。</x:v>
       </x:c>
       <x:c r="BA25" t="str">
-        <x:v>Not specified in checked abstract/card.</x:v>
+        <x:v>已核验摘要未明确说明；需查阅论文方法与实验章节。</x:v>
       </x:c>
       <x:c r="BB25" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -34169,30 +34173,30 @@
       </x:c>
       <x:c r="CF25"/>
       <x:c r="CG25" t="str">
-        <x:v>Evidence-backed — In this work we propose a novel discriminative framework for dexterous grasp generation named Dexterous Grasp TRansformer (DGTR) capable of predicting a diverse set of feasible grasp poses by processing the object point cloud with only one forward pass.</x:v>
+        <x:v>灵巧手抓取不仅要可行，还要生成多样姿态。</x:v>
       </x:c>
       <x:c r="CH25" t="str">
-        <x:v>However we identify that this set prediction paradigm encounters several optimization challenges in the field of dexterous grasping and results in restricted performance.</x:v>
+        <x:v>单一回归结果容易忽略同一物体的多个可用抓法。</x:v>
       </x:c>
       <x:c r="CI25" t="str">
-        <x:v>In this work we propose a novel discriminative framework for dexterous grasp generation named Dexterous Grasp TRansformer (DGTR) capable of predicting a diverse set of feasible grasp poses by processing the object point cloud with only one forward pass.</x:v>
+        <x:v>Dexterous Grasp Transformer 用判别式 Transformer 生成和筛选多样灵巧抓取。</x:v>
       </x:c>
       <x:c r="CJ25" t="str"/>
       <x:c r="CK25" t="str">
-        <x:v>Notably while keeping high quality the diversity of grasp poses predicted by DGTR significantly outperforms previous works in multiple metrics without any data pre-processing.</x:v>
+        <x:v>作者报告保持抓取质量时，预测姿态多样性优于先前方法；具体数值需核对表格。</x:v>
       </x:c>
       <x:c r="CL25" t="str">
-        <x:v>Provides a concrete method or benchmark for the documented gap: However we identify that this set prediction paradigm encounters several optimization challenges in the field of dexterous…</x:v>
+        <x:v>提醒抓取策略不应只保留单一候选动作。</x:v>
       </x:c>
       <x:c r="CM25" t="str">
-        <x:v>Not established by the checked summary source; consult the full paper.</x:v>
+        <x:v>灵巧手抓取多样性指标不能直接替代双臂任务成功率。</x:v>
       </x:c>
       <x:c r="CN25" t="str"/>
       <x:c r="CO25" t="str">
-        <x:v>Medium — transferable learning ideas may apply, but the hand hardware differs from ordinary grippers.</x:v>
+        <x:v>Medium：双普通夹爪也可能需要多候选抓取与可行性筛选。</x:v>
       </x:c>
       <x:c r="CP25" t="str">
-        <x:v>Official abstract / paper page; https://openaccess.thecvf.com/content/CVPR2024/html/Xu_Dexterous_Grasp_Transformer_CVPR_2024_paper.html; checked 2026-09-23. Rapid summary only; existing Evidence Quality is unchanged.</x:v>
+        <x:v>官方摘要/论文页; https://openaccess.thecvf.com/content/CVPR2024/html/Xu_Dexterous_Grasp_Transformer_CVPR_2024_paper.html; 核验于 2026-09-23. 仅为摘要级速读；原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="CQ25" t="str">
         <x:v>Exact work identity verified</x:v>
@@ -34353,7 +34357,7 @@
         <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AX26" t="str">
-        <x:v>Mobile manipulation is the fundamental challenge for robotics to assist humans with diverse tasks and environments in everyday life.</x:v>
+        <x:v>移动操作需要跨任务和跨环境泛化；固定底座 VLA 的设置不直接覆盖移动机器人。</x:v>
       </x:c>
       <x:c r="AY26" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -34362,7 +34366,7 @@
         <x:v>以 `Mobile Manipulation` 为主要方法/能力线索；更细的结构和消融结论待正文核验。</x:v>
       </x:c>
       <x:c r="BA26" t="str">
-        <x:v>Not specified in checked abstract/card.</x:v>
+        <x:v>论文报告 OVMM 与真机评测；数据集和任务细节需继续核对正文。</x:v>
       </x:c>
       <x:c r="BB26" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -34452,30 +34456,30 @@
       </x:c>
       <x:c r="CF26"/>
       <x:c r="CG26" t="str">
-        <x:v>Evidence-backed — Mobile manipulation is the fundamental challenge for robotics to assist humans with diverse tasks and environments in everyday life.</x:v>
+        <x:v>移动操作需要跨任务和跨环境泛化；固定底座 VLA 的设置不直接覆盖移动机器人。</x:v>
       </x:c>
       <x:c r="CH26" t="str">
-        <x:v>However, conventional mobile manipulation approaches often struggle to generalize across different tasks and environments because of the lack of large-scale training.In contrast, recent advances in vision-language-action (VLA) models have shown impressive…</x:v>
+        <x:v>固定底座 VLA 不能直接解决移动机器人在不同场景中导航与操作耦合的问题。</x:v>
       </x:c>
       <x:c r="CI26" t="str">
-        <x:v>However, conventional mobile manipulation approaches often struggle to generalize across different tasks and environments because of the lack of large-scale training.In contrast, recent advances in vision-language-action (VLA) models have shown impressive generalization capabilities, but these foundation models are developed for fixed-base manipulation…</x:v>
+        <x:v>MoManipVLA 将 VLA 迁移到移动操作，结合移动底座与机械臂的任务执行。具体模块以原论文为准。</x:v>
       </x:c>
       <x:c r="CJ26" t="str"/>
       <x:c r="CK26" t="str">
-        <x:v>Extensive experimental results on OVMM and the real world demonstrate that our method achieves a 4.2% higher success rate than the state-of-the-art mobile manipulation, and only requires 50 training cost for real world deployment due to the strong…</x:v>
+        <x:v>官方摘要报告在 OVMM 和真机任务中优于所比较方法，整体成功率约高 4.2%；具体实验分组需回原文核对。</x:v>
       </x:c>
       <x:c r="CL26" t="str">
-        <x:v>Provides a concrete method or benchmark for the documented gap: However, conventional mobile manipulation approaches often struggle to generalize across different tasks and environments because…</x:v>
+        <x:v>提醒本项目区分“操作策略泛化”和“移动平台泛化”。</x:v>
       </x:c>
       <x:c r="CM26" t="str">
-        <x:v>Not established by the checked summary source; consult the full paper.</x:v>
+        <x:v>当前可核验的摘要不足以判断跨平台和长时序任务的完整失败情况。</x:v>
       </x:c>
       <x:c r="CN26" t="str"/>
       <x:c r="CO26" t="str">
-        <x:v>High — informs language-conditioned manipulation and VLA design.</x:v>
+        <x:v>High：有助于研究语言条件操作与 VLA 设计。</x:v>
       </x:c>
       <x:c r="CP26" t="str">
-        <x:v>Official abstract / paper page; https://openaccess.thecvf.com/content/CVPR2025/html/Wu_MoManipVLA_Transferring_Vision-language-action_Models_for_General_Mobile_Manipulation_CVPR_2025_paper.html; checked 2026-09-23. Rapid summary only; existing Evidence Quality is unchanged.</x:v>
+        <x:v>官方摘要/论文页; https://openaccess.thecvf.com/content/CVPR2025/html/Wu_MoManipVLA_Transferring_Vision-language-action_Models_for_General_Mobile_Manipulation_CVPR_2025_paper.html; 核验于 2026-09-23. 仅为摘要级速读；原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="CQ26" t="str">
         <x:v>Exact work identity verified</x:v>
@@ -34636,7 +34640,7 @@
         <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AX27" t="str">
-        <x:v>Training generalist agents capable of solving diverse tasks is challenging, often requiring large datasets of expert demonstrations.</x:v>
+        <x:v>多任务机器人策略通常需要大量专家示范。</x:v>
       </x:c>
       <x:c r="AY27" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -34645,7 +34649,7 @@
         <x:v>以 `Action Chunking / Multi-task Policy` 为主要方法/能力线索；更细的结构和消融结论待正文核验。</x:v>
       </x:c>
       <x:c r="BA27" t="str">
-        <x:v>Not specified in checked abstract/card.</x:v>
+        <x:v>已核验摘要未明确说明；需查阅论文方法与实验章节。</x:v>
       </x:c>
       <x:c r="BB27" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -34735,30 +34739,30 @@
       </x:c>
       <x:c r="CF27"/>
       <x:c r="CG27" t="str">
-        <x:v>Evidence-backed — Training generalist agents capable of solving diverse tasks is challenging, often requiring large datasets of expert demonstrations.</x:v>
+        <x:v>多任务机器人策略通常需要大量专家示范。</x:v>
       </x:c>
       <x:c r="CH27" t="str">
-        <x:v>BAKU builds upon recent advancements in offline imitation learning and meticulously combines observation trunks, action chunking, multi-sensory observations, and action heads to substantially improve upon prior work.</x:v>
+        <x:v>复杂通用策略可能难以在少量示范下稳定学习。</x:v>
       </x:c>
       <x:c r="CI27" t="str">
-        <x:v>In this work, we present BAKU, a simple transformer architecture that enables efficient learning of multi-task robot policies.</x:v>
+        <x:v>BAKU 用相对简洁的 Transformer 架构训练多任务机器人策略。</x:v>
       </x:c>
       <x:c r="CJ27" t="str"/>
       <x:c r="CK27" t="str">
-        <x:v>On 30 real-world manipulation tasks, given an average of just 17 demonstrations per task, BAKU achieves a 91% success rate.</x:v>
+        <x:v>论文报告 30 项真机操作任务、每项平均约 17 条示范时，成功率达 91%。</x:v>
       </x:c>
       <x:c r="CL27" t="str">
-        <x:v>Provides a concrete method or benchmark for the documented gap: BAKU builds upon recent advancements in offline imitation learning and meticulously combines observation trunks, action chunking…</x:v>
+        <x:v>为小数据多任务操作提供实证基线。</x:v>
       </x:c>
       <x:c r="CM27" t="str">
-        <x:v>Not established by the checked summary source; consult the full paper.</x:v>
+        <x:v>30 项任务的本体与任务分布未必覆盖本项目的双臂普通夹爪。</x:v>
       </x:c>
       <x:c r="CN27" t="str"/>
       <x:c r="CO27" t="str">
-        <x:v>Medium — relevant to robot manipulation; transfer to dual-arm real hardware needs validation.</x:v>
+        <x:v>High：双臂示范昂贵，值得比较数据效率。</x:v>
       </x:c>
       <x:c r="CP27" t="str">
-        <x:v>Official abstract / paper page; https://proceedings.neurips.cc/paper_files/paper/2024/hash/ff887781480973bd3cb6026feb378d1e-Abstract-Conference.html; checked 2026-09-23. Rapid summary only; existing Evidence Quality is unchanged.</x:v>
+        <x:v>官方摘要/论文页; https://proceedings.neurips.cc/paper_files/paper/2024/hash/ff887781480973bd3cb6026feb378d1e-Abstract-Conference.html; 核验于 2026-09-23. 仅为摘要级速读；原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="CQ27" t="str">
         <x:v>Exact work identity verified</x:v>
@@ -34919,7 +34923,7 @@
         <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AX28" t="str">
-        <x:v>Despite advancements in robotic-assisted surgery, automating complex tasks like suturing remains challenging due to the need for adaptability and precision.</x:v>
+        <x:v>手术机器人自动缝合等复杂任务需要高精度和适应变化的控制。</x:v>
       </x:c>
       <x:c r="AY28" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -34928,7 +34932,7 @@
         <x:v>以 `Surgical Robotics` 为主要方法/能力线索；更细的结构和消融结论待正文核验。</x:v>
       </x:c>
       <x:c r="BA28" t="str">
-        <x:v>Not specified in checked abstract/card.</x:v>
+        <x:v>SurgicAI 手术机器人基准；任务与数据规模需查正文。</x:v>
       </x:c>
       <x:c r="BB28" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -35018,30 +35022,30 @@
       </x:c>
       <x:c r="CF28"/>
       <x:c r="CG28" t="str">
-        <x:v>Evidence-backed — Despite advancements in robotic-assisted surgery, automating complex tasks like suturing remains challenging due to the need for adaptability and precision.</x:v>
+        <x:v>手术机器人自动缝合等复杂任务需要高精度和适应变化的控制。</x:v>
       </x:c>
       <x:c r="CH28" t="str">
-        <x:v>However, current platforms often include only relatively simple, non-dexterous manipulations and lack the flexibility required for effective learning and generalization.</x:v>
+        <x:v>既有平台多局限于简单、低灵巧度操作，难以灵活支持分解式强化学习。</x:v>
       </x:c>
       <x:c r="CI28" t="str">
-        <x:v>We introduce SurgicAI, a novel platform for development and benchmarking that addresses these challenges by providing the flexibility to accommodate both modular subtasks and more importantly task decomposition in RL-based surgical robotics.</x:v>
+        <x:v>SurgicAI 构建手术机器人开发与评测平台，支持模块化子任务及强化学习任务分解。</x:v>
       </x:c>
       <x:c r="CJ28" t="str"/>
       <x:c r="CK28" t="str">
-        <x:v>Qualitative or numerical result not established by checked source.</x:v>
+        <x:v>摘要没有给出足够明确、可复述的量化性能。</x:v>
       </x:c>
       <x:c r="CL28" t="str">
-        <x:v>Provides a concrete method or benchmark for the documented gap: However, current platforms often include only relatively simple, non-dexterous manipulations and lack the flexibility required…</x:v>
+        <x:v>为复杂长程任务的子任务拆解提供特定领域案例。</x:v>
       </x:c>
       <x:c r="CM28" t="str">
-        <x:v>Not established by the checked summary source; consult the full paper.</x:v>
+        <x:v>摘要不能证明该平台上的策略能迁移到一般家庭操作。</x:v>
       </x:c>
       <x:c r="CN28" t="str"/>
       <x:c r="CO28" t="str">
-        <x:v>High — directly informs dual-arm coordination, data or ordinary-gripper policy design.</x:v>
+        <x:v>Medium：任务分解思路可借鉴，但手术场景与本项目普通夹爪任务不同。</x:v>
       </x:c>
       <x:c r="CP28" t="str">
-        <x:v>Official abstract / paper page; https://proceedings.neurips.cc/paper_files/paper/2024/hash/74c4f2b87b7499d365422152c76fd916-Abstract-Datasets_and_Benchmarks_Track.html; checked 2026-09-23. Rapid summary only; existing Evidence Quality is unchanged.</x:v>
+        <x:v>官方摘要/论文页; https://proceedings.neurips.cc/paper_files/paper/2024/hash/74c4f2b87b7499d365422152c76fd916-Abstract-Datasets_and_Benchmarks_Track.html; 核验于 2026-09-23. 仅为摘要级速读；原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="CQ28" t="str">
         <x:v>Exact work identity verified</x:v>
@@ -35202,7 +35206,7 @@
         <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AX29" t="str">
-        <x:v>Reward specification is one of the most tricky problems in Reinforcement Learning, which usually requires tedious hand engineering in practice.</x:v>
+        <x:v>强化学习的奖励设计通常要大量人工工程。</x:v>
       </x:c>
       <x:c r="AY29" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -35211,7 +35215,7 @@
         <x:v>以 `Video Demonstration / Reward Learning` 为主要方法/能力线索；更细的结构和消融结论待正文核验。</x:v>
       </x:c>
       <x:c r="BA29" t="str">
-        <x:v>Not specified in checked abstract/card.</x:v>
+        <x:v>已核验摘要未明确说明；需查阅论文方法与实验章节。</x:v>
       </x:c>
       <x:c r="BB29" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -35301,30 +35305,30 @@
       </x:c>
       <x:c r="CF29"/>
       <x:c r="CG29" t="str">
-        <x:v>Evidence-backed — Reward specification is one of the most tricky problems in Reinforcement Learning, which usually requires tedious hand engineering in practice.</x:v>
+        <x:v>强化学习的奖励设计通常要大量人工工程。</x:v>
       </x:c>
       <x:c r="CH29" t="str">
-        <x:v>One promising approach to tackle this challenge is to adopt existing expert video demonstrations for policy learning.</x:v>
+        <x:v>只比较单帧状态容易忽略示范中的动作时间顺序。</x:v>
       </x:c>
       <x:c r="CI29" t="str">
-        <x:v>To address this issue, in this paper, we introduce the Temporal Optimal Transport (TemporalOT) reward to incorporate temporal order information for learning a more accurate OT-based proxy reward.</x:v>
+        <x:v>Temporal Optimal Transport Reward 把时间顺序纳入示范与策略轨迹的匹配，构造学习奖励。</x:v>
       </x:c>
       <x:c r="CJ29" t="str"/>
       <x:c r="CK29" t="str">
-        <x:v>Qualitative or numerical result not established by checked source.</x:v>
+        <x:v>已核验摘要没有可安全复述的统一量化结果。</x:v>
       </x:c>
       <x:c r="CL29" t="str">
-        <x:v>Provides a concrete method or benchmark for the documented gap: One promising approach to tackle this challenge is to adopt existing expert video demonstrations for policy learning.</x:v>
+        <x:v>为长时序操作提供不依赖逐步手写奖励的方向。</x:v>
       </x:c>
       <x:c r="CM29" t="str">
-        <x:v>Not established by the checked summary source; consult the full paper.</x:v>
+        <x:v>时间对齐错误可能误导奖励；需审计长任务失败样例。</x:v>
       </x:c>
       <x:c r="CN29" t="str"/>
       <x:c r="CO29" t="str">
-        <x:v>Medium — relevant to robot manipulation; transfer to dual-arm real hardware needs validation.</x:v>
+        <x:v>Medium：双臂轨迹评价可参考，但真实接触仍需验证。</x:v>
       </x:c>
       <x:c r="CP29" t="str">
-        <x:v>Official abstract / paper page; https://proceedings.neurips.cc/paper_files/paper/2024/hash/dcd297696d0bb304ba426b3c5a679c37-Abstract-Conference.html; checked 2026-09-23. Rapid summary only; existing Evidence Quality is unchanged.</x:v>
+        <x:v>官方摘要/论文页; https://proceedings.neurips.cc/paper_files/paper/2024/hash/dcd297696d0bb304ba426b3c5a679c37-Abstract-Conference.html; 核验于 2026-09-23. 仅为摘要级速读；原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="CQ29" t="str">
         <x:v>Exact work identity verified</x:v>
@@ -35485,7 +35489,7 @@
         <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AX30" t="str">
-        <x:v>Despite significant progress in robotics and embodied AI in recent years, deploying robots for long-horizon tasks remains a great challenge.</x:v>
+        <x:v>机器人长任务容易因局部错误累积而失败。</x:v>
       </x:c>
       <x:c r="AY30" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -35494,7 +35498,7 @@
         <x:v>以 `Long-Hori</x:v>
       </x:c>
       <x:c r="BA30" t="str">
-        <x:v>Not specified in checked abstract/card.</x:v>
+        <x:v>CALVIN 与真机操作任务。</x:v>
       </x:c>
       <x:c r="BB30" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -35584,30 +35588,30 @@
       </x:c>
       <x:c r="CF30"/>
       <x:c r="CG30" t="str">
-        <x:v>Evidence-backed — Despite significant progress in robotics and embodied AI in recent years, deploying robots for long-horizon tasks remains a great challenge.</x:v>
+        <x:v>机器人长任务容易因局部错误累积而失败。</x:v>
       </x:c>
       <x:c r="CH30" t="str">
-        <x:v>Majority of prior arts adhere to an open-loop philosophy and lack real-time feedback, leading to error accumulation and undesirable robustness.</x:v>
+        <x:v>只按当前观测输出动作，缺少对下一状态的预期与检查。</x:v>
       </x:c>
       <x:c r="CI30" t="str">
-        <x:v>Inspired by classic closed-loop control systems, we propose CLOVER, a closed-loop visuomotor control framework that incorporates feedback mechanisms to improve adaptive robotic control.</x:v>
+        <x:v>CLOVER 借鉴闭环控制，把生成式未来预期与视觉运动策略结合，持续比较执行进展。</x:v>
       </x:c>
       <x:c r="CJ30" t="str"/>
       <x:c r="CK30" t="str">
-        <x:v>Our framework exhibits notable advancement in real-world robotic tasks and achieves state-of-the-art on CALVIN benchmark, improving by 8% over previous open-loop counterparts.</x:v>
+        <x:v>作者报告 CALVIN 上达到所比较方法中的先进表现，并展示真机任务改善；具体数字需查正文。</x:v>
       </x:c>
       <x:c r="CL30" t="str">
-        <x:v>Provides a concrete method or benchmark for the documented gap: Majority of prior arts adhere to an open-loop philosophy and lack real-time feedback, leading to error accumulation and…</x:v>
+        <x:v>为动作后验证和失败检测提供闭环思路。</x:v>
       </x:c>
       <x:c r="CM30" t="str">
-        <x:v>Not established by the checked summary source; consult the full paper.</x:v>
+        <x:v>未来预测误差与真实接触误差如何区分仍需验证。</x:v>
       </x:c>
       <x:c r="CN30" t="str"/>
       <x:c r="CO30" t="str">
-        <x:v>Medium — relevant to robot manipulation; transfer to dual-arm real hardware needs validation.</x:v>
+        <x:v>High：双臂长任务尤其需要检查每步结果。</x:v>
       </x:c>
       <x:c r="CP30" t="str">
-        <x:v>Official abstract / paper page; https://proceedings.neurips.cc/paper_files/paper/2024/hash/fad8962279154544ed69bb63eb14d677-Abstract-Conference.html; checked 2026-09-23. Rapid summary only; existing Evidence Quality is unchanged.</x:v>
+        <x:v>官方摘要/论文页; https://proceedings.neurips.cc/paper_files/paper/2024/hash/fad8962279154544ed69bb63eb14d677-Abstract-Conference.html; 核验于 2026-09-23. 仅为摘要级速读；原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="CQ30" t="str">
         <x:v>Exact work identity verified</x:v>
@@ -35768,7 +35772,7 @@
         <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AX31" t="str">
-        <x:v>In robot learning, the observation space is crucial due to the distinct characteristics of different modalities, which can potentially become a bottleneck alongside policy design.</x:v>
+        <x:v>在机器人学习中，观测模态可能像策略设计一样限制操作能力。</x:v>
       </x:c>
       <x:c r="AY31" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -35777,7 +35781,7 @@
         <x:v>以 `3D Observation / Contact-rich` 为主要方法/能力线索；更细的结构和消融结论待正文核验。</x:v>
       </x:c>
       <x:c r="BA31" t="str">
-        <x:v>Not specified in checked abstract/card.</x:v>
+        <x:v>OBSBench：两个仿真器、125 项任务。</x:v>
       </x:c>
       <x:c r="BB31" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -35867,30 +35871,30 @@
       </x:c>
       <x:c r="CF31"/>
       <x:c r="CG31" t="str">
-        <x:v>Evidence-backed — In robot learning, the observation space is crucial due to the distinct characteristics of different modalities, which can potentially become a bottleneck alongside policy design.</x:v>
+        <x:v>在机器人学习中，观测模态可能像策略设计一样限制操作能力。</x:v>
       </x:c>
       <x:c r="CH31" t="str">
-        <x:v>Not established in checked summary source.</x:v>
+        <x:v>已核验摘要未明确说明；需查阅论文方法与实验章节。</x:v>
       </x:c>
       <x:c r="CI31" t="str">
-        <x:v>We introduce OBSBench, a benchmark comprising two simulators and 125 tasks, along with standardized pipelines for various encoders and policy baselines.</x:v>
+        <x:v>论文提出 OBSBench，统一比较不同观测编码器和策略基线；基准覆盖两个仿真器、125 项任务。</x:v>
       </x:c>
       <x:c r="CJ31" t="str"/>
       <x:c r="CK31" t="str">
-        <x:v>Furthermore, our findings demonstrate that point cloud observations often yield better policy performance and significantly stronger generalization capabilities across various geometric and visual conditions.</x:v>
+        <x:v>摘要指出点云观测常带来更好的策略表现，并在几何与视觉变化下表现出更强泛化；具体幅度需查实验表格。</x:v>
       </x:c>
       <x:c r="CL31" t="str">
-        <x:v>Medium — useful for method selection, data design and evaluation.</x:v>
+        <x:v>提示选择 RGB、点云等输入时，应在同一策略和任务设置下比较。</x:v>
       </x:c>
       <x:c r="CM31" t="str">
-        <x:v>Not established by the checked summary source; consult the full paper.</x:v>
+        <x:v>摘要未说明点云优势在传感器成本、遮挡和真实平台上的边界。</x:v>
       </x:c>
       <x:c r="CN31" t="str"/>
       <x:c r="CO31" t="str">
-        <x:v>Medium — useful for method selection, data design and evaluation.</x:v>
+        <x:v>Medium：可用于设计普通夹爪操作的观测消融实验。</x:v>
       </x:c>
       <x:c r="CP31" t="str">
-        <x:v>Official abstract / paper page; https://proceedings.neurips.cc/paper_files/paper/2024/hash/8e5dc5969a6174fcaaececd890c7f59b-Abstract-Datasets_and_Benchmarks_Track.html; checked 2026-09-23. Rapid summary only; existing Evidence Quality is unchanged.</x:v>
+        <x:v>官方摘要/论文页; https://proceedings.neurips.cc/paper_files/paper/2024/hash/8e5dc5969a6174fcaaececd890c7f59b-Abstract-Datasets_and_Benchmarks_Track.html; 核验于 2026-09-23. 仅为摘要级速读；原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="CQ31" t="str">
         <x:v>Exact work identity verified</x:v>
@@ -36051,7 +36055,7 @@
         <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AX32" t="str">
-        <x:v>Training an agent to achieve particular goals or perform desired behaviors is often accomplished through reinforcement learning, especially in the absence of expert demonstrations.</x:v>
+        <x:v>机器人策略需要按文字目标学习行为，而奖励设计成本较高。</x:v>
       </x:c>
       <x:c r="AY32" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -36060,7 +36064,7 @@
         <x:v>以 `Text-conditioned Reward` 为主要方法/能力线索；更细的结构和消融结论待正文核验。</x:v>
       </x:c>
       <x:c r="BA32" t="str">
-        <x:v>Not specified in checked abstract/card.</x:v>
+        <x:v>Meta-World 机器人操作环境。</x:v>
       </x:c>
       <x:c r="BB32" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -36150,30 +36154,30 @@
       </x:c>
       <x:c r="CF32"/>
       <x:c r="CG32" t="str">
-        <x:v>Evidence-backed — Training an agent to achieve particular goals or perform desired behaviors is often accomplished through reinforcement learning, especially in the absence of expert demonstrations.</x:v>
+        <x:v>机器人策略需要按文字目标学习行为，而奖励设计成本较高。</x:v>
       </x:c>
       <x:c r="CH32" t="str">
-        <x:v>However, supporting novel goals or behaviors through reinforcement learning requires the ad-hoc design of appropriate reward functions, which quickly becomes intractable.</x:v>
+        <x:v>普通扩散生成不能自动判断行为是否符合语言描述。</x:v>
       </x:c>
       <x:c r="CI32" t="str">
-        <x:v>To address this challenge, we propose Text-Aware Diffusion for Policy Learning (TADPoLe), which uses a pretrained, frozen text-conditioned diffusion model to compute dense zero-shot reward signals for text-aligned policy learning.</x:v>
+        <x:v>TADPoLe 利用冻结的文本条件模型，为策略学习提供语言相关的信号。</x:v>
       </x:c>
       <x:c r="CJ32" t="str"/>
       <x:c r="CK32" t="str">
-        <x:v>We further show that TADPoLe performs competitively when applied to robotic manipulation tasks in the Meta-World environment, without having access to any in-domain demonstrations.</x:v>
+        <x:v>作者报告在 Meta-World 任务上有竞争力的表现；具体数字见实验表。</x:v>
       </x:c>
       <x:c r="CL32" t="str">
-        <x:v>Provides a concrete method or benchmark for the documented gap: However, supporting novel goals or behaviors through reinforcement learning requires the ad-hoc design of appropriate reward…</x:v>
+        <x:v>可比较语言约束进入奖励还是进入动作生成器。</x:v>
       </x:c>
       <x:c r="CM32" t="str">
-        <x:v>Not established by the checked summary source; consult the full paper.</x:v>
+        <x:v>冻结模型的语言判断可能与真实物理成功不一致。</x:v>
       </x:c>
       <x:c r="CN32" t="str"/>
       <x:c r="CO32" t="str">
-        <x:v>Medium — relevant to robot manipulation; transfer to dual-arm real hardware needs validation.</x:v>
+        <x:v>Medium：对未来 VLA 有参考价值，真机双臂需独立验证。</x:v>
       </x:c>
       <x:c r="CP32" t="str">
-        <x:v>Official abstract / paper page; https://proceedings.neurips.cc/paper_files/paper/2024/hash/5227ce00add5aa0a12d1c4ee92fcd2dc-Abstract-Conference.html; checked 2026-09-23. Rapid summary only; existing Evidence Quality is unchanged.</x:v>
+        <x:v>官方摘要/论文页; https://proceedings.neurips.cc/paper_files/paper/2024/hash/5227ce00add5aa0a12d1c4ee92fcd2dc-Abstract-Conference.html; 核验于 2026-09-23. 仅为摘要级速读；原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="CQ32" t="str">
         <x:v>Exact work identity verified</x:v>
@@ -36334,7 +36338,7 @@
         <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AX33" t="str">
-        <x:v>Learning generalizable visual representations across different embodied environments is essential for effective robotic manipulation in real-world scenarios.</x:v>
+        <x:v>从人类视频预训练的视觉表示与机器人视角存在域差异。</x:v>
       </x:c>
       <x:c r="AY33" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -36343,7 +36347,7 @@
         <x:v>以 `Human-Robot Domain Adaptation` 为主要方法/能力线索；更细的结构和消融结论待正文核验。</x:v>
       </x:c>
       <x:c r="BA33" t="str">
-        <x:v>Not specified in checked abstract/card.</x:v>
+        <x:v>已核验摘要未明确说明；需查阅论文方法与实验章节。</x:v>
       </x:c>
       <x:c r="BB33" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -36433,30 +36437,30 @@
       </x:c>
       <x:c r="CF33"/>
       <x:c r="CG33" t="str">
-        <x:v>Evidence-backed — Learning generalizable visual representations across different embodied environments is essential for effective robotic manipulation in real-world scenarios.</x:v>
+        <x:v>从人类视频预训练的视觉表示与机器人视角存在域差异。</x:v>
       </x:c>
       <x:c r="CH33" t="str">
-        <x:v>However, the limited scale and diversity of robot demonstration data pose a significant challenge.</x:v>
+        <x:v>直接将人类视频特征用于机器人操作，可能识别不到关键交互区域。</x:v>
       </x:c>
       <x:c r="CI33" t="str">
-        <x:v>To overcome this, we propose a novel adaptation paradigm that leverages readily available paired human-robot video data to bridge the domain gap.</x:v>
+        <x:v>利用配对的人类—机器人视频对视觉表示做适配，缩小两种视角/本体差距。</x:v>
       </x:c>
       <x:c r="CJ33" t="str"/>
       <x:c r="CK33" t="str">
-        <x:v>Compared to existing pre-trained models, our adaptation method improves the average success rate by over 7% across multiple tasks on both simulated benchmarks and real-world evaluations.</x:v>
+        <x:v>作者报告多个操作任务的平均成功率提高超过 7%；具体比较条件见论文。</x:v>
       </x:c>
       <x:c r="CL33" t="str">
-        <x:v>Provides a concrete method or benchmark for the documented gap: However, the limited scale and diversity of robot demonstration data pose a significant challenge.</x:v>
+        <x:v>为低成本视频数据用于普通夹爪策略提供域适配方法。</x:v>
       </x:c>
       <x:c r="CM33" t="str">
-        <x:v>Not established by the checked summary source; consult the full paper.</x:v>
+        <x:v>视觉特征对齐不等于动作空间和接触动力学也对齐。</x:v>
       </x:c>
       <x:c r="CN33" t="str"/>
       <x:c r="CO33" t="str">
-        <x:v>Medium — relevant to robot manipulation; transfer to dual-arm real hardware needs validation.</x:v>
+        <x:v>Medium：人类视频可能补充双臂数据，但动作仍需重定向。</x:v>
       </x:c>
       <x:c r="CP33" t="str">
-        <x:v>Official abstract / paper page; https://openaccess.thecvf.com/content/CVPR2025/html/Zhou_Mitigating_the_Human-Robot_Domain_Discrepancy_in_Visual_Pre-training_for_Robotic_CVPR_2025_paper.html; checked 2026-09-23. Rapid summary only; existing Evidence Quality is unchanged.</x:v>
+        <x:v>官方摘要/论文页; https://openaccess.thecvf.com/content/CVPR2025/html/Zhou_Mitigating_the_Human-Robot_Domain_Discrepancy_in_Visual_Pre-training_for_Robotic_CVPR_2025_paper.html; 核验于 2026-09-23. 仅为摘要级速读；原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="CQ33" t="str">
         <x:v>Unresolved</x:v>
@@ -36617,7 +36621,7 @@
         <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AX34" t="str">
-        <x:v>Recent advancements in robotic manipulation have highlighted the potential of intermediate representations for improving policy generalization.</x:v>
+        <x:v>机器人策略需要可靠地定位目标物体与放置区域，才能在新场景中泛化。</x:v>
       </x:c>
       <x:c r="AY34" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -36626,7 +36630,7 @@
         <x:v>以 `Grounding / Synthetic Data` 为主要方法/能力线索；更细的结构和消融结论待正文核验。</x:v>
       </x:c>
       <x:c r="BA34" t="str">
-        <x:v>RoboCasa-based generated set with 24K demonstrations, 112K instructions, 3,526 objects and 176 categories; Objaverse contributes 1,017 tabletop objects (Sec. 3, App. B).</x:v>
+        <x:v>论文使用基于 RoboCasa 的合成数据；卡片记录 24K 示范、112K 指令以及对象类别规模（Sec. 3、Appendix B）。</x:v>
       </x:c>
       <x:c r="BB34" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -36716,30 +36720,30 @@
       </x:c>
       <x:c r="CF34"/>
       <x:c r="CG34" t="str">
-        <x:v>Evidence-backed — Recent advancements in robotic manipulation have highlighted the potential of intermediate representations for improving policy generalization.</x:v>
+        <x:v>机器人策略需要可靠地定位目标物体与放置区域，才能在新场景中泛化。</x:v>
       </x:c>
       <x:c r="CH34" t="str">
-        <x:v>In this work, we explore grounding masks as an effective intermediate representation, balancing two key advantages: (1) effective spatial guidance that specifies target objects and placement areas while also conveying information about object shape and size…</x:v>
+        <x:v>只靠最终动作监督，策略未必能学会稳定识别目标物体和放置区域。</x:v>
       </x:c>
       <x:c r="CI34" t="str">
-        <x:v>We introduce \method, a grounding-aware robotic manipulation policy that leverages grounding masks as an intermediate representation to guide policy networks in object manipulation tasks.</x:v>
+        <x:v>RoboGround 使用 Grounding mask 作为中间表示，向操作策略提供目标及空间形状信息。</x:v>
       </x:c>
       <x:c r="CJ34" t="str"/>
       <x:c r="CK34" t="str">
-        <x:v>Extensive experiments show the value of our dataset and the effectiveness of grounding masks as intermediate guidance, significantly enhancing the generalization abilities of robot policies.</x:v>
+        <x:v>官方摘要报告 Grounding mask 能改善策略泛化；快速摘要不填入未核对实验表的数字。</x:v>
       </x:c>
       <x:c r="CL34" t="str">
-        <x:v>Provides a concrete method or benchmark for the documented gap: In this work, we explore grounding masks as an effective intermediate representation, balancing two key advantages: (1) effective…</x:v>
+        <x:v>可与 ReconVLA 比较“显式 mask”与“隐式目标区域重建”两种 Grounding 路线。</x:v>
       </x:c>
       <x:c r="CM34" t="str">
-        <x:v>Author-stated — synthetic data and grounding quality bound transfer; Library Analysis — real-robot evidence is limited relative to simulation.</x:v>
+        <x:v>合成数据和 mask 质量会影响迁移；真机覆盖范围仍需按论文实验表核验。</x:v>
       </x:c>
       <x:c r="CN34" t="str"/>
       <x:c r="CO34" t="str">
-        <x:v>High — informs language-conditioned manipulation and VLA design.</x:v>
+        <x:v>High：有助于研究语言条件操作与 VLA 设计。</x:v>
       </x:c>
       <x:c r="CP34" t="str">
-        <x:v>Official abstract / paper page; https://arxiv.org/html/2504.21530; checked 2026-09-23. Rapid summary only; existing Evidence Quality is unchanged.</x:v>
+        <x:v>官方摘要/论文页; https://arxiv.org/html/2504.21530; 核验于 2026-09-23. 仅为摘要级速读；原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="CQ34" t="str">
         <x:v>Exact work identity verified</x:v>
@@ -36900,7 +36904,7 @@
         <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AX35" t="str">
-        <x:v>Robotic manipulation in embodied AI critically depends on large-scale, high-quality datasets that reflect realistic object interactions and physical dynamics.</x:v>
+        <x:v>机器人操作需要规模大且接近真实交互的训练场景。</x:v>
       </x:c>
       <x:c r="AY35" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -36909,7 +36913,7 @@
         <x:v>以 `Synthetic Data / Scene Generation` 为主要方法/能力线索；更细的结构和消融结论待正文核验。</x:v>
       </x:c>
       <x:c r="BA35" t="str">
-        <x:v>Not specified in checked abstract/card.</x:v>
+        <x:v>已核验摘要未明确说明；需查阅论文方法与实验章节。</x:v>
       </x:c>
       <x:c r="BB35" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -36999,30 +37003,30 @@
       </x:c>
       <x:c r="CF35"/>
       <x:c r="CG35" t="str">
-        <x:v>Evidence-backed — Robotic manipulation in embodied AI critically depends on large-scale, high-quality datasets that reflect realistic object interactions and physical dynamics.</x:v>
+        <x:v>机器人操作需要规模大且接近真实交互的训练场景。</x:v>
       </x:c>
       <x:c r="CH35" t="str">
-        <x:v>However, existing data collection pipelines are often slow, expensive, and heavily reliant on manual efforts.</x:v>
+        <x:v>人工制作动态场景速度慢，动作多样性不足。</x:v>
       </x:c>
       <x:c r="CI35" t="str">
-        <x:v>We present DynScene, a diffusion-based framework for generating dynamic robotic manipulation scenes directly from textual instructions.</x:v>
+        <x:v>DynScene 根据文字指令用扩散模型生成动态机器人操作场景。</x:v>
       </x:c>
       <x:c r="CJ35" t="str"/>
       <x:c r="CK35" t="str">
-        <x:v>Experiments show DynScene achieves 26.8x faster generation, 1.84x higher accuracy, and 28% greater action diversity than human-crafted data.</x:v>
+        <x:v>卡片记录生成速度提高 26.8 倍、准确率提高 1.84 倍、动作多样性提高 28%；指标定义见原文。</x:v>
       </x:c>
       <x:c r="CL35" t="str">
-        <x:v>Provides a concrete method or benchmark for the documented gap: However, existing data collection pipelines are often slow, expensive, and heavily reliant on manual efforts.</x:v>
+        <x:v>为扩展双臂训练环境提供合成数据思路。</x:v>
       </x:c>
       <x:c r="CM35" t="str">
-        <x:v>Not established by the checked summary source; consult the full paper.</x:v>
+        <x:v>场景多样性不一定等于真实机器人成功率提升。</x:v>
       </x:c>
       <x:c r="CN35" t="str"/>
       <x:c r="CO35" t="str">
-        <x:v>Medium — useful for method selection, data design and evaluation.</x:v>
+        <x:v>Medium：生成场景需经过真机接触与任务相关性验证。</x:v>
       </x:c>
       <x:c r="CP35" t="str">
-        <x:v>Official abstract / paper page; https://openaccess.thecvf.com/content/CVPR2025/html/Lee_DynScene_Scalable_Generation_of_Dynamic_Robotic_Manipulation_Scenes_for_Embodied_CVPR_2025_paper.html; checked 2026-09-23. Rapid summary only; existing Evidence Quality is unchanged.</x:v>
+        <x:v>官方摘要/论文页; https://openaccess.thecvf.com/content/CVPR2025/html/Lee_DynScene_Scalable_Generation_of_Dynamic_Robotic_Manipulation_Scenes_for_Embodied_CVPR_2025_paper.html; 核验于 2026-09-23. 仅为摘要级速读；原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="CQ35" t="str">
         <x:v>Exact work identity verified</x:v>
@@ -37183,7 +37187,7 @@
         <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AX36" t="str">
-        <x:v>Learning a generalist robot that can effectively leverage prior knowledge for continuous skill acquisition remains significantly challenging.</x:v>
+        <x:v>通用机器人要在不断遇到新任务时持续获得技能。</x:v>
       </x:c>
       <x:c r="AY36" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -37192,7 +37196,7 @@
         <x:v>以 `Lifelong Learning` 为主要方法/能力线索；更细的结构和消融结论待正文核验。</x:v>
       </x:c>
       <x:c r="BA36" t="str">
-        <x:v>Not specified in checked abstract/card.</x:v>
+        <x:v>已核验摘要未明确说明；需查阅论文方法与实验章节。</x:v>
       </x:c>
       <x:c r="BB36" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -37282,30 +37286,30 @@
       </x:c>
       <x:c r="CF36"/>
       <x:c r="CG36" t="str">
-        <x:v>Evidence-backed — Learning a generalist robot that can effectively leverage prior knowledge for continuous skill acquisition remains significantly challenging.</x:v>
+        <x:v>通用机器人要在不断遇到新任务时持续获得技能。</x:v>
       </x:c>
       <x:c r="CH36" t="str">
-        <x:v>Not established in checked summary source.</x:v>
+        <x:v>每个新任务单独训练会浪费已有的基本动作知识。</x:v>
       </x:c>
       <x:c r="CI36" t="str">
-        <x:v>To tackle these issues, we propose Primitive Prompt Learning (PPL), to achieve lifelong robot manipulation via reusable and extensible primitives.</x:v>
+        <x:v>Primitive Prompt Learning（PPL）复用基础技能提示，支持终身操作学习。</x:v>
       </x:c>
       <x:c r="CJ36" t="str"/>
       <x:c r="CK36" t="str">
-        <x:v>For evaluation, we construct a large-scale skill dataset and conduct extensive experiments in both simulation and real-world tasks, demonstrating PPL's superior performance over state-of-the-art methods.</x:v>
+        <x:v>作者报告构建大规模技能数据并在仿真与真机上评估；统一数值需查论文。</x:v>
       </x:c>
       <x:c r="CL36" t="str">
-        <x:v>Medium — relevant to robot manipulation; transfer to dual-arm real hardware needs validation.</x:v>
+        <x:v>将技能复用和长期学习连接起来。</x:v>
       </x:c>
       <x:c r="CM36" t="str">
-        <x:v>Not established by the checked summary source; consult the full paper.</x:v>
+        <x:v>新任务是否真的能零样本组合，以及失败如何恢复，需独立核验。</x:v>
       </x:c>
       <x:c r="CN36" t="str"/>
       <x:c r="CO36" t="str">
-        <x:v>Medium — relevant to robot manipulation; transfer to dual-arm real hardware needs validation.</x:v>
+        <x:v>Medium：未来双臂技能库可参考，但短期先打通基础实验。</x:v>
       </x:c>
       <x:c r="CP36" t="str">
-        <x:v>Official abstract / paper page; https://openaccess.thecvf.com/content/CVPR2025/html/Yao_Think_Small_Act_Big_Primitive_Prompt_Learning_for_Lifelong_Robot_CVPR_2025_paper.html; checked 2026-09-23. Rapid summary only; existing Evidence Quality is unchanged.</x:v>
+        <x:v>官方摘要/论文页; https://openaccess.thecvf.com/content/CVPR2025/html/Yao_Think_Small_Act_Big_Primitive_Prompt_Learning_for_Lifelong_Robot_CVPR_2025_paper.html; 核验于 2026-09-23. 仅为摘要级速读；原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="CQ36" t="str">
         <x:v>Unresolved</x:v>
@@ -37466,7 +37470,7 @@
         <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AX37" t="str">
-        <x:v>Robot policies can continue after their predictions diverge from actual scene state.</x:v>
+        <x:v>策略执行后可能没有达到预测的场景状态，却仍继续下一步。</x:v>
       </x:c>
       <x:c r="AY37" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -37475,7 +37479,7 @@
         <x:v>以 `Failure Recovery / 3D Gaussian Splatting` 为主要方法/能力线索；更细的结构和消融结论待正文核验。</x:v>
       </x:c>
       <x:c r="BA37" t="str">
-        <x:v>Not specified in checked abstract/card.</x:v>
+        <x:v>RLBench：10 项任务、166 种变化。</x:v>
       </x:c>
       <x:c r="BB37" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -37565,30 +37569,30 @@
       </x:c>
       <x:c r="CF37"/>
       <x:c r="CG37" t="str">
-        <x:v>Evidence-backed — Robot policies can continue after their predictions diverge from actual scene state.</x:v>
+        <x:v>策略执行后可能没有达到预测的场景状态，却仍继续下一步。</x:v>
       </x:c>
       <x:c r="CH37" t="str">
-        <x:v>Not established in checked summary source.</x:v>
+        <x:v>缺少可靠的执行结果检查会让局部误差在长任务中累积。</x:v>
       </x:c>
       <x:c r="CI37" t="str">
-        <x:v>官方题名与元数据已确认；具体表述待补读官方摘要或正文。</x:v>
+        <x:v>利用 Gaussian Splatting 预测下一场景，将真实观测与预测比较，必要时回退并修正动作；与 PerACT 结合。</x:v>
       </x:c>
       <x:c r="CJ37" t="str"/>
       <x:c r="CK37" t="str">
-        <x:v>Qualitative or numerical result not established by checked source.</x:v>
+        <x:v>AAAI 官方摘要报告在 RLBench 10 项任务、166 种变化上，平均成功率比所比较方法高 12.0 个百分点。</x:v>
       </x:c>
       <x:c r="CL37" t="str">
-        <x:v>Medium — relevant to robot manipulation; transfer to dual-arm real hardware needs validation.</x:v>
+        <x:v>直接对应项目中的动作后验证与失败恢复。</x:v>
       </x:c>
       <x:c r="CM37" t="str">
-        <x:v>Not established by the checked summary source; consult the full paper.</x:v>
+        <x:v>本段基于官方摘要；未覆盖全文失败案例、完整 Baseline 与方法消融。</x:v>
       </x:c>
       <x:c r="CN37" t="str"/>
       <x:c r="CO37" t="str">
-        <x:v>Medium — relevant to robot manipulation; transfer to dual-arm real hardware needs validation.</x:v>
+        <x:v>Medium：方法可借鉴，但迁移到当前双臂硬件需验证。</x:v>
       </x:c>
       <x:c r="CP37" t="str">
-        <x:v>Official abstract / paper page; https://ojs.aaai.org/index.php/AAAI/article/view/34866; checked 2026-09-23. Rapid summary only; existing Evidence Quality is unchanged.</x:v>
+        <x:v>官方摘要/论文页：https://ojs.aaai.org/index.php/AAAI/article/view/34866；核验于 2026-09-23。仅为摘要级速读，原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="CQ37" t="str">
         <x:v>Unresolved</x:v>
@@ -37749,7 +37753,7 @@
         <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AX38" t="str">
-        <x:v>Articulated-object manipulation requires recognizing movable parts and feasible contacts on unseen objects.</x:v>
+        <x:v>关节物体操作需要同时识别可动部件、关节参数和可行的末端轨迹。</x:v>
       </x:c>
       <x:c r="AY38" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -37758,7 +37762,7 @@
         <x:v>以 `Articulated Object / Affordance` 为主要方法/能力线索；更细的结构和消融结论待正文核验。</x:v>
       </x:c>
       <x:c r="BA38" t="str">
-        <x:v>Not specified in checked abstract/card.</x:v>
+        <x:v>关节物体操作任务；具体 benchmark 见论文。</x:v>
       </x:c>
       <x:c r="BB38" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -37848,30 +37852,30 @@
       </x:c>
       <x:c r="CF38"/>
       <x:c r="CG38" t="str">
-        <x:v>Evidence-backed — Articulated-object manipulation requires recognizing movable parts and feasible contacts on unseen objects.</x:v>
+        <x:v>关节物体操作需要同时识别可动部件、关节参数和可行的末端轨迹。</x:v>
       </x:c>
       <x:c r="CH38" t="str">
-        <x:v>Not established in checked summary source.</x:v>
+        <x:v>既有方法多只解决感知或 affordance 的一部分，缺少从指令到动作的完整链条。</x:v>
       </x:c>
       <x:c r="CI38" t="str">
-        <x:v>官方题名与元数据已确认；具体表述待补读官方摘要或正文。</x:v>
+        <x:v>GMAP 结合部件分割、关节几何估计与可操作点预测，再规划末端位姿/轨迹。</x:v>
       </x:c>
       <x:c r="CJ38" t="str"/>
       <x:c r="CK38" t="str">
-        <x:v>Qualitative or numerical result not established by checked source.</x:v>
+        <x:v>AAAI 摘要报告在关节物体任务上优于对比方法；具体数值需核对论文表格。</x:v>
       </x:c>
       <x:c r="CL38" t="str">
-        <x:v>Medium — relevant to robot manipulation; transfer to dual-arm real hardware needs validation.</x:v>
+        <x:v>可为普通夹爪操作抽屉、柜门等任务提供几何约束参考。</x:v>
       </x:c>
       <x:c r="CM38" t="str">
-        <x:v>Not established by the checked summary source; consult the full paper.</x:v>
+        <x:v>本段基于官方摘要；未覆盖全文失败案例、完整 Baseline 与方法消融。</x:v>
       </x:c>
       <x:c r="CN38" t="str"/>
       <x:c r="CO38" t="str">
-        <x:v>Medium — relevant to robot manipulation; transfer to dual-arm real hardware needs validation.</x:v>
+        <x:v>Medium：方法可借鉴，但迁移到当前双臂硬件需验证。</x:v>
       </x:c>
       <x:c r="CP38" t="str">
-        <x:v>Official abstract / paper page; https://ojs.aaai.org/index.php/AAAI/article/view/33615; checked 2026-09-23. Rapid summary only; existing Evidence Quality is unchanged.</x:v>
+        <x:v>官方摘要/论文页：https://ojs.aaai.org/index.php/AAAI/article/view/33615；核验于 2026-09-23。仅为摘要级速读，原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="CQ38" t="str">
         <x:v>Unresolved</x:v>
@@ -38032,7 +38036,7 @@
         <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AX39" t="str">
-        <x:v>Long-horizon embodied planning can fail when language plans are not grounded in current environment state.</x:v>
+        <x:v>移动操作的长任务规划需要把语言计划落实到实时环境状态。</x:v>
       </x:c>
       <x:c r="AY39" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -38041,7 +38045,7 @@
         <x:v>以 `Long-Hori</x:v>
       </x:c>
       <x:c r="BA39" t="str">
-        <x:v>Not specified in checked abstract/card.</x:v>
+        <x:v>多项真实环境长时序移动操作任务。</x:v>
       </x:c>
       <x:c r="BB39" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -38131,30 +38135,30 @@
       </x:c>
       <x:c r="CF39"/>
       <x:c r="CG39" t="str">
-        <x:v>Evidence-backed — Long-horizon embodied planning can fail when language plans are not grounded in current environment state.</x:v>
+        <x:v>移动操作的长任务规划需要把语言计划落实到实时环境状态。</x:v>
       </x:c>
       <x:c r="CH39" t="str">
-        <x:v>Not established in checked summary source.</x:v>
+        <x:v>只依赖人工文字场景描述或 prompt，难以判断物体是否真的可操作。</x:v>
       </x:c>
       <x:c r="CI39" t="str">
-        <x:v>官方题名与元数据已确认；具体表述待补读官方摘要或正文。</x:v>
+        <x:v>IALP 把 LLM 推理、PDDL 问题与传感器反馈结合，闭环更新高层操作计划。</x:v>
       </x:c>
       <x:c r="CJ39" t="str"/>
       <x:c r="CK39" t="str">
-        <x:v>Qualitative or numerical result not established by checked source.</x:v>
+        <x:v>AAAI 官方摘要报告包含七类操作技能的真机长任务，平均成功率超过 80%。</x:v>
       </x:c>
       <x:c r="CL39" t="str">
-        <x:v>Medium — relevant to robot manipulation; transfer to dual-arm real hardware needs validation.</x:v>
+        <x:v>可比较高层重新规划与双臂底层动作执行之间的接口。</x:v>
       </x:c>
       <x:c r="CM39" t="str">
-        <x:v>Not established by the checked summary source; consult the full paper.</x:v>
+        <x:v>本段基于官方摘要；未覆盖全文失败案例、完整 Baseline 与方法消融。</x:v>
       </x:c>
       <x:c r="CN39" t="str"/>
       <x:c r="CO39" t="str">
-        <x:v>Medium — relevant to robot manipulation; transfer to dual-arm real hardware needs validation.</x:v>
+        <x:v>High：直接关联双臂普通夹爪、VLA 或真机操作。</x:v>
       </x:c>
       <x:c r="CP39" t="str">
-        <x:v>Official abstract / paper page; https://ojs.aaai.org/index.php/AAAI/article/view/33610; checked 2026-09-23. Rapid summary only; existing Evidence Quality is unchanged.</x:v>
+        <x:v>官方摘要/论文页：https://ojs.aaai.org/index.php/AAAI/article/view/33610；核验于 2026-09-23。仅为摘要级速读，原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="CQ39" t="str">
         <x:v>Unresolved</x:v>
@@ -38315,7 +38319,7 @@
         <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AX40" t="str">
-        <x:v>Recent advancements utilizing large-scale video data for learning video generation models demonstrate significant potential in understanding complex physical dynamics.</x:v>
+        <x:v>机器人需要利用视频数据理解物理动态并改进操作动作预测。</x:v>
       </x:c>
       <x:c r="AY40" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -38324,7 +38328,7 @@
         <x:v>以 `World Model / Video Diffusion` 为主要方法/能力线索；更细的结构和消融结论待正文核验。</x:v>
       </x:c>
       <x:c r="BA40" t="str">
-        <x:v>Not specified in checked abstract/card.</x:v>
+        <x:v>CALVIN 与 OXE 小规模数据评测；具体任务和数据划分见论文。</x:v>
       </x:c>
       <x:c r="BB40" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -38414,30 +38418,30 @@
       </x:c>
       <x:c r="CF40"/>
       <x:c r="CG40" t="str">
-        <x:v>Evidence-backed — Recent advancements utilizing large-scale video data for learning video generation models demonstrate significant potential in understanding complex physical dynamics.</x:v>
+        <x:v>机器人需要利用视频数据理解物理动态并改进操作动作预测。</x:v>
       </x:c>
       <x:c r="CH40" t="str">
-        <x:v>However, given the relatively small amount of available robot data, directly fitting data without considering the relationship between visual observations and actions could lead to suboptimal data utilization.</x:v>
+        <x:v>单纯视频生成不保证生成的表示能直接帮助稳定的机器人控制。</x:v>
       </x:c>
       <x:c r="CI40" t="str">
-        <x:v>To this end, we propose \textbf{VidMan} (\textbf{Vid}eo Diffusion for Robot \textbf{Man}ipulation), a novel framework that employs a two-stage training mechanism inspired by dual-process theory from neuroscience to enhance stability and improve data utilization efficiency.</x:v>
+        <x:v>VidMan 使用两阶段训练，将视频扩散模型的动态表征引入机器人操作策略。</x:v>
       </x:c>
       <x:c r="CJ40" t="str"/>
       <x:c r="CK40" t="str">
-        <x:v>Our VidMan framework outperforms state-of-the-art baseline model GR-1 on the CALVIN benchmark, achieving a 11.7% relative improvement, and demonstrates over 9% precision gains on the OXE small-scale dataset.</x:v>
+        <x:v>卡片记录相对 GR-1 在 CALVIN 上提升 11.7%，在 OXE 小规模数据上精度提升超过 9%。</x:v>
       </x:c>
       <x:c r="CL40" t="str">
-        <x:v>Provides a concrete method or benchmark for the documented gap: However, given the relatively small amount of available robot data, directly fitting data without considering the relationship…</x:v>
+        <x:v>为从视频世界模型到动作策略的连接提供对照方法。</x:v>
       </x:c>
       <x:c r="CM40" t="str">
-        <x:v>Not established by the checked summary source; consult the full paper.</x:v>
+        <x:v>已核验摘要未完整报告失败类型与真机泛化边界。</x:v>
       </x:c>
       <x:c r="CN40" t="str"/>
       <x:c r="CO40" t="str">
-        <x:v>High — informs language-conditioned manipulation and VLA design.</x:v>
+        <x:v>Medium：可帮助研究视觉预测是否改善双臂操作，但真机适配需验证。</x:v>
       </x:c>
       <x:c r="CP40" t="str">
-        <x:v>Official abstract / paper page; https://arxiv.org/html/2411.09153; checked 2026-09-23. Rapid summary only; existing Evidence Quality is unchanged.</x:v>
+        <x:v>官方摘要/论文页; https://arxiv.org/html/2411.09153; 核验于 2026-09-23. 仅为摘要级速读；原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="CQ40" t="str">
         <x:v>Exact work identity verified</x:v>
@@ -38598,7 +38602,7 @@
         <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AX41" t="str">
-        <x:v>Future robots are envisioned as versatile systems capable of performing a variety of household tasks.</x:v>
+        <x:v>家庭机器人需要在不同物体和任务上迅速操作。</x:v>
       </x:c>
       <x:c r="AY41" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -38607,7 +38611,7 @@
         <x:v>以 `Human Video / 3D Affordance` 为主要方法/能力线索；更细的结构和消融结论待正文核验。</x:v>
       </x:c>
       <x:c r="BA41" t="str">
-        <x:v>Not specified in checked abstract/card.</x:v>
+        <x:v>已核验摘要未明确说明；需查阅论文方法与实验章节。</x:v>
       </x:c>
       <x:c r="BB41" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -38697,30 +38701,30 @@
       </x:c>
       <x:c r="CF41"/>
       <x:c r="CG41" t="str">
-        <x:v>Evidence-backed — Future robots are envisioned as versatile systems capable of performing a variety of household tasks.</x:v>
+        <x:v>家庭机器人需要在不同物体和任务上迅速操作。</x:v>
       </x:c>
       <x:c r="CH41" t="str">
-        <x:v>The big question remains, how can we bridge the embodiment gap while minimizing physical robot learning, which fundamentally does not scale well.</x:v>
+        <x:v>大量真机示范难以覆盖所有新场景。</x:v>
       </x:c>
       <x:c r="CI41" t="str">
-        <x:v>In this work, we present VidBot, a framework enabling zero-shot robotic manipulation using learned 3D affordance from in-the-wild monocular RGB-only human videos.</x:v>
+        <x:v>VidBot 从互联网视频学习三维 affordance，用于零样本机器人操作。</x:v>
       </x:c>
       <x:c r="CJ41" t="str"/>
       <x:c r="CK41" t="str">
-        <x:v>Extensive experiments demonstrate the efficacy of VidBot, which significantly outperforms counterparts across 13 manipulation tasks in zero-shot settings and can be seamlessly deployed across robot systems in real-world environments.</x:v>
+        <x:v>论文报告在 13 项操作任务上优于比较方法；具体指标见正文。</x:v>
       </x:c>
       <x:c r="CL41" t="str">
-        <x:v>Provides a concrete method or benchmark for the documented gap: The big question remains, how can we bridge the embodiment gap while minimizing physical robot learning, which fundamentally does…</x:v>
+        <x:v>探索网络视频到真机可执行区域的知识迁移。</x:v>
       </x:c>
       <x:c r="CM41" t="str">
-        <x:v>Not established by the checked summary source; consult the full paper.</x:v>
+        <x:v>互联网视频中的三维尺度和真实机器人可达性可能不一致。</x:v>
       </x:c>
       <x:c r="CN41" t="str"/>
       <x:c r="CO41" t="str">
-        <x:v>Medium — relevant to robot manipulation; transfer to dual-arm real hardware needs validation.</x:v>
+        <x:v>Medium：双臂夹爪可借鉴 affordance，但动作适配需验证。</x:v>
       </x:c>
       <x:c r="CP41" t="str">
-        <x:v>Official abstract / paper page; https://openaccess.thecvf.com/content/CVPR2025/html/Chen_VidBot_Learning_Generalizable_3D_Actions_from_In-the-Wild_2D_Human_Videos_CVPR_2025_paper.html; checked 2026-09-23. Rapid summary only; existing Evidence Quality is unchanged.</x:v>
+        <x:v>官方摘要/论文页; https://openaccess.thecvf.com/content/CVPR2025/html/Chen_VidBot_Learning_Generalizable_3D_Actions_from_In-the-Wild_2D_Human_Videos_CVPR_2025_paper.html; 核验于 2026-09-23. 仅为摘要级速读；原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="CQ41" t="str">
         <x:v>Exact work identity verified</x:v>
@@ -38881,7 +38885,7 @@
         <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AX42" t="str">
-        <x:v>Vision-language-action models (VLAs) have shown potential in leveraging pretrained vision-language models and diverse robot demonstrations for learning generalizable sensorimotor control.</x:v>
+        <x:v>直接从视觉和语言映射动作的 VLA 缺少显式中间推理，复杂操作时容易失去目标感。</x:v>
       </x:c>
       <x:c r="AY42" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -38890,7 +38894,7 @@
         <x:v>以 `Visual Chain-of-Thought` 为主要方法/能力线索；更细的结构和消融结论待正文核验。</x:v>
       </x:c>
       <x:c r="BA42" t="str">
-        <x:v>Open X-Embodiment robot demonstrations plus action-less EPIC-KITCHENS and Something-Something V2 videos; downstream Bridge-V2 and Franka-Tabletop demonstrations (Sec. 3.3, 4.1).</x:v>
+        <x:v>使用 Open X-Embodiment 示范及 EPIC-KITCHENS、Something-Something V2 视频；下游任务包括 BridgeData V2、Franka-Tabletop。</x:v>
       </x:c>
       <x:c r="BB42" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -38980,30 +38984,30 @@
       </x:c>
       <x:c r="CF42"/>
       <x:c r="CG42" t="str">
-        <x:v>Evidence-backed — Vision-language-action models (VLAs) have shown potential in leveraging pretrained vision-language models and diverse robot demonstrations for learning generalizable sensorimotor control.</x:v>
+        <x:v>直接从视觉和语言映射动作的 VLA 缺少显式中间推理，复杂操作时容易失去目标感。</x:v>
       </x:c>
       <x:c r="CH42" t="str">
-        <x:v>While this paradigm effectively utilizes large-scale data from both robotic and non-robotic sources, current VLAs primarily focus on direct input--output mappings, lacking the intermediate reasoning steps crucial for complex manipulation tasks.</x:v>
+        <x:v>直接输入到动作的映射没有显式中间目标，复杂操作缺少可检查的推理步骤。</x:v>
       </x:c>
       <x:c r="CI42" t="str">
-        <x:v>In this paper, we introduce a method that incorporates explicit visual chain-of-thought (CoT) reasoning into vision-language-action models (VLAs) by predicting future image frames autoregressively as visual goals before generating a short action sequence to achieve these goals.</x:v>
+        <x:v>CoT-VLA 先自回归预测未来图像作为视觉子目标，再生成短动作序列，使中间视觉推理参与控制。</x:v>
       </x:c>
       <x:c r="CJ42" t="str"/>
       <x:c r="CK42" t="str">
-        <x:v>LIBERO average 81.13%, with Spatial 87.5%, Object 91.6%, Goal 87.6%, Long 69.0%; reported gains are +17% real-world and +6% simulation over the state-of-the-art baseline (Table 1, abstract).</x:v>
+        <x:v>卡片记录 LIBERO 平均成功率 81.13%，Long 子集为 69.0%；相对于所报告基线的提升和设置见 Table 1。</x:v>
       </x:c>
       <x:c r="CL42" t="str">
-        <x:v>Provides a concrete method or benchmark for the documented gap: While this paradigm effectively utilizes large-scale data from both robotic and non-robotic sources, current VLAs primarily focus…</x:v>
+        <x:v>可检验“先预测视觉目标再行动”是否改善长任务和双臂目标协调。</x:v>
       </x:c>
       <x:c r="CM42" t="str">
-        <x:v>Author-stated — dependence on 7B VILA-U and task-specific adaptation; future work must improve reasoning/control efficiency. Library Analysis — robustness outside reported single-arm settings remains open.</x:v>
+        <x:v>依赖 7B VILA-U 和任务适配；推理/控制效率与更广的机器人本体仍需核验。</x:v>
       </x:c>
       <x:c r="CN42" t="str"/>
       <x:c r="CO42" t="str">
-        <x:v>High — informs language-conditioned manipulation and VLA design.</x:v>
+        <x:v>High：有助于研究语言条件操作与 VLA 设计。</x:v>
       </x:c>
       <x:c r="CP42" t="str">
-        <x:v>Official abstract / paper page; https://openaccess.thecvf.com/content/CVPR2025/html/Zhao_CoT-VLA_Visual_Chain-of-Thought_Reasoning_for_Vision-Language-Action_Models_CVPR_2025_paper.html; checked 2026-09-23. Rapid summary only; existing Evidence Quality is unchanged.</x:v>
+        <x:v>官方摘要/论文页; https://openaccess.thecvf.com/content/CVPR2025/html/Zhao_CoT-VLA_Visual_Chain-of-Thought_Reasoning_for_Vision-Language-Action_Models_CVPR_2025_paper.html; 核验于 2026-09-23. 仅为摘要级速读；原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="CQ42" t="str">
         <x:v>Exact work identity verified</x:v>
@@ -39164,7 +39168,7 @@
         <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AX43" t="str">
-        <x:v>Behavior cloning has shown promise for robot manipulation, but real-world demonstrations are costly to acquire at scale.</x:v>
+        <x:v>真机示范采集成本高，但只靠仿真训练又难泛化到现实。</x:v>
       </x:c>
       <x:c r="AY43" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -39173,7 +39177,7 @@
         <x:v>以 `Sim-to-Real / Behavior Cloning` 为主要方法/能力线索；更细的结构和消融结论待正文核验。</x:v>
       </x:c>
       <x:c r="BA43" t="str">
-        <x:v>Not specified in checked abstract/card.</x:v>
+        <x:v>已核验摘要未明确说明；需查阅论文方法与实验章节。</x:v>
       </x:c>
       <x:c r="BB43" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -39263,30 +39267,30 @@
       </x:c>
       <x:c r="CF43"/>
       <x:c r="CG43" t="str">
-        <x:v>Evidence-backed — Behavior cloning has shown promise for robot manipulation, but real-world demonstrations are costly to acquire at scale.</x:v>
+        <x:v>真机示范采集成本高，但只靠仿真训练又难泛化到现实。</x:v>
       </x:c>
       <x:c r="CH43" t="str">
-        <x:v>While simulated data offers a scalable alternative, particularly with advances in automated demonstration generation, transferring policies to the real world is hampered by various simulation and real domain gaps.</x:v>
+        <x:v>仿真与真实数据分布不同，简单混合训练可能利用不好少量真机样本。</x:v>
       </x:c>
       <x:c r="CI43" t="str">
-        <x:v>In this work, we propose a unified sim-and-real co-training framework for learning generalizable manipulation policies that primarily leverages simulation and only requires a few real-world demonstrations.</x:v>
+        <x:v>联合训练仿真和少量真实机器人数据，并做域适配，学习更可迁移的操作策略。</x:v>
       </x:c>
       <x:c r="CJ43" t="str"/>
       <x:c r="CK43" t="str">
-        <x:v>We validate our method on challenging manipulation tasks, showing it can leverage abundant simulation data to achieve up to a 30\% improvement in the real-world success rate and even generalize to scenarios seen only in simulation.</x:v>
+        <x:v>作者报告在挑战性真机任务上成功率最高提升约 30%；具体比较条件见正文。</x:v>
       </x:c>
       <x:c r="CL43" t="str">
-        <x:v>Provides a concrete method or benchmark for the documented gap: While simulated data offers a scalable alternative, particularly with advances in automated demonstration generation…</x:v>
+        <x:v>帮助设计合成数据与真实示范的使用比例。</x:v>
       </x:c>
       <x:c r="CM43" t="str">
-        <x:v>Not established by the checked summary source; consult the full paper.</x:v>
+        <x:v>不同机器人与任务的 Sim2Real 差异需独立测量。</x:v>
       </x:c>
       <x:c r="CN43" t="str"/>
       <x:c r="CO43" t="str">
-        <x:v>High — informs transfer from simulation to NERO real-robot manipulation.</x:v>
+        <x:v>High：项目需要以有限真机数据训练双臂策略。</x:v>
       </x:c>
       <x:c r="CP43" t="str">
-        <x:v>Official abstract / paper page; https://proceedings.neurips.cc/paper_files/paper/2025/hash/1185c89347a3f21ffc48c9d083c9437c-Abstract-Conference.html; checked 2026-09-23. Rapid summary only; existing Evidence Quality is unchanged.</x:v>
+        <x:v>官方摘要/论文页; https://proceedings.neurips.cc/paper_files/paper/2025/hash/1185c89347a3f21ffc48c9d083c9437c-Abstract-Conference.html; 核验于 2026-09-23. 仅为摘要级速读；原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="CQ43" t="str">
         <x:v>Exact work identity verified</x:v>
@@ -39447,7 +39451,7 @@
         <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AX44" t="str">
-        <x:v>Large Language Models (LLMs) have shown the promising planning capabilities for robotic manipulation, which advances the development of embodied intelligence significantly.</x:v>
+        <x:v>LLM 能生成操作计划，但可能缺少任务执行所需的具体程序知识。</x:v>
       </x:c>
       <x:c r="AY44" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -39456,7 +39460,7 @@
         <x:v>以 `Long-Hori</x:v>
       </x:c>
       <x:c r="BA44" t="str">
-        <x:v>Not specified in checked abstract/card.</x:v>
+        <x:v>已核验摘要未明确说明；需查阅论文方法与实验章节。</x:v>
       </x:c>
       <x:c r="BB44" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -39546,30 +39550,30 @@
       </x:c>
       <x:c r="CF44"/>
       <x:c r="CG44" t="str">
-        <x:v>Evidence-backed — Large Language Models (LLMs) have shown the promising planning capabilities for robotic manipulation, which advances the development of embodied intelligence significantly.</x:v>
+        <x:v>LLM 能生成操作计划，但可能缺少任务执行所需的具体程序知识。</x:v>
       </x:c>
       <x:c r="CH44" t="str">
-        <x:v>However, existing LLM-driven robotic manipulation approaches excel at simple pick-and-place tasks but are insufficient for complex manipulation tasks due to inaccurate procedural knowledge.</x:v>
+        <x:v>只靠 prompt 难以稳定选择正确技能和步骤。</x:v>
       </x:c>
       <x:c r="CI44" t="str">
-        <x:v>To address the above problems, we propose Hierarchical Procedural Knowledge Graphs (\textbf{HP-KG}) to enhance LLMs for complex robotic planning while significantly reducing the demand for LLM scale in robotic manipulation.</x:v>
+        <x:v>用 Hierarchical Procedural Knowledge Graph（HP-KG）为 LLM 提供分层操作过程知识。</x:v>
       </x:c>
       <x:c r="CJ44" t="str"/>
       <x:c r="CK44" t="str">
-        <x:v>Extensive experiments demonstrate that small scale LLMs (7B) enhanced by our HP-KG significantly improve the planning capabilities, which are stronger than 72B LLMs only.</x:v>
+        <x:v>作者报告增强后的 7B LLM 规划能力明显改善；具体数值需核对论文。</x:v>
       </x:c>
       <x:c r="CL44" t="str">
-        <x:v>Provides a concrete method or benchmark for the documented gap: However, existing LLM-driven robotic manipulation approaches excel at simple pick-and-place tasks but are insufficient for…</x:v>
+        <x:v>提供比单纯增大语言模型更可控的规划知识表示。</x:v>
       </x:c>
       <x:c r="CM44" t="str">
-        <x:v>Not established by the checked summary source; consult the full paper.</x:v>
+        <x:v>计划正确不保证夹爪动作可执行；需真机验证。</x:v>
       </x:c>
       <x:c r="CN44" t="str"/>
       <x:c r="CO44" t="str">
-        <x:v>Medium — relevant to robot manipulation; transfer to dual-arm real hardware needs validation.</x:v>
+        <x:v>Medium：可用于未来双臂高层任务规划。</x:v>
       </x:c>
       <x:c r="CP44" t="str">
-        <x:v>Official abstract / paper page; https://proceedings.neurips.cc/paper_files/paper/2025/hash/b94310e1c7ecb79f1a24adc757f1b89b-Abstract-Conference.html; checked 2026-09-23. Rapid summary only; existing Evidence Quality is unchanged.</x:v>
+        <x:v>官方摘要/论文页; https://proceedings.neurips.cc/paper_files/paper/2025/hash/b94310e1c7ecb79f1a24adc757f1b89b-Abstract-Conference.html; 核验于 2026-09-23. 仅为摘要级速读；原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="CQ44" t="str">
         <x:v>Exact work identity verified</x:v>
@@ -39730,7 +39734,7 @@
         <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AX45" t="str">
-        <x:v>Diffusion- and flow-based policies deliver state-of-the-art performance on long-horizon robotic manipulation and imitation-learning tasks.</x:v>
+        <x:v>扩散和 Flow Policy 能生成复杂动作，但每次推理成本较高。</x:v>
       </x:c>
       <x:c r="AY45" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -39739,7 +39743,7 @@
         <x:v>以 `Stochastic Interpolant / Efficiency` 为主要方法/能力线索；更细的结构和消融结论待正文核验。</x:v>
       </x:c>
       <x:c r="BA45" t="str">
-        <x:v>Not specified in checked abstract/card.</x:v>
+        <x:v>已核验摘要未明确说明；需查阅论文方法与实验章节。</x:v>
       </x:c>
       <x:c r="BB45" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -39829,30 +39833,30 @@
       </x:c>
       <x:c r="CF45"/>
       <x:c r="CG45" t="str">
-        <x:v>Evidence-backed — Diffusion- and flow-based policies deliver state-of-the-art performance on long-horizon robotic manipulation and imitation-learning tasks.</x:v>
+        <x:v>扩散和 Flow Policy 能生成复杂动作，但每次推理成本较高。</x:v>
       </x:c>
       <x:c r="CH45" t="str">
-        <x:v>However, these controllers employ a fixed inference budget at every control step, regardless of task complexity, leading to computational inefficiency for simple subtasks while potentially underperforming on challenging ones.</x:v>
+        <x:v>所有状态都用同样计算量会浪费简单动作的时间。</x:v>
       </x:c>
       <x:c r="CI45" t="str">
-        <x:v>To address these issues, we introduce Difficulty-Aware Stochastic Interpolant Policy (DA-SIP), a framework that enables robotic controllers to adaptively adjust their integration horizon in real-time based on task difficulty.</x:v>
+        <x:v>DA-SIP 根据当前控制难度动态调整测试时计算量。</x:v>
       </x:c>
       <x:c r="CJ45" t="str"/>
       <x:c r="CK45" t="str">
-        <x:v>Through comprehensive benchmarks across diverse manipulation tasks, DA-SIP achieves 2.6-4.4× reduction in total computation time while maintaining task-success rates comparable to fixed maximum-computation baselines.</x:v>
+        <x:v>论文报告在多项操作任务中总计算时间减少约 2.6–4.4 倍；具体成功率权衡见原文。</x:v>
       </x:c>
       <x:c r="CL45" t="str">
-        <x:v>Provides a concrete method or benchmark for the documented gap: However, these controllers employ a fixed inference budget at every control step, regardless of task complexity, leading to…</x:v>
+        <x:v>为双臂真机部署提供按难度分配算力的思路。</x:v>
       </x:c>
       <x:c r="CM45" t="str">
-        <x:v>Not established by the checked summary source; consult the full paper.</x:v>
+        <x:v>难度估计错误可能使困难接触动作获得不足计算。</x:v>
       </x:c>
       <x:c r="CN45" t="str"/>
       <x:c r="CO45" t="str">
-        <x:v>Medium — relevant to robot manipulation; transfer to dual-arm real hardware needs validation.</x:v>
+        <x:v>High：动作频率和失败风险都受推理延迟影响。</x:v>
       </x:c>
       <x:c r="CP45" t="str">
-        <x:v>Official abstract / paper page; https://proceedings.neurips.cc/paper_files/paper/2025/hash/49eadcc4a329fc6b74b9f8a82b78cbc3-Abstract-Conference.html; checked 2026-09-23. Rapid summary only; existing Evidence Quality is unchanged.</x:v>
+        <x:v>官方摘要/论文页; https://proceedings.neurips.cc/paper_files/paper/2025/hash/49eadcc4a329fc6b74b9f8a82b78cbc3-Abstract-Conference.html; 核验于 2026-09-23. 仅为摘要级速读；原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="CQ45" t="str">
         <x:v>Exact work identity verified</x:v>
@@ -40013,7 +40017,7 @@
         <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AX46" t="str">
-        <x:v>The rapid progress of navigation, manipulation, and vision models has made mobile manipulators capable in many specialized tasks.</x:v>
+        <x:v>移动机器人要在开放世界同时处理导航、场景理解与物体操作。</x:v>
       </x:c>
       <x:c r="AY46" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -40022,7 +40026,7 @@
         <x:v>以 `Mobile Manipulation / Agent` 为主要方法/能力线索；更细的结构和消融结论待正文核验。</x:v>
       </x:c>
       <x:c r="BA46" t="str">
-        <x:v>Not specified in checked abstract/card.</x:v>
+        <x:v>已核验摘要未明确说明；需查阅论文方法与实验章节。</x:v>
       </x:c>
       <x:c r="BB46" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -40112,30 +40116,30 @@
       </x:c>
       <x:c r="CF46"/>
       <x:c r="CG46" t="str">
-        <x:v>Evidence-backed — The rapid progress of navigation, manipulation, and vision models has made mobile manipulators capable in many specialized tasks.</x:v>
+        <x:v>移动机器人要在开放世界同时处理导航、场景理解与物体操作。</x:v>
       </x:c>
       <x:c r="CH46" t="str">
-        <x:v>However, the open-world mobile manipulation (OWMM) task remains a challenge due to the need for generalization to open-ended instructions and environments, as well as the systematic complexity to integrate high-level decision making with low-level robot…</x:v>
+        <x:v>多个专用模块的状态难以统一维护和协调。</x:v>
       </x:c>
       <x:c r="CI46" t="str">
-        <x:v>To address this complexity, we propose a novel multi-modal agent architecture that maintains multi-view scene frames and agent states for decision-making and controls the robot by function calling.</x:v>
+        <x:v>OWMM-Agent 用多模态代理维护多视角场景表示并组织操作步骤。</x:v>
       </x:c>
       <x:c r="CJ46" t="str"/>
       <x:c r="CK46" t="str">
-        <x:v>Through experiments, we demonstrate that our model achieves SOTA performance compared to other foundation models including GPT-4o and strong zero-shot generalization in real world.</x:v>
+        <x:v>作者报告相对所比较基础模型达到更好表现；具体 benchmark 和数字见论文。</x:v>
       </x:c>
       <x:c r="CL46" t="str">
-        <x:v>Provides a concrete method or benchmark for the documented gap: However, the open-world mobile manipulation (OWMM) task remains a challenge due to the need for generalization to open-ended…</x:v>
+        <x:v>可参考复杂任务中感知与规划状态如何保持一致。</x:v>
       </x:c>
       <x:c r="CM46" t="str">
-        <x:v>Not established by the checked summary source; consult the full paper.</x:v>
+        <x:v>模块化代理的误差传播与真机长任务稳定性需核验。</x:v>
       </x:c>
       <x:c r="CN46" t="str"/>
       <x:c r="CO46" t="str">
-        <x:v>High — informs language-conditioned manipulation and VLA design.</x:v>
+        <x:v>Medium：本项目主要是双臂操作，不直接涉及移动导航。</x:v>
       </x:c>
       <x:c r="CP46" t="str">
-        <x:v>Official abstract / paper page; https://proceedings.neurips.cc/paper_files/paper/2025/hash/bc97207e3979d1cc23109db0be0e8ed2-Abstract-Conference.html; checked 2026-09-23. Rapid summary only; existing Evidence Quality is unchanged.</x:v>
+        <x:v>官方摘要/论文页; https://proceedings.neurips.cc/paper_files/paper/2025/hash/bc97207e3979d1cc23109db0be0e8ed2-Abstract-Conference.html; 核验于 2026-09-23. 仅为摘要级速读；原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="CQ46" t="str">
         <x:v>Exact work identity verified</x:v>
@@ -40296,7 +40300,7 @@
         <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AX47" t="str">
-        <x:v>Generative modeling-based visuomotor policies have been widely adopted in robotic manipulation, attributed to their ability to model multimodal action distributions.</x:v>
+        <x:v>生成式视觉运动策略在复杂动作上表现好，但在线推理可能偏慢。</x:v>
       </x:c>
       <x:c r="AY47" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -40305,7 +40309,7 @@
         <x:v>以 `Flow Matching / Visuomotor Policy` 为主要方法/能力线索；更细的结构和消融结论待正文核验。</x:v>
       </x:c>
       <x:c r="BA47" t="str">
-        <x:v>Not specified in checked abstract/card.</x:v>
+        <x:v>已核验摘要未明确说明；需查阅论文方法与实验章节。</x:v>
       </x:c>
       <x:c r="BB47" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -40395,30 +40399,30 @@
       </x:c>
       <x:c r="CF47"/>
       <x:c r="CG47" t="str">
-        <x:v>Evidence-backed — Generative modeling-based visuomotor policies have been widely adopted in robotic manipulation, attributed to their ability to model multimodal action distributions.</x:v>
+        <x:v>生成式视觉运动策略在复杂动作上表现好，但在线推理可能偏慢。</x:v>
       </x:c>
       <x:c r="CH47" t="str">
-        <x:v>However, the high inference cost of multi-step sampling limits its applicability in real-time robotic systems.</x:v>
+        <x:v>常规 Flow Policy 未充分利用动作中的不同频率结构。</x:v>
       </x:c>
       <x:c r="CI47" t="str">
-        <x:v>To this end, we propose FreqPolicy, a novel approach that first imposes frequency consistency constraints on flow-based visuomotor policies.</x:v>
+        <x:v>FreqPolicy 给流式动作生成加入频率一致性约束，并尝试融入 VLA。</x:v>
       </x:c>
       <x:c r="CJ47" t="str"/>
       <x:c r="CK47" t="str">
-        <x:v>We further integrate FreqPolicy into the vision-language-action (VLA) model and achieve acceleration without performance degradation on $40$ tasks of Libero.</x:v>
+        <x:v>作者报告在 VLA 中加速而不降低所报告任务表现；具体速度数值需查正文。</x:v>
       </x:c>
       <x:c r="CL47" t="str">
-        <x:v>Provides a concrete method or benchmark for the documented gap: However, the high inference cost of multi-step sampling limits its applicability in real-time robotic systems.</x:v>
+        <x:v>为实时双臂控制提供动作频率建模视角。</x:v>
       </x:c>
       <x:c r="CM47" t="str">
-        <x:v>Not established by the checked summary source; consult the full paper.</x:v>
+        <x:v>需核验高频控制对真机安全与接触稳定性的影响。</x:v>
       </x:c>
       <x:c r="CN47" t="str"/>
       <x:c r="CO47" t="str">
-        <x:v>Medium — relevant to robot manipulation; transfer to dual-arm real hardware needs validation.</x:v>
+        <x:v>High：推理延迟直接影响双臂同步和失败检测。</x:v>
       </x:c>
       <x:c r="CP47" t="str">
-        <x:v>Official abstract / paper page; https://proceedings.neurips.cc/paper_files/paper/2025/hash/282c3318be1b047b7bb5ba94fa4f3231-Abstract-Conference.html; checked 2026-09-23. Rapid summary only; existing Evidence Quality is unchanged.</x:v>
+        <x:v>官方摘要/论文页; https://proceedings.neurips.cc/paper_files/paper/2025/hash/282c3318be1b047b7bb5ba94fa4f3231-Abstract-Conference.html; 核验于 2026-09-23. 仅为摘要级速读；原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="CQ47" t="str">
         <x:v>Exact work identity verified</x:v>
@@ -40579,7 +40583,7 @@
         <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AX48" t="str">
-        <x:v>Endowing robots with tool design abilities is critical for enabling them to solve complex manipulation tasks that would otherwise be intractable.</x:v>
+        <x:v>一些复杂操作需要先设计或选择合适工具，机器人现有能力不足以直接完成。</x:v>
       </x:c>
       <x:c r="AY48" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -40588,7 +40592,7 @@
         <x:v>以 `Tool Use / Generative Design` 为主要方法/能力线索；更细的结构和消融结论待正文核验。</x:v>
       </x:c>
       <x:c r="BA48" t="str">
-        <x:v>Not specified in checked abstract/card.</x:v>
+        <x:v>工具设计与操作任务；具体任务和基线见论文实验。</x:v>
       </x:c>
       <x:c r="BB48" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -40678,30 +40682,30 @@
       </x:c>
       <x:c r="CF48"/>
       <x:c r="CG48" t="str">
-        <x:v>Evidence-backed — Endowing robots with tool design abilities is critical for enabling them to solve complex manipulation tasks that would otherwise be intractable.</x:v>
+        <x:v>一些复杂操作需要先设计或选择合适工具，机器人现有能力不足以直接完成。</x:v>
       </x:c>
       <x:c r="CH48" t="str">
-        <x:v>While recent generative frameworks can automatically synthesize task settings, such as 3D scenes and reward functions, they have not yet addressed the challenge of tool-use scenarios.</x:v>
+        <x:v>只靠视觉语言模型可能不了解真实物理约束；只检索现有工具也会限制任务覆盖。</x:v>
       </x:c>
       <x:c r="CI48" t="str">
-        <x:v>To address these limitations, we propose RobotSmith , an automated pipeline that leverages the implicit physical knowledge embedded in vision-language models (VLMs) alongside the more accurate physics provided by physics simulations to design and use tools for robotic manipulation.</x:v>
+        <x:v>RobotSmith 结合 VLM 中的物理常识和仿真提供的更精确物理反馈，自动设计并使用工具。</x:v>
       </x:c>
       <x:c r="CJ48" t="str"/>
       <x:c r="CK48" t="str">
-        <x:v>Notably, our approach achieves a 50.0% average success rate, significantly surpassing other baselines such as 3D generation (21.4%) and tool retrieval (11.1%).</x:v>
+        <x:v>论文报告平均成功率 50.0%，高于 3D 生成基线 21.4% 和工具检索基线 11.1%。</x:v>
       </x:c>
       <x:c r="CL48" t="str">
-        <x:v>Provides a concrete method or benchmark for the documented gap: While recent generative frameworks can automatically synthesize task settings, such as 3D scenes and reward functions, they have…</x:v>
+        <x:v>展示语言模型与物理仿真协同设计工具的可能性。</x:v>
       </x:c>
       <x:c r="CM48" t="str">
-        <x:v>Not established by the checked summary source; consult the full paper.</x:v>
+        <x:v>摘要未明确说明全部真机失败类型和工具制造约束。</x:v>
       </x:c>
       <x:c r="CN48" t="str"/>
       <x:c r="CO48" t="str">
-        <x:v>Medium — relevant to robot manipulation; transfer to dual-arm real hardware needs validation.</x:v>
+        <x:v>Medium：工具规划思路可借鉴，但本项目当前重点仍是双臂普通夹爪。</x:v>
       </x:c>
       <x:c r="CP48" t="str">
-        <x:v>Official abstract / paper page; https://arxiv.org/html/2506.14763; checked 2026-09-23. Rapid summary only; existing Evidence Quality is unchanged.</x:v>
+        <x:v>官方摘要/论文页; https://arxiv.org/html/2506.14763; 核验于 2026-09-23. 仅为摘要级速读；原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="CQ48" t="str">
         <x:v>Exact work identity verified</x:v>
@@ -40862,7 +40866,7 @@
         <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AX49" t="str">
-        <x:v>Robotic manipulation systems benefit from complementary sensing modalities, where each provides unique environmental information.</x:v>
+        <x:v>多种传感输入各有优势，如何保留点云中的局部几何信息。</x:v>
       </x:c>
       <x:c r="AY49" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -40871,7 +40875,7 @@
         <x:v>以 `3D Manipulation / Multimodal Policy` 为主要方法/能力线索；更细的结构和消融结论待正文核验。</x:v>
       </x:c>
       <x:c r="BA49" t="str">
-        <x:v>Not specified in checked abstract/card.</x:v>
+        <x:v>RoboCasa、CALVIN 与真机评测。</x:v>
       </x:c>
       <x:c r="BB49" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -40961,30 +40965,30 @@
       </x:c>
       <x:c r="CF49"/>
       <x:c r="CG49" t="str">
-        <x:v>Evidence-backed — Robotic manipulation systems benefit from complementary sensing modalities, where each provides unique environmental information.</x:v>
+        <x:v>多种传感输入各有优势，如何保留点云中的局部几何信息。</x:v>
       </x:c>
       <x:c r="CH49" t="str">
-        <x:v>Point clouds capture detailed geometric structure, while RGB images provide rich semantic context.</x:v>
+        <x:v>点云下采样可能丢掉接触附近的关键结构。</x:v>
       </x:c>
       <x:c r="CI49" t="str">
-        <x:v>We introduce PointMapPolicy, a novel approach that conditions diffusion policies on structured grids of points without downsampling.</x:v>
+        <x:v>PointMapPolicy 把结构化点网格作为扩散策略条件，减少对大幅下采样的依赖。</x:v>
       </x:c>
       <x:c r="CJ49" t="str"/>
       <x:c r="CK49" t="str">
-        <x:v>Through extensive experiments on the RoboCasa and CALVIN benchmarks and real robot evaluations, we demonstrate that our method achieves state-of-the-art performance across diverse manipulation tasks.</x:v>
+        <x:v>论文报告在上述 benchmark 和真机任务中取得较好表现；具体数值见正文。</x:v>
       </x:c>
       <x:c r="CL49" t="str">
-        <x:v>Provides a concrete method or benchmark for the documented gap: Point clouds capture detailed geometric structure, while RGB images provide rich semantic context.</x:v>
+        <x:v>有助于研究普通夹爪接触区域的三维表示。</x:v>
       </x:c>
       <x:c r="CM49" t="str">
-        <x:v>Not established by the checked summary source; consult the full paper.</x:v>
+        <x:v>高密度点数据会增加显存与在线计算成本。</x:v>
       </x:c>
       <x:c r="CN49" t="str"/>
       <x:c r="CO49" t="str">
-        <x:v>Medium — relevant to robot manipulation; transfer to dual-arm real hardware needs validation.</x:v>
+        <x:v>Medium：双臂空间定位相关，部署延迟需验证。</x:v>
       </x:c>
       <x:c r="CP49" t="str">
-        <x:v>Official abstract / paper page; https://proceedings.neurips.cc/paper_files/paper/2025/hash/eacc8ae341d15d2c13c02fef88189db3-Abstract-Conference.html; checked 2026-09-23. Rapid summary only; existing Evidence Quality is unchanged.</x:v>
+        <x:v>官方摘要/论文页; https://proceedings.neurips.cc/paper_files/paper/2025/hash/eacc8ae341d15d2c13c02fef88189db3-Abstract-Conference.html; 核验于 2026-09-23. 仅为摘要级速读；原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="CQ49" t="str">
         <x:v>Exact work identity verified</x:v>
@@ -41145,7 +41149,7 @@
         <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AX50" t="str">
-        <x:v>Vision-Language Models (VLMs) acquire real-world knowledge and general reasoning ability through Internet-scale image-text corpora.</x:v>
+        <x:v>互联网图文训练的 VLM 缺少机器人特定的视觉与操作知识。</x:v>
       </x:c>
       <x:c r="AY50" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -41154,7 +41158,7 @@
         <x:v>以 `Robot Data / Spatial Reasoning` 为主要方法/能力线索；更细的结构和消融结论待正文核验。</x:v>
       </x:c>
       <x:c r="BA50" t="str">
-        <x:v>Not specified in checked abstract/card.</x:v>
+        <x:v>已核验摘要未明确说明；需查阅论文方法与实验章节。</x:v>
       </x:c>
       <x:c r="BB50" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -41244,30 +41248,30 @@
       </x:c>
       <x:c r="CF50"/>
       <x:c r="CG50" t="str">
-        <x:v>Evidence-backed — Vision-Language Models (VLMs) acquire real-world knowledge and general reasoning ability through Internet-scale image-text corpora.</x:v>
+        <x:v>互联网图文训练的 VLM 缺少机器人特定的视觉与操作知识。</x:v>
       </x:c>
       <x:c r="CH50" t="str">
-        <x:v>Not established in checked summary source.</x:v>
+        <x:v>通用问答数据不一定包含机器人动作和物体可操作性。</x:v>
       </x:c>
       <x:c r="CI50" t="str">
-        <x:v>In this paper, we present Robo2VLM, a Visual Question Answering (VQA) dataset generation framework for VLMs.</x:v>
+        <x:v>Robo2VLM 构建机器人相关 VQA 数据，用于训练或评估 VLM 的具身理解。</x:v>
       </x:c>
       <x:c r="CJ50" t="str"/>
       <x:c r="CK50" t="str">
-        <x:v>Qualitative or numerical result not established by checked source.</x:v>
+        <x:v>已核验摘要未给可安全复述的统一量化结果。</x:v>
       </x:c>
       <x:c r="CL50" t="str">
-        <x:v>Medium — useful for method selection, data design and evaluation.</x:v>
+        <x:v>可辅助检查 VLA 的语言/视觉前端是否理解机器人场景。</x:v>
       </x:c>
       <x:c r="CM50" t="str">
-        <x:v>Not established by the checked summary source; consult the full paper.</x:v>
+        <x:v>VQA 指标不能直接代表可执行动作质量。</x:v>
       </x:c>
       <x:c r="CN50" t="str"/>
       <x:c r="CO50" t="str">
-        <x:v>Medium — useful for method selection, data design and evaluation.</x:v>
+        <x:v>Medium：问答能力与真机动作成功要分开评测。</x:v>
       </x:c>
       <x:c r="CP50" t="str">
-        <x:v>Official abstract / paper page; https://proceedings.neurips.cc/paper_files/paper/2025/hash/1f467c3e37abf9f86c78f44c6a27ee7c-Abstract-Datasets_and_Benchmarks_Track.html; checked 2026-09-23. Rapid summary only; existing Evidence Quality is unchanged.</x:v>
+        <x:v>官方摘要/论文页; https://proceedings.neurips.cc/paper_files/paper/2025/hash/1f467c3e37abf9f86c78f44c6a27ee7c-Abstract-Datasets_and_Benchmarks_Track.html; 核验于 2026-09-23. 仅为摘要级速读；原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="CQ50" t="str">
         <x:v>Exact work identity verified</x:v>
@@ -41428,7 +41432,7 @@
         <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AX51" t="str">
-        <x:v>Robotic task planning in real-world environments requires reasoning over implicit constraints from language and vision.</x:v>
+        <x:v>真实机器人规划要理解语言和视觉中没有明说的约束。</x:v>
       </x:c>
       <x:c r="AY51" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -41437,7 +41441,7 @@
         <x:v>以 `Task Planning / Demonstrations` 为主要方法/能力线索；更细的结构和消融结论待正文核验。</x:v>
       </x:c>
       <x:c r="BA51" t="str">
-        <x:v>Not specified in checked abstract/card.</x:v>
+        <x:v>已核验摘要未明确说明；需查阅论文方法与实验章节。</x:v>
       </x:c>
       <x:c r="BB51" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -41527,30 +41531,30 @@
       </x:c>
       <x:c r="CF51"/>
       <x:c r="CG51" t="str">
-        <x:v>Evidence-backed — Robotic task planning in real-world environments requires reasoning over implicit constraints from language and vision.</x:v>
+        <x:v>真实机器人规划要理解语言和视觉中没有明说的约束。</x:v>
       </x:c>
       <x:c r="CH51" t="str">
-        <x:v>While LLMs and VLMs offer strong priors, they struggle with long-horizon structure and symbolic grounding.</x:v>
+        <x:v>人工写 PDDL 领域规则成本高，面对未见任务又易遗漏条件。</x:v>
       </x:c>
       <x:c r="CI51" t="str">
-        <x:v>We propose UniDomain, a framework that pre-trains a PDDL domain from robot manipulation demonstrations and applies it for online robotic task planning.</x:v>
+        <x:v>UniDomain 从机器人示范中预训练 PDDL domain，再用于零样本任务规划。</x:v>
       </x:c>
       <x:c r="CJ51" t="str"/>
       <x:c r="CK51" t="str">
-        <x:v>Experiments on diverse real-world tasks show that UniDomain solves complex, unseen tasks in a zero-shot manner, achieving up to 58% higher task success and 160% improvement in plan optimality over state-of-the-art LLM and LLM-PDDL baselines.</x:v>
+        <x:v>作者报告在多项真实任务中解决未见复杂任务；具体成功率见论文。</x:v>
       </x:c>
       <x:c r="CL51" t="str">
-        <x:v>Provides a concrete method or benchmark for the documented gap: While LLMs and VLMs offer strong priors, they struggle with long-horizon structure and symbolic grounding.</x:v>
+        <x:v>为从示范自动获得可解释规划约束提供方法。</x:v>
       </x:c>
       <x:c r="CM51" t="str">
-        <x:v>Not established by the checked summary source; consult the full paper.</x:v>
+        <x:v>推断的规则若不准确，计划可能在真机接触时失败。</x:v>
       </x:c>
       <x:c r="CN51" t="str"/>
       <x:c r="CO51" t="str">
-        <x:v>Medium — relevant to robot manipulation; transfer to dual-arm real hardware needs validation.</x:v>
+        <x:v>Medium：可帮助双臂任务定义前提与执行检查。</x:v>
       </x:c>
       <x:c r="CP51" t="str">
-        <x:v>Official abstract / paper page; https://proceedings.neurips.cc/paper_files/paper/2025/hash/b8358a00e5b870194b974ddf8dd415c3-Abstract-Conference.html; checked 2026-09-23. Rapid summary only; existing Evidence Quality is unchanged.</x:v>
+        <x:v>官方摘要/论文页; https://proceedings.neurips.cc/paper_files/paper/2025/hash/b8358a00e5b870194b974ddf8dd415c3-Abstract-Conference.html; 核验于 2026-09-23. 仅为摘要级速读；原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="CQ51" t="str">
         <x:v>Exact work identity verified</x:v>
@@ -41711,7 +41715,7 @@
         <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AX52" t="str">
-        <x:v>Handover between a human and a dexterous robotic hand is a fundamental yet challenging task in human-robot collaboration.</x:v>
+        <x:v>人向灵巧手机器人递交物体时，动态抓取需要兼顾时机和接触稳定性。</x:v>
       </x:c>
       <x:c r="AY52" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -41720,7 +41724,7 @@
         <x:v>以 `Unknown` 为主要方法/能力线索；更细的结构和消融结论待正文核验。</x:v>
       </x:c>
       <x:c r="BA52" t="str">
-        <x:v>Not specified in checked abstract/card.</x:v>
+        <x:v>DexH2R 人机交接数据集；具体样本规模与指标需查正文。</x:v>
       </x:c>
       <x:c r="BB52" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -41810,30 +41814,30 @@
       </x:c>
       <x:c r="CF52"/>
       <x:c r="CG52" t="str">
-        <x:v>Evidence-backed — Handover between a human and a dexterous robotic hand is a fundamental yet challenging task in human-robot collaboration.</x:v>
+        <x:v>人向灵巧手机器人递交物体时，动态抓取需要兼顾时机和接触稳定性。</x:v>
       </x:c>
       <x:c r="CH52" t="str">
-        <x:v>However, progress in developing effective dynamic dexterous grasping methods is limited by the absence of high-quality, real-world human-to-robot handover datasets.</x:v>
+        <x:v>高质量真实人机交接数据不足，限制动态灵巧抓取方法评测。</x:v>
       </x:c>
       <x:c r="CI52" t="str">
-        <x:v>In this paper, we introduce DexH2R, a comprehensive real-world dataset for human-to-robot handovers, built on a dexterous robotic hand.</x:v>
+        <x:v>DexH2R 建立真实人向机器人交接数据集和评测基准，并给出任务解决方案。</x:v>
       </x:c>
       <x:c r="CJ52" t="str"/>
       <x:c r="CK52" t="str">
-        <x:v>We believe our benchmark will drive advancements in human-to-robot handover research by offering a high-quality dataset, effective solutions, and comprehensive evaluation metrics.</x:v>
+        <x:v>摘要描述数据、方法和评测贡献；本轮未确认可引用的量化性能。</x:v>
       </x:c>
       <x:c r="CL52" t="str">
-        <x:v>Provides a concrete method or benchmark for the documented gap: However, progress in developing effective dynamic dexterous grasping methods is limited by the absence of high-quality…</x:v>
+        <x:v>动态交接提供了感知、时序控制与接触安全的共同测试场景。</x:v>
       </x:c>
       <x:c r="CM52" t="str">
-        <x:v>Not established by the checked summary source; consult the full paper.</x:v>
+        <x:v>摘要不足以判定方法对普通夹爪的可迁移性。</x:v>
       </x:c>
       <x:c r="CN52" t="str"/>
       <x:c r="CO52" t="str">
-        <x:v>Medium — transferable learning ideas may apply, but the hand hardware differs from ordinary grippers.</x:v>
+        <x:v>Medium：时序与交接问题可借鉴，但灵巧手硬件不同于普通夹爪。</x:v>
       </x:c>
       <x:c r="CP52" t="str">
-        <x:v>Official abstract / paper page; https://openaccess.thecvf.com/content/ICCV2025/html/Wang_DexH2R_A_Benchmark_for_Dynamic_Dexterous_Grasping_in_Human-to-Robot_Handover_ICCV_2025_paper.html; checked 2026-09-23. Rapid summary only; existing Evidence Quality is unchanged.</x:v>
+        <x:v>官方摘要/论文页; https://openaccess.thecvf.com/content/ICCV2025/html/Wang_DexH2R_A_Benchmark_for_Dynamic_Dexterous_Grasping_in_Human-to-Robot_Handover_ICCV_2025_paper.html; 核验于 2026-09-23. 仅为摘要级速读；原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="CQ52" t="str">
         <x:v>Exact work identity verified</x:v>
@@ -41994,7 +41998,7 @@
         <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AX53" t="str">
-        <x:v>We present BimArt, a novel generative approach for synthesizing 3D bimanual hand interactions with articulated objects.</x:v>
+        <x:v>关节物体上的双手接触与运动具有多种合理方式，难以生成。</x:v>
       </x:c>
       <x:c r="AY53" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -42003,7 +42007,7 @@
         <x:v>以 `Unknown` 为主要方法/能力线索；更细的结构和消融结论待正文核验。</x:v>
       </x:c>
       <x:c r="BA53" t="str">
-        <x:v>3D bimanual hand-object interaction synthesis; quantitative motion-quality and diversity comparisons against prior motion generators.</x:v>
+        <x:v>关节物体双手交互数据；具体对象和指标见论文。</x:v>
       </x:c>
       <x:c r="BB53" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -42093,30 +42097,30 @@
       </x:c>
       <x:c r="CF53"/>
       <x:c r="CG53" t="str">
-        <x:v>Evidence-backed — We present BimArt, a novel generative approach for synthesizing 3D bimanual hand interactions with articulated objects.</x:v>
+        <x:v>关节物体上的双手接触与运动具有多种合理方式，难以生成。</x:v>
       </x:c>
       <x:c r="CH53" t="str">
-        <x:v>Unlike prior works, we do not rely on a reference grasp, a coarse hand trajectory, or separate modes for grasping and articulating.</x:v>
+        <x:v>只预测单个抓点不能表达物体关节运动和双手接触关系。</x:v>
       </x:c>
       <x:c r="CI53" t="str">
-        <x:v>We present BimArt, a novel generative approach for synthesizing 3D bimanual hand interactions with articulated objects.</x:v>
+        <x:v>BimArt 先根据物体轨迹生成接触距离图，再合成与关节结构一致的三维双手交互。</x:v>
       </x:c>
       <x:c r="CJ53" t="str"/>
       <x:c r="CK53" t="str">
-        <x:v>To achieve this, we first generate distance-based contact maps conditioned on the object trajectory with an articulation-aware feature representation, revealing rich bimanual patterns for manipulation.</x:v>
+        <x:v>摘要说明生成的接触图可以表达多样双手交互；本轮未核验统一量化结果。</x:v>
       </x:c>
       <x:c r="CL53" t="str">
-        <x:v>Provides a concrete method or benchmark for the documented gap: Unlike prior works, we do not rely on a reference grasp, a coarse hand trajectory, or separate modes for grasping and…</x:v>
+        <x:v>为双臂支撑—操作任务提供接触表示参考。</x:v>
       </x:c>
       <x:c r="CM53" t="str">
-        <x:v>Not established by the checked summary source; consult the full paper.</x:v>
+        <x:v>人手生成结果与真实机械臂碰撞、可达性之间的关系尚需检查。</x:v>
       </x:c>
       <x:c r="CN53" t="str"/>
       <x:c r="CO53" t="str">
-        <x:v>High — directly informs dual-arm coordination, data or ordinary-gripper policy design.</x:v>
+        <x:v>Medium：手部交互可借鉴，转换为普通夹爪动作仍需验证。</x:v>
       </x:c>
       <x:c r="CP53" t="str">
-        <x:v>Official abstract / paper page; https://arxiv.org/html/2412.05066; checked 2026-09-23. Rapid summary only; existing Evidence Quality is unchanged.</x:v>
+        <x:v>官方摘要/论文页; https://arxiv.org/html/2412.05066; 核验于 2026-09-23. 仅为摘要级速读；原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="CQ53" t="str">
         <x:v>Exact work identity verified</x:v>
@@ -42277,7 +42281,7 @@
         <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AX54" t="str">
-        <x:v>Large vision-language models have rarely been scaled for language-aligned dexterous grasping because high-quality dexterous pose data is difficult to collect.</x:v>
+        <x:v>高质量灵巧抓取位姿数据不足，语言与抓取动作难对齐。</x:v>
       </x:c>
       <x:c r="AY54" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -42286,7 +42290,7 @@
         <x:v>以 `Unknown` 为主要方法/能力线索；更细的结构和消融结论待正文核验。</x:v>
       </x:c>
       <x:c r="BA54" t="str">
-        <x:v>Training Dataset: DexGraspNet 3.0, 170M part-aligned grasp poses over 174k objects (Sec. 3.1, Table 1). - Evaluation Benchmark: LVIS-Seen, LVIS-Unseen, and SamPart3D part-aware…</x:v>
+        <x:v>LVIS-Seen、LVIS-Unseen、SamPart3D。</x:v>
       </x:c>
       <x:c r="BB54" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -42378,34 +42382,34 @@
       </x:c>
       <x:c r="CF54"/>
       <x:c r="CG54" t="str">
-        <x:v>Evidence-backed — Large vision-language models have rarely been scaled for language-aligned dexterous grasping because high-quality dexterous pose data is difficult to collect.</x:v>
+        <x:v>高质量灵巧抓取位姿数据不足，语言与抓取动作难对齐。</x:v>
       </x:c>
       <x:c r="CH54" t="str">
-        <x:v>Author-stated: prior large-model robotic work focuses mainly on simple grippers, leaving functional grasping with human-like dexterous hands underexplored.</x:v>
+        <x:v>大视觉语言模型缺少足够的三维接触监督。</x:v>
       </x:c>
       <x:c r="CI54" t="str">
-        <x:v>DexVLG uses single-view RGB-D, a point-cloud encoder and Florence-2 language model with a flow-matching pose head. The head predicts hand-base translation/rotation and finger joint angles conditioned on language and 3D features.</x:v>
+        <x:v>DexVLG 结合单视角 RGB-D、点云编码、Florence-2 与 Flow Matching 位姿头，预测语言条件抓取。</x:v>
       </x:c>
       <x:c r="CJ54" t="str">
         <x:v>Compared against DexGraspNet2.0 retrained on DexGraspNet3.0 (DGN2.0*) and DGN2.0* + CLIP. Metrics are simulation success (Suc), part-touch accuracy (PTA) and part-grasp accuracy (PGA).</x:v>
       </x:c>
       <x:c r="CK54" t="str">
-        <x:v>On LVIS-Seen, Unseen and SamPart3D, the reported Suc values are 87.7/79.1/76.3%; PGA values are 62.1/36.3/52.0%. The project reports over 76% zero-shot execution success and successful part-aligned real grasps.</x:v>
+        <x:v>卡片记录三个测试集的 Suc 为 87.7/79.1/76.3%；完整 PGA 指标和对比见原卡。</x:v>
       </x:c>
       <x:c r="CL54" t="str">
-        <x:v>Provides a concrete method or benchmark for the documented gap: Author-stated: prior large-model robotic work focuses mainly on simple grippers, leaving functional grasping with human-like…</x:v>
+        <x:v>连接视觉语言理解与三维抓取位姿生成。</x:v>
       </x:c>
       <x:c r="CM54" t="str">
-        <x:v>Evidence boundary: full failure taxonomy, checkpoint/data license and long-horizon manipulation beyond grasp execution require follow-up.</x:v>
+        <x:v>结果集中于桌面抓取，长任务与普通夹爪双臂迁移未证实。</x:v>
       </x:c>
       <x:c r="CN54" t="str">
         <x:v>Library Analysis: language-aligned dexterous grasp generation still needs validation for bimanual coordination and ordinary-gripper transfer.</x:v>
       </x:c>
       <x:c r="CO54" t="str">
-        <x:v>High — informs language-conditioned manipulation and VLA design.</x:v>
+        <x:v>Medium：Grounding 思路可迁移，手型动作头需替换。</x:v>
       </x:c>
       <x:c r="CP54" t="str">
-        <x:v>Official abstract / paper page; https://openaccess.thecvf.com/content/ICCV2025/html/He_DexVLG_Dexterous_Vision-Language-Grasp_Model_at_Scale_ICCV_2025_paper.html; checked 2026-09-23. Rapid summary only; existing Evidence Quality is unchanged.</x:v>
+        <x:v>官方摘要/论文页; https://openaccess.thecvf.com/content/ICCV2025/html/He_DexVLG_Dexterous_Vision-Language-Grasp_Model_at_Scale_ICCV_2025_paper.html; 核验于 2026-09-23. 仅为摘要级速读；原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="CQ54" t="str">
         <x:v>Exact work identity verified</x:v>
@@ -42566,7 +42570,7 @@
         <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AX55" t="str">
-        <x:v>Current research on generating 3D hand-object interaction motion primarily focuses on in-domain objects.</x:v>
+        <x:v>三维手—物交互生成对训练外新物体的泛化不足。</x:v>
       </x:c>
       <x:c r="AY55" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -42575,7 +42579,7 @@
         <x:v>以 `Unknown` 为主要方法/能力线索；更细的结构和消融结论待正文核验。</x:v>
       </x:c>
       <x:c r="BA55" t="str">
-        <x:v>Not specified in checked abstract/card.</x:v>
+        <x:v>已核验摘要未明确说明；需查阅论文方法与实验章节。</x:v>
       </x:c>
       <x:c r="BB55" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -42665,30 +42669,30 @@
       </x:c>
       <x:c r="CF55"/>
       <x:c r="CG55" t="str">
-        <x:v>Evidence-backed — Current research on generating 3D hand-object interaction motion primarily focuses on in-domain objects.</x:v>
+        <x:v>三维手—物交互生成对训练外新物体的泛化不足。</x:v>
       </x:c>
       <x:c r="CH55" t="str">
-        <x:v>Generalization to unseen objects is essential for practical applications, yet it remains both challenging and largely unexplored.In this paper, we propose LatentHOI, a novel approach designed to tackle the challenges of generalizing hand-object interaction to…</x:v>
+        <x:v>只在已见物体分布上建模，难适应未见几何。</x:v>
       </x:c>
       <x:c r="CI55" t="str">
-        <x:v>Generalization to unseen objects is essential for practical applications, yet it remains both challenging and largely unexplored.In this paper, we propose LatentHOI, a novel approach designed to tackle the challenges of generalizing hand-object interaction to unseen objects.Our main insight lies in decoupling high-level temporal motion from fine-grained…</x:v>
+        <x:v>LatentHOI 学习潜在手—物交互表示，生成未见物体上的单手抓取和双手运动。</x:v>
       </x:c>
       <x:c r="CJ55" t="str"/>
       <x:c r="CK55" t="str">
-        <x:v>We conducted extensive experiments in an unseen-object setting on both single-hand grasping and bi-manual motion datasets, including GRAB, DexYCB, and OakInk.Quantitative and qualitative evaluations demonstrate that our method significantly enhances the…</x:v>
+        <x:v>作者报告在未见物体设置的单手与双手数据集上评测；具体指标需查表格。</x:v>
       </x:c>
       <x:c r="CL55" t="str">
-        <x:v>Provides a concrete method or benchmark for the documented gap: Generalization to unseen objects is essential for practical applications, yet it remains both challenging and largely…</x:v>
+        <x:v>为跨物体泛化提供交互表示视角。</x:v>
       </x:c>
       <x:c r="CM55" t="str">
-        <x:v>Not established by the checked summary source; consult the full paper.</x:v>
+        <x:v>生成的人手运动还需转成机器人可达动作。</x:v>
       </x:c>
       <x:c r="CN55" t="str"/>
       <x:c r="CO55" t="str">
-        <x:v>High — directly informs dual-arm coordination, data or ordinary-gripper policy design.</x:v>
+        <x:v>Medium：双臂普通夹爪可借鉴物体中心表示。</x:v>
       </x:c>
       <x:c r="CP55" t="str">
-        <x:v>Official abstract / paper page; https://openaccess.thecvf.com/content/CVPR2025/html/Li_LatentHOI_On_the_Generalizable_Hand_Object_Motion_Generation_with_Latent_CVPR_2025_paper.html; checked 2026-09-23. Rapid summary only; existing Evidence Quality is unchanged.</x:v>
+        <x:v>官方摘要/论文页; https://openaccess.thecvf.com/content/CVPR2025/html/Li_LatentHOI_On_the_Generalizable_Hand_Object_Motion_Generation_with_Latent_CVPR_2025_paper.html; 核验于 2026-09-23. 仅为摘要级速读；原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="CQ55" t="str">
         <x:v>Exact work identity verified</x:v>
@@ -42849,7 +42853,7 @@
         <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AX56" t="str">
-        <x:v>Bimanual tool-action-object understanding lacks sufficiently varied annotated interaction data.</x:v>
+        <x:v>双手工具—动作—物体理解缺少足够多样且标注完整的数据。</x:v>
       </x:c>
       <x:c r="AY56" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -42858,7 +42862,7 @@
         <x:v>以 `Unknown` 为主要方法/能力线索；更细的结构和消融结论待正文核验。</x:v>
       </x:c>
       <x:c r="BA56" t="str">
-        <x:v>Not specified in checked abstract/card.</x:v>
+        <x:v>TACO：约 2500 条序列及三个基准任务。</x:v>
       </x:c>
       <x:c r="BB56" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -42948,30 +42952,30 @@
       </x:c>
       <x:c r="CF56"/>
       <x:c r="CG56" t="str">
-        <x:v>Evidence-backed — Bimanual tool-action-object understanding lacks sufficiently varied annotated interaction data.</x:v>
+        <x:v>双手工具—动作—物体理解缺少足够多样且标注完整的数据。</x:v>
       </x:c>
       <x:c r="CH56" t="str">
-        <x:v>Not established in checked summary source.</x:v>
+        <x:v>已有手—物交互数据多集中在单手、单物体场景。</x:v>
       </x:c>
       <x:c r="CI56" t="str">
-        <x:v>官方题名与元数据已确认；具体表述待补读官方摘要或正文。</x:v>
+        <x:v>TACO 提供约 2500 条双手交互序列、第三人称与第一人称视角、三维网格和动作标签。</x:v>
       </x:c>
       <x:c r="CJ56" t="str"/>
       <x:c r="CK56" t="str">
-        <x:v>Qualitative or numerical result not established by checked source.</x:v>
+        <x:v>CVPR 官方论文评测组合动作识别、手—物运动预测与协同抓取生成；摘要未给统一成功率。</x:v>
       </x:c>
       <x:c r="CL56" t="str">
-        <x:v>High — directly informs dual-arm coordination, data or ordinary-gripper policy design.</x:v>
+        <x:v>可用于理解双手协同与工具功能，但人手动作迁移到普通夹爪需验证。</x:v>
       </x:c>
       <x:c r="CM56" t="str">
-        <x:v>Not established by the checked summary source; consult the full paper.</x:v>
+        <x:v>本段基于官方摘要；未覆盖全文失败案例、完整 Baseline 与方法消融。</x:v>
       </x:c>
       <x:c r="CN56" t="str"/>
       <x:c r="CO56" t="str">
-        <x:v>High — directly informs dual-arm coordination, data or ordinary-gripper policy design.</x:v>
+        <x:v>Medium：方法可借鉴，但迁移到当前双臂硬件需验证。</x:v>
       </x:c>
       <x:c r="CP56" t="str">
-        <x:v>Official abstract / paper page; https://openaccess.thecvf.com/content/CVPR2024/papers/Liu_TACO_Benchmarking_Generalizable_Bimanual_Tool-ACtion-Object_Understanding_CVPR_2024_paper.pdf; checked 2026-09-23. Rapid summary only; existing Evidence Quality is unchanged.</x:v>
+        <x:v>官方摘要/论文页：https://openaccess.thecvf.com/content/CVPR2024/papers/Liu_TACO_Benchmarking_Generalizable_Bimanual_Tool-ACtion-Object_Understanding_CVPR_2024_paper.pdf；核验于 2026-09-23。仅为摘要级速读，原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="CQ56" t="str">
         <x:v>Unresolved</x:v>
@@ -43132,7 +43136,7 @@
         <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AX57" t="str">
-        <x:v>While there has been remarkable progress recently in the fields of manipulation and locomotion mobile manipulation remains a long-standing challenge.</x:v>
+        <x:v>移动操作既要行走/移动，又要持续感知并及时控制机械臂。</x:v>
       </x:c>
       <x:c r="AY57" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -43141,7 +43145,7 @@
         <x:v>以 `Unknown` 为主要方法/能力线索；更细的结构和消融结论待正文核验。</x:v>
       </x:c>
       <x:c r="BA57" t="str">
-        <x:v>Not specified in checked abstract/card.</x:v>
+        <x:v>移动操作任务；具体平台、数据集和评测协议需查原论文。</x:v>
       </x:c>
       <x:c r="BB57" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -43231,30 +43235,30 @@
       </x:c>
       <x:c r="CF57"/>
       <x:c r="CG57" t="str">
-        <x:v>Evidence-backed — While there has been remarkable progress recently in the fields of manipulation and locomotion mobile manipulation remains a long-standing challenge.</x:v>
+        <x:v>移动操作既要行走/移动，又要持续感知并及时控制机械臂。</x:v>
       </x:c>
       <x:c r="CH57" t="str">
-        <x:v>While the applications are broad and interesting there are a plethora of challenges in developing these systems such as coordination between the base and arm reliance on onboard perception for perceiving and interacting with the environment and most…</x:v>
+        <x:v>静态感知或开环策略难以应对移动过程中变化的场景。</x:v>
       </x:c>
       <x:c r="CI57" t="str">
-        <x:v>In this work we present a reactive mobile manipulation framework that uses an active visual system to consciously perceive and react to its environment.</x:v>
+        <x:v>SPIN 使用主动视觉系统建立反应式移动操作框架，让机器人持续观察环境并调整执行。</x:v>
       </x:c>
       <x:c r="CJ57" t="str"/>
       <x:c r="CK57" t="str">
-        <x:v>Qualitative or numerical result not established by checked source.</x:v>
+        <x:v>已核验摘要未给出可安全复述的统一量化结果。</x:v>
       </x:c>
       <x:c r="CL57" t="str">
-        <x:v>Provides a concrete method or benchmark for the documented gap: While the applications are broad and interesting there are a plethora of challenges in developing these systems such as…</x:v>
+        <x:v>提醒长时序真机任务必须将主动感知与动作闭环结合。</x:v>
       </x:c>
       <x:c r="CM57" t="str">
-        <x:v>Not established by the checked summary source; consult the full paper.</x:v>
+        <x:v>摘要没有明确列出失败案例；需进一步核对实验与限制。</x:v>
       </x:c>
       <x:c r="CN57" t="str"/>
       <x:c r="CO57" t="str">
-        <x:v>Medium — relevant to robot manipulation; transfer to dual-arm real hardware needs validation.</x:v>
+        <x:v>Medium：反应式感知思路相关，但移动平台与本项目固定双臂设置不同。</x:v>
       </x:c>
       <x:c r="CP57" t="str">
-        <x:v>Official abstract / paper page; https://openaccess.thecvf.com/content/CVPR2024/html/Uppal_SPIN_Simultaneous_Perception_Interaction_and_Navigation_CVPR_2024_paper.html; checked 2026-09-23. Rapid summary only; existing Evidence Quality is unchanged.</x:v>
+        <x:v>官方摘要/论文页; https://openaccess.thecvf.com/content/CVPR2024/html/Uppal_SPIN_Simultaneous_Perception_Interaction_and_Navigation_CVPR_2024_paper.html; 核验于 2026-09-23. 仅为摘要级速读；原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="CQ57" t="str">
         <x:v>Exact work identity verified</x:v>
@@ -43415,7 +43419,7 @@
         <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AX58" t="str">
-        <x:v>General language-conditioned bimanual manipulation requires expensive bimanual demonstrations and faces a high-dimensional action space.</x:v>
+        <x:v>语言条件双臂操作的示范成本高，动作空间也更复杂。</x:v>
       </x:c>
       <x:c r="AY58" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -43424,7 +43428,7 @@
         <x:v>以 `Unknown` 为主要方法/能力线索；更细的结构和消融结论待正文核验。</x:v>
       </x:c>
       <x:c r="BA58" t="str">
-        <x:v>Evaluation uses 12 simulated RLBench2 tasks and 9 real-world tasks. Training uses few bimanual demonstrations; exact count is not stated in the abstract evidence.</x:v>
+        <x:v>12 项仿真任务和 9 项真机任务。</x:v>
       </x:c>
       <x:c r="BB58" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -43516,34 +43520,34 @@
       </x:c>
       <x:c r="CF58"/>
       <x:c r="CG58" t="str">
-        <x:v>Evidence-backed — General language-conditioned bimanual manipulation requires expensive bimanual demonstrations and faces a high-dimensional action space.</x:v>
+        <x:v>语言条件双臂操作的示范成本高，动作空间也更复杂。</x:v>
       </x:c>
       <x:c r="CH58" t="str">
-        <x:v>Author-stated: fixed cooperation patterns and hand-designed atomic movements do not generalize across diverse bimanual tasks; unimanual policies contain reusable manipulation knowledge but observe a different workspace.</x:v>
+        <x:v>从单臂策略直接迁移到双臂时，两臂观测和动作不一定对齐。</x:v>
       </x:c>
       <x:c r="CI58" t="str">
-        <x:v>AnyBimanual is a model-agnostic plug-and-play transfer module. A skill manager schedules skill primitives with task-oriented compensation; a voxel/visual aligner creates spatial soft masks so each arm sees inputs aligned with unimanual pretraining.</x:v>
+        <x:v>用技能管理器安排双臂子技能，并以体素/视觉对齐模块协调两臂输入，使预训练单臂策略可复用。</x:v>
       </x:c>
       <x:c r="CJ58" t="str">
         <x:v>Compared with prior bimanual manipulation methods on RLBench2 and real-world tasks; the abstract reports superiority over previous methods without naming every baseline.</x:v>
       </x:c>
       <x:c r="CK58" t="str">
-        <x:v>12 simulated tasks: 12.67% success-rate improvement over previous methods. 9 real-world tasks: average success rate 84.62%.</x:v>
+        <x:v>卡片记录仿真成功率较先前方法提高 12.67%，真机任务平均成功率为 84.62%。</x:v>
       </x:c>
       <x:c r="CL58" t="str">
-        <x:v>Provides a concrete method or benchmark for the documented gap: Author-stated: fixed cooperation patterns and hand-designed atomic movements do not generalize across diverse bimanual tasks…</x:v>
+        <x:v>提供节约双臂数据成本的一条可测试路线。</x:v>
       </x:c>
       <x:c r="CM58" t="str">
-        <x:v>Author-stated / evidence boundary: few-shot transfer still depends on bimanual demonstrations and the transfer assumes reusable unimanual policy representations.</x:v>
+        <x:v>仍依赖少量双臂示范，且假设单臂预训练表示可以复用。</x:v>
       </x:c>
       <x:c r="CN58" t="str">
         <x:v>Library Analysis: transfer under substantially different grippers, camera layouts and contact-rich coordination remains an open validation target.</x:v>
       </x:c>
       <x:c r="CO58" t="str">
-        <x:v>High — directly informs dual-arm coordination, data or ordinary-gripper policy design.</x:v>
+        <x:v>High：直接针对从单臂到普通夹爪双臂任务的迁移。</x:v>
       </x:c>
       <x:c r="CP58" t="str">
-        <x:v>Official abstract / paper page; https://arxiv.org/html/2412.06779; checked 2026-09-23. Rapid summary only; existing Evidence Quality is unchanged.</x:v>
+        <x:v>官方摘要/论文页; https://arxiv.org/html/2412.06779; 核验于 2026-09-23. 仅为摘要级速读；原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="CQ58" t="str">
         <x:v>Exact work identity verified</x:v>
@@ -43704,7 +43708,7 @@
         <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AX59" t="str">
-        <x:v>Universal dexterous control is limited by expensive robot teleoperation data, heterogeneous hand embodiments and high-dimensional action spaces.</x:v>
+        <x:v>通用灵巧操作受昂贵遥操作数据、不同手型和高维动作影响。</x:v>
       </x:c>
       <x:c r="AY59" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -43713,7 +43717,7 @@
         <x:v>以 `Unknown` 为主要方法/能力线索；更细的结构和消融结论待正文核验。</x:v>
       </x:c>
       <x:c r="BA59" t="str">
-        <x:v>Training Dataset: UniDex-Dataset with 9M paired image–pointcloud–action frames, over 50K trajectories, eight hands, and 6–24 DoF (abstract and Sec. 3.1). - Evaluation Benchmark /…</x:v>
+        <x:v>已核验摘要未明确说明；需查阅论文方法与实验章节。</x:v>
       </x:c>
       <x:c r="BB59" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -43805,34 +43809,34 @@
       </x:c>
       <x:c r="CF59"/>
       <x:c r="CG59" t="str">
-        <x:v>Evidence-backed — Universal dexterous control is limited by expensive robot teleoperation data, heterogeneous hand embodiments and high-dimensional action spaces.</x:v>
+        <x:v>通用灵巧操作受昂贵遥操作数据、不同手型和高维动作影响。</x:v>
       </x:c>
       <x:c r="CH59" t="str">
-        <x:v>Author-stated: prior methods do not jointly solve cross-hand transfer, scalable human-video-to-robot data conversion and unified action parameterization.</x:v>
+        <x:v>人类视频中的动作不能直接变成各机器人手的控制命令。</x:v>
       </x:c>
       <x:c r="CI59" t="str">
-        <x:v>UniDex constructs robot-centric trajectories from egocentric human videos using human-in-the-loop retargeting and explicit 3D point clouds. FAAS maps functionally similar actuators to shared coordinates; UniDex-VLA is pretrained then fine-tuned with task demonstrations; UniDex-Cap captures synchronized RGB-D and hand poses.</x:v>
+        <x:v>UniDex 结合人类视频、人工参与的动作重定向和三维点云，形成机器人中心的训练轨迹。</x:v>
       </x:c>
       <x:c r="CJ59" t="str">
         <x:v>Official CVPR abstract reports outperforming prior VLA baselines by a large margin; exact baseline names and table metrics require full PDF extraction.</x:v>
       </x:c>
       <x:c r="CK59" t="str">
-        <x:v>UniDex-VLA achieves 81% average task progress on the reported tool-use tasks and shows spatial, object and zero-shot cross-hand generalization.</x:v>
+        <x:v>卡片记录 UniDex-VLA 在报告的工具使用任务中平均任务进度为 81%。</x:v>
       </x:c>
       <x:c r="CL59" t="str">
-        <x:v>Provides a concrete method or benchmark for the documented gap: Author-stated: prior methods do not jointly solve cross-hand transfer, scalable human-video-to-robot data conversion and unified…</x:v>
+        <x:v>展示如何把人类视频与机器人可执行轨迹连接起来。</x:v>
       </x:c>
       <x:c r="CM59" t="str">
-        <x:v>Evidence boundary: exact hand models, task-by-task scores, ablations and checkpoint/data license details require full PDF/repository inspection.</x:v>
+        <x:v>跨手型与零样本表现需按任务和平台逐项核验。</x:v>
       </x:c>
       <x:c r="CN59" t="str">
         <x:v>Library Analysis: transfer from dexterous-hand action spaces to ordinary parallel grippers remains untested by this card.</x:v>
       </x:c>
       <x:c r="CO59" t="str">
-        <x:v>High — informs language-conditioned manipulation and VLA design.</x:v>
+        <x:v>Medium：采集与重定向思路相关，但普通夹爪动作空间不同。</x:v>
       </x:c>
       <x:c r="CP59" t="str">
-        <x:v>Official abstract / paper page; https://openaccess.thecvf.com/content/CVPR2026/html/Zhang_UniDex_A_Robot_Foundation_Suite_for_Universal_Dexterous_Hand_Control_CVPR_2026_paper.html; checked 2026-09-23. Rapid summary only; existing Evidence Quality is unchanged.</x:v>
+        <x:v>官方摘要/论文页; https://openaccess.thecvf.com/content/CVPR2026/html/Zhang_UniDex_A_Robot_Foundation_Suite_for_Universal_Dexterous_Hand_Control_CVPR_2026_paper.html; 核验于 2026-09-23. 仅为摘要级速读；原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="CQ59" t="str">
         <x:v>Exact work identity verified</x:v>
@@ -43993,7 +43997,7 @@
         <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AX60" t="str">
-        <x:v>We address key limitations in existing datasets and models for task-oriented hand-object interaction video generation, a critical approach of generating video demonstrations for robotic imitation learning.</x:v>
+        <x:v>任务导向的人手—物体视频生成缺少足够数据和精准姿态。</x:v>
       </x:c>
       <x:c r="AY60" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -44002,7 +44006,7 @@
         <x:v>以 `Unknown` 为主要方法/能力线索；更细的结构和消融结论待正文核验。</x:v>
       </x:c>
       <x:c r="BA60" t="str">
-        <x:v>Not specified in checked abstract/card.</x:v>
+        <x:v>已核验摘要未明确说明；需查阅论文方法与实验章节。</x:v>
       </x:c>
       <x:c r="BB60" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -44092,30 +44096,30 @@
       </x:c>
       <x:c r="CF60"/>
       <x:c r="CG60" t="str">
-        <x:v>Evidence-backed — We address key limitations in existing datasets and models for task-oriented hand-object interaction video generation, a critical approach of generating video demonstrations for robotic imitation learning.</x:v>
+        <x:v>任务导向的人手—物体视频生成缺少足够数据和精准姿态。</x:v>
       </x:c>
       <x:c r="CH60" t="str">
-        <x:v>Not established in checked summary source.</x:v>
+        <x:v>普通生成视频不一定保留与机器人操作有关的接触和动作结构。</x:v>
       </x:c>
       <x:c r="CI60" t="str">
-        <x:v>Towards this end, we introduce TASTE-Rob -- a pioneering large-scale dataset of 100,856 ego-centric hand-object interaction videos.</x:v>
+        <x:v>TASTE-Rob 建立约 100,856 条第一人称手—物交互数据，并加入姿态细化以生成任务相关视频。</x:v>
       </x:c>
       <x:c r="CJ60" t="str"/>
       <x:c r="CK60" t="str">
-        <x:v>Our curated dataset, coupled with the specialized pose-refinement framework, provides notable performance gains in generating high-quality, task-oriented hand-object interaction videos, resulting in achieving superior generalizable robotic manipulation.</x:v>
+        <x:v>作者报告数据与姿态细化带来生成质量提升；具体指标见论文。</x:v>
       </x:c>
       <x:c r="CL60" t="str">
-        <x:v>Medium — relevant to robot manipulation; transfer to dual-arm real hardware needs validation.</x:v>
+        <x:v>可作为从人类视频提取操作结构的数据来源。</x:v>
       </x:c>
       <x:c r="CM60" t="str">
-        <x:v>Not established by the checked summary source; consult the full paper.</x:v>
+        <x:v>视频生成质量不能直接代表真机操作成功。</x:v>
       </x:c>
       <x:c r="CN60" t="str"/>
       <x:c r="CO60" t="str">
-        <x:v>Medium — relevant to robot manipulation; transfer to dual-arm real hardware needs validation.</x:v>
+        <x:v>Medium：人手动作转双普通夹爪仍需重定向。</x:v>
       </x:c>
       <x:c r="CP60" t="str">
-        <x:v>Official abstract / paper page; https://openaccess.thecvf.com/content/CVPR2025/html/Zhao_TASTE-Rob_Advancing_Video_Generation_of_Task-Oriented_Hand-Object_Interaction_for_Generalizable_CVPR_2025_paper.html; checked 2026-09-23. Rapid summary only; existing Evidence Quality is unchanged.</x:v>
+        <x:v>官方摘要/论文页; https://openaccess.thecvf.com/content/CVPR2025/html/Zhao_TASTE-Rob_Advancing_Video_Generation_of_Task-Oriented_Hand-Object_Interaction_for_Generalizable_CVPR_2025_paper.html; 核验于 2026-09-23. 仅为摘要级速读；原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="CQ60" t="str">
         <x:v>Unresolved</x:v>
@@ -44276,7 +44280,7 @@
         <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AX61" t="str">
-        <x:v>The inherent difficulty and limited scalability of collecting manipulation data using multi-fingered robot hand hardware platforms have resulted in severe data scarcity, impeding research on data-driven dexterous manipulation policy learning.</x:v>
+        <x:v>多指机器人手的数据采集昂贵，跨手型迁移难。</x:v>
       </x:c>
       <x:c r="AY61" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -44285,7 +44289,7 @@
         <x:v>以 `Unknown` 为主要方法/能力线索；更细的结构和消融结论待正文核验。</x:v>
       </x:c>
       <x:c r="BA61" t="str">
-        <x:v>Not specified in checked abstract/card.</x:v>
+        <x:v>已核验摘要未明确说明；需查阅论文方法与实验章节。</x:v>
       </x:c>
       <x:c r="BB61" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -44375,30 +44379,30 @@
       </x:c>
       <x:c r="CF61"/>
       <x:c r="CG61" t="str">
-        <x:v>Evidence-backed — The inherent difficulty and limited scalability of collecting manipulation data using multi-fingered robot hand hardware platforms have resulted in severe data scarcity, impeding research on data-driven dexterous manipulation policy learning.</x:v>
+        <x:v>多指机器人手的数据采集昂贵，跨手型迁移难。</x:v>
       </x:c>
       <x:c r="CH61" t="str">
-        <x:v>To address this challenge, we present a hand-agnostic manipulation transfer system.</x:v>
+        <x:v>运动学与动力学差异使直接重定向的动作不平滑或不可执行。</x:v>
       </x:c>
       <x:c r="CI61" t="str">
-        <x:v>官方题名与元数据已确认；具体表述待补读官方摘要或正文。</x:v>
+        <x:v>逐步对齐运动学和动力学，再把操作行为迁移到目标灵巧手；模块细节仍需查官方正文。</x:v>
       </x:c>
       <x:c r="CJ61" t="str"/>
       <x:c r="CK61" t="str">
-        <x:v>Extensive experimental results demonstrate that our framework can automatically generate smooth and semantically correct dexterous hand manipulation that faithfully reproduces human intentions, achieving high efficiency and strong generalizability with an…</x:v>
+        <x:v>作者报告生成的动作更平滑且语义正确；未核验统一数值。</x:v>
       </x:c>
       <x:c r="CL61" t="str">
-        <x:v>Provides a concrete method or benchmark for the documented gap: To address this challenge, we present a hand-agnostic manipulation transfer system.</x:v>
+        <x:v>提示本项目从单臂模型迁移双臂时也要检查物理可执行性。</x:v>
       </x:c>
       <x:c r="CM61" t="str">
-        <x:v>Not established by the checked summary source; consult the full paper.</x:v>
+        <x:v>原卡方法细节尚有占位，不能据此宣称已复现。</x:v>
       </x:c>
       <x:c r="CN61" t="str"/>
       <x:c r="CO61" t="str">
-        <x:v>Medium — transferable learning ideas may apply, but the hand hardware differs from ordinary grippers.</x:v>
+        <x:v>Medium：对齐思想可借鉴，目标硬件不同。</x:v>
       </x:c>
       <x:c r="CP61" t="str">
-        <x:v>OpenAlex indexed abstract; https://api.openalex.org/works/W7138113519; checked 2026-09-23. Rapid summary only; existing Evidence Quality is unchanged.</x:v>
+        <x:v>OpenAlex 索引摘要; https://api.openalex.org/works/W7138113519; 核验于 2026-09-23. 仅为摘要级速读；原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="CQ61" t="str">
         <x:v>Exact work identity verified</x:v>
@@ -44559,7 +44563,7 @@
         <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AX62" t="str">
-        <x:v>For robotic manipulation, existing robotics datasets and simulation benchmarks predominantly cater to robot-arm platforms.</x:v>
+        <x:v>许多机器人操作数据和仿真 benchmark 偏机械臂，缺少人形机器人操作数据。</x:v>
       </x:c>
       <x:c r="AY62" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -44568,7 +44572,7 @@
         <x:v>以 `Unknown` 为主要方法/能力线索；更细的结构和消融结论待正文核验。</x:v>
       </x:c>
       <x:c r="BA62" t="str">
-        <x:v>Not specified in checked abstract/card.</x:v>
+        <x:v>生成的人形操作数据；具体任务与数据规模见论文。</x:v>
       </x:c>
       <x:c r="BB62" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -44658,30 +44662,30 @@
       </x:c>
       <x:c r="CF62"/>
       <x:c r="CG62" t="str">
-        <x:v>Evidence-backed — For robotic manipulation, existing robotics datasets and simulation benchmarks predominantly cater to robot-arm platforms.</x:v>
+        <x:v>许多机器人操作数据和仿真 benchmark 偏机械臂，缺少人形机器人操作数据。</x:v>
       </x:c>
       <x:c r="CH62" t="str">
-        <x:v>However, for humanoid robots equipped with dual arms and dexterous hands, simulation tasks and high-quality demonstrations are notably lacking.</x:v>
+        <x:v>数据本体分布不足会限制策略对人形平台的适配。</x:v>
       </x:c>
       <x:c r="CI62" t="str">
-        <x:v>For robotic manipulation, existing robotics datasets and simulation benchmarks predominantly cater to robot-arm platforms.</x:v>
+        <x:v>HumanoidGen 扩展人形机器人操作数据，用生成数据训练和评估 2D/3D Diffusion Policy。</x:v>
       </x:c>
       <x:c r="CJ62" t="str"/>
       <x:c r="CK62" t="str">
-        <x:v>The results show that the performance of the 2D and 3D diffusion policies can scale with the generated dataset.</x:v>
+        <x:v>摘要报告 2D 与 3D 扩散策略表现会随生成数据增加而提升；未核验统一成功率。</x:v>
       </x:c>
       <x:c r="CL62" t="str">
-        <x:v>Provides a concrete method or benchmark for the documented gap: However, for humanoid robots equipped with dual arms and dexterous hands, simulation tasks and high-quality demonstrations are…</x:v>
+        <x:v>提醒跨本体数据设计比单纯增加示范数量更重要。</x:v>
       </x:c>
       <x:c r="CM62" t="str">
-        <x:v>Not established by the checked summary source; consult the full paper.</x:v>
+        <x:v>仿真生成数据到普通夹爪真机的迁移需另行验证。</x:v>
       </x:c>
       <x:c r="CN62" t="str"/>
       <x:c r="CO62" t="str">
-        <x:v>High — directly informs dual-arm coordination, data or ordinary-gripper policy design.</x:v>
+        <x:v>Medium：本项目不是人形手，但双臂数据覆盖问题相通。</x:v>
       </x:c>
       <x:c r="CP62" t="str">
-        <x:v>Official abstract / paper page; https://proceedings.neurips.cc/paper_files/paper/2025/hash/e4ef7454447baa15a424314e6284441b-Abstract-Conference.html; checked 2026-09-23. Rapid summary only; existing Evidence Quality is unchanged.</x:v>
+        <x:v>官方摘要/论文页; https://proceedings.neurips.cc/paper_files/paper/2025/hash/e4ef7454447baa15a424314e6284441b-Abstract-Conference.html; 核验于 2026-09-23. 仅为摘要级速读；原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="CQ62" t="str">
         <x:v>Exact work identity verified</x:v>
@@ -44842,7 +44846,7 @@
         <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AX63" t="str">
-        <x:v>A dexterous hand capable of generalizable grasping objects is fundamental for the development of general-purpose embodied AI.</x:v>
+        <x:v>灵巧手要在未见物体上抓取，还需要理解物体可供性。</x:v>
       </x:c>
       <x:c r="AY63" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -44851,7 +44855,7 @@
         <x:v>以 `Unknown` 为主要方法/能力线索；更细的结构和消融结论待正文核验。</x:v>
       </x:c>
       <x:c r="BA63" t="str">
-        <x:v>Not specified in checked abstract/card.</x:v>
+        <x:v>已核验摘要未明确说明；需查阅论文方法与实验章节。</x:v>
       </x:c>
       <x:c r="BB63" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -44941,30 +44945,30 @@
       </x:c>
       <x:c r="CF63"/>
       <x:c r="CG63" t="str">
-        <x:v>Evidence-backed — A dexterous hand capable of generalizable grasping objects is fundamental for the development of general-purpose embodied AI.</x:v>
+        <x:v>灵巧手要在未见物体上抓取，还需要理解物体可供性。</x:v>
       </x:c>
       <x:c r="CH63" t="str">
-        <x:v>However, previous methods focus narrowly on low-level grasp stability metrics, neglecting affordance-aware positioning and human-like poses which are crucial for downstream manipulation.</x:v>
+        <x:v>只利用几何抓取先验可能忽略人类使用物体的方式。</x:v>
       </x:c>
       <x:c r="CI63" t="str">
-        <x:v>官方题名与元数据已确认；具体表述待补读官方摘要或正文。</x:v>
+        <x:v>AffordDex 引入人类式先验与 affordance，学习可泛化的灵巧抓取。具体模块需核对正文。</x:v>
       </x:c>
       <x:c r="CJ63" t="str"/>
       <x:c r="CK63" t="str">
-        <x:v>As a result, AffordDex significantly outperforms state-of-the-art baselines across seen objects, unseen instances, and even entirely novel categories.</x:v>
+        <x:v>作者报告在已见物体、未见实例和未见类别上优于基线；统一数字未核验。</x:v>
       </x:c>
       <x:c r="CL63" t="str">
-        <x:v>Provides a concrete method or benchmark for the documented gap: However, previous methods focus narrowly on low-level grasp stability metrics, neglecting affordance-aware positioning and…</x:v>
+        <x:v>强调抓取的用途和接触位置比单纯抓住更重要。</x:v>
       </x:c>
       <x:c r="CM63" t="str">
-        <x:v>Not established by the checked summary source; consult the full paper.</x:v>
+        <x:v>原卡方法细节尚有占位；真实双臂夹爪转移需验证。</x:v>
       </x:c>
       <x:c r="CN63" t="str"/>
       <x:c r="CO63" t="str">
-        <x:v>Medium — transferable learning ideas may apply, but the hand hardware differs from ordinary grippers.</x:v>
+        <x:v>Medium：普通夹爪也需任务相关抓取，但手型不同。</x:v>
       </x:c>
       <x:c r="CP63" t="str">
-        <x:v>OpenAlex indexed abstract; https://api.openalex.org/works/W7138302344; checked 2026-09-23. Rapid summary only; existing Evidence Quality is unchanged.</x:v>
+        <x:v>OpenAlex 索引摘要; https://api.openalex.org/works/W7138302344; 核验于 2026-09-23. 仅为摘要级速读；原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="CQ63" t="str">
         <x:v>Exact work identity verified</x:v>
@@ -45125,7 +45129,7 @@
         <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AX64" t="str">
-        <x:v>Bimanual dexterous manipulation is a critical yet underexplored area in robotics.</x:v>
+        <x:v>从人类示范学习多样双手灵巧技能具有本体差异和数据成本。</x:v>
       </x:c>
       <x:c r="AY64" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -45134,7 +45138,7 @@
         <x:v>以 `Unknown` 为主要方法/能力线索；更细的结构和消融结论待正文核验。</x:v>
       </x:c>
       <x:c r="BA64" t="str">
-        <x:v>Not specified in checked abstract/card.</x:v>
+        <x:v>ARCTIC 协同任务与论文训练任务。</x:v>
       </x:c>
       <x:c r="BB64" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -45224,30 +45228,30 @@
       </x:c>
       <x:c r="CF64"/>
       <x:c r="CG64" t="str">
-        <x:v>Evidence-backed — Bimanual dexterous manipulation is a critical yet underexplored area in robotics.</x:v>
+        <x:v>从人类示范学习多样双手灵巧技能具有本体差异和数据成本。</x:v>
       </x:c>
       <x:c r="CH64" t="str">
-        <x:v>Its high-dimensional action space and inherent task complexity present significant challenges for policy learning, and the limited task diversity in existing benchmarks hinders general-purpose skill development.</x:v>
+        <x:v>只模仿固定动作难以覆盖未见物体与协同方式。</x:v>
       </x:c>
       <x:c r="CI64" t="str">
-        <x:v>官方题名与元数据已确认；具体表述待补读官方摘要或正文。</x:v>
+        <x:v>BiDexHD 从人类双手示范提取可迁移技能并学习双手灵巧操作。具体模块需回正文核验。</x:v>
       </x:c>
       <x:c r="CJ64" t="str"/>
       <x:c r="CK64" t="str">
-        <x:v>We further transfer BiDexHD to 11 ARCTIC collaborative tasks and achieve an average of 80.49% task fulfillment rate on trained tasks and 65.99% on unseen task.</x:v>
+        <x:v>卡片记录迁移到 11 项 ARCTIC 任务：已训练任务平均完成率 80.49%，未见任务 65.99%。</x:v>
       </x:c>
       <x:c r="CL64" t="str">
-        <x:v>Provides a concrete method or benchmark for the documented gap: Its high-dimensional action space and inherent task complexity present significant challenges for policy learning, and the…</x:v>
+        <x:v>说明人类双手数据可为双臂策略提供技能先验。</x:v>
       </x:c>
       <x:c r="CM64" t="str">
-        <x:v>Not established by the checked summary source; consult the full paper.</x:v>
+        <x:v>原卡方法细节尚有占位，需核对官方论文与失败案例。</x:v>
       </x:c>
       <x:c r="CN64" t="str"/>
       <x:c r="CO64" t="str">
-        <x:v>High — directly informs dual-arm coordination, data or ordinary-gripper policy design.</x:v>
+        <x:v>Medium：灵巧手与普通夹爪之间的动作转译需研究。</x:v>
       </x:c>
       <x:c r="CP64" t="str">
-        <x:v>OpenAlex indexed abstract; https://api.openalex.org/works/W7138037195; checked 2026-09-23. Rapid summary only; existing Evidence Quality is unchanged.</x:v>
+        <x:v>OpenAlex 索引摘要; https://api.openalex.org/works/W7138037195; 核验于 2026-09-23. 仅为摘要级速读；原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="CQ64" t="str">
         <x:v>Exact work identity verified</x:v>
@@ -45408,7 +45412,7 @@
         <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AX65" t="str">
-        <x:v>Learning to forecast bimanual object manipulation sequences from unimanual observations has broad applications in assistive robots and augmented reality.</x:v>
+        <x:v>只观察单手交互时，预测完整双手物体操作序列并不容易。</x:v>
       </x:c>
       <x:c r="AY65" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -45417,7 +45421,7 @@
         <x:v>以 `Unknown` 为主要方法/能力线索；更细的结构和消融结论待正文核验。</x:v>
       </x:c>
       <x:c r="BA65" t="str">
-        <x:v>Not specified in checked abstract/card.</x:v>
+        <x:v>论文的双手操作序列数据集；具体设置需核对官方正文。</x:v>
       </x:c>
       <x:c r="BB65" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -45507,30 +45511,30 @@
       </x:c>
       <x:c r="CF65"/>
       <x:c r="CG65" t="str">
-        <x:v>Evidence-backed — Learning to forecast bimanual object manipulation sequences from unimanual observations has broad applications in assistive robots and augmented reality.</x:v>
+        <x:v>只观察单手交互时，预测完整双手物体操作序列并不容易。</x:v>
       </x:c>
       <x:c r="CH65" t="str">
-        <x:v>This challenging task requires us to first infer motion from the missing arm and the object it would have been manipulating were the person bimanual, then forecast the human and object motion while maintaining hand-object contact during manipulation.</x:v>
+        <x:v>单手观测没有直接提供另一只手的未来接触与运动。</x:v>
       </x:c>
       <x:c r="CI65" t="str">
-        <x:v>官方题名与元数据已确认；具体表述待补读官方摘要或正文。</x:v>
+        <x:v>从单手观测推断物体与双手的后续运动，形成双手操作序列预测。</x:v>
       </x:c>
       <x:c r="CJ65" t="str"/>
       <x:c r="CK65" t="str">
-        <x:v>Our approach outperforms the state-of-the-art pose forecasting methods on bimanual manipulation datasets.</x:v>
+        <x:v>作者摘要报告优于所比较的位姿预测方法；未核验统一数字。</x:v>
       </x:c>
       <x:c r="CL65" t="str">
-        <x:v>Provides a concrete method or benchmark for the documented gap: This challenging task requires us to first infer motion from the missing arm and the object it would have been manipulating were…</x:v>
+        <x:v>为从单手数据推断双臂任务结构提供可能的监督信号。</x:v>
       </x:c>
       <x:c r="CM65" t="str">
-        <x:v>Not established by the checked summary source; consult the full paper.</x:v>
+        <x:v>卡片原先的方法细节占位，需回官方论文核对预测结构与失败案例。</x:v>
       </x:c>
       <x:c r="CN65" t="str"/>
       <x:c r="CO65" t="str">
-        <x:v>High — directly informs dual-arm coordination, data or ordinary-gripper policy design.</x:v>
+        <x:v>Medium：人体动作到普通夹爪仍有本体差异。</x:v>
       </x:c>
       <x:c r="CP65" t="str">
-        <x:v>OpenAlex indexed abstract; https://api.openalex.org/works/W4393158202; checked 2026-09-23. Rapid summary only; existing Evidence Quality is unchanged.</x:v>
+        <x:v>OpenAlex 索引摘要; https://api.openalex.org/works/W4393158202; 核验于 2026-09-23. 仅为摘要级速读；原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="CQ65" t="str">
         <x:v>Exact work identity verified</x:v>
@@ -45691,7 +45695,7 @@
         <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AX66" t="str">
-        <x:v>Human videos contain rich bimanual interactions but generic affordance labels often lack precise, actionable regions for left/right/both-hand interaction.</x:v>
+        <x:v>人类视频包含丰富双手交互，但普通 affordance 标签难指出左右手各自可操作的区域。</x:v>
       </x:c>
       <x:c r="AY66" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -45700,7 +45704,7 @@
         <x:v>以 `Unknown` 为主要方法/能力线索；更细的结构和消融结论待正文核验。</x:v>
       </x:c>
       <x:c r="BA66" t="str">
-        <x:v>Training Dataset: 2HANDS, 278K images with affordance masks and narration-derived labels. - Evaluation Benchmark: ActAffordance and its modified version; Table 2 compares…</x:v>
+        <x:v>ActAffordance 等双手 affordance 评测；具体分数见官方 PDF。</x:v>
       </x:c>
       <x:c r="BB66" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -45792,34 +45796,34 @@
       </x:c>
       <x:c r="CF66"/>
       <x:c r="CG66" t="str">
-        <x:v>Evidence-backed — Human videos contain rich bimanual interactions but generic affordance labels often lack precise, actionable regions for left/right/both-hand interaction.</x:v>
+        <x:v>人类视频包含丰富双手交互，但普通 affordance 标签难指出左右手各自可操作的区域。</x:v>
       </x:c>
       <x:c r="CH66" t="str">
-        <x:v>Author-stated: object-part labels do not necessarily identify the precise interaction region, and affordance prediction is multi-modal.</x:v>
+        <x:v>只标记物体可抓取，不足以指导双手分工和具体接触位置。</x:v>
       </x:c>
       <x:c r="CI66" t="str">
-        <x:v>A VLM emits a [SEG] token consumed by left/right SAM-based mask decoders and a hand-taxonomy classifier; LoRA adapts a LLaVA-13B while freezing the image encoder and most VLM parameters. A CLIP-based alternative is also trained.</x:v>
+        <x:v>用 VLM 产生分割提示，再由左右手 mask 解码器预测可执行区域，并分类单手或双手交互。</x:v>
       </x:c>
       <x:c r="CJ66" t="str">
         <x:v>VLM-based model compared with 2HandedAfforder-CLIP; exact additional baselines and table values require full PDF extraction.</x:v>
       </x:c>
       <x:c r="CK66" t="str">
-        <x:v>The accessible official PDF evidence confirms ActAffordance and actionable-affordance evaluation; exact numerical scores were not re-extracted.</x:v>
+        <x:v>已访问的官方 PDF 支持方法与评测设置；快速摘要暂不填入未重新提取的数值。</x:v>
       </x:c>
       <x:c r="CL66" t="str">
-        <x:v>Provides a concrete method or benchmark for the documented gap: Author-stated: object-part labels do not necessarily identify the precise interaction region, and affordance prediction is…</x:v>
+        <x:v>直接关系到普通夹爪在同一物体上的双臂接触分工。</x:v>
       </x:c>
       <x:c r="CM66" t="str">
-        <x:v>Evidence boundary: real-robot transfer results and exact metrics require full PDF and supplementary extraction.</x:v>
+        <x:v>精确数值与失败图例仍需对照论文图表；人手区域到普通夹爪的迁移需验证。</x:v>
       </x:c>
       <x:c r="CN66" t="str">
         <x:v>Library Analysis: converting human-video affordance masks into robust closed-loop dual-arm gripper actions remains open.</x:v>
       </x:c>
       <x:c r="CO66" t="str">
-        <x:v>High — directly informs dual-arm coordination, data or ordinary-gripper policy design.</x:v>
+        <x:v>High：可用于双臂 joint affordance 和动作前检查。</x:v>
       </x:c>
       <x:c r="CP66" t="str">
-        <x:v>Official abstract / paper page; https://openaccess.thecvf.com/content/ICCV2025/html/Heidinger_2HandedAfforder_Learning_Precise_Actionable_Bimanual_Affordances_from_Human_Videos_ICCV_2025_paper.html; checked 2026-09-23. Rapid summary only; existing Evidence Quality is unchanged.</x:v>
+        <x:v>官方摘要/论文页; https://openaccess.thecvf.com/content/ICCV2025/html/Heidinger_2HandedAfforder_Learning_Precise_Actionable_Bimanual_Affordances_from_Human_Videos_ICCV_2025_paper.html; 核验于 2026-09-23. 仅为摘要级速读；原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="CQ66" t="str">
         <x:v>Exact work identity verified</x:v>
@@ -45980,7 +45984,7 @@
         <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AX67" t="str">
-        <x:v>Current VLAs may spread visual attention across irrelevant regions instead of the task target, weakening precise manipulation and generalization.</x:v>
+        <x:v>VLA 的视觉注意可能落在任务无关区域，削弱精细操作与泛化。</x:v>
       </x:c>
       <x:c r="AY67" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -45989,7 +45993,7 @@
         <x:v>模型从 VLA 的视觉输出生成重建条件，由轻量 diffusion transformer 从噪声重建对应目标操作对象的 ga</x:v>
       </x:c>
       <x:c r="BA67" t="str">
-        <x:v>Training Dataset: BridgeData V2, LIBERO, and CALVIN-derived open robotic data (Sec. 3.4); the constructed pretraining corpus contains over 100k trajectories and 2M samples…</x:v>
+        <x:v>卡片记录 BridgeData V2、LIBERO、CALVIN 相关数据和评测；具体分工与规模见论文 Sec. 3.4。</x:v>
       </x:c>
       <x:c r="BB67" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -46081,34 +46085,34 @@
       </x:c>
       <x:c r="CF67"/>
       <x:c r="CG67" t="str">
-        <x:v>Evidence-backed — Current VLAs may spread visual attention across irrelevant regions instead of the task target, weakening precise manipulation and generalization.</x:v>
+        <x:v>VLA 的视觉注意可能落在任务无关区域，削弱精细操作与泛化。</x:v>
       </x:c>
       <x:c r="CH67" t="str">
-        <x:v>Author-stated: existing VLAs struggle to allocate visual attention to target regions; ReconVLA addresses this with implicit grounding rather than requiring explicit grounding inputs.</x:v>
+        <x:v>原有 VLA 难以稳定把视觉注意对准目标区域；显式标注 Grounding 的方案又可能增加数据要求。</x:v>
       </x:c>
       <x:c r="CI67" t="str">
-        <x:v>A diffusion transformer reconstructs the gaze region of the manipulated object conditioned on the VLA visual outputs, jointly encouraging task-specific visual representations while preserving action prediction.</x:v>
+        <x:v>ReconVLA 用扩散式重建目标注视区域，促使视觉表示聚焦被操作物体，同时保留动作预测。</x:v>
       </x:c>
       <x:c r="CJ67" t="str">
         <x:v>Official abstract confirms comparison of implicit grounding against alternative grounding paradigms; exact named baselines and metric table require full PDF extraction.</x:v>
       </x:c>
       <x:c r="CK67" t="str">
-        <x:v>Official AAAI abstract reports improved precise manipulation and generalization, but no numeric result is entered without table-level extraction.</x:v>
+        <x:v>AAAI 官方摘要报告操作精度和泛化改善；快速摘要不添加尚未核对表格的数值。</x:v>
       </x:c>
       <x:c r="CL67" t="str">
-        <x:v>Provides a concrete method or benchmark for the documented gap: Author-stated: existing VLAs struggle to allocate visual attention to target regions; ReconVLA addresses this with implicit…</x:v>
+        <x:v>直接对应本项目的目标 Grounding 与动作前目标核验。</x:v>
       </x:c>
       <x:c r="CM67" t="str">
-        <x:v>Author-stated: performance depends on reconstructing the correct target region and the reported evaluation is concentrated on CALVIN plus a limited real-world suite (Sec. 4.6 and conclusion). - Library Analysis: broader…</x:v>
+        <x:v>作者指出性能取决于目标区域重建是否正确；公开评测主要集中在 CALVIN 与有限真机任务。跨本体和新相机条件仍需验证。</x:v>
       </x:c>
       <x:c r="CN67" t="str">
         <x:v>Library Analysis: calibration of reconstructed attention under occlusion, clutter and multi-object bimanual scenes remains open.</x:v>
       </x:c>
       <x:c r="CO67" t="str">
-        <x:v>High — informs language-conditioned manipulation and VLA design.</x:v>
+        <x:v>High：有助于研究语言条件操作与 VLA 设计。</x:v>
       </x:c>
       <x:c r="CP67" t="str">
-        <x:v>Official abstract / paper page; https://arxiv.org/html/2508.10333; checked 2026-09-23. Rapid summary only; existing Evidence Quality is unchanged.</x:v>
+        <x:v>官方摘要/论文页; https://arxiv.org/html/2508.10333; 核验于 2026-09-23. 仅为摘要级速读；原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="CQ67" t="str">
         <x:v>Exact work identity verified</x:v>
@@ -46155,7 +46159,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6c60bd683e36464c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R74c9fd2cd0fb4e26"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -46582,7 +46586,7 @@
         <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AN2" t="str">
-        <x:v>合成数据训练的 VLA 在真实机器人上受到 Sim2Real 外观、物体和桌面变化影响，且长时序操作的 affordance 结构容易丢失。</x:v>
+        <x:v>纯合成数据训练的 VLA 在真实场景中容易受到外观和动力学差异影响。</x:v>
       </x:c>
       <x:c r="AO2" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -46591,7 +46595,7 @@
         <x:v>Reconstruct ga</x:v>
       </x:c>
       <x:c r="AQ2" t="str">
-        <x:v>Synthetic manipulation-skill trajectories generated by the project pipeline; evaluation covers six tasks: table rearrangement, single-arm pouring, dual-arm pouring, basket…</x:v>
+        <x:v>合成操作轨迹与真实机器人评测；具体任务见项目页。</x:v>
       </x:c>
       <x:c r="AR2" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -46680,34 +46684,34 @@
       </x:c>
       <x:c r="BU2"/>
       <x:c r="BV2" t="str">
-        <x:v>Evidence-backed — 合成数据训练的 VLA 在真实机器人上受到 Sim2Real 外观、物体和桌面变化影响，且长时序操作的 affordance 结构容易丢失。</x:v>
+        <x:v>纯合成数据训练的 VLA 在真实场景中容易受到外观和动力学差异影响。</x:v>
       </x:c>
       <x:c r="BW2" t="str">
-        <x:v>Author-stated: synthetic-only VLA training has a persistent simulation-to-real gap; the paper targets zero-shot transfer without manual real-world fine-tuning.</x:v>
+        <x:v>仿真里学到的操作技能并不自动具备真机零样本泛化。</x:v>
       </x:c>
       <x:c r="BX2" t="str">
-        <x:v>The paper uses a dual-system design: a high-level planner infers chains of affordances and a low-level actor executes and validates tokenized actions. Automatic skill acquisition generates simulator trajectories from atomic tasks, affordance supervision, inverse kinematics and rendered observations.</x:v>
+        <x:v>Sim2Real-VLA 只用合成数据训练通用控制模型，并研究仿真技能迁移到真实操作。</x:v>
       </x:c>
       <x:c r="BY2" t="str">
         <x:v>Official project comparison reports success rate and step count across six tasks; exact baseline names and full table values require full-paper table extraction.</x:v>
       </x:c>
       <x:c r="BZ2" t="str">
-        <x:v>Official project page reports the best success-rate and step-count performance across all six tasks and metrics. No unverified numeric values are added here.</x:v>
+        <x:v>作者项目页报告多种真实操作任务的零样本迁移；完整数值和硬件条件仍需正文核验。</x:v>
       </x:c>
       <x:c r="CA2" t="str">
-        <x:v>Provides a concrete method or benchmark for the documented gap: Author-stated: synthetic-only VLA training has a persistent simulation-to-real gap; the paper targets zero-shot transfer without…</x:v>
+        <x:v>直接对应双臂 Sim2Real 与合成/真实数据配比问题。</x:v>
       </x:c>
       <x:c r="CB2" t="str">
-        <x:v>Author-stated / evidence boundary: exact hardware inventory, complete benchmark table, checkpoint release and complete dataset release were not confirmed from the accessible official sources.</x:v>
+        <x:v>本段基于官方摘要；未覆盖全文失败案例、完整 Baseline 与方法消融。</x:v>
       </x:c>
       <x:c r="CC2" t="str">
         <x:v>Library Analysis: robustness under broader embodiment, contact dynamics and unseen long-horizon compositions remains open.</x:v>
       </x:c>
       <x:c r="CD2" t="str">
-        <x:v>High — directly informs dual-arm coordination, data or ordinary-gripper policy design.</x:v>
+        <x:v>High：直接关联双臂普通夹爪、VLA 或真机操作。</x:v>
       </x:c>
       <x:c r="CE2" t="str">
-        <x:v>Official abstract / paper page; https://edem-ai.github.io/sim2realvla.github.io/; checked 2026-09-23. Rapid summary only; existing Evidence Quality is unchanged.</x:v>
+        <x:v>官方摘要/论文页：https://edem-ai.github.io/sim2realvla.github.io/；核验于 2026-09-23。仅为摘要级速读，原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="CF2" t="str">
         <x:v>Unresolved</x:v>
@@ -46838,7 +46842,7 @@
         <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AN3" t="str">
-        <x:v>Learning coordinated bimanual skills with low demonstration cost.</x:v>
+        <x:v>低成本示范条件下，如何学会协调的双臂技能。</x:v>
       </x:c>
       <x:c r="AO3" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -46847,7 +46851,7 @@
         <x:v>One-shot human video becomes structured keyframe trajectories and scalable robot demonstrations.</x:v>
       </x:c>
       <x:c r="AQ3" t="str">
-        <x:v>Not specified in checked abstract/card.</x:v>
+        <x:v>论文评估五项复杂的长时序双臂任务。</x:v>
       </x:c>
       <x:c r="AR3" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -46934,30 +46938,30 @@
       </x:c>
       <x:c r="BU3"/>
       <x:c r="BV3" t="str">
-        <x:v>Evidence-backed — Learning coordinated bimanual skills with low demonstration cost.</x:v>
+        <x:v>低成本示范条件下，如何学会协调的双臂技能。</x:v>
       </x:c>
       <x:c r="BW3" t="str">
-        <x:v>Bimanual robotic manipulation is a long-standing challenge of embodied intelligence due to its characteristics of dual-arm spatial-temporal coordination and high-dimensional action spaces.</x:v>
+        <x:v>一段人类视频不能直接提供机器人两臂的连续可执行动作。</x:v>
       </x:c>
       <x:c r="BX3" t="str">
-        <x:v>One-shot human video becomes structured keyframe trajectories and scalable robot demonstrations.</x:v>
+        <x:v>把单段人类视频转换为结构化关键帧轨迹，并扩展成机器人示范。</x:v>
       </x:c>
       <x:c r="BY3" t="str"/>
       <x:c r="BZ3" t="str">
-        <x:v>In experiments, YOTO achieves impressive performance in mimicking 5 intricate long-horizon bimanual tasks, possesses strong generalization under different visual and spatial conditions, and outperforms existing visuomotor imitation learning methods in…</x:v>
+        <x:v>作者报告可模仿五项双臂任务，并对视觉和空间变化有一定泛化；具体数值需看原文。</x:v>
       </x:c>
       <x:c r="CA3" t="str">
-        <x:v>Provides a concrete method or benchmark for the documented gap: Bimanual robotic manipulation is a long-standing challenge of embodied intelligence due to its characteristics of dual-arm…</x:v>
+        <x:v>可帮助研究 Human Video → Robot Action 的数据成本。</x:v>
       </x:c>
       <x:c r="CB3" t="str">
-        <x:v>Not established by the checked summary source; consult the full paper.</x:v>
+        <x:v>人类视频关键帧到真机连续控制仍需验证可达性与接触安全。</x:v>
       </x:c>
       <x:c r="CC3" t="str"/>
       <x:c r="CD3" t="str">
-        <x:v>High — directly informs dual-arm coordination, data or ordinary-gripper policy design.</x:v>
+        <x:v>High：与双臂普通夹爪和低示范预算直接相关。</x:v>
       </x:c>
       <x:c r="CE3" t="str">
-        <x:v>Official abstract / paper page; https://www.roboticsproceedings.org/rss21/p149.html; checked 2026-09-23. Rapid summary only; existing Evidence Quality is unchanged.</x:v>
+        <x:v>官方摘要/论文页; https://www.roboticsproceedings.org/rss21/p149.html; 核验于 2026-09-23. 仅为摘要级速读；原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="CF3" t="str">
         <x:v>Exact work identity verified</x:v>
@@ -47088,7 +47092,7 @@
         <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AN4" t="str">
-        <x:v>Bimanual policies must combine spatial localization with flexible continuous trajectories.</x:v>
+        <x:v>双臂策略要兼顾目标的空间定位和连续轨迹的灵活性。</x:v>
       </x:c>
       <x:c r="AO4" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -47097,7 +47101,7 @@
         <x:v>Use spatial interfaces to guide continuous bimanual actions.</x:v>
       </x:c>
       <x:c r="AQ4" t="str">
-        <x:v>Not specified in checked abstract/card.</x:v>
+        <x:v>仿真与真机双臂任务；完整 benchmark 见论文。</x:v>
       </x:c>
       <x:c r="AR4" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -47184,30 +47188,30 @@
       </x:c>
       <x:c r="BU4"/>
       <x:c r="BV4" t="str">
-        <x:v>Evidence-backed — Bimanual policies must combine spatial localization with flexible continuous trajectories.</x:v>
+        <x:v>双臂策略要兼顾目标的空间定位和连续轨迹的灵活性。</x:v>
       </x:c>
       <x:c r="BW4" t="str">
-        <x:v>Bimanual manipulation is a challenging yet crucial robotic capability, demanding precise spatial localization and versatile motion trajectories, which pose significant challenges to existing approaches.</x:v>
+        <x:v>单独使用离散空间提示或连续动作预测，可能难同时实现定位与平滑控制。</x:v>
       </x:c>
       <x:c r="BX4" t="str">
-        <x:v>Use spatial interfaces to guide continuous bimanual actions.</x:v>
+        <x:v>PPI 用空间接口引导连续双臂动作生成。</x:v>
       </x:c>
       <x:c r="BY4" t="str"/>
       <x:c r="BZ4" t="str">
-        <x:v>In extensive evaluations, PPI significantly outperforms prior methods in both simulated and realworld experiments, achieving state-of-the-art performance with a +16.1% improvement on the RLBench2 simulation benchmark and an average of +27.5% gain across four…</x:v>
+        <x:v>论文报告相对先前方法在仿真和真机上提升，卡片记录平均提升 16.1%；指标定义需回原文核对。</x:v>
       </x:c>
       <x:c r="CA4" t="str">
-        <x:v>Provides a concrete method or benchmark for the documented gap: Bimanual manipulation is a challenging yet crucial robotic capability, demanding precise spatial localization and versatile…</x:v>
+        <x:v>适合比较空间表示如何约束普通夹爪的双臂动作。</x:v>
       </x:c>
       <x:c r="CB4" t="str">
-        <x:v>Not established by the checked summary source; consult the full paper.</x:v>
+        <x:v>需进一步核验任务分布、失败类型和动作频率。</x:v>
       </x:c>
       <x:c r="CC4" t="str"/>
       <x:c r="CD4" t="str">
-        <x:v>High — directly informs dual-arm coordination, data or ordinary-gripper policy design.</x:v>
+        <x:v>High：直接对应双臂空间接口和连续动作。</x:v>
       </x:c>
       <x:c r="CE4" t="str">
-        <x:v>Official abstract / paper page; https://www.roboticsproceedings.org/rss21/p160.html; checked 2026-09-23. Rapid summary only; existing Evidence Quality is unchanged.</x:v>
+        <x:v>官方摘要/论文页; https://www.roboticsproceedings.org/rss21/p160.html; 核验于 2026-09-23. 仅为摘要级速读；原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="CF4" t="str">
         <x:v>Exact work identity verified</x:v>
@@ -47338,7 +47342,7 @@
         <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AN5" t="str">
-        <x:v>Collecting detailed, portable human-hand demonstrations for dexterous robot learning.</x:v>
+        <x:v>灵巧机器人学习缺少可携带、细节完整的人手示范。</x:v>
       </x:c>
       <x:c r="AO5" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -47347,7 +47351,7 @@
         <x:v>Capture wrist and finger motion with environment-grounded 3D observations.</x:v>
       </x:c>
       <x:c r="AQ5" t="str">
-        <x:v>Not specified in checked abstract/card.</x:v>
+        <x:v>已核验摘要未明确说明；需查阅论文方法与实验章节。</x:v>
       </x:c>
       <x:c r="AR5" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -47434,30 +47438,30 @@
       </x:c>
       <x:c r="BU5"/>
       <x:c r="BV5" t="str">
-        <x:v>Evidence-backed — Collecting detailed, portable human-hand demonstrations for dexterous robot learning.</x:v>
+        <x:v>灵巧机器人学习缺少可携带、细节完整的人手示范。</x:v>
       </x:c>
       <x:c r="BW5" t="str">
-        <x:v>Despite this potential, substantial challenges persist, particularly with the portability of existing hand motion capture (mocap) systems and the complexity of translating mocap data into effective robotic policies.</x:v>
+        <x:v>只记录视频，难准确捕捉手腕、手指和环境的三维关系。</x:v>
       </x:c>
       <x:c r="BX5" t="str">
-        <x:v>Capture wrist and finger motion with environment-grounded 3D observations.</x:v>
+        <x:v>DexCap 同步采集手腕与手指运动以及环境三维观测，形成可迁移的人手操作数据。</x:v>
       </x:c>
       <x:c r="BY5" t="str"/>
       <x:c r="BZ5" t="str">
-        <x:v>Through extensive evaluation across six challenging dexterous manipulation tasks, our approach not only demonstrates superior performance but also showcases the system's capability to effectively learn from in-the-wild mocap data, paving the way for future…</x:v>
+        <x:v>作者报告在六项灵巧操作任务上验证采集与学习价值；具体数值需查正文。</x:v>
       </x:c>
       <x:c r="CA5" t="str">
-        <x:v>Provides a concrete method or benchmark for the documented gap: Despite this potential, substantial challenges persist, particularly with the portability of existing hand motion capture (mocap)…</x:v>
+        <x:v>提醒示范采集装置决定后续策略能学到什么。</x:v>
       </x:c>
       <x:c r="CB5" t="str">
-        <x:v>Not established by the checked summary source; consult the full paper.</x:v>
+        <x:v>人手示范迁移到普通夹爪仍需动作重定向。</x:v>
       </x:c>
       <x:c r="CC5" t="str"/>
       <x:c r="CD5" t="str">
-        <x:v>Medium — transferable learning ideas may apply, but the hand hardware differs from ordinary grippers.</x:v>
+        <x:v>Medium：普通夹爪不需手指细节，但腕部和环境标定有用。</x:v>
       </x:c>
       <x:c r="CE5" t="str">
-        <x:v>Official abstract / paper page; https://roboticsproceedings.org/rss20/p043.html; checked 2026-09-23. Rapid summary only; existing Evidence Quality is unchanged.</x:v>
+        <x:v>官方摘要/论文页; https://roboticsproceedings.org/rss20/p043.html; 核验于 2026-09-23. 仅为摘要级速读；原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="CF5" t="str">
         <x:v>Unresolved</x:v>
@@ -47588,7 +47592,7 @@
         <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AN6" t="str">
-        <x:v>Manipulation policies are often evaluated too close to training conditions.</x:v>
+        <x:v>操作策略若只在接近训练条件的环境中评测，难以判断其鲁棒性。</x:v>
       </x:c>
       <x:c r="AO6" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -47597,7 +47601,7 @@
         <x:v>Stress-test policies through controlled environmental changes.</x:v>
       </x:c>
       <x:c r="AQ6" t="str">
-        <x:v>THE COLOSSEUM benchmark</x:v>
+        <x:v>THE COLOSSEUM 基准；具体扰动维度和策略清单需核对正文。</x:v>
       </x:c>
       <x:c r="AR6" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -47684,30 +47688,30 @@
       </x:c>
       <x:c r="BU6"/>
       <x:c r="BV6" t="str">
-        <x:v>Evidence-backed — Manipulation policies are often evaluated too close to training conditions.</x:v>
+        <x:v>操作策略若只在接近训练条件的环境中评测，难以判断其鲁棒性。</x:v>
       </x:c>
       <x:c r="BW6" t="str">
-        <x:v>Not established in checked summary source.</x:v>
+        <x:v>已核验摘要未明确说明；需查阅论文方法与实验章节。</x:v>
       </x:c>
       <x:c r="BX6" t="str">
-        <x:v>Stress-test policies through controlled environmental changes.</x:v>
+        <x:v>THE COLOSSEUM 通过受控环境扰动对策略进行压力测试。</x:v>
       </x:c>
       <x:c r="BY6" t="str"/>
       <x:c r="BZ6" t="str">
-        <x:v>To verify the ecological validity of our results, we show that our results in simulation are correlated ( ̄R2 = 0.614) to similar perturbations in real-world experiments.</x:v>
+        <x:v>官方摘要报告，仿真扰动结果与相似真实扰动实验存在相关性，调整后的 R² = 0.614。</x:v>
       </x:c>
       <x:c r="CA6" t="str">
-        <x:v>Medium — useful for method selection, data design and evaluation.</x:v>
+        <x:v>可帮助设计跨光照、外观和几何变化的泛化评测。</x:v>
       </x:c>
       <x:c r="CB6" t="str">
-        <x:v>Not established by the checked summary source; consult the full paper.</x:v>
+        <x:v>相关性并不意味着单个策略的真实成功率可由仿真精确预测。</x:v>
       </x:c>
       <x:c r="CC6" t="str"/>
       <x:c r="CD6" t="str">
-        <x:v>Medium — useful for method selection, data design and evaluation.</x:v>
+        <x:v>Medium：适合构建本项目的分布外评测，但需匹配实际传感器和夹爪。</x:v>
       </x:c>
       <x:c r="CE6" t="str">
-        <x:v>Official abstract / paper page; https://www.roboticsproceedings.org/rss20/p133.html; checked 2026-09-23. Rapid summary only; existing Evidence Quality is unchanged.</x:v>
+        <x:v>官方摘要/论文页; https://www.roboticsproceedings.org/rss20/p133.html; 核验于 2026-09-23. 仅为摘要级速读；原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="CF6" t="str">
         <x:v>Unresolved</x:v>
@@ -47838,7 +47842,7 @@
         <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AN7" t="str">
-        <x:v>Planning while maintaining a fixed transform between two end effectors creates difficult equality constraints.</x:v>
+        <x:v>双臂共同操作时，两只末端之间常需保持固定相对位姿。</x:v>
       </x:c>
       <x:c r="AO7" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -47847,7 +47851,7 @@
         <x:v>Make the constrained bimanual manifold directly searchable.</x:v>
       </x:c>
       <x:c r="AQ7" t="str">
-        <x:v>Not applicable</x:v>
+        <x:v>约束双臂规划场景；具体 benchmark 需核对正文。</x:v>
       </x:c>
       <x:c r="AR7" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -47934,30 +47938,30 @@
       </x:c>
       <x:c r="BU7"/>
       <x:c r="BV7" t="str">
-        <x:v>Evidence-backed — Planning while maintaining a fixed transform between two end effectors creates difficult equality constraints.</x:v>
+        <x:v>双臂共同操作时，两只末端之间常需保持固定相对位姿。</x:v>
       </x:c>
       <x:c r="BW7" t="str">
-        <x:v>In addition, the set of feasible configurations becomes a measure zero set, which presents a challenge to sampling-based motion planners.</x:v>
+        <x:v>这种等式约束使普通规划器难以高效搜索可行动作。</x:v>
       </x:c>
       <x:c r="BX7" t="str">
-        <x:v>Make the constrained bimanual manifold directly searchable.</x:v>
+        <x:v>直接在满足双臂相对位姿约束的运动流形上搜索轨迹。</x:v>
       </x:c>
       <x:c r="BY7" t="str"/>
       <x:c r="BZ7" t="str">
-        <x:v>Qualitative or numerical result not established by checked source.</x:v>
+        <x:v>已核验摘要未提供可安全复述的统一量化结果。</x:v>
       </x:c>
       <x:c r="CA7" t="str">
-        <x:v>Provides a concrete method or benchmark for the documented gap: In addition, the set of feasible configurations becomes a measure zero set, which presents a challenge to sampling-based motion…</x:v>
+        <x:v>为普通夹爪共同搬运物体提供几何约束基线。</x:v>
       </x:c>
       <x:c r="CB7" t="str">
-        <x:v>Author-stated — analytic solutions depend on arm kinematic classes; Library Analysis — learned perception and uncertain contact are outside scope.</x:v>
+        <x:v>需评估模型化固定相对位姿与真实滑动、形变之间的差异。</x:v>
       </x:c>
       <x:c r="CC7" t="str"/>
       <x:c r="CD7" t="str">
-        <x:v>High — directly informs dual-arm coordination, data or ordinary-gripper policy design.</x:v>
+        <x:v>High：双臂同步和共同约束是本项目基础问题。</x:v>
       </x:c>
       <x:c r="CE7" t="str">
-        <x:v>Official abstract / paper page; https://arxiv.org/html/2309.08770; checked 2026-09-23. Rapid summary only; existing Evidence Quality is unchanged.</x:v>
+        <x:v>官方摘要/论文页; https://arxiv.org/html/2309.08770; 核验于 2026-09-23. 仅为摘要级速读；原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="CF7" t="str">
         <x:v>Exact work identity verified</x:v>
@@ -48088,7 +48092,7 @@
         <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AN8" t="str">
-        <x:v>Contact-rich imitation must reproduce forces and switch sensing/control modes reliably.</x:v>
+        <x:v>接触密集操作既要视觉定位，也要复现合适接触力。</x:v>
       </x:c>
       <x:c r="AO8" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -48097,7 +48101,7 @@
         <x:v>Use see-through tactile feedback both during demonstration adaptation and policy execution.</x:v>
       </x:c>
       <x:c r="AQ8" t="str">
-        <x:v>Not specified in checked abstract/card.</x:v>
+        <x:v>已核验摘要未明确说明；需查阅论文方法与实验章节。</x:v>
       </x:c>
       <x:c r="AR8" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -48184,30 +48188,30 @@
       </x:c>
       <x:c r="BU8"/>
       <x:c r="BV8" t="str">
-        <x:v>Evidence-backed — Contact-rich imitation must reproduce forces and switch sensing/control modes reliably.</x:v>
+        <x:v>接触密集操作既要视觉定位，也要复现合适接触力。</x:v>
       </x:c>
       <x:c r="BW8" t="str">
-        <x:v>Contact-rich tasks continue to present many challenges for robotic manipulation.</x:v>
+        <x:v>只看图像的模仿策略可能忽略力反馈和感知模式切换。</x:v>
       </x:c>
       <x:c r="BX8" t="str">
-        <x:v>Use see-through tactile feedback both during demonstration adaptation and policy execution.</x:v>
+        <x:v>在示范适配与策略执行中使用透视式触觉反馈，并加入力匹配和视觉—触觉模式切换。</x:v>
       </x:c>
       <x:c r="BY8" t="str"/>
       <x:c r="BZ8" t="str">
-        <x:v>Our results show that the inclusion of force matching raises average policy success rates by 62.5%, visuotactile mode switching by 30.3%, and visuotactile data as a policy input by 42.5%, emphasizing the value of see-through tactile sensing for IL, both for…</x:v>
+        <x:v>卡片记录力匹配使平均成功率提高 62.5%；模式切换的独立贡献见原文。</x:v>
       </x:c>
       <x:c r="CA8" t="str">
-        <x:v>Provides a concrete method or benchmark for the documented gap: Contact-rich tasks continue to present many challenges for robotic manipulation.</x:v>
+        <x:v>提示普通夹爪接触任务可能需要力信号而不只是相机。</x:v>
       </x:c>
       <x:c r="CB8" t="str">
-        <x:v>Not established by the checked summary source; consult the full paper.</x:v>
+        <x:v>需检查本项目硬件是否具备相应触觉/力传感。</x:v>
       </x:c>
       <x:c r="CC8" t="str"/>
       <x:c r="CD8" t="str">
-        <x:v>Medium — relevant to robot manipulation; transfer to dual-arm real hardware needs validation.</x:v>
+        <x:v>High：双臂共同接触物体时，夹持力和滑动风险关键。</x:v>
       </x:c>
       <x:c r="CE8" t="str">
-        <x:v>OpenAlex indexed abstract; https://api.openalex.org/works/W4405753615; checked 2026-09-23. Rapid summary only; existing Evidence Quality is unchanged.</x:v>
+        <x:v>OpenAlex 索引摘要; https://api.openalex.org/works/W4405753615; 核验于 2026-09-23. 仅为摘要级速读；原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="CF8" t="str">
         <x:v>Exact work identity verified</x:v>
@@ -48338,7 +48342,7 @@
         <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AN9" t="str">
-        <x:v>Multiple arms need online trajectory adaptation and collision avoidance in shared workspaces.</x:v>
+        <x:v>多只机械臂共享工作空间时，需要在线修改轨迹并避免碰撞。</x:v>
       </x:c>
       <x:c r="AO9" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -48347,7 +48351,7 @@
         <x:v>Modulate demonstrated trajectories online while coordinating shared-space motion.</x:v>
       </x:c>
       <x:c r="AQ9" t="str">
-        <x:v>Not specified in checked abstract/card.</x:v>
+        <x:v>多臂协调场景；具体任务和平台需查正文。</x:v>
       </x:c>
       <x:c r="AR9" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -48434,30 +48438,30 @@
       </x:c>
       <x:c r="BU9"/>
       <x:c r="BV9" t="str">
-        <x:v>Evidence-backed — Multiple arms need online trajectory adaptation and collision avoidance in shared workspaces.</x:v>
+        <x:v>多只机械臂共享工作空间时，需要在线修改轨迹并避免碰撞。</x:v>
       </x:c>
       <x:c r="BW9" t="str">
-        <x:v>Introducing real-time motion modulation adds an extra layer of challenge to this coordination task.</x:v>
+        <x:v>离线示范轨迹不能保证在动态变化下仍安全可行。</x:v>
       </x:c>
       <x:c r="BX9" t="str">
-        <x:v>Modulate demonstrated trajectories online while coordinating shared-space motion.</x:v>
+        <x:v>对示范轨迹做在线调制，并在共享空间中协调多臂运动。</x:v>
       </x:c>
       <x:c r="BY9" t="str"/>
       <x:c r="BZ9" t="str">
-        <x:v>Qualitative or numerical result not established by checked source.</x:v>
+        <x:v>已核验摘要未给可安全复述的统一量化结果。</x:v>
       </x:c>
       <x:c r="CA9" t="str">
-        <x:v>Provides a concrete method or benchmark for the documented gap: Introducing real-time motion modulation adds an extra layer of challenge to this coordination task.</x:v>
+        <x:v>为双臂策略外部增加安全协调层提供参照。</x:v>
       </x:c>
       <x:c r="CB9" t="str">
-        <x:v>Not established by the checked summary source; consult the full paper.</x:v>
+        <x:v>需验证在线修正是否破坏原策略的任务意图。</x:v>
       </x:c>
       <x:c r="CC9" t="str"/>
       <x:c r="CD9" t="str">
-        <x:v>High — directly informs dual-arm coordination, data or ordinary-gripper policy design.</x:v>
+        <x:v>High：普通夹爪双臂真机必须处理共享空间碰撞。</x:v>
       </x:c>
       <x:c r="CE9" t="str">
-        <x:v>OpenAlex indexed abstract; https://api.openalex.org/works/W4404520558; checked 2026-09-23. Rapid summary only; existing Evidence Quality is unchanged.</x:v>
+        <x:v>OpenAlex 索引摘要; https://api.openalex.org/works/W4404520558; 核验于 2026-09-23. 仅为摘要级速读；原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="CF9" t="str">
         <x:v>Exact work identity verified</x:v>
@@ -48588,7 +48592,7 @@
         <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AN10" t="str">
-        <x:v>State and action representations may not transfer across reality gaps or hand geometries.</x:v>
+        <x:v>灵巧手策略要跨仿真/现实和不同手型迁移。</x:v>
       </x:c>
       <x:c r="AO10" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -48597,7 +48601,7 @@
         <x:v>Reduce hand-specific state information to improve transfer robustness.</x:v>
       </x:c>
       <x:c r="AQ10" t="str">
-        <x:v>Not specified in checked abstract/card.</x:v>
+        <x:v>两项手内操作任务；具体机器人与设置见 RA-L 正文。</x:v>
       </x:c>
       <x:c r="AR10" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -48684,30 +48688,30 @@
       </x:c>
       <x:c r="BU10"/>
       <x:c r="BV10" t="str">
-        <x:v>Evidence-backed — State and action representations may not transfer across reality gaps or hand geometries.</x:v>
+        <x:v>灵巧手策略要跨仿真/现实和不同手型迁移。</x:v>
       </x:c>
       <x:c r="BW10" t="str">
-        <x:v>Not established in checked summary source.</x:v>
+        <x:v>域随机化等方法不能完全弥合观测与动作定义造成的差异。</x:v>
       </x:c>
       <x:c r="BX10" t="str">
-        <x:v>Reduce hand-specific state information to improve transfer robustness.</x:v>
+        <x:v>比较不同 State Space 与 Action Space 的选择，检验其对两类迁移的影响。</x:v>
       </x:c>
       <x:c r="BY10" t="str"/>
       <x:c r="BZ10" t="str">
-        <x:v>Results show that a reduced state space avoiding hand-specific information improves robustness despite containing less information.</x:v>
+        <x:v>IEEE RA-L 摘要报告：在两项示例操作任务中，去除手型特有信息的较小状态空间更利于迁移。</x:v>
       </x:c>
       <x:c r="CA10" t="str">
-        <x:v>High — informs transfer from simulation to NERO real-robot manipulation.</x:v>
+        <x:v>提醒本项目先确定哪些状态和动作维度可跨两只夹爪复用。</x:v>
       </x:c>
       <x:c r="CB10" t="str">
-        <x:v>Not established by the checked summary source; consult the full paper.</x:v>
+        <x:v>本段基于官方摘要；未覆盖全文失败案例、完整 Baseline 与方法消融。</x:v>
       </x:c>
       <x:c r="CC10" t="str"/>
       <x:c r="CD10" t="str">
-        <x:v>High — informs transfer from simulation to NERO real-robot manipulation.</x:v>
+        <x:v>Medium：方法可借鉴，但迁移到当前双臂硬件需验证。</x:v>
       </x:c>
       <x:c r="CE10" t="str">
-        <x:v>Official abstract / paper page; https://ieeexplore.ieee.org/document/10955245/; checked 2026-09-23. Rapid summary only; existing Evidence Quality is unchanged.</x:v>
+        <x:v>官方摘要/论文页：https://ieeexplore.ieee.org/document/10955245/；核验于 2026-09-23。仅为摘要级速读，原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="CF10" t="str">
         <x:v>Unresolved</x:v>
@@ -48816,7 +48820,7 @@
         <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AN11" t="str">
-        <x:v>Large policies pretrained on diverse robot datasets have the potential to transform robotic learning: instead of training new policies from scratch, such generalist robot policies may be finetuned with only a little in-domain data, yet generalize broadly.</x:v>
+        <x:v>通用机器人策略需要同时适配不同相机、动作空间和机器人平台。</x:v>
       </x:c>
       <x:c r="AO11" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -48825,7 +48829,7 @@
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
       </x:c>
       <x:c r="AQ11" t="str">
-        <x:v>Open X-Embodiment contains ~1.5M episodes; Octo curates 800k. Zero-shot and finetuning evaluations cover WidowX BridgeV2, UR5, RT-1 and six downstream tasks (Secs. II–IV, App. F).</x:v>
+        <x:v>从 Open X-Embodiment 整理约 80 万条训练轨迹，在 9 种机器人平台和多项下游任务上评估。</x:v>
       </x:c>
       <x:c r="AR11" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -48912,30 +48916,30 @@
       </x:c>
       <x:c r="BU11"/>
       <x:c r="BV11" t="str">
-        <x:v>Evidence-backed — Large policies pretrained on diverse robot datasets have the potential to transform robotic learning: instead of training new policies from scratch, such generalist robot policies may be finetuned with only a little in-domain data, yet generalize broadly.</x:v>
+        <x:v>通用机器人策略需要同时适配不同相机、动作空间和机器人平台。</x:v>
       </x:c>
       <x:c r="BW11" t="str">
-        <x:v>However, to be widely applicable across a range of robotic learning scenarios, environments, and tasks, such policies need to handle diverse sensors and action spaces, accommodate a variety of commonly used robotic platforms, and finetune readily and…</x:v>
+        <x:v>各机器人平台的相机、动作空间与任务不同，单一策略难以直接跨平台使用。</x:v>
       </x:c>
       <x:c r="BX11" t="str">
-        <x:v>As a first step, we introduce Octo, a large transformer-based policy trained on 800k trajectories from the Open X-Embodiment dataset, the largest robot manipulation dataset to date.</x:v>
+        <x:v>Octo 在 Open X-Embodiment 约 80 万条轨迹上训练 Transformer 策略，并提供可微调的通用初始化。</x:v>
       </x:c>
       <x:c r="BY11" t="str"/>
       <x:c r="BZ11" t="str">
-        <x:v>In experiments across 9 robotic platforms, we demonstrate that Octo serves as a versatile policy initialization that can be effectively finetuned to new observation and action spaces.</x:v>
+        <x:v>论文在 9 种机器人平台上评测，表明 Octo 可迁移到新的观测和动作空间；具体成功率见原卡实验表。</x:v>
       </x:c>
       <x:c r="CA11" t="str">
-        <x:v>Provides a concrete method or benchmark for the documented gap: However, to be widely applicable across a range of robotic learning scenarios, environments, and tasks, such policies need to…</x:v>
+        <x:v>是研究共享机器人数据与跨本体微调的重要开放基线。</x:v>
       </x:c>
       <x:c r="CB11" t="str">
-        <x:v>Author-stated — only 27% of data includes wrist cameras, 56% includes language, training uses optimal demonstrations, and evaluation is limited to single/dual-arm manipulators (Sec. V).</x:v>
+        <x:v>训练数据的腕部相机和语言覆盖不均；评测主要在论文列出的单臂/双臂平台。</x:v>
       </x:c>
       <x:c r="CC11" t="str"/>
       <x:c r="CD11" t="str">
-        <x:v>High — informs language-conditioned manipulation and VLA design.</x:v>
+        <x:v>High：有助于研究语言条件操作与 VLA 设计。</x:v>
       </x:c>
       <x:c r="CE11" t="str">
-        <x:v>Official abstract / paper page; https://arxiv.org/html/2405.12213; checked 2026-09-23. Rapid summary only; existing Evidence Quality is unchanged.</x:v>
+        <x:v>官方摘要/论文页; https://arxiv.org/html/2405.12213; 核验于 2026-09-23. 仅为摘要级速读；原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="CF11" t="str">
         <x:v>Exact work identity verified</x:v>
@@ -49040,7 +49044,7 @@
         <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AN12" t="str">
-        <x:v>The creation of large, diverse, high-quality robot manipulation datasets is an important stepping stone on the path toward more capable and robust robotic manipulation policies.</x:v>
+        <x:v>通用操作策略需要规模大、场景多样且质量可靠的机器人交互数据。</x:v>
       </x:c>
       <x:c r="AO12" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -49049,7 +49053,7 @@
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
       </x:c>
       <x:c r="AQ12" t="str">
-        <x:v>Not specified in checked abstract/card.</x:v>
+        <x:v>DROID：约 6.5 万条轨迹／350 小时、564 个场景、86 项任务，50 名采集人员在 12 个月内完成。</x:v>
       </x:c>
       <x:c r="AR12" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -49136,30 +49140,30 @@
       </x:c>
       <x:c r="BU12"/>
       <x:c r="BV12" t="str">
-        <x:v>Evidence-backed — The creation of large, diverse, high-quality robot manipulation datasets is an important stepping stone on the path toward more capable and robust robotic manipulation policies.</x:v>
+        <x:v>通用操作策略需要规模大、场景多样且质量可靠的机器人交互数据。</x:v>
       </x:c>
       <x:c r="BW12" t="str">
-        <x:v>However, creating such datasets is challenging: collecting robot manipulation data in diverse environments poses logistical and safety challenges and requires substantial investments in hardware and human labour.</x:v>
+        <x:v>跨环境采集成本高，并受安全、硬件和人力协调限制。</x:v>
       </x:c>
       <x:c r="BX12" t="str">
-        <x:v>In this work, we introduce DROID (Distributed Robot Interaction Dataset), a diverse robot manipulation dataset with 65k demonstration trajectories or 350h of interaction data, collected across 564 scenes and 86 tasks by 50 data collectors in North America, Asia, and Europe over the course of 12 months.</x:v>
+        <x:v>DROID 组织分布式采集，形成 6.5 万条示范轨迹、约 350 小时交互，覆盖 564 个场景和 86 项任务。</x:v>
       </x:c>
       <x:c r="BY12" t="str"/>
       <x:c r="BZ12" t="str">
-        <x:v>We demonstrate that training with DROID leads to policies with higher performance, greater robustness, and improved generalization ability.</x:v>
+        <x:v>论文摘要报告，使用 DROID 训练的策略在性能、鲁棒性和泛化上改善；此处不附加未经实验表格核实的增幅。</x:v>
       </x:c>
       <x:c r="CA12" t="str">
-        <x:v>Provides a concrete method or benchmark for the documented gap: However, creating such datasets is challenging: collecting robot manipulation data in diverse environments poses logistical and…</x:v>
+        <x:v>为跨场景数据采集和数据规模设计提供具体参照。</x:v>
       </x:c>
       <x:c r="CB12" t="str">
-        <x:v>Not established by the checked summary source; consult the full paper.</x:v>
+        <x:v>摘要不能分离数据量、场景多样性与策略结构各自的贡献。</x:v>
       </x:c>
       <x:c r="CC12" t="str"/>
       <x:c r="CD12" t="str">
-        <x:v>Medium — useful for method selection, data design and evaluation.</x:v>
+        <x:v>Medium：可借鉴采集协议，但需核对与本项目机器人形态和动作接口的差异。</x:v>
       </x:c>
       <x:c r="CE12" t="str">
-        <x:v>Official abstract / paper page; https://roboticsproceedings.org/rss20/p120.html; checked 2026-09-23. Rapid summary only; existing Evidence Quality is unchanged.</x:v>
+        <x:v>官方摘要/论文页; https://roboticsproceedings.org/rss20/p120.html; 核验于 2026-09-23. 仅为摘要级速读；原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="CF12" t="str">
         <x:v>Unresolved</x:v>
@@ -49207,14 +49211,16 @@
       <x:c r="M13"/>
       <x:c r="N13"/>
       <x:c r="O13" t="str">
-        <x:v>https://roboticsproceedings.org/rss20/p074.html</x:v>
+        <x:v>https://www.roboticsproceedings.org/rss20/p050.html</x:v>
       </x:c>
       <x:c r="P13" t="str">
         <x:v>https://robocasa.ai/</x:v>
       </x:c>
-      <x:c r="Q13"/>
+      <x:c r="Q13" t="str">
+        <x:v>https://github.com/robocasa/robocasa</x:v>
+      </x:c>
       <x:c r="R13" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Released（官方仓库已公开；本轮未运行验证）</x:v>
       </x:c>
       <x:c r="S13"/>
       <x:c r="T13"/>
@@ -49264,7 +49270,7 @@
         <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AN13" t="str">
-        <x:v>Building upon our previous contributions, this paper introduces Arena 3.0, an extension of Arena-Bench, Arena 1.0, and Arena 2.0 focusing on the development, simulation, and benchmarking of social navigation approaches in collaborative environments.</x:v>
+        <x:v>真实机器人数据难以低成本扩展，限制通用家庭操作策略训练。</x:v>
       </x:c>
       <x:c r="AO13" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -49273,7 +49279,7 @@
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
       </x:c>
       <x:c r="AQ13" t="str">
-        <x:v>Not specified in checked abstract/card.</x:v>
+        <x:v>RSS 2024 原版 RoboCasa：100 项任务、超过 150 个物体类别及大量 3D 资产；不要与后续 RoboCasa365 的规模混同。</x:v>
       </x:c>
       <x:c r="AR13" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -49360,30 +49366,30 @@
       </x:c>
       <x:c r="BU13"/>
       <x:c r="BV13" t="str">
-        <x:v>Evidence-backed — Building upon our previous contributions, this paper introduces Arena 3.0, an extension of Arena-Bench, Arena 1.0, and Arena 2.0 focusing on the development, simulation, and benchmarking of social navigation approaches in collaborative environments.</x:v>
+        <x:v>真实机器人数据难以低成本扩展，限制通用家庭操作策略训练。</x:v>
       </x:c>
       <x:c r="BW13" t="str">
-        <x:v>Not established in checked summary source.</x:v>
+        <x:v>场景、任务和示范的规模不足；仅靠真机采集难以覆盖家庭环境多样性。</x:v>
       </x:c>
       <x:c r="BX13" t="str">
-        <x:v>We significantly enhance the realism of human behavior simulation by incorporating a diverse array of new social force models and interaction patterns, encompassing both human-human and human-robot dynamics.</x:v>
+        <x:v>RoboCasa 建立以厨房为中心的大规模仿真框架，结合生成式资产、语言模型辅助任务设计、人类示范和自动轨迹生成。</x:v>
       </x:c>
       <x:c r="BY13" t="str"/>
       <x:c r="BZ13" t="str">
-        <x:v>The platform’s efficacy has been validated through an extensive benchmark and user evaluations of the platform by a global community of researchers and students, which noted the substantial improvement compared to previous versions and expressed interests to…</x:v>
+        <x:v>RSS 官方摘要报告，合成数据用于大规模模仿学习呈现规模效应；本轮不转述未经表格核验的成功率。</x:v>
       </x:c>
       <x:c r="CA13" t="str">
-        <x:v>Medium — useful for method selection, data design and evaluation.</x:v>
+        <x:v>可用于研究仿真数据扩增及与真实机器人数据联合训练。</x:v>
       </x:c>
       <x:c r="CB13" t="str">
-        <x:v>Not established by the checked summary source; consult the full paper.</x:v>
+        <x:v>摘要不能保证仿真训练所得提升直接迁移至本项目真机。</x:v>
       </x:c>
       <x:c r="CC13" t="str"/>
       <x:c r="CD13" t="str">
-        <x:v>Medium — useful for method selection, data design and evaluation.</x:v>
+        <x:v>Medium：家庭操作仿真可借鉴，但与本项目场景、双臂配置和真实部署有差异。</x:v>
       </x:c>
       <x:c r="CE13" t="str">
-        <x:v>Official abstract / paper page; https://roboticsproceedings.org/rss20/p074.html; checked 2026-09-23. Rapid summary only; existing Evidence Quality is unchanged.</x:v>
+        <x:v>官方摘要/论文页; https://www.roboticsproceedings.org/rss20/p050.html; 核验于 2026-09-23. 仅为摘要级速读；原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="CF13" t="str">
         <x:v>Exact work identity verified</x:v>
@@ -49488,7 +49494,7 @@
         <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AN14" t="str">
-        <x:v>Robot-learning datasets are fragmented across embodiments, tasks and formats.</x:v>
+        <x:v>机器人数据分散在不同机构、平台和格式中，难以训练通用策略。</x:v>
       </x:c>
       <x:c r="AO14" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -49497,7 +49503,7 @@
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
       </x:c>
       <x:c r="AQ14" t="str">
-        <x:v>Not specified in checked abstract/card.</x:v>
+        <x:v>Open X-Embodiment 数据混合及 RT-X 评测。</x:v>
       </x:c>
       <x:c r="AR14" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -49584,30 +49590,30 @@
       </x:c>
       <x:c r="BU14"/>
       <x:c r="BV14" t="str">
-        <x:v>Evidence-backed — Robot-learning datasets are fragmented across embodiments, tasks and formats.</x:v>
+        <x:v>机器人数据分散在不同机构、平台和格式中，难以训练通用策略。</x:v>
       </x:c>
       <x:c r="BW14" t="str">
-        <x:v>Not established in checked summary source.</x:v>
+        <x:v>每个机器人和任务单独训练模型，跨平台复用成本高。</x:v>
       </x:c>
       <x:c r="BX14" t="str">
-        <x:v>We present Open X-Embodiment, a standardized multi-institution dataset mixture with RT-X generalist policy experiments.</x:v>
+        <x:v>Open X-Embodiment 整合标准化的跨机器人数据，并训练 RT-X 模型测试共享学习。</x:v>
       </x:c>
       <x:c r="BY14" t="str"/>
       <x:c r="BZ14" t="str">
-        <x:v>Qualitative or numerical result not established by checked source.</x:v>
+        <x:v>官方项目与论文报告跨机器人训练带来的泛化收益；具体任务数值见原论文。</x:v>
       </x:c>
       <x:c r="CA14" t="str">
-        <x:v>High — informs language-conditioned manipulation and VLA design.</x:v>
+        <x:v>是审计跨本体数据、动作格式和策略迁移的基础入口。</x:v>
       </x:c>
       <x:c r="CB14" t="str">
-        <x:v>Not established by the checked summary source; consult the full paper.</x:v>
+        <x:v>本段基于官方摘要；未覆盖全文失败案例、完整 Baseline 与方法消融。</x:v>
       </x:c>
       <x:c r="CC14" t="str"/>
       <x:c r="CD14" t="str">
-        <x:v>High — informs language-conditioned manipulation and VLA design.</x:v>
+        <x:v>Medium：方法可借鉴，但迁移到当前双臂硬件需验证。</x:v>
       </x:c>
       <x:c r="CE14" t="str">
-        <x:v>Official abstract / paper page; https://robotics-transformer-x.github.io/; checked 2026-09-23. Rapid summary only; existing Evidence Quality is unchanged.</x:v>
+        <x:v>官方摘要/论文页：https://robotics-transformer-x.github.io/；核验于 2026-09-23。仅为摘要级速读，原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="CF14" t="str">
         <x:v>Exact work identity verified</x:v>
@@ -49738,7 +49744,7 @@
         <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AN15" t="str">
-        <x:v>Large language models contain semantic knowledge for decomposing abstract, temporally extended instructions but are not grounded in a robot embodiment, current scene, action repertoire or execution consequences. A text-only answer can therefore be sensible in language yet infeasible or unsafe for the robot.</x:v>
+        <x:v>LLM 能拆解长指令，但不知道当前机器人真正能做什么。</x:v>
       </x:c>
       <x:c r="AO15" t="str">
         <x:v>Useful decomposition and feasible execution were not jointly scored.</x:v>
@@ -49747,7 +49753,7 @@
         <x:v>SayCan p(cπ|s,ℓπ) × p(ℓπ|i), skill-level receding horizon.</x:v>
       </x:c>
       <x:c r="AQ15" t="str">
-        <x:v>The main test contains 101 natural-language instructions in 7 families: NL single primitive, NL nouns, NL verbs, structured language, embodiment variations, crowd-sourced requests…</x:v>
+        <x:v>Mock Kitchen 与真实办公室厨房任务。</x:v>
       </x:c>
       <x:c r="AR15" t="str">
         <x:v>No VF; Generative; FLAN-SayCan; BC NL/USE.</x:v>
@@ -49838,23 +49844,23 @@
         <x:v>Completed-A</x:v>
       </x:c>
       <x:c r="BV15" t="str">
-        <x:v>Evidence-backed — Large language models contain semantic knowledge for decomposing abstract, temporally extended instructions but are not grounded in a robot embodiment, current scene, action repertoire or execution consequences. A text-only answer can therefore be sensible in language yet infeasible or unsafe for the robot.</x:v>
+        <x:v>LLM 能拆解长指令，但不知道当前机器人真正能做什么。</x:v>
       </x:c>
       <x:c r="BW15" t="str">
-        <x:v>Prior language-conditioned robot systems typically handle short atomic commands, while LLM planning can suggest actions outside the robot's skill set. The missing bridge is a shared interface that scores usefulness toward the instruction and feasibility in…</x:v>
+        <x:v>只按语言相关性选技能，可能生成物理上不可执行的计划。</x:v>
       </x:c>
       <x:c r="BX15" t="str">
-        <x:v>We propose to provide real-world grounding by means of pretrained skills, which are used to constrain the model to propose natural language actions that are both feasible and contextually appropriate.</x:v>
+        <x:v>SayCan 结合语言模型的技能匹配分数与技能价值/可供性估计，逐步选择当前可执行的操作。</x:v>
       </x:c>
       <x:c r="BY15" t="str"/>
       <x:c r="BZ15" t="str">
-        <x:v>Mock Kitchen / training environment (Table 2): PaLM-SayCan plan 84%, execute 74% over 101 instructions. - Real office kitchen (Table 2): plan 81%, execute 60%. - PaLM vs FLAN (Table 3): PaLM-SayCan 84% plan / 74% execute; FLAN-SayCan 70% / 61%. - No…</x:v>
+        <x:v>卡片记录 Mock Kitchen 101 条指令中规划成功 84%、物理执行 74%；真实办公室厨房规划 81%，完整执行值见 Table 2。</x:v>
       </x:c>
       <x:c r="CA15" t="str">
-        <x:v>Provides a concrete method or benchmark for the documented gap: Prior language-conditioned robot systems typically handle short atomic commands, while LLM planning can suggest actions outside…</x:v>
+        <x:v>把语言规划和机器人可执行性明确连接起来。</x:v>
       </x:c>
       <x:c r="CB15" t="str">
-        <x:v>Author-stated: vanilla SayCan only receives environmental feedback through current-step value functions; after a skill fails or the environment changes, necessary feedback may be unavailable. The authors point to…</x:v>
+        <x:v>技能库、价值估计和环境假设依赖特定机器人；规划成功不保证动作完成。</x:v>
       </x:c>
       <x:c r="CC15" t="str">
         <x:v>1. Open-ended tasks outside the fixed skill library remain unsupported (Sec. 3–4 evidence).
@@ -49864,10 +49870,10 @@
 5. Joint feasibility and role allocation for bimanual ordinary-gripper systems are not evaluated (library/project analysis).</x:v>
       </x:c>
       <x:c r="CD15" t="str">
-        <x:v>High — informs transfer from simulation to NERO real-robot manipulation.</x:v>
+        <x:v>High：双臂普通夹爪需要在动作前判断技能是否可行。</x:v>
       </x:c>
       <x:c r="CE15" t="str">
-        <x:v>Official abstract / paper page; https://arxiv.org/html/2204.01691; checked 2026-09-23. Rapid summary only; existing Evidence Quality is unchanged.</x:v>
+        <x:v>官方摘要/论文页; https://arxiv.org/html/2204.01691; 核验于 2026-09-23. 仅为摘要级速读；原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="CF15" t="str">
         <x:v>Exact work identity verified</x:v>
@@ -49896,7 +49902,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8c1e048ccf2f4363"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9b6f9198ed0e4d4d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/00_Paper_Pool/Paper_Pool.xlsx
+++ b/00_Paper_Pool/Paper_Pool.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Papers" sheetId="1" r:id="Rf34e3ef76b4247fd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rejected" sheetId="2" r:id="R72e1a1bcb5f740e0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Venues" sheetId="3" r:id="R81f52f8342df421e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Keywords" sheetId="4" r:id="R82d4680386654c31"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Discovery" sheetId="5" r:id="R06b05290bbbe48c6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CCF_A_Library" sheetId="6" r:id="Rf1c22db630ed47e2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Robotics_Core_Library" sheetId="7" r:id="Rb1f17bc3bb304c1c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Papers" sheetId="1" r:id="R0692eb68bb314a8d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rejected" sheetId="2" r:id="Ra523ac2a0d98410e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Venues" sheetId="3" r:id="R2663c1e840cc4fd3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Keywords" sheetId="4" r:id="Rc9a5428bbbb4414d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Discovery" sheetId="5" r:id="R481916f3a87340d0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CCF_A_Library" sheetId="6" r:id="R0a70830d5045435b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Robotics_Core_Library" sheetId="7" r:id="R0f837519acb64b12"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -300,7 +300,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="74" name="PapersTable" displayName="PapersTable" ref="A1:CE6" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="78" name="PapersTable" displayName="PapersTable" ref="A1:CE6" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="83">
     <x:tableColumn id="1" name="编号 ID"/>
     <x:tableColumn id="2" name="论文标题 Title"/>
@@ -436,7 +436,7 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="75" name="DiscoveryTable" displayName="DiscoveryTable" ref="A1:BZ79" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="79" name="DiscoveryTable" displayName="DiscoveryTable" ref="A1:BZ79" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="78">
     <x:tableColumn id="1" name="编号 ID"/>
     <x:tableColumn id="2" name="论文标题 Title"/>
@@ -522,7 +522,7 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="76" name="CCFALibraryTable" displayName="CCFALibraryTable" ref="A1:CS67" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="80" name="CCFALibraryTable" displayName="CCFALibraryTable" ref="A1:CS67" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="97">
     <x:tableColumn id="1" name="编号 ID"/>
     <x:tableColumn id="2" name="论文标题 Title"/>
@@ -627,7 +627,7 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="77" name="RoboticsCoreLibraryTable" displayName="RoboticsCoreLibraryTable" ref="A1:CH15" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="81" name="RoboticsCoreLibraryTable" displayName="RoboticsCoreLibraryTable" ref="A1:CH15" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="86">
     <x:tableColumn id="1" name="ID"/>
     <x:tableColumn id="2" name="Title"/>
@@ -5331,7 +5331,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9f302552a21844f9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1ef4e32889f440e6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8627,7 +8627,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3f032058dcc948d8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9f9c45a596a24bf1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8978,7 +8978,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R785ce104cd4d4572"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R395670ce787f406d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9724,7 +9724,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3af23533ecd0437a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R84dd079b53594eaf"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -26596,7 +26596,9 @@
       <x:c r="AY77" t="str">
         <x:v>Unknown</x:v>
       </x:c>
-      <x:c r="AZ77"/>
+      <x:c r="AZ77" t="str">
+        <x:v>https://www.roboticsproceedings.org/rss20/p050.pdf</x:v>
+      </x:c>
       <x:c r="BA77" t="str">
         <x:v>No</x:v>
       </x:c>
@@ -26622,10 +26624,10 @@
         <x:v>Not Checked</x:v>
       </x:c>
       <x:c r="BI77" t="str">
-        <x:v>Not Found After Verification</x:v>
+        <x:v>Verified DOI</x:v>
       </x:c>
       <x:c r="BJ77" t="str">
-        <x:v>Not Found After Verification</x:v>
+        <x:v>Verified - 2406.02523</x:v>
       </x:c>
       <x:c r="BK77" t="str">
         <x:v>Audit logged - deep extraction pending</x:v>
@@ -27142,7 +27144,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfbf8d6f51f124fa0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5fc28476572740b6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -46159,7 +46161,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R74c9fd2cd0fb4e26"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd374438b095542f0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -49327,7 +49329,9 @@
       <x:c r="BG13" t="str">
         <x:v>Unknown</x:v>
       </x:c>
-      <x:c r="BH13"/>
+      <x:c r="BH13" t="str">
+        <x:v>https://www.roboticsproceedings.org/rss20/p050.pdf</x:v>
+      </x:c>
       <x:c r="BI13" t="str">
         <x:v>No</x:v>
       </x:c>
@@ -49353,10 +49357,10 @@
         <x:v>Not Checked</x:v>
       </x:c>
       <x:c r="BQ13" t="str">
-        <x:v>Not Found After Verification</x:v>
+        <x:v>Verified DOI</x:v>
       </x:c>
       <x:c r="BR13" t="str">
-        <x:v>Not Found After Verification</x:v>
+        <x:v>Verified - 2406.02523</x:v>
       </x:c>
       <x:c r="BS13" t="str">
         <x:v>Audit logged - deep extraction pending</x:v>
@@ -49902,7 +49906,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9b6f9198ed0e4d4d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdfa19e8e776f4a68"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/00_Paper_Pool/Paper_Pool.xlsx
+++ b/00_Paper_Pool/Paper_Pool.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Papers" sheetId="1" r:id="R0692eb68bb314a8d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rejected" sheetId="2" r:id="Ra523ac2a0d98410e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Venues" sheetId="3" r:id="R2663c1e840cc4fd3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Keywords" sheetId="4" r:id="Rc9a5428bbbb4414d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Discovery" sheetId="5" r:id="R481916f3a87340d0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CCF_A_Library" sheetId="6" r:id="R0a70830d5045435b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Robotics_Core_Library" sheetId="7" r:id="R0f837519acb64b12"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Papers" sheetId="1" r:id="R8e8680133f6744ee"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rejected" sheetId="2" r:id="Rfbc7fd01bc0a4c45"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Venues" sheetId="3" r:id="R111515c5ef16488e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Keywords" sheetId="4" r:id="R6a9f89f4ea9f4881"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Discovery" sheetId="5" r:id="Rb379095cf2a84993"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CCF_A_Library" sheetId="6" r:id="R9eacbb2abac74b15"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Robotics_Core_Library" sheetId="7" r:id="R2113a9d0d58f46f7"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1406,7 +1406,7 @@
       </x:c>
       <x:c r="BR2"/>
       <x:c r="BS2" t="str">
-        <x:v>多模态大模型能理解图像和语言，但不一定能给出可执行的接触点与夹爪姿态。</x:v>
+        <x:v>研究问题：多模态大模型能理解图像和语言，但不一定能给出可执行的接触点与夹爪姿态。；之前方法的问题：物体级 Grounding 与精确接触几何没有自然地从语言推理转成机器人动作。；核心思路：ManipLLM 结合物体类别识别、affordance 推理和位姿微调，预测接触点与夹爪朝向，并通过分步推理和主动交互改进执行。；输入：物体视觉信息与操作指令；具体相机和状态接口见论文方法。；输出与动作：接触点、夹爪朝向及后续操作位姿。；数据集与评测基准：论文中的物体操作任务与消融设置；具体数据集名称见原卡实验部分。；为什么重要：让语言推理落到普通夹爪可执行的接触几何上。；与当前项目的关系：High：直接对应夹爪接触点、动作前可行性验证和真机操作。；主要局限：作者指出视觉位置预测仍受域变化影响；特定吸盘硬件约束需要测试时适配。</x:v>
       </x:c>
       <x:c r="BT2" t="str">
         <x:v>物体级 Grounding 与精确接触几何没有自然地从语言推理转成机器人动作。</x:v>
@@ -1538,7 +1538,7 @@
         <x:v>Real Robot 字段为 `Unknown`；Dataset、Benchmark、Robot Platform 中的 Unknown 继续保留，不从题名推断。</x:v>
       </x:c>
       <x:c r="AP3" t="str">
-        <x:v>Unknown / Needs Full-Paper Verification</x:v>
+        <x:v>作者报告成功率、动作保真度与训练效率优于所比较方法；摘要未给统一数字。</x:v>
       </x:c>
       <x:c r="AQ3" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -1619,7 +1619,7 @@
       </x:c>
       <x:c r="BR3"/>
       <x:c r="BS3" t="str">
-        <x:v>人类双手操作能力丰富，但难以直接迁移到机器人灵巧手。</x:v>
+        <x:v>研究问题：人类双手操作能力丰富，但难以直接迁移到机器人灵巧手。；之前方法的问题：人手和机器人手的运动学、接触方式不同，逐帧模仿不能保证可执行。；核心思路：ManipTrans 用两阶段流程，在仿真中把人类双手技能迁移到机器人灵巧手策略。；数据集与评测基准：双手灵巧操作仿真任务；详细任务和基线见论文。；主要结果：作者报告成功率、动作保真度与训练效率优于所比较方法；摘要未给统一数字。；为什么重要：展示 Human Video / Human Motion 到机器人双手动作的转换思路。；与当前项目的关系：Medium：手型不同，普通夹爪适配仍需单独建模。；主要局限：仿真到真机与普通夹爪迁移尚不能从摘要确认。</x:v>
       </x:c>
       <x:c r="BT3" t="str">
         <x:v>人手和机器人手的运动学、接触方式不同，逐帧模仿不能保证可执行。</x:v>
@@ -1747,7 +1747,7 @@
         <x:v>Real Robot 字段为 `Unknown`；Dataset、Benchmark、Robot Platform 中的 Unknown 继续保留，不从题名推断。</x:v>
       </x:c>
       <x:c r="AP4" t="str">
-        <x:v>Unknown / Needs Full-Paper Verification</x:v>
+        <x:v>官方摘要报告目标自适应任务平均成功率 70.7%。</x:v>
       </x:c>
       <x:c r="AQ4" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -1828,7 +1828,7 @@
       </x:c>
       <x:c r="BR4"/>
       <x:c r="BS4" t="str">
-        <x:v>接触密集的灵巧操作需要根据目标与环境变化调整动作。</x:v>
+        <x:v>研究问题：接触密集的灵巧操作需要根据目标与环境变化调整动作。；之前方法的问题：固定轨迹或单一接触模式难适应复杂手—物交互。；核心思路：DexHandDiff 用交互感知的扩散式规划生成可适应目标变化的灵巧手动作。；主要结果：官方摘要报告目标自适应任务平均成功率 70.7%。；为什么重要：展示生成式策略如何表达多种接触动作。；与当前项目的关系：Medium：可借鉴动作生成机制，但灵巧手与普通夹爪不同。；主要局限：需检查真机接触、动作延迟和跨硬件泛化。</x:v>
       </x:c>
       <x:c r="BT4" t="str">
         <x:v>固定轨迹或单一接触模式难适应复杂手—物交互。</x:v>
@@ -1956,7 +1956,7 @@
         <x:v>Real Robot 字段为 `Unknown`；Dataset、Benchmark、Robot Platform 中的 Unknown 继续保留，不从题名推断。</x:v>
       </x:c>
       <x:c r="AP5" t="str">
-        <x:v>Unknown / Needs Full-Paper Verification</x:v>
+        <x:v>作者报告小样本设置下优于所比较方法；摘要未给可安全复述的统一数值。</x:v>
       </x:c>
       <x:c r="AQ5" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -2037,7 +2037,7 @@
       </x:c>
       <x:c r="BR5"/>
       <x:c r="BS5" t="str">
-        <x:v>视觉机器人操作要根据语言、视觉和状态输出可执行动作。</x:v>
+        <x:v>研究问题：视觉机器人操作要根据语言、视觉和状态输出可执行动作。；之前方法的问题：只依赖少量机器人示范，难以利用大量人类动作视频。；核心思路：AR-VRM 显式利用人类动作视频学习视觉操作表示，再适配机器人策略。；主要结果：作者报告小样本设置下优于所比较方法；摘要未给可安全复述的统一数值。；为什么重要：为人类视频转机器人动作提供另一种数据路线。；与当前项目的关系：Medium：与低成本数据收集相关，双臂夹爪迁移待验。；主要局限：人体动作和机器人动作空间差异需要明确对齐。</x:v>
       </x:c>
       <x:c r="BT5" t="str">
         <x:v>只依赖少量机器人示范，难以利用大量人类动作视频。</x:v>
@@ -2282,7 +2282,7 @@
         <x:v>Completed-A</x:v>
       </x:c>
       <x:c r="BS6" t="str">
-        <x:v>LLM 能拆解长指令，但不知道当前机器人真正能做什么。</x:v>
+        <x:v>研究问题：LLM 能拆解长指令，但不知道当前机器人真正能做什么。；之前方法的问题：只按语言相关性选技能，可能生成物理上不可执行的计划。；核心思路：SayCan 结合语言模型的技能匹配分数与技能价值/可供性估计，逐步选择当前可执行的操作。；数据集与评测基准：Mock Kitchen 与真实办公室厨房任务。；为什么重要：把语言规划和机器人可执行性明确连接起来。；与当前项目的关系：High：双臂普通夹爪需要在动作前判断技能是否可行。；主要局限：技能库、价值估计和环境假设依赖特定机器人；规划成功不保证动作完成。</x:v>
       </x:c>
       <x:c r="BT6" t="str">
         <x:v>只按语言相关性选技能，可能生成物理上不可执行的计划。</x:v>
@@ -5331,7 +5331,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1ef4e32889f440e6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4c2fc9d3eb5f41ed"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8627,7 +8627,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9f9c45a596a24bf1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3d4521498537435b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8978,7 +8978,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R395670ce787f406d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R42de853929034cda"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9724,7 +9724,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R84dd079b53594eaf"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfefdd591593c42fb"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10102,7 +10102,7 @@
         <x:v>Real Robot 字段为 `Mixed`；Dataset、Benchmark、Robot Platform 中的 Unknown 继续保留，不从题名推断。</x:v>
       </x:c>
       <x:c r="AK2" t="str">
-        <x:v>Unknown / Needs Full-Paper Verification</x:v>
+        <x:v>作者报告仿真和真机成功率高于所比较方法；具体数值见实验表。</x:v>
       </x:c>
       <x:c r="AL2" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -10119,7 +10119,7 @@
       <x:c r="AP2" t="str">
         <x:v>B</x:v>
       </x:c>
-      <x:c r="AQ2" t="str"/>
+      <x:c r="AQ2"/>
       <x:c r="AR2" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
@@ -10183,7 +10183,7 @@
       </x:c>
       <x:c r="BM2"/>
       <x:c r="BN2" t="str">
-        <x:v>多任务机器人操作要同时决定高层子目标和符合运动学的连续动作。</x:v>
+        <x:v>研究问题：多任务机器人操作要同时决定高层子目标和符合运动学的连续动作。；之前方法的问题：单层扩散策略可能难兼顾长任务结构与局部可达性。；核心思路：Hierarchical Diffusion Policy 将任务规划与运动学感知的动作生成分层处理。；主要结果：作者报告仿真和真机成功率高于所比较方法；具体数值见实验表。；为什么重要：可对照双臂任务中高层分工与低层动作生成。；与当前项目的关系：High：双臂普通夹爪也需要运动学约束和任务分解。；主要局限：需核验在两臂共享工作空间中的约束处理。</x:v>
       </x:c>
       <x:c r="BO2" t="str">
         <x:v>单层扩散策略可能难兼顾长任务结构与局部可达性。</x:v>
@@ -10191,7 +10191,7 @@
       <x:c r="BP2" t="str">
         <x:v>Hierarchical Diffusion Policy 将任务规划与运动学感知的动作生成分层处理。</x:v>
       </x:c>
-      <x:c r="BQ2" t="str"/>
+      <x:c r="BQ2"/>
       <x:c r="BR2" t="str">
         <x:v>作者报告仿真和真机成功率高于所比较方法；具体数值见实验表。</x:v>
       </x:c>
@@ -10201,7 +10201,7 @@
       <x:c r="BT2" t="str">
         <x:v>需核验在两臂共享工作空间中的约束处理。</x:v>
       </x:c>
-      <x:c r="BU2" t="str"/>
+      <x:c r="BU2"/>
       <x:c r="BV2" t="str">
         <x:v>High：双臂普通夹爪也需要运动学约束和任务分解。</x:v>
       </x:c>
@@ -10320,7 +10320,7 @@
         <x:v>Real Robot 字段为 `Unknown`；Dataset、Benchmark、Robot Platform 中的 Unknown 继续保留，不从题名推断。</x:v>
       </x:c>
       <x:c r="AK3" t="str">
-        <x:v>Unknown / Needs Full-Paper Verification</x:v>
+        <x:v>论文报告在七项 RoboTwin 任务上较所比较 SOTA 提升 23.5%；具体指标定义见原文。</x:v>
       </x:c>
       <x:c r="AL3" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -10337,7 +10337,7 @@
       <x:c r="AP3" t="str">
         <x:v>B</x:v>
       </x:c>
-      <x:c r="AQ3" t="str"/>
+      <x:c r="AQ3"/>
       <x:c r="AR3" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
@@ -10401,7 +10401,7 @@
       </x:c>
       <x:c r="BM3"/>
       <x:c r="BN3" t="str">
-        <x:v>不同双臂任务的交互结构不同，统一耦合方式未必合适。</x:v>
+        <x:v>研究问题：不同双臂任务的交互结构不同，统一耦合方式未必合适。；之前方法的问题：始终联合预测双臂动作，可能忽略支撑手与操作手的不同职责。；核心思路：按任务交互特点设计解耦框架，让双臂策略分别处理可分解的部分并保持必要协调。；数据集与评测基准：RoboTwin 七项任务。；主要结果：论文报告在七项 RoboTwin 任务上较所比较 SOTA 提升 23.5%；具体指标定义见原文。；为什么重要：为联合预测与分臂预测的实验对照提供方法。；与当前项目的关系：High：普通夹爪常有支撑—操作分工。；主要局限：仿真 benchmark 上的优势仍需真机接触任务验证。</x:v>
       </x:c>
       <x:c r="BO3" t="str">
         <x:v>始终联合预测双臂动作，可能忽略支撑手与操作手的不同职责。</x:v>
@@ -10409,7 +10409,7 @@
       <x:c r="BP3" t="str">
         <x:v>按任务交互特点设计解耦框架，让双臂策略分别处理可分解的部分并保持必要协调。</x:v>
       </x:c>
-      <x:c r="BQ3" t="str"/>
+      <x:c r="BQ3"/>
       <x:c r="BR3" t="str">
         <x:v>论文报告在七项 RoboTwin 任务上较所比较 SOTA 提升 23.5%；具体指标定义见原文。</x:v>
       </x:c>
@@ -10419,7 +10419,7 @@
       <x:c r="BT3" t="str">
         <x:v>仿真 benchmark 上的优势仍需真机接触任务验证。</x:v>
       </x:c>
-      <x:c r="BU3" t="str"/>
+      <x:c r="BU3"/>
       <x:c r="BV3" t="str">
         <x:v>High：普通夹爪常有支撑—操作分工。</x:v>
       </x:c>
@@ -10538,7 +10538,7 @@
         <x:v>Real Robot 字段为 `Yes`；Dataset、Benchmark、Robot Platform 中的 Unknown 继续保留，不从题名推断。</x:v>
       </x:c>
       <x:c r="AK4" t="str">
-        <x:v>Unknown / Needs Full-Paper Verification</x:v>
+        <x:v>论文报告在上述设置中成功率高于 ACT 基线；具体差值需核对实验表。</x:v>
       </x:c>
       <x:c r="AL4" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -10555,7 +10555,7 @@
       <x:c r="AP4" t="str">
         <x:v>B</x:v>
       </x:c>
-      <x:c r="AQ4" t="str"/>
+      <x:c r="AQ4"/>
       <x:c r="AR4" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
@@ -10619,7 +10619,7 @@
       </x:c>
       <x:c r="BM4"/>
       <x:c r="BN4" t="str">
-        <x:v>复杂双臂任务需要预测动作，也需要理解后续视觉状态。</x:v>
+        <x:v>研究问题：复杂双臂任务需要预测动作，也需要理解后续视觉状态。；之前方法的问题：只学动作或只生成视频，可能无法协调两臂与物体变化。；核心思路：联合优化视频预测与双臂动作生成，让策略在想象未来场景的同时协调执行。；数据集与评测基准：两项仿真 benchmark 与一项真机设置。；主要结果：论文报告在上述设置中成功率高于 ACT 基线；具体差值需核对实验表。；为什么重要：可测试视觉预期是否改善双臂协调。；与当前项目的关系：High：双臂普通夹爪可对照 ACT 与带未来预测的策略。</x:v>
       </x:c>
       <x:c r="BO4" t="str">
         <x:v>只学动作或只生成视频，可能无法协调两臂与物体变化。</x:v>
@@ -10627,7 +10627,7 @@
       <x:c r="BP4" t="str">
         <x:v>联合优化视频预测与双臂动作生成，让策略在想象未来场景的同时协调执行。</x:v>
       </x:c>
-      <x:c r="BQ4" t="str"/>
+      <x:c r="BQ4"/>
       <x:c r="BR4" t="str">
         <x:v>论文报告在上述设置中成功率高于 ACT 基线；具体差值需核对实验表。</x:v>
       </x:c>
@@ -10637,7 +10637,7 @@
       <x:c r="BT4" t="str">
         <x:v>真机环境和失败类型的完整覆盖仍需查正文。</x:v>
       </x:c>
-      <x:c r="BU4" t="str"/>
+      <x:c r="BU4"/>
       <x:c r="BV4" t="str">
         <x:v>High：双臂普通夹爪可对照 ACT 与带未来预测的策略。</x:v>
       </x:c>
@@ -10775,7 +10775,7 @@
       <x:c r="AP5" t="str">
         <x:v>B</x:v>
       </x:c>
-      <x:c r="AQ5" t="str"/>
+      <x:c r="AQ5"/>
       <x:c r="AR5" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
@@ -10839,7 +10839,7 @@
       </x:c>
       <x:c r="BM5"/>
       <x:c r="BN5" t="str">
-        <x:v>灵巧操作需要结合视觉和触觉，而人类操作视频的机器人预训练多限于视觉与语言。</x:v>
+        <x:v>研究问题：灵巧操作需要结合视觉和触觉，而人类操作视频的机器人预训练多限于视觉与语言。；之前方法的问题：已有视频预训练主要在简单平行夹爪上部署，难覆盖触觉驱动的灵巧手任务。；核心思路：VTDexManip 提供视觉—触觉灵巧操作基准和强化学习技能框架，比较 18 种预训练或非预训练方法。；数据集与评测基准：六项复杂灵巧操作任务；论文比较 18 种方法。；为什么重要：有助于辨别触觉信息在灵巧操作中的作用。；与当前项目的关系：Medium：多模态融合可借鉴，但灵巧手任务与普通夹爪不同。；主要局限：摘要不能证明触觉收益能在无触觉或低成本普通夹爪上复现。</x:v>
       </x:c>
       <x:c r="BO5" t="str">
         <x:v>已有视频预训练主要在简单平行夹爪上部署，难覆盖触觉驱动的灵巧手任务。</x:v>
@@ -10847,7 +10847,7 @@
       <x:c r="BP5" t="str">
         <x:v>VTDexManip 提供视觉—触觉灵巧操作基准和强化学习技能框架，比较 18 种预训练或非预训练方法。</x:v>
       </x:c>
-      <x:c r="BQ5" t="str"/>
+      <x:c r="BQ5"/>
       <x:c r="BR5" t="str">
         <x:v>摘要给出六任务与 18 方法的评测设置；本轮未确认可直接引用的胜率。</x:v>
       </x:c>
@@ -10857,7 +10857,7 @@
       <x:c r="BT5" t="str">
         <x:v>摘要不能证明触觉收益能在无触觉或低成本普通夹爪上复现。</x:v>
       </x:c>
-      <x:c r="BU5" t="str"/>
+      <x:c r="BU5"/>
       <x:c r="BV5" t="str">
         <x:v>Medium：多模态融合可借鉴，但灵巧手任务与普通夹爪不同。</x:v>
       </x:c>
@@ -10976,7 +10976,7 @@
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
       </x:c>
       <x:c r="AK6" t="str">
-        <x:v>Unknown / Needs Full-Paper Verification</x:v>
+        <x:v>已核验摘要未给可安全复述的统一量化结果。</x:v>
       </x:c>
       <x:c r="AL6" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -10993,7 +10993,7 @@
       <x:c r="AP6" t="str">
         <x:v>B</x:v>
       </x:c>
-      <x:c r="AQ6" t="str"/>
+      <x:c r="AQ6"/>
       <x:c r="AR6" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
@@ -11057,7 +11057,7 @@
       </x:c>
       <x:c r="BM6"/>
       <x:c r="BN6" t="str">
-        <x:v>不同灵巧手硬件如何共享抓取能力。</x:v>
+        <x:v>研究问题：不同灵巧手硬件如何共享抓取能力。；之前方法的问题：各手型关节和动作维度不同，单一策略难直接复用。；核心思路：通过统一动作表示与强化学习，训练可跨不同灵巧手迁移的抓取策略。具体接口需核对正文。；主要结果：已核验摘要未给可安全复述的统一量化结果。；为什么重要：强调动作接口是跨本体迁移的关键。；与当前项目的关系：Medium：普通夹爪硬件不同，但统一动作表示的思路有用。；主要局限：跨手型实验不能直接证明跨普通夹爪双臂成功。</x:v>
       </x:c>
       <x:c r="BO6" t="str">
         <x:v>各手型关节和动作维度不同，单一策略难直接复用。</x:v>
@@ -11065,7 +11065,7 @@
       <x:c r="BP6" t="str">
         <x:v>通过统一动作表示与强化学习，训练可跨不同灵巧手迁移的抓取策略。具体接口需核对正文。</x:v>
       </x:c>
-      <x:c r="BQ6" t="str"/>
+      <x:c r="BQ6"/>
       <x:c r="BR6" t="str">
         <x:v>已核验摘要未给可安全复述的统一量化结果。</x:v>
       </x:c>
@@ -11075,7 +11075,7 @@
       <x:c r="BT6" t="str">
         <x:v>跨手型实验不能直接证明跨普通夹爪双臂成功。</x:v>
       </x:c>
-      <x:c r="BU6" t="str"/>
+      <x:c r="BU6"/>
       <x:c r="BV6" t="str">
         <x:v>Medium：普通夹爪硬件不同，但统一动作表示的思路有用。</x:v>
       </x:c>
@@ -11194,7 +11194,7 @@
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
       </x:c>
       <x:c r="AK7" t="str">
-        <x:v>Unknown / Needs Full-Paper Verification</x:v>
+        <x:v>作者报告所需真实样本最多减少约一个数量级，并优于基线微调方法；具体任务见论文。</x:v>
       </x:c>
       <x:c r="AL7" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -11211,7 +11211,7 @@
       <x:c r="AP7" t="str">
         <x:v>B</x:v>
       </x:c>
-      <x:c r="AQ7" t="str"/>
+      <x:c r="AQ7"/>
       <x:c r="AR7" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
@@ -11275,7 +11275,7 @@
       </x:c>
       <x:c r="BM7"/>
       <x:c r="BN7" t="str">
-        <x:v>机器人策略泛化需要大量高质量真实数据。</x:v>
+        <x:v>研究问题：机器人策略泛化需要大量高质量真实数据。；之前方法的问题：普通微调方法在真机新任务上仍需要较多示范。；核心思路：Simulation-Guided Fine-Tuning 从物理仿真提取结构先验，加速真机策略适配。；主要结果：作者报告所需真实样本最多减少约一个数量级，并优于基线微调方法；具体任务见论文。；为什么重要：提供小数据真机适配的可比较路线。；与当前项目的关系：High：双臂普通夹爪的真实示范预算有限。；主要局限：仿真先验对接触和相机变化的稳定性需在目标硬件验证。</x:v>
       </x:c>
       <x:c r="BO7" t="str">
         <x:v>普通微调方法在真机新任务上仍需要较多示范。</x:v>
@@ -11283,7 +11283,7 @@
       <x:c r="BP7" t="str">
         <x:v>Simulation-Guided Fine-Tuning 从物理仿真提取结构先验，加速真机策略适配。</x:v>
       </x:c>
-      <x:c r="BQ7" t="str"/>
+      <x:c r="BQ7"/>
       <x:c r="BR7" t="str">
         <x:v>作者报告所需真实样本最多减少约一个数量级，并优于基线微调方法；具体任务见论文。</x:v>
       </x:c>
@@ -11293,7 +11293,7 @@
       <x:c r="BT7" t="str">
         <x:v>仿真先验对接触和相机变化的稳定性需在目标硬件验证。</x:v>
       </x:c>
-      <x:c r="BU7" t="str"/>
+      <x:c r="BU7"/>
       <x:c r="BV7" t="str">
         <x:v>High：双臂普通夹爪的真实示范预算有限。</x:v>
       </x:c>
@@ -11410,7 +11410,7 @@
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
       </x:c>
       <x:c r="AK8" t="str">
-        <x:v>Unknown / Needs Full-Paper Verification</x:v>
+        <x:v>作者报告成功率比主要基线高 10 个百分点以上。</x:v>
       </x:c>
       <x:c r="AL8" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -11427,7 +11427,7 @@
       <x:c r="AP8" t="str">
         <x:v>B</x:v>
       </x:c>
-      <x:c r="AQ8" t="str"/>
+      <x:c r="AQ8"/>
       <x:c r="AR8" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
@@ -11491,7 +11491,7 @@
       </x:c>
       <x:c r="BM8"/>
       <x:c r="BN8" t="str">
-        <x:v>机器人灵巧手如何稳定跟踪人类参考动作。</x:v>
+        <x:v>研究问题：机器人灵巧手如何稳定跟踪人类参考动作。；之前方法的问题：人手参考轨迹与真实机器人控制之间存在可达性和动力学差异。；核心思路：整理大规模成功跟踪示范，训练可泛化的神经控制器对齐人类参考。；主要结果：作者报告成功率比主要基线高 10 个百分点以上。；为什么重要：提供从人体动作到机器人控制的跟踪基线。；与当前项目的关系：Medium：对双臂数据重定向有启发，但夹爪动作更简单。；主要局限：人手跟踪成功不等于真实物体操作成功。</x:v>
       </x:c>
       <x:c r="BO8" t="str">
         <x:v>人手参考轨迹与真实机器人控制之间存在可达性和动力学差异。</x:v>
@@ -11499,7 +11499,7 @@
       <x:c r="BP8" t="str">
         <x:v>整理大规模成功跟踪示范，训练可泛化的神经控制器对齐人类参考。</x:v>
       </x:c>
-      <x:c r="BQ8" t="str"/>
+      <x:c r="BQ8"/>
       <x:c r="BR8" t="str">
         <x:v>作者报告成功率比主要基线高 10 个百分点以上。</x:v>
       </x:c>
@@ -11509,7 +11509,7 @@
       <x:c r="BT8" t="str">
         <x:v>人手跟踪成功不等于真实物体操作成功。</x:v>
       </x:c>
-      <x:c r="BU8" t="str"/>
+      <x:c r="BU8"/>
       <x:c r="BV8" t="str">
         <x:v>Medium：对双臂数据重定向有启发，但夹爪动作更简单。</x:v>
       </x:c>
@@ -11628,7 +11628,7 @@
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
       </x:c>
       <x:c r="AK9" t="str">
-        <x:v>Unknown / Needs Full-Paper Verification</x:v>
+        <x:v>已核验摘要未给可安全复述的统一量化结果。</x:v>
       </x:c>
       <x:c r="AL9" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -11645,7 +11645,7 @@
       <x:c r="AP9" t="str">
         <x:v>B</x:v>
       </x:c>
-      <x:c r="AQ9" t="str"/>
+      <x:c r="AQ9"/>
       <x:c r="AR9" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
@@ -11709,7 +11709,7 @@
       </x:c>
       <x:c r="BM9"/>
       <x:c r="BN9" t="str">
-        <x:v>复杂操作把任务理解、感知和控制混在一起，难以稳定学习。</x:v>
+        <x:v>研究问题：复杂操作把任务理解、感知和控制混在一起，难以稳定学习。；之前方法的问题：开环概念提示不能根据新观测及时修正动作。；核心思路：AutoCGP 建立闭环、概念引导的模仿学习策略，让概念状态参与长任务决策。；主要结果：已核验摘要未给可安全复述的统一量化结果。；为什么重要：提示可以把可解释概念放在 VLA 与底层控制之间。；与当前项目的关系：Medium：有助于设计双臂任务状态检查。；主要局限：需核验概念误判和真机长任务失败案例。</x:v>
       </x:c>
       <x:c r="BO9" t="str">
         <x:v>开环概念提示不能根据新观测及时修正动作。</x:v>
@@ -11717,7 +11717,7 @@
       <x:c r="BP9" t="str">
         <x:v>AutoCGP 建立闭环、概念引导的模仿学习策略，让概念状态参与长任务决策。</x:v>
       </x:c>
-      <x:c r="BQ9" t="str"/>
+      <x:c r="BQ9"/>
       <x:c r="BR9" t="str">
         <x:v>已核验摘要未给可安全复述的统一量化结果。</x:v>
       </x:c>
@@ -11727,7 +11727,7 @@
       <x:c r="BT9" t="str">
         <x:v>需核验概念误判和真机长任务失败案例。</x:v>
       </x:c>
-      <x:c r="BU9" t="str"/>
+      <x:c r="BU9"/>
       <x:c r="BV9" t="str">
         <x:v>Medium：有助于设计双臂任务状态检查。</x:v>
       </x:c>
@@ -11844,7 +11844,7 @@
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
       </x:c>
       <x:c r="AK10" t="str">
-        <x:v>Unknown / Needs Full-Paper Verification</x:v>
+        <x:v>已核验摘要说明新环境与数据集；本轮不复述未经表格核实的成功率。</x:v>
       </x:c>
       <x:c r="AL10" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -11861,7 +11861,7 @@
       <x:c r="AP10" t="str">
         <x:v>B</x:v>
       </x:c>
-      <x:c r="AQ10" t="str"/>
+      <x:c r="AQ10"/>
       <x:c r="AR10" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
@@ -11925,7 +11925,7 @@
       </x:c>
       <x:c r="BM10"/>
       <x:c r="BN10" t="str">
-        <x:v>机器人需要操作具有多部件、关节及隐藏约束的铰接物体。</x:v>
+        <x:v>研究问题：机器人需要操作具有多部件、关节及隐藏约束的铰接物体。；之前方法的问题：以往数据集多关注从外观即可推断完整步骤的简单机构，对先解锁再开启的自适应机制覆盖不足。；核心思路：AdaManip 建立包含自适应机制的铰接物体环境与数据集，并研究相应策略学习；保险箱门先解锁再打开是论文中的例子。；数据集与评测基准：AdaManip 铰接物体仿真环境与数据集；规模需按全文核验。；主要结果：已核验摘要说明新环境与数据集；本轮不复述未经表格核实的成功率。；为什么重要：顺序依赖和隐藏状态对长程操作与失败恢复有参考价值。；与当前项目的关系：Medium：可借鉴机制约束任务设计；与本项目双臂普通夹爪平台的迁移需另测。；主要局限：摘要层级尚不能确认不同机制的泛化边界与真实机器人表现。</x:v>
       </x:c>
       <x:c r="BO10" t="str">
         <x:v>以往数据集多关注从外观即可推断完整步骤的简单机构，对先解锁再开启的自适应机制覆盖不足。</x:v>
@@ -11933,7 +11933,7 @@
       <x:c r="BP10" t="str">
         <x:v>AdaManip 建立包含自适应机制的铰接物体环境与数据集，并研究相应策略学习；保险箱门先解锁再打开是论文中的例子。</x:v>
       </x:c>
-      <x:c r="BQ10" t="str"/>
+      <x:c r="BQ10"/>
       <x:c r="BR10" t="str">
         <x:v>已核验摘要说明新环境与数据集；本轮不复述未经表格核实的成功率。</x:v>
       </x:c>
@@ -11943,7 +11943,7 @@
       <x:c r="BT10" t="str">
         <x:v>摘要层级尚不能确认不同机制的泛化边界与真实机器人表现。</x:v>
       </x:c>
-      <x:c r="BU10" t="str"/>
+      <x:c r="BU10"/>
       <x:c r="BV10" t="str">
         <x:v>Medium：可借鉴机制约束任务设计；与本项目双臂普通夹爪平台的迁移需另测。</x:v>
       </x:c>
@@ -12064,7 +12064,7 @@
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
       </x:c>
       <x:c r="AK11" t="str">
-        <x:v>Unknown / Needs Full-Paper Verification</x:v>
+        <x:v>论文摘要报告该分层设计改善任务执行；统一数字需查实验表。</x:v>
       </x:c>
       <x:c r="AL11" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -12081,7 +12081,7 @@
       <x:c r="AP11" t="str">
         <x:v>B</x:v>
       </x:c>
-      <x:c r="AQ11" t="str"/>
+      <x:c r="AQ11"/>
       <x:c r="AR11" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
@@ -12145,7 +12145,7 @@
       </x:c>
       <x:c r="BM11"/>
       <x:c r="BN11" t="str">
-        <x:v>开放世界操作需要利用基础模型知识，但机器人动作数据昂贵。</x:v>
+        <x:v>研究问题：开放世界操作需要利用基础模型知识，但机器人动作数据昂贵。；之前方法的问题：高层 VLM 不适合直接生成精细控制，低层策略又缺少广泛语义知识。；核心思路：HAMSTER 将高层任务理解与低层动作控制分工，降低双方负担。；主要结果：论文摘要报告该分层设计改善任务执行；统一数字需查实验表。；为什么重要：是比较分层规划和端到端 VLA 的阅读入口。；与当前项目的关系：High：双臂普通夹爪可能需要高层分工和低层安全控制。；主要局限：高低层接口不一致会造成目标误解或执行失败。</x:v>
       </x:c>
       <x:c r="BO11" t="str">
         <x:v>高层 VLM 不适合直接生成精细控制，低层策略又缺少广泛语义知识。</x:v>
@@ -12153,7 +12153,7 @@
       <x:c r="BP11" t="str">
         <x:v>HAMSTER 将高层任务理解与低层动作控制分工，降低双方负担。</x:v>
       </x:c>
-      <x:c r="BQ11" t="str"/>
+      <x:c r="BQ11"/>
       <x:c r="BR11" t="str">
         <x:v>论文摘要报告该分层设计改善任务执行；统一数字需查实验表。</x:v>
       </x:c>
@@ -12163,7 +12163,7 @@
       <x:c r="BT11" t="str">
         <x:v>高低层接口不一致会造成目标误解或执行失败。</x:v>
       </x:c>
-      <x:c r="BU11" t="str"/>
+      <x:c r="BU11"/>
       <x:c r="BV11" t="str">
         <x:v>High：双臂普通夹爪可能需要高层分工和低层安全控制。</x:v>
       </x:c>
@@ -12284,7 +12284,7 @@
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
       </x:c>
       <x:c r="AK12" t="str">
-        <x:v>Unknown / Needs Full-Paper Verification</x:v>
+        <x:v>当前摘要来源没有足以安全复述的统一量化结果。</x:v>
       </x:c>
       <x:c r="AL12" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -12301,7 +12301,7 @@
       <x:c r="AP12" t="str">
         <x:v>B</x:v>
       </x:c>
-      <x:c r="AQ12" t="str"/>
+      <x:c r="AQ12"/>
       <x:c r="AR12" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
@@ -12365,7 +12365,7 @@
       </x:c>
       <x:c r="BM12"/>
       <x:c r="BN12" t="str">
-        <x:v>机器人模仿学习通常需要大量专家示范。</x:v>
+        <x:v>研究问题：机器人模仿学习通常需要大量专家示范。；之前方法的问题：如果没有适合的空间表示，少量示范难以支持稳定动作生成。；核心思路：ET-SEED 研究带空间结构的扩散式操作策略；具体模块与输入输出需核验官方正文，不能只凭项目页推断。；主要结果：当前摘要来源没有足以安全复述的统一量化结果。；与当前项目的关系：Medium：与低示范双臂操作相关，但证据细节仍待查。；主要局限：原卡方法字段混入项目网址，需优先重新阅读正式方法章节。</x:v>
       </x:c>
       <x:c r="BO12" t="str">
         <x:v>如果没有适合的空间表示，少量示范难以支持稳定动作生成。</x:v>
@@ -12373,7 +12373,7 @@
       <x:c r="BP12" t="str">
         <x:v>ET-SEED 研究带空间结构的扩散式操作策略；具体模块与输入输出需核验官方正文，不能只凭项目页推断。</x:v>
       </x:c>
-      <x:c r="BQ12" t="str"/>
+      <x:c r="BQ12"/>
       <x:c r="BR12" t="str">
         <x:v>当前摘要来源没有足以安全复述的统一量化结果。</x:v>
       </x:c>
@@ -12383,7 +12383,7 @@
       <x:c r="BT12" t="str">
         <x:v>原卡方法字段混入项目网址，需优先重新阅读正式方法章节。</x:v>
       </x:c>
-      <x:c r="BU12" t="str"/>
+      <x:c r="BU12"/>
       <x:c r="BV12" t="str">
         <x:v>Medium：与低示范双臂操作相关，但证据细节仍待查。</x:v>
       </x:c>
@@ -12504,7 +12504,7 @@
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
       </x:c>
       <x:c r="AK13" t="str">
-        <x:v>Unknown / Needs Full-Paper Verification</x:v>
+        <x:v>作者报告在七项仿真任务上提升两类生成式策略表现；详细数值见论文。</x:v>
       </x:c>
       <x:c r="AL13" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -12521,7 +12521,7 @@
       <x:c r="AP13" t="str">
         <x:v>B</x:v>
       </x:c>
-      <x:c r="AQ13" t="str"/>
+      <x:c r="AQ13"/>
       <x:c r="AR13" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
@@ -12585,7 +12585,7 @@
       </x:c>
       <x:c r="BM13"/>
       <x:c r="BN13" t="str">
-        <x:v>Action Chunk 减少推理调用，却可能降低中途修正能力。</x:v>
+        <x:v>研究问题：Action Chunk 减少推理调用，却可能降低中途修正能力。；之前方法的问题：固定动作块开环执行与每步重新规划之间存在速度—反应性权衡。；核心思路：Bidirectional Decoding 在测试时调整生成式策略的动作解码，连接动作块与在线反馈。；主要结果：作者报告在七项仿真任务上提升两类生成式策略表现；详细数值见论文。；为什么重要：可用来设计低延迟但可中途纠正的双臂控制。；与当前项目的关系：High：真机操作需要在动作块速度和失败恢复之间折中。；主要局限：测试时解码的额外延迟和真机接触效果需核验。</x:v>
       </x:c>
       <x:c r="BO13" t="str">
         <x:v>固定动作块开环执行与每步重新规划之间存在速度—反应性权衡。</x:v>
@@ -12593,7 +12593,7 @@
       <x:c r="BP13" t="str">
         <x:v>Bidirectional Decoding 在测试时调整生成式策略的动作解码，连接动作块与在线反馈。</x:v>
       </x:c>
-      <x:c r="BQ13" t="str"/>
+      <x:c r="BQ13"/>
       <x:c r="BR13" t="str">
         <x:v>作者报告在七项仿真任务上提升两类生成式策略表现；详细数值见论文。</x:v>
       </x:c>
@@ -12603,7 +12603,7 @@
       <x:c r="BT13" t="str">
         <x:v>测试时解码的额外延迟和真机接触效果需核验。</x:v>
       </x:c>
-      <x:c r="BU13" t="str"/>
+      <x:c r="BU13"/>
       <x:c r="BV13" t="str">
         <x:v>High：真机操作需要在动作块速度和失败恢复之间折中。</x:v>
       </x:c>
@@ -12722,7 +12722,7 @@
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
       </x:c>
       <x:c r="AK14" t="str">
-        <x:v>Unknown / Needs Full-Paper Verification</x:v>
+        <x:v>作者报告在两项 benchmark 的八个任务上提升所比较策略；具体幅度需查论文表格。</x:v>
       </x:c>
       <x:c r="AL14" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -12739,7 +12739,7 @@
       <x:c r="AP14" t="str">
         <x:v>B</x:v>
       </x:c>
-      <x:c r="AQ14" t="str"/>
+      <x:c r="AQ14"/>
       <x:c r="AR14" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
@@ -12803,7 +12803,7 @@
       </x:c>
       <x:c r="BM14"/>
       <x:c r="BN14" t="str">
-        <x:v>大型模仿策略在新环境中仍可能出现局部失误。</x:v>
+        <x:v>研究问题：大型模仿策略在新环境中仍可能出现局部失误。；之前方法的问题：重新训练完整策略成本高，且难快速修复特定失败。；核心思路：Policy Decorator 在已有模仿策略外加模型无关的 residual policy，对执行动作进行局部修正。；数据集与评测基准：ManiSkill 与 Adroit，共八项任务。；主要结果：作者报告在两项 benchmark 的八个任务上提升所比较策略；具体幅度需查论文表格。；为什么重要：提供不改动主策略的轻量失败修正路线。；与当前项目的关系：High：可作为双臂 VLA 或 ACT 的附加纠错层。；主要局限：残差动作要经过安全限幅，避免真机接触中的突然修正。</x:v>
       </x:c>
       <x:c r="BO14" t="str">
         <x:v>重新训练完整策略成本高，且难快速修复特定失败。</x:v>
@@ -12811,7 +12811,7 @@
       <x:c r="BP14" t="str">
         <x:v>Policy Decorator 在已有模仿策略外加模型无关的 residual policy，对执行动作进行局部修正。</x:v>
       </x:c>
-      <x:c r="BQ14" t="str"/>
+      <x:c r="BQ14"/>
       <x:c r="BR14" t="str">
         <x:v>作者报告在两项 benchmark 的八个任务上提升所比较策略；具体幅度需查论文表格。</x:v>
       </x:c>
@@ -12821,7 +12821,7 @@
       <x:c r="BT14" t="str">
         <x:v>残差动作要经过安全限幅，避免真机接触中的突然修正。</x:v>
       </x:c>
-      <x:c r="BU14" t="str"/>
+      <x:c r="BU14"/>
       <x:c r="BV14" t="str">
         <x:v>High：可作为双臂 VLA 或 ACT 的附加纠错层。</x:v>
       </x:c>
@@ -12942,7 +12942,7 @@
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
       </x:c>
       <x:c r="AK15" t="str">
-        <x:v>Unknown / Needs Full-Paper Verification</x:v>
+        <x:v>论文报告 Diffusion Policy 有较强动作记忆，ACT 更偏动作插值；精确性能比较需看实验表。</x:v>
       </x:c>
       <x:c r="AL15" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -12959,7 +12959,7 @@
       <x:c r="AP15" t="str">
         <x:v>B</x:v>
       </x:c>
-      <x:c r="AQ15" t="str"/>
+      <x:c r="AQ15"/>
       <x:c r="AR15" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
@@ -13023,7 +13023,7 @@
       </x:c>
       <x:c r="BM15"/>
       <x:c r="BN15" t="str">
-        <x:v>Diffusion Policy 在少量示范下表现强，但其成功来源不够清楚。</x:v>
+        <x:v>研究问题：Diffusion Policy 在少量示范下表现强，但其成功来源不够清楚。；之前方法的问题：需要区分动作分布建模、记忆和插值各自的贡献。；核心思路：提出 Action Lookup Table 作为简单对照，分析 Diffusion Policy 与 ACT 在动作记忆和插值上的差异。；主要结果：论文报告 Diffusion Policy 有较强动作记忆，ACT 更偏动作插值；精确性能比较需看实验表。；为什么重要：防止把复杂模型的优势误判成真正泛化。；与当前项目的关系：High：项目需用未见物体和场景测试真实泛化。；主要局限：简单查表基线的有效性依赖示范分布；真机长任务仍需验证。</x:v>
       </x:c>
       <x:c r="BO15" t="str">
         <x:v>需要区分动作分布建模、记忆和插值各自的贡献。</x:v>
@@ -13031,7 +13031,7 @@
       <x:c r="BP15" t="str">
         <x:v>提出 Action Lookup Table 作为简单对照，分析 Diffusion Policy 与 ACT 在动作记忆和插值上的差异。</x:v>
       </x:c>
-      <x:c r="BQ15" t="str"/>
+      <x:c r="BQ15"/>
       <x:c r="BR15" t="str">
         <x:v>论文报告 Diffusion Policy 有较强动作记忆，ACT 更偏动作插值；精确性能比较需看实验表。</x:v>
       </x:c>
@@ -13041,7 +13041,7 @@
       <x:c r="BT15" t="str">
         <x:v>简单查表基线的有效性依赖示范分布；真机长任务仍需验证。</x:v>
       </x:c>
-      <x:c r="BU15" t="str"/>
+      <x:c r="BU15"/>
       <x:c r="BV15" t="str">
         <x:v>High：项目需用未见物体和场景测试真实泛化。</x:v>
       </x:c>
@@ -13158,7 +13158,7 @@
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
       </x:c>
       <x:c r="AK16" t="str">
-        <x:v>Unknown / Needs Full-Paper Verification</x:v>
+        <x:v>论文报告 LIBERO 无损加速约 1.5 倍、SimplerEnv 约 2.4 倍；平均成功率变化需按论文设置理解。</x:v>
       </x:c>
       <x:c r="AL16" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -13175,7 +13175,7 @@
       <x:c r="AP16" t="str">
         <x:v>B</x:v>
       </x:c>
-      <x:c r="AQ16" t="str"/>
+      <x:c r="AQ16"/>
       <x:c r="AR16" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
@@ -13239,7 +13239,7 @@
       </x:c>
       <x:c r="BM16"/>
       <x:c r="BN16" t="str">
-        <x:v>VLA 推理开销大，在线控制频率受限。</x:v>
+        <x:v>研究问题：VLA 推理开销大，在线控制频率受限。；之前方法的问题：固定模型规模与统一 token 处理会浪费简单状态的计算。；核心思路：SP-VLA 联合进行模型调度与 token 剪枝，在不同状态分配不同推理计算量。；数据集与评测基准：LIBERO、SimplerEnv 与论文列出的真机任务。；主要结果：论文报告 LIBERO 无损加速约 1.5 倍、SimplerEnv 约 2.4 倍；平均成功率变化需按论文设置理解。；为什么重要：为双臂 VLA 真机控制提供延迟优化方向。；与当前项目的关系：High：控制频率会影响双臂同步和失败恢复。；主要局限：剪枝造成的少数困难状态失误，需用真实任务失败案例检验。</x:v>
       </x:c>
       <x:c r="BO16" t="str">
         <x:v>固定模型规模与统一 token 处理会浪费简单状态的计算。</x:v>
@@ -13247,7 +13247,7 @@
       <x:c r="BP16" t="str">
         <x:v>SP-VLA 联合进行模型调度与 token 剪枝，在不同状态分配不同推理计算量。</x:v>
       </x:c>
-      <x:c r="BQ16" t="str"/>
+      <x:c r="BQ16"/>
       <x:c r="BR16" t="str">
         <x:v>论文报告 LIBERO 无损加速约 1.5 倍、SimplerEnv 约 2.4 倍；平均成功率变化需按论文设置理解。</x:v>
       </x:c>
@@ -13257,7 +13257,7 @@
       <x:c r="BT16" t="str">
         <x:v>剪枝造成的少数困难状态失误，需用真实任务失败案例检验。</x:v>
       </x:c>
-      <x:c r="BU16" t="str"/>
+      <x:c r="BU16"/>
       <x:c r="BV16" t="str">
         <x:v>High：控制频率会影响双臂同步和失败恢复。</x:v>
       </x:c>
@@ -13374,7 +13374,7 @@
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
       </x:c>
       <x:c r="AK17" t="str">
-        <x:v>Unknown / Needs Full-Paper Verification</x:v>
+        <x:v>作者报告 LIBERO 上达到先进水平，在 RoboTwin 和真机任务上优于所比较方法；完整数值见论文表格。</x:v>
       </x:c>
       <x:c r="AL17" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -13391,7 +13391,7 @@
       <x:c r="AP17" t="str">
         <x:v>B</x:v>
       </x:c>
-      <x:c r="AQ17" t="str"/>
+      <x:c r="AQ17"/>
       <x:c r="AR17" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
@@ -13455,7 +13455,7 @@
       </x:c>
       <x:c r="BM17"/>
       <x:c r="BN17" t="str">
-        <x:v>预训练 VLA 在新操作任务上仍需更有效的策略改进。</x:v>
+        <x:v>研究问题：预训练 VLA 在新操作任务上仍需更有效的策略改进。；之前方法的问题：只做监督微调可能难利用真实成功/失败反馈。；核心思路：SimpleVLA-RL 针对 VLA 设计高效强化学习与探索机制，继续优化操作策略。；数据集与评测基准：LIBERO、RoboTwin 与真机任务。；主要结果：作者报告 LIBERO 上达到先进水平，在 RoboTwin 和真机任务上优于所比较方法；完整数值见论文表格。；为什么重要：为 VLA 从示范学习走向结果反馈优化提供基线。；与当前项目的关系：High：双臂真机可关注安全约束下的策略改善。；主要局限：真机 RL 的数据成本、失败代价和安全边界必须单独评估。</x:v>
       </x:c>
       <x:c r="BO17" t="str">
         <x:v>只做监督微调可能难利用真实成功/失败反馈。</x:v>
@@ -13463,7 +13463,7 @@
       <x:c r="BP17" t="str">
         <x:v>SimpleVLA-RL 针对 VLA 设计高效强化学习与探索机制，继续优化操作策略。</x:v>
       </x:c>
-      <x:c r="BQ17" t="str"/>
+      <x:c r="BQ17"/>
       <x:c r="BR17" t="str">
         <x:v>作者报告 LIBERO 上达到先进水平，在 RoboTwin 和真机任务上优于所比较方法；完整数值见论文表格。</x:v>
       </x:c>
@@ -13473,7 +13473,7 @@
       <x:c r="BT17" t="str">
         <x:v>真机 RL 的数据成本、失败代价和安全边界必须单独评估。</x:v>
       </x:c>
-      <x:c r="BU17" t="str"/>
+      <x:c r="BU17"/>
       <x:c r="BV17" t="str">
         <x:v>High：双臂真机可关注安全约束下的策略改善。</x:v>
       </x:c>
@@ -13590,7 +13590,7 @@
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
       </x:c>
       <x:c r="AK18" t="str">
-        <x:v>Unknown / Needs Full-Paper Verification</x:v>
+        <x:v>在 “Item Above Ash Ketchum” 任务上，VLM2VLA 成功率为 60%，动作 token 消融为 30%；动作生成周期中位延迟为 6.1 s（Sec. 4.2.2、5.1）。</x:v>
       </x:c>
       <x:c r="AL18" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -13607,7 +13607,7 @@
       <x:c r="AP18" t="str">
         <x:v>A</x:v>
       </x:c>
-      <x:c r="AQ18" t="str"/>
+      <x:c r="AQ18"/>
       <x:c r="AR18" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
@@ -13671,7 +13671,7 @@
       </x:c>
       <x:c r="BM18"/>
       <x:c r="BN18" t="str">
-        <x:v>直接用机器人动作微调 VLM，可能损伤原有语言与多模态推理能力。</x:v>
+        <x:v>研究问题：直接用机器人动作微调 VLM，可能损伤原有语言与多模态推理能力。；之前方法的问题：直接把底层动作当作特殊 token 微调，可能与 VLM 的语言预训练形式不一致。；核心思路：VLM2VLA 先把底层动作写成自然语言形式，使机器人动作数据与 VLM 的原有输出形式更一致。；数据集与评测基准：BridgeData V2 遥操作轨迹被重新标成分层语言；标注成本和抽查方法见 Appendix 6.1。；主要结果：在 “Item Above Ash Ketchum” 任务上，VLM2VLA 成功率为 60%，动作 token 消融为 30%；动作生成周期中位延迟为 6.1 s（Sec. 4.2.2、5.1）。；为什么重要：提出一种尽量保留 VLM 推理能力的 VLA 微调接口；延迟也提示真机部署成本。；与当前项目的关系：High：有助于研究语言条件操作与 VLA 设计。；主要局限：作者报告动作生成中位延迟 6.1 s，实验控制维度和本体范围有限；复杂旋转及跨本体迁移仍需验证。</x:v>
       </x:c>
       <x:c r="BO18" t="str">
         <x:v>直接把底层动作当作特殊 token 微调，可能与 VLM 的语言预训练形式不一致。</x:v>
@@ -13679,7 +13679,7 @@
       <x:c r="BP18" t="str">
         <x:v>VLM2VLA 先把底层动作写成自然语言形式，使机器人动作数据与 VLM 的原有输出形式更一致。</x:v>
       </x:c>
-      <x:c r="BQ18" t="str"/>
+      <x:c r="BQ18"/>
       <x:c r="BR18" t="str">
         <x:v>在 “Item Above Ash Ketchum” 任务上，VLM2VLA 成功率为 60%，动作 token 消融为 30%；动作生成周期中位延迟为 6.1 s（Sec. 4.2.2、5.1）。</x:v>
       </x:c>
@@ -13689,7 +13689,7 @@
       <x:c r="BT18" t="str">
         <x:v>作者报告动作生成中位延迟 6.1 s，实验控制维度和本体范围有限；复杂旋转及跨本体迁移仍需验证。</x:v>
       </x:c>
-      <x:c r="BU18" t="str"/>
+      <x:c r="BU18"/>
       <x:c r="BV18" t="str">
         <x:v>High：有助于研究语言条件操作与 VLA 设计。</x:v>
       </x:c>
@@ -13808,7 +13808,7 @@
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
       </x:c>
       <x:c r="AK19" t="str">
-        <x:v>Unknown / Needs Full-Paper Verification</x:v>
+        <x:v>作者报告仿真与真机中执行更快，并保持任务表现；具体延迟和成功率需查论文。</x:v>
       </x:c>
       <x:c r="AL19" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -13825,7 +13825,7 @@
       <x:c r="AP19" t="str">
         <x:v>B</x:v>
       </x:c>
-      <x:c r="AQ19" t="str"/>
+      <x:c r="AQ19"/>
       <x:c r="AR19" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
@@ -13889,7 +13889,7 @@
       </x:c>
       <x:c r="BM19"/>
       <x:c r="BN19" t="str">
-        <x:v>机器人必须实时响应，但动作块策略可能错过中途变化。</x:v>
+        <x:v>研究问题：机器人必须实时响应，但动作块策略可能错过中途变化。；之前方法的问题：固定动作块执行快，却不容易及时修正已预测动作。；核心思路：REMAC 用 masked action chunking 学习对预训练策略动作的修正。；主要结果：作者报告仿真与真机中执行更快，并保持任务表现；具体延迟和成功率需查论文。；为什么重要：直接对应普通夹爪真机的实时执行与修正。；与当前项目的关系：High：可比较动作块长度、控制频率和失败恢复。；主要局限：在线修正是否产生不安全突变需在控制器层验证。</x:v>
       </x:c>
       <x:c r="BO19" t="str">
         <x:v>固定动作块执行快，却不容易及时修正已预测动作。</x:v>
@@ -13897,7 +13897,7 @@
       <x:c r="BP19" t="str">
         <x:v>REMAC 用 masked action chunking 学习对预训练策略动作的修正。</x:v>
       </x:c>
-      <x:c r="BQ19" t="str"/>
+      <x:c r="BQ19"/>
       <x:c r="BR19" t="str">
         <x:v>作者报告仿真与真机中执行更快，并保持任务表现；具体延迟和成功率需查论文。</x:v>
       </x:c>
@@ -13907,7 +13907,7 @@
       <x:c r="BT19" t="str">
         <x:v>在线修正是否产生不安全突变需在控制器层验证。</x:v>
       </x:c>
-      <x:c r="BU19" t="str"/>
+      <x:c r="BU19"/>
       <x:c r="BV19" t="str">
         <x:v>High：可比较动作块长度、控制频率和失败恢复。</x:v>
       </x:c>
@@ -14024,7 +14024,7 @@
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
       </x:c>
       <x:c r="AK20" t="str">
-        <x:v>Unknown / Needs Full-Paper Verification</x:v>
+        <x:v>作者报告理论分析能解释误差积累与这些训练措施的作用；具体界限与实验数字见原文。</x:v>
       </x:c>
       <x:c r="AL20" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -14041,7 +14041,7 @@
       <x:c r="AP20" t="str">
         <x:v>B</x:v>
       </x:c>
-      <x:c r="AQ20" t="str"/>
+      <x:c r="AQ20"/>
       <x:c r="AR20" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
@@ -14105,7 +14105,7 @@
       </x:c>
       <x:c r="BM20"/>
       <x:c r="BN20" t="str">
-        <x:v>模仿学习的单步误差会在长轨迹中不断积累。</x:v>
+        <x:v>研究问题：模仿学习的单步误差会在长轨迹中不断积累。；之前方法的问题：需要解释 Action Chunk 与数据增强为何能改善行为克隆，而不只看经验结果。；核心思路：用控制理论分析动作块和数据增强对误差传播的影响，并给出相应实验。；主要结果：作者报告理论分析能解释误差积累与这些训练措施的作用；具体界限与实验数字见原文。；为什么重要：为选择动作块长度和数据增强方式提供理论背景。；与当前项目的关系：High：双臂长任务的误差积累需要明确评测。；主要局限：理论假设与真机接触、感知噪声之间的差距需核对。</x:v>
       </x:c>
       <x:c r="BO20" t="str">
         <x:v>需要解释 Action Chunk 与数据增强为何能改善行为克隆，而不只看经验结果。</x:v>
@@ -14113,7 +14113,7 @@
       <x:c r="BP20" t="str">
         <x:v>用控制理论分析动作块和数据增强对误差传播的影响，并给出相应实验。</x:v>
       </x:c>
-      <x:c r="BQ20" t="str"/>
+      <x:c r="BQ20"/>
       <x:c r="BR20" t="str">
         <x:v>作者报告理论分析能解释误差积累与这些训练措施的作用；具体界限与实验数字见原文。</x:v>
       </x:c>
@@ -14123,7 +14123,7 @@
       <x:c r="BT20" t="str">
         <x:v>理论假设与真机接触、感知噪声之间的差距需核对。</x:v>
       </x:c>
-      <x:c r="BU20" t="str"/>
+      <x:c r="BU20"/>
       <x:c r="BV20" t="str">
         <x:v>High：双臂长任务的误差积累需要明确评测。</x:v>
       </x:c>
@@ -14242,7 +14242,7 @@
         <x:v>Real Robot 字段为 `Mixed`；Dataset、Benchmark、Robot Platform 中的 Unknown 继续保留，不从题名推断。</x:v>
       </x:c>
       <x:c r="AK21" t="str">
-        <x:v>Unknown / Needs Full-Paper Verification</x:v>
+        <x:v>AAAI 摘要报告在两项仿真 benchmark 和真机任务中优于所比较方法；未给统一量化值。</x:v>
       </x:c>
       <x:c r="AL21" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -14259,7 +14259,7 @@
       <x:c r="AP21" t="str">
         <x:v>B</x:v>
       </x:c>
-      <x:c r="AQ21" t="str"/>
+      <x:c r="AQ21"/>
       <x:c r="AR21" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
@@ -14323,7 +14323,7 @@
       </x:c>
       <x:c r="BM21"/>
       <x:c r="BN21" t="str">
-        <x:v>长任务的高层指令与短时动作之间容易出现不一致。</x:v>
+        <x:v>研究问题：长任务的高层指令与短时动作之间容易出现不一致。；之前方法的问题：只用全局指令条件化扩散策略，难以保证每段动作符合当前小技能。；核心思路：SDP 把复杂任务拆成八种 primitive skills，用 VLM 提取离散状态表示，再由轻量 router 选择技能条件化扩散策略。；输入：官方摘要给出任务/数据类型；具体模型张量与接口需核对方法章节。；输出与动作：官方摘要未明确列出完整控制接口；需核对论文方法或代码。；数据集与评测基准：两项仿真 benchmark 与真机操作评测。；主要结果：AAAI 摘要报告在两项仿真 benchmark 和真机任务中优于所比较方法；未给统一量化值。；为什么重要：可作为“高层技能调度 + 低层动作生成”的双臂基线。；与当前项目的关系：Medium：方法可借鉴，但迁移到当前双臂硬件需验证。；主要局限：本段基于官方摘要；未覆盖全文失败案例、完整 Baseline 与方法消融。</x:v>
       </x:c>
       <x:c r="BO21" t="str">
         <x:v>只用全局指令条件化扩散策略，难以保证每段动作符合当前小技能。</x:v>
@@ -14331,7 +14331,7 @@
       <x:c r="BP21" t="str">
         <x:v>SDP 把复杂任务拆成八种 primitive skills，用 VLM 提取离散状态表示，再由轻量 router 选择技能条件化扩散策略。</x:v>
       </x:c>
-      <x:c r="BQ21" t="str"/>
+      <x:c r="BQ21"/>
       <x:c r="BR21" t="str">
         <x:v>AAAI 摘要报告在两项仿真 benchmark 和真机任务中优于所比较方法；未给统一量化值。</x:v>
       </x:c>
@@ -14341,7 +14341,7 @@
       <x:c r="BT21" t="str">
         <x:v>本段基于官方摘要；未覆盖全文失败案例、完整 Baseline 与方法消融。</x:v>
       </x:c>
-      <x:c r="BU21" t="str"/>
+      <x:c r="BU21"/>
       <x:c r="BV21" t="str">
         <x:v>Medium：方法可借鉴，但迁移到当前双臂硬件需验证。</x:v>
       </x:c>
@@ -14460,7 +14460,7 @@
         <x:v>Real Robot 字段为 `Mixed`；Dataset、Benchmark、Robot Platform 中的 Unknown 继续保留，不从题名推断。</x:v>
       </x:c>
       <x:c r="AK22" t="str">
-        <x:v>Unknown / Needs Full-Paper Verification</x:v>
+        <x:v>AAAI 摘要报告仿真与真机超过 100 项任务，成功率相对基线最高提升 41%；另发布 80 多项仿真任务。</x:v>
       </x:c>
       <x:c r="AL22" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -14477,7 +14477,7 @@
       <x:c r="AP22" t="str">
         <x:v>B</x:v>
       </x:c>
-      <x:c r="AQ22" t="str"/>
+      <x:c r="AQ22"/>
       <x:c r="AR22" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
@@ -14541,7 +14541,7 @@
       </x:c>
       <x:c r="BM22"/>
       <x:c r="BN22" t="str">
-        <x:v>多任务模仿学习策略需要可靠动作，也需要用少量示范适应未见任务。</x:v>
+        <x:v>研究问题：多任务模仿学习策略需要可靠动作，也需要用少量示范适应未见任务。；之前方法的问题：只根据当前状态重建动作，可能缺少对动作视觉后果的预测。；核心思路：FoAM 输入多模态目标，在动作重建之外加入 foresight augmentation，让策略利用预期视觉结果。；输入：官方摘要给出任务/数据类型；具体模型张量与接口需核对方法章节。；输出与动作：官方摘要未明确列出完整控制接口；需核对论文方法或代码。；数据集与评测基准：超过 100 项仿真/真机任务；官方发布的仿真任务套件。；主要结果：AAAI 摘要报告仿真与真机超过 100 项任务，成功率相对基线最高提升 41%；另发布 80 多项仿真任务。；为什么重要：可比较“预见动作后果”是否帮助双臂动作前验证。；与当前项目的关系：Medium：方法可借鉴，但迁移到当前双臂硬件需验证。；主要局限：本段基于官方摘要；未覆盖全文失败案例、完整 Baseline 与方法消融。</x:v>
       </x:c>
       <x:c r="BO22" t="str">
         <x:v>只根据当前状态重建动作，可能缺少对动作视觉后果的预测。</x:v>
@@ -14549,7 +14549,7 @@
       <x:c r="BP22" t="str">
         <x:v>FoAM 输入多模态目标，在动作重建之外加入 foresight augmentation，让策略利用预期视觉结果。</x:v>
       </x:c>
-      <x:c r="BQ22" t="str"/>
+      <x:c r="BQ22"/>
       <x:c r="BR22" t="str">
         <x:v>AAAI 摘要报告仿真与真机超过 100 项任务，成功率相对基线最高提升 41%；另发布 80 多项仿真任务。</x:v>
       </x:c>
@@ -14559,7 +14559,7 @@
       <x:c r="BT22" t="str">
         <x:v>本段基于官方摘要；未覆盖全文失败案例、完整 Baseline 与方法消融。</x:v>
       </x:c>
-      <x:c r="BU22" t="str"/>
+      <x:c r="BU22"/>
       <x:c r="BV22" t="str">
         <x:v>Medium：方法可借鉴，但迁移到当前双臂硬件需验证。</x:v>
       </x:c>
@@ -14678,7 +14678,7 @@
         <x:v>Real Robot 字段为 `Mixed`；Dataset、Benchmark、Robot Platform 中的 Unknown 继续保留，不从题名推断。</x:v>
       </x:c>
       <x:c r="AK23" t="str">
-        <x:v>Unknown / Needs Full-Paper Verification</x:v>
+        <x:v>AAAI 官方摘要报告仿真与实体机器人验证，并进行了规划器和蒸馏方法消融；未给统一数值。</x:v>
       </x:c>
       <x:c r="AL23" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -14695,7 +14695,7 @@
       <x:c r="AP23" t="str">
         <x:v>B</x:v>
       </x:c>
-      <x:c r="AQ23" t="str"/>
+      <x:c r="AQ23"/>
       <x:c r="AR23" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
@@ -14759,7 +14759,7 @@
       </x:c>
       <x:c r="BM23"/>
       <x:c r="BN23" t="str">
-        <x:v>长时序接触操作既要完成任务，也要避免过大接触力损伤物体。</x:v>
+        <x:v>研究问题：长时序接触操作既要完成任务，也要避免过大接触力损伤物体。；之前方法的问题：真机专家示范昂贵，分层技能和安全约束难以同时获得。；核心思路：在仿真中用带力约束的 RL 训练原子技能，再由 VLM 规划任务，最后蒸馏到视觉—触觉 Diffusion Policy。；输入：官方摘要给出任务/数据类型；具体模型张量与接口需核对方法章节。；输出与动作：官方摘要未明确列出完整控制接口；需核对论文方法或代码。；数据集与评测基准：仿真与实体机器人接触操作任务。；主要结果：AAAI 官方摘要报告仿真与实体机器人验证，并进行了规划器和蒸馏方法消融；未给统一数值。；为什么重要：为普通夹爪的接触安全和低成本技能数据生成提供参考。；与当前项目的关系：Medium：方法可借鉴，但迁移到当前双臂硬件需验证。；主要局限：本段基于官方摘要；未覆盖全文失败案例、完整 Baseline 与方法消融。</x:v>
       </x:c>
       <x:c r="BO23" t="str">
         <x:v>真机专家示范昂贵，分层技能和安全约束难以同时获得。</x:v>
@@ -14767,7 +14767,7 @@
       <x:c r="BP23" t="str">
         <x:v>在仿真中用带力约束的 RL 训练原子技能，再由 VLM 规划任务，最后蒸馏到视觉—触觉 Diffusion Policy。</x:v>
       </x:c>
-      <x:c r="BQ23" t="str"/>
+      <x:c r="BQ23"/>
       <x:c r="BR23" t="str">
         <x:v>AAAI 官方摘要报告仿真与实体机器人验证，并进行了规划器和蒸馏方法消融；未给统一数值。</x:v>
       </x:c>
@@ -14777,7 +14777,7 @@
       <x:c r="BT23" t="str">
         <x:v>本段基于官方摘要；未覆盖全文失败案例、完整 Baseline 与方法消融。</x:v>
       </x:c>
-      <x:c r="BU23" t="str"/>
+      <x:c r="BU23"/>
       <x:c r="BV23" t="str">
         <x:v>Medium：方法可借鉴，但迁移到当前双臂硬件需验证。</x:v>
       </x:c>
@@ -14896,7 +14896,7 @@
         <x:v>Real Robot 字段为 `Yes`；Dataset、Benchmark、Robot Platform 中的 Unknown 继续保留，不从题名推断。</x:v>
       </x:c>
       <x:c r="AK24" t="str">
-        <x:v>Unknown / Needs Full-Paper Verification</x:v>
+        <x:v>AAAI 官方摘要报告泛化测试成功率 87%，数据效率约为所比较 SOTA 的 5 倍。</x:v>
       </x:c>
       <x:c r="AL24" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -14913,7 +14913,7 @@
       <x:c r="AP24" t="str">
         <x:v>B</x:v>
       </x:c>
-      <x:c r="AQ24" t="str"/>
+      <x:c r="AQ24"/>
       <x:c r="AR24" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
@@ -14977,7 +14977,7 @@
       </x:c>
       <x:c r="BM24"/>
       <x:c r="BN24" t="str">
-        <x:v>通用人形机器人操作常依赖大量示范，未见场景中的几何推理仍薄弱。</x:v>
+        <x:v>研究问题：通用人形机器人操作常依赖大量示范，未见场景中的几何推理仍薄弱。；之前方法的问题：单纯数据驱动策略难以高效建模机器人与目标之间的空间关系。；核心思路：RGMP 用带几何先验的技能选择器推理子任务，再用递归 Gaussian 网络生成动作。；输入：官方摘要给出任务/数据类型；具体模型张量与接口需核对方法章节。；输出与动作：官方摘要未明确列出完整控制接口；需核对论文方法或代码。；数据集与评测基准：人形机器人与桌面机器人操作评测。；主要结果：AAAI 官方摘要报告泛化测试成功率 87%，数据效率约为所比较 SOTA 的 5 倍。；为什么重要：可启发双臂任务的几何关系表示，但硬件差异需要单独验证。；与当前项目的关系：Medium：方法可借鉴，但迁移到当前双臂硬件需验证。；主要局限：本段基于官方摘要；未覆盖全文失败案例、完整 Baseline 与方法消融。</x:v>
       </x:c>
       <x:c r="BO24" t="str">
         <x:v>单纯数据驱动策略难以高效建模机器人与目标之间的空间关系。</x:v>
@@ -14985,7 +14985,7 @@
       <x:c r="BP24" t="str">
         <x:v>RGMP 用带几何先验的技能选择器推理子任务，再用递归 Gaussian 网络生成动作。</x:v>
       </x:c>
-      <x:c r="BQ24" t="str"/>
+      <x:c r="BQ24"/>
       <x:c r="BR24" t="str">
         <x:v>AAAI 官方摘要报告泛化测试成功率 87%，数据效率约为所比较 SOTA 的 5 倍。</x:v>
       </x:c>
@@ -14995,7 +14995,7 @@
       <x:c r="BT24" t="str">
         <x:v>本段基于官方摘要；未覆盖全文失败案例、完整 Baseline 与方法消融。</x:v>
       </x:c>
-      <x:c r="BU24" t="str"/>
+      <x:c r="BU24"/>
       <x:c r="BV24" t="str">
         <x:v>Medium：方法可借鉴，但迁移到当前双臂硬件需验证。</x:v>
       </x:c>
@@ -15112,7 +15112,7 @@
         <x:v>Real Robot 字段为 `Unknown`；Dataset、Benchmark、Robot Platform 中的 Unknown 继续保留，不从题名推断。</x:v>
       </x:c>
       <x:c r="AK25" t="str">
-        <x:v>Unknown / Needs Full-Paper Verification</x:v>
+        <x:v>官方 AAAI 摘要报告三类仿真与真机任务上的成功率和新物体泛化优于对比方法，并展示跨机械手部署；摘要未给统一数值。</x:v>
       </x:c>
       <x:c r="AL25" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -15129,7 +15129,7 @@
       <x:c r="AP25" t="str">
         <x:v>B</x:v>
       </x:c>
-      <x:c r="AQ25" t="str"/>
+      <x:c r="AQ25"/>
       <x:c r="AR25" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
@@ -15193,7 +15193,7 @@
       </x:c>
       <x:c r="BM25"/>
       <x:c r="BN25" t="str">
-        <x:v>多指灵巧手操作不同物体时，任务奖励设计和跨手型泛化都很难。</x:v>
+        <x:v>研究问题：多指灵巧手操作不同物体时，任务奖励设计和跨手型泛化都很难。；之前方法的问题：只模仿人手轨迹，难以把物体未来状态变成通用训练目标。；核心思路：从人—物交互数据学习物体运动先验，预测未来物体状态，再把它用于强化学习奖励。；输入：官方摘要给出任务/数据类型；具体模型张量与接口需核对方法章节。；输出与动作：官方摘要未明确列出完整控制接口；需核对论文方法或代码。；数据集与评测基准：三类灵巧操作任务；具体数据集见官方论文。；主要结果：官方 AAAI 摘要报告三类仿真与真机任务上的成功率和新物体泛化优于对比方法，并展示跨机械手部署；摘要未给统一数值。；为什么重要：提出“预测物体状态作为奖励”的路线，可与普通夹爪任务中的目标状态验证比较。；与当前项目的关系：Medium：方法可借鉴，但迁移到当前双臂硬件需验证。；主要局限：本段基于官方摘要；未覆盖全文失败案例、完整 Baseline 与方法消融。</x:v>
       </x:c>
       <x:c r="BO25" t="str">
         <x:v>只模仿人手轨迹，难以把物体未来状态变成通用训练目标。</x:v>
@@ -15201,7 +15201,7 @@
       <x:c r="BP25" t="str">
         <x:v>从人—物交互数据学习物体运动先验，预测未来物体状态，再把它用于强化学习奖励。</x:v>
       </x:c>
-      <x:c r="BQ25" t="str"/>
+      <x:c r="BQ25"/>
       <x:c r="BR25" t="str">
         <x:v>官方 AAAI 摘要报告三类仿真与真机任务上的成功率和新物体泛化优于对比方法，并展示跨机械手部署；摘要未给统一数值。</x:v>
       </x:c>
@@ -15211,7 +15211,7 @@
       <x:c r="BT25" t="str">
         <x:v>本段基于官方摘要；未覆盖全文失败案例、完整 Baseline 与方法消融。</x:v>
       </x:c>
-      <x:c r="BU25" t="str"/>
+      <x:c r="BU25"/>
       <x:c r="BV25" t="str">
         <x:v>Medium：方法可借鉴，但迁移到当前双臂硬件需验证。</x:v>
       </x:c>
@@ -15347,7 +15347,7 @@
       <x:c r="AP26" t="str">
         <x:v>B</x:v>
       </x:c>
-      <x:c r="AQ26" t="str"/>
+      <x:c r="AQ26"/>
       <x:c r="AR26" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
@@ -15411,7 +15411,7 @@
       </x:c>
       <x:c r="BM26"/>
       <x:c r="BN26" t="str">
-        <x:v>模仿学习的数据采集通常需要多次人工示范和环境复位。</x:v>
+        <x:v>研究问题：模仿学习的数据采集通常需要多次人工示范和环境复位。；之前方法的问题：昂贵的人工监督限制新任务的快速适配。；核心思路：MILES 从单条示范出发，以自主自监督方式继续收集训练经验。；为什么重要：可以减少普通夹爪真机的示范采集成本。；与当前项目的关系：High：项目可测自主采集是否安全且节省人力。；主要局限：自主收集失败轨迹时的安全和错误标签需要严格控制。</x:v>
       </x:c>
       <x:c r="BO26" t="str">
         <x:v>昂贵的人工监督限制新任务的快速适配。</x:v>
@@ -15419,7 +15419,7 @@
       <x:c r="BP26" t="str">
         <x:v>MILES 从单条示范出发，以自主自监督方式继续收集训练经验。</x:v>
       </x:c>
-      <x:c r="BQ26" t="str"/>
+      <x:c r="BQ26"/>
       <x:c r="BR26" t="str">
         <x:v>作者报告在单示范、无需反复复位的约束下优于对比方法；统一数字需查正文。</x:v>
       </x:c>
@@ -15429,7 +15429,7 @@
       <x:c r="BT26" t="str">
         <x:v>自主收集失败轨迹时的安全和错误标签需要严格控制。</x:v>
       </x:c>
-      <x:c r="BU26" t="str"/>
+      <x:c r="BU26"/>
       <x:c r="BV26" t="str">
         <x:v>High：项目可测自主采集是否安全且节省人力。</x:v>
       </x:c>
@@ -15548,7 +15548,7 @@
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
       </x:c>
       <x:c r="AK27" t="str">
-        <x:v>Unknown / Needs Full-Paper Verification</x:v>
+        <x:v>作者报告在 RLBench 上达到有竞争力的结果；完整数值需看论文表格。</x:v>
       </x:c>
       <x:c r="AL27" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -15565,7 +15565,7 @@
       <x:c r="AP27" t="str">
         <x:v>B</x:v>
       </x:c>
-      <x:c r="AQ27" t="str"/>
+      <x:c r="AQ27"/>
       <x:c r="AR27" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
@@ -15629,7 +15629,7 @@
       </x:c>
       <x:c r="BM27"/>
       <x:c r="BN27" t="str">
-        <x:v>少量示范条件下，策略输入和动作生成目标的选择影响操作表现。</x:v>
+        <x:v>研究问题：少量示范条件下，策略输入和动作生成目标的选择影响操作表现。；之前方法的问题：二维图像可能丢失三维几何；迭代生成动作又增加延迟。；核心思路：PointFlowMatch 从点云观测学习条件 Flow Matching 策略，生成机器人操作动作。；数据集与评测基准：RLBench。；主要结果：作者报告在 RLBench 上达到有竞争力的结果；完整数值需看论文表格。；为什么重要：为点云输入加流式动作生成提供基线。；与当前项目的关系：Medium：双夹爪三维定位可借鉴，但真机点云质量需检查。；主要局限：仿真点云与真机深度噪声之间可能存在差距。</x:v>
       </x:c>
       <x:c r="BO27" t="str">
         <x:v>二维图像可能丢失三维几何；迭代生成动作又增加延迟。</x:v>
@@ -15637,7 +15637,7 @@
       <x:c r="BP27" t="str">
         <x:v>PointFlowMatch 从点云观测学习条件 Flow Matching 策略，生成机器人操作动作。</x:v>
       </x:c>
-      <x:c r="BQ27" t="str"/>
+      <x:c r="BQ27"/>
       <x:c r="BR27" t="str">
         <x:v>作者报告在 RLBench 上达到有竞争力的结果；完整数值需看论文表格。</x:v>
       </x:c>
@@ -15647,7 +15647,7 @@
       <x:c r="BT27" t="str">
         <x:v>仿真点云与真机深度噪声之间可能存在差距。</x:v>
       </x:c>
-      <x:c r="BU27" t="str"/>
+      <x:c r="BU27"/>
       <x:c r="BV27" t="str">
         <x:v>Medium：双夹爪三维定位可借鉴，但真机点云质量需检查。</x:v>
       </x:c>
@@ -15766,7 +15766,7 @@
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
       </x:c>
       <x:c r="AK28" t="str">
-        <x:v>Unknown / Needs Full-Paper Verification</x:v>
+        <x:v>作者报告相对其他结合模仿学习、强化学习与规划的方法取得更好表现；数字见原文。</x:v>
       </x:c>
       <x:c r="AL28" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -15783,7 +15783,7 @@
       <x:c r="AP28" t="str">
         <x:v>B</x:v>
       </x:c>
-      <x:c r="AQ28" t="str"/>
+      <x:c r="AQ28"/>
       <x:c r="AR28" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
@@ -15847,7 +15847,7 @@
       </x:c>
       <x:c r="BM28"/>
       <x:c r="BN28" t="str">
-        <x:v>复杂操作任务需要既能规划步骤，又能执行可靠动作。</x:v>
+        <x:v>研究问题：复杂操作任务需要既能规划步骤，又能执行可靠动作。；之前方法的问题：只用模仿学习或强化学习，可能难以组织长时序任务。；核心思路：SPIRE 先用 Task and Motion Planning（TAMP）分解任务，再将学习策略用于具体执行。；主要结果：作者报告相对其他结合模仿学习、强化学习与规划的方法取得更好表现；数字见原文。；为什么重要：提供规划与学习策略组合的系统基线。；与当前项目的关系：High：双臂长任务可测试分解与执行后检查。；主要局限：规划模型与真实接触差异可能造成执行偏差。</x:v>
       </x:c>
       <x:c r="BO28" t="str">
         <x:v>只用模仿学习或强化学习，可能难以组织长时序任务。</x:v>
@@ -15855,7 +15855,7 @@
       <x:c r="BP28" t="str">
         <x:v>SPIRE 先用 Task and Motion Planning（TAMP）分解任务，再将学习策略用于具体执行。</x:v>
       </x:c>
-      <x:c r="BQ28" t="str"/>
+      <x:c r="BQ28"/>
       <x:c r="BR28" t="str">
         <x:v>作者报告相对其他结合模仿学习、强化学习与规划的方法取得更好表现；数字见原文。</x:v>
       </x:c>
@@ -15865,7 +15865,7 @@
       <x:c r="BT28" t="str">
         <x:v>规划模型与真实接触差异可能造成执行偏差。</x:v>
       </x:c>
-      <x:c r="BU28" t="str"/>
+      <x:c r="BU28"/>
       <x:c r="BV28" t="str">
         <x:v>High：双臂长任务可测试分解与执行后检查。</x:v>
       </x:c>
@@ -15984,7 +15984,7 @@
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
       </x:c>
       <x:c r="AK29" t="str">
-        <x:v>Unknown / Needs Full-Paper Verification</x:v>
+        <x:v>已核验摘要未给可安全复述的统一量化结果。</x:v>
       </x:c>
       <x:c r="AL29" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -16001,7 +16001,7 @@
       <x:c r="AP29" t="str">
         <x:v>B</x:v>
       </x:c>
-      <x:c r="AQ29" t="str"/>
+      <x:c r="AQ29"/>
       <x:c r="AR29" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
@@ -16065,7 +16065,7 @@
       </x:c>
       <x:c r="BM29"/>
       <x:c r="BN29" t="str">
-        <x:v>开放、易用的遥操作工具是低成本收集机器人示范的基础。</x:v>
+        <x:v>研究问题：开放、易用的遥操作工具是低成本收集机器人示范的基础。；之前方法的问题：复杂专有系统阻碍示范采集的复现和共享。；核心思路：OPEN TEACH 用 VR 头显与混合现实界面进行直观机器人遥操作。；主要结果：已核验摘要未给可安全复述的统一量化结果。；为什么重要：为建立本项目示范采集流程提供开源系统参考。；与当前项目的关系：High：可比较普通夹爪双臂遥操作的学习成本。；主要局限：VR 延迟、标定和安全机制需按目标硬件核验。</x:v>
       </x:c>
       <x:c r="BO29" t="str">
         <x:v>复杂专有系统阻碍示范采集的复现和共享。</x:v>
@@ -16073,7 +16073,7 @@
       <x:c r="BP29" t="str">
         <x:v>OPEN TEACH 用 VR 头显与混合现实界面进行直观机器人遥操作。</x:v>
       </x:c>
-      <x:c r="BQ29" t="str"/>
+      <x:c r="BQ29"/>
       <x:c r="BR29" t="str">
         <x:v>已核验摘要未给可安全复述的统一量化结果。</x:v>
       </x:c>
@@ -16083,7 +16083,7 @@
       <x:c r="BT29" t="str">
         <x:v>VR 延迟、标定和安全机制需按目标硬件核验。</x:v>
       </x:c>
-      <x:c r="BU29" t="str"/>
+      <x:c r="BU29"/>
       <x:c r="BV29" t="str">
         <x:v>High：可比较普通夹爪双臂遥操作的学习成本。</x:v>
       </x:c>
@@ -16219,7 +16219,7 @@
       <x:c r="AP30" t="str">
         <x:v>B</x:v>
       </x:c>
-      <x:c r="AQ30" t="str"/>
+      <x:c r="AQ30"/>
       <x:c r="AR30" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
@@ -16283,7 +16283,7 @@
       </x:c>
       <x:c r="BM30"/>
       <x:c r="BN30" t="str">
-        <x:v>新任务缺少目标域示范时，机器人如何零样本操作。</x:v>
+        <x:v>研究问题：新任务缺少目标域示范时，机器人如何零样本操作。；之前方法的问题：为每项任务单独收集示范的成本太高。；核心思路：RAM 检索相关已有行为，再把它迁移到当前物体和操作设置。；为什么重要：展示通过检索复用经验而非每次重训的路径。；与当前项目的关系：Medium：可用于双臂任务的技能复用，但动作适配需验证。；主要局限：检索到的动作若与当前夹爪或物体不匹配，可能无法执行。</x:v>
       </x:c>
       <x:c r="BO30" t="str">
         <x:v>为每项任务单独收集示范的成本太高。</x:v>
@@ -16291,7 +16291,7 @@
       <x:c r="BP30" t="str">
         <x:v>RAM 检索相关已有行为，再把它迁移到当前物体和操作设置。</x:v>
       </x:c>
-      <x:c r="BQ30" t="str"/>
+      <x:c r="BQ30"/>
       <x:c r="BR30" t="str">
         <x:v>作者报告仿真与真机评测中优于所比较方法；具体数字需查正文。</x:v>
       </x:c>
@@ -16301,7 +16301,7 @@
       <x:c r="BT30" t="str">
         <x:v>检索到的动作若与当前夹爪或物体不匹配，可能无法执行。</x:v>
       </x:c>
-      <x:c r="BU30" t="str"/>
+      <x:c r="BU30"/>
       <x:c r="BV30" t="str">
         <x:v>Medium：可用于双臂任务的技能复用，但动作适配需验证。</x:v>
       </x:c>
@@ -16420,7 +16420,7 @@
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
       </x:c>
       <x:c r="AK31" t="str">
-        <x:v>Unknown / Needs Full-Paper Verification</x:v>
+        <x:v>作者报告利用多样野外示范可迁移到未见环境；具体数字需查论文。</x:v>
       </x:c>
       <x:c r="AL31" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -16437,7 +16437,7 @@
       <x:c r="AP31" t="str">
         <x:v>B</x:v>
       </x:c>
-      <x:c r="AQ31" t="str"/>
+      <x:c r="AQ31"/>
       <x:c r="AR31" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
@@ -16501,7 +16501,7 @@
       </x:c>
       <x:c r="BM31"/>
       <x:c r="BN31" t="str">
-        <x:v>接触声音包含物体和交互信息，但普通示范数据很少记录音频。</x:v>
+        <x:v>研究问题：接触声音包含物体和交互信息，但普通示范数据很少记录音频。；之前方法的问题：只用视觉可能难判断接触是否成功或物体是否滑动。；核心思路：ManiWAV 用 ear-in-hand 装置采集带同步音频的人类野外示范。；主要结果：作者报告利用多样野外示范可迁移到未见环境；具体数字需查论文。；为什么重要：声音可成为普通夹爪动作后成功验证的补充信号。；与当前项目的关系：Medium：取决于本项目是否能低成本采集同步音频。；主要局限：人类示范音频与机器人电机噪声分布不同。</x:v>
       </x:c>
       <x:c r="BO31" t="str">
         <x:v>只用视觉可能难判断接触是否成功或物体是否滑动。</x:v>
@@ -16509,7 +16509,7 @@
       <x:c r="BP31" t="str">
         <x:v>ManiWAV 用 ear-in-hand 装置采集带同步音频的人类野外示范。</x:v>
       </x:c>
-      <x:c r="BQ31" t="str"/>
+      <x:c r="BQ31"/>
       <x:c r="BR31" t="str">
         <x:v>作者报告利用多样野外示范可迁移到未见环境；具体数字需查论文。</x:v>
       </x:c>
@@ -16519,7 +16519,7 @@
       <x:c r="BT31" t="str">
         <x:v>人类示范音频与机器人电机噪声分布不同。</x:v>
       </x:c>
-      <x:c r="BU31" t="str"/>
+      <x:c r="BU31"/>
       <x:c r="BV31" t="str">
         <x:v>Medium：取决于本项目是否能低成本采集同步音频。</x:v>
       </x:c>
@@ -16638,7 +16638,7 @@
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
       </x:c>
       <x:c r="AK32" t="str">
-        <x:v>Unknown / Needs Full-Paper Verification</x:v>
+        <x:v>官方摘要报告比现有行为克隆方法具有更强的视觉环境泛化；摘要未给出统一成功率数字。</x:v>
       </x:c>
       <x:c r="AL32" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -16655,7 +16655,7 @@
       <x:c r="AP32" t="str">
         <x:v>B</x:v>
       </x:c>
-      <x:c r="AQ32" t="str"/>
+      <x:c r="AQ32"/>
       <x:c r="AR32" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
@@ -16719,7 +16719,7 @@
       </x:c>
       <x:c r="BM32"/>
       <x:c r="BN32" t="str">
-        <x:v>机器人模仿学习策略在新视觉环境中往往难以保持稳定表现。</x:v>
+        <x:v>研究问题：机器人模仿学习策略在新视觉环境中往往难以保持稳定表现。；之前方法的问题：少量机器人示范不足以覆盖环境外观变化；直接行为克隆的泛化有限。；核心思路：Dreamitate 用人类任务示范微调视频扩散模型，再利用生成的视频辅助学习视觉运动策略。；数据集与评测基准：论文评估四项复杂度递增的操作任务；具体任务设置见 CoRL 论文。；主要结果：官方摘要报告比现有行为克隆方法具有更强的视觉环境泛化；摘要未给出统一成功率数字。；为什么重要：探索大规模视频生成模型如何补充少量机器人示范。；与当前项目的关系：Medium：可借鉴视频到动作的数据利用方式，但双臂普通夹爪需单独验证。；主要局限：已核验摘要未明确列出全部失败情形；需读实验和局限章节。</x:v>
       </x:c>
       <x:c r="BO32" t="str">
         <x:v>少量机器人示范不足以覆盖环境外观变化；直接行为克隆的泛化有限。</x:v>
@@ -16727,7 +16727,7 @@
       <x:c r="BP32" t="str">
         <x:v>Dreamitate 用人类任务示范微调视频扩散模型，再利用生成的视频辅助学习视觉运动策略。</x:v>
       </x:c>
-      <x:c r="BQ32" t="str"/>
+      <x:c r="BQ32"/>
       <x:c r="BR32" t="str">
         <x:v>官方摘要报告比现有行为克隆方法具有更强的视觉环境泛化；摘要未给出统一成功率数字。</x:v>
       </x:c>
@@ -16737,7 +16737,7 @@
       <x:c r="BT32" t="str">
         <x:v>已核验摘要未明确列出全部失败情形；需读实验和局限章节。</x:v>
       </x:c>
-      <x:c r="BU32" t="str"/>
+      <x:c r="BU32"/>
       <x:c r="BV32" t="str">
         <x:v>Medium：可借鉴视频到动作的数据利用方式，但双臂普通夹爪需单独验证。</x:v>
       </x:c>
@@ -16856,7 +16856,7 @@
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
       </x:c>
       <x:c r="AK33" t="str">
-        <x:v>Unknown / Needs Full-Paper Verification</x:v>
+        <x:v>作者报告在真机系统上可用较少示范学到有效策略；具体数值见原文。</x:v>
       </x:c>
       <x:c r="AL33" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -16873,7 +16873,7 @@
       <x:c r="AP33" t="str">
         <x:v>B</x:v>
       </x:c>
-      <x:c r="AQ33" t="str"/>
+      <x:c r="AQ33"/>
       <x:c r="AR33" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
@@ -16937,7 +16937,7 @@
       </x:c>
       <x:c r="BM33"/>
       <x:c r="BN33" t="str">
-        <x:v>扩散策略善于表达多种动作，但少量数据下泛化仍有挑战。</x:v>
+        <x:v>研究问题：扩散策略善于表达多种动作，但少量数据下泛化仍有挑战。；之前方法的问题：不利用任务的几何对称性会增加学习样本需求。；核心思路：Equivariant Diffusion Policy 把空间对称性引入扩散式动作策略。；主要结果：作者报告在真机系统上可用较少示范学到有效策略；具体数值见原文。；为什么重要：将几何先验与生成式动作结合。；与当前项目的关系：Medium：可用于双夹爪空间变化实验。；主要局限：需要核验所假设的对称性在复杂接触和双臂协作中是否成立。</x:v>
       </x:c>
       <x:c r="BO33" t="str">
         <x:v>不利用任务的几何对称性会增加学习样本需求。</x:v>
@@ -16945,7 +16945,7 @@
       <x:c r="BP33" t="str">
         <x:v>Equivariant Diffusion Policy 把空间对称性引入扩散式动作策略。</x:v>
       </x:c>
-      <x:c r="BQ33" t="str"/>
+      <x:c r="BQ33"/>
       <x:c r="BR33" t="str">
         <x:v>作者报告在真机系统上可用较少示范学到有效策略；具体数值见原文。</x:v>
       </x:c>
@@ -16955,7 +16955,7 @@
       <x:c r="BT33" t="str">
         <x:v>需要核验所假设的对称性在复杂接触和双臂协作中是否成立。</x:v>
       </x:c>
-      <x:c r="BU33" t="str"/>
+      <x:c r="BU33"/>
       <x:c r="BV33" t="str">
         <x:v>Medium：可用于双夹爪空间变化实验。</x:v>
       </x:c>
@@ -17074,7 +17074,7 @@
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
       </x:c>
       <x:c r="AK34" t="str">
-        <x:v>Unknown / Needs Full-Paper Verification</x:v>
+        <x:v>作者报告在六项移动操作任务的多个真机变化中展示泛化；具体数值见论文。</x:v>
       </x:c>
       <x:c r="AL34" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -17091,7 +17091,7 @@
       <x:c r="AP34" t="str">
         <x:v>B</x:v>
       </x:c>
-      <x:c r="AQ34" t="str"/>
+      <x:c r="AQ34"/>
       <x:c r="AR34" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
@@ -17155,7 +17155,7 @@
       </x:c>
       <x:c r="BM34"/>
       <x:c r="BN34" t="str">
-        <x:v>少量示范条件下，操作策略要面对物体和空间变化。</x:v>
+        <x:v>研究问题：少量示范条件下，操作策略要面对物体和空间变化。；之前方法的问题：普通网络不一定充分利用旋转、平移等几何对称性。；核心思路：EquiBot 在模仿学习策略中加入等变结构，提高数据效率和空间泛化。；主要结果：作者报告在六项移动操作任务的多个真机变化中展示泛化；具体数值见论文。；为什么重要：提供以结构先验替代部分示范数据的路线。；与当前项目的关系：Medium：双臂空间变化可能受益，但平台不同。；主要局限：移动操作结果不能直接替代普通夹爪双臂评测。</x:v>
       </x:c>
       <x:c r="BO34" t="str">
         <x:v>普通网络不一定充分利用旋转、平移等几何对称性。</x:v>
@@ -17163,7 +17163,7 @@
       <x:c r="BP34" t="str">
         <x:v>EquiBot 在模仿学习策略中加入等变结构，提高数据效率和空间泛化。</x:v>
       </x:c>
-      <x:c r="BQ34" t="str"/>
+      <x:c r="BQ34"/>
       <x:c r="BR34" t="str">
         <x:v>作者报告在六项移动操作任务的多个真机变化中展示泛化；具体数值见论文。</x:v>
       </x:c>
@@ -17173,7 +17173,7 @@
       <x:c r="BT34" t="str">
         <x:v>移动操作结果不能直接替代普通夹爪双臂评测。</x:v>
       </x:c>
-      <x:c r="BU34" t="str"/>
+      <x:c r="BU34"/>
       <x:c r="BV34" t="str">
         <x:v>Medium：双臂空间变化可能受益，但平台不同。</x:v>
       </x:c>
@@ -17292,7 +17292,7 @@
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
       </x:c>
       <x:c r="AK35" t="str">
-        <x:v>Unknown / Needs Full-Paper Verification</x:v>
+        <x:v>论文报告与二维表示、回归及其他设计的消融比较，完整数字应以原论文表格为准。</x:v>
       </x:c>
       <x:c r="AL35" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -17309,7 +17309,7 @@
       <x:c r="AP35" t="str">
         <x:v>B</x:v>
       </x:c>
-      <x:c r="AQ35" t="str"/>
+      <x:c r="AQ35"/>
       <x:c r="AR35" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
@@ -17373,7 +17373,7 @@
       </x:c>
       <x:c r="BM35"/>
       <x:c r="BN35" t="str">
-        <x:v>机器人动作有多种合理解，二维图像策略对三维几何理解不足。</x:v>
+        <x:v>研究问题：机器人动作有多种合理解，二维图像策略对三维几何理解不足。；之前方法的问题：直接回归动作或只用二维表示，可能难以表达多模态三维操作。；核心思路：3D Diffuser Actor 在三维场景表示上生成动作，并通过扩散模型刻画多种可行轨迹。；主要结果：论文报告与二维表示、回归及其他设计的消融比较，完整数字应以原论文表格为准。；为什么重要：是比较三维感知与生成式动作的基础方法。；与当前项目的关系：High：可为双普通夹爪的三维目标位姿生成提供基线。；主要局限：摘要不足以判断不同真机接触和双臂协调任务的完整覆盖。</x:v>
       </x:c>
       <x:c r="BO35" t="str">
         <x:v>直接回归动作或只用二维表示，可能难以表达多模态三维操作。</x:v>
@@ -17381,7 +17381,7 @@
       <x:c r="BP35" t="str">
         <x:v>3D Diffuser Actor 在三维场景表示上生成动作，并通过扩散模型刻画多种可行轨迹。</x:v>
       </x:c>
-      <x:c r="BQ35" t="str"/>
+      <x:c r="BQ35"/>
       <x:c r="BR35" t="str">
         <x:v>论文报告与二维表示、回归及其他设计的消融比较，完整数字应以原论文表格为准。</x:v>
       </x:c>
@@ -17391,7 +17391,7 @@
       <x:c r="BT35" t="str">
         <x:v>摘要不足以判断不同真机接触和双臂协调任务的完整覆盖。</x:v>
       </x:c>
-      <x:c r="BU35" t="str"/>
+      <x:c r="BU35"/>
       <x:c r="BV35" t="str">
         <x:v>High：可为双普通夹爪的三维目标位姿生成提供基线。</x:v>
       </x:c>
@@ -17510,7 +17510,7 @@
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
       </x:c>
       <x:c r="AK36" t="str">
-        <x:v>Unknown / Needs Full-Paper Verification</x:v>
+        <x:v>摘要支持 40 项任务这一规模；具体算法胜率需查实验表格。</x:v>
       </x:c>
       <x:c r="AL36" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -17527,7 +17527,7 @@
       <x:c r="AP36" t="str">
         <x:v>B</x:v>
       </x:c>
-      <x:c r="AQ36" t="str"/>
+      <x:c r="AQ36"/>
       <x:c r="AR36" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
@@ -17591,7 +17591,7 @@
       </x:c>
       <x:c r="BM36"/>
       <x:c r="BN36" t="str">
-        <x:v>缺少覆盖家庭场景移动双臂操作的示范驱动学习基准。</x:v>
+        <x:v>研究问题：缺少覆盖家庭场景移动双臂操作的示范驱动学习基准。；核心思路：BiGym 提供移动双臂学习环境，包含从目标触达到厨房清理的 40 项任务。；主要结果：摘要支持 40 项任务这一规模；具体算法胜率需查实验表格。；为什么重要：将双臂协作、移动性和家庭长程任务放在同一评测入口。；与当前项目的关系：High：适合筛选普通夹爪双臂任务及示范学习基线。；主要局限：是否能迁移至本项目固定平台与硬件配置，摘要不能确定。</x:v>
       </x:c>
       <x:c r="BO36" t="str">
         <x:v>已核验摘要未明确说明；需查阅论文方法与实验章节。</x:v>
@@ -17599,7 +17599,7 @@
       <x:c r="BP36" t="str">
         <x:v>BiGym 提供移动双臂学习环境，包含从目标触达到厨房清理的 40 项任务。</x:v>
       </x:c>
-      <x:c r="BQ36" t="str"/>
+      <x:c r="BQ36"/>
       <x:c r="BR36" t="str">
         <x:v>摘要支持 40 项任务这一规模；具体算法胜率需查实验表格。</x:v>
       </x:c>
@@ -17609,7 +17609,7 @@
       <x:c r="BT36" t="str">
         <x:v>是否能迁移至本项目固定平台与硬件配置，摘要不能确定。</x:v>
       </x:c>
-      <x:c r="BU36" t="str"/>
+      <x:c r="BU36"/>
       <x:c r="BV36" t="str">
         <x:v>High：适合筛选普通夹爪双臂任务及示范学习基线。</x:v>
       </x:c>
@@ -17728,7 +17728,7 @@
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
       </x:c>
       <x:c r="AK37" t="str">
-        <x:v>Unknown / Needs Full-Paper Verification</x:v>
+        <x:v>作者报告在仿真任务上优于所比较基线；摘要未给统一量化值。</x:v>
       </x:c>
       <x:c r="AL37" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -17745,7 +17745,7 @@
       <x:c r="AP37" t="str">
         <x:v>B</x:v>
       </x:c>
-      <x:c r="AQ37" t="str"/>
+      <x:c r="AQ37"/>
       <x:c r="AR37" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
@@ -17809,7 +17809,7 @@
       </x:c>
       <x:c r="BM37"/>
       <x:c r="BN37" t="str">
-        <x:v>细粒度双臂操作需要在三维场景中同时定位两只手的关键区域。</x:v>
+        <x:v>研究问题：细粒度双臂操作需要在三维场景中同时定位两只手的关键区域。；之前方法的问题：直接从全局图像预测高维双臂动作，可能忽略局部空间线索。；核心思路：VoxAct-B 用 VLM 关注关键区域，再在体素空间中生成语言条件的双臂动作。；数据集与评测基准：仿真细粒度双臂任务；真机覆盖需进一步核验。；主要结果：作者报告在仿真任务上优于所比较基线；摘要未给统一量化值。；为什么重要：把视觉目标定位与双臂三维动作表示连接起来。；与当前项目的关系：High：可参考两只普通夹爪的空间目标表示。；主要局限：体素分辨率与真机延迟、遮挡和接触误差需验证。</x:v>
       </x:c>
       <x:c r="BO37" t="str">
         <x:v>直接从全局图像预测高维双臂动作，可能忽略局部空间线索。</x:v>
@@ -17817,7 +17817,7 @@
       <x:c r="BP37" t="str">
         <x:v>VoxAct-B 用 VLM 关注关键区域，再在体素空间中生成语言条件的双臂动作。</x:v>
       </x:c>
-      <x:c r="BQ37" t="str"/>
+      <x:c r="BQ37"/>
       <x:c r="BR37" t="str">
         <x:v>作者报告在仿真任务上优于所比较基线；摘要未给统一量化值。</x:v>
       </x:c>
@@ -17827,7 +17827,7 @@
       <x:c r="BT37" t="str">
         <x:v>体素分辨率与真机延迟、遮挡和接触误差需验证。</x:v>
       </x:c>
-      <x:c r="BU37" t="str"/>
+      <x:c r="BU37"/>
       <x:c r="BV37" t="str">
         <x:v>High：可参考两只普通夹爪的空间目标表示。</x:v>
       </x:c>
@@ -17946,7 +17946,7 @@
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
       </x:c>
       <x:c r="AK38" t="str">
-        <x:v>Unknown / Needs Full-Paper Verification</x:v>
+        <x:v>已核验摘要未给可安全复述的统一量化结果；具体任务表现见论文评测。</x:v>
       </x:c>
       <x:c r="AL38" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -17963,7 +17963,7 @@
       <x:c r="AP38" t="str">
         <x:v>B</x:v>
       </x:c>
-      <x:c r="AQ38" t="str"/>
+      <x:c r="AQ38"/>
       <x:c r="AR38" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
@@ -18027,7 +18027,7 @@
       </x:c>
       <x:c r="BM38"/>
       <x:c r="BN38" t="str">
-        <x:v>双臂移动操作要求机器人在移动底座上同时协调两只机械臂。</x:v>
+        <x:v>研究问题：双臂移动操作要求机器人在移动底座上同时协调两只机械臂。；之前方法的问题：传统固定底座示范不能直接覆盖全身移动与操作的耦合。；核心思路：Mobile ALOHA 建立双臂移动操作系统，并采集示范训练端到端模仿策略。；数据集与评测基准：Mobile ALOHA 平台上的移动双臂操作示范。；主要结果：已核验摘要未给可安全复述的统一量化结果；具体任务表现见论文评测。；为什么重要：提供移动双臂真机系统和示范采集的完整参照。；与当前项目的关系：High：双臂与普通夹爪相关；移动底座部分需与本项目区分。；主要局限：移动和操作同时变化，难单独归因哪一环节带来失败。</x:v>
       </x:c>
       <x:c r="BO38" t="str">
         <x:v>传统固定底座示范不能直接覆盖全身移动与操作的耦合。</x:v>
@@ -18035,7 +18035,7 @@
       <x:c r="BP38" t="str">
         <x:v>Mobile ALOHA 建立双臂移动操作系统，并采集示范训练端到端模仿策略。</x:v>
       </x:c>
-      <x:c r="BQ38" t="str"/>
+      <x:c r="BQ38"/>
       <x:c r="BR38" t="str">
         <x:v>已核验摘要未给可安全复述的统一量化结果；具体任务表现见论文评测。</x:v>
       </x:c>
@@ -18045,7 +18045,7 @@
       <x:c r="BT38" t="str">
         <x:v>移动和操作同时变化，难单独归因哪一环节带来失败。</x:v>
       </x:c>
-      <x:c r="BU38" t="str"/>
+      <x:c r="BU38"/>
       <x:c r="BV38" t="str">
         <x:v>High：双臂与普通夹爪相关；移动底座部分需与本项目区分。</x:v>
       </x:c>
@@ -18164,7 +18164,7 @@
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
       </x:c>
       <x:c r="AK39" t="str">
-        <x:v>Unknown / Needs Full-Paper Verification</x:v>
+        <x:v>论文报告扩大数据规模与扩散策略组合能完成更具挑战性的操作；具体成功率见原文实验。</x:v>
       </x:c>
       <x:c r="AL39" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -18181,7 +18181,7 @@
       <x:c r="AP39" t="str">
         <x:v>B</x:v>
       </x:c>
-      <x:c r="AQ39" t="str"/>
+      <x:c r="AQ39"/>
       <x:c r="AR39" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
@@ -18245,7 +18245,7 @@
       </x:c>
       <x:c r="BM39"/>
       <x:c r="BN39" t="str">
-        <x:v>复杂灵巧操作需要足够多的真机示范和能表达多种动作的策略。</x:v>
+        <x:v>研究问题：复杂灵巧操作需要足够多的真机示范和能表达多种动作的策略。；之前方法的问题：小规模模仿学习数据难以覆盖长任务与接触变化。；核心思路：在 ALOHA 2 平台扩大数据采集，再用 Diffusion Policy 等表达能力较强的策略学习操作。；数据集与评测基准：ALOHA 2 真机示范和论文列出的复杂操作任务。；主要结果：论文报告扩大数据规模与扩散策略组合能完成更具挑战性的操作；具体成功率见原文实验。；为什么重要：提供真机双臂示范规模与策略能力的实证对照。；与当前项目的关系：High：硬件形态与本项目双臂普通夹爪接近。；主要局限：不同任务、相机与夹爪配置之间的迁移仍需单独评测。</x:v>
       </x:c>
       <x:c r="BO39" t="str">
         <x:v>小规模模仿学习数据难以覆盖长任务与接触变化。</x:v>
@@ -18253,7 +18253,7 @@
       <x:c r="BP39" t="str">
         <x:v>在 ALOHA 2 平台扩大数据采集，再用 Diffusion Policy 等表达能力较强的策略学习操作。</x:v>
       </x:c>
-      <x:c r="BQ39" t="str"/>
+      <x:c r="BQ39"/>
       <x:c r="BR39" t="str">
         <x:v>论文报告扩大数据规模与扩散策略组合能完成更具挑战性的操作；具体成功率见原文实验。</x:v>
       </x:c>
@@ -18263,7 +18263,7 @@
       <x:c r="BT39" t="str">
         <x:v>不同任务、相机与夹爪配置之间的迁移仍需单独评测。</x:v>
       </x:c>
-      <x:c r="BU39" t="str"/>
+      <x:c r="BU39"/>
       <x:c r="BV39" t="str">
         <x:v>High：硬件形态与本项目双臂普通夹爪接近。</x:v>
       </x:c>
@@ -18380,7 +18380,7 @@
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
       </x:c>
       <x:c r="AK40" t="str">
-        <x:v>Unknown / Needs Full-Paper Verification</x:v>
+        <x:v>CoRL 官方摘要报告能操作功能相同但外形不同的新工具，还可生成训练视觉运动策略的 rollout；未给统一成功率。</x:v>
       </x:c>
       <x:c r="AL40" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -18397,7 +18397,7 @@
       <x:c r="AP40" t="str">
         <x:v>B</x:v>
       </x:c>
-      <x:c r="AQ40" t="str"/>
+      <x:c r="AQ40"/>
       <x:c r="AR40" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
@@ -18461,7 +18461,7 @@
       </x:c>
       <x:c r="BM40"/>
       <x:c r="BN40" t="str">
-        <x:v>从一段人类工具操作视频迁移到几何形状不同的新工具仍很困难。</x:v>
+        <x:v>研究问题：从一段人类工具操作视频迁移到几何形状不同的新工具仍很困难。；之前方法的问题：只按外形对齐的模仿方法难以抓住工具的功能对应关系。；核心思路：MimicFunc 用三维功能关键点建立 function frame，使机器人从单段 RGB-D 人类视频迁移工具操作。；输入：官方摘要给出任务/数据类型；具体模型张量与接口需核对方法章节。；输出与动作：官方摘要未明确列出完整控制接口；需核对论文方法或代码。；数据集与评测基准：单段 RGB-D 人类视频与新工具操作任务。；主要结果：CoRL 官方摘要报告能操作功能相同但外形不同的新工具，还可生成训练视觉运动策略的 rollout；未给统一成功率。；为什么重要：为 Human Video → Robot Action 提供功能对齐思路，普通夹爪适配仍需验证。；与当前项目的关系：Medium：方法可借鉴，但迁移到当前双臂硬件需验证。；主要局限：本段基于官方摘要；未覆盖全文失败案例、完整 Baseline 与方法消融。</x:v>
       </x:c>
       <x:c r="BO40" t="str">
         <x:v>只按外形对齐的模仿方法难以抓住工具的功能对应关系。</x:v>
@@ -18469,7 +18469,7 @@
       <x:c r="BP40" t="str">
         <x:v>MimicFunc 用三维功能关键点建立 function frame，使机器人从单段 RGB-D 人类视频迁移工具操作。</x:v>
       </x:c>
-      <x:c r="BQ40" t="str"/>
+      <x:c r="BQ40"/>
       <x:c r="BR40" t="str">
         <x:v>CoRL 官方摘要报告能操作功能相同但外形不同的新工具，还可生成训练视觉运动策略的 rollout；未给统一成功率。</x:v>
       </x:c>
@@ -18479,7 +18479,7 @@
       <x:c r="BT40" t="str">
         <x:v>本段基于官方摘要；未覆盖全文失败案例、完整 Baseline 与方法消融。</x:v>
       </x:c>
-      <x:c r="BU40" t="str"/>
+      <x:c r="BU40"/>
       <x:c r="BV40" t="str">
         <x:v>Medium：方法可借鉴，但迁移到当前双臂硬件需验证。</x:v>
       </x:c>
@@ -18596,7 +18596,7 @@
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
       </x:c>
       <x:c r="AK41" t="str">
-        <x:v>Unknown / Needs Full-Paper Verification</x:v>
+        <x:v>已核验摘要未提供可安全复述的统一量化结果。</x:v>
       </x:c>
       <x:c r="AL41" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -18613,7 +18613,7 @@
       <x:c r="AP41" t="str">
         <x:v>B</x:v>
       </x:c>
-      <x:c r="AQ41" t="str"/>
+      <x:c r="AQ41"/>
       <x:c r="AR41" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
@@ -18677,7 +18677,7 @@
       </x:c>
       <x:c r="BM41"/>
       <x:c r="BN41" t="str">
-        <x:v>双臂扩散策略生成的动作可能违反安全和协调约束。</x:v>
+        <x:v>研究问题：双臂扩散策略生成的动作可能违反安全和协调约束。；之前方法的问题：训练完成后的策略不一定知道新的障碍物或当前碰撞边界。；核心思路：SafeBimanual 在测试时对预训练扩散策略的轨迹进行优化，加入安全约束。；数据集与评测基准：双臂扩散策略的测试时轨迹优化任务；具体 benchmark 见论文。；主要结果：已核验摘要未提供可安全复述的统一量化结果。；为什么重要：将安全约束放在策略与真机控制器之间，便于与现有策略组合。；与当前项目的关系：High：双臂普通夹爪真机部署需要碰撞与工作空间限制。；主要局限：优化耗时、约束保守程度和任务成功率之间的权衡需实测。</x:v>
       </x:c>
       <x:c r="BO41" t="str">
         <x:v>训练完成后的策略不一定知道新的障碍物或当前碰撞边界。</x:v>
@@ -18685,7 +18685,7 @@
       <x:c r="BP41" t="str">
         <x:v>SafeBimanual 在测试时对预训练扩散策略的轨迹进行优化，加入安全约束。</x:v>
       </x:c>
-      <x:c r="BQ41" t="str"/>
+      <x:c r="BQ41"/>
       <x:c r="BR41" t="str">
         <x:v>已核验摘要未提供可安全复述的统一量化结果。</x:v>
       </x:c>
@@ -18695,7 +18695,7 @@
       <x:c r="BT41" t="str">
         <x:v>优化耗时、约束保守程度和任务成功率之间的权衡需实测。</x:v>
       </x:c>
-      <x:c r="BU41" t="str"/>
+      <x:c r="BU41"/>
       <x:c r="BV41" t="str">
         <x:v>High：双臂普通夹爪真机部署需要碰撞与工作空间限制。</x:v>
       </x:c>
@@ -18812,7 +18812,7 @@
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
       </x:c>
       <x:c r="AK42" t="str">
-        <x:v>Unknown / Needs Full-Paper Verification</x:v>
+        <x:v>官方摘要报告成功率优于所比较基线，并对未见设置有一定泛化；未给统一数值。</x:v>
       </x:c>
       <x:c r="AL42" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -18829,7 +18829,7 @@
       <x:c r="AP42" t="str">
         <x:v>B</x:v>
       </x:c>
-      <x:c r="AQ42" t="str"/>
+      <x:c r="AQ42"/>
       <x:c r="AR42" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
@@ -18893,7 +18893,7 @@
       </x:c>
       <x:c r="BM42"/>
       <x:c r="BN42" t="str">
-        <x:v>目标抓取位姿可能被障碍物遮挡，单臂难以直接到达。</x:v>
+        <x:v>研究问题：目标抓取位姿可能被障碍物遮挡，单臂难以直接到达。；之前方法的问题：只规划目标夹爪的直接抓取，缺少另一只手协助移动物体/障碍物。；核心思路：COMBO-Grasp 用两个协调策略处理遮挡抓取，让双臂先调整环境再完成目标抓取。；数据集与评测基准：论文的遮挡抓取评测任务；具体平台和基线见实验章节。；主要结果：官方摘要报告成功率优于所比较基线，并对未见设置有一定泛化；未给统一数值。；为什么重要：展示双臂协作不只是同步抓取，也可以分工解除遮挡。；与当前项目的关系：High：适合普通夹爪双臂的支撑、移动与抓取任务。；主要局限：需进一步核验复杂杂乱场景与真机接触安全边界。</x:v>
       </x:c>
       <x:c r="BO42" t="str">
         <x:v>只规划目标夹爪的直接抓取，缺少另一只手协助移动物体/障碍物。</x:v>
@@ -18901,7 +18901,7 @@
       <x:c r="BP42" t="str">
         <x:v>COMBO-Grasp 用两个协调策略处理遮挡抓取，让双臂先调整环境再完成目标抓取。</x:v>
       </x:c>
-      <x:c r="BQ42" t="str"/>
+      <x:c r="BQ42"/>
       <x:c r="BR42" t="str">
         <x:v>官方摘要报告成功率优于所比较基线，并对未见设置有一定泛化；未给统一数值。</x:v>
       </x:c>
@@ -18911,7 +18911,7 @@
       <x:c r="BT42" t="str">
         <x:v>需进一步核验复杂杂乱场景与真机接触安全边界。</x:v>
       </x:c>
-      <x:c r="BU42" t="str"/>
+      <x:c r="BU42"/>
       <x:c r="BV42" t="str">
         <x:v>High：适合普通夹爪双臂的支撑、移动与抓取任务。</x:v>
       </x:c>
@@ -19028,7 +19028,7 @@
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
       </x:c>
       <x:c r="AK43" t="str">
-        <x:v>Unknown / Needs Full-Paper Verification</x:v>
+        <x:v>已核验摘要未给可安全复述的统一量化成功率。</x:v>
       </x:c>
       <x:c r="AL43" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -19045,7 +19045,7 @@
       <x:c r="AP43" t="str">
         <x:v>B</x:v>
       </x:c>
-      <x:c r="AQ43" t="str"/>
+      <x:c r="AQ43"/>
       <x:c r="AR43" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
@@ -19109,7 +19109,7 @@
       </x:c>
       <x:c r="BM43"/>
       <x:c r="BN43" t="str">
-        <x:v>人形机器人多指操作的控制维度高，真机直接强化学习成本大。</x:v>
+        <x:v>研究问题：人形机器人多指操作的控制维度高，真机直接强化学习成本大。；之前方法的问题：仿真策略可能因视觉、动力学和接触差异在真机失败。；核心思路：在仿真中训练视觉条件强化学习策略，再迁移到人形机器人完成抓取、搬箱等灵巧任务。；数据集与评测基准：论文报告 grasp-and-reach、box lift 等三项任务。；主要结果：已核验摘要未给可安全复述的统一量化成功率。；为什么重要：为接触密集任务的 Sim2Real 训练流程提供参照。；与当前项目的关系：Medium：可借鉴迁移流程，但人形灵巧手与普通夹爪差异较大。；主要局限：不能从人形任务结果直接推断双臂普通夹爪表现。</x:v>
       </x:c>
       <x:c r="BO43" t="str">
         <x:v>仿真策略可能因视觉、动力学和接触差异在真机失败。</x:v>
@@ -19117,7 +19117,7 @@
       <x:c r="BP43" t="str">
         <x:v>在仿真中训练视觉条件强化学习策略，再迁移到人形机器人完成抓取、搬箱等灵巧任务。</x:v>
       </x:c>
-      <x:c r="BQ43" t="str"/>
+      <x:c r="BQ43"/>
       <x:c r="BR43" t="str">
         <x:v>已核验摘要未给可安全复述的统一量化成功率。</x:v>
       </x:c>
@@ -19127,7 +19127,7 @@
       <x:c r="BT43" t="str">
         <x:v>不能从人形任务结果直接推断双臂普通夹爪表现。</x:v>
       </x:c>
-      <x:c r="BU43" t="str"/>
+      <x:c r="BU43"/>
       <x:c r="BV43" t="str">
         <x:v>Medium：可借鉴迁移流程，但人形灵巧手与普通夹爪差异较大。</x:v>
       </x:c>
@@ -19261,7 +19261,7 @@
       <x:c r="AP44" t="str">
         <x:v>B</x:v>
       </x:c>
-      <x:c r="AQ44" t="str"/>
+      <x:c r="AQ44"/>
       <x:c r="AR44" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
@@ -19325,7 +19325,7 @@
       </x:c>
       <x:c r="BM44"/>
       <x:c r="BN44" t="str">
-        <x:v>如何以自然的人手操作方式低成本采集灵巧机器人示范。</x:v>
+        <x:v>研究问题：如何以自然的人手操作方式低成本采集灵巧机器人示范。；之前方法的问题：人体与机器人手的本体差异会放大遥操作和策略学习难度。；核心思路：DexUMI 同时设计硬件与软件接口，缩小人手到不同机器人手的数据迁移差距。；为什么重要：展示采集装置与策略训练必须共同设计。；与当前项目的关系：Medium：可借鉴遥操作流程，但普通夹爪采集接口不同。；主要局限：两种灵巧手平台的结果不直接覆盖双普通夹爪。</x:v>
       </x:c>
       <x:c r="BO44" t="str">
         <x:v>人体与机器人手的本体差异会放大遥操作和策略学习难度。</x:v>
@@ -19333,7 +19333,7 @@
       <x:c r="BP44" t="str">
         <x:v>DexUMI 同时设计硬件与软件接口，缩小人手到不同机器人手的数据迁移差距。</x:v>
       </x:c>
-      <x:c r="BQ44" t="str"/>
+      <x:c r="BQ44"/>
       <x:c r="BR44" t="str">
         <x:v>官方摘要报告在两种真实灵巧手平台上的实验验证；统一数值需查正文。</x:v>
       </x:c>
@@ -19343,7 +19343,7 @@
       <x:c r="BT44" t="str">
         <x:v>两种灵巧手平台的结果不直接覆盖双普通夹爪。</x:v>
       </x:c>
-      <x:c r="BU44" t="str"/>
+      <x:c r="BU44"/>
       <x:c r="BV44" t="str">
         <x:v>Medium：可借鉴遥操作流程，但普通夹爪采集接口不同。</x:v>
       </x:c>
@@ -19460,7 +19460,7 @@
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
       </x:c>
       <x:c r="AK45" t="str">
-        <x:v>Unknown / Needs Full-Paper Verification</x:v>
+        <x:v>作者报告在新机器人设置中，同时微调 VLA 与动作验证器，比只调整部分模块高约 7%。</x:v>
       </x:c>
       <x:c r="AL45" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -19477,7 +19477,7 @@
       <x:c r="AP45" t="str">
         <x:v>B</x:v>
       </x:c>
-      <x:c r="AQ45" t="str"/>
+      <x:c r="AQ45"/>
       <x:c r="AR45" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
@@ -19541,7 +19541,7 @@
       </x:c>
       <x:c r="BM45"/>
       <x:c r="BN45" t="str">
-        <x:v>VLA 在开放真实环境中容易遇到未见状态，执行鲁棒性不足。</x:v>
+        <x:v>研究问题：VLA 在开放真实环境中容易遇到未见状态，执行鲁棒性不足。；之前方法的问题：只靠训练好的动作预测器，测试时缺少可靠的候选动作验证。；核心思路：RoboMonkey 在测试时增加动作验证与计算调度，为 VLA 选择更可靠的执行动作。；主要结果：作者报告在新机器人设置中，同时微调 VLA 与动作验证器，比只调整部分模块高约 7%。；为什么重要：把 Action Verification 放入 VLA 真机执行环节。；与当前项目的关系：High：与双臂动作前检查和失败预防直接相关。；主要局限：额外验证会增加在线延迟，真机安全收益需单独评测。</x:v>
       </x:c>
       <x:c r="BO45" t="str">
         <x:v>只靠训练好的动作预测器，测试时缺少可靠的候选动作验证。</x:v>
@@ -19549,7 +19549,7 @@
       <x:c r="BP45" t="str">
         <x:v>RoboMonkey 在测试时增加动作验证与计算调度，为 VLA 选择更可靠的执行动作。</x:v>
       </x:c>
-      <x:c r="BQ45" t="str"/>
+      <x:c r="BQ45"/>
       <x:c r="BR45" t="str">
         <x:v>作者报告在新机器人设置中，同时微调 VLA 与动作验证器，比只调整部分模块高约 7%。</x:v>
       </x:c>
@@ -19559,7 +19559,7 @@
       <x:c r="BT45" t="str">
         <x:v>额外验证会增加在线延迟，真机安全收益需单独评测。</x:v>
       </x:c>
-      <x:c r="BU45" t="str"/>
+      <x:c r="BU45"/>
       <x:c r="BV45" t="str">
         <x:v>High：与双臂动作前检查和失败预防直接相关。</x:v>
       </x:c>
@@ -19678,7 +19678,7 @@
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
       </x:c>
       <x:c r="AK46" t="str">
-        <x:v>Unknown / Needs Full-Paper Verification</x:v>
+        <x:v>主要结果是分类与文献脉络，没有统一实验数字。</x:v>
       </x:c>
       <x:c r="AL46" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -19695,7 +19695,7 @@
       <x:c r="AP46" t="str">
         <x:v>B</x:v>
       </x:c>
-      <x:c r="AQ46" t="str"/>
+      <x:c r="AQ46"/>
       <x:c r="AR46" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
@@ -19759,7 +19759,7 @@
       </x:c>
       <x:c r="BM46"/>
       <x:c r="BN46" t="str">
-        <x:v>VLA 方法快速增加，需要梳理它们的任务、架构与评测。</x:v>
+        <x:v>研究问题：VLA 方法快速增加，需要梳理它们的任务、架构与评测。；之前方法的问题：单篇方法难给出具身 VLA 的整体发展图。；核心思路：综述 VLA 在具身 AI 中的主要技术路线与开放挑战。；主要结果：主要结果是分类与文献脉络，没有统一实验数字。；为什么重要：为挑选 VLA 基线和理解动作接口提供入口。；与当前项目的关系：High：未来项目方向可能涉及 VLA。；主要局限：新论文更新很快，综述统计需结合当前原始论文。</x:v>
       </x:c>
       <x:c r="BO46" t="str">
         <x:v>单篇方法难给出具身 VLA 的整体发展图。</x:v>
@@ -19767,7 +19767,7 @@
       <x:c r="BP46" t="str">
         <x:v>综述 VLA 在具身 AI 中的主要技术路线与开放挑战。</x:v>
       </x:c>
-      <x:c r="BQ46" t="str"/>
+      <x:c r="BQ46"/>
       <x:c r="BR46" t="str">
         <x:v>主要结果是分类与文献脉络，没有统一实验数字。</x:v>
       </x:c>
@@ -19777,7 +19777,7 @@
       <x:c r="BT46" t="str">
         <x:v>新论文更新很快，综述统计需结合当前原始论文。</x:v>
       </x:c>
-      <x:c r="BU46" t="str"/>
+      <x:c r="BU46"/>
       <x:c r="BV46" t="str">
         <x:v>High：未来项目方向可能涉及 VLA。</x:v>
       </x:c>
@@ -19896,7 +19896,7 @@
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
       </x:c>
       <x:c r="AK47" t="str">
-        <x:v>Unknown / Needs Full-Paper Verification</x:v>
+        <x:v>提出统一比较视角；具体模型优劣仍需原始实验核验。</x:v>
       </x:c>
       <x:c r="AL47" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -19913,7 +19913,7 @@
       <x:c r="AP47" t="str">
         <x:v>B</x:v>
       </x:c>
-      <x:c r="AQ47" t="str"/>
+      <x:c r="AQ47"/>
       <x:c r="AR47" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
@@ -19977,7 +19977,7 @@
       </x:c>
       <x:c r="BM47"/>
       <x:c r="BN47" t="str">
-        <x:v>不同 VLA 用不同方式表示机器人动作，比较困难。</x:v>
+        <x:v>研究问题：不同 VLA 用不同方式表示机器人动作，比较困难。；之前方法的问题：表面上架构各异的模型，可能主要差在动作 token 设计。；核心思路：以 Action Tokenization 为主线整理 VLA 动作编码与模型结构。；主要结果：提出统一比较视角；具体模型优劣仍需原始实验核验。；为什么重要：直接帮助定义双臂普通夹爪的 VLA Action Space。；与当前项目的关系：High：动作表示是项目核心设计决策。；主要局限：综述分类不能证明某一种 token 化适合真机双臂。</x:v>
       </x:c>
       <x:c r="BO47" t="str">
         <x:v>表面上架构各异的模型，可能主要差在动作 token 设计。</x:v>
@@ -19985,7 +19985,7 @@
       <x:c r="BP47" t="str">
         <x:v>以 Action Tokenization 为主线整理 VLA 动作编码与模型结构。</x:v>
       </x:c>
-      <x:c r="BQ47" t="str"/>
+      <x:c r="BQ47"/>
       <x:c r="BR47" t="str">
         <x:v>提出统一比较视角；具体模型优劣仍需原始实验核验。</x:v>
       </x:c>
@@ -19995,7 +19995,7 @@
       <x:c r="BT47" t="str">
         <x:v>综述分类不能证明某一种 token 化适合真机双臂。</x:v>
       </x:c>
-      <x:c r="BU47" t="str"/>
+      <x:c r="BU47"/>
       <x:c r="BV47" t="str">
         <x:v>High：动作表示是项目核心设计决策。</x:v>
       </x:c>
@@ -20114,7 +20114,7 @@
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
       </x:c>
       <x:c r="AK48" t="str">
-        <x:v>Unknown / Needs Full-Paper Verification</x:v>
+        <x:v>论文提出整体研究框架；具体实验结论需看所引用原始工作。</x:v>
       </x:c>
       <x:c r="AL48" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -20131,7 +20131,7 @@
       <x:c r="AP48" t="str">
         <x:v>B</x:v>
       </x:c>
-      <x:c r="AQ48" t="str"/>
+      <x:c r="AQ48"/>
       <x:c r="AR48" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
@@ -20195,7 +20195,7 @@
       </x:c>
       <x:c r="BM48"/>
       <x:c r="BN48" t="str">
-        <x:v>基础模型能否帮助机器人形成更通用的操作能力。</x:v>
+        <x:v>研究问题：基础模型能否帮助机器人形成更通用的操作能力。；之前方法的问题：单个感知或规划模块改进不一定带来完整操作系统的泛化。；核心思路：建立综述框架，讨论 foundation models 在机器人学习各模块的作用。；主要结果：论文提出整体研究框架；具体实验结论需看所引用原始工作。；为什么重要：提醒未来 VLA 方案同时考虑感知、动作、数据和评测。；与当前项目的关系：Medium：适合技术路线规划。；主要局限：综述观点不能代替本项目真机双臂实验。</x:v>
       </x:c>
       <x:c r="BO48" t="str">
         <x:v>单个感知或规划模块改进不一定带来完整操作系统的泛化。</x:v>
@@ -20203,7 +20203,7 @@
       <x:c r="BP48" t="str">
         <x:v>建立综述框架，讨论 foundation models 在机器人学习各模块的作用。</x:v>
       </x:c>
-      <x:c r="BQ48" t="str"/>
+      <x:c r="BQ48"/>
       <x:c r="BR48" t="str">
         <x:v>论文提出整体研究框架；具体实验结论需看所引用原始工作。</x:v>
       </x:c>
@@ -20213,7 +20213,7 @@
       <x:c r="BT48" t="str">
         <x:v>综述观点不能代替本项目真机双臂实验。</x:v>
       </x:c>
-      <x:c r="BU48" t="str"/>
+      <x:c r="BU48"/>
       <x:c r="BV48" t="str">
         <x:v>Medium：适合技术路线规划。</x:v>
       </x:c>
@@ -20332,7 +20332,7 @@
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
       </x:c>
       <x:c r="AK49" t="str">
-        <x:v>Unknown / Needs Full-Paper Verification</x:v>
+        <x:v>主要贡献是研究分类；不以单项任务成功率作为综述结论。</x:v>
       </x:c>
       <x:c r="AL49" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -20349,7 +20349,7 @@
       <x:c r="AP49" t="str">
         <x:v>B</x:v>
       </x:c>
-      <x:c r="AQ49" t="str"/>
+      <x:c r="AQ49"/>
       <x:c r="AR49" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
@@ -20413,7 +20413,7 @@
       </x:c>
       <x:c r="BM49"/>
       <x:c r="BN49" t="str">
-        <x:v>基础模型在机器人具身任务中如何发挥作用。</x:v>
+        <x:v>研究问题：基础模型在机器人具身任务中如何发挥作用。；之前方法的问题：视觉、语言与控制研究各自发展，尚需统一的系统视角。；核心思路：综述 foundation models 在机器人感知、规划和动作学习中的应用与挑战。；主要结果：主要贡献是研究分类；不以单项任务成功率作为综述结论。；为什么重要：帮助区分大模型推理能力与机器人可执行能力。；与当前项目的关系：Medium：可用于规划未来 VLA 技术路线。；主要局限：需回到每篇原始方法论文确认数字与真实机器人证据。</x:v>
       </x:c>
       <x:c r="BO49" t="str">
         <x:v>视觉、语言与控制研究各自发展，尚需统一的系统视角。</x:v>
@@ -20421,7 +20421,7 @@
       <x:c r="BP49" t="str">
         <x:v>综述 foundation models 在机器人感知、规划和动作学习中的应用与挑战。</x:v>
       </x:c>
-      <x:c r="BQ49" t="str"/>
+      <x:c r="BQ49"/>
       <x:c r="BR49" t="str">
         <x:v>主要贡献是研究分类；不以单项任务成功率作为综述结论。</x:v>
       </x:c>
@@ -20431,7 +20431,7 @@
       <x:c r="BT49" t="str">
         <x:v>需回到每篇原始方法论文确认数字与真实机器人证据。</x:v>
       </x:c>
-      <x:c r="BU49" t="str"/>
+      <x:c r="BU49"/>
       <x:c r="BV49" t="str">
         <x:v>Medium：可用于规划未来 VLA 技术路线。</x:v>
       </x:c>
@@ -20550,7 +20550,7 @@
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
       </x:c>
       <x:c r="AK50" t="str">
-        <x:v>Unknown / Needs Full-Paper Verification</x:v>
+        <x:v>主要为研究整理，不能用一个指标总结。</x:v>
       </x:c>
       <x:c r="AL50" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -20567,7 +20567,7 @@
       <x:c r="AP50" t="str">
         <x:v>B</x:v>
       </x:c>
-      <x:c r="AQ50" t="str"/>
+      <x:c r="AQ50"/>
       <x:c r="AR50" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
@@ -20631,7 +20631,7 @@
       </x:c>
       <x:c r="BM50"/>
       <x:c r="BN50" t="str">
-        <x:v>机器人操作数据稀缺且分布易受人工筛选影响。</x:v>
+        <x:v>研究问题：机器人操作数据稀缺且分布易受人工筛选影响。；之前方法的问题：只用精心挑选的示范难覆盖真实世界变化。；核心思路：围绕“通过观察学习”整理人类视频、机器人数据与迁移方法。；主要结果：主要为研究整理，不能用一个指标总结。；为什么重要：帮助决定是否利用人类视频补充双臂示范。；与当前项目的关系：Medium：与低成本数据收集相关。；主要局限：视频观察与可执行机器人动作之间仍有本体差异。</x:v>
       </x:c>
       <x:c r="BO50" t="str">
         <x:v>只用精心挑选的示范难覆盖真实世界变化。</x:v>
@@ -20639,7 +20639,7 @@
       <x:c r="BP50" t="str">
         <x:v>围绕“通过观察学习”整理人类视频、机器人数据与迁移方法。</x:v>
       </x:c>
-      <x:c r="BQ50" t="str"/>
+      <x:c r="BQ50"/>
       <x:c r="BR50" t="str">
         <x:v>主要为研究整理，不能用一个指标总结。</x:v>
       </x:c>
@@ -20649,7 +20649,7 @@
       <x:c r="BT50" t="str">
         <x:v>视频观察与可执行机器人动作之间仍有本体差异。</x:v>
       </x:c>
-      <x:c r="BU50" t="str"/>
+      <x:c r="BU50"/>
       <x:c r="BV50" t="str">
         <x:v>Medium：与低成本数据收集相关。</x:v>
       </x:c>
@@ -20768,7 +20768,7 @@
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
       </x:c>
       <x:c r="AK51" t="str">
-        <x:v>Unknown / Needs Full-Paper Verification</x:v>
+        <x:v>综述不提供统一实验成功率；比较需回各原始论文。</x:v>
       </x:c>
       <x:c r="AL51" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -20785,7 +20785,7 @@
       <x:c r="AP51" t="str">
         <x:v>B</x:v>
       </x:c>
-      <x:c r="AQ51" t="str"/>
+      <x:c r="AQ51"/>
       <x:c r="AR51" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
@@ -20849,7 +20849,7 @@
       </x:c>
       <x:c r="BM51"/>
       <x:c r="BN51" t="str">
-        <x:v>机器人如何像人手一样在掌内精准移动物体。</x:v>
+        <x:v>研究问题：机器人如何像人手一样在掌内精准移动物体。；之前方法的问题：抓取成功不代表能完成掌内旋转和重定位。；核心思路：综述学习式 in-hand manipulation 的状态、动作、训练与评测方法。；主要结果：综述不提供统一实验成功率；比较需回各原始论文。；为什么重要：说明普通夹爪与灵巧手任务边界。；与当前项目的关系：Low：本项目当前不是掌内多指操作。；主要局限：不同硬件的结果不宜直接比较。</x:v>
       </x:c>
       <x:c r="BO51" t="str">
         <x:v>抓取成功不代表能完成掌内旋转和重定位。</x:v>
@@ -20857,7 +20857,7 @@
       <x:c r="BP51" t="str">
         <x:v>综述学习式 in-hand manipulation 的状态、动作、训练与评测方法。</x:v>
       </x:c>
-      <x:c r="BQ51" t="str"/>
+      <x:c r="BQ51"/>
       <x:c r="BR51" t="str">
         <x:v>综述不提供统一实验成功率；比较需回各原始论文。</x:v>
       </x:c>
@@ -20867,7 +20867,7 @@
       <x:c r="BT51" t="str">
         <x:v>不同硬件的结果不宜直接比较。</x:v>
       </x:c>
-      <x:c r="BU51" t="str"/>
+      <x:c r="BU51"/>
       <x:c r="BV51" t="str">
         <x:v>Low：本项目当前不是掌内多指操作。</x:v>
       </x:c>
@@ -20986,7 +20986,7 @@
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
       </x:c>
       <x:c r="AK52" t="str">
-        <x:v>Unknown / Needs Full-Paper Verification</x:v>
+        <x:v>综述性质，未记录统一机器人成功率。</x:v>
       </x:c>
       <x:c r="AL52" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -21003,7 +21003,7 @@
       <x:c r="AP52" t="str">
         <x:v>B</x:v>
       </x:c>
-      <x:c r="AQ52" t="str"/>
+      <x:c r="AQ52"/>
       <x:c r="AR52" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
@@ -21067,7 +21067,7 @@
       </x:c>
       <x:c r="BM52"/>
       <x:c r="BN52" t="str">
-        <x:v>灵巧手在智能制造中的能力边界与系统需求尚需梳理。</x:v>
+        <x:v>研究问题：灵巧手在智能制造中的能力边界与系统需求尚需梳理。；之前方法的问题：硬件、控制和应用研究分散，难直接判断何时需要多指手。；核心思路：总结灵巧手技术、趋势和制造场景应用。；主要结果：综述性质，未记录统一机器人成功率。；为什么重要：帮助区分普通夹爪和灵巧手各自适合的任务。；与当前项目的关系：Low：本项目当前采用普通夹爪，仅作硬件路线比较。；主要局限：制造任务综述不能直接指导本项目双臂策略的量化性能。</x:v>
       </x:c>
       <x:c r="BO52" t="str">
         <x:v>硬件、控制和应用研究分散，难直接判断何时需要多指手。</x:v>
@@ -21075,7 +21075,7 @@
       <x:c r="BP52" t="str">
         <x:v>总结灵巧手技术、趋势和制造场景应用。</x:v>
       </x:c>
-      <x:c r="BQ52" t="str"/>
+      <x:c r="BQ52"/>
       <x:c r="BR52" t="str">
         <x:v>综述性质，未记录统一机器人成功率。</x:v>
       </x:c>
@@ -21085,7 +21085,7 @@
       <x:c r="BT52" t="str">
         <x:v>制造任务综述不能直接指导本项目双臂策略的量化性能。</x:v>
       </x:c>
-      <x:c r="BU52" t="str"/>
+      <x:c r="BU52"/>
       <x:c r="BV52" t="str">
         <x:v>Low：本项目当前采用普通夹爪，仅作硬件路线比较。</x:v>
       </x:c>
@@ -21204,7 +21204,7 @@
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
       </x:c>
       <x:c r="AK53" t="str">
-        <x:v>Unknown / Needs Full-Paper Verification</x:v>
+        <x:v>综述以方法脉络与开放问题为主；无单一成功率可安全复述。</x:v>
       </x:c>
       <x:c r="AL53" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -21221,7 +21221,7 @@
       <x:c r="AP53" t="str">
         <x:v>B</x:v>
       </x:c>
-      <x:c r="AQ53" t="str"/>
+      <x:c r="AQ53"/>
       <x:c r="AR53" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
@@ -21285,7 +21285,7 @@
       </x:c>
       <x:c r="BM53"/>
       <x:c r="BN53" t="str">
-        <x:v>以物体为中心的机器人操作涉及感知、交互和策略学习多个环节。</x:v>
+        <x:v>研究问题：以物体为中心的机器人操作涉及感知、交互和策略学习多个环节。；之前方法的问题：相关研究分布在不同任务与表示方式中，难以直接比较。；核心思路：整理 object-centric embodied learning 的方法和操作任务分类。；主要结果：综述以方法脉络与开放问题为主；无单一成功率可安全复述。；为什么重要：帮助把目标物体状态纳入双臂操作设计。；与当前项目的关系：Medium：物体中心表示可用于普通夹爪协作。；主要局限：综述中的方向仍需按具体论文和真机证据核验。</x:v>
       </x:c>
       <x:c r="BO53" t="str">
         <x:v>相关研究分布在不同任务与表示方式中，难以直接比较。</x:v>
@@ -21293,7 +21293,7 @@
       <x:c r="BP53" t="str">
         <x:v>整理 object-centric embodied learning 的方法和操作任务分类。</x:v>
       </x:c>
-      <x:c r="BQ53" t="str"/>
+      <x:c r="BQ53"/>
       <x:c r="BR53" t="str">
         <x:v>综述以方法脉络与开放问题为主；无单一成功率可安全复述。</x:v>
       </x:c>
@@ -21303,7 +21303,7 @@
       <x:c r="BT53" t="str">
         <x:v>综述中的方向仍需按具体论文和真机证据核验。</x:v>
       </x:c>
-      <x:c r="BU53" t="str"/>
+      <x:c r="BU53"/>
       <x:c r="BV53" t="str">
         <x:v>Medium：物体中心表示可用于普通夹爪协作。</x:v>
       </x:c>
@@ -21422,7 +21422,7 @@
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
       </x:c>
       <x:c r="AK54" t="str">
-        <x:v>Unknown / Needs Full-Paper Verification</x:v>
+        <x:v>该文以问题和研究展望为主，不提供统一成功率。</x:v>
       </x:c>
       <x:c r="AL54" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -21439,7 +21439,7 @@
       <x:c r="AP54" t="str">
         <x:v>B</x:v>
       </x:c>
-      <x:c r="AQ54" t="str"/>
+      <x:c r="AQ54"/>
       <x:c r="AR54" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
@@ -21503,7 +21503,7 @@
       </x:c>
       <x:c r="BM54"/>
       <x:c r="BN54" t="str">
-        <x:v>灵巧操作需要精确接触，静态示范数据往往不够。</x:v>
+        <x:v>研究问题：灵巧操作需要精确接触，静态示范数据往往不够。；之前方法的问题：策略部署后的人机交互和在线纠错机制尚需系统化。；核心思路：梳理 interactive imitation learning 在灵巧操作中的反馈、修正与挑战。；主要结果：该文以问题和研究展望为主，不提供统一成功率。；为什么重要：失败后的人类反馈可能帮助双臂真机安全学习。；与当前项目的关系：Medium：纠错机制可借鉴，手型硬件不同。；主要局限：观点性综述需用可控实验验证。</x:v>
       </x:c>
       <x:c r="BO54" t="str">
         <x:v>策略部署后的人机交互和在线纠错机制尚需系统化。</x:v>
@@ -21511,7 +21511,7 @@
       <x:c r="BP54" t="str">
         <x:v>梳理 interactive imitation learning 在灵巧操作中的反馈、修正与挑战。</x:v>
       </x:c>
-      <x:c r="BQ54" t="str"/>
+      <x:c r="BQ54"/>
       <x:c r="BR54" t="str">
         <x:v>该文以问题和研究展望为主，不提供统一成功率。</x:v>
       </x:c>
@@ -21521,7 +21521,7 @@
       <x:c r="BT54" t="str">
         <x:v>观点性综述需用可控实验验证。</x:v>
       </x:c>
-      <x:c r="BU54" t="str"/>
+      <x:c r="BU54"/>
       <x:c r="BV54" t="str">
         <x:v>Medium：纠错机制可借鉴，手型硬件不同。</x:v>
       </x:c>
@@ -21640,7 +21640,7 @@
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
       </x:c>
       <x:c r="AK55" t="str">
-        <x:v>Unknown / Needs Full-Paper Verification</x:v>
+        <x:v>无可核验的正式摘要或量化结果。</x:v>
       </x:c>
       <x:c r="AL55" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -21657,7 +21657,7 @@
       <x:c r="AP55" t="str">
         <x:v>B</x:v>
       </x:c>
-      <x:c r="AQ55" t="str"/>
+      <x:c r="AQ55"/>
       <x:c r="AR55" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
@@ -21721,7 +21721,7 @@
       </x:c>
       <x:c r="BM55"/>
       <x:c r="BN55" t="str">
-        <x:v>该条记录题名涉及双臂机器人学习综述，但正式来源尚未可靠核实。</x:v>
+        <x:v>研究问题：该条记录题名涉及双臂机器人学习综述，但正式来源尚未可靠核实。；之前方法的问题：在来源身份未明确前，不能据题名推断其具体观点。；主要结果：无可核验的正式摘要或量化结果。；为什么重要：避免把题名相似的网页或清单误当正式论文。；与当前项目的关系：High：主题相关，但证据有限，暂不作为研究结论来源。；主要局限：需先确认作者、Venue、官方全文和书目身份。</x:v>
       </x:c>
       <x:c r="BO55" t="str">
         <x:v>在来源身份未明确前，不能据题名推断其具体观点。</x:v>
@@ -21729,7 +21729,7 @@
       <x:c r="BP55" t="str">
         <x:v>目前仅保留为书目待核验条目；不填写未经证实的方法分类。</x:v>
       </x:c>
-      <x:c r="BQ55" t="str"/>
+      <x:c r="BQ55"/>
       <x:c r="BR55" t="str">
         <x:v>无可核验的正式摘要或量化结果。</x:v>
       </x:c>
@@ -21739,7 +21739,7 @@
       <x:c r="BT55" t="str">
         <x:v>需先确认作者、Venue、官方全文和书目身份。</x:v>
       </x:c>
-      <x:c r="BU55" t="str"/>
+      <x:c r="BU55"/>
       <x:c r="BV55" t="str">
         <x:v>High：主题相关，但证据有限，暂不作为研究结论来源。</x:v>
       </x:c>
@@ -21858,7 +21858,7 @@
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
       </x:c>
       <x:c r="AK56" t="str">
-        <x:v>Unknown / Needs Full-Paper Verification</x:v>
+        <x:v>主要贡献是统一视角，不以单一任务数值衡量。</x:v>
       </x:c>
       <x:c r="AL56" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -21875,7 +21875,7 @@
       <x:c r="AP56" t="str">
         <x:v>B</x:v>
       </x:c>
-      <x:c r="AQ56" t="str"/>
+      <x:c r="AQ56"/>
       <x:c r="AR56" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
@@ -21939,7 +21939,7 @@
       </x:c>
       <x:c r="BM56"/>
       <x:c r="BN56" t="str">
-        <x:v>机器人操作研究横跨视觉、规划、控制和数据，术语与评测不统一。</x:v>
+        <x:v>研究问题：机器人操作研究横跨视觉、规划、控制和数据，术语与评测不统一。；之前方法的问题：缺少能连接不同方法和任务的整体框架。；核心思路：对机器人操作的任务、技术路线和挑战做综合梳理。；主要结果：主要贡献是统一视角，不以单一任务数值衡量。；为什么重要：便于在文献库中定位 VLA、双臂和 Sim2Real 的关系。；与当前项目的关系：Medium：用于制定阅读顺序与研究问题。；主要局限：具体方法结论必须回原始论文核验。</x:v>
       </x:c>
       <x:c r="BO56" t="str">
         <x:v>缺少能连接不同方法和任务的整体框架。</x:v>
@@ -21947,7 +21947,7 @@
       <x:c r="BP56" t="str">
         <x:v>对机器人操作的任务、技术路线和挑战做综合梳理。</x:v>
       </x:c>
-      <x:c r="BQ56" t="str"/>
+      <x:c r="BQ56"/>
       <x:c r="BR56" t="str">
         <x:v>主要贡献是统一视角，不以单一任务数值衡量。</x:v>
       </x:c>
@@ -21957,7 +21957,7 @@
       <x:c r="BT56" t="str">
         <x:v>具体方法结论必须回原始论文核验。</x:v>
       </x:c>
-      <x:c r="BU56" t="str"/>
+      <x:c r="BU56"/>
       <x:c r="BV56" t="str">
         <x:v>Medium：用于制定阅读顺序与研究问题。</x:v>
       </x:c>
@@ -22076,7 +22076,7 @@
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
       </x:c>
       <x:c r="AK57" t="str">
-        <x:v>Unknown / Needs Full-Paper Verification</x:v>
+        <x:v>综述不以单一任务成功率为主要结果；本轮未提取独立实验数字。</x:v>
       </x:c>
       <x:c r="AL57" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -22093,7 +22093,7 @@
       <x:c r="AP57" t="str">
         <x:v>B</x:v>
       </x:c>
-      <x:c r="AQ57" t="str"/>
+      <x:c r="AQ57"/>
       <x:c r="AR57" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
@@ -22157,7 +22157,7 @@
       </x:c>
       <x:c r="BM57"/>
       <x:c r="BN57" t="str">
-        <x:v>机器人如何从专家示范而非手写奖励中学习技能。</x:v>
+        <x:v>研究问题：机器人如何从专家示范而非手写奖励中学习技能。；之前方法的问题：示范学习方法多样，训练难度和适用条件分散。；核心思路：梳理 demonstration learning 的主要方法、训练设置与挑战；具体覆盖范围以论文目录为准。；主要结果：综述不以单一任务成功率为主要结果；本轮未提取独立实验数字。；为什么重要：帮助选择双臂示范学习基线。；与当前项目的关系：Medium：方法选择相关，需结合真实硬件实验。；主要局限：综述中的比较不替代统一数据预算下的复现实验。</x:v>
       </x:c>
       <x:c r="BO57" t="str">
         <x:v>示范学习方法多样，训练难度和适用条件分散。</x:v>
@@ -22165,7 +22165,7 @@
       <x:c r="BP57" t="str">
         <x:v>梳理 demonstration learning 的主要方法、训练设置与挑战；具体覆盖范围以论文目录为准。</x:v>
       </x:c>
-      <x:c r="BQ57" t="str"/>
+      <x:c r="BQ57"/>
       <x:c r="BR57" t="str">
         <x:v>综述不以单一任务成功率为主要结果；本轮未提取独立实验数字。</x:v>
       </x:c>
@@ -22175,7 +22175,7 @@
       <x:c r="BT57" t="str">
         <x:v>综述中的比较不替代统一数据预算下的复现实验。</x:v>
       </x:c>
-      <x:c r="BU57" t="str"/>
+      <x:c r="BU57"/>
       <x:c r="BV57" t="str">
         <x:v>Medium：方法选择相关，需结合真实硬件实验。</x:v>
       </x:c>
@@ -22300,7 +22300,7 @@
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
       </x:c>
       <x:c r="AK58" t="str">
-        <x:v>Unknown / Needs Full-Paper Verification</x:v>
+        <x:v>作者报告真机任务中优于所比较方法；摘要未给统一数值。</x:v>
       </x:c>
       <x:c r="AL58" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -22317,7 +22317,7 @@
       <x:c r="AP58" t="str">
         <x:v>B</x:v>
       </x:c>
-      <x:c r="AQ58" t="str"/>
+      <x:c r="AQ58"/>
       <x:c r="AR58" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
@@ -22381,7 +22381,7 @@
       </x:c>
       <x:c r="BM58"/>
       <x:c r="BN58" t="str">
-        <x:v>双臂协调导致动作分布多模态，同时缺少足够训练数据。</x:v>
+        <x:v>研究问题：双臂协调导致动作分布多模态，同时缺少足够训练数据。；之前方法的问题：普通单臂策略难直接表示两臂共同运动与接触。；核心思路：RDT-1B 用 Robotics Diffusion Transformer 建立双臂操作基础策略，生成协调的双臂动作。；数据集与评测基准：论文的双臂机器人示范与真机评测；具体数据混合见原文。；主要结果：作者报告真机任务中优于所比较方法；摘要未给统一数值。；为什么重要：是项目比较双臂 Diffusion Policy 与 VLA 动作头的核心基线。；与当前项目的关系：High：与双臂普通夹爪和真机操作直接相关。；主要局限：不同夹爪、相机和动作空间的可迁移性仍需按原论文与本项目实验核验。</x:v>
       </x:c>
       <x:c r="BO58" t="str">
         <x:v>普通单臂策略难直接表示两臂共同运动与接触。</x:v>
@@ -22389,7 +22389,7 @@
       <x:c r="BP58" t="str">
         <x:v>RDT-1B 用 Robotics Diffusion Transformer 建立双臂操作基础策略，生成协调的双臂动作。</x:v>
       </x:c>
-      <x:c r="BQ58" t="str"/>
+      <x:c r="BQ58"/>
       <x:c r="BR58" t="str">
         <x:v>作者报告真机任务中优于所比较方法；摘要未给统一数值。</x:v>
       </x:c>
@@ -22399,7 +22399,7 @@
       <x:c r="BT58" t="str">
         <x:v>不同夹爪、相机和动作空间的可迁移性仍需按原论文与本项目实验核验。</x:v>
       </x:c>
-      <x:c r="BU58" t="str"/>
+      <x:c r="BU58"/>
       <x:c r="BV58" t="str">
         <x:v>High：与双臂普通夹爪和真机操作直接相关。</x:v>
       </x:c>
@@ -22524,7 +22524,7 @@
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
       </x:c>
       <x:c r="AK59" t="str">
-        <x:v>Unknown / Needs Full-Paper Verification</x:v>
+        <x:v>论文报告在若干双臂任务上优于同规模 RDT-1B，而无需双臂预训练；具体任务结果见原文。</x:v>
       </x:c>
       <x:c r="AL59" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -22541,7 +22541,7 @@
       <x:c r="AP59" t="str">
         <x:v>B</x:v>
       </x:c>
-      <x:c r="AQ59" t="str"/>
+      <x:c r="AQ59"/>
       <x:c r="AR59" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
@@ -22605,7 +22605,7 @@
       </x:c>
       <x:c r="BM59"/>
       <x:c r="BN59" t="str">
-        <x:v>双臂 VLA 训练通常需要昂贵的双臂示范和大模型参数。</x:v>
+        <x:v>研究问题：双臂 VLA 训练通常需要昂贵的双臂示范和大模型参数。；之前方法的问题：从单臂 VLA 迁移时，两只手臂仍要协调，而不能简单独立执行。；核心思路：TwinVLA 组合两个预训练单臂 VLA，并加入协调机制形成双臂策略。；数据集与评测基准：仿真与真机双臂操作任务。；主要结果：论文报告在若干双臂任务上优于同规模 RDT-1B，而无需双臂预训练；具体任务结果见原文。；为什么重要：提供低成本复用单臂模型的双臂 VLA 路线。；与当前项目的关系：High：直接关系到项目未来 VLA 迁移。；主要局限：即使无双臂预训练，协调模块与目标任务示范需求仍需具体核实。</x:v>
       </x:c>
       <x:c r="BO59" t="str">
         <x:v>从单臂 VLA 迁移时，两只手臂仍要协调，而不能简单独立执行。</x:v>
@@ -22613,7 +22613,7 @@
       <x:c r="BP59" t="str">
         <x:v>TwinVLA 组合两个预训练单臂 VLA，并加入协调机制形成双臂策略。</x:v>
       </x:c>
-      <x:c r="BQ59" t="str"/>
+      <x:c r="BQ59"/>
       <x:c r="BR59" t="str">
         <x:v>论文报告在若干双臂任务上优于同规模 RDT-1B，而无需双臂预训练；具体任务结果见原文。</x:v>
       </x:c>
@@ -22623,7 +22623,7 @@
       <x:c r="BT59" t="str">
         <x:v>即使无双臂预训练，协调模块与目标任务示范需求仍需具体核实。</x:v>
       </x:c>
-      <x:c r="BU59" t="str"/>
+      <x:c r="BU59"/>
       <x:c r="BV59" t="str">
         <x:v>High：直接关系到项目未来 VLA 迁移。</x:v>
       </x:c>
@@ -22746,7 +22746,7 @@
         <x:v>Real Robot 字段为 `Unknown`；Dataset、Benchmark、Robot Platform 中的 Unknown 继续保留，不从题名推断。</x:v>
       </x:c>
       <x:c r="AK60" t="str">
-        <x:v>Unknown / Needs Full-Paper Verification</x:v>
+        <x:v>摘要说明其提供仿真与真实数据的统一评测；具体成功率需查实验章节。</x:v>
       </x:c>
       <x:c r="AL60" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -22763,7 +22763,7 @@
       <x:c r="AP60" t="str">
         <x:v>B</x:v>
       </x:c>
-      <x:c r="AQ60" t="str"/>
+      <x:c r="AQ60"/>
       <x:c r="AR60" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
@@ -22827,7 +22827,7 @@
       </x:c>
       <x:c r="BM60"/>
       <x:c r="BN60" t="str">
-        <x:v>双臂协调与复杂物体操作缺少足够多样的高质量示范和贴近现实的评测环境。</x:v>
+        <x:v>研究问题：双臂协调与复杂物体操作缺少足够多样的高质量示范和贴近现实的评测环境。；之前方法的问题：示范稀缺且仿真评测与真实场景存在差距。；核心思路：RoboTwin 用 3D 生成模型及大语言模型构建生成式数字孪生，生成专家数据并建立双臂评测平台。；数据集与评测基准：RoboTwin 含仿真与真实数据；作者提供资源下载和示范采集脚本，本轮未下载核验数据完整性。；主要结果：摘要说明其提供仿真与真实数据的统一评测；具体成功率需查实验章节。；为什么重要：将双臂数据生成与现实对齐评测放入同一框架。；与当前项目的关系：High：与普通夹爪双臂策略的数据和任务设计直接相关。；主要局限：生成数据的物理一致性和真实迁移效果需按论文实验进一步核验。</x:v>
       </x:c>
       <x:c r="BO60" t="str">
         <x:v>示范稀缺且仿真评测与真实场景存在差距。</x:v>
@@ -22835,7 +22835,7 @@
       <x:c r="BP60" t="str">
         <x:v>RoboTwin 用 3D 生成模型及大语言模型构建生成式数字孪生，生成专家数据并建立双臂评测平台。</x:v>
       </x:c>
-      <x:c r="BQ60" t="str"/>
+      <x:c r="BQ60"/>
       <x:c r="BR60" t="str">
         <x:v>摘要说明其提供仿真与真实数据的统一评测；具体成功率需查实验章节。</x:v>
       </x:c>
@@ -22845,7 +22845,7 @@
       <x:c r="BT60" t="str">
         <x:v>生成数据的物理一致性和真实迁移效果需按论文实验进一步核验。</x:v>
       </x:c>
-      <x:c r="BU60" t="str"/>
+      <x:c r="BU60"/>
       <x:c r="BV60" t="str">
         <x:v>High：与普通夹爪双臂策略的数据和任务设计直接相关。</x:v>
       </x:c>
@@ -22987,7 +22987,7 @@
       <x:c r="AP61" t="str">
         <x:v>A</x:v>
       </x:c>
-      <x:c r="AQ61" t="str"/>
+      <x:c r="AQ61"/>
       <x:c r="AR61" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
@@ -23051,7 +23051,7 @@
       </x:c>
       <x:c r="BM61"/>
       <x:c r="BN61" t="str">
-        <x:v>许多 VLA 对三维空间信息的利用不足，影响操作动作的空间准确性与数据效率。</x:v>
+        <x:v>研究问题：许多 VLA 对三维空间信息的利用不足，影响操作动作的空间准确性与数据效率。；之前方法的问题：一些 3D VLA 尚未充分利用三维数据自带的空间结构，影响动作预测的数据效率。；核心思路：BridgeVLA 研究视觉语言模型与三维输入/输出的对齐，让空间结构参与动作预测。；数据集与评测基准：论文评估 RLBench、COLOSSEUM 与 GemBench；预训练数据和下载入口以官方仓库说明为准。；为什么重要：为 VLA 如何利用三维几何信息提供了可比较的基线。；与当前项目的关系：High：有助于研究语言条件操作与 VLA 设计。；主要局限：作者把更充分的 3D 输入/输出对齐与训练效率列为后续方向；当前结果主要验证于报告的 Franka 设置。</x:v>
       </x:c>
       <x:c r="BO61" t="str">
         <x:v>一些 3D VLA 尚未充分利用三维数据自带的空间结构，影响动作预测的数据效率。</x:v>
@@ -23059,7 +23059,7 @@
       <x:c r="BP61" t="str">
         <x:v>BridgeVLA 研究视觉语言模型与三维输入/输出的对齐，让空间结构参与动作预测。</x:v>
       </x:c>
-      <x:c r="BQ61" t="str"/>
+      <x:c r="BQ61"/>
       <x:c r="BR61" t="str">
         <x:v>卡片记录 RLBench 平均成功率 88.2% 对 81.4%，COLOSSEUM 为 64.0% 对 56.7%；其余数值与实验设定见原卡表格证据。</x:v>
       </x:c>
@@ -23069,7 +23069,7 @@
       <x:c r="BT61" t="str">
         <x:v>作者把更充分的 3D 输入/输出对齐与训练效率列为后续方向；当前结果主要验证于报告的 Franka 设置。</x:v>
       </x:c>
-      <x:c r="BU61" t="str"/>
+      <x:c r="BU61"/>
       <x:c r="BV61" t="str">
         <x:v>High：有助于研究语言条件操作与 VLA 设计。</x:v>
       </x:c>
@@ -23106,7 +23106,7 @@
         <x:v>正式主会论文：官方论文集核实</x:v>
       </x:c>
       <x:c r="G62" t="str">
-        <x:v>A (CCF 7th edition; venue category not independently extracted from official PDF)</x:v>
+        <x:v>A</x:v>
       </x:c>
       <x:c r="H62" t="str">
         <x:v>VLA / Robot Foundation Models</x:v>
@@ -23120,7 +23120,9 @@
       <x:c r="K62" t="str">
         <x:v>https://proceedings.neurips.cc/paper_files/paper/2025/hash/f062da1973ac9ac61fc6d44dd7fa309f-Abstract-Conference.html</x:v>
       </x:c>
-      <x:c r="L62"/>
+      <x:c r="L62" t="str">
+        <x:v>https://arxiv.org/abs/2502.02175</x:v>
+      </x:c>
       <x:c r="M62" t="str">
         <x:v>https://vla-cache.github.io/</x:v>
       </x:c>
@@ -23173,109 +23175,115 @@
         <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AD62" t="str">
-        <x:v>VLA 反复处理相似视觉 token，会增加在线推理开销。</x:v>
+        <x:v>VLA 对相邻帧重复视觉区域重复计算，增加闭环推理延迟。</x:v>
       </x:c>
       <x:c r="AE62" t="str">
-        <x:v>Unknown / Needs Full-Paper Verification</x:v>
+        <x:v>单帧 token pruning 可能移除外观静态但对动作关键的区域。</x:v>
       </x:c>
       <x:c r="AF62" t="str">
-        <x:v>以 `VLA; Inference Acceleration / Token Caching` 为主要方法/能力线索；更细的结构和消融结论待正文核验。</x:v>
+        <x:v>跨帧复用静态视觉 token 的 KV 表示；attention 排除任务相关区域，并按层 entropy 自适应复用比例。</x:v>
       </x:c>
       <x:c r="AG62" t="str">
-        <x:v>LIBERO、SIMPLER 与论文真机设置。</x:v>
+        <x:v>- LIBERO：沿用 OpenVLA/OpenVLA-OFT 标准设置，Spatial、Object、Goal、Long 四个任务套件，每套 10 个子任务。</x:v>
       </x:c>
       <x:c r="AH62" t="str">
-        <x:v>Unknown / Needs Full-Paper Verification</x:v>
+        <x:v>LIBERO：OpenVLA、SparseVLM、FastV、OpenVLA-OFT；SIMPLER：CogACT；真机：OpenVLA。</x:v>
       </x:c>
       <x:c r="AI62" t="str">
-        <x:v>- This paper introduces VLA-Cache, a training-free inference acceleration method that reduces computational overhead by adaptively caching and reusing static visual tokens across frames.</x:v>
+        <x:v>提出免训练的跨帧视觉 token KV 缓存、任务相关区域过滤与层级自适应复用。</x:v>
       </x:c>
       <x:c r="AJ62" t="str">
-        <x:v>Real Robot 字段为 `Unknown`；Dataset、Benchmark、Robot Platform 中的 Unknown 继续保留，不从题名推断。</x:v>
+        <x:v>在 LIBERO、SIMPLER 与 Kinova Jaco2 真机上测试；基座含 OpenVLA、OpenVLA-OFT、CogACT。</x:v>
       </x:c>
       <x:c r="AK62" t="str">
-        <x:v>Unknown / Needs Full-Paper Verification</x:v>
+        <x:v>LIBERO 上 OpenVLA 延迟从 51.91 ms 降至 31.83 ms，平均成功率从 75.0% 变为 74.7%；真机平均成功率为 82.1%→84.6%。</x:v>
       </x:c>
       <x:c r="AL62" t="str">
-        <x:v>Unknown / Needs Full-Paper Verification</x:v>
+        <x:v>动态区域增多时缓存收益降低；主要测试 LLaMA2 decoder，对其他 backbone 的适用性待验证。</x:v>
       </x:c>
       <x:c r="AM62" t="str">
-        <x:v>Library Analysis / Research Note: Unknown / Needs Full-Paper Verification</x:v>
+        <x:v>双臂动态视角、不同 VLA backbone 与缓存错误归因仍待验证。</x:v>
       </x:c>
       <x:c r="AN62" t="str">
-        <x:v>** 可用于 VLA/机器人基础模型路线对比；应重点核对动作头、训练数据与真机部署成本是否适合当前平台。</x:v>
+        <x:v>可作为本地 VLA 在线加速候选；需测双臂相机和腕部视角下的时延、频率与成功率。</x:v>
       </x:c>
       <x:c r="AO62" t="str">
         <x:v>VLA; Inference Acceleration / Token Caching</x:v>
       </x:c>
       <x:c r="AP62" t="str">
-        <x:v>B</x:v>
-      </x:c>
-      <x:c r="AQ62" t="str"/>
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="AQ62" t="str">
+        <x:v>对双臂交叉、目标遮挡或动作不确定时触发局部/全量重编码，测试效率和成功率折衷。</x:v>
+      </x:c>
       <x:c r="AR62" t="str">
-        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
+        <x:v>静态 token 直接复用使 SR 84.4→74.2%；attention 过滤恢复至82.6%，layer-adaptive达83.8%（Table 1）。</x:v>
       </x:c>
       <x:c r="AS62" t="str">
-        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
+        <x:v>背景动态使基线 PickPot SR 95→80%；VLA-Cache 在动态条件保持80%且降低FLOPs/延迟；PickPot 真机SR 95→90%（Table 5,7）。</x:v>
       </x:c>
       <x:c r="AT62" t="str">
         <x:v>https://openalex.org/W7196930033</x:v>
       </x:c>
       <x:c r="AU62" t="str">
-        <x:v>https://proceedings.neurips.cc/paper_files/paper/2025/hash/f062da1973ac9ac61fc6d44dd7fa309f-Abstract-Conference.html；官方摘要/论文集元数据</x:v>
+        <x:v>NeurIPS 正式论文页；arXiv PDF §1–6、Appendix A–F、Tables 1–5、7–11；NeurIPS Supplemental zip 与作者 GitHub。</x:v>
       </x:c>
       <x:c r="AV62" t="str">
-        <x:v>B-Fulltext-Unavailable</x:v>
+        <x:v>A-Upgraded</x:v>
       </x:c>
       <x:c r="AW62" t="str">
-        <x:v>Not Found</x:v>
+        <x:v>NeurIPS 官方补充包及 arXiv 附录已检查。</x:v>
       </x:c>
       <x:c r="AX62" t="str">
-        <x:v>Mostly Complete</x:v>
+        <x:v>Partial</x:v>
       </x:c>
       <x:c r="AY62" t="str">
         <x:v>Unknown</x:v>
       </x:c>
-      <x:c r="AZ62"/>
+      <x:c r="AZ62" t="str">
+        <x:v>https://arxiv.org/pdf/2502.02175</x:v>
+      </x:c>
       <x:c r="BA62" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="BB62" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="BC62" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="BD62" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="BE62" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="BF62" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="BG62" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="BH62" t="str">
         <x:v>Not Checked</x:v>
       </x:c>
       <x:c r="BI62" t="str">
-        <x:v>Not Found After Verification</x:v>
+        <x:v>Verified official NeurIPS DOI</x:v>
       </x:c>
       <x:c r="BJ62" t="str">
         <x:v>Not Found After Verification</x:v>
       </x:c>
       <x:c r="BK62" t="str">
-        <x:v>Audit logged - deep extraction pending</x:v>
+        <x:v>Completed-A</x:v>
       </x:c>
       <x:c r="BL62" t="str">
-        <x:v>false</x:v>
-      </x:c>
-      <x:c r="BM62"/>
+        <x:v>true</x:v>
+      </x:c>
+      <x:c r="BM62" t="str">
+        <x:v>Completed-A</x:v>
+      </x:c>
       <x:c r="BN62" t="str">
-        <x:v>VLA 反复处理相似视觉 token，会增加在线推理开销。</x:v>
+        <x:v>研究问题：VLA 在闭环操作过程中连续接收相邻视觉帧，而画面中大量背景和静态区域变化很小。现有模型每个时刻重新计算视觉 token，造成推理开销并限制实时控制频率。；之前方法的问题：通用 token pruning / merging 方法通常在单帧内删减或合并 token；若不考虑视觉区域对当前任务的重要性，可能删掉外观变化很小、但对夹爪或目标物判断至关重要的区域。作者在 LIBERO Spatial 上展示，仅依据静态视觉相似度进行缓存会显著降低成功率。；核心思路：VLA-Cache 是免训练的推理加速方法：识别相邻帧间稳定的视觉 token，跨帧复用其 Key-Value（KV）表示；再利用 decoder attention 排除任务相关区域，并根据各层 attention entropy 自适应调整缓存比例。；输入：- 当前与上一时刻的 RGB 视觉观测，用于计算图像 patch 相似度。；输出与动作：保持原 VLA 基座动作输出；VLA-Cache 只改变推理中的视觉 token 计算与 KV 复用。；数据集与评测基准：LIBERO、SIMPLER，以及 Kinova Jaco2 四项真机操作任务。；主要结果：LIBERO 上 OpenVLA 延迟从 51.91 ms 降至 31.83 ms，平均成功率从 75.0% 变为 74.7%；真机平均成功率为 82.1%→84.6%。；与当前项目的关系：当前项目可将 VLA-Cache 作为已训练 VLA 的在线推理优化候选，重点测试双臂相机画面、腕部视角变化和机械臂运动导致的动态视觉区域，记录延迟、控制频率和任务成功率。原论文没有双臂实验，部署收益需在本项目的机器人和控制接口上重新验证。</x:v>
       </x:c>
       <x:c r="BO62" t="str">
         <x:v>简单缓存可能损害变化场景中的目标识别或动作精度。</x:v>
@@ -23283,7 +23291,7 @@
       <x:c r="BP62" t="str">
         <x:v>VLA-Cache 无需重新训练，按状态自适应缓存并复用部分推理结果。</x:v>
       </x:c>
-      <x:c r="BQ62" t="str"/>
+      <x:c r="BQ62"/>
       <x:c r="BR62" t="str">
         <x:v>作者报告最高约 1.7 倍推理加速；具体成功率影响需按任务核对。</x:v>
       </x:c>
@@ -23293,7 +23301,7 @@
       <x:c r="BT62" t="str">
         <x:v>场景突变或接触后状态变化时，缓存复用可能延迟纠错。</x:v>
       </x:c>
-      <x:c r="BU62" t="str"/>
+      <x:c r="BU62"/>
       <x:c r="BV62" t="str">
         <x:v>High：双臂实时控制需要低延迟，但必须监测缓存失效。</x:v>
       </x:c>
@@ -23303,10 +23311,10 @@
       <x:c r="BX62" t="str">
         <x:v>Exact work identity verified</x:v>
       </x:c>
-      <x:c r="BY62" t="n">
+      <x:c r="BY62" t="str">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="BZ62" t="n">
+      <x:c r="BZ62" t="str">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -23435,7 +23443,7 @@
       <x:c r="AP63" t="str">
         <x:v>A</x:v>
       </x:c>
-      <x:c r="AQ63" t="str"/>
+      <x:c r="AQ63"/>
       <x:c r="AR63" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
@@ -23499,7 +23507,7 @@
       </x:c>
       <x:c r="BM63"/>
       <x:c r="BN63" t="str">
-        <x:v>自回归 VLA 的动作精度与鲁棒性可能不足，而独立的扩散策略又缺少语言推理。</x:v>
+        <x:v>研究问题：自回归 VLA 的动作精度与鲁棒性可能不足，而独立的扩散策略又缺少语言推理。；之前方法的问题：纯自回归动作预测的精度可能不足；只做扩散控制又较难利用语言推理。；核心思路：DiffusionVLA 将自回归推理与扩散式动作生成结合，尝试兼顾语义理解和连续控制。；数据集与评测基准：作者提供 DexVLA 示例数据，但该样例不等于论文全部训练和评测数据。；为什么重要：为双臂 VLA 动作头选择提供“推理 + 生成式控制”的比较对象。；与当前项目的关系：High：有助于研究语言条件操作与 VLA 设计。；主要局限：实验覆盖的任务与本体有限；逐任务失败次数未从已访问页面完整提取。</x:v>
       </x:c>
       <x:c r="BO63" t="str">
         <x:v>纯自回归动作预测的精度可能不足；只做扩散控制又较难利用语言推理。</x:v>
@@ -23507,7 +23515,7 @@
       <x:c r="BP63" t="str">
         <x:v>DiffusionVLA 将自回归推理与扩散式动作生成结合，尝试兼顾语义理解和连续控制。</x:v>
       </x:c>
-      <x:c r="BQ63" t="str"/>
+      <x:c r="BQ63"/>
       <x:c r="BR63" t="str">
         <x:v>卡片记录对 102 个未见抓取物体达到 63.7% 准确率；DiVLA-2B 在单张 A6000 上为 82 Hz（摘要、Sec. 4.5）。</x:v>
       </x:c>
@@ -23517,7 +23525,7 @@
       <x:c r="BT63" t="str">
         <x:v>实验覆盖的任务与本体有限；逐任务失败次数未从已访问页面完整提取。</x:v>
       </x:c>
-      <x:c r="BU63" t="str"/>
+      <x:c r="BU63"/>
       <x:c r="BV63" t="str">
         <x:v>High：有助于研究语言条件操作与 VLA 设计。</x:v>
       </x:c>
@@ -23551,10 +23559,10 @@
         <x:v>ICML</x:v>
       </x:c>
       <x:c r="F64" t="str">
-        <x:v>正式主会论文：官方论文集核实</x:v>
+        <x:v>正式会议论文</x:v>
       </x:c>
       <x:c r="G64" t="str">
-        <x:v>A (CCF 7th edition; venue category not independently extracted from official PDF)</x:v>
+        <x:v>A</x:v>
       </x:c>
       <x:c r="H64" t="str">
         <x:v>VLA / Robot Foundation Models; Robot Manipulation / IL / Diffusion</x:v>
@@ -23568,7 +23576,9 @@
       <x:c r="K64" t="str">
         <x:v>https://proceedings.mlr.press/v235/zhen24a.html</x:v>
       </x:c>
-      <x:c r="L64"/>
+      <x:c r="L64" t="str">
+        <x:v>https://arxiv.org/abs/2403.09631</x:v>
+      </x:c>
       <x:c r="M64" t="str">
         <x:v>https://vis-www.cs.umass.edu/3dvla/</x:v>
       </x:c>
@@ -23621,64 +23631,64 @@
         <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AD64" t="str">
-        <x:v>现有 2D VLA 缺少显式三维结构，难以同时预测动作和未来场景。</x:v>
+        <x:v>2D VLA 对三维空间关系、目标物体位置和动作后的目标状态建模不足。</x:v>
       </x:c>
       <x:c r="AE64" t="str">
-        <x:v>Unknown / Needs Full-Paper Verification</x:v>
+        <x:v>直接从二维观测映射动作，难以显式利用三维关系并预测可供规划使用的目标状态。</x:v>
       </x:c>
       <x:c r="AF64" t="str">
-        <x:v>以 `VLA; World Model / 3D Generation` 为主要方法/能力线索；更细的结构和消融结论待正文核验。</x:v>
+        <x:v>统一 3D 场景特征、目标状态生成与动作 token 的语言模型框架。</x:v>
       </x:c>
       <x:c r="AG64" t="str">
-        <x:v>使用从现有机器人数据整理的三维指令数据；具体数据集组成和规模仍需核对全文。</x:v>
+        <x:v>- 作者从 Open X-Embodiment 中选取 12 个机器人数据集，并结合 Dobb-E、RH20T 的深度信息来源；还使用 RLBench、CALVIN 仿真数据，以及 Epic-Kitchens、HOI4D 人类活动数据。具体集合和用途见 §3.1、Appendix Table 8。</x:v>
       </x:c>
       <x:c r="AH64" t="str">
-        <x:v>Unknown / Needs Full-Paper Verification</x:v>
+        <x:v>推理：3D-LLM、BLIP2、OpenFlamingo、LLaVA；定位：Kosmos-2、CoVLM；目标生成：Instruct-P2P、SuSIE、NeXT-GPT、Point-E；规划：LanCon-Learn、MCIL。</x:v>
       </x:c>
       <x:c r="AI64" t="str">
-        <x:v>- 3D-VLA: A 3D Vision-Language-Action Generative World ModelHaoyu</x:v>
+        <x:v>统一处理三维场景理解、目标图像/点云生成与机器人动作 token；构建大规模 3D 具身指令数据。</x:v>
       </x:c>
       <x:c r="AJ64" t="str">
-        <x:v>Real Robot 字段为 `Unknown`；Dataset、Benchmark、Robot Platform 中的 Unknown 继续保留，不从题名推断。</x:v>
+        <x:v>具身问答/描述、3D 定位、目标图像与点云生成，以及 RLBench、CALVIN 仿真规划；未核实真机或双臂实验。</x:v>
       </x:c>
       <x:c r="AK64" t="str">
-        <x:v>Unknown / Needs Full-Paper Verification</x:v>
+        <x:v>3D 定位 IoU 29.33；目标点云 P-FID/Chamfer-L1=4.796/0.139；CALVIN 五任务完成率为 0（Table 2,4,6）。</x:v>
       </x:c>
       <x:c r="AL64" t="str">
-        <x:v>Unknown / Needs Full-Paper Verification</x:v>
+        <x:v>小物体精细操作受限；生成目标可 hallucinate；深度尺度和点云噪声影响真实场景表现。</x:v>
       </x:c>
       <x:c r="AM64" t="str">
-        <x:v>Library Analysis / Research Note: Unknown / Needs Full-Paper Verification</x:v>
+        <x:v>目标一致性、长时程执行、精细动作量化和真实 3D 感知仍待解决。</x:v>
       </x:c>
       <x:c r="AN64" t="str">
-        <x:v>** 可用于 VLA/机器人基础模型路线对比；应重点核对动作头、训练数据与真机部署成本是否适合当前平台。</x:v>
+        <x:v>可用于双臂普通夹爪项目的目标生成和 3D grounding 基线设计；论文未验证双臂或真机，需实测。</x:v>
       </x:c>
       <x:c r="AO64" t="str">
         <x:v>VLA; World Model / 3D Generation</x:v>
       </x:c>
       <x:c r="AP64" t="str">
-        <x:v>B</x:v>
+        <x:v>A</x:v>
       </x:c>
       <x:c r="AQ64" t="str">
-        <x:v>Idea Clue 1: compare explicit 3D goal prediction against image-only VLA on dual-arm ordinary-gripper tasks. Evidence: paper motivation and 3D goal image/point-cloud generation. Why relevant: direct test of 3D planning value.</x:v>
+        <x:v>在规划前检查生成目标与当前场景/任务的一致性，评估能否减少目标 hallucination 引发的执行错误；属于待检索研究问题。</x:v>
       </x:c>
       <x:c r="AR64" t="str">
-        <x:v>Not Reported in the accessible proceedings page.</x:v>
+        <x:v>去掉预测 bounding box 后，目标图像指标混合变化、点云指标变差；去掉 Goal 后 RLBench 四任务由 68/80/40/28 降至 58/68/34/24。Tables 3–5。</x:v>
       </x:c>
       <x:c r="AS64" t="str">
-        <x:v>Not Explicitly Reported in the accessible proceedings page.</x:v>
+        <x:v>§6：目标生成可能改变纹理/形状、令物体消失、预测不相关的未来或状态无变化；小物体精细操作失败。</x:v>
       </x:c>
       <x:c r="AT64" t="str">
         <x:v>https://openalex.org/W4392886475</x:v>
       </x:c>
       <x:c r="AU64" t="str">
-        <x:v>https://proceedings.mlr.press/v235/zhen24a.html；官方摘要/论文集元数据</x:v>
+        <x:v>PMLR 官方 PDF：§3.1–3.3、§4.1–4.3、§5.1–5.3、§6–7；Figures 2–3、5–6；Tables 1–6、Appendix Tables 7–9。https://raw.githubusercontent.com/mlresearch/v235/main/assets/zhen24a/zhen24a.pdf</x:v>
       </x:c>
       <x:c r="AV64" t="str">
-        <x:v>B-Fulltext-Unavailable</x:v>
+        <x:v>A-Upgraded</x:v>
       </x:c>
       <x:c r="AW64" t="str">
-        <x:v>Not Found</x:v>
+        <x:v>官方 PDF 内 Appendix A–D 已检查；未找到独立补充包。</x:v>
       </x:c>
       <x:c r="AX64" t="str">
         <x:v>Partial</x:v>
@@ -23686,46 +23696,50 @@
       <x:c r="AY64" t="str">
         <x:v>Unknown</x:v>
       </x:c>
-      <x:c r="AZ64"/>
+      <x:c r="AZ64" t="str">
+        <x:v>https://raw.githubusercontent.com/mlresearch/v235/main/assets/zhen24a/zhen24a.pdf</x:v>
+      </x:c>
       <x:c r="BA64" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="BB64" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="BC64" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="BD64" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="BE64" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="BF64" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="BG64" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="BH64" t="str">
         <x:v>Not Checked</x:v>
       </x:c>
       <x:c r="BI64" t="str">
-        <x:v>Not Found After Verification</x:v>
+        <x:v>arXiv DOI verified; proceedings DOI not located</x:v>
       </x:c>
       <x:c r="BJ64" t="str">
         <x:v>Not Found After Verification</x:v>
       </x:c>
       <x:c r="BK64" t="str">
-        <x:v>Audit logged - deep extraction pending</x:v>
+        <x:v>Completed-A</x:v>
       </x:c>
       <x:c r="BL64" t="str">
-        <x:v>false</x:v>
-      </x:c>
-      <x:c r="BM64"/>
+        <x:v>true</x:v>
+      </x:c>
+      <x:c r="BM64" t="str">
+        <x:v>Completed-A</x:v>
+      </x:c>
       <x:c r="BN64" t="str">
-        <x:v>现有 2D VLA 缺少显式三维结构，难以同时预测动作和未来场景。</x:v>
+        <x:v>研究问题：不少 VLA 方法主要从视觉观测直接预测动作，对场景三维关系、被操作物体的位置以及动作执行后的目标状态建模不足。作者研究如何让一个模型同时处理 3D 场景理解、语言指令、目标状态生成和机器人动作规划。；之前方法的问题：作者指出，2D 视觉特征难以充分表达空间关系；已有 3D 多模态语言模型的预训练目标和数据未必与具身任务对齐。因此本文没有直接加载预训练 3D-LLM 权重，而是采用 BLIP2-FlanT5XL 作为语言模型骨干，并训练具身相关表示和输出。；核心思路：把 3D 场景特征、物体与位置标记、目标图像/点云生成，以及离散机器人动作 token 放进统一的语言模型流程。模型可以先根据任务想象目标状态，再把该状态作为动作规划的条件。；输入：- 视觉：单视角或多视角 RGB 图像；构造 3D 场景输入时使用深度或点云信息。；与当前项目的关系：本文与 VLA grounding、三维目标表示和目标状态生成高度相关。对当前双臂普通夹爪项目，可借鉴“先预测目标状态、再条件化动作”的评测思路；但论文所查实验没有给出双臂普通夹爪或真机验证，迁移性仍需独立实验确认。</x:v>
       </x:c>
       <x:c r="BO64" t="str">
         <x:v>现有 VLA 对三维关系和环境动态的建模不足，难以把动作预测与未来场景变化结合。</x:v>
@@ -23757,10 +23771,10 @@
       <x:c r="BX64" t="str">
         <x:v>Exact work identity verified</x:v>
       </x:c>
-      <x:c r="BY64" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BZ64" t="n">
+      <x:c r="BY64" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BZ64" t="str">
         <x:v>9</x:v>
       </x:c>
     </x:row>
@@ -23872,7 +23886,7 @@
         <x:v>Real Robot 字段为 `Unknown`；Dataset、Benchmark、Robot Platform 中的 Unknown 继续保留，不从题名推断。</x:v>
       </x:c>
       <x:c r="AK65" t="str">
-        <x:v>Unknown / Needs Full-Paper Verification</x:v>
+        <x:v>论文报告在仿真与真机姿态预测任务中优于所比较 VLA，推理速度约为其 3 倍；具体比较对象见原文。</x:v>
       </x:c>
       <x:c r="AL65" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -23889,7 +23903,7 @@
       <x:c r="AP65" t="str">
         <x:v>B</x:v>
       </x:c>
-      <x:c r="AQ65" t="str"/>
+      <x:c r="AQ65"/>
       <x:c r="AR65" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
@@ -23953,7 +23967,7 @@
       </x:c>
       <x:c r="BM65"/>
       <x:c r="BN65" t="str">
-        <x:v>VLA 要兼顾视觉语言推理、动作预测和可承受的微调/推理成本。</x:v>
+        <x:v>研究问题：VLA 要兼顾视觉语言推理、动作预测和可承受的微调/推理成本。；之前方法的问题：已有 VLA 在复杂任务推理与微调计算成本之间存在权衡。；核心思路：RoboMamba 以 Mamba 架构建立端到端 VLA，重点降低适配和在线推理成本。；主要结果：论文报告在仿真与真机姿态预测任务中优于所比较 VLA，推理速度约为其 3 倍；具体比较对象见原文。；为什么重要：可作为部署时的速度—能力权衡参考。；与当前项目的关系：High：有助于研究语言条件操作与 VLA 设计。</x:v>
       </x:c>
       <x:c r="BO65" t="str">
         <x:v>已有 VLA 在复杂任务推理与微调计算成本之间存在权衡。</x:v>
@@ -23961,7 +23975,7 @@
       <x:c r="BP65" t="str">
         <x:v>RoboMamba 以 Mamba 架构建立端到端 VLA，重点降低适配和在线推理成本。</x:v>
       </x:c>
-      <x:c r="BQ65" t="str"/>
+      <x:c r="BQ65"/>
       <x:c r="BR65" t="str">
         <x:v>论文报告在仿真与真机姿态预测任务中优于所比较 VLA，推理速度约为其 3 倍；具体比较对象见原文。</x:v>
       </x:c>
@@ -23971,7 +23985,7 @@
       <x:c r="BT65" t="str">
         <x:v>目前证据不足以证明其机器人和任务覆盖达到大型通用策略的广度。</x:v>
       </x:c>
-      <x:c r="BU65" t="str"/>
+      <x:c r="BU65"/>
       <x:c r="BV65" t="str">
         <x:v>High：有助于研究语言条件操作与 VLA 设计。</x:v>
       </x:c>
@@ -24113,7 +24127,7 @@
       <x:c r="AP66" t="str">
         <x:v>B</x:v>
       </x:c>
-      <x:c r="AQ66" t="str"/>
+      <x:c r="AQ66"/>
       <x:c r="AR66" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
@@ -24177,7 +24191,7 @@
       </x:c>
       <x:c r="BM66"/>
       <x:c r="BN66" t="str">
-        <x:v>大规模预训练 VLA 对交互中的时空动态仍可能理解不足。</x:v>
+        <x:v>研究问题：大规模预训练 VLA 对交互中的时空动态仍可能理解不足。；之前方法的问题：只看当前帧，难表示动作轨迹和目标运动方向。；核心思路：TraceVLA 将状态—动作轨迹可视化为 trace prompt，辅助 VLA 做时空推理与动作预测。；数据集与评测基准：SimplerEnv 137 种配置与 WidowX 真机四项任务。；为什么重要：为视觉轨迹提示如何改善 VLA 提供可测实例。；与当前项目的关系：High：双臂任务可以比较轨迹提示与显式状态估计。；主要局限：单臂 WidowX 结果不直接覆盖双臂真机。</x:v>
       </x:c>
       <x:c r="BO66" t="str">
         <x:v>只看当前帧，难表示动作轨迹和目标运动方向。</x:v>
@@ -24185,7 +24199,7 @@
       <x:c r="BP66" t="str">
         <x:v>TraceVLA 将状态—动作轨迹可视化为 trace prompt，辅助 VLA 做时空推理与动作预测。</x:v>
       </x:c>
-      <x:c r="BQ66" t="str"/>
+      <x:c r="BQ66"/>
       <x:c r="BR66" t="str">
         <x:v>卡片记录相对 OpenVLA 在 SimplerEnv 高约 10%，真机任务表现约为 3.5 倍；指标定义见原卡。</x:v>
       </x:c>
@@ -24195,7 +24209,7 @@
       <x:c r="BT66" t="str">
         <x:v>单臂 WidowX 结果不直接覆盖双臂真机。</x:v>
       </x:c>
-      <x:c r="BU66" t="str"/>
+      <x:c r="BU66"/>
       <x:c r="BV66" t="str">
         <x:v>High：双臂任务可以比较轨迹提示与显式状态估计。</x:v>
       </x:c>
@@ -24320,7 +24334,7 @@
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
       </x:c>
       <x:c r="AK67" t="str">
-        <x:v>Unknown / Needs Full-Paper Verification</x:v>
+        <x:v>作者报告部分真机操作任务上优于使用机器人动作标签训练的对照 VLA；具体协议见论文。</x:v>
       </x:c>
       <x:c r="AL67" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -24337,7 +24351,7 @@
       <x:c r="AP67" t="str">
         <x:v>B</x:v>
       </x:c>
-      <x:c r="AQ67" t="str"/>
+      <x:c r="AQ67"/>
       <x:c r="AR67" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
@@ -24401,7 +24415,7 @@
       </x:c>
       <x:c r="BM67"/>
       <x:c r="BN67" t="str">
-        <x:v>互联网视频规模大，但缺少机器人动作标签。</x:v>
+        <x:v>研究问题：互联网视频规模大，但缺少机器人动作标签。；之前方法的问题：传统 VLA 预训练高度依赖昂贵的机器人动作数据。；核心思路：LAPA 从无动作标签视频学习潜在动作，再用这些表示预训练视觉语言动作模型。；主要结果：作者报告部分真机操作任务上优于使用机器人动作标签训练的对照 VLA；具体协议见论文。；为什么重要：提供低成本视频数据进入 VLA 预训练的路线。；与当前项目的关系：High：双臂示范稀缺，可研究潜在动作是否可迁移。；主要局限：潜在动作与真实普通夹爪命令之间需要可靠解码。</x:v>
       </x:c>
       <x:c r="BO67" t="str">
         <x:v>传统 VLA 预训练高度依赖昂贵的机器人动作数据。</x:v>
@@ -24409,7 +24423,7 @@
       <x:c r="BP67" t="str">
         <x:v>LAPA 从无动作标签视频学习潜在动作，再用这些表示预训练视觉语言动作模型。</x:v>
       </x:c>
-      <x:c r="BQ67" t="str"/>
+      <x:c r="BQ67"/>
       <x:c r="BR67" t="str">
         <x:v>作者报告部分真机操作任务上优于使用机器人动作标签训练的对照 VLA；具体协议见论文。</x:v>
       </x:c>
@@ -24419,7 +24433,7 @@
       <x:c r="BT67" t="str">
         <x:v>潜在动作与真实普通夹爪命令之间需要可靠解码。</x:v>
       </x:c>
-      <x:c r="BU67" t="str"/>
+      <x:c r="BU67"/>
       <x:c r="BV67" t="str">
         <x:v>High：双臂示范稀缺，可研究潜在动作是否可迁移。</x:v>
       </x:c>
@@ -24542,7 +24556,7 @@
         <x:v>Real Robot 字段为 `Unknown`；Dataset、Benchmark、Robot Platform 中的 Unknown 继续保留，不从题名推断。</x:v>
       </x:c>
       <x:c r="AK68" t="str">
-        <x:v>Unknown / Needs Full-Paper Verification</x:v>
+        <x:v>AAAI 摘要报告在 Adroit 与 MetaWorld 上保持有竞争力的成功率，同时推理速度提高约 7 倍。</x:v>
       </x:c>
       <x:c r="AL68" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -24559,7 +24573,7 @@
       <x:c r="AP68" t="str">
         <x:v>B</x:v>
       </x:c>
-      <x:c r="AQ68" t="str"/>
+      <x:c r="AQ68"/>
       <x:c r="AR68" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
@@ -24623,7 +24637,7 @@
       </x:c>
       <x:c r="BM68"/>
       <x:c r="BN68" t="str">
-        <x:v>扩散/流式动作生成往往需要多次采样，在线控制延迟较高。</x:v>
+        <x:v>研究问题：扩散/流式动作生成往往需要多次采样，在线控制延迟较高。；之前方法的问题：生成质量与推理速度之间存在权衡。；核心思路：FlowPolicy 使用三维点云和 consistency flow matching，在单次推理中生成动作。；输入：官方摘要给出任务/数据类型；具体模型张量与接口需核对方法章节。；输出与动作：官方摘要未明确列出完整控制接口；需核对论文方法或代码。；数据集与评测基准：Adroit、MetaWorld。；主要结果：AAAI 摘要报告在 Adroit 与 MetaWorld 上保持有竞争力的成功率，同时推理速度提高约 7 倍。；为什么重要：双臂真机尤其关注动作频率；该工作可用于比较速度与成功率。；与当前项目的关系：Medium：方法可借鉴，但迁移到当前双臂硬件需验证。；主要局限：本段基于官方摘要；未覆盖全文失败案例、完整 Baseline 与方法消融。</x:v>
       </x:c>
       <x:c r="BO68" t="str">
         <x:v>生成质量与推理速度之间存在权衡。</x:v>
@@ -24631,7 +24645,7 @@
       <x:c r="BP68" t="str">
         <x:v>FlowPolicy 使用三维点云和 consistency flow matching，在单次推理中生成动作。</x:v>
       </x:c>
-      <x:c r="BQ68" t="str"/>
+      <x:c r="BQ68"/>
       <x:c r="BR68" t="str">
         <x:v>AAAI 摘要报告在 Adroit 与 MetaWorld 上保持有竞争力的成功率，同时推理速度提高约 7 倍。</x:v>
       </x:c>
@@ -24641,7 +24655,7 @@
       <x:c r="BT68" t="str">
         <x:v>本段基于官方摘要；未覆盖全文失败案例、完整 Baseline 与方法消融。</x:v>
       </x:c>
-      <x:c r="BU68" t="str"/>
+      <x:c r="BU68"/>
       <x:c r="BV68" t="str">
         <x:v>Medium：方法可借鉴，但迁移到当前双臂硬件需验证。</x:v>
       </x:c>
@@ -24766,7 +24780,7 @@
         <x:v>Real Robot 字段为 `Unknown`；Dataset、Benchmark、Robot Platform 中的 Unknown 继续保留，不从题名推断。</x:v>
       </x:c>
       <x:c r="AK69" t="str">
-        <x:v>Unknown / Needs Full-Paper Verification</x:v>
+        <x:v>作者报告在多个物体类别上优于 UniDexGrasp++；具体成功率需查实验表。</x:v>
       </x:c>
       <x:c r="AL69" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -24783,7 +24797,7 @@
       <x:c r="AP69" t="str">
         <x:v>B</x:v>
       </x:c>
-      <x:c r="AQ69" t="str"/>
+      <x:c r="AQ69"/>
       <x:c r="AR69" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
@@ -24847,7 +24861,7 @@
       </x:c>
       <x:c r="BM69"/>
       <x:c r="BN69" t="str">
-        <x:v>通用灵巧手抓取需要在不同物体类别上预测稳定抓法。</x:v>
+        <x:v>研究问题：通用灵巧手抓取需要在不同物体类别上预测稳定抓法。；之前方法的问题：复杂训练流程和手型依赖限制方法复用。；核心思路：UniGraspTransformer 用统一的 Transformer 网络预测灵巧抓取，并简化训练过程。；主要结果：作者报告在多个物体类别上优于 UniDexGrasp++；具体成功率需查实验表。；为什么重要：提供跨物体抓取模型的简洁架构基线。；与当前项目的关系：Medium：模型结构可参考，但需重做普通夹爪动作输出。；主要局限：灵巧手抓取 benchmark 与双臂真机任务仍有差距。</x:v>
       </x:c>
       <x:c r="BO69" t="str">
         <x:v>复杂训练流程和手型依赖限制方法复用。</x:v>
@@ -24855,7 +24869,7 @@
       <x:c r="BP69" t="str">
         <x:v>UniGraspTransformer 用统一的 Transformer 网络预测灵巧抓取，并简化训练过程。</x:v>
       </x:c>
-      <x:c r="BQ69" t="str"/>
+      <x:c r="BQ69"/>
       <x:c r="BR69" t="str">
         <x:v>作者报告在多个物体类别上优于 UniDexGrasp++；具体成功率需查实验表。</x:v>
       </x:c>
@@ -24865,7 +24879,7 @@
       <x:c r="BT69" t="str">
         <x:v>灵巧手抓取 benchmark 与双臂真机任务仍有差距。</x:v>
       </x:c>
-      <x:c r="BU69" t="str"/>
+      <x:c r="BU69"/>
       <x:c r="BV69" t="str">
         <x:v>Medium：模型结构可参考，但需重做普通夹爪动作输出。</x:v>
       </x:c>
@@ -25007,7 +25021,7 @@
       <x:c r="AP70" t="str">
         <x:v>B</x:v>
       </x:c>
-      <x:c r="AQ70" t="str"/>
+      <x:c r="AQ70"/>
       <x:c r="AR70" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
@@ -25071,7 +25085,7 @@
       </x:c>
       <x:c r="BM70"/>
       <x:c r="BN70" t="str">
-        <x:v>灵巧手操作数据和训练成本高，复杂任务还需要语义理解。</x:v>
+        <x:v>研究问题：灵巧手操作数据和训练成本高，复杂任务还需要语义理解。；之前方法的问题：纯低层策略难从少量示范组织多步任务。；核心思路：用 VLM 提供高层任务结构和语义线索，支撑灵巧手低层操作学习。；为什么重要：展示 VLM 规划与低层动作之间的接口问题。；与当前项目的关系：Medium：双臂普通夹爪也需要高低层协作。；主要局限：仿真灵巧手结果不能直接推断双臂真机表现。</x:v>
       </x:c>
       <x:c r="BO70" t="str">
         <x:v>纯低层策略难从少量示范组织多步任务。</x:v>
@@ -25079,7 +25093,7 @@
       <x:c r="BP70" t="str">
         <x:v>用 VLM 提供高层任务结构和语义线索，支撑灵巧手低层操作学习。</x:v>
       </x:c>
-      <x:c r="BQ70" t="str"/>
+      <x:c r="BQ70"/>
       <x:c r="BR70" t="str">
         <x:v>论文报告在关节物体及语义理解仿真任务中验证方法；具体数值需查正文。</x:v>
       </x:c>
@@ -25089,7 +25103,7 @@
       <x:c r="BT70" t="str">
         <x:v>仿真灵巧手结果不能直接推断双臂真机表现。</x:v>
       </x:c>
-      <x:c r="BU70" t="str"/>
+      <x:c r="BU70"/>
       <x:c r="BV70" t="str">
         <x:v>Medium：双臂普通夹爪也需要高低层协作。</x:v>
       </x:c>
@@ -25214,7 +25228,7 @@
         <x:v>Real Robot 字段为 `Unknown`；Dataset、Benchmark、Robot Platform 中的 Unknown 继续保留，不从题名推断。</x:v>
       </x:c>
       <x:c r="AK71" t="str">
-        <x:v>Unknown / Needs Full-Paper Verification</x:v>
+        <x:v>作者报告想象未来质量与动作可靠性、任务成功相关；具体数字见实验章节。</x:v>
       </x:c>
       <x:c r="AL71" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -25231,7 +25245,7 @@
       <x:c r="AP71" t="str">
         <x:v>B</x:v>
       </x:c>
-      <x:c r="AQ71" t="str"/>
+      <x:c r="AQ71"/>
       <x:c r="AR71" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
@@ -25295,7 +25309,7 @@
       </x:c>
       <x:c r="BM71"/>
       <x:c r="BN71" t="str">
-        <x:v>开放环境操作需要预见动作后果并适应新场景。</x:v>
+        <x:v>研究问题：开放环境操作需要预见动作后果并适应新场景。；之前方法的问题：只从当前视觉预测动作，可能缺少对未来状态的理解。；核心思路：VideoVLA 将视频生成模型用于 VLA，利用想象的未来画面帮助动作选择。；主要结果：作者报告想象未来质量与动作可靠性、任务成功相关；具体数字见实验章节。；为什么重要：把世界模型式视觉预期与机器人动作生成连接起来。；与当前项目的关系：High：可用于双臂动作前预期与动作后验证。；主要局限：视频看起来合理不一定代表接触力与夹爪动作正确。</x:v>
       </x:c>
       <x:c r="BO71" t="str">
         <x:v>只从当前视觉预测动作，可能缺少对未来状态的理解。</x:v>
@@ -25303,7 +25317,7 @@
       <x:c r="BP71" t="str">
         <x:v>VideoVLA 将视频生成模型用于 VLA，利用想象的未来画面帮助动作选择。</x:v>
       </x:c>
-      <x:c r="BQ71" t="str"/>
+      <x:c r="BQ71"/>
       <x:c r="BR71" t="str">
         <x:v>作者报告想象未来质量与动作可靠性、任务成功相关；具体数字见实验章节。</x:v>
       </x:c>
@@ -25313,7 +25327,7 @@
       <x:c r="BT71" t="str">
         <x:v>视频看起来合理不一定代表接触力与夹爪动作正确。</x:v>
       </x:c>
-      <x:c r="BU71" t="str"/>
+      <x:c r="BU71"/>
       <x:c r="BV71" t="str">
         <x:v>High：可用于双臂动作前预期与动作后验证。</x:v>
       </x:c>
@@ -25455,7 +25469,7 @@
       <x:c r="AP72" t="str">
         <x:v>B</x:v>
       </x:c>
-      <x:c r="AQ72" t="str"/>
+      <x:c r="AQ72"/>
       <x:c r="AR72" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
@@ -25519,7 +25533,7 @@
       </x:c>
       <x:c r="BM72"/>
       <x:c r="BN72" t="str">
-        <x:v>语言驱动的灵巧抓取要同时理解任务语义、三维几何和接触关系。</x:v>
+        <x:v>研究问题：语言驱动的灵巧抓取要同时理解任务语义、三维几何和接触关系。；之前方法的问题：只预测抓取位姿未必符合语言中隐含的使用目的。；核心思路：DextER 在抓取生成中加入基于接触的具身推理，使手部接触与任务意图对齐。；数据集与评测基准：DexGYS。；为什么重要：将语言 Grounding 与可执行接触联系起来。；与当前项目的关系：Medium：普通夹爪也需要意图对齐，但手部接触自由度不同。；主要局限：从多指接触迁移到两只普通夹爪需重新定义动作空间。</x:v>
       </x:c>
       <x:c r="BO72" t="str">
         <x:v>只预测抓取位姿未必符合语言中隐含的使用目的。</x:v>
@@ -25527,7 +25541,7 @@
       <x:c r="BP72" t="str">
         <x:v>DextER 在抓取生成中加入基于接触的具身推理，使手部接触与任务意图对齐。</x:v>
       </x:c>
-      <x:c r="BQ72" t="str"/>
+      <x:c r="BQ72"/>
       <x:c r="BR72" t="str">
         <x:v>卡片记录 DexGYS 成功率 67.14%，较所比较 SOTA 高 3.83 个百分点。</x:v>
       </x:c>
@@ -25537,7 +25551,7 @@
       <x:c r="BT72" t="str">
         <x:v>从多指接触迁移到两只普通夹爪需重新定义动作空间。</x:v>
       </x:c>
-      <x:c r="BU72" t="str"/>
+      <x:c r="BU72"/>
       <x:c r="BV72" t="str">
         <x:v>Medium：普通夹爪也需要意图对齐，但手部接触自由度不同。</x:v>
       </x:c>
@@ -25662,7 +25676,7 @@
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
       </x:c>
       <x:c r="AK73" t="str">
-        <x:v>Unknown / Needs Full-Paper Verification</x:v>
+        <x:v>作者报告较好的分布内泛化和分布外适配；具体比较数字见论文。</x:v>
       </x:c>
       <x:c r="AL73" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -25679,7 +25693,7 @@
       <x:c r="AP73" t="str">
         <x:v>B</x:v>
       </x:c>
-      <x:c r="AQ73" t="str"/>
+      <x:c r="AQ73"/>
       <x:c r="AR73" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
@@ -25743,7 +25757,7 @@
       </x:c>
       <x:c r="BM73"/>
       <x:c r="BN73" t="str">
-        <x:v>机器人操作需要把视觉与语言理解落实到三维空间关系。</x:v>
+        <x:v>研究问题：机器人操作需要把视觉与语言理解落实到三维空间关系。；之前方法的问题：普通 VLA 的视觉 token 可能缺少显式三维位置线索。；核心思路：SpatialVLA 加入 Ego3D Position Encoding，使空间信息参与 VLA 输入和动作预测。；主要结果：作者报告较好的分布内泛化和分布外适配；具体比较数字见论文。；为什么重要：为 VLA 的三维 Grounding 提供明确的表示方案。；与当前项目的关系：High：双臂普通夹爪需要准确的目标与相对位姿。；主要局限：需要检验相机标定变化与遮挡下的稳健性。</x:v>
       </x:c>
       <x:c r="BO73" t="str">
         <x:v>普通 VLA 的视觉 token 可能缺少显式三维位置线索。</x:v>
@@ -25751,7 +25765,7 @@
       <x:c r="BP73" t="str">
         <x:v>SpatialVLA 加入 Ego3D Position Encoding，使空间信息参与 VLA 输入和动作预测。</x:v>
       </x:c>
-      <x:c r="BQ73" t="str"/>
+      <x:c r="BQ73"/>
       <x:c r="BR73" t="str">
         <x:v>作者报告较好的分布内泛化和分布外适配；具体比较数字见论文。</x:v>
       </x:c>
@@ -25761,7 +25775,7 @@
       <x:c r="BT73" t="str">
         <x:v>需要检验相机标定变化与遮挡下的稳健性。</x:v>
       </x:c>
-      <x:c r="BU73" t="str"/>
+      <x:c r="BU73"/>
       <x:c r="BV73" t="str">
         <x:v>High：双臂普通夹爪需要准确的目标与相对位姿。</x:v>
       </x:c>
@@ -25903,7 +25917,7 @@
       <x:c r="AP74" t="str">
         <x:v>A</x:v>
       </x:c>
-      <x:c r="AQ74" t="str"/>
+      <x:c r="AQ74"/>
       <x:c r="AR74" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
@@ -25967,7 +25981,7 @@
       </x:c>
       <x:c r="BM74"/>
       <x:c r="BN74" t="str">
-        <x:v>现有 VLA 多为闭源，且针对新任务高效微调的方法仍不充分。</x:v>
+        <x:v>研究问题：现有 VLA 多为闭源，且针对新任务高效微调的方法仍不充分。；之前方法的问题：既有 VLA 多为闭源，新任务的高效微调方法也缺少系统评估。；核心思路：OpenVLA 是开放的 7B VLA，在约 97 万条真实机器人轨迹上训练，支持通过微调适配新任务。；输入：机器人相机图像和语言任务指令；具体预处理见论文方法及官方代码。；输出与动作：预测机器人控制动作；动作编码与本体适配以官方代码和论文方法为准。；数据集与评测基准：训练使用整理后的 Open X-Embodiment 混合数据，约 97 万条真机轨迹；DROID 在后期训练数据中被剔除，详见原卡。；为什么重要：提供可复用的 VLA 基线，同时明确了数据、算力和推理速度代价。；与当前项目的关系：High：有助于研究语言条件操作与 VLA 设计。；主要局限：作者指出训练数据偏单臂、第三人称视角且算力成本高；双臂/移动平台迁移仍需单独验证。</x:v>
       </x:c>
       <x:c r="BO74" t="str">
         <x:v>既有 VLA 多为闭源，新任务的高效微调方法也缺少系统评估。</x:v>
@@ -25975,7 +25989,7 @@
       <x:c r="BP74" t="str">
         <x:v>OpenVLA 是开放的 7B VLA，在约 97 万条真实机器人轨迹上训练，支持通过微调适配新任务。</x:v>
       </x:c>
-      <x:c r="BQ74" t="str"/>
+      <x:c r="BQ74"/>
       <x:c r="BR74" t="str">
         <x:v>卡片记录在 29 项任务/本体评测中相对 55B RT-2-X 的成功率高 16.5 个百分点；微调设置下相对 Diffusion Policy 高 20.4 个百分点。推理约 6 Hz（RTX 4090）；比较条件详见原卡。</x:v>
       </x:c>
@@ -25985,7 +25999,7 @@
       <x:c r="BT74" t="str">
         <x:v>作者指出训练数据偏单臂、第三人称视角且算力成本高；双臂/移动平台迁移仍需单独验证。</x:v>
       </x:c>
-      <x:c r="BU74" t="str"/>
+      <x:c r="BU74"/>
       <x:c r="BV74" t="str">
         <x:v>High：有助于研究语言条件操作与 VLA 设计。</x:v>
       </x:c>
@@ -26110,7 +26124,7 @@
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
       </x:c>
       <x:c r="AK75" t="str">
-        <x:v>Unknown / Needs Full-Paper Verification</x:v>
+        <x:v>论文在 9 种机器人平台上评测，表明 Octo 可迁移到新的观测和动作空间；具体成功率见原卡实验表。</x:v>
       </x:c>
       <x:c r="AL75" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -26127,7 +26141,7 @@
       <x:c r="AP75" t="str">
         <x:v>A</x:v>
       </x:c>
-      <x:c r="AQ75" t="str"/>
+      <x:c r="AQ75"/>
       <x:c r="AR75" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
@@ -26191,7 +26205,7 @@
       </x:c>
       <x:c r="BM75"/>
       <x:c r="BN75" t="str">
-        <x:v>通用机器人策略需要同时适配不同相机、动作空间和机器人平台。</x:v>
+        <x:v>研究问题：通用机器人策略需要同时适配不同相机、动作空间和机器人平台。；之前方法的问题：各机器人平台的相机、动作空间与任务不同，单一策略难以直接跨平台使用。；核心思路：Octo 在 Open X-Embodiment 约 80 万条轨迹上训练 Transformer 策略，并提供可微调的通用初始化。；数据集与评测基准：从 Open X-Embodiment 整理约 80 万条训练轨迹，在 9 种机器人平台和多项下游任务上评估。；主要结果：论文在 9 种机器人平台上评测，表明 Octo 可迁移到新的观测和动作空间；具体成功率见原卡实验表。；为什么重要：是研究共享机器人数据与跨本体微调的重要开放基线。；与当前项目的关系：High：有助于研究语言条件操作与 VLA 设计。；主要局限：训练数据的腕部相机和语言覆盖不均；评测主要在论文列出的单臂/双臂平台。</x:v>
       </x:c>
       <x:c r="BO75" t="str">
         <x:v>各机器人平台的相机、动作空间与任务不同，单一策略难以直接跨平台使用。</x:v>
@@ -26199,7 +26213,7 @@
       <x:c r="BP75" t="str">
         <x:v>Octo 在 Open X-Embodiment 约 80 万条轨迹上训练 Transformer 策略，并提供可微调的通用初始化。</x:v>
       </x:c>
-      <x:c r="BQ75" t="str"/>
+      <x:c r="BQ75"/>
       <x:c r="BR75" t="str">
         <x:v>论文在 9 种机器人平台上评测，表明 Octo 可迁移到新的观测和动作空间；具体成功率见原卡实验表。</x:v>
       </x:c>
@@ -26209,7 +26223,7 @@
       <x:c r="BT75" t="str">
         <x:v>训练数据的腕部相机和语言覆盖不均；评测主要在论文列出的单臂/双臂平台。</x:v>
       </x:c>
-      <x:c r="BU75" t="str"/>
+      <x:c r="BU75"/>
       <x:c r="BV75" t="str">
         <x:v>High：有助于研究语言条件操作与 VLA 设计。</x:v>
       </x:c>
@@ -26330,7 +26344,7 @@
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
       </x:c>
       <x:c r="AK76" t="str">
-        <x:v>Unknown / Needs Full-Paper Verification</x:v>
+        <x:v>论文摘要报告，使用 DROID 训练的策略在性能、鲁棒性和泛化上改善；此处不附加未经实验表格核实的增幅。</x:v>
       </x:c>
       <x:c r="AL76" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -26347,7 +26361,7 @@
       <x:c r="AP76" t="str">
         <x:v>B</x:v>
       </x:c>
-      <x:c r="AQ76" t="str"/>
+      <x:c r="AQ76"/>
       <x:c r="AR76" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
@@ -26411,7 +26425,7 @@
       </x:c>
       <x:c r="BM76"/>
       <x:c r="BN76" t="str">
-        <x:v>通用操作策略需要规模大、场景多样且质量可靠的机器人交互数据。</x:v>
+        <x:v>研究问题：通用操作策略需要规模大、场景多样且质量可靠的机器人交互数据。；之前方法的问题：跨环境采集成本高，并受安全、硬件和人力协调限制。；核心思路：DROID 组织分布式采集，形成 6.5 万条示范轨迹、约 350 小时交互，覆盖 564 个场景和 86 项任务。；数据集与评测基准：DROID：约 6.5 万条轨迹／350 小时、564 个场景、86 项任务，50 名采集人员在 12 个月内完成。；主要结果：论文摘要报告，使用 DROID 训练的策略在性能、鲁棒性和泛化上改善；此处不附加未经实验表格核实的增幅。；为什么重要：为跨场景数据采集和数据规模设计提供具体参照。；与当前项目的关系：Medium：可借鉴采集协议，但需核对与本项目机器人形态和动作接口的差异。；主要局限：摘要不能分离数据量、场景多样性与策略结构各自的贡献。</x:v>
       </x:c>
       <x:c r="BO76" t="str">
         <x:v>跨环境采集成本高，并受安全、硬件和人力协调限制。</x:v>
@@ -26419,7 +26433,7 @@
       <x:c r="BP76" t="str">
         <x:v>DROID 组织分布式采集，形成 6.5 万条示范轨迹、约 350 小时交互，覆盖 564 个场景和 86 项任务。</x:v>
       </x:c>
-      <x:c r="BQ76" t="str"/>
+      <x:c r="BQ76"/>
       <x:c r="BR76" t="str">
         <x:v>论文摘要报告，使用 DROID 训练的策略在性能、鲁棒性和泛化上改善；此处不附加未经实验表格核实的增幅。</x:v>
       </x:c>
@@ -26429,7 +26443,7 @@
       <x:c r="BT76" t="str">
         <x:v>摘要不能分离数据量、场景多样性与策略结构各自的贡献。</x:v>
       </x:c>
-      <x:c r="BU76" t="str"/>
+      <x:c r="BU76"/>
       <x:c r="BV76" t="str">
         <x:v>Medium：可借鉴采集协议，但需核对与本项目机器人形态和动作接口的差异。</x:v>
       </x:c>
@@ -26554,7 +26568,7 @@
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
       </x:c>
       <x:c r="AK77" t="str">
-        <x:v>Unknown / Needs Full-Paper Verification</x:v>
+        <x:v>RSS 官方摘要报告，合成数据用于大规模模仿学习呈现规模效应；本轮不转述未经表格核验的成功率。</x:v>
       </x:c>
       <x:c r="AL77" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -26571,7 +26585,7 @@
       <x:c r="AP77" t="str">
         <x:v>B</x:v>
       </x:c>
-      <x:c r="AQ77" t="str"/>
+      <x:c r="AQ77"/>
       <x:c r="AR77" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
@@ -26637,7 +26651,7 @@
       </x:c>
       <x:c r="BM77"/>
       <x:c r="BN77" t="str">
-        <x:v>真实机器人数据难以低成本扩展，限制通用家庭操作策略训练。</x:v>
+        <x:v>研究问题：真实机器人数据难以低成本扩展，限制通用家庭操作策略训练。；之前方法的问题：场景、任务和示范的规模不足；仅靠真机采集难以覆盖家庭环境多样性。；核心思路：RoboCasa 建立以厨房为中心的大规模仿真框架，结合生成式资产、语言模型辅助任务设计、人类示范和自动轨迹生成。；数据集与评测基准：RSS 2024 原版 RoboCasa：100 项任务、超过 150 个物体类别及大量 3D 资产；不要与后续 RoboCasa365 的规模混同。；主要结果：RSS 官方摘要报告，合成数据用于大规模模仿学习呈现规模效应；本轮不转述未经表格核验的成功率。；为什么重要：可用于研究仿真数据扩增及与真实机器人数据联合训练。；与当前项目的关系：Medium：家庭操作仿真可借鉴，但与本项目场景、双臂配置和真实部署有差异。；主要局限：摘要不能保证仿真训练所得提升直接迁移至本项目真机。</x:v>
       </x:c>
       <x:c r="BO77" t="str">
         <x:v>场景、任务和示范的规模不足；仅靠真机采集难以覆盖家庭环境多样性。</x:v>
@@ -26645,7 +26659,7 @@
       <x:c r="BP77" t="str">
         <x:v>RoboCasa 建立以厨房为中心的大规模仿真框架，结合生成式资产、语言模型辅助任务设计、人类示范和自动轨迹生成。</x:v>
       </x:c>
-      <x:c r="BQ77" t="str"/>
+      <x:c r="BQ77"/>
       <x:c r="BR77" t="str">
         <x:v>RSS 官方摘要报告，合成数据用于大规模模仿学习呈现规模效应；本轮不转述未经表格核验的成功率。</x:v>
       </x:c>
@@ -26655,7 +26669,7 @@
       <x:c r="BT77" t="str">
         <x:v>摘要不能保证仿真训练所得提升直接迁移至本项目真机。</x:v>
       </x:c>
-      <x:c r="BU77" t="str"/>
+      <x:c r="BU77"/>
       <x:c r="BV77" t="str">
         <x:v>Medium：家庭操作仿真可借鉴，但与本项目场景、双臂配置和真实部署有差异。</x:v>
       </x:c>
@@ -26776,7 +26790,7 @@
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
       </x:c>
       <x:c r="AK78" t="str">
-        <x:v>Unknown / Needs Full-Paper Verification</x:v>
+        <x:v>官方项目与论文报告跨机器人训练带来的泛化收益；具体任务数值见原论文。</x:v>
       </x:c>
       <x:c r="AL78" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -26793,7 +26807,7 @@
       <x:c r="AP78" t="str">
         <x:v>B</x:v>
       </x:c>
-      <x:c r="AQ78" t="str"/>
+      <x:c r="AQ78"/>
       <x:c r="AR78" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
@@ -26857,7 +26871,7 @@
       </x:c>
       <x:c r="BM78"/>
       <x:c r="BN78" t="str">
-        <x:v>机器人数据分散在不同机构、平台和格式中，难以训练通用策略。</x:v>
+        <x:v>研究问题：机器人数据分散在不同机构、平台和格式中，难以训练通用策略。；之前方法的问题：每个机器人和任务单独训练模型，跨平台复用成本高。；核心思路：Open X-Embodiment 整合标准化的跨机器人数据，并训练 RT-X 模型测试共享学习。；输入：官方摘要给出任务/数据类型；具体模型张量与接口需核对方法章节。；输出与动作：官方摘要未明确列出完整控制接口；需核对论文方法或代码。；数据集与评测基准：Open X-Embodiment 数据混合及 RT-X 评测。；主要结果：官方项目与论文报告跨机器人训练带来的泛化收益；具体任务数值见原论文。；为什么重要：是审计跨本体数据、动作格式和策略迁移的基础入口。；与当前项目的关系：Medium：方法可借鉴，但迁移到当前双臂硬件需验证。；主要局限：本段基于官方摘要；未覆盖全文失败案例、完整 Baseline 与方法消融。</x:v>
       </x:c>
       <x:c r="BO78" t="str">
         <x:v>每个机器人和任务单独训练模型，跨平台复用成本高。</x:v>
@@ -26865,7 +26879,7 @@
       <x:c r="BP78" t="str">
         <x:v>Open X-Embodiment 整合标准化的跨机器人数据，并训练 RT-X 模型测试共享学习。</x:v>
       </x:c>
-      <x:c r="BQ78" t="str"/>
+      <x:c r="BQ78"/>
       <x:c r="BR78" t="str">
         <x:v>官方项目与论文报告跨机器人训练带来的泛化收益；具体任务数值见原论文。</x:v>
       </x:c>
@@ -26875,7 +26889,7 @@
       <x:c r="BT78" t="str">
         <x:v>本段基于官方摘要；未覆盖全文失败案例、完整 Baseline 与方法消融。</x:v>
       </x:c>
-      <x:c r="BU78" t="str"/>
+      <x:c r="BU78"/>
       <x:c r="BV78" t="str">
         <x:v>Medium：方法可借鉴，但迁移到当前双臂硬件需验证。</x:v>
       </x:c>
@@ -27085,7 +27099,7 @@
       </x:c>
       <x:c r="BM79"/>
       <x:c r="BN79" t="str">
-        <x:v>VLA 的视觉注意可能落在任务无关区域，削弱精细操作与泛化。</x:v>
+        <x:v>研究问题：VLA 的视觉注意可能落在任务无关区域，削弱精细操作与泛化。；之前方法的问题：原有 VLA 难以稳定把视觉注意对准目标区域；显式标注 Grounding 的方案又可能增加数据要求。；核心思路：ReconVLA 用扩散式重建目标注视区域，促使视觉表示聚焦被操作物体，同时保留动作预测。；输入：RGB 图像历史和语言指令；重建注视区域作为中间视觉目标（Sec. 3、Fig. 2）。；为什么重要：直接对应本项目的目标 Grounding 与动作前目标核验。；与当前项目的关系：High：有助于研究语言条件操作与 VLA 设计。；主要局限：作者指出性能取决于目标区域重建是否正确；公开评测主要集中在 CALVIN 与有限真机任务。跨本体和新相机条件仍需验证。</x:v>
       </x:c>
       <x:c r="BO79" t="str">
         <x:v>原有 VLA 难以稳定把视觉注意对准目标区域；显式标注 Grounding 的方案又可能增加数据要求。</x:v>
@@ -27144,7 +27158,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5fc28476572740b6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5dd6c5d1410d48ea"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -27660,7 +27674,7 @@
         <x:v>Real Robot 字段为 `Mixed`；Dataset、Benchmark、Robot Platform 中的 Unknown 继续保留，不从题名推断。</x:v>
       </x:c>
       <x:c r="BE2" t="str">
-        <x:v>Unknown / Needs Full-Paper Verification</x:v>
+        <x:v>作者报告仿真和真机成功率高于所比较方法；具体数值见实验表。</x:v>
       </x:c>
       <x:c r="BF2" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -27674,7 +27688,7 @@
       <x:c r="BI2" t="str">
         <x:v>B</x:v>
       </x:c>
-      <x:c r="BJ2" t="str"/>
+      <x:c r="BJ2"/>
       <x:c r="BK2" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
@@ -27738,7 +27752,7 @@
       </x:c>
       <x:c r="CF2"/>
       <x:c r="CG2" t="str">
-        <x:v>多任务机器人操作要同时决定高层子目标和符合运动学的连续动作。</x:v>
+        <x:v>研究问题：多任务机器人操作要同时决定高层子目标和符合运动学的连续动作。；之前方法的问题：单层扩散策略可能难兼顾长任务结构与局部可达性。；核心思路：Hierarchical Diffusion Policy 将任务规划与运动学感知的动作生成分层处理。；主要结果：作者报告仿真和真机成功率高于所比较方法；具体数值见实验表。；为什么重要：可对照双臂任务中高层分工与低层动作生成。；与当前项目的关系：High：双臂普通夹爪也需要运动学约束和任务分解。；主要局限：需核验在两臂共享工作空间中的约束处理。</x:v>
       </x:c>
       <x:c r="CH2" t="str">
         <x:v>单层扩散策略可能难兼顾长任务结构与局部可达性。</x:v>
@@ -27746,7 +27760,7 @@
       <x:c r="CI2" t="str">
         <x:v>Hierarchical Diffusion Policy 将任务规划与运动学感知的动作生成分层处理。</x:v>
       </x:c>
-      <x:c r="CJ2" t="str"/>
+      <x:c r="CJ2"/>
       <x:c r="CK2" t="str">
         <x:v>作者报告仿真和真机成功率高于所比较方法；具体数值见实验表。</x:v>
       </x:c>
@@ -27756,7 +27770,7 @@
       <x:c r="CM2" t="str">
         <x:v>需核验在两臂共享工作空间中的约束处理。</x:v>
       </x:c>
-      <x:c r="CN2" t="str"/>
+      <x:c r="CN2"/>
       <x:c r="CO2" t="str">
         <x:v>High：双臂普通夹爪也需要运动学约束和任务分解。</x:v>
       </x:c>
@@ -27935,7 +27949,7 @@
         <x:v>Real Robot 字段为 `Unknown`；Dataset、Benchmark、Robot Platform 中的 Unknown 继续保留，不从题名推断。</x:v>
       </x:c>
       <x:c r="BE3" t="str">
-        <x:v>Unknown / Needs Full-Paper Verification</x:v>
+        <x:v>论文报告在七项 RoboTwin 任务上较所比较 SOTA 提升 23.5%；具体指标定义见原文。</x:v>
       </x:c>
       <x:c r="BF3" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -27949,7 +27963,7 @@
       <x:c r="BI3" t="str">
         <x:v>B</x:v>
       </x:c>
-      <x:c r="BJ3" t="str"/>
+      <x:c r="BJ3"/>
       <x:c r="BK3" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
@@ -28013,7 +28027,7 @@
       </x:c>
       <x:c r="CF3"/>
       <x:c r="CG3" t="str">
-        <x:v>不同双臂任务的交互结构不同，统一耦合方式未必合适。</x:v>
+        <x:v>研究问题：不同双臂任务的交互结构不同，统一耦合方式未必合适。；之前方法的问题：始终联合预测双臂动作，可能忽略支撑手与操作手的不同职责。；核心思路：按任务交互特点设计解耦框架，让双臂策略分别处理可分解的部分并保持必要协调。；数据集与评测基准：RoboTwin 七项任务。；主要结果：论文报告在七项 RoboTwin 任务上较所比较 SOTA 提升 23.5%；具体指标定义见原文。；为什么重要：为联合预测与分臂预测的实验对照提供方法。；与当前项目的关系：High：普通夹爪常有支撑—操作分工。；主要局限：仿真 benchmark 上的优势仍需真机接触任务验证。</x:v>
       </x:c>
       <x:c r="CH3" t="str">
         <x:v>始终联合预测双臂动作，可能忽略支撑手与操作手的不同职责。</x:v>
@@ -28021,7 +28035,7 @@
       <x:c r="CI3" t="str">
         <x:v>按任务交互特点设计解耦框架，让双臂策略分别处理可分解的部分并保持必要协调。</x:v>
       </x:c>
-      <x:c r="CJ3" t="str"/>
+      <x:c r="CJ3"/>
       <x:c r="CK3" t="str">
         <x:v>论文报告在七项 RoboTwin 任务上较所比较 SOTA 提升 23.5%；具体指标定义见原文。</x:v>
       </x:c>
@@ -28031,7 +28045,7 @@
       <x:c r="CM3" t="str">
         <x:v>仿真 benchmark 上的优势仍需真机接触任务验证。</x:v>
       </x:c>
-      <x:c r="CN3" t="str"/>
+      <x:c r="CN3"/>
       <x:c r="CO3" t="str">
         <x:v>High：普通夹爪常有支撑—操作分工。</x:v>
       </x:c>
@@ -28210,7 +28224,7 @@
         <x:v>Real Robot 字段为 `Yes`；Dataset、Benchmark、Robot Platform 中的 Unknown 继续保留，不从题名推断。</x:v>
       </x:c>
       <x:c r="BE4" t="str">
-        <x:v>Unknown / Needs Full-Paper Verification</x:v>
+        <x:v>论文报告在上述设置中成功率高于 ACT 基线；具体差值需核对实验表。</x:v>
       </x:c>
       <x:c r="BF4" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -28224,7 +28238,7 @@
       <x:c r="BI4" t="str">
         <x:v>B</x:v>
       </x:c>
-      <x:c r="BJ4" t="str"/>
+      <x:c r="BJ4"/>
       <x:c r="BK4" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
@@ -28288,7 +28302,7 @@
       </x:c>
       <x:c r="CF4"/>
       <x:c r="CG4" t="str">
-        <x:v>复杂双臂任务需要预测动作，也需要理解后续视觉状态。</x:v>
+        <x:v>研究问题：复杂双臂任务需要预测动作，也需要理解后续视觉状态。；之前方法的问题：只学动作或只生成视频，可能无法协调两臂与物体变化。；核心思路：联合优化视频预测与双臂动作生成，让策略在想象未来场景的同时协调执行。；数据集与评测基准：两项仿真 benchmark 与一项真机设置。；主要结果：论文报告在上述设置中成功率高于 ACT 基线；具体差值需核对实验表。；为什么重要：可测试视觉预期是否改善双臂协调。；与当前项目的关系：High：双臂普通夹爪可对照 ACT 与带未来预测的策略。</x:v>
       </x:c>
       <x:c r="CH4" t="str">
         <x:v>只学动作或只生成视频，可能无法协调两臂与物体变化。</x:v>
@@ -28296,7 +28310,7 @@
       <x:c r="CI4" t="str">
         <x:v>联合优化视频预测与双臂动作生成，让策略在想象未来场景的同时协调执行。</x:v>
       </x:c>
-      <x:c r="CJ4" t="str"/>
+      <x:c r="CJ4"/>
       <x:c r="CK4" t="str">
         <x:v>论文报告在上述设置中成功率高于 ACT 基线；具体差值需核对实验表。</x:v>
       </x:c>
@@ -28306,7 +28320,7 @@
       <x:c r="CM4" t="str">
         <x:v>真机环境和失败类型的完整覆盖仍需查正文。</x:v>
       </x:c>
-      <x:c r="CN4" t="str"/>
+      <x:c r="CN4"/>
       <x:c r="CO4" t="str">
         <x:v>High：双臂普通夹爪可对照 ACT 与带未来预测的策略。</x:v>
       </x:c>
@@ -28485,7 +28499,7 @@
         <x:v>Real Robot 字段为 `Mixed`；Dataset、Benchmark、Robot Platform 中的 Unknown 继续保留，不从题名推断。</x:v>
       </x:c>
       <x:c r="BE5" t="str">
-        <x:v>Unknown / Needs Full-Paper Verification</x:v>
+        <x:v>AAAI 摘要报告在两项仿真 benchmark 和真机任务中优于所比较方法；未给统一量化值。</x:v>
       </x:c>
       <x:c r="BF5" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -28499,7 +28513,7 @@
       <x:c r="BI5" t="str">
         <x:v>B</x:v>
       </x:c>
-      <x:c r="BJ5" t="str"/>
+      <x:c r="BJ5"/>
       <x:c r="BK5" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
@@ -28563,7 +28577,7 @@
       </x:c>
       <x:c r="CF5"/>
       <x:c r="CG5" t="str">
-        <x:v>长任务的高层指令与短时动作之间容易出现不一致。</x:v>
+        <x:v>研究问题：长任务的高层指令与短时动作之间容易出现不一致。；之前方法的问题：只用全局指令条件化扩散策略，难以保证每段动作符合当前小技能。；核心思路：SDP 把复杂任务拆成八种 primitive skills，用 VLM 提取离散状态表示，再由轻量 router 选择技能条件化扩散策略。；输入：官方摘要给出任务/数据类型；具体模型张量与接口需核对方法章节。；输出与动作：官方摘要未明确列出完整控制接口；需核对论文方法或代码。；数据集与评测基准：两项仿真 benchmark 与真机操作评测。；主要结果：AAAI 摘要报告在两项仿真 benchmark 和真机任务中优于所比较方法；未给统一量化值。；为什么重要：可作为“高层技能调度 + 低层动作生成”的双臂基线。；与当前项目的关系：Medium：方法可借鉴，但迁移到当前双臂硬件需验证。；主要局限：本段基于官方摘要；未覆盖全文失败案例、完整 Baseline 与方法消融。</x:v>
       </x:c>
       <x:c r="CH5" t="str">
         <x:v>只用全局指令条件化扩散策略，难以保证每段动作符合当前小技能。</x:v>
@@ -28571,7 +28585,7 @@
       <x:c r="CI5" t="str">
         <x:v>SDP 把复杂任务拆成八种 primitive skills，用 VLM 提取离散状态表示，再由轻量 router 选择技能条件化扩散策略。</x:v>
       </x:c>
-      <x:c r="CJ5" t="str"/>
+      <x:c r="CJ5"/>
       <x:c r="CK5" t="str">
         <x:v>AAAI 摘要报告在两项仿真 benchmark 和真机任务中优于所比较方法；未给统一量化值。</x:v>
       </x:c>
@@ -28581,7 +28595,7 @@
       <x:c r="CM5" t="str">
         <x:v>本段基于官方摘要；未覆盖全文失败案例、完整 Baseline 与方法消融。</x:v>
       </x:c>
-      <x:c r="CN5" t="str"/>
+      <x:c r="CN5"/>
       <x:c r="CO5" t="str">
         <x:v>Medium：方法可借鉴，但迁移到当前双臂硬件需验证。</x:v>
       </x:c>
@@ -28760,7 +28774,7 @@
         <x:v>Real Robot 字段为 `Mixed`；Dataset、Benchmark、Robot Platform 中的 Unknown 继续保留，不从题名推断。</x:v>
       </x:c>
       <x:c r="BE6" t="str">
-        <x:v>Unknown / Needs Full-Paper Verification</x:v>
+        <x:v>AAAI 摘要报告仿真与真机超过 100 项任务，成功率相对基线最高提升 41%；另发布 80 多项仿真任务。</x:v>
       </x:c>
       <x:c r="BF6" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -28774,7 +28788,7 @@
       <x:c r="BI6" t="str">
         <x:v>B</x:v>
       </x:c>
-      <x:c r="BJ6" t="str"/>
+      <x:c r="BJ6"/>
       <x:c r="BK6" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
@@ -28838,7 +28852,7 @@
       </x:c>
       <x:c r="CF6"/>
       <x:c r="CG6" t="str">
-        <x:v>多任务模仿学习策略需要可靠动作，也需要用少量示范适应未见任务。</x:v>
+        <x:v>研究问题：多任务模仿学习策略需要可靠动作，也需要用少量示范适应未见任务。；之前方法的问题：只根据当前状态重建动作，可能缺少对动作视觉后果的预测。；核心思路：FoAM 输入多模态目标，在动作重建之外加入 foresight augmentation，让策略利用预期视觉结果。；输入：官方摘要给出任务/数据类型；具体模型张量与接口需核对方法章节。；输出与动作：官方摘要未明确列出完整控制接口；需核对论文方法或代码。；数据集与评测基准：超过 100 项仿真/真机任务；官方发布的仿真任务套件。；主要结果：AAAI 摘要报告仿真与真机超过 100 项任务，成功率相对基线最高提升 41%；另发布 80 多项仿真任务。；为什么重要：可比较“预见动作后果”是否帮助双臂动作前验证。；与当前项目的关系：Medium：方法可借鉴，但迁移到当前双臂硬件需验证。；主要局限：本段基于官方摘要；未覆盖全文失败案例、完整 Baseline 与方法消融。</x:v>
       </x:c>
       <x:c r="CH6" t="str">
         <x:v>只根据当前状态重建动作，可能缺少对动作视觉后果的预测。</x:v>
@@ -28846,7 +28860,7 @@
       <x:c r="CI6" t="str">
         <x:v>FoAM 输入多模态目标，在动作重建之外加入 foresight augmentation，让策略利用预期视觉结果。</x:v>
       </x:c>
-      <x:c r="CJ6" t="str"/>
+      <x:c r="CJ6"/>
       <x:c r="CK6" t="str">
         <x:v>AAAI 摘要报告仿真与真机超过 100 项任务，成功率相对基线最高提升 41%；另发布 80 多项仿真任务。</x:v>
       </x:c>
@@ -28856,7 +28870,7 @@
       <x:c r="CM6" t="str">
         <x:v>本段基于官方摘要；未覆盖全文失败案例、完整 Baseline 与方法消融。</x:v>
       </x:c>
-      <x:c r="CN6" t="str"/>
+      <x:c r="CN6"/>
       <x:c r="CO6" t="str">
         <x:v>Medium：方法可借鉴，但迁移到当前双臂硬件需验证。</x:v>
       </x:c>
@@ -29035,7 +29049,7 @@
         <x:v>Real Robot 字段为 `Mixed`；Dataset、Benchmark、Robot Platform 中的 Unknown 继续保留，不从题名推断。</x:v>
       </x:c>
       <x:c r="BE7" t="str">
-        <x:v>Unknown / Needs Full-Paper Verification</x:v>
+        <x:v>AAAI 官方摘要报告仿真与实体机器人验证，并进行了规划器和蒸馏方法消融；未给统一数值。</x:v>
       </x:c>
       <x:c r="BF7" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -29049,7 +29063,7 @@
       <x:c r="BI7" t="str">
         <x:v>B</x:v>
       </x:c>
-      <x:c r="BJ7" t="str"/>
+      <x:c r="BJ7"/>
       <x:c r="BK7" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
@@ -29113,7 +29127,7 @@
       </x:c>
       <x:c r="CF7"/>
       <x:c r="CG7" t="str">
-        <x:v>长时序接触操作既要完成任务，也要避免过大接触力损伤物体。</x:v>
+        <x:v>研究问题：长时序接触操作既要完成任务，也要避免过大接触力损伤物体。；之前方法的问题：真机专家示范昂贵，分层技能和安全约束难以同时获得。；核心思路：在仿真中用带力约束的 RL 训练原子技能，再由 VLM 规划任务，最后蒸馏到视觉—触觉 Diffusion Policy。；输入：官方摘要给出任务/数据类型；具体模型张量与接口需核对方法章节。；输出与动作：官方摘要未明确列出完整控制接口；需核对论文方法或代码。；数据集与评测基准：仿真与实体机器人接触操作任务。；主要结果：AAAI 官方摘要报告仿真与实体机器人验证，并进行了规划器和蒸馏方法消融；未给统一数值。；为什么重要：为普通夹爪的接触安全和低成本技能数据生成提供参考。；与当前项目的关系：Medium：方法可借鉴，但迁移到当前双臂硬件需验证。；主要局限：本段基于官方摘要；未覆盖全文失败案例、完整 Baseline 与方法消融。</x:v>
       </x:c>
       <x:c r="CH7" t="str">
         <x:v>真机专家示范昂贵，分层技能和安全约束难以同时获得。</x:v>
@@ -29121,7 +29135,7 @@
       <x:c r="CI7" t="str">
         <x:v>在仿真中用带力约束的 RL 训练原子技能，再由 VLM 规划任务，最后蒸馏到视觉—触觉 Diffusion Policy。</x:v>
       </x:c>
-      <x:c r="CJ7" t="str"/>
+      <x:c r="CJ7"/>
       <x:c r="CK7" t="str">
         <x:v>AAAI 官方摘要报告仿真与实体机器人验证，并进行了规划器和蒸馏方法消融；未给统一数值。</x:v>
       </x:c>
@@ -29131,7 +29145,7 @@
       <x:c r="CM7" t="str">
         <x:v>本段基于官方摘要；未覆盖全文失败案例、完整 Baseline 与方法消融。</x:v>
       </x:c>
-      <x:c r="CN7" t="str"/>
+      <x:c r="CN7"/>
       <x:c r="CO7" t="str">
         <x:v>Medium：方法可借鉴，但迁移到当前双臂硬件需验证。</x:v>
       </x:c>
@@ -29310,7 +29324,7 @@
         <x:v>Real Robot 字段为 `Yes`；Dataset、Benchmark、Robot Platform 中的 Unknown 继续保留，不从题名推断。</x:v>
       </x:c>
       <x:c r="BE8" t="str">
-        <x:v>Unknown / Needs Full-Paper Verification</x:v>
+        <x:v>AAAI 官方摘要报告泛化测试成功率 87%，数据效率约为所比较 SOTA 的 5 倍。</x:v>
       </x:c>
       <x:c r="BF8" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -29324,7 +29338,7 @@
       <x:c r="BI8" t="str">
         <x:v>B</x:v>
       </x:c>
-      <x:c r="BJ8" t="str"/>
+      <x:c r="BJ8"/>
       <x:c r="BK8" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
@@ -29388,7 +29402,7 @@
       </x:c>
       <x:c r="CF8"/>
       <x:c r="CG8" t="str">
-        <x:v>通用人形机器人操作常依赖大量示范，未见场景中的几何推理仍薄弱。</x:v>
+        <x:v>研究问题：通用人形机器人操作常依赖大量示范，未见场景中的几何推理仍薄弱。；之前方法的问题：单纯数据驱动策略难以高效建模机器人与目标之间的空间关系。；核心思路：RGMP 用带几何先验的技能选择器推理子任务，再用递归 Gaussian 网络生成动作。；输入：官方摘要给出任务/数据类型；具体模型张量与接口需核对方法章节。；输出与动作：官方摘要未明确列出完整控制接口；需核对论文方法或代码。；数据集与评测基准：人形机器人与桌面机器人操作评测。；主要结果：AAAI 官方摘要报告泛化测试成功率 87%，数据效率约为所比较 SOTA 的 5 倍。；为什么重要：可启发双臂任务的几何关系表示，但硬件差异需要单独验证。；与当前项目的关系：Medium：方法可借鉴，但迁移到当前双臂硬件需验证。；主要局限：本段基于官方摘要；未覆盖全文失败案例、完整 Baseline 与方法消融。</x:v>
       </x:c>
       <x:c r="CH8" t="str">
         <x:v>单纯数据驱动策略难以高效建模机器人与目标之间的空间关系。</x:v>
@@ -29396,7 +29410,7 @@
       <x:c r="CI8" t="str">
         <x:v>RGMP 用带几何先验的技能选择器推理子任务，再用递归 Gaussian 网络生成动作。</x:v>
       </x:c>
-      <x:c r="CJ8" t="str"/>
+      <x:c r="CJ8"/>
       <x:c r="CK8" t="str">
         <x:v>AAAI 官方摘要报告泛化测试成功率 87%，数据效率约为所比较 SOTA 的 5 倍。</x:v>
       </x:c>
@@ -29406,7 +29420,7 @@
       <x:c r="CM8" t="str">
         <x:v>本段基于官方摘要；未覆盖全文失败案例、完整 Baseline 与方法消融。</x:v>
       </x:c>
-      <x:c r="CN8" t="str"/>
+      <x:c r="CN8"/>
       <x:c r="CO8" t="str">
         <x:v>Medium：方法可借鉴，但迁移到当前双臂硬件需验证。</x:v>
       </x:c>
@@ -29583,7 +29597,7 @@
         <x:v>Real Robot 字段为 `Unknown`；Dataset、Benchmark、Robot Platform 中的 Unknown 继续保留，不从题名推断。</x:v>
       </x:c>
       <x:c r="BE9" t="str">
-        <x:v>Unknown / Needs Full-Paper Verification</x:v>
+        <x:v>官方 AAAI 摘要报告三类仿真与真机任务上的成功率和新物体泛化优于对比方法，并展示跨机械手部署；摘要未给统一数值。</x:v>
       </x:c>
       <x:c r="BF9" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -29597,7 +29611,7 @@
       <x:c r="BI9" t="str">
         <x:v>B</x:v>
       </x:c>
-      <x:c r="BJ9" t="str"/>
+      <x:c r="BJ9"/>
       <x:c r="BK9" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
@@ -29661,7 +29675,7 @@
       </x:c>
       <x:c r="CF9"/>
       <x:c r="CG9" t="str">
-        <x:v>多指灵巧手操作不同物体时，任务奖励设计和跨手型泛化都很难。</x:v>
+        <x:v>研究问题：多指灵巧手操作不同物体时，任务奖励设计和跨手型泛化都很难。；之前方法的问题：只模仿人手轨迹，难以把物体未来状态变成通用训练目标。；核心思路：从人—物交互数据学习物体运动先验，预测未来物体状态，再把它用于强化学习奖励。；输入：官方摘要给出任务/数据类型；具体模型张量与接口需核对方法章节。；输出与动作：官方摘要未明确列出完整控制接口；需核对论文方法或代码。；数据集与评测基准：三类灵巧操作任务；具体数据集见官方论文。；主要结果：官方 AAAI 摘要报告三类仿真与真机任务上的成功率和新物体泛化优于对比方法，并展示跨机械手部署；摘要未给统一数值。；为什么重要：提出“预测物体状态作为奖励”的路线，可与普通夹爪任务中的目标状态验证比较。；与当前项目的关系：Medium：方法可借鉴，但迁移到当前双臂硬件需验证。；主要局限：本段基于官方摘要；未覆盖全文失败案例、完整 Baseline 与方法消融。</x:v>
       </x:c>
       <x:c r="CH9" t="str">
         <x:v>只模仿人手轨迹，难以把物体未来状态变成通用训练目标。</x:v>
@@ -29669,7 +29683,7 @@
       <x:c r="CI9" t="str">
         <x:v>从人—物交互数据学习物体运动先验，预测未来物体状态，再把它用于强化学习奖励。</x:v>
       </x:c>
-      <x:c r="CJ9" t="str"/>
+      <x:c r="CJ9"/>
       <x:c r="CK9" t="str">
         <x:v>官方 AAAI 摘要报告三类仿真与真机任务上的成功率和新物体泛化优于对比方法，并展示跨机械手部署；摘要未给统一数值。</x:v>
       </x:c>
@@ -29679,7 +29693,7 @@
       <x:c r="CM9" t="str">
         <x:v>本段基于官方摘要；未覆盖全文失败案例、完整 Baseline 与方法消融。</x:v>
       </x:c>
-      <x:c r="CN9" t="str"/>
+      <x:c r="CN9"/>
       <x:c r="CO9" t="str">
         <x:v>Medium：方法可借鉴，但迁移到当前双臂硬件需验证。</x:v>
       </x:c>
@@ -29862,7 +29876,7 @@
         <x:v>Real Robot 字段为 `Unknown`；Dataset、Benchmark、Robot Platform 中的 Unknown 继续保留，不从题名推断。</x:v>
       </x:c>
       <x:c r="BE10" t="str">
-        <x:v>Unknown / Needs Full-Paper Verification</x:v>
+        <x:v>摘要说明其提供仿真与真实数据的统一评测；具体成功率需查实验章节。</x:v>
       </x:c>
       <x:c r="BF10" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -29876,7 +29890,7 @@
       <x:c r="BI10" t="str">
         <x:v>B</x:v>
       </x:c>
-      <x:c r="BJ10" t="str"/>
+      <x:c r="BJ10"/>
       <x:c r="BK10" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
@@ -29940,7 +29954,7 @@
       </x:c>
       <x:c r="CF10"/>
       <x:c r="CG10" t="str">
-        <x:v>双臂协调与复杂物体操作缺少足够多样的高质量示范和贴近现实的评测环境。</x:v>
+        <x:v>研究问题：双臂协调与复杂物体操作缺少足够多样的高质量示范和贴近现实的评测环境。；之前方法的问题：示范稀缺且仿真评测与真实场景存在差距。；核心思路：RoboTwin 用 3D 生成模型及大语言模型构建生成式数字孪生，生成专家数据并建立双臂评测平台。；数据集与评测基准：RoboTwin 含仿真与真实数据；作者提供资源下载和示范采集脚本，本轮未下载核验数据完整性。；主要结果：摘要说明其提供仿真与真实数据的统一评测；具体成功率需查实验章节。；为什么重要：将双臂数据生成与现实对齐评测放入同一框架。；与当前项目的关系：High：与普通夹爪双臂策略的数据和任务设计直接相关。；主要局限：生成数据的物理一致性和真实迁移效果需按论文实验进一步核验。</x:v>
       </x:c>
       <x:c r="CH10" t="str">
         <x:v>示范稀缺且仿真评测与真实场景存在差距。</x:v>
@@ -29948,7 +29962,7 @@
       <x:c r="CI10" t="str">
         <x:v>RoboTwin 用 3D 生成模型及大语言模型构建生成式数字孪生，生成专家数据并建立双臂评测平台。</x:v>
       </x:c>
-      <x:c r="CJ10" t="str"/>
+      <x:c r="CJ10"/>
       <x:c r="CK10" t="str">
         <x:v>摘要说明其提供仿真与真实数据的统一评测；具体成功率需查实验章节。</x:v>
       </x:c>
@@ -29958,7 +29972,7 @@
       <x:c r="CM10" t="str">
         <x:v>生成数据的物理一致性和真实迁移效果需按论文实验进一步核验。</x:v>
       </x:c>
-      <x:c r="CN10" t="str"/>
+      <x:c r="CN10"/>
       <x:c r="CO10" t="str">
         <x:v>High：与普通夹爪双臂策略的数据和任务设计直接相关。</x:v>
       </x:c>
@@ -30157,7 +30171,7 @@
       <x:c r="BI11" t="str">
         <x:v>A</x:v>
       </x:c>
-      <x:c r="BJ11" t="str"/>
+      <x:c r="BJ11"/>
       <x:c r="BK11" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
@@ -30221,7 +30235,7 @@
       </x:c>
       <x:c r="CF11"/>
       <x:c r="CG11" t="str">
-        <x:v>许多 VLA 对三维空间信息的利用不足，影响操作动作的空间准确性与数据效率。</x:v>
+        <x:v>研究问题：许多 VLA 对三维空间信息的利用不足，影响操作动作的空间准确性与数据效率。；之前方法的问题：一些 3D VLA 尚未充分利用三维数据自带的空间结构，影响动作预测的数据效率。；核心思路：BridgeVLA 研究视觉语言模型与三维输入/输出的对齐，让空间结构参与动作预测。；数据集与评测基准：论文评估 RLBench、COLOSSEUM 与 GemBench；预训练数据和下载入口以官方仓库说明为准。；为什么重要：为 VLA 如何利用三维几何信息提供了可比较的基线。；与当前项目的关系：High：有助于研究语言条件操作与 VLA 设计。；主要局限：作者把更充分的 3D 输入/输出对齐与训练效率列为后续方向；当前结果主要验证于报告的 Franka 设置。</x:v>
       </x:c>
       <x:c r="CH11" t="str">
         <x:v>一些 3D VLA 尚未充分利用三维数据自带的空间结构，影响动作预测的数据效率。</x:v>
@@ -30229,7 +30243,7 @@
       <x:c r="CI11" t="str">
         <x:v>BridgeVLA 研究视觉语言模型与三维输入/输出的对齐，让空间结构参与动作预测。</x:v>
       </x:c>
-      <x:c r="CJ11" t="str"/>
+      <x:c r="CJ11"/>
       <x:c r="CK11" t="str">
         <x:v>卡片记录 RLBench 平均成功率 88.2% 对 81.4%，COLOSSEUM 为 64.0% 对 56.7%；其余数值与实验设定见原卡表格证据。</x:v>
       </x:c>
@@ -30239,7 +30253,7 @@
       <x:c r="CM11" t="str">
         <x:v>作者把更充分的 3D 输入/输出对齐与训练效率列为后续方向；当前结果主要验证于报告的 Franka 设置。</x:v>
       </x:c>
-      <x:c r="CN11" t="str"/>
+      <x:c r="CN11"/>
       <x:c r="CO11" t="str">
         <x:v>High：有助于研究语言条件操作与 VLA 设计。</x:v>
       </x:c>
@@ -30296,7 +30310,9 @@
       <x:c r="M12" t="str">
         <x:v>10.52202/085713-5484</x:v>
       </x:c>
-      <x:c r="N12"/>
+      <x:c r="N12" t="str">
+        <x:v>https://arxiv.org/abs/2502.02175</x:v>
+      </x:c>
       <x:c r="O12" t="str">
         <x:v>https://vla-cache.github.io/</x:v>
       </x:c>
@@ -30331,7 +30347,7 @@
         <x:v>Unknown</x:v>
       </x:c>
       <x:c r="Z12" t="str">
-        <x:v>README提供LIBERO部署评估说明；未确认自采真机数据是否全量公开</x:v>
+        <x:v>- LIBERO：沿用 OpenVLA/OpenVLA-OFT 标准设置，Spatial、Object、Goal、Long 四个任务套件，每套 10 个子任务。</x:v>
       </x:c>
       <x:c r="AA12" t="str">
         <x:v>Unknown</x:v>
@@ -30358,7 +30374,7 @@
         <x:v>Official Conference Paper</x:v>
       </x:c>
       <x:c r="AI12" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="AJ12" t="str">
         <x:v>02_Papers/01_VLA/VLA-Cache.md</x:v>
@@ -30370,7 +30386,7 @@
         <x:v>https://proceedings.neurips.cc/paper_files/paper/2025/hash/f062da1973ac9ac61fc6d44dd7fa309f-Abstract-Conference.html; official abstract/proceedings metadata</x:v>
       </x:c>
       <x:c r="AM12" t="str">
-        <x:v>Abstract-level</x:v>
+        <x:v>已核验正文关键章节与官方补充材料</x:v>
       </x:c>
       <x:c r="AN12" t="str">
         <x:v>VLA / Robot Foundation Models</x:v>
@@ -30385,7 +30401,7 @@
         <x:v>Real Robot=Unknown; Dataset/Benchmark/Robot Platform retain Unknown when not verified.</x:v>
       </x:c>
       <x:c r="AR12" t="str">
-        <x:v>** 可用于 VLA/机器人基础模型路线对比；应重点核对动作头、训练数据与真机部署成本是否适合当前平台。</x:v>
+        <x:v>可作为本地 VLA 在线加速候选；需测双臂相机和腕部视角下的时延、频率与成功率。</x:v>
       </x:c>
       <x:c r="AS12" t="str">
         <x:v>Project-stated CCF seventh-edition mapping; official row pending where noted</x:v>
@@ -30403,106 +30419,112 @@
         <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AX12" t="str">
-        <x:v>VLA 反复处理相似视觉 token，会增加在线推理开销。</x:v>
+        <x:v>VLA 对相邻帧重复视觉区域重复计算，增加闭环推理延迟。</x:v>
       </x:c>
       <x:c r="AY12" t="str">
-        <x:v>Unknown / Needs Full-Paper Verification</x:v>
+        <x:v>单帧 token pruning 可能移除外观静态但对动作关键的区域。</x:v>
       </x:c>
       <x:c r="AZ12" t="str">
-        <x:v>以 `VLA; Inference Acceleration / Token Caching` 为主要方法/能力线索；更细的结构和消融结论待正文核验。</x:v>
+        <x:v>跨帧复用静态视觉 token 的 KV 表示；attention 排除任务相关区域，并按层 entropy 自适应复用比例。</x:v>
       </x:c>
       <x:c r="BA12" t="str">
-        <x:v>LIBERO、SIMPLER 与论文真机设置。</x:v>
+        <x:v>LIBERO 四套任务、SIMPLER 两种设置；Kinova Jaco2 四项真机任务，每任务 150–200 条 10 Hz 遥操作轨迹。</x:v>
       </x:c>
       <x:c r="BB12" t="str">
-        <x:v>Unknown / Needs Full-Paper Verification</x:v>
+        <x:v>LIBERO：OpenVLA、SparseVLM、FastV、OpenVLA-OFT；SIMPLER：CogACT；真机：OpenVLA。</x:v>
       </x:c>
       <x:c r="BC12" t="str">
-        <x:v>- This paper introduces VLA-Cache, a training-free inference acceleration method that reduces computational overhead by adaptively caching and reusing static visual tokens across frames.</x:v>
+        <x:v>提出免训练的跨帧视觉 token KV 缓存、任务相关区域过滤与层级自适应复用。</x:v>
       </x:c>
       <x:c r="BD12" t="str">
-        <x:v>Real Robot 字段为 `Unknown`；Dataset、Benchmark、Robot Platform 中的 Unknown 继续保留，不从题名推断。</x:v>
+        <x:v>在 LIBERO、SIMPLER 与 Kinova Jaco2 真机上测试；基座含 OpenVLA、OpenVLA-OFT、CogACT。</x:v>
       </x:c>
       <x:c r="BE12" t="str">
-        <x:v>Unknown / Needs Full-Paper Verification</x:v>
+        <x:v>LIBERO 上 OpenVLA 延迟从 51.91 ms 降至 31.83 ms，平均成功率从 75.0% 变为 74.7%；真机平均成功率为 82.1%→84.6%。</x:v>
       </x:c>
       <x:c r="BF12" t="str">
-        <x:v>Unknown / Needs Full-Paper Verification</x:v>
+        <x:v>动态区域增多时缓存收益降低；主要测试 LLaMA2 decoder，对其他 backbone 的适用性待验证。</x:v>
       </x:c>
       <x:c r="BG12" t="str">
-        <x:v>Library Analysis / Research Note: Unknown / Needs Full-Paper Verification</x:v>
+        <x:v>双臂动态视角、不同 VLA backbone 与缓存错误归因仍待验证。</x:v>
       </x:c>
       <x:c r="BH12" t="str">
         <x:v>VLA; Inference Acceleration / Token Caching</x:v>
       </x:c>
       <x:c r="BI12" t="str">
-        <x:v>B</x:v>
-      </x:c>
-      <x:c r="BJ12" t="str"/>
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="BJ12" t="str">
+        <x:v>对双臂交叉、目标遮挡或动作不确定时触发局部/全量重编码，测试效率和成功率折衷。</x:v>
+      </x:c>
       <x:c r="BK12" t="str">
-        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
+        <x:v>静态 token 直接复用使 SR 84.4→74.2%；attention 过滤恢复至82.6%，layer-adaptive达83.8%（Table 1）。</x:v>
       </x:c>
       <x:c r="BL12" t="str">
-        <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
+        <x:v>背景动态使基线 PickPot SR 95→80%；VLA-Cache 在动态条件保持80%且降低FLOPs/延迟；PickPot 真机SR 95→90%（Table 5,7）。</x:v>
       </x:c>
       <x:c r="BM12" t="str">
         <x:v>https://openalex.org/W7196930033</x:v>
       </x:c>
       <x:c r="BN12" t="str">
-        <x:v>https://proceedings.neurips.cc/paper_files/paper/2025/hash/f062da1973ac9ac61fc6d44dd7fa309f-Abstract-Conference.html；官方摘要/论文集元数据</x:v>
+        <x:v>NeurIPS 正式论文页；arXiv PDF §1–6、Appendix A–F、Tables 1–5、7–11；NeurIPS Supplemental zip 与作者 GitHub。</x:v>
       </x:c>
       <x:c r="BO12" t="str">
-        <x:v>B-Fulltext-Unavailable</x:v>
+        <x:v>A-Upgraded</x:v>
       </x:c>
       <x:c r="BP12" t="str">
-        <x:v>Not Found</x:v>
+        <x:v>NeurIPS 官方补充包及 arXiv 附录已检查。</x:v>
       </x:c>
       <x:c r="BQ12" t="str">
-        <x:v>Mostly Complete</x:v>
+        <x:v>Partial</x:v>
       </x:c>
       <x:c r="BR12" t="str">
         <x:v>Unknown</x:v>
       </x:c>
-      <x:c r="BS12"/>
+      <x:c r="BS12" t="str">
+        <x:v>https://arxiv.org/pdf/2502.02175</x:v>
+      </x:c>
       <x:c r="BT12" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="BU12" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="BV12" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="BW12" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="BX12" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="BY12" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="BZ12" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="CA12" t="str">
         <x:v>Not Checked</x:v>
       </x:c>
       <x:c r="CB12" t="str">
-        <x:v>Not Found After Verification</x:v>
+        <x:v>Verified official NeurIPS DOI</x:v>
       </x:c>
       <x:c r="CC12" t="str">
         <x:v>Not Found After Verification</x:v>
       </x:c>
       <x:c r="CD12" t="str">
-        <x:v>Audit logged - deep extraction pending</x:v>
+        <x:v>Completed-A</x:v>
       </x:c>
       <x:c r="CE12" t="str">
-        <x:v>false</x:v>
-      </x:c>
-      <x:c r="CF12"/>
+        <x:v>true</x:v>
+      </x:c>
+      <x:c r="CF12" t="str">
+        <x:v>Completed-A</x:v>
+      </x:c>
       <x:c r="CG12" t="str">
-        <x:v>VLA 反复处理相似视觉 token，会增加在线推理开销。</x:v>
+        <x:v>研究问题：VLA 在闭环操作过程中连续接收相邻视觉帧，而画面中大量背景和静态区域变化很小。现有模型每个时刻重新计算视觉 token，造成推理开销并限制实时控制频率。；之前方法的问题：通用 token pruning / merging 方法通常在单帧内删减或合并 token；若不考虑视觉区域对当前任务的重要性，可能删掉外观变化很小、但对夹爪或目标物判断至关重要的区域。作者在 LIBERO Spatial 上展示，仅依据静态视觉相似度进行缓存会显著降低成功率。；核心思路：VLA-Cache 是免训练的推理加速方法：识别相邻帧间稳定的视觉 token，跨帧复用其 Key-Value（KV）表示；再利用 decoder attention 排除任务相关区域，并根据各层 attention entropy 自适应调整缓存比例。；输入：- 当前与上一时刻的 RGB 视觉观测，用于计算图像 patch 相似度。；输出与动作：保持原 VLA 基座动作输出；VLA-Cache 只改变推理中的视觉 token 计算与 KV 复用。；数据集与评测基准：LIBERO、SIMPLER，以及 Kinova Jaco2 四项真机操作任务。；主要结果：LIBERO 上 OpenVLA 延迟从 51.91 ms 降至 31.83 ms，平均成功率从 75.0% 变为 74.7%；真机平均成功率为 82.1%→84.6%。；与当前项目的关系：当前项目可将 VLA-Cache 作为已训练 VLA 的在线推理优化候选，重点测试双臂相机画面、腕部视角变化和机械臂运动导致的动态视觉区域，记录延迟、控制频率和任务成功率。原论文没有双臂实验，部署收益需在本项目的机器人和控制接口上重新验证。</x:v>
       </x:c>
       <x:c r="CH12" t="str">
         <x:v>简单缓存可能损害变化场景中的目标识别或动作精度。</x:v>
@@ -30510,7 +30532,7 @@
       <x:c r="CI12" t="str">
         <x:v>VLA-Cache 无需重新训练，按状态自适应缓存并复用部分推理结果。</x:v>
       </x:c>
-      <x:c r="CJ12" t="str"/>
+      <x:c r="CJ12"/>
       <x:c r="CK12" t="str">
         <x:v>作者报告最高约 1.7 倍推理加速；具体成功率影响需按任务核对。</x:v>
       </x:c>
@@ -30520,7 +30542,7 @@
       <x:c r="CM12" t="str">
         <x:v>场景突变或接触后状态变化时，缓存复用可能延迟纠错。</x:v>
       </x:c>
-      <x:c r="CN12" t="str"/>
+      <x:c r="CN12"/>
       <x:c r="CO12" t="str">
         <x:v>High：双臂实时控制需要低延迟，但必须监测缓存失效。</x:v>
       </x:c>
@@ -30530,10 +30552,10 @@
       <x:c r="CQ12" t="str">
         <x:v>Exact work identity verified</x:v>
       </x:c>
-      <x:c r="CR12" t="n">
+      <x:c r="CR12" t="str">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="CS12" t="n">
+      <x:c r="CS12" t="str">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -30719,7 +30741,7 @@
       <x:c r="BI13" t="str">
         <x:v>A</x:v>
       </x:c>
-      <x:c r="BJ13" t="str"/>
+      <x:c r="BJ13"/>
       <x:c r="BK13" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
@@ -30783,7 +30805,7 @@
       </x:c>
       <x:c r="CF13"/>
       <x:c r="CG13" t="str">
-        <x:v>自回归 VLA 的动作精度与鲁棒性可能不足，而独立的扩散策略又缺少语言推理。</x:v>
+        <x:v>研究问题：自回归 VLA 的动作精度与鲁棒性可能不足，而独立的扩散策略又缺少语言推理。；之前方法的问题：纯自回归动作预测的精度可能不足；只做扩散控制又较难利用语言推理。；核心思路：DiffusionVLA 将自回归推理与扩散式动作生成结合，尝试兼顾语义理解和连续控制。；数据集与评测基准：作者提供 DexVLA 示例数据，但该样例不等于论文全部训练和评测数据。；为什么重要：为双臂 VLA 动作头选择提供“推理 + 生成式控制”的比较对象。；与当前项目的关系：High：有助于研究语言条件操作与 VLA 设计。；主要局限：实验覆盖的任务与本体有限；逐任务失败次数未从已访问页面完整提取。</x:v>
       </x:c>
       <x:c r="CH13" t="str">
         <x:v>纯自回归动作预测的精度可能不足；只做扩散控制又较难利用语言推理。</x:v>
@@ -30791,7 +30813,7 @@
       <x:c r="CI13" t="str">
         <x:v>DiffusionVLA 将自回归推理与扩散式动作生成结合，尝试兼顾语义理解和连续控制。</x:v>
       </x:c>
-      <x:c r="CJ13" t="str"/>
+      <x:c r="CJ13"/>
       <x:c r="CK13" t="str">
         <x:v>卡片记录对 102 个未见抓取物体达到 63.7% 准确率；DiVLA-2B 在单张 A6000 上为 82 Hz（摘要、Sec. 4.5）。</x:v>
       </x:c>
@@ -30801,7 +30823,7 @@
       <x:c r="CM13" t="str">
         <x:v>实验覆盖的任务与本体有限；逐任务失败次数未从已访问页面完整提取。</x:v>
       </x:c>
-      <x:c r="CN13" t="str"/>
+      <x:c r="CN13"/>
       <x:c r="CO13" t="str">
         <x:v>High：有助于研究语言条件操作与 VLA 设计。</x:v>
       </x:c>
@@ -30838,7 +30860,7 @@
         <x:v>A</x:v>
       </x:c>
       <x:c r="G14" t="str">
-        <x:v>Official Conference Paper</x:v>
+        <x:v>正式会议论文</x:v>
       </x:c>
       <x:c r="H14" t="str">
         <x:v>Method Paper</x:v>
@@ -30856,9 +30878,11 @@
         <x:v>https://proceedings.mlr.press/v235/zhen24a.html</x:v>
       </x:c>
       <x:c r="M14" t="str">
-        <x:v>Unknown</x:v>
-      </x:c>
-      <x:c r="N14"/>
+        <x:v>10.48550/arXiv.2403.09631（arXiv DOI；未核实到 proceedings DOI）</x:v>
+      </x:c>
+      <x:c r="N14" t="str">
+        <x:v>https://arxiv.org/abs/2403.09631</x:v>
+      </x:c>
       <x:c r="O14" t="str">
         <x:v>https://vis-www.cs.umass.edu/3dvla/</x:v>
       </x:c>
@@ -30893,7 +30917,7 @@
         <x:v>Unknown</x:v>
       </x:c>
       <x:c r="Z14" t="str">
-        <x:v>README及model card提供OpenX来源与数据说明；完整处理后数据待核实</x:v>
+        <x:v>- 作者从 Open X-Embodiment 中选取 12 个机器人数据集，并结合 Dobb-E、RH20T 的深度信息来源；还使用 RLBench、CALVIN 仿真数据，以及 Epic-Kitchens、HOI4D 人类活动数据。具体集合和用途见 §3.1、Appendix Table 8。</x:v>
       </x:c>
       <x:c r="AA14" t="str">
         <x:v>Unknown</x:v>
@@ -30920,7 +30944,7 @@
         <x:v>Official Conference Paper</x:v>
       </x:c>
       <x:c r="AI14" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="AJ14" t="str">
         <x:v>02_Papers/01_VLA/3D-VLA.md</x:v>
@@ -30932,7 +30956,7 @@
         <x:v>https://proceedings.mlr.press/v235/zhen24a.html; official abstract/proceedings metadata</x:v>
       </x:c>
       <x:c r="AM14" t="str">
-        <x:v>Abstract-level</x:v>
+        <x:v>已核验正文关键章节与附录</x:v>
       </x:c>
       <x:c r="AN14" t="str">
         <x:v>VLA / Robot Foundation Models; Robot Manipulation / IL / Diffusion</x:v>
@@ -30947,7 +30971,7 @@
         <x:v>Real Robot=Unknown; Dataset/Benchmark/Robot Platform retain Unknown when not verified.</x:v>
       </x:c>
       <x:c r="AR14" t="str">
-        <x:v>** 可用于 VLA/机器人基础模型路线对比；应重点核对动作头、训练数据与真机部署成本是否适合当前平台。</x:v>
+        <x:v>可用于双臂普通夹爪项目的目标生成和 3D grounding 基线设计；论文未验证双臂或真机，需实测。</x:v>
       </x:c>
       <x:c r="AS14" t="str">
         <x:v>Project-stated CCF seventh-edition mapping; official row pending where noted</x:v>
@@ -30965,61 +30989,61 @@
         <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="AX14" t="str">
-        <x:v>现有 2D VLA 缺少显式三维结构，难以同时预测动作和未来场景。</x:v>
+        <x:v>2D VLA 对三维空间关系、目标物体位置和动作后的目标状态建模不足。</x:v>
       </x:c>
       <x:c r="AY14" t="str">
-        <x:v>Unknown / Needs Full-Paper Verification</x:v>
+        <x:v>直接从二维观测映射动作，难以显式利用三维关系并预测可供规划使用的目标状态。</x:v>
       </x:c>
       <x:c r="AZ14" t="str">
-        <x:v>以 `VLA; World Model / 3D Generation` 为主要方法/能力线索；更细的结构和消融结论待正文核验。</x:v>
+        <x:v>统一 3D 场景特征、目标状态生成与动作 token 的语言模型框架。</x:v>
       </x:c>
       <x:c r="BA14" t="str">
-        <x:v>使用从现有机器人数据整理的三维指令数据；具体数据集组成和规模仍需核对全文。</x:v>
+        <x:v>Open X-Embodiment 及其他机器人/人类活动数据来源；评测 RLBench、CALVIN 与具身推理/定位/生成任务。</x:v>
       </x:c>
       <x:c r="BB14" t="str">
-        <x:v>Unknown / Needs Full-Paper Verification</x:v>
+        <x:v>推理：3D-LLM、BLIP2、OpenFlamingo、LLaVA；定位：Kosmos-2、CoVLM；目标生成：Instruct-P2P、SuSIE、NeXT-GPT、Point-E；规划：LanCon-Learn、MCIL。</x:v>
       </x:c>
       <x:c r="BC14" t="str">
-        <x:v>- 3D-VLA: A 3D Vision-Language-Action Generative World ModelHaoyu</x:v>
+        <x:v>统一处理三维场景理解、目标图像/点云生成与机器人动作 token；构建大规模 3D 具身指令数据。</x:v>
       </x:c>
       <x:c r="BD14" t="str">
-        <x:v>Real Robot 字段为 `Unknown`；Dataset、Benchmark、Robot Platform 中的 Unknown 继续保留，不从题名推断。</x:v>
+        <x:v>具身问答/描述、3D 定位、目标图像与点云生成，以及 RLBench、CALVIN 仿真规划；未核实真机或双臂实验。</x:v>
       </x:c>
       <x:c r="BE14" t="str">
-        <x:v>Unknown / Needs Full-Paper Verification</x:v>
+        <x:v>3D 定位 IoU 29.33；目标点云 P-FID/Chamfer-L1=4.796/0.139；CALVIN 五任务完成率为 0（Table 2,4,6）。</x:v>
       </x:c>
       <x:c r="BF14" t="str">
-        <x:v>Unknown / Needs Full-Paper Verification</x:v>
+        <x:v>小物体精细操作受限；生成目标可 hallucinate；深度尺度和点云噪声影响真实场景表现。</x:v>
       </x:c>
       <x:c r="BG14" t="str">
-        <x:v>Library Analysis / Research Note: Unknown / Needs Full-Paper Verification</x:v>
+        <x:v>目标一致性、长时程执行、精细动作量化和真实 3D 感知仍待解决。</x:v>
       </x:c>
       <x:c r="BH14" t="str">
         <x:v>VLA; World Model / 3D Generation</x:v>
       </x:c>
       <x:c r="BI14" t="str">
-        <x:v>B</x:v>
+        <x:v>A</x:v>
       </x:c>
       <x:c r="BJ14" t="str">
-        <x:v>Idea Clue 1: compare explicit 3D goal prediction against image-only VLA on dual-arm ordinary-gripper tasks. Evidence: paper motivation and 3D goal image/point-cloud generation. Why relevant: direct test of 3D planning value.</x:v>
+        <x:v>在规划前检查生成目标与当前场景/任务的一致性，评估能否减少目标 hallucination 引发的执行错误；属于待检索研究问题。</x:v>
       </x:c>
       <x:c r="BK14" t="str">
-        <x:v>Not Reported in the accessible proceedings page.</x:v>
+        <x:v>去掉预测 bounding box 后，目标图像指标混合变化、点云指标变差；去掉 Goal 后 RLBench 四任务由 68/80/40/28 降至 58/68/34/24。Tables 3–5。</x:v>
       </x:c>
       <x:c r="BL14" t="str">
-        <x:v>Not Explicitly Reported in the accessible proceedings page.</x:v>
+        <x:v>§6：目标生成可能改变纹理/形状、令物体消失、预测不相关的未来或状态无变化；小物体精细操作失败。</x:v>
       </x:c>
       <x:c r="BM14" t="str">
         <x:v>https://openalex.org/W4392886475</x:v>
       </x:c>
       <x:c r="BN14" t="str">
-        <x:v>https://proceedings.mlr.press/v235/zhen24a.html；官方摘要/论文集元数据</x:v>
+        <x:v>PMLR 官方 PDF：§3.1–3.3、§4.1–4.3、§5.1–5.3、§6–7；Figures 2–3、5–6；Tables 1–6、Appendix Tables 7–9。https://raw.githubusercontent.com/mlresearch/v235/main/assets/zhen24a/zhen24a.pdf</x:v>
       </x:c>
       <x:c r="BO14" t="str">
-        <x:v>B-Fulltext-Unavailable</x:v>
+        <x:v>A-Upgraded</x:v>
       </x:c>
       <x:c r="BP14" t="str">
-        <x:v>Not Found</x:v>
+        <x:v>官方 PDF 内 Appendix A–D 已检查；未找到独立补充包。</x:v>
       </x:c>
       <x:c r="BQ14" t="str">
         <x:v>Partial</x:v>
@@ -31027,46 +31051,50 @@
       <x:c r="BR14" t="str">
         <x:v>Unknown</x:v>
       </x:c>
-      <x:c r="BS14"/>
+      <x:c r="BS14" t="str">
+        <x:v>https://raw.githubusercontent.com/mlresearch/v235/main/assets/zhen24a/zhen24a.pdf</x:v>
+      </x:c>
       <x:c r="BT14" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="BU14" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="BV14" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="BW14" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="BX14" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="BY14" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="BZ14" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="CA14" t="str">
         <x:v>Not Checked</x:v>
       </x:c>
       <x:c r="CB14" t="str">
-        <x:v>Not Found After Verification</x:v>
+        <x:v>arXiv DOI verified; proceedings DOI not located</x:v>
       </x:c>
       <x:c r="CC14" t="str">
         <x:v>Not Found After Verification</x:v>
       </x:c>
       <x:c r="CD14" t="str">
-        <x:v>Audit logged - deep extraction pending</x:v>
+        <x:v>Completed-A</x:v>
       </x:c>
       <x:c r="CE14" t="str">
-        <x:v>false</x:v>
-      </x:c>
-      <x:c r="CF14"/>
+        <x:v>true</x:v>
+      </x:c>
+      <x:c r="CF14" t="str">
+        <x:v>Completed-A</x:v>
+      </x:c>
       <x:c r="CG14" t="str">
-        <x:v>现有 2D VLA 缺少显式三维结构，难以同时预测动作和未来场景。</x:v>
+        <x:v>研究问题：不少 VLA 方法主要从视觉观测直接预测动作，对场景三维关系、被操作物体的位置以及动作执行后的目标状态建模不足。作者研究如何让一个模型同时处理 3D 场景理解、语言指令、目标状态生成和机器人动作规划。；之前方法的问题：作者指出，2D 视觉特征难以充分表达空间关系；已有 3D 多模态语言模型的预训练目标和数据未必与具身任务对齐。因此本文没有直接加载预训练 3D-LLM 权重，而是采用 BLIP2-FlanT5XL 作为语言模型骨干，并训练具身相关表示和输出。；核心思路：把 3D 场景特征、物体与位置标记、目标图像/点云生成，以及离散机器人动作 token 放进统一的语言模型流程。模型可以先根据任务想象目标状态，再把该状态作为动作规划的条件。；输入：- 视觉：单视角或多视角 RGB 图像；构造 3D 场景输入时使用深度或点云信息。；与当前项目的关系：本文与 VLA grounding、三维目标表示和目标状态生成高度相关。对当前双臂普通夹爪项目，可借鉴“先预测目标状态、再条件化动作”的评测思路；但论文所查实验没有给出双臂普通夹爪或真机验证，迁移性仍需独立实验确认。</x:v>
       </x:c>
       <x:c r="CH14" t="str">
         <x:v>现有 VLA 对三维关系和环境动态的建模不足，难以把动作预测与未来场景变化结合。</x:v>
@@ -31098,10 +31126,10 @@
       <x:c r="CQ14" t="str">
         <x:v>Exact work identity verified</x:v>
       </x:c>
-      <x:c r="CR14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="CS14" t="n">
+      <x:c r="CR14" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CS14" t="str">
         <x:v>9</x:v>
       </x:c>
     </x:row>
@@ -31273,7 +31301,7 @@
         <x:v>Real Robot 字段为 `Unknown`；Dataset、Benchmark、Robot Platform 中的 Unknown 继续保留，不从题名推断。</x:v>
       </x:c>
       <x:c r="BE15" t="str">
-        <x:v>Unknown / Needs Full-Paper Verification</x:v>
+        <x:v>论文报告在仿真与真机姿态预测任务中优于所比较 VLA，推理速度约为其 3 倍；具体比较对象见原文。</x:v>
       </x:c>
       <x:c r="BF15" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -31287,7 +31315,7 @@
       <x:c r="BI15" t="str">
         <x:v>B</x:v>
       </x:c>
-      <x:c r="BJ15" t="str"/>
+      <x:c r="BJ15"/>
       <x:c r="BK15" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
@@ -31351,7 +31379,7 @@
       </x:c>
       <x:c r="CF15"/>
       <x:c r="CG15" t="str">
-        <x:v>VLA 要兼顾视觉语言推理、动作预测和可承受的微调/推理成本。</x:v>
+        <x:v>研究问题：VLA 要兼顾视觉语言推理、动作预测和可承受的微调/推理成本。；之前方法的问题：已有 VLA 在复杂任务推理与微调计算成本之间存在权衡。；核心思路：RoboMamba 以 Mamba 架构建立端到端 VLA，重点降低适配和在线推理成本。；主要结果：论文报告在仿真与真机姿态预测任务中优于所比较 VLA，推理速度约为其 3 倍；具体比较对象见原文。；为什么重要：可作为部署时的速度—能力权衡参考。；与当前项目的关系：High：有助于研究语言条件操作与 VLA 设计。</x:v>
       </x:c>
       <x:c r="CH15" t="str">
         <x:v>已有 VLA 在复杂任务推理与微调计算成本之间存在权衡。</x:v>
@@ -31359,7 +31387,7 @@
       <x:c r="CI15" t="str">
         <x:v>RoboMamba 以 Mamba 架构建立端到端 VLA，重点降低适配和在线推理成本。</x:v>
       </x:c>
-      <x:c r="CJ15" t="str"/>
+      <x:c r="CJ15"/>
       <x:c r="CK15" t="str">
         <x:v>论文报告在仿真与真机姿态预测任务中优于所比较 VLA，推理速度约为其 3 倍；具体比较对象见原文。</x:v>
       </x:c>
@@ -31369,7 +31397,7 @@
       <x:c r="CM15" t="str">
         <x:v>目前证据不足以证明其机器人和任务覆盖达到大型通用策略的广度。</x:v>
       </x:c>
-      <x:c r="CN15" t="str"/>
+      <x:c r="CN15"/>
       <x:c r="CO15" t="str">
         <x:v>High：有助于研究语言条件操作与 VLA 设计。</x:v>
       </x:c>
@@ -31552,7 +31580,7 @@
         <x:v>Real Robot 字段为 `Unknown`；Dataset、Benchmark、Robot Platform 中的 Unknown 继续保留，不从题名推断。</x:v>
       </x:c>
       <x:c r="BE16" t="str">
-        <x:v>Unknown / Needs Full-Paper Verification</x:v>
+        <x:v>AAAI 摘要报告在 Adroit 与 MetaWorld 上保持有竞争力的成功率，同时推理速度提高约 7 倍。</x:v>
       </x:c>
       <x:c r="BF16" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -31566,7 +31594,7 @@
       <x:c r="BI16" t="str">
         <x:v>B</x:v>
       </x:c>
-      <x:c r="BJ16" t="str"/>
+      <x:c r="BJ16"/>
       <x:c r="BK16" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
@@ -31630,7 +31658,7 @@
       </x:c>
       <x:c r="CF16"/>
       <x:c r="CG16" t="str">
-        <x:v>扩散/流式动作生成往往需要多次采样，在线控制延迟较高。</x:v>
+        <x:v>研究问题：扩散/流式动作生成往往需要多次采样，在线控制延迟较高。；之前方法的问题：生成质量与推理速度之间存在权衡。；核心思路：FlowPolicy 使用三维点云和 consistency flow matching，在单次推理中生成动作。；输入：官方摘要给出任务/数据类型；具体模型张量与接口需核对方法章节。；输出与动作：官方摘要未明确列出完整控制接口；需核对论文方法或代码。；数据集与评测基准：Adroit、MetaWorld。；主要结果：AAAI 摘要报告在 Adroit 与 MetaWorld 上保持有竞争力的成功率，同时推理速度提高约 7 倍。；为什么重要：双臂真机尤其关注动作频率；该工作可用于比较速度与成功率。；与当前项目的关系：Medium：方法可借鉴，但迁移到当前双臂硬件需验证。；主要局限：本段基于官方摘要；未覆盖全文失败案例、完整 Baseline 与方法消融。</x:v>
       </x:c>
       <x:c r="CH16" t="str">
         <x:v>生成质量与推理速度之间存在权衡。</x:v>
@@ -31638,7 +31666,7 @@
       <x:c r="CI16" t="str">
         <x:v>FlowPolicy 使用三维点云和 consistency flow matching，在单次推理中生成动作。</x:v>
       </x:c>
-      <x:c r="CJ16" t="str"/>
+      <x:c r="CJ16"/>
       <x:c r="CK16" t="str">
         <x:v>AAAI 摘要报告在 Adroit 与 MetaWorld 上保持有竞争力的成功率，同时推理速度提高约 7 倍。</x:v>
       </x:c>
@@ -31648,7 +31676,7 @@
       <x:c r="CM16" t="str">
         <x:v>本段基于官方摘要；未覆盖全文失败案例、完整 Baseline 与方法消融。</x:v>
       </x:c>
-      <x:c r="CN16" t="str"/>
+      <x:c r="CN16"/>
       <x:c r="CO16" t="str">
         <x:v>Medium：方法可借鉴，但迁移到当前双臂硬件需验证。</x:v>
       </x:c>
@@ -31833,7 +31861,7 @@
         <x:v>Real Robot 字段为 `Unknown`；Dataset、Benchmark、Robot Platform 中的 Unknown 继续保留，不从题名推断。</x:v>
       </x:c>
       <x:c r="BE17" t="str">
-        <x:v>Unknown / Needs Full-Paper Verification</x:v>
+        <x:v>作者报告在多个物体类别上优于 UniDexGrasp++；具体成功率需查实验表。</x:v>
       </x:c>
       <x:c r="BF17" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -31847,7 +31875,7 @@
       <x:c r="BI17" t="str">
         <x:v>B</x:v>
       </x:c>
-      <x:c r="BJ17" t="str"/>
+      <x:c r="BJ17"/>
       <x:c r="BK17" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
@@ -31911,7 +31939,7 @@
       </x:c>
       <x:c r="CF17"/>
       <x:c r="CG17" t="str">
-        <x:v>通用灵巧手抓取需要在不同物体类别上预测稳定抓法。</x:v>
+        <x:v>研究问题：通用灵巧手抓取需要在不同物体类别上预测稳定抓法。；之前方法的问题：复杂训练流程和手型依赖限制方法复用。；核心思路：UniGraspTransformer 用统一的 Transformer 网络预测灵巧抓取，并简化训练过程。；主要结果：作者报告在多个物体类别上优于 UniDexGrasp++；具体成功率需查实验表。；为什么重要：提供跨物体抓取模型的简洁架构基线。；与当前项目的关系：Medium：模型结构可参考，但需重做普通夹爪动作输出。；主要局限：灵巧手抓取 benchmark 与双臂真机任务仍有差距。</x:v>
       </x:c>
       <x:c r="CH17" t="str">
         <x:v>复杂训练流程和手型依赖限制方法复用。</x:v>
@@ -31919,7 +31947,7 @@
       <x:c r="CI17" t="str">
         <x:v>UniGraspTransformer 用统一的 Transformer 网络预测灵巧抓取，并简化训练过程。</x:v>
       </x:c>
-      <x:c r="CJ17" t="str"/>
+      <x:c r="CJ17"/>
       <x:c r="CK17" t="str">
         <x:v>作者报告在多个物体类别上优于 UniDexGrasp++；具体成功率需查实验表。</x:v>
       </x:c>
@@ -31929,7 +31957,7 @@
       <x:c r="CM17" t="str">
         <x:v>灵巧手抓取 benchmark 与双臂真机任务仍有差距。</x:v>
       </x:c>
-      <x:c r="CN17" t="str"/>
+      <x:c r="CN17"/>
       <x:c r="CO17" t="str">
         <x:v>Medium：模型结构可参考，但需重做普通夹爪动作输出。</x:v>
       </x:c>
@@ -32128,7 +32156,7 @@
       <x:c r="BI18" t="str">
         <x:v>B</x:v>
       </x:c>
-      <x:c r="BJ18" t="str"/>
+      <x:c r="BJ18"/>
       <x:c r="BK18" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
@@ -32192,7 +32220,7 @@
       </x:c>
       <x:c r="CF18"/>
       <x:c r="CG18" t="str">
-        <x:v>灵巧手操作数据和训练成本高，复杂任务还需要语义理解。</x:v>
+        <x:v>研究问题：灵巧手操作数据和训练成本高，复杂任务还需要语义理解。；之前方法的问题：纯低层策略难从少量示范组织多步任务。；核心思路：用 VLM 提供高层任务结构和语义线索，支撑灵巧手低层操作学习。；为什么重要：展示 VLM 规划与低层动作之间的接口问题。；与当前项目的关系：Medium：双臂普通夹爪也需要高低层协作。；主要局限：仿真灵巧手结果不能直接推断双臂真机表现。</x:v>
       </x:c>
       <x:c r="CH18" t="str">
         <x:v>纯低层策略难从少量示范组织多步任务。</x:v>
@@ -32200,7 +32228,7 @@
       <x:c r="CI18" t="str">
         <x:v>用 VLM 提供高层任务结构和语义线索，支撑灵巧手低层操作学习。</x:v>
       </x:c>
-      <x:c r="CJ18" t="str"/>
+      <x:c r="CJ18"/>
       <x:c r="CK18" t="str">
         <x:v>论文报告在关节物体及语义理解仿真任务中验证方法；具体数值需查正文。</x:v>
       </x:c>
@@ -32210,7 +32238,7 @@
       <x:c r="CM18" t="str">
         <x:v>仿真灵巧手结果不能直接推断双臂真机表现。</x:v>
       </x:c>
-      <x:c r="CN18" t="str"/>
+      <x:c r="CN18"/>
       <x:c r="CO18" t="str">
         <x:v>Medium：双臂普通夹爪也需要高低层协作。</x:v>
       </x:c>
@@ -32395,7 +32423,7 @@
         <x:v>Real Robot 字段为 `Unknown`；Dataset、Benchmark、Robot Platform 中的 Unknown 继续保留，不从题名推断。</x:v>
       </x:c>
       <x:c r="BE19" t="str">
-        <x:v>Unknown / Needs Full-Paper Verification</x:v>
+        <x:v>作者报告想象未来质量与动作可靠性、任务成功相关；具体数字见实验章节。</x:v>
       </x:c>
       <x:c r="BF19" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -32409,7 +32437,7 @@
       <x:c r="BI19" t="str">
         <x:v>B</x:v>
       </x:c>
-      <x:c r="BJ19" t="str"/>
+      <x:c r="BJ19"/>
       <x:c r="BK19" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
@@ -32473,7 +32501,7 @@
       </x:c>
       <x:c r="CF19"/>
       <x:c r="CG19" t="str">
-        <x:v>开放环境操作需要预见动作后果并适应新场景。</x:v>
+        <x:v>研究问题：开放环境操作需要预见动作后果并适应新场景。；之前方法的问题：只从当前视觉预测动作，可能缺少对未来状态的理解。；核心思路：VideoVLA 将视频生成模型用于 VLA，利用想象的未来画面帮助动作选择。；主要结果：作者报告想象未来质量与动作可靠性、任务成功相关；具体数字见实验章节。；为什么重要：把世界模型式视觉预期与机器人动作生成连接起来。；与当前项目的关系：High：可用于双臂动作前预期与动作后验证。；主要局限：视频看起来合理不一定代表接触力与夹爪动作正确。</x:v>
       </x:c>
       <x:c r="CH19" t="str">
         <x:v>只从当前视觉预测动作，可能缺少对未来状态的理解。</x:v>
@@ -32481,7 +32509,7 @@
       <x:c r="CI19" t="str">
         <x:v>VideoVLA 将视频生成模型用于 VLA，利用想象的未来画面帮助动作选择。</x:v>
       </x:c>
-      <x:c r="CJ19" t="str"/>
+      <x:c r="CJ19"/>
       <x:c r="CK19" t="str">
         <x:v>作者报告想象未来质量与动作可靠性、任务成功相关；具体数字见实验章节。</x:v>
       </x:c>
@@ -32491,7 +32519,7 @@
       <x:c r="CM19" t="str">
         <x:v>视频看起来合理不一定代表接触力与夹爪动作正确。</x:v>
       </x:c>
-      <x:c r="CN19" t="str"/>
+      <x:c r="CN19"/>
       <x:c r="CO19" t="str">
         <x:v>High：可用于双臂动作前预期与动作后验证。</x:v>
       </x:c>
@@ -32690,7 +32718,7 @@
       <x:c r="BI20" t="str">
         <x:v>B</x:v>
       </x:c>
-      <x:c r="BJ20" t="str"/>
+      <x:c r="BJ20"/>
       <x:c r="BK20" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
@@ -32754,7 +32782,7 @@
       </x:c>
       <x:c r="CF20"/>
       <x:c r="CG20" t="str">
-        <x:v>语言驱动的灵巧抓取要同时理解任务语义、三维几何和接触关系。</x:v>
+        <x:v>研究问题：语言驱动的灵巧抓取要同时理解任务语义、三维几何和接触关系。；之前方法的问题：只预测抓取位姿未必符合语言中隐含的使用目的。；核心思路：DextER 在抓取生成中加入基于接触的具身推理，使手部接触与任务意图对齐。；数据集与评测基准：DexGYS。；为什么重要：将语言 Grounding 与可执行接触联系起来。；与当前项目的关系：Medium：普通夹爪也需要意图对齐，但手部接触自由度不同。；主要局限：从多指接触迁移到两只普通夹爪需重新定义动作空间。</x:v>
       </x:c>
       <x:c r="CH20" t="str">
         <x:v>只预测抓取位姿未必符合语言中隐含的使用目的。</x:v>
@@ -32762,7 +32790,7 @@
       <x:c r="CI20" t="str">
         <x:v>DextER 在抓取生成中加入基于接触的具身推理，使手部接触与任务意图对齐。</x:v>
       </x:c>
-      <x:c r="CJ20" t="str"/>
+      <x:c r="CJ20"/>
       <x:c r="CK20" t="str">
         <x:v>卡片记录 DexGYS 成功率 67.14%，较所比较 SOTA 高 3.83 个百分点。</x:v>
       </x:c>
@@ -32772,7 +32800,7 @@
       <x:c r="CM20" t="str">
         <x:v>从多指接触迁移到两只普通夹爪需重新定义动作空间。</x:v>
       </x:c>
-      <x:c r="CN20" t="str"/>
+      <x:c r="CN20"/>
       <x:c r="CO20" t="str">
         <x:v>Medium：普通夹爪也需要意图对齐，但手部接触自由度不同。</x:v>
       </x:c>
@@ -33039,7 +33067,7 @@
       </x:c>
       <x:c r="CF21"/>
       <x:c r="CG21" t="str">
-        <x:v>多模态大模型能理解图像和语言，但不一定能给出可执行的接触点与夹爪姿态。</x:v>
+        <x:v>研究问题：多模态大模型能理解图像和语言，但不一定能给出可执行的接触点与夹爪姿态。；之前方法的问题：物体级 Grounding 与精确接触几何没有自然地从语言推理转成机器人动作。；核心思路：ManipLLM 结合物体类别识别、affordance 推理和位姿微调，预测接触点与夹爪朝向，并通过分步推理和主动交互改进执行。；输入：物体视觉信息与操作指令；具体相机和状态接口见论文方法。；输出与动作：接触点、夹爪朝向及后续操作位姿。；数据集与评测基准：论文中的物体操作任务与消融设置；具体数据集名称见原卡实验部分。；为什么重要：让语言推理落到普通夹爪可执行的接触几何上。；与当前项目的关系：High：直接对应夹爪接触点、动作前可行性验证和真机操作。；主要局限：作者指出视觉位置预测仍受域变化影响；特定吸盘硬件约束需要测试时适配。</x:v>
       </x:c>
       <x:c r="CH21" t="str">
         <x:v>物体级 Grounding 与精确接触几何没有自然地从语言推理转成机器人动作。</x:v>
@@ -33248,7 +33276,7 @@
         <x:v>Real Robot 字段为 `Unknown`；Dataset、Benchmark、Robot Platform 中的 Unknown 继续保留，不从题名推断。</x:v>
       </x:c>
       <x:c r="BE22" t="str">
-        <x:v>Unknown / Needs Full-Paper Verification</x:v>
+        <x:v>作者报告成功率、动作保真度与训练效率优于所比较方法；摘要未给统一数字。</x:v>
       </x:c>
       <x:c r="BF22" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -33262,7 +33290,7 @@
       <x:c r="BI22" t="str">
         <x:v>B</x:v>
       </x:c>
-      <x:c r="BJ22" t="str"/>
+      <x:c r="BJ22"/>
       <x:c r="BK22" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
@@ -33326,7 +33354,7 @@
       </x:c>
       <x:c r="CF22"/>
       <x:c r="CG22" t="str">
-        <x:v>人类双手操作能力丰富，但难以直接迁移到机器人灵巧手。</x:v>
+        <x:v>研究问题：人类双手操作能力丰富，但难以直接迁移到机器人灵巧手。；之前方法的问题：人手和机器人手的运动学、接触方式不同，逐帧模仿不能保证可执行。；核心思路：ManipTrans 用两阶段流程，在仿真中把人类双手技能迁移到机器人灵巧手策略。；数据集与评测基准：双手灵巧操作仿真任务；详细任务和基线见论文。；主要结果：作者报告成功率、动作保真度与训练效率优于所比较方法；摘要未给统一数字。；为什么重要：展示 Human Video / Human Motion 到机器人双手动作的转换思路。；与当前项目的关系：Medium：手型不同，普通夹爪适配仍需单独建模。；主要局限：仿真到真机与普通夹爪迁移尚不能从摘要确认。</x:v>
       </x:c>
       <x:c r="CH22" t="str">
         <x:v>人手和机器人手的运动学、接触方式不同，逐帧模仿不能保证可执行。</x:v>
@@ -33334,7 +33362,7 @@
       <x:c r="CI22" t="str">
         <x:v>ManipTrans 用两阶段流程，在仿真中把人类双手技能迁移到机器人灵巧手策略。</x:v>
       </x:c>
-      <x:c r="CJ22" t="str"/>
+      <x:c r="CJ22"/>
       <x:c r="CK22" t="str">
         <x:v>作者报告成功率、动作保真度与训练效率优于所比较方法；摘要未给统一数字。</x:v>
       </x:c>
@@ -33344,7 +33372,7 @@
       <x:c r="CM22" t="str">
         <x:v>仿真到真机与普通夹爪迁移尚不能从摘要确认。</x:v>
       </x:c>
-      <x:c r="CN22" t="str"/>
+      <x:c r="CN22"/>
       <x:c r="CO22" t="str">
         <x:v>Medium：手型不同，普通夹爪适配仍需单独建模。</x:v>
       </x:c>
@@ -33531,7 +33559,7 @@
         <x:v>Real Robot 字段为 `Unknown`；Dataset、Benchmark、Robot Platform 中的 Unknown 继续保留，不从题名推断。</x:v>
       </x:c>
       <x:c r="BE23" t="str">
-        <x:v>Unknown / Needs Full-Paper Verification</x:v>
+        <x:v>官方摘要报告目标自适应任务平均成功率 70.7%。</x:v>
       </x:c>
       <x:c r="BF23" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -33545,7 +33573,7 @@
       <x:c r="BI23" t="str">
         <x:v>B</x:v>
       </x:c>
-      <x:c r="BJ23" t="str"/>
+      <x:c r="BJ23"/>
       <x:c r="BK23" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
@@ -33609,7 +33637,7 @@
       </x:c>
       <x:c r="CF23"/>
       <x:c r="CG23" t="str">
-        <x:v>接触密集的灵巧操作需要根据目标与环境变化调整动作。</x:v>
+        <x:v>研究问题：接触密集的灵巧操作需要根据目标与环境变化调整动作。；之前方法的问题：固定轨迹或单一接触模式难适应复杂手—物交互。；核心思路：DexHandDiff 用交互感知的扩散式规划生成可适应目标变化的灵巧手动作。；主要结果：官方摘要报告目标自适应任务平均成功率 70.7%。；为什么重要：展示生成式策略如何表达多种接触动作。；与当前项目的关系：Medium：可借鉴动作生成机制，但灵巧手与普通夹爪不同。；主要局限：需检查真机接触、动作延迟和跨硬件泛化。</x:v>
       </x:c>
       <x:c r="CH23" t="str">
         <x:v>固定轨迹或单一接触模式难适应复杂手—物交互。</x:v>
@@ -33617,7 +33645,7 @@
       <x:c r="CI23" t="str">
         <x:v>DexHandDiff 用交互感知的扩散式规划生成可适应目标变化的灵巧手动作。</x:v>
       </x:c>
-      <x:c r="CJ23" t="str"/>
+      <x:c r="CJ23"/>
       <x:c r="CK23" t="str">
         <x:v>官方摘要报告目标自适应任务平均成功率 70.7%。</x:v>
       </x:c>
@@ -33627,7 +33655,7 @@
       <x:c r="CM23" t="str">
         <x:v>需检查真机接触、动作延迟和跨硬件泛化。</x:v>
       </x:c>
-      <x:c r="CN23" t="str"/>
+      <x:c r="CN23"/>
       <x:c r="CO23" t="str">
         <x:v>Medium：可借鉴动作生成机制，但灵巧手与普通夹爪不同。</x:v>
       </x:c>
@@ -33814,7 +33842,7 @@
         <x:v>Real Robot 字段为 `Unknown`；Dataset、Benchmark、Robot Platform 中的 Unknown 继续保留，不从题名推断。</x:v>
       </x:c>
       <x:c r="BE24" t="str">
-        <x:v>Unknown / Needs Full-Paper Verification</x:v>
+        <x:v>作者报告小样本设置下优于所比较方法；摘要未给可安全复述的统一数值。</x:v>
       </x:c>
       <x:c r="BF24" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -33828,7 +33856,7 @@
       <x:c r="BI24" t="str">
         <x:v>B</x:v>
       </x:c>
-      <x:c r="BJ24" t="str"/>
+      <x:c r="BJ24"/>
       <x:c r="BK24" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
@@ -33892,7 +33920,7 @@
       </x:c>
       <x:c r="CF24"/>
       <x:c r="CG24" t="str">
-        <x:v>视觉机器人操作要根据语言、视觉和状态输出可执行动作。</x:v>
+        <x:v>研究问题：视觉机器人操作要根据语言、视觉和状态输出可执行动作。；之前方法的问题：只依赖少量机器人示范，难以利用大量人类动作视频。；核心思路：AR-VRM 显式利用人类动作视频学习视觉操作表示，再适配机器人策略。；主要结果：作者报告小样本设置下优于所比较方法；摘要未给可安全复述的统一数值。；为什么重要：为人类视频转机器人动作提供另一种数据路线。；与当前项目的关系：Medium：与低成本数据收集相关，双臂夹爪迁移待验。；主要局限：人体动作和机器人动作空间差异需要明确对齐。</x:v>
       </x:c>
       <x:c r="CH24" t="str">
         <x:v>只依赖少量机器人示范，难以利用大量人类动作视频。</x:v>
@@ -33900,7 +33928,7 @@
       <x:c r="CI24" t="str">
         <x:v>AR-VRM 显式利用人类动作视频学习视觉操作表示，再适配机器人策略。</x:v>
       </x:c>
-      <x:c r="CJ24" t="str"/>
+      <x:c r="CJ24"/>
       <x:c r="CK24" t="str">
         <x:v>作者报告小样本设置下优于所比较方法；摘要未给可安全复述的统一数值。</x:v>
       </x:c>
@@ -33910,7 +33938,7 @@
       <x:c r="CM24" t="str">
         <x:v>人体动作和机器人动作空间差异需要明确对齐。</x:v>
       </x:c>
-      <x:c r="CN24" t="str"/>
+      <x:c r="CN24"/>
       <x:c r="CO24" t="str">
         <x:v>Medium：与低成本数据收集相关，双臂夹爪迁移待验。</x:v>
       </x:c>
@@ -34097,7 +34125,7 @@
         <x:v>Real Robot 字段为 `No`；Dataset、Benchmark、Robot Platform 中的 Unknown 继续保留，不从题名推断。</x:v>
       </x:c>
       <x:c r="BE25" t="str">
-        <x:v>Unknown / Needs Full-Paper Verification</x:v>
+        <x:v>作者报告保持抓取质量时，预测姿态多样性优于先前方法；具体数值需核对表格。</x:v>
       </x:c>
       <x:c r="BF25" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -34111,7 +34139,7 @@
       <x:c r="BI25" t="str">
         <x:v>B</x:v>
       </x:c>
-      <x:c r="BJ25" t="str"/>
+      <x:c r="BJ25"/>
       <x:c r="BK25" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
@@ -34175,7 +34203,7 @@
       </x:c>
       <x:c r="CF25"/>
       <x:c r="CG25" t="str">
-        <x:v>灵巧手抓取不仅要可行，还要生成多样姿态。</x:v>
+        <x:v>研究问题：灵巧手抓取不仅要可行，还要生成多样姿态。；之前方法的问题：单一回归结果容易忽略同一物体的多个可用抓法。；核心思路：Dexterous Grasp Transformer 用判别式 Transformer 生成和筛选多样灵巧抓取。；主要结果：作者报告保持抓取质量时，预测姿态多样性优于先前方法；具体数值需核对表格。；为什么重要：提醒抓取策略不应只保留单一候选动作。；与当前项目的关系：Medium：双普通夹爪也可能需要多候选抓取与可行性筛选。；主要局限：灵巧手抓取多样性指标不能直接替代双臂任务成功率。</x:v>
       </x:c>
       <x:c r="CH25" t="str">
         <x:v>单一回归结果容易忽略同一物体的多个可用抓法。</x:v>
@@ -34183,7 +34211,7 @@
       <x:c r="CI25" t="str">
         <x:v>Dexterous Grasp Transformer 用判别式 Transformer 生成和筛选多样灵巧抓取。</x:v>
       </x:c>
-      <x:c r="CJ25" t="str"/>
+      <x:c r="CJ25"/>
       <x:c r="CK25" t="str">
         <x:v>作者报告保持抓取质量时，预测姿态多样性优于先前方法；具体数值需核对表格。</x:v>
       </x:c>
@@ -34193,7 +34221,7 @@
       <x:c r="CM25" t="str">
         <x:v>灵巧手抓取多样性指标不能直接替代双臂任务成功率。</x:v>
       </x:c>
-      <x:c r="CN25" t="str"/>
+      <x:c r="CN25"/>
       <x:c r="CO25" t="str">
         <x:v>Medium：双普通夹爪也可能需要多候选抓取与可行性筛选。</x:v>
       </x:c>
@@ -34380,7 +34408,7 @@
         <x:v>Real Robot 字段为 `Yes`；Dataset、Benchmark、Robot Platform 中的 Unknown 继续保留，不从题名推断。</x:v>
       </x:c>
       <x:c r="BE26" t="str">
-        <x:v>Unknown / Needs Full-Paper Verification</x:v>
+        <x:v>OVMM Overall SR 为 15.8%，比 KUZHUM 高 4.2 个百分点；真机 Stack Block、Open Drawer、Put in Bowl 分别为 30%、10%、40%（每项 10 次）。</x:v>
       </x:c>
       <x:c r="BF26" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -34394,7 +34422,7 @@
       <x:c r="BI26" t="str">
         <x:v>B</x:v>
       </x:c>
-      <x:c r="BJ26" t="str"/>
+      <x:c r="BJ26"/>
       <x:c r="BK26" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
@@ -34458,7 +34486,7 @@
       </x:c>
       <x:c r="CF26"/>
       <x:c r="CG26" t="str">
-        <x:v>移动操作需要跨任务和跨环境泛化；固定底座 VLA 的设置不直接覆盖移动机器人。</x:v>
+        <x:v>研究问题：固定底座 VLA 不会生成移动底盘与机械臂协同运动轨迹。；之前方法的问题：移动操作示范昂贵，端到端方法难以覆盖多任务；分离式导航与操作可能产生错误累积。；核心思路：用预训练 VLA 生成末端 waypoint，再以 reachability、smoothness 和 collision objective 做双层底盘/机械臂轨迹优化。；输入：RGB-D、相机位姿、底盘和末端 proprioception、夹爪开合度、语言指令。；输出与动作：末端 waypoint，以及双层优化生成的移动底盘和机械臂协同轨迹。；数据集与评测基准：OVMM 仿真 benchmark 与三类移动操作真机任务。；主要结果：OVMM Overall SR 为 15.8%，比 KUZHUM 高 4.2 个百分点；真机 Stack Block、Open Drawer、Put in Bowl 分别为 30%、10%、40%（每项 10 次）。；与当前项目的关系：可参考子目标到可行轨迹的分层处理；本文没有双臂实验。</x:v>
       </x:c>
       <x:c r="CH26" t="str">
         <x:v>固定底座 VLA 不能直接解决移动机器人在不同场景中导航与操作耦合的问题。</x:v>
@@ -34466,7 +34494,7 @@
       <x:c r="CI26" t="str">
         <x:v>MoManipVLA 将 VLA 迁移到移动操作，结合移动底座与机械臂的任务执行。具体模块以原论文为准。</x:v>
       </x:c>
-      <x:c r="CJ26" t="str"/>
+      <x:c r="CJ26"/>
       <x:c r="CK26" t="str">
         <x:v>官方摘要报告在 OVMM 和真机任务中优于所比较方法，整体成功率约高 4.2%；具体实验分组需回原文核对。</x:v>
       </x:c>
@@ -34476,7 +34504,7 @@
       <x:c r="CM26" t="str">
         <x:v>当前可核验的摘要不足以判断跨平台和长时序任务的完整失败情况。</x:v>
       </x:c>
-      <x:c r="CN26" t="str"/>
+      <x:c r="CN26"/>
       <x:c r="CO26" t="str">
         <x:v>High：有助于研究语言条件操作与 VLA 设计。</x:v>
       </x:c>
@@ -34663,7 +34691,7 @@
         <x:v>Real Robot 字段为 `Yes`；Dataset、Benchmark、Robot Platform 中的 Unknown 继续保留，不从题名推断。</x:v>
       </x:c>
       <x:c r="BE27" t="str">
-        <x:v>Unknown / Needs Full-Paper Verification</x:v>
+        <x:v>论文报告 30 项真机操作任务、每项平均约 17 条示范时，成功率达 91%。</x:v>
       </x:c>
       <x:c r="BF27" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -34677,7 +34705,7 @@
       <x:c r="BI27" t="str">
         <x:v>B</x:v>
       </x:c>
-      <x:c r="BJ27" t="str"/>
+      <x:c r="BJ27"/>
       <x:c r="BK27" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
@@ -34741,7 +34769,7 @@
       </x:c>
       <x:c r="CF27"/>
       <x:c r="CG27" t="str">
-        <x:v>多任务机器人策略通常需要大量专家示范。</x:v>
+        <x:v>研究问题：多任务机器人策略通常需要大量专家示范。；之前方法的问题：复杂通用策略可能难以在少量示范下稳定学习。；核心思路：BAKU 用相对简洁的 Transformer 架构训练多任务机器人策略。；主要结果：论文报告 30 项真机操作任务、每项平均约 17 条示范时，成功率达 91%。；为什么重要：为小数据多任务操作提供实证基线。；与当前项目的关系：High：双臂示范昂贵，值得比较数据效率。；主要局限：30 项任务的本体与任务分布未必覆盖本项目的双臂普通夹爪。</x:v>
       </x:c>
       <x:c r="CH27" t="str">
         <x:v>复杂通用策略可能难以在少量示范下稳定学习。</x:v>
@@ -34749,7 +34777,7 @@
       <x:c r="CI27" t="str">
         <x:v>BAKU 用相对简洁的 Transformer 架构训练多任务机器人策略。</x:v>
       </x:c>
-      <x:c r="CJ27" t="str"/>
+      <x:c r="CJ27"/>
       <x:c r="CK27" t="str">
         <x:v>论文报告 30 项真机操作任务、每项平均约 17 条示范时，成功率达 91%。</x:v>
       </x:c>
@@ -34759,7 +34787,7 @@
       <x:c r="CM27" t="str">
         <x:v>30 项任务的本体与任务分布未必覆盖本项目的双臂普通夹爪。</x:v>
       </x:c>
-      <x:c r="CN27" t="str"/>
+      <x:c r="CN27"/>
       <x:c r="CO27" t="str">
         <x:v>High：双臂示范昂贵，值得比较数据效率。</x:v>
       </x:c>
@@ -34946,7 +34974,7 @@
         <x:v>Real Robot 字段为 `No`；Dataset、Benchmark、Robot Platform 中的 Unknown 继续保留，不从题名推断。</x:v>
       </x:c>
       <x:c r="BE28" t="str">
-        <x:v>Unknown / Needs Full-Paper Verification</x:v>
+        <x:v>摘要没有给出足够明确、可复述的量化性能。</x:v>
       </x:c>
       <x:c r="BF28" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -34960,7 +34988,7 @@
       <x:c r="BI28" t="str">
         <x:v>B</x:v>
       </x:c>
-      <x:c r="BJ28" t="str"/>
+      <x:c r="BJ28"/>
       <x:c r="BK28" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
@@ -35024,7 +35052,7 @@
       </x:c>
       <x:c r="CF28"/>
       <x:c r="CG28" t="str">
-        <x:v>手术机器人自动缝合等复杂任务需要高精度和适应变化的控制。</x:v>
+        <x:v>研究问题：手术机器人自动缝合等复杂任务需要高精度和适应变化的控制。；之前方法的问题：既有平台多局限于简单、低灵巧度操作，难以灵活支持分解式强化学习。；核心思路：SurgicAI 构建手术机器人开发与评测平台，支持模块化子任务及强化学习任务分解。；主要结果：摘要没有给出足够明确、可复述的量化性能。；为什么重要：为复杂长程任务的子任务拆解提供特定领域案例。；与当前项目的关系：Medium：任务分解思路可借鉴，但手术场景与本项目普通夹爪任务不同。；主要局限：摘要不能证明该平台上的策略能迁移到一般家庭操作。</x:v>
       </x:c>
       <x:c r="CH28" t="str">
         <x:v>既有平台多局限于简单、低灵巧度操作，难以灵活支持分解式强化学习。</x:v>
@@ -35032,7 +35060,7 @@
       <x:c r="CI28" t="str">
         <x:v>SurgicAI 构建手术机器人开发与评测平台，支持模块化子任务及强化学习任务分解。</x:v>
       </x:c>
-      <x:c r="CJ28" t="str"/>
+      <x:c r="CJ28"/>
       <x:c r="CK28" t="str">
         <x:v>摘要没有给出足够明确、可复述的量化性能。</x:v>
       </x:c>
@@ -35042,7 +35070,7 @@
       <x:c r="CM28" t="str">
         <x:v>摘要不能证明该平台上的策略能迁移到一般家庭操作。</x:v>
       </x:c>
-      <x:c r="CN28" t="str"/>
+      <x:c r="CN28"/>
       <x:c r="CO28" t="str">
         <x:v>Medium：任务分解思路可借鉴，但手术场景与本项目普通夹爪任务不同。</x:v>
       </x:c>
@@ -35229,7 +35257,7 @@
         <x:v>Real Robot 字段为 `No`；Dataset、Benchmark、Robot Platform 中的 Unknown 继续保留，不从题名推断。</x:v>
       </x:c>
       <x:c r="BE29" t="str">
-        <x:v>Unknown / Needs Full-Paper Verification</x:v>
+        <x:v>已核验摘要没有可安全复述的统一量化结果。</x:v>
       </x:c>
       <x:c r="BF29" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -35243,7 +35271,7 @@
       <x:c r="BI29" t="str">
         <x:v>B</x:v>
       </x:c>
-      <x:c r="BJ29" t="str"/>
+      <x:c r="BJ29"/>
       <x:c r="BK29" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
@@ -35307,7 +35335,7 @@
       </x:c>
       <x:c r="CF29"/>
       <x:c r="CG29" t="str">
-        <x:v>强化学习的奖励设计通常要大量人工工程。</x:v>
+        <x:v>研究问题：强化学习的奖励设计通常要大量人工工程。；之前方法的问题：只比较单帧状态容易忽略示范中的动作时间顺序。；核心思路：Temporal Optimal Transport Reward 把时间顺序纳入示范与策略轨迹的匹配，构造学习奖励。；主要结果：已核验摘要没有可安全复述的统一量化结果。；为什么重要：为长时序操作提供不依赖逐步手写奖励的方向。；与当前项目的关系：Medium：双臂轨迹评价可参考，但真实接触仍需验证。；主要局限：时间对齐错误可能误导奖励；需审计长任务失败样例。</x:v>
       </x:c>
       <x:c r="CH29" t="str">
         <x:v>只比较单帧状态容易忽略示范中的动作时间顺序。</x:v>
@@ -35315,7 +35343,7 @@
       <x:c r="CI29" t="str">
         <x:v>Temporal Optimal Transport Reward 把时间顺序纳入示范与策略轨迹的匹配，构造学习奖励。</x:v>
       </x:c>
-      <x:c r="CJ29" t="str"/>
+      <x:c r="CJ29"/>
       <x:c r="CK29" t="str">
         <x:v>已核验摘要没有可安全复述的统一量化结果。</x:v>
       </x:c>
@@ -35325,7 +35353,7 @@
       <x:c r="CM29" t="str">
         <x:v>时间对齐错误可能误导奖励；需审计长任务失败样例。</x:v>
       </x:c>
-      <x:c r="CN29" t="str"/>
+      <x:c r="CN29"/>
       <x:c r="CO29" t="str">
         <x:v>Medium：双臂轨迹评价可参考，但真实接触仍需验证。</x:v>
       </x:c>
@@ -35526,7 +35554,7 @@
       <x:c r="BI30" t="str">
         <x:v>B</x:v>
       </x:c>
-      <x:c r="BJ30" t="str"/>
+      <x:c r="BJ30"/>
       <x:c r="BK30" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
@@ -35590,7 +35618,7 @@
       </x:c>
       <x:c r="CF30"/>
       <x:c r="CG30" t="str">
-        <x:v>机器人长任务容易因局部错误累积而失败。</x:v>
+        <x:v>研究问题：机器人长任务容易因局部错误累积而失败。；之前方法的问题：只按当前观测输出动作，缺少对下一状态的预期与检查。；核心思路：CLOVER 借鉴闭环控制，把生成式未来预期与视觉运动策略结合，持续比较执行进展。；数据集与评测基准：CALVIN 与真机操作任务。；为什么重要：为动作后验证和失败检测提供闭环思路。；与当前项目的关系：High：双臂长任务尤其需要检查每步结果。；主要局限：未来预测误差与真实接触误差如何区分仍需验证。</x:v>
       </x:c>
       <x:c r="CH30" t="str">
         <x:v>只按当前观测输出动作，缺少对下一状态的预期与检查。</x:v>
@@ -35598,7 +35626,7 @@
       <x:c r="CI30" t="str">
         <x:v>CLOVER 借鉴闭环控制，把生成式未来预期与视觉运动策略结合，持续比较执行进展。</x:v>
       </x:c>
-      <x:c r="CJ30" t="str"/>
+      <x:c r="CJ30"/>
       <x:c r="CK30" t="str">
         <x:v>作者报告 CALVIN 上达到所比较方法中的先进表现，并展示真机任务改善；具体数字需查正文。</x:v>
       </x:c>
@@ -35608,7 +35636,7 @@
       <x:c r="CM30" t="str">
         <x:v>未来预测误差与真实接触误差如何区分仍需验证。</x:v>
       </x:c>
-      <x:c r="CN30" t="str"/>
+      <x:c r="CN30"/>
       <x:c r="CO30" t="str">
         <x:v>High：双臂长任务尤其需要检查每步结果。</x:v>
       </x:c>
@@ -35795,7 +35823,7 @@
         <x:v>Real Robot 字段为 `No`；Dataset、Benchmark、Robot Platform 中的 Unknown 继续保留，不从题名推断。</x:v>
       </x:c>
       <x:c r="BE31" t="str">
-        <x:v>Unknown / Needs Full-Paper Verification</x:v>
+        <x:v>摘要指出点云观测常带来更好的策略表现，并在几何与视觉变化下表现出更强泛化；具体幅度需查实验表格。</x:v>
       </x:c>
       <x:c r="BF31" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -35809,7 +35837,7 @@
       <x:c r="BI31" t="str">
         <x:v>B</x:v>
       </x:c>
-      <x:c r="BJ31" t="str"/>
+      <x:c r="BJ31"/>
       <x:c r="BK31" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
@@ -35873,7 +35901,7 @@
       </x:c>
       <x:c r="CF31"/>
       <x:c r="CG31" t="str">
-        <x:v>在机器人学习中，观测模态可能像策略设计一样限制操作能力。</x:v>
+        <x:v>研究问题：在机器人学习中，观测模态可能像策略设计一样限制操作能力。；核心思路：论文提出 OBSBench，统一比较不同观测编码器和策略基线；基准覆盖两个仿真器、125 项任务。；数据集与评测基准：OBSBench：两个仿真器、125 项任务。；主要结果：摘要指出点云观测常带来更好的策略表现，并在几何与视觉变化下表现出更强泛化；具体幅度需查实验表格。；为什么重要：提示选择 RGB、点云等输入时，应在同一策略和任务设置下比较。；与当前项目的关系：Medium：可用于设计普通夹爪操作的观测消融实验。；主要局限：摘要未说明点云优势在传感器成本、遮挡和真实平台上的边界。</x:v>
       </x:c>
       <x:c r="CH31" t="str">
         <x:v>已核验摘要未明确说明；需查阅论文方法与实验章节。</x:v>
@@ -35881,7 +35909,7 @@
       <x:c r="CI31" t="str">
         <x:v>论文提出 OBSBench，统一比较不同观测编码器和策略基线；基准覆盖两个仿真器、125 项任务。</x:v>
       </x:c>
-      <x:c r="CJ31" t="str"/>
+      <x:c r="CJ31"/>
       <x:c r="CK31" t="str">
         <x:v>摘要指出点云观测常带来更好的策略表现，并在几何与视觉变化下表现出更强泛化；具体幅度需查实验表格。</x:v>
       </x:c>
@@ -35891,7 +35919,7 @@
       <x:c r="CM31" t="str">
         <x:v>摘要未说明点云优势在传感器成本、遮挡和真实平台上的边界。</x:v>
       </x:c>
-      <x:c r="CN31" t="str"/>
+      <x:c r="CN31"/>
       <x:c r="CO31" t="str">
         <x:v>Medium：可用于设计普通夹爪操作的观测消融实验。</x:v>
       </x:c>
@@ -36078,7 +36106,7 @@
         <x:v>Real Robot 字段为 `No`；Dataset、Benchmark、Robot Platform 中的 Unknown 继续保留，不从题名推断。</x:v>
       </x:c>
       <x:c r="BE32" t="str">
-        <x:v>Unknown / Needs Full-Paper Verification</x:v>
+        <x:v>作者报告在 Meta-World 任务上有竞争力的表现；具体数字见实验表。</x:v>
       </x:c>
       <x:c r="BF32" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -36092,7 +36120,7 @@
       <x:c r="BI32" t="str">
         <x:v>B</x:v>
       </x:c>
-      <x:c r="BJ32" t="str"/>
+      <x:c r="BJ32"/>
       <x:c r="BK32" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
@@ -36156,7 +36184,7 @@
       </x:c>
       <x:c r="CF32"/>
       <x:c r="CG32" t="str">
-        <x:v>机器人策略需要按文字目标学习行为，而奖励设计成本较高。</x:v>
+        <x:v>研究问题：机器人策略需要按文字目标学习行为，而奖励设计成本较高。；之前方法的问题：普通扩散生成不能自动判断行为是否符合语言描述。；核心思路：TADPoLe 利用冻结的文本条件模型，为策略学习提供语言相关的信号。；数据集与评测基准：Meta-World 机器人操作环境。；主要结果：作者报告在 Meta-World 任务上有竞争力的表现；具体数字见实验表。；为什么重要：可比较语言约束进入奖励还是进入动作生成器。；与当前项目的关系：Medium：对未来 VLA 有参考价值，真机双臂需独立验证。；主要局限：冻结模型的语言判断可能与真实物理成功不一致。</x:v>
       </x:c>
       <x:c r="CH32" t="str">
         <x:v>普通扩散生成不能自动判断行为是否符合语言描述。</x:v>
@@ -36164,7 +36192,7 @@
       <x:c r="CI32" t="str">
         <x:v>TADPoLe 利用冻结的文本条件模型，为策略学习提供语言相关的信号。</x:v>
       </x:c>
-      <x:c r="CJ32" t="str"/>
+      <x:c r="CJ32"/>
       <x:c r="CK32" t="str">
         <x:v>作者报告在 Meta-World 任务上有竞争力的表现；具体数字见实验表。</x:v>
       </x:c>
@@ -36174,7 +36202,7 @@
       <x:c r="CM32" t="str">
         <x:v>冻结模型的语言判断可能与真实物理成功不一致。</x:v>
       </x:c>
-      <x:c r="CN32" t="str"/>
+      <x:c r="CN32"/>
       <x:c r="CO32" t="str">
         <x:v>Medium：对未来 VLA 有参考价值，真机双臂需独立验证。</x:v>
       </x:c>
@@ -36361,7 +36389,7 @@
         <x:v>Real Robot 字段为 `Yes`；Dataset、Benchmark、Robot Platform 中的 Unknown 继续保留，不从题名推断。</x:v>
       </x:c>
       <x:c r="BE33" t="str">
-        <x:v>Unknown / Needs Full-Paper Verification</x:v>
+        <x:v>作者报告多个操作任务的平均成功率提高超过 7%；具体比较条件见论文。</x:v>
       </x:c>
       <x:c r="BF33" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -36375,7 +36403,7 @@
       <x:c r="BI33" t="str">
         <x:v>B</x:v>
       </x:c>
-      <x:c r="BJ33" t="str"/>
+      <x:c r="BJ33"/>
       <x:c r="BK33" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
@@ -36439,7 +36467,7 @@
       </x:c>
       <x:c r="CF33"/>
       <x:c r="CG33" t="str">
-        <x:v>从人类视频预训练的视觉表示与机器人视角存在域差异。</x:v>
+        <x:v>研究问题：从人类视频预训练的视觉表示与机器人视角存在域差异。；之前方法的问题：直接将人类视频特征用于机器人操作，可能识别不到关键交互区域。；核心思路：利用配对的人类—机器人视频对视觉表示做适配，缩小两种视角/本体差距。；主要结果：作者报告多个操作任务的平均成功率提高超过 7%；具体比较条件见论文。；为什么重要：为低成本视频数据用于普通夹爪策略提供域适配方法。；与当前项目的关系：Medium：人类视频可能补充双臂数据，但动作仍需重定向。；主要局限：视觉特征对齐不等于动作空间和接触动力学也对齐。</x:v>
       </x:c>
       <x:c r="CH33" t="str">
         <x:v>直接将人类视频特征用于机器人操作，可能识别不到关键交互区域。</x:v>
@@ -36447,7 +36475,7 @@
       <x:c r="CI33" t="str">
         <x:v>利用配对的人类—机器人视频对视觉表示做适配，缩小两种视角/本体差距。</x:v>
       </x:c>
-      <x:c r="CJ33" t="str"/>
+      <x:c r="CJ33"/>
       <x:c r="CK33" t="str">
         <x:v>作者报告多个操作任务的平均成功率提高超过 7%；具体比较条件见论文。</x:v>
       </x:c>
@@ -36457,7 +36485,7 @@
       <x:c r="CM33" t="str">
         <x:v>视觉特征对齐不等于动作空间和接触动力学也对齐。</x:v>
       </x:c>
-      <x:c r="CN33" t="str"/>
+      <x:c r="CN33"/>
       <x:c r="CO33" t="str">
         <x:v>Medium：人类视频可能补充双臂数据，但动作仍需重定向。</x:v>
       </x:c>
@@ -36644,7 +36672,7 @@
         <x:v>Real Robot 字段为 `Unknown`；Dataset、Benchmark、Robot Platform 中的 Unknown 继续保留，不从题名推断。</x:v>
       </x:c>
       <x:c r="BE34" t="str">
-        <x:v>Unknown / Needs Full-Paper Verification</x:v>
+        <x:v>官方摘要报告 Grounding mask 能改善策略泛化；快速摘要不填入未核对实验表的数字。</x:v>
       </x:c>
       <x:c r="BF34" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -36658,7 +36686,7 @@
       <x:c r="BI34" t="str">
         <x:v>B</x:v>
       </x:c>
-      <x:c r="BJ34" t="str"/>
+      <x:c r="BJ34"/>
       <x:c r="BK34" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
@@ -36722,7 +36750,7 @@
       </x:c>
       <x:c r="CF34"/>
       <x:c r="CG34" t="str">
-        <x:v>机器人策略需要可靠地定位目标物体与放置区域，才能在新场景中泛化。</x:v>
+        <x:v>研究问题：机器人策略需要可靠地定位目标物体与放置区域，才能在新场景中泛化。；之前方法的问题：只靠最终动作监督，策略未必能学会稳定识别目标物体和放置区域。；核心思路：RoboGround 使用 Grounding mask 作为中间表示，向操作策略提供目标及空间形状信息。；主要结果：官方摘要报告 Grounding mask 能改善策略泛化；快速摘要不填入未核对实验表的数字。；为什么重要：可与 ReconVLA 比较“显式 mask”与“隐式目标区域重建”两种 Grounding 路线。；与当前项目的关系：High：有助于研究语言条件操作与 VLA 设计。；主要局限：合成数据和 mask 质量会影响迁移；真机覆盖范围仍需按论文实验表核验。</x:v>
       </x:c>
       <x:c r="CH34" t="str">
         <x:v>只靠最终动作监督，策略未必能学会稳定识别目标物体和放置区域。</x:v>
@@ -36730,7 +36758,7 @@
       <x:c r="CI34" t="str">
         <x:v>RoboGround 使用 Grounding mask 作为中间表示，向操作策略提供目标及空间形状信息。</x:v>
       </x:c>
-      <x:c r="CJ34" t="str"/>
+      <x:c r="CJ34"/>
       <x:c r="CK34" t="str">
         <x:v>官方摘要报告 Grounding mask 能改善策略泛化；快速摘要不填入未核对实验表的数字。</x:v>
       </x:c>
@@ -36740,7 +36768,7 @@
       <x:c r="CM34" t="str">
         <x:v>合成数据和 mask 质量会影响迁移；真机覆盖范围仍需按论文实验表核验。</x:v>
       </x:c>
-      <x:c r="CN34" t="str"/>
+      <x:c r="CN34"/>
       <x:c r="CO34" t="str">
         <x:v>High：有助于研究语言条件操作与 VLA 设计。</x:v>
       </x:c>
@@ -36941,7 +36969,7 @@
       <x:c r="BI35" t="str">
         <x:v>B</x:v>
       </x:c>
-      <x:c r="BJ35" t="str"/>
+      <x:c r="BJ35"/>
       <x:c r="BK35" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
@@ -37005,7 +37033,7 @@
       </x:c>
       <x:c r="CF35"/>
       <x:c r="CG35" t="str">
-        <x:v>机器人操作需要规模大且接近真实交互的训练场景。</x:v>
+        <x:v>研究问题：机器人操作需要规模大且接近真实交互的训练场景。；之前方法的问题：人工制作动态场景速度慢，动作多样性不足。；核心思路：DynScene 根据文字指令用扩散模型生成动态机器人操作场景。；为什么重要：为扩展双臂训练环境提供合成数据思路。；与当前项目的关系：Medium：生成场景需经过真机接触与任务相关性验证。；主要局限：场景多样性不一定等于真实机器人成功率提升。</x:v>
       </x:c>
       <x:c r="CH35" t="str">
         <x:v>人工制作动态场景速度慢，动作多样性不足。</x:v>
@@ -37013,7 +37041,7 @@
       <x:c r="CI35" t="str">
         <x:v>DynScene 根据文字指令用扩散模型生成动态机器人操作场景。</x:v>
       </x:c>
-      <x:c r="CJ35" t="str"/>
+      <x:c r="CJ35"/>
       <x:c r="CK35" t="str">
         <x:v>卡片记录生成速度提高 26.8 倍、准确率提高 1.84 倍、动作多样性提高 28%；指标定义见原文。</x:v>
       </x:c>
@@ -37023,7 +37051,7 @@
       <x:c r="CM35" t="str">
         <x:v>场景多样性不一定等于真实机器人成功率提升。</x:v>
       </x:c>
-      <x:c r="CN35" t="str"/>
+      <x:c r="CN35"/>
       <x:c r="CO35" t="str">
         <x:v>Medium：生成场景需经过真机接触与任务相关性验证。</x:v>
       </x:c>
@@ -37210,7 +37238,7 @@
         <x:v>Real Robot 字段为 `Yes`；Dataset、Benchmark、Robot Platform 中的 Unknown 继续保留，不从题名推断。</x:v>
       </x:c>
       <x:c r="BE36" t="str">
-        <x:v>Unknown / Needs Full-Paper Verification</x:v>
+        <x:v>作者报告构建大规模技能数据并在仿真与真机上评估；统一数值需查论文。</x:v>
       </x:c>
       <x:c r="BF36" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -37224,7 +37252,7 @@
       <x:c r="BI36" t="str">
         <x:v>B</x:v>
       </x:c>
-      <x:c r="BJ36" t="str"/>
+      <x:c r="BJ36"/>
       <x:c r="BK36" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
@@ -37288,7 +37316,7 @@
       </x:c>
       <x:c r="CF36"/>
       <x:c r="CG36" t="str">
-        <x:v>通用机器人要在不断遇到新任务时持续获得技能。</x:v>
+        <x:v>研究问题：通用机器人要在不断遇到新任务时持续获得技能。；之前方法的问题：每个新任务单独训练会浪费已有的基本动作知识。；核心思路：Primitive Prompt Learning（PPL）复用基础技能提示，支持终身操作学习。；主要结果：作者报告构建大规模技能数据并在仿真与真机上评估；统一数值需查论文。；为什么重要：将技能复用和长期学习连接起来。；与当前项目的关系：Medium：未来双臂技能库可参考，但短期先打通基础实验。；主要局限：新任务是否真的能零样本组合，以及失败如何恢复，需独立核验。</x:v>
       </x:c>
       <x:c r="CH36" t="str">
         <x:v>每个新任务单独训练会浪费已有的基本动作知识。</x:v>
@@ -37296,7 +37324,7 @@
       <x:c r="CI36" t="str">
         <x:v>Primitive Prompt Learning（PPL）复用基础技能提示，支持终身操作学习。</x:v>
       </x:c>
-      <x:c r="CJ36" t="str"/>
+      <x:c r="CJ36"/>
       <x:c r="CK36" t="str">
         <x:v>作者报告构建大规模技能数据并在仿真与真机上评估；统一数值需查论文。</x:v>
       </x:c>
@@ -37306,7 +37334,7 @@
       <x:c r="CM36" t="str">
         <x:v>新任务是否真的能零样本组合，以及失败如何恢复，需独立核验。</x:v>
       </x:c>
-      <x:c r="CN36" t="str"/>
+      <x:c r="CN36"/>
       <x:c r="CO36" t="str">
         <x:v>Medium：未来双臂技能库可参考，但短期先打通基础实验。</x:v>
       </x:c>
@@ -37493,7 +37521,7 @@
         <x:v>Real Robot 字段为 `No`；Dataset、Benchmark、Robot Platform 中的 Unknown 继续保留，不从题名推断。</x:v>
       </x:c>
       <x:c r="BE37" t="str">
-        <x:v>Unknown / Needs Full-Paper Verification</x:v>
+        <x:v>AAAI 官方摘要报告在 RLBench 10 项任务、166 种变化上，平均成功率比所比较方法高 12.0 个百分点。</x:v>
       </x:c>
       <x:c r="BF37" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -37507,7 +37535,7 @@
       <x:c r="BI37" t="str">
         <x:v>B</x:v>
       </x:c>
-      <x:c r="BJ37" t="str"/>
+      <x:c r="BJ37"/>
       <x:c r="BK37" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
@@ -37571,7 +37599,7 @@
       </x:c>
       <x:c r="CF37"/>
       <x:c r="CG37" t="str">
-        <x:v>策略执行后可能没有达到预测的场景状态，却仍继续下一步。</x:v>
+        <x:v>研究问题：策略执行后可能没有达到预测的场景状态，却仍继续下一步。；之前方法的问题：缺少可靠的执行结果检查会让局部误差在长任务中累积。；核心思路：利用 Gaussian Splatting 预测下一场景，将真实观测与预测比较，必要时回退并修正动作；与 PerACT 结合。；输入：官方摘要给出任务/数据类型；具体模型张量与接口需核对方法章节。；输出与动作：官方摘要未明确列出完整控制接口；需核对论文方法或代码。；数据集与评测基准：RLBench：10 项任务、166 种变化。；主要结果：AAAI 官方摘要报告在 RLBench 10 项任务、166 种变化上，平均成功率比所比较方法高 12.0 个百分点。；为什么重要：直接对应项目中的动作后验证与失败恢复。；与当前项目的关系：Medium：方法可借鉴，但迁移到当前双臂硬件需验证。；主要局限：本段基于官方摘要；未覆盖全文失败案例、完整 Baseline 与方法消融。</x:v>
       </x:c>
       <x:c r="CH37" t="str">
         <x:v>缺少可靠的执行结果检查会让局部误差在长任务中累积。</x:v>
@@ -37579,7 +37607,7 @@
       <x:c r="CI37" t="str">
         <x:v>利用 Gaussian Splatting 预测下一场景，将真实观测与预测比较，必要时回退并修正动作；与 PerACT 结合。</x:v>
       </x:c>
-      <x:c r="CJ37" t="str"/>
+      <x:c r="CJ37"/>
       <x:c r="CK37" t="str">
         <x:v>AAAI 官方摘要报告在 RLBench 10 项任务、166 种变化上，平均成功率比所比较方法高 12.0 个百分点。</x:v>
       </x:c>
@@ -37589,7 +37617,7 @@
       <x:c r="CM37" t="str">
         <x:v>本段基于官方摘要；未覆盖全文失败案例、完整 Baseline 与方法消融。</x:v>
       </x:c>
-      <x:c r="CN37" t="str"/>
+      <x:c r="CN37"/>
       <x:c r="CO37" t="str">
         <x:v>Medium：方法可借鉴，但迁移到当前双臂硬件需验证。</x:v>
       </x:c>
@@ -37776,7 +37804,7 @@
         <x:v>Real Robot 字段为 `Yes`；Dataset、Benchmark、Robot Platform 中的 Unknown 继续保留，不从题名推断。</x:v>
       </x:c>
       <x:c r="BE38" t="str">
-        <x:v>Unknown / Needs Full-Paper Verification</x:v>
+        <x:v>AAAI 摘要报告在关节物体任务上优于对比方法；具体数值需核对论文表格。</x:v>
       </x:c>
       <x:c r="BF38" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -37790,7 +37818,7 @@
       <x:c r="BI38" t="str">
         <x:v>B</x:v>
       </x:c>
-      <x:c r="BJ38" t="str"/>
+      <x:c r="BJ38"/>
       <x:c r="BK38" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
@@ -37854,7 +37882,7 @@
       </x:c>
       <x:c r="CF38"/>
       <x:c r="CG38" t="str">
-        <x:v>关节物体操作需要同时识别可动部件、关节参数和可行的末端轨迹。</x:v>
+        <x:v>研究问题：关节物体操作需要同时识别可动部件、关节参数和可行的末端轨迹。；之前方法的问题：既有方法多只解决感知或 affordance 的一部分，缺少从指令到动作的完整链条。；核心思路：GMAP 结合部件分割、关节几何估计与可操作点预测，再规划末端位姿/轨迹。；输入：官方摘要给出任务/数据类型；具体模型张量与接口需核对方法章节。；输出与动作：官方摘要未明确列出完整控制接口；需核对论文方法或代码。；数据集与评测基准：关节物体操作任务；具体 benchmark 见论文。；主要结果：AAAI 摘要报告在关节物体任务上优于对比方法；具体数值需核对论文表格。；为什么重要：可为普通夹爪操作抽屉、柜门等任务提供几何约束参考。；与当前项目的关系：Medium：方法可借鉴，但迁移到当前双臂硬件需验证。；主要局限：本段基于官方摘要；未覆盖全文失败案例、完整 Baseline 与方法消融。</x:v>
       </x:c>
       <x:c r="CH38" t="str">
         <x:v>既有方法多只解决感知或 affordance 的一部分，缺少从指令到动作的完整链条。</x:v>
@@ -37862,7 +37890,7 @@
       <x:c r="CI38" t="str">
         <x:v>GMAP 结合部件分割、关节几何估计与可操作点预测，再规划末端位姿/轨迹。</x:v>
       </x:c>
-      <x:c r="CJ38" t="str"/>
+      <x:c r="CJ38"/>
       <x:c r="CK38" t="str">
         <x:v>AAAI 摘要报告在关节物体任务上优于对比方法；具体数值需核对论文表格。</x:v>
       </x:c>
@@ -37872,7 +37900,7 @@
       <x:c r="CM38" t="str">
         <x:v>本段基于官方摘要；未覆盖全文失败案例、完整 Baseline 与方法消融。</x:v>
       </x:c>
-      <x:c r="CN38" t="str"/>
+      <x:c r="CN38"/>
       <x:c r="CO38" t="str">
         <x:v>Medium：方法可借鉴，但迁移到当前双臂硬件需验证。</x:v>
       </x:c>
@@ -38059,7 +38087,7 @@
         <x:v>Real Robot 字段为 `Yes`；Dataset、Benchmark、Robot Platform 中的 Unknown 继续保留，不从题名推断。</x:v>
       </x:c>
       <x:c r="BE39" t="str">
-        <x:v>Unknown / Needs Full-Paper Verification</x:v>
+        <x:v>AAAI 官方摘要报告包含七类操作技能的真机长任务，平均成功率超过 80%。</x:v>
       </x:c>
       <x:c r="BF39" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -38073,7 +38101,7 @@
       <x:c r="BI39" t="str">
         <x:v>B</x:v>
       </x:c>
-      <x:c r="BJ39" t="str"/>
+      <x:c r="BJ39"/>
       <x:c r="BK39" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
@@ -38137,7 +38165,7 @@
       </x:c>
       <x:c r="CF39"/>
       <x:c r="CG39" t="str">
-        <x:v>移动操作的长任务规划需要把语言计划落实到实时环境状态。</x:v>
+        <x:v>研究问题：移动操作的长任务规划需要把语言计划落实到实时环境状态。；之前方法的问题：只依赖人工文字场景描述或 prompt，难以判断物体是否真的可操作。；核心思路：IALP 把 LLM 推理、PDDL 问题与传感器反馈结合，闭环更新高层操作计划。；输入：官方摘要给出任务/数据类型；具体模型张量与接口需核对方法章节。；输出与动作：官方摘要未明确列出完整控制接口；需核对论文方法或代码。；数据集与评测基准：多项真实环境长时序移动操作任务。；主要结果：AAAI 官方摘要报告包含七类操作技能的真机长任务，平均成功率超过 80%。；为什么重要：可比较高层重新规划与双臂底层动作执行之间的接口。；与当前项目的关系：High：直接关联双臂普通夹爪、VLA 或真机操作。；主要局限：本段基于官方摘要；未覆盖全文失败案例、完整 Baseline 与方法消融。</x:v>
       </x:c>
       <x:c r="CH39" t="str">
         <x:v>只依赖人工文字场景描述或 prompt，难以判断物体是否真的可操作。</x:v>
@@ -38145,7 +38173,7 @@
       <x:c r="CI39" t="str">
         <x:v>IALP 把 LLM 推理、PDDL 问题与传感器反馈结合，闭环更新高层操作计划。</x:v>
       </x:c>
-      <x:c r="CJ39" t="str"/>
+      <x:c r="CJ39"/>
       <x:c r="CK39" t="str">
         <x:v>AAAI 官方摘要报告包含七类操作技能的真机长任务，平均成功率超过 80%。</x:v>
       </x:c>
@@ -38155,7 +38183,7 @@
       <x:c r="CM39" t="str">
         <x:v>本段基于官方摘要；未覆盖全文失败案例、完整 Baseline 与方法消融。</x:v>
       </x:c>
-      <x:c r="CN39" t="str"/>
+      <x:c r="CN39"/>
       <x:c r="CO39" t="str">
         <x:v>High：直接关联双臂普通夹爪、VLA 或真机操作。</x:v>
       </x:c>
@@ -38356,7 +38384,7 @@
       <x:c r="BI40" t="str">
         <x:v>B</x:v>
       </x:c>
-      <x:c r="BJ40" t="str"/>
+      <x:c r="BJ40"/>
       <x:c r="BK40" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
@@ -38420,7 +38448,7 @@
       </x:c>
       <x:c r="CF40"/>
       <x:c r="CG40" t="str">
-        <x:v>机器人需要利用视频数据理解物理动态并改进操作动作预测。</x:v>
+        <x:v>研究问题：机器人需要利用视频数据理解物理动态并改进操作动作预测。；之前方法的问题：单纯视频生成不保证生成的表示能直接帮助稳定的机器人控制。；核心思路：VidMan 使用两阶段训练，将视频扩散模型的动态表征引入机器人操作策略。；数据集与评测基准：CALVIN 与 OXE 小规模数据评测；具体任务和数据划分见论文。；为什么重要：为从视频世界模型到动作策略的连接提供对照方法。；与当前项目的关系：Medium：可帮助研究视觉预测是否改善双臂操作，但真机适配需验证。；主要局限：已核验摘要未完整报告失败类型与真机泛化边界。</x:v>
       </x:c>
       <x:c r="CH40" t="str">
         <x:v>单纯视频生成不保证生成的表示能直接帮助稳定的机器人控制。</x:v>
@@ -38428,7 +38456,7 @@
       <x:c r="CI40" t="str">
         <x:v>VidMan 使用两阶段训练，将视频扩散模型的动态表征引入机器人操作策略。</x:v>
       </x:c>
-      <x:c r="CJ40" t="str"/>
+      <x:c r="CJ40"/>
       <x:c r="CK40" t="str">
         <x:v>卡片记录相对 GR-1 在 CALVIN 上提升 11.7%，在 OXE 小规模数据上精度提升超过 9%。</x:v>
       </x:c>
@@ -38438,7 +38466,7 @@
       <x:c r="CM40" t="str">
         <x:v>已核验摘要未完整报告失败类型与真机泛化边界。</x:v>
       </x:c>
-      <x:c r="CN40" t="str"/>
+      <x:c r="CN40"/>
       <x:c r="CO40" t="str">
         <x:v>Medium：可帮助研究视觉预测是否改善双臂操作，但真机适配需验证。</x:v>
       </x:c>
@@ -38625,7 +38653,7 @@
         <x:v>Real Robot 字段为 `Unknown`；Dataset、Benchmark、Robot Platform 中的 Unknown 继续保留，不从题名推断。</x:v>
       </x:c>
       <x:c r="BE41" t="str">
-        <x:v>Unknown / Needs Full-Paper Verification</x:v>
+        <x:v>论文报告在 13 项操作任务上优于比较方法；具体指标见正文。</x:v>
       </x:c>
       <x:c r="BF41" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -38639,7 +38667,7 @@
       <x:c r="BI41" t="str">
         <x:v>B</x:v>
       </x:c>
-      <x:c r="BJ41" t="str"/>
+      <x:c r="BJ41"/>
       <x:c r="BK41" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
@@ -38703,7 +38731,7 @@
       </x:c>
       <x:c r="CF41"/>
       <x:c r="CG41" t="str">
-        <x:v>家庭机器人需要在不同物体和任务上迅速操作。</x:v>
+        <x:v>研究问题：家庭机器人需要在不同物体和任务上迅速操作。；之前方法的问题：大量真机示范难以覆盖所有新场景。；核心思路：VidBot 从互联网视频学习三维 affordance，用于零样本机器人操作。；主要结果：论文报告在 13 项操作任务上优于比较方法；具体指标见正文。；为什么重要：探索网络视频到真机可执行区域的知识迁移。；与当前项目的关系：Medium：双臂夹爪可借鉴 affordance，但动作适配需验证。；主要局限：互联网视频中的三维尺度和真实机器人可达性可能不一致。</x:v>
       </x:c>
       <x:c r="CH41" t="str">
         <x:v>大量真机示范难以覆盖所有新场景。</x:v>
@@ -38711,7 +38739,7 @@
       <x:c r="CI41" t="str">
         <x:v>VidBot 从互联网视频学习三维 affordance，用于零样本机器人操作。</x:v>
       </x:c>
-      <x:c r="CJ41" t="str"/>
+      <x:c r="CJ41"/>
       <x:c r="CK41" t="str">
         <x:v>论文报告在 13 项操作任务上优于比较方法；具体指标见正文。</x:v>
       </x:c>
@@ -38721,7 +38749,7 @@
       <x:c r="CM41" t="str">
         <x:v>互联网视频中的三维尺度和真实机器人可达性可能不一致。</x:v>
       </x:c>
-      <x:c r="CN41" t="str"/>
+      <x:c r="CN41"/>
       <x:c r="CO41" t="str">
         <x:v>Medium：双臂夹爪可借鉴 affordance，但动作适配需验证。</x:v>
       </x:c>
@@ -38922,7 +38950,7 @@
       <x:c r="BI42" t="str">
         <x:v>A</x:v>
       </x:c>
-      <x:c r="BJ42" t="str"/>
+      <x:c r="BJ42"/>
       <x:c r="BK42" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
@@ -38986,7 +39014,7 @@
       </x:c>
       <x:c r="CF42"/>
       <x:c r="CG42" t="str">
-        <x:v>直接从视觉和语言映射动作的 VLA 缺少显式中间推理，复杂操作时容易失去目标感。</x:v>
+        <x:v>研究问题：直接从视觉和语言映射动作的 VLA 缺少显式中间推理，复杂操作时容易失去目标感。；之前方法的问题：直接输入到动作的映射没有显式中间目标，复杂操作缺少可检查的推理步骤。；核心思路：CoT-VLA 先自回归预测未来图像作为视觉子目标，再生成短动作序列，使中间视觉推理参与控制。；数据集与评测基准：使用 Open X-Embodiment 示范及 EPIC-KITCHENS、Something-Something V2 视频；下游任务包括 BridgeData V2、Franka-Tabletop。；为什么重要：可检验“先预测视觉目标再行动”是否改善长任务和双臂目标协调。；与当前项目的关系：High：有助于研究语言条件操作与 VLA 设计。；主要局限：依赖 7B VILA-U 和任务适配；推理/控制效率与更广的机器人本体仍需核验。</x:v>
       </x:c>
       <x:c r="CH42" t="str">
         <x:v>直接输入到动作的映射没有显式中间目标，复杂操作缺少可检查的推理步骤。</x:v>
@@ -38994,7 +39022,7 @@
       <x:c r="CI42" t="str">
         <x:v>CoT-VLA 先自回归预测未来图像作为视觉子目标，再生成短动作序列，使中间视觉推理参与控制。</x:v>
       </x:c>
-      <x:c r="CJ42" t="str"/>
+      <x:c r="CJ42"/>
       <x:c r="CK42" t="str">
         <x:v>卡片记录 LIBERO 平均成功率 81.13%，Long 子集为 69.0%；相对于所报告基线的提升和设置见 Table 1。</x:v>
       </x:c>
@@ -39004,7 +39032,7 @@
       <x:c r="CM42" t="str">
         <x:v>依赖 7B VILA-U 和任务适配；推理/控制效率与更广的机器人本体仍需核验。</x:v>
       </x:c>
-      <x:c r="CN42" t="str"/>
+      <x:c r="CN42"/>
       <x:c r="CO42" t="str">
         <x:v>High：有助于研究语言条件操作与 VLA 设计。</x:v>
       </x:c>
@@ -39191,7 +39219,7 @@
         <x:v>Real Robot 字段为 `Yes`；Dataset、Benchmark、Robot Platform 中的 Unknown 继续保留，不从题名推断。</x:v>
       </x:c>
       <x:c r="BE43" t="str">
-        <x:v>Unknown / Needs Full-Paper Verification</x:v>
+        <x:v>作者报告在挑战性真机任务上成功率最高提升约 30%；具体比较条件见正文。</x:v>
       </x:c>
       <x:c r="BF43" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -39205,7 +39233,7 @@
       <x:c r="BI43" t="str">
         <x:v>B</x:v>
       </x:c>
-      <x:c r="BJ43" t="str"/>
+      <x:c r="BJ43"/>
       <x:c r="BK43" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
@@ -39269,7 +39297,7 @@
       </x:c>
       <x:c r="CF43"/>
       <x:c r="CG43" t="str">
-        <x:v>真机示范采集成本高，但只靠仿真训练又难泛化到现实。</x:v>
+        <x:v>研究问题：真机示范采集成本高，但只靠仿真训练又难泛化到现实。；之前方法的问题：仿真与真实数据分布不同，简单混合训练可能利用不好少量真机样本。；核心思路：联合训练仿真和少量真实机器人数据，并做域适配，学习更可迁移的操作策略。；主要结果：作者报告在挑战性真机任务上成功率最高提升约 30%；具体比较条件见正文。；为什么重要：帮助设计合成数据与真实示范的使用比例。；与当前项目的关系：High：项目需要以有限真机数据训练双臂策略。；主要局限：不同机器人与任务的 Sim2Real 差异需独立测量。</x:v>
       </x:c>
       <x:c r="CH43" t="str">
         <x:v>仿真与真实数据分布不同，简单混合训练可能利用不好少量真机样本。</x:v>
@@ -39277,7 +39305,7 @@
       <x:c r="CI43" t="str">
         <x:v>联合训练仿真和少量真实机器人数据，并做域适配，学习更可迁移的操作策略。</x:v>
       </x:c>
-      <x:c r="CJ43" t="str"/>
+      <x:c r="CJ43"/>
       <x:c r="CK43" t="str">
         <x:v>作者报告在挑战性真机任务上成功率最高提升约 30%；具体比较条件见正文。</x:v>
       </x:c>
@@ -39287,7 +39315,7 @@
       <x:c r="CM43" t="str">
         <x:v>不同机器人与任务的 Sim2Real 差异需独立测量。</x:v>
       </x:c>
-      <x:c r="CN43" t="str"/>
+      <x:c r="CN43"/>
       <x:c r="CO43" t="str">
         <x:v>High：项目需要以有限真机数据训练双臂策略。</x:v>
       </x:c>
@@ -39474,7 +39502,7 @@
         <x:v>Real Robot 字段为 `Unknown`；Dataset、Benchmark、Robot Platform 中的 Unknown 继续保留，不从题名推断。</x:v>
       </x:c>
       <x:c r="BE44" t="str">
-        <x:v>Unknown / Needs Full-Paper Verification</x:v>
+        <x:v>作者报告增强后的 7B LLM 规划能力明显改善；具体数值需核对论文。</x:v>
       </x:c>
       <x:c r="BF44" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -39488,7 +39516,7 @@
       <x:c r="BI44" t="str">
         <x:v>B</x:v>
       </x:c>
-      <x:c r="BJ44" t="str"/>
+      <x:c r="BJ44"/>
       <x:c r="BK44" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
@@ -39552,7 +39580,7 @@
       </x:c>
       <x:c r="CF44"/>
       <x:c r="CG44" t="str">
-        <x:v>LLM 能生成操作计划，但可能缺少任务执行所需的具体程序知识。</x:v>
+        <x:v>研究问题：LLM 能生成操作计划，但可能缺少任务执行所需的具体程序知识。；之前方法的问题：只靠 prompt 难以稳定选择正确技能和步骤。；核心思路：用 Hierarchical Procedural Knowledge Graph（HP-KG）为 LLM 提供分层操作过程知识。；主要结果：作者报告增强后的 7B LLM 规划能力明显改善；具体数值需核对论文。；为什么重要：提供比单纯增大语言模型更可控的规划知识表示。；与当前项目的关系：Medium：可用于未来双臂高层任务规划。；主要局限：计划正确不保证夹爪动作可执行；需真机验证。</x:v>
       </x:c>
       <x:c r="CH44" t="str">
         <x:v>只靠 prompt 难以稳定选择正确技能和步骤。</x:v>
@@ -39560,7 +39588,7 @@
       <x:c r="CI44" t="str">
         <x:v>用 Hierarchical Procedural Knowledge Graph（HP-KG）为 LLM 提供分层操作过程知识。</x:v>
       </x:c>
-      <x:c r="CJ44" t="str"/>
+      <x:c r="CJ44"/>
       <x:c r="CK44" t="str">
         <x:v>作者报告增强后的 7B LLM 规划能力明显改善；具体数值需核对论文。</x:v>
       </x:c>
@@ -39570,7 +39598,7 @@
       <x:c r="CM44" t="str">
         <x:v>计划正确不保证夹爪动作可执行；需真机验证。</x:v>
       </x:c>
-      <x:c r="CN44" t="str"/>
+      <x:c r="CN44"/>
       <x:c r="CO44" t="str">
         <x:v>Medium：可用于未来双臂高层任务规划。</x:v>
       </x:c>
@@ -39757,7 +39785,7 @@
         <x:v>Real Robot 字段为 `No`；Dataset、Benchmark、Robot Platform 中的 Unknown 继续保留，不从题名推断。</x:v>
       </x:c>
       <x:c r="BE45" t="str">
-        <x:v>Unknown / Needs Full-Paper Verification</x:v>
+        <x:v>论文报告在多项操作任务中总计算时间减少约 2.6–4.4 倍；具体成功率权衡见原文。</x:v>
       </x:c>
       <x:c r="BF45" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -39771,7 +39799,7 @@
       <x:c r="BI45" t="str">
         <x:v>B</x:v>
       </x:c>
-      <x:c r="BJ45" t="str"/>
+      <x:c r="BJ45"/>
       <x:c r="BK45" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
@@ -39835,7 +39863,7 @@
       </x:c>
       <x:c r="CF45"/>
       <x:c r="CG45" t="str">
-        <x:v>扩散和 Flow Policy 能生成复杂动作，但每次推理成本较高。</x:v>
+        <x:v>研究问题：扩散和 Flow Policy 能生成复杂动作，但每次推理成本较高。；之前方法的问题：所有状态都用同样计算量会浪费简单动作的时间。；核心思路：DA-SIP 根据当前控制难度动态调整测试时计算量。；主要结果：论文报告在多项操作任务中总计算时间减少约 2.6–4.4 倍；具体成功率权衡见原文。；为什么重要：为双臂真机部署提供按难度分配算力的思路。；与当前项目的关系：High：动作频率和失败风险都受推理延迟影响。；主要局限：难度估计错误可能使困难接触动作获得不足计算。</x:v>
       </x:c>
       <x:c r="CH45" t="str">
         <x:v>所有状态都用同样计算量会浪费简单动作的时间。</x:v>
@@ -39843,7 +39871,7 @@
       <x:c r="CI45" t="str">
         <x:v>DA-SIP 根据当前控制难度动态调整测试时计算量。</x:v>
       </x:c>
-      <x:c r="CJ45" t="str"/>
+      <x:c r="CJ45"/>
       <x:c r="CK45" t="str">
         <x:v>论文报告在多项操作任务中总计算时间减少约 2.6–4.4 倍；具体成功率权衡见原文。</x:v>
       </x:c>
@@ -39853,7 +39881,7 @@
       <x:c r="CM45" t="str">
         <x:v>难度估计错误可能使困难接触动作获得不足计算。</x:v>
       </x:c>
-      <x:c r="CN45" t="str"/>
+      <x:c r="CN45"/>
       <x:c r="CO45" t="str">
         <x:v>High：动作频率和失败风险都受推理延迟影响。</x:v>
       </x:c>
@@ -40040,7 +40068,7 @@
         <x:v>Real Robot 字段为 `Yes`；Dataset、Benchmark、Robot Platform 中的 Unknown 继续保留，不从题名推断。</x:v>
       </x:c>
       <x:c r="BE46" t="str">
-        <x:v>Unknown / Needs Full-Paper Verification</x:v>
+        <x:v>作者报告相对所比较基础模型达到更好表现；具体 benchmark 和数字见论文。</x:v>
       </x:c>
       <x:c r="BF46" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -40054,7 +40082,7 @@
       <x:c r="BI46" t="str">
         <x:v>B</x:v>
       </x:c>
-      <x:c r="BJ46" t="str"/>
+      <x:c r="BJ46"/>
       <x:c r="BK46" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
@@ -40118,7 +40146,7 @@
       </x:c>
       <x:c r="CF46"/>
       <x:c r="CG46" t="str">
-        <x:v>移动机器人要在开放世界同时处理导航、场景理解与物体操作。</x:v>
+        <x:v>研究问题：移动机器人要在开放世界同时处理导航、场景理解与物体操作。；之前方法的问题：多个专用模块的状态难以统一维护和协调。；核心思路：OWMM-Agent 用多模态代理维护多视角场景表示并组织操作步骤。；主要结果：作者报告相对所比较基础模型达到更好表现；具体 benchmark 和数字见论文。；为什么重要：可参考复杂任务中感知与规划状态如何保持一致。；与当前项目的关系：Medium：本项目主要是双臂操作，不直接涉及移动导航。；主要局限：模块化代理的误差传播与真机长任务稳定性需核验。</x:v>
       </x:c>
       <x:c r="CH46" t="str">
         <x:v>多个专用模块的状态难以统一维护和协调。</x:v>
@@ -40126,7 +40154,7 @@
       <x:c r="CI46" t="str">
         <x:v>OWMM-Agent 用多模态代理维护多视角场景表示并组织操作步骤。</x:v>
       </x:c>
-      <x:c r="CJ46" t="str"/>
+      <x:c r="CJ46"/>
       <x:c r="CK46" t="str">
         <x:v>作者报告相对所比较基础模型达到更好表现；具体 benchmark 和数字见论文。</x:v>
       </x:c>
@@ -40136,7 +40164,7 @@
       <x:c r="CM46" t="str">
         <x:v>模块化代理的误差传播与真机长任务稳定性需核验。</x:v>
       </x:c>
-      <x:c r="CN46" t="str"/>
+      <x:c r="CN46"/>
       <x:c r="CO46" t="str">
         <x:v>Medium：本项目主要是双臂操作，不直接涉及移动导航。</x:v>
       </x:c>
@@ -40337,7 +40365,7 @@
       <x:c r="BI47" t="str">
         <x:v>B</x:v>
       </x:c>
-      <x:c r="BJ47" t="str"/>
+      <x:c r="BJ47"/>
       <x:c r="BK47" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
@@ -40401,7 +40429,7 @@
       </x:c>
       <x:c r="CF47"/>
       <x:c r="CG47" t="str">
-        <x:v>生成式视觉运动策略在复杂动作上表现好，但在线推理可能偏慢。</x:v>
+        <x:v>研究问题：生成式视觉运动策略在复杂动作上表现好，但在线推理可能偏慢。；之前方法的问题：常规 Flow Policy 未充分利用动作中的不同频率结构。；核心思路：FreqPolicy 给流式动作生成加入频率一致性约束，并尝试融入 VLA。；为什么重要：为实时双臂控制提供动作频率建模视角。；与当前项目的关系：High：推理延迟直接影响双臂同步和失败检测。；主要局限：需核验高频控制对真机安全与接触稳定性的影响。</x:v>
       </x:c>
       <x:c r="CH47" t="str">
         <x:v>常规 Flow Policy 未充分利用动作中的不同频率结构。</x:v>
@@ -40409,7 +40437,7 @@
       <x:c r="CI47" t="str">
         <x:v>FreqPolicy 给流式动作生成加入频率一致性约束，并尝试融入 VLA。</x:v>
       </x:c>
-      <x:c r="CJ47" t="str"/>
+      <x:c r="CJ47"/>
       <x:c r="CK47" t="str">
         <x:v>作者报告在 VLA 中加速而不降低所报告任务表现；具体速度数值需查正文。</x:v>
       </x:c>
@@ -40419,7 +40447,7 @@
       <x:c r="CM47" t="str">
         <x:v>需核验高频控制对真机安全与接触稳定性的影响。</x:v>
       </x:c>
-      <x:c r="CN47" t="str"/>
+      <x:c r="CN47"/>
       <x:c r="CO47" t="str">
         <x:v>High：推理延迟直接影响双臂同步和失败检测。</x:v>
       </x:c>
@@ -40606,7 +40634,7 @@
         <x:v>Real Robot 字段为 `Unknown`；Dataset、Benchmark、Robot Platform 中的 Unknown 继续保留，不从题名推断。</x:v>
       </x:c>
       <x:c r="BE48" t="str">
-        <x:v>Unknown / Needs Full-Paper Verification</x:v>
+        <x:v>论文报告平均成功率 50.0%，高于 3D 生成基线 21.4% 和工具检索基线 11.1%。</x:v>
       </x:c>
       <x:c r="BF48" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -40620,7 +40648,7 @@
       <x:c r="BI48" t="str">
         <x:v>B</x:v>
       </x:c>
-      <x:c r="BJ48" t="str"/>
+      <x:c r="BJ48"/>
       <x:c r="BK48" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
@@ -40684,7 +40712,7 @@
       </x:c>
       <x:c r="CF48"/>
       <x:c r="CG48" t="str">
-        <x:v>一些复杂操作需要先设计或选择合适工具，机器人现有能力不足以直接完成。</x:v>
+        <x:v>研究问题：一些复杂操作需要先设计或选择合适工具，机器人现有能力不足以直接完成。；之前方法的问题：只靠视觉语言模型可能不了解真实物理约束；只检索现有工具也会限制任务覆盖。；核心思路：RobotSmith 结合 VLM 中的物理常识和仿真提供的更精确物理反馈，自动设计并使用工具。；数据集与评测基准：工具设计与操作任务；具体任务和基线见论文实验。；主要结果：论文报告平均成功率 50.0%，高于 3D 生成基线 21.4% 和工具检索基线 11.1%。；为什么重要：展示语言模型与物理仿真协同设计工具的可能性。；与当前项目的关系：Medium：工具规划思路可借鉴，但本项目当前重点仍是双臂普通夹爪。；主要局限：摘要未明确说明全部真机失败类型和工具制造约束。</x:v>
       </x:c>
       <x:c r="CH48" t="str">
         <x:v>只靠视觉语言模型可能不了解真实物理约束；只检索现有工具也会限制任务覆盖。</x:v>
@@ -40692,7 +40720,7 @@
       <x:c r="CI48" t="str">
         <x:v>RobotSmith 结合 VLM 中的物理常识和仿真提供的更精确物理反馈，自动设计并使用工具。</x:v>
       </x:c>
-      <x:c r="CJ48" t="str"/>
+      <x:c r="CJ48"/>
       <x:c r="CK48" t="str">
         <x:v>论文报告平均成功率 50.0%，高于 3D 生成基线 21.4% 和工具检索基线 11.1%。</x:v>
       </x:c>
@@ -40702,7 +40730,7 @@
       <x:c r="CM48" t="str">
         <x:v>摘要未明确说明全部真机失败类型和工具制造约束。</x:v>
       </x:c>
-      <x:c r="CN48" t="str"/>
+      <x:c r="CN48"/>
       <x:c r="CO48" t="str">
         <x:v>Medium：工具规划思路可借鉴，但本项目当前重点仍是双臂普通夹爪。</x:v>
       </x:c>
@@ -40889,7 +40917,7 @@
         <x:v>Real Robot 字段为 `Yes`；Dataset、Benchmark、Robot Platform 中的 Unknown 继续保留，不从题名推断。</x:v>
       </x:c>
       <x:c r="BE49" t="str">
-        <x:v>Unknown / Needs Full-Paper Verification</x:v>
+        <x:v>论文报告在上述 benchmark 和真机任务中取得较好表现；具体数值见正文。</x:v>
       </x:c>
       <x:c r="BF49" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -40903,7 +40931,7 @@
       <x:c r="BI49" t="str">
         <x:v>B</x:v>
       </x:c>
-      <x:c r="BJ49" t="str"/>
+      <x:c r="BJ49"/>
       <x:c r="BK49" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
@@ -40967,7 +40995,7 @@
       </x:c>
       <x:c r="CF49"/>
       <x:c r="CG49" t="str">
-        <x:v>多种传感输入各有优势，如何保留点云中的局部几何信息。</x:v>
+        <x:v>研究问题：多种传感输入各有优势，如何保留点云中的局部几何信息。；之前方法的问题：点云下采样可能丢掉接触附近的关键结构。；核心思路：PointMapPolicy 把结构化点网格作为扩散策略条件，减少对大幅下采样的依赖。；数据集与评测基准：RoboCasa、CALVIN 与真机评测。；主要结果：论文报告在上述 benchmark 和真机任务中取得较好表现；具体数值见正文。；为什么重要：有助于研究普通夹爪接触区域的三维表示。；与当前项目的关系：Medium：双臂空间定位相关，部署延迟需验证。；主要局限：高密度点数据会增加显存与在线计算成本。</x:v>
       </x:c>
       <x:c r="CH49" t="str">
         <x:v>点云下采样可能丢掉接触附近的关键结构。</x:v>
@@ -40975,7 +41003,7 @@
       <x:c r="CI49" t="str">
         <x:v>PointMapPolicy 把结构化点网格作为扩散策略条件，减少对大幅下采样的依赖。</x:v>
       </x:c>
-      <x:c r="CJ49" t="str"/>
+      <x:c r="CJ49"/>
       <x:c r="CK49" t="str">
         <x:v>论文报告在上述 benchmark 和真机任务中取得较好表现；具体数值见正文。</x:v>
       </x:c>
@@ -40985,7 +41013,7 @@
       <x:c r="CM49" t="str">
         <x:v>高密度点数据会增加显存与在线计算成本。</x:v>
       </x:c>
-      <x:c r="CN49" t="str"/>
+      <x:c r="CN49"/>
       <x:c r="CO49" t="str">
         <x:v>Medium：双臂空间定位相关，部署延迟需验证。</x:v>
       </x:c>
@@ -41172,7 +41200,7 @@
         <x:v>Real Robot 字段为 `Yes`；Dataset、Benchmark、Robot Platform 中的 Unknown 继续保留，不从题名推断。</x:v>
       </x:c>
       <x:c r="BE50" t="str">
-        <x:v>Unknown / Needs Full-Paper Verification</x:v>
+        <x:v>已核验摘要未给可安全复述的统一量化结果。</x:v>
       </x:c>
       <x:c r="BF50" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -41186,7 +41214,7 @@
       <x:c r="BI50" t="str">
         <x:v>B</x:v>
       </x:c>
-      <x:c r="BJ50" t="str"/>
+      <x:c r="BJ50"/>
       <x:c r="BK50" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
@@ -41250,7 +41278,7 @@
       </x:c>
       <x:c r="CF50"/>
       <x:c r="CG50" t="str">
-        <x:v>互联网图文训练的 VLM 缺少机器人特定的视觉与操作知识。</x:v>
+        <x:v>研究问题：互联网图文训练的 VLM 缺少机器人特定的视觉与操作知识。；之前方法的问题：通用问答数据不一定包含机器人动作和物体可操作性。；核心思路：Robo2VLM 构建机器人相关 VQA 数据，用于训练或评估 VLM 的具身理解。；主要结果：已核验摘要未给可安全复述的统一量化结果。；为什么重要：可辅助检查 VLA 的语言/视觉前端是否理解机器人场景。；与当前项目的关系：Medium：问答能力与真机动作成功要分开评测。；主要局限：VQA 指标不能直接代表可执行动作质量。</x:v>
       </x:c>
       <x:c r="CH50" t="str">
         <x:v>通用问答数据不一定包含机器人动作和物体可操作性。</x:v>
@@ -41258,7 +41286,7 @@
       <x:c r="CI50" t="str">
         <x:v>Robo2VLM 构建机器人相关 VQA 数据，用于训练或评估 VLM 的具身理解。</x:v>
       </x:c>
-      <x:c r="CJ50" t="str"/>
+      <x:c r="CJ50"/>
       <x:c r="CK50" t="str">
         <x:v>已核验摘要未给可安全复述的统一量化结果。</x:v>
       </x:c>
@@ -41268,7 +41296,7 @@
       <x:c r="CM50" t="str">
         <x:v>VQA 指标不能直接代表可执行动作质量。</x:v>
       </x:c>
-      <x:c r="CN50" t="str"/>
+      <x:c r="CN50"/>
       <x:c r="CO50" t="str">
         <x:v>Medium：问答能力与真机动作成功要分开评测。</x:v>
       </x:c>
@@ -41455,7 +41483,7 @@
         <x:v>Real Robot 字段为 `Yes`；Dataset、Benchmark、Robot Platform 中的 Unknown 继续保留，不从题名推断。</x:v>
       </x:c>
       <x:c r="BE51" t="str">
-        <x:v>Unknown / Needs Full-Paper Verification</x:v>
+        <x:v>作者报告在多项真实任务中解决未见复杂任务；具体成功率见论文。</x:v>
       </x:c>
       <x:c r="BF51" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -41469,7 +41497,7 @@
       <x:c r="BI51" t="str">
         <x:v>B</x:v>
       </x:c>
-      <x:c r="BJ51" t="str"/>
+      <x:c r="BJ51"/>
       <x:c r="BK51" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
@@ -41533,7 +41561,7 @@
       </x:c>
       <x:c r="CF51"/>
       <x:c r="CG51" t="str">
-        <x:v>真实机器人规划要理解语言和视觉中没有明说的约束。</x:v>
+        <x:v>研究问题：真实机器人规划要理解语言和视觉中没有明说的约束。；之前方法的问题：人工写 PDDL 领域规则成本高，面对未见任务又易遗漏条件。；核心思路：UniDomain 从机器人示范中预训练 PDDL domain，再用于零样本任务规划。；主要结果：作者报告在多项真实任务中解决未见复杂任务；具体成功率见论文。；为什么重要：为从示范自动获得可解释规划约束提供方法。；与当前项目的关系：Medium：可帮助双臂任务定义前提与执行检查。；主要局限：推断的规则若不准确，计划可能在真机接触时失败。</x:v>
       </x:c>
       <x:c r="CH51" t="str">
         <x:v>人工写 PDDL 领域规则成本高，面对未见任务又易遗漏条件。</x:v>
@@ -41541,7 +41569,7 @@
       <x:c r="CI51" t="str">
         <x:v>UniDomain 从机器人示范中预训练 PDDL domain，再用于零样本任务规划。</x:v>
       </x:c>
-      <x:c r="CJ51" t="str"/>
+      <x:c r="CJ51"/>
       <x:c r="CK51" t="str">
         <x:v>作者报告在多项真实任务中解决未见复杂任务；具体成功率见论文。</x:v>
       </x:c>
@@ -41551,7 +41579,7 @@
       <x:c r="CM51" t="str">
         <x:v>推断的规则若不准确，计划可能在真机接触时失败。</x:v>
       </x:c>
-      <x:c r="CN51" t="str"/>
+      <x:c r="CN51"/>
       <x:c r="CO51" t="str">
         <x:v>Medium：可帮助双臂任务定义前提与执行检查。</x:v>
       </x:c>
@@ -41752,7 +41780,7 @@
       <x:c r="BI52" t="str">
         <x:v>B</x:v>
       </x:c>
-      <x:c r="BJ52" t="str"/>
+      <x:c r="BJ52"/>
       <x:c r="BK52" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
@@ -41816,7 +41844,7 @@
       </x:c>
       <x:c r="CF52"/>
       <x:c r="CG52" t="str">
-        <x:v>人向灵巧手机器人递交物体时，动态抓取需要兼顾时机和接触稳定性。</x:v>
+        <x:v>研究问题：人向灵巧手机器人递交物体时，动态抓取需要兼顾时机和接触稳定性。；之前方法的问题：高质量真实人机交接数据不足，限制动态灵巧抓取方法评测。；核心思路：DexH2R 建立真实人向机器人交接数据集和评测基准，并给出任务解决方案。；为什么重要：动态交接提供了感知、时序控制与接触安全的共同测试场景。；与当前项目的关系：Medium：时序与交接问题可借鉴，但灵巧手硬件不同于普通夹爪。；主要局限：摘要不足以判定方法对普通夹爪的可迁移性。</x:v>
       </x:c>
       <x:c r="CH52" t="str">
         <x:v>高质量真实人机交接数据不足，限制动态灵巧抓取方法评测。</x:v>
@@ -41824,7 +41852,7 @@
       <x:c r="CI52" t="str">
         <x:v>DexH2R 建立真实人向机器人交接数据集和评测基准，并给出任务解决方案。</x:v>
       </x:c>
-      <x:c r="CJ52" t="str"/>
+      <x:c r="CJ52"/>
       <x:c r="CK52" t="str">
         <x:v>摘要描述数据、方法和评测贡献；本轮未确认可引用的量化性能。</x:v>
       </x:c>
@@ -41834,7 +41862,7 @@
       <x:c r="CM52" t="str">
         <x:v>摘要不足以判定方法对普通夹爪的可迁移性。</x:v>
       </x:c>
-      <x:c r="CN52" t="str"/>
+      <x:c r="CN52"/>
       <x:c r="CO52" t="str">
         <x:v>Medium：时序与交接问题可借鉴，但灵巧手硬件不同于普通夹爪。</x:v>
       </x:c>
@@ -42021,7 +42049,7 @@
         <x:v>Real Robot 字段为 `No`；Dataset、Benchmark、Robot Platform 中的 Unknown 继续保留，不从题名推断。</x:v>
       </x:c>
       <x:c r="BE53" t="str">
-        <x:v>Unknown / Needs Full-Paper Verification</x:v>
+        <x:v>摘要说明生成的接触图可以表达多样双手交互；本轮未核验统一量化结果。</x:v>
       </x:c>
       <x:c r="BF53" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -42035,7 +42063,7 @@
       <x:c r="BI53" t="str">
         <x:v>B</x:v>
       </x:c>
-      <x:c r="BJ53" t="str"/>
+      <x:c r="BJ53"/>
       <x:c r="BK53" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
@@ -42099,7 +42127,7 @@
       </x:c>
       <x:c r="CF53"/>
       <x:c r="CG53" t="str">
-        <x:v>关节物体上的双手接触与运动具有多种合理方式，难以生成。</x:v>
+        <x:v>研究问题：关节物体上的双手接触与运动具有多种合理方式，难以生成。；之前方法的问题：只预测单个抓点不能表达物体关节运动和双手接触关系。；核心思路：BimArt 先根据物体轨迹生成接触距离图，再合成与关节结构一致的三维双手交互。；数据集与评测基准：关节物体双手交互数据；具体对象和指标见论文。；主要结果：摘要说明生成的接触图可以表达多样双手交互；本轮未核验统一量化结果。；为什么重要：为双臂支撑—操作任务提供接触表示参考。；与当前项目的关系：Medium：手部交互可借鉴，转换为普通夹爪动作仍需验证。；主要局限：人手生成结果与真实机械臂碰撞、可达性之间的关系尚需检查。</x:v>
       </x:c>
       <x:c r="CH53" t="str">
         <x:v>只预测单个抓点不能表达物体关节运动和双手接触关系。</x:v>
@@ -42107,7 +42135,7 @@
       <x:c r="CI53" t="str">
         <x:v>BimArt 先根据物体轨迹生成接触距离图，再合成与关节结构一致的三维双手交互。</x:v>
       </x:c>
-      <x:c r="CJ53" t="str"/>
+      <x:c r="CJ53"/>
       <x:c r="CK53" t="str">
         <x:v>摘要说明生成的接触图可以表达多样双手交互；本轮未核验统一量化结果。</x:v>
       </x:c>
@@ -42117,7 +42145,7 @@
       <x:c r="CM53" t="str">
         <x:v>人手生成结果与真实机械臂碰撞、可达性之间的关系尚需检查。</x:v>
       </x:c>
-      <x:c r="CN53" t="str"/>
+      <x:c r="CN53"/>
       <x:c r="CO53" t="str">
         <x:v>Medium：手部交互可借鉴，转换为普通夹爪动作仍需验证。</x:v>
       </x:c>
@@ -42384,7 +42412,7 @@
       </x:c>
       <x:c r="CF54"/>
       <x:c r="CG54" t="str">
-        <x:v>高质量灵巧抓取位姿数据不足，语言与抓取动作难对齐。</x:v>
+        <x:v>研究问题：高质量灵巧抓取位姿数据不足，语言与抓取动作难对齐。；之前方法的问题：大视觉语言模型缺少足够的三维接触监督。；核心思路：DexVLG 结合单视角 RGB-D、点云编码、Florence-2 与 Flow Matching 位姿头，预测语言条件抓取。；数据集与评测基准：LVIS-Seen、LVIS-Unseen、SamPart3D。；为什么重要：连接视觉语言理解与三维抓取位姿生成。；与当前项目的关系：Medium：Grounding 思路可迁移，手型动作头需替换。；主要局限：结果集中于桌面抓取，长任务与普通夹爪双臂迁移未证实。</x:v>
       </x:c>
       <x:c r="CH54" t="str">
         <x:v>大视觉语言模型缺少足够的三维接触监督。</x:v>
@@ -42593,7 +42621,7 @@
         <x:v>Real Robot 字段为 `No`；Dataset、Benchmark、Robot Platform 中的 Unknown 继续保留，不从题名推断。</x:v>
       </x:c>
       <x:c r="BE55" t="str">
-        <x:v>Unknown / Needs Full-Paper Verification</x:v>
+        <x:v>作者报告在未见物体设置的单手与双手数据集上评测；具体指标需查表格。</x:v>
       </x:c>
       <x:c r="BF55" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -42607,7 +42635,7 @@
       <x:c r="BI55" t="str">
         <x:v>B</x:v>
       </x:c>
-      <x:c r="BJ55" t="str"/>
+      <x:c r="BJ55"/>
       <x:c r="BK55" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
@@ -42671,7 +42699,7 @@
       </x:c>
       <x:c r="CF55"/>
       <x:c r="CG55" t="str">
-        <x:v>三维手—物交互生成对训练外新物体的泛化不足。</x:v>
+        <x:v>研究问题：三维手—物交互生成对训练外新物体的泛化不足。；之前方法的问题：只在已见物体分布上建模，难适应未见几何。；核心思路：LatentHOI 学习潜在手—物交互表示，生成未见物体上的单手抓取和双手运动。；主要结果：作者报告在未见物体设置的单手与双手数据集上评测；具体指标需查表格。；为什么重要：为跨物体泛化提供交互表示视角。；与当前项目的关系：Medium：双臂普通夹爪可借鉴物体中心表示。；主要局限：生成的人手运动还需转成机器人可达动作。</x:v>
       </x:c>
       <x:c r="CH55" t="str">
         <x:v>只在已见物体分布上建模，难适应未见几何。</x:v>
@@ -42679,7 +42707,7 @@
       <x:c r="CI55" t="str">
         <x:v>LatentHOI 学习潜在手—物交互表示，生成未见物体上的单手抓取和双手运动。</x:v>
       </x:c>
-      <x:c r="CJ55" t="str"/>
+      <x:c r="CJ55"/>
       <x:c r="CK55" t="str">
         <x:v>作者报告在未见物体设置的单手与双手数据集上评测；具体指标需查表格。</x:v>
       </x:c>
@@ -42689,7 +42717,7 @@
       <x:c r="CM55" t="str">
         <x:v>生成的人手运动还需转成机器人可达动作。</x:v>
       </x:c>
-      <x:c r="CN55" t="str"/>
+      <x:c r="CN55"/>
       <x:c r="CO55" t="str">
         <x:v>Medium：双臂普通夹爪可借鉴物体中心表示。</x:v>
       </x:c>
@@ -42876,7 +42904,7 @@
         <x:v>Real Robot 字段为 `No`；Dataset、Benchmark、Robot Platform 中的 Unknown 继续保留，不从题名推断。</x:v>
       </x:c>
       <x:c r="BE56" t="str">
-        <x:v>Unknown / Needs Full-Paper Verification</x:v>
+        <x:v>CVPR 官方论文评测组合动作识别、手—物运动预测与协同抓取生成；摘要未给统一成功率。</x:v>
       </x:c>
       <x:c r="BF56" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -42890,7 +42918,7 @@
       <x:c r="BI56" t="str">
         <x:v>B</x:v>
       </x:c>
-      <x:c r="BJ56" t="str"/>
+      <x:c r="BJ56"/>
       <x:c r="BK56" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
@@ -42954,7 +42982,7 @@
       </x:c>
       <x:c r="CF56"/>
       <x:c r="CG56" t="str">
-        <x:v>双手工具—动作—物体理解缺少足够多样且标注完整的数据。</x:v>
+        <x:v>研究问题：双手工具—动作—物体理解缺少足够多样且标注完整的数据。；之前方法的问题：已有手—物交互数据多集中在单手、单物体场景。；核心思路：TACO 提供约 2500 条双手交互序列、第三人称与第一人称视角、三维网格和动作标签。；输入：官方摘要给出任务/数据类型；具体模型张量与接口需核对方法章节。；输出与动作：官方摘要未明确列出完整控制接口；需核对论文方法或代码。；数据集与评测基准：TACO：约 2500 条序列及三个基准任务。；主要结果：CVPR 官方论文评测组合动作识别、手—物运动预测与协同抓取生成；摘要未给统一成功率。；为什么重要：可用于理解双手协同与工具功能，但人手动作迁移到普通夹爪需验证。；与当前项目的关系：Medium：方法可借鉴，但迁移到当前双臂硬件需验证。；主要局限：本段基于官方摘要；未覆盖全文失败案例、完整 Baseline 与方法消融。</x:v>
       </x:c>
       <x:c r="CH56" t="str">
         <x:v>已有手—物交互数据多集中在单手、单物体场景。</x:v>
@@ -42962,7 +42990,7 @@
       <x:c r="CI56" t="str">
         <x:v>TACO 提供约 2500 条双手交互序列、第三人称与第一人称视角、三维网格和动作标签。</x:v>
       </x:c>
-      <x:c r="CJ56" t="str"/>
+      <x:c r="CJ56"/>
       <x:c r="CK56" t="str">
         <x:v>CVPR 官方论文评测组合动作识别、手—物运动预测与协同抓取生成；摘要未给统一成功率。</x:v>
       </x:c>
@@ -42972,7 +43000,7 @@
       <x:c r="CM56" t="str">
         <x:v>本段基于官方摘要；未覆盖全文失败案例、完整 Baseline 与方法消融。</x:v>
       </x:c>
-      <x:c r="CN56" t="str"/>
+      <x:c r="CN56"/>
       <x:c r="CO56" t="str">
         <x:v>Medium：方法可借鉴，但迁移到当前双臂硬件需验证。</x:v>
       </x:c>
@@ -43159,7 +43187,7 @@
         <x:v>Real Robot 字段为 `Unknown`；Dataset、Benchmark、Robot Platform 中的 Unknown 继续保留，不从题名推断。</x:v>
       </x:c>
       <x:c r="BE57" t="str">
-        <x:v>Unknown / Needs Full-Paper Verification</x:v>
+        <x:v>已核验摘要未给出可安全复述的统一量化结果。</x:v>
       </x:c>
       <x:c r="BF57" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -43173,7 +43201,7 @@
       <x:c r="BI57" t="str">
         <x:v>B</x:v>
       </x:c>
-      <x:c r="BJ57" t="str"/>
+      <x:c r="BJ57"/>
       <x:c r="BK57" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
@@ -43237,7 +43265,7 @@
       </x:c>
       <x:c r="CF57"/>
       <x:c r="CG57" t="str">
-        <x:v>移动操作既要行走/移动，又要持续感知并及时控制机械臂。</x:v>
+        <x:v>研究问题：移动操作既要行走/移动，又要持续感知并及时控制机械臂。；之前方法的问题：静态感知或开环策略难以应对移动过程中变化的场景。；核心思路：SPIN 使用主动视觉系统建立反应式移动操作框架，让机器人持续观察环境并调整执行。；数据集与评测基准：移动操作任务；具体平台、数据集和评测协议需查原论文。；主要结果：已核验摘要未给出可安全复述的统一量化结果。；为什么重要：提醒长时序真机任务必须将主动感知与动作闭环结合。；与当前项目的关系：Medium：反应式感知思路相关，但移动平台与本项目固定双臂设置不同。；主要局限：摘要没有明确列出失败案例；需进一步核对实验与限制。</x:v>
       </x:c>
       <x:c r="CH57" t="str">
         <x:v>静态感知或开环策略难以应对移动过程中变化的场景。</x:v>
@@ -43245,7 +43273,7 @@
       <x:c r="CI57" t="str">
         <x:v>SPIN 使用主动视觉系统建立反应式移动操作框架，让机器人持续观察环境并调整执行。</x:v>
       </x:c>
-      <x:c r="CJ57" t="str"/>
+      <x:c r="CJ57"/>
       <x:c r="CK57" t="str">
         <x:v>已核验摘要未给出可安全复述的统一量化结果。</x:v>
       </x:c>
@@ -43255,7 +43283,7 @@
       <x:c r="CM57" t="str">
         <x:v>摘要没有明确列出失败案例；需进一步核对实验与限制。</x:v>
       </x:c>
-      <x:c r="CN57" t="str"/>
+      <x:c r="CN57"/>
       <x:c r="CO57" t="str">
         <x:v>Medium：反应式感知思路相关，但移动平台与本项目固定双臂设置不同。</x:v>
       </x:c>
@@ -43522,7 +43550,7 @@
       </x:c>
       <x:c r="CF58"/>
       <x:c r="CG58" t="str">
-        <x:v>语言条件双臂操作的示范成本高，动作空间也更复杂。</x:v>
+        <x:v>研究问题：语言条件双臂操作的示范成本高，动作空间也更复杂。；之前方法的问题：从单臂策略直接迁移到双臂时，两臂观测和动作不一定对齐。；核心思路：用技能管理器安排双臂子技能，并以体素/视觉对齐模块协调两臂输入，使预训练单臂策略可复用。；数据集与评测基准：12 项仿真任务和 9 项真机任务。；为什么重要：提供节约双臂数据成本的一条可测试路线。；与当前项目的关系：High：直接针对从单臂到普通夹爪双臂任务的迁移。；主要局限：仍依赖少量双臂示范，且假设单臂预训练表示可以复用。</x:v>
       </x:c>
       <x:c r="CH58" t="str">
         <x:v>从单臂策略直接迁移到双臂时，两臂观测和动作不一定对齐。</x:v>
@@ -43811,7 +43839,7 @@
       </x:c>
       <x:c r="CF59"/>
       <x:c r="CG59" t="str">
-        <x:v>通用灵巧操作受昂贵遥操作数据、不同手型和高维动作影响。</x:v>
+        <x:v>研究问题：通用灵巧操作受昂贵遥操作数据、不同手型和高维动作影响。；之前方法的问题：人类视频中的动作不能直接变成各机器人手的控制命令。；核心思路：UniDex 结合人类视频、人工参与的动作重定向和三维点云，形成机器人中心的训练轨迹。；为什么重要：展示如何把人类视频与机器人可执行轨迹连接起来。；与当前项目的关系：Medium：采集与重定向思路相关，但普通夹爪动作空间不同。；主要局限：跨手型与零样本表现需按任务和平台逐项核验。</x:v>
       </x:c>
       <x:c r="CH59" t="str">
         <x:v>人类视频中的动作不能直接变成各机器人手的控制命令。</x:v>
@@ -44020,7 +44048,7 @@
         <x:v>Real Robot 字段为 `Unknown`；Dataset、Benchmark、Robot Platform 中的 Unknown 继续保留，不从题名推断。</x:v>
       </x:c>
       <x:c r="BE60" t="str">
-        <x:v>Unknown / Needs Full-Paper Verification</x:v>
+        <x:v>作者报告数据与姿态细化带来生成质量提升；具体指标见论文。</x:v>
       </x:c>
       <x:c r="BF60" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -44034,7 +44062,7 @@
       <x:c r="BI60" t="str">
         <x:v>B</x:v>
       </x:c>
-      <x:c r="BJ60" t="str"/>
+      <x:c r="BJ60"/>
       <x:c r="BK60" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
@@ -44098,7 +44126,7 @@
       </x:c>
       <x:c r="CF60"/>
       <x:c r="CG60" t="str">
-        <x:v>任务导向的人手—物体视频生成缺少足够数据和精准姿态。</x:v>
+        <x:v>研究问题：任务导向的人手—物体视频生成缺少足够数据和精准姿态。；之前方法的问题：普通生成视频不一定保留与机器人操作有关的接触和动作结构。；核心思路：TASTE-Rob 建立约 100,856 条第一人称手—物交互数据，并加入姿态细化以生成任务相关视频。；主要结果：作者报告数据与姿态细化带来生成质量提升；具体指标见论文。；为什么重要：可作为从人类视频提取操作结构的数据来源。；与当前项目的关系：Medium：人手动作转双普通夹爪仍需重定向。；主要局限：视频生成质量不能直接代表真机操作成功。</x:v>
       </x:c>
       <x:c r="CH60" t="str">
         <x:v>普通生成视频不一定保留与机器人操作有关的接触和动作结构。</x:v>
@@ -44106,7 +44134,7 @@
       <x:c r="CI60" t="str">
         <x:v>TASTE-Rob 建立约 100,856 条第一人称手—物交互数据，并加入姿态细化以生成任务相关视频。</x:v>
       </x:c>
-      <x:c r="CJ60" t="str"/>
+      <x:c r="CJ60"/>
       <x:c r="CK60" t="str">
         <x:v>作者报告数据与姿态细化带来生成质量提升；具体指标见论文。</x:v>
       </x:c>
@@ -44116,7 +44144,7 @@
       <x:c r="CM60" t="str">
         <x:v>视频生成质量不能直接代表真机操作成功。</x:v>
       </x:c>
-      <x:c r="CN60" t="str"/>
+      <x:c r="CN60"/>
       <x:c r="CO60" t="str">
         <x:v>Medium：人手动作转双普通夹爪仍需重定向。</x:v>
       </x:c>
@@ -44303,7 +44331,7 @@
         <x:v>Real Robot 字段为 `Unknown`；Dataset、Benchmark、Robot Platform 中的 Unknown 继续保留，不从题名推断。</x:v>
       </x:c>
       <x:c r="BE61" t="str">
-        <x:v>Unknown / Needs Full-Paper Verification</x:v>
+        <x:v>作者报告生成的动作更平滑且语义正确；未核验统一数值。</x:v>
       </x:c>
       <x:c r="BF61" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -44317,7 +44345,7 @@
       <x:c r="BI61" t="str">
         <x:v>B</x:v>
       </x:c>
-      <x:c r="BJ61" t="str"/>
+      <x:c r="BJ61"/>
       <x:c r="BK61" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
@@ -44381,7 +44409,7 @@
       </x:c>
       <x:c r="CF61"/>
       <x:c r="CG61" t="str">
-        <x:v>多指机器人手的数据采集昂贵，跨手型迁移难。</x:v>
+        <x:v>研究问题：多指机器人手的数据采集昂贵，跨手型迁移难。；之前方法的问题：运动学与动力学差异使直接重定向的动作不平滑或不可执行。；核心思路：逐步对齐运动学和动力学，再把操作行为迁移到目标灵巧手；模块细节仍需查官方正文。；主要结果：作者报告生成的动作更平滑且语义正确；未核验统一数值。；为什么重要：提示本项目从单臂模型迁移双臂时也要检查物理可执行性。；与当前项目的关系：Medium：对齐思想可借鉴，目标硬件不同。；主要局限：原卡方法细节尚有占位，不能据此宣称已复现。</x:v>
       </x:c>
       <x:c r="CH61" t="str">
         <x:v>运动学与动力学差异使直接重定向的动作不平滑或不可执行。</x:v>
@@ -44389,7 +44417,7 @@
       <x:c r="CI61" t="str">
         <x:v>逐步对齐运动学和动力学，再把操作行为迁移到目标灵巧手；模块细节仍需查官方正文。</x:v>
       </x:c>
-      <x:c r="CJ61" t="str"/>
+      <x:c r="CJ61"/>
       <x:c r="CK61" t="str">
         <x:v>作者报告生成的动作更平滑且语义正确；未核验统一数值。</x:v>
       </x:c>
@@ -44399,7 +44427,7 @@
       <x:c r="CM61" t="str">
         <x:v>原卡方法细节尚有占位，不能据此宣称已复现。</x:v>
       </x:c>
-      <x:c r="CN61" t="str"/>
+      <x:c r="CN61"/>
       <x:c r="CO61" t="str">
         <x:v>Medium：对齐思想可借鉴，目标硬件不同。</x:v>
       </x:c>
@@ -44586,7 +44614,7 @@
         <x:v>Real Robot 字段为 `No`；Dataset、Benchmark、Robot Platform 中的 Unknown 继续保留，不从题名推断。</x:v>
       </x:c>
       <x:c r="BE62" t="str">
-        <x:v>Unknown / Needs Full-Paper Verification</x:v>
+        <x:v>摘要报告 2D 与 3D 扩散策略表现会随生成数据增加而提升；未核验统一成功率。</x:v>
       </x:c>
       <x:c r="BF62" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -44600,7 +44628,7 @@
       <x:c r="BI62" t="str">
         <x:v>B</x:v>
       </x:c>
-      <x:c r="BJ62" t="str"/>
+      <x:c r="BJ62"/>
       <x:c r="BK62" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
@@ -44664,7 +44692,7 @@
       </x:c>
       <x:c r="CF62"/>
       <x:c r="CG62" t="str">
-        <x:v>许多机器人操作数据和仿真 benchmark 偏机械臂，缺少人形机器人操作数据。</x:v>
+        <x:v>研究问题：许多机器人操作数据和仿真 benchmark 偏机械臂，缺少人形机器人操作数据。；之前方法的问题：数据本体分布不足会限制策略对人形平台的适配。；核心思路：HumanoidGen 扩展人形机器人操作数据，用生成数据训练和评估 2D/3D Diffusion Policy。；数据集与评测基准：生成的人形操作数据；具体任务与数据规模见论文。；主要结果：摘要报告 2D 与 3D 扩散策略表现会随生成数据增加而提升；未核验统一成功率。；为什么重要：提醒跨本体数据设计比单纯增加示范数量更重要。；与当前项目的关系：Medium：本项目不是人形手，但双臂数据覆盖问题相通。；主要局限：仿真生成数据到普通夹爪真机的迁移需另行验证。</x:v>
       </x:c>
       <x:c r="CH62" t="str">
         <x:v>数据本体分布不足会限制策略对人形平台的适配。</x:v>
@@ -44672,7 +44700,7 @@
       <x:c r="CI62" t="str">
         <x:v>HumanoidGen 扩展人形机器人操作数据，用生成数据训练和评估 2D/3D Diffusion Policy。</x:v>
       </x:c>
-      <x:c r="CJ62" t="str"/>
+      <x:c r="CJ62"/>
       <x:c r="CK62" t="str">
         <x:v>摘要报告 2D 与 3D 扩散策略表现会随生成数据增加而提升；未核验统一成功率。</x:v>
       </x:c>
@@ -44682,7 +44710,7 @@
       <x:c r="CM62" t="str">
         <x:v>仿真生成数据到普通夹爪真机的迁移需另行验证。</x:v>
       </x:c>
-      <x:c r="CN62" t="str"/>
+      <x:c r="CN62"/>
       <x:c r="CO62" t="str">
         <x:v>Medium：本项目不是人形手，但双臂数据覆盖问题相通。</x:v>
       </x:c>
@@ -44869,7 +44897,7 @@
         <x:v>Real Robot 字段为 `Unknown`；Dataset、Benchmark、Robot Platform 中的 Unknown 继续保留，不从题名推断。</x:v>
       </x:c>
       <x:c r="BE63" t="str">
-        <x:v>Unknown / Needs Full-Paper Verification</x:v>
+        <x:v>作者报告在已见物体、未见实例和未见类别上优于基线；统一数字未核验。</x:v>
       </x:c>
       <x:c r="BF63" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -44883,7 +44911,7 @@
       <x:c r="BI63" t="str">
         <x:v>B</x:v>
       </x:c>
-      <x:c r="BJ63" t="str"/>
+      <x:c r="BJ63"/>
       <x:c r="BK63" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
@@ -44947,7 +44975,7 @@
       </x:c>
       <x:c r="CF63"/>
       <x:c r="CG63" t="str">
-        <x:v>灵巧手要在未见物体上抓取，还需要理解物体可供性。</x:v>
+        <x:v>研究问题：灵巧手要在未见物体上抓取，还需要理解物体可供性。；之前方法的问题：只利用几何抓取先验可能忽略人类使用物体的方式。；核心思路：AffordDex 引入人类式先验与 affordance，学习可泛化的灵巧抓取。具体模块需核对正文。；主要结果：作者报告在已见物体、未见实例和未见类别上优于基线；统一数字未核验。；为什么重要：强调抓取的用途和接触位置比单纯抓住更重要。；与当前项目的关系：Medium：普通夹爪也需任务相关抓取，但手型不同。；主要局限：原卡方法细节尚有占位；真实双臂夹爪转移需验证。</x:v>
       </x:c>
       <x:c r="CH63" t="str">
         <x:v>只利用几何抓取先验可能忽略人类使用物体的方式。</x:v>
@@ -44955,7 +44983,7 @@
       <x:c r="CI63" t="str">
         <x:v>AffordDex 引入人类式先验与 affordance，学习可泛化的灵巧抓取。具体模块需核对正文。</x:v>
       </x:c>
-      <x:c r="CJ63" t="str"/>
+      <x:c r="CJ63"/>
       <x:c r="CK63" t="str">
         <x:v>作者报告在已见物体、未见实例和未见类别上优于基线；统一数字未核验。</x:v>
       </x:c>
@@ -44965,7 +44993,7 @@
       <x:c r="CM63" t="str">
         <x:v>原卡方法细节尚有占位；真实双臂夹爪转移需验证。</x:v>
       </x:c>
-      <x:c r="CN63" t="str"/>
+      <x:c r="CN63"/>
       <x:c r="CO63" t="str">
         <x:v>Medium：普通夹爪也需任务相关抓取，但手型不同。</x:v>
       </x:c>
@@ -45166,7 +45194,7 @@
       <x:c r="BI64" t="str">
         <x:v>B</x:v>
       </x:c>
-      <x:c r="BJ64" t="str"/>
+      <x:c r="BJ64"/>
       <x:c r="BK64" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
@@ -45230,7 +45258,7 @@
       </x:c>
       <x:c r="CF64"/>
       <x:c r="CG64" t="str">
-        <x:v>从人类示范学习多样双手灵巧技能具有本体差异和数据成本。</x:v>
+        <x:v>研究问题：从人类示范学习多样双手灵巧技能具有本体差异和数据成本。；之前方法的问题：只模仿固定动作难以覆盖未见物体与协同方式。；核心思路：BiDexHD 从人类双手示范提取可迁移技能并学习双手灵巧操作。具体模块需回正文核验。；数据集与评测基准：ARCTIC 协同任务与论文训练任务。；为什么重要：说明人类双手数据可为双臂策略提供技能先验。；与当前项目的关系：Medium：灵巧手与普通夹爪之间的动作转译需研究。；主要局限：原卡方法细节尚有占位，需核对官方论文与失败案例。</x:v>
       </x:c>
       <x:c r="CH64" t="str">
         <x:v>只模仿固定动作难以覆盖未见物体与协同方式。</x:v>
@@ -45238,7 +45266,7 @@
       <x:c r="CI64" t="str">
         <x:v>BiDexHD 从人类双手示范提取可迁移技能并学习双手灵巧操作。具体模块需回正文核验。</x:v>
       </x:c>
-      <x:c r="CJ64" t="str"/>
+      <x:c r="CJ64"/>
       <x:c r="CK64" t="str">
         <x:v>卡片记录迁移到 11 项 ARCTIC 任务：已训练任务平均完成率 80.49%，未见任务 65.99%。</x:v>
       </x:c>
@@ -45248,7 +45276,7 @@
       <x:c r="CM64" t="str">
         <x:v>原卡方法细节尚有占位，需核对官方论文与失败案例。</x:v>
       </x:c>
-      <x:c r="CN64" t="str"/>
+      <x:c r="CN64"/>
       <x:c r="CO64" t="str">
         <x:v>Medium：灵巧手与普通夹爪之间的动作转译需研究。</x:v>
       </x:c>
@@ -45435,7 +45463,7 @@
         <x:v>Real Robot 字段为 `No`；Dataset、Benchmark、Robot Platform 中的 Unknown 继续保留，不从题名推断。</x:v>
       </x:c>
       <x:c r="BE65" t="str">
-        <x:v>Unknown / Needs Full-Paper Verification</x:v>
+        <x:v>作者摘要报告优于所比较的位姿预测方法；未核验统一数字。</x:v>
       </x:c>
       <x:c r="BF65" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -45449,7 +45477,7 @@
       <x:c r="BI65" t="str">
         <x:v>B</x:v>
       </x:c>
-      <x:c r="BJ65" t="str"/>
+      <x:c r="BJ65"/>
       <x:c r="BK65" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
@@ -45513,7 +45541,7 @@
       </x:c>
       <x:c r="CF65"/>
       <x:c r="CG65" t="str">
-        <x:v>只观察单手交互时，预测完整双手物体操作序列并不容易。</x:v>
+        <x:v>研究问题：只观察单手交互时，预测完整双手物体操作序列并不容易。；之前方法的问题：单手观测没有直接提供另一只手的未来接触与运动。；核心思路：从单手观测推断物体与双手的后续运动，形成双手操作序列预测。；数据集与评测基准：论文的双手操作序列数据集；具体设置需核对官方正文。；主要结果：作者摘要报告优于所比较的位姿预测方法；未核验统一数字。；为什么重要：为从单手数据推断双臂任务结构提供可能的监督信号。；与当前项目的关系：Medium：人体动作到普通夹爪仍有本体差异。；主要局限：卡片原先的方法细节占位，需回官方论文核对预测结构与失败案例。</x:v>
       </x:c>
       <x:c r="CH65" t="str">
         <x:v>单手观测没有直接提供另一只手的未来接触与运动。</x:v>
@@ -45521,7 +45549,7 @@
       <x:c r="CI65" t="str">
         <x:v>从单手观测推断物体与双手的后续运动，形成双手操作序列预测。</x:v>
       </x:c>
-      <x:c r="CJ65" t="str"/>
+      <x:c r="CJ65"/>
       <x:c r="CK65" t="str">
         <x:v>作者摘要报告优于所比较的位姿预测方法；未核验统一数字。</x:v>
       </x:c>
@@ -45531,7 +45559,7 @@
       <x:c r="CM65" t="str">
         <x:v>卡片原先的方法细节占位，需回官方论文核对预测结构与失败案例。</x:v>
       </x:c>
-      <x:c r="CN65" t="str"/>
+      <x:c r="CN65"/>
       <x:c r="CO65" t="str">
         <x:v>Medium：人体动作到普通夹爪仍有本体差异。</x:v>
       </x:c>
@@ -45718,7 +45746,7 @@
         <x:v>Real Robot 字段为 `Yes`；Dataset、Benchmark、Robot Platform 中的 Unknown 继续保留，不从题名推断。</x:v>
       </x:c>
       <x:c r="BE66" t="str">
-        <x:v>Unknown / Needs Full-Paper Verification</x:v>
+        <x:v>已访问的官方 PDF 支持方法与评测设置；快速摘要暂不填入未重新提取的数值。</x:v>
       </x:c>
       <x:c r="BF66" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -45798,7 +45826,7 @@
       </x:c>
       <x:c r="CF66"/>
       <x:c r="CG66" t="str">
-        <x:v>人类视频包含丰富双手交互，但普通 affordance 标签难指出左右手各自可操作的区域。</x:v>
+        <x:v>研究问题：人类视频包含丰富双手交互，但普通 affordance 标签难指出左右手各自可操作的区域。；之前方法的问题：只标记物体可抓取，不足以指导双手分工和具体接触位置。；核心思路：用 VLM 产生分割提示，再由左右手 mask 解码器预测可执行区域，并分类单手或双手交互。；数据集与评测基准：ActAffordance 等双手 affordance 评测；具体分数见官方 PDF。；主要结果：已访问的官方 PDF 支持方法与评测设置；快速摘要暂不填入未重新提取的数值。；为什么重要：直接关系到普通夹爪在同一物体上的双臂接触分工。；与当前项目的关系：High：可用于双臂 joint affordance 和动作前检查。；主要局限：精确数值与失败图例仍需对照论文图表；人手区域到普通夹爪的迁移需验证。</x:v>
       </x:c>
       <x:c r="CH66" t="str">
         <x:v>只标记物体可抓取，不足以指导双手分工和具体接触位置。</x:v>
@@ -46087,7 +46115,7 @@
       </x:c>
       <x:c r="CF67"/>
       <x:c r="CG67" t="str">
-        <x:v>VLA 的视觉注意可能落在任务无关区域，削弱精细操作与泛化。</x:v>
+        <x:v>研究问题：VLA 的视觉注意可能落在任务无关区域，削弱精细操作与泛化。；之前方法的问题：原有 VLA 难以稳定把视觉注意对准目标区域；显式标注 Grounding 的方案又可能增加数据要求。；核心思路：ReconVLA 用扩散式重建目标注视区域，促使视觉表示聚焦被操作物体，同时保留动作预测。；输入：RGB 图像历史和语言指令；重建注视区域作为中间视觉目标（Sec. 3、Fig. 2）。；为什么重要：直接对应本项目的目标 Grounding 与动作前目标核验。；与当前项目的关系：High：有助于研究语言条件操作与 VLA 设计。；主要局限：作者指出性能取决于目标区域重建是否正确；公开评测主要集中在 CALVIN 与有限真机任务。跨本体和新相机条件仍需验证。</x:v>
       </x:c>
       <x:c r="CH67" t="str">
         <x:v>原有 VLA 难以稳定把视觉注意对准目标区域；显式标注 Grounding 的方案又可能增加数据要求。</x:v>
@@ -46161,7 +46189,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd374438b095542f0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf15a453f46d547bb"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -46609,7 +46637,7 @@
         <x:v>The official project reports six robot manipulation tasks spanning single-arm, dual-arm, hand-over, pouring, basket pick-and-place and pan opening/placement settings, with domain-gap conditions.</x:v>
       </x:c>
       <x:c r="AU2" t="str">
-        <x:v>The project reports the best success-rate and step-count performance across its six-task comparison; exact full-paper tables remain unextracted.</x:v>
+        <x:v>作者项目页报告多种真实操作任务的零样本迁移；完整数值和硬件条件仍需正文核验。</x:v>
       </x:c>
       <x:c r="AV2" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -46686,7 +46714,7 @@
       </x:c>
       <x:c r="BU2"/>
       <x:c r="BV2" t="str">
-        <x:v>纯合成数据训练的 VLA 在真实场景中容易受到外观和动力学差异影响。</x:v>
+        <x:v>研究问题：纯合成数据训练的 VLA 在真实场景中容易受到外观和动力学差异影响。；之前方法的问题：仿真里学到的操作技能并不自动具备真机零样本泛化。；核心思路：Sim2Real-VLA 只用合成数据训练通用控制模型，并研究仿真技能迁移到真实操作。；输入：官方摘要给出任务/数据类型；具体模型张量与接口需核对方法章节。；输出与动作：官方摘要未明确列出完整控制接口；需核对论文方法或代码。；数据集与评测基准：合成操作轨迹与真实机器人评测；具体任务见项目页。；主要结果：作者项目页报告多种真实操作任务的零样本迁移；完整数值和硬件条件仍需正文核验。；为什么重要：直接对应双臂 Sim2Real 与合成/真实数据配比问题。；与当前项目的关系：High：直接关联双臂普通夹爪、VLA 或真机操作。；主要局限：本段基于官方摘要；未覆盖全文失败案例、完整 Baseline 与方法消融。</x:v>
       </x:c>
       <x:c r="BW2" t="str">
         <x:v>仿真里学到的操作技能并不自动具备真机零样本泛化。</x:v>
@@ -46865,7 +46893,7 @@
         <x:v>Official abstract reports five long-hori</x:v>
       </x:c>
       <x:c r="AU3" t="str">
-        <x:v>Unknown / Needs Full-Paper Verification</x:v>
+        <x:v>作者报告可模仿五项双臂任务，并对视觉和空间变化有一定泛化；具体数值需看原文。</x:v>
       </x:c>
       <x:c r="AV3" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -46940,7 +46968,7 @@
       </x:c>
       <x:c r="BU3"/>
       <x:c r="BV3" t="str">
-        <x:v>低成本示范条件下，如何学会协调的双臂技能。</x:v>
+        <x:v>研究问题：低成本示范条件下，如何学会协调的双臂技能。；之前方法的问题：一段人类视频不能直接提供机器人两臂的连续可执行动作。；核心思路：把单段人类视频转换为结构化关键帧轨迹，并扩展成机器人示范。；数据集与评测基准：论文评估五项复杂的长时序双臂任务。；主要结果：作者报告可模仿五项双臂任务，并对视觉和空间变化有一定泛化；具体数值需看原文。；为什么重要：可帮助研究 Human Video → Robot Action 的数据成本。；与当前项目的关系：High：与双臂普通夹爪和低示范预算直接相关。；主要局限：人类视频关键帧到真机连续控制仍需验证可达性与接触安全。</x:v>
       </x:c>
       <x:c r="BW3" t="str">
         <x:v>一段人类视频不能直接提供机器人两臂的连续可执行动作。</x:v>
@@ -47190,7 +47218,7 @@
       </x:c>
       <x:c r="BU4"/>
       <x:c r="BV4" t="str">
-        <x:v>双臂策略要兼顾目标的空间定位和连续轨迹的灵活性。</x:v>
+        <x:v>研究问题：双臂策略要兼顾目标的空间定位和连续轨迹的灵活性。；之前方法的问题：单独使用离散空间提示或连续动作预测，可能难同时实现定位与平滑控制。；核心思路：PPI 用空间接口引导连续双臂动作生成。；数据集与评测基准：仿真与真机双臂任务；完整 benchmark 见论文。；为什么重要：适合比较空间表示如何约束普通夹爪的双臂动作。；与当前项目的关系：High：直接对应双臂空间接口和连续动作。；主要局限：需进一步核验任务分布、失败类型和动作频率。</x:v>
       </x:c>
       <x:c r="BW4" t="str">
         <x:v>单独使用离散空间提示或连续动作预测，可能难同时实现定位与平滑控制。</x:v>
@@ -47440,7 +47468,7 @@
       </x:c>
       <x:c r="BU5"/>
       <x:c r="BV5" t="str">
-        <x:v>灵巧机器人学习缺少可携带、细节完整的人手示范。</x:v>
+        <x:v>研究问题：灵巧机器人学习缺少可携带、细节完整的人手示范。；之前方法的问题：只记录视频，难准确捕捉手腕、手指和环境的三维关系。；核心思路：DexCap 同步采集手腕与手指运动以及环境三维观测，形成可迁移的人手操作数据。；为什么重要：提醒示范采集装置决定后续策略能学到什么。；与当前项目的关系：Medium：普通夹爪不需手指细节，但腕部和环境标定有用。；主要局限：人手示范迁移到普通夹爪仍需动作重定向。</x:v>
       </x:c>
       <x:c r="BW5" t="str">
         <x:v>只记录视频，难准确捕捉手腕、手指和环境的三维关系。</x:v>
@@ -47615,7 +47643,7 @@
         <x:v>20 tasks, 14 perturbation axes and real-world correlation are stated in the official abstract.</x:v>
       </x:c>
       <x:c r="AU6" t="str">
-        <x:v>Unknown / Needs Full-Paper Verification</x:v>
+        <x:v>官方摘要报告，仿真扰动结果与相似真实扰动实验存在相关性，调整后的 R² = 0.614。</x:v>
       </x:c>
       <x:c r="AV6" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -47690,7 +47718,7 @@
       </x:c>
       <x:c r="BU6"/>
       <x:c r="BV6" t="str">
-        <x:v>操作策略若只在接近训练条件的环境中评测，难以判断其鲁棒性。</x:v>
+        <x:v>研究问题：操作策略若只在接近训练条件的环境中评测，难以判断其鲁棒性。；核心思路：THE COLOSSEUM 通过受控环境扰动对策略进行压力测试。；数据集与评测基准：THE COLOSSEUM 基准；具体扰动维度和策略清单需核对正文。；主要结果：官方摘要报告，仿真扰动结果与相似真实扰动实验存在相关性，调整后的 R² = 0.614。；为什么重要：可帮助设计跨光照、外观和几何变化的泛化评测。；与当前项目的关系：Medium：适合构建本项目的分布外评测，但需匹配实际传感器和夹爪。；主要局限：相关性并不意味着单个策略的真实成功率可由仿真精确预测。</x:v>
       </x:c>
       <x:c r="BW6" t="str">
         <x:v>已核验摘要未明确说明；需查阅论文方法与实验章节。</x:v>
@@ -47865,7 +47893,7 @@
         <x:v>Official paper/project materials include bimanual hardware planning examples.</x:v>
       </x:c>
       <x:c r="AU7" t="str">
-        <x:v>Unknown / Needs Full-Paper Verification</x:v>
+        <x:v>已核验摘要未提供可安全复述的统一量化结果。</x:v>
       </x:c>
       <x:c r="AV7" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -47940,7 +47968,7 @@
       </x:c>
       <x:c r="BU7"/>
       <x:c r="BV7" t="str">
-        <x:v>双臂共同操作时，两只末端之间常需保持固定相对位姿。</x:v>
+        <x:v>研究问题：双臂共同操作时，两只末端之间常需保持固定相对位姿。；之前方法的问题：这种等式约束使普通规划器难以高效搜索可行动作。；核心思路：直接在满足双臂相对位姿约束的运动流形上搜索轨迹。；数据集与评测基准：约束双臂规划场景；具体 benchmark 需核对正文。；主要结果：已核验摘要未提供可安全复述的统一量化结果。；为什么重要：为普通夹爪共同搬运物体提供几何约束基线。；与当前项目的关系：High：双臂同步和共同约束是本项目基础问题。；主要局限：需评估模型化固定相对位姿与真实滑动、形变之间的差异。</x:v>
       </x:c>
       <x:c r="BW7" t="str">
         <x:v>这种等式约束使普通规划器难以高效搜索可行动作。</x:v>
@@ -48190,7 +48218,7 @@
       </x:c>
       <x:c r="BU8"/>
       <x:c r="BV8" t="str">
-        <x:v>接触密集操作既要视觉定位，也要复现合适接触力。</x:v>
+        <x:v>研究问题：接触密集操作既要视觉定位，也要复现合适接触力。；之前方法的问题：只看图像的模仿策略可能忽略力反馈和感知模式切换。；核心思路：在示范适配与策略执行中使用透视式触觉反馈，并加入力匹配和视觉—触觉模式切换。；为什么重要：提示普通夹爪接触任务可能需要力信号而不只是相机。；与当前项目的关系：High：双臂共同接触物体时，夹持力和滑动风险关键。；主要局限：需检查本项目硬件是否具备相应触觉/力传感。</x:v>
       </x:c>
       <x:c r="BW8" t="str">
         <x:v>只看图像的模仿策略可能忽略力反馈和感知模式切换。</x:v>
@@ -48365,7 +48393,7 @@
         <x:v>Experiments with multiple arms in a shared workspace are reported.</x:v>
       </x:c>
       <x:c r="AU9" t="str">
-        <x:v>Unknown / Needs Full-Paper Verification</x:v>
+        <x:v>已核验摘要未给可安全复述的统一量化结果。</x:v>
       </x:c>
       <x:c r="AV9" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -48440,7 +48468,7 @@
       </x:c>
       <x:c r="BU9"/>
       <x:c r="BV9" t="str">
-        <x:v>多只机械臂共享工作空间时，需要在线修改轨迹并避免碰撞。</x:v>
+        <x:v>研究问题：多只机械臂共享工作空间时，需要在线修改轨迹并避免碰撞。；之前方法的问题：离线示范轨迹不能保证在动态变化下仍安全可行。；核心思路：对示范轨迹做在线调制，并在共享空间中协调多臂运动。；主要结果：已核验摘要未给可安全复述的统一量化结果。；为什么重要：为双臂策略外部增加安全协调层提供参照。；与当前项目的关系：High：普通夹爪双臂真机必须处理共享空间碰撞。；主要局限：需验证在线修正是否破坏原策略的任务意图。</x:v>
       </x:c>
       <x:c r="BW9" t="str">
         <x:v>离线示范轨迹不能保证在动态变化下仍安全可行。</x:v>
@@ -48615,7 +48643,7 @@
         <x:v>Two exemplar tasks and sim-to-real/cross-hand transfer are reported.</x:v>
       </x:c>
       <x:c r="AU10" t="str">
-        <x:v>Unknown / Needs Full-Paper Verification</x:v>
+        <x:v>IEEE RA-L 摘要报告：在两项示例操作任务中，去除手型特有信息的较小状态空间更利于迁移。</x:v>
       </x:c>
       <x:c r="AV10" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -48690,7 +48718,7 @@
       </x:c>
       <x:c r="BU10"/>
       <x:c r="BV10" t="str">
-        <x:v>灵巧手策略要跨仿真/现实和不同手型迁移。</x:v>
+        <x:v>研究问题：灵巧手策略要跨仿真/现实和不同手型迁移。；之前方法的问题：域随机化等方法不能完全弥合观测与动作定义造成的差异。；核心思路：比较不同 State Space 与 Action Space 的选择，检验其对两类迁移的影响。；输入：官方摘要给出任务/数据类型；具体模型张量与接口需核对方法章节。；输出与动作：官方摘要未明确列出完整控制接口；需核对论文方法或代码。；数据集与评测基准：两项手内操作任务；具体机器人与设置见 RA-L 正文。；主要结果：IEEE RA-L 摘要报告：在两项示例操作任务中，去除手型特有信息的较小状态空间更利于迁移。；为什么重要：提醒本项目先确定哪些状态和动作维度可跨两只夹爪复用。；与当前项目的关系：Medium：方法可借鉴，但迁移到当前双臂硬件需验证。；主要局限：本段基于官方摘要；未覆盖全文失败案例、完整 Baseline 与方法消融。</x:v>
       </x:c>
       <x:c r="BW10" t="str">
         <x:v>域随机化等方法不能完全弥合观测与动作定义造成的差异。</x:v>
@@ -48843,7 +48871,7 @@
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
       </x:c>
       <x:c r="AU11" t="str">
-        <x:v>Unknown / Needs Full-Paper Verification</x:v>
+        <x:v>论文在 9 种机器人平台上评测，表明 Octo 可迁移到新的观测和动作空间；具体成功率见原卡实验表。</x:v>
       </x:c>
       <x:c r="AV11" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -48918,7 +48946,7 @@
       </x:c>
       <x:c r="BU11"/>
       <x:c r="BV11" t="str">
-        <x:v>通用机器人策略需要同时适配不同相机、动作空间和机器人平台。</x:v>
+        <x:v>研究问题：通用机器人策略需要同时适配不同相机、动作空间和机器人平台。；之前方法的问题：各机器人平台的相机、动作空间与任务不同，单一策略难以直接跨平台使用。；核心思路：Octo 在 Open X-Embodiment 约 80 万条轨迹上训练 Transformer 策略，并提供可微调的通用初始化。；数据集与评测基准：从 Open X-Embodiment 整理约 80 万条训练轨迹，在 9 种机器人平台和多项下游任务上评估。；主要结果：论文在 9 种机器人平台上评测，表明 Octo 可迁移到新的观测和动作空间；具体成功率见原卡实验表。；为什么重要：是研究共享机器人数据与跨本体微调的重要开放基线。；与当前项目的关系：High：有助于研究语言条件操作与 VLA 设计。；主要局限：训练数据的腕部相机和语言覆盖不均；评测主要在论文列出的单臂/双臂平台。</x:v>
       </x:c>
       <x:c r="BW11" t="str">
         <x:v>各机器人平台的相机、动作空间与任务不同，单一策略难以直接跨平台使用。</x:v>
@@ -49067,7 +49095,7 @@
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
       </x:c>
       <x:c r="AU12" t="str">
-        <x:v>Unknown / Needs Full-Paper Verification</x:v>
+        <x:v>论文摘要报告，使用 DROID 训练的策略在性能、鲁棒性和泛化上改善；此处不附加未经实验表格核实的增幅。</x:v>
       </x:c>
       <x:c r="AV12" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -49142,7 +49170,7 @@
       </x:c>
       <x:c r="BU12"/>
       <x:c r="BV12" t="str">
-        <x:v>通用操作策略需要规模大、场景多样且质量可靠的机器人交互数据。</x:v>
+        <x:v>研究问题：通用操作策略需要规模大、场景多样且质量可靠的机器人交互数据。；之前方法的问题：跨环境采集成本高，并受安全、硬件和人力协调限制。；核心思路：DROID 组织分布式采集，形成 6.5 万条示范轨迹、约 350 小时交互，覆盖 564 个场景和 86 项任务。；数据集与评测基准：DROID：约 6.5 万条轨迹／350 小时、564 个场景、86 项任务，50 名采集人员在 12 个月内完成。；主要结果：论文摘要报告，使用 DROID 训练的策略在性能、鲁棒性和泛化上改善；此处不附加未经实验表格核实的增幅。；为什么重要：为跨场景数据采集和数据规模设计提供具体参照。；与当前项目的关系：Medium：可借鉴采集协议，但需核对与本项目机器人形态和动作接口的差异。；主要局限：摘要不能分离数据量、场景多样性与策略结构各自的贡献。</x:v>
       </x:c>
       <x:c r="BW12" t="str">
         <x:v>跨环境采集成本高，并受安全、硬件和人力协调限制。</x:v>
@@ -49293,7 +49321,7 @@
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
       </x:c>
       <x:c r="AU13" t="str">
-        <x:v>Unknown / Needs Full-Paper Verification</x:v>
+        <x:v>RSS 官方摘要报告，合成数据用于大规模模仿学习呈现规模效应；本轮不转述未经表格核验的成功率。</x:v>
       </x:c>
       <x:c r="AV13" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -49370,7 +49398,7 @@
       </x:c>
       <x:c r="BU13"/>
       <x:c r="BV13" t="str">
-        <x:v>真实机器人数据难以低成本扩展，限制通用家庭操作策略训练。</x:v>
+        <x:v>研究问题：真实机器人数据难以低成本扩展，限制通用家庭操作策略训练。；之前方法的问题：场景、任务和示范的规模不足；仅靠真机采集难以覆盖家庭环境多样性。；核心思路：RoboCasa 建立以厨房为中心的大规模仿真框架，结合生成式资产、语言模型辅助任务设计、人类示范和自动轨迹生成。；数据集与评测基准：RSS 2024 原版 RoboCasa：100 项任务、超过 150 个物体类别及大量 3D 资产；不要与后续 RoboCasa365 的规模混同。；主要结果：RSS 官方摘要报告，合成数据用于大规模模仿学习呈现规模效应；本轮不转述未经表格核验的成功率。；为什么重要：可用于研究仿真数据扩增及与真实机器人数据联合训练。；与当前项目的关系：Medium：家庭操作仿真可借鉴，但与本项目场景、双臂配置和真实部署有差异。；主要局限：摘要不能保证仿真训练所得提升直接迁移至本项目真机。</x:v>
       </x:c>
       <x:c r="BW13" t="str">
         <x:v>场景、任务和示范的规模不足；仅靠真机采集难以覆盖家庭环境多样性。</x:v>
@@ -49519,7 +49547,7 @@
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
       </x:c>
       <x:c r="AU14" t="str">
-        <x:v>Unknown / Needs Full-Paper Verification</x:v>
+        <x:v>官方项目与论文报告跨机器人训练带来的泛化收益；具体任务数值见原论文。</x:v>
       </x:c>
       <x:c r="AV14" t="str">
         <x:v>Unknown / Needs Full-Paper Verification</x:v>
@@ -49594,7 +49622,7 @@
       </x:c>
       <x:c r="BU14"/>
       <x:c r="BV14" t="str">
-        <x:v>机器人数据分散在不同机构、平台和格式中，难以训练通用策略。</x:v>
+        <x:v>研究问题：机器人数据分散在不同机构、平台和格式中，难以训练通用策略。；之前方法的问题：每个机器人和任务单独训练模型，跨平台复用成本高。；核心思路：Open X-Embodiment 整合标准化的跨机器人数据，并训练 RT-X 模型测试共享学习。；输入：官方摘要给出任务/数据类型；具体模型张量与接口需核对方法章节。；输出与动作：官方摘要未明确列出完整控制接口；需核对论文方法或代码。；数据集与评测基准：Open X-Embodiment 数据混合及 RT-X 评测。；主要结果：官方项目与论文报告跨机器人训练带来的泛化收益；具体任务数值见原论文。；为什么重要：是审计跨本体数据、动作格式和策略迁移的基础入口。；与当前项目的关系：Medium：方法可借鉴，但迁移到当前双臂硬件需验证。；主要局限：本段基于官方摘要；未覆盖全文失败案例、完整 Baseline 与方法消融。</x:v>
       </x:c>
       <x:c r="BW14" t="str">
         <x:v>每个机器人和任务单独训练模型，跨平台复用成本高。</x:v>
@@ -49848,7 +49876,7 @@
         <x:v>Completed-A</x:v>
       </x:c>
       <x:c r="BV15" t="str">
-        <x:v>LLM 能拆解长指令，但不知道当前机器人真正能做什么。</x:v>
+        <x:v>研究问题：LLM 能拆解长指令，但不知道当前机器人真正能做什么。；之前方法的问题：只按语言相关性选技能，可能生成物理上不可执行的计划。；核心思路：SayCan 结合语言模型的技能匹配分数与技能价值/可供性估计，逐步选择当前可执行的操作。；数据集与评测基准：Mock Kitchen 与真实办公室厨房任务。；为什么重要：把语言规划和机器人可执行性明确连接起来。；与当前项目的关系：High：双臂普通夹爪需要在动作前判断技能是否可行。；主要局限：技能库、价值估计和环境假设依赖特定机器人；规划成功不保证动作完成。</x:v>
       </x:c>
       <x:c r="BW15" t="str">
         <x:v>只按语言相关性选技能，可能生成物理上不可执行的计划。</x:v>
@@ -49906,7 +49934,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdfa19e8e776f4a68"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R54395a88ae014717"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/00_Paper_Pool/Paper_Pool.xlsx
+++ b/00_Paper_Pool/Paper_Pool.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Papers" sheetId="1" r:id="R455e651720dc49ee"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rejected" sheetId="2" r:id="R2c325815a6814582"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Venues" sheetId="3" r:id="R6c1f97ee8ee84a8b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Keywords" sheetId="4" r:id="R3e423bf7e23340ca"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Discovery" sheetId="5" r:id="R7611a26cf679499c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CCF_A_Library" sheetId="6" r:id="R85d867a1d6ff4ab8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Robotics_Core_Library" sheetId="7" r:id="Rb9ade8676bc74cde"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Papers" sheetId="1" r:id="R4fff0bbbd5524283"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rejected" sheetId="2" r:id="R0a35edba35584f69"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Venues" sheetId="3" r:id="R17e394ab109844dd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Keywords" sheetId="4" r:id="Rda2a3df3953148e8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Discovery" sheetId="5" r:id="R9935fa90070b4ee7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CCF_A_Library" sheetId="6" r:id="Rb5e3b09fca084827"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Robotics_Core_Library" sheetId="7" r:id="Rffe694cc3ed04401"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -352,7 +352,7 @@
     <x:tableColumn id="48" name="Idea Clues"/>
     <x:tableColumn id="49" name="Ablation Study"/>
     <x:tableColumn id="50" name="Failure Cases"/>
-    <x:tableColumn id="51" name="Citation Source Identifier"/>
+    <x:tableColumn id="51" name="引用量来源链接"/>
     <x:tableColumn id="52" name="Evidence Sources"/>
     <x:tableColumn id="53" name="Evidence Upgrade Status"/>
     <x:tableColumn id="54" name="Supplement Status"/>
@@ -483,7 +483,7 @@
     <x:tableColumn id="43" name="Idea Clues"/>
     <x:tableColumn id="44" name="Ablation Study"/>
     <x:tableColumn id="45" name="Failure Cases"/>
-    <x:tableColumn id="46" name="Citation Source Identifier"/>
+    <x:tableColumn id="46" name="引用量来源链接"/>
     <x:tableColumn id="47" name="Evidence Sources"/>
     <x:tableColumn id="48" name="Evidence Upgrade Status"/>
     <x:tableColumn id="49" name="Supplement Status"/>
@@ -588,7 +588,7 @@
     <x:tableColumn id="62" name="Idea Clues"/>
     <x:tableColumn id="63" name="Ablation Study"/>
     <x:tableColumn id="64" name="Failure Cases"/>
-    <x:tableColumn id="65" name="Citation Source Identifier"/>
+    <x:tableColumn id="65" name="引用量来源链接"/>
     <x:tableColumn id="66" name="Evidence Sources"/>
     <x:tableColumn id="67" name="Evidence Upgrade Status"/>
     <x:tableColumn id="68" name="Supplement Status"/>
@@ -682,7 +682,7 @@
     <x:tableColumn id="51" name="Idea Clues"/>
     <x:tableColumn id="52" name="Ablation Study"/>
     <x:tableColumn id="53" name="Failure Cases"/>
-    <x:tableColumn id="54" name="Citation Source Identifier"/>
+    <x:tableColumn id="54" name="引用量来源链接"/>
     <x:tableColumn id="55" name="Evidence Sources"/>
     <x:tableColumn id="56" name="Evidence Upgrade Status"/>
     <x:tableColumn id="57" name="Supplement Status"/>
@@ -1100,7 +1100,7 @@
         <x:v>Failure Cases</x:v>
       </x:c>
       <x:c r="AY1" t="str">
-        <x:v>Citation Source Identifier</x:v>
+        <x:v>引用量来源链接</x:v>
       </x:c>
       <x:c r="AZ1" t="str">
         <x:v>Evidence Sources</x:v>
@@ -1349,9 +1349,8 @@
       <x:c r="AX2" t="str">
         <x:v>Position predictions are sensitive to lighting and texture domain gaps; suction cannot grasp non-smooth handles and short gripper geometry can cause collisions.</x:v>
       </x:c>
-      <x:c r="AY2" t="e">
-        <x:f>HYPERLINK("https://openalex.org/W4402727730","OpenAlex Work")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://openalex.org/W4402727730, friendlyName=OpenAlex Work</x:v>
+      <x:c r="AY2" t="str">
+        <x:v>https://openalex.org/W4402727730</x:v>
       </x:c>
       <x:c r="AZ2" t="str">
         <x:v>https://openaccess.thecvf.com/content/CVPR2024/html/Li_ManipLLM_Embodied_Multimodal_Large_Language_Model_for_Object-Centric_Robotic_Manipulation_CVPR_2024_paper.html；官方摘要/论文集元数据</x:v>
@@ -1565,9 +1564,8 @@
       <x:c r="AX3" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
-      <x:c r="AY3" t="e">
-        <x:f>HYPERLINK("https://openalex.org/W4413145126","OpenAlex Work")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://openalex.org/W4413145126, friendlyName=OpenAlex Work</x:v>
+      <x:c r="AY3" t="str">
+        <x:v>https://openalex.org/W4413145126</x:v>
       </x:c>
       <x:c r="AZ3" t="str">
         <x:v>https://openaccess.thecvf.com/content/CVPR2025/html/Li_ManipTrans_Efficient_Dexterous_Bimanual_Manipulation_Transfer_via_Residual_Learning_CVPR_2025_paper.html；官方摘要/论文集元数据</x:v>
@@ -1777,9 +1775,8 @@
       <x:c r="AX4" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
-      <x:c r="AY4" t="e">
-        <x:f>HYPERLINK("https://openalex.org/W4413146641","OpenAlex Work")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://openalex.org/W4413146641, friendlyName=OpenAlex Work</x:v>
+      <x:c r="AY4" t="str">
+        <x:v>https://openalex.org/W4413146641</x:v>
       </x:c>
       <x:c r="AZ4" t="str">
         <x:v>https://openaccess.thecvf.com/content/CVPR2025/html/Liang_DexHandDiff_Interaction-aware_Diffusion_Planning_for_Adaptive_Dexterous_Manipulation_CVPR_2025_paper.html; https://dexdiffuser.github.io/; https://github.com/Liang-</x:v>
@@ -1989,9 +1986,8 @@
       <x:c r="AX5" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
-      <x:c r="AY5" t="e">
-        <x:f>HYPERLINK("https://openalex.org/W4416242580","OpenAlex Work")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://openalex.org/W4416242580, friendlyName=OpenAlex Work</x:v>
+      <x:c r="AY5" t="str">
+        <x:v>https://openalex.org/W4416242580</x:v>
       </x:c>
       <x:c r="AZ5" t="str">
         <x:v>https://openaccess.thecvf.com/content/ICCV2025/html/Yang_AR-VRM_Imitating_Human_Motions_for_Visual_Robot_Manipulation_with_Analogical_ICCV_2025_paper.html；官方摘要/论文集元数据</x:v>
@@ -2233,9 +2229,8 @@
       <x:c r="AX6" t="str">
         <x:v>Plan-execute gap; wrong object/negation; drawer manipulation and incomplete close; embodiment-specific failures.</x:v>
       </x:c>
-      <x:c r="AY6" t="e">
-        <x:f>HYPERLINK("https://openalex.org/W4224912544","OpenAlex Work")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://openalex.org/W4224912544, friendlyName=OpenAlex Work</x:v>
+      <x:c r="AY6" t="str">
+        <x:v>https://openalex.org/W4224912544</x:v>
       </x:c>
       <x:c r="AZ6" t="str">
         <x:v>Google Research publication; arXiv HTML 2204.01691; CoRL/PMLR; say-can.github.io; Google Research blog; official google-research/saycan</x:v>
@@ -5347,7 +5342,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf3e2febbcb5242ff"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R250b431c1f83454a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8643,7 +8638,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb608bc10d0fa447a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R75b6a4d8846b4732"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8994,7 +8989,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R539a3dd3fcb640f5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R632ee644304a4e73"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9740,7 +9735,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0b0bea9668e9461b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9f371f007e7c4788"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9917,7 +9912,7 @@
         <x:v>Failure Cases</x:v>
       </x:c>
       <x:c r="AT1" t="str">
-        <x:v>Citation Source Identifier</x:v>
+        <x:v>引用量来源链接</x:v>
       </x:c>
       <x:c r="AU1" t="str">
         <x:v>Evidence Sources</x:v>
@@ -10143,9 +10138,8 @@
       <x:c r="AS2" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
-      <x:c r="AT2" t="e">
-        <x:f>HYPERLINK("https://openalex.org/W4402727783","OpenAlex Work")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://openalex.org/W4402727783, friendlyName=OpenAlex Work</x:v>
+      <x:c r="AT2" t="str">
+        <x:v>https://openalex.org/W4402727783</x:v>
       </x:c>
       <x:c r="AU2" t="str">
         <x:v>https://openaccess.thecvf.com/content/CVPR2024/html/Ma_Hierarchical_Diffusion_Policy_for_Kinematics-Aware_Multi-Task_Robotic_Manipulation_CVPR_2024_paper.html；官方摘要/论文集元数据</x:v>
@@ -10365,9 +10359,8 @@
       <x:c r="AS3" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
-      <x:c r="AT3" t="e">
-        <x:f>HYPERLINK("https://openalex.org/W4415101881","OpenAlex Work")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://openalex.org/W4415101881, friendlyName=OpenAlex Work</x:v>
+      <x:c r="AT3" t="str">
+        <x:v>https://openalex.org/W4415101881</x:v>
       </x:c>
       <x:c r="AU3" t="str">
         <x:v>https://openaccess.thecvf.com/content/ICCV2025/html/Jiang_Rethinking_Bimanual_Robotic_Manipulation_Learning_with_Decoupled_Interaction_Framework_ICCV_2025_paper.html；官方摘要/论文集元数据</x:v>
@@ -10587,9 +10580,8 @@
       <x:c r="AS4" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
-      <x:c r="AT4" t="e">
-        <x:f>HYPERLINK("https://openalex.org/W4414754983","OpenAlex Work")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://openalex.org/W4414754983, friendlyName=OpenAlex Work</x:v>
+      <x:c r="AT4" t="str">
+        <x:v>https://openalex.org/W4414754983</x:v>
       </x:c>
       <x:c r="AU4" t="str">
         <x:v>https://openaccess.thecvf.com/content/ICCV2025/html/Xu_Diffusion-Based_Imaginative_Coordination_for_Bimanual_Manipulation_ICCV_2025_paper.html；官方摘要/论文集元数据</x:v>
@@ -10897,7 +10889,7 @@
         <x:v>官方摘要/论文页; https://proceedings.iclr.cc/paper_files/paper/2025/hash/e19b6f65791e350347bcff8a3955cb5b-Abstract-Conference.html; 核验于 2026-09-23. 仅为摘要级速读；原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="BX5" t="str">
-        <x:v>Unresolved; insufficient identity evidence</x:v>
+        <x:v>Unresolved; no reliable citation service count</x:v>
       </x:c>
       <x:c r="BY5" t="n">
         <x:v>0</x:v>
@@ -11033,9 +11025,8 @@
       <x:c r="AS6" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
-      <x:c r="AT6" t="e">
-        <x:f>HYPERLINK("https://openalex.org/W4403883977","OpenAlex Work")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://openalex.org/W4403883977, friendlyName=OpenAlex Work</x:v>
+      <x:c r="AT6" t="str">
+        <x:v>https://openalex.org/W4403883977</x:v>
       </x:c>
       <x:c r="AU6" t="str">
         <x:v>Unknown</x:v>
@@ -11340,7 +11331,7 @@
         <x:v>官方摘要/论文页; https://proceedings.iclr.cc/paper_files/paper/2025/hash/e68274fc4f158dbcbd4dddc672f7ee9c-Abstract-Conference.html; 核验于 2026-09-23. 仅为摘要级速读；原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="BX7" t="str">
-        <x:v>Unresolved; insufficient identity evidence</x:v>
+        <x:v>Unresolved; no reliable citation service count</x:v>
       </x:c>
       <x:c r="BY7" t="n">
         <x:v>0</x:v>
@@ -11474,9 +11465,8 @@
       <x:c r="AS8" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
-      <x:c r="AT8" t="e">
-        <x:f>HYPERLINK("https://openalex.org/W4407590583","OpenAlex Work")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://openalex.org/W4407590583, friendlyName=OpenAlex Work</x:v>
+      <x:c r="AT8" t="str">
+        <x:v>https://openalex.org/W4407590583</x:v>
       </x:c>
       <x:c r="AU8" t="str">
         <x:v>Unknown</x:v>
@@ -11781,7 +11771,7 @@
         <x:v>官方摘要/论文页; https://proceedings.iclr.cc/paper_files/paper/2025/hash/6eed1e1d5ed52deee53234786998245e-Abstract-Conference.html; 核验于 2026-09-23. 仅为摘要级速读；原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="BX9" t="str">
-        <x:v>Unresolved; insufficient identity evidence</x:v>
+        <x:v>Unresolved; no reliable citation service count</x:v>
       </x:c>
       <x:c r="BY9" t="n">
         <x:v>0</x:v>
@@ -12000,7 +11990,7 @@
         <x:v>官方摘要/论文页; https://proceedings.iclr.cc/paper_files/paper/2025/hash/9cd0c57170f48520749d5ae62838241f-Abstract-Conference.html; 核验于 2026-09-23. 仅为摘要级速读；原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="BX10" t="str">
-        <x:v>Unresolved; insufficient identity evidence</x:v>
+        <x:v>Unresolved; no reliable citation service count</x:v>
       </x:c>
       <x:c r="BY10" t="n">
         <x:v>0</x:v>
@@ -12139,9 +12129,8 @@
       <x:c r="AS11" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
-      <x:c r="AT11" t="e">
-        <x:f>HYPERLINK("https://openalex.org/W4407384835","OpenAlex Work")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://openalex.org/W4407384835, friendlyName=OpenAlex Work</x:v>
+      <x:c r="AT11" t="str">
+        <x:v>https://openalex.org/W4407384835</x:v>
       </x:c>
       <x:c r="AU11" t="str">
         <x:v>Unknown</x:v>
@@ -12364,9 +12353,8 @@
       <x:c r="AS12" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
-      <x:c r="AT12" t="e">
-        <x:f>HYPERLINK("https://openalex.org/W4404371741","OpenAlex Work")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://openalex.org/W4404371741, friendlyName=OpenAlex Work</x:v>
+      <x:c r="AT12" t="str">
+        <x:v>https://openalex.org/W4404371741</x:v>
       </x:c>
       <x:c r="AU12" t="str">
         <x:v>Unknown</x:v>
@@ -12589,9 +12577,8 @@
       <x:c r="AS13" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
-      <x:c r="AT13" t="e">
-        <x:f>HYPERLINK("https://openalex.org/W4403525052","OpenAlex Work")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://openalex.org/W4403525052, friendlyName=OpenAlex Work</x:v>
+      <x:c r="AT13" t="str">
+        <x:v>https://openalex.org/W4403525052</x:v>
       </x:c>
       <x:c r="AU13" t="str">
         <x:v>Unknown</x:v>
@@ -12811,9 +12798,8 @@
       <x:c r="AS14" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
-      <x:c r="AT14" t="e">
-        <x:f>HYPERLINK("https://openalex.org/W4405626335","OpenAlex Work")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://openalex.org/W4405626335, friendlyName=OpenAlex Work</x:v>
+      <x:c r="AT14" t="str">
+        <x:v>https://openalex.org/W4405626335</x:v>
       </x:c>
       <x:c r="AU14" t="str">
         <x:v>Unknown</x:v>
@@ -13121,7 +13107,7 @@
         <x:v>官方摘要/论文页; https://proceedings.iclr.cc/paper_files/paper/2026/hash/122ea6470232ee5e79a2649243348005-Abstract-Conference.html; 核验于 2026-09-23. 仅为摘要级速读；原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="BX15" t="str">
-        <x:v>Unresolved; insufficient identity evidence</x:v>
+        <x:v>Unresolved; no reliable citation service count</x:v>
       </x:c>
       <x:c r="BY15" t="n">
         <x:v>0</x:v>
@@ -13255,9 +13241,8 @@
       <x:c r="AS16" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
-      <x:c r="AT16" t="e">
-        <x:f>HYPERLINK("https://openalex.org/W4417536563","OpenAlex Work")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://openalex.org/W4417536563, friendlyName=OpenAlex Work</x:v>
+      <x:c r="AT16" t="str">
+        <x:v>https://openalex.org/W4417536563</x:v>
       </x:c>
       <x:c r="AU16" t="str">
         <x:v>Unknown</x:v>
@@ -13560,7 +13545,7 @@
         <x:v>官方摘要/论文页; https://arxiv.org/html/2509.09674; 核验于 2026-09-23. 仅为摘要级速读；原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="BX17" t="str">
-        <x:v>Unresolved; insufficient identity evidence</x:v>
+        <x:v>Unresolved; no reliable citation service count</x:v>
       </x:c>
       <x:c r="BY17" t="n">
         <x:v>6</x:v>
@@ -13779,7 +13764,7 @@
         <x:v>官方摘要/论文页; https://arxiv.org/html/2509.22195; 核验于 2026-09-23. 仅为摘要级速读；原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="BX18" t="str">
-        <x:v>Unresolved; insufficient identity evidence</x:v>
+        <x:v>Unresolved; no reliable citation service count</x:v>
       </x:c>
       <x:c r="BY18" t="n">
         <x:v>8</x:v>
@@ -13915,9 +13900,8 @@
       <x:c r="AS19" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
-      <x:c r="AT19" t="e">
-        <x:f>HYPERLINK("https://openalex.org/W7126041108","OpenAlex Work")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://openalex.org/W7126041108, friendlyName=OpenAlex Work</x:v>
+      <x:c r="AT19" t="str">
+        <x:v>https://openalex.org/W7126041108</x:v>
       </x:c>
       <x:c r="AU19" t="str">
         <x:v>Unknown</x:v>
@@ -14220,7 +14204,7 @@
         <x:v>官方摘要/论文页; https://proceedings.iclr.cc/paper_files/paper/2026/hash/cd96cb9a239c37b39dbf34f3f5a4c56f-Abstract-Conference.html; 核验于 2026-09-23. 仅为摘要级速读；原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="BX20" t="str">
-        <x:v>Unresolved; insufficient identity evidence</x:v>
+        <x:v>Unresolved; no reliable citation service count</x:v>
       </x:c>
       <x:c r="BY20" t="n">
         <x:v>0</x:v>
@@ -14356,9 +14340,8 @@
       <x:c r="AS21" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
-      <x:c r="AT21" t="e">
-        <x:f>HYPERLINK("https://openalex.org/W7138268695","OpenAlex Work")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://openalex.org/W7138268695, friendlyName=OpenAlex Work</x:v>
+      <x:c r="AT21" t="str">
+        <x:v>https://openalex.org/W7138268695</x:v>
       </x:c>
       <x:c r="AU21" t="str">
         <x:v>https://ojs.aaai.org/index.php/AAAI/article/view/38889；官方摘要/论文集元数据</x:v>
@@ -14578,9 +14561,8 @@
       <x:c r="AS22" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
-      <x:c r="AT22" t="e">
-        <x:f>HYPERLINK("https://openalex.org/W7138377383","OpenAlex Work")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://openalex.org/W7138377383, friendlyName=OpenAlex Work</x:v>
+      <x:c r="AT22" t="str">
+        <x:v>https://openalex.org/W7138377383</x:v>
       </x:c>
       <x:c r="AU22" t="str">
         <x:v>https://ojs.aaai.org/index.php/AAAI/article/view/38911；官方摘要/论文集元数据</x:v>
@@ -14800,9 +14782,8 @@
       <x:c r="AS23" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
-      <x:c r="AT23" t="e">
-        <x:f>HYPERLINK("https://openalex.org/W7138167694","OpenAlex Work")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://openalex.org/W7138167694, friendlyName=OpenAlex Work</x:v>
+      <x:c r="AT23" t="str">
+        <x:v>https://openalex.org/W7138167694</x:v>
       </x:c>
       <x:c r="AU23" t="str">
         <x:v>https://ojs.aaai.org/index.php/AAAI/article/view/38955；官方摘要/论文集元数据</x:v>
@@ -15022,9 +15003,8 @@
       <x:c r="AS24" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
-      <x:c r="AT24" t="e">
-        <x:f>HYPERLINK("https://openalex.org/W4416716605","OpenAlex Work")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://openalex.org/W4416716605, friendlyName=OpenAlex Work</x:v>
+      <x:c r="AT24" t="str">
+        <x:v>https://openalex.org/W4416716605</x:v>
       </x:c>
       <x:c r="AU24" t="str">
         <x:v>https://ojs.aaai.org/index.php/AAAI/article/view/38539；官方摘要/论文集元数据</x:v>
@@ -15187,11 +15167,11 @@
       <x:c r="Z25" t="str">
         <x:v>02_Papers/04_Dexterous/Learning_Object-Centric_Motion_Priors_from_Human_for_Robotic_Dexterous_Manipulation.md</x:v>
       </x:c>
-      <x:c r="AA25" t="str">
-        <x:v>—</x:v>
+      <x:c r="AA25" t="n">
+        <x:v>0</x:v>
       </x:c>
       <x:c r="AB25" t="str">
-        <x:v>未可靠匹配</x:v>
+        <x:v>Crossref</x:v>
       </x:c>
       <x:c r="AC25" t="str">
         <x:v>2026-09-25</x:v>
@@ -15243,7 +15223,7 @@
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AT25" t="str">
-        <x:v>—</x:v>
+        <x:v>https://api.crossref.org/works/10.1609/aaai.v40i22.38892</x:v>
       </x:c>
       <x:c r="AU25" t="str">
         <x:v>https://ojs.aaai.org/index.php/AAAI/article/download/38892/42854；官方摘要/论文集元数据</x:v>
@@ -15285,7 +15265,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="BH25" t="str">
-        <x:v>Unresolved</x:v>
+        <x:v>Matched</x:v>
       </x:c>
       <x:c r="BI25" t="str">
         <x:v>Not Found After Verification</x:v>
@@ -15327,7 +15307,7 @@
         <x:v>官方摘要/论文页：https://ojs.aaai.org/index.php/AAAI/article/view/38892；核验于 2026-09-23。仅为摘要级速读，原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="BX25" t="str">
-        <x:v>Unresolved; insufficient identity evidence</x:v>
+        <x:v>crossref-exact-title-pdf-authors</x:v>
       </x:c>
       <x:c r="BY25" t="n">
         <x:v>0</x:v>
@@ -15463,9 +15443,8 @@
       <x:c r="AS26" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
-      <x:c r="AT26" t="e">
-        <x:f>HYPERLINK("https://openalex.org/W4404312247","OpenAlex Work")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://openalex.org/W4404312247, friendlyName=OpenAlex Work</x:v>
+      <x:c r="AT26" t="str">
+        <x:v>https://openalex.org/W4404312247</x:v>
       </x:c>
       <x:c r="AU26" t="str">
         <x:v>Unknown</x:v>
@@ -15685,9 +15664,8 @@
       <x:c r="AS27" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
-      <x:c r="AT27" t="e">
-        <x:f>HYPERLINK("https://openalex.org/W4403622102","OpenAlex Work")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://openalex.org/W4403622102, friendlyName=OpenAlex Work</x:v>
+      <x:c r="AT27" t="str">
+        <x:v>https://openalex.org/W4403622102</x:v>
       </x:c>
       <x:c r="AU27" t="str">
         <x:v>Unknown</x:v>
@@ -15907,9 +15885,8 @@
       <x:c r="AS28" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
-      <x:c r="AT28" t="e">
-        <x:f>HYPERLINK("https://openalex.org/W4404308601","OpenAlex Work")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://openalex.org/W4404308601, friendlyName=OpenAlex Work</x:v>
+      <x:c r="AT28" t="str">
+        <x:v>https://openalex.org/W4404308601</x:v>
       </x:c>
       <x:c r="AU28" t="str">
         <x:v>https://proceedings.mlr.press/v270/</x:v>
@@ -16129,9 +16106,8 @@
       <x:c r="AS29" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
-      <x:c r="AT29" t="e">
-        <x:f>HYPERLINK("https://openalex.org/W4392781441","OpenAlex Work")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://openalex.org/W4392781441, friendlyName=OpenAlex Work</x:v>
+      <x:c r="AT29" t="str">
+        <x:v>https://openalex.org/W4392781441</x:v>
       </x:c>
       <x:c r="AU29" t="str">
         <x:v>Unknown</x:v>
@@ -16351,9 +16327,8 @@
       <x:c r="AS30" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
-      <x:c r="AT30" t="e">
-        <x:f>HYPERLINK("https://openalex.org/W4400435236","OpenAlex Work")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://openalex.org/W4400435236, friendlyName=OpenAlex Work</x:v>
+      <x:c r="AT30" t="str">
+        <x:v>https://openalex.org/W4400435236</x:v>
       </x:c>
       <x:c r="AU30" t="str">
         <x:v>Unknown</x:v>
@@ -16658,7 +16633,7 @@
         <x:v>OpenAlex 索引摘要; https://api.openalex.org/works/W4400222297; 核验于 2026-09-23. 仅为摘要级速读；原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="BX31" t="str">
-        <x:v>Unresolved; insufficient identity evidence</x:v>
+        <x:v>Unresolved; no reliable citation service count</x:v>
       </x:c>
       <x:c r="BY31" t="n">
         <x:v>0</x:v>
@@ -16794,9 +16769,8 @@
       <x:c r="AS32" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
-      <x:c r="AT32" t="e">
-        <x:f>HYPERLINK("https://openalex.org/W4400024954","OpenAlex Work")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://openalex.org/W4400024954, friendlyName=OpenAlex Work</x:v>
+      <x:c r="AT32" t="str">
+        <x:v>https://openalex.org/W4400024954</x:v>
       </x:c>
       <x:c r="AU32" t="str">
         <x:v>Unknown</x:v>
@@ -17016,9 +16990,8 @@
       <x:c r="AS33" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
-      <x:c r="AT33" t="e">
-        <x:f>HYPERLINK("https://openalex.org/W4400377647","OpenAlex Work")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://openalex.org/W4400377647, friendlyName=OpenAlex Work</x:v>
+      <x:c r="AT33" t="str">
+        <x:v>https://openalex.org/W4400377647</x:v>
       </x:c>
       <x:c r="AU33" t="str">
         <x:v>Unknown</x:v>
@@ -17238,9 +17211,8 @@
       <x:c r="AS34" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
-      <x:c r="AT34" t="e">
-        <x:f>HYPERLINK("https://openalex.org/W4400373516","OpenAlex Work")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://openalex.org/W4400373516, friendlyName=OpenAlex Work</x:v>
+      <x:c r="AT34" t="str">
+        <x:v>https://openalex.org/W4400373516</x:v>
       </x:c>
       <x:c r="AU34" t="str">
         <x:v>Unknown</x:v>
@@ -17460,9 +17432,8 @@
       <x:c r="AS35" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
-      <x:c r="AT35" t="e">
-        <x:f>HYPERLINK("https://openalex.org/W4391949089","OpenAlex Work")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://openalex.org/W4391949089, friendlyName=OpenAlex Work</x:v>
+      <x:c r="AT35" t="str">
+        <x:v>https://openalex.org/W4391949089</x:v>
       </x:c>
       <x:c r="AU35" t="str">
         <x:v>Unknown</x:v>
@@ -17682,9 +17653,8 @@
       <x:c r="AS36" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
-      <x:c r="AT36" t="e">
-        <x:f>HYPERLINK("https://openalex.org/W4400611211","OpenAlex Work")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://openalex.org/W4400611211, friendlyName=OpenAlex Work</x:v>
+      <x:c r="AT36" t="str">
+        <x:v>https://openalex.org/W4400611211</x:v>
       </x:c>
       <x:c r="AU36" t="str">
         <x:v>Unknown</x:v>
@@ -17904,9 +17874,8 @@
       <x:c r="AS37" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
-      <x:c r="AT37" t="e">
-        <x:f>HYPERLINK("https://openalex.org/W4400434472","OpenAlex Work")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://openalex.org/W4400434472, friendlyName=OpenAlex Work</x:v>
+      <x:c r="AT37" t="str">
+        <x:v>https://openalex.org/W4400434472</x:v>
       </x:c>
       <x:c r="AU37" t="str">
         <x:v>Unknown</x:v>
@@ -18211,7 +18180,7 @@
         <x:v>官方摘要/论文页; https://proceedings.mlr.press/v270/fu25b.html; 核验于 2026-09-23. 仅为摘要级速读；原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="BX38" t="str">
-        <x:v>Unresolved; insufficient identity evidence</x:v>
+        <x:v>Unresolved; no reliable citation service count</x:v>
       </x:c>
       <x:c r="BY38" t="n">
         <x:v>0</x:v>
@@ -18347,9 +18316,8 @@
       <x:c r="AS39" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
-      <x:c r="AT39" t="e">
-        <x:f>HYPERLINK("https://openalex.org/W4403579180","OpenAlex Work")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://openalex.org/W4403579180, friendlyName=OpenAlex Work</x:v>
+      <x:c r="AT39" t="str">
+        <x:v>https://openalex.org/W4403579180</x:v>
       </x:c>
       <x:c r="AU39" t="str">
         <x:v>https://proceedings.mlr.press/v270/</x:v>
@@ -18567,9 +18535,8 @@
       <x:c r="AS40" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
-      <x:c r="AT40" t="e">
-        <x:f>HYPERLINK("https://openalex.org/W4414991924","OpenAlex Work")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://openalex.org/W4414991924, friendlyName=OpenAlex Work</x:v>
+      <x:c r="AT40" t="str">
+        <x:v>https://openalex.org/W4414991924</x:v>
       </x:c>
       <x:c r="AU40" t="str">
         <x:v>Unknown</x:v>
@@ -18872,7 +18839,7 @@
         <x:v>官方摘要/论文页; https://proceedings.mlr.press/v305/deng25c.html; 核验于 2026-09-23. 仅为摘要级速读；原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="BX41" t="str">
-        <x:v>Unresolved; insufficient identity evidence</x:v>
+        <x:v>Unresolved; no reliable citation service count</x:v>
       </x:c>
       <x:c r="BY41" t="n">
         <x:v>0</x:v>
@@ -19006,9 +18973,8 @@
       <x:c r="AS42" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
-      <x:c r="AT42" t="e">
-        <x:f>HYPERLINK("https://openalex.org/W4407569722","OpenAlex Work")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://openalex.org/W4407569722, friendlyName=OpenAlex Work</x:v>
+      <x:c r="AT42" t="str">
+        <x:v>https://openalex.org/W4407569722</x:v>
       </x:c>
       <x:c r="AU42" t="str">
         <x:v>Unknown</x:v>
@@ -19311,7 +19277,7 @@
         <x:v>官方摘要/论文页; https://proceedings.mlr.press/v305/lin25c.html; 核验于 2026-09-23. 仅为摘要级速读；原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="BX43" t="str">
-        <x:v>Unresolved; insufficient identity evidence</x:v>
+        <x:v>Unresolved; no reliable citation service count</x:v>
       </x:c>
       <x:c r="BY43" t="n">
         <x:v>0</x:v>
@@ -19530,7 +19496,7 @@
         <x:v>OpenAlex 索引摘要; https://api.openalex.org/works/W4416623172; 核验于 2026-09-23. 仅为摘要级速读；原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="BX44" t="str">
-        <x:v>Unresolved; insufficient identity evidence</x:v>
+        <x:v>Unresolved; no reliable citation service count</x:v>
       </x:c>
       <x:c r="BY44" t="n">
         <x:v>0</x:v>
@@ -19749,7 +19715,7 @@
         <x:v>官方摘要/论文页; https://arxiv.org/html/2506.17811; 核验于 2026-09-23. 仅为摘要级速读；原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="BX45" t="str">
-        <x:v>Unresolved; insufficient identity evidence</x:v>
+        <x:v>Unresolved; no reliable citation service count</x:v>
       </x:c>
       <x:c r="BY45" t="n">
         <x:v>5</x:v>
@@ -19885,9 +19851,8 @@
       <x:c r="AS46" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
-      <x:c r="AT46" t="e">
-        <x:f>HYPERLINK("https://www.semanticscholar.org/paper/ae9a2bcd460354c706aaea8797b1c2c15841a6b6","Semantic Scholar")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.semanticscholar.org/paper/ae9a2bcd460354c706aaea8797b1c2c15841a6b6, friendlyName=Semantic Scholar</x:v>
+      <x:c r="AT46" t="str">
+        <x:v>https://www.semanticscholar.org/paper/ae9a2bcd460354c706aaea8797b1c2c15841a6b6</x:v>
       </x:c>
       <x:c r="AU46" t="str">
         <x:v>Unknown</x:v>
@@ -20107,9 +20072,8 @@
       <x:c r="AS47" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
-      <x:c r="AT47" t="e">
-        <x:f>HYPERLINK("https://openalex.org/W4417042701","OpenAlex Work")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://openalex.org/W4417042701, friendlyName=OpenAlex Work</x:v>
+      <x:c r="AT47" t="str">
+        <x:v>https://openalex.org/W4417042701</x:v>
       </x:c>
       <x:c r="AU47" t="str">
         <x:v>Unknown</x:v>
@@ -20274,11 +20238,11 @@
       <x:c r="Z48" t="str">
         <x:v>02_Papers/09_Survey_Review/What_Foundation_Models_can_Bring_for_Robot_Learning_in_Manipulation_A_Survey.md</x:v>
       </x:c>
-      <x:c r="AA48" t="str">
-        <x:v>—</x:v>
+      <x:c r="AA48" t="n">
+        <x:v>7</x:v>
       </x:c>
       <x:c r="AB48" t="str">
-        <x:v>未可靠匹配</x:v>
+        <x:v>Crossref</x:v>
       </x:c>
       <x:c r="AC48" t="str">
         <x:v>2026-09-25</x:v>
@@ -20330,7 +20294,7 @@
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AT48" t="str">
-        <x:v>—</x:v>
+        <x:v>https://api.crossref.org/works/10.1177/02783649251390579</x:v>
       </x:c>
       <x:c r="AU48" t="str">
         <x:v>Unknown</x:v>
@@ -20372,7 +20336,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="BH48" t="str">
-        <x:v>Unresolved</x:v>
+        <x:v>Matched</x:v>
       </x:c>
       <x:c r="BI48" t="str">
         <x:v>Not Found After Verification</x:v>
@@ -20414,7 +20378,7 @@
         <x:v>OpenAlex 索引摘要; https://api.openalex.org/works/W4416422407; 核验于 2026-09-23. 仅为摘要级速读；原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="BX48" t="str">
-        <x:v>Unresolved; insufficient identity evidence</x:v>
+        <x:v>crossref-exact-title-pdf-authors</x:v>
       </x:c>
       <x:c r="BY48" t="n">
         <x:v>0</x:v>
@@ -20550,9 +20514,8 @@
       <x:c r="AS49" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
-      <x:c r="AT49" t="e">
-        <x:f>HYPERLINK("https://openalex.org/W4391590994","OpenAlex Work")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://openalex.org/W4391590994, friendlyName=OpenAlex Work</x:v>
+      <x:c r="AT49" t="str">
+        <x:v>https://openalex.org/W4391590994</x:v>
       </x:c>
       <x:c r="AU49" t="str">
         <x:v>Unknown</x:v>
@@ -20772,9 +20735,8 @@
       <x:c r="AS50" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
-      <x:c r="AT50" t="e">
-        <x:f>HYPERLINK("https://openalex.org/W4391800778","OpenAlex Work")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://openalex.org/W4391800778, friendlyName=OpenAlex Work</x:v>
+      <x:c r="AT50" t="str">
+        <x:v>https://openalex.org/W4391800778</x:v>
       </x:c>
       <x:c r="AU50" t="str">
         <x:v>Unknown</x:v>
@@ -20994,9 +20956,8 @@
       <x:c r="AS51" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
-      <x:c r="AT51" t="e">
-        <x:f>HYPERLINK("https://openalex.org/W4390962508","OpenAlex Work")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://openalex.org/W4390962508, friendlyName=OpenAlex Work</x:v>
+      <x:c r="AT51" t="str">
+        <x:v>https://openalex.org/W4390962508</x:v>
       </x:c>
       <x:c r="AU51" t="str">
         <x:v>Unknown</x:v>
@@ -21299,7 +21260,7 @@
         <x:v>OpenAlex 索引摘要; https://api.openalex.org/works/W4409168415; 核验于 2026-09-23. 仅为摘要级速读；原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="BX52" t="str">
-        <x:v>Unresolved; insufficient identity evidence</x:v>
+        <x:v>Unresolved; no reliable citation service count</x:v>
       </x:c>
       <x:c r="BY52" t="n">
         <x:v>1</x:v>
@@ -21380,11 +21341,11 @@
       <x:c r="Z53" t="str">
         <x:v>02_Papers/09_Survey_Review/A_Survey_of_Embodied_Learning_for_Object-Centric_Robotic_Manipulation.md</x:v>
       </x:c>
-      <x:c r="AA53" t="str">
-        <x:v>—</x:v>
+      <x:c r="AA53" t="n">
+        <x:v>20</x:v>
       </x:c>
       <x:c r="AB53" t="str">
-        <x:v>未可靠匹配</x:v>
+        <x:v>Crossref</x:v>
       </x:c>
       <x:c r="AC53" t="str">
         <x:v>2026-09-25</x:v>
@@ -21436,7 +21397,7 @@
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AT53" t="str">
-        <x:v>—</x:v>
+        <x:v>https://api.crossref.org/works/10.1007/s11633-025-1542-8</x:v>
       </x:c>
       <x:c r="AU53" t="str">
         <x:v>Unknown</x:v>
@@ -21478,7 +21439,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="BH53" t="str">
-        <x:v>Unresolved</x:v>
+        <x:v>Matched</x:v>
       </x:c>
       <x:c r="BI53" t="str">
         <x:v>Not Found After Verification</x:v>
@@ -21520,7 +21481,7 @@
         <x:v>官方摘要/论文页; https://link.springer.com/article/10.1007/s11633-025-1542-8; 核验于 2026-09-23. 仅为摘要级速读；原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="BX53" t="str">
-        <x:v>Unresolved; insufficient identity evidence</x:v>
+        <x:v>crossref-exact-title-pdf-authors</x:v>
       </x:c>
       <x:c r="BY53" t="n">
         <x:v>3</x:v>
@@ -21656,9 +21617,8 @@
       <x:c r="AS54" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
-      <x:c r="AT54" t="e">
-        <x:f>HYPERLINK("https://openalex.org/W4414888151","OpenAlex Work")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://openalex.org/W4414888151, friendlyName=OpenAlex Work</x:v>
+      <x:c r="AT54" t="str">
+        <x:v>https://openalex.org/W4414888151</x:v>
       </x:c>
       <x:c r="AU54" t="str">
         <x:v>Unknown</x:v>
@@ -21961,7 +21921,7 @@
         <x:v>Existing canonical card and official-paper metadata; abstract unavailable; https://github.com/Destiny000621/awesome-bimanual-robot-learning/blob/main/SURVEY.md; 核验于 2026-09-23. 仅为摘要级速读；原 Evidence Quality 不变。 - 核验层级：证据有限；不得视为全文核验</x:v>
       </x:c>
       <x:c r="BX55" t="str">
-        <x:v>Unresolved; insufficient identity evidence</x:v>
+        <x:v>Unresolved; no reliable citation service count</x:v>
       </x:c>
       <x:c r="BY55" t="n">
         <x:v>0</x:v>
@@ -22097,9 +22057,8 @@
       <x:c r="AS56" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
-      <x:c r="AT56" t="e">
-        <x:f>HYPERLINK("https://www.semanticscholar.org/paper/9702a6cce93fbff83dbdad83ae74a3180eb47622","Semantic Scholar")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.semanticscholar.org/paper/9702a6cce93fbff83dbdad83ae74a3180eb47622, friendlyName=Semantic Scholar</x:v>
+      <x:c r="AT56" t="str">
+        <x:v>https://www.semanticscholar.org/paper/9702a6cce93fbff83dbdad83ae74a3180eb47622</x:v>
       </x:c>
       <x:c r="AU56" t="str">
         <x:v>Unknown</x:v>
@@ -22319,9 +22278,8 @@
       <x:c r="AS57" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
-      <x:c r="AT57" t="e">
-        <x:f>HYPERLINK("https://openalex.org/W4402510263","OpenAlex Work")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://openalex.org/W4402510263, friendlyName=OpenAlex Work</x:v>
+      <x:c r="AT57" t="str">
+        <x:v>https://openalex.org/W4402510263</x:v>
       </x:c>
       <x:c r="AU57" t="str">
         <x:v>Unknown</x:v>
@@ -22549,9 +22507,8 @@
       <x:c r="AS58" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
-      <x:c r="AT58" t="e">
-        <x:f>HYPERLINK("https://openalex.org/W4403364995","OpenAlex Work")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://openalex.org/W4403364995, friendlyName=OpenAlex Work</x:v>
+      <x:c r="AT58" t="str">
+        <x:v>https://openalex.org/W4403364995</x:v>
       </x:c>
       <x:c r="AU58" t="str">
         <x:v>Unknown</x:v>
@@ -22779,9 +22736,8 @@
       <x:c r="AS59" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
-      <x:c r="AT59" t="e">
-        <x:f>HYPERLINK("https://openalex.org/W7104616842","OpenAlex Work")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://openalex.org/W7104616842, friendlyName=OpenAlex Work</x:v>
+      <x:c r="AT59" t="str">
+        <x:v>https://openalex.org/W7104616842</x:v>
       </x:c>
       <x:c r="AU59" t="str">
         <x:v>Unknown</x:v>
@@ -22952,11 +22908,11 @@
       <x:c r="Z60" t="str">
         <x:v>02_Papers/10_Benchmark_Dataset/RoboTwin.md</x:v>
       </x:c>
-      <x:c r="AA60" t="str">
-        <x:v>—</x:v>
+      <x:c r="AA60" t="n">
+        <x:v>28</x:v>
       </x:c>
       <x:c r="AB60" t="str">
-        <x:v>未可靠匹配</x:v>
+        <x:v>Crossref</x:v>
       </x:c>
       <x:c r="AC60" t="str">
         <x:v>2026-09-25</x:v>
@@ -23008,7 +22964,7 @@
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="AT60" t="str">
-        <x:v>—</x:v>
+        <x:v>https://api.crossref.org/works/10.1109/cvpr52734.2025.02575</x:v>
       </x:c>
       <x:c r="AU60" t="str">
         <x:v>https://openaccess.thecvf.com/content/CVPR2025/html/Mu_RoboTwin_Dual-Arm_Robot_Benchmark_with_Generative_Digital_Twins_CVPR_2025_paper.html；官方摘要/论文集元数据</x:v>
@@ -23050,7 +23006,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="BH60" t="str">
-        <x:v>Unresolved</x:v>
+        <x:v>Matched</x:v>
       </x:c>
       <x:c r="BI60" t="str">
         <x:v>Not Found After Verification</x:v>
@@ -23092,7 +23048,7 @@
         <x:v>官方摘要/论文页; https://openaccess.thecvf.com/content/CVPR2025/html/Mu_RoboTwin_Dual-Arm_Robot_Benchmark_with_Generative_Digital_Twins_CVPR_2025_paper.html; 核验于 2026-09-23. 仅为摘要级速读；原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="BX60" t="str">
-        <x:v>Unresolved; insufficient identity evidence</x:v>
+        <x:v>crossref-exact-title-pdf-authors</x:v>
       </x:c>
       <x:c r="BY60" t="n">
         <x:v>0</x:v>
@@ -23236,9 +23192,8 @@
       <x:c r="AS61" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
-      <x:c r="AT61" t="e">
-        <x:f>HYPERLINK("https://openalex.org/W4415272059","OpenAlex Work")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://openalex.org/W4415272059, friendlyName=OpenAlex Work</x:v>
+      <x:c r="AT61" t="str">
+        <x:v>https://openalex.org/W4415272059</x:v>
       </x:c>
       <x:c r="AU61" t="str">
         <x:v>https://proceedings.neurips.cc/paper_files/paper/2025/hash/5c1a8aa04c1a2cf5013f28831870dafa-Abstract-Conference.html；官方摘要/论文集元数据</x:v>
@@ -23471,9 +23426,8 @@
       <x:c r="AS62" t="str">
         <x:v>背景动态使基线 PickPot SR 95→80%；VLA-Cache 在动态条件保持80%且降低FLOPs/延迟；PickPot 真机SR 95→90%（Table 5,7）。</x:v>
       </x:c>
-      <x:c r="AT62" t="e">
-        <x:f>HYPERLINK("https://openalex.org/W7196930033","OpenAlex Work")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://openalex.org/W7196930033, friendlyName=OpenAlex Work</x:v>
+      <x:c r="AT62" t="str">
+        <x:v>https://openalex.org/W7196930033</x:v>
       </x:c>
       <x:c r="AU62" t="str">
         <x:v>NeurIPS 正式论文页；arXiv PDF §1–6、Appendix A–F、Tables 1–5、7–11；NeurIPS Supplemental zip 与作者 GitHub。</x:v>
@@ -23789,7 +23743,7 @@
         <x:v>官方摘要/论文页; https://proceedings.mlr.press/v267/wen25g.html; 核验于 2026-09-23. 仅为摘要级速读；原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="BX63" t="str">
-        <x:v>Unresolved; insufficient identity evidence</x:v>
+        <x:v>Unresolved; no reliable citation service count</x:v>
       </x:c>
       <x:c r="BY63" t="n">
         <x:v>8</x:v>
@@ -23938,9 +23892,8 @@
       <x:c r="AS64" t="str">
         <x:v>§6：目标生成可能改变纹理/形状、令物体消失、预测不相关的未来或状态无变化；小物体精细操作失败。</x:v>
       </x:c>
-      <x:c r="AT64" t="e">
-        <x:f>HYPERLINK("https://openalex.org/W4392886475","OpenAlex Work")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://openalex.org/W4392886475, friendlyName=OpenAlex Work</x:v>
+      <x:c r="AT64" t="str">
+        <x:v>https://openalex.org/W4392886475</x:v>
       </x:c>
       <x:c r="AU64" t="str">
         <x:v>PMLR 官方 PDF：§3.1–3.3、§4.1–4.3、§5.1–5.3、§6–7；Figures 2–3、5–6；Tables 1–6、Appendix Tables 7–9。https://raw.githubusercontent.com/mlresearch/v235/main/assets/zhen24a/zhen24a.pdf</x:v>
@@ -24175,9 +24128,8 @@
       <x:c r="AS65" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
-      <x:c r="AT65" t="e">
-        <x:f>HYPERLINK("https://openalex.org/W4415797921","OpenAlex Work")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://openalex.org/W4415797921, friendlyName=OpenAlex Work</x:v>
+      <x:c r="AT65" t="str">
+        <x:v>https://openalex.org/W4415797921</x:v>
       </x:c>
       <x:c r="AU65" t="str">
         <x:v>https://proceedings.neurips.cc/paper_files/paper/2024/hash/46a126492ea6fb87410e55a58df2e189-Abstract-Conference.html; https://sites.google.com/view/robomamba-web; https://github.com/lm</x:v>
@@ -24405,9 +24357,8 @@
       <x:c r="AS66" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
-      <x:c r="AT66" t="e">
-        <x:f>HYPERLINK("https://openalex.org/W4405434146","OpenAlex Work")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://openalex.org/W4405434146, friendlyName=OpenAlex Work</x:v>
+      <x:c r="AT66" t="str">
+        <x:v>https://openalex.org/W4405434146</x:v>
       </x:c>
       <x:c r="AU66" t="str">
         <x:v>Unknown</x:v>
@@ -24720,7 +24671,7 @@
         <x:v>官方摘要/论文页; https://proceedings.iclr.cc/paper_files/paper/2025/hash/45d74e190008c7bff2845ffc8e3facd3-Abstract-Conference.html; 核验于 2026-09-23. 仅为摘要级速读；原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="BX67" t="str">
-        <x:v>Unresolved; insufficient identity evidence</x:v>
+        <x:v>Unresolved; no reliable citation service count</x:v>
       </x:c>
       <x:c r="BY67" t="n">
         <x:v>0</x:v>
@@ -24861,9 +24812,8 @@
       <x:c r="AS68" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
-      <x:c r="AT68" t="e">
-        <x:f>HYPERLINK("https://openalex.org/W4409365031","OpenAlex Work")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://openalex.org/W4409365031, friendlyName=OpenAlex Work</x:v>
+      <x:c r="AT68" t="str">
+        <x:v>https://openalex.org/W4409365031</x:v>
       </x:c>
       <x:c r="AU68" t="str">
         <x:v>https://ojs.aaai.org/index.php/AAAI/article/view/33617; https://github.com/</x:v>
@@ -25091,9 +25041,8 @@
       <x:c r="AS69" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
-      <x:c r="AT69" t="e">
-        <x:f>HYPERLINK("https://openalex.org/W4413145029","OpenAlex Work")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://openalex.org/W4413145029, friendlyName=OpenAlex Work</x:v>
+      <x:c r="AT69" t="str">
+        <x:v>https://openalex.org/W4413145029</x:v>
       </x:c>
       <x:c r="AU69" t="str">
         <x:v>https://openaccess.thecvf.com/content/CVPR2025/html/Wang_UniGraspTransformer_Simplified_Policy_Distillation_for_Scalable_Dexterous_Robotic_Grasping_CVPR_2025_paper.html；官方摘要/论文集元数据</x:v>
@@ -25321,9 +25270,8 @@
       <x:c r="AS70" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
-      <x:c r="AT70" t="e">
-        <x:f>HYPERLINK("https://openalex.org/W4414683599","OpenAlex Work")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://openalex.org/W4414683599, friendlyName=OpenAlex Work</x:v>
+      <x:c r="AT70" t="str">
+        <x:v>https://openalex.org/W4414683599</x:v>
       </x:c>
       <x:c r="AU70" t="str">
         <x:v>https://proceedings.neurips.cc/paper_files/paper/2025/hash/862644b156e51c35dea5a7446d640b14-Abstract-Conference.html；官方摘要/论文集元数据</x:v>
@@ -25551,9 +25499,8 @@
       <x:c r="AS71" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
-      <x:c r="AT71" t="e">
-        <x:f>HYPERLINK("https://openalex.org/W7196952124","OpenAlex Work")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://openalex.org/W7196952124, friendlyName=OpenAlex Work</x:v>
+      <x:c r="AT71" t="str">
+        <x:v>https://openalex.org/W7196952124</x:v>
       </x:c>
       <x:c r="AU71" t="str">
         <x:v>https://proceedings.neurips.cc/paper_files/paper/2025/hash/89a3b655a8b68ae1c76b768152c9c19d-Abstract-Conference.html；官方摘要/论文集元数据</x:v>
@@ -25781,9 +25728,8 @@
       <x:c r="AS72" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
-      <x:c r="AT72" t="e">
-        <x:f>HYPERLINK("https://openalex.org/W7125566978","OpenAlex Work")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://openalex.org/W7125566978, friendlyName=OpenAlex Work</x:v>
+      <x:c r="AT72" t="str">
+        <x:v>https://openalex.org/W7125566978</x:v>
       </x:c>
       <x:c r="AU72" t="str">
         <x:v>https://openaccess.thecvf.com/content/CVPR2026/html/Lee_DextER_Language-driven_Dexterous_Grasp_Generation_with_Embodied_Reasoning_CVPR_2026_paper.html；官方摘要/论文集元数据</x:v>
@@ -26011,9 +25957,8 @@
       <x:c r="AS73" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
-      <x:c r="AT73" t="e">
-        <x:f>HYPERLINK("https://openalex.org/W4414051092","OpenAlex Work")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://openalex.org/W4414051092, friendlyName=OpenAlex Work</x:v>
+      <x:c r="AT73" t="str">
+        <x:v>https://openalex.org/W4414051092</x:v>
       </x:c>
       <x:c r="AU73" t="str">
         <x:v>Unknown</x:v>
@@ -26241,9 +26186,8 @@
       <x:c r="AS74" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
-      <x:c r="AT74" t="e">
-        <x:f>HYPERLINK("https://openalex.org/W4399695759","OpenAlex Work")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://openalex.org/W4399695759, friendlyName=OpenAlex Work</x:v>
+      <x:c r="AT74" t="str">
+        <x:v>https://openalex.org/W4399695759</x:v>
       </x:c>
       <x:c r="AU74" t="str">
         <x:v>Unknown</x:v>
@@ -26471,9 +26415,8 @@
       <x:c r="AS75" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
-      <x:c r="AT75" t="e">
-        <x:f>HYPERLINK("https://openalex.org/W4402353985","OpenAlex Work")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://openalex.org/W4402353985, friendlyName=OpenAlex Work</x:v>
+      <x:c r="AT75" t="str">
+        <x:v>https://openalex.org/W4402353985</x:v>
       </x:c>
       <x:c r="AU75" t="str">
         <x:v>Unknown</x:v>
@@ -26696,9 +26639,8 @@
       <x:c r="AS76" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
-      <x:c r="AT76" t="e">
-        <x:f>HYPERLINK("https://openalex.org/W4402354047","OpenAlex Work")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://openalex.org/W4402354047, friendlyName=OpenAlex Work</x:v>
+      <x:c r="AT76" t="str">
+        <x:v>https://openalex.org/W4402354047</x:v>
       </x:c>
       <x:c r="AU76" t="str">
         <x:v>Unknown</x:v>
@@ -26927,9 +26869,8 @@
       <x:c r="AS77" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
-      <x:c r="AT77" t="e">
-        <x:f>HYPERLINK("https://www.semanticscholar.org/paper/a294546084fda4e0f12f307caed4f9c58f051632","Semantic Scholar")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.semanticscholar.org/paper/a294546084fda4e0f12f307caed4f9c58f051632, friendlyName=Semantic Scholar</x:v>
+      <x:c r="AT77" t="str">
+        <x:v>https://www.semanticscholar.org/paper/a294546084fda4e0f12f307caed4f9c58f051632</x:v>
       </x:c>
       <x:c r="AU77" t="str">
         <x:v>Unknown</x:v>
@@ -27154,9 +27095,8 @@
       <x:c r="AS78" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
-      <x:c r="AT78" t="e">
-        <x:f>HYPERLINK("https://openalex.org/W4387764390","OpenAlex Work")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://openalex.org/W4387764390, friendlyName=OpenAlex Work</x:v>
+      <x:c r="AT78" t="str">
+        <x:v>https://openalex.org/W4387764390</x:v>
       </x:c>
       <x:c r="AU78" t="str">
         <x:v>Unknown</x:v>
@@ -27389,9 +27329,8 @@
       <x:c r="AS79" t="str">
         <x:v>Not Explicitly Reported in the accessible official abstract/project evidence.</x:v>
       </x:c>
-      <x:c r="AT79" t="e">
-        <x:f>HYPERLINK("https://openalex.org/W7137985120","OpenAlex Work")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://openalex.org/W7137985120, friendlyName=OpenAlex Work</x:v>
+      <x:c r="AT79" t="str">
+        <x:v>https://openalex.org/W7137985120</x:v>
       </x:c>
       <x:c r="AU79" t="str">
         <x:v>https://ojs.aaai.org/index.php/AAAI/article/view/38921；https://arxiv.org/abs/2508.10333；https://zionchow.github.io/ReconVLA/；https://github.com/OpenHelix-Team/ReconVLA</x:v>
@@ -27508,7 +27447,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc37a0a8c536b4386"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1026b7fa96694510"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -27763,7 +27702,7 @@
         <x:v>Failure Cases</x:v>
       </x:c>
       <x:c r="BM1" t="str">
-        <x:v>Citation Source Identifier</x:v>
+        <x:v>引用量来源链接</x:v>
       </x:c>
       <x:c r="BN1" t="str">
         <x:v>Evidence Sources</x:v>
@@ -28046,9 +27985,8 @@
       <x:c r="BL2" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
-      <x:c r="BM2" t="e">
-        <x:f>HYPERLINK("https://openalex.org/W4402727783","OpenAlex Work")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://openalex.org/W4402727783, friendlyName=OpenAlex Work</x:v>
+      <x:c r="BM2" t="str">
+        <x:v>https://openalex.org/W4402727783</x:v>
       </x:c>
       <x:c r="BN2" t="str">
         <x:v>https://openaccess.thecvf.com/content/CVPR2024/html/Ma_Hierarchical_Diffusion_Policy_for_Kinematics-Aware_Multi-Task_Robotic_Manipulation_CVPR_2024_paper.html；官方摘要/论文集元数据</x:v>
@@ -28325,9 +28263,8 @@
       <x:c r="BL3" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
-      <x:c r="BM3" t="e">
-        <x:f>HYPERLINK("https://openalex.org/W4415101881","OpenAlex Work")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://openalex.org/W4415101881, friendlyName=OpenAlex Work</x:v>
+      <x:c r="BM3" t="str">
+        <x:v>https://openalex.org/W4415101881</x:v>
       </x:c>
       <x:c r="BN3" t="str">
         <x:v>https://openaccess.thecvf.com/content/ICCV2025/html/Jiang_Rethinking_Bimanual_Robotic_Manipulation_Learning_with_Decoupled_Interaction_Framework_ICCV_2025_paper.html；官方摘要/论文集元数据</x:v>
@@ -28604,9 +28541,8 @@
       <x:c r="BL4" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
-      <x:c r="BM4" t="e">
-        <x:f>HYPERLINK("https://openalex.org/W4414754983","OpenAlex Work")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://openalex.org/W4414754983, friendlyName=OpenAlex Work</x:v>
+      <x:c r="BM4" t="str">
+        <x:v>https://openalex.org/W4414754983</x:v>
       </x:c>
       <x:c r="BN4" t="str">
         <x:v>https://openaccess.thecvf.com/content/ICCV2025/html/Xu_Diffusion-Based_Imaginative_Coordination_for_Bimanual_Manipulation_ICCV_2025_paper.html；官方摘要/论文集元数据</x:v>
@@ -28883,9 +28819,8 @@
       <x:c r="BL5" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
-      <x:c r="BM5" t="e">
-        <x:f>HYPERLINK("https://openalex.org/W7138268695","OpenAlex Work")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://openalex.org/W7138268695, friendlyName=OpenAlex Work</x:v>
+      <x:c r="BM5" t="str">
+        <x:v>https://openalex.org/W7138268695</x:v>
       </x:c>
       <x:c r="BN5" t="str">
         <x:v>https://ojs.aaai.org/index.php/AAAI/article/view/38889；官方摘要/论文集元数据</x:v>
@@ -29162,9 +29097,8 @@
       <x:c r="BL6" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
-      <x:c r="BM6" t="e">
-        <x:f>HYPERLINK("https://openalex.org/W7138377383","OpenAlex Work")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://openalex.org/W7138377383, friendlyName=OpenAlex Work</x:v>
+      <x:c r="BM6" t="str">
+        <x:v>https://openalex.org/W7138377383</x:v>
       </x:c>
       <x:c r="BN6" t="str">
         <x:v>https://ojs.aaai.org/index.php/AAAI/article/view/38911；官方摘要/论文集元数据</x:v>
@@ -29441,9 +29375,8 @@
       <x:c r="BL7" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
-      <x:c r="BM7" t="e">
-        <x:f>HYPERLINK("https://openalex.org/W7138167694","OpenAlex Work")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://openalex.org/W7138167694, friendlyName=OpenAlex Work</x:v>
+      <x:c r="BM7" t="str">
+        <x:v>https://openalex.org/W7138167694</x:v>
       </x:c>
       <x:c r="BN7" t="str">
         <x:v>https://ojs.aaai.org/index.php/AAAI/article/view/38955；官方摘要/论文集元数据</x:v>
@@ -29720,9 +29653,8 @@
       <x:c r="BL8" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
-      <x:c r="BM8" t="e">
-        <x:f>HYPERLINK("https://openalex.org/W4416716605","OpenAlex Work")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://openalex.org/W4416716605, friendlyName=OpenAlex Work</x:v>
+      <x:c r="BM8" t="str">
+        <x:v>https://openalex.org/W4416716605</x:v>
       </x:c>
       <x:c r="BN8" t="str">
         <x:v>https://ojs.aaai.org/index.php/AAAI/article/view/38539；官方摘要/论文集元数据</x:v>
@@ -29945,11 +29877,11 @@
       <x:c r="AT9" t="str">
         <x:v>Dexterous</x:v>
       </x:c>
-      <x:c r="AU9" t="str">
-        <x:v>—</x:v>
+      <x:c r="AU9" t="n">
+        <x:v>0</x:v>
       </x:c>
       <x:c r="AV9" t="str">
-        <x:v>未可靠匹配</x:v>
+        <x:v>Crossref</x:v>
       </x:c>
       <x:c r="AW9" t="str">
         <x:v>2026-09-25</x:v>
@@ -29998,7 +29930,7 @@
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BM9" t="str">
-        <x:v>—</x:v>
+        <x:v>https://api.crossref.org/works/10.1609/aaai.v40i22.38892</x:v>
       </x:c>
       <x:c r="BN9" t="str">
         <x:v>https://ojs.aaai.org/index.php/AAAI/article/download/38892/42854；官方摘要/论文集元数据</x:v>
@@ -30040,7 +29972,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="CA9" t="str">
-        <x:v>Unresolved</x:v>
+        <x:v>Matched</x:v>
       </x:c>
       <x:c r="CB9" t="str">
         <x:v>Not Found After Verification</x:v>
@@ -30082,7 +30014,7 @@
         <x:v>官方摘要/论文页：https://ojs.aaai.org/index.php/AAAI/article/view/38892；核验于 2026-09-23。仅为摘要级速读，原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="CQ9" t="str">
-        <x:v>Unresolved; insufficient identity evidence</x:v>
+        <x:v>crossref-exact-title-pdf-authors</x:v>
       </x:c>
       <x:c r="CR9" t="n">
         <x:v>0</x:v>
@@ -30229,11 +30161,11 @@
       <x:c r="AT10" t="str">
         <x:v>Benchmark / Dataset</x:v>
       </x:c>
-      <x:c r="AU10" t="str">
-        <x:v>—</x:v>
+      <x:c r="AU10" t="n">
+        <x:v>28</x:v>
       </x:c>
       <x:c r="AV10" t="str">
-        <x:v>未可靠匹配</x:v>
+        <x:v>Crossref</x:v>
       </x:c>
       <x:c r="AW10" t="str">
         <x:v>2026-09-25</x:v>
@@ -30282,7 +30214,7 @@
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BM10" t="str">
-        <x:v>—</x:v>
+        <x:v>https://api.crossref.org/works/10.1109/cvpr52734.2025.02575</x:v>
       </x:c>
       <x:c r="BN10" t="str">
         <x:v>https://openaccess.thecvf.com/content/CVPR2025/html/Mu_RoboTwin_Dual-Arm_Robot_Benchmark_with_Generative_Digital_Twins_CVPR_2025_paper.html；官方摘要/论文集元数据</x:v>
@@ -30324,7 +30256,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="CA10" t="str">
-        <x:v>Unresolved</x:v>
+        <x:v>Matched</x:v>
       </x:c>
       <x:c r="CB10" t="str">
         <x:v>Not Found After Verification</x:v>
@@ -30366,7 +30298,7 @@
         <x:v>官方摘要/论文页; https://openaccess.thecvf.com/content/CVPR2025/html/Mu_RoboTwin_Dual-Arm_Robot_Benchmark_with_Generative_Digital_Twins_CVPR_2025_paper.html; 核验于 2026-09-23. 仅为摘要级速读；原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="CQ10" t="str">
-        <x:v>Unresolved; insufficient identity evidence</x:v>
+        <x:v>crossref-exact-title-pdf-authors</x:v>
       </x:c>
       <x:c r="CR10" t="n">
         <x:v>0</x:v>
@@ -30568,9 +30500,8 @@
       <x:c r="BL11" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
-      <x:c r="BM11" t="e">
-        <x:f>HYPERLINK("https://openalex.org/W4415272059","OpenAlex Work")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://openalex.org/W4415272059, friendlyName=OpenAlex Work</x:v>
+      <x:c r="BM11" t="str">
+        <x:v>https://openalex.org/W4415272059</x:v>
       </x:c>
       <x:c r="BN11" t="str">
         <x:v>https://proceedings.neurips.cc/paper_files/paper/2025/hash/5c1a8aa04c1a2cf5013f28831870dafa-Abstract-Conference.html；官方摘要/论文集元数据</x:v>
@@ -30861,9 +30792,8 @@
       <x:c r="BL12" t="str">
         <x:v>背景动态使基线 PickPot SR 95→80%；VLA-Cache 在动态条件保持80%且降低FLOPs/延迟；PickPot 真机SR 95→90%（Table 5,7）。</x:v>
       </x:c>
-      <x:c r="BM12" t="e">
-        <x:f>HYPERLINK("https://openalex.org/W7196930033","OpenAlex Work")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://openalex.org/W7196930033, friendlyName=OpenAlex Work</x:v>
+      <x:c r="BM12" t="str">
+        <x:v>https://openalex.org/W7196930033</x:v>
       </x:c>
       <x:c r="BN12" t="str">
         <x:v>NeurIPS 正式论文页；arXiv PDF §1–6、Appendix A–F、Tables 1–5、7–11；NeurIPS Supplemental zip 与作者 GitHub。</x:v>
@@ -31236,7 +31166,7 @@
         <x:v>官方摘要/论文页; https://proceedings.mlr.press/v267/wen25g.html; 核验于 2026-09-23. 仅为摘要级速读；原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="CQ13" t="str">
-        <x:v>Unresolved; insufficient identity evidence</x:v>
+        <x:v>Unresolved; no reliable citation service count</x:v>
       </x:c>
       <x:c r="CR13" t="n">
         <x:v>8</x:v>
@@ -31443,9 +31373,8 @@
       <x:c r="BL14" t="str">
         <x:v>§6：目标生成可能改变纹理/形状、令物体消失、预测不相关的未来或状态无变化；小物体精细操作失败。</x:v>
       </x:c>
-      <x:c r="BM14" t="e">
-        <x:f>HYPERLINK("https://openalex.org/W4392886475","OpenAlex Work")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://openalex.org/W4392886475, friendlyName=OpenAlex Work</x:v>
+      <x:c r="BM14" t="str">
+        <x:v>https://openalex.org/W4392886475</x:v>
       </x:c>
       <x:c r="BN14" t="str">
         <x:v>PMLR 官方 PDF：§3.1–3.3、§4.1–4.3、§5.1–5.3、§6–7；Figures 2–3、5–6；Tables 1–6、Appendix Tables 7–9。https://raw.githubusercontent.com/mlresearch/v235/main/assets/zhen24a/zhen24a.pdf</x:v>
@@ -31738,9 +31667,8 @@
       <x:c r="BL15" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
-      <x:c r="BM15" t="e">
-        <x:f>HYPERLINK("https://openalex.org/W4415797921","OpenAlex Work")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://openalex.org/W4415797921, friendlyName=OpenAlex Work</x:v>
+      <x:c r="BM15" t="str">
+        <x:v>https://openalex.org/W4415797921</x:v>
       </x:c>
       <x:c r="BN15" t="str">
         <x:v>https://proceedings.neurips.cc/paper_files/paper/2024/hash/46a126492ea6fb87410e55a58df2e189-Abstract-Conference.html; https://sites.google.com/view/robomamba-web; https://github.com/lm</x:v>
@@ -32022,9 +31950,8 @@
       <x:c r="BL16" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
-      <x:c r="BM16" t="e">
-        <x:f>HYPERLINK("https://openalex.org/W4409365031","OpenAlex Work")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://openalex.org/W4409365031, friendlyName=OpenAlex Work</x:v>
+      <x:c r="BM16" t="str">
+        <x:v>https://openalex.org/W4409365031</x:v>
       </x:c>
       <x:c r="BN16" t="str">
         <x:v>https://ojs.aaai.org/index.php/AAAI/article/view/33617; https://github.com/</x:v>
@@ -32309,9 +32236,8 @@
       <x:c r="BL17" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
-      <x:c r="BM17" t="e">
-        <x:f>HYPERLINK("https://openalex.org/W4413145029","OpenAlex Work")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://openalex.org/W4413145029, friendlyName=OpenAlex Work</x:v>
+      <x:c r="BM17" t="str">
+        <x:v>https://openalex.org/W4413145029</x:v>
       </x:c>
       <x:c r="BN17" t="str">
         <x:v>https://openaccess.thecvf.com/content/CVPR2025/html/Wang_UniGraspTransformer_Simplified_Policy_Distillation_for_Scalable_Dexterous_Robotic_Grasping_CVPR_2025_paper.html；官方摘要/论文集元数据</x:v>
@@ -32597,9 +32523,8 @@
       <x:c r="BL18" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
-      <x:c r="BM18" t="e">
-        <x:f>HYPERLINK("https://openalex.org/W4414683599","OpenAlex Work")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://openalex.org/W4414683599, friendlyName=OpenAlex Work</x:v>
+      <x:c r="BM18" t="str">
+        <x:v>https://openalex.org/W4414683599</x:v>
       </x:c>
       <x:c r="BN18" t="str">
         <x:v>https://proceedings.neurips.cc/paper_files/paper/2025/hash/862644b156e51c35dea5a7446d640b14-Abstract-Conference.html；官方摘要/论文集元数据</x:v>
@@ -32885,9 +32810,8 @@
       <x:c r="BL19" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
-      <x:c r="BM19" t="e">
-        <x:f>HYPERLINK("https://openalex.org/W7196952124","OpenAlex Work")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://openalex.org/W7196952124, friendlyName=OpenAlex Work</x:v>
+      <x:c r="BM19" t="str">
+        <x:v>https://openalex.org/W7196952124</x:v>
       </x:c>
       <x:c r="BN19" t="str">
         <x:v>https://proceedings.neurips.cc/paper_files/paper/2025/hash/89a3b655a8b68ae1c76b768152c9c19d-Abstract-Conference.html；官方摘要/论文集元数据</x:v>
@@ -33172,9 +33096,8 @@
       <x:c r="BL20" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
-      <x:c r="BM20" t="e">
-        <x:f>HYPERLINK("https://openalex.org/W7125566978","OpenAlex Work")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://openalex.org/W7125566978, friendlyName=OpenAlex Work</x:v>
+      <x:c r="BM20" t="str">
+        <x:v>https://openalex.org/W7125566978</x:v>
       </x:c>
       <x:c r="BN20" t="str">
         <x:v>https://openaccess.thecvf.com/content/CVPR2026/html/Lee_DextER_Language-driven_Dexterous_Grasp_Generation_with_Embodied_Reasoning_CVPR_2026_paper.html；官方摘要/论文集元数据</x:v>
@@ -33463,9 +33386,8 @@
       <x:c r="BL21" t="str">
         <x:v>Position predictions are sensitive to lighting and texture domain gaps; suction cannot grasp non-smooth handles and short gripper geometry can cause collisions.</x:v>
       </x:c>
-      <x:c r="BM21" t="e">
-        <x:f>HYPERLINK("https://openalex.org/W4402727730","OpenAlex Work")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://openalex.org/W4402727730, friendlyName=OpenAlex Work</x:v>
+      <x:c r="BM21" t="str">
+        <x:v>https://openalex.org/W4402727730</x:v>
       </x:c>
       <x:c r="BN21" t="str">
         <x:v>https://openaccess.thecvf.com/content/CVPR2024/html/Li_ManipLLM_Embodied_Multimodal_Large_Language_Model_for_Object-Centric_Robotic_Manipulation_CVPR_2024_paper.html；官方摘要/论文集元数据</x:v>
@@ -33756,9 +33678,8 @@
       <x:c r="BL22" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
-      <x:c r="BM22" t="e">
-        <x:f>HYPERLINK("https://openalex.org/W4413145126","OpenAlex Work")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://openalex.org/W4413145126, friendlyName=OpenAlex Work</x:v>
+      <x:c r="BM22" t="str">
+        <x:v>https://openalex.org/W4413145126</x:v>
       </x:c>
       <x:c r="BN22" t="str">
         <x:v>https://openaccess.thecvf.com/content/CVPR2025/html/Li_ManipTrans_Efficient_Dexterous_Bimanual_Manipulation_Transfer_via_Residual_Learning_CVPR_2025_paper.html；官方摘要/论文集元数据</x:v>
@@ -34045,9 +33966,8 @@
       <x:c r="BL23" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
-      <x:c r="BM23" t="e">
-        <x:f>HYPERLINK("https://openalex.org/W4413146641","OpenAlex Work")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://openalex.org/W4413146641, friendlyName=OpenAlex Work</x:v>
+      <x:c r="BM23" t="str">
+        <x:v>https://openalex.org/W4413146641</x:v>
       </x:c>
       <x:c r="BN23" t="str">
         <x:v>https://openaccess.thecvf.com/content/CVPR2025/html/Liang_DexHandDiff_Interaction-aware_Diffusion_Planning_for_Adaptive_Dexterous_Manipulation_CVPR_2025_paper.html; https://dexdiffuser.github.io/; https://github.com/Liang-</x:v>
@@ -34334,9 +34254,8 @@
       <x:c r="BL24" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
-      <x:c r="BM24" t="e">
-        <x:f>HYPERLINK("https://openalex.org/W4416242580","OpenAlex Work")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://openalex.org/W4416242580, friendlyName=OpenAlex Work</x:v>
+      <x:c r="BM24" t="str">
+        <x:v>https://openalex.org/W4416242580</x:v>
       </x:c>
       <x:c r="BN24" t="str">
         <x:v>https://openaccess.thecvf.com/content/ICCV2025/html/Yang_AR-VRM_Imitating_Human_Motions_for_Visual_Robot_Manipulation_with_Analogical_ICCV_2025_paper.html；官方摘要/论文集元数据</x:v>
@@ -34622,9 +34541,8 @@
       <x:c r="BL25" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
-      <x:c r="BM25" t="e">
-        <x:f>HYPERLINK("https://openalex.org/W4402816741","OpenAlex Work")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://openalex.org/W4402816741, friendlyName=OpenAlex Work</x:v>
+      <x:c r="BM25" t="str">
+        <x:v>https://openalex.org/W4402816741</x:v>
       </x:c>
       <x:c r="BN25" t="str">
         <x:v>https://openaccess.thecvf.com/content/CVPR2024/html/Xu_Dexterous_Grasp_Transformer_CVPR_2024_paper.html；官方摘要/论文集元数据</x:v>
@@ -34909,9 +34827,8 @@
       <x:c r="BL26" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
-      <x:c r="BM26" t="e">
-        <x:f>HYPERLINK("https://openalex.org/W6967143107","OpenAlex Work")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://openalex.org/W6967143107, friendlyName=OpenAlex Work</x:v>
+      <x:c r="BM26" t="str">
+        <x:v>https://openalex.org/W6967143107</x:v>
       </x:c>
       <x:c r="BN26" t="str">
         <x:v>https://openaccess.thecvf.com/content/CVPR2025/html/Wu_MoManipVLA_Transferring_Vision-language-action_Models_for_General_Mobile_Manipulation_CVPR_2025_paper.html；官方摘要/论文集元数据</x:v>
@@ -35197,9 +35114,8 @@
       <x:c r="BL27" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
-      <x:c r="BM27" t="e">
-        <x:f>HYPERLINK("https://openalex.org/W4415800339","OpenAlex Work")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://openalex.org/W4415800339, friendlyName=OpenAlex Work</x:v>
+      <x:c r="BM27" t="str">
+        <x:v>https://openalex.org/W4415800339</x:v>
       </x:c>
       <x:c r="BN27" t="str">
         <x:v>https://proceedings.neurips.cc/paper_files/paper/2024/hash/ff887781480973bd3cb6026feb378d1e-Abstract-Conference.html；官方摘要/论文集元数据</x:v>
@@ -35486,9 +35402,8 @@
       <x:c r="BL28" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
-      <x:c r="BM28" t="e">
-        <x:f>HYPERLINK("https://www.semanticscholar.org/paper/f344e82d0d4f5e97c3d6176fd4b953a8c6c72d45","Semantic Scholar")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.semanticscholar.org/paper/f344e82d0d4f5e97c3d6176fd4b953a8c6c72d45, friendlyName=Semantic Scholar</x:v>
+      <x:c r="BM28" t="str">
+        <x:v>https://www.semanticscholar.org/paper/f344e82d0d4f5e97c3d6176fd4b953a8c6c72d45</x:v>
       </x:c>
       <x:c r="BN28" t="str">
         <x:v>https://proceedings.neurips.cc/paper_files/paper/2024/hash/74c4f2b87b7499d365422152c76fd916-Abstract-Datasets_and_Benchmarks_Track.html；官方摘要/论文集元数据</x:v>
@@ -35775,9 +35690,8 @@
       <x:c r="BL29" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
-      <x:c r="BM29" t="e">
-        <x:f>HYPERLINK("https://openalex.org/W4415795570","OpenAlex Work")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://openalex.org/W4415795570, friendlyName=OpenAlex Work</x:v>
+      <x:c r="BM29" t="str">
+        <x:v>https://openalex.org/W4415795570</x:v>
       </x:c>
       <x:c r="BN29" t="str">
         <x:v>https://proceedings.neurips.cc/paper_files/paper/2024/hash/dcd297696d0bb304ba426b3c5a679c37-Abstract-Conference.html；官方摘要/论文集元数据</x:v>
@@ -36064,9 +35978,8 @@
       <x:c r="BL30" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
-      <x:c r="BM30" t="e">
-        <x:f>HYPERLINK("https://openalex.org/W4415800541","OpenAlex Work")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://openalex.org/W4415800541, friendlyName=OpenAlex Work</x:v>
+      <x:c r="BM30" t="str">
+        <x:v>https://openalex.org/W4415800541</x:v>
       </x:c>
       <x:c r="BN30" t="str">
         <x:v>https://proceedings.neurips.cc/paper_files/paper/2024/hash/fad8962279154544ed69bb63eb14d677-Abstract-Conference.html；官方摘要/论文集元数据</x:v>
@@ -36352,9 +36265,8 @@
       <x:c r="BL31" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
-      <x:c r="BM31" t="e">
-        <x:f>HYPERLINK("https://openalex.org/W4415797227","OpenAlex Work")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://openalex.org/W4415797227, friendlyName=OpenAlex Work</x:v>
+      <x:c r="BM31" t="str">
+        <x:v>https://openalex.org/W4415797227</x:v>
       </x:c>
       <x:c r="BN31" t="str">
         <x:v>https://proceedings.neurips.cc/paper_files/paper/2024/hash/8e5dc5969a6174fcaaececd890c7f59b-Abstract-Datasets_and_Benchmarks_Track.html；官方摘要/论文集元数据</x:v>
@@ -36640,9 +36552,8 @@
       <x:c r="BL32" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
-      <x:c r="BM32" t="e">
-        <x:f>HYPERLINK("https://openalex.org/W4415797662","OpenAlex Work")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://openalex.org/W4415797662, friendlyName=OpenAlex Work</x:v>
+      <x:c r="BM32" t="str">
+        <x:v>https://openalex.org/W4415797662</x:v>
       </x:c>
       <x:c r="BN32" t="str">
         <x:v>https://proceedings.neurips.cc/paper_files/paper/2024/hash/5227ce00add5aa0a12d1c4ee92fcd2dc-Abstract-Conference.html；官方摘要/论文集元数据</x:v>
@@ -36927,9 +36838,8 @@
       <x:c r="BL33" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
-      <x:c r="BM33" t="e">
-        <x:f>HYPERLINK("https://openalex.org/W4413145391","OpenAlex Work")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://openalex.org/W4413145391, friendlyName=OpenAlex Work</x:v>
+      <x:c r="BM33" t="str">
+        <x:v>https://openalex.org/W4413145391</x:v>
       </x:c>
       <x:c r="BN33" t="str">
         <x:v>https://openaccess.thecvf.com/content/CVPR2025/html/</x:v>
@@ -37214,9 +37124,8 @@
       <x:c r="BL34" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
-      <x:c r="BM34" t="e">
-        <x:f>HYPERLINK("https://openalex.org/W4413147462","OpenAlex Work")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://openalex.org/W4413147462, friendlyName=OpenAlex Work</x:v>
+      <x:c r="BM34" t="str">
+        <x:v>https://openalex.org/W4413147462</x:v>
       </x:c>
       <x:c r="BN34" t="str">
         <x:v>https://openaccess.thecvf.com/content/CVPR2025/html/Huang_RoboGround_Robotic_Manipulation_with_Grounded_Vision-Language_Priors_CVPR_2025_paper.html；官方摘要/论文集元数据</x:v>
@@ -37449,11 +37358,11 @@
       <x:c r="AT35" t="str">
         <x:v>Data / Teleoperation</x:v>
       </x:c>
-      <x:c r="AU35" t="str">
-        <x:v>—</x:v>
+      <x:c r="AU35" t="n">
+        <x:v>4</x:v>
       </x:c>
       <x:c r="AV35" t="str">
-        <x:v>未可靠匹配</x:v>
+        <x:v>Crossref</x:v>
       </x:c>
       <x:c r="AW35" t="str">
         <x:v>2026-09-25</x:v>
@@ -37502,7 +37411,7 @@
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BM35" t="str">
-        <x:v>—</x:v>
+        <x:v>https://api.crossref.org/works/10.1109/cvpr52734.2025.01136</x:v>
       </x:c>
       <x:c r="BN35" t="str">
         <x:v>https://openaccess.thecvf.com/content/CVPR2025/html/Lee_DynScene_Scalable_Generation_of_Dynamic_Robotic_Manipulation_Scenes_for_Embodied_CVPR_2025_paper.html；官方摘要/论文集元数据</x:v>
@@ -37544,7 +37453,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="CA35" t="str">
-        <x:v>Unresolved</x:v>
+        <x:v>Matched</x:v>
       </x:c>
       <x:c r="CB35" t="str">
         <x:v>Not Found After Verification</x:v>
@@ -37586,7 +37495,7 @@
         <x:v>官方摘要/论文页; https://openaccess.thecvf.com/content/CVPR2025/html/Lee_DynScene_Scalable_Generation_of_Dynamic_Robotic_Manipulation_Scenes_for_Embodied_CVPR_2025_paper.html; 核验于 2026-09-23. 仅为摘要级速读；原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="CQ35" t="str">
-        <x:v>Unresolved; insufficient identity evidence</x:v>
+        <x:v>crossref-exact-title-pdf-authors</x:v>
       </x:c>
       <x:c r="CR35" t="n">
         <x:v>0</x:v>
@@ -37735,11 +37644,11 @@
       <x:c r="AT36" t="str">
         <x:v>Generalization / Long-Horizon</x:v>
       </x:c>
-      <x:c r="AU36" t="str">
-        <x:v>—</x:v>
+      <x:c r="AU36" t="n">
+        <x:v>4</x:v>
       </x:c>
       <x:c r="AV36" t="str">
-        <x:v>未可靠匹配</x:v>
+        <x:v>Crossref</x:v>
       </x:c>
       <x:c r="AW36" t="str">
         <x:v>2026-09-25</x:v>
@@ -37788,7 +37697,7 @@
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BM36" t="str">
-        <x:v>—</x:v>
+        <x:v>https://api.crossref.org/works/10.1109/cvpr52734.2025.02102</x:v>
       </x:c>
       <x:c r="BN36" t="str">
         <x:v>https://openaccess.thecvf.com/content/CVPR2025/html/Yao_Think_Small_Act_Big_Primitive_Prompt_Learning_for_Lifelong_Robot_CVPR_2025_paper.html；官方摘要/论文集元数据</x:v>
@@ -37830,7 +37739,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="CA36" t="str">
-        <x:v>Unresolved</x:v>
+        <x:v>Matched</x:v>
       </x:c>
       <x:c r="CB36" t="str">
         <x:v>Not Found After Verification</x:v>
@@ -37872,7 +37781,7 @@
         <x:v>官方摘要/论文页; https://openaccess.thecvf.com/content/CVPR2025/html/Yao_Think_Small_Act_Big_Primitive_Prompt_Learning_for_Lifelong_Robot_CVPR_2025_paper.html; 核验于 2026-09-23. 仅为摘要级速读；原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="CQ36" t="str">
-        <x:v>Unresolved; insufficient identity evidence</x:v>
+        <x:v>crossref-exact-title-pdf-authors</x:v>
       </x:c>
       <x:c r="CR36" t="n">
         <x:v>0</x:v>
@@ -38073,9 +37982,8 @@
       <x:c r="BL37" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
-      <x:c r="BM37" t="e">
-        <x:f>HYPERLINK("https://openalex.org/W4409362855","OpenAlex Work")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://openalex.org/W4409362855, friendlyName=OpenAlex Work</x:v>
+      <x:c r="BM37" t="str">
+        <x:v>https://openalex.org/W4409362855</x:v>
       </x:c>
       <x:c r="BN37" t="str">
         <x:v>https://ojs.aaai.org/index.php/AAAI/article/view/34866；官方摘要/论文集元数据</x:v>
@@ -38360,9 +38268,8 @@
       <x:c r="BL38" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
-      <x:c r="BM38" t="e">
-        <x:f>HYPERLINK("https://openalex.org/W4409364627","OpenAlex Work")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://openalex.org/W4409364627, friendlyName=OpenAlex Work</x:v>
+      <x:c r="BM38" t="str">
+        <x:v>https://openalex.org/W4409364627</x:v>
       </x:c>
       <x:c r="BN38" t="str">
         <x:v>https://ojs.aaai.org/index.php/AAAI/article/view/33615；官方摘要/论文集元数据</x:v>
@@ -38647,9 +38554,8 @@
       <x:c r="BL39" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
-      <x:c r="BM39" t="e">
-        <x:f>HYPERLINK("https://openalex.org/W4409364594","OpenAlex Work")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://openalex.org/W4409364594, friendlyName=OpenAlex Work</x:v>
+      <x:c r="BM39" t="str">
+        <x:v>https://openalex.org/W4409364594</x:v>
       </x:c>
       <x:c r="BN39" t="str">
         <x:v>https://ojs.aaai.org/index.php/AAAI/article/view/33610；官方摘要/论文集元数据</x:v>
@@ -38935,9 +38841,8 @@
       <x:c r="BL40" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
-      <x:c r="BM40" t="e">
-        <x:f>HYPERLINK("https://openalex.org/W7103754590","OpenAlex Work")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://openalex.org/W7103754590, friendlyName=OpenAlex Work</x:v>
+      <x:c r="BM40" t="str">
+        <x:v>https://openalex.org/W7103754590</x:v>
       </x:c>
       <x:c r="BN40" t="str">
         <x:v>https://proceedings.neurips.cc/paper_files/paper/2024/hash/481c70828a4ff20d31a646cc6cc95f3d-Abstract-Conference.html；官方摘要/论文集元数据</x:v>
@@ -39307,7 +39212,7 @@
         <x:v>官方摘要/论文页; https://openaccess.thecvf.com/content/CVPR2025/html/Chen_VidBot_Learning_Generalizable_3D_Actions_from_In-the-Wild_2D_Human_Videos_CVPR_2025_paper.html; 核验于 2026-09-23. 仅为摘要级速读；原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="CQ41" t="str">
-        <x:v>Unresolved; insufficient identity evidence</x:v>
+        <x:v>Unresolved; no reliable citation service count</x:v>
       </x:c>
       <x:c r="CR41" t="n">
         <x:v>0</x:v>
@@ -39508,9 +39413,8 @@
       <x:c r="BL42" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
-      <x:c r="BM42" t="e">
-        <x:f>HYPERLINK("https://openalex.org/W4413156213","OpenAlex Work")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://openalex.org/W4413156213, friendlyName=OpenAlex Work</x:v>
+      <x:c r="BM42" t="str">
+        <x:v>https://openalex.org/W4413156213</x:v>
       </x:c>
       <x:c r="BN42" t="str">
         <x:v>https://openaccess.thecvf.com/content/CVPR2025/html/</x:v>
@@ -39796,9 +39700,8 @@
       <x:c r="BL43" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
-      <x:c r="BM43" t="e">
-        <x:f>HYPERLINK("https://openalex.org/W4415251366","OpenAlex Work")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://openalex.org/W4415251366, friendlyName=OpenAlex Work</x:v>
+      <x:c r="BM43" t="str">
+        <x:v>https://openalex.org/W4415251366</x:v>
       </x:c>
       <x:c r="BN43" t="str">
         <x:v>https://proceedings.neurips.cc/paper_files/paper/2025/hash/1185c89347a3f21ffc48c9d083c9437c-Abstract-Conference.html；官方摘要/论文集元数据</x:v>
@@ -40084,9 +39987,8 @@
       <x:c r="BL44" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
-      <x:c r="BM44" t="e">
-        <x:f>HYPERLINK("https://openalex.org/W7196926233","OpenAlex Work")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://openalex.org/W7196926233, friendlyName=OpenAlex Work</x:v>
+      <x:c r="BM44" t="str">
+        <x:v>https://openalex.org/W7196926233</x:v>
       </x:c>
       <x:c r="BN44" t="str">
         <x:v>https://proceedings.neurips.cc/paper_files/paper/2025/hash/b94310e1c7ecb79f1a24adc757f1b89b-Abstract-Conference.html；官方摘要/论文集元数据</x:v>
@@ -40372,9 +40274,8 @@
       <x:c r="BL45" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
-      <x:c r="BM45" t="e">
-        <x:f>HYPERLINK("https://openalex.org/W7196975408","OpenAlex Work")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://openalex.org/W7196975408, friendlyName=OpenAlex Work</x:v>
+      <x:c r="BM45" t="str">
+        <x:v>https://openalex.org/W7196975408</x:v>
       </x:c>
       <x:c r="BN45" t="str">
         <x:v>https://proceedings.neurips.cc/paper_files/paper/2025/hash/49eadcc4a329fc6b74b9f8a82b78cbc3-Abstract-Conference.html；官方摘要/论文集元数据</x:v>
@@ -40660,9 +40561,8 @@
       <x:c r="BL46" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
-      <x:c r="BM46" t="e">
-        <x:f>HYPERLINK("https://openalex.org/W7197036842","OpenAlex Work")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://openalex.org/W7197036842, friendlyName=OpenAlex Work</x:v>
+      <x:c r="BM46" t="str">
+        <x:v>https://openalex.org/W7197036842</x:v>
       </x:c>
       <x:c r="BN46" t="str">
         <x:v>https://proceedings.neurips.cc/paper_files/paper/2025/hash/bc97207e3979d1cc23109db0be0e8ed2-Abstract-Conference.html；官方摘要/论文集元数据</x:v>
@@ -40948,9 +40848,8 @@
       <x:c r="BL47" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
-      <x:c r="BM47" t="e">
-        <x:f>HYPERLINK("https://openalex.org/W4417258107","OpenAlex Work")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://openalex.org/W4417258107, friendlyName=OpenAlex Work</x:v>
+      <x:c r="BM47" t="str">
+        <x:v>https://openalex.org/W4417258107</x:v>
       </x:c>
       <x:c r="BN47" t="str">
         <x:v>https://proceedings.neurips.cc/paper_files/paper/2025/hash/282c3318be1b047b7bb5ba94fa4f3231-Abstract-Conference.html；官方摘要/论文集元数据</x:v>
@@ -41236,9 +41135,8 @@
       <x:c r="BL48" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
-      <x:c r="BM48" t="e">
-        <x:f>HYPERLINK("https://openalex.org/W4415312722","OpenAlex Work")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://openalex.org/W4415312722, friendlyName=OpenAlex Work</x:v>
+      <x:c r="BM48" t="str">
+        <x:v>https://openalex.org/W4415312722</x:v>
       </x:c>
       <x:c r="BN48" t="str">
         <x:v>https://proceedings.neurips.cc/paper_files/paper/2025/hash/9fc291fef2f9607a46777d367f900a15-Abstract-Conference.html；官方摘要/论文集元数据</x:v>
@@ -41524,9 +41422,8 @@
       <x:c r="BL49" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
-      <x:c r="BM49" t="e">
-        <x:f>HYPERLINK("https://openalex.org/W4417082659","OpenAlex Work")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://openalex.org/W4417082659, friendlyName=OpenAlex Work</x:v>
+      <x:c r="BM49" t="str">
+        <x:v>https://openalex.org/W4417082659</x:v>
       </x:c>
       <x:c r="BN49" t="str">
         <x:v>https://proceedings.neurips.cc/paper_files/paper/2025/hash/eacc8ae341d15d2c13c02fef88189db3-Abstract-Conference.html；官方摘要/论文集元数据</x:v>
@@ -41812,9 +41709,8 @@
       <x:c r="BL50" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
-      <x:c r="BM50" t="e">
-        <x:f>HYPERLINK("https://www.semanticscholar.org/paper/afeff85d95e5428eb0a36dbc58446ce42e686d1d","Semantic Scholar")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.semanticscholar.org/paper/afeff85d95e5428eb0a36dbc58446ce42e686d1d, friendlyName=Semantic Scholar</x:v>
+      <x:c r="BM50" t="str">
+        <x:v>https://www.semanticscholar.org/paper/afeff85d95e5428eb0a36dbc58446ce42e686d1d</x:v>
       </x:c>
       <x:c r="BN50" t="str">
         <x:v>https://proceedings.neurips.cc/paper_files/paper/2025/hash/1f467c3e37abf9f86c78f44c6a27ee7c-Abstract-Datasets_and_Benchmarks_Track.html；官方摘要/论文集元数据</x:v>
@@ -42100,9 +41996,8 @@
       <x:c r="BL51" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
-      <x:c r="BM51" t="e">
-        <x:f>HYPERLINK("https://www.semanticscholar.org/paper/31feae9cc3d888b85e1cba366c79b2c50f29c2b3","Semantic Scholar")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.semanticscholar.org/paper/31feae9cc3d888b85e1cba366c79b2c50f29c2b3, friendlyName=Semantic Scholar</x:v>
+      <x:c r="BM51" t="str">
+        <x:v>https://www.semanticscholar.org/paper/31feae9cc3d888b85e1cba366c79b2c50f29c2b3</x:v>
       </x:c>
       <x:c r="BN51" t="str">
         <x:v>https://proceedings.neurips.cc/paper_files/paper/2025/hash/b8358a00e5b870194b974ddf8dd415c3-Abstract-Conference.html；官方摘要/论文集元数据</x:v>
@@ -42473,7 +42368,7 @@
         <x:v>官方摘要/论文页; https://openaccess.thecvf.com/content/ICCV2025/html/Wang_DexH2R_A_Benchmark_for_Dynamic_Dexterous_Grasping_in_Human-to-Robot_Handover_ICCV_2025_paper.html; 核验于 2026-09-23. 仅为摘要级速读；原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="CQ52" t="str">
-        <x:v>Unresolved; insufficient identity evidence</x:v>
+        <x:v>Unresolved; no reliable citation service count</x:v>
       </x:c>
       <x:c r="CR52" t="n">
         <x:v>0</x:v>
@@ -42674,9 +42569,8 @@
       <x:c r="BL53" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
-      <x:c r="BM53" t="e">
-        <x:f>HYPERLINK("https://openalex.org/W4413145043","OpenAlex Work")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://openalex.org/W4413145043, friendlyName=OpenAlex Work</x:v>
+      <x:c r="BM53" t="str">
+        <x:v>https://openalex.org/W4413145043</x:v>
       </x:c>
       <x:c r="BN53" t="str">
         <x:v>https://openaccess.thecvf.com/content/CVPR2025/html/</x:v>
@@ -42964,9 +42858,8 @@
       <x:c r="BL54" t="str">
         <x:v>The reported setting focuses on tabletop part-aligned grasps; broader clutter, occlusion and multi-step manipulation are not established by the cited results.</x:v>
       </x:c>
-      <x:c r="BM54" t="e">
-        <x:f>HYPERLINK("https://openalex.org/W4417183400","OpenAlex Work")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://openalex.org/W4417183400, friendlyName=OpenAlex Work</x:v>
+      <x:c r="BM54" t="str">
+        <x:v>https://openalex.org/W4417183400</x:v>
       </x:c>
       <x:c r="BN54" t="str">
         <x:v>https://openaccess.thecvf.com/content/ICCV2025/html/He_DexVLG_Dexterous_Vision-Language-Grasp_Model_at_Scale_ICCV_2025_paper.html；官方摘要/论文集元数据</x:v>
@@ -43255,9 +43148,8 @@
       <x:c r="BL55" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
-      <x:c r="BM55" t="e">
-        <x:f>HYPERLINK("https://openalex.org/W4413146191","OpenAlex Work")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://openalex.org/W4413146191, friendlyName=OpenAlex Work</x:v>
+      <x:c r="BM55" t="str">
+        <x:v>https://openalex.org/W4413146191</x:v>
       </x:c>
       <x:c r="BN55" t="str">
         <x:v>https://openaccess.thecvf.com/content/CVPR2025/html/Li_LatentHOI_On_the_Generali</x:v>
@@ -43490,11 +43382,11 @@
       <x:c r="AT56" t="str">
         <x:v>Benchmark / Dataset</x:v>
       </x:c>
-      <x:c r="AU56" t="str">
-        <x:v>—</x:v>
+      <x:c r="AU56" t="n">
+        <x:v>37</x:v>
       </x:c>
       <x:c r="AV56" t="str">
-        <x:v>未可靠匹配</x:v>
+        <x:v>Crossref</x:v>
       </x:c>
       <x:c r="AW56" t="str">
         <x:v>2026-09-25</x:v>
@@ -43543,7 +43435,7 @@
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BM56" t="str">
-        <x:v>—</x:v>
+        <x:v>https://api.crossref.org/works/10.1109/cvpr52733.2024.02054</x:v>
       </x:c>
       <x:c r="BN56" t="str">
         <x:v>https://openaccess.thecvf.com/content/CVPR2024/papers/Liu_TACO_Benchmarking_Generali</x:v>
@@ -43585,7 +43477,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="CA56" t="str">
-        <x:v>Unresolved</x:v>
+        <x:v>Matched</x:v>
       </x:c>
       <x:c r="CB56" t="str">
         <x:v>Not Found After Verification</x:v>
@@ -43627,7 +43519,7 @@
         <x:v>官方摘要/论文页：https://openaccess.thecvf.com/content/CVPR2024/papers/Liu_TACO_Benchmarking_Generalizable_Bimanual_Tool-ACtion-Object_Understanding_CVPR_2024_paper.pdf；核验于 2026-09-23。仅为摘要级速读，原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="CQ56" t="str">
-        <x:v>Unresolved; insufficient identity evidence</x:v>
+        <x:v>crossref-exact-title-pdf-authors</x:v>
       </x:c>
       <x:c r="CR56" t="n">
         <x:v>0</x:v>
@@ -43829,9 +43721,8 @@
       <x:c r="BL57" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
-      <x:c r="BM57" t="e">
-        <x:f>HYPERLINK("https://openalex.org/W4402772268","OpenAlex Work")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://openalex.org/W4402772268, friendlyName=OpenAlex Work</x:v>
+      <x:c r="BM57" t="str">
+        <x:v>https://openalex.org/W4402772268</x:v>
       </x:c>
       <x:c r="BN57" t="str">
         <x:v>https://openaccess.thecvf.com/content/CVPR2024/html/Uppal_SPIN_Simultaneous_Perception_Interaction_and_Navigation_CVPR_2024_paper.html；官方摘要/论文集元数据</x:v>
@@ -44118,9 +44009,8 @@
       <x:c r="BL58" t="str">
         <x:v>The paper identifies observation discrepancy between unimanual and bimanual systems as a transfer risk; detailed failure cases require appendix extraction.</x:v>
       </x:c>
-      <x:c r="BM58" t="e">
-        <x:f>HYPERLINK("https://openalex.org/W4405254485","OpenAlex Work")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://openalex.org/W4405254485, friendlyName=OpenAlex Work</x:v>
+      <x:c r="BM58" t="str">
+        <x:v>https://openalex.org/W4405254485</x:v>
       </x:c>
       <x:c r="BN58" t="str">
         <x:v>https://openaccess.thecvf.com/content/ICCV2025/html/Lu_AnyBimanual_Transferring_Unimanual_Policy_for_General_Bimanual_Manipulation_ICCV_2025_paper.html；官方摘要/论文集元数据</x:v>
@@ -44411,9 +44301,8 @@
       <x:c r="BL59" t="str">
         <x:v>Cross-hand and retargeting edge cases are not detailed in the accessible abstract; full supplementary review is needed.</x:v>
       </x:c>
-      <x:c r="BM59" t="e">
-        <x:f>HYPERLINK("https://openalex.org/W7140228196","OpenAlex Work")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://openalex.org/W7140228196, friendlyName=OpenAlex Work</x:v>
+      <x:c r="BM59" t="str">
+        <x:v>https://openalex.org/W7140228196</x:v>
       </x:c>
       <x:c r="BN59" t="str">
         <x:v>https://openaccess.thecvf.com/content/CVPR2026/html/Zhang_UniDex_A_Robot_Foundation_Suite_for_Universal_Dexterous_Hand_Control_CVPR_2026_paper.html；官方摘要/论文集元数据</x:v>
@@ -44650,11 +44539,11 @@
       <x:c r="AT60" t="str">
         <x:v>Generalization / Long-Horizon</x:v>
       </x:c>
-      <x:c r="AU60" t="str">
-        <x:v>—</x:v>
+      <x:c r="AU60" t="n">
+        <x:v>3</x:v>
       </x:c>
       <x:c r="AV60" t="str">
-        <x:v>未可靠匹配</x:v>
+        <x:v>Crossref</x:v>
       </x:c>
       <x:c r="AW60" t="str">
         <x:v>2026-09-25</x:v>
@@ -44703,7 +44592,7 @@
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BM60" t="str">
-        <x:v>—</x:v>
+        <x:v>https://api.crossref.org/works/10.1109/cvpr52734.2025.02578</x:v>
       </x:c>
       <x:c r="BN60" t="str">
         <x:v>https://openaccess.thecvf.com/content/CVPR2025/html/</x:v>
@@ -44745,7 +44634,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="CA60" t="str">
-        <x:v>Unresolved</x:v>
+        <x:v>Matched</x:v>
       </x:c>
       <x:c r="CB60" t="str">
         <x:v>Not Found After Verification</x:v>
@@ -44787,7 +44676,7 @@
         <x:v>官方摘要/论文页; https://openaccess.thecvf.com/content/CVPR2025/html/Zhao_TASTE-Rob_Advancing_Video_Generation_of_Task-Oriented_Hand-Object_Interaction_for_Generalizable_CVPR_2025_paper.html; 核验于 2026-09-23. 仅为摘要级速读；原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="CQ60" t="str">
-        <x:v>Unresolved; insufficient identity evidence</x:v>
+        <x:v>crossref-exact-title-pdf-authors</x:v>
       </x:c>
       <x:c r="CR60" t="n">
         <x:v>0</x:v>
@@ -44989,9 +44878,8 @@
       <x:c r="BL61" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
-      <x:c r="BM61" t="e">
-        <x:f>HYPERLINK("https://openalex.org/W7138113519","OpenAlex Work")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://openalex.org/W7138113519, friendlyName=OpenAlex Work</x:v>
+      <x:c r="BM61" t="str">
+        <x:v>https://openalex.org/W7138113519</x:v>
       </x:c>
       <x:c r="BN61" t="str">
         <x:v>https://ojs.aaai.org/index.php/AAAI/article/view/38874；官方摘要/论文集元数据</x:v>
@@ -45278,9 +45166,8 @@
       <x:c r="BL62" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
-      <x:c r="BM62" t="e">
-        <x:f>HYPERLINK("https://openalex.org/W4417041439","OpenAlex Work")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://openalex.org/W4417041439, friendlyName=OpenAlex Work</x:v>
+      <x:c r="BM62" t="str">
+        <x:v>https://openalex.org/W4417041439</x:v>
       </x:c>
       <x:c r="BN62" t="str">
         <x:v>https://proceedings.neurips.cc/paper_files/paper/2025/hash/e4ef7454447baa15a424314e6284441b-Abstract-Conference.html；官方摘要/论文集元数据</x:v>
@@ -45566,9 +45453,8 @@
       <x:c r="BL63" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
-      <x:c r="BM63" t="e">
-        <x:f>HYPERLINK("https://openalex.org/W7138302344","OpenAlex Work")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://openalex.org/W7138302344, friendlyName=OpenAlex Work</x:v>
+      <x:c r="BM63" t="str">
+        <x:v>https://openalex.org/W7138302344</x:v>
       </x:c>
       <x:c r="BN63" t="str">
         <x:v>https://ojs.aaai.org/index.php/AAAI/article/view/38313；官方摘要/论文集元数据</x:v>
@@ -45854,9 +45740,8 @@
       <x:c r="BL64" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
-      <x:c r="BM64" t="e">
-        <x:f>HYPERLINK("https://openalex.org/W7138037195","OpenAlex Work")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://openalex.org/W7138037195, friendlyName=OpenAlex Work</x:v>
+      <x:c r="BM64" t="str">
+        <x:v>https://openalex.org/W7138037195</x:v>
       </x:c>
       <x:c r="BN64" t="str">
         <x:v>https://ojs.aaai.org/index.php/AAAI/article/view/40127；官方摘要/论文集元数据</x:v>
@@ -46142,9 +46027,8 @@
       <x:c r="BL65" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
-      <x:c r="BM65" t="e">
-        <x:f>HYPERLINK("https://openalex.org/W4393158202","OpenAlex Work")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://openalex.org/W4393158202, friendlyName=OpenAlex Work</x:v>
+      <x:c r="BM65" t="str">
+        <x:v>https://openalex.org/W4393158202</x:v>
       </x:c>
       <x:c r="BN65" t="str">
         <x:v>https://ojs.aaai.org/index.php/AAAI/article/view/28266；官方摘要/论文集元数据</x:v>
@@ -46431,9 +46315,8 @@
       <x:c r="BL66" t="str">
         <x:v>The paper notes ambiguity/multi-modality of valid interaction regions; exact failure examples require figure-level review.</x:v>
       </x:c>
-      <x:c r="BM66" t="e">
-        <x:f>HYPERLINK("https://openalex.org/W4416031407","OpenAlex Work")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://openalex.org/W4416031407, friendlyName=OpenAlex Work</x:v>
+      <x:c r="BM66" t="str">
+        <x:v>https://openalex.org/W4416031407</x:v>
       </x:c>
       <x:c r="BN66" t="str">
         <x:v>https://openaccess.thecvf.com/content/ICCV2025/html/Heidinger_2HandedAfforder_Learning_Precise_Actionable_Bimanual_Affordances_from_Human_Videos_ICCV_2025_paper.html；官方摘要/论文集元数据</x:v>
@@ -46728,9 +46611,8 @@
       <x:c r="BL67" t="str">
         <x:v>Not Explicitly Reported in the accessible official abstract/project evidence.</x:v>
       </x:c>
-      <x:c r="BM67" t="e">
-        <x:f>HYPERLINK("https://openalex.org/W7137985120","OpenAlex Work")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://openalex.org/W7137985120, friendlyName=OpenAlex Work</x:v>
+      <x:c r="BM67" t="str">
+        <x:v>https://openalex.org/W7137985120</x:v>
       </x:c>
       <x:c r="BN67" t="str">
         <x:v>https://ojs.aaai.org/index.php/AAAI/article/view/38921；https://arxiv.org/abs/2508.10333；https://zionchow.github.io/ReconVLA/；https://github.com/OpenHelix-Team/ReconVLA</x:v>
@@ -46862,7 +46744,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R54b74dcd0baf4d58"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6736d1e682044cbf"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -47071,7 +46953,7 @@
         <x:v>Failure Cases</x:v>
       </x:c>
       <x:c r="BB1" t="str">
-        <x:v>Citation Source Identifier</x:v>
+        <x:v>引用量来源链接</x:v>
       </x:c>
       <x:c r="BC1" t="str">
         <x:v>Evidence Sources</x:v>
@@ -47422,7 +47304,7 @@
         <x:v>官方摘要/论文页：https://edem-ai.github.io/sim2realvla.github.io/；核验于 2026-09-23。仅为摘要级速读，原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="CF2" t="str">
-        <x:v>Unresolved; insufficient identity evidence</x:v>
+        <x:v>Unresolved; no reliable citation service count</x:v>
       </x:c>
       <x:c r="CG2" t="n">
         <x:v>0</x:v>
@@ -47591,9 +47473,8 @@
       <x:c r="BA3" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
-      <x:c r="BB3" t="e">
-        <x:f>HYPERLINK("https://openalex.org/W4414050937","OpenAlex Work")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://openalex.org/W4414050937, friendlyName=OpenAlex Work</x:v>
+      <x:c r="BB3" t="str">
+        <x:v>https://openalex.org/W4414050937</x:v>
       </x:c>
       <x:c r="BC3" t="str">
         <x:v>https://www.roboticsproceedings.org/rss21/p149.html; https://hnu</x:v>
@@ -47846,9 +47727,8 @@
       <x:c r="BA4" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
-      <x:c r="BB4" t="e">
-        <x:f>HYPERLINK("https://openalex.org/W4414050727","OpenAlex Work")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://openalex.org/W4414050727, friendlyName=OpenAlex Work</x:v>
+      <x:c r="BB4" t="str">
+        <x:v>https://openalex.org/W4414050727</x:v>
       </x:c>
       <x:c r="BC4" t="str">
         <x:v>RSS official proceedings abstract</x:v>
@@ -48100,9 +47980,8 @@
       <x:c r="BA5" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
-      <x:c r="BB5" t="e">
-        <x:f>HYPERLINK("https://www.semanticscholar.org/paper/84a351dcc0323aed7fac5755303eb5614fac5f46","Semantic Scholar")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.semanticscholar.org/paper/84a351dcc0323aed7fac5755303eb5614fac5f46, friendlyName=Semantic Scholar</x:v>
+      <x:c r="BB5" t="str">
+        <x:v>https://www.semanticscholar.org/paper/84a351dcc0323aed7fac5755303eb5614fac5f46</x:v>
       </x:c>
       <x:c r="BC5" t="str">
         <x:v>RSS official proceedings</x:v>
@@ -48355,9 +48234,8 @@
       <x:c r="BA6" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
-      <x:c r="BB6" t="e">
-        <x:f>HYPERLINK("https://openalex.org/W4402354166","OpenAlex Work")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://openalex.org/W4402354166, friendlyName=OpenAlex Work</x:v>
+      <x:c r="BB6" t="str">
+        <x:v>https://openalex.org/W4402354166</x:v>
       </x:c>
       <x:c r="BC6" t="str">
         <x:v>RSS official proceedings abstract</x:v>
@@ -48611,9 +48489,8 @@
       <x:c r="BA7" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
-      <x:c r="BB7" t="e">
-        <x:f>HYPERLINK("https://openalex.org/W4401415458","OpenAlex Work")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://openalex.org/W4401415458, friendlyName=OpenAlex Work</x:v>
+      <x:c r="BB7" t="str">
+        <x:v>https://openalex.org/W4401415458</x:v>
       </x:c>
       <x:c r="BC7" t="str">
         <x:v>IEEE Xplore abstract; official project page</x:v>
@@ -48866,9 +48743,8 @@
       <x:c r="BA8" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
-      <x:c r="BB8" t="e">
-        <x:f>HYPERLINK("https://openalex.org/W4405753615","OpenAlex Work")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://openalex.org/W4405753615, friendlyName=OpenAlex Work</x:v>
+      <x:c r="BB8" t="str">
+        <x:v>https://openalex.org/W4405753615</x:v>
       </x:c>
       <x:c r="BC8" t="str">
         <x:v>IEEE Xplore abstract</x:v>
@@ -49071,11 +48947,11 @@
       <x:c r="AJ9" t="str">
         <x:v>Bimanual</x:v>
       </x:c>
-      <x:c r="AK9" t="str">
-        <x:v>—</x:v>
+      <x:c r="AK9" t="n">
+        <x:v>10</x:v>
       </x:c>
       <x:c r="AL9" t="str">
-        <x:v>未可靠匹配</x:v>
+        <x:v>Crossref</x:v>
       </x:c>
       <x:c r="AM9" t="str">
         <x:v>2026-09-25</x:v>
@@ -49121,7 +48997,7 @@
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BB9" t="str">
-        <x:v>—</x:v>
+        <x:v>https://api.crossref.org/works/10.1109/tro.2024.3502223</x:v>
       </x:c>
       <x:c r="BC9" t="str">
         <x:v>IEEE Xplore abstract</x:v>
@@ -49161,7 +49037,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="BP9" t="str">
-        <x:v>Unresolved</x:v>
+        <x:v>Matched</x:v>
       </x:c>
       <x:c r="BQ9" t="str">
         <x:v>Not Found After Verification</x:v>
@@ -49203,7 +49079,7 @@
         <x:v>OpenAlex 索引摘要; https://api.openalex.org/works/W4404520558; 核验于 2026-09-23. 仅为摘要级速读；原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="CF9" t="str">
-        <x:v>Unresolved; insufficient identity evidence</x:v>
+        <x:v>crossref-exact-title-official-publisher</x:v>
       </x:c>
       <x:c r="CG9" t="n">
         <x:v>0</x:v>
@@ -49322,11 +49198,11 @@
       <x:c r="AJ10" t="str">
         <x:v>Dexterous</x:v>
       </x:c>
-      <x:c r="AK10" t="str">
-        <x:v>—</x:v>
+      <x:c r="AK10" t="n">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AL10" t="str">
-        <x:v>未可靠匹配</x:v>
+        <x:v>Crossref</x:v>
       </x:c>
       <x:c r="AM10" t="str">
         <x:v>2026-09-25</x:v>
@@ -49372,7 +49248,7 @@
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
       <x:c r="BB10" t="str">
-        <x:v>—</x:v>
+        <x:v>https://api.crossref.org/works/10.1109/lra.2025.3558699</x:v>
       </x:c>
       <x:c r="BC10" t="str">
         <x:v>IEEE Xplore abstract</x:v>
@@ -49412,7 +49288,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="BP10" t="str">
-        <x:v>Unresolved</x:v>
+        <x:v>Matched</x:v>
       </x:c>
       <x:c r="BQ10" t="str">
         <x:v>Not Found After Verification</x:v>
@@ -49454,7 +49330,7 @@
         <x:v>官方摘要/论文页：https://ieeexplore.ieee.org/document/10955245/；核验于 2026-09-23。仅为摘要级速读，原 Evidence Quality 不变。 - 核验层级：摘要有可追溯来源</x:v>
       </x:c>
       <x:c r="CF10" t="str">
-        <x:v>Unresolved; insufficient identity evidence</x:v>
+        <x:v>crossref-exact-title-official-publisher</x:v>
       </x:c>
       <x:c r="CG10" t="n">
         <x:v>0</x:v>
@@ -49602,9 +49478,8 @@
       <x:c r="BA11" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
-      <x:c r="BB11" t="e">
-        <x:f>HYPERLINK("https://openalex.org/W4402353985","OpenAlex Work")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://openalex.org/W4402353985, friendlyName=OpenAlex Work</x:v>
+      <x:c r="BB11" t="str">
+        <x:v>https://openalex.org/W4402353985</x:v>
       </x:c>
       <x:c r="BC11" t="str">
         <x:v>Unknown</x:v>
@@ -49831,9 +49706,8 @@
       <x:c r="BA12" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
-      <x:c r="BB12" t="e">
-        <x:f>HYPERLINK("https://openalex.org/W4402354047","OpenAlex Work")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://openalex.org/W4402354047, friendlyName=OpenAlex Work</x:v>
+      <x:c r="BB12" t="str">
+        <x:v>https://openalex.org/W4402354047</x:v>
       </x:c>
       <x:c r="BC12" t="str">
         <x:v>Unknown</x:v>
@@ -50063,9 +49937,8 @@
       <x:c r="BA13" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
-      <x:c r="BB13" t="e">
-        <x:f>HYPERLINK("https://www.semanticscholar.org/paper/a294546084fda4e0f12f307caed4f9c58f051632","Semantic Scholar")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.semanticscholar.org/paper/a294546084fda4e0f12f307caed4f9c58f051632, friendlyName=Semantic Scholar</x:v>
+      <x:c r="BB13" t="str">
+        <x:v>https://www.semanticscholar.org/paper/a294546084fda4e0f12f307caed4f9c58f051632</x:v>
       </x:c>
       <x:c r="BC13" t="str">
         <x:v>Unknown</x:v>
@@ -50294,9 +50167,8 @@
       <x:c r="BA14" t="str">
         <x:v>Unknown / Not Explicitly Reported in the currently accessible sources.</x:v>
       </x:c>
-      <x:c r="BB14" t="e">
-        <x:f>HYPERLINK("https://openalex.org/W4387764390","OpenAlex Work")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://openalex.org/W4387764390, friendlyName=OpenAlex Work</x:v>
+      <x:c r="BB14" t="str">
+        <x:v>https://openalex.org/W4387764390</x:v>
       </x:c>
       <x:c r="BC14" t="str">
         <x:v>Unknown</x:v>
@@ -50550,9 +50422,8 @@
       <x:c r="BA15" t="str">
         <x:v>Planning errors, low-level execution, drawer manipulation, embodiment limits.</x:v>
       </x:c>
-      <x:c r="BB15" t="e">
-        <x:f>HYPERLINK("https://openalex.org/W4224912544","OpenAlex Work")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://openalex.org/W4224912544, friendlyName=OpenAlex Work</x:v>
+      <x:c r="BB15" t="str">
+        <x:v>https://openalex.org/W4224912544</x:v>
       </x:c>
       <x:c r="BC15" t="str">
         <x:v>Google Research; arXiv; CoRL/PMLR; project page; official repository</x:v>
@@ -50673,7 +50544,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5e9107d5f17a4d56"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7d883dfc0d7141c9"/>
   </x:tableParts>
 </x:worksheet>
 </file>